--- a/Open Positions.xlsx
+++ b/Open Positions.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\RodWal-Portfolio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\StockSillines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C550248E-F68A-456F-B0DD-568EDE7F7AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{879A82F2-D606-405C-815B-A5C5FB79C475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Positions" sheetId="1" r:id="rId1"/>
@@ -45,9 +45,6 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Ticket</t>
-  </si>
-  <si>
     <t>Date</t>
   </si>
   <si>
@@ -298,6 +295,9 @@
   </si>
   <si>
     <t>Risk Mix</t>
+  </si>
+  <si>
+    <t>Ticker</t>
   </si>
 </sst>
 </file>
@@ -706,16 +706,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:S32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.42578125" style="8" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="1" customWidth="1"/>
     <col min="8" max="8" width="9.85546875" style="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.42578125" style="10" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.140625" style="10"/>
@@ -732,72 +733,72 @@
   <sheetData>
     <row r="1" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B1" s="16" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="E1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="F1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="G1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="19" t="s">
-        <v>5</v>
-      </c>
       <c r="H1" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L1" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="M1" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N1" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="I1" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="J1" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="K1" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="L1" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="M1" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="N1" s="16" t="s">
+      <c r="O1" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="P1" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="P1" s="16" t="s">
+      <c r="Q1" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="Q1" s="16" t="s">
+      <c r="R1" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="S1" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="R1" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="S1" s="16" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D2" s="8">
         <v>45507</v>
@@ -806,27 +807,33 @@
         <v>9.9999999999999998E-46</v>
       </c>
       <c r="F2" s="1">
-        <v>63.3</v>
+        <v>41.8</v>
       </c>
       <c r="G2" s="1">
         <f t="shared" ref="G2:G31" si="0">E2*F2</f>
-        <v>6.3299999999999997E-44</v>
-      </c>
-      <c r="J2" s="9" t="str">
+        <v>4.1799999999999994E-44</v>
+      </c>
+      <c r="H2" s="11">
+        <v>0</v>
+      </c>
+      <c r="I2" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="J2" s="9">
         <f t="shared" ref="J2:J31" si="1">IFERROR(H2/I2,"")</f>
-        <v/>
-      </c>
-      <c r="K2" s="9" t="str">
+        <v>0</v>
+      </c>
+      <c r="K2" s="9">
         <f t="shared" ref="K2:K32" si="2">IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L2" s="12">
         <f t="shared" ref="L2:L31" si="3">F2/(1-(F2*(1+H2)-F2)/(F2*(1+H2)))</f>
-        <v>63.3</v>
+        <v>41.8</v>
       </c>
       <c r="M2" s="12">
         <f t="shared" ref="M2:M31" si="4">F2/(1+I2-H2)</f>
-        <v>63.3</v>
+        <v>29.857142857142858</v>
       </c>
       <c r="N2" s="12">
         <f t="shared" ref="N2:N31" si="5">L2-F2</f>
@@ -834,34 +841,34 @@
       </c>
       <c r="O2" s="12">
         <f t="shared" ref="O2:O31" si="6">0.5*(M2-F2)</f>
-        <v>0</v>
+        <v>-5.9714285714285698</v>
       </c>
       <c r="P2" s="15">
         <f t="shared" ref="P2:P31" si="7">N2+O2</f>
-        <v>0</v>
+        <v>-5.9714285714285698</v>
       </c>
       <c r="Q2" s="12">
         <f>MAX($P$2:$P$280)-P2</f>
-        <v>38.33801960784308</v>
+        <v>89.398549926326339</v>
       </c>
       <c r="R2" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q2)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>2.6083767764452363E-2</v>
+        <v>1.1185863762042041E-2</v>
       </c>
       <c r="S2" s="9">
         <f t="shared" ref="S2:S32" si="8">Q2/MAX($Q$2:$Q$28)</f>
-        <v>0.88019658171881077</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.29521259291506552</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D3" s="8">
         <v>45574</v>
@@ -870,62 +877,69 @@
         <v>9.9999999999999998E-46</v>
       </c>
       <c r="F3" s="1">
-        <v>46.53</v>
+        <v>47.42</v>
       </c>
       <c r="G3" s="1">
         <f t="shared" si="0"/>
-        <v>4.6529999999999999E-44</v>
-      </c>
-      <c r="J3" s="9" t="str">
+        <v>4.7420000000000006E-44</v>
+      </c>
+      <c r="H3" s="11">
+        <f>48.37/F3-1</f>
+        <v>2.0033741037536856E-2</v>
+      </c>
+      <c r="I3" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="J3" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K3" s="9" t="str">
+        <v>5.0084352593842141E-2</v>
+      </c>
+      <c r="K3" s="9">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1.0095425032941828E-2</v>
       </c>
       <c r="L3" s="12">
         <f t="shared" si="3"/>
-        <v>46.53</v>
+        <v>48.37</v>
       </c>
       <c r="M3" s="12">
         <f t="shared" si="4"/>
-        <v>46.53</v>
+        <v>34.36315902075247</v>
       </c>
       <c r="N3" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.94999999999999574</v>
       </c>
       <c r="O3" s="12">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-6.5284204896237661</v>
       </c>
       <c r="P3" s="15">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-5.5784204896237704</v>
       </c>
       <c r="Q3" s="12">
         <f t="shared" ref="Q3:Q32" si="9">MAX($P$2:$P$280)-P3</f>
-        <v>38.33801960784308</v>
+        <v>89.005541844521531</v>
       </c>
       <c r="R3" s="9">
         <f t="shared" ref="R3:R32" si="10">IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q3)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>2.6083767764452363E-2</v>
+        <v>1.1235255460236852E-2</v>
       </c>
       <c r="S3" s="9">
         <f t="shared" si="8"/>
-        <v>0.88019658171881077</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.29391479854410774</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="14" t="s">
         <v>32</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>33</v>
       </c>
       <c r="D4" s="8">
         <v>45511</v>
@@ -940,6 +954,8 @@
         <f t="shared" si="0"/>
         <v>1.1348000000000001E-20</v>
       </c>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
       <c r="J4" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -970,26 +986,26 @@
       </c>
       <c r="Q4" s="12">
         <f t="shared" si="9"/>
-        <v>38.33801960784308</v>
+        <v>83.427121354897764</v>
       </c>
       <c r="R4" s="9">
         <f t="shared" si="10"/>
-        <v>2.6083767764452363E-2</v>
+        <v>1.1986509707628705E-2</v>
       </c>
       <c r="S4" s="9">
         <f t="shared" si="8"/>
-        <v>0.88019658171881077</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.27549369463951967</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D5" s="8">
         <v>45511</v>
@@ -1004,6 +1020,8 @@
         <f t="shared" si="0"/>
         <v>1.5740000000000001E-21</v>
       </c>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
       <c r="J5" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1034,26 +1052,26 @@
       </c>
       <c r="Q5" s="12">
         <f t="shared" si="9"/>
-        <v>38.33801960784308</v>
+        <v>83.427121354897764</v>
       </c>
       <c r="R5" s="9">
         <f t="shared" si="10"/>
-        <v>2.6083767764452363E-2</v>
+        <v>1.1986509707628705E-2</v>
       </c>
       <c r="S5" s="9">
         <f t="shared" si="8"/>
-        <v>0.88019658171881077</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.27549369463951967</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D6" s="8">
         <v>45511</v>
@@ -1068,6 +1086,8 @@
         <f t="shared" si="0"/>
         <v>2.3091E-20</v>
       </c>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
       <c r="J6" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1098,26 +1118,26 @@
       </c>
       <c r="Q6" s="12">
         <f t="shared" si="9"/>
-        <v>38.33801960784308</v>
+        <v>83.427121354897764</v>
       </c>
       <c r="R6" s="9">
         <f t="shared" si="10"/>
-        <v>2.6083767764452363E-2</v>
+        <v>1.1986509707628705E-2</v>
       </c>
       <c r="S6" s="9">
         <f t="shared" si="8"/>
-        <v>0.88019658171881077</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.27549369463951967</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D7" s="8">
         <v>45511</v>
@@ -1132,6 +1152,8 @@
         <f t="shared" si="0"/>
         <v>2.0110000000000001E-21</v>
       </c>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
       <c r="J7" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1162,26 +1184,26 @@
       </c>
       <c r="Q7" s="12">
         <f t="shared" si="9"/>
-        <v>38.33801960784308</v>
+        <v>83.427121354897764</v>
       </c>
       <c r="R7" s="9">
         <f t="shared" si="10"/>
-        <v>2.6083767764452363E-2</v>
+        <v>1.1986509707628705E-2</v>
       </c>
       <c r="S7" s="9">
         <f t="shared" si="8"/>
-        <v>0.88019658171881077</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.27549369463951967</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" t="s">
         <v>55</v>
-      </c>
-      <c r="C8" t="s">
-        <v>56</v>
       </c>
       <c r="D8" s="8">
         <v>45511</v>
@@ -1196,6 +1218,8 @@
         <f t="shared" si="0"/>
         <v>1.2800000000000001E-21</v>
       </c>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
       <c r="J8" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1226,516 +1250,518 @@
       </c>
       <c r="Q8" s="12">
         <f t="shared" si="9"/>
-        <v>38.33801960784308</v>
+        <v>83.427121354897764</v>
       </c>
       <c r="R8" s="9">
         <f t="shared" si="10"/>
-        <v>2.6083767764452363E-2</v>
+        <v>1.1986509707628705E-2</v>
       </c>
       <c r="S8" s="9">
         <f t="shared" si="8"/>
-        <v>0.88019658171881077</v>
+        <v>0.27549369463951967</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>8</v>
+        <v>36</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D9" s="8">
-        <v>45511</v>
+        <v>45574</v>
       </c>
       <c r="E9" s="2">
-        <v>0.14610000000000001</v>
+        <v>0.13370000000000001</v>
       </c>
       <c r="F9" s="1">
-        <v>273.45999999999998</v>
+        <v>423.77</v>
       </c>
       <c r="G9" s="1">
-        <f t="shared" si="0"/>
-        <v>39.952506</v>
+        <f>E9*F9</f>
+        <v>56.658049000000005</v>
       </c>
       <c r="H9" s="11">
-        <v>0.15</v>
+        <v>1.14E-2</v>
       </c>
       <c r="I9" s="11">
-        <v>0.17</v>
+        <v>0.1963</v>
       </c>
       <c r="J9" s="9">
-        <f t="shared" si="1"/>
-        <v>0.88235294117647045</v>
+        <f>IFERROR(H9/I9,"")</f>
+        <v>5.8074375955170655E-2</v>
       </c>
       <c r="K9" s="9">
-        <f t="shared" si="2"/>
-        <v>9.6518568995655959E-2</v>
+        <f>IFERROR(J9/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>1.1705961611299503E-2</v>
       </c>
       <c r="L9" s="12">
-        <f t="shared" si="3"/>
-        <v>314.47899999999993</v>
+        <f>F9/(1-(F9*(1+H9)-F9)/(F9*(1+H9)))</f>
+        <v>428.600978</v>
       </c>
       <c r="M9" s="12">
-        <f t="shared" si="4"/>
-        <v>268.09803921568624</v>
+        <f>F9/(1+I9-H9)</f>
+        <v>357.64199510507217</v>
       </c>
       <c r="N9" s="12">
-        <f t="shared" si="5"/>
-        <v>41.018999999999949</v>
+        <f>L9-F9</f>
+        <v>4.830978000000016</v>
       </c>
       <c r="O9" s="12">
-        <f t="shared" si="6"/>
-        <v>-2.6809803921568687</v>
+        <f>0.5*(M9-F9)</f>
+        <v>-33.064002447463906</v>
       </c>
       <c r="P9" s="15">
-        <f t="shared" si="7"/>
-        <v>38.33801960784308</v>
+        <f>N9+O9</f>
+        <v>-28.23302444746389</v>
       </c>
       <c r="Q9" s="12">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f>MAX($P$2:$P$280)-P9</f>
+        <v>111.66014580236165</v>
       </c>
       <c r="R9" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q9)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>8.9557468585971488E-3</v>
       </c>
       <c r="S9" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f>Q9/MAX($Q$2:$Q$28)</f>
+        <v>0.36872500946329412</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="D10" s="8">
-        <v>45580</v>
+        <v>45553</v>
       </c>
       <c r="E10" s="2">
-        <v>0.19139999999999999</v>
+        <v>1.0751999999999999</v>
       </c>
       <c r="F10" s="1">
-        <v>135.82</v>
+        <v>51.15</v>
       </c>
       <c r="G10" s="1">
-        <f t="shared" si="0"/>
-        <v>25.995947999999999</v>
+        <f>E10*F10</f>
+        <v>54.996479999999998</v>
       </c>
       <c r="H10" s="11">
-        <v>0.15</v>
+        <f>16.68%+7%/4</f>
+        <v>0.18430000000000002</v>
       </c>
       <c r="I10" s="11">
-        <v>0.22</v>
+        <v>0.19980000000000001</v>
       </c>
       <c r="J10" s="9">
-        <f t="shared" si="1"/>
-        <v>0.68181818181818177</v>
+        <f>IFERROR(H10/I10,"")</f>
+        <v>0.92242242242242245</v>
       </c>
       <c r="K10" s="9">
-        <f t="shared" si="2"/>
-        <v>7.4582530587552348E-2</v>
+        <f>IFERROR(J10/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>0.18593125261671253</v>
       </c>
       <c r="L10" s="12">
-        <f t="shared" si="3"/>
-        <v>156.19299999999998</v>
+        <f>F10/(1-(F10*(1+H10)-F10)/(F10*(1+H10)))</f>
+        <v>60.576944999999995</v>
       </c>
       <c r="M10" s="12">
-        <f t="shared" si="4"/>
-        <v>126.93457943925232</v>
+        <f>F10/(1+I10-H10)</f>
+        <v>50.369276218611525</v>
       </c>
       <c r="N10" s="12">
-        <f t="shared" si="5"/>
-        <v>20.37299999999999</v>
+        <f>L10-F10</f>
+        <v>9.4269449999999964</v>
       </c>
       <c r="O10" s="12">
-        <f t="shared" si="6"/>
-        <v>-4.4427102803738379</v>
+        <f>0.5*(M10-F10)</f>
+        <v>-0.39036189069423699</v>
       </c>
       <c r="P10" s="15">
-        <f t="shared" si="7"/>
-        <v>15.930289719626153</v>
+        <f>N10+O10</f>
+        <v>9.0365831093057594</v>
       </c>
       <c r="Q10" s="12">
-        <f t="shared" si="9"/>
-        <v>22.407729888216927</v>
+        <f>MAX($P$2:$P$280)-P10</f>
+        <v>74.390538245592012</v>
       </c>
       <c r="R10" s="9">
-        <f t="shared" si="10"/>
-        <v>4.4627456908334501E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q10)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.3442569762012102E-2</v>
       </c>
       <c r="S10" s="9">
-        <f t="shared" si="8"/>
-        <v>0.51445555752316563</v>
+        <f>Q10/MAX($Q$2:$Q$28)</f>
+        <v>0.24565301900228498</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>27</v>
+        <v>36</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D11" s="8">
-        <v>45511</v>
+        <v>45482</v>
       </c>
       <c r="E11" s="2">
-        <v>0.1933</v>
+        <v>0.18820000000000001</v>
       </c>
       <c r="F11" s="1">
-        <v>77.53</v>
+        <v>227.38</v>
       </c>
       <c r="G11" s="1">
-        <f t="shared" si="0"/>
-        <v>14.986549</v>
+        <f>E11*F11</f>
+        <v>42.792915999999998</v>
       </c>
       <c r="H11" s="11">
-        <v>0.15</v>
+        <v>4.9299999999999997E-2</v>
       </c>
       <c r="I11" s="11">
-        <v>0.26</v>
+        <v>0.2271</v>
       </c>
       <c r="J11" s="9">
-        <f t="shared" si="1"/>
-        <v>0.57692307692307687</v>
+        <f>IFERROR(H11/I11,"")</f>
+        <v>0.21708498458828709</v>
       </c>
       <c r="K11" s="9">
-        <f t="shared" si="2"/>
-        <v>6.3108295112544288E-2</v>
+        <f>IFERROR(J11/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>4.3757482610603554E-2</v>
       </c>
       <c r="L11" s="12">
-        <f t="shared" si="3"/>
-        <v>89.159499999999994</v>
+        <f>F11/(1-(F11*(1+H11)-F11)/(F11*(1+H11)))</f>
+        <v>238.58983399999997</v>
       </c>
       <c r="M11" s="12">
-        <f t="shared" si="4"/>
-        <v>69.846846846846844</v>
+        <f>F11/(1+I11-H11)</f>
+        <v>193.05484802173541</v>
       </c>
       <c r="N11" s="12">
-        <f t="shared" si="5"/>
-        <v>11.629499999999993</v>
+        <f>L11-F11</f>
+        <v>11.209833999999972</v>
       </c>
       <c r="O11" s="12">
-        <f t="shared" si="6"/>
-        <v>-3.8415765765765784</v>
+        <f>0.5*(M11-F11)</f>
+        <v>-17.162575989132293</v>
       </c>
       <c r="P11" s="15">
-        <f t="shared" si="7"/>
-        <v>7.7879234234234147</v>
+        <f>N11+O11</f>
+        <v>-5.9527419891323206</v>
       </c>
       <c r="Q11" s="12">
-        <f t="shared" si="9"/>
-        <v>30.550096184419665</v>
+        <f>MAX($P$2:$P$280)-P11</f>
+        <v>89.379863344030085</v>
       </c>
       <c r="R11" s="9">
-        <f t="shared" si="10"/>
-        <v>3.2733121164770444E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q11)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.1188202382352297E-2</v>
       </c>
       <c r="S11" s="9">
-        <f t="shared" si="8"/>
-        <v>0.70139486879510005</v>
+        <f>Q11/MAX($Q$2:$Q$28)</f>
+        <v>0.29515088593640709</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>24</v>
+      <c r="B12" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="C12" t="s">
         <v>25</v>
       </c>
       <c r="D12" s="8">
-        <v>45482</v>
+        <v>45511</v>
       </c>
       <c r="E12" s="2">
-        <v>0.15210000000000001</v>
+        <v>0.14610000000000001</v>
       </c>
       <c r="F12" s="1">
-        <v>131.38</v>
+        <v>273.45999999999998</v>
       </c>
       <c r="G12" s="1">
-        <f t="shared" si="0"/>
-        <v>19.982898000000002</v>
+        <f>E12*F12</f>
+        <v>39.952506</v>
       </c>
       <c r="H12" s="11">
-        <v>0.3</v>
+        <v>0.16769999999999999</v>
       </c>
       <c r="I12" s="11">
-        <v>0.52</v>
+        <v>0.16700000000000001</v>
       </c>
       <c r="J12" s="9">
-        <f t="shared" si="1"/>
-        <v>0.57692307692307687</v>
+        <f>IFERROR(H12/I12,"")</f>
+        <v>1.0041916167664668</v>
       </c>
       <c r="K12" s="9">
-        <f t="shared" si="2"/>
-        <v>6.3108295112544288E-2</v>
+        <f>IFERROR(J12/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>0.20241334190712787</v>
       </c>
       <c r="L12" s="12">
-        <f t="shared" si="3"/>
-        <v>170.79400000000001</v>
+        <f>F12/(1-(F12*(1+H12)-F12)/(F12*(1+H12)))</f>
+        <v>319.31924199999997</v>
       </c>
       <c r="M12" s="12">
-        <f t="shared" si="4"/>
-        <v>107.68852459016394</v>
+        <f>F12/(1+I12-H12)</f>
+        <v>273.65155608926244</v>
       </c>
       <c r="N12" s="12">
-        <f t="shared" si="5"/>
-        <v>39.414000000000016</v>
+        <f>L12-F12</f>
+        <v>45.859241999999995</v>
       </c>
       <c r="O12" s="12">
-        <f t="shared" si="6"/>
-        <v>-11.845737704918029</v>
+        <f>0.5*(M12-F12)</f>
+        <v>9.5778044631231296E-2</v>
       </c>
       <c r="P12" s="15">
-        <f t="shared" si="7"/>
-        <v>27.568262295081986</v>
+        <f>N12+O12</f>
+        <v>45.955020044631226</v>
       </c>
       <c r="Q12" s="12">
-        <f t="shared" si="9"/>
-        <v>10.769757312761094</v>
+        <f>MAX($P$2:$P$280)-P12</f>
+        <v>37.472101310266538</v>
       </c>
       <c r="R12" s="9">
-        <f t="shared" si="10"/>
-        <v>9.2852602984386592E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q12)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>2.6686520505483952E-2</v>
       </c>
       <c r="S12" s="9">
-        <f t="shared" si="8"/>
-        <v>0.24726116971086817</v>
+        <f>Q12/MAX($Q$2:$Q$28)</f>
+        <v>0.12374066692240798</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D13" s="8">
-        <v>45484</v>
+        <v>45544</v>
       </c>
       <c r="E13" s="2">
-        <v>0.18179999999999999</v>
+        <v>0.1928</v>
       </c>
       <c r="F13" s="1">
-        <v>192.37</v>
+        <v>188.12</v>
       </c>
       <c r="G13" s="1">
-        <f t="shared" si="0"/>
-        <v>34.972865999999996</v>
+        <f>E13*F13</f>
+        <v>36.269536000000002</v>
       </c>
       <c r="H13" s="11">
-        <v>0.2</v>
+        <v>-6.8599999999999994E-2</v>
       </c>
       <c r="I13" s="11">
-        <v>0.35</v>
+        <v>0.37780000000000002</v>
       </c>
       <c r="J13" s="9">
-        <f t="shared" si="1"/>
-        <v>0.57142857142857151</v>
+        <f>IFERROR(H13/I13,"")</f>
+        <v>-0.18157755426151401</v>
       </c>
       <c r="K13" s="9">
-        <f t="shared" si="2"/>
-        <v>6.2507263730520068E-2</v>
+        <f>IFERROR(J13/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>-3.6600305120793777E-2</v>
       </c>
       <c r="L13" s="12">
-        <f t="shared" si="3"/>
-        <v>230.84399999999999</v>
+        <f>F13/(1-(F13*(1+H13)-F13)/(F13*(1+H13)))</f>
+        <v>175.214968</v>
       </c>
       <c r="M13" s="12">
-        <f t="shared" si="4"/>
-        <v>167.2782608695652</v>
+        <f>F13/(1+I13-H13)</f>
+        <v>130.06084070796459</v>
       </c>
       <c r="N13" s="12">
-        <f t="shared" si="5"/>
-        <v>38.47399999999999</v>
+        <f>L13-F13</f>
+        <v>-12.905032000000006</v>
       </c>
       <c r="O13" s="12">
-        <f t="shared" si="6"/>
-        <v>-12.545869565217401</v>
+        <f>0.5*(M13-F13)</f>
+        <v>-29.029579646017709</v>
       </c>
       <c r="P13" s="15">
-        <f t="shared" si="7"/>
-        <v>25.928130434782588</v>
+        <f>N13+O13</f>
+        <v>-41.934611646017714</v>
       </c>
       <c r="Q13" s="12">
-        <f t="shared" si="9"/>
-        <v>12.409889173060492</v>
+        <f>MAX($P$2:$P$280)-P13</f>
+        <v>125.36173300091548</v>
       </c>
       <c r="R13" s="9">
-        <f t="shared" si="10"/>
-        <v>8.058089690041792E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q13)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>7.9769158902158552E-3</v>
       </c>
       <c r="S13" s="9">
-        <f t="shared" si="8"/>
-        <v>0.28491669995918356</v>
+        <f>Q13/MAX($Q$2:$Q$28)</f>
+        <v>0.4139704982018737</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>9</v>
+      <c r="B14" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D14" s="8">
-        <v>45511</v>
+        <v>45544</v>
       </c>
       <c r="E14" s="2">
-        <v>3.2899999999999999E-2</v>
+        <v>0.24390000000000001</v>
       </c>
       <c r="F14" s="1">
-        <v>455.4</v>
+        <v>144.28</v>
       </c>
       <c r="G14" s="1">
-        <f t="shared" si="0"/>
-        <v>14.982659999999999</v>
+        <f>E14*F14</f>
+        <v>35.189892</v>
       </c>
       <c r="H14" s="11">
-        <v>0.1</v>
+        <v>-2.8000000000000001E-2</v>
       </c>
       <c r="I14" s="11">
-        <v>0.18</v>
+        <v>0.18340000000000001</v>
       </c>
       <c r="J14" s="9">
-        <f t="shared" si="1"/>
-        <v>0.55555555555555558</v>
+        <f>IFERROR(H14/I14,"")</f>
+        <v>-0.15267175572519084</v>
       </c>
       <c r="K14" s="9">
-        <f t="shared" si="2"/>
-        <v>6.0770950849116732E-2</v>
+        <f>IFERROR(J14/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>-3.0773808280408366E-2</v>
       </c>
       <c r="L14" s="12">
-        <f t="shared" si="3"/>
-        <v>500.94</v>
+        <f>F14/(1-(F14*(1+H14)-F14)/(F14*(1+H14)))</f>
+        <v>140.24016</v>
       </c>
       <c r="M14" s="12">
-        <f t="shared" si="4"/>
-        <v>421.66666666666669</v>
+        <f>F14/(1+I14-H14)</f>
+        <v>119.10186561003798</v>
       </c>
       <c r="N14" s="12">
-        <f t="shared" si="5"/>
-        <v>45.54000000000002</v>
+        <f>L14-F14</f>
+        <v>-4.0398399999999981</v>
       </c>
       <c r="O14" s="12">
-        <f t="shared" si="6"/>
-        <v>-16.866666666666646</v>
+        <f>0.5*(M14-F14)</f>
+        <v>-12.589067194981013</v>
       </c>
       <c r="P14" s="15">
-        <f t="shared" si="7"/>
-        <v>28.673333333333375</v>
+        <f>N14+O14</f>
+        <v>-16.628907194981011</v>
       </c>
       <c r="Q14" s="12">
-        <f t="shared" si="9"/>
-        <v>9.6646862745097053</v>
+        <f>MAX($P$2:$P$280)-P14</f>
+        <v>100.05602854987877</v>
       </c>
       <c r="R14" s="9">
-        <f t="shared" si="10"/>
-        <v>0.10346947346210993</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q14)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.9944002824526607E-3</v>
       </c>
       <c r="S14" s="9">
-        <f t="shared" si="8"/>
-        <v>0.22189001699158839</v>
+        <f>Q14/MAX($Q$2:$Q$28)</f>
+        <v>0.33040580243567419</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D15" s="8">
-        <v>45482</v>
+        <v>45484</v>
       </c>
       <c r="E15" s="2">
-        <v>0.18820000000000001</v>
+        <v>0.24990000000000001</v>
       </c>
       <c r="F15" s="1">
-        <v>227.38</v>
+        <v>191.91</v>
       </c>
       <c r="G15" s="1">
-        <f t="shared" si="0"/>
-        <v>42.792915999999998</v>
+        <f>E15*F15</f>
+        <v>47.958309</v>
       </c>
       <c r="H15" s="11">
-        <v>0.1</v>
-      </c>
-      <c r="I15" s="13">
-        <v>0.22500000000000001</v>
+        <f>227.4/F15-1</f>
+        <v>0.18493043614194149</v>
+      </c>
+      <c r="I15" s="11">
+        <v>0.37</v>
       </c>
       <c r="J15" s="9">
-        <f t="shared" si="1"/>
-        <v>0.44444444444444448</v>
+        <f>IFERROR(H15/I15,"")</f>
+        <v>0.49981198957281486</v>
       </c>
       <c r="K15" s="9">
-        <f t="shared" si="2"/>
-        <v>4.8616760679293387E-2</v>
+        <f>IFERROR(J15/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>0.10074632514902941</v>
       </c>
       <c r="L15" s="12">
-        <f t="shared" si="3"/>
-        <v>250.11800000000002</v>
+        <f>F15/(1-(F15*(1+H15)-F15)/(F15*(1+H15)))</f>
+        <v>227.39999999999998</v>
       </c>
       <c r="M15" s="12">
-        <f t="shared" si="4"/>
-        <v>202.11555555555555</v>
+        <f>F15/(1+I15-H15)</f>
+        <v>161.93986062322494</v>
       </c>
       <c r="N15" s="12">
-        <f t="shared" si="5"/>
-        <v>22.738000000000028</v>
+        <f>L15-F15</f>
+        <v>35.489999999999981</v>
       </c>
       <c r="O15" s="12">
-        <f t="shared" si="6"/>
-        <v>-12.632222222222225</v>
+        <f>0.5*(M15-F15)</f>
+        <v>-14.985069688387526</v>
       </c>
       <c r="P15" s="15">
-        <f t="shared" si="7"/>
-        <v>10.105777777777803</v>
+        <f>N15+O15</f>
+        <v>20.504930311612455</v>
       </c>
       <c r="Q15" s="12">
-        <f t="shared" si="9"/>
-        <v>28.232241830065277</v>
+        <f>MAX($P$2:$P$280)-P15</f>
+        <v>62.922191043285309</v>
       </c>
       <c r="R15" s="9">
-        <f t="shared" si="10"/>
-        <v>3.5420495687844132E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q15)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.5892644286847574E-2</v>
       </c>
       <c r="S15" s="9">
-        <f t="shared" si="8"/>
-        <v>0.6481796140559789</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+        <f>Q15/MAX($Q$2:$Q$28)</f>
+        <v>0.20778215289949825</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="C16" t="s">
         <v>76</v>
-      </c>
-      <c r="C16" t="s">
-        <v>77</v>
       </c>
       <c r="D16" s="8">
         <v>45562</v>
@@ -1747,7 +1773,7 @@
         <v>56</v>
       </c>
       <c r="G16" s="1">
-        <f t="shared" si="0"/>
+        <f>E16*F16</f>
         <v>5.5999999999999999E-34</v>
       </c>
       <c r="H16" s="11">
@@ -1757,55 +1783,55 @@
         <v>0.19</v>
       </c>
       <c r="J16" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H16/I16,"")</f>
         <v>0.42105263157894735</v>
       </c>
       <c r="K16" s="9">
-        <f t="shared" si="2"/>
-        <v>4.6057983801435831E-2</v>
+        <f>IFERROR(J16/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>8.4870923889126232E-2</v>
       </c>
       <c r="L16" s="12">
-        <f t="shared" si="3"/>
+        <f>F16/(1-(F16*(1+H16)-F16)/(F16*(1+H16)))</f>
         <v>60.480000000000004</v>
       </c>
       <c r="M16" s="12">
-        <f t="shared" si="4"/>
+        <f>F16/(1+I16-H16)</f>
         <v>50.450450450450454</v>
       </c>
       <c r="N16" s="12">
-        <f t="shared" si="5"/>
+        <f>L16-F16</f>
         <v>4.480000000000004</v>
       </c>
       <c r="O16" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(M16-F16)</f>
         <v>-2.7747747747747731</v>
       </c>
       <c r="P16" s="15">
-        <f t="shared" si="7"/>
+        <f>N16+O16</f>
         <v>1.7052252252252309</v>
       </c>
       <c r="Q16" s="12">
-        <f t="shared" si="9"/>
-        <v>36.632794382617845</v>
+        <f>MAX($P$2:$P$280)-P16</f>
+        <v>81.72189612967253</v>
       </c>
       <c r="R16" s="9">
-        <f t="shared" si="10"/>
-        <v>2.7297944829305656E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q16)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.223662258659841E-2</v>
       </c>
       <c r="S16" s="9">
-        <f t="shared" si="8"/>
-        <v>0.8410465831102002</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+        <f>Q16/MAX($Q$2:$Q$28)</f>
+        <v>0.26986268652296996</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" t="s">
         <v>57</v>
-      </c>
-      <c r="C17" t="s">
-        <v>58</v>
       </c>
       <c r="D17" s="8">
         <v>45505</v>
@@ -1814,138 +1840,139 @@
         <v>1E-35</v>
       </c>
       <c r="F17" s="1">
-        <v>82.17</v>
+        <v>86.6</v>
       </c>
       <c r="G17" s="1">
-        <f t="shared" si="0"/>
-        <v>8.2170000000000005E-34</v>
+        <f>E17*F17</f>
+        <v>8.6599999999999988E-34</v>
       </c>
       <c r="H17" s="11">
-        <v>0.08</v>
+        <f>89.44/F17-1</f>
+        <v>3.2794457274826883E-2</v>
       </c>
       <c r="I17" s="11">
-        <v>0.19</v>
+        <v>0.17249999999999999</v>
       </c>
       <c r="J17" s="9">
-        <f t="shared" si="1"/>
-        <v>0.42105263157894735</v>
+        <f>IFERROR(H17/I17,"")</f>
+        <v>0.19011279579609788</v>
       </c>
       <c r="K17" s="9">
-        <f t="shared" si="2"/>
-        <v>4.6057983801435831E-2</v>
+        <f>IFERROR(J17/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>3.8320740478104097E-2</v>
       </c>
       <c r="L17" s="12">
-        <f t="shared" si="3"/>
-        <v>88.743600000000001</v>
+        <f>F17/(1-(F17*(1+H17)-F17)/(F17*(1+H17)))</f>
+        <v>89.44</v>
       </c>
       <c r="M17" s="12">
-        <f t="shared" si="4"/>
-        <v>74.027027027027032</v>
+        <f>F17/(1+I17-H17)</f>
+        <v>75.984538772119137</v>
       </c>
       <c r="N17" s="12">
-        <f t="shared" si="5"/>
-        <v>6.573599999999999</v>
+        <f>L17-F17</f>
+        <v>2.8400000000000034</v>
       </c>
       <c r="O17" s="12">
-        <f t="shared" si="6"/>
-        <v>-4.071486486486485</v>
+        <f>0.5*(M17-F17)</f>
+        <v>-5.3077306139404286</v>
       </c>
       <c r="P17" s="15">
-        <f t="shared" si="7"/>
-        <v>2.502113513513514</v>
+        <f>N17+O17</f>
+        <v>-2.4677306139404251</v>
       </c>
       <c r="Q17" s="12">
-        <f t="shared" si="9"/>
-        <v>35.835906094329566</v>
+        <f>MAX($P$2:$P$280)-P17</f>
+        <v>85.894851968838196</v>
       </c>
       <c r="R17" s="9">
-        <f t="shared" si="10"/>
-        <v>2.7904973223440644E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q17)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.1642141258509767E-2</v>
       </c>
       <c r="S17" s="9">
-        <f t="shared" si="8"/>
-        <v>0.82275094983185515</v>
+        <f>Q17/MAX($Q$2:$Q$28)</f>
+        <v>0.28364265403268213</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>12</v>
+        <v>38</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D18" s="8">
-        <v>45574</v>
+        <v>45460</v>
       </c>
       <c r="E18" s="2">
-        <v>0.13370000000000001</v>
+        <v>0.1807</v>
       </c>
       <c r="F18" s="1">
-        <v>423.77</v>
+        <v>165.59</v>
       </c>
       <c r="G18" s="1">
-        <f t="shared" si="0"/>
-        <v>56.658049000000005</v>
+        <f>E18*F18</f>
+        <v>29.922113</v>
       </c>
       <c r="H18" s="11">
-        <v>7.0000000000000007E-2</v>
+        <v>6.7199999999999996E-2</v>
       </c>
       <c r="I18" s="11">
-        <v>0.19</v>
+        <v>0.16439999999999999</v>
       </c>
       <c r="J18" s="9">
-        <f t="shared" si="1"/>
-        <v>0.36842105263157898</v>
+        <f>IFERROR(H18/I18,"")</f>
+        <v>0.40875912408759124</v>
       </c>
       <c r="K18" s="9">
-        <f t="shared" si="2"/>
-        <v>4.0300735826256359E-2</v>
+        <f>IFERROR(J18/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>8.2392940709881665E-2</v>
       </c>
       <c r="L18" s="12">
-        <f t="shared" si="3"/>
-        <v>453.43389999999999</v>
+        <f>F18/(1-(F18*(1+H18)-F18)/(F18*(1+H18)))</f>
+        <v>176.717648</v>
       </c>
       <c r="M18" s="12">
-        <f t="shared" si="4"/>
-        <v>378.36607142857144</v>
+        <f>F18/(1+I18-H18)</f>
+        <v>150.92052497265766</v>
       </c>
       <c r="N18" s="12">
-        <f t="shared" si="5"/>
-        <v>29.663900000000012</v>
+        <f>L18-F18</f>
+        <v>11.127647999999994</v>
       </c>
       <c r="O18" s="12">
-        <f t="shared" si="6"/>
-        <v>-22.701964285714268</v>
+        <f>0.5*(M18-F18)</f>
+        <v>-7.3347375136711719</v>
       </c>
       <c r="P18" s="15">
-        <f t="shared" si="7"/>
-        <v>6.9619357142857439</v>
+        <f>N18+O18</f>
+        <v>3.7929104863288217</v>
       </c>
       <c r="Q18" s="12">
-        <f t="shared" si="9"/>
-        <v>31.376083893557336</v>
+        <f>MAX($P$2:$P$280)-P18</f>
+        <v>79.634210868568942</v>
       </c>
       <c r="R18" s="9">
-        <f t="shared" si="10"/>
-        <v>3.1871408917456927E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q18)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.2557417083600347E-2</v>
       </c>
       <c r="S18" s="9">
-        <f t="shared" si="8"/>
-        <v>0.7203585911146535</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+        <f>Q18/MAX($Q$2:$Q$28)</f>
+        <v>0.26296871587547221</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="C19" t="s">
         <v>79</v>
-      </c>
-      <c r="C19" t="s">
-        <v>80</v>
       </c>
       <c r="D19" s="8">
         <v>45580</v>
@@ -1957,7 +1984,7 @@
         <v>20.399999999999999</v>
       </c>
       <c r="G19" s="1">
-        <f t="shared" si="0"/>
+        <f>E19*F19</f>
         <v>2.0399999999999999E-34</v>
       </c>
       <c r="H19" s="11">
@@ -1967,405 +1994,407 @@
         <v>0.15</v>
       </c>
       <c r="J19" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H19/I19,"")</f>
         <v>0.33333333333333337</v>
       </c>
       <c r="K19" s="9">
-        <f t="shared" si="2"/>
-        <v>3.6462570509470042E-2</v>
+        <f>IFERROR(J19/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>6.7189481412224944E-2</v>
       </c>
       <c r="L19" s="12">
-        <f t="shared" si="3"/>
+        <f>F19/(1-(F19*(1+H19)-F19)/(F19*(1+H19)))</f>
         <v>21.419999999999998</v>
       </c>
       <c r="M19" s="12">
-        <f t="shared" si="4"/>
+        <f>F19/(1+I19-H19)</f>
         <v>18.545454545454547</v>
       </c>
       <c r="N19" s="12">
-        <f t="shared" si="5"/>
+        <f>L19-F19</f>
         <v>1.0199999999999996</v>
       </c>
       <c r="O19" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(M19-F19)</f>
         <v>-0.92727272727272592</v>
       </c>
       <c r="P19" s="15">
-        <f t="shared" si="7"/>
+        <f>N19+O19</f>
         <v>9.2727272727273657E-2</v>
       </c>
       <c r="Q19" s="12">
-        <f t="shared" si="9"/>
-        <v>38.245292335115806</v>
+        <f>MAX($P$2:$P$280)-P19</f>
+        <v>83.33439408217049</v>
       </c>
       <c r="R19" s="9">
-        <f t="shared" si="10"/>
-        <v>2.6147008924333064E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q19)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.199984725411175E-2</v>
       </c>
       <c r="S19" s="9">
-        <f t="shared" si="8"/>
-        <v>0.87806767080161885</v>
+        <f>Q19/MAX($Q$2:$Q$28)</f>
+        <v>0.27518748991205688</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="D20" s="8">
-        <v>45580</v>
+        <v>45562</v>
       </c>
       <c r="E20" s="2">
-        <v>0.18010000000000001</v>
+        <v>4.0300000000000002E-2</v>
       </c>
       <c r="F20" s="1">
-        <v>133.19999999999999</v>
+        <v>668.82</v>
       </c>
       <c r="G20" s="1">
-        <f t="shared" si="0"/>
-        <v>23.989319999999999</v>
+        <f>E20*F20</f>
+        <v>26.953446000000003</v>
       </c>
       <c r="H20" s="11">
-        <v>0.05</v>
+        <f>553.57/F20-1</f>
+        <v>-0.17231841153075567</v>
       </c>
       <c r="I20" s="11">
-        <v>0.16</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="J20" s="9">
-        <f t="shared" si="1"/>
-        <v>0.3125</v>
+        <f>IFERROR(H20/I20,"")</f>
+        <v>-0.61542289832412733</v>
       </c>
       <c r="K20" s="9">
-        <f t="shared" si="2"/>
-        <v>3.4183659852628161E-2</v>
+        <f>IFERROR(J20/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>-0.12404983616281964</v>
       </c>
       <c r="L20" s="12">
-        <f t="shared" si="3"/>
-        <v>139.85999999999999</v>
+        <f>F20/(1-(F20*(1+H20)-F20)/(F20*(1+H20)))</f>
+        <v>553.57000000000005</v>
       </c>
       <c r="M20" s="12">
-        <f t="shared" si="4"/>
-        <v>120</v>
+        <f>F20/(1+I20-H20)</f>
+        <v>460.51884675555289</v>
       </c>
       <c r="N20" s="12">
-        <f t="shared" si="5"/>
-        <v>6.6599999999999966</v>
+        <f>L20-F20</f>
+        <v>-115.25</v>
       </c>
       <c r="O20" s="12">
-        <f t="shared" si="6"/>
-        <v>-6.5999999999999943</v>
+        <f>0.5*(M20-F20)</f>
+        <v>-104.15057662222358</v>
       </c>
       <c r="P20" s="15">
-        <f t="shared" si="7"/>
-        <v>6.0000000000002274E-2</v>
+        <f>N20+O20</f>
+        <v>-219.40057662222358</v>
       </c>
       <c r="Q20" s="12">
-        <f t="shared" si="9"/>
-        <v>38.278019607843078</v>
+        <f>MAX($P$2:$P$280)-P20</f>
+        <v>302.82769797712137</v>
       </c>
       <c r="R20" s="9">
-        <f t="shared" si="10"/>
-        <v>2.6124653528185725E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q20)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>3.3022078451871001E-3</v>
       </c>
       <c r="S20" s="9">
-        <f t="shared" si="8"/>
-        <v>0.87881905112533354</v>
+        <f>Q20/MAX($Q$2:$Q$28)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>16</v>
+      <c r="B21" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="D21" s="8">
-        <v>45460</v>
+        <v>45580</v>
       </c>
       <c r="E21" s="2">
-        <v>0.1807</v>
+        <v>0.19139999999999999</v>
       </c>
       <c r="F21" s="1">
-        <v>165.59</v>
+        <v>135.82</v>
       </c>
       <c r="G21" s="1">
-        <f t="shared" si="0"/>
-        <v>29.922113</v>
+        <f>E21*F21</f>
+        <v>25.995947999999999</v>
       </c>
       <c r="H21" s="11">
-        <v>0.06</v>
+        <v>0.1202</v>
       </c>
       <c r="I21" s="11">
-        <v>0.21</v>
+        <v>0.33710000000000001</v>
       </c>
       <c r="J21" s="9">
-        <f t="shared" si="1"/>
-        <v>0.2857142857142857</v>
+        <f>IFERROR(H21/I21,"")</f>
+        <v>0.35657075051913378</v>
       </c>
       <c r="K21" s="9">
-        <f t="shared" si="2"/>
-        <v>3.1253631865260027E-2</v>
+        <f>IFERROR(J21/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>7.1873411442445301E-2</v>
       </c>
       <c r="L21" s="12">
-        <f t="shared" si="3"/>
-        <v>175.52540000000002</v>
+        <f>F21/(1-(F21*(1+H21)-F21)/(F21*(1+H21)))</f>
+        <v>152.14556400000001</v>
       </c>
       <c r="M21" s="12">
-        <f t="shared" si="4"/>
-        <v>143.99130434782609</v>
+        <f>F21/(1+I21-H21)</f>
+        <v>111.61147177253677</v>
       </c>
       <c r="N21" s="12">
-        <f t="shared" si="5"/>
-        <v>9.9354000000000156</v>
+        <f>L21-F21</f>
+        <v>16.325564000000014</v>
       </c>
       <c r="O21" s="12">
-        <f t="shared" si="6"/>
-        <v>-10.799347826086958</v>
+        <f>0.5*(M21-F21)</f>
+        <v>-12.10426411373161</v>
       </c>
       <c r="P21" s="15">
-        <f t="shared" si="7"/>
-        <v>-0.86394782608694243</v>
+        <f>N21+O21</f>
+        <v>4.2212998862684046</v>
       </c>
       <c r="Q21" s="12">
-        <f t="shared" si="9"/>
-        <v>39.201967433930022</v>
+        <f>MAX($P$2:$P$280)-P21</f>
+        <v>79.205821468629352</v>
       </c>
       <c r="R21" s="9">
-        <f t="shared" si="10"/>
-        <v>2.5508923797903104E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q21)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.2625334621345541E-2</v>
       </c>
       <c r="S21" s="9">
-        <f t="shared" si="8"/>
-        <v>0.90003182441219065</v>
+        <f>Q21/MAX($Q$2:$Q$28)</f>
+        <v>0.26155408503819672</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>7</v>
+      <c r="B22" s="6" t="s">
+        <v>60</v>
       </c>
       <c r="C22" t="s">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="D22" s="8">
-        <v>45553</v>
+        <v>45580</v>
       </c>
       <c r="E22" s="2">
-        <v>1.0751999999999999</v>
+        <v>0.18010000000000001</v>
       </c>
       <c r="F22" s="1">
-        <v>51.15</v>
+        <v>133.19999999999999</v>
       </c>
       <c r="G22" s="1">
-        <f t="shared" si="0"/>
-        <v>54.996479999999998</v>
+        <f>E22*F22</f>
+        <v>23.989319999999999</v>
       </c>
       <c r="H22" s="11">
-        <v>7.1999999999999995E-2</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="I22" s="11">
-        <v>0.251</v>
+        <v>0.1623</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" si="1"/>
-        <v>0.28685258964143423</v>
+        <f>IFERROR(H22/I22,"")</f>
+        <v>3.0807147258163893E-2</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" si="2"/>
-        <v>3.1378148326874612E-2</v>
+        <f>IFERROR(J22/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>6.2097487441982379E-3</v>
       </c>
       <c r="L22" s="12">
-        <f t="shared" si="3"/>
-        <v>54.832799999999999</v>
+        <f>F22/(1-(F22*(1+H22)-F22)/(F22*(1+H22)))</f>
+        <v>133.86599999999999</v>
       </c>
       <c r="M22" s="12">
-        <f t="shared" si="4"/>
-        <v>43.384223918575067</v>
+        <f>F22/(1+I22-H22)</f>
+        <v>115.09548086062384</v>
       </c>
       <c r="N22" s="12">
-        <f t="shared" si="5"/>
-        <v>3.6828000000000003</v>
+        <f>L22-F22</f>
+        <v>0.66599999999999682</v>
       </c>
       <c r="O22" s="12">
-        <f t="shared" si="6"/>
-        <v>-3.8828880407124657</v>
+        <f>0.5*(M22-F22)</f>
+        <v>-9.0522595696880757</v>
       </c>
       <c r="P22" s="15">
-        <f t="shared" si="7"/>
-        <v>-0.20008804071246544</v>
+        <f>N22+O22</f>
+        <v>-8.3862595696880788</v>
       </c>
       <c r="Q22" s="12">
-        <f t="shared" si="9"/>
-        <v>38.538107648555545</v>
+        <f>MAX($P$2:$P$280)-P22</f>
+        <v>91.813380924585843</v>
       </c>
       <c r="R22" s="9">
-        <f t="shared" si="10"/>
-        <v>2.5948342070124485E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q22)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.0891658600627999E-2</v>
       </c>
       <c r="S22" s="9">
-        <f t="shared" si="8"/>
-        <v>0.88479037167664931</v>
+        <f>Q22/MAX($Q$2:$Q$28)</f>
+        <v>0.30318686678231904</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>39</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>20</v>
+        <v>36</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="C23" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D23" s="8">
-        <v>45544</v>
+        <v>45482</v>
       </c>
       <c r="E23" s="2">
-        <v>0.24390000000000001</v>
+        <v>0.15210000000000001</v>
       </c>
       <c r="F23" s="1">
-        <v>144.28</v>
+        <v>147.01</v>
       </c>
       <c r="G23" s="1">
-        <f t="shared" si="0"/>
-        <v>35.189892</v>
+        <f>E23*F23</f>
+        <v>22.360220999999999</v>
       </c>
       <c r="H23" s="11">
-        <v>0.06</v>
+        <f>193.73/F23-1</f>
+        <v>0.3178015101013536</v>
       </c>
       <c r="I23" s="11">
-        <v>0.21</v>
+        <v>0.52380000000000004</v>
       </c>
       <c r="J23" s="9">
-        <f t="shared" si="1"/>
-        <v>0.2857142857142857</v>
+        <f>IFERROR(H23/I23,"")</f>
+        <v>0.60672300515722333</v>
       </c>
       <c r="K23" s="9">
-        <f t="shared" si="2"/>
-        <v>3.1253631865260027E-2</v>
+        <f>IFERROR(J23/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>0.12229621223214153</v>
       </c>
       <c r="L23" s="12">
-        <f t="shared" si="3"/>
-        <v>152.93680000000001</v>
+        <f>F23/(1-(F23*(1+H23)-F23)/(F23*(1+H23)))</f>
+        <v>193.72999999999996</v>
       </c>
       <c r="M23" s="12">
-        <f t="shared" si="4"/>
-        <v>125.46086956521741</v>
+        <f>F23/(1+I23-H23)</f>
+        <v>121.89899177432211</v>
       </c>
       <c r="N23" s="12">
-        <f t="shared" si="5"/>
-        <v>8.656800000000004</v>
+        <f>L23-F23</f>
+        <v>46.71999999999997</v>
       </c>
       <c r="O23" s="12">
-        <f t="shared" si="6"/>
-        <v>-9.4095652173912967</v>
+        <f>0.5*(M23-F23)</f>
+        <v>-12.555504112838939</v>
       </c>
       <c r="P23" s="15">
-        <f t="shared" si="7"/>
-        <v>-0.75276521739129265</v>
+        <f>N23+O23</f>
+        <v>34.164495887161031</v>
       </c>
       <c r="Q23" s="12">
-        <f t="shared" si="9"/>
-        <v>39.090784825234373</v>
+        <f>MAX($P$2:$P$280)-P23</f>
+        <v>49.262625467736733</v>
       </c>
       <c r="R23" s="9">
-        <f t="shared" si="10"/>
-        <v>2.5581476669521035E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q23)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>2.0299364690883635E-2</v>
       </c>
       <c r="S23" s="9">
-        <f t="shared" si="8"/>
-        <v>0.89747920032984307</v>
+        <f>Q23/MAX($Q$2:$Q$28)</f>
+        <v>0.16267542829407408</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="C24" t="s">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="D24" s="8">
-        <v>45544</v>
+        <v>45481</v>
       </c>
       <c r="E24" s="2">
-        <v>0.1928</v>
+        <v>2.8500000000000001E-2</v>
       </c>
       <c r="F24" s="1">
-        <v>188.12</v>
+        <v>700.32</v>
       </c>
       <c r="G24" s="1">
-        <f t="shared" si="0"/>
-        <v>36.269536000000002</v>
+        <f>E24*F24</f>
+        <v>19.959120000000002</v>
       </c>
       <c r="H24" s="11">
-        <v>0.1</v>
+        <v>-6.6500000000000004E-2</v>
       </c>
       <c r="I24" s="11">
-        <v>0.37</v>
+        <v>0.45340000000000003</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" si="1"/>
-        <v>0.27027027027027029</v>
+        <f>IFERROR(H24/I24,"")</f>
+        <v>-0.14666960741067489</v>
       </c>
       <c r="K24" s="9">
-        <f t="shared" si="2"/>
-        <v>2.956424635902976E-2</v>
+        <f>IFERROR(J24/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>-2.9563964582573606E-2</v>
       </c>
       <c r="L24" s="12">
-        <f t="shared" si="3"/>
-        <v>206.93200000000002</v>
+        <f>F24/(1-(F24*(1+H24)-F24)/(F24*(1+H24)))</f>
+        <v>653.74872000000005</v>
       </c>
       <c r="M24" s="12">
-        <f t="shared" si="4"/>
-        <v>148.1259842519685</v>
+        <f>F24/(1+I24-H24)</f>
+        <v>460.76715573392988</v>
       </c>
       <c r="N24" s="12">
-        <f t="shared" si="5"/>
-        <v>18.812000000000012</v>
+        <f>L24-F24</f>
+        <v>-46.571280000000002</v>
       </c>
       <c r="O24" s="12">
-        <f t="shared" si="6"/>
-        <v>-19.99700787401575</v>
+        <f>0.5*(M24-F24)</f>
+        <v>-119.77642213303508</v>
       </c>
       <c r="P24" s="15">
-        <f t="shared" si="7"/>
-        <v>-1.1850078740157386</v>
+        <f>N24+O24</f>
+        <v>-166.34770213303509</v>
       </c>
       <c r="Q24" s="12">
-        <f t="shared" si="9"/>
-        <v>39.523027481858819</v>
+        <f>MAX($P$2:$P$280)-P24</f>
+        <v>249.77482348793285</v>
       </c>
       <c r="R24" s="9">
-        <f t="shared" si="10"/>
-        <v>2.5301705454092625E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q24)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>4.0036060722041193E-3</v>
       </c>
       <c r="S24" s="9">
-        <f t="shared" si="8"/>
-        <v>0.90740299171827632</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+        <f>Q24/MAX($Q$2:$Q$28)</f>
+        <v>0.82480838165207504</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D25" s="8">
         <v>45483</v>
@@ -2374,68 +2403,69 @@
         <v>9.9999999999999997E-29</v>
       </c>
       <c r="F25" s="1">
-        <v>174.26</v>
+        <v>178.12</v>
       </c>
       <c r="G25" s="1">
-        <f t="shared" si="0"/>
-        <v>1.7425999999999999E-26</v>
+        <f>E25*F25</f>
+        <v>1.7812E-26</v>
       </c>
       <c r="H25" s="11">
-        <v>7.0000000000000007E-2</v>
+        <f>190.41/F25-1</f>
+        <v>6.8998428026049829E-2</v>
       </c>
       <c r="I25" s="11">
-        <v>0.26</v>
+        <v>0.26790000000000003</v>
       </c>
       <c r="J25" s="9">
-        <f t="shared" si="1"/>
-        <v>0.26923076923076927</v>
+        <f>IFERROR(H25/I25,"")</f>
+        <v>0.25755292282959996</v>
       </c>
       <c r="K25" s="9">
-        <f t="shared" si="2"/>
-        <v>2.945053771918734E-2</v>
+        <f>IFERROR(J25/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>5.1914541963370829E-2</v>
       </c>
       <c r="L25" s="12">
-        <f t="shared" si="3"/>
-        <v>186.45820000000001</v>
+        <f>F25/(1-(F25*(1+H25)-F25)/(F25*(1+H25)))</f>
+        <v>190.41</v>
       </c>
       <c r="M25" s="12">
-        <f t="shared" si="4"/>
-        <v>146.43697478991598</v>
+        <f>F25/(1+I25-H25)</f>
+        <v>148.56932726072878</v>
       </c>
       <c r="N25" s="12">
-        <f t="shared" si="5"/>
-        <v>12.198200000000014</v>
+        <f>L25-F25</f>
+        <v>12.289999999999992</v>
       </c>
       <c r="O25" s="12">
-        <f t="shared" si="6"/>
-        <v>-13.911512605042006</v>
+        <f>0.5*(M25-F25)</f>
+        <v>-14.77533636963561</v>
       </c>
       <c r="P25" s="15">
-        <f t="shared" si="7"/>
-        <v>-1.7133126050419918</v>
+        <f>N25+O25</f>
+        <v>-2.4853363696356183</v>
       </c>
       <c r="Q25" s="12">
-        <f t="shared" si="9"/>
-        <v>40.051332212885072</v>
+        <f>MAX($P$2:$P$280)-P25</f>
+        <v>85.912457724533382</v>
       </c>
       <c r="R25" s="9">
-        <f t="shared" si="10"/>
-        <v>2.4967958485992287E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q25)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.1639755473023065E-2</v>
       </c>
       <c r="S25" s="9">
-        <f t="shared" si="8"/>
-        <v>0.91953225721273213</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+        <f>Q25/MAX($Q$2:$Q$28)</f>
+        <v>0.28370079189725922</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" t="s">
         <v>30</v>
-      </c>
-      <c r="C26" t="s">
-        <v>31</v>
       </c>
       <c r="D26" s="8">
         <v>45481</v>
@@ -2444,278 +2474,280 @@
         <v>1E-22</v>
       </c>
       <c r="F26" s="1">
-        <v>246</v>
+        <v>169.34</v>
       </c>
       <c r="G26" s="1">
-        <f t="shared" si="0"/>
-        <v>2.4600000000000001E-20</v>
+        <f>E26*F26</f>
+        <v>1.6934000000000002E-20</v>
       </c>
       <c r="H26" s="11">
-        <v>0.1</v>
+        <f>174.52/F26-1</f>
+        <v>3.0589346876107371E-2</v>
       </c>
       <c r="I26" s="11">
-        <v>0.42</v>
+        <v>0.4259</v>
       </c>
       <c r="J26" s="9">
-        <f t="shared" si="1"/>
-        <v>0.23809523809523811</v>
+        <f>IFERROR(H26/I26,"")</f>
+        <v>7.1822838403633182E-2</v>
       </c>
       <c r="K26" s="9">
-        <f t="shared" si="2"/>
-        <v>2.6044693221050026E-2</v>
+        <f>IFERROR(J26/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>1.447721779768244E-2</v>
       </c>
       <c r="L26" s="12">
-        <f t="shared" si="3"/>
-        <v>270.60000000000002</v>
+        <f>F26/(1-(F26*(1+H26)-F26)/(F26*(1+H26)))</f>
+        <v>174.52000000000004</v>
       </c>
       <c r="M26" s="12">
-        <f t="shared" si="4"/>
-        <v>186.36363636363637</v>
+        <f>F26/(1+I26-H26)</f>
+        <v>121.36365448143965</v>
       </c>
       <c r="N26" s="12">
-        <f t="shared" si="5"/>
-        <v>24.600000000000023</v>
+        <f>L26-F26</f>
+        <v>5.1800000000000352</v>
       </c>
       <c r="O26" s="12">
-        <f t="shared" si="6"/>
-        <v>-29.818181818181813</v>
+        <f>0.5*(M26-F26)</f>
+        <v>-23.988172759280175</v>
       </c>
       <c r="P26" s="15">
-        <f t="shared" si="7"/>
-        <v>-5.2181818181817903</v>
+        <f>N26+O26</f>
+        <v>-18.80817275928014</v>
       </c>
       <c r="Q26" s="12">
-        <f t="shared" si="9"/>
-        <v>43.55620142602487</v>
+        <f>MAX($P$2:$P$280)-P26</f>
+        <v>102.2352941141779</v>
       </c>
       <c r="R26" s="9">
-        <f t="shared" si="10"/>
-        <v>2.2958843224618275E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q26)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.7813578829556158E-3</v>
       </c>
       <c r="S26" s="9">
-        <f t="shared" si="8"/>
-        <v>1</v>
+        <f>Q26/MAX($Q$2:$Q$28)</f>
+        <v>0.33760219027884886</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>34</v>
+      <c r="B27" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D27" s="8">
-        <v>45562</v>
+        <v>45511</v>
       </c>
       <c r="E27" s="2">
-        <v>4.0300000000000002E-2</v>
+        <v>0.1933</v>
       </c>
       <c r="F27" s="1">
-        <v>668.82</v>
+        <v>77.53</v>
       </c>
       <c r="G27" s="1">
-        <f t="shared" si="0"/>
-        <v>26.953446000000003</v>
+        <f>E27*F27</f>
+        <v>14.986549</v>
       </c>
       <c r="H27" s="11">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="I27" s="11">
-        <v>0.28000000000000003</v>
+        <v>0.26</v>
       </c>
       <c r="J27" s="9">
-        <f t="shared" si="1"/>
-        <v>0.2857142857142857</v>
+        <f>IFERROR(H27/I27,"")</f>
+        <v>0.57692307692307687</v>
       </c>
       <c r="K27" s="9">
-        <f t="shared" si="2"/>
-        <v>3.1253631865260027E-2</v>
+        <f>IFERROR(J27/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>0.11628948705962007</v>
       </c>
       <c r="L27" s="12">
-        <f t="shared" si="3"/>
-        <v>722.32560000000012</v>
+        <f>F27/(1-(F27*(1+H27)-F27)/(F27*(1+H27)))</f>
+        <v>89.159499999999994</v>
       </c>
       <c r="M27" s="12">
-        <f t="shared" si="4"/>
-        <v>557.35</v>
+        <f>F27/(1+I27-H27)</f>
+        <v>69.846846846846844</v>
       </c>
       <c r="N27" s="12">
-        <f t="shared" si="5"/>
-        <v>53.505600000000072</v>
+        <f>L27-F27</f>
+        <v>11.629499999999993</v>
       </c>
       <c r="O27" s="12">
-        <f t="shared" si="6"/>
-        <v>-55.735000000000014</v>
+        <f>0.5*(M27-F27)</f>
+        <v>-3.8415765765765784</v>
       </c>
       <c r="P27" s="15">
-        <f t="shared" si="7"/>
-        <v>-2.2293999999999414</v>
+        <f>N27+O27</f>
+        <v>7.7879234234234147</v>
       </c>
       <c r="Q27" s="12">
-        <f t="shared" si="9"/>
-        <v>40.567419607843021</v>
+        <f>MAX($P$2:$P$280)-P27</f>
+        <v>75.639197931474342</v>
       </c>
       <c r="R27" s="9">
-        <f t="shared" si="10"/>
-        <v>2.4650323083567953E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q27)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.3220658433025086E-2</v>
       </c>
       <c r="S27" s="9">
-        <f t="shared" si="8"/>
-        <v>0.93138102680377333</v>
+        <f>Q27/MAX($Q$2:$Q$28)</f>
+        <v>0.24977635281297447</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>41</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>51</v>
+        <v>37</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" t="s">
+        <v>28</v>
       </c>
       <c r="D28" s="8">
         <v>45511</v>
       </c>
       <c r="E28" s="2">
-        <v>1</v>
+        <v>3.2899999999999999E-2</v>
       </c>
       <c r="F28" s="1">
-        <v>10.4</v>
+        <v>455.4</v>
       </c>
       <c r="G28" s="1">
-        <f t="shared" si="0"/>
-        <v>10.4</v>
+        <f>E28*F28</f>
+        <v>14.982659999999999</v>
       </c>
       <c r="H28" s="11">
-        <v>0.2</v>
-      </c>
-      <c r="I28" s="13">
-        <v>1.7672000000000001</v>
+        <v>0.17460000000000001</v>
+      </c>
+      <c r="I28" s="11">
+        <v>0.15770000000000001</v>
       </c>
       <c r="J28" s="9">
-        <f t="shared" si="1"/>
-        <v>0.11317338162064282</v>
+        <f>IFERROR(H28/I28,"")</f>
+        <v>1.1071655041217501</v>
       </c>
       <c r="K28" s="9">
-        <f t="shared" si="2"/>
-        <v>1.2379777221413547E-2</v>
+        <f>IFERROR(J28/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>0.22316962817833491</v>
       </c>
       <c r="L28" s="12">
-        <f t="shared" si="3"/>
-        <v>12.48</v>
+        <f>F28/(1-(F28*(1+H28)-F28)/(F28*(1+H28)))</f>
+        <v>534.91283999999996</v>
       </c>
       <c r="M28" s="12">
-        <f t="shared" si="4"/>
-        <v>4.0511062636335309</v>
+        <f>F28/(1+I28-H28)</f>
+        <v>463.22856270979554</v>
       </c>
       <c r="N28" s="12">
-        <f t="shared" si="5"/>
-        <v>2.08</v>
+        <f>L28-F28</f>
+        <v>79.512839999999983</v>
       </c>
       <c r="O28" s="12">
-        <f t="shared" si="6"/>
-        <v>-3.1744468681832347</v>
+        <f>0.5*(M28-F28)</f>
+        <v>3.9142813548977813</v>
       </c>
       <c r="P28" s="15">
-        <f t="shared" si="7"/>
-        <v>-1.0944468681832347</v>
+        <f>N28+O28</f>
+        <v>83.427121354897764</v>
       </c>
       <c r="Q28" s="12">
-        <f t="shared" si="9"/>
-        <v>39.432466476026313</v>
+        <f>MAX($P$2:$P$280)-P28</f>
+        <v>0</v>
       </c>
       <c r="R28" s="9">
-        <f t="shared" si="10"/>
-        <v>2.5359813609629724E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q28)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>0</v>
       </c>
       <c r="S28" s="9">
-        <f t="shared" si="8"/>
-        <v>0.90532381578310406</v>
+        <f>Q28/MAX($Q$2:$Q$28)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C29" t="s">
-        <v>63</v>
+        <v>40</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>50</v>
       </c>
       <c r="D29" s="8">
-        <v>45481</v>
+        <v>45511</v>
       </c>
       <c r="E29" s="2">
-        <v>2.8500000000000001E-2</v>
+        <v>1</v>
       </c>
       <c r="F29" s="1">
-        <v>700.32</v>
+        <v>10.4</v>
       </c>
       <c r="G29" s="1">
-        <f t="shared" si="0"/>
-        <v>19.959120000000002</v>
+        <f>E29*F29</f>
+        <v>10.4</v>
       </c>
       <c r="H29" s="11">
-        <v>0.127</v>
-      </c>
-      <c r="I29" s="11">
-        <v>0.44</v>
+        <f>8.33/G29-1</f>
+        <v>-0.19903846153846161</v>
+      </c>
+      <c r="I29" s="13">
+        <v>2</v>
       </c>
       <c r="J29" s="9">
-        <f t="shared" si="1"/>
-        <v>0.28863636363636364</v>
+        <f>IFERROR(H29/I29,"")</f>
+        <v>-9.9519230769230804E-2</v>
       </c>
       <c r="K29" s="9">
-        <f t="shared" si="2"/>
-        <v>3.1573271282063824E-2</v>
+        <f>IFERROR(J29/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>-2.0059936517784469E-2</v>
       </c>
       <c r="L29" s="12">
-        <f t="shared" si="3"/>
-        <v>789.26064000000008</v>
+        <f>F29/(1-(F29*(1+H29)-F29)/(F29*(1+H29)))</f>
+        <v>8.33</v>
       </c>
       <c r="M29" s="12">
-        <f t="shared" si="4"/>
-        <v>533.37395277989344</v>
+        <f>F29/(1+I29-H29)</f>
+        <v>3.2509768560264503</v>
       </c>
       <c r="N29" s="12">
-        <f t="shared" si="5"/>
-        <v>88.94064000000003</v>
+        <f>L29-F29</f>
+        <v>-2.0700000000000003</v>
       </c>
       <c r="O29" s="12">
-        <f t="shared" si="6"/>
-        <v>-83.473023610053303</v>
+        <f>0.5*(M29-F29)</f>
+        <v>-3.574511571986775</v>
       </c>
       <c r="P29" s="15">
-        <f t="shared" si="7"/>
-        <v>5.4676163899467269</v>
+        <f>N29+O29</f>
+        <v>-5.6445115719867758</v>
       </c>
       <c r="Q29" s="12">
-        <f t="shared" si="9"/>
-        <v>32.870403217896353</v>
+        <f>MAX($P$2:$P$280)-P29</f>
+        <v>89.071632926884547</v>
       </c>
       <c r="R29" s="9">
-        <f t="shared" si="10"/>
-        <v>3.0422504809905958E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q29)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.1226918909422725E-2</v>
       </c>
       <c r="S29" s="9">
-        <f t="shared" si="8"/>
-        <v>0.7546664342096705</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+        <f>Q29/MAX($Q$2:$Q$28)</f>
+        <v>0.29413304503478377</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D30" s="8">
         <v>45511</v>
@@ -2727,7 +2759,7 @@
         <v>29.94</v>
       </c>
       <c r="G30" s="1">
-        <f t="shared" si="0"/>
+        <f>E30*F30</f>
         <v>2.9940000000000003E-21</v>
       </c>
       <c r="H30" s="13">
@@ -2737,68 +2769,68 @@
         <v>0.72</v>
       </c>
       <c r="J30" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H30/I30,"")</f>
         <v>0.10416666666666667</v>
       </c>
       <c r="K30" s="9">
-        <f t="shared" si="2"/>
-        <v>1.1394553284209387E-2</v>
+        <f>IFERROR(J30/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>2.0996712941320293E-2</v>
       </c>
       <c r="L30" s="12">
-        <f t="shared" si="3"/>
+        <f>F30/(1-(F30*(1+H30)-F30)/(F30*(1+H30)))</f>
         <v>32.185499999999998</v>
       </c>
       <c r="M30" s="12">
-        <f t="shared" si="4"/>
+        <f>F30/(1+I30-H30)</f>
         <v>18.200607902735563</v>
       </c>
       <c r="N30" s="12">
-        <f t="shared" si="5"/>
+        <f>L30-F30</f>
         <v>2.2454999999999963</v>
       </c>
       <c r="O30" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(M30-F30)</f>
         <v>-5.8696960486322194</v>
       </c>
       <c r="P30" s="15">
-        <f t="shared" si="7"/>
+        <f>N30+O30</f>
         <v>-3.6241960486322231</v>
       </c>
       <c r="Q30" s="12">
-        <f t="shared" si="9"/>
-        <v>41.962215656475301</v>
+        <f>MAX($P$2:$P$280)-P30</f>
+        <v>87.051317403529993</v>
       </c>
       <c r="R30" s="9">
-        <f t="shared" si="10"/>
-        <v>2.3830962792492281E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q30)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.1487476925414677E-2</v>
       </c>
       <c r="S30" s="9">
-        <f t="shared" si="8"/>
-        <v>0.96340393061463891</v>
+        <f>Q30/MAX($Q$2:$Q$28)</f>
+        <v>0.28746154326380913</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B31" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C31" t="s">
         <v>81</v>
-      </c>
-      <c r="C31" t="s">
-        <v>82</v>
       </c>
       <c r="D31" s="8">
         <v>45574</v>
       </c>
       <c r="E31" s="2">
-        <v>0.13370000000000001</v>
+        <v>0</v>
       </c>
       <c r="F31" s="1">
         <v>153.7552</v>
       </c>
       <c r="G31" s="1">
-        <f t="shared" si="0"/>
-        <v>20.557070240000002</v>
+        <f>E31*F31</f>
+        <v>0</v>
       </c>
       <c r="H31" s="11">
         <v>7.0000000000000007E-2</v>
@@ -2807,59 +2839,59 @@
         <v>0.19</v>
       </c>
       <c r="J31" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H31/I31,"")</f>
         <v>0.36842105263157898</v>
       </c>
       <c r="K31" s="9">
-        <f t="shared" si="2"/>
-        <v>4.0300735826256359E-2</v>
+        <f>IFERROR(J31/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>7.4262058402985456E-2</v>
       </c>
       <c r="L31" s="12">
-        <f t="shared" si="3"/>
+        <f>F31/(1-(F31*(1+H31)-F31)/(F31*(1+H31)))</f>
         <v>164.51806400000001</v>
       </c>
       <c r="M31" s="12">
-        <f t="shared" si="4"/>
+        <f>F31/(1+I31-H31)</f>
         <v>137.28142857142859</v>
       </c>
       <c r="N31" s="12">
-        <f t="shared" si="5"/>
+        <f>L31-F31</f>
         <v>10.762864000000008</v>
       </c>
       <c r="O31" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(M31-F31)</f>
         <v>-8.2368857142857053</v>
       </c>
       <c r="P31" s="15">
-        <f t="shared" si="7"/>
+        <f>N31+O31</f>
         <v>2.5259782857143023</v>
       </c>
       <c r="Q31" s="12">
-        <f t="shared" si="9"/>
-        <v>35.812041322128778</v>
+        <f>MAX($P$2:$P$280)-P31</f>
+        <v>80.901143069183462</v>
       </c>
       <c r="R31" s="9">
-        <f t="shared" si="10"/>
-        <v>2.7923568807625761E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q31)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.2360764781096351E-2</v>
       </c>
       <c r="S31" s="9">
-        <f t="shared" si="8"/>
-        <v>0.82220304226830598</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+        <f>Q31/MAX($Q$2:$Q$28)</f>
+        <v>0.26715238932766161</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B32" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C32" s="14" t="s">
         <v>83</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>84</v>
       </c>
       <c r="D32" s="8">
         <f ca="1">TODAY()-20</f>
-        <v>45594</v>
+        <v>45599</v>
       </c>
       <c r="E32" s="2">
         <v>1E-35</v>
@@ -2883,7 +2915,7 @@
       </c>
       <c r="K32" s="9">
         <f t="shared" si="2"/>
-        <v>2.1877542305682025E-2</v>
+        <v>4.0313688847334959E-2</v>
       </c>
       <c r="L32" s="12">
         <f t="shared" ref="L32" si="13">F32/(1-(F32*(1+H32)-F32)/(F32*(1+H32)))</f>
@@ -2907,21 +2939,41 @@
       </c>
       <c r="Q32" s="12">
         <f t="shared" si="9"/>
-        <v>155.8908767506997</v>
+        <v>200.97997849775439</v>
       </c>
       <c r="R32" s="9">
         <f t="shared" si="10"/>
-        <v>6.4147435747583708E-3</v>
+        <v>4.9756199969499615E-3</v>
       </c>
       <c r="S32" s="9">
         <f t="shared" si="8"/>
-        <v>3.5790741994676045</v>
+        <v>0.66367766172081932</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:S32" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S30">
-      <sortCondition descending="1" ref="K1:K29"/>
+    <filterColumn colId="4">
+      <filters>
+        <filter val="0.0285"/>
+        <filter val="0.0329"/>
+        <filter val="0.0403"/>
+        <filter val="0.1337"/>
+        <filter val="0.1461"/>
+        <filter val="0.1521"/>
+        <filter val="0.1801"/>
+        <filter val="0.1807"/>
+        <filter val="0.1818"/>
+        <filter val="0.1882"/>
+        <filter val="0.1914"/>
+        <filter val="0.1928"/>
+        <filter val="0.1933"/>
+        <filter val="0.2439"/>
+        <filter val="1.0000"/>
+        <filter val="1.0752"/>
+      </filters>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:S31">
+      <sortCondition descending="1" ref="G1:G32"/>
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="R2:R32">

--- a/Open Positions.xlsx
+++ b/Open Positions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\StockSillines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{879A82F2-D606-405C-815B-A5C5FB79C475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADF54B0F-A9C0-42B8-B071-1D48FD713ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -706,7 +706,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:S32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -790,7 +789,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -810,7 +809,7 @@
         <v>41.8</v>
       </c>
       <c r="G2" s="1">
-        <f t="shared" ref="G2:G31" si="0">E2*F2</f>
+        <f t="shared" ref="G2:G8" si="0">E2*F2</f>
         <v>4.1799999999999994E-44</v>
       </c>
       <c r="H2" s="11">
@@ -820,7 +819,7 @@
         <v>0.4</v>
       </c>
       <c r="J2" s="9">
-        <f t="shared" ref="J2:J31" si="1">IFERROR(H2/I2,"")</f>
+        <f t="shared" ref="J2:J8" si="1">IFERROR(H2/I2,"")</f>
         <v>0</v>
       </c>
       <c r="K2" s="9">
@@ -828,23 +827,23 @@
         <v>0</v>
       </c>
       <c r="L2" s="12">
-        <f t="shared" ref="L2:L31" si="3">F2/(1-(F2*(1+H2)-F2)/(F2*(1+H2)))</f>
+        <f t="shared" ref="L2:L8" si="3">F2/(1-(F2*(1+H2)-F2)/(F2*(1+H2)))</f>
         <v>41.8</v>
       </c>
       <c r="M2" s="12">
-        <f t="shared" ref="M2:M31" si="4">F2/(1+I2-H2)</f>
+        <f t="shared" ref="M2:M8" si="4">F2/(1+I2-H2)</f>
         <v>29.857142857142858</v>
       </c>
       <c r="N2" s="12">
-        <f t="shared" ref="N2:N31" si="5">L2-F2</f>
+        <f t="shared" ref="N2:N8" si="5">L2-F2</f>
         <v>0</v>
       </c>
       <c r="O2" s="12">
-        <f t="shared" ref="O2:O31" si="6">0.5*(M2-F2)</f>
+        <f t="shared" ref="O2:O8" si="6">0.5*(M2-F2)</f>
         <v>-5.9714285714285698</v>
       </c>
       <c r="P2" s="15">
-        <f t="shared" ref="P2:P31" si="7">N2+O2</f>
+        <f t="shared" ref="P2:P8" si="7">N2+O2</f>
         <v>-5.9714285714285698</v>
       </c>
       <c r="Q2" s="12">
@@ -853,14 +852,14 @@
       </c>
       <c r="R2" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q2)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.1185863762042041E-2</v>
+        <v>1.118586376204204E-2</v>
       </c>
       <c r="S2" s="9">
         <f t="shared" ref="S2:S32" si="8">Q2/MAX($Q$2:$Q$28)</f>
         <v>0.29521259291506552</v>
       </c>
     </row>
-    <row r="3" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>39</v>
       </c>
@@ -896,7 +895,7 @@
       </c>
       <c r="K3" s="9">
         <f t="shared" si="2"/>
-        <v>1.0095425032941828E-2</v>
+        <v>8.6101675868140801E-3</v>
       </c>
       <c r="L3" s="12">
         <f t="shared" si="3"/>
@@ -924,14 +923,14 @@
       </c>
       <c r="R3" s="9">
         <f t="shared" ref="R3:R32" si="10">IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q3)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.1235255460236852E-2</v>
+        <v>1.123525546023685E-2</v>
       </c>
       <c r="S3" s="9">
         <f t="shared" si="8"/>
         <v>0.29391479854410774</v>
       </c>
     </row>
-    <row r="4" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>40</v>
       </c>
@@ -948,56 +947,61 @@
         <v>1E-22</v>
       </c>
       <c r="F4" s="1">
-        <v>113.48</v>
+        <v>113.58</v>
       </c>
       <c r="G4" s="1">
         <f t="shared" si="0"/>
-        <v>1.1348000000000001E-20</v>
-      </c>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="9" t="str">
+        <v>1.1358E-20</v>
+      </c>
+      <c r="H4" s="11">
+        <f>121.15/F4-1</f>
+        <v>6.664905793273479E-2</v>
+      </c>
+      <c r="I4" s="11">
+        <v>0.16439999999999999</v>
+      </c>
+      <c r="J4" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K4" s="9" t="str">
+        <v>0.40540789496797319</v>
+      </c>
+      <c r="K4" s="9">
         <f t="shared" si="2"/>
-        <v/>
+        <v>6.9695019220852264E-2</v>
       </c>
       <c r="L4" s="12">
         <f t="shared" si="3"/>
-        <v>113.48</v>
+        <v>121.15000000000002</v>
       </c>
       <c r="M4" s="12">
         <f t="shared" si="4"/>
-        <v>113.48</v>
+        <v>103.46609203186667</v>
       </c>
       <c r="N4" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7.5700000000000216</v>
       </c>
       <c r="O4" s="12">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-5.0569539840666664</v>
       </c>
       <c r="P4" s="15">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2.5130460159333552</v>
       </c>
       <c r="Q4" s="12">
         <f t="shared" si="9"/>
-        <v>83.427121354897764</v>
+        <v>80.914075338964409</v>
       </c>
       <c r="R4" s="9">
         <f t="shared" si="10"/>
-        <v>1.1986509707628705E-2</v>
+        <v>1.2358789194720577E-2</v>
       </c>
       <c r="S4" s="9">
         <f t="shared" si="8"/>
-        <v>0.27549369463951967</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.26719509437038835</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -1014,56 +1018,61 @@
         <v>1E-22</v>
       </c>
       <c r="F5" s="1">
-        <v>15.74</v>
+        <v>11.05</v>
       </c>
       <c r="G5" s="1">
         <f t="shared" si="0"/>
-        <v>1.5740000000000001E-21</v>
-      </c>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="9" t="str">
+        <v>1.1050000000000002E-21</v>
+      </c>
+      <c r="H5" s="11">
+        <f>9.52/F5-1</f>
+        <v>-0.13846153846153852</v>
+      </c>
+      <c r="I5" s="11">
+        <v>0.72170000000000001</v>
+      </c>
+      <c r="J5" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K5" s="9" t="str">
+        <v>-0.19185470203898922</v>
+      </c>
+      <c r="K5" s="9">
         <f t="shared" si="2"/>
-        <v/>
+        <v>-3.2982379751816525E-2</v>
       </c>
       <c r="L5" s="12">
         <f t="shared" si="3"/>
-        <v>15.74</v>
+        <v>9.52</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="4"/>
-        <v>15.74</v>
+        <v>5.9403443042581081</v>
       </c>
       <c r="N5" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-1.5300000000000011</v>
       </c>
       <c r="O5" s="12">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-2.5548278478709463</v>
       </c>
       <c r="P5" s="15">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-4.0848278478709474</v>
       </c>
       <c r="Q5" s="12">
         <f t="shared" si="9"/>
-        <v>83.427121354897764</v>
+        <v>87.511949202768704</v>
       </c>
       <c r="R5" s="9">
         <f t="shared" si="10"/>
-        <v>1.1986509707628705E-2</v>
+        <v>1.142701092947844E-2</v>
       </c>
       <c r="S5" s="9">
         <f t="shared" si="8"/>
-        <v>0.27549369463951967</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.28898264520499783</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>40</v>
       </c>
@@ -1080,56 +1089,61 @@
         <v>1E-22</v>
       </c>
       <c r="F6" s="1">
-        <v>230.91</v>
+        <v>187.36</v>
       </c>
       <c r="G6" s="1">
         <f t="shared" si="0"/>
-        <v>2.3091E-20</v>
-      </c>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="9" t="str">
+        <v>1.8736000000000003E-20</v>
+      </c>
+      <c r="H6" s="11">
+        <f>196.02/F6-1</f>
+        <v>4.6221178479931568E-2</v>
+      </c>
+      <c r="I6" s="11">
+        <v>0.52980000000000005</v>
+      </c>
+      <c r="J6" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K6" s="9" t="str">
+        <v>8.7242692487602053E-2</v>
+      </c>
+      <c r="K6" s="9">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1.4998181350865584E-2</v>
       </c>
       <c r="L6" s="12">
         <f t="shared" si="3"/>
-        <v>230.91</v>
+        <v>196.01999999999998</v>
       </c>
       <c r="M6" s="12">
         <f t="shared" si="4"/>
-        <v>230.91</v>
+        <v>126.28921179127629</v>
       </c>
       <c r="N6" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>8.6599999999999682</v>
       </c>
       <c r="O6" s="12">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-30.535394104361863</v>
       </c>
       <c r="P6" s="15">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-21.875394104361895</v>
       </c>
       <c r="Q6" s="12">
         <f t="shared" si="9"/>
-        <v>83.427121354897764</v>
+        <v>105.30251545925967</v>
       </c>
       <c r="R6" s="9">
         <f t="shared" si="10"/>
-        <v>1.1986509707628705E-2</v>
+        <v>9.4964493073946415E-3</v>
       </c>
       <c r="S6" s="9">
         <f t="shared" si="8"/>
-        <v>0.27549369463951967</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.34773079266750317</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -1146,56 +1160,61 @@
         <v>1E-22</v>
       </c>
       <c r="F7" s="1">
-        <v>20.11</v>
+        <v>10.47</v>
       </c>
       <c r="G7" s="1">
         <f t="shared" si="0"/>
-        <v>2.0110000000000001E-21</v>
-      </c>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="9" t="str">
+        <v>1.0470000000000001E-21</v>
+      </c>
+      <c r="H7" s="11">
+        <f>6.42/F7-1</f>
+        <v>-0.38681948424068768</v>
+      </c>
+      <c r="I7" s="11">
+        <v>0.85599999999999998</v>
+      </c>
+      <c r="J7" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="9" t="str">
+        <v>-0.45189192084192487</v>
+      </c>
+      <c r="K7" s="9">
         <f t="shared" si="2"/>
-        <v/>
+        <v>-7.768624267002458E-2</v>
       </c>
       <c r="L7" s="12">
         <f t="shared" si="3"/>
-        <v>20.11</v>
+        <v>6.419999999999999</v>
       </c>
       <c r="M7" s="12">
         <f t="shared" si="4"/>
-        <v>20.11</v>
+        <v>4.6682312480197874</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-4.0500000000000016</v>
       </c>
       <c r="O7" s="12">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-2.9008843759901066</v>
       </c>
       <c r="P7" s="15">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-6.9508843759901087</v>
       </c>
       <c r="Q7" s="12">
         <f t="shared" si="9"/>
-        <v>83.427121354897764</v>
+        <v>90.378005730887878</v>
       </c>
       <c r="R7" s="9">
         <f t="shared" si="10"/>
-        <v>1.1986509707628705E-2</v>
+        <v>1.1064638923076355E-2</v>
       </c>
       <c r="S7" s="9">
         <f t="shared" si="8"/>
-        <v>0.27549369463951967</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.29844695955690265</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -1212,53 +1231,58 @@
         <v>1E-22</v>
       </c>
       <c r="F8" s="1">
-        <v>12.8</v>
+        <v>13.04</v>
       </c>
       <c r="G8" s="1">
         <f t="shared" si="0"/>
-        <v>1.2800000000000001E-21</v>
-      </c>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="9" t="str">
+        <v>1.304E-21</v>
+      </c>
+      <c r="H8" s="11">
+        <f>13.72/F8-1</f>
+        <v>5.2147239263803824E-2</v>
+      </c>
+      <c r="I8" s="11">
+        <v>0.30159999999999998</v>
+      </c>
+      <c r="J8" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="9" t="str">
+        <v>0.17290198694895167</v>
+      </c>
+      <c r="K8" s="9">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2.9724155482178521E-2</v>
       </c>
       <c r="L8" s="12">
         <f t="shared" si="3"/>
-        <v>12.8</v>
+        <v>13.72</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" si="4"/>
-        <v>12.8</v>
+        <v>10.436569040286594</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.68000000000000149</v>
       </c>
       <c r="O8" s="12">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-1.3017154798567026</v>
       </c>
       <c r="P8" s="15">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-0.62171547985670106</v>
       </c>
       <c r="Q8" s="12">
         <f t="shared" si="9"/>
-        <v>83.427121354897764</v>
+        <v>84.048836834754468</v>
       </c>
       <c r="R8" s="9">
         <f t="shared" si="10"/>
-        <v>1.1986509707628705E-2</v>
+        <v>1.1897844606297951E-2</v>
       </c>
       <c r="S8" s="9">
         <f t="shared" si="8"/>
-        <v>0.27549369463951967</v>
+        <v>0.27754672837457672</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
@@ -1281,7 +1305,7 @@
         <v>423.77</v>
       </c>
       <c r="G9" s="1">
-        <f>E9*F9</f>
+        <f t="shared" ref="G9:G31" si="11">E9*F9</f>
         <v>56.658049000000005</v>
       </c>
       <c r="H9" s="11">
@@ -1291,43 +1315,43 @@
         <v>0.1963</v>
       </c>
       <c r="J9" s="9">
-        <f>IFERROR(H9/I9,"")</f>
+        <f t="shared" ref="J9:J31" si="12">IFERROR(H9/I9,"")</f>
         <v>5.8074375955170655E-2</v>
       </c>
       <c r="K9" s="9">
-        <f>IFERROR(J9/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.1705961611299503E-2</v>
+        <f t="shared" ref="K9:K31" si="13">IFERROR(J9/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>9.9837590699963247E-3</v>
       </c>
       <c r="L9" s="12">
-        <f>F9/(1-(F9*(1+H9)-F9)/(F9*(1+H9)))</f>
+        <f t="shared" ref="L9:L31" si="14">F9/(1-(F9*(1+H9)-F9)/(F9*(1+H9)))</f>
         <v>428.600978</v>
       </c>
       <c r="M9" s="12">
-        <f>F9/(1+I9-H9)</f>
+        <f t="shared" ref="M9:M31" si="15">F9/(1+I9-H9)</f>
         <v>357.64199510507217</v>
       </c>
       <c r="N9" s="12">
-        <f>L9-F9</f>
+        <f t="shared" ref="N9:N31" si="16">L9-F9</f>
         <v>4.830978000000016</v>
       </c>
       <c r="O9" s="12">
-        <f>0.5*(M9-F9)</f>
+        <f t="shared" ref="O9:O31" si="17">0.5*(M9-F9)</f>
         <v>-33.064002447463906</v>
       </c>
       <c r="P9" s="15">
-        <f>N9+O9</f>
+        <f t="shared" ref="P9:P31" si="18">N9+O9</f>
         <v>-28.23302444746389</v>
       </c>
       <c r="Q9" s="12">
-        <f>MAX($P$2:$P$280)-P9</f>
+        <f t="shared" ref="Q9:Q31" si="19">MAX($P$2:$P$280)-P9</f>
         <v>111.66014580236165</v>
       </c>
       <c r="R9" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q9)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" ref="R9:R31" si="20">IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q9)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
         <v>8.9557468585971488E-3</v>
       </c>
       <c r="S9" s="9">
-        <f>Q9/MAX($Q$2:$Q$28)</f>
+        <f t="shared" ref="S9:S31" si="21">Q9/MAX($Q$2:$Q$28)</f>
         <v>0.36872500946329412</v>
       </c>
     </row>
@@ -1351,7 +1375,7 @@
         <v>51.15</v>
       </c>
       <c r="G10" s="1">
-        <f>E10*F10</f>
+        <f t="shared" si="11"/>
         <v>54.996479999999998</v>
       </c>
       <c r="H10" s="11">
@@ -1362,43 +1386,43 @@
         <v>0.19980000000000001</v>
       </c>
       <c r="J10" s="9">
-        <f>IFERROR(H10/I10,"")</f>
+        <f t="shared" si="12"/>
         <v>0.92242242242242245</v>
       </c>
       <c r="K10" s="9">
-        <f>IFERROR(J10/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.18593125261671253</v>
+        <f t="shared" si="13"/>
+        <v>0.15857670572881799</v>
       </c>
       <c r="L10" s="12">
-        <f>F10/(1-(F10*(1+H10)-F10)/(F10*(1+H10)))</f>
+        <f t="shared" si="14"/>
         <v>60.576944999999995</v>
       </c>
       <c r="M10" s="12">
-        <f>F10/(1+I10-H10)</f>
+        <f t="shared" si="15"/>
         <v>50.369276218611525</v>
       </c>
       <c r="N10" s="12">
-        <f>L10-F10</f>
+        <f t="shared" si="16"/>
         <v>9.4269449999999964</v>
       </c>
       <c r="O10" s="12">
-        <f>0.5*(M10-F10)</f>
+        <f t="shared" si="17"/>
         <v>-0.39036189069423699</v>
       </c>
       <c r="P10" s="15">
-        <f>N10+O10</f>
+        <f t="shared" si="18"/>
         <v>9.0365831093057594</v>
       </c>
       <c r="Q10" s="12">
-        <f>MAX($P$2:$P$280)-P10</f>
+        <f t="shared" si="19"/>
         <v>74.390538245592012</v>
       </c>
       <c r="R10" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q10)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.3442569762012102E-2</v>
+        <f t="shared" si="20"/>
+        <v>1.3442569762012101E-2</v>
       </c>
       <c r="S10" s="9">
-        <f>Q10/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="21"/>
         <v>0.24565301900228498</v>
       </c>
     </row>
@@ -1422,7 +1446,7 @@
         <v>227.38</v>
       </c>
       <c r="G11" s="1">
-        <f>E11*F11</f>
+        <f t="shared" si="11"/>
         <v>42.792915999999998</v>
       </c>
       <c r="H11" s="11">
@@ -1432,43 +1456,43 @@
         <v>0.2271</v>
       </c>
       <c r="J11" s="9">
-        <f>IFERROR(H11/I11,"")</f>
+        <f t="shared" si="12"/>
         <v>0.21708498458828709</v>
       </c>
       <c r="K11" s="9">
-        <f>IFERROR(J11/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.3757482610603554E-2</v>
+        <f t="shared" si="13"/>
+        <v>3.7319801516530214E-2</v>
       </c>
       <c r="L11" s="12">
-        <f>F11/(1-(F11*(1+H11)-F11)/(F11*(1+H11)))</f>
+        <f t="shared" si="14"/>
         <v>238.58983399999997</v>
       </c>
       <c r="M11" s="12">
-        <f>F11/(1+I11-H11)</f>
+        <f t="shared" si="15"/>
         <v>193.05484802173541</v>
       </c>
       <c r="N11" s="12">
-        <f>L11-F11</f>
+        <f t="shared" si="16"/>
         <v>11.209833999999972</v>
       </c>
       <c r="O11" s="12">
-        <f>0.5*(M11-F11)</f>
+        <f t="shared" si="17"/>
         <v>-17.162575989132293</v>
       </c>
       <c r="P11" s="15">
-        <f>N11+O11</f>
+        <f t="shared" si="18"/>
         <v>-5.9527419891323206</v>
       </c>
       <c r="Q11" s="12">
-        <f>MAX($P$2:$P$280)-P11</f>
+        <f t="shared" si="19"/>
         <v>89.379863344030085</v>
       </c>
       <c r="R11" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q11)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.1188202382352297E-2</v>
+        <f t="shared" si="20"/>
+        <v>1.1188202382352295E-2</v>
       </c>
       <c r="S11" s="9">
-        <f>Q11/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="21"/>
         <v>0.29515088593640709</v>
       </c>
     </row>
@@ -1492,7 +1516,7 @@
         <v>273.45999999999998</v>
       </c>
       <c r="G12" s="1">
-        <f>E12*F12</f>
+        <f t="shared" si="11"/>
         <v>39.952506</v>
       </c>
       <c r="H12" s="11">
@@ -1502,43 +1526,43 @@
         <v>0.16700000000000001</v>
       </c>
       <c r="J12" s="9">
-        <f>IFERROR(H12/I12,"")</f>
+        <f t="shared" si="12"/>
         <v>1.0041916167664668</v>
       </c>
       <c r="K12" s="9">
-        <f>IFERROR(J12/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.20241334190712787</v>
+        <f t="shared" si="13"/>
+        <v>0.17263391981423187</v>
       </c>
       <c r="L12" s="12">
-        <f>F12/(1-(F12*(1+H12)-F12)/(F12*(1+H12)))</f>
+        <f t="shared" si="14"/>
         <v>319.31924199999997</v>
       </c>
       <c r="M12" s="12">
-        <f>F12/(1+I12-H12)</f>
+        <f t="shared" si="15"/>
         <v>273.65155608926244</v>
       </c>
       <c r="N12" s="12">
-        <f>L12-F12</f>
+        <f t="shared" si="16"/>
         <v>45.859241999999995</v>
       </c>
       <c r="O12" s="12">
-        <f>0.5*(M12-F12)</f>
+        <f t="shared" si="17"/>
         <v>9.5778044631231296E-2</v>
       </c>
       <c r="P12" s="15">
-        <f>N12+O12</f>
+        <f t="shared" si="18"/>
         <v>45.955020044631226</v>
       </c>
       <c r="Q12" s="12">
-        <f>MAX($P$2:$P$280)-P12</f>
+        <f t="shared" si="19"/>
         <v>37.472101310266538</v>
       </c>
       <c r="R12" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q12)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>2.6686520505483952E-2</v>
+        <f t="shared" si="20"/>
+        <v>2.6686520505483948E-2</v>
       </c>
       <c r="S12" s="9">
-        <f>Q12/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="21"/>
         <v>0.12374066692240798</v>
       </c>
     </row>
@@ -1562,7 +1586,7 @@
         <v>188.12</v>
       </c>
       <c r="G13" s="1">
-        <f>E13*F13</f>
+        <f t="shared" si="11"/>
         <v>36.269536000000002</v>
       </c>
       <c r="H13" s="11">
@@ -1572,43 +1596,43 @@
         <v>0.37780000000000002</v>
       </c>
       <c r="J13" s="9">
-        <f>IFERROR(H13/I13,"")</f>
+        <f t="shared" si="12"/>
         <v>-0.18157755426151401</v>
       </c>
       <c r="K13" s="9">
-        <f>IFERROR(J13/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-3.6600305120793777E-2</v>
+        <f t="shared" si="13"/>
+        <v>-3.1215601105477483E-2</v>
       </c>
       <c r="L13" s="12">
-        <f>F13/(1-(F13*(1+H13)-F13)/(F13*(1+H13)))</f>
+        <f t="shared" si="14"/>
         <v>175.214968</v>
       </c>
       <c r="M13" s="12">
-        <f>F13/(1+I13-H13)</f>
+        <f t="shared" si="15"/>
         <v>130.06084070796459</v>
       </c>
       <c r="N13" s="12">
-        <f>L13-F13</f>
+        <f t="shared" si="16"/>
         <v>-12.905032000000006</v>
       </c>
       <c r="O13" s="12">
-        <f>0.5*(M13-F13)</f>
+        <f t="shared" si="17"/>
         <v>-29.029579646017709</v>
       </c>
       <c r="P13" s="15">
-        <f>N13+O13</f>
+        <f t="shared" si="18"/>
         <v>-41.934611646017714</v>
       </c>
       <c r="Q13" s="12">
-        <f>MAX($P$2:$P$280)-P13</f>
+        <f t="shared" si="19"/>
         <v>125.36173300091548</v>
       </c>
       <c r="R13" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q13)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="20"/>
         <v>7.9769158902158552E-3</v>
       </c>
       <c r="S13" s="9">
-        <f>Q13/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="21"/>
         <v>0.4139704982018737</v>
       </c>
     </row>
@@ -1632,7 +1656,7 @@
         <v>144.28</v>
       </c>
       <c r="G14" s="1">
-        <f>E14*F14</f>
+        <f t="shared" si="11"/>
         <v>35.189892</v>
       </c>
       <c r="H14" s="11">
@@ -1642,43 +1666,43 @@
         <v>0.18340000000000001</v>
       </c>
       <c r="J14" s="9">
-        <f>IFERROR(H14/I14,"")</f>
+        <f t="shared" si="12"/>
         <v>-0.15267175572519084</v>
       </c>
       <c r="K14" s="9">
-        <f>IFERROR(J14/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-3.0773808280408366E-2</v>
+        <f t="shared" si="13"/>
+        <v>-2.6246309166201669E-2</v>
       </c>
       <c r="L14" s="12">
-        <f>F14/(1-(F14*(1+H14)-F14)/(F14*(1+H14)))</f>
+        <f t="shared" si="14"/>
         <v>140.24016</v>
       </c>
       <c r="M14" s="12">
-        <f>F14/(1+I14-H14)</f>
+        <f t="shared" si="15"/>
         <v>119.10186561003798</v>
       </c>
       <c r="N14" s="12">
-        <f>L14-F14</f>
+        <f t="shared" si="16"/>
         <v>-4.0398399999999981</v>
       </c>
       <c r="O14" s="12">
-        <f>0.5*(M14-F14)</f>
+        <f t="shared" si="17"/>
         <v>-12.589067194981013</v>
       </c>
       <c r="P14" s="15">
-        <f>N14+O14</f>
+        <f t="shared" si="18"/>
         <v>-16.628907194981011</v>
       </c>
       <c r="Q14" s="12">
-        <f>MAX($P$2:$P$280)-P14</f>
+        <f t="shared" si="19"/>
         <v>100.05602854987877</v>
       </c>
       <c r="R14" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q14)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.9944002824526607E-3</v>
+        <f t="shared" si="20"/>
+        <v>9.9944002824526625E-3</v>
       </c>
       <c r="S14" s="9">
-        <f>Q14/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="21"/>
         <v>0.33040580243567419</v>
       </c>
     </row>
@@ -1702,7 +1726,7 @@
         <v>191.91</v>
       </c>
       <c r="G15" s="1">
-        <f>E15*F15</f>
+        <f t="shared" si="11"/>
         <v>47.958309</v>
       </c>
       <c r="H15" s="11">
@@ -1713,47 +1737,47 @@
         <v>0.37</v>
       </c>
       <c r="J15" s="9">
-        <f>IFERROR(H15/I15,"")</f>
+        <f t="shared" si="12"/>
         <v>0.49981198957281486</v>
       </c>
       <c r="K15" s="9">
-        <f>IFERROR(J15/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.10074632514902941</v>
+        <f t="shared" si="13"/>
+        <v>8.5924341021631129E-2</v>
       </c>
       <c r="L15" s="12">
-        <f>F15/(1-(F15*(1+H15)-F15)/(F15*(1+H15)))</f>
+        <f t="shared" si="14"/>
         <v>227.39999999999998</v>
       </c>
       <c r="M15" s="12">
-        <f>F15/(1+I15-H15)</f>
+        <f t="shared" si="15"/>
         <v>161.93986062322494</v>
       </c>
       <c r="N15" s="12">
-        <f>L15-F15</f>
+        <f t="shared" si="16"/>
         <v>35.489999999999981</v>
       </c>
       <c r="O15" s="12">
-        <f>0.5*(M15-F15)</f>
+        <f t="shared" si="17"/>
         <v>-14.985069688387526</v>
       </c>
       <c r="P15" s="15">
-        <f>N15+O15</f>
+        <f t="shared" si="18"/>
         <v>20.504930311612455</v>
       </c>
       <c r="Q15" s="12">
-        <f>MAX($P$2:$P$280)-P15</f>
+        <f t="shared" si="19"/>
         <v>62.922191043285309</v>
       </c>
       <c r="R15" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q15)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="20"/>
         <v>1.5892644286847574E-2</v>
       </c>
       <c r="S15" s="9">
-        <f>Q15/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="21"/>
         <v>0.20778215289949825</v>
       </c>
     </row>
-    <row r="16" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>74</v>
       </c>
@@ -1773,7 +1797,7 @@
         <v>56</v>
       </c>
       <c r="G16" s="1">
-        <f>E16*F16</f>
+        <f t="shared" si="11"/>
         <v>5.5999999999999999E-34</v>
       </c>
       <c r="H16" s="11">
@@ -1783,47 +1807,47 @@
         <v>0.19</v>
       </c>
       <c r="J16" s="9">
-        <f>IFERROR(H16/I16,"")</f>
+        <f t="shared" si="12"/>
         <v>0.42105263157894735</v>
       </c>
       <c r="K16" s="9">
-        <f>IFERROR(J16/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>8.4870923889126232E-2</v>
+        <f t="shared" si="13"/>
+        <v>7.2384557910998279E-2</v>
       </c>
       <c r="L16" s="12">
-        <f>F16/(1-(F16*(1+H16)-F16)/(F16*(1+H16)))</f>
+        <f t="shared" si="14"/>
         <v>60.480000000000004</v>
       </c>
       <c r="M16" s="12">
-        <f>F16/(1+I16-H16)</f>
+        <f t="shared" si="15"/>
         <v>50.450450450450454</v>
       </c>
       <c r="N16" s="12">
-        <f>L16-F16</f>
+        <f t="shared" si="16"/>
         <v>4.480000000000004</v>
       </c>
       <c r="O16" s="12">
-        <f>0.5*(M16-F16)</f>
+        <f t="shared" si="17"/>
         <v>-2.7747747747747731</v>
       </c>
       <c r="P16" s="15">
-        <f>N16+O16</f>
+        <f t="shared" si="18"/>
         <v>1.7052252252252309</v>
       </c>
       <c r="Q16" s="12">
-        <f>MAX($P$2:$P$280)-P16</f>
+        <f t="shared" si="19"/>
         <v>81.72189612967253</v>
       </c>
       <c r="R16" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q16)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="20"/>
         <v>1.223662258659841E-2</v>
       </c>
       <c r="S16" s="9">
-        <f>Q16/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="21"/>
         <v>0.26986268652296996</v>
       </c>
     </row>
-    <row r="17" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -1843,7 +1867,7 @@
         <v>86.6</v>
       </c>
       <c r="G17" s="1">
-        <f>E17*F17</f>
+        <f t="shared" si="11"/>
         <v>8.6599999999999988E-34</v>
       </c>
       <c r="H17" s="11">
@@ -1854,43 +1878,43 @@
         <v>0.17249999999999999</v>
       </c>
       <c r="J17" s="9">
-        <f>IFERROR(H17/I17,"")</f>
+        <f t="shared" si="12"/>
         <v>0.19011279579609788</v>
       </c>
       <c r="K17" s="9">
-        <f>IFERROR(J17/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.8320740478104097E-2</v>
+        <f t="shared" si="13"/>
+        <v>3.2682922857695543E-2</v>
       </c>
       <c r="L17" s="12">
-        <f>F17/(1-(F17*(1+H17)-F17)/(F17*(1+H17)))</f>
+        <f t="shared" si="14"/>
         <v>89.44</v>
       </c>
       <c r="M17" s="12">
-        <f>F17/(1+I17-H17)</f>
+        <f t="shared" si="15"/>
         <v>75.984538772119137</v>
       </c>
       <c r="N17" s="12">
-        <f>L17-F17</f>
+        <f t="shared" si="16"/>
         <v>2.8400000000000034</v>
       </c>
       <c r="O17" s="12">
-        <f>0.5*(M17-F17)</f>
+        <f t="shared" si="17"/>
         <v>-5.3077306139404286</v>
       </c>
       <c r="P17" s="15">
-        <f>N17+O17</f>
+        <f t="shared" si="18"/>
         <v>-2.4677306139404251</v>
       </c>
       <c r="Q17" s="12">
-        <f>MAX($P$2:$P$280)-P17</f>
+        <f t="shared" si="19"/>
         <v>85.894851968838196</v>
       </c>
       <c r="R17" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q17)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="20"/>
         <v>1.1642141258509767E-2</v>
       </c>
       <c r="S17" s="9">
-        <f>Q17/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="21"/>
         <v>0.28364265403268213</v>
       </c>
     </row>
@@ -1914,7 +1938,7 @@
         <v>165.59</v>
       </c>
       <c r="G18" s="1">
-        <f>E18*F18</f>
+        <f t="shared" si="11"/>
         <v>29.922113</v>
       </c>
       <c r="H18" s="11">
@@ -1924,47 +1948,47 @@
         <v>0.16439999999999999</v>
       </c>
       <c r="J18" s="9">
-        <f>IFERROR(H18/I18,"")</f>
+        <f t="shared" si="12"/>
         <v>0.40875912408759124</v>
       </c>
       <c r="K18" s="9">
-        <f>IFERROR(J18/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>8.2392940709881665E-2</v>
+        <f t="shared" si="13"/>
+        <v>7.027114016177205E-2</v>
       </c>
       <c r="L18" s="12">
-        <f>F18/(1-(F18*(1+H18)-F18)/(F18*(1+H18)))</f>
+        <f t="shared" si="14"/>
         <v>176.717648</v>
       </c>
       <c r="M18" s="12">
-        <f>F18/(1+I18-H18)</f>
+        <f t="shared" si="15"/>
         <v>150.92052497265766</v>
       </c>
       <c r="N18" s="12">
-        <f>L18-F18</f>
+        <f t="shared" si="16"/>
         <v>11.127647999999994</v>
       </c>
       <c r="O18" s="12">
-        <f>0.5*(M18-F18)</f>
+        <f t="shared" si="17"/>
         <v>-7.3347375136711719</v>
       </c>
       <c r="P18" s="15">
-        <f>N18+O18</f>
+        <f t="shared" si="18"/>
         <v>3.7929104863288217</v>
       </c>
       <c r="Q18" s="12">
-        <f>MAX($P$2:$P$280)-P18</f>
+        <f t="shared" si="19"/>
         <v>79.634210868568942</v>
       </c>
       <c r="R18" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q18)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="20"/>
         <v>1.2557417083600347E-2</v>
       </c>
       <c r="S18" s="9">
-        <f>Q18/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="21"/>
         <v>0.26296871587547221</v>
       </c>
     </row>
-    <row r="19" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>77</v>
       </c>
@@ -1984,7 +2008,7 @@
         <v>20.399999999999999</v>
       </c>
       <c r="G19" s="1">
-        <f>E19*F19</f>
+        <f t="shared" si="11"/>
         <v>2.0399999999999999E-34</v>
       </c>
       <c r="H19" s="11">
@@ -1994,43 +2018,43 @@
         <v>0.15</v>
       </c>
       <c r="J19" s="9">
-        <f>IFERROR(H19/I19,"")</f>
+        <f t="shared" si="12"/>
         <v>0.33333333333333337</v>
       </c>
       <c r="K19" s="9">
-        <f>IFERROR(J19/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>6.7189481412224944E-2</v>
+        <f t="shared" si="13"/>
+        <v>5.7304441679540311E-2</v>
       </c>
       <c r="L19" s="12">
-        <f>F19/(1-(F19*(1+H19)-F19)/(F19*(1+H19)))</f>
+        <f t="shared" si="14"/>
         <v>21.419999999999998</v>
       </c>
       <c r="M19" s="12">
-        <f>F19/(1+I19-H19)</f>
+        <f t="shared" si="15"/>
         <v>18.545454545454547</v>
       </c>
       <c r="N19" s="12">
-        <f>L19-F19</f>
+        <f t="shared" si="16"/>
         <v>1.0199999999999996</v>
       </c>
       <c r="O19" s="12">
-        <f>0.5*(M19-F19)</f>
+        <f t="shared" si="17"/>
         <v>-0.92727272727272592</v>
       </c>
       <c r="P19" s="15">
-        <f>N19+O19</f>
+        <f t="shared" si="18"/>
         <v>9.2727272727273657E-2</v>
       </c>
       <c r="Q19" s="12">
-        <f>MAX($P$2:$P$280)-P19</f>
+        <f t="shared" si="19"/>
         <v>83.33439408217049</v>
       </c>
       <c r="R19" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q19)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.199984725411175E-2</v>
+        <f t="shared" si="20"/>
+        <v>1.1999847254111748E-2</v>
       </c>
       <c r="S19" s="9">
-        <f>Q19/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="21"/>
         <v>0.27518748991205688</v>
       </c>
     </row>
@@ -2054,7 +2078,7 @@
         <v>668.82</v>
       </c>
       <c r="G20" s="1">
-        <f>E20*F20</f>
+        <f t="shared" si="11"/>
         <v>26.953446000000003</v>
       </c>
       <c r="H20" s="11">
@@ -2065,43 +2089,43 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="J20" s="9">
-        <f>IFERROR(H20/I20,"")</f>
+        <f t="shared" si="12"/>
         <v>-0.61542289832412733</v>
       </c>
       <c r="K20" s="9">
-        <f>IFERROR(J20/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-0.12404983616281964</v>
+        <f t="shared" si="13"/>
+        <v>-0.10579939675580585</v>
       </c>
       <c r="L20" s="12">
-        <f>F20/(1-(F20*(1+H20)-F20)/(F20*(1+H20)))</f>
+        <f t="shared" si="14"/>
         <v>553.57000000000005</v>
       </c>
       <c r="M20" s="12">
-        <f>F20/(1+I20-H20)</f>
+        <f t="shared" si="15"/>
         <v>460.51884675555289</v>
       </c>
       <c r="N20" s="12">
-        <f>L20-F20</f>
+        <f t="shared" si="16"/>
         <v>-115.25</v>
       </c>
       <c r="O20" s="12">
-        <f>0.5*(M20-F20)</f>
+        <f t="shared" si="17"/>
         <v>-104.15057662222358</v>
       </c>
       <c r="P20" s="15">
-        <f>N20+O20</f>
+        <f t="shared" si="18"/>
         <v>-219.40057662222358</v>
       </c>
       <c r="Q20" s="12">
-        <f>MAX($P$2:$P$280)-P20</f>
+        <f t="shared" si="19"/>
         <v>302.82769797712137</v>
       </c>
       <c r="R20" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q20)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="20"/>
         <v>3.3022078451871001E-3</v>
       </c>
       <c r="S20" s="9">
-        <f>Q20/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
     </row>
@@ -2125,7 +2149,7 @@
         <v>135.82</v>
       </c>
       <c r="G21" s="1">
-        <f>E21*F21</f>
+        <f t="shared" si="11"/>
         <v>25.995947999999999</v>
       </c>
       <c r="H21" s="11">
@@ -2135,43 +2159,43 @@
         <v>0.33710000000000001</v>
       </c>
       <c r="J21" s="9">
-        <f>IFERROR(H21/I21,"")</f>
+        <f t="shared" si="12"/>
         <v>0.35657075051913378</v>
       </c>
       <c r="K21" s="9">
-        <f>IFERROR(J21/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>7.1873411442445301E-2</v>
+        <f t="shared" si="13"/>
+        <v>6.1299263333260856E-2</v>
       </c>
       <c r="L21" s="12">
-        <f>F21/(1-(F21*(1+H21)-F21)/(F21*(1+H21)))</f>
+        <f t="shared" si="14"/>
         <v>152.14556400000001</v>
       </c>
       <c r="M21" s="12">
-        <f>F21/(1+I21-H21)</f>
+        <f t="shared" si="15"/>
         <v>111.61147177253677</v>
       </c>
       <c r="N21" s="12">
-        <f>L21-F21</f>
+        <f t="shared" si="16"/>
         <v>16.325564000000014</v>
       </c>
       <c r="O21" s="12">
-        <f>0.5*(M21-F21)</f>
+        <f t="shared" si="17"/>
         <v>-12.10426411373161</v>
       </c>
       <c r="P21" s="15">
-        <f>N21+O21</f>
+        <f t="shared" si="18"/>
         <v>4.2212998862684046</v>
       </c>
       <c r="Q21" s="12">
-        <f>MAX($P$2:$P$280)-P21</f>
+        <f t="shared" si="19"/>
         <v>79.205821468629352</v>
       </c>
       <c r="R21" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q21)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.2625334621345541E-2</v>
+        <f t="shared" si="20"/>
+        <v>1.2625334621345539E-2</v>
       </c>
       <c r="S21" s="9">
-        <f>Q21/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="21"/>
         <v>0.26155408503819672</v>
       </c>
     </row>
@@ -2195,7 +2219,7 @@
         <v>133.19999999999999</v>
       </c>
       <c r="G22" s="1">
-        <f>E22*F22</f>
+        <f t="shared" si="11"/>
         <v>23.989319999999999</v>
       </c>
       <c r="H22" s="11">
@@ -2205,43 +2229,43 @@
         <v>0.1623</v>
       </c>
       <c r="J22" s="9">
-        <f>IFERROR(H22/I22,"")</f>
+        <f t="shared" si="12"/>
         <v>3.0807147258163893E-2</v>
       </c>
       <c r="K22" s="9">
-        <f>IFERROR(J22/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>6.2097487441982379E-3</v>
+        <f t="shared" si="13"/>
+        <v>5.2961591201053891E-3</v>
       </c>
       <c r="L22" s="12">
-        <f>F22/(1-(F22*(1+H22)-F22)/(F22*(1+H22)))</f>
+        <f t="shared" si="14"/>
         <v>133.86599999999999</v>
       </c>
       <c r="M22" s="12">
-        <f>F22/(1+I22-H22)</f>
+        <f t="shared" si="15"/>
         <v>115.09548086062384</v>
       </c>
       <c r="N22" s="12">
-        <f>L22-F22</f>
+        <f t="shared" si="16"/>
         <v>0.66599999999999682</v>
       </c>
       <c r="O22" s="12">
-        <f>0.5*(M22-F22)</f>
+        <f t="shared" si="17"/>
         <v>-9.0522595696880757</v>
       </c>
       <c r="P22" s="15">
-        <f>N22+O22</f>
+        <f t="shared" si="18"/>
         <v>-8.3862595696880788</v>
       </c>
       <c r="Q22" s="12">
-        <f>MAX($P$2:$P$280)-P22</f>
+        <f t="shared" si="19"/>
         <v>91.813380924585843</v>
       </c>
       <c r="R22" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q22)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="20"/>
         <v>1.0891658600627999E-2</v>
       </c>
       <c r="S22" s="9">
-        <f>Q22/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="21"/>
         <v>0.30318686678231904</v>
       </c>
     </row>
@@ -2265,7 +2289,7 @@
         <v>147.01</v>
       </c>
       <c r="G23" s="1">
-        <f>E23*F23</f>
+        <f t="shared" si="11"/>
         <v>22.360220999999999</v>
       </c>
       <c r="H23" s="11">
@@ -2276,43 +2300,43 @@
         <v>0.52380000000000004</v>
       </c>
       <c r="J23" s="9">
-        <f>IFERROR(H23/I23,"")</f>
+        <f t="shared" si="12"/>
         <v>0.60672300515722333</v>
       </c>
       <c r="K23" s="9">
-        <f>IFERROR(J23/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.12229621223214153</v>
+        <f t="shared" si="13"/>
+        <v>0.10430376919400261</v>
       </c>
       <c r="L23" s="12">
-        <f>F23/(1-(F23*(1+H23)-F23)/(F23*(1+H23)))</f>
+        <f t="shared" si="14"/>
         <v>193.72999999999996</v>
       </c>
       <c r="M23" s="12">
-        <f>F23/(1+I23-H23)</f>
+        <f t="shared" si="15"/>
         <v>121.89899177432211</v>
       </c>
       <c r="N23" s="12">
-        <f>L23-F23</f>
+        <f t="shared" si="16"/>
         <v>46.71999999999997</v>
       </c>
       <c r="O23" s="12">
-        <f>0.5*(M23-F23)</f>
+        <f t="shared" si="17"/>
         <v>-12.555504112838939</v>
       </c>
       <c r="P23" s="15">
-        <f>N23+O23</f>
+        <f t="shared" si="18"/>
         <v>34.164495887161031</v>
       </c>
       <c r="Q23" s="12">
-        <f>MAX($P$2:$P$280)-P23</f>
+        <f t="shared" si="19"/>
         <v>49.262625467736733</v>
       </c>
       <c r="R23" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q23)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="20"/>
         <v>2.0299364690883635E-2</v>
       </c>
       <c r="S23" s="9">
-        <f>Q23/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="21"/>
         <v>0.16267542829407408</v>
       </c>
     </row>
@@ -2336,7 +2360,7 @@
         <v>700.32</v>
       </c>
       <c r="G24" s="1">
-        <f>E24*F24</f>
+        <f t="shared" si="11"/>
         <v>19.959120000000002</v>
       </c>
       <c r="H24" s="11">
@@ -2346,47 +2370,47 @@
         <v>0.45340000000000003</v>
       </c>
       <c r="J24" s="9">
-        <f>IFERROR(H24/I24,"")</f>
+        <f t="shared" si="12"/>
         <v>-0.14666960741067489</v>
       </c>
       <c r="K24" s="9">
-        <f>IFERROR(J24/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-2.9563964582573606E-2</v>
+        <f t="shared" si="13"/>
+        <v>-2.5214459892078277E-2</v>
       </c>
       <c r="L24" s="12">
-        <f>F24/(1-(F24*(1+H24)-F24)/(F24*(1+H24)))</f>
+        <f t="shared" si="14"/>
         <v>653.74872000000005</v>
       </c>
       <c r="M24" s="12">
-        <f>F24/(1+I24-H24)</f>
+        <f t="shared" si="15"/>
         <v>460.76715573392988</v>
       </c>
       <c r="N24" s="12">
-        <f>L24-F24</f>
+        <f t="shared" si="16"/>
         <v>-46.571280000000002</v>
       </c>
       <c r="O24" s="12">
-        <f>0.5*(M24-F24)</f>
+        <f t="shared" si="17"/>
         <v>-119.77642213303508</v>
       </c>
       <c r="P24" s="15">
-        <f>N24+O24</f>
+        <f t="shared" si="18"/>
         <v>-166.34770213303509</v>
       </c>
       <c r="Q24" s="12">
-        <f>MAX($P$2:$P$280)-P24</f>
+        <f t="shared" si="19"/>
         <v>249.77482348793285</v>
       </c>
       <c r="R24" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q24)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="20"/>
         <v>4.0036060722041193E-3</v>
       </c>
       <c r="S24" s="9">
-        <f>Q24/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="21"/>
         <v>0.82480838165207504</v>
       </c>
     </row>
-    <row r="25" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>36</v>
       </c>
@@ -2406,7 +2430,7 @@
         <v>178.12</v>
       </c>
       <c r="G25" s="1">
-        <f>E25*F25</f>
+        <f t="shared" si="11"/>
         <v>1.7812E-26</v>
       </c>
       <c r="H25" s="11">
@@ -2417,47 +2441,47 @@
         <v>0.26790000000000003</v>
       </c>
       <c r="J25" s="9">
-        <f>IFERROR(H25/I25,"")</f>
+        <f t="shared" si="12"/>
         <v>0.25755292282959996</v>
       </c>
       <c r="K25" s="9">
-        <f>IFERROR(J25/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>5.1914541963370829E-2</v>
+        <f t="shared" si="13"/>
+        <v>4.4276779337051868E-2</v>
       </c>
       <c r="L25" s="12">
-        <f>F25/(1-(F25*(1+H25)-F25)/(F25*(1+H25)))</f>
+        <f t="shared" si="14"/>
         <v>190.41</v>
       </c>
       <c r="M25" s="12">
-        <f>F25/(1+I25-H25)</f>
+        <f t="shared" si="15"/>
         <v>148.56932726072878</v>
       </c>
       <c r="N25" s="12">
-        <f>L25-F25</f>
+        <f t="shared" si="16"/>
         <v>12.289999999999992</v>
       </c>
       <c r="O25" s="12">
-        <f>0.5*(M25-F25)</f>
+        <f t="shared" si="17"/>
         <v>-14.77533636963561</v>
       </c>
       <c r="P25" s="15">
-        <f>N25+O25</f>
+        <f t="shared" si="18"/>
         <v>-2.4853363696356183</v>
       </c>
       <c r="Q25" s="12">
-        <f>MAX($P$2:$P$280)-P25</f>
+        <f t="shared" si="19"/>
         <v>85.912457724533382</v>
       </c>
       <c r="R25" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q25)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.1639755473023065E-2</v>
+        <f t="shared" si="20"/>
+        <v>1.1639755473023062E-2</v>
       </c>
       <c r="S25" s="9">
-        <f>Q25/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="21"/>
         <v>0.28370079189725922</v>
       </c>
     </row>
-    <row r="26" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>36</v>
       </c>
@@ -2477,7 +2501,7 @@
         <v>169.34</v>
       </c>
       <c r="G26" s="1">
-        <f>E26*F26</f>
+        <f t="shared" si="11"/>
         <v>1.6934000000000002E-20</v>
       </c>
       <c r="H26" s="11">
@@ -2488,43 +2512,43 @@
         <v>0.4259</v>
       </c>
       <c r="J26" s="9">
-        <f>IFERROR(H26/I26,"")</f>
+        <f t="shared" si="12"/>
         <v>7.1822838403633182E-2</v>
       </c>
       <c r="K26" s="9">
-        <f>IFERROR(J26/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.447721779768244E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.2347302963680137E-2</v>
       </c>
       <c r="L26" s="12">
-        <f>F26/(1-(F26*(1+H26)-F26)/(F26*(1+H26)))</f>
+        <f t="shared" si="14"/>
         <v>174.52000000000004</v>
       </c>
       <c r="M26" s="12">
-        <f>F26/(1+I26-H26)</f>
+        <f t="shared" si="15"/>
         <v>121.36365448143965</v>
       </c>
       <c r="N26" s="12">
-        <f>L26-F26</f>
+        <f t="shared" si="16"/>
         <v>5.1800000000000352</v>
       </c>
       <c r="O26" s="12">
-        <f>0.5*(M26-F26)</f>
+        <f t="shared" si="17"/>
         <v>-23.988172759280175</v>
       </c>
       <c r="P26" s="15">
-        <f>N26+O26</f>
+        <f t="shared" si="18"/>
         <v>-18.80817275928014</v>
       </c>
       <c r="Q26" s="12">
-        <f>MAX($P$2:$P$280)-P26</f>
+        <f t="shared" si="19"/>
         <v>102.2352941141779</v>
       </c>
       <c r="R26" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q26)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="20"/>
         <v>9.7813578829556158E-3</v>
       </c>
       <c r="S26" s="9">
-        <f>Q26/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="21"/>
         <v>0.33760219027884886</v>
       </c>
     </row>
@@ -2548,54 +2572,55 @@
         <v>77.53</v>
       </c>
       <c r="G27" s="1">
-        <f>E27*F27</f>
+        <f t="shared" si="11"/>
         <v>14.986549</v>
       </c>
       <c r="H27" s="11">
-        <v>0.15</v>
+        <f>83.34/F27-1</f>
+        <v>7.4938733393525192E-2</v>
       </c>
       <c r="I27" s="11">
-        <v>0.26</v>
+        <v>0.25990000000000002</v>
       </c>
       <c r="J27" s="9">
-        <f>IFERROR(H27/I27,"")</f>
-        <v>0.57692307692307687</v>
+        <f t="shared" si="12"/>
+        <v>0.28833679643526428</v>
       </c>
       <c r="K27" s="9">
-        <f>IFERROR(J27/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.11628948705962007</v>
+        <f t="shared" si="13"/>
+        <v>4.9568937406170265E-2</v>
       </c>
       <c r="L27" s="12">
-        <f>F27/(1-(F27*(1+H27)-F27)/(F27*(1+H27)))</f>
-        <v>89.159499999999994</v>
+        <f t="shared" si="14"/>
+        <v>83.34</v>
       </c>
       <c r="M27" s="12">
-        <f>F27/(1+I27-H27)</f>
-        <v>69.846846846846844</v>
+        <f t="shared" si="15"/>
+        <v>65.428298953629579</v>
       </c>
       <c r="N27" s="12">
-        <f>L27-F27</f>
-        <v>11.629499999999993</v>
+        <f t="shared" si="16"/>
+        <v>5.8100000000000023</v>
       </c>
       <c r="O27" s="12">
-        <f>0.5*(M27-F27)</f>
-        <v>-3.8415765765765784</v>
+        <f t="shared" si="17"/>
+        <v>-6.0508505231852112</v>
       </c>
       <c r="P27" s="15">
-        <f>N27+O27</f>
-        <v>7.7879234234234147</v>
+        <f t="shared" si="18"/>
+        <v>-0.24085052318520894</v>
       </c>
       <c r="Q27" s="12">
-        <f>MAX($P$2:$P$280)-P27</f>
-        <v>75.639197931474342</v>
+        <f t="shared" si="19"/>
+        <v>83.667971878082966</v>
       </c>
       <c r="R27" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q27)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.3220658433025086E-2</v>
+        <f t="shared" si="20"/>
+        <v>1.1952004782154312E-2</v>
       </c>
       <c r="S27" s="9">
-        <f>Q27/MAX($Q$2:$Q$28)</f>
-        <v>0.24977635281297447</v>
+        <f t="shared" si="21"/>
+        <v>0.27628903312669928</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
@@ -2618,7 +2643,7 @@
         <v>455.4</v>
       </c>
       <c r="G28" s="1">
-        <f>E28*F28</f>
+        <f t="shared" si="11"/>
         <v>14.982659999999999</v>
       </c>
       <c r="H28" s="11">
@@ -2628,43 +2653,43 @@
         <v>0.15770000000000001</v>
       </c>
       <c r="J28" s="9">
-        <f>IFERROR(H28/I28,"")</f>
+        <f t="shared" si="12"/>
         <v>1.1071655041217501</v>
       </c>
       <c r="K28" s="9">
-        <f>IFERROR(J28/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.22316962817833491</v>
+        <f t="shared" si="13"/>
+        <v>0.19033650318163101</v>
       </c>
       <c r="L28" s="12">
-        <f>F28/(1-(F28*(1+H28)-F28)/(F28*(1+H28)))</f>
+        <f t="shared" si="14"/>
         <v>534.91283999999996</v>
       </c>
       <c r="M28" s="12">
-        <f>F28/(1+I28-H28)</f>
+        <f t="shared" si="15"/>
         <v>463.22856270979554</v>
       </c>
       <c r="N28" s="12">
-        <f>L28-F28</f>
+        <f t="shared" si="16"/>
         <v>79.512839999999983</v>
       </c>
       <c r="O28" s="12">
-        <f>0.5*(M28-F28)</f>
+        <f t="shared" si="17"/>
         <v>3.9142813548977813</v>
       </c>
       <c r="P28" s="15">
-        <f>N28+O28</f>
+        <f t="shared" si="18"/>
         <v>83.427121354897764</v>
       </c>
       <c r="Q28" s="12">
-        <f>MAX($P$2:$P$280)-P28</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R28" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q28)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S28" s="9">
-        <f>Q28/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -2688,58 +2713,58 @@
         <v>10.4</v>
       </c>
       <c r="G29" s="1">
-        <f>E29*F29</f>
+        <f t="shared" si="11"/>
         <v>10.4</v>
       </c>
       <c r="H29" s="11">
-        <f>8.33/G29-1</f>
-        <v>-0.19903846153846161</v>
+        <f>2.89/F29-1</f>
+        <v>-0.7221153846153846</v>
       </c>
       <c r="I29" s="13">
-        <v>2</v>
+        <v>1.8652</v>
       </c>
       <c r="J29" s="9">
-        <f>IFERROR(H29/I29,"")</f>
-        <v>-9.9519230769230804E-2</v>
+        <f t="shared" si="12"/>
+        <v>-0.38715171810818388</v>
       </c>
       <c r="K29" s="9">
-        <f>IFERROR(J29/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-2.0059936517784469E-2</v>
+        <f t="shared" si="13"/>
+        <v>-6.655653915439276E-2</v>
       </c>
       <c r="L29" s="12">
-        <f>F29/(1-(F29*(1+H29)-F29)/(F29*(1+H29)))</f>
-        <v>8.33</v>
+        <f t="shared" si="14"/>
+        <v>2.8900000000000006</v>
       </c>
       <c r="M29" s="12">
-        <f>F29/(1+I29-H29)</f>
-        <v>3.2509768560264503</v>
+        <f t="shared" si="15"/>
+        <v>2.8991038938481961</v>
       </c>
       <c r="N29" s="12">
-        <f>L29-F29</f>
-        <v>-2.0700000000000003</v>
+        <f t="shared" si="16"/>
+        <v>-7.51</v>
       </c>
       <c r="O29" s="12">
-        <f>0.5*(M29-F29)</f>
-        <v>-3.574511571986775</v>
+        <f t="shared" si="17"/>
+        <v>-3.7504480530759023</v>
       </c>
       <c r="P29" s="15">
-        <f>N29+O29</f>
-        <v>-5.6445115719867758</v>
+        <f t="shared" si="18"/>
+        <v>-11.260448053075901</v>
       </c>
       <c r="Q29" s="12">
-        <f>MAX($P$2:$P$280)-P29</f>
-        <v>89.071632926884547</v>
+        <f t="shared" si="19"/>
+        <v>94.687569407973669</v>
       </c>
       <c r="R29" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q29)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.1226918909422725E-2</v>
+        <f t="shared" si="20"/>
+        <v>1.0561048364135005E-2</v>
       </c>
       <c r="S29" s="9">
-        <f>Q29/MAX($Q$2:$Q$28)</f>
-        <v>0.29413304503478377</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="21"/>
+        <v>0.31267803454070875</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>40</v>
       </c>
@@ -2756,57 +2781,58 @@
         <v>1E-22</v>
       </c>
       <c r="F30" s="1">
-        <v>29.94</v>
+        <v>20.82</v>
       </c>
       <c r="G30" s="1">
-        <f>E30*F30</f>
-        <v>2.9940000000000003E-21</v>
+        <f t="shared" si="11"/>
+        <v>2.0820000000000001E-21</v>
       </c>
       <c r="H30" s="13">
-        <v>7.4999999999999997E-2</v>
+        <f>19.07/F30-1</f>
+        <v>-8.4053794428434192E-2</v>
       </c>
       <c r="I30" s="11">
-        <v>0.72</v>
+        <v>0.7389</v>
       </c>
       <c r="J30" s="9">
-        <f>IFERROR(H30/I30,"")</f>
-        <v>0.10416666666666667</v>
+        <f t="shared" si="12"/>
+        <v>-0.11375530440984462</v>
       </c>
       <c r="K30" s="9">
-        <f>IFERROR(J30/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.0996712941320293E-2</v>
+        <f t="shared" si="13"/>
+        <v>-1.9556052621876884E-2</v>
       </c>
       <c r="L30" s="12">
-        <f>F30/(1-(F30*(1+H30)-F30)/(F30*(1+H30)))</f>
-        <v>32.185499999999998</v>
+        <f t="shared" si="14"/>
+        <v>19.070000000000004</v>
       </c>
       <c r="M30" s="12">
-        <f>F30/(1+I30-H30)</f>
-        <v>18.200607902735563</v>
+        <f t="shared" si="15"/>
+        <v>11.421024528231593</v>
       </c>
       <c r="N30" s="12">
-        <f>L30-F30</f>
-        <v>2.2454999999999963</v>
+        <f t="shared" si="16"/>
+        <v>-1.7499999999999964</v>
       </c>
       <c r="O30" s="12">
-        <f>0.5*(M30-F30)</f>
-        <v>-5.8696960486322194</v>
+        <f t="shared" si="17"/>
+        <v>-4.6994877358842038</v>
       </c>
       <c r="P30" s="15">
-        <f>N30+O30</f>
-        <v>-3.6241960486322231</v>
+        <f t="shared" si="18"/>
+        <v>-6.4494877358842002</v>
       </c>
       <c r="Q30" s="12">
-        <f>MAX($P$2:$P$280)-P30</f>
-        <v>87.051317403529993</v>
+        <f t="shared" si="19"/>
+        <v>89.876609090781969</v>
       </c>
       <c r="R30" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q30)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.1487476925414677E-2</v>
+        <f t="shared" si="20"/>
+        <v>1.1126365470574516E-2</v>
       </c>
       <c r="S30" s="9">
-        <f>Q30/MAX($Q$2:$Q$28)</f>
-        <v>0.28746154326380913</v>
+        <f t="shared" si="21"/>
+        <v>0.29679124363839449</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
@@ -2829,7 +2855,7 @@
         <v>153.7552</v>
       </c>
       <c r="G31" s="1">
-        <f>E31*F31</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="H31" s="11">
@@ -2839,47 +2865,47 @@
         <v>0.19</v>
       </c>
       <c r="J31" s="9">
-        <f>IFERROR(H31/I31,"")</f>
+        <f t="shared" si="12"/>
         <v>0.36842105263157898</v>
       </c>
       <c r="K31" s="9">
-        <f>IFERROR(J31/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>7.4262058402985456E-2</v>
+        <f t="shared" si="13"/>
+        <v>6.3336488172123506E-2</v>
       </c>
       <c r="L31" s="12">
-        <f>F31/(1-(F31*(1+H31)-F31)/(F31*(1+H31)))</f>
+        <f t="shared" si="14"/>
         <v>164.51806400000001</v>
       </c>
       <c r="M31" s="12">
-        <f>F31/(1+I31-H31)</f>
+        <f t="shared" si="15"/>
         <v>137.28142857142859</v>
       </c>
       <c r="N31" s="12">
-        <f>L31-F31</f>
+        <f t="shared" si="16"/>
         <v>10.762864000000008</v>
       </c>
       <c r="O31" s="12">
-        <f>0.5*(M31-F31)</f>
+        <f t="shared" si="17"/>
         <v>-8.2368857142857053</v>
       </c>
       <c r="P31" s="15">
-        <f>N31+O31</f>
+        <f t="shared" si="18"/>
         <v>2.5259782857143023</v>
       </c>
       <c r="Q31" s="12">
-        <f>MAX($P$2:$P$280)-P31</f>
+        <f t="shared" si="19"/>
         <v>80.901143069183462</v>
       </c>
       <c r="R31" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q31)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.2360764781096351E-2</v>
+        <f t="shared" si="20"/>
+        <v>1.2360764781096349E-2</v>
       </c>
       <c r="S31" s="9">
-        <f>Q31/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="21"/>
         <v>0.26715238932766161</v>
       </c>
     </row>
-    <row r="32" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>77</v>
       </c>
@@ -2900,7 +2926,7 @@
         <v>2742.9</v>
       </c>
       <c r="G32" s="1">
-        <f t="shared" ref="G32" si="11">E32*F32</f>
+        <f t="shared" ref="G32" si="22">E32*F32</f>
         <v>2.7429E-32</v>
       </c>
       <c r="H32" s="11">
@@ -2910,31 +2936,31 @@
         <v>0.5</v>
       </c>
       <c r="J32" s="9">
-        <f t="shared" ref="J32" si="12">IFERROR(H32/I32,"")</f>
+        <f t="shared" ref="J32" si="23">IFERROR(H32/I32,"")</f>
         <v>0.2</v>
       </c>
       <c r="K32" s="9">
         <f t="shared" si="2"/>
-        <v>4.0313688847334959E-2</v>
+        <v>3.4382665007724189E-2</v>
       </c>
       <c r="L32" s="12">
-        <f t="shared" ref="L32" si="13">F32/(1-(F32*(1+H32)-F32)/(F32*(1+H32)))</f>
+        <f t="shared" ref="L32" si="24">F32/(1-(F32*(1+H32)-F32)/(F32*(1+H32)))</f>
         <v>3017.1900000000005</v>
       </c>
       <c r="M32" s="12">
-        <f t="shared" ref="M32" si="14">F32/(1+I32-H32)</f>
+        <f t="shared" ref="M32" si="25">F32/(1+I32-H32)</f>
         <v>1959.214285714286</v>
       </c>
       <c r="N32" s="12">
-        <f t="shared" ref="N32" si="15">L32-F32</f>
+        <f t="shared" ref="N32" si="26">L32-F32</f>
         <v>274.29000000000042</v>
       </c>
       <c r="O32" s="12">
-        <f t="shared" ref="O32" si="16">0.5*(M32-F32)</f>
+        <f t="shared" ref="O32" si="27">0.5*(M32-F32)</f>
         <v>-391.84285714285704</v>
       </c>
       <c r="P32" s="15">
-        <f t="shared" ref="P32" si="17">N32+O32</f>
+        <f t="shared" ref="P32" si="28">N32+O32</f>
         <v>-117.55285714285662</v>
       </c>
       <c r="Q32" s="12">
@@ -2951,31 +2977,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S32" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="0.0285"/>
-        <filter val="0.0329"/>
-        <filter val="0.0403"/>
-        <filter val="0.1337"/>
-        <filter val="0.1461"/>
-        <filter val="0.1521"/>
-        <filter val="0.1801"/>
-        <filter val="0.1807"/>
-        <filter val="0.1818"/>
-        <filter val="0.1882"/>
-        <filter val="0.1914"/>
-        <filter val="0.1928"/>
-        <filter val="0.1933"/>
-        <filter val="0.2439"/>
-        <filter val="1.0000"/>
-        <filter val="1.0752"/>
-      </filters>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:S31">
-      <sortCondition descending="1" ref="G1:G32"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:S32" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="R2:R32">
     <cfRule type="iconSet" priority="1">
       <iconSet iconSet="3Symbols">

--- a/Open Positions.xlsx
+++ b/Open Positions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\StockSillines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADF54B0F-A9C0-42B8-B071-1D48FD713ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{134FF921-831A-4707-B79E-C591403248A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="88">
   <si>
     <t>Name</t>
   </si>
@@ -298,6 +298,12 @@
   </si>
   <si>
     <t>Ticker</t>
+  </si>
+  <si>
+    <t>Palantir</t>
+  </si>
+  <si>
+    <t>PLTR</t>
   </si>
 </sst>
 </file>
@@ -706,13 +712,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S32"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:S33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.42578125" style="8" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="30.42578125" style="8" customWidth="1"/>
     <col min="5" max="5" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="1" customWidth="1"/>
@@ -789,7 +796,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -823,7 +830,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="9">
-        <f t="shared" ref="K2:K32" si="2">IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" ref="K2:K33" si="2">IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>0</v>
       </c>
       <c r="L2" s="12">
@@ -852,14 +859,14 @@
       </c>
       <c r="R2" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q2)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.118586376204204E-2</v>
+        <v>1.1185863762042041E-2</v>
       </c>
       <c r="S2" s="9">
-        <f t="shared" ref="S2:S32" si="8">Q2/MAX($Q$2:$Q$28)</f>
+        <f t="shared" ref="S2:S33" si="8">Q2/MAX($Q$2:$Q$28)</f>
         <v>0.29521259291506552</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>39</v>
       </c>
@@ -895,7 +902,7 @@
       </c>
       <c r="K3" s="9">
         <f t="shared" si="2"/>
-        <v>8.6101675868140801E-3</v>
+        <v>3.0521065278950023E-2</v>
       </c>
       <c r="L3" s="12">
         <f t="shared" si="3"/>
@@ -918,11 +925,11 @@
         <v>-5.5784204896237704</v>
       </c>
       <c r="Q3" s="12">
-        <f t="shared" ref="Q3:Q32" si="9">MAX($P$2:$P$280)-P3</f>
+        <f t="shared" ref="Q3:Q33" si="9">MAX($P$2:$P$280)-P3</f>
         <v>89.005541844521531</v>
       </c>
       <c r="R3" s="9">
-        <f t="shared" ref="R3:R32" si="10">IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q3)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" ref="R3:R33" si="10">IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q3)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
         <v>1.123525546023685E-2</v>
       </c>
       <c r="S3" s="9">
@@ -930,7 +937,7 @@
         <v>0.29391479854410774</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>40</v>
       </c>
@@ -966,7 +973,7 @@
       </c>
       <c r="K4" s="9">
         <f t="shared" si="2"/>
-        <v>6.9695019220852264E-2</v>
+        <v>0.24705282560526781</v>
       </c>
       <c r="L4" s="12">
         <f t="shared" si="3"/>
@@ -994,14 +1001,14 @@
       </c>
       <c r="R4" s="9">
         <f t="shared" si="10"/>
-        <v>1.2358789194720577E-2</v>
+        <v>1.2358789194720575E-2</v>
       </c>
       <c r="S4" s="9">
         <f t="shared" si="8"/>
         <v>0.26719509437038835</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -1037,7 +1044,7 @@
       </c>
       <c r="K5" s="9">
         <f t="shared" si="2"/>
-        <v>-3.2982379751816525E-2</v>
+        <v>-0.1169149561039837</v>
       </c>
       <c r="L5" s="12">
         <f t="shared" si="3"/>
@@ -1072,7 +1079,7 @@
         <v>0.28898264520499783</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>40</v>
       </c>
@@ -1108,7 +1115,7 @@
       </c>
       <c r="K6" s="9">
         <f t="shared" si="2"/>
-        <v>1.4998181350865584E-2</v>
+        <v>5.3165105958719094E-2</v>
       </c>
       <c r="L6" s="12">
         <f t="shared" si="3"/>
@@ -1143,7 +1150,7 @@
         <v>0.34773079266750317</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -1179,7 +1186,7 @@
       </c>
       <c r="K7" s="9">
         <f t="shared" si="2"/>
-        <v>-7.768624267002458E-2</v>
+        <v>-0.27537987616400289</v>
       </c>
       <c r="L7" s="12">
         <f t="shared" si="3"/>
@@ -1207,14 +1214,14 @@
       </c>
       <c r="R7" s="9">
         <f t="shared" si="10"/>
-        <v>1.1064638923076355E-2</v>
+        <v>1.1064638923076357E-2</v>
       </c>
       <c r="S7" s="9">
         <f t="shared" si="8"/>
         <v>0.29844695955690265</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -1250,7 +1257,7 @@
       </c>
       <c r="K8" s="9">
         <f t="shared" si="2"/>
-        <v>2.9724155482178521E-2</v>
+        <v>0.10536529988365954</v>
       </c>
       <c r="L8" s="12">
         <f t="shared" si="3"/>
@@ -1278,7 +1285,7 @@
       </c>
       <c r="R8" s="9">
         <f t="shared" si="10"/>
-        <v>1.1897844606297951E-2</v>
+        <v>1.1897844606297952E-2</v>
       </c>
       <c r="S8" s="9">
         <f t="shared" si="8"/>
@@ -1320,7 +1327,7 @@
       </c>
       <c r="K9" s="9">
         <f t="shared" ref="K9:K31" si="13">IFERROR(J9/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>9.9837590699963247E-3</v>
+        <v>3.539013140363477E-2</v>
       </c>
       <c r="L9" s="12">
         <f t="shared" ref="L9:L31" si="14">F9/(1-(F9*(1+H9)-F9)/(F9*(1+H9)))</f>
@@ -1355,7 +1362,7 @@
         <v>0.36872500946329412</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -1391,7 +1398,7 @@
       </c>
       <c r="K10" s="9">
         <f t="shared" si="13"/>
-        <v>0.15857670572881799</v>
+        <v>0.56211797720199363</v>
       </c>
       <c r="L10" s="12">
         <f t="shared" si="14"/>
@@ -1419,7 +1426,7 @@
       </c>
       <c r="R10" s="9">
         <f t="shared" si="20"/>
-        <v>1.3442569762012101E-2</v>
+        <v>1.3442569762012102E-2</v>
       </c>
       <c r="S10" s="9">
         <f t="shared" si="21"/>
@@ -1461,7 +1468,7 @@
       </c>
       <c r="K11" s="9">
         <f t="shared" si="13"/>
-        <v>3.7319801516530214E-2</v>
+        <v>0.1322901194197246</v>
       </c>
       <c r="L11" s="12">
         <f t="shared" si="14"/>
@@ -1496,7 +1503,7 @@
         <v>0.29515088593640709</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -1531,7 +1538,7 @@
       </c>
       <c r="K12" s="9">
         <f t="shared" si="13"/>
-        <v>0.17263391981423187</v>
+        <v>0.61194757046079873</v>
       </c>
       <c r="L12" s="12">
         <f t="shared" si="14"/>
@@ -1601,7 +1608,7 @@
       </c>
       <c r="K13" s="9">
         <f t="shared" si="13"/>
-        <v>-3.1215601105477483E-2</v>
+        <v>-0.11065213184944192</v>
       </c>
       <c r="L13" s="12">
         <f t="shared" si="14"/>
@@ -1636,7 +1643,7 @@
         <v>0.4139704982018737</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -1671,7 +1678,7 @@
       </c>
       <c r="K14" s="9">
         <f t="shared" si="13"/>
-        <v>-2.6246309166201669E-2</v>
+        <v>-9.3037133983306625E-2</v>
       </c>
       <c r="L14" s="12">
         <f t="shared" si="14"/>
@@ -1742,7 +1749,7 @@
       </c>
       <c r="K15" s="9">
         <f t="shared" si="13"/>
-        <v>8.5924341021631129E-2</v>
+        <v>0.30458204151428614</v>
       </c>
       <c r="L15" s="12">
         <f t="shared" si="14"/>
@@ -1777,7 +1784,7 @@
         <v>0.20778215289949825</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>74</v>
       </c>
@@ -1812,7 +1819,7 @@
       </c>
       <c r="K16" s="9">
         <f t="shared" si="13"/>
-        <v>7.2384557910998279E-2</v>
+        <v>0.25658662214343508</v>
       </c>
       <c r="L16" s="12">
         <f t="shared" si="14"/>
@@ -1847,7 +1854,7 @@
         <v>0.26986268652296996</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -1883,7 +1890,7 @@
       </c>
       <c r="K17" s="9">
         <f t="shared" si="13"/>
-        <v>3.2682922857695543E-2</v>
+        <v>0.11585345023646783</v>
       </c>
       <c r="L17" s="12">
         <f t="shared" si="14"/>
@@ -1911,14 +1918,14 @@
       </c>
       <c r="R17" s="9">
         <f t="shared" si="20"/>
-        <v>1.1642141258509767E-2</v>
+        <v>1.1642141258509766E-2</v>
       </c>
       <c r="S17" s="9">
         <f t="shared" si="21"/>
         <v>0.28364265403268213</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>38</v>
       </c>
@@ -1953,7 +1960,7 @@
       </c>
       <c r="K18" s="9">
         <f t="shared" si="13"/>
-        <v>7.027114016177205E-2</v>
+        <v>0.24909504193486764</v>
       </c>
       <c r="L18" s="12">
         <f t="shared" si="14"/>
@@ -1988,7 +1995,7 @@
         <v>0.26296871587547221</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>77</v>
       </c>
@@ -2023,7 +2030,7 @@
       </c>
       <c r="K19" s="9">
         <f t="shared" si="13"/>
-        <v>5.7304441679540311E-2</v>
+        <v>0.20313107586355281</v>
       </c>
       <c r="L19" s="12">
         <f t="shared" si="14"/>
@@ -2051,14 +2058,14 @@
       </c>
       <c r="R19" s="9">
         <f t="shared" si="20"/>
-        <v>1.1999847254111748E-2</v>
+        <v>1.199984725411175E-2</v>
       </c>
       <c r="S19" s="9">
         <f t="shared" si="21"/>
         <v>0.27518748991205688</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>39</v>
       </c>
@@ -2094,7 +2101,7 @@
       </c>
       <c r="K20" s="9">
         <f t="shared" si="13"/>
-        <v>-0.10579939675580585</v>
+        <v>-0.37503454634293754</v>
       </c>
       <c r="L20" s="12">
         <f t="shared" si="14"/>
@@ -2122,14 +2129,14 @@
       </c>
       <c r="R20" s="9">
         <f t="shared" si="20"/>
-        <v>3.3022078451871001E-3</v>
+        <v>3.3022078451871006E-3</v>
       </c>
       <c r="S20" s="9">
         <f t="shared" si="21"/>
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>39</v>
       </c>
@@ -2164,7 +2171,7 @@
       </c>
       <c r="K21" s="9">
         <f t="shared" si="13"/>
-        <v>6.1299263333260856E-2</v>
+        <v>0.21729180052327834</v>
       </c>
       <c r="L21" s="12">
         <f t="shared" si="14"/>
@@ -2199,7 +2206,7 @@
         <v>0.26155408503819672</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>39</v>
       </c>
@@ -2234,7 +2241,7 @@
       </c>
       <c r="K22" s="9">
         <f t="shared" si="13"/>
-        <v>5.2961591201053891E-3</v>
+        <v>1.8773666900513197E-2</v>
       </c>
       <c r="L22" s="12">
         <f t="shared" si="14"/>
@@ -2262,7 +2269,7 @@
       </c>
       <c r="R22" s="9">
         <f t="shared" si="20"/>
-        <v>1.0891658600627999E-2</v>
+        <v>1.0891658600627997E-2</v>
       </c>
       <c r="S22" s="9">
         <f t="shared" si="21"/>
@@ -2305,7 +2312,7 @@
       </c>
       <c r="K23" s="9">
         <f t="shared" si="13"/>
-        <v>0.10430376919400261</v>
+        <v>0.369732890366264</v>
       </c>
       <c r="L23" s="12">
         <f t="shared" si="14"/>
@@ -2375,7 +2382,7 @@
       </c>
       <c r="K24" s="9">
         <f t="shared" si="13"/>
-        <v>-2.5214459892078277E-2</v>
+        <v>-8.9379465449445916E-2</v>
       </c>
       <c r="L24" s="12">
         <f t="shared" si="14"/>
@@ -2446,7 +2453,7 @@
       </c>
       <c r="K25" s="9">
         <f t="shared" si="13"/>
-        <v>4.4276779337051868E-2</v>
+        <v>0.15695100691853767</v>
       </c>
       <c r="L25" s="12">
         <f t="shared" si="14"/>
@@ -2474,7 +2481,7 @@
       </c>
       <c r="R25" s="9">
         <f t="shared" si="20"/>
-        <v>1.1639755473023062E-2</v>
+        <v>1.1639755473023063E-2</v>
       </c>
       <c r="S25" s="9">
         <f t="shared" si="21"/>
@@ -2517,7 +2524,7 @@
       </c>
       <c r="K26" s="9">
         <f t="shared" si="13"/>
-        <v>1.2347302963680137E-2</v>
+        <v>4.3768351309512316E-2</v>
       </c>
       <c r="L26" s="12">
         <f t="shared" si="14"/>
@@ -2552,7 +2559,7 @@
         <v>0.33760219027884886</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -2588,7 +2595,7 @@
       </c>
       <c r="K27" s="9">
         <f t="shared" si="13"/>
-        <v>4.9568937406170265E-2</v>
+        <v>0.17571049101283634</v>
       </c>
       <c r="L27" s="12">
         <f t="shared" si="14"/>
@@ -2616,14 +2623,14 @@
       </c>
       <c r="R27" s="9">
         <f t="shared" si="20"/>
-        <v>1.1952004782154312E-2</v>
+        <v>1.1952004782154311E-2</v>
       </c>
       <c r="S27" s="9">
         <f t="shared" si="21"/>
         <v>0.27628903312669928</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>37</v>
       </c>
@@ -2658,7 +2665,7 @@
       </c>
       <c r="K28" s="9">
         <f t="shared" si="13"/>
-        <v>0.19033650318163101</v>
+        <v>0.6746991600337916</v>
       </c>
       <c r="L28" s="12">
         <f t="shared" si="14"/>
@@ -2693,7 +2700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -2729,7 +2736,7 @@
       </c>
       <c r="K29" s="9">
         <f t="shared" si="13"/>
-        <v>-6.655653915439276E-2</v>
+        <v>-0.23592763506521491</v>
       </c>
       <c r="L29" s="12">
         <f t="shared" si="14"/>
@@ -2757,14 +2764,14 @@
       </c>
       <c r="R29" s="9">
         <f t="shared" si="20"/>
-        <v>1.0561048364135005E-2</v>
+        <v>1.0561048364135003E-2</v>
       </c>
       <c r="S29" s="9">
         <f t="shared" si="21"/>
         <v>0.31267803454070875</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>40</v>
       </c>
@@ -2800,7 +2807,7 @@
       </c>
       <c r="K30" s="9">
         <f t="shared" si="13"/>
-        <v>-1.9556052621876884E-2</v>
+        <v>-6.9321712109873063E-2</v>
       </c>
       <c r="L30" s="12">
         <f t="shared" si="14"/>
@@ -2828,14 +2835,14 @@
       </c>
       <c r="R30" s="9">
         <f t="shared" si="20"/>
-        <v>1.1126365470574516E-2</v>
+        <v>1.1126365470574514E-2</v>
       </c>
       <c r="S30" s="9">
         <f t="shared" si="21"/>
         <v>0.29679124363839449</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>77</v>
       </c>
@@ -2870,7 +2877,7 @@
       </c>
       <c r="K31" s="9">
         <f t="shared" si="13"/>
-        <v>6.3336488172123506E-2</v>
+        <v>0.22451329437550574</v>
       </c>
       <c r="L31" s="12">
         <f t="shared" si="14"/>
@@ -2905,7 +2912,7 @@
         <v>0.26715238932766161</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>77</v>
       </c>
@@ -2917,7 +2924,7 @@
       </c>
       <c r="D32" s="8">
         <f ca="1">TODAY()-20</f>
-        <v>45599</v>
+        <v>45600</v>
       </c>
       <c r="E32" s="2">
         <v>1E-35</v>
@@ -2926,7 +2933,7 @@
         <v>2742.9</v>
       </c>
       <c r="G32" s="1">
-        <f t="shared" ref="G32" si="22">E32*F32</f>
+        <f t="shared" ref="G32:G33" si="22">E32*F32</f>
         <v>2.7429E-32</v>
       </c>
       <c r="H32" s="11">
@@ -2936,31 +2943,31 @@
         <v>0.5</v>
       </c>
       <c r="J32" s="9">
-        <f t="shared" ref="J32" si="23">IFERROR(H32/I32,"")</f>
+        <f t="shared" ref="J32:J33" si="23">IFERROR(H32/I32,"")</f>
         <v>0.2</v>
       </c>
       <c r="K32" s="9">
         <f t="shared" si="2"/>
-        <v>3.4382665007724189E-2</v>
+        <v>0.12187864551813167</v>
       </c>
       <c r="L32" s="12">
-        <f t="shared" ref="L32" si="24">F32/(1-(F32*(1+H32)-F32)/(F32*(1+H32)))</f>
+        <f t="shared" ref="L32:L33" si="24">F32/(1-(F32*(1+H32)-F32)/(F32*(1+H32)))</f>
         <v>3017.1900000000005</v>
       </c>
       <c r="M32" s="12">
-        <f t="shared" ref="M32" si="25">F32/(1+I32-H32)</f>
+        <f t="shared" ref="M32:M33" si="25">F32/(1+I32-H32)</f>
         <v>1959.214285714286</v>
       </c>
       <c r="N32" s="12">
-        <f t="shared" ref="N32" si="26">L32-F32</f>
+        <f t="shared" ref="N32:N33" si="26">L32-F32</f>
         <v>274.29000000000042</v>
       </c>
       <c r="O32" s="12">
-        <f t="shared" ref="O32" si="27">0.5*(M32-F32)</f>
+        <f t="shared" ref="O32:O33" si="27">0.5*(M32-F32)</f>
         <v>-391.84285714285704</v>
       </c>
       <c r="P32" s="15">
-        <f t="shared" ref="P32" si="28">N32+O32</f>
+        <f t="shared" ref="P32:P33" si="28">N32+O32</f>
         <v>-117.55285714285662</v>
       </c>
       <c r="Q32" s="12">
@@ -2976,10 +2983,87 @@
         <v>0.66367766172081932</v>
       </c>
     </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C33" t="s">
+        <v>87</v>
+      </c>
+      <c r="D33" s="8">
+        <v>45481</v>
+      </c>
+      <c r="E33" s="2">
+        <v>1E-22</v>
+      </c>
+      <c r="F33" s="1">
+        <v>64.349999999999994</v>
+      </c>
+      <c r="G33" s="1">
+        <f t="shared" si="22"/>
+        <v>6.4349999999999995E-21</v>
+      </c>
+      <c r="H33" s="11">
+        <f>75.53/F33-1</f>
+        <v>0.17373737373737397</v>
+      </c>
+      <c r="I33" s="11">
+        <v>0.67300000000000004</v>
+      </c>
+      <c r="J33" s="9">
+        <f t="shared" si="23"/>
+        <v>0.25815360139282906</v>
+      </c>
+      <c r="K33" s="9">
+        <f t="shared" si="2"/>
+        <v>0.15731705636692836</v>
+      </c>
+      <c r="L33" s="12">
+        <f t="shared" si="24"/>
+        <v>75.53</v>
+      </c>
+      <c r="M33" s="12">
+        <f t="shared" si="25"/>
+        <v>42.921099260916144</v>
+      </c>
+      <c r="N33" s="12">
+        <f t="shared" si="26"/>
+        <v>11.180000000000007</v>
+      </c>
+      <c r="O33" s="12">
+        <f t="shared" si="27"/>
+        <v>-10.714450369541925</v>
+      </c>
+      <c r="P33" s="15">
+        <f t="shared" si="28"/>
+        <v>0.46554963045808151</v>
+      </c>
+      <c r="Q33" s="12">
+        <f t="shared" si="9"/>
+        <v>82.961571724439679</v>
+      </c>
+      <c r="R33" s="9">
+        <f t="shared" si="10"/>
+        <v>1.2053773563036409E-2</v>
+      </c>
+      <c r="S33" s="9">
+        <f t="shared" si="8"/>
+        <v>0.27395635299749704</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S32" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="R2:R32">
-    <cfRule type="iconSet" priority="1">
+  <autoFilter ref="A1:S32" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Tech"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="R2:R33">
+    <cfRule type="iconSet" priority="3">
       <iconSet iconSet="3Symbols">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="33"/>
@@ -2993,7 +3077,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="5" id="{2048185B-3E19-4351-A3A9-6DB74B32B9C2}">
+          <x14:cfRule type="iconSet" priority="7" id="{2048185B-3E19-4351-A3A9-6DB74B32B9C2}">
             <x14:iconSet iconSet="5Arrows" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -3017,7 +3101,7 @@
               <x14:cfIcon iconSet="3Arrows" iconId="0"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>S2:S32</xm:sqref>
+          <xm:sqref>S2:S33</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/Open Positions.xlsx
+++ b/Open Positions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\StockSillines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{134FF921-831A-4707-B79E-C591403248A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F7B9D9F-2DDF-4EDA-BB36-C5277B5FE46C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Positions!$A$1:$S$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Positions!$A$1:$S$33</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="89">
   <si>
     <t>Name</t>
   </si>
@@ -304,6 +304,9 @@
   </si>
   <si>
     <t>PLTR</t>
+  </si>
+  <si>
+    <t>Forex2</t>
   </si>
 </sst>
 </file>
@@ -902,7 +905,7 @@
       </c>
       <c r="K3" s="9">
         <f t="shared" si="2"/>
-        <v>3.0521065278950023E-2</v>
+        <v>6.03528490259903E-2</v>
       </c>
       <c r="L3" s="12">
         <f t="shared" si="3"/>
@@ -973,7 +976,7 @@
       </c>
       <c r="K4" s="9">
         <f t="shared" si="2"/>
-        <v>0.24705282560526781</v>
+        <v>0.48852626043437952</v>
       </c>
       <c r="L4" s="12">
         <f t="shared" si="3"/>
@@ -1001,7 +1004,7 @@
       </c>
       <c r="R4" s="9">
         <f t="shared" si="10"/>
-        <v>1.2358789194720575E-2</v>
+        <v>1.2358789194720577E-2</v>
       </c>
       <c r="S4" s="9">
         <f t="shared" si="8"/>
@@ -1044,7 +1047,7 @@
       </c>
       <c r="K5" s="9">
         <f t="shared" si="2"/>
-        <v>-0.1169149561039837</v>
+        <v>-0.23118952861355549</v>
       </c>
       <c r="L5" s="12">
         <f t="shared" si="3"/>
@@ -1072,7 +1075,7 @@
       </c>
       <c r="R5" s="9">
         <f t="shared" si="10"/>
-        <v>1.142701092947844E-2</v>
+        <v>1.1427010929478438E-2</v>
       </c>
       <c r="S5" s="9">
         <f t="shared" si="8"/>
@@ -1115,7 +1118,7 @@
       </c>
       <c r="K6" s="9">
         <f t="shared" si="2"/>
-        <v>5.3165105958719094E-2</v>
+        <v>0.10512954197540167</v>
       </c>
       <c r="L6" s="12">
         <f t="shared" si="3"/>
@@ -1186,7 +1189,7 @@
       </c>
       <c r="K7" s="9">
         <f t="shared" si="2"/>
-        <v>-0.27537987616400289</v>
+        <v>-0.54454062920223623</v>
       </c>
       <c r="L7" s="12">
         <f t="shared" si="3"/>
@@ -1257,7 +1260,7 @@
       </c>
       <c r="K8" s="9">
         <f t="shared" si="2"/>
-        <v>0.10536529988365954</v>
+        <v>0.20835105126040546</v>
       </c>
       <c r="L8" s="12">
         <f t="shared" si="3"/>
@@ -1285,14 +1288,14 @@
       </c>
       <c r="R8" s="9">
         <f t="shared" si="10"/>
-        <v>1.1897844606297952E-2</v>
+        <v>1.1897844606297951E-2</v>
       </c>
       <c r="S8" s="9">
         <f t="shared" si="8"/>
         <v>0.27754672837457672</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>36</v>
       </c>
@@ -1327,7 +1330,7 @@
       </c>
       <c r="K9" s="9">
         <f t="shared" ref="K9:K31" si="13">IFERROR(J9/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.539013140363477E-2</v>
+        <v>6.9981019276107184E-2</v>
       </c>
       <c r="L9" s="12">
         <f t="shared" ref="L9:L31" si="14">F9/(1-(F9*(1+H9)-F9)/(F9*(1+H9)))</f>
@@ -1398,7 +1401,7 @@
       </c>
       <c r="K10" s="9">
         <f t="shared" si="13"/>
-        <v>0.56211797720199363</v>
+        <v>1.1115411963115487</v>
       </c>
       <c r="L10" s="12">
         <f t="shared" si="14"/>
@@ -1433,7 +1436,7 @@
         <v>0.24565301900228498</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>36</v>
       </c>
@@ -1468,7 +1471,7 @@
       </c>
       <c r="K11" s="9">
         <f t="shared" si="13"/>
-        <v>0.1322901194197246</v>
+        <v>0.26159262568319935</v>
       </c>
       <c r="L11" s="12">
         <f t="shared" si="14"/>
@@ -1538,7 +1541,7 @@
       </c>
       <c r="K12" s="9">
         <f t="shared" si="13"/>
-        <v>0.61194757046079873</v>
+        <v>1.2100750414276724</v>
       </c>
       <c r="L12" s="12">
         <f t="shared" si="14"/>
@@ -1566,14 +1569,14 @@
       </c>
       <c r="R12" s="9">
         <f t="shared" si="20"/>
-        <v>2.6686520505483948E-2</v>
+        <v>2.6686520505483952E-2</v>
       </c>
       <c r="S12" s="9">
         <f t="shared" si="21"/>
         <v>0.12374066692240798</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -1608,7 +1611,7 @@
       </c>
       <c r="K13" s="9">
         <f t="shared" si="13"/>
-        <v>-0.11065213184944192</v>
+        <v>-0.21880531845391346</v>
       </c>
       <c r="L13" s="12">
         <f t="shared" si="14"/>
@@ -1678,7 +1681,7 @@
       </c>
       <c r="K14" s="9">
         <f t="shared" si="13"/>
-        <v>-9.3037133983306625E-2</v>
+        <v>-0.18397313625150449</v>
       </c>
       <c r="L14" s="12">
         <f t="shared" si="14"/>
@@ -1706,14 +1709,14 @@
       </c>
       <c r="R14" s="9">
         <f t="shared" si="20"/>
-        <v>9.9944002824526625E-3</v>
+        <v>9.9944002824526607E-3</v>
       </c>
       <c r="S14" s="9">
         <f t="shared" si="21"/>
         <v>0.33040580243567419</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -1749,7 +1752,7 @@
       </c>
       <c r="K15" s="9">
         <f t="shared" si="13"/>
-        <v>0.30458204151428614</v>
+        <v>0.60228546413868833</v>
       </c>
       <c r="L15" s="12">
         <f t="shared" si="14"/>
@@ -1777,7 +1780,7 @@
       </c>
       <c r="R15" s="9">
         <f t="shared" si="20"/>
-        <v>1.5892644286847574E-2</v>
+        <v>1.5892644286847578E-2</v>
       </c>
       <c r="S15" s="9">
         <f t="shared" si="21"/>
@@ -1819,7 +1822,7 @@
       </c>
       <c r="K16" s="9">
         <f t="shared" si="13"/>
-        <v>0.25658662214343508</v>
+        <v>0.5073785441883597</v>
       </c>
       <c r="L16" s="12">
         <f t="shared" si="14"/>
@@ -1847,7 +1850,7 @@
       </c>
       <c r="R16" s="9">
         <f t="shared" si="20"/>
-        <v>1.223662258659841E-2</v>
+        <v>1.2236622586598408E-2</v>
       </c>
       <c r="S16" s="9">
         <f t="shared" si="21"/>
@@ -1890,7 +1893,7 @@
       </c>
       <c r="K17" s="9">
         <f t="shared" si="13"/>
-        <v>0.11585345023646783</v>
+        <v>0.22909048971118229</v>
       </c>
       <c r="L17" s="12">
         <f t="shared" si="14"/>
@@ -1918,7 +1921,7 @@
       </c>
       <c r="R17" s="9">
         <f t="shared" si="20"/>
-        <v>1.1642141258509766E-2</v>
+        <v>1.1642141258509767E-2</v>
       </c>
       <c r="S17" s="9">
         <f t="shared" si="21"/>
@@ -1960,7 +1963,7 @@
       </c>
       <c r="K18" s="9">
         <f t="shared" si="13"/>
-        <v>0.24909504193486764</v>
+        <v>0.49256457209526899</v>
       </c>
       <c r="L18" s="12">
         <f t="shared" si="14"/>
@@ -1995,7 +1998,7 @@
         <v>0.26296871587547221</v>
       </c>
     </row>
-    <row r="19" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>77</v>
       </c>
@@ -2019,50 +2022,50 @@
         <v>2.0399999999999999E-34</v>
       </c>
       <c r="H19" s="11">
-        <v>0.05</v>
+        <f>L19/F19-1</f>
+        <v>3.9215686274509887E-2</v>
       </c>
       <c r="I19" s="11">
         <v>0.15</v>
       </c>
       <c r="J19" s="9">
         <f t="shared" si="12"/>
-        <v>0.33333333333333337</v>
+        <v>0.2614379084967326</v>
       </c>
       <c r="K19" s="9">
         <f t="shared" si="13"/>
-        <v>0.20313107586355281</v>
+        <v>0.31503896534571424</v>
       </c>
       <c r="L19" s="12">
-        <f t="shared" si="14"/>
-        <v>21.419999999999998</v>
+        <v>21.2</v>
       </c>
       <c r="M19" s="12">
         <f t="shared" si="15"/>
-        <v>18.545454545454547</v>
+        <v>18.365401588702561</v>
       </c>
       <c r="N19" s="12">
         <f t="shared" si="16"/>
-        <v>1.0199999999999996</v>
+        <v>0.80000000000000071</v>
       </c>
       <c r="O19" s="12">
         <f t="shared" si="17"/>
-        <v>-0.92727272727272592</v>
+        <v>-1.0172992056487189</v>
       </c>
       <c r="P19" s="15">
         <f t="shared" si="18"/>
-        <v>9.2727272727273657E-2</v>
+        <v>-0.21729920564871819</v>
       </c>
       <c r="Q19" s="12">
         <f t="shared" si="19"/>
-        <v>83.33439408217049</v>
+        <v>83.644420560546479</v>
       </c>
       <c r="R19" s="9">
         <f t="shared" si="20"/>
-        <v>1.199984725411175E-2</v>
+        <v>1.1955370044988768E-2</v>
       </c>
       <c r="S19" s="9">
         <f t="shared" si="21"/>
-        <v>0.27518748991205688</v>
+        <v>0.27621126178116578</v>
       </c>
     </row>
     <row r="20" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
@@ -2101,7 +2104,7 @@
       </c>
       <c r="K20" s="9">
         <f t="shared" si="13"/>
-        <v>-0.37503454634293754</v>
+        <v>-0.74159938875320708</v>
       </c>
       <c r="L20" s="12">
         <f t="shared" si="14"/>
@@ -2171,7 +2174,7 @@
       </c>
       <c r="K21" s="9">
         <f t="shared" si="13"/>
-        <v>0.21729180052327834</v>
+        <v>0.42967632720905369</v>
       </c>
       <c r="L21" s="12">
         <f t="shared" si="14"/>
@@ -2199,7 +2202,7 @@
       </c>
       <c r="R21" s="9">
         <f t="shared" si="20"/>
-        <v>1.2625334621345539E-2</v>
+        <v>1.2625334621345541E-2</v>
       </c>
       <c r="S21" s="9">
         <f t="shared" si="21"/>
@@ -2241,7 +2244,7 @@
       </c>
       <c r="K22" s="9">
         <f t="shared" si="13"/>
-        <v>1.8773666900513197E-2</v>
+        <v>3.7123353125303585E-2</v>
       </c>
       <c r="L22" s="12">
         <f t="shared" si="14"/>
@@ -2269,14 +2272,14 @@
       </c>
       <c r="R22" s="9">
         <f t="shared" si="20"/>
-        <v>1.0891658600627997E-2</v>
+        <v>1.0891658600627999E-2</v>
       </c>
       <c r="S22" s="9">
         <f t="shared" si="21"/>
         <v>0.30318686678231904</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>36</v>
       </c>
@@ -2312,7 +2315,7 @@
       </c>
       <c r="K23" s="9">
         <f t="shared" si="13"/>
-        <v>0.369732890366264</v>
+        <v>0.73111580832036438</v>
       </c>
       <c r="L23" s="12">
         <f t="shared" si="14"/>
@@ -2347,7 +2350,7 @@
         <v>0.16267542829407408</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>36</v>
       </c>
@@ -2382,7 +2385,7 @@
       </c>
       <c r="K24" s="9">
         <f t="shared" si="13"/>
-        <v>-8.9379465449445916E-2</v>
+        <v>-0.1767404032261779</v>
       </c>
       <c r="L24" s="12">
         <f t="shared" si="14"/>
@@ -2417,7 +2420,7 @@
         <v>0.82480838165207504</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>36</v>
       </c>
@@ -2453,7 +2456,7 @@
       </c>
       <c r="K25" s="9">
         <f t="shared" si="13"/>
-        <v>0.15695100691853767</v>
+        <v>0.31035746421225607</v>
       </c>
       <c r="L25" s="12">
         <f t="shared" si="14"/>
@@ -2488,7 +2491,7 @@
         <v>0.28370079189725922</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>36</v>
       </c>
@@ -2524,7 +2527,7 @@
       </c>
       <c r="K26" s="9">
         <f t="shared" si="13"/>
-        <v>4.3768351309512316E-2</v>
+        <v>8.6548247073189144E-2</v>
       </c>
       <c r="L26" s="12">
         <f t="shared" si="14"/>
@@ -2595,7 +2598,7 @@
       </c>
       <c r="K27" s="9">
         <f t="shared" si="13"/>
-        <v>0.17571049101283634</v>
+        <v>0.34745277202674207</v>
       </c>
       <c r="L27" s="12">
         <f t="shared" si="14"/>
@@ -2665,7 +2668,7 @@
       </c>
       <c r="K28" s="9">
         <f t="shared" si="13"/>
-        <v>0.6746991600337916</v>
+        <v>1.3341610514350544</v>
       </c>
       <c r="L28" s="12">
         <f t="shared" si="14"/>
@@ -2736,7 +2739,7 @@
       </c>
       <c r="K29" s="9">
         <f t="shared" si="13"/>
-        <v>-0.23592763506521491</v>
+        <v>-0.46652712839516236</v>
       </c>
       <c r="L29" s="12">
         <f t="shared" si="14"/>
@@ -2807,7 +2810,7 @@
       </c>
       <c r="K30" s="9">
         <f t="shared" si="13"/>
-        <v>-6.9321712109873063E-2</v>
+        <v>-0.13707787676978034</v>
       </c>
       <c r="L30" s="12">
         <f t="shared" si="14"/>
@@ -2842,9 +2845,9 @@
         <v>0.29679124363839449</v>
       </c>
     </row>
-    <row r="31" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>80</v>
@@ -2877,7 +2880,7 @@
       </c>
       <c r="K31" s="9">
         <f t="shared" si="13"/>
-        <v>0.22451329437550574</v>
+        <v>0.44395622616481484</v>
       </c>
       <c r="L31" s="12">
         <f t="shared" si="14"/>
@@ -2905,16 +2908,16 @@
       </c>
       <c r="R31" s="9">
         <f t="shared" si="20"/>
-        <v>1.2360764781096349E-2</v>
+        <v>1.2360764781096351E-2</v>
       </c>
       <c r="S31" s="9">
         <f t="shared" si="21"/>
         <v>0.26715238932766161</v>
       </c>
     </row>
-    <row r="32" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>82</v>
@@ -2924,7 +2927,7 @@
       </c>
       <c r="D32" s="8">
         <f ca="1">TODAY()-20</f>
-        <v>45600</v>
+        <v>45602</v>
       </c>
       <c r="E32" s="2">
         <v>1E-35</v>
@@ -2948,7 +2951,7 @@
       </c>
       <c r="K32" s="9">
         <f t="shared" si="2"/>
-        <v>0.12187864551813167</v>
+        <v>0.2410048084894709</v>
       </c>
       <c r="L32" s="12">
         <f t="shared" ref="L32:L33" si="24">F32/(1-(F32*(1+H32)-F32)/(F32*(1+H32)))</f>
@@ -2983,7 +2986,7 @@
         <v>0.66367766172081932</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -3019,7 +3022,7 @@
       </c>
       <c r="K33" s="9">
         <f t="shared" si="2"/>
-        <v>0.15731705636692836</v>
+        <v>0.31108129632272985</v>
       </c>
       <c r="L33" s="12">
         <f t="shared" si="24"/>
@@ -3047,7 +3050,7 @@
       </c>
       <c r="R33" s="9">
         <f t="shared" si="10"/>
-        <v>1.2053773563036409E-2</v>
+        <v>1.2053773563036411E-2</v>
       </c>
       <c r="S33" s="9">
         <f t="shared" si="8"/>
@@ -3055,10 +3058,10 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S32" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:S33" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Tech"/>
+        <filter val="Forex"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/Open Positions.xlsx
+++ b/Open Positions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\StockSillines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F7B9D9F-2DDF-4EDA-BB36-C5277B5FE46C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7C223C1-ADAA-4B9D-8BBA-525A176F5820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="88">
   <si>
     <t>Name</t>
   </si>
@@ -304,9 +304,6 @@
   </si>
   <si>
     <t>PLTR</t>
-  </si>
-  <si>
-    <t>Forex2</t>
   </si>
 </sst>
 </file>
@@ -715,7 +712,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:S33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -799,2271 +795,2269 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>42</v>
+        <v>36</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="D2" s="8">
-        <v>45507</v>
+        <v>45574</v>
       </c>
       <c r="E2" s="2">
-        <v>9.9999999999999998E-46</v>
+        <v>0.13370000000000001</v>
       </c>
       <c r="F2" s="1">
-        <v>41.8</v>
+        <v>423.77</v>
       </c>
       <c r="G2" s="1">
-        <f t="shared" ref="G2:G8" si="0">E2*F2</f>
-        <v>4.1799999999999994E-44</v>
+        <f>E2*F2</f>
+        <v>56.658049000000005</v>
       </c>
       <c r="H2" s="11">
-        <v>0</v>
+        <v>1.14E-2</v>
       </c>
       <c r="I2" s="11">
-        <v>0.4</v>
+        <v>0.1963</v>
       </c>
       <c r="J2" s="9">
-        <f t="shared" ref="J2:J8" si="1">IFERROR(H2/I2,"")</f>
-        <v>0</v>
+        <f>IFERROR(H2/I2,"")</f>
+        <v>5.8074375955170655E-2</v>
       </c>
       <c r="K2" s="9">
-        <f t="shared" ref="K2:K33" si="2">IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0</v>
+        <f>IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>9.2730039949282667E-3</v>
       </c>
       <c r="L2" s="12">
-        <f t="shared" ref="L2:L8" si="3">F2/(1-(F2*(1+H2)-F2)/(F2*(1+H2)))</f>
-        <v>41.8</v>
+        <f>F2/(1-(F2*(1+H2)-F2)/(F2*(1+H2)))</f>
+        <v>428.600978</v>
       </c>
       <c r="M2" s="12">
-        <f t="shared" ref="M2:M8" si="4">F2/(1+I2-H2)</f>
-        <v>29.857142857142858</v>
+        <f>F2/(1+I2-H2)</f>
+        <v>357.64199510507217</v>
       </c>
       <c r="N2" s="12">
-        <f t="shared" ref="N2:N8" si="5">L2-F2</f>
-        <v>0</v>
+        <f>L2-F2</f>
+        <v>4.830978000000016</v>
       </c>
       <c r="O2" s="12">
-        <f t="shared" ref="O2:O8" si="6">0.5*(M2-F2)</f>
-        <v>-5.9714285714285698</v>
+        <f>0.5*(M2-F2)</f>
+        <v>-33.064002447463906</v>
       </c>
       <c r="P2" s="15">
-        <f t="shared" ref="P2:P8" si="7">N2+O2</f>
-        <v>-5.9714285714285698</v>
+        <f>N2+O2</f>
+        <v>-28.23302444746389</v>
       </c>
       <c r="Q2" s="12">
         <f>MAX($P$2:$P$280)-P2</f>
-        <v>89.398549926326339</v>
+        <v>111.66014580236165</v>
       </c>
       <c r="R2" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q2)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.1185863762042041E-2</v>
+        <v>8.9557468585971488E-3</v>
       </c>
       <c r="S2" s="9">
-        <f t="shared" ref="S2:S33" si="8">Q2/MAX($Q$2:$Q$28)</f>
-        <v>0.29521259291506552</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <f>Q2/MAX($Q$2:$Q$28)</f>
+        <v>0.36872500946329412</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>59</v>
+        <v>38</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>5</v>
       </c>
       <c r="D3" s="8">
-        <v>45574</v>
+        <v>45553</v>
       </c>
       <c r="E3" s="2">
-        <v>9.9999999999999998E-46</v>
+        <v>1.0751999999999999</v>
       </c>
       <c r="F3" s="1">
-        <v>47.42</v>
+        <v>51.15</v>
       </c>
       <c r="G3" s="1">
-        <f t="shared" si="0"/>
-        <v>4.7420000000000006E-44</v>
+        <f>E3*F3</f>
+        <v>54.996479999999998</v>
       </c>
       <c r="H3" s="11">
-        <f>48.37/F3-1</f>
-        <v>2.0033741037536856E-2</v>
+        <f>16.68%+7%/4</f>
+        <v>0.18430000000000002</v>
       </c>
       <c r="I3" s="11">
-        <v>0.4</v>
+        <v>0.19980000000000001</v>
       </c>
       <c r="J3" s="9">
-        <f t="shared" si="1"/>
-        <v>5.0084352593842141E-2</v>
+        <f>IFERROR(H3/I3,"")</f>
+        <v>0.92242242242242245</v>
       </c>
       <c r="K3" s="9">
-        <f t="shared" si="2"/>
-        <v>6.03528490259903E-2</v>
+        <f>IFERROR(J3/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>0.14728745109094815</v>
       </c>
       <c r="L3" s="12">
-        <f t="shared" si="3"/>
-        <v>48.37</v>
+        <f>F3/(1-(F3*(1+H3)-F3)/(F3*(1+H3)))</f>
+        <v>60.576944999999995</v>
       </c>
       <c r="M3" s="12">
-        <f t="shared" si="4"/>
-        <v>34.36315902075247</v>
+        <f>F3/(1+I3-H3)</f>
+        <v>50.369276218611525</v>
       </c>
       <c r="N3" s="12">
-        <f t="shared" si="5"/>
-        <v>0.94999999999999574</v>
+        <f>L3-F3</f>
+        <v>9.4269449999999964</v>
       </c>
       <c r="O3" s="12">
-        <f t="shared" si="6"/>
-        <v>-6.5284204896237661</v>
+        <f>0.5*(M3-F3)</f>
+        <v>-0.39036189069423699</v>
       </c>
       <c r="P3" s="15">
-        <f t="shared" si="7"/>
-        <v>-5.5784204896237704</v>
+        <f>N3+O3</f>
+        <v>9.0365831093057594</v>
       </c>
       <c r="Q3" s="12">
-        <f t="shared" ref="Q3:Q33" si="9">MAX($P$2:$P$280)-P3</f>
-        <v>89.005541844521531</v>
+        <f>MAX($P$2:$P$280)-P3</f>
+        <v>74.390538245592012</v>
       </c>
       <c r="R3" s="9">
-        <f t="shared" ref="R3:R33" si="10">IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q3)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.123525546023685E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q3)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.3442569762012102E-2</v>
       </c>
       <c r="S3" s="9">
-        <f t="shared" si="8"/>
-        <v>0.29391479854410774</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <f>Q3/MAX($Q$2:$Q$28)</f>
+        <v>0.24565301900228498</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>32</v>
+        <v>36</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
       </c>
       <c r="D4" s="8">
-        <v>45511</v>
+        <v>45484</v>
       </c>
       <c r="E4" s="2">
-        <v>1E-22</v>
+        <v>0.24990000000000001</v>
       </c>
       <c r="F4" s="1">
-        <v>113.58</v>
+        <v>191.91</v>
       </c>
       <c r="G4" s="1">
-        <f t="shared" si="0"/>
-        <v>1.1358E-20</v>
+        <f>E4*F4</f>
+        <v>47.958309</v>
       </c>
       <c r="H4" s="11">
-        <f>121.15/F4-1</f>
-        <v>6.664905793273479E-2</v>
+        <f>227.4/F4-1</f>
+        <v>0.18493043614194149</v>
       </c>
       <c r="I4" s="11">
-        <v>0.16439999999999999</v>
+        <v>0.37</v>
       </c>
       <c r="J4" s="9">
-        <f t="shared" si="1"/>
-        <v>0.40540789496797319</v>
+        <f>IFERROR(H4/I4,"")</f>
+        <v>0.49981198957281486</v>
       </c>
       <c r="K4" s="9">
-        <f t="shared" si="2"/>
-        <v>0.48852626043437952</v>
+        <f>IFERROR(J4/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>7.9807290216936055E-2</v>
       </c>
       <c r="L4" s="12">
-        <f t="shared" si="3"/>
-        <v>121.15000000000002</v>
+        <f>F4/(1-(F4*(1+H4)-F4)/(F4*(1+H4)))</f>
+        <v>227.39999999999998</v>
       </c>
       <c r="M4" s="12">
-        <f t="shared" si="4"/>
-        <v>103.46609203186667</v>
+        <f>F4/(1+I4-H4)</f>
+        <v>161.93986062322494</v>
       </c>
       <c r="N4" s="12">
-        <f t="shared" si="5"/>
-        <v>7.5700000000000216</v>
+        <f>L4-F4</f>
+        <v>35.489999999999981</v>
       </c>
       <c r="O4" s="12">
-        <f t="shared" si="6"/>
-        <v>-5.0569539840666664</v>
+        <f>0.5*(M4-F4)</f>
+        <v>-14.985069688387526</v>
       </c>
       <c r="P4" s="15">
-        <f t="shared" si="7"/>
-        <v>2.5130460159333552</v>
+        <f>N4+O4</f>
+        <v>20.504930311612455</v>
       </c>
       <c r="Q4" s="12">
-        <f t="shared" si="9"/>
-        <v>80.914075338964409</v>
+        <f>MAX($P$2:$P$280)-P4</f>
+        <v>62.922191043285309</v>
       </c>
       <c r="R4" s="9">
-        <f t="shared" si="10"/>
-        <v>1.2358789194720577E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q4)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.5892644286847574E-2</v>
       </c>
       <c r="S4" s="9">
-        <f t="shared" si="8"/>
-        <v>0.26719509437038835</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <f>Q4/MAX($Q$2:$Q$28)</f>
+        <v>0.20778215289949825</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>45</v>
+        <v>36</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="D5" s="8">
-        <v>45511</v>
+        <v>45482</v>
       </c>
       <c r="E5" s="2">
-        <v>1E-22</v>
+        <v>0.18820000000000001</v>
       </c>
       <c r="F5" s="1">
-        <v>11.05</v>
+        <v>227.38</v>
       </c>
       <c r="G5" s="1">
-        <f t="shared" si="0"/>
-        <v>1.1050000000000002E-21</v>
+        <f>E5*F5</f>
+        <v>42.792915999999998</v>
       </c>
       <c r="H5" s="11">
-        <f>9.52/F5-1</f>
-        <v>-0.13846153846153852</v>
+        <v>4.9299999999999997E-2</v>
       </c>
       <c r="I5" s="11">
-        <v>0.72170000000000001</v>
+        <v>0.2271</v>
       </c>
       <c r="J5" s="9">
-        <f t="shared" si="1"/>
-        <v>-0.19185470203898922</v>
+        <f>IFERROR(H5/I5,"")</f>
+        <v>0.21708498458828709</v>
       </c>
       <c r="K5" s="9">
-        <f t="shared" si="2"/>
-        <v>-0.23118952861355549</v>
+        <f>IFERROR(J5/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>3.4662962730413936E-2</v>
       </c>
       <c r="L5" s="12">
-        <f t="shared" si="3"/>
-        <v>9.52</v>
+        <f>F5/(1-(F5*(1+H5)-F5)/(F5*(1+H5)))</f>
+        <v>238.58983399999997</v>
       </c>
       <c r="M5" s="12">
-        <f t="shared" si="4"/>
-        <v>5.9403443042581081</v>
+        <f>F5/(1+I5-H5)</f>
+        <v>193.05484802173541</v>
       </c>
       <c r="N5" s="12">
-        <f t="shared" si="5"/>
-        <v>-1.5300000000000011</v>
+        <f>L5-F5</f>
+        <v>11.209833999999972</v>
       </c>
       <c r="O5" s="12">
-        <f t="shared" si="6"/>
-        <v>-2.5548278478709463</v>
+        <f>0.5*(M5-F5)</f>
+        <v>-17.162575989132293</v>
       </c>
       <c r="P5" s="15">
-        <f t="shared" si="7"/>
-        <v>-4.0848278478709474</v>
+        <f>N5+O5</f>
+        <v>-5.9527419891323206</v>
       </c>
       <c r="Q5" s="12">
-        <f t="shared" si="9"/>
-        <v>87.511949202768704</v>
+        <f>MAX($P$2:$P$280)-P5</f>
+        <v>89.379863344030085</v>
       </c>
       <c r="R5" s="9">
-        <f t="shared" si="10"/>
-        <v>1.1427010929478438E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q5)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.1188202382352295E-2</v>
       </c>
       <c r="S5" s="9">
-        <f t="shared" si="8"/>
-        <v>0.28898264520499783</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <f>Q5/MAX($Q$2:$Q$28)</f>
+        <v>0.29515088593640709</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>47</v>
+        <v>37</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="D6" s="8">
         <v>45511</v>
       </c>
       <c r="E6" s="2">
-        <v>1E-22</v>
+        <v>0.14610000000000001</v>
       </c>
       <c r="F6" s="1">
-        <v>187.36</v>
+        <v>273.45999999999998</v>
       </c>
       <c r="G6" s="1">
-        <f t="shared" si="0"/>
-        <v>1.8736000000000003E-20</v>
+        <f>E6*F6</f>
+        <v>39.952506</v>
       </c>
       <c r="H6" s="11">
-        <f>196.02/F6-1</f>
-        <v>4.6221178479931568E-2</v>
+        <v>0.16769999999999999</v>
       </c>
       <c r="I6" s="11">
-        <v>0.52980000000000005</v>
+        <v>0.16700000000000001</v>
       </c>
       <c r="J6" s="9">
-        <f t="shared" si="1"/>
-        <v>8.7242692487602053E-2</v>
+        <f>IFERROR(H6/I6,"")</f>
+        <v>1.0041916167664668</v>
       </c>
       <c r="K6" s="9">
-        <f t="shared" si="2"/>
-        <v>0.10512954197540167</v>
+        <f>IFERROR(J6/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>0.16034391624176961</v>
       </c>
       <c r="L6" s="12">
-        <f t="shared" si="3"/>
-        <v>196.01999999999998</v>
+        <f>F6/(1-(F6*(1+H6)-F6)/(F6*(1+H6)))</f>
+        <v>319.31924199999997</v>
       </c>
       <c r="M6" s="12">
-        <f t="shared" si="4"/>
-        <v>126.28921179127629</v>
+        <f>F6/(1+I6-H6)</f>
+        <v>273.65155608926244</v>
       </c>
       <c r="N6" s="12">
-        <f t="shared" si="5"/>
-        <v>8.6599999999999682</v>
+        <f>L6-F6</f>
+        <v>45.859241999999995</v>
       </c>
       <c r="O6" s="12">
-        <f t="shared" si="6"/>
-        <v>-30.535394104361863</v>
+        <f>0.5*(M6-F6)</f>
+        <v>9.5778044631231296E-2</v>
       </c>
       <c r="P6" s="15">
-        <f t="shared" si="7"/>
-        <v>-21.875394104361895</v>
+        <f>N6+O6</f>
+        <v>45.955020044631226</v>
       </c>
       <c r="Q6" s="12">
-        <f t="shared" si="9"/>
-        <v>105.30251545925967</v>
+        <f>MAX($P$2:$P$280)-P6</f>
+        <v>37.472101310266538</v>
       </c>
       <c r="R6" s="9">
-        <f t="shared" si="10"/>
-        <v>9.4964493073946415E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q6)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>2.6686520505483952E-2</v>
       </c>
       <c r="S6" s="9">
-        <f t="shared" si="8"/>
-        <v>0.34773079266750317</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <f>Q6/MAX($Q$2:$Q$28)</f>
+        <v>0.12374066692240798</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>53</v>
+        <v>36</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D7" s="8">
-        <v>45511</v>
+        <v>45544</v>
       </c>
       <c r="E7" s="2">
-        <v>1E-22</v>
+        <v>0.1928</v>
       </c>
       <c r="F7" s="1">
-        <v>10.47</v>
+        <v>188.12</v>
       </c>
       <c r="G7" s="1">
-        <f t="shared" si="0"/>
-        <v>1.0470000000000001E-21</v>
+        <f>E7*F7</f>
+        <v>36.269536000000002</v>
       </c>
       <c r="H7" s="11">
-        <f>6.42/F7-1</f>
-        <v>-0.38681948424068768</v>
+        <v>-6.8599999999999994E-2</v>
       </c>
       <c r="I7" s="11">
-        <v>0.85599999999999998</v>
+        <v>0.37780000000000002</v>
       </c>
       <c r="J7" s="9">
-        <f t="shared" si="1"/>
-        <v>-0.45189192084192487</v>
+        <f>IFERROR(H7/I7,"")</f>
+        <v>-0.18157755426151401</v>
       </c>
       <c r="K7" s="9">
-        <f t="shared" si="2"/>
-        <v>-0.54454062920223623</v>
+        <f>IFERROR(J7/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>-2.8993327235338276E-2</v>
       </c>
       <c r="L7" s="12">
-        <f t="shared" si="3"/>
-        <v>6.419999999999999</v>
+        <f>F7/(1-(F7*(1+H7)-F7)/(F7*(1+H7)))</f>
+        <v>175.214968</v>
       </c>
       <c r="M7" s="12">
-        <f t="shared" si="4"/>
-        <v>4.6682312480197874</v>
+        <f>F7/(1+I7-H7)</f>
+        <v>130.06084070796459</v>
       </c>
       <c r="N7" s="12">
-        <f t="shared" si="5"/>
-        <v>-4.0500000000000016</v>
+        <f>L7-F7</f>
+        <v>-12.905032000000006</v>
       </c>
       <c r="O7" s="12">
-        <f t="shared" si="6"/>
-        <v>-2.9008843759901066</v>
+        <f>0.5*(M7-F7)</f>
+        <v>-29.029579646017709</v>
       </c>
       <c r="P7" s="15">
-        <f t="shared" si="7"/>
-        <v>-6.9508843759901087</v>
+        <f>N7+O7</f>
+        <v>-41.934611646017714</v>
       </c>
       <c r="Q7" s="12">
-        <f t="shared" si="9"/>
-        <v>90.378005730887878</v>
+        <f>MAX($P$2:$P$280)-P7</f>
+        <v>125.36173300091548</v>
       </c>
       <c r="R7" s="9">
-        <f t="shared" si="10"/>
-        <v>1.1064638923076357E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q7)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>7.9769158902158535E-3</v>
       </c>
       <c r="S7" s="9">
-        <f t="shared" si="8"/>
-        <v>0.29844695955690265</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <f>Q7/MAX($Q$2:$Q$28)</f>
+        <v>0.4139704982018737</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>54</v>
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="D8" s="8">
-        <v>45511</v>
+        <v>45544</v>
       </c>
       <c r="E8" s="2">
-        <v>1E-22</v>
+        <v>0.24390000000000001</v>
       </c>
       <c r="F8" s="1">
-        <v>13.04</v>
+        <v>144.28</v>
       </c>
       <c r="G8" s="1">
-        <f t="shared" si="0"/>
-        <v>1.304E-21</v>
+        <f>E8*F8</f>
+        <v>35.189892</v>
       </c>
       <c r="H8" s="11">
-        <f>13.72/F8-1</f>
-        <v>5.2147239263803824E-2</v>
+        <v>-2.8000000000000001E-2</v>
       </c>
       <c r="I8" s="11">
-        <v>0.30159999999999998</v>
+        <v>0.18340000000000001</v>
       </c>
       <c r="J8" s="9">
-        <f t="shared" si="1"/>
-        <v>0.17290198694895167</v>
+        <f>IFERROR(H8/I8,"")</f>
+        <v>-0.15267175572519084</v>
       </c>
       <c r="K8" s="9">
-        <f t="shared" si="2"/>
-        <v>0.20835105126040546</v>
+        <f>IFERROR(J8/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>-2.437780479716645E-2</v>
       </c>
       <c r="L8" s="12">
-        <f t="shared" si="3"/>
-        <v>13.72</v>
+        <f>F8/(1-(F8*(1+H8)-F8)/(F8*(1+H8)))</f>
+        <v>140.24016</v>
       </c>
       <c r="M8" s="12">
-        <f t="shared" si="4"/>
-        <v>10.436569040286594</v>
+        <f>F8/(1+I8-H8)</f>
+        <v>119.10186561003798</v>
       </c>
       <c r="N8" s="12">
-        <f t="shared" si="5"/>
-        <v>0.68000000000000149</v>
+        <f>L8-F8</f>
+        <v>-4.0398399999999981</v>
       </c>
       <c r="O8" s="12">
-        <f t="shared" si="6"/>
-        <v>-1.3017154798567026</v>
+        <f>0.5*(M8-F8)</f>
+        <v>-12.589067194981013</v>
       </c>
       <c r="P8" s="15">
-        <f t="shared" si="7"/>
-        <v>-0.62171547985670106</v>
+        <f>N8+O8</f>
+        <v>-16.628907194981011</v>
       </c>
       <c r="Q8" s="12">
-        <f t="shared" si="9"/>
-        <v>84.048836834754468</v>
+        <f>MAX($P$2:$P$280)-P8</f>
+        <v>100.05602854987877</v>
       </c>
       <c r="R8" s="9">
-        <f t="shared" si="10"/>
-        <v>1.1897844606297951E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q8)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.9944002824526625E-3</v>
       </c>
       <c r="S8" s="9">
-        <f t="shared" si="8"/>
-        <v>0.27754672837457672</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <f>Q8/MAX($Q$2:$Q$28)</f>
+        <v>0.33040580243567419</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>11</v>
+        <v>38</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D9" s="8">
-        <v>45574</v>
+        <v>45460</v>
       </c>
       <c r="E9" s="2">
-        <v>0.13370000000000001</v>
+        <v>0.1807</v>
       </c>
       <c r="F9" s="1">
-        <v>423.77</v>
+        <v>165.59</v>
       </c>
       <c r="G9" s="1">
-        <f t="shared" ref="G9:G31" si="11">E9*F9</f>
-        <v>56.658049000000005</v>
+        <f>E9*F9</f>
+        <v>29.922113</v>
       </c>
       <c r="H9" s="11">
-        <v>1.14E-2</v>
+        <v>6.7199999999999996E-2</v>
       </c>
       <c r="I9" s="11">
-        <v>0.1963</v>
+        <v>0.16439999999999999</v>
       </c>
       <c r="J9" s="9">
-        <f t="shared" ref="J9:J31" si="12">IFERROR(H9/I9,"")</f>
-        <v>5.8074375955170655E-2</v>
+        <f>IFERROR(H9/I9,"")</f>
+        <v>0.40875912408759124</v>
       </c>
       <c r="K9" s="9">
-        <f t="shared" ref="K9:K31" si="13">IFERROR(J9/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>6.9981019276107184E-2</v>
+        <f>IFERROR(J9/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>6.5268458391245648E-2</v>
       </c>
       <c r="L9" s="12">
-        <f t="shared" ref="L9:L31" si="14">F9/(1-(F9*(1+H9)-F9)/(F9*(1+H9)))</f>
-        <v>428.600978</v>
+        <f>F9/(1-(F9*(1+H9)-F9)/(F9*(1+H9)))</f>
+        <v>176.717648</v>
       </c>
       <c r="M9" s="12">
-        <f t="shared" ref="M9:M31" si="15">F9/(1+I9-H9)</f>
-        <v>357.64199510507217</v>
+        <f>F9/(1+I9-H9)</f>
+        <v>150.92052497265766</v>
       </c>
       <c r="N9" s="12">
-        <f t="shared" ref="N9:N31" si="16">L9-F9</f>
-        <v>4.830978000000016</v>
+        <f>L9-F9</f>
+        <v>11.127647999999994</v>
       </c>
       <c r="O9" s="12">
-        <f t="shared" ref="O9:O31" si="17">0.5*(M9-F9)</f>
-        <v>-33.064002447463906</v>
+        <f>0.5*(M9-F9)</f>
+        <v>-7.3347375136711719</v>
       </c>
       <c r="P9" s="15">
-        <f t="shared" ref="P9:P31" si="18">N9+O9</f>
-        <v>-28.23302444746389</v>
+        <f>N9+O9</f>
+        <v>3.7929104863288217</v>
       </c>
       <c r="Q9" s="12">
-        <f t="shared" ref="Q9:Q31" si="19">MAX($P$2:$P$280)-P9</f>
-        <v>111.66014580236165</v>
+        <f>MAX($P$2:$P$280)-P9</f>
+        <v>79.634210868568942</v>
       </c>
       <c r="R9" s="9">
-        <f t="shared" ref="R9:R31" si="20">IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q9)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>8.9557468585971488E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q9)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.2557417083600347E-2</v>
       </c>
       <c r="S9" s="9">
-        <f t="shared" ref="S9:S31" si="21">Q9/MAX($Q$2:$Q$28)</f>
-        <v>0.36872500946329412</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <f>Q9/MAX($Q$2:$Q$28)</f>
+        <v>0.26296871587547221</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>6</v>
+        <v>39</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="D10" s="8">
-        <v>45553</v>
+        <v>45562</v>
       </c>
       <c r="E10" s="2">
-        <v>1.0751999999999999</v>
+        <v>4.0300000000000002E-2</v>
       </c>
       <c r="F10" s="1">
-        <v>51.15</v>
+        <v>668.82</v>
       </c>
       <c r="G10" s="1">
-        <f t="shared" si="11"/>
-        <v>54.996479999999998</v>
+        <f>E10*F10</f>
+        <v>26.953446000000003</v>
       </c>
       <c r="H10" s="11">
-        <f>16.68%+7%/4</f>
-        <v>0.18430000000000002</v>
+        <f>553.57/F10-1</f>
+        <v>-0.17231841153075567</v>
       </c>
       <c r="I10" s="11">
-        <v>0.19980000000000001</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="J10" s="9">
-        <f t="shared" si="12"/>
-        <v>0.92242242242242245</v>
+        <f>IFERROR(H10/I10,"")</f>
+        <v>-0.61542289832412733</v>
       </c>
       <c r="K10" s="9">
-        <f t="shared" si="13"/>
-        <v>1.1115411963115487</v>
+        <f>IFERROR(J10/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>-9.826741830399055E-2</v>
       </c>
       <c r="L10" s="12">
-        <f t="shared" si="14"/>
-        <v>60.576944999999995</v>
+        <f>F10/(1-(F10*(1+H10)-F10)/(F10*(1+H10)))</f>
+        <v>553.57000000000005</v>
       </c>
       <c r="M10" s="12">
-        <f t="shared" si="15"/>
-        <v>50.369276218611525</v>
+        <f>F10/(1+I10-H10)</f>
+        <v>460.51884675555289</v>
       </c>
       <c r="N10" s="12">
-        <f t="shared" si="16"/>
-        <v>9.4269449999999964</v>
+        <f>L10-F10</f>
+        <v>-115.25</v>
       </c>
       <c r="O10" s="12">
-        <f t="shared" si="17"/>
-        <v>-0.39036189069423699</v>
+        <f>0.5*(M10-F10)</f>
+        <v>-104.15057662222358</v>
       </c>
       <c r="P10" s="15">
-        <f t="shared" si="18"/>
-        <v>9.0365831093057594</v>
+        <f>N10+O10</f>
+        <v>-219.40057662222358</v>
       </c>
       <c r="Q10" s="12">
-        <f t="shared" si="19"/>
-        <v>74.390538245592012</v>
+        <f>MAX($P$2:$P$280)-P10</f>
+        <v>302.82769797712137</v>
       </c>
       <c r="R10" s="9">
-        <f t="shared" si="20"/>
-        <v>1.3442569762012102E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q10)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>3.3022078451871001E-3</v>
       </c>
       <c r="S10" s="9">
-        <f t="shared" si="21"/>
-        <v>0.24565301900228498</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <f>Q10/MAX($Q$2:$Q$28)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>14</v>
+        <v>39</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="D11" s="8">
-        <v>45482</v>
+        <v>45580</v>
       </c>
       <c r="E11" s="2">
-        <v>0.18820000000000001</v>
+        <v>0.19139999999999999</v>
       </c>
       <c r="F11" s="1">
-        <v>227.38</v>
+        <v>135.82</v>
       </c>
       <c r="G11" s="1">
-        <f t="shared" si="11"/>
-        <v>42.792915999999998</v>
+        <f>E11*F11</f>
+        <v>25.995947999999999</v>
       </c>
       <c r="H11" s="11">
-        <v>4.9299999999999997E-2</v>
+        <v>0.1202</v>
       </c>
       <c r="I11" s="11">
-        <v>0.2271</v>
+        <v>0.33710000000000001</v>
       </c>
       <c r="J11" s="9">
-        <f t="shared" si="12"/>
-        <v>0.21708498458828709</v>
+        <f>IFERROR(H11/I11,"")</f>
+        <v>0.35657075051913378</v>
       </c>
       <c r="K11" s="9">
-        <f t="shared" si="13"/>
-        <v>0.26159262568319935</v>
+        <f>IFERROR(J11/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>5.6935299599101506E-2</v>
       </c>
       <c r="L11" s="12">
-        <f t="shared" si="14"/>
-        <v>238.58983399999997</v>
+        <f>F11/(1-(F11*(1+H11)-F11)/(F11*(1+H11)))</f>
+        <v>152.14556400000001</v>
       </c>
       <c r="M11" s="12">
-        <f t="shared" si="15"/>
-        <v>193.05484802173541</v>
+        <f>F11/(1+I11-H11)</f>
+        <v>111.61147177253677</v>
       </c>
       <c r="N11" s="12">
-        <f t="shared" si="16"/>
-        <v>11.209833999999972</v>
+        <f>L11-F11</f>
+        <v>16.325564000000014</v>
       </c>
       <c r="O11" s="12">
-        <f t="shared" si="17"/>
-        <v>-17.162575989132293</v>
+        <f>0.5*(M11-F11)</f>
+        <v>-12.10426411373161</v>
       </c>
       <c r="P11" s="15">
-        <f t="shared" si="18"/>
-        <v>-5.9527419891323206</v>
+        <f>N11+O11</f>
+        <v>4.2212998862684046</v>
       </c>
       <c r="Q11" s="12">
-        <f t="shared" si="19"/>
-        <v>89.379863344030085</v>
+        <f>MAX($P$2:$P$280)-P11</f>
+        <v>79.205821468629352</v>
       </c>
       <c r="R11" s="9">
-        <f t="shared" si="20"/>
-        <v>1.1188202382352295E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q11)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.2625334621345539E-2</v>
       </c>
       <c r="S11" s="9">
-        <f t="shared" si="21"/>
-        <v>0.29515088593640709</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <f>Q11/MAX($Q$2:$Q$28)</f>
+        <v>0.26155408503819672</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>7</v>
+        <v>39</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="D12" s="8">
-        <v>45511</v>
+        <v>45580</v>
       </c>
       <c r="E12" s="2">
-        <v>0.14610000000000001</v>
+        <v>0.18010000000000001</v>
       </c>
       <c r="F12" s="1">
-        <v>273.45999999999998</v>
+        <v>133.19999999999999</v>
       </c>
       <c r="G12" s="1">
-        <f t="shared" si="11"/>
-        <v>39.952506</v>
+        <f>E12*F12</f>
+        <v>23.989319999999999</v>
       </c>
       <c r="H12" s="11">
-        <v>0.16769999999999999</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="I12" s="11">
-        <v>0.16700000000000001</v>
+        <v>0.1623</v>
       </c>
       <c r="J12" s="9">
-        <f t="shared" si="12"/>
-        <v>1.0041916167664668</v>
+        <f>IFERROR(H12/I12,"")</f>
+        <v>3.0807147258163893E-2</v>
       </c>
       <c r="K12" s="9">
-        <f t="shared" si="13"/>
-        <v>1.2100750414276724</v>
+        <f>IFERROR(J12/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>4.9191195755218806E-3</v>
       </c>
       <c r="L12" s="12">
-        <f t="shared" si="14"/>
-        <v>319.31924199999997</v>
+        <f>F12/(1-(F12*(1+H12)-F12)/(F12*(1+H12)))</f>
+        <v>133.86599999999999</v>
       </c>
       <c r="M12" s="12">
-        <f t="shared" si="15"/>
-        <v>273.65155608926244</v>
+        <f>F12/(1+I12-H12)</f>
+        <v>115.09548086062384</v>
       </c>
       <c r="N12" s="12">
-        <f t="shared" si="16"/>
-        <v>45.859241999999995</v>
+        <f>L12-F12</f>
+        <v>0.66599999999999682</v>
       </c>
       <c r="O12" s="12">
-        <f t="shared" si="17"/>
-        <v>9.5778044631231296E-2</v>
+        <f>0.5*(M12-F12)</f>
+        <v>-9.0522595696880757</v>
       </c>
       <c r="P12" s="15">
-        <f t="shared" si="18"/>
-        <v>45.955020044631226</v>
+        <f>N12+O12</f>
+        <v>-8.3862595696880788</v>
       </c>
       <c r="Q12" s="12">
-        <f t="shared" si="19"/>
-        <v>37.472101310266538</v>
+        <f>MAX($P$2:$P$280)-P12</f>
+        <v>91.813380924585843</v>
       </c>
       <c r="R12" s="9">
-        <f t="shared" si="20"/>
-        <v>2.6686520505483952E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q12)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.0891658600627997E-2</v>
       </c>
       <c r="S12" s="9">
-        <f t="shared" si="21"/>
-        <v>0.12374066692240798</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <f>Q12/MAX($Q$2:$Q$28)</f>
+        <v>0.30318686678231904</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>36</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="D13" s="8">
-        <v>45544</v>
+        <v>45481</v>
       </c>
       <c r="E13" s="2">
-        <v>0.1928</v>
+        <v>2.8500000000000001E-2</v>
       </c>
       <c r="F13" s="1">
-        <v>188.12</v>
+        <v>700.32</v>
       </c>
       <c r="G13" s="1">
-        <f t="shared" si="11"/>
-        <v>36.269536000000002</v>
+        <f>E13*F13</f>
+        <v>19.959120000000002</v>
       </c>
       <c r="H13" s="11">
-        <v>-6.8599999999999994E-2</v>
+        <v>-6.6500000000000004E-2</v>
       </c>
       <c r="I13" s="11">
-        <v>0.37780000000000002</v>
+        <v>0.45340000000000003</v>
       </c>
       <c r="J13" s="9">
-        <f t="shared" si="12"/>
-        <v>-0.18157755426151401</v>
+        <f>IFERROR(H13/I13,"")</f>
+        <v>-0.14666960741067489</v>
       </c>
       <c r="K13" s="9">
-        <f t="shared" si="13"/>
-        <v>-0.21880531845391346</v>
+        <f>IFERROR(J13/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>-2.341941403733078E-2</v>
       </c>
       <c r="L13" s="12">
-        <f t="shared" si="14"/>
-        <v>175.214968</v>
+        <f>F13/(1-(F13*(1+H13)-F13)/(F13*(1+H13)))</f>
+        <v>653.74872000000005</v>
       </c>
       <c r="M13" s="12">
-        <f t="shared" si="15"/>
-        <v>130.06084070796459</v>
+        <f>F13/(1+I13-H13)</f>
+        <v>460.76715573392988</v>
       </c>
       <c r="N13" s="12">
-        <f t="shared" si="16"/>
-        <v>-12.905032000000006</v>
+        <f>L13-F13</f>
+        <v>-46.571280000000002</v>
       </c>
       <c r="O13" s="12">
-        <f t="shared" si="17"/>
-        <v>-29.029579646017709</v>
+        <f>0.5*(M13-F13)</f>
+        <v>-119.77642213303508</v>
       </c>
       <c r="P13" s="15">
-        <f t="shared" si="18"/>
-        <v>-41.934611646017714</v>
+        <f>N13+O13</f>
+        <v>-166.34770213303509</v>
       </c>
       <c r="Q13" s="12">
-        <f t="shared" si="19"/>
-        <v>125.36173300091548</v>
+        <f>MAX($P$2:$P$280)-P13</f>
+        <v>249.77482348793285</v>
       </c>
       <c r="R13" s="9">
-        <f t="shared" si="20"/>
-        <v>7.9769158902158552E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q13)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>4.0036060722041193E-3</v>
       </c>
       <c r="S13" s="9">
-        <f t="shared" si="21"/>
-        <v>0.4139704982018737</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <f>Q13/MAX($Q$2:$Q$28)</f>
+        <v>0.82480838165207504</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>19</v>
+        <v>40</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D14" s="8">
-        <v>45544</v>
+        <v>45511</v>
       </c>
       <c r="E14" s="2">
-        <v>0.24390000000000001</v>
+        <v>0.1933</v>
       </c>
       <c r="F14" s="1">
-        <v>144.28</v>
+        <v>77.53</v>
       </c>
       <c r="G14" s="1">
-        <f t="shared" si="11"/>
-        <v>35.189892</v>
+        <f>E14*F14</f>
+        <v>14.986549</v>
       </c>
       <c r="H14" s="11">
-        <v>-2.8000000000000001E-2</v>
+        <f>83.34/F14-1</f>
+        <v>7.4938733393525192E-2</v>
       </c>
       <c r="I14" s="11">
-        <v>0.18340000000000001</v>
+        <v>0.25990000000000002</v>
       </c>
       <c r="J14" s="9">
-        <f t="shared" si="12"/>
-        <v>-0.15267175572519084</v>
+        <f>IFERROR(H14/I14,"")</f>
+        <v>0.28833679643526428</v>
       </c>
       <c r="K14" s="9">
-        <f t="shared" si="13"/>
-        <v>-0.18397313625150449</v>
+        <f>IFERROR(J14/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>4.6040068812671704E-2</v>
       </c>
       <c r="L14" s="12">
-        <f t="shared" si="14"/>
-        <v>140.24016</v>
+        <f>F14/(1-(F14*(1+H14)-F14)/(F14*(1+H14)))</f>
+        <v>83.34</v>
       </c>
       <c r="M14" s="12">
-        <f t="shared" si="15"/>
-        <v>119.10186561003798</v>
+        <f>F14/(1+I14-H14)</f>
+        <v>65.428298953629579</v>
       </c>
       <c r="N14" s="12">
-        <f t="shared" si="16"/>
-        <v>-4.0398399999999981</v>
+        <f>L14-F14</f>
+        <v>5.8100000000000023</v>
       </c>
       <c r="O14" s="12">
-        <f t="shared" si="17"/>
-        <v>-12.589067194981013</v>
+        <f>0.5*(M14-F14)</f>
+        <v>-6.0508505231852112</v>
       </c>
       <c r="P14" s="15">
-        <f t="shared" si="18"/>
-        <v>-16.628907194981011</v>
+        <f>N14+O14</f>
+        <v>-0.24085052318520894</v>
       </c>
       <c r="Q14" s="12">
-        <f t="shared" si="19"/>
-        <v>100.05602854987877</v>
+        <f>MAX($P$2:$P$280)-P14</f>
+        <v>83.667971878082966</v>
       </c>
       <c r="R14" s="9">
-        <f t="shared" si="20"/>
-        <v>9.9944002824526607E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q14)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.1952004782154311E-2</v>
       </c>
       <c r="S14" s="9">
-        <f t="shared" si="21"/>
-        <v>0.33040580243567419</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <f>Q14/MAX($Q$2:$Q$28)</f>
+        <v>0.27628903312669928</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="8">
+        <v>45511</v>
+      </c>
+      <c r="E15" s="2">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="F15" s="1">
+        <v>455.4</v>
+      </c>
+      <c r="G15" s="1">
+        <f>E15*F15</f>
+        <v>14.982659999999999</v>
+      </c>
+      <c r="H15" s="11">
+        <v>0.17460000000000001</v>
+      </c>
+      <c r="I15" s="11">
+        <v>0.15770000000000001</v>
+      </c>
+      <c r="J15" s="9">
+        <f>IFERROR(H15/I15,"")</f>
+        <v>1.1071655041217501</v>
+      </c>
+      <c r="K15" s="9">
+        <f>IFERROR(J15/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>0.1767862327215185</v>
+      </c>
+      <c r="L15" s="12">
+        <f>F15/(1-(F15*(1+H15)-F15)/(F15*(1+H15)))</f>
+        <v>534.91283999999996</v>
+      </c>
+      <c r="M15" s="12">
+        <f>F15/(1+I15-H15)</f>
+        <v>463.22856270979554</v>
+      </c>
+      <c r="N15" s="12">
+        <f>L15-F15</f>
+        <v>79.512839999999983</v>
+      </c>
+      <c r="O15" s="12">
+        <f>0.5*(M15-F15)</f>
+        <v>3.9142813548977813</v>
+      </c>
+      <c r="P15" s="15">
+        <f>N15+O15</f>
+        <v>83.427121354897764</v>
+      </c>
+      <c r="Q15" s="12">
+        <f>MAX($P$2:$P$280)-P15</f>
+        <v>0</v>
+      </c>
+      <c r="R15" s="9">
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q15)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>0</v>
+      </c>
+      <c r="S15" s="9">
+        <f>Q15/MAX($Q$2:$Q$28)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="8">
+        <v>45511</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1</v>
+      </c>
+      <c r="F16" s="1">
+        <v>10.4</v>
+      </c>
+      <c r="G16" s="1">
+        <f>E16*F16</f>
+        <v>10.4</v>
+      </c>
+      <c r="H16" s="11">
+        <f>2.89/F16-1</f>
+        <v>-0.7221153846153846</v>
+      </c>
+      <c r="I16" s="13">
+        <v>1.8652</v>
+      </c>
+      <c r="J16" s="9">
+        <f>IFERROR(H16/I16,"")</f>
+        <v>-0.38715171810818388</v>
+      </c>
+      <c r="K16" s="9">
+        <f>IFERROR(J16/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>-6.1818304021584419E-2</v>
+      </c>
+      <c r="L16" s="12">
+        <f>F16/(1-(F16*(1+H16)-F16)/(F16*(1+H16)))</f>
+        <v>2.8900000000000006</v>
+      </c>
+      <c r="M16" s="12">
+        <f>F16/(1+I16-H16)</f>
+        <v>2.8991038938481961</v>
+      </c>
+      <c r="N16" s="12">
+        <f>L16-F16</f>
+        <v>-7.51</v>
+      </c>
+      <c r="O16" s="12">
+        <f>0.5*(M16-F16)</f>
+        <v>-3.7504480530759023</v>
+      </c>
+      <c r="P16" s="15">
+        <f>N16+O16</f>
+        <v>-11.260448053075901</v>
+      </c>
+      <c r="Q16" s="12">
+        <f>MAX($P$2:$P$280)-P16</f>
+        <v>94.687569407973669</v>
+      </c>
+      <c r="R16" s="9">
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q16)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.0561048364135003E-2</v>
+      </c>
+      <c r="S16" s="9">
+        <f>Q16/MAX($Q$2:$Q$28)</f>
+        <v>0.31267803454070875</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="8">
-        <v>45484</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0.24990000000000001</v>
-      </c>
-      <c r="F15" s="1">
-        <v>191.91</v>
-      </c>
-      <c r="G15" s="1">
-        <f t="shared" si="11"/>
-        <v>47.958309</v>
-      </c>
-      <c r="H15" s="11">
-        <f>227.4/F15-1</f>
-        <v>0.18493043614194149</v>
-      </c>
-      <c r="I15" s="11">
-        <v>0.37</v>
-      </c>
-      <c r="J15" s="9">
-        <f t="shared" si="12"/>
-        <v>0.49981198957281486</v>
-      </c>
-      <c r="K15" s="9">
-        <f t="shared" si="13"/>
-        <v>0.60228546413868833</v>
-      </c>
-      <c r="L15" s="12">
-        <f t="shared" si="14"/>
-        <v>227.39999999999998</v>
-      </c>
-      <c r="M15" s="12">
-        <f t="shared" si="15"/>
-        <v>161.93986062322494</v>
-      </c>
-      <c r="N15" s="12">
-        <f t="shared" si="16"/>
-        <v>35.489999999999981</v>
-      </c>
-      <c r="O15" s="12">
-        <f t="shared" si="17"/>
-        <v>-14.985069688387526</v>
-      </c>
-      <c r="P15" s="15">
-        <f t="shared" si="18"/>
-        <v>20.504930311612455</v>
-      </c>
-      <c r="Q15" s="12">
-        <f t="shared" si="19"/>
-        <v>62.922191043285309</v>
-      </c>
-      <c r="R15" s="9">
-        <f t="shared" si="20"/>
-        <v>1.5892644286847578E-2</v>
-      </c>
-      <c r="S15" s="9">
-        <f t="shared" si="21"/>
-        <v>0.20778215289949825</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>74</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" t="s">
-        <v>76</v>
-      </c>
-      <c r="D16" s="8">
-        <v>45562</v>
-      </c>
-      <c r="E16" s="2">
-        <v>1E-35</v>
-      </c>
-      <c r="F16" s="1">
-        <v>56</v>
-      </c>
-      <c r="G16" s="1">
-        <f t="shared" si="11"/>
-        <v>5.5999999999999999E-34</v>
-      </c>
-      <c r="H16" s="11">
-        <v>0.08</v>
-      </c>
-      <c r="I16" s="11">
-        <v>0.19</v>
-      </c>
-      <c r="J16" s="9">
-        <f t="shared" si="12"/>
-        <v>0.42105263157894735</v>
-      </c>
-      <c r="K16" s="9">
-        <f t="shared" si="13"/>
-        <v>0.5073785441883597</v>
-      </c>
-      <c r="L16" s="12">
-        <f t="shared" si="14"/>
-        <v>60.480000000000004</v>
-      </c>
-      <c r="M16" s="12">
-        <f t="shared" si="15"/>
-        <v>50.450450450450454</v>
-      </c>
-      <c r="N16" s="12">
-        <f t="shared" si="16"/>
-        <v>4.480000000000004</v>
-      </c>
-      <c r="O16" s="12">
-        <f t="shared" si="17"/>
-        <v>-2.7747747747747731</v>
-      </c>
-      <c r="P16" s="15">
-        <f t="shared" si="18"/>
-        <v>1.7052252252252309</v>
-      </c>
-      <c r="Q16" s="12">
-        <f t="shared" si="19"/>
-        <v>81.72189612967253</v>
-      </c>
-      <c r="R16" s="9">
-        <f t="shared" si="20"/>
-        <v>1.2236622586598408E-2</v>
-      </c>
-      <c r="S16" s="9">
-        <f t="shared" si="21"/>
-        <v>0.26986268652296996</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>56</v>
+      <c r="B17" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="D17" s="8">
-        <v>45505</v>
+        <v>45482</v>
       </c>
       <c r="E17" s="2">
-        <v>1E-35</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F17" s="1">
-        <v>86.6</v>
+        <v>147.01</v>
       </c>
       <c r="G17" s="1">
-        <f t="shared" si="11"/>
-        <v>8.6599999999999988E-34</v>
+        <f>E17*F17</f>
+        <v>1.4700999999999999E-17</v>
       </c>
       <c r="H17" s="11">
-        <f>89.44/F17-1</f>
-        <v>3.2794457274826883E-2</v>
+        <f>193.73/F17-1</f>
+        <v>0.3178015101013536</v>
       </c>
       <c r="I17" s="11">
-        <v>0.17249999999999999</v>
+        <v>0.52380000000000004</v>
       </c>
       <c r="J17" s="9">
-        <f t="shared" si="12"/>
-        <v>0.19011279579609788</v>
+        <f>IFERROR(H17/I17,"")</f>
+        <v>0.60672300515722333</v>
       </c>
       <c r="K17" s="9">
-        <f t="shared" si="13"/>
-        <v>0.22909048971118229</v>
+        <f>IFERROR(J17/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>9.6878266156158174E-2</v>
       </c>
       <c r="L17" s="12">
-        <f t="shared" si="14"/>
-        <v>89.44</v>
+        <f>F17/(1-(F17*(1+H17)-F17)/(F17*(1+H17)))</f>
+        <v>193.72999999999996</v>
       </c>
       <c r="M17" s="12">
-        <f t="shared" si="15"/>
-        <v>75.984538772119137</v>
+        <f>F17/(1+I17-H17)</f>
+        <v>121.89899177432211</v>
       </c>
       <c r="N17" s="12">
-        <f t="shared" si="16"/>
-        <v>2.8400000000000034</v>
+        <f>L17-F17</f>
+        <v>46.71999999999997</v>
       </c>
       <c r="O17" s="12">
-        <f t="shared" si="17"/>
-        <v>-5.3077306139404286</v>
+        <f>0.5*(M17-F17)</f>
+        <v>-12.555504112838939</v>
       </c>
       <c r="P17" s="15">
-        <f t="shared" si="18"/>
-        <v>-2.4677306139404251</v>
+        <f>N17+O17</f>
+        <v>34.164495887161031</v>
       </c>
       <c r="Q17" s="12">
-        <f t="shared" si="19"/>
-        <v>85.894851968838196</v>
+        <f>MAX($P$2:$P$280)-P17</f>
+        <v>49.262625467736733</v>
       </c>
       <c r="R17" s="9">
-        <f t="shared" si="20"/>
-        <v>1.1642141258509767E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q17)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>2.0299364690883635E-2</v>
       </c>
       <c r="S17" s="9">
-        <f t="shared" si="21"/>
-        <v>0.28364265403268213</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <f>Q17/MAX($Q$2:$Q$28)</f>
+        <v>0.16267542829407408</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>15</v>
+        <v>40</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="D18" s="8">
-        <v>45460</v>
+        <v>45511</v>
       </c>
       <c r="E18" s="2">
-        <v>0.1807</v>
+        <v>1E-22</v>
       </c>
       <c r="F18" s="1">
-        <v>165.59</v>
+        <v>187.36</v>
       </c>
       <c r="G18" s="1">
-        <f t="shared" si="11"/>
-        <v>29.922113</v>
+        <f>E18*F18</f>
+        <v>1.8736000000000003E-20</v>
       </c>
       <c r="H18" s="11">
-        <v>6.7199999999999996E-2</v>
+        <f>196.02/F18-1</f>
+        <v>4.6221178479931568E-2</v>
       </c>
       <c r="I18" s="11">
-        <v>0.16439999999999999</v>
+        <v>0.52980000000000005</v>
       </c>
       <c r="J18" s="9">
-        <f t="shared" si="12"/>
-        <v>0.40875912408759124</v>
+        <f>IFERROR(H18/I18,"")</f>
+        <v>8.7242692487602053E-2</v>
       </c>
       <c r="K18" s="9">
-        <f t="shared" si="13"/>
-        <v>0.49256457209526899</v>
+        <f>IFERROR(J18/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>1.3930443894744987E-2</v>
       </c>
       <c r="L18" s="12">
-        <f t="shared" si="14"/>
-        <v>176.717648</v>
+        <f>F18/(1-(F18*(1+H18)-F18)/(F18*(1+H18)))</f>
+        <v>196.01999999999998</v>
       </c>
       <c r="M18" s="12">
-        <f t="shared" si="15"/>
-        <v>150.92052497265766</v>
+        <f>F18/(1+I18-H18)</f>
+        <v>126.28921179127629</v>
       </c>
       <c r="N18" s="12">
-        <f t="shared" si="16"/>
-        <v>11.127647999999994</v>
+        <f>L18-F18</f>
+        <v>8.6599999999999682</v>
       </c>
       <c r="O18" s="12">
-        <f t="shared" si="17"/>
-        <v>-7.3347375136711719</v>
+        <f>0.5*(M18-F18)</f>
+        <v>-30.535394104361863</v>
       </c>
       <c r="P18" s="15">
-        <f t="shared" si="18"/>
-        <v>3.7929104863288217</v>
+        <f>N18+O18</f>
+        <v>-21.875394104361895</v>
       </c>
       <c r="Q18" s="12">
-        <f t="shared" si="19"/>
-        <v>79.634210868568942</v>
+        <f>MAX($P$2:$P$280)-P18</f>
+        <v>105.30251545925967</v>
       </c>
       <c r="R18" s="9">
-        <f t="shared" si="20"/>
-        <v>1.2557417083600347E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q18)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.4964493073946415E-3</v>
       </c>
       <c r="S18" s="9">
-        <f t="shared" si="21"/>
-        <v>0.26296871587547221</v>
+        <f>Q18/MAX($Q$2:$Q$28)</f>
+        <v>0.34773079266750317</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>77</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>78</v>
+        <v>36</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="D19" s="8">
-        <v>45580</v>
+        <v>45481</v>
       </c>
       <c r="E19" s="2">
-        <v>1E-35</v>
+        <v>1E-22</v>
       </c>
       <c r="F19" s="1">
-        <v>20.399999999999999</v>
+        <v>169.34</v>
       </c>
       <c r="G19" s="1">
-        <f t="shared" si="11"/>
-        <v>2.0399999999999999E-34</v>
+        <f>E19*F19</f>
+        <v>1.6934000000000002E-20</v>
       </c>
       <c r="H19" s="11">
-        <f>L19/F19-1</f>
-        <v>3.9215686274509887E-2</v>
+        <f>174.52/F19-1</f>
+        <v>3.0589346876107371E-2</v>
       </c>
       <c r="I19" s="11">
-        <v>0.15</v>
+        <v>0.4259</v>
       </c>
       <c r="J19" s="9">
-        <f t="shared" si="12"/>
-        <v>0.2614379084967326</v>
+        <f>IFERROR(H19/I19,"")</f>
+        <v>7.1822838403633182E-2</v>
       </c>
       <c r="K19" s="9">
-        <f t="shared" si="13"/>
-        <v>0.31503896534571424</v>
+        <f>IFERROR(J19/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>1.1468284531513408E-2</v>
       </c>
       <c r="L19" s="12">
-        <v>21.2</v>
+        <f>F19/(1-(F19*(1+H19)-F19)/(F19*(1+H19)))</f>
+        <v>174.52000000000004</v>
       </c>
       <c r="M19" s="12">
-        <f t="shared" si="15"/>
-        <v>18.365401588702561</v>
+        <f>F19/(1+I19-H19)</f>
+        <v>121.36365448143965</v>
       </c>
       <c r="N19" s="12">
-        <f t="shared" si="16"/>
-        <v>0.80000000000000071</v>
+        <f>L19-F19</f>
+        <v>5.1800000000000352</v>
       </c>
       <c r="O19" s="12">
-        <f t="shared" si="17"/>
-        <v>-1.0172992056487189</v>
+        <f>0.5*(M19-F19)</f>
+        <v>-23.988172759280175</v>
       </c>
       <c r="P19" s="15">
-        <f t="shared" si="18"/>
-        <v>-0.21729920564871819</v>
+        <f>N19+O19</f>
+        <v>-18.80817275928014</v>
       </c>
       <c r="Q19" s="12">
-        <f t="shared" si="19"/>
-        <v>83.644420560546479</v>
+        <f>MAX($P$2:$P$280)-P19</f>
+        <v>102.2352941141779</v>
       </c>
       <c r="R19" s="9">
-        <f t="shared" si="20"/>
-        <v>1.1955370044988768E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q19)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.7813578829556158E-3</v>
       </c>
       <c r="S19" s="9">
-        <f t="shared" si="21"/>
-        <v>0.27621126178116578</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <f>Q19/MAX($Q$2:$Q$28)</f>
+        <v>0.33760219027884886</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>32</v>
       </c>
       <c r="D20" s="8">
-        <v>45562</v>
+        <v>45511</v>
       </c>
       <c r="E20" s="2">
-        <v>4.0300000000000002E-2</v>
+        <v>1E-22</v>
       </c>
       <c r="F20" s="1">
-        <v>668.82</v>
+        <v>113.58</v>
       </c>
       <c r="G20" s="1">
-        <f t="shared" si="11"/>
-        <v>26.953446000000003</v>
+        <f>E20*F20</f>
+        <v>1.1358E-20</v>
       </c>
       <c r="H20" s="11">
-        <f>553.57/F20-1</f>
-        <v>-0.17231841153075567</v>
+        <f>121.15/F20-1</f>
+        <v>6.664905793273479E-2</v>
       </c>
       <c r="I20" s="11">
-        <v>0.28000000000000003</v>
+        <v>0.16439999999999999</v>
       </c>
       <c r="J20" s="9">
-        <f t="shared" si="12"/>
-        <v>-0.61542289832412733</v>
+        <f>IFERROR(H20/I20,"")</f>
+        <v>0.40540789496797319</v>
       </c>
       <c r="K20" s="9">
-        <f t="shared" si="13"/>
-        <v>-0.74159938875320708</v>
+        <f>IFERROR(J20/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>6.4733352150274134E-2</v>
       </c>
       <c r="L20" s="12">
-        <f t="shared" si="14"/>
-        <v>553.57000000000005</v>
+        <f>F20/(1-(F20*(1+H20)-F20)/(F20*(1+H20)))</f>
+        <v>121.15000000000002</v>
       </c>
       <c r="M20" s="12">
-        <f t="shared" si="15"/>
-        <v>460.51884675555289</v>
+        <f>F20/(1+I20-H20)</f>
+        <v>103.46609203186667</v>
       </c>
       <c r="N20" s="12">
-        <f t="shared" si="16"/>
-        <v>-115.25</v>
+        <f>L20-F20</f>
+        <v>7.5700000000000216</v>
       </c>
       <c r="O20" s="12">
-        <f t="shared" si="17"/>
-        <v>-104.15057662222358</v>
+        <f>0.5*(M20-F20)</f>
+        <v>-5.0569539840666664</v>
       </c>
       <c r="P20" s="15">
-        <f t="shared" si="18"/>
-        <v>-219.40057662222358</v>
+        <f>N20+O20</f>
+        <v>2.5130460159333552</v>
       </c>
       <c r="Q20" s="12">
-        <f t="shared" si="19"/>
-        <v>302.82769797712137</v>
+        <f>MAX($P$2:$P$280)-P20</f>
+        <v>80.914075338964409</v>
       </c>
       <c r="R20" s="9">
-        <f t="shared" si="20"/>
-        <v>3.3022078451871006E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q20)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.2358789194720577E-2</v>
       </c>
       <c r="S20" s="9">
-        <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <f>Q20/MAX($Q$2:$Q$28)</f>
+        <v>0.26719509437038835</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>42</v>
+        <v>36</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>86</v>
       </c>
       <c r="C21" t="s">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="D21" s="8">
-        <v>45580</v>
+        <v>45481</v>
       </c>
       <c r="E21" s="2">
-        <v>0.19139999999999999</v>
+        <v>1E-22</v>
       </c>
       <c r="F21" s="1">
-        <v>135.82</v>
+        <v>64.349999999999994</v>
       </c>
       <c r="G21" s="1">
-        <f t="shared" si="11"/>
-        <v>25.995947999999999</v>
+        <f>E21*F21</f>
+        <v>6.4349999999999995E-21</v>
       </c>
       <c r="H21" s="11">
-        <v>0.1202</v>
+        <f>75.53/F21-1</f>
+        <v>0.17373737373737397</v>
       </c>
       <c r="I21" s="11">
-        <v>0.33710000000000001</v>
+        <v>0.67300000000000004</v>
       </c>
       <c r="J21" s="9">
-        <f t="shared" si="12"/>
-        <v>0.35657075051913378</v>
+        <f>IFERROR(H21/I21,"")</f>
+        <v>0.25815360139282906</v>
       </c>
       <c r="K21" s="9">
-        <f t="shared" si="13"/>
-        <v>0.42967632720905369</v>
+        <f>IFERROR(J21/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>4.1220578570981374E-2</v>
       </c>
       <c r="L21" s="12">
-        <f t="shared" si="14"/>
-        <v>152.14556400000001</v>
+        <f>F21/(1-(F21*(1+H21)-F21)/(F21*(1+H21)))</f>
+        <v>75.53</v>
       </c>
       <c r="M21" s="12">
-        <f t="shared" si="15"/>
-        <v>111.61147177253677</v>
+        <f>F21/(1+I21-H21)</f>
+        <v>42.921099260916144</v>
       </c>
       <c r="N21" s="12">
-        <f t="shared" si="16"/>
-        <v>16.325564000000014</v>
+        <f>L21-F21</f>
+        <v>11.180000000000007</v>
       </c>
       <c r="O21" s="12">
-        <f t="shared" si="17"/>
-        <v>-12.10426411373161</v>
+        <f>0.5*(M21-F21)</f>
+        <v>-10.714450369541925</v>
       </c>
       <c r="P21" s="15">
-        <f t="shared" si="18"/>
-        <v>4.2212998862684046</v>
+        <f>N21+O21</f>
+        <v>0.46554963045808151</v>
       </c>
       <c r="Q21" s="12">
-        <f t="shared" si="19"/>
-        <v>79.205821468629352</v>
+        <f>MAX($P$2:$P$280)-P21</f>
+        <v>82.961571724439679</v>
       </c>
       <c r="R21" s="9">
-        <f t="shared" si="20"/>
-        <v>1.2625334621345541E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q21)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.2053773563036411E-2</v>
       </c>
       <c r="S21" s="9">
-        <f t="shared" si="21"/>
-        <v>0.26155408503819672</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <f>Q21/MAX($Q$2:$Q$28)</f>
+        <v>0.27395635299749704</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>39</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C22" t="s">
-        <v>61</v>
+        <v>40</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>48</v>
       </c>
       <c r="D22" s="8">
-        <v>45580</v>
+        <v>45511</v>
       </c>
       <c r="E22" s="2">
-        <v>0.18010000000000001</v>
+        <v>1E-22</v>
       </c>
       <c r="F22" s="1">
-        <v>133.19999999999999</v>
+        <v>20.82</v>
       </c>
       <c r="G22" s="1">
-        <f t="shared" si="11"/>
-        <v>23.989319999999999</v>
-      </c>
-      <c r="H22" s="11">
-        <v>5.0000000000000001E-3</v>
+        <f>E22*F22</f>
+        <v>2.0820000000000001E-21</v>
+      </c>
+      <c r="H22" s="13">
+        <f>19.07/F22-1</f>
+        <v>-8.4053794428434192E-2</v>
       </c>
       <c r="I22" s="11">
-        <v>0.1623</v>
+        <v>0.7389</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" si="12"/>
-        <v>3.0807147258163893E-2</v>
+        <f>IFERROR(H22/I22,"")</f>
+        <v>-0.11375530440984462</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" si="13"/>
-        <v>3.7123353125303585E-2</v>
+        <f>IFERROR(J22/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>-1.8163835166322632E-2</v>
       </c>
       <c r="L22" s="12">
-        <f t="shared" si="14"/>
-        <v>133.86599999999999</v>
+        <f>F22/(1-(F22*(1+H22)-F22)/(F22*(1+H22)))</f>
+        <v>19.070000000000004</v>
       </c>
       <c r="M22" s="12">
-        <f t="shared" si="15"/>
-        <v>115.09548086062384</v>
+        <f>F22/(1+I22-H22)</f>
+        <v>11.421024528231593</v>
       </c>
       <c r="N22" s="12">
-        <f t="shared" si="16"/>
-        <v>0.66599999999999682</v>
+        <f>L22-F22</f>
+        <v>-1.7499999999999964</v>
       </c>
       <c r="O22" s="12">
-        <f t="shared" si="17"/>
-        <v>-9.0522595696880757</v>
+        <f>0.5*(M22-F22)</f>
+        <v>-4.6994877358842038</v>
       </c>
       <c r="P22" s="15">
-        <f t="shared" si="18"/>
-        <v>-8.3862595696880788</v>
+        <f>N22+O22</f>
+        <v>-6.4494877358842002</v>
       </c>
       <c r="Q22" s="12">
-        <f t="shared" si="19"/>
-        <v>91.813380924585843</v>
+        <f>MAX($P$2:$P$280)-P22</f>
+        <v>89.876609090781969</v>
       </c>
       <c r="R22" s="9">
-        <f t="shared" si="20"/>
-        <v>1.0891658600627999E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q22)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.1126365470574514E-2</v>
       </c>
       <c r="S22" s="9">
-        <f t="shared" si="21"/>
-        <v>0.30318686678231904</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <f>Q22/MAX($Q$2:$Q$28)</f>
+        <v>0.29679124363839449</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>36</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>23</v>
+        <v>40</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="C23" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="D23" s="8">
-        <v>45482</v>
+        <v>45511</v>
       </c>
       <c r="E23" s="2">
-        <v>0.15210000000000001</v>
+        <v>1E-22</v>
       </c>
       <c r="F23" s="1">
-        <v>147.01</v>
+        <v>13.04</v>
       </c>
       <c r="G23" s="1">
-        <f t="shared" si="11"/>
-        <v>22.360220999999999</v>
+        <f>E23*F23</f>
+        <v>1.304E-21</v>
       </c>
       <c r="H23" s="11">
-        <f>193.73/F23-1</f>
-        <v>0.3178015101013536</v>
+        <f>13.72/F23-1</f>
+        <v>5.2147239263803824E-2</v>
       </c>
       <c r="I23" s="11">
-        <v>0.52380000000000004</v>
+        <v>0.30159999999999998</v>
       </c>
       <c r="J23" s="9">
-        <f t="shared" si="12"/>
-        <v>0.60672300515722333</v>
+        <f>IFERROR(H23/I23,"")</f>
+        <v>0.17290198694895167</v>
       </c>
       <c r="K23" s="9">
-        <f t="shared" si="13"/>
-        <v>0.73111580832036438</v>
+        <f>IFERROR(J23/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>2.7608059309088662E-2</v>
       </c>
       <c r="L23" s="12">
-        <f t="shared" si="14"/>
-        <v>193.72999999999996</v>
+        <f>F23/(1-(F23*(1+H23)-F23)/(F23*(1+H23)))</f>
+        <v>13.72</v>
       </c>
       <c r="M23" s="12">
-        <f t="shared" si="15"/>
-        <v>121.89899177432211</v>
+        <f>F23/(1+I23-H23)</f>
+        <v>10.436569040286594</v>
       </c>
       <c r="N23" s="12">
-        <f t="shared" si="16"/>
-        <v>46.71999999999997</v>
+        <f>L23-F23</f>
+        <v>0.68000000000000149</v>
       </c>
       <c r="O23" s="12">
-        <f t="shared" si="17"/>
-        <v>-12.555504112838939</v>
+        <f>0.5*(M23-F23)</f>
+        <v>-1.3017154798567026</v>
       </c>
       <c r="P23" s="15">
-        <f t="shared" si="18"/>
-        <v>34.164495887161031</v>
+        <f>N23+O23</f>
+        <v>-0.62171547985670106</v>
       </c>
       <c r="Q23" s="12">
-        <f t="shared" si="19"/>
-        <v>49.262625467736733</v>
+        <f>MAX($P$2:$P$280)-P23</f>
+        <v>84.048836834754468</v>
       </c>
       <c r="R23" s="9">
-        <f t="shared" si="20"/>
-        <v>2.0299364690883635E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q23)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.1897844606297952E-2</v>
       </c>
       <c r="S23" s="9">
-        <f t="shared" si="21"/>
-        <v>0.16267542829407408</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <f>Q23/MAX($Q$2:$Q$28)</f>
+        <v>0.27754672837457672</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>62</v>
+        <v>40</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>45</v>
       </c>
       <c r="C24" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="D24" s="8">
-        <v>45481</v>
+        <v>45511</v>
       </c>
       <c r="E24" s="2">
-        <v>2.8500000000000001E-2</v>
+        <v>1E-22</v>
       </c>
       <c r="F24" s="1">
-        <v>700.32</v>
+        <v>11.05</v>
       </c>
       <c r="G24" s="1">
-        <f t="shared" si="11"/>
-        <v>19.959120000000002</v>
+        <f>E24*F24</f>
+        <v>1.1050000000000002E-21</v>
       </c>
       <c r="H24" s="11">
-        <v>-6.6500000000000004E-2</v>
+        <f>9.52/F24-1</f>
+        <v>-0.13846153846153852</v>
       </c>
       <c r="I24" s="11">
-        <v>0.45340000000000003</v>
+        <v>0.72170000000000001</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" si="12"/>
-        <v>-0.14666960741067489</v>
+        <f>IFERROR(H24/I24,"")</f>
+        <v>-0.19185470203898922</v>
       </c>
       <c r="K24" s="9">
-        <f t="shared" si="13"/>
-        <v>-0.1767404032261779</v>
+        <f>IFERROR(J24/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>-3.0634326915998825E-2</v>
       </c>
       <c r="L24" s="12">
-        <f t="shared" si="14"/>
-        <v>653.74872000000005</v>
+        <f>F24/(1-(F24*(1+H24)-F24)/(F24*(1+H24)))</f>
+        <v>9.52</v>
       </c>
       <c r="M24" s="12">
-        <f t="shared" si="15"/>
-        <v>460.76715573392988</v>
+        <f>F24/(1+I24-H24)</f>
+        <v>5.9403443042581081</v>
       </c>
       <c r="N24" s="12">
-        <f t="shared" si="16"/>
-        <v>-46.571280000000002</v>
+        <f>L24-F24</f>
+        <v>-1.5300000000000011</v>
       </c>
       <c r="O24" s="12">
-        <f t="shared" si="17"/>
-        <v>-119.77642213303508</v>
+        <f>0.5*(M24-F24)</f>
+        <v>-2.5548278478709463</v>
       </c>
       <c r="P24" s="15">
-        <f t="shared" si="18"/>
-        <v>-166.34770213303509</v>
+        <f>N24+O24</f>
+        <v>-4.0848278478709474</v>
       </c>
       <c r="Q24" s="12">
-        <f t="shared" si="19"/>
-        <v>249.77482348793285</v>
+        <f>MAX($P$2:$P$280)-P24</f>
+        <v>87.511949202768704</v>
       </c>
       <c r="R24" s="9">
-        <f t="shared" si="20"/>
-        <v>4.0036060722041193E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q24)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.1427010929478438E-2</v>
       </c>
       <c r="S24" s="9">
-        <f t="shared" si="21"/>
-        <v>0.82480838165207504</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <f>Q24/MAX($Q$2:$Q$28)</f>
+        <v>0.28898264520499783</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>18</v>
+        <v>40</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="C25" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="D25" s="8">
-        <v>45483</v>
+        <v>45511</v>
       </c>
       <c r="E25" s="2">
-        <v>9.9999999999999997E-29</v>
+        <v>1E-22</v>
       </c>
       <c r="F25" s="1">
-        <v>178.12</v>
+        <v>10.47</v>
       </c>
       <c r="G25" s="1">
-        <f t="shared" si="11"/>
-        <v>1.7812E-26</v>
+        <f>E25*F25</f>
+        <v>1.0470000000000001E-21</v>
       </c>
       <c r="H25" s="11">
-        <f>190.41/F25-1</f>
-        <v>6.8998428026049829E-2</v>
+        <f>6.42/F25-1</f>
+        <v>-0.38681948424068768</v>
       </c>
       <c r="I25" s="11">
-        <v>0.26790000000000003</v>
+        <v>0.85599999999999998</v>
       </c>
       <c r="J25" s="9">
-        <f t="shared" si="12"/>
-        <v>0.25755292282959996</v>
+        <f>IFERROR(H25/I25,"")</f>
+        <v>-0.45189192084192487</v>
       </c>
       <c r="K25" s="9">
-        <f t="shared" si="13"/>
-        <v>0.31035746421225607</v>
+        <f>IFERROR(J25/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>-7.2155671383841796E-2</v>
       </c>
       <c r="L25" s="12">
-        <f t="shared" si="14"/>
-        <v>190.41</v>
+        <f>F25/(1-(F25*(1+H25)-F25)/(F25*(1+H25)))</f>
+        <v>6.419999999999999</v>
       </c>
       <c r="M25" s="12">
-        <f t="shared" si="15"/>
-        <v>148.56932726072878</v>
+        <f>F25/(1+I25-H25)</f>
+        <v>4.6682312480197874</v>
       </c>
       <c r="N25" s="12">
-        <f t="shared" si="16"/>
-        <v>12.289999999999992</v>
+        <f>L25-F25</f>
+        <v>-4.0500000000000016</v>
       </c>
       <c r="O25" s="12">
-        <f t="shared" si="17"/>
-        <v>-14.77533636963561</v>
+        <f>0.5*(M25-F25)</f>
+        <v>-2.9008843759901066</v>
       </c>
       <c r="P25" s="15">
-        <f t="shared" si="18"/>
-        <v>-2.4853363696356183</v>
+        <f>N25+O25</f>
+        <v>-6.9508843759901087</v>
       </c>
       <c r="Q25" s="12">
-        <f t="shared" si="19"/>
-        <v>85.912457724533382</v>
+        <f>MAX($P$2:$P$280)-P25</f>
+        <v>90.378005730887878</v>
       </c>
       <c r="R25" s="9">
-        <f t="shared" si="20"/>
-        <v>1.1639755473023063E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q25)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.1064638923076357E-2</v>
       </c>
       <c r="S25" s="9">
-        <f t="shared" si="21"/>
-        <v>0.28370079189725922</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <f>Q25/MAX($Q$2:$Q$28)</f>
+        <v>0.29844695955690265</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D26" s="8">
-        <v>45481</v>
+        <v>45483</v>
       </c>
       <c r="E26" s="2">
-        <v>1E-22</v>
+        <v>0.1195</v>
       </c>
       <c r="F26" s="1">
-        <v>169.34</v>
+        <v>167.24</v>
       </c>
       <c r="G26" s="1">
-        <f t="shared" si="11"/>
-        <v>1.6934000000000002E-20</v>
+        <f>E26*F26</f>
+        <v>19.98518</v>
       </c>
       <c r="H26" s="11">
-        <f>174.52/F26-1</f>
-        <v>3.0589346876107371E-2</v>
+        <f>190.41/F26-1</f>
+        <v>0.13854341066730447</v>
       </c>
       <c r="I26" s="11">
-        <v>0.4259</v>
+        <v>0.26790000000000003</v>
       </c>
       <c r="J26" s="9">
-        <f t="shared" si="12"/>
-        <v>7.1822838403633182E-2</v>
+        <f>IFERROR(H26/I26,"")</f>
+        <v>0.51714598979956872</v>
       </c>
       <c r="K26" s="9">
-        <f t="shared" si="13"/>
-        <v>8.6548247073189144E-2</v>
+        <f>IFERROR(J26/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>8.2575090140862145E-2</v>
       </c>
       <c r="L26" s="12">
-        <f t="shared" si="14"/>
-        <v>174.52000000000004</v>
+        <f>F26/(1-(F26*(1+H26)-F26)/(F26*(1+H26)))</f>
+        <v>190.41</v>
       </c>
       <c r="M26" s="12">
-        <f t="shared" si="15"/>
-        <v>121.36365448143965</v>
+        <f>F26/(1+I26-H26)</f>
+        <v>148.08431772538498</v>
       </c>
       <c r="N26" s="12">
-        <f t="shared" si="16"/>
-        <v>5.1800000000000352</v>
+        <f>L26-F26</f>
+        <v>23.169999999999987</v>
       </c>
       <c r="O26" s="12">
-        <f t="shared" si="17"/>
-        <v>-23.988172759280175</v>
+        <f>0.5*(M26-F26)</f>
+        <v>-9.5778411373075159</v>
       </c>
       <c r="P26" s="15">
-        <f t="shared" si="18"/>
-        <v>-18.80817275928014</v>
+        <f>N26+O26</f>
+        <v>13.592158862692472</v>
       </c>
       <c r="Q26" s="12">
-        <f t="shared" si="19"/>
-        <v>102.2352941141779</v>
+        <f>MAX($P$2:$P$280)-P26</f>
+        <v>69.834962492205293</v>
       </c>
       <c r="R26" s="9">
-        <f t="shared" si="20"/>
-        <v>9.7813578829556158E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q26)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.4319475006686174E-2</v>
       </c>
       <c r="S26" s="9">
-        <f t="shared" si="21"/>
-        <v>0.33760219027884886</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <f>Q26/MAX($Q$2:$Q$28)</f>
+        <v>0.23060956101010721</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C27" t="s">
-        <v>27</v>
+        <v>82</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>83</v>
       </c>
       <c r="D27" s="8">
-        <v>45511</v>
+        <f ca="1">TODAY()-20</f>
+        <v>45602</v>
       </c>
       <c r="E27" s="2">
-        <v>0.1933</v>
+        <v>1E-35</v>
       </c>
       <c r="F27" s="1">
-        <v>77.53</v>
+        <v>2742.9</v>
       </c>
       <c r="G27" s="1">
-        <f t="shared" si="11"/>
-        <v>14.986549</v>
+        <f>E27*F27</f>
+        <v>2.7429E-32</v>
       </c>
       <c r="H27" s="11">
-        <f>83.34/F27-1</f>
-        <v>7.4938733393525192E-2</v>
+        <v>0.1</v>
       </c>
       <c r="I27" s="11">
-        <v>0.25990000000000002</v>
+        <v>0.5</v>
       </c>
       <c r="J27" s="9">
-        <f t="shared" si="12"/>
-        <v>0.28833679643526428</v>
+        <f>IFERROR(H27/I27,"")</f>
+        <v>0.2</v>
       </c>
       <c r="K27" s="9">
-        <f t="shared" si="13"/>
-        <v>0.34745277202674207</v>
+        <f>IFERROR(J27/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>3.1934924284288055E-2</v>
       </c>
       <c r="L27" s="12">
-        <f t="shared" si="14"/>
-        <v>83.34</v>
+        <f>F27/(1-(F27*(1+H27)-F27)/(F27*(1+H27)))</f>
+        <v>3017.1900000000005</v>
       </c>
       <c r="M27" s="12">
-        <f t="shared" si="15"/>
-        <v>65.428298953629579</v>
+        <f>F27/(1+I27-H27)</f>
+        <v>1959.214285714286</v>
       </c>
       <c r="N27" s="12">
-        <f t="shared" si="16"/>
-        <v>5.8100000000000023</v>
+        <f>L27-F27</f>
+        <v>274.29000000000042</v>
       </c>
       <c r="O27" s="12">
-        <f t="shared" si="17"/>
-        <v>-6.0508505231852112</v>
+        <f>0.5*(M27-F27)</f>
+        <v>-391.84285714285704</v>
       </c>
       <c r="P27" s="15">
-        <f t="shared" si="18"/>
-        <v>-0.24085052318520894</v>
+        <f>N27+O27</f>
+        <v>-117.55285714285662</v>
       </c>
       <c r="Q27" s="12">
-        <f t="shared" si="19"/>
-        <v>83.667971878082966</v>
+        <f>MAX($P$2:$P$280)-P27</f>
+        <v>200.97997849775439</v>
       </c>
       <c r="R27" s="9">
-        <f t="shared" si="20"/>
-        <v>1.1952004782154311E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q27)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>4.9756199969499615E-3</v>
       </c>
       <c r="S27" s="9">
-        <f t="shared" si="21"/>
-        <v>0.27628903312669928</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <f>Q27/MAX($Q$2:$Q$28)</f>
+        <v>0.66367766172081932</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>8</v>
+        <v>38</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="C28" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="D28" s="8">
-        <v>45511</v>
+        <v>45505</v>
       </c>
       <c r="E28" s="2">
-        <v>3.2899999999999999E-2</v>
+        <v>1E-35</v>
       </c>
       <c r="F28" s="1">
-        <v>455.4</v>
+        <v>86.6</v>
       </c>
       <c r="G28" s="1">
-        <f t="shared" si="11"/>
-        <v>14.982659999999999</v>
+        <f>E28*F28</f>
+        <v>8.6599999999999988E-34</v>
       </c>
       <c r="H28" s="11">
-        <v>0.17460000000000001</v>
+        <f>89.44/F28-1</f>
+        <v>3.2794457274826883E-2</v>
       </c>
       <c r="I28" s="11">
-        <v>0.15770000000000001</v>
+        <v>0.17249999999999999</v>
       </c>
       <c r="J28" s="9">
-        <f t="shared" si="12"/>
-        <v>1.1071655041217501</v>
+        <f>IFERROR(H28/I28,"")</f>
+        <v>0.19011279579609788</v>
       </c>
       <c r="K28" s="9">
-        <f t="shared" si="13"/>
-        <v>1.3341610514350544</v>
+        <f>IFERROR(J28/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>3.0356188696113506E-2</v>
       </c>
       <c r="L28" s="12">
-        <f t="shared" si="14"/>
-        <v>534.91283999999996</v>
+        <f>F28/(1-(F28*(1+H28)-F28)/(F28*(1+H28)))</f>
+        <v>89.44</v>
       </c>
       <c r="M28" s="12">
-        <f t="shared" si="15"/>
-        <v>463.22856270979554</v>
+        <f>F28/(1+I28-H28)</f>
+        <v>75.984538772119137</v>
       </c>
       <c r="N28" s="12">
-        <f t="shared" si="16"/>
-        <v>79.512839999999983</v>
+        <f>L28-F28</f>
+        <v>2.8400000000000034</v>
       </c>
       <c r="O28" s="12">
-        <f t="shared" si="17"/>
-        <v>3.9142813548977813</v>
+        <f>0.5*(M28-F28)</f>
+        <v>-5.3077306139404286</v>
       </c>
       <c r="P28" s="15">
-        <f t="shared" si="18"/>
-        <v>83.427121354897764</v>
+        <f>N28+O28</f>
+        <v>-2.4677306139404251</v>
       </c>
       <c r="Q28" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>MAX($P$2:$P$280)-P28</f>
+        <v>85.894851968838196</v>
       </c>
       <c r="R28" s="9">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q28)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.1642141258509766E-2</v>
       </c>
       <c r="S28" s="9">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <f>Q28/MAX($Q$2:$Q$28)</f>
+        <v>0.28364265403268213</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C29" s="14" t="s">
-        <v>50</v>
+        <v>74</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" t="s">
+        <v>76</v>
       </c>
       <c r="D29" s="8">
-        <v>45511</v>
+        <v>45562</v>
       </c>
       <c r="E29" s="2">
-        <v>1</v>
+        <v>1E-35</v>
       </c>
       <c r="F29" s="1">
-        <v>10.4</v>
+        <v>56</v>
       </c>
       <c r="G29" s="1">
-        <f t="shared" si="11"/>
-        <v>10.4</v>
+        <f>E29*F29</f>
+        <v>5.5999999999999999E-34</v>
       </c>
       <c r="H29" s="11">
-        <f>2.89/F29-1</f>
-        <v>-0.7221153846153846</v>
-      </c>
-      <c r="I29" s="13">
-        <v>1.8652</v>
+        <v>0.08</v>
+      </c>
+      <c r="I29" s="11">
+        <v>0.19</v>
       </c>
       <c r="J29" s="9">
-        <f t="shared" si="12"/>
-        <v>-0.38715171810818388</v>
+        <f>IFERROR(H29/I29,"")</f>
+        <v>0.42105263157894735</v>
       </c>
       <c r="K29" s="9">
-        <f t="shared" si="13"/>
-        <v>-0.46652712839516236</v>
+        <f>IFERROR(J29/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>6.7231419545869572E-2</v>
       </c>
       <c r="L29" s="12">
-        <f t="shared" si="14"/>
-        <v>2.8900000000000006</v>
+        <f>F29/(1-(F29*(1+H29)-F29)/(F29*(1+H29)))</f>
+        <v>60.480000000000004</v>
       </c>
       <c r="M29" s="12">
-        <f t="shared" si="15"/>
-        <v>2.8991038938481961</v>
+        <f>F29/(1+I29-H29)</f>
+        <v>50.450450450450454</v>
       </c>
       <c r="N29" s="12">
-        <f t="shared" si="16"/>
-        <v>-7.51</v>
+        <f>L29-F29</f>
+        <v>4.480000000000004</v>
       </c>
       <c r="O29" s="12">
-        <f t="shared" si="17"/>
-        <v>-3.7504480530759023</v>
+        <f>0.5*(M29-F29)</f>
+        <v>-2.7747747747747731</v>
       </c>
       <c r="P29" s="15">
-        <f t="shared" si="18"/>
-        <v>-11.260448053075901</v>
+        <f>N29+O29</f>
+        <v>1.7052252252252309</v>
       </c>
       <c r="Q29" s="12">
-        <f t="shared" si="19"/>
-        <v>94.687569407973669</v>
+        <f>MAX($P$2:$P$280)-P29</f>
+        <v>81.72189612967253</v>
       </c>
       <c r="R29" s="9">
-        <f t="shared" si="20"/>
-        <v>1.0561048364135003E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q29)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.223662258659841E-2</v>
       </c>
       <c r="S29" s="9">
-        <f t="shared" si="21"/>
-        <v>0.31267803454070875</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <f>Q29/MAX($Q$2:$Q$28)</f>
+        <v>0.26986268652296996</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>48</v>
+        <v>77</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C30" t="s">
+        <v>79</v>
       </c>
       <c r="D30" s="8">
-        <v>45511</v>
+        <v>45580</v>
       </c>
       <c r="E30" s="2">
-        <v>1E-22</v>
+        <v>1E-35</v>
       </c>
       <c r="F30" s="1">
-        <v>20.82</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="G30" s="1">
-        <f t="shared" si="11"/>
-        <v>2.0820000000000001E-21</v>
-      </c>
-      <c r="H30" s="13">
-        <f>19.07/F30-1</f>
-        <v>-8.4053794428434192E-2</v>
+        <f>E30*F30</f>
+        <v>2.0399999999999999E-34</v>
+      </c>
+      <c r="H30" s="11">
+        <f>L30/F30-1</f>
+        <v>3.9215686274509887E-2</v>
       </c>
       <c r="I30" s="11">
-        <v>0.7389</v>
+        <v>0.15</v>
       </c>
       <c r="J30" s="9">
-        <f t="shared" si="12"/>
-        <v>-0.11375530440984462</v>
+        <f>IFERROR(H30/I30,"")</f>
+        <v>0.2614379084967326</v>
       </c>
       <c r="K30" s="9">
-        <f t="shared" si="13"/>
-        <v>-0.13707787676978034</v>
+        <f>IFERROR(J30/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>4.1744999064428918E-2</v>
       </c>
       <c r="L30" s="12">
-        <f t="shared" si="14"/>
-        <v>19.070000000000004</v>
+        <v>21.2</v>
       </c>
       <c r="M30" s="12">
-        <f t="shared" si="15"/>
-        <v>11.421024528231593</v>
+        <f>F30/(1+I30-H30)</f>
+        <v>18.365401588702561</v>
       </c>
       <c r="N30" s="12">
-        <f t="shared" si="16"/>
-        <v>-1.7499999999999964</v>
+        <f>L30-F30</f>
+        <v>0.80000000000000071</v>
       </c>
       <c r="O30" s="12">
-        <f t="shared" si="17"/>
-        <v>-4.6994877358842038</v>
+        <f>0.5*(M30-F30)</f>
+        <v>-1.0172992056487189</v>
       </c>
       <c r="P30" s="15">
-        <f t="shared" si="18"/>
-        <v>-6.4494877358842002</v>
+        <f>N30+O30</f>
+        <v>-0.21729920564871819</v>
       </c>
       <c r="Q30" s="12">
-        <f t="shared" si="19"/>
-        <v>89.876609090781969</v>
+        <f>MAX($P$2:$P$280)-P30</f>
+        <v>83.644420560546479</v>
       </c>
       <c r="R30" s="9">
-        <f t="shared" si="20"/>
-        <v>1.1126365470574514E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q30)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.1955370044988768E-2</v>
       </c>
       <c r="S30" s="9">
-        <f t="shared" si="21"/>
-        <v>0.29679124363839449</v>
+        <f>Q30/MAX($Q$2:$Q$28)</f>
+        <v>0.27621126178116578</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>88</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>80</v>
+        <v>39</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="C31" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="D31" s="8">
         <v>45574</v>
       </c>
       <c r="E31" s="2">
-        <v>0</v>
+        <v>9.9999999999999998E-46</v>
       </c>
       <c r="F31" s="1">
-        <v>153.7552</v>
+        <v>47.42</v>
       </c>
       <c r="G31" s="1">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f>E31*F31</f>
+        <v>4.7420000000000006E-44</v>
       </c>
       <c r="H31" s="11">
-        <v>7.0000000000000007E-2</v>
+        <f>48.37/F31-1</f>
+        <v>2.0033741037536856E-2</v>
       </c>
       <c r="I31" s="11">
-        <v>0.19</v>
+        <v>0.4</v>
       </c>
       <c r="J31" s="9">
-        <f t="shared" si="12"/>
-        <v>0.36842105263157898</v>
+        <f>IFERROR(H31/I31,"")</f>
+        <v>5.0084352593842141E-2</v>
       </c>
       <c r="K31" s="9">
-        <f t="shared" si="13"/>
-        <v>0.44395622616481484</v>
+        <f>IFERROR(J31/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>7.9972000395596727E-3</v>
       </c>
       <c r="L31" s="12">
-        <f t="shared" si="14"/>
-        <v>164.51806400000001</v>
+        <f>F31/(1-(F31*(1+H31)-F31)/(F31*(1+H31)))</f>
+        <v>48.37</v>
       </c>
       <c r="M31" s="12">
-        <f t="shared" si="15"/>
-        <v>137.28142857142859</v>
+        <f>F31/(1+I31-H31)</f>
+        <v>34.36315902075247</v>
       </c>
       <c r="N31" s="12">
-        <f t="shared" si="16"/>
-        <v>10.762864000000008</v>
+        <f>L31-F31</f>
+        <v>0.94999999999999574</v>
       </c>
       <c r="O31" s="12">
-        <f t="shared" si="17"/>
-        <v>-8.2368857142857053</v>
+        <f>0.5*(M31-F31)</f>
+        <v>-6.5284204896237661</v>
       </c>
       <c r="P31" s="15">
-        <f t="shared" si="18"/>
-        <v>2.5259782857143023</v>
+        <f>N31+O31</f>
+        <v>-5.5784204896237704</v>
       </c>
       <c r="Q31" s="12">
-        <f t="shared" si="19"/>
-        <v>80.901143069183462</v>
+        <f>MAX($P$2:$P$280)-P31</f>
+        <v>89.005541844521531</v>
       </c>
       <c r="R31" s="9">
-        <f t="shared" si="20"/>
-        <v>1.2360764781096351E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q31)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.123525546023685E-2</v>
       </c>
       <c r="S31" s="9">
-        <f t="shared" si="21"/>
-        <v>0.26715238932766161</v>
+        <f>Q31/MAX($Q$2:$Q$28)</f>
+        <v>0.29391479854410774</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>88</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>83</v>
+        <v>39</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" t="s">
+        <v>41</v>
       </c>
       <c r="D32" s="8">
-        <f ca="1">TODAY()-20</f>
-        <v>45602</v>
+        <v>45507</v>
       </c>
       <c r="E32" s="2">
-        <v>1E-35</v>
+        <v>9.9999999999999998E-46</v>
       </c>
       <c r="F32" s="1">
-        <v>2742.9</v>
+        <v>41.8</v>
       </c>
       <c r="G32" s="1">
-        <f t="shared" ref="G32:G33" si="22">E32*F32</f>
-        <v>2.7429E-32</v>
+        <f>E32*F32</f>
+        <v>4.1799999999999994E-44</v>
       </c>
       <c r="H32" s="11">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I32" s="11">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J32" s="9">
-        <f t="shared" ref="J32:J33" si="23">IFERROR(H32/I32,"")</f>
-        <v>0.2</v>
+        <f>IFERROR(H32/I32,"")</f>
+        <v>0</v>
       </c>
       <c r="K32" s="9">
-        <f t="shared" si="2"/>
-        <v>0.2410048084894709</v>
+        <f>IFERROR(J32/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>0</v>
       </c>
       <c r="L32" s="12">
-        <f t="shared" ref="L32:L33" si="24">F32/(1-(F32*(1+H32)-F32)/(F32*(1+H32)))</f>
-        <v>3017.1900000000005</v>
+        <f>F32/(1-(F32*(1+H32)-F32)/(F32*(1+H32)))</f>
+        <v>41.8</v>
       </c>
       <c r="M32" s="12">
-        <f t="shared" ref="M32:M33" si="25">F32/(1+I32-H32)</f>
-        <v>1959.214285714286</v>
+        <f>F32/(1+I32-H32)</f>
+        <v>29.857142857142858</v>
       </c>
       <c r="N32" s="12">
-        <f t="shared" ref="N32:N33" si="26">L32-F32</f>
-        <v>274.29000000000042</v>
+        <f>L32-F32</f>
+        <v>0</v>
       </c>
       <c r="O32" s="12">
-        <f t="shared" ref="O32:O33" si="27">0.5*(M32-F32)</f>
-        <v>-391.84285714285704</v>
+        <f>0.5*(M32-F32)</f>
+        <v>-5.9714285714285698</v>
       </c>
       <c r="P32" s="15">
-        <f t="shared" ref="P32:P33" si="28">N32+O32</f>
-        <v>-117.55285714285662</v>
+        <f>N32+O32</f>
+        <v>-5.9714285714285698</v>
       </c>
       <c r="Q32" s="12">
-        <f t="shared" si="9"/>
-        <v>200.97997849775439</v>
+        <f>MAX($P$2:$P$280)-P32</f>
+        <v>89.398549926326339</v>
       </c>
       <c r="R32" s="9">
-        <f t="shared" si="10"/>
-        <v>4.9756199969499615E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q32)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.1185863762042041E-2</v>
       </c>
       <c r="S32" s="9">
-        <f t="shared" si="8"/>
-        <v>0.66367766172081932</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <f>Q32/MAX($Q$2:$Q$28)</f>
+        <v>0.29521259291506552</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>36</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>86</v>
+        <v>77</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="C33" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D33" s="8">
-        <v>45481</v>
+        <v>45574</v>
       </c>
       <c r="E33" s="2">
-        <v>1E-22</v>
+        <v>0</v>
       </c>
       <c r="F33" s="1">
-        <v>64.349999999999994</v>
+        <v>153.7552</v>
       </c>
       <c r="G33" s="1">
-        <f t="shared" si="22"/>
-        <v>6.4349999999999995E-21</v>
+        <f>E33*F33</f>
+        <v>0</v>
       </c>
       <c r="H33" s="11">
-        <f>75.53/F33-1</f>
-        <v>0.17373737373737397</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I33" s="11">
-        <v>0.67300000000000004</v>
+        <v>0.19</v>
       </c>
       <c r="J33" s="9">
-        <f t="shared" si="23"/>
-        <v>0.25815360139282906</v>
+        <f>IFERROR(H33/I33,"")</f>
+        <v>0.36842105263157898</v>
       </c>
       <c r="K33" s="9">
-        <f t="shared" si="2"/>
-        <v>0.31108129632272985</v>
+        <f>IFERROR(J33/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>5.8827492102635888E-2</v>
       </c>
       <c r="L33" s="12">
-        <f t="shared" si="24"/>
-        <v>75.53</v>
+        <f>F33/(1-(F33*(1+H33)-F33)/(F33*(1+H33)))</f>
+        <v>164.51806400000001</v>
       </c>
       <c r="M33" s="12">
-        <f t="shared" si="25"/>
-        <v>42.921099260916144</v>
+        <f>F33/(1+I33-H33)</f>
+        <v>137.28142857142859</v>
       </c>
       <c r="N33" s="12">
-        <f t="shared" si="26"/>
-        <v>11.180000000000007</v>
+        <f>L33-F33</f>
+        <v>10.762864000000008</v>
       </c>
       <c r="O33" s="12">
-        <f t="shared" si="27"/>
-        <v>-10.714450369541925</v>
+        <f>0.5*(M33-F33)</f>
+        <v>-8.2368857142857053</v>
       </c>
       <c r="P33" s="15">
-        <f t="shared" si="28"/>
-        <v>0.46554963045808151</v>
+        <f>N33+O33</f>
+        <v>2.5259782857143023</v>
       </c>
       <c r="Q33" s="12">
-        <f t="shared" si="9"/>
-        <v>82.961571724439679</v>
+        <f>MAX($P$2:$P$280)-P33</f>
+        <v>80.901143069183462</v>
       </c>
       <c r="R33" s="9">
-        <f t="shared" si="10"/>
-        <v>1.2053773563036411E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q33)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.2360764781096351E-2</v>
       </c>
       <c r="S33" s="9">
-        <f t="shared" si="8"/>
-        <v>0.27395635299749704</v>
+        <f>Q33/MAX($Q$2:$Q$28)</f>
+        <v>0.26715238932766161</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:S33" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Forex"/>
-      </filters>
-    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S33">
+      <sortCondition descending="1" ref="G1:G33"/>
+    </sortState>
   </autoFilter>
   <conditionalFormatting sqref="R2:R33">
     <cfRule type="iconSet" priority="3">

--- a/Open Positions.xlsx
+++ b/Open Positions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\StockSillines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7C223C1-ADAA-4B9D-8BBA-525A176F5820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02260CCE-BB48-45B5-9D7C-0FDB7BD3B96A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="90">
   <si>
     <t>Name</t>
   </si>
@@ -304,6 +304,12 @@
   </si>
   <si>
     <t>PLTR</t>
+  </si>
+  <si>
+    <t>ING Group NV</t>
+  </si>
+  <si>
+    <t>ING</t>
   </si>
 </sst>
 </file>
@@ -712,7 +718,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S33"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:S34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
@@ -795,7 +802,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>36</v>
       </c>
@@ -815,7 +822,7 @@
         <v>423.77</v>
       </c>
       <c r="G2" s="1">
-        <f>E2*F2</f>
+        <f t="shared" ref="G2:G33" si="0">E2*F2</f>
         <v>56.658049000000005</v>
       </c>
       <c r="H2" s="11">
@@ -825,47 +832,47 @@
         <v>0.1963</v>
       </c>
       <c r="J2" s="9">
-        <f>IFERROR(H2/I2,"")</f>
+        <f t="shared" ref="J2:J33" si="1">IFERROR(H2/I2,"")</f>
         <v>5.8074375955170655E-2</v>
       </c>
       <c r="K2" s="9">
-        <f>IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>9.2730039949282667E-3</v>
+        <f t="shared" ref="K2:K33" si="2">IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>2.1599897449786014E-2</v>
       </c>
       <c r="L2" s="12">
-        <f>F2/(1-(F2*(1+H2)-F2)/(F2*(1+H2)))</f>
+        <f t="shared" ref="L2:L29" si="3">F2/(1-(F2*(1+H2)-F2)/(F2*(1+H2)))</f>
         <v>428.600978</v>
       </c>
       <c r="M2" s="12">
-        <f>F2/(1+I2-H2)</f>
+        <f t="shared" ref="M2:M33" si="4">F2/(1+I2-H2)</f>
         <v>357.64199510507217</v>
       </c>
       <c r="N2" s="12">
-        <f>L2-F2</f>
+        <f t="shared" ref="N2:N33" si="5">L2-F2</f>
         <v>4.830978000000016</v>
       </c>
       <c r="O2" s="12">
-        <f>0.5*(M2-F2)</f>
+        <f t="shared" ref="O2:O33" si="6">0.5*(M2-F2)</f>
         <v>-33.064002447463906</v>
       </c>
       <c r="P2" s="15">
-        <f>N2+O2</f>
+        <f t="shared" ref="P2:P33" si="7">N2+O2</f>
         <v>-28.23302444746389</v>
       </c>
       <c r="Q2" s="12">
-        <f>MAX($P$2:$P$280)-P2</f>
-        <v>111.66014580236165</v>
+        <f t="shared" ref="Q2:Q33" si="8">MAX($P$2:$P$280)-P2</f>
+        <v>131.86153447611721</v>
       </c>
       <c r="R2" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q2)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>8.9557468585971488E-3</v>
+        <f t="shared" ref="R2:R33" si="9">IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q2)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>7.5837127481716074E-3</v>
       </c>
       <c r="S2" s="9">
-        <f>Q2/MAX($Q$2:$Q$28)</f>
-        <v>0.36872500946329412</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+        <f t="shared" ref="S2:S33" si="10">Q2/MAX($Q$2:$Q$28)</f>
+        <v>0.4082032854788411</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>38</v>
       </c>
@@ -885,7 +892,7 @@
         <v>51.15</v>
       </c>
       <c r="G3" s="1">
-        <f>E3*F3</f>
+        <f t="shared" si="0"/>
         <v>54.996479999999998</v>
       </c>
       <c r="H3" s="11">
@@ -896,47 +903,47 @@
         <v>0.19980000000000001</v>
       </c>
       <c r="J3" s="9">
-        <f>IFERROR(H3/I3,"")</f>
+        <f t="shared" si="1"/>
         <v>0.92242242242242245</v>
       </c>
       <c r="K3" s="9">
-        <f>IFERROR(J3/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.14728745109094815</v>
+        <f t="shared" si="2"/>
+        <v>0.3430812540299637</v>
       </c>
       <c r="L3" s="12">
-        <f>F3/(1-(F3*(1+H3)-F3)/(F3*(1+H3)))</f>
+        <f t="shared" si="3"/>
         <v>60.576944999999995</v>
       </c>
       <c r="M3" s="12">
-        <f>F3/(1+I3-H3)</f>
+        <f t="shared" si="4"/>
         <v>50.369276218611525</v>
       </c>
       <c r="N3" s="12">
-        <f>L3-F3</f>
+        <f t="shared" si="5"/>
         <v>9.4269449999999964</v>
       </c>
       <c r="O3" s="12">
-        <f>0.5*(M3-F3)</f>
+        <f t="shared" si="6"/>
         <v>-0.39036189069423699</v>
       </c>
       <c r="P3" s="15">
-        <f>N3+O3</f>
+        <f t="shared" si="7"/>
         <v>9.0365831093057594</v>
       </c>
       <c r="Q3" s="12">
-        <f>MAX($P$2:$P$280)-P3</f>
-        <v>74.390538245592012</v>
+        <f t="shared" si="8"/>
+        <v>94.591926919347571</v>
       </c>
       <c r="R3" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q3)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.3442569762012102E-2</v>
+        <f t="shared" si="9"/>
+        <v>1.0571726706155754E-2</v>
       </c>
       <c r="S3" s="9">
-        <f>Q3/MAX($Q$2:$Q$28)</f>
-        <v>0.24565301900228498</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>0.29282789330231596</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -950,64 +957,64 @@
         <v>45484</v>
       </c>
       <c r="E4" s="2">
-        <v>0.24990000000000001</v>
+        <v>0.33389999999999997</v>
       </c>
       <c r="F4" s="1">
-        <v>191.91</v>
+        <v>188.53</v>
       </c>
       <c r="G4" s="1">
-        <f>E4*F4</f>
-        <v>47.958309</v>
+        <f t="shared" si="0"/>
+        <v>62.950166999999993</v>
       </c>
       <c r="H4" s="11">
         <f>227.4/F4-1</f>
-        <v>0.18493043614194149</v>
+        <v>0.20617408370020684</v>
       </c>
       <c r="I4" s="11">
         <v>0.37</v>
       </c>
       <c r="J4" s="9">
-        <f>IFERROR(H4/I4,"")</f>
-        <v>0.49981198957281486</v>
+        <f t="shared" si="1"/>
+        <v>0.55722725324380229</v>
       </c>
       <c r="K4" s="9">
-        <f>IFERROR(J4/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>7.9807290216936055E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.20725236093080118</v>
       </c>
       <c r="L4" s="12">
-        <f>F4/(1-(F4*(1+H4)-F4)/(F4*(1+H4)))</f>
-        <v>227.39999999999998</v>
+        <f t="shared" si="3"/>
+        <v>227.4</v>
       </c>
       <c r="M4" s="12">
-        <f>F4/(1+I4-H4)</f>
-        <v>161.93986062322494</v>
+        <f t="shared" si="4"/>
+        <v>161.9915808365931</v>
       </c>
       <c r="N4" s="12">
-        <f>L4-F4</f>
-        <v>35.489999999999981</v>
+        <f t="shared" si="5"/>
+        <v>38.870000000000005</v>
       </c>
       <c r="O4" s="12">
-        <f>0.5*(M4-F4)</f>
-        <v>-14.985069688387526</v>
+        <f t="shared" si="6"/>
+        <v>-13.26920958170345</v>
       </c>
       <c r="P4" s="15">
-        <f>N4+O4</f>
-        <v>20.504930311612455</v>
+        <f t="shared" si="7"/>
+        <v>25.600790418296555</v>
       </c>
       <c r="Q4" s="12">
-        <f>MAX($P$2:$P$280)-P4</f>
-        <v>62.922191043285309</v>
+        <f t="shared" si="8"/>
+        <v>78.027719610356769</v>
       </c>
       <c r="R4" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q4)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.5892644286847574E-2</v>
+        <f t="shared" si="9"/>
+        <v>1.2815958290126269E-2</v>
       </c>
       <c r="S4" s="9">
-        <f>Q4/MAX($Q$2:$Q$28)</f>
-        <v>0.20778215289949825</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>0.24155013537430298</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -1027,7 +1034,7 @@
         <v>227.38</v>
       </c>
       <c r="G5" s="1">
-        <f>E5*F5</f>
+        <f t="shared" si="0"/>
         <v>42.792915999999998</v>
       </c>
       <c r="H5" s="11">
@@ -1037,44 +1044,44 @@
         <v>0.2271</v>
       </c>
       <c r="J5" s="9">
-        <f>IFERROR(H5/I5,"")</f>
+        <f t="shared" si="1"/>
         <v>0.21708498458828709</v>
       </c>
       <c r="K5" s="9">
-        <f>IFERROR(J5/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.4662962730413936E-2</v>
+        <f t="shared" si="2"/>
+        <v>8.074152029829762E-2</v>
       </c>
       <c r="L5" s="12">
-        <f>F5/(1-(F5*(1+H5)-F5)/(F5*(1+H5)))</f>
+        <f t="shared" si="3"/>
         <v>238.58983399999997</v>
       </c>
       <c r="M5" s="12">
-        <f>F5/(1+I5-H5)</f>
+        <f t="shared" si="4"/>
         <v>193.05484802173541</v>
       </c>
       <c r="N5" s="12">
-        <f>L5-F5</f>
+        <f t="shared" si="5"/>
         <v>11.209833999999972</v>
       </c>
       <c r="O5" s="12">
-        <f>0.5*(M5-F5)</f>
+        <f t="shared" si="6"/>
         <v>-17.162575989132293</v>
       </c>
       <c r="P5" s="15">
-        <f>N5+O5</f>
+        <f t="shared" si="7"/>
         <v>-5.9527419891323206</v>
       </c>
       <c r="Q5" s="12">
-        <f>MAX($P$2:$P$280)-P5</f>
-        <v>89.379863344030085</v>
+        <f t="shared" si="8"/>
+        <v>109.58125201778564</v>
       </c>
       <c r="R5" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q5)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.1188202382352295E-2</v>
+        <f t="shared" si="9"/>
+        <v>9.1256486085566392E-3</v>
       </c>
       <c r="S5" s="9">
-        <f>Q5/MAX($Q$2:$Q$28)</f>
-        <v>0.29515088593640709</v>
+        <f t="shared" si="10"/>
+        <v>0.33923029394631193</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
@@ -1097,57 +1104,57 @@
         <v>273.45999999999998</v>
       </c>
       <c r="G6" s="1">
-        <f>E6*F6</f>
+        <f t="shared" si="0"/>
         <v>39.952506</v>
       </c>
       <c r="H6" s="11">
-        <v>0.16769999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="I6" s="11">
-        <v>0.16700000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="J6" s="9">
-        <f>IFERROR(H6/I6,"")</f>
-        <v>1.0041916167664668</v>
+        <f t="shared" si="1"/>
+        <v>0.96153846153846145</v>
       </c>
       <c r="K6" s="9">
-        <f>IFERROR(J6/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.16034391624176961</v>
+        <f t="shared" si="2"/>
+        <v>0.35762988102167631</v>
       </c>
       <c r="L6" s="12">
         <f>F6/(1-(F6*(1+H6)-F6)/(F6*(1+H6)))</f>
-        <v>319.31924199999997</v>
+        <v>341.82499999999999</v>
       </c>
       <c r="M6" s="12">
-        <f>F6/(1+I6-H6)</f>
-        <v>273.65155608926244</v>
+        <f t="shared" si="4"/>
+        <v>270.75247524752473</v>
       </c>
       <c r="N6" s="12">
-        <f>L6-F6</f>
-        <v>45.859241999999995</v>
+        <f t="shared" si="5"/>
+        <v>68.365000000000009</v>
       </c>
       <c r="O6" s="12">
-        <f>0.5*(M6-F6)</f>
-        <v>9.5778044631231296E-2</v>
+        <f t="shared" si="6"/>
+        <v>-1.3537623762376256</v>
       </c>
       <c r="P6" s="15">
-        <f>N6+O6</f>
-        <v>45.955020044631226</v>
+        <f t="shared" si="7"/>
+        <v>67.011237623762383</v>
       </c>
       <c r="Q6" s="12">
-        <f>MAX($P$2:$P$280)-P6</f>
-        <v>37.472101310266538</v>
+        <f t="shared" si="8"/>
+        <v>36.61727240489094</v>
       </c>
       <c r="R6" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q6)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>2.6686520505483952E-2</v>
+        <f t="shared" si="9"/>
+        <v>2.7309516365463388E-2</v>
       </c>
       <c r="S6" s="9">
-        <f>Q6/MAX($Q$2:$Q$28)</f>
-        <v>0.12374066692240798</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>0.1133559605561654</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>36</v>
       </c>
@@ -1167,7 +1174,7 @@
         <v>188.12</v>
       </c>
       <c r="G7" s="1">
-        <f>E7*F7</f>
+        <f t="shared" si="0"/>
         <v>36.269536000000002</v>
       </c>
       <c r="H7" s="11">
@@ -1177,47 +1184,47 @@
         <v>0.37780000000000002</v>
       </c>
       <c r="J7" s="9">
-        <f>IFERROR(H7/I7,"")</f>
+        <f t="shared" si="1"/>
         <v>-0.18157755426151401</v>
       </c>
       <c r="K7" s="9">
-        <f>IFERROR(J7/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-2.8993327235338276E-2</v>
+        <f t="shared" si="2"/>
+        <v>-6.7535061491822326E-2</v>
       </c>
       <c r="L7" s="12">
-        <f>F7/(1-(F7*(1+H7)-F7)/(F7*(1+H7)))</f>
+        <f t="shared" si="3"/>
         <v>175.214968</v>
       </c>
       <c r="M7" s="12">
-        <f>F7/(1+I7-H7)</f>
+        <f t="shared" si="4"/>
         <v>130.06084070796459</v>
       </c>
       <c r="N7" s="12">
-        <f>L7-F7</f>
+        <f t="shared" si="5"/>
         <v>-12.905032000000006</v>
       </c>
       <c r="O7" s="12">
-        <f>0.5*(M7-F7)</f>
+        <f t="shared" si="6"/>
         <v>-29.029579646017709</v>
       </c>
       <c r="P7" s="15">
-        <f>N7+O7</f>
+        <f t="shared" si="7"/>
         <v>-41.934611646017714</v>
       </c>
       <c r="Q7" s="12">
-        <f>MAX($P$2:$P$280)-P7</f>
-        <v>125.36173300091548</v>
+        <f t="shared" si="8"/>
+        <v>145.56312167467104</v>
       </c>
       <c r="R7" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q7)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>7.9769158902158535E-3</v>
+        <f t="shared" si="9"/>
+        <v>6.8698719050211653E-3</v>
       </c>
       <c r="S7" s="9">
-        <f>Q7/MAX($Q$2:$Q$28)</f>
-        <v>0.4139704982018737</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>0.45061924046484586</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -1237,7 +1244,7 @@
         <v>144.28</v>
       </c>
       <c r="G8" s="1">
-        <f>E8*F8</f>
+        <f t="shared" si="0"/>
         <v>35.189892</v>
       </c>
       <c r="H8" s="11">
@@ -1247,47 +1254,47 @@
         <v>0.18340000000000001</v>
       </c>
       <c r="J8" s="9">
-        <f>IFERROR(H8/I8,"")</f>
+        <f t="shared" si="1"/>
         <v>-0.15267175572519084</v>
       </c>
       <c r="K8" s="9">
-        <f>IFERROR(J8/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-2.437780479716645E-2</v>
+        <f t="shared" si="2"/>
+        <v>-5.6783981108785249E-2</v>
       </c>
       <c r="L8" s="12">
-        <f>F8/(1-(F8*(1+H8)-F8)/(F8*(1+H8)))</f>
+        <f t="shared" si="3"/>
         <v>140.24016</v>
       </c>
       <c r="M8" s="12">
-        <f>F8/(1+I8-H8)</f>
+        <f t="shared" si="4"/>
         <v>119.10186561003798</v>
       </c>
       <c r="N8" s="12">
-        <f>L8-F8</f>
+        <f t="shared" si="5"/>
         <v>-4.0398399999999981</v>
       </c>
       <c r="O8" s="12">
-        <f>0.5*(M8-F8)</f>
+        <f t="shared" si="6"/>
         <v>-12.589067194981013</v>
       </c>
       <c r="P8" s="15">
-        <f>N8+O8</f>
+        <f t="shared" si="7"/>
         <v>-16.628907194981011</v>
       </c>
       <c r="Q8" s="12">
-        <f>MAX($P$2:$P$280)-P8</f>
-        <v>100.05602854987877</v>
+        <f t="shared" si="8"/>
+        <v>120.25741722363433</v>
       </c>
       <c r="R8" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q8)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.9944002824526625E-3</v>
+        <f t="shared" si="9"/>
+        <v>8.3154954021702442E-3</v>
       </c>
       <c r="S8" s="9">
-        <f>Q8/MAX($Q$2:$Q$28)</f>
-        <v>0.33040580243567419</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>0.37228046077970073</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>38</v>
       </c>
@@ -1307,7 +1314,7 @@
         <v>165.59</v>
       </c>
       <c r="G9" s="1">
-        <f>E9*F9</f>
+        <f t="shared" si="0"/>
         <v>29.922113</v>
       </c>
       <c r="H9" s="11">
@@ -1317,47 +1324,47 @@
         <v>0.16439999999999999</v>
       </c>
       <c r="J9" s="9">
-        <f>IFERROR(H9/I9,"")</f>
+        <f t="shared" si="1"/>
         <v>0.40875912408759124</v>
       </c>
       <c r="K9" s="9">
-        <f>IFERROR(J9/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>6.5268458391245648E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.15203185599052868</v>
       </c>
       <c r="L9" s="12">
-        <f>F9/(1-(F9*(1+H9)-F9)/(F9*(1+H9)))</f>
+        <f t="shared" si="3"/>
         <v>176.717648</v>
       </c>
       <c r="M9" s="12">
-        <f>F9/(1+I9-H9)</f>
+        <f t="shared" si="4"/>
         <v>150.92052497265766</v>
       </c>
       <c r="N9" s="12">
-        <f>L9-F9</f>
+        <f t="shared" si="5"/>
         <v>11.127647999999994</v>
       </c>
       <c r="O9" s="12">
-        <f>0.5*(M9-F9)</f>
+        <f t="shared" si="6"/>
         <v>-7.3347375136711719</v>
       </c>
       <c r="P9" s="15">
-        <f>N9+O9</f>
+        <f t="shared" si="7"/>
         <v>3.7929104863288217</v>
       </c>
       <c r="Q9" s="12">
-        <f>MAX($P$2:$P$280)-P9</f>
-        <v>79.634210868568942</v>
+        <f t="shared" si="8"/>
+        <v>99.835599542324502</v>
       </c>
       <c r="R9" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q9)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.2557417083600347E-2</v>
+        <f t="shared" si="9"/>
+        <v>1.0016467117784552E-2</v>
       </c>
       <c r="S9" s="9">
-        <f>Q9/MAX($Q$2:$Q$28)</f>
-        <v>0.26296871587547221</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>0.30906071207830499</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -1377,7 +1384,7 @@
         <v>668.82</v>
       </c>
       <c r="G10" s="1">
-        <f>E10*F10</f>
+        <f t="shared" si="0"/>
         <v>26.953446000000003</v>
       </c>
       <c r="H10" s="11">
@@ -1388,47 +1395,47 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="J10" s="9">
-        <f>IFERROR(H10/I10,"")</f>
+        <f t="shared" si="1"/>
         <v>-0.61542289832412733</v>
       </c>
       <c r="K10" s="9">
-        <f>IFERROR(J10/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-9.826741830399055E-2</v>
+        <f t="shared" si="2"/>
+        <v>-0.22889736262189977</v>
       </c>
       <c r="L10" s="12">
-        <f>F10/(1-(F10*(1+H10)-F10)/(F10*(1+H10)))</f>
+        <f t="shared" si="3"/>
         <v>553.57000000000005</v>
       </c>
       <c r="M10" s="12">
-        <f>F10/(1+I10-H10)</f>
+        <f t="shared" si="4"/>
         <v>460.51884675555289</v>
       </c>
       <c r="N10" s="12">
-        <f>L10-F10</f>
+        <f t="shared" si="5"/>
         <v>-115.25</v>
       </c>
       <c r="O10" s="12">
-        <f>0.5*(M10-F10)</f>
+        <f t="shared" si="6"/>
         <v>-104.15057662222358</v>
       </c>
       <c r="P10" s="15">
-        <f>N10+O10</f>
+        <f t="shared" si="7"/>
         <v>-219.40057662222358</v>
       </c>
       <c r="Q10" s="12">
-        <f>MAX($P$2:$P$280)-P10</f>
-        <v>302.82769797712137</v>
+        <f t="shared" si="8"/>
+        <v>323.02908665087693</v>
       </c>
       <c r="R10" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q10)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>3.3022078451871001E-3</v>
+        <f t="shared" si="9"/>
+        <v>3.0956964599314209E-3</v>
       </c>
       <c r="S10" s="9">
-        <f>Q10/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>39</v>
       </c>
@@ -1448,7 +1455,7 @@
         <v>135.82</v>
       </c>
       <c r="G11" s="1">
-        <f>E11*F11</f>
+        <f t="shared" si="0"/>
         <v>25.995947999999999</v>
       </c>
       <c r="H11" s="11">
@@ -1458,47 +1465,47 @@
         <v>0.33710000000000001</v>
       </c>
       <c r="J11" s="9">
-        <f>IFERROR(H11/I11,"")</f>
+        <f t="shared" si="1"/>
         <v>0.35657075051913378</v>
       </c>
       <c r="K11" s="9">
-        <f>IFERROR(J11/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>5.6935299599101506E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.13262116928732634</v>
       </c>
       <c r="L11" s="12">
-        <f>F11/(1-(F11*(1+H11)-F11)/(F11*(1+H11)))</f>
+        <f t="shared" si="3"/>
         <v>152.14556400000001</v>
       </c>
       <c r="M11" s="12">
-        <f>F11/(1+I11-H11)</f>
+        <f t="shared" si="4"/>
         <v>111.61147177253677</v>
       </c>
       <c r="N11" s="12">
-        <f>L11-F11</f>
+        <f t="shared" si="5"/>
         <v>16.325564000000014</v>
       </c>
       <c r="O11" s="12">
-        <f>0.5*(M11-F11)</f>
+        <f t="shared" si="6"/>
         <v>-12.10426411373161</v>
       </c>
       <c r="P11" s="15">
-        <f>N11+O11</f>
+        <f t="shared" si="7"/>
         <v>4.2212998862684046</v>
       </c>
       <c r="Q11" s="12">
-        <f>MAX($P$2:$P$280)-P11</f>
-        <v>79.205821468629352</v>
+        <f t="shared" si="8"/>
+        <v>99.407210142384912</v>
       </c>
       <c r="R11" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q11)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.2625334621345539E-2</v>
+        <f t="shared" si="9"/>
+        <v>1.0059632481061082E-2</v>
       </c>
       <c r="S11" s="9">
-        <f>Q11/MAX($Q$2:$Q$28)</f>
-        <v>0.26155408503819672</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>0.30773454852943982</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>39</v>
       </c>
@@ -1518,7 +1525,7 @@
         <v>133.19999999999999</v>
       </c>
       <c r="G12" s="1">
-        <f>E12*F12</f>
+        <f t="shared" si="0"/>
         <v>23.989319999999999</v>
       </c>
       <c r="H12" s="11">
@@ -1528,47 +1535,47 @@
         <v>0.1623</v>
       </c>
       <c r="J12" s="9">
-        <f>IFERROR(H12/I12,"")</f>
+        <f t="shared" si="1"/>
         <v>3.0807147258163893E-2</v>
       </c>
       <c r="K12" s="9">
-        <f>IFERROR(J12/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.9191195755218806E-3</v>
+        <f t="shared" si="2"/>
+        <v>1.1458258664896592E-2</v>
       </c>
       <c r="L12" s="12">
-        <f>F12/(1-(F12*(1+H12)-F12)/(F12*(1+H12)))</f>
+        <f t="shared" si="3"/>
         <v>133.86599999999999</v>
       </c>
       <c r="M12" s="12">
-        <f>F12/(1+I12-H12)</f>
+        <f t="shared" si="4"/>
         <v>115.09548086062384</v>
       </c>
       <c r="N12" s="12">
-        <f>L12-F12</f>
+        <f t="shared" si="5"/>
         <v>0.66599999999999682</v>
       </c>
       <c r="O12" s="12">
-        <f>0.5*(M12-F12)</f>
+        <f t="shared" si="6"/>
         <v>-9.0522595696880757</v>
       </c>
       <c r="P12" s="15">
-        <f>N12+O12</f>
+        <f t="shared" si="7"/>
         <v>-8.3862595696880788</v>
       </c>
       <c r="Q12" s="12">
-        <f>MAX($P$2:$P$280)-P12</f>
-        <v>91.813380924585843</v>
+        <f t="shared" si="8"/>
+        <v>112.0147695983414</v>
       </c>
       <c r="R12" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q12)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.0891658600627997E-2</v>
+        <f t="shared" si="9"/>
+        <v>8.9273941604822715E-3</v>
       </c>
       <c r="S12" s="9">
-        <f>Q12/MAX($Q$2:$Q$28)</f>
-        <v>0.30318686678231904</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>0.34676372570561925</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -1588,7 +1595,7 @@
         <v>700.32</v>
       </c>
       <c r="G13" s="1">
-        <f>E13*F13</f>
+        <f t="shared" si="0"/>
         <v>19.959120000000002</v>
       </c>
       <c r="H13" s="11">
@@ -1598,47 +1605,47 @@
         <v>0.45340000000000003</v>
       </c>
       <c r="J13" s="9">
-        <f>IFERROR(H13/I13,"")</f>
+        <f t="shared" si="1"/>
         <v>-0.14666960741067489</v>
       </c>
       <c r="K13" s="9">
-        <f>IFERROR(J13/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-2.341941403733078E-2</v>
+        <f t="shared" si="2"/>
+        <v>-5.4551571617686659E-2</v>
       </c>
       <c r="L13" s="12">
-        <f>F13/(1-(F13*(1+H13)-F13)/(F13*(1+H13)))</f>
+        <f t="shared" si="3"/>
         <v>653.74872000000005</v>
       </c>
       <c r="M13" s="12">
-        <f>F13/(1+I13-H13)</f>
+        <f t="shared" si="4"/>
         <v>460.76715573392988</v>
       </c>
       <c r="N13" s="12">
-        <f>L13-F13</f>
+        <f t="shared" si="5"/>
         <v>-46.571280000000002</v>
       </c>
       <c r="O13" s="12">
-        <f>0.5*(M13-F13)</f>
+        <f t="shared" si="6"/>
         <v>-119.77642213303508</v>
       </c>
       <c r="P13" s="15">
-        <f>N13+O13</f>
+        <f t="shared" si="7"/>
         <v>-166.34770213303509</v>
       </c>
       <c r="Q13" s="12">
-        <f>MAX($P$2:$P$280)-P13</f>
-        <v>249.77482348793285</v>
+        <f t="shared" si="8"/>
+        <v>269.97621216168841</v>
       </c>
       <c r="R13" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q13)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>4.0036060722041193E-3</v>
+        <f t="shared" si="9"/>
+        <v>3.7040300402507364E-3</v>
       </c>
       <c r="S13" s="9">
-        <f>Q13/MAX($Q$2:$Q$28)</f>
-        <v>0.82480838165207504</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>0.83576440425463305</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1658,7 +1665,7 @@
         <v>77.53</v>
       </c>
       <c r="G14" s="1">
-        <f>E14*F14</f>
+        <f t="shared" si="0"/>
         <v>14.986549</v>
       </c>
       <c r="H14" s="11">
@@ -1669,44 +1676,44 @@
         <v>0.25990000000000002</v>
       </c>
       <c r="J14" s="9">
-        <f>IFERROR(H14/I14,"")</f>
+        <f t="shared" si="1"/>
         <v>0.28833679643526428</v>
       </c>
       <c r="K14" s="9">
-        <f>IFERROR(J14/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.6040068812671704E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.10724256837144747</v>
       </c>
       <c r="L14" s="12">
-        <f>F14/(1-(F14*(1+H14)-F14)/(F14*(1+H14)))</f>
+        <f t="shared" si="3"/>
         <v>83.34</v>
       </c>
       <c r="M14" s="12">
-        <f>F14/(1+I14-H14)</f>
+        <f t="shared" si="4"/>
         <v>65.428298953629579</v>
       </c>
       <c r="N14" s="12">
-        <f>L14-F14</f>
+        <f t="shared" si="5"/>
         <v>5.8100000000000023</v>
       </c>
       <c r="O14" s="12">
-        <f>0.5*(M14-F14)</f>
+        <f t="shared" si="6"/>
         <v>-6.0508505231852112</v>
       </c>
       <c r="P14" s="15">
-        <f>N14+O14</f>
+        <f t="shared" si="7"/>
         <v>-0.24085052318520894</v>
       </c>
       <c r="Q14" s="12">
-        <f>MAX($P$2:$P$280)-P14</f>
-        <v>83.667971878082966</v>
+        <f t="shared" si="8"/>
+        <v>103.86936055183853</v>
       </c>
       <c r="R14" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q14)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.1952004782154311E-2</v>
+        <f t="shared" si="9"/>
+        <v>9.6274781580168254E-3</v>
       </c>
       <c r="S14" s="9">
-        <f>Q14/MAX($Q$2:$Q$28)</f>
-        <v>0.27628903312669928</v>
+        <f t="shared" si="10"/>
+        <v>0.32154801175566694</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
@@ -1729,57 +1736,57 @@
         <v>455.4</v>
       </c>
       <c r="G15" s="1">
-        <f>E15*F15</f>
+        <f t="shared" si="0"/>
         <v>14.982659999999999</v>
       </c>
       <c r="H15" s="11">
-        <v>0.17460000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="I15" s="11">
-        <v>0.15770000000000001</v>
+        <v>0.29699999999999999</v>
       </c>
       <c r="J15" s="9">
-        <f>IFERROR(H15/I15,"")</f>
-        <v>1.1071655041217501</v>
+        <f t="shared" si="1"/>
+        <v>0.84175084175084181</v>
       </c>
       <c r="K15" s="9">
-        <f>IFERROR(J15/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.1767862327215185</v>
+        <f t="shared" si="2"/>
+        <v>0.31307666352065944</v>
       </c>
       <c r="L15" s="12">
-        <f>F15/(1-(F15*(1+H15)-F15)/(F15*(1+H15)))</f>
-        <v>534.91283999999996</v>
+        <f t="shared" si="3"/>
+        <v>569.25</v>
       </c>
       <c r="M15" s="12">
-        <f>F15/(1+I15-H15)</f>
-        <v>463.22856270979554</v>
+        <f t="shared" si="4"/>
+        <v>434.95702005730658</v>
       </c>
       <c r="N15" s="12">
-        <f>L15-F15</f>
-        <v>79.512839999999983</v>
+        <f t="shared" si="5"/>
+        <v>113.85000000000002</v>
       </c>
       <c r="O15" s="12">
-        <f>0.5*(M15-F15)</f>
-        <v>3.9142813548977813</v>
+        <f t="shared" si="6"/>
+        <v>-10.221489971346699</v>
       </c>
       <c r="P15" s="15">
-        <f>N15+O15</f>
-        <v>83.427121354897764</v>
+        <f t="shared" si="7"/>
+        <v>103.62851002865332</v>
       </c>
       <c r="Q15" s="12">
-        <f>MAX($P$2:$P$280)-P15</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R15" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q15)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S15" s="9">
-        <f>Q15/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -1799,7 +1806,7 @@
         <v>10.4</v>
       </c>
       <c r="G16" s="1">
-        <f>E16*F16</f>
+        <f t="shared" si="0"/>
         <v>10.4</v>
       </c>
       <c r="H16" s="11">
@@ -1810,47 +1817,47 @@
         <v>1.8652</v>
       </c>
       <c r="J16" s="9">
-        <f>IFERROR(H16/I16,"")</f>
+        <f t="shared" si="1"/>
         <v>-0.38715171810818388</v>
       </c>
       <c r="K16" s="9">
-        <f>IFERROR(J16/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-6.1818304021584419E-2</v>
+        <f t="shared" si="2"/>
+        <v>-0.14399530379974207</v>
       </c>
       <c r="L16" s="12">
-        <f>F16/(1-(F16*(1+H16)-F16)/(F16*(1+H16)))</f>
+        <f t="shared" si="3"/>
         <v>2.8900000000000006</v>
       </c>
       <c r="M16" s="12">
-        <f>F16/(1+I16-H16)</f>
+        <f t="shared" si="4"/>
         <v>2.8991038938481961</v>
       </c>
       <c r="N16" s="12">
-        <f>L16-F16</f>
+        <f t="shared" si="5"/>
         <v>-7.51</v>
       </c>
       <c r="O16" s="12">
-        <f>0.5*(M16-F16)</f>
+        <f t="shared" si="6"/>
         <v>-3.7504480530759023</v>
       </c>
       <c r="P16" s="15">
-        <f>N16+O16</f>
+        <f t="shared" si="7"/>
         <v>-11.260448053075901</v>
       </c>
       <c r="Q16" s="12">
-        <f>MAX($P$2:$P$280)-P16</f>
-        <v>94.687569407973669</v>
+        <f t="shared" si="8"/>
+        <v>114.88895808172923</v>
       </c>
       <c r="R16" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q16)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.0561048364135003E-2</v>
+        <f t="shared" si="9"/>
+        <v>8.7040566534568459E-3</v>
       </c>
       <c r="S16" s="9">
-        <f>Q16/MAX($Q$2:$Q$28)</f>
-        <v>0.31267803454070875</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>0.35566134081881862</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>36</v>
       </c>
@@ -1870,7 +1877,7 @@
         <v>147.01</v>
       </c>
       <c r="G17" s="1">
-        <f>E17*F17</f>
+        <f t="shared" si="0"/>
         <v>1.4700999999999999E-17</v>
       </c>
       <c r="H17" s="11">
@@ -1881,47 +1888,47 @@
         <v>0.52380000000000004</v>
       </c>
       <c r="J17" s="9">
-        <f>IFERROR(H17/I17,"")</f>
+        <f t="shared" si="1"/>
         <v>0.60672300515722333</v>
       </c>
       <c r="K17" s="9">
-        <f>IFERROR(J17/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>9.6878266156158174E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.22566156719339137</v>
       </c>
       <c r="L17" s="12">
-        <f>F17/(1-(F17*(1+H17)-F17)/(F17*(1+H17)))</f>
+        <f t="shared" si="3"/>
         <v>193.72999999999996</v>
       </c>
       <c r="M17" s="12">
-        <f>F17/(1+I17-H17)</f>
+        <f t="shared" si="4"/>
         <v>121.89899177432211</v>
       </c>
       <c r="N17" s="12">
-        <f>L17-F17</f>
+        <f t="shared" si="5"/>
         <v>46.71999999999997</v>
       </c>
       <c r="O17" s="12">
-        <f>0.5*(M17-F17)</f>
+        <f t="shared" si="6"/>
         <v>-12.555504112838939</v>
       </c>
       <c r="P17" s="15">
-        <f>N17+O17</f>
+        <f t="shared" si="7"/>
         <v>34.164495887161031</v>
       </c>
       <c r="Q17" s="12">
-        <f>MAX($P$2:$P$280)-P17</f>
-        <v>49.262625467736733</v>
+        <f t="shared" si="8"/>
+        <v>69.464014141492299</v>
       </c>
       <c r="R17" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q17)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>2.0299364690883635E-2</v>
+        <f t="shared" si="9"/>
+        <v>1.4395943170849369E-2</v>
       </c>
       <c r="S17" s="9">
-        <f>Q17/MAX($Q$2:$Q$28)</f>
-        <v>0.16267542829407408</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>0.21503950267044389</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -1941,7 +1948,7 @@
         <v>187.36</v>
       </c>
       <c r="G18" s="1">
-        <f>E18*F18</f>
+        <f t="shared" si="0"/>
         <v>1.8736000000000003E-20</v>
       </c>
       <c r="H18" s="11">
@@ -1952,47 +1959,47 @@
         <v>0.52980000000000005</v>
       </c>
       <c r="J18" s="9">
-        <f>IFERROR(H18/I18,"")</f>
+        <f t="shared" si="1"/>
         <v>8.7242692487602053E-2</v>
       </c>
       <c r="K18" s="9">
-        <f>IFERROR(J18/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.3930443894744987E-2</v>
+        <f t="shared" si="2"/>
+        <v>3.2448617483725892E-2</v>
       </c>
       <c r="L18" s="12">
-        <f>F18/(1-(F18*(1+H18)-F18)/(F18*(1+H18)))</f>
+        <f t="shared" si="3"/>
         <v>196.01999999999998</v>
       </c>
       <c r="M18" s="12">
-        <f>F18/(1+I18-H18)</f>
+        <f t="shared" si="4"/>
         <v>126.28921179127629</v>
       </c>
       <c r="N18" s="12">
-        <f>L18-F18</f>
+        <f t="shared" si="5"/>
         <v>8.6599999999999682</v>
       </c>
       <c r="O18" s="12">
-        <f>0.5*(M18-F18)</f>
+        <f t="shared" si="6"/>
         <v>-30.535394104361863</v>
       </c>
       <c r="P18" s="15">
-        <f>N18+O18</f>
+        <f t="shared" si="7"/>
         <v>-21.875394104361895</v>
       </c>
       <c r="Q18" s="12">
-        <f>MAX($P$2:$P$280)-P18</f>
-        <v>105.30251545925967</v>
+        <f t="shared" si="8"/>
+        <v>125.50390413301523</v>
       </c>
       <c r="R18" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q18)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.4964493073946415E-3</v>
+        <f t="shared" si="9"/>
+        <v>7.9678796202240099E-3</v>
       </c>
       <c r="S18" s="9">
-        <f>Q18/MAX($Q$2:$Q$28)</f>
-        <v>0.34773079266750317</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>0.38852199173214769</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -2012,7 +2019,7 @@
         <v>169.34</v>
       </c>
       <c r="G19" s="1">
-        <f>E19*F19</f>
+        <f t="shared" si="0"/>
         <v>1.6934000000000002E-20</v>
       </c>
       <c r="H19" s="11">
@@ -2023,47 +2030,47 @@
         <v>0.4259</v>
       </c>
       <c r="J19" s="9">
-        <f>IFERROR(H19/I19,"")</f>
+        <f t="shared" si="1"/>
         <v>7.1822838403633182E-2</v>
       </c>
       <c r="K19" s="9">
-        <f>IFERROR(J19/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.1468284531513408E-2</v>
+        <f t="shared" si="2"/>
+        <v>2.6713432879047636E-2</v>
       </c>
       <c r="L19" s="12">
-        <f>F19/(1-(F19*(1+H19)-F19)/(F19*(1+H19)))</f>
+        <f t="shared" si="3"/>
         <v>174.52000000000004</v>
       </c>
       <c r="M19" s="12">
-        <f>F19/(1+I19-H19)</f>
+        <f t="shared" si="4"/>
         <v>121.36365448143965</v>
       </c>
       <c r="N19" s="12">
-        <f>L19-F19</f>
+        <f t="shared" si="5"/>
         <v>5.1800000000000352</v>
       </c>
       <c r="O19" s="12">
-        <f>0.5*(M19-F19)</f>
+        <f t="shared" si="6"/>
         <v>-23.988172759280175</v>
       </c>
       <c r="P19" s="15">
-        <f>N19+O19</f>
+        <f t="shared" si="7"/>
         <v>-18.80817275928014</v>
       </c>
       <c r="Q19" s="12">
-        <f>MAX($P$2:$P$280)-P19</f>
-        <v>102.2352941141779</v>
+        <f t="shared" si="8"/>
+        <v>122.43668278793346</v>
       </c>
       <c r="R19" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q19)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.7813578829556158E-3</v>
+        <f t="shared" si="9"/>
+        <v>8.1674868775402105E-3</v>
       </c>
       <c r="S19" s="9">
-        <f>Q19/MAX($Q$2:$Q$28)</f>
-        <v>0.33760219027884886</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>0.37902680547235196</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>40</v>
       </c>
@@ -2083,7 +2090,7 @@
         <v>113.58</v>
       </c>
       <c r="G20" s="1">
-        <f>E20*F20</f>
+        <f t="shared" si="0"/>
         <v>1.1358E-20</v>
       </c>
       <c r="H20" s="11">
@@ -2094,47 +2101,47 @@
         <v>0.16439999999999999</v>
       </c>
       <c r="J20" s="9">
-        <f>IFERROR(H20/I20,"")</f>
+        <f t="shared" si="1"/>
         <v>0.40540789496797319</v>
       </c>
       <c r="K20" s="9">
-        <f>IFERROR(J20/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>6.4733352150274134E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.15078541633235029</v>
       </c>
       <c r="L20" s="12">
-        <f>F20/(1-(F20*(1+H20)-F20)/(F20*(1+H20)))</f>
+        <f t="shared" si="3"/>
         <v>121.15000000000002</v>
       </c>
       <c r="M20" s="12">
-        <f>F20/(1+I20-H20)</f>
+        <f t="shared" si="4"/>
         <v>103.46609203186667</v>
       </c>
       <c r="N20" s="12">
-        <f>L20-F20</f>
+        <f t="shared" si="5"/>
         <v>7.5700000000000216</v>
       </c>
       <c r="O20" s="12">
-        <f>0.5*(M20-F20)</f>
+        <f t="shared" si="6"/>
         <v>-5.0569539840666664</v>
       </c>
       <c r="P20" s="15">
-        <f>N20+O20</f>
+        <f t="shared" si="7"/>
         <v>2.5130460159333552</v>
       </c>
       <c r="Q20" s="12">
-        <f>MAX($P$2:$P$280)-P20</f>
-        <v>80.914075338964409</v>
+        <f t="shared" si="8"/>
+        <v>101.11546401271997</v>
       </c>
       <c r="R20" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q20)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.2358789194720577E-2</v>
+        <f t="shared" si="9"/>
+        <v>9.8896841325299516E-3</v>
       </c>
       <c r="S20" s="9">
-        <f>Q20/MAX($Q$2:$Q$28)</f>
-        <v>0.26719509437038835</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>0.3130227839885002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -2154,7 +2161,7 @@
         <v>64.349999999999994</v>
       </c>
       <c r="G21" s="1">
-        <f>E21*F21</f>
+        <f t="shared" si="0"/>
         <v>6.4349999999999995E-21</v>
       </c>
       <c r="H21" s="11">
@@ -2165,47 +2172,47 @@
         <v>0.67300000000000004</v>
       </c>
       <c r="J21" s="9">
-        <f>IFERROR(H21/I21,"")</f>
+        <f t="shared" si="1"/>
         <v>0.25815360139282906</v>
       </c>
       <c r="K21" s="9">
-        <f>IFERROR(J21/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.1220578570981374E-2</v>
+        <f t="shared" si="2"/>
+        <v>9.6016379421492104E-2</v>
       </c>
       <c r="L21" s="12">
-        <f>F21/(1-(F21*(1+H21)-F21)/(F21*(1+H21)))</f>
+        <f t="shared" si="3"/>
         <v>75.53</v>
       </c>
       <c r="M21" s="12">
-        <f>F21/(1+I21-H21)</f>
+        <f t="shared" si="4"/>
         <v>42.921099260916144</v>
       </c>
       <c r="N21" s="12">
-        <f>L21-F21</f>
+        <f t="shared" si="5"/>
         <v>11.180000000000007</v>
       </c>
       <c r="O21" s="12">
-        <f>0.5*(M21-F21)</f>
+        <f t="shared" si="6"/>
         <v>-10.714450369541925</v>
       </c>
       <c r="P21" s="15">
-        <f>N21+O21</f>
+        <f t="shared" si="7"/>
         <v>0.46554963045808151</v>
       </c>
       <c r="Q21" s="12">
-        <f>MAX($P$2:$P$280)-P21</f>
-        <v>82.961571724439679</v>
+        <f t="shared" si="8"/>
+        <v>103.16296039819524</v>
       </c>
       <c r="R21" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q21)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.2053773563036411E-2</v>
+        <f t="shared" si="9"/>
+        <v>9.6934015478048873E-3</v>
       </c>
       <c r="S21" s="9">
-        <f>Q21/MAX($Q$2:$Q$28)</f>
-        <v>0.27395635299749704</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>0.31936121130073841</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>40</v>
       </c>
@@ -2225,7 +2232,7 @@
         <v>20.82</v>
       </c>
       <c r="G22" s="1">
-        <f>E22*F22</f>
+        <f t="shared" si="0"/>
         <v>2.0820000000000001E-21</v>
       </c>
       <c r="H22" s="13">
@@ -2236,47 +2243,47 @@
         <v>0.7389</v>
       </c>
       <c r="J22" s="9">
-        <f>IFERROR(H22/I22,"")</f>
+        <f t="shared" si="1"/>
         <v>-0.11375530440984462</v>
       </c>
       <c r="K22" s="9">
-        <f>IFERROR(J22/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-1.8163835166322632E-2</v>
+        <f t="shared" si="2"/>
+        <v>-4.2309587820944392E-2</v>
       </c>
       <c r="L22" s="12">
-        <f>F22/(1-(F22*(1+H22)-F22)/(F22*(1+H22)))</f>
+        <f t="shared" si="3"/>
         <v>19.070000000000004</v>
       </c>
       <c r="M22" s="12">
-        <f>F22/(1+I22-H22)</f>
+        <f t="shared" si="4"/>
         <v>11.421024528231593</v>
       </c>
       <c r="N22" s="12">
-        <f>L22-F22</f>
+        <f t="shared" si="5"/>
         <v>-1.7499999999999964</v>
       </c>
       <c r="O22" s="12">
-        <f>0.5*(M22-F22)</f>
+        <f t="shared" si="6"/>
         <v>-4.6994877358842038</v>
       </c>
       <c r="P22" s="15">
-        <f>N22+O22</f>
+        <f t="shared" si="7"/>
         <v>-6.4494877358842002</v>
       </c>
       <c r="Q22" s="12">
-        <f>MAX($P$2:$P$280)-P22</f>
-        <v>89.876609090781969</v>
+        <f t="shared" si="8"/>
+        <v>110.07799776453753</v>
       </c>
       <c r="R22" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q22)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.1126365470574514E-2</v>
+        <f t="shared" si="9"/>
+        <v>9.0844675621648847E-3</v>
       </c>
       <c r="S22" s="9">
-        <f>Q22/MAX($Q$2:$Q$28)</f>
-        <v>0.29679124363839449</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>0.34076806799601772</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -2296,7 +2303,7 @@
         <v>13.04</v>
       </c>
       <c r="G23" s="1">
-        <f>E23*F23</f>
+        <f t="shared" si="0"/>
         <v>1.304E-21</v>
       </c>
       <c r="H23" s="11">
@@ -2307,47 +2314,47 @@
         <v>0.30159999999999998</v>
       </c>
       <c r="J23" s="9">
-        <f>IFERROR(H23/I23,"")</f>
+        <f t="shared" si="1"/>
         <v>0.17290198694895167</v>
       </c>
       <c r="K23" s="9">
-        <f>IFERROR(J23/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.7608059309088662E-2</v>
+        <f t="shared" si="2"/>
+        <v>6.4308313701803621E-2</v>
       </c>
       <c r="L23" s="12">
-        <f>F23/(1-(F23*(1+H23)-F23)/(F23*(1+H23)))</f>
+        <f t="shared" si="3"/>
         <v>13.72</v>
       </c>
       <c r="M23" s="12">
-        <f>F23/(1+I23-H23)</f>
+        <f t="shared" si="4"/>
         <v>10.436569040286594</v>
       </c>
       <c r="N23" s="12">
-        <f>L23-F23</f>
+        <f t="shared" si="5"/>
         <v>0.68000000000000149</v>
       </c>
       <c r="O23" s="12">
-        <f>0.5*(M23-F23)</f>
+        <f t="shared" si="6"/>
         <v>-1.3017154798567026</v>
       </c>
       <c r="P23" s="15">
-        <f>N23+O23</f>
+        <f t="shared" si="7"/>
         <v>-0.62171547985670106</v>
       </c>
       <c r="Q23" s="12">
-        <f>MAX($P$2:$P$280)-P23</f>
-        <v>84.048836834754468</v>
+        <f t="shared" si="8"/>
+        <v>104.25022550851003</v>
       </c>
       <c r="R23" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q23)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.1897844606297952E-2</v>
+        <f t="shared" si="9"/>
+        <v>9.5923053894820514E-3</v>
       </c>
       <c r="S23" s="9">
-        <f>Q23/MAX($Q$2:$Q$28)</f>
-        <v>0.27754672837457672</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>0.3227270540537468</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -2367,7 +2374,7 @@
         <v>11.05</v>
       </c>
       <c r="G24" s="1">
-        <f>E24*F24</f>
+        <f t="shared" si="0"/>
         <v>1.1050000000000002E-21</v>
       </c>
       <c r="H24" s="11">
@@ -2378,47 +2385,47 @@
         <v>0.72170000000000001</v>
       </c>
       <c r="J24" s="9">
-        <f>IFERROR(H24/I24,"")</f>
+        <f t="shared" si="1"/>
         <v>-0.19185470203898922</v>
       </c>
       <c r="K24" s="9">
-        <f>IFERROR(J24/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-3.0634326915998825E-2</v>
+        <f t="shared" si="2"/>
+        <v>-7.1357493234198988E-2</v>
       </c>
       <c r="L24" s="12">
-        <f>F24/(1-(F24*(1+H24)-F24)/(F24*(1+H24)))</f>
+        <f t="shared" si="3"/>
         <v>9.52</v>
       </c>
       <c r="M24" s="12">
-        <f>F24/(1+I24-H24)</f>
+        <f t="shared" si="4"/>
         <v>5.9403443042581081</v>
       </c>
       <c r="N24" s="12">
-        <f>L24-F24</f>
+        <f t="shared" si="5"/>
         <v>-1.5300000000000011</v>
       </c>
       <c r="O24" s="12">
-        <f>0.5*(M24-F24)</f>
+        <f t="shared" si="6"/>
         <v>-2.5548278478709463</v>
       </c>
       <c r="P24" s="15">
-        <f>N24+O24</f>
+        <f t="shared" si="7"/>
         <v>-4.0848278478709474</v>
       </c>
       <c r="Q24" s="12">
-        <f>MAX($P$2:$P$280)-P24</f>
-        <v>87.511949202768704</v>
+        <f t="shared" si="8"/>
+        <v>107.71333787652426</v>
       </c>
       <c r="R24" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q24)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.1427010929478438E-2</v>
+        <f t="shared" si="9"/>
+        <v>9.2839013228457976E-3</v>
       </c>
       <c r="S24" s="9">
-        <f>Q24/MAX($Q$2:$Q$28)</f>
-        <v>0.28898264520499783</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>0.33344779875175323</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -2438,7 +2445,7 @@
         <v>10.47</v>
       </c>
       <c r="G25" s="1">
-        <f>E25*F25</f>
+        <f t="shared" si="0"/>
         <v>1.0470000000000001E-21</v>
       </c>
       <c r="H25" s="11">
@@ -2449,47 +2456,47 @@
         <v>0.85599999999999998</v>
       </c>
       <c r="J25" s="9">
-        <f>IFERROR(H25/I25,"")</f>
+        <f t="shared" si="1"/>
         <v>-0.45189192084192487</v>
       </c>
       <c r="K25" s="9">
-        <f>IFERROR(J25/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>-7.2155671383841796E-2</v>
+        <f t="shared" si="2"/>
+        <v>-0.16807445604076854</v>
       </c>
       <c r="L25" s="12">
-        <f>F25/(1-(F25*(1+H25)-F25)/(F25*(1+H25)))</f>
+        <f t="shared" si="3"/>
         <v>6.419999999999999</v>
       </c>
       <c r="M25" s="12">
-        <f>F25/(1+I25-H25)</f>
+        <f t="shared" si="4"/>
         <v>4.6682312480197874</v>
       </c>
       <c r="N25" s="12">
-        <f>L25-F25</f>
+        <f t="shared" si="5"/>
         <v>-4.0500000000000016</v>
       </c>
       <c r="O25" s="12">
-        <f>0.5*(M25-F25)</f>
+        <f t="shared" si="6"/>
         <v>-2.9008843759901066</v>
       </c>
       <c r="P25" s="15">
-        <f>N25+O25</f>
+        <f t="shared" si="7"/>
         <v>-6.9508843759901087</v>
       </c>
       <c r="Q25" s="12">
-        <f>MAX($P$2:$P$280)-P25</f>
-        <v>90.378005730887878</v>
+        <f t="shared" si="8"/>
+        <v>110.57939440464344</v>
       </c>
       <c r="R25" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q25)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.1064638923076357E-2</v>
+        <f t="shared" si="9"/>
+        <v>9.043276149087032E-3</v>
       </c>
       <c r="S25" s="9">
-        <f>Q25/MAX($Q$2:$Q$28)</f>
-        <v>0.29844695955690265</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>0.34232023979981507</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>36</v>
       </c>
@@ -2509,7 +2516,7 @@
         <v>167.24</v>
       </c>
       <c r="G26" s="1">
-        <f>E26*F26</f>
+        <f t="shared" si="0"/>
         <v>19.98518</v>
       </c>
       <c r="H26" s="11">
@@ -2520,47 +2527,47 @@
         <v>0.26790000000000003</v>
       </c>
       <c r="J26" s="9">
-        <f>IFERROR(H26/I26,"")</f>
+        <f t="shared" si="1"/>
         <v>0.51714598979956872</v>
       </c>
       <c r="K26" s="9">
-        <f>IFERROR(J26/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>8.2575090140862145E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.19234473315497108</v>
       </c>
       <c r="L26" s="12">
-        <f>F26/(1-(F26*(1+H26)-F26)/(F26*(1+H26)))</f>
+        <f t="shared" si="3"/>
         <v>190.41</v>
       </c>
       <c r="M26" s="12">
-        <f>F26/(1+I26-H26)</f>
+        <f t="shared" si="4"/>
         <v>148.08431772538498</v>
       </c>
       <c r="N26" s="12">
-        <f>L26-F26</f>
+        <f t="shared" si="5"/>
         <v>23.169999999999987</v>
       </c>
       <c r="O26" s="12">
-        <f>0.5*(M26-F26)</f>
+        <f t="shared" si="6"/>
         <v>-9.5778411373075159</v>
       </c>
       <c r="P26" s="15">
-        <f>N26+O26</f>
+        <f t="shared" si="7"/>
         <v>13.592158862692472</v>
       </c>
       <c r="Q26" s="12">
-        <f>MAX($P$2:$P$280)-P26</f>
-        <v>69.834962492205293</v>
+        <f t="shared" si="8"/>
+        <v>90.036351165960852</v>
       </c>
       <c r="R26" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q26)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.4319475006686174E-2</v>
+        <f t="shared" si="9"/>
+        <v>1.1106625124742505E-2</v>
       </c>
       <c r="S26" s="9">
-        <f>Q26/MAX($Q$2:$Q$28)</f>
-        <v>0.23060956101010721</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>0.27872521356960728</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>77</v>
       </c>
@@ -2572,7 +2579,7 @@
       </c>
       <c r="D27" s="8">
         <f ca="1">TODAY()-20</f>
-        <v>45602</v>
+        <v>45603</v>
       </c>
       <c r="E27" s="2">
         <v>1E-35</v>
@@ -2581,7 +2588,7 @@
         <v>2742.9</v>
       </c>
       <c r="G27" s="1">
-        <f>E27*F27</f>
+        <f t="shared" si="0"/>
         <v>2.7429E-32</v>
       </c>
       <c r="H27" s="11">
@@ -2591,47 +2598,47 @@
         <v>0.5</v>
       </c>
       <c r="J27" s="9">
-        <f>IFERROR(H27/I27,"")</f>
+        <f t="shared" si="1"/>
         <v>0.2</v>
       </c>
       <c r="K27" s="9">
-        <f>IFERROR(J27/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.1934924284288055E-2</v>
+        <f t="shared" si="2"/>
+        <v>7.4387015252508681E-2</v>
       </c>
       <c r="L27" s="12">
-        <f>F27/(1-(F27*(1+H27)-F27)/(F27*(1+H27)))</f>
+        <f t="shared" si="3"/>
         <v>3017.1900000000005</v>
       </c>
       <c r="M27" s="12">
-        <f>F27/(1+I27-H27)</f>
+        <f t="shared" si="4"/>
         <v>1959.214285714286</v>
       </c>
       <c r="N27" s="12">
-        <f>L27-F27</f>
+        <f t="shared" si="5"/>
         <v>274.29000000000042</v>
       </c>
       <c r="O27" s="12">
-        <f>0.5*(M27-F27)</f>
+        <f t="shared" si="6"/>
         <v>-391.84285714285704</v>
       </c>
       <c r="P27" s="15">
-        <f>N27+O27</f>
+        <f t="shared" si="7"/>
         <v>-117.55285714285662</v>
       </c>
       <c r="Q27" s="12">
-        <f>MAX($P$2:$P$280)-P27</f>
-        <v>200.97997849775439</v>
+        <f t="shared" si="8"/>
+        <v>221.18136717150995</v>
       </c>
       <c r="R27" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q27)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>4.9756199969499615E-3</v>
+        <f t="shared" si="9"/>
+        <v>4.5211765022890611E-3</v>
       </c>
       <c r="S27" s="9">
-        <f>Q27/MAX($Q$2:$Q$28)</f>
-        <v>0.66367766172081932</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>0.68471037535563517</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>38</v>
       </c>
@@ -2651,7 +2658,7 @@
         <v>86.6</v>
       </c>
       <c r="G28" s="1">
-        <f>E28*F28</f>
+        <f t="shared" si="0"/>
         <v>8.6599999999999988E-34</v>
       </c>
       <c r="H28" s="11">
@@ -2662,47 +2669,47 @@
         <v>0.17249999999999999</v>
       </c>
       <c r="J28" s="9">
-        <f>IFERROR(H28/I28,"")</f>
+        <f t="shared" si="1"/>
         <v>0.19011279579609788</v>
       </c>
       <c r="K28" s="9">
-        <f>IFERROR(J28/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.0356188696113506E-2</v>
+        <f t="shared" si="2"/>
+        <v>7.0709617202906999E-2</v>
       </c>
       <c r="L28" s="12">
-        <f>F28/(1-(F28*(1+H28)-F28)/(F28*(1+H28)))</f>
+        <f t="shared" si="3"/>
         <v>89.44</v>
       </c>
       <c r="M28" s="12">
-        <f>F28/(1+I28-H28)</f>
+        <f t="shared" si="4"/>
         <v>75.984538772119137</v>
       </c>
       <c r="N28" s="12">
-        <f>L28-F28</f>
+        <f t="shared" si="5"/>
         <v>2.8400000000000034</v>
       </c>
       <c r="O28" s="12">
-        <f>0.5*(M28-F28)</f>
+        <f t="shared" si="6"/>
         <v>-5.3077306139404286</v>
       </c>
       <c r="P28" s="15">
-        <f>N28+O28</f>
+        <f t="shared" si="7"/>
         <v>-2.4677306139404251</v>
       </c>
       <c r="Q28" s="12">
-        <f>MAX($P$2:$P$280)-P28</f>
-        <v>85.894851968838196</v>
+        <f t="shared" si="8"/>
+        <v>106.09624064259376</v>
       </c>
       <c r="R28" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q28)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.1642141258509766E-2</v>
+        <f t="shared" si="9"/>
+        <v>9.4254046509404475E-3</v>
       </c>
       <c r="S28" s="9">
-        <f>Q28/MAX($Q$2:$Q$28)</f>
-        <v>0.28364265403268213</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>0.32844175656930963</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>74</v>
       </c>
@@ -2722,7 +2729,7 @@
         <v>56</v>
       </c>
       <c r="G29" s="1">
-        <f>E29*F29</f>
+        <f t="shared" si="0"/>
         <v>5.5999999999999999E-34</v>
       </c>
       <c r="H29" s="11">
@@ -2732,47 +2739,47 @@
         <v>0.19</v>
       </c>
       <c r="J29" s="9">
-        <f>IFERROR(H29/I29,"")</f>
+        <f t="shared" si="1"/>
         <v>0.42105263157894735</v>
       </c>
       <c r="K29" s="9">
-        <f>IFERROR(J29/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>6.7231419545869572E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.15660424263686035</v>
       </c>
       <c r="L29" s="12">
-        <f>F29/(1-(F29*(1+H29)-F29)/(F29*(1+H29)))</f>
+        <f t="shared" si="3"/>
         <v>60.480000000000004</v>
       </c>
       <c r="M29" s="12">
-        <f>F29/(1+I29-H29)</f>
+        <f t="shared" si="4"/>
         <v>50.450450450450454</v>
       </c>
       <c r="N29" s="12">
-        <f>L29-F29</f>
+        <f t="shared" si="5"/>
         <v>4.480000000000004</v>
       </c>
       <c r="O29" s="12">
-        <f>0.5*(M29-F29)</f>
+        <f t="shared" si="6"/>
         <v>-2.7747747747747731</v>
       </c>
       <c r="P29" s="15">
-        <f>N29+O29</f>
+        <f t="shared" si="7"/>
         <v>1.7052252252252309</v>
       </c>
       <c r="Q29" s="12">
-        <f>MAX($P$2:$P$280)-P29</f>
-        <v>81.72189612967253</v>
+        <f t="shared" si="8"/>
+        <v>101.92328480342809</v>
       </c>
       <c r="R29" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q29)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.223662258659841E-2</v>
+        <f t="shared" si="9"/>
+        <v>9.811300743776322E-3</v>
       </c>
       <c r="S29" s="9">
-        <f>Q29/MAX($Q$2:$Q$28)</f>
-        <v>0.26986268652296996</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>0.31552355195055437</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>77</v>
       </c>
@@ -2792,7 +2799,7 @@
         <v>20.399999999999999</v>
       </c>
       <c r="G30" s="1">
-        <f>E30*F30</f>
+        <f t="shared" si="0"/>
         <v>2.0399999999999999E-34</v>
       </c>
       <c r="H30" s="11">
@@ -2803,46 +2810,46 @@
         <v>0.15</v>
       </c>
       <c r="J30" s="9">
-        <f>IFERROR(H30/I30,"")</f>
+        <f t="shared" si="1"/>
         <v>0.2614379084967326</v>
       </c>
       <c r="K30" s="9">
-        <f>IFERROR(J30/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.1744999064428918E-2</v>
+        <f t="shared" si="2"/>
+        <v>9.7237928434652079E-2</v>
       </c>
       <c r="L30" s="12">
         <v>21.2</v>
       </c>
       <c r="M30" s="12">
-        <f>F30/(1+I30-H30)</f>
+        <f t="shared" si="4"/>
         <v>18.365401588702561</v>
       </c>
       <c r="N30" s="12">
-        <f>L30-F30</f>
+        <f t="shared" si="5"/>
         <v>0.80000000000000071</v>
       </c>
       <c r="O30" s="12">
-        <f>0.5*(M30-F30)</f>
+        <f t="shared" si="6"/>
         <v>-1.0172992056487189</v>
       </c>
       <c r="P30" s="15">
-        <f>N30+O30</f>
+        <f t="shared" si="7"/>
         <v>-0.21729920564871819</v>
       </c>
       <c r="Q30" s="12">
-        <f>MAX($P$2:$P$280)-P30</f>
-        <v>83.644420560546479</v>
+        <f t="shared" si="8"/>
+        <v>103.84580923430204</v>
       </c>
       <c r="R30" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q30)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.1955370044988768E-2</v>
+        <f t="shared" si="9"/>
+        <v>9.6296615855123308E-3</v>
       </c>
       <c r="S30" s="9">
-        <f>Q30/MAX($Q$2:$Q$28)</f>
-        <v>0.27621126178116578</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>0.32147510402534252</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -2862,7 +2869,7 @@
         <v>47.42</v>
       </c>
       <c r="G31" s="1">
-        <f>E31*F31</f>
+        <f t="shared" si="0"/>
         <v>4.7420000000000006E-44</v>
       </c>
       <c r="H31" s="11">
@@ -2873,47 +2880,47 @@
         <v>0.4</v>
       </c>
       <c r="J31" s="9">
-        <f>IFERROR(H31/I31,"")</f>
+        <f t="shared" si="1"/>
         <v>5.0084352593842141E-2</v>
       </c>
       <c r="K31" s="9">
-        <f>IFERROR(J31/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>7.9972000395596727E-3</v>
+        <f t="shared" si="2"/>
+        <v>1.8628127501550788E-2</v>
       </c>
       <c r="L31" s="12">
         <f>F31/(1-(F31*(1+H31)-F31)/(F31*(1+H31)))</f>
         <v>48.37</v>
       </c>
       <c r="M31" s="12">
-        <f>F31/(1+I31-H31)</f>
+        <f t="shared" si="4"/>
         <v>34.36315902075247</v>
       </c>
       <c r="N31" s="12">
-        <f>L31-F31</f>
+        <f t="shared" si="5"/>
         <v>0.94999999999999574</v>
       </c>
       <c r="O31" s="12">
-        <f>0.5*(M31-F31)</f>
+        <f t="shared" si="6"/>
         <v>-6.5284204896237661</v>
       </c>
       <c r="P31" s="15">
-        <f>N31+O31</f>
+        <f t="shared" si="7"/>
         <v>-5.5784204896237704</v>
       </c>
       <c r="Q31" s="12">
-        <f>MAX($P$2:$P$280)-P31</f>
-        <v>89.005541844521531</v>
+        <f t="shared" si="8"/>
+        <v>109.20693051827709</v>
       </c>
       <c r="R31" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q31)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.123525546023685E-2</v>
+        <f t="shared" si="9"/>
+        <v>9.1569280013106668E-3</v>
       </c>
       <c r="S31" s="9">
-        <f>Q31/MAX($Q$2:$Q$28)</f>
-        <v>0.29391479854410774</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>0.33807150820540705</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>39</v>
       </c>
@@ -2933,7 +2940,7 @@
         <v>41.8</v>
       </c>
       <c r="G32" s="1">
-        <f>E32*F32</f>
+        <f t="shared" si="0"/>
         <v>4.1799999999999994E-44</v>
       </c>
       <c r="H32" s="11">
@@ -2943,11 +2950,11 @@
         <v>0.4</v>
       </c>
       <c r="J32" s="9">
-        <f>IFERROR(H32/I32,"")</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K32" s="9">
-        <f>IFERROR(J32/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L32" s="12">
@@ -2955,35 +2962,35 @@
         <v>41.8</v>
       </c>
       <c r="M32" s="12">
-        <f>F32/(1+I32-H32)</f>
+        <f t="shared" si="4"/>
         <v>29.857142857142858</v>
       </c>
       <c r="N32" s="12">
-        <f>L32-F32</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O32" s="12">
-        <f>0.5*(M32-F32)</f>
+        <f t="shared" si="6"/>
         <v>-5.9714285714285698</v>
       </c>
       <c r="P32" s="15">
-        <f>N32+O32</f>
+        <f t="shared" si="7"/>
         <v>-5.9714285714285698</v>
       </c>
       <c r="Q32" s="12">
-        <f>MAX($P$2:$P$280)-P32</f>
-        <v>89.398549926326339</v>
+        <f t="shared" si="8"/>
+        <v>109.5999386000819</v>
       </c>
       <c r="R32" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q32)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.1185863762042041E-2</v>
+        <f t="shared" si="9"/>
+        <v>9.1240927027239471E-3</v>
       </c>
       <c r="S32" s="9">
-        <f>Q32/MAX($Q$2:$Q$28)</f>
-        <v>0.29521259291506552</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>0.33928814193297463</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>77</v>
       </c>
@@ -3003,7 +3010,7 @@
         <v>153.7552</v>
       </c>
       <c r="G33" s="1">
-        <f>E33*F33</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H33" s="11">
@@ -3013,53 +3020,128 @@
         <v>0.19</v>
       </c>
       <c r="J33" s="9">
-        <f>IFERROR(H33/I33,"")</f>
+        <f t="shared" si="1"/>
         <v>0.36842105263157898</v>
       </c>
       <c r="K33" s="9">
-        <f>IFERROR(J33/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>5.8827492102635888E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.13702871230725283</v>
       </c>
       <c r="L33" s="12">
         <f>F33/(1-(F33*(1+H33)-F33)/(F33*(1+H33)))</f>
         <v>164.51806400000001</v>
       </c>
       <c r="M33" s="12">
-        <f>F33/(1+I33-H33)</f>
+        <f t="shared" si="4"/>
         <v>137.28142857142859</v>
       </c>
       <c r="N33" s="12">
-        <f>L33-F33</f>
+        <f t="shared" si="5"/>
         <v>10.762864000000008</v>
       </c>
       <c r="O33" s="12">
-        <f>0.5*(M33-F33)</f>
+        <f t="shared" si="6"/>
         <v>-8.2368857142857053</v>
       </c>
       <c r="P33" s="15">
-        <f>N33+O33</f>
+        <f t="shared" si="7"/>
         <v>2.5259782857143023</v>
       </c>
       <c r="Q33" s="12">
-        <f>MAX($P$2:$P$280)-P33</f>
-        <v>80.901143069183462</v>
+        <f t="shared" si="8"/>
+        <v>101.10253174293902</v>
       </c>
       <c r="R33" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q33)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.2360764781096351E-2</v>
+        <f t="shared" si="9"/>
+        <v>9.8909491459875324E-3</v>
       </c>
       <c r="S33" s="9">
-        <f>Q33/MAX($Q$2:$Q$28)</f>
-        <v>0.26715238932766161</v>
+        <f t="shared" si="10"/>
+        <v>0.31298274960672046</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" t="s">
+        <v>89</v>
+      </c>
+      <c r="D34" s="8">
+        <v>45623</v>
+      </c>
+      <c r="E34" s="2">
+        <v>1.9595</v>
+      </c>
+      <c r="F34" s="1">
+        <v>15.3</v>
+      </c>
+      <c r="G34" s="1">
+        <f t="shared" ref="G34" si="11">E34*F34</f>
+        <v>29.980350000000001</v>
+      </c>
+      <c r="H34" s="11">
+        <v>0.35</v>
+      </c>
+      <c r="I34" s="11">
+        <v>0.39532299999999998</v>
+      </c>
+      <c r="J34" s="9">
+        <f t="shared" ref="J34" si="12">IFERROR(H34/I34,"")</f>
+        <v>0.88535197800279775</v>
+      </c>
+      <c r="K34" s="9">
+        <f t="shared" ref="K34" si="13">IFERROR(J34/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>0.3292934554576642</v>
+      </c>
+      <c r="L34" s="12">
+        <f t="shared" ref="L34" si="14">F34/(1-(F34*(1+H34)-F34)/(F34*(1+H34)))</f>
+        <v>20.655000000000001</v>
+      </c>
+      <c r="M34" s="12">
+        <f t="shared" ref="M34" si="15">F34/(1+I34-H34)</f>
+        <v>14.636624277854791</v>
+      </c>
+      <c r="N34" s="12">
+        <f t="shared" ref="N34" si="16">L34-F34</f>
+        <v>5.3550000000000004</v>
+      </c>
+      <c r="O34" s="12">
+        <f t="shared" ref="O34" si="17">0.5*(M34-F34)</f>
+        <v>-0.33168786107260484</v>
+      </c>
+      <c r="P34" s="15">
+        <f t="shared" ref="P34" si="18">N34+O34</f>
+        <v>5.0233121389273956</v>
+      </c>
+      <c r="Q34" s="12">
+        <f t="shared" ref="Q34" si="19">MAX($P$2:$P$280)-P34</f>
+        <v>98.605197889725929</v>
+      </c>
+      <c r="R34" s="9">
+        <f t="shared" ref="R34" si="20">IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q34)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.0141453203291973E-2</v>
+      </c>
+      <c r="S34" s="9">
+        <f t="shared" ref="S34" si="21">Q34/MAX($Q$2:$Q$28)</f>
+        <v>0.30525176203806181</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:S33" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Banking"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S33">
       <sortCondition descending="1" ref="G1:G33"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="R2:R33">
+  <conditionalFormatting sqref="R2:R34">
     <cfRule type="iconSet" priority="3">
       <iconSet iconSet="3Symbols">
         <cfvo type="percent" val="0"/>
@@ -3098,7 +3180,7 @@
               <x14:cfIcon iconSet="3Arrows" iconId="0"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>S2:S33</xm:sqref>
+          <xm:sqref>S2:S34</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/Open Positions.xlsx
+++ b/Open Positions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\StockSillines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02260CCE-BB48-45B5-9D7C-0FDB7BD3B96A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84E69184-605A-494E-A83C-E5412893D444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Positions" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="98">
   <si>
     <t>Name</t>
   </si>
@@ -246,70 +246,94 @@
     <t>Tolerance</t>
   </si>
   <si>
+    <t>Unit Profit</t>
+  </si>
+  <si>
+    <t>Unit Half Loss</t>
+  </si>
+  <si>
+    <t>Balance Risk</t>
+  </si>
+  <si>
+    <t>Normalized Risk</t>
+  </si>
+  <si>
+    <t>Normalized Risk %</t>
+  </si>
+  <si>
+    <t>Automotive</t>
+  </si>
+  <si>
+    <t>Aptive Autoparts</t>
+  </si>
+  <si>
+    <t>APTV</t>
+  </si>
+  <si>
+    <t>Forex</t>
+  </si>
+  <si>
+    <t>Mexican Peso</t>
+  </si>
+  <si>
+    <t>USDMXN=X</t>
+  </si>
+  <si>
+    <t>Japan Yen</t>
+  </si>
+  <si>
+    <t>USDJPY=X</t>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <t>GC=F</t>
+  </si>
+  <si>
+    <t>Risk Mix</t>
+  </si>
+  <si>
+    <t>Ticker</t>
+  </si>
+  <si>
+    <t>Palantir</t>
+  </si>
+  <si>
+    <t>PLTR</t>
+  </si>
+  <si>
+    <t>ING Group NV</t>
+  </si>
+  <si>
+    <t>ING</t>
+  </si>
+  <si>
+    <t>Industrials</t>
+  </si>
+  <si>
+    <t>3M</t>
+  </si>
+  <si>
+    <t>MMM</t>
+  </si>
+  <si>
+    <t>Excelon</t>
+  </si>
+  <si>
+    <t>EXC</t>
+  </si>
+  <si>
+    <t>PCG</t>
+  </si>
+  <si>
+    <t>PG&amp;E</t>
+  </si>
+  <si>
+    <t>APA</t>
+  </si>
+  <si>
     <t>Expected Return QoQ%</t>
-  </si>
-  <si>
-    <t>Unit Profit</t>
-  </si>
-  <si>
-    <t>Unit Half Loss</t>
-  </si>
-  <si>
-    <t>Balance Risk</t>
-  </si>
-  <si>
-    <t>Normalized Risk</t>
-  </si>
-  <si>
-    <t>Normalized Risk %</t>
-  </si>
-  <si>
-    <t>Automotive</t>
-  </si>
-  <si>
-    <t>Aptive Autoparts</t>
-  </si>
-  <si>
-    <t>APTV</t>
-  </si>
-  <si>
-    <t>Forex</t>
-  </si>
-  <si>
-    <t>Mexican Peso</t>
-  </si>
-  <si>
-    <t>USDMXN=X</t>
-  </si>
-  <si>
-    <t>Japan Yen</t>
-  </si>
-  <si>
-    <t>USDJPY=X</t>
-  </si>
-  <si>
-    <t>Gold</t>
-  </si>
-  <si>
-    <t>GC=F</t>
-  </si>
-  <si>
-    <t>Risk Mix</t>
-  </si>
-  <si>
-    <t>Ticker</t>
-  </si>
-  <si>
-    <t>Palantir</t>
-  </si>
-  <si>
-    <t>PLTR</t>
-  </si>
-  <si>
-    <t>ING Group NV</t>
-  </si>
-  <si>
-    <t>ING</t>
   </si>
 </sst>
 </file>
@@ -718,8 +742,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:S34"/>
+  <dimension ref="A1:S38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
@@ -751,7 +774,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D1" s="17" t="s">
         <v>1</v>
@@ -766,7 +789,7 @@
         <v>4</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="I1" s="16" t="s">
         <v>63</v>
@@ -784,25 +807,25 @@
         <v>67</v>
       </c>
       <c r="N1" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="O1" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="P1" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="P1" s="16" t="s">
+      <c r="Q1" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="Q1" s="16" t="s">
+      <c r="R1" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="S1" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="R1" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="S1" s="16" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>36</v>
       </c>
@@ -837,7 +860,7 @@
       </c>
       <c r="K2" s="9">
         <f t="shared" ref="K2:K33" si="2">IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.1599897449786014E-2</v>
+        <v>6.2462790329697289E-3</v>
       </c>
       <c r="L2" s="12">
         <f t="shared" ref="L2:L29" si="3">F2/(1-(F2*(1+H2)-F2)/(F2*(1+H2)))</f>
@@ -865,14 +888,14 @@
       </c>
       <c r="R2" s="9">
         <f t="shared" ref="R2:R33" si="9">IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q2)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>7.5837127481716074E-3</v>
+        <v>7.5837127481716065E-3</v>
       </c>
       <c r="S2" s="9">
         <f t="shared" ref="S2:S33" si="10">Q2/MAX($Q$2:$Q$28)</f>
         <v>0.4082032854788411</v>
       </c>
     </row>
-    <row r="3" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>38</v>
       </c>
@@ -908,7 +931,7 @@
       </c>
       <c r="K3" s="9">
         <f t="shared" si="2"/>
-        <v>0.3430812540299637</v>
+        <v>9.9212565644544476E-2</v>
       </c>
       <c r="L3" s="12">
         <f t="shared" si="3"/>
@@ -943,7 +966,7 @@
         <v>0.29282789330231596</v>
       </c>
     </row>
-    <row r="4" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -979,7 +1002,7 @@
       </c>
       <c r="K4" s="9">
         <f t="shared" si="2"/>
-        <v>0.20725236093080118</v>
+        <v>5.9933436240844885E-2</v>
       </c>
       <c r="L4" s="12">
         <f t="shared" si="3"/>
@@ -1007,14 +1030,14 @@
       </c>
       <c r="R4" s="9">
         <f t="shared" si="9"/>
-        <v>1.2815958290126269E-2</v>
+        <v>1.2815958290126271E-2</v>
       </c>
       <c r="S4" s="9">
         <f t="shared" si="10"/>
         <v>0.24155013537430298</v>
       </c>
     </row>
-    <row r="5" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -1049,7 +1072,7 @@
       </c>
       <c r="K5" s="9">
         <f t="shared" si="2"/>
-        <v>8.074152029829762E-2</v>
+        <v>2.3348910174309765E-2</v>
       </c>
       <c r="L5" s="12">
         <f t="shared" si="3"/>
@@ -1119,7 +1142,7 @@
       </c>
       <c r="K6" s="9">
         <f t="shared" si="2"/>
-        <v>0.35762988102167631</v>
+        <v>0.10341975153272248</v>
       </c>
       <c r="L6" s="12">
         <f>F6/(1-(F6*(1+H6)-F6)/(F6*(1+H6)))</f>
@@ -1154,7 +1177,7 @@
         <v>0.1133559605561654</v>
       </c>
     </row>
-    <row r="7" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>36</v>
       </c>
@@ -1189,7 +1212,7 @@
       </c>
       <c r="K7" s="9">
         <f t="shared" si="2"/>
-        <v>-6.7535061491822326E-2</v>
+        <v>-1.9529853767471024E-2</v>
       </c>
       <c r="L7" s="12">
         <f t="shared" si="3"/>
@@ -1224,7 +1247,7 @@
         <v>0.45061924046484586</v>
       </c>
     </row>
-    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -1259,7 +1282,7 @@
       </c>
       <c r="K8" s="9">
         <f t="shared" si="2"/>
-        <v>-5.6783981108785249E-2</v>
+        <v>-1.6420846044890289E-2</v>
       </c>
       <c r="L8" s="12">
         <f t="shared" si="3"/>
@@ -1294,7 +1317,7 @@
         <v>0.37228046077970073</v>
       </c>
     </row>
-    <row r="9" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>38</v>
       </c>
@@ -1329,7 +1352,7 @@
       </c>
       <c r="K9" s="9">
         <f t="shared" si="2"/>
-        <v>0.15203185599052868</v>
+        <v>4.3964717731866845E-2</v>
       </c>
       <c r="L9" s="12">
         <f t="shared" si="3"/>
@@ -1357,14 +1380,14 @@
       </c>
       <c r="R9" s="9">
         <f t="shared" si="9"/>
-        <v>1.0016467117784552E-2</v>
+        <v>1.0016467117784554E-2</v>
       </c>
       <c r="S9" s="9">
         <f t="shared" si="10"/>
         <v>0.30906071207830499</v>
       </c>
     </row>
-    <row r="10" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -1400,7 +1423,7 @@
       </c>
       <c r="K10" s="9">
         <f t="shared" si="2"/>
-        <v>-0.22889736262189977</v>
+        <v>-6.619275856151835E-2</v>
       </c>
       <c r="L10" s="12">
         <f t="shared" si="3"/>
@@ -1428,14 +1451,14 @@
       </c>
       <c r="R10" s="9">
         <f t="shared" si="9"/>
-        <v>3.0956964599314209E-3</v>
+        <v>3.0956964599314213E-3</v>
       </c>
       <c r="S10" s="9">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>39</v>
       </c>
@@ -1470,7 +1493,7 @@
       </c>
       <c r="K11" s="9">
         <f t="shared" si="2"/>
-        <v>0.13262116928732634</v>
+        <v>3.8351516759426205E-2</v>
       </c>
       <c r="L11" s="12">
         <f t="shared" si="3"/>
@@ -1498,14 +1521,14 @@
       </c>
       <c r="R11" s="9">
         <f t="shared" si="9"/>
-        <v>1.0059632481061082E-2</v>
+        <v>1.0059632481061084E-2</v>
       </c>
       <c r="S11" s="9">
         <f t="shared" si="10"/>
         <v>0.30773454852943982</v>
       </c>
     </row>
-    <row r="12" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>39</v>
       </c>
@@ -1540,7 +1563,7 @@
       </c>
       <c r="K12" s="9">
         <f t="shared" si="2"/>
-        <v>1.1458258664896592E-2</v>
+        <v>3.3135102154661549E-3</v>
       </c>
       <c r="L12" s="12">
         <f t="shared" si="3"/>
@@ -1575,7 +1598,7 @@
         <v>0.34676372570561925</v>
       </c>
     </row>
-    <row r="13" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -1610,7 +1633,7 @@
       </c>
       <c r="K13" s="9">
         <f t="shared" si="2"/>
-        <v>-5.4551571617686659E-2</v>
+        <v>-1.5775275730046508E-2</v>
       </c>
       <c r="L13" s="12">
         <f t="shared" si="3"/>
@@ -1645,7 +1668,7 @@
         <v>0.83576440425463305</v>
       </c>
     </row>
-    <row r="14" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1681,7 +1704,7 @@
       </c>
       <c r="K14" s="9">
         <f t="shared" si="2"/>
-        <v>0.10724256837144747</v>
+        <v>3.1012508638879263E-2</v>
       </c>
       <c r="L14" s="12">
         <f t="shared" si="3"/>
@@ -1709,7 +1732,7 @@
       </c>
       <c r="R14" s="9">
         <f t="shared" si="9"/>
-        <v>9.6274781580168254E-3</v>
+        <v>9.6274781580168271E-3</v>
       </c>
       <c r="S14" s="9">
         <f t="shared" si="10"/>
@@ -1751,7 +1774,7 @@
       </c>
       <c r="K15" s="9">
         <f t="shared" si="2"/>
-        <v>0.31307666352065944</v>
+        <v>9.053580942258535E-2</v>
       </c>
       <c r="L15" s="12">
         <f t="shared" si="3"/>
@@ -1786,7 +1809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -1822,7 +1845,7 @@
       </c>
       <c r="K16" s="9">
         <f t="shared" si="2"/>
-        <v>-0.14399530379974207</v>
+        <v>-4.1640699871903594E-2</v>
       </c>
       <c r="L16" s="12">
         <f t="shared" si="3"/>
@@ -1857,7 +1880,7 @@
         <v>0.35566134081881862</v>
       </c>
     </row>
-    <row r="17" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>36</v>
       </c>
@@ -1893,7 +1916,7 @@
       </c>
       <c r="K17" s="9">
         <f t="shared" si="2"/>
-        <v>0.22566156719339137</v>
+        <v>6.5257028140248613E-2</v>
       </c>
       <c r="L17" s="12">
         <f t="shared" si="3"/>
@@ -1928,7 +1951,7 @@
         <v>0.21503950267044389</v>
       </c>
     </row>
-    <row r="18" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -1964,7 +1987,7 @@
       </c>
       <c r="K18" s="9">
         <f t="shared" si="2"/>
-        <v>3.2448617483725892E-2</v>
+        <v>9.38352228331806E-3</v>
       </c>
       <c r="L18" s="12">
         <f t="shared" si="3"/>
@@ -1992,14 +2015,14 @@
       </c>
       <c r="R18" s="9">
         <f t="shared" si="9"/>
-        <v>7.9678796202240099E-3</v>
+        <v>7.9678796202240117E-3</v>
       </c>
       <c r="S18" s="9">
         <f t="shared" si="10"/>
         <v>0.38852199173214769</v>
       </c>
     </row>
-    <row r="19" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -2035,7 +2058,7 @@
       </c>
       <c r="K19" s="9">
         <f t="shared" si="2"/>
-        <v>2.6713432879047636E-2</v>
+        <v>7.7250161061617672E-3</v>
       </c>
       <c r="L19" s="12">
         <f t="shared" si="3"/>
@@ -2070,7 +2093,7 @@
         <v>0.37902680547235196</v>
       </c>
     </row>
-    <row r="20" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>40</v>
       </c>
@@ -2106,7 +2129,7 @@
       </c>
       <c r="K20" s="9">
         <f t="shared" si="2"/>
-        <v>0.15078541633235029</v>
+        <v>4.3604271117671518E-2</v>
       </c>
       <c r="L20" s="12">
         <f t="shared" si="3"/>
@@ -2141,15 +2164,15 @@
         <v>0.3130227839885002</v>
       </c>
     </row>
-    <row r="21" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>36</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" t="s">
         <v>86</v>
-      </c>
-      <c r="C21" t="s">
-        <v>87</v>
       </c>
       <c r="D21" s="8">
         <v>45481</v>
@@ -2177,7 +2200,7 @@
       </c>
       <c r="K21" s="9">
         <f t="shared" si="2"/>
-        <v>9.6016379421492104E-2</v>
+        <v>2.7766108565856817E-2</v>
       </c>
       <c r="L21" s="12">
         <f t="shared" si="3"/>
@@ -2212,7 +2235,7 @@
         <v>0.31936121130073841</v>
       </c>
     </row>
-    <row r="22" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>40</v>
       </c>
@@ -2248,7 +2271,7 @@
       </c>
       <c r="K22" s="9">
         <f t="shared" si="2"/>
-        <v>-4.2309587820944392E-2</v>
+        <v>-1.2235127130299155E-2</v>
       </c>
       <c r="L22" s="12">
         <f t="shared" si="3"/>
@@ -2276,14 +2299,14 @@
       </c>
       <c r="R22" s="9">
         <f t="shared" si="9"/>
-        <v>9.0844675621648847E-3</v>
+        <v>9.0844675621648864E-3</v>
       </c>
       <c r="S22" s="9">
         <f t="shared" si="10"/>
         <v>0.34076806799601772</v>
       </c>
     </row>
-    <row r="23" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -2319,7 +2342,7 @@
       </c>
       <c r="K23" s="9">
         <f t="shared" si="2"/>
-        <v>6.4308313701803621E-2</v>
+        <v>1.8596739750965593E-2</v>
       </c>
       <c r="L23" s="12">
         <f t="shared" si="3"/>
@@ -2354,7 +2377,7 @@
         <v>0.3227270540537468</v>
       </c>
     </row>
-    <row r="24" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -2390,7 +2413,7 @@
       </c>
       <c r="K24" s="9">
         <f t="shared" si="2"/>
-        <v>-7.1357493234198988E-2</v>
+        <v>-2.0635228239867041E-2</v>
       </c>
       <c r="L24" s="12">
         <f t="shared" si="3"/>
@@ -2425,7 +2448,7 @@
         <v>0.33344779875175323</v>
       </c>
     </row>
-    <row r="25" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -2461,7 +2484,7 @@
       </c>
       <c r="K25" s="9">
         <f t="shared" si="2"/>
-        <v>-0.16807445604076854</v>
+        <v>-4.8603932180041234E-2</v>
       </c>
       <c r="L25" s="12">
         <f t="shared" si="3"/>
@@ -2496,7 +2519,7 @@
         <v>0.34232023979981507</v>
       </c>
     </row>
-    <row r="26" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>36</v>
       </c>
@@ -2532,7 +2555,7 @@
       </c>
       <c r="K26" s="9">
         <f t="shared" si="2"/>
-        <v>0.19234473315497108</v>
+        <v>5.5622434162063847E-2</v>
       </c>
       <c r="L26" s="12">
         <f t="shared" si="3"/>
@@ -2560,26 +2583,26 @@
       </c>
       <c r="R26" s="9">
         <f t="shared" si="9"/>
-        <v>1.1106625124742505E-2</v>
+        <v>1.1106625124742506E-2</v>
       </c>
       <c r="S26" s="9">
         <f t="shared" si="10"/>
         <v>0.27872521356960728</v>
       </c>
     </row>
-    <row r="27" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B27" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C27" s="14" t="s">
         <v>82</v>
-      </c>
-      <c r="C27" s="14" t="s">
-        <v>83</v>
       </c>
       <c r="D27" s="8">
         <f ca="1">TODAY()-20</f>
-        <v>45603</v>
+        <v>45607</v>
       </c>
       <c r="E27" s="2">
         <v>1E-35</v>
@@ -2603,7 +2626,7 @@
       </c>
       <c r="K27" s="9">
         <f t="shared" si="2"/>
-        <v>7.4387015252508681E-2</v>
+        <v>2.151130831880628E-2</v>
       </c>
       <c r="L27" s="12">
         <f t="shared" si="3"/>
@@ -2631,14 +2654,14 @@
       </c>
       <c r="R27" s="9">
         <f t="shared" si="9"/>
-        <v>4.5211765022890611E-3</v>
+        <v>4.5211765022890619E-3</v>
       </c>
       <c r="S27" s="9">
         <f t="shared" si="10"/>
         <v>0.68471037535563517</v>
       </c>
     </row>
-    <row r="28" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>38</v>
       </c>
@@ -2674,7 +2697,7 @@
       </c>
       <c r="K28" s="9">
         <f t="shared" si="2"/>
-        <v>7.0709617202906999E-2</v>
+        <v>2.0447874828600599E-2</v>
       </c>
       <c r="L28" s="12">
         <f t="shared" si="3"/>
@@ -2702,22 +2725,22 @@
       </c>
       <c r="R28" s="9">
         <f t="shared" si="9"/>
-        <v>9.4254046509404475E-3</v>
+        <v>9.4254046509404457E-3</v>
       </c>
       <c r="S28" s="9">
         <f t="shared" si="10"/>
         <v>0.32844175656930963</v>
       </c>
     </row>
-    <row r="29" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>73</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="C29" t="s">
         <v>75</v>
-      </c>
-      <c r="C29" t="s">
-        <v>76</v>
       </c>
       <c r="D29" s="8">
         <v>45562</v>
@@ -2744,7 +2767,7 @@
       </c>
       <c r="K29" s="9">
         <f t="shared" si="2"/>
-        <v>0.15660424263686035</v>
+        <v>4.5286964881697422E-2</v>
       </c>
       <c r="L29" s="12">
         <f t="shared" si="3"/>
@@ -2779,15 +2802,15 @@
         <v>0.31552355195055437</v>
       </c>
     </row>
-    <row r="30" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>76</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="C30" t="s">
         <v>78</v>
-      </c>
-      <c r="C30" t="s">
-        <v>79</v>
       </c>
       <c r="D30" s="8">
         <v>45580</v>
@@ -2815,7 +2838,7 @@
       </c>
       <c r="K30" s="9">
         <f t="shared" si="2"/>
-        <v>9.7237928434652079E-2</v>
+        <v>2.8119357279485394E-2</v>
       </c>
       <c r="L30" s="12">
         <v>21.2</v>
@@ -2849,7 +2872,7 @@
         <v>0.32147510402534252</v>
       </c>
     </row>
-    <row r="31" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -2885,7 +2908,7 @@
       </c>
       <c r="K31" s="9">
         <f t="shared" si="2"/>
-        <v>1.8628127501550788E-2</v>
+        <v>5.3868997529697166E-3</v>
       </c>
       <c r="L31" s="12">
         <f>F31/(1-(F31*(1+H31)-F31)/(F31*(1+H31)))</f>
@@ -2920,7 +2943,7 @@
         <v>0.33807150820540705</v>
       </c>
     </row>
-    <row r="32" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>39</v>
       </c>
@@ -2990,15 +3013,15 @@
         <v>0.33928814193297463</v>
       </c>
     </row>
-    <row r="33" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B33" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C33" t="s">
         <v>80</v>
-      </c>
-      <c r="C33" t="s">
-        <v>81</v>
       </c>
       <c r="D33" s="8">
         <v>45574</v>
@@ -3025,7 +3048,7 @@
       </c>
       <c r="K33" s="9">
         <f t="shared" si="2"/>
-        <v>0.13702871230725283</v>
+        <v>3.9626094271485252E-2</v>
       </c>
       <c r="L33" s="12">
         <f>F33/(1-(F33*(1+H33)-F33)/(F33*(1+H33)))</f>
@@ -3065,10 +3088,10 @@
         <v>37</v>
       </c>
       <c r="B34" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C34" t="s">
         <v>88</v>
-      </c>
-      <c r="C34" t="s">
-        <v>89</v>
       </c>
       <c r="D34" s="8">
         <v>45623</v>
@@ -3080,7 +3103,7 @@
         <v>15.3</v>
       </c>
       <c r="G34" s="1">
-        <f t="shared" ref="G34" si="11">E34*F34</f>
+        <f t="shared" ref="G34:G35" si="11">E34*F34</f>
         <v>29.980350000000001</v>
       </c>
       <c r="H34" s="11">
@@ -3090,58 +3113,329 @@
         <v>0.39532299999999998</v>
       </c>
       <c r="J34" s="9">
-        <f t="shared" ref="J34" si="12">IFERROR(H34/I34,"")</f>
+        <f t="shared" ref="J34:J35" si="12">IFERROR(H34/I34,"")</f>
         <v>0.88535197800279775</v>
       </c>
       <c r="K34" s="9">
-        <f t="shared" ref="K34" si="13">IFERROR(J34/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.3292934554576642</v>
+        <f t="shared" ref="K34:K35" si="13">IFERROR(J34/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>9.5225396847415877E-2</v>
       </c>
       <c r="L34" s="12">
         <f t="shared" ref="L34" si="14">F34/(1-(F34*(1+H34)-F34)/(F34*(1+H34)))</f>
         <v>20.655000000000001</v>
       </c>
       <c r="M34" s="12">
-        <f t="shared" ref="M34" si="15">F34/(1+I34-H34)</f>
+        <f t="shared" ref="M34:M35" si="15">F34/(1+I34-H34)</f>
         <v>14.636624277854791</v>
       </c>
       <c r="N34" s="12">
-        <f t="shared" ref="N34" si="16">L34-F34</f>
+        <f t="shared" ref="N34:N35" si="16">L34-F34</f>
         <v>5.3550000000000004</v>
       </c>
       <c r="O34" s="12">
-        <f t="shared" ref="O34" si="17">0.5*(M34-F34)</f>
+        <f t="shared" ref="O34:O35" si="17">0.5*(M34-F34)</f>
         <v>-0.33168786107260484</v>
       </c>
       <c r="P34" s="15">
-        <f t="shared" ref="P34" si="18">N34+O34</f>
+        <f t="shared" ref="P34:P35" si="18">N34+O34</f>
         <v>5.0233121389273956</v>
       </c>
       <c r="Q34" s="12">
-        <f t="shared" ref="Q34" si="19">MAX($P$2:$P$280)-P34</f>
+        <f t="shared" ref="Q34:Q35" si="19">MAX($P$2:$P$280)-P34</f>
         <v>98.605197889725929</v>
       </c>
       <c r="R34" s="9">
-        <f t="shared" ref="R34" si="20">IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q34)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" ref="R34:R35" si="20">IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q34)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
         <v>1.0141453203291973E-2</v>
       </c>
       <c r="S34" s="9">
-        <f t="shared" ref="S34" si="21">Q34/MAX($Q$2:$Q$28)</f>
+        <f t="shared" ref="S34:S35" si="21">Q34/MAX($Q$2:$Q$28)</f>
         <v>0.30525176203806181</v>
       </c>
     </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>89</v>
+      </c>
+      <c r="B35" t="s">
+        <v>90</v>
+      </c>
+      <c r="C35" t="s">
+        <v>91</v>
+      </c>
+      <c r="D35" s="8">
+        <v>45627</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0</v>
+      </c>
+      <c r="F35" s="1">
+        <v>133.53</v>
+      </c>
+      <c r="G35" s="1">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H35" s="11">
+        <v>0.12</v>
+      </c>
+      <c r="I35" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="J35" s="9">
+        <f t="shared" si="12"/>
+        <v>0.6</v>
+      </c>
+      <c r="K35" s="9">
+        <f t="shared" si="13"/>
+        <v>6.4533924956418839E-2</v>
+      </c>
+      <c r="L35" s="12">
+        <f>F35/(1-(F35*(1+H35)-F35)/(F35*(1+H35)))</f>
+        <v>149.55360000000002</v>
+      </c>
+      <c r="M35" s="12">
+        <f t="shared" si="15"/>
+        <v>123.63888888888889</v>
+      </c>
+      <c r="N35" s="12">
+        <f t="shared" si="16"/>
+        <v>16.023600000000016</v>
+      </c>
+      <c r="O35" s="12">
+        <f t="shared" si="17"/>
+        <v>-4.9455555555555577</v>
+      </c>
+      <c r="P35" s="15">
+        <f t="shared" si="18"/>
+        <v>11.078044444444458</v>
+      </c>
+      <c r="Q35" s="12">
+        <f t="shared" si="19"/>
+        <v>92.550465584208865</v>
+      </c>
+      <c r="R35" s="9">
+        <f t="shared" si="20"/>
+        <v>1.0804915930867257E-2</v>
+      </c>
+      <c r="S35" s="9">
+        <f t="shared" si="21"/>
+        <v>0.28650814867404023</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>89</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C36" t="s">
+        <v>93</v>
+      </c>
+      <c r="D36" s="8">
+        <v>45627</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0</v>
+      </c>
+      <c r="F36" s="1">
+        <v>39.56</v>
+      </c>
+      <c r="G36" s="1">
+        <f t="shared" ref="G36" si="22">E36*F36</f>
+        <v>0</v>
+      </c>
+      <c r="H36" s="11">
+        <v>0.12</v>
+      </c>
+      <c r="I36" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="J36" s="9">
+        <f t="shared" ref="J36" si="23">IFERROR(H36/I36,"")</f>
+        <v>0.6</v>
+      </c>
+      <c r="K36" s="9">
+        <f t="shared" ref="K36" si="24">IFERROR(J36/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>6.4533924956418839E-2</v>
+      </c>
+      <c r="L36" s="12">
+        <f>F36/(1-(F36*(1+H36)-F36)/(F36*(1+H36)))</f>
+        <v>44.307200000000009</v>
+      </c>
+      <c r="M36" s="12">
+        <f t="shared" ref="M36" si="25">F36/(1+I36-H36)</f>
+        <v>36.629629629629626</v>
+      </c>
+      <c r="N36" s="12">
+        <f t="shared" ref="N36" si="26">L36-F36</f>
+        <v>4.7472000000000065</v>
+      </c>
+      <c r="O36" s="12">
+        <f t="shared" ref="O36" si="27">0.5*(M36-F36)</f>
+        <v>-1.465185185185188</v>
+      </c>
+      <c r="P36" s="15">
+        <f t="shared" ref="P36" si="28">N36+O36</f>
+        <v>3.2820148148148185</v>
+      </c>
+      <c r="Q36" s="12">
+        <f t="shared" ref="Q36" si="29">MAX($P$2:$P$280)-P36</f>
+        <v>100.34649521383851</v>
+      </c>
+      <c r="R36" s="9">
+        <f t="shared" ref="R36" si="30">IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q36)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.9654701229873414E-3</v>
+      </c>
+      <c r="S36" s="9">
+        <f t="shared" ref="S36" si="31">Q36/MAX($Q$2:$Q$28)</f>
+        <v>0.31064229000000515</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>89</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C37" t="s">
+        <v>94</v>
+      </c>
+      <c r="D37" s="8">
+        <v>45627</v>
+      </c>
+      <c r="E37" s="2">
+        <v>0</v>
+      </c>
+      <c r="F37" s="1">
+        <v>26.63</v>
+      </c>
+      <c r="G37" s="1">
+        <f t="shared" ref="G37" si="32">E37*F37</f>
+        <v>0</v>
+      </c>
+      <c r="H37" s="11">
+        <v>0.12</v>
+      </c>
+      <c r="I37" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="J37" s="9">
+        <f t="shared" ref="J37" si="33">IFERROR(H37/I37,"")</f>
+        <v>0.6</v>
+      </c>
+      <c r="K37" s="9">
+        <f t="shared" ref="K37" si="34">IFERROR(J37/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>6.4533924956418839E-2</v>
+      </c>
+      <c r="L37" s="12">
+        <f>F37/(1-(F37*(1+H37)-F37)/(F37*(1+H37)))</f>
+        <v>29.825600000000001</v>
+      </c>
+      <c r="M37" s="12">
+        <f t="shared" ref="M37" si="35">F37/(1+I37-H37)</f>
+        <v>24.657407407407405</v>
+      </c>
+      <c r="N37" s="12">
+        <f t="shared" ref="N37" si="36">L37-F37</f>
+        <v>3.1956000000000024</v>
+      </c>
+      <c r="O37" s="12">
+        <f t="shared" ref="O37" si="37">0.5*(M37-F37)</f>
+        <v>-0.98629629629629711</v>
+      </c>
+      <c r="P37" s="15">
+        <f t="shared" ref="P37" si="38">N37+O37</f>
+        <v>2.2093037037037053</v>
+      </c>
+      <c r="Q37" s="12">
+        <f t="shared" ref="Q37" si="39">MAX($P$2:$P$280)-P37</f>
+        <v>101.41920632494961</v>
+      </c>
+      <c r="R37" s="9">
+        <f t="shared" ref="R37" si="40">IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q37)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.8600653292037765E-3</v>
+      </c>
+      <c r="S37" s="9">
+        <f t="shared" ref="S37" si="41">Q37/MAX($Q$2:$Q$28)</f>
+        <v>0.31396307798920092</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>89</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C38" t="s">
+        <v>96</v>
+      </c>
+      <c r="D38" s="8">
+        <v>45627</v>
+      </c>
+      <c r="E38" s="2">
+        <v>0</v>
+      </c>
+      <c r="F38" s="1">
+        <v>22.65</v>
+      </c>
+      <c r="G38" s="1">
+        <f t="shared" ref="G38" si="42">E38*F38</f>
+        <v>0</v>
+      </c>
+      <c r="H38" s="11">
+        <v>0.12</v>
+      </c>
+      <c r="I38" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="J38" s="9">
+        <f t="shared" ref="J38" si="43">IFERROR(H38/I38,"")</f>
+        <v>0.6</v>
+      </c>
+      <c r="K38" s="9">
+        <f t="shared" ref="K38" si="44">IFERROR(J38/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>6.4533924956418839E-2</v>
+      </c>
+      <c r="L38" s="12">
+        <f>F38/(1-(F38*(1+H38)-F38)/(F38*(1+H38)))</f>
+        <v>25.368000000000002</v>
+      </c>
+      <c r="M38" s="12">
+        <f t="shared" ref="M38" si="45">F38/(1+I38-H38)</f>
+        <v>20.972222222222218</v>
+      </c>
+      <c r="N38" s="12">
+        <f t="shared" ref="N38" si="46">L38-F38</f>
+        <v>2.7180000000000035</v>
+      </c>
+      <c r="O38" s="12">
+        <f t="shared" ref="O38" si="47">0.5*(M38-F38)</f>
+        <v>-0.83888888888889035</v>
+      </c>
+      <c r="P38" s="15">
+        <f t="shared" ref="P38" si="48">N38+O38</f>
+        <v>1.8791111111111132</v>
+      </c>
+      <c r="Q38" s="12">
+        <f t="shared" ref="Q38" si="49">MAX($P$2:$P$280)-P38</f>
+        <v>101.74939891754221</v>
+      </c>
+      <c r="R38" s="9">
+        <f t="shared" ref="R38" si="50">IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q38)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.8280678867734717E-3</v>
+      </c>
+      <c r="S38" s="9">
+        <f t="shared" ref="S38" si="51">Q38/MAX($Q$2:$Q$28)</f>
+        <v>0.31498525402918537</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S33" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Banking"/>
-      </filters>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S33">
-      <sortCondition descending="1" ref="G1:G33"/>
-    </sortState>
-  </autoFilter>
-  <conditionalFormatting sqref="R2:R34">
+  <autoFilter ref="A1:S33" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="R2:R38">
     <cfRule type="iconSet" priority="3">
       <iconSet iconSet="3Symbols">
         <cfvo type="percent" val="0"/>
@@ -3180,7 +3474,7 @@
               <x14:cfIcon iconSet="3Arrows" iconId="0"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>S2:S34</xm:sqref>
+          <xm:sqref>S2:S38</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/Open Positions.xlsx
+++ b/Open Positions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\StockSillines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84E69184-605A-494E-A83C-E5412893D444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78192D40-48C9-45AA-91FF-EF1520505E3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Positions" sheetId="1" r:id="rId1"/>
@@ -830,211 +830,211 @@
         <v>36</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D2" s="8">
-        <v>45574</v>
+        <v>45484</v>
       </c>
       <c r="E2" s="2">
-        <v>0.13370000000000001</v>
+        <v>0.33389999999999997</v>
       </c>
       <c r="F2" s="1">
-        <v>423.77</v>
+        <v>188.53</v>
       </c>
       <c r="G2" s="1">
-        <f t="shared" ref="G2:G33" si="0">E2*F2</f>
-        <v>56.658049000000005</v>
+        <f>E2*F2</f>
+        <v>62.950166999999993</v>
       </c>
       <c r="H2" s="11">
-        <v>1.14E-2</v>
+        <f>227.4/F2-1</f>
+        <v>0.20617408370020684</v>
       </c>
       <c r="I2" s="11">
-        <v>0.1963</v>
+        <v>0.37</v>
       </c>
       <c r="J2" s="9">
-        <f t="shared" ref="J2:J33" si="1">IFERROR(H2/I2,"")</f>
-        <v>5.8074375955170655E-2</v>
+        <f>IFERROR(H2/I2,"")</f>
+        <v>0.55722725324380229</v>
       </c>
       <c r="K2" s="9">
-        <f t="shared" ref="K2:K33" si="2">IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>6.2462790329697289E-3</v>
+        <f>IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>3.6612204034604294E-2</v>
       </c>
       <c r="L2" s="12">
-        <f t="shared" ref="L2:L29" si="3">F2/(1-(F2*(1+H2)-F2)/(F2*(1+H2)))</f>
-        <v>428.600978</v>
+        <f>F2/(1-(F2*(1+H2)-F2)/(F2*(1+H2)))</f>
+        <v>227.4</v>
       </c>
       <c r="M2" s="12">
-        <f t="shared" ref="M2:M33" si="4">F2/(1+I2-H2)</f>
-        <v>357.64199510507217</v>
+        <f>F2/(1+I2-H2)</f>
+        <v>161.9915808365931</v>
       </c>
       <c r="N2" s="12">
-        <f t="shared" ref="N2:N33" si="5">L2-F2</f>
-        <v>4.830978000000016</v>
+        <f>L2-F2</f>
+        <v>38.870000000000005</v>
       </c>
       <c r="O2" s="12">
-        <f t="shared" ref="O2:O33" si="6">0.5*(M2-F2)</f>
-        <v>-33.064002447463906</v>
+        <f>0.5*(M2-F2)</f>
+        <v>-13.26920958170345</v>
       </c>
       <c r="P2" s="15">
-        <f t="shared" ref="P2:P33" si="7">N2+O2</f>
-        <v>-28.23302444746389</v>
+        <f>N2+O2</f>
+        <v>25.600790418296555</v>
       </c>
       <c r="Q2" s="12">
-        <f t="shared" ref="Q2:Q33" si="8">MAX($P$2:$P$280)-P2</f>
-        <v>131.86153447611721</v>
+        <f>MAX($P$2:$P$280)-P2</f>
+        <v>78.027719610356769</v>
       </c>
       <c r="R2" s="9">
-        <f t="shared" ref="R2:R33" si="9">IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q2)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>7.5837127481716065E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q2)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.2815958290126271E-2</v>
       </c>
       <c r="S2" s="9">
-        <f t="shared" ref="S2:S33" si="10">Q2/MAX($Q$2:$Q$28)</f>
-        <v>0.4082032854788411</v>
+        <f>Q2/MAX($Q$2:$Q$28)</f>
+        <v>0.35277709242954441</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="8">
+        <v>45574</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0.13370000000000001</v>
+      </c>
+      <c r="F3" s="1">
+        <v>423.77</v>
+      </c>
+      <c r="G3" s="1">
+        <f>E3*F3</f>
+        <v>56.658049000000005</v>
+      </c>
+      <c r="H3" s="11">
+        <v>0.15</v>
+      </c>
+      <c r="I3" s="11">
+        <v>0.1963</v>
+      </c>
+      <c r="J3" s="9">
+        <f>IFERROR(H3/I3,"")</f>
+        <v>0.76413652572592972</v>
+      </c>
+      <c r="K3" s="9">
+        <f>IFERROR(J3/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>5.0207024561899537E-2</v>
+      </c>
+      <c r="L3" s="12">
+        <f>F3/(1-(F3*(1+H3)-F3)/(F3*(1+H3)))</f>
+        <v>487.33549999999991</v>
+      </c>
+      <c r="M3" s="12">
+        <f>F3/(1+I3-H3)</f>
+        <v>405.01768135334032</v>
+      </c>
+      <c r="N3" s="12">
+        <f>L3-F3</f>
+        <v>63.565499999999929</v>
+      </c>
+      <c r="O3" s="12">
+        <f>0.5*(M3-F3)</f>
+        <v>-9.3761593233298299</v>
+      </c>
+      <c r="P3" s="15">
+        <f>N3+O3</f>
+        <v>54.189340676670099</v>
+      </c>
+      <c r="Q3" s="12">
+        <f>MAX($P$2:$P$280)-P3</f>
+        <v>49.439169351983224</v>
+      </c>
+      <c r="R3" s="9">
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q3)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>2.0226877051280505E-2</v>
+      </c>
+      <c r="S3" s="9">
+        <f>Q3/MAX($Q$2:$Q$28)</f>
+        <v>0.22352321076687609</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C4" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D4" s="8">
         <v>45553</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E4" s="2">
         <v>1.0751999999999999</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F4" s="1">
         <v>51.15</v>
       </c>
-      <c r="G3" s="1">
-        <f t="shared" si="0"/>
+      <c r="G4" s="1">
+        <f>E4*F4</f>
         <v>54.996479999999998</v>
       </c>
-      <c r="H3" s="11">
+      <c r="H4" s="11">
         <f>16.68%+7%/4</f>
         <v>0.18430000000000002</v>
       </c>
-      <c r="I3" s="11">
+      <c r="I4" s="11">
         <v>0.19980000000000001</v>
       </c>
-      <c r="J3" s="9">
-        <f t="shared" si="1"/>
+      <c r="J4" s="9">
+        <f>IFERROR(H4/I4,"")</f>
         <v>0.92242242242242245</v>
       </c>
-      <c r="K3" s="9">
-        <f t="shared" si="2"/>
-        <v>9.9212565644544476E-2</v>
-      </c>
-      <c r="L3" s="12">
-        <f t="shared" si="3"/>
+      <c r="K4" s="9">
+        <f>IFERROR(J4/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>6.0607082189943672E-2</v>
+      </c>
+      <c r="L4" s="12">
+        <f>F4/(1-(F4*(1+H4)-F4)/(F4*(1+H4)))</f>
         <v>60.576944999999995</v>
       </c>
-      <c r="M3" s="12">
-        <f t="shared" si="4"/>
+      <c r="M4" s="12">
+        <f>F4/(1+I4-H4)</f>
         <v>50.369276218611525</v>
       </c>
-      <c r="N3" s="12">
-        <f t="shared" si="5"/>
+      <c r="N4" s="12">
+        <f>L4-F4</f>
         <v>9.4269449999999964</v>
       </c>
-      <c r="O3" s="12">
-        <f t="shared" si="6"/>
+      <c r="O4" s="12">
+        <f>0.5*(M4-F4)</f>
         <v>-0.39036189069423699</v>
       </c>
-      <c r="P3" s="15">
-        <f t="shared" si="7"/>
+      <c r="P4" s="15">
+        <f>N4+O4</f>
         <v>9.0365831093057594</v>
       </c>
-      <c r="Q3" s="12">
-        <f t="shared" si="8"/>
+      <c r="Q4" s="12">
+        <f>MAX($P$2:$P$280)-P4</f>
         <v>94.591926919347571</v>
       </c>
-      <c r="R3" s="9">
-        <f t="shared" si="9"/>
-        <v>1.0571726706155754E-2</v>
-      </c>
-      <c r="S3" s="9">
-        <f t="shared" si="10"/>
-        <v>0.29282789330231596</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="8">
-        <v>45484</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0.33389999999999997</v>
-      </c>
-      <c r="F4" s="1">
-        <v>188.53</v>
-      </c>
-      <c r="G4" s="1">
-        <f t="shared" si="0"/>
-        <v>62.950166999999993</v>
-      </c>
-      <c r="H4" s="11">
-        <f>227.4/F4-1</f>
-        <v>0.20617408370020684</v>
-      </c>
-      <c r="I4" s="11">
-        <v>0.37</v>
-      </c>
-      <c r="J4" s="9">
-        <f t="shared" si="1"/>
-        <v>0.55722725324380229</v>
-      </c>
-      <c r="K4" s="9">
-        <f t="shared" si="2"/>
-        <v>5.9933436240844885E-2</v>
-      </c>
-      <c r="L4" s="12">
-        <f t="shared" si="3"/>
-        <v>227.4</v>
-      </c>
-      <c r="M4" s="12">
-        <f t="shared" si="4"/>
-        <v>161.9915808365931</v>
-      </c>
-      <c r="N4" s="12">
-        <f t="shared" si="5"/>
-        <v>38.870000000000005</v>
-      </c>
-      <c r="O4" s="12">
-        <f t="shared" si="6"/>
-        <v>-13.26920958170345</v>
-      </c>
-      <c r="P4" s="15">
-        <f t="shared" si="7"/>
-        <v>25.600790418296555</v>
-      </c>
-      <c r="Q4" s="12">
-        <f t="shared" si="8"/>
-        <v>78.027719610356769</v>
-      </c>
       <c r="R4" s="9">
-        <f t="shared" si="9"/>
-        <v>1.2815958290126271E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q4)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.0571726706155752E-2</v>
       </c>
       <c r="S4" s="9">
-        <f t="shared" si="10"/>
-        <v>0.24155013537430298</v>
+        <f>Q4/MAX($Q$2:$Q$28)</f>
+        <v>0.42766679729399837</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
@@ -1057,54 +1057,54 @@
         <v>227.38</v>
       </c>
       <c r="G5" s="1">
-        <f t="shared" si="0"/>
+        <f>E5*F5</f>
         <v>42.792915999999998</v>
       </c>
       <c r="H5" s="11">
-        <v>4.9299999999999997E-2</v>
+        <v>0.15</v>
       </c>
       <c r="I5" s="11">
         <v>0.2271</v>
       </c>
       <c r="J5" s="9">
-        <f t="shared" si="1"/>
-        <v>0.21708498458828709</v>
+        <f>IFERROR(H5/I5,"")</f>
+        <v>0.66050198150594452</v>
       </c>
       <c r="K5" s="9">
-        <f t="shared" si="2"/>
-        <v>2.3348910174309765E-2</v>
+        <f>IFERROR(J5/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>4.3397793577722936E-2</v>
       </c>
       <c r="L5" s="12">
-        <f t="shared" si="3"/>
-        <v>238.58983399999997</v>
+        <f>F5/(1-(F5*(1+H5)-F5)/(F5*(1+H5)))</f>
+        <v>261.48699999999997</v>
       </c>
       <c r="M5" s="12">
-        <f t="shared" si="4"/>
-        <v>193.05484802173541</v>
+        <f>F5/(1+I5-H5)</f>
+        <v>211.10389007520189</v>
       </c>
       <c r="N5" s="12">
-        <f t="shared" si="5"/>
-        <v>11.209833999999972</v>
+        <f>L5-F5</f>
+        <v>34.106999999999971</v>
       </c>
       <c r="O5" s="12">
-        <f t="shared" si="6"/>
-        <v>-17.162575989132293</v>
+        <f>0.5*(M5-F5)</f>
+        <v>-8.1380549623990532</v>
       </c>
       <c r="P5" s="15">
-        <f t="shared" si="7"/>
-        <v>-5.9527419891323206</v>
+        <f>N5+O5</f>
+        <v>25.968945037600918</v>
       </c>
       <c r="Q5" s="12">
-        <f t="shared" si="8"/>
-        <v>109.58125201778564</v>
+        <f>MAX($P$2:$P$280)-P5</f>
+        <v>77.659564991052406</v>
       </c>
       <c r="R5" s="9">
-        <f t="shared" si="9"/>
-        <v>9.1256486085566392E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q5)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.2876713900151458E-2</v>
       </c>
       <c r="S5" s="9">
-        <f t="shared" si="10"/>
-        <v>0.33923029394631193</v>
+        <f>Q5/MAX($Q$2:$Q$28)</f>
+        <v>0.35111260041553638</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
@@ -1127,7 +1127,7 @@
         <v>273.45999999999998</v>
       </c>
       <c r="G6" s="1">
-        <f t="shared" si="0"/>
+        <f>E6*F6</f>
         <v>39.952506</v>
       </c>
       <c r="H6" s="11">
@@ -1137,44 +1137,44 @@
         <v>0.26</v>
       </c>
       <c r="J6" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H6/I6,"")</f>
         <v>0.96153846153846145</v>
       </c>
       <c r="K6" s="9">
-        <f t="shared" si="2"/>
-        <v>0.10341975153272248</v>
+        <f>IFERROR(J6/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>6.3177172573723572E-2</v>
       </c>
       <c r="L6" s="12">
         <f>F6/(1-(F6*(1+H6)-F6)/(F6*(1+H6)))</f>
         <v>341.82499999999999</v>
       </c>
       <c r="M6" s="12">
-        <f t="shared" si="4"/>
+        <f>F6/(1+I6-H6)</f>
         <v>270.75247524752473</v>
       </c>
       <c r="N6" s="12">
-        <f t="shared" si="5"/>
+        <f>L6-F6</f>
         <v>68.365000000000009</v>
       </c>
       <c r="O6" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(M6-F6)</f>
         <v>-1.3537623762376256</v>
       </c>
       <c r="P6" s="15">
-        <f t="shared" si="7"/>
+        <f>N6+O6</f>
         <v>67.011237623762383</v>
       </c>
       <c r="Q6" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($P$2:$P$280)-P6</f>
         <v>36.61727240489094</v>
       </c>
       <c r="R6" s="9">
-        <f t="shared" si="9"/>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q6)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
         <v>2.7309516365463388E-2</v>
       </c>
       <c r="S6" s="9">
-        <f t="shared" si="10"/>
-        <v>0.1133559605561654</v>
+        <f>Q6/MAX($Q$2:$Q$28)</f>
+        <v>0.1655531515749106</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
@@ -1197,54 +1197,54 @@
         <v>188.12</v>
       </c>
       <c r="G7" s="1">
-        <f t="shared" si="0"/>
+        <f>E7*F7</f>
         <v>36.269536000000002</v>
       </c>
       <c r="H7" s="11">
-        <v>-6.8599999999999994E-2</v>
+        <v>0.15</v>
       </c>
       <c r="I7" s="11">
         <v>0.37780000000000002</v>
       </c>
       <c r="J7" s="9">
-        <f t="shared" si="1"/>
-        <v>-0.18157755426151401</v>
+        <f>IFERROR(H7/I7,"")</f>
+        <v>0.39703546850185278</v>
       </c>
       <c r="K7" s="9">
-        <f t="shared" si="2"/>
-        <v>-1.9529853767471024E-2</v>
+        <f>IFERROR(J7/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>2.6086921443887974E-2</v>
       </c>
       <c r="L7" s="12">
-        <f t="shared" si="3"/>
-        <v>175.214968</v>
+        <f>F7/(1-(F7*(1+H7)-F7)/(F7*(1+H7)))</f>
+        <v>216.33799999999999</v>
       </c>
       <c r="M7" s="12">
-        <f t="shared" si="4"/>
-        <v>130.06084070796459</v>
+        <f>F7/(1+I7-H7)</f>
+        <v>153.21713634142367</v>
       </c>
       <c r="N7" s="12">
-        <f t="shared" si="5"/>
-        <v>-12.905032000000006</v>
+        <f>L7-F7</f>
+        <v>28.217999999999989</v>
       </c>
       <c r="O7" s="12">
-        <f t="shared" si="6"/>
-        <v>-29.029579646017709</v>
+        <f>0.5*(M7-F7)</f>
+        <v>-17.451431829288168</v>
       </c>
       <c r="P7" s="15">
-        <f t="shared" si="7"/>
-        <v>-41.934611646017714</v>
+        <f>N7+O7</f>
+        <v>10.766568170711821</v>
       </c>
       <c r="Q7" s="12">
-        <f t="shared" si="8"/>
-        <v>145.56312167467104</v>
+        <f>MAX($P$2:$P$280)-P7</f>
+        <v>92.861941857941503</v>
       </c>
       <c r="R7" s="9">
-        <f t="shared" si="9"/>
-        <v>6.8698719050211653E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q7)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.0768674227486882E-2</v>
       </c>
       <c r="S7" s="9">
-        <f t="shared" si="10"/>
-        <v>0.45061924046484586</v>
+        <f>Q7/MAX($Q$2:$Q$28)</f>
+        <v>0.41984522948505815</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
@@ -1261,201 +1261,200 @@
         <v>45544</v>
       </c>
       <c r="E8" s="2">
-        <v>0.24390000000000001</v>
+        <v>0.35149999999999998</v>
       </c>
       <c r="F8" s="1">
-        <v>144.28</v>
+        <v>142.78</v>
       </c>
       <c r="G8" s="1">
-        <f t="shared" si="0"/>
-        <v>35.189892</v>
+        <f>E8*F8</f>
+        <v>50.187169999999995</v>
       </c>
       <c r="H8" s="11">
-        <v>-2.8000000000000001E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I8" s="11">
         <v>0.18340000000000001</v>
       </c>
       <c r="J8" s="9">
-        <f t="shared" si="1"/>
-        <v>-0.15267175572519084</v>
+        <f>IFERROR(H8/I8,"")</f>
+        <v>0.38167938931297712</v>
       </c>
       <c r="K8" s="9">
-        <f t="shared" si="2"/>
-        <v>-1.6420846044890289E-2</v>
+        <f>IFERROR(J8/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>2.5077961632317756E-2</v>
       </c>
       <c r="L8" s="12">
-        <f t="shared" si="3"/>
-        <v>140.24016</v>
+        <f>F8/(1-(F8*(1+H8)-F8)/(F8*(1+H8)))</f>
+        <v>152.77460000000002</v>
       </c>
       <c r="M8" s="12">
-        <f t="shared" si="4"/>
-        <v>119.10186561003798</v>
+        <f>F8/(1+I8-H8)</f>
+        <v>128.23783007005568</v>
       </c>
       <c r="N8" s="12">
-        <f t="shared" si="5"/>
-        <v>-4.0398399999999981</v>
+        <f>L8-F8</f>
+        <v>9.9946000000000197</v>
       </c>
       <c r="O8" s="12">
-        <f t="shared" si="6"/>
-        <v>-12.589067194981013</v>
+        <f>0.5*(M8-F8)</f>
+        <v>-7.2710849649721609</v>
       </c>
       <c r="P8" s="15">
-        <f t="shared" si="7"/>
-        <v>-16.628907194981011</v>
+        <f>N8+O8</f>
+        <v>2.7235150350278587</v>
       </c>
       <c r="Q8" s="12">
-        <f t="shared" si="8"/>
-        <v>120.25741722363433</v>
+        <f>MAX($P$2:$P$280)-P8</f>
+        <v>100.90499499362546</v>
       </c>
       <c r="R8" s="9">
-        <f t="shared" si="9"/>
-        <v>8.3154954021702442E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q8)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.9103121709997969E-3</v>
       </c>
       <c r="S8" s="9">
-        <f t="shared" si="10"/>
-        <v>0.37228046077970073</v>
+        <f>Q8/MAX($Q$2:$Q$28)</f>
+        <v>0.45620929232877483</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>15</v>
+        <v>37</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="D9" s="8">
-        <v>45460</v>
+        <v>45623</v>
       </c>
       <c r="E9" s="2">
-        <v>0.1807</v>
+        <v>1.9595</v>
       </c>
       <c r="F9" s="1">
-        <v>165.59</v>
+        <v>15.3</v>
       </c>
       <c r="G9" s="1">
-        <f t="shared" si="0"/>
-        <v>29.922113</v>
+        <f>E9*F9</f>
+        <v>29.980350000000001</v>
       </c>
       <c r="H9" s="11">
-        <v>6.7199999999999996E-2</v>
+        <v>0.35</v>
       </c>
       <c r="I9" s="11">
-        <v>0.16439999999999999</v>
+        <v>0.39532299999999998</v>
       </c>
       <c r="J9" s="9">
-        <f t="shared" si="1"/>
-        <v>0.40875912408759124</v>
+        <f>IFERROR(H9/I9,"")</f>
+        <v>0.88535197800279775</v>
       </c>
       <c r="K9" s="9">
-        <f t="shared" si="2"/>
-        <v>4.3964717731866845E-2</v>
+        <f>IFERROR(J9/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>5.8171396090881088E-2</v>
       </c>
       <c r="L9" s="12">
-        <f t="shared" si="3"/>
-        <v>176.717648</v>
+        <f>F9/(1-(F9*(1+H9)-F9)/(F9*(1+H9)))</f>
+        <v>20.655000000000001</v>
       </c>
       <c r="M9" s="12">
-        <f t="shared" si="4"/>
-        <v>150.92052497265766</v>
+        <f>F9/(1+I9-H9)</f>
+        <v>14.636624277854791</v>
       </c>
       <c r="N9" s="12">
-        <f t="shared" si="5"/>
-        <v>11.127647999999994</v>
+        <f>L9-F9</f>
+        <v>5.3550000000000004</v>
       </c>
       <c r="O9" s="12">
-        <f t="shared" si="6"/>
-        <v>-7.3347375136711719</v>
+        <f>0.5*(M9-F9)</f>
+        <v>-0.33168786107260484</v>
       </c>
       <c r="P9" s="15">
-        <f t="shared" si="7"/>
-        <v>3.7929104863288217</v>
+        <f>N9+O9</f>
+        <v>5.0233121389273956</v>
       </c>
       <c r="Q9" s="12">
-        <f t="shared" si="8"/>
-        <v>99.835599542324502</v>
+        <f>MAX($P$2:$P$280)-P9</f>
+        <v>98.605197889725929</v>
       </c>
       <c r="R9" s="9">
-        <f t="shared" si="9"/>
-        <v>1.0016467117784554E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q9)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.0141453203291975E-2</v>
       </c>
       <c r="S9" s="9">
-        <f t="shared" si="10"/>
-        <v>0.30906071207830499</v>
+        <f>Q9/MAX($Q$2:$Q$28)</f>
+        <v>0.44581150370259182</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>33</v>
+        <v>38</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="D10" s="8">
-        <v>45562</v>
+        <v>45460</v>
       </c>
       <c r="E10" s="2">
-        <v>4.0300000000000002E-2</v>
+        <v>0.2727</v>
       </c>
       <c r="F10" s="1">
-        <v>668.82</v>
+        <v>164.91</v>
       </c>
       <c r="G10" s="1">
-        <f t="shared" si="0"/>
-        <v>26.953446000000003</v>
+        <f>E10*F10</f>
+        <v>44.970956999999999</v>
       </c>
       <c r="H10" s="11">
-        <f>553.57/F10-1</f>
-        <v>-0.17231841153075567</v>
+        <v>6.7199999999999996E-2</v>
       </c>
       <c r="I10" s="11">
-        <v>0.28000000000000003</v>
+        <v>0.16439999999999999</v>
       </c>
       <c r="J10" s="9">
-        <f t="shared" si="1"/>
-        <v>-0.61542289832412733</v>
+        <f>IFERROR(H10/I10,"")</f>
+        <v>0.40875912408759124</v>
       </c>
       <c r="K10" s="9">
-        <f t="shared" si="2"/>
-        <v>-6.619275856151835E-2</v>
+        <f>IFERROR(J10/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>2.6857215552508477E-2</v>
       </c>
       <c r="L10" s="12">
-        <f t="shared" si="3"/>
-        <v>553.57000000000005</v>
+        <f>F10/(1-(F10*(1+H10)-F10)/(F10*(1+H10)))</f>
+        <v>175.991952</v>
       </c>
       <c r="M10" s="12">
-        <f t="shared" si="4"/>
-        <v>460.51884675555289</v>
+        <f>F10/(1+I10-H10)</f>
+        <v>150.30076558512576</v>
       </c>
       <c r="N10" s="12">
-        <f t="shared" si="5"/>
-        <v>-115.25</v>
+        <f>L10-F10</f>
+        <v>11.081952000000001</v>
       </c>
       <c r="O10" s="12">
-        <f t="shared" si="6"/>
-        <v>-104.15057662222358</v>
+        <f>0.5*(M10-F10)</f>
+        <v>-7.3046172074371185</v>
       </c>
       <c r="P10" s="15">
-        <f t="shared" si="7"/>
-        <v>-219.40057662222358</v>
+        <f>N10+O10</f>
+        <v>3.7773347925628826</v>
       </c>
       <c r="Q10" s="12">
-        <f t="shared" si="8"/>
-        <v>323.02908665087693</v>
+        <f>MAX($P$2:$P$280)-P10</f>
+        <v>99.851175236090441</v>
       </c>
       <c r="R10" s="9">
-        <f t="shared" si="9"/>
-        <v>3.0956964599314213E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q10)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.0014904658213353E-2</v>
       </c>
       <c r="S10" s="9">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f>Q10/MAX($Q$2:$Q$28)</f>
+        <v>0.45144478720335951</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
@@ -1463,69 +1462,69 @@
         <v>39</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D11" s="8">
-        <v>45580</v>
+        <v>45562</v>
       </c>
       <c r="E11" s="2">
-        <v>0.19139999999999999</v>
+        <v>4.0300000000000002E-2</v>
       </c>
       <c r="F11" s="1">
-        <v>135.82</v>
+        <v>668.82</v>
       </c>
       <c r="G11" s="1">
-        <f t="shared" si="0"/>
-        <v>25.995947999999999</v>
+        <f>E11*F11</f>
+        <v>26.953446000000003</v>
       </c>
       <c r="H11" s="11">
-        <v>0.1202</v>
+        <v>0.05</v>
       </c>
       <c r="I11" s="11">
-        <v>0.33710000000000001</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="J11" s="9">
-        <f t="shared" si="1"/>
-        <v>0.35657075051913378</v>
+        <f>IFERROR(H11/I11,"")</f>
+        <v>0.17857142857142858</v>
       </c>
       <c r="K11" s="9">
-        <f t="shared" si="2"/>
-        <v>3.8351516759426205E-2</v>
+        <f>IFERROR(J11/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>1.1732903477977237E-2</v>
       </c>
       <c r="L11" s="12">
-        <f t="shared" si="3"/>
-        <v>152.14556400000001</v>
+        <f>F11/(1-(F11*(1+H11)-F11)/(F11*(1+H11)))</f>
+        <v>702.26100000000008</v>
       </c>
       <c r="M11" s="12">
-        <f t="shared" si="4"/>
-        <v>111.61147177253677</v>
+        <f>F11/(1+I11-H11)</f>
+        <v>543.7560975609756</v>
       </c>
       <c r="N11" s="12">
-        <f t="shared" si="5"/>
-        <v>16.325564000000014</v>
+        <f>L11-F11</f>
+        <v>33.441000000000031</v>
       </c>
       <c r="O11" s="12">
-        <f t="shared" si="6"/>
-        <v>-12.10426411373161</v>
+        <f>0.5*(M11-F11)</f>
+        <v>-62.531951219512223</v>
       </c>
       <c r="P11" s="15">
-        <f t="shared" si="7"/>
-        <v>4.2212998862684046</v>
+        <f>N11+O11</f>
+        <v>-29.090951219512192</v>
       </c>
       <c r="Q11" s="12">
-        <f t="shared" si="8"/>
-        <v>99.407210142384912</v>
+        <f>MAX($P$2:$P$280)-P11</f>
+        <v>132.71946124816552</v>
       </c>
       <c r="R11" s="9">
-        <f t="shared" si="9"/>
-        <v>1.0059632481061084E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q11)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>7.5346900190481469E-3</v>
       </c>
       <c r="S11" s="9">
-        <f t="shared" si="10"/>
-        <v>0.30773454852943982</v>
+        <f>Q11/MAX($Q$2:$Q$28)</f>
+        <v>0.60004810959166965</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
@@ -1533,280 +1532,280 @@
         <v>39</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="D12" s="8">
         <v>45580</v>
       </c>
       <c r="E12" s="2">
-        <v>0.18010000000000001</v>
+        <v>0.19139999999999999</v>
       </c>
       <c r="F12" s="1">
-        <v>133.19999999999999</v>
+        <v>135.82</v>
       </c>
       <c r="G12" s="1">
-        <f t="shared" si="0"/>
-        <v>23.989319999999999</v>
+        <f>E12*F12</f>
+        <v>25.995947999999999</v>
       </c>
       <c r="H12" s="11">
-        <v>5.0000000000000001E-3</v>
+        <v>0.1202</v>
       </c>
       <c r="I12" s="11">
-        <v>0.1623</v>
+        <v>0.33710000000000001</v>
       </c>
       <c r="J12" s="9">
-        <f t="shared" si="1"/>
-        <v>3.0807147258163893E-2</v>
+        <f>IFERROR(H12/I12,"")</f>
+        <v>0.35657075051913378</v>
       </c>
       <c r="K12" s="9">
-        <f t="shared" si="2"/>
-        <v>3.3135102154661549E-3</v>
+        <f>IFERROR(J12/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>2.3428217113901029E-2</v>
       </c>
       <c r="L12" s="12">
-        <f t="shared" si="3"/>
-        <v>133.86599999999999</v>
+        <f>F12/(1-(F12*(1+H12)-F12)/(F12*(1+H12)))</f>
+        <v>152.14556400000001</v>
       </c>
       <c r="M12" s="12">
-        <f t="shared" si="4"/>
-        <v>115.09548086062384</v>
+        <f>F12/(1+I12-H12)</f>
+        <v>111.61147177253677</v>
       </c>
       <c r="N12" s="12">
-        <f t="shared" si="5"/>
-        <v>0.66599999999999682</v>
+        <f>L12-F12</f>
+        <v>16.325564000000014</v>
       </c>
       <c r="O12" s="12">
-        <f t="shared" si="6"/>
-        <v>-9.0522595696880757</v>
+        <f>0.5*(M12-F12)</f>
+        <v>-12.10426411373161</v>
       </c>
       <c r="P12" s="15">
-        <f t="shared" si="7"/>
-        <v>-8.3862595696880788</v>
+        <f>N12+O12</f>
+        <v>4.2212998862684046</v>
       </c>
       <c r="Q12" s="12">
-        <f t="shared" si="8"/>
-        <v>112.0147695983414</v>
+        <f>MAX($P$2:$P$280)-P12</f>
+        <v>99.407210142384912</v>
       </c>
       <c r="R12" s="9">
-        <f t="shared" si="9"/>
-        <v>8.9273941604822715E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q12)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.0059632481061084E-2</v>
       </c>
       <c r="S12" s="9">
-        <f t="shared" si="10"/>
-        <v>0.34676372570561925</v>
+        <f>Q12/MAX($Q$2:$Q$28)</f>
+        <v>0.44943754265386154</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>62</v>
+        <v>39</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>60</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D13" s="8">
-        <v>45481</v>
+        <v>45580</v>
       </c>
       <c r="E13" s="2">
-        <v>2.8500000000000001E-2</v>
+        <v>0.18010000000000001</v>
       </c>
       <c r="F13" s="1">
-        <v>700.32</v>
+        <v>133.19999999999999</v>
       </c>
       <c r="G13" s="1">
-        <f t="shared" si="0"/>
-        <v>19.959120000000002</v>
+        <f>E13*F13</f>
+        <v>23.989319999999999</v>
       </c>
       <c r="H13" s="11">
-        <v>-6.6500000000000004E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I13" s="11">
-        <v>0.45340000000000003</v>
+        <v>0.1623</v>
       </c>
       <c r="J13" s="9">
-        <f t="shared" si="1"/>
-        <v>-0.14666960741067489</v>
+        <f>IFERROR(H13/I13,"")</f>
+        <v>0.43130006161429457</v>
       </c>
       <c r="K13" s="9">
-        <f t="shared" si="2"/>
-        <v>-1.5775275730046508E-2</v>
+        <f>IFERROR(J13/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>2.8338251160610457E-2</v>
       </c>
       <c r="L13" s="12">
-        <f t="shared" si="3"/>
-        <v>653.74872000000005</v>
+        <f>F13/(1-(F13*(1+H13)-F13)/(F13*(1+H13)))</f>
+        <v>142.524</v>
       </c>
       <c r="M13" s="12">
-        <f t="shared" si="4"/>
-        <v>460.76715573392988</v>
+        <f>F13/(1+I13-H13)</f>
+        <v>121.94452073606151</v>
       </c>
       <c r="N13" s="12">
-        <f t="shared" si="5"/>
-        <v>-46.571280000000002</v>
+        <f>L13-F13</f>
+        <v>9.3240000000000123</v>
       </c>
       <c r="O13" s="12">
-        <f t="shared" si="6"/>
-        <v>-119.77642213303508</v>
+        <f>0.5*(M13-F13)</f>
+        <v>-5.6277396319692414</v>
       </c>
       <c r="P13" s="15">
-        <f t="shared" si="7"/>
-        <v>-166.34770213303509</v>
+        <f>N13+O13</f>
+        <v>3.6962603680307708</v>
       </c>
       <c r="Q13" s="12">
-        <f t="shared" si="8"/>
-        <v>269.97621216168841</v>
+        <f>MAX($P$2:$P$280)-P13</f>
+        <v>99.932249660622546</v>
       </c>
       <c r="R13" s="9">
-        <f t="shared" si="9"/>
-        <v>3.7040300402507364E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q13)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.0006779627158154E-2</v>
       </c>
       <c r="S13" s="9">
-        <f t="shared" si="10"/>
-        <v>0.83576440425463305</v>
+        <f>Q13/MAX($Q$2:$Q$28)</f>
+        <v>0.45181133898649067</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>26</v>
+        <v>36</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D14" s="8">
-        <v>45511</v>
+        <v>45483</v>
       </c>
       <c r="E14" s="2">
-        <v>0.1933</v>
+        <v>0.1195</v>
       </c>
       <c r="F14" s="1">
-        <v>77.53</v>
+        <v>167.24</v>
       </c>
       <c r="G14" s="1">
-        <f t="shared" si="0"/>
-        <v>14.986549</v>
+        <f>E14*F14</f>
+        <v>19.98518</v>
       </c>
       <c r="H14" s="11">
-        <f>83.34/F14-1</f>
-        <v>7.4938733393525192E-2</v>
+        <f>190.41/F14-1</f>
+        <v>0.13854341066730447</v>
       </c>
       <c r="I14" s="11">
-        <v>0.25990000000000002</v>
+        <v>0.26790000000000003</v>
       </c>
       <c r="J14" s="9">
-        <f t="shared" si="1"/>
-        <v>0.28833679643526428</v>
+        <f>IFERROR(H14/I14,"")</f>
+        <v>0.51714598979956872</v>
       </c>
       <c r="K14" s="9">
-        <f t="shared" si="2"/>
-        <v>3.1012508638879263E-2</v>
+        <f>IFERROR(J14/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>3.3978694301111501E-2</v>
       </c>
       <c r="L14" s="12">
-        <f t="shared" si="3"/>
-        <v>83.34</v>
+        <f>F14/(1-(F14*(1+H14)-F14)/(F14*(1+H14)))</f>
+        <v>190.41</v>
       </c>
       <c r="M14" s="12">
-        <f t="shared" si="4"/>
-        <v>65.428298953629579</v>
+        <f>F14/(1+I14-H14)</f>
+        <v>148.08431772538498</v>
       </c>
       <c r="N14" s="12">
-        <f t="shared" si="5"/>
-        <v>5.8100000000000023</v>
+        <f>L14-F14</f>
+        <v>23.169999999999987</v>
       </c>
       <c r="O14" s="12">
-        <f t="shared" si="6"/>
-        <v>-6.0508505231852112</v>
+        <f>0.5*(M14-F14)</f>
+        <v>-9.5778411373075159</v>
       </c>
       <c r="P14" s="15">
-        <f t="shared" si="7"/>
-        <v>-0.24085052318520894</v>
+        <f>N14+O14</f>
+        <v>13.592158862692472</v>
       </c>
       <c r="Q14" s="12">
-        <f t="shared" si="8"/>
-        <v>103.86936055183853</v>
+        <f>MAX($P$2:$P$280)-P14</f>
+        <v>90.036351165960852</v>
       </c>
       <c r="R14" s="9">
-        <f t="shared" si="9"/>
-        <v>9.6274781580168271E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q14)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.1106625124742505E-2</v>
       </c>
       <c r="S14" s="9">
-        <f t="shared" si="10"/>
-        <v>0.32154801175566694</v>
+        <f>Q14/MAX($Q$2:$Q$28)</f>
+        <v>0.40707023524338853</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>8</v>
+        <v>36</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="D15" s="8">
-        <v>45511</v>
+        <v>45481</v>
       </c>
       <c r="E15" s="2">
-        <v>3.2899999999999999E-2</v>
+        <v>2.8500000000000001E-2</v>
       </c>
       <c r="F15" s="1">
-        <v>455.4</v>
+        <v>700.32</v>
       </c>
       <c r="G15" s="1">
-        <f t="shared" si="0"/>
-        <v>14.982659999999999</v>
+        <f>E15*F15</f>
+        <v>19.959120000000002</v>
       </c>
       <c r="H15" s="11">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="I15" s="11">
-        <v>0.29699999999999999</v>
+        <v>0.45340000000000003</v>
       </c>
       <c r="J15" s="9">
-        <f t="shared" si="1"/>
-        <v>0.84175084175084181</v>
+        <f>IFERROR(H15/I15,"")</f>
+        <v>0.22055580061755625</v>
       </c>
       <c r="K15" s="9">
-        <f t="shared" si="2"/>
-        <v>9.053580942258535E-2</v>
+        <f>IFERROR(J15/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>1.4491455552861165E-2</v>
       </c>
       <c r="L15" s="12">
-        <f t="shared" si="3"/>
-        <v>569.25</v>
+        <f>F15/(1-(F15*(1+H15)-F15)/(F15*(1+H15)))</f>
+        <v>770.35200000000009</v>
       </c>
       <c r="M15" s="12">
-        <f t="shared" si="4"/>
-        <v>434.95702005730658</v>
+        <f>F15/(1+I15-H15)</f>
+        <v>517.45234224915032</v>
       </c>
       <c r="N15" s="12">
-        <f t="shared" si="5"/>
-        <v>113.85000000000002</v>
+        <f>L15-F15</f>
+        <v>70.032000000000039</v>
       </c>
       <c r="O15" s="12">
-        <f t="shared" si="6"/>
-        <v>-10.221489971346699</v>
+        <f>0.5*(M15-F15)</f>
+        <v>-91.433828875424865</v>
       </c>
       <c r="P15" s="15">
-        <f t="shared" si="7"/>
-        <v>103.62851002865332</v>
+        <f>N15+O15</f>
+        <v>-21.401828875424826</v>
       </c>
       <c r="Q15" s="12">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f>MAX($P$2:$P$280)-P15</f>
+        <v>125.03033890407815</v>
       </c>
       <c r="R15" s="9">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q15)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>7.9980587812945834E-3</v>
       </c>
       <c r="S15" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f>Q15/MAX($Q$2:$Q$28)</f>
+        <v>0.565284230326356</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
@@ -1814,141 +1813,139 @@
         <v>40</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>50</v>
+        <v>26</v>
+      </c>
+      <c r="C16" t="s">
+        <v>27</v>
       </c>
       <c r="D16" s="8">
         <v>45511</v>
       </c>
       <c r="E16" s="2">
-        <v>1</v>
+        <v>0.45179999999999998</v>
       </c>
       <c r="F16" s="1">
-        <v>10.4</v>
+        <v>77.430000000000007</v>
       </c>
       <c r="G16" s="1">
-        <f t="shared" si="0"/>
-        <v>10.4</v>
+        <f>E16*F16</f>
+        <v>34.982874000000002</v>
       </c>
       <c r="H16" s="11">
-        <f>2.89/F16-1</f>
-        <v>-0.7221153846153846</v>
-      </c>
-      <c r="I16" s="13">
-        <v>1.8652</v>
+        <v>0.1</v>
+      </c>
+      <c r="I16" s="11">
+        <v>0.25990000000000002</v>
       </c>
       <c r="J16" s="9">
-        <f t="shared" si="1"/>
-        <v>-0.38715171810818388</v>
+        <f>IFERROR(H16/I16,"")</f>
+        <v>0.38476337052712584</v>
       </c>
       <c r="K16" s="9">
-        <f t="shared" si="2"/>
-        <v>-4.1640699871903594E-2</v>
+        <f>IFERROR(J16/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>2.5280592334233368E-2</v>
       </c>
       <c r="L16" s="12">
-        <f t="shared" si="3"/>
-        <v>2.8900000000000006</v>
+        <f>F16/(1-(F16*(1+H16)-F16)/(F16*(1+H16)))</f>
+        <v>85.173000000000016</v>
       </c>
       <c r="M16" s="12">
-        <f t="shared" si="4"/>
-        <v>2.8991038938481961</v>
+        <f>F16/(1+I16-H16)</f>
+        <v>66.755754806448849</v>
       </c>
       <c r="N16" s="12">
-        <f t="shared" si="5"/>
-        <v>-7.51</v>
+        <f>L16-F16</f>
+        <v>7.7430000000000092</v>
       </c>
       <c r="O16" s="12">
-        <f t="shared" si="6"/>
-        <v>-3.7504480530759023</v>
+        <f>0.5*(M16-F16)</f>
+        <v>-5.3371225967755791</v>
       </c>
       <c r="P16" s="15">
-        <f t="shared" si="7"/>
-        <v>-11.260448053075901</v>
+        <f>N16+O16</f>
+        <v>2.4058774032244301</v>
       </c>
       <c r="Q16" s="12">
-        <f t="shared" si="8"/>
-        <v>114.88895808172923</v>
+        <f>MAX($P$2:$P$280)-P16</f>
+        <v>101.2226326254289</v>
       </c>
       <c r="R16" s="9">
-        <f t="shared" si="9"/>
-        <v>8.7040566534568459E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q16)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.8792135124608719E-3</v>
       </c>
       <c r="S16" s="9">
-        <f t="shared" si="10"/>
-        <v>0.35566134081881862</v>
+        <f>Q16/MAX($Q$2:$Q$28)</f>
+        <v>0.45764538812592725</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>23</v>
+        <v>37</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D17" s="8">
-        <v>45482</v>
+        <v>45511</v>
       </c>
       <c r="E17" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>3.2899999999999999E-2</v>
       </c>
       <c r="F17" s="1">
-        <v>147.01</v>
+        <v>455.4</v>
       </c>
       <c r="G17" s="1">
-        <f t="shared" si="0"/>
-        <v>1.4700999999999999E-17</v>
+        <f>E17*F17</f>
+        <v>14.982659999999999</v>
       </c>
       <c r="H17" s="11">
-        <f>193.73/F17-1</f>
-        <v>0.3178015101013536</v>
+        <v>0.25</v>
       </c>
       <c r="I17" s="11">
-        <v>0.52380000000000004</v>
+        <v>0.29699999999999999</v>
       </c>
       <c r="J17" s="9">
-        <f t="shared" si="1"/>
-        <v>0.60672300515722333</v>
+        <f>IFERROR(H17/I17,"")</f>
+        <v>0.84175084175084181</v>
       </c>
       <c r="K17" s="9">
-        <f t="shared" si="2"/>
-        <v>6.5257028140248613E-2</v>
+        <f>IFERROR(J17/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>5.5306615721104818E-2</v>
       </c>
       <c r="L17" s="12">
-        <f t="shared" si="3"/>
-        <v>193.72999999999996</v>
+        <f>F17/(1-(F17*(1+H17)-F17)/(F17*(1+H17)))</f>
+        <v>569.25</v>
       </c>
       <c r="M17" s="12">
-        <f t="shared" si="4"/>
-        <v>121.89899177432211</v>
+        <f>F17/(1+I17-H17)</f>
+        <v>434.95702005730658</v>
       </c>
       <c r="N17" s="12">
-        <f t="shared" si="5"/>
-        <v>46.71999999999997</v>
+        <f>L17-F17</f>
+        <v>113.85000000000002</v>
       </c>
       <c r="O17" s="12">
-        <f t="shared" si="6"/>
-        <v>-12.555504112838939</v>
+        <f>0.5*(M17-F17)</f>
+        <v>-10.221489971346699</v>
       </c>
       <c r="P17" s="15">
-        <f t="shared" si="7"/>
-        <v>34.164495887161031</v>
+        <f>N17+O17</f>
+        <v>103.62851002865332</v>
       </c>
       <c r="Q17" s="12">
-        <f t="shared" si="8"/>
-        <v>69.464014141492299</v>
+        <f>MAX($P$2:$P$280)-P17</f>
+        <v>0</v>
       </c>
       <c r="R17" s="9">
-        <f t="shared" si="9"/>
-        <v>1.4395943170849369E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q17)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>0</v>
       </c>
       <c r="S17" s="9">
-        <f t="shared" si="10"/>
-        <v>0.21503950267044389</v>
+        <f>Q17/MAX($Q$2:$Q$28)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
@@ -1956,70 +1953,69 @@
         <v>40</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18" t="s">
-        <v>46</v>
+        <v>51</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>50</v>
       </c>
       <c r="D18" s="8">
         <v>45511</v>
       </c>
       <c r="E18" s="2">
-        <v>1E-22</v>
+        <v>1</v>
       </c>
       <c r="F18" s="1">
-        <v>187.36</v>
+        <v>10.92</v>
       </c>
       <c r="G18" s="1">
-        <f t="shared" si="0"/>
-        <v>1.8736000000000003E-20</v>
+        <f>E18*F18</f>
+        <v>10.92</v>
       </c>
       <c r="H18" s="11">
-        <f>196.02/F18-1</f>
-        <v>4.6221178479931568E-2</v>
-      </c>
-      <c r="I18" s="11">
-        <v>0.52980000000000005</v>
+        <v>1</v>
+      </c>
+      <c r="I18" s="13">
+        <v>1.8652</v>
       </c>
       <c r="J18" s="9">
-        <f t="shared" si="1"/>
-        <v>8.7242692487602053E-2</v>
+        <f>IFERROR(H18/I18,"")</f>
+        <v>0.53613553506326406</v>
       </c>
       <c r="K18" s="9">
-        <f t="shared" si="2"/>
-        <v>9.38352228331806E-3</v>
+        <f>IFERROR(J18/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>3.5226388310461362E-2</v>
       </c>
       <c r="L18" s="12">
-        <f t="shared" si="3"/>
-        <v>196.01999999999998</v>
+        <f>F18/(1-(F18*(1+H18)-F18)/(F18*(1+H18)))</f>
+        <v>21.84</v>
       </c>
       <c r="M18" s="12">
-        <f t="shared" si="4"/>
-        <v>126.28921179127629</v>
+        <f>F18/(1+I18-H18)</f>
+        <v>5.8546000428908433</v>
       </c>
       <c r="N18" s="12">
-        <f t="shared" si="5"/>
-        <v>8.6599999999999682</v>
+        <f>L18-F18</f>
+        <v>10.92</v>
       </c>
       <c r="O18" s="12">
-        <f t="shared" si="6"/>
-        <v>-30.535394104361863</v>
+        <f>0.5*(M18-F18)</f>
+        <v>-2.5326999785545783</v>
       </c>
       <c r="P18" s="15">
-        <f t="shared" si="7"/>
-        <v>-21.875394104361895</v>
+        <f>N18+O18</f>
+        <v>8.3873000214454212</v>
       </c>
       <c r="Q18" s="12">
-        <f t="shared" si="8"/>
-        <v>125.50390413301523</v>
+        <f>MAX($P$2:$P$280)-P18</f>
+        <v>95.241210007207897</v>
       </c>
       <c r="R18" s="9">
-        <f t="shared" si="9"/>
-        <v>7.9678796202240117E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q18)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.0499656607935993E-2</v>
       </c>
       <c r="S18" s="9">
-        <f t="shared" si="10"/>
-        <v>0.38852199173214769</v>
+        <f>Q18/MAX($Q$2:$Q$28)</f>
+        <v>0.43060232073416616</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
@@ -2027,70 +2023,69 @@
         <v>36</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D19" s="8">
-        <v>45481</v>
+        <v>45482</v>
       </c>
       <c r="E19" s="2">
-        <v>1E-22</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F19" s="1">
-        <v>169.34</v>
+        <v>147.01</v>
       </c>
       <c r="G19" s="1">
-        <f t="shared" si="0"/>
-        <v>1.6934000000000002E-20</v>
+        <f>E19*F19</f>
+        <v>1.4700999999999999E-17</v>
       </c>
       <c r="H19" s="11">
-        <f>174.52/F19-1</f>
-        <v>3.0589346876107371E-2</v>
+        <v>0.15</v>
       </c>
       <c r="I19" s="11">
-        <v>0.4259</v>
+        <v>0.52380000000000004</v>
       </c>
       <c r="J19" s="9">
-        <f t="shared" si="1"/>
-        <v>7.1822838403633182E-2</v>
+        <f>IFERROR(H19/I19,"")</f>
+        <v>0.28636884306987398</v>
       </c>
       <c r="K19" s="9">
-        <f t="shared" si="2"/>
-        <v>7.7250161061617672E-3</v>
+        <f>IFERROR(J19/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>1.8815652771097514E-2</v>
       </c>
       <c r="L19" s="12">
-        <f t="shared" si="3"/>
-        <v>174.52000000000004</v>
+        <f>F19/(1-(F19*(1+H19)-F19)/(F19*(1+H19)))</f>
+        <v>169.06149999999997</v>
       </c>
       <c r="M19" s="12">
-        <f t="shared" si="4"/>
-        <v>121.36365448143965</v>
+        <f>F19/(1+I19-H19)</f>
+        <v>107.00975396709855</v>
       </c>
       <c r="N19" s="12">
-        <f t="shared" si="5"/>
-        <v>5.1800000000000352</v>
+        <f>L19-F19</f>
+        <v>22.051499999999976</v>
       </c>
       <c r="O19" s="12">
-        <f t="shared" si="6"/>
-        <v>-23.988172759280175</v>
+        <f>0.5*(M19-F19)</f>
+        <v>-20.000123016450722</v>
       </c>
       <c r="P19" s="15">
-        <f t="shared" si="7"/>
-        <v>-18.80817275928014</v>
+        <f>N19+O19</f>
+        <v>2.0513769835492539</v>
       </c>
       <c r="Q19" s="12">
-        <f t="shared" si="8"/>
-        <v>122.43668278793346</v>
+        <f>MAX($P$2:$P$280)-P19</f>
+        <v>101.57713304510406</v>
       </c>
       <c r="R19" s="9">
-        <f t="shared" si="9"/>
-        <v>8.1674868775402105E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q19)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.8447354244184312E-3</v>
       </c>
       <c r="S19" s="9">
-        <f t="shared" si="10"/>
-        <v>0.37902680547235196</v>
+        <f>Q19/MAX($Q$2:$Q$28)</f>
+        <v>0.45924814709341422</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
@@ -2098,10 +2093,10 @@
         <v>40</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>32</v>
+        <v>47</v>
+      </c>
+      <c r="C20" t="s">
+        <v>46</v>
       </c>
       <c r="D20" s="8">
         <v>45511</v>
@@ -2110,58 +2105,58 @@
         <v>1E-22</v>
       </c>
       <c r="F20" s="1">
-        <v>113.58</v>
+        <v>187.36</v>
       </c>
       <c r="G20" s="1">
-        <f t="shared" si="0"/>
-        <v>1.1358E-20</v>
+        <f>E20*F20</f>
+        <v>1.8736000000000003E-20</v>
       </c>
       <c r="H20" s="11">
-        <f>121.15/F20-1</f>
-        <v>6.664905793273479E-2</v>
+        <f>196.02/F20-1</f>
+        <v>4.6221178479931568E-2</v>
       </c>
       <c r="I20" s="11">
-        <v>0.16439999999999999</v>
+        <v>0.52980000000000005</v>
       </c>
       <c r="J20" s="9">
-        <f t="shared" si="1"/>
-        <v>0.40540789496797319</v>
+        <f>IFERROR(H20/I20,"")</f>
+        <v>8.7242692487602053E-2</v>
       </c>
       <c r="K20" s="9">
-        <f t="shared" si="2"/>
-        <v>4.3604271117671518E-2</v>
+        <f>IFERROR(J20/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>5.7322165046489537E-3</v>
       </c>
       <c r="L20" s="12">
-        <f t="shared" si="3"/>
-        <v>121.15000000000002</v>
+        <f>F20/(1-(F20*(1+H20)-F20)/(F20*(1+H20)))</f>
+        <v>196.01999999999998</v>
       </c>
       <c r="M20" s="12">
-        <f t="shared" si="4"/>
-        <v>103.46609203186667</v>
+        <f>F20/(1+I20-H20)</f>
+        <v>126.28921179127629</v>
       </c>
       <c r="N20" s="12">
-        <f t="shared" si="5"/>
-        <v>7.5700000000000216</v>
+        <f>L20-F20</f>
+        <v>8.6599999999999682</v>
       </c>
       <c r="O20" s="12">
-        <f t="shared" si="6"/>
-        <v>-5.0569539840666664</v>
+        <f>0.5*(M20-F20)</f>
+        <v>-30.535394104361863</v>
       </c>
       <c r="P20" s="15">
-        <f t="shared" si="7"/>
-        <v>2.5130460159333552</v>
+        <f>N20+O20</f>
+        <v>-21.875394104361895</v>
       </c>
       <c r="Q20" s="12">
-        <f t="shared" si="8"/>
-        <v>101.11546401271997</v>
+        <f>MAX($P$2:$P$280)-P20</f>
+        <v>125.50390413301523</v>
       </c>
       <c r="R20" s="9">
-        <f t="shared" si="9"/>
-        <v>9.8896841325299516E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q20)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>7.9678796202240099E-3</v>
       </c>
       <c r="S20" s="9">
-        <f t="shared" si="10"/>
-        <v>0.3130227839885002</v>
+        <f>Q20/MAX($Q$2:$Q$28)</f>
+        <v>0.5674253023117275</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
@@ -2169,10 +2164,10 @@
         <v>36</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="C21" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
       <c r="D21" s="8">
         <v>45481</v>
@@ -2181,58 +2176,57 @@
         <v>1E-22</v>
       </c>
       <c r="F21" s="1">
-        <v>64.349999999999994</v>
+        <v>169.34</v>
       </c>
       <c r="G21" s="1">
-        <f t="shared" si="0"/>
-        <v>6.4349999999999995E-21</v>
+        <f>E21*F21</f>
+        <v>1.6934000000000002E-20</v>
       </c>
       <c r="H21" s="11">
-        <f>75.53/F21-1</f>
-        <v>0.17373737373737397</v>
+        <v>0.1</v>
       </c>
       <c r="I21" s="11">
-        <v>0.67300000000000004</v>
+        <v>0.4259</v>
       </c>
       <c r="J21" s="9">
-        <f t="shared" si="1"/>
-        <v>0.25815360139282906</v>
+        <f>IFERROR(H21/I21,"")</f>
+        <v>0.23479690068091102</v>
       </c>
       <c r="K21" s="9">
-        <f t="shared" si="2"/>
-        <v>2.7766108565856817E-2</v>
+        <f>IFERROR(J21/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>1.5427156486657085E-2</v>
       </c>
       <c r="L21" s="12">
-        <f t="shared" si="3"/>
-        <v>75.53</v>
+        <f>F21/(1-(F21*(1+H21)-F21)/(F21*(1+H21)))</f>
+        <v>186.27400000000003</v>
       </c>
       <c r="M21" s="12">
-        <f t="shared" si="4"/>
-        <v>42.921099260916144</v>
+        <f>F21/(1+I21-H21)</f>
+        <v>127.71702239987934</v>
       </c>
       <c r="N21" s="12">
-        <f t="shared" si="5"/>
-        <v>11.180000000000007</v>
+        <f>L21-F21</f>
+        <v>16.934000000000026</v>
       </c>
       <c r="O21" s="12">
-        <f t="shared" si="6"/>
-        <v>-10.714450369541925</v>
+        <f>0.5*(M21-F21)</f>
+        <v>-20.811488800060332</v>
       </c>
       <c r="P21" s="15">
-        <f t="shared" si="7"/>
-        <v>0.46554963045808151</v>
+        <f>N21+O21</f>
+        <v>-3.8774888000603056</v>
       </c>
       <c r="Q21" s="12">
-        <f t="shared" si="8"/>
-        <v>103.16296039819524</v>
+        <f>MAX($P$2:$P$280)-P21</f>
+        <v>107.50599882871363</v>
       </c>
       <c r="R21" s="9">
-        <f t="shared" si="9"/>
-        <v>9.6934015478048873E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q21)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.3018065121488955E-3</v>
       </c>
       <c r="S21" s="9">
-        <f t="shared" si="10"/>
-        <v>0.31936121130073841</v>
+        <f>Q21/MAX($Q$2:$Q$28)</f>
+        <v>0.48605359575949542</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
@@ -2240,10 +2234,10 @@
         <v>40</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D22" s="8">
         <v>45511</v>
@@ -2252,129 +2246,128 @@
         <v>1E-22</v>
       </c>
       <c r="F22" s="1">
-        <v>20.82</v>
+        <v>113.58</v>
       </c>
       <c r="G22" s="1">
-        <f t="shared" si="0"/>
-        <v>2.0820000000000001E-21</v>
-      </c>
-      <c r="H22" s="13">
-        <f>19.07/F22-1</f>
-        <v>-8.4053794428434192E-2</v>
+        <f>E22*F22</f>
+        <v>1.1358E-20</v>
+      </c>
+      <c r="H22" s="11">
+        <f>121.15/F22-1</f>
+        <v>6.664905793273479E-2</v>
       </c>
       <c r="I22" s="11">
-        <v>0.7389</v>
+        <v>0.16439999999999999</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" si="1"/>
-        <v>-0.11375530440984462</v>
+        <f>IFERROR(H22/I22,"")</f>
+        <v>0.40540789496797319</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" si="2"/>
-        <v>-1.2235127130299155E-2</v>
+        <f>IFERROR(J22/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>2.6637025524867311E-2</v>
       </c>
       <c r="L22" s="12">
-        <f t="shared" si="3"/>
-        <v>19.070000000000004</v>
+        <f>F22/(1-(F22*(1+H22)-F22)/(F22*(1+H22)))</f>
+        <v>121.15000000000002</v>
       </c>
       <c r="M22" s="12">
-        <f t="shared" si="4"/>
-        <v>11.421024528231593</v>
+        <f>F22/(1+I22-H22)</f>
+        <v>103.46609203186667</v>
       </c>
       <c r="N22" s="12">
-        <f t="shared" si="5"/>
-        <v>-1.7499999999999964</v>
+        <f>L22-F22</f>
+        <v>7.5700000000000216</v>
       </c>
       <c r="O22" s="12">
-        <f t="shared" si="6"/>
-        <v>-4.6994877358842038</v>
+        <f>0.5*(M22-F22)</f>
+        <v>-5.0569539840666664</v>
       </c>
       <c r="P22" s="15">
-        <f t="shared" si="7"/>
-        <v>-6.4494877358842002</v>
+        <f>N22+O22</f>
+        <v>2.5130460159333552</v>
       </c>
       <c r="Q22" s="12">
-        <f t="shared" si="8"/>
-        <v>110.07799776453753</v>
+        <f>MAX($P$2:$P$280)-P22</f>
+        <v>101.11546401271997</v>
       </c>
       <c r="R22" s="9">
-        <f t="shared" si="9"/>
-        <v>9.0844675621648864E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q22)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.8896841325299516E-3</v>
       </c>
       <c r="S22" s="9">
-        <f t="shared" si="10"/>
-        <v>0.34076806799601772</v>
+        <f>Q22/MAX($Q$2:$Q$28)</f>
+        <v>0.45716085991236471</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>40</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>54</v>
+        <v>36</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="D23" s="8">
-        <v>45511</v>
+        <v>45481</v>
       </c>
       <c r="E23" s="2">
         <v>1E-22</v>
       </c>
       <c r="F23" s="1">
-        <v>13.04</v>
+        <v>64.349999999999994</v>
       </c>
       <c r="G23" s="1">
-        <f t="shared" si="0"/>
-        <v>1.304E-21</v>
+        <f>E23*F23</f>
+        <v>6.4349999999999995E-21</v>
       </c>
       <c r="H23" s="11">
-        <f>13.72/F23-1</f>
-        <v>5.2147239263803824E-2</v>
+        <v>0.15</v>
       </c>
       <c r="I23" s="11">
-        <v>0.30159999999999998</v>
+        <v>0.67300000000000004</v>
       </c>
       <c r="J23" s="9">
-        <f t="shared" si="1"/>
-        <v>0.17290198694895167</v>
+        <f>IFERROR(H23/I23,"")</f>
+        <v>0.22288261515601782</v>
       </c>
       <c r="K23" s="9">
-        <f t="shared" si="2"/>
-        <v>1.8596739750965593E-2</v>
+        <f>IFERROR(J23/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>1.4644337179050337E-2</v>
       </c>
       <c r="L23" s="12">
-        <f t="shared" si="3"/>
-        <v>13.72</v>
+        <f>F23/(1-(F23*(1+H23)-F23)/(F23*(1+H23)))</f>
+        <v>74.002499999999984</v>
       </c>
       <c r="M23" s="12">
-        <f t="shared" si="4"/>
-        <v>10.436569040286594</v>
+        <f>F23/(1+I23-H23)</f>
+        <v>42.252133946158892</v>
       </c>
       <c r="N23" s="12">
-        <f t="shared" si="5"/>
-        <v>0.68000000000000149</v>
+        <f>L23-F23</f>
+        <v>9.6524999999999892</v>
       </c>
       <c r="O23" s="12">
-        <f t="shared" si="6"/>
-        <v>-1.3017154798567026</v>
+        <f>0.5*(M23-F23)</f>
+        <v>-11.048933026920551</v>
       </c>
       <c r="P23" s="15">
-        <f t="shared" si="7"/>
-        <v>-0.62171547985670106</v>
+        <f>N23+O23</f>
+        <v>-1.3964330269205618</v>
       </c>
       <c r="Q23" s="12">
-        <f t="shared" si="8"/>
-        <v>104.25022550851003</v>
+        <f>MAX($P$2:$P$280)-P23</f>
+        <v>105.02494305557389</v>
       </c>
       <c r="R23" s="9">
-        <f t="shared" si="9"/>
-        <v>9.5923053894820514E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q23)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.5215476524548141E-3</v>
       </c>
       <c r="S23" s="9">
-        <f t="shared" si="10"/>
-        <v>0.3227270540537468</v>
+        <f>Q23/MAX($Q$2:$Q$28)</f>
+        <v>0.47483630469710741</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
@@ -2382,10 +2375,10 @@
         <v>40</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C24" t="s">
-        <v>44</v>
+        <v>49</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>48</v>
       </c>
       <c r="D24" s="8">
         <v>45511</v>
@@ -2394,58 +2387,57 @@
         <v>1E-22</v>
       </c>
       <c r="F24" s="1">
-        <v>11.05</v>
+        <v>20.82</v>
       </c>
       <c r="G24" s="1">
-        <f t="shared" si="0"/>
-        <v>1.1050000000000002E-21</v>
-      </c>
-      <c r="H24" s="11">
-        <f>9.52/F24-1</f>
-        <v>-0.13846153846153852</v>
+        <f>E24*F24</f>
+        <v>2.0820000000000001E-21</v>
+      </c>
+      <c r="H24" s="13">
+        <v>0.05</v>
       </c>
       <c r="I24" s="11">
-        <v>0.72170000000000001</v>
+        <v>0.7389</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" si="1"/>
-        <v>-0.19185470203898922</v>
+        <f>IFERROR(H24/I24,"")</f>
+        <v>6.7668155366084726E-2</v>
       </c>
       <c r="K24" s="9">
-        <f t="shared" si="2"/>
-        <v>-2.0635228239867041E-2</v>
+        <f>IFERROR(J24/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>4.4460860384810206E-3</v>
       </c>
       <c r="L24" s="12">
-        <f t="shared" si="3"/>
-        <v>9.52</v>
+        <f>F24/(1-(F24*(1+H24)-F24)/(F24*(1+H24)))</f>
+        <v>21.861000000000001</v>
       </c>
       <c r="M24" s="12">
-        <f t="shared" si="4"/>
-        <v>5.9403443042581081</v>
+        <f>F24/(1+I24-H24)</f>
+        <v>12.327550476641601</v>
       </c>
       <c r="N24" s="12">
-        <f t="shared" si="5"/>
-        <v>-1.5300000000000011</v>
+        <f>L24-F24</f>
+        <v>1.0410000000000004</v>
       </c>
       <c r="O24" s="12">
-        <f t="shared" si="6"/>
-        <v>-2.5548278478709463</v>
+        <f>0.5*(M24-F24)</f>
+        <v>-4.2462247616791995</v>
       </c>
       <c r="P24" s="15">
-        <f t="shared" si="7"/>
-        <v>-4.0848278478709474</v>
+        <f>N24+O24</f>
+        <v>-3.2052247616791991</v>
       </c>
       <c r="Q24" s="12">
-        <f t="shared" si="8"/>
-        <v>107.71333787652426</v>
+        <f>MAX($P$2:$P$280)-P24</f>
+        <v>106.83373479033253</v>
       </c>
       <c r="R24" s="9">
-        <f t="shared" si="9"/>
-        <v>9.2839013228457976E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q24)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.3603392408077718E-3</v>
       </c>
       <c r="S24" s="9">
-        <f t="shared" si="10"/>
-        <v>0.33344779875175323</v>
+        <f>Q24/MAX($Q$2:$Q$28)</f>
+        <v>0.48301417138583286</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
@@ -2453,10 +2445,10 @@
         <v>40</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C25" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D25" s="8">
         <v>45511</v>
@@ -2465,482 +2457,478 @@
         <v>1E-22</v>
       </c>
       <c r="F25" s="1">
-        <v>10.47</v>
+        <v>13.04</v>
       </c>
       <c r="G25" s="1">
-        <f t="shared" si="0"/>
-        <v>1.0470000000000001E-21</v>
+        <f>E25*F25</f>
+        <v>1.304E-21</v>
       </c>
       <c r="H25" s="11">
-        <f>6.42/F25-1</f>
-        <v>-0.38681948424068768</v>
+        <f>13.72/F25-1</f>
+        <v>5.2147239263803824E-2</v>
       </c>
       <c r="I25" s="11">
-        <v>0.85599999999999998</v>
+        <v>0.30159999999999998</v>
       </c>
       <c r="J25" s="9">
-        <f t="shared" si="1"/>
-        <v>-0.45189192084192487</v>
+        <f>IFERROR(H25/I25,"")</f>
+        <v>0.17290198694895167</v>
       </c>
       <c r="K25" s="9">
-        <f t="shared" si="2"/>
-        <v>-4.8603932180041234E-2</v>
+        <f>IFERROR(J25/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>1.1360397014526166E-2</v>
       </c>
       <c r="L25" s="12">
-        <f t="shared" si="3"/>
-        <v>6.419999999999999</v>
+        <f>F25/(1-(F25*(1+H25)-F25)/(F25*(1+H25)))</f>
+        <v>13.72</v>
       </c>
       <c r="M25" s="12">
-        <f t="shared" si="4"/>
-        <v>4.6682312480197874</v>
+        <f>F25/(1+I25-H25)</f>
+        <v>10.436569040286594</v>
       </c>
       <c r="N25" s="12">
-        <f t="shared" si="5"/>
-        <v>-4.0500000000000016</v>
+        <f>L25-F25</f>
+        <v>0.68000000000000149</v>
       </c>
       <c r="O25" s="12">
-        <f t="shared" si="6"/>
-        <v>-2.9008843759901066</v>
+        <f>0.5*(M25-F25)</f>
+        <v>-1.3017154798567026</v>
       </c>
       <c r="P25" s="15">
-        <f t="shared" si="7"/>
-        <v>-6.9508843759901087</v>
+        <f>N25+O25</f>
+        <v>-0.62171547985670106</v>
       </c>
       <c r="Q25" s="12">
-        <f t="shared" si="8"/>
-        <v>110.57939440464344</v>
+        <f>MAX($P$2:$P$280)-P25</f>
+        <v>104.25022550851003</v>
       </c>
       <c r="R25" s="9">
-        <f t="shared" si="9"/>
-        <v>9.043276149087032E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q25)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.5923053894820514E-3</v>
       </c>
       <c r="S25" s="9">
-        <f t="shared" si="10"/>
-        <v>0.34232023979981507</v>
+        <f>Q25/MAX($Q$2:$Q$28)</f>
+        <v>0.47133366992741127</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>18</v>
+        <v>40</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="D26" s="8">
-        <v>45483</v>
+        <v>45511</v>
       </c>
       <c r="E26" s="2">
-        <v>0.1195</v>
+        <v>1E-22</v>
       </c>
       <c r="F26" s="1">
-        <v>167.24</v>
+        <v>11.05</v>
       </c>
       <c r="G26" s="1">
-        <f t="shared" si="0"/>
-        <v>19.98518</v>
+        <f>E26*F26</f>
+        <v>1.1050000000000002E-21</v>
       </c>
       <c r="H26" s="11">
-        <f>190.41/F26-1</f>
-        <v>0.13854341066730447</v>
+        <v>0.05</v>
       </c>
       <c r="I26" s="11">
-        <v>0.26790000000000003</v>
+        <v>0.72170000000000001</v>
       </c>
       <c r="J26" s="9">
-        <f t="shared" si="1"/>
-        <v>0.51714598979956872</v>
+        <f>IFERROR(H26/I26,"")</f>
+        <v>6.9280864625190522E-2</v>
       </c>
       <c r="K26" s="9">
-        <f t="shared" si="2"/>
-        <v>5.5622434162063847E-2</v>
+        <f>IFERROR(J26/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>4.5520479061017406E-3</v>
       </c>
       <c r="L26" s="12">
-        <f t="shared" si="3"/>
-        <v>190.41</v>
+        <f>F26/(1-(F26*(1+H26)-F26)/(F26*(1+H26)))</f>
+        <v>11.602500000000001</v>
       </c>
       <c r="M26" s="12">
-        <f t="shared" si="4"/>
-        <v>148.08431772538498</v>
+        <f>F26/(1+I26-H26)</f>
+        <v>6.6100376861877139</v>
       </c>
       <c r="N26" s="12">
-        <f t="shared" si="5"/>
-        <v>23.169999999999987</v>
+        <f>L26-F26</f>
+        <v>0.55250000000000021</v>
       </c>
       <c r="O26" s="12">
-        <f t="shared" si="6"/>
-        <v>-9.5778411373075159</v>
+        <f>0.5*(M26-F26)</f>
+        <v>-2.2199811569061434</v>
       </c>
       <c r="P26" s="15">
-        <f t="shared" si="7"/>
-        <v>13.592158862692472</v>
+        <f>N26+O26</f>
+        <v>-1.6674811569061432</v>
       </c>
       <c r="Q26" s="12">
-        <f t="shared" si="8"/>
-        <v>90.036351165960852</v>
+        <f>MAX($P$2:$P$280)-P26</f>
+        <v>105.29599118555947</v>
       </c>
       <c r="R26" s="9">
-        <f t="shared" si="9"/>
-        <v>1.1106625124742506E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q26)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.4970377194867252E-3</v>
       </c>
       <c r="S26" s="9">
-        <f t="shared" si="10"/>
-        <v>0.27872521356960728</v>
+        <f>Q26/MAX($Q$2:$Q$28)</f>
+        <v>0.47606176113338761</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C27" s="14" t="s">
-        <v>82</v>
+        <v>53</v>
+      </c>
+      <c r="C27" t="s">
+        <v>52</v>
       </c>
       <c r="D27" s="8">
-        <f ca="1">TODAY()-20</f>
-        <v>45607</v>
+        <v>45511</v>
       </c>
       <c r="E27" s="2">
-        <v>1E-35</v>
+        <v>1E-22</v>
       </c>
       <c r="F27" s="1">
-        <v>2742.9</v>
+        <v>10.47</v>
       </c>
       <c r="G27" s="1">
-        <f t="shared" si="0"/>
-        <v>2.7429E-32</v>
+        <f>E27*F27</f>
+        <v>1.0470000000000001E-21</v>
       </c>
       <c r="H27" s="11">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="I27" s="11">
-        <v>0.5</v>
+        <v>0.85599999999999998</v>
       </c>
       <c r="J27" s="9">
-        <f t="shared" si="1"/>
-        <v>0.2</v>
+        <f>IFERROR(H27/I27,"")</f>
+        <v>5.8411214953271035E-2</v>
       </c>
       <c r="K27" s="9">
-        <f t="shared" si="2"/>
-        <v>2.151130831880628E-2</v>
+        <f>IFERROR(J27/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>3.837865623637414E-3</v>
       </c>
       <c r="L27" s="12">
-        <f t="shared" si="3"/>
-        <v>3017.1900000000005</v>
+        <f>F27/(1-(F27*(1+H27)-F27)/(F27*(1+H27)))</f>
+        <v>10.993500000000001</v>
       </c>
       <c r="M27" s="12">
-        <f t="shared" si="4"/>
-        <v>1959.214285714286</v>
+        <f>F27/(1+I27-H27)</f>
+        <v>5.7973421926910307</v>
       </c>
       <c r="N27" s="12">
-        <f t="shared" si="5"/>
-        <v>274.29000000000042</v>
+        <f>L27-F27</f>
+        <v>0.5235000000000003</v>
       </c>
       <c r="O27" s="12">
-        <f t="shared" si="6"/>
-        <v>-391.84285714285704</v>
+        <f>0.5*(M27-F27)</f>
+        <v>-2.336328903654485</v>
       </c>
       <c r="P27" s="15">
-        <f t="shared" si="7"/>
-        <v>-117.55285714285662</v>
+        <f>N27+O27</f>
+        <v>-1.8128289036544847</v>
       </c>
       <c r="Q27" s="12">
-        <f t="shared" si="8"/>
-        <v>221.18136717150995</v>
+        <f>MAX($P$2:$P$280)-P27</f>
+        <v>105.44133893230781</v>
       </c>
       <c r="R27" s="9">
-        <f t="shared" si="9"/>
-        <v>4.5211765022890619E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q27)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.4839463357155301E-3</v>
       </c>
       <c r="S27" s="9">
-        <f t="shared" si="10"/>
-        <v>0.68471037535563517</v>
+        <f>Q27/MAX($Q$2:$Q$28)</f>
+        <v>0.47671890395064692</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C28" t="s">
-        <v>57</v>
+        <v>76</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>82</v>
       </c>
       <c r="D28" s="8">
-        <v>45505</v>
+        <f ca="1">TODAY()-20</f>
+        <v>45608</v>
       </c>
       <c r="E28" s="2">
         <v>1E-35</v>
       </c>
       <c r="F28" s="1">
-        <v>86.6</v>
+        <v>2742.9</v>
       </c>
       <c r="G28" s="1">
-        <f t="shared" si="0"/>
-        <v>8.6599999999999988E-34</v>
+        <f>E28*F28</f>
+        <v>2.7429E-32</v>
       </c>
       <c r="H28" s="11">
-        <f>89.44/F28-1</f>
-        <v>3.2794457274826883E-2</v>
+        <v>0.1</v>
       </c>
       <c r="I28" s="11">
-        <v>0.17249999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J28" s="9">
-        <f t="shared" si="1"/>
-        <v>0.19011279579609788</v>
+        <f>IFERROR(H28/I28,"")</f>
+        <v>0.2</v>
       </c>
       <c r="K28" s="9">
-        <f t="shared" si="2"/>
-        <v>2.0447874828600599E-2</v>
+        <f>IFERROR(J28/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>1.3140851895334505E-2</v>
       </c>
       <c r="L28" s="12">
-        <f t="shared" si="3"/>
-        <v>89.44</v>
+        <f>F28/(1-(F28*(1+H28)-F28)/(F28*(1+H28)))</f>
+        <v>3017.1900000000005</v>
       </c>
       <c r="M28" s="12">
-        <f t="shared" si="4"/>
-        <v>75.984538772119137</v>
+        <f>F28/(1+I28-H28)</f>
+        <v>1959.214285714286</v>
       </c>
       <c r="N28" s="12">
-        <f t="shared" si="5"/>
-        <v>2.8400000000000034</v>
+        <f>L28-F28</f>
+        <v>274.29000000000042</v>
       </c>
       <c r="O28" s="12">
-        <f t="shared" si="6"/>
-        <v>-5.3077306139404286</v>
+        <f>0.5*(M28-F28)</f>
+        <v>-391.84285714285704</v>
       </c>
       <c r="P28" s="15">
-        <f t="shared" si="7"/>
-        <v>-2.4677306139404251</v>
+        <f>N28+O28</f>
+        <v>-117.55285714285662</v>
       </c>
       <c r="Q28" s="12">
-        <f t="shared" si="8"/>
-        <v>106.09624064259376</v>
+        <f>MAX($P$2:$P$280)-P28</f>
+        <v>221.18136717150995</v>
       </c>
       <c r="R28" s="9">
-        <f t="shared" si="9"/>
-        <v>9.4254046509404457E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q28)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>4.5211765022890619E-3</v>
       </c>
       <c r="S28" s="9">
-        <f t="shared" si="10"/>
-        <v>0.32844175656930963</v>
+        <f>Q28/MAX($Q$2:$Q$28)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="C29" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="D29" s="8">
-        <v>45562</v>
+        <v>45505</v>
       </c>
       <c r="E29" s="2">
         <v>1E-35</v>
       </c>
       <c r="F29" s="1">
-        <v>56</v>
+        <v>86.6</v>
       </c>
       <c r="G29" s="1">
-        <f t="shared" si="0"/>
-        <v>5.5999999999999999E-34</v>
+        <f>E29*F29</f>
+        <v>8.6599999999999988E-34</v>
       </c>
       <c r="H29" s="11">
-        <v>0.08</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I29" s="11">
-        <v>0.19</v>
+        <v>0.17249999999999999</v>
       </c>
       <c r="J29" s="9">
-        <f t="shared" si="1"/>
-        <v>0.42105263157894735</v>
+        <f>IFERROR(H29/I29,"")</f>
+        <v>0.40579710144927544</v>
       </c>
       <c r="K29" s="9">
-        <f t="shared" si="2"/>
-        <v>4.5286964881697422E-2</v>
+        <f>IFERROR(J29/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>2.6662598048504797E-2</v>
       </c>
       <c r="L29" s="12">
-        <f t="shared" si="3"/>
-        <v>60.480000000000004</v>
+        <f>F29/(1-(F29*(1+H29)-F29)/(F29*(1+H29)))</f>
+        <v>92.662000000000006</v>
       </c>
       <c r="M29" s="12">
-        <f t="shared" si="4"/>
-        <v>50.450450450450454</v>
+        <f>F29/(1+I29-H29)</f>
+        <v>78.548752834467123</v>
       </c>
       <c r="N29" s="12">
-        <f t="shared" si="5"/>
-        <v>4.480000000000004</v>
+        <f>L29-F29</f>
+        <v>6.0620000000000118</v>
       </c>
       <c r="O29" s="12">
-        <f t="shared" si="6"/>
-        <v>-2.7747747747747731</v>
+        <f>0.5*(M29-F29)</f>
+        <v>-4.0256235827664355</v>
       </c>
       <c r="P29" s="15">
-        <f t="shared" si="7"/>
-        <v>1.7052252252252309</v>
+        <f>N29+O29</f>
+        <v>2.0363764172335763</v>
       </c>
       <c r="Q29" s="12">
-        <f t="shared" si="8"/>
-        <v>101.92328480342809</v>
+        <f>MAX($P$2:$P$280)-P29</f>
+        <v>101.59213361141974</v>
       </c>
       <c r="R29" s="9">
-        <f t="shared" si="9"/>
-        <v>9.811300743776322E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q29)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.8432818019641658E-3</v>
       </c>
       <c r="S29" s="9">
-        <f t="shared" si="10"/>
-        <v>0.31552355195055437</v>
+        <f>Q29/MAX($Q$2:$Q$28)</f>
+        <v>0.45931596730136171</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D30" s="8">
-        <v>45580</v>
+        <v>45562</v>
       </c>
       <c r="E30" s="2">
         <v>1E-35</v>
       </c>
       <c r="F30" s="1">
-        <v>20.399999999999999</v>
+        <v>56</v>
       </c>
       <c r="G30" s="1">
-        <f t="shared" si="0"/>
-        <v>2.0399999999999999E-34</v>
+        <f>E30*F30</f>
+        <v>5.5999999999999999E-34</v>
       </c>
       <c r="H30" s="11">
-        <f>L30/F30-1</f>
-        <v>3.9215686274509887E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I30" s="11">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="J30" s="9">
-        <f t="shared" si="1"/>
-        <v>0.2614379084967326</v>
+        <f>IFERROR(H30/I30,"")</f>
+        <v>0.36842105263157898</v>
       </c>
       <c r="K30" s="9">
-        <f t="shared" si="2"/>
-        <v>2.8119357279485394E-2</v>
+        <f>IFERROR(J30/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>2.4206832438774088E-2</v>
       </c>
       <c r="L30" s="12">
-        <v>21.2</v>
+        <f>F30/(1-(F30*(1+H30)-F30)/(F30*(1+H30)))</f>
+        <v>59.92</v>
       </c>
       <c r="M30" s="12">
-        <f t="shared" si="4"/>
-        <v>18.365401588702561</v>
+        <f>F30/(1+I30-H30)</f>
+        <v>50.000000000000007</v>
       </c>
       <c r="N30" s="12">
-        <f t="shared" si="5"/>
-        <v>0.80000000000000071</v>
+        <f>L30-F30</f>
+        <v>3.9200000000000017</v>
       </c>
       <c r="O30" s="12">
-        <f t="shared" si="6"/>
-        <v>-1.0172992056487189</v>
+        <f>0.5*(M30-F30)</f>
+        <v>-2.9999999999999964</v>
       </c>
       <c r="P30" s="15">
-        <f t="shared" si="7"/>
-        <v>-0.21729920564871819</v>
+        <f>N30+O30</f>
+        <v>0.92000000000000526</v>
       </c>
       <c r="Q30" s="12">
-        <f t="shared" si="8"/>
-        <v>103.84580923430204</v>
+        <f>MAX($P$2:$P$280)-P30</f>
+        <v>102.70851002865332</v>
       </c>
       <c r="R30" s="9">
-        <f t="shared" si="9"/>
-        <v>9.6296615855123308E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q30)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.7362915665023548E-3</v>
       </c>
       <c r="S30" s="9">
-        <f t="shared" si="10"/>
-        <v>0.32147510402534252</v>
+        <f>Q30/MAX($Q$2:$Q$28)</f>
+        <v>0.46436330212666782</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>59</v>
+        <v>76</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>77</v>
       </c>
       <c r="C31" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="D31" s="8">
-        <v>45574</v>
+        <v>45580</v>
       </c>
       <c r="E31" s="2">
-        <v>9.9999999999999998E-46</v>
+        <v>1E-35</v>
       </c>
       <c r="F31" s="1">
-        <v>47.42</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="G31" s="1">
-        <f t="shared" si="0"/>
-        <v>4.7420000000000006E-44</v>
+        <f>E31*F31</f>
+        <v>2.0399999999999999E-34</v>
       </c>
       <c r="H31" s="11">
-        <f>48.37/F31-1</f>
-        <v>2.0033741037536856E-2</v>
+        <v>0.1</v>
       </c>
       <c r="I31" s="11">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
       <c r="J31" s="9">
-        <f t="shared" si="1"/>
-        <v>5.0084352593842141E-2</v>
+        <f>IFERROR(H31/I31,"")</f>
+        <v>0.66666666666666674</v>
       </c>
       <c r="K31" s="9">
-        <f t="shared" si="2"/>
-        <v>5.3868997529697166E-3</v>
+        <f>IFERROR(J31/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>4.3802839651115019E-2</v>
       </c>
       <c r="L31" s="12">
-        <f>F31/(1-(F31*(1+H31)-F31)/(F31*(1+H31)))</f>
-        <v>48.37</v>
+        <v>21.2</v>
       </c>
       <c r="M31" s="12">
-        <f t="shared" si="4"/>
-        <v>34.36315902075247</v>
+        <f>F31/(1+I31-H31)</f>
+        <v>19.428571428571431</v>
       </c>
       <c r="N31" s="12">
-        <f t="shared" si="5"/>
-        <v>0.94999999999999574</v>
+        <f>L31-F31</f>
+        <v>0.80000000000000071</v>
       </c>
       <c r="O31" s="12">
-        <f t="shared" si="6"/>
-        <v>-6.5284204896237661</v>
+        <f>0.5*(M31-F31)</f>
+        <v>-0.48571428571428399</v>
       </c>
       <c r="P31" s="15">
-        <f t="shared" si="7"/>
-        <v>-5.5784204896237704</v>
+        <f>N31+O31</f>
+        <v>0.31428571428571672</v>
       </c>
       <c r="Q31" s="12">
-        <f t="shared" si="8"/>
-        <v>109.20693051827709</v>
+        <f>MAX($P$2:$P$280)-P31</f>
+        <v>103.31422431436761</v>
       </c>
       <c r="R31" s="9">
-        <f t="shared" si="9"/>
-        <v>9.1569280013106668E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q31)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.6792092921993977E-3</v>
       </c>
       <c r="S31" s="9">
-        <f t="shared" si="10"/>
-        <v>0.33807150820540705</v>
+        <f>Q31/MAX($Q$2:$Q$28)</f>
+        <v>0.46710184332234006</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
@@ -2948,209 +2936,209 @@
         <v>39</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="C32" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="D32" s="8">
-        <v>45507</v>
+        <v>45574</v>
       </c>
       <c r="E32" s="2">
         <v>9.9999999999999998E-46</v>
       </c>
       <c r="F32" s="1">
-        <v>41.8</v>
+        <v>47.42</v>
       </c>
       <c r="G32" s="1">
-        <f t="shared" si="0"/>
-        <v>4.1799999999999994E-44</v>
+        <f>E32*F32</f>
+        <v>4.7420000000000006E-44</v>
       </c>
       <c r="H32" s="11">
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I32" s="11">
         <v>0.4</v>
       </c>
       <c r="J32" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>IFERROR(H32/I32,"")</f>
+        <v>0.17500000000000002</v>
       </c>
       <c r="K32" s="9">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>IFERROR(J32/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>1.1498245408417693E-2</v>
       </c>
       <c r="L32" s="12">
         <f>F32/(1-(F32*(1+H32)-F32)/(F32*(1+H32)))</f>
-        <v>41.8</v>
+        <v>50.739400000000003</v>
       </c>
       <c r="M32" s="12">
-        <f t="shared" si="4"/>
-        <v>29.857142857142858</v>
+        <f>F32/(1+I32-H32)</f>
+        <v>35.654135338345867</v>
       </c>
       <c r="N32" s="12">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>L32-F32</f>
+        <v>3.3194000000000017</v>
       </c>
       <c r="O32" s="12">
-        <f t="shared" si="6"/>
-        <v>-5.9714285714285698</v>
+        <f>0.5*(M32-F32)</f>
+        <v>-5.8829323308270673</v>
       </c>
       <c r="P32" s="15">
-        <f t="shared" si="7"/>
-        <v>-5.9714285714285698</v>
+        <f>N32+O32</f>
+        <v>-2.5635323308270657</v>
       </c>
       <c r="Q32" s="12">
-        <f t="shared" si="8"/>
-        <v>109.5999386000819</v>
+        <f>MAX($P$2:$P$280)-P32</f>
+        <v>106.19204235948038</v>
       </c>
       <c r="R32" s="9">
-        <f t="shared" si="9"/>
-        <v>9.1240927027239471E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q32)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.4169014719088714E-3</v>
       </c>
       <c r="S32" s="9">
-        <f t="shared" si="10"/>
-        <v>0.33928814193297463</v>
+        <f>Q32/MAX($Q$2:$Q$28)</f>
+        <v>0.48011296664576736</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>76</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>79</v>
+        <v>39</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="C33" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="D33" s="8">
-        <v>45574</v>
+        <v>45507</v>
       </c>
       <c r="E33" s="2">
-        <v>0</v>
+        <v>9.9999999999999998E-46</v>
       </c>
       <c r="F33" s="1">
-        <v>153.7552</v>
+        <v>41.8</v>
       </c>
       <c r="G33" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>E33*F33</f>
+        <v>4.1799999999999994E-44</v>
       </c>
       <c r="H33" s="11">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="I33" s="11">
-        <v>0.19</v>
+        <v>0.4</v>
       </c>
       <c r="J33" s="9">
-        <f t="shared" si="1"/>
-        <v>0.36842105263157898</v>
+        <f>IFERROR(H33/I33,"")</f>
+        <v>0.17500000000000002</v>
       </c>
       <c r="K33" s="9">
-        <f t="shared" si="2"/>
-        <v>3.9626094271485252E-2</v>
+        <f>IFERROR(J33/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>1.1498245408417693E-2</v>
       </c>
       <c r="L33" s="12">
         <f>F33/(1-(F33*(1+H33)-F33)/(F33*(1+H33)))</f>
-        <v>164.51806400000001</v>
+        <v>44.725999999999999</v>
       </c>
       <c r="M33" s="12">
-        <f t="shared" si="4"/>
-        <v>137.28142857142859</v>
+        <f>F33/(1+I33-H33)</f>
+        <v>31.428571428571431</v>
       </c>
       <c r="N33" s="12">
-        <f t="shared" si="5"/>
-        <v>10.762864000000008</v>
+        <f>L33-F33</f>
+        <v>2.9260000000000019</v>
       </c>
       <c r="O33" s="12">
-        <f t="shared" si="6"/>
-        <v>-8.2368857142857053</v>
+        <f>0.5*(M33-F33)</f>
+        <v>-5.1857142857142833</v>
       </c>
       <c r="P33" s="15">
-        <f t="shared" si="7"/>
-        <v>2.5259782857143023</v>
+        <f>N33+O33</f>
+        <v>-2.2597142857142813</v>
       </c>
       <c r="Q33" s="12">
-        <f t="shared" si="8"/>
-        <v>101.10253174293902</v>
+        <f>MAX($P$2:$P$280)-P33</f>
+        <v>105.8882243143676</v>
       </c>
       <c r="R33" s="9">
-        <f t="shared" si="9"/>
-        <v>9.8909491459875324E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q33)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.4439207614922058E-3</v>
       </c>
       <c r="S33" s="9">
-        <f t="shared" si="10"/>
-        <v>0.31298274960672046</v>
+        <f>Q33/MAX($Q$2:$Q$28)</f>
+        <v>0.47873935163923209</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>87</v>
+        <v>76</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="C34" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D34" s="8">
-        <v>45623</v>
+        <v>45574</v>
       </c>
       <c r="E34" s="2">
-        <v>1.9595</v>
+        <v>0</v>
       </c>
       <c r="F34" s="1">
-        <v>15.3</v>
+        <v>153.7552</v>
       </c>
       <c r="G34" s="1">
-        <f t="shared" ref="G34:G35" si="11">E34*F34</f>
-        <v>29.980350000000001</v>
+        <f>E34*F34</f>
+        <v>0</v>
       </c>
       <c r="H34" s="11">
-        <v>0.35</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I34" s="11">
-        <v>0.39532299999999998</v>
+        <v>0.19</v>
       </c>
       <c r="J34" s="9">
-        <f t="shared" ref="J34:J35" si="12">IFERROR(H34/I34,"")</f>
-        <v>0.88535197800279775</v>
+        <f>IFERROR(H34/I34,"")</f>
+        <v>0.36842105263157898</v>
       </c>
       <c r="K34" s="9">
-        <f t="shared" ref="K34:K35" si="13">IFERROR(J34/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>9.5225396847415877E-2</v>
+        <f>IFERROR(J34/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>2.4206832438774088E-2</v>
       </c>
       <c r="L34" s="12">
-        <f t="shared" ref="L34" si="14">F34/(1-(F34*(1+H34)-F34)/(F34*(1+H34)))</f>
-        <v>20.655000000000001</v>
+        <f>F34/(1-(F34*(1+H34)-F34)/(F34*(1+H34)))</f>
+        <v>164.51806400000001</v>
       </c>
       <c r="M34" s="12">
-        <f t="shared" ref="M34:M35" si="15">F34/(1+I34-H34)</f>
-        <v>14.636624277854791</v>
+        <f>F34/(1+I34-H34)</f>
+        <v>137.28142857142859</v>
       </c>
       <c r="N34" s="12">
-        <f t="shared" ref="N34:N35" si="16">L34-F34</f>
-        <v>5.3550000000000004</v>
+        <f>L34-F34</f>
+        <v>10.762864000000008</v>
       </c>
       <c r="O34" s="12">
-        <f t="shared" ref="O34:O35" si="17">0.5*(M34-F34)</f>
-        <v>-0.33168786107260484</v>
+        <f>0.5*(M34-F34)</f>
+        <v>-8.2368857142857053</v>
       </c>
       <c r="P34" s="15">
-        <f t="shared" ref="P34:P35" si="18">N34+O34</f>
-        <v>5.0233121389273956</v>
+        <f>N34+O34</f>
+        <v>2.5259782857143023</v>
       </c>
       <c r="Q34" s="12">
-        <f t="shared" ref="Q34:Q35" si="19">MAX($P$2:$P$280)-P34</f>
-        <v>98.605197889725929</v>
+        <f>MAX($P$2:$P$280)-P34</f>
+        <v>101.10253174293902</v>
       </c>
       <c r="R34" s="9">
-        <f t="shared" ref="R34:R35" si="20">IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q34)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.0141453203291973E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q34)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.8909491459875307E-3</v>
       </c>
       <c r="S34" s="9">
-        <f t="shared" ref="S34:S35" si="21">Q34/MAX($Q$2:$Q$28)</f>
-        <v>0.30525176203806181</v>
+        <f>Q34/MAX($Q$2:$Q$28)</f>
+        <v>0.45710239083810988</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
@@ -3173,59 +3161,59 @@
         <v>133.53</v>
       </c>
       <c r="G35" s="1">
-        <f t="shared" si="11"/>
+        <f>E35*F35</f>
         <v>0</v>
       </c>
       <c r="H35" s="11">
-        <v>0.12</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I35" s="11">
         <v>0.2</v>
       </c>
       <c r="J35" s="9">
-        <f t="shared" si="12"/>
-        <v>0.6</v>
+        <f>IFERROR(H35/I35,"")</f>
+        <v>0.35000000000000003</v>
       </c>
       <c r="K35" s="9">
-        <f t="shared" si="13"/>
-        <v>6.4533924956418839E-2</v>
+        <f>IFERROR(J35/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>2.2996490816835385E-2</v>
       </c>
       <c r="L35" s="12">
         <f>F35/(1-(F35*(1+H35)-F35)/(F35*(1+H35)))</f>
-        <v>149.55360000000002</v>
+        <v>142.87710000000001</v>
       </c>
       <c r="M35" s="12">
-        <f t="shared" si="15"/>
-        <v>123.63888888888889</v>
+        <f>F35/(1+I35-H35)</f>
+        <v>118.16814159292036</v>
       </c>
       <c r="N35" s="12">
-        <f t="shared" si="16"/>
-        <v>16.023600000000016</v>
+        <f>L35-F35</f>
+        <v>9.3471000000000117</v>
       </c>
       <c r="O35" s="12">
-        <f t="shared" si="17"/>
-        <v>-4.9455555555555577</v>
+        <f>0.5*(M35-F35)</f>
+        <v>-7.6809292035398187</v>
       </c>
       <c r="P35" s="15">
-        <f t="shared" si="18"/>
-        <v>11.078044444444458</v>
+        <f>N35+O35</f>
+        <v>1.6661707964601931</v>
       </c>
       <c r="Q35" s="12">
-        <f t="shared" si="19"/>
-        <v>92.550465584208865</v>
+        <f>MAX($P$2:$P$280)-P35</f>
+        <v>101.96233923219313</v>
       </c>
       <c r="R35" s="9">
-        <f t="shared" si="20"/>
-        <v>1.0804915930867257E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q35)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.8075427410777224E-3</v>
       </c>
       <c r="S35" s="9">
-        <f t="shared" si="21"/>
-        <v>0.28650814867404023</v>
+        <f>Q35/MAX($Q$2:$Q$28)</f>
+        <v>0.46098973225501771</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>92</v>
@@ -3243,59 +3231,59 @@
         <v>39.56</v>
       </c>
       <c r="G36" s="1">
-        <f t="shared" ref="G36" si="22">E36*F36</f>
+        <f>E36*F36</f>
         <v>0</v>
       </c>
       <c r="H36" s="11">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I36" s="11">
         <v>0.2</v>
       </c>
       <c r="J36" s="9">
-        <f t="shared" ref="J36" si="23">IFERROR(H36/I36,"")</f>
-        <v>0.6</v>
+        <f>IFERROR(H36/I36,"")</f>
+        <v>0.5</v>
       </c>
       <c r="K36" s="9">
-        <f t="shared" ref="K36" si="24">IFERROR(J36/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>6.4533924956418839E-2</v>
+        <f>IFERROR(J36/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>3.2852129738336261E-2</v>
       </c>
       <c r="L36" s="12">
         <f>F36/(1-(F36*(1+H36)-F36)/(F36*(1+H36)))</f>
-        <v>44.307200000000009</v>
+        <v>43.516000000000005</v>
       </c>
       <c r="M36" s="12">
-        <f t="shared" ref="M36" si="25">F36/(1+I36-H36)</f>
-        <v>36.629629629629626</v>
+        <f>F36/(1+I36-H36)</f>
+        <v>35.963636363636368</v>
       </c>
       <c r="N36" s="12">
-        <f t="shared" ref="N36" si="26">L36-F36</f>
-        <v>4.7472000000000065</v>
+        <f>L36-F36</f>
+        <v>3.9560000000000031</v>
       </c>
       <c r="O36" s="12">
-        <f t="shared" ref="O36" si="27">0.5*(M36-F36)</f>
-        <v>-1.465185185185188</v>
+        <f>0.5*(M36-F36)</f>
+        <v>-1.798181818181817</v>
       </c>
       <c r="P36" s="15">
-        <f t="shared" ref="P36" si="28">N36+O36</f>
-        <v>3.2820148148148185</v>
+        <f>N36+O36</f>
+        <v>2.1578181818181861</v>
       </c>
       <c r="Q36" s="12">
-        <f t="shared" ref="Q36" si="29">MAX($P$2:$P$280)-P36</f>
-        <v>100.34649521383851</v>
+        <f>MAX($P$2:$P$280)-P36</f>
+        <v>101.47069184683514</v>
       </c>
       <c r="R36" s="9">
-        <f t="shared" ref="R36" si="30">IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q36)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.9654701229873414E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q36)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.8550624007713392E-3</v>
       </c>
       <c r="S36" s="9">
-        <f t="shared" ref="S36" si="31">Q36/MAX($Q$2:$Q$28)</f>
-        <v>0.31064229000000515</v>
+        <f>Q36/MAX($Q$2:$Q$28)</f>
+        <v>0.4587669076489253</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>95</v>
@@ -3313,59 +3301,59 @@
         <v>26.63</v>
       </c>
       <c r="G37" s="1">
-        <f t="shared" ref="G37" si="32">E37*F37</f>
+        <f>E37*F37</f>
         <v>0</v>
       </c>
       <c r="H37" s="11">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I37" s="11">
         <v>0.2</v>
       </c>
       <c r="J37" s="9">
-        <f t="shared" ref="J37" si="33">IFERROR(H37/I37,"")</f>
-        <v>0.6</v>
+        <f>IFERROR(H37/I37,"")</f>
+        <v>0.5</v>
       </c>
       <c r="K37" s="9">
-        <f t="shared" ref="K37" si="34">IFERROR(J37/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>6.4533924956418839E-2</v>
+        <f>IFERROR(J37/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>3.2852129738336261E-2</v>
       </c>
       <c r="L37" s="12">
         <f>F37/(1-(F37*(1+H37)-F37)/(F37*(1+H37)))</f>
-        <v>29.825600000000001</v>
+        <v>29.293000000000003</v>
       </c>
       <c r="M37" s="12">
-        <f t="shared" ref="M37" si="35">F37/(1+I37-H37)</f>
-        <v>24.657407407407405</v>
+        <f>F37/(1+I37-H37)</f>
+        <v>24.209090909090911</v>
       </c>
       <c r="N37" s="12">
-        <f t="shared" ref="N37" si="36">L37-F37</f>
-        <v>3.1956000000000024</v>
+        <f>L37-F37</f>
+        <v>2.6630000000000038</v>
       </c>
       <c r="O37" s="12">
-        <f t="shared" ref="O37" si="37">0.5*(M37-F37)</f>
-        <v>-0.98629629629629711</v>
+        <f>0.5*(M37-F37)</f>
+        <v>-1.2104545454545441</v>
       </c>
       <c r="P37" s="15">
-        <f t="shared" ref="P37" si="38">N37+O37</f>
-        <v>2.2093037037037053</v>
+        <f>N37+O37</f>
+        <v>1.4525454545454597</v>
       </c>
       <c r="Q37" s="12">
-        <f t="shared" ref="Q37" si="39">MAX($P$2:$P$280)-P37</f>
-        <v>101.41920632494961</v>
+        <f>MAX($P$2:$P$280)-P37</f>
+        <v>102.17596457410787</v>
       </c>
       <c r="R37" s="9">
-        <f t="shared" ref="R37" si="40">IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q37)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.8600653292037765E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q37)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.7870375304820682E-3</v>
       </c>
       <c r="S37" s="9">
-        <f t="shared" ref="S37" si="41">Q37/MAX($Q$2:$Q$28)</f>
-        <v>0.31396307798920092</v>
+        <f>Q37/MAX($Q$2:$Q$28)</f>
+        <v>0.46195557013117605</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>96</v>
@@ -3383,58 +3371,62 @@
         <v>22.65</v>
       </c>
       <c r="G38" s="1">
-        <f t="shared" ref="G38" si="42">E38*F38</f>
+        <f>E38*F38</f>
         <v>0</v>
       </c>
       <c r="H38" s="11">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I38" s="11">
         <v>0.2</v>
       </c>
       <c r="J38" s="9">
-        <f t="shared" ref="J38" si="43">IFERROR(H38/I38,"")</f>
-        <v>0.6</v>
+        <f>IFERROR(H38/I38,"")</f>
+        <v>0.5</v>
       </c>
       <c r="K38" s="9">
-        <f t="shared" ref="K38" si="44">IFERROR(J38/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>6.4533924956418839E-2</v>
+        <f>IFERROR(J38/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>3.2852129738336261E-2</v>
       </c>
       <c r="L38" s="12">
         <f>F38/(1-(F38*(1+H38)-F38)/(F38*(1+H38)))</f>
-        <v>25.368000000000002</v>
+        <v>24.914999999999999</v>
       </c>
       <c r="M38" s="12">
-        <f t="shared" ref="M38" si="45">F38/(1+I38-H38)</f>
-        <v>20.972222222222218</v>
+        <f>F38/(1+I38-H38)</f>
+        <v>20.590909090909093</v>
       </c>
       <c r="N38" s="12">
-        <f t="shared" ref="N38" si="46">L38-F38</f>
-        <v>2.7180000000000035</v>
+        <f>L38-F38</f>
+        <v>2.2650000000000006</v>
       </c>
       <c r="O38" s="12">
-        <f t="shared" ref="O38" si="47">0.5*(M38-F38)</f>
-        <v>-0.83888888888889035</v>
+        <f>0.5*(M38-F38)</f>
+        <v>-1.0295454545454525</v>
       </c>
       <c r="P38" s="15">
-        <f t="shared" ref="P38" si="48">N38+O38</f>
-        <v>1.8791111111111132</v>
+        <f>N38+O38</f>
+        <v>1.235454545454548</v>
       </c>
       <c r="Q38" s="12">
-        <f t="shared" ref="Q38" si="49">MAX($P$2:$P$280)-P38</f>
-        <v>101.74939891754221</v>
+        <f>MAX($P$2:$P$280)-P38</f>
+        <v>102.39305548319878</v>
       </c>
       <c r="R38" s="9">
-        <f t="shared" ref="R38" si="50">IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q38)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.8280678867734717E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q38)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.7662873256486194E-3</v>
       </c>
       <c r="S38" s="9">
-        <f t="shared" ref="S38" si="51">Q38/MAX($Q$2:$Q$28)</f>
-        <v>0.31498525402918537</v>
+        <f>Q38/MAX($Q$2:$Q$28)</f>
+        <v>0.46293707644821847</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S33" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:S33" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S38">
+      <sortCondition descending="1" ref="G1:G33"/>
+    </sortState>
+  </autoFilter>
   <conditionalFormatting sqref="R2:R38">
     <cfRule type="iconSet" priority="3">
       <iconSet iconSet="3Symbols">

--- a/Open Positions.xlsx
+++ b/Open Positions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\StockSillines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78192D40-48C9-45AA-91FF-EF1520505E3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7CB8625-6588-42E4-9EFB-844A8A74F10B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Open Positions.xlsx
+++ b/Open Positions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\StockSillines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7CB8625-6588-42E4-9EFB-844A8A74F10B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27F885E9-960E-415C-868D-BE949A6D127A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="105">
   <si>
     <t>Name</t>
   </si>
@@ -334,6 +334,27 @@
   </si>
   <si>
     <t>Expected Return QoQ%</t>
+  </si>
+  <si>
+    <t>Health</t>
+  </si>
+  <si>
+    <t>Agios</t>
+  </si>
+  <si>
+    <t>ACI</t>
+  </si>
+  <si>
+    <t>HCA</t>
+  </si>
+  <si>
+    <t>AGIO</t>
+  </si>
+  <si>
+    <t>Albertson Companies</t>
+  </si>
+  <si>
+    <t>HCA Healthcare</t>
   </si>
 </sst>
 </file>
@@ -742,7 +763,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S38"/>
+  <dimension ref="A1:S41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
@@ -827,354 +848,353 @@
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>21</v>
+        <v>37</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="D2" s="8">
-        <v>45484</v>
+        <v>45623</v>
       </c>
       <c r="E2" s="2">
-        <v>0.33389999999999997</v>
+        <v>1.9595</v>
       </c>
       <c r="F2" s="1">
-        <v>188.53</v>
+        <v>15.3</v>
       </c>
       <c r="G2" s="1">
         <f>E2*F2</f>
-        <v>62.950166999999993</v>
+        <v>29.980350000000001</v>
       </c>
       <c r="H2" s="11">
-        <f>227.4/F2-1</f>
-        <v>0.20617408370020684</v>
+        <v>0.35</v>
       </c>
       <c r="I2" s="11">
-        <v>0.37</v>
+        <v>0.39532299999999998</v>
       </c>
       <c r="J2" s="9">
         <f>IFERROR(H2/I2,"")</f>
-        <v>0.55722725324380229</v>
+        <v>0.88535197800279775</v>
       </c>
       <c r="K2" s="9">
         <f>IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.6612204034604294E-2</v>
+        <v>4.8593079231157639E-2</v>
       </c>
       <c r="L2" s="12">
         <f>F2/(1-(F2*(1+H2)-F2)/(F2*(1+H2)))</f>
-        <v>227.4</v>
+        <v>20.655000000000001</v>
       </c>
       <c r="M2" s="12">
         <f>F2/(1+I2-H2)</f>
-        <v>161.9915808365931</v>
+        <v>14.636624277854791</v>
       </c>
       <c r="N2" s="12">
         <f>L2-F2</f>
-        <v>38.870000000000005</v>
+        <v>5.3550000000000004</v>
       </c>
       <c r="O2" s="12">
         <f>0.5*(M2-F2)</f>
-        <v>-13.26920958170345</v>
+        <v>-0.33168786107260484</v>
       </c>
       <c r="P2" s="15">
         <f>N2+O2</f>
-        <v>25.600790418296555</v>
+        <v>5.0233121389273956</v>
       </c>
       <c r="Q2" s="12">
         <f>MAX($P$2:$P$280)-P2</f>
-        <v>78.027719610356769</v>
+        <v>98.605197889725929</v>
       </c>
       <c r="R2" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q2)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.2815958290126271E-2</v>
+        <v>1.0141453203291973E-2</v>
       </c>
       <c r="S2" s="9">
         <f>Q2/MAX($Q$2:$Q$28)</f>
-        <v>0.35277709242954441</v>
+        <v>0.44581150370259182</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>11</v>
+        <v>38</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D3" s="8">
-        <v>45574</v>
+        <v>45553</v>
       </c>
       <c r="E3" s="2">
-        <v>0.13370000000000001</v>
+        <v>1.0751999999999999</v>
       </c>
       <c r="F3" s="1">
-        <v>423.77</v>
+        <v>51.15</v>
       </c>
       <c r="G3" s="1">
         <f>E3*F3</f>
-        <v>56.658049000000005</v>
+        <v>54.996479999999998</v>
       </c>
       <c r="H3" s="11">
-        <v>0.15</v>
+        <f>16.68%+7%/4</f>
+        <v>0.18430000000000002</v>
       </c>
       <c r="I3" s="11">
-        <v>0.1963</v>
+        <v>0.19980000000000001</v>
       </c>
       <c r="J3" s="9">
         <f>IFERROR(H3/I3,"")</f>
-        <v>0.76413652572592972</v>
+        <v>0.92242242242242245</v>
       </c>
       <c r="K3" s="9">
         <f>IFERROR(J3/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>5.0207024561899537E-2</v>
+        <v>5.0627713012493539E-2</v>
       </c>
       <c r="L3" s="12">
         <f>F3/(1-(F3*(1+H3)-F3)/(F3*(1+H3)))</f>
-        <v>487.33549999999991</v>
+        <v>60.576944999999995</v>
       </c>
       <c r="M3" s="12">
         <f>F3/(1+I3-H3)</f>
-        <v>405.01768135334032</v>
+        <v>50.369276218611525</v>
       </c>
       <c r="N3" s="12">
         <f>L3-F3</f>
-        <v>63.565499999999929</v>
+        <v>9.4269449999999964</v>
       </c>
       <c r="O3" s="12">
         <f>0.5*(M3-F3)</f>
-        <v>-9.3761593233298299</v>
+        <v>-0.39036189069423699</v>
       </c>
       <c r="P3" s="15">
         <f>N3+O3</f>
-        <v>54.189340676670099</v>
+        <v>9.0365831093057594</v>
       </c>
       <c r="Q3" s="12">
         <f>MAX($P$2:$P$280)-P3</f>
-        <v>49.439169351983224</v>
+        <v>94.591926919347571</v>
       </c>
       <c r="R3" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q3)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>2.0226877051280505E-2</v>
+        <v>1.0571726706155752E-2</v>
       </c>
       <c r="S3" s="9">
         <f>Q3/MAX($Q$2:$Q$28)</f>
-        <v>0.22352321076687609</v>
+        <v>0.42766679729399837</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
+        <v>40</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>50</v>
       </c>
       <c r="D4" s="8">
-        <v>45553</v>
+        <v>45511</v>
       </c>
       <c r="E4" s="2">
-        <v>1.0751999999999999</v>
+        <v>1</v>
       </c>
       <c r="F4" s="1">
-        <v>51.15</v>
+        <v>10.92</v>
       </c>
       <c r="G4" s="1">
         <f>E4*F4</f>
-        <v>54.996479999999998</v>
+        <v>10.92</v>
       </c>
       <c r="H4" s="11">
-        <f>16.68%+7%/4</f>
-        <v>0.18430000000000002</v>
-      </c>
-      <c r="I4" s="11">
-        <v>0.19980000000000001</v>
+        <v>1</v>
+      </c>
+      <c r="I4" s="13">
+        <v>1.8652</v>
       </c>
       <c r="J4" s="9">
         <f>IFERROR(H4/I4,"")</f>
-        <v>0.92242242242242245</v>
+        <v>0.53613553506326406</v>
       </c>
       <c r="K4" s="9">
         <f>IFERROR(J4/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>6.0607082189943672E-2</v>
+        <v>2.9426123373822697E-2</v>
       </c>
       <c r="L4" s="12">
         <f>F4/(1-(F4*(1+H4)-F4)/(F4*(1+H4)))</f>
-        <v>60.576944999999995</v>
+        <v>21.84</v>
       </c>
       <c r="M4" s="12">
         <f>F4/(1+I4-H4)</f>
-        <v>50.369276218611525</v>
+        <v>5.8546000428908433</v>
       </c>
       <c r="N4" s="12">
         <f>L4-F4</f>
-        <v>9.4269449999999964</v>
+        <v>10.92</v>
       </c>
       <c r="O4" s="12">
         <f>0.5*(M4-F4)</f>
-        <v>-0.39036189069423699</v>
+        <v>-2.5326999785545783</v>
       </c>
       <c r="P4" s="15">
         <f>N4+O4</f>
-        <v>9.0365831093057594</v>
+        <v>8.3873000214454212</v>
       </c>
       <c r="Q4" s="12">
         <f>MAX($P$2:$P$280)-P4</f>
-        <v>94.591926919347571</v>
+        <v>95.241210007207897</v>
       </c>
       <c r="R4" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q4)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.0571726706155752E-2</v>
+        <v>1.0499656607935993E-2</v>
       </c>
       <c r="S4" s="9">
         <f>Q4/MAX($Q$2:$Q$28)</f>
-        <v>0.42766679729399837</v>
+        <v>0.43060232073416616</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>14</v>
+        <v>40</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D5" s="8">
-        <v>45482</v>
+        <v>45511</v>
       </c>
       <c r="E5" s="2">
-        <v>0.18820000000000001</v>
+        <v>0.45179999999999998</v>
       </c>
       <c r="F5" s="1">
-        <v>227.38</v>
+        <v>77.430000000000007</v>
       </c>
       <c r="G5" s="1">
         <f>E5*F5</f>
-        <v>42.792915999999998</v>
+        <v>34.982874000000002</v>
       </c>
       <c r="H5" s="11">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I5" s="11">
-        <v>0.2271</v>
+        <v>0.25990000000000002</v>
       </c>
       <c r="J5" s="9">
         <f>IFERROR(H5/I5,"")</f>
-        <v>0.66050198150594452</v>
+        <v>0.38476337052712584</v>
       </c>
       <c r="K5" s="9">
         <f>IFERROR(J5/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.3397793577722936E-2</v>
+        <v>2.1117970495134315E-2</v>
       </c>
       <c r="L5" s="12">
         <f>F5/(1-(F5*(1+H5)-F5)/(F5*(1+H5)))</f>
-        <v>261.48699999999997</v>
+        <v>85.173000000000016</v>
       </c>
       <c r="M5" s="12">
         <f>F5/(1+I5-H5)</f>
-        <v>211.10389007520189</v>
+        <v>66.755754806448849</v>
       </c>
       <c r="N5" s="12">
         <f>L5-F5</f>
-        <v>34.106999999999971</v>
+        <v>7.7430000000000092</v>
       </c>
       <c r="O5" s="12">
         <f>0.5*(M5-F5)</f>
-        <v>-8.1380549623990532</v>
+        <v>-5.3371225967755791</v>
       </c>
       <c r="P5" s="15">
         <f>N5+O5</f>
-        <v>25.968945037600918</v>
+        <v>2.4058774032244301</v>
       </c>
       <c r="Q5" s="12">
         <f>MAX($P$2:$P$280)-P5</f>
-        <v>77.659564991052406</v>
+        <v>101.2226326254289</v>
       </c>
       <c r="R5" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q5)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.2876713900151458E-2</v>
+        <v>9.8792135124608736E-3</v>
       </c>
       <c r="S5" s="9">
         <f>Q5/MAX($Q$2:$Q$28)</f>
-        <v>0.35111260041553638</v>
+        <v>0.45764538812592725</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>7</v>
+        <v>38</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D6" s="8">
-        <v>45511</v>
+        <v>45544</v>
       </c>
       <c r="E6" s="2">
-        <v>0.14610000000000001</v>
+        <v>0.35149999999999998</v>
       </c>
       <c r="F6" s="1">
-        <v>273.45999999999998</v>
+        <v>142.78</v>
       </c>
       <c r="G6" s="1">
         <f>E6*F6</f>
-        <v>39.952506</v>
+        <v>50.187169999999995</v>
       </c>
       <c r="H6" s="11">
-        <v>0.25</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I6" s="11">
-        <v>0.26</v>
+        <v>0.18340000000000001</v>
       </c>
       <c r="J6" s="9">
         <f>IFERROR(H6/I6,"")</f>
-        <v>0.96153846153846145</v>
+        <v>0.38167938931297712</v>
       </c>
       <c r="K6" s="9">
         <f>IFERROR(J6/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>6.3177172573723572E-2</v>
+        <v>2.0948704319409959E-2</v>
       </c>
       <c r="L6" s="12">
         <f>F6/(1-(F6*(1+H6)-F6)/(F6*(1+H6)))</f>
-        <v>341.82499999999999</v>
+        <v>152.77460000000002</v>
       </c>
       <c r="M6" s="12">
         <f>F6/(1+I6-H6)</f>
-        <v>270.75247524752473</v>
+        <v>128.23783007005568</v>
       </c>
       <c r="N6" s="12">
         <f>L6-F6</f>
-        <v>68.365000000000009</v>
+        <v>9.9946000000000197</v>
       </c>
       <c r="O6" s="12">
         <f>0.5*(M6-F6)</f>
-        <v>-1.3537623762376256</v>
+        <v>-7.2710849649721609</v>
       </c>
       <c r="P6" s="15">
         <f>N6+O6</f>
-        <v>67.011237623762383</v>
+        <v>2.7235150350278587</v>
       </c>
       <c r="Q6" s="12">
         <f>MAX($P$2:$P$280)-P6</f>
-        <v>36.61727240489094</v>
+        <v>100.90499499362546</v>
       </c>
       <c r="R6" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q6)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>2.7309516365463388E-2</v>
+        <v>9.9103121709997969E-3</v>
       </c>
       <c r="S6" s="9">
         <f>Q6/MAX($Q$2:$Q$28)</f>
-        <v>0.1655531515749106</v>
+        <v>0.45620929232877483</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
@@ -1182,69 +1202,70 @@
         <v>36</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D7" s="8">
-        <v>45544</v>
+        <v>45484</v>
       </c>
       <c r="E7" s="2">
-        <v>0.1928</v>
+        <v>0.33389999999999997</v>
       </c>
       <c r="F7" s="1">
-        <v>188.12</v>
+        <v>188.53</v>
       </c>
       <c r="G7" s="1">
         <f>E7*F7</f>
-        <v>36.269536000000002</v>
+        <v>62.950166999999993</v>
       </c>
       <c r="H7" s="11">
-        <v>0.15</v>
+        <f>227.4/F7-1</f>
+        <v>0.20617408370020684</v>
       </c>
       <c r="I7" s="11">
-        <v>0.37780000000000002</v>
+        <v>0.37</v>
       </c>
       <c r="J7" s="9">
         <f>IFERROR(H7/I7,"")</f>
-        <v>0.39703546850185278</v>
+        <v>0.55722725324380229</v>
       </c>
       <c r="K7" s="9">
         <f>IFERROR(J7/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.6086921443887974E-2</v>
+        <v>3.0583755093334032E-2</v>
       </c>
       <c r="L7" s="12">
         <f>F7/(1-(F7*(1+H7)-F7)/(F7*(1+H7)))</f>
-        <v>216.33799999999999</v>
+        <v>227.4</v>
       </c>
       <c r="M7" s="12">
         <f>F7/(1+I7-H7)</f>
-        <v>153.21713634142367</v>
+        <v>161.9915808365931</v>
       </c>
       <c r="N7" s="12">
         <f>L7-F7</f>
-        <v>28.217999999999989</v>
+        <v>38.870000000000005</v>
       </c>
       <c r="O7" s="12">
         <f>0.5*(M7-F7)</f>
-        <v>-17.451431829288168</v>
+        <v>-13.26920958170345</v>
       </c>
       <c r="P7" s="15">
         <f>N7+O7</f>
-        <v>10.766568170711821</v>
+        <v>25.600790418296555</v>
       </c>
       <c r="Q7" s="12">
         <f>MAX($P$2:$P$280)-P7</f>
-        <v>92.861941857941503</v>
+        <v>78.027719610356769</v>
       </c>
       <c r="R7" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q7)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.0768674227486882E-2</v>
+        <v>1.2815958290126271E-2</v>
       </c>
       <c r="S7" s="9">
         <f>Q7/MAX($Q$2:$Q$28)</f>
-        <v>0.41984522948505815</v>
+        <v>0.35277709242954441</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
@@ -1252,279 +1273,279 @@
         <v>38</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D8" s="8">
-        <v>45544</v>
+        <v>45460</v>
       </c>
       <c r="E8" s="2">
-        <v>0.35149999999999998</v>
+        <v>0.33529999999999999</v>
       </c>
       <c r="F8" s="1">
-        <v>142.78</v>
+        <v>163.15</v>
       </c>
       <c r="G8" s="1">
         <f>E8*F8</f>
-        <v>50.187169999999995</v>
+        <v>54.704194999999999</v>
       </c>
       <c r="H8" s="11">
-        <v>7.0000000000000007E-2</v>
+        <v>6.7199999999999996E-2</v>
       </c>
       <c r="I8" s="11">
-        <v>0.18340000000000001</v>
+        <v>0.16439999999999999</v>
       </c>
       <c r="J8" s="9">
         <f>IFERROR(H8/I8,"")</f>
-        <v>0.38167938931297712</v>
+        <v>0.40875912408759124</v>
       </c>
       <c r="K8" s="9">
         <f>IFERROR(J8/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.5077961632317756E-2</v>
+        <v>2.2434991954334519E-2</v>
       </c>
       <c r="L8" s="12">
         <f>F8/(1-(F8*(1+H8)-F8)/(F8*(1+H8)))</f>
-        <v>152.77460000000002</v>
+        <v>174.11367999999999</v>
       </c>
       <c r="M8" s="12">
         <f>F8/(1+I8-H8)</f>
-        <v>128.23783007005568</v>
+        <v>148.69668246445497</v>
       </c>
       <c r="N8" s="12">
         <f>L8-F8</f>
-        <v>9.9946000000000197</v>
+        <v>10.963679999999982</v>
       </c>
       <c r="O8" s="12">
         <f>0.5*(M8-F8)</f>
-        <v>-7.2710849649721609</v>
+        <v>-7.2266587677725198</v>
       </c>
       <c r="P8" s="15">
         <f>N8+O8</f>
-        <v>2.7235150350278587</v>
+        <v>3.7370212322274625</v>
       </c>
       <c r="Q8" s="12">
         <f>MAX($P$2:$P$280)-P8</f>
-        <v>100.90499499362546</v>
+        <v>99.891488796425861</v>
       </c>
       <c r="R8" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q8)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.9103121709997969E-3</v>
+        <v>1.0010862907829442E-2</v>
       </c>
       <c r="S8" s="9">
         <f>Q8/MAX($Q$2:$Q$28)</f>
-        <v>0.45620929232877483</v>
+        <v>0.45162705192507163</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>87</v>
+        <v>36</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>9</v>
       </c>
       <c r="D9" s="8">
-        <v>45623</v>
+        <v>45544</v>
       </c>
       <c r="E9" s="2">
-        <v>1.9595</v>
+        <v>0.1928</v>
       </c>
       <c r="F9" s="1">
-        <v>15.3</v>
+        <v>188.12</v>
       </c>
       <c r="G9" s="1">
         <f>E9*F9</f>
-        <v>29.980350000000001</v>
+        <v>36.269536000000002</v>
       </c>
       <c r="H9" s="11">
-        <v>0.35</v>
+        <v>0.15</v>
       </c>
       <c r="I9" s="11">
-        <v>0.39532299999999998</v>
+        <v>0.37780000000000002</v>
       </c>
       <c r="J9" s="9">
         <f>IFERROR(H9/I9,"")</f>
-        <v>0.88535197800279775</v>
+        <v>0.39703546850185278</v>
       </c>
       <c r="K9" s="9">
         <f>IFERROR(J9/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>5.8171396090881088E-2</v>
+        <v>2.1791532020984945E-2</v>
       </c>
       <c r="L9" s="12">
         <f>F9/(1-(F9*(1+H9)-F9)/(F9*(1+H9)))</f>
-        <v>20.655000000000001</v>
+        <v>216.33799999999999</v>
       </c>
       <c r="M9" s="12">
         <f>F9/(1+I9-H9)</f>
-        <v>14.636624277854791</v>
+        <v>153.21713634142367</v>
       </c>
       <c r="N9" s="12">
         <f>L9-F9</f>
-        <v>5.3550000000000004</v>
+        <v>28.217999999999989</v>
       </c>
       <c r="O9" s="12">
         <f>0.5*(M9-F9)</f>
-        <v>-0.33168786107260484</v>
+        <v>-17.451431829288168</v>
       </c>
       <c r="P9" s="15">
         <f>N9+O9</f>
-        <v>5.0233121389273956</v>
+        <v>10.766568170711821</v>
       </c>
       <c r="Q9" s="12">
         <f>MAX($P$2:$P$280)-P9</f>
-        <v>98.605197889725929</v>
+        <v>92.861941857941503</v>
       </c>
       <c r="R9" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q9)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.0141453203291975E-2</v>
+        <v>1.0768674227486882E-2</v>
       </c>
       <c r="S9" s="9">
         <f>Q9/MAX($Q$2:$Q$28)</f>
-        <v>0.44581150370259182</v>
+        <v>0.41984522948505815</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>15</v>
+        <v>39</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="D10" s="8">
-        <v>45460</v>
+        <v>45580</v>
       </c>
       <c r="E10" s="2">
-        <v>0.2727</v>
+        <v>0.19139999999999999</v>
       </c>
       <c r="F10" s="1">
-        <v>164.91</v>
+        <v>135.82</v>
       </c>
       <c r="G10" s="1">
         <f>E10*F10</f>
-        <v>44.970956999999999</v>
+        <v>25.995947999999999</v>
       </c>
       <c r="H10" s="11">
-        <v>6.7199999999999996E-2</v>
+        <v>0.1202</v>
       </c>
       <c r="I10" s="11">
-        <v>0.16439999999999999</v>
+        <v>0.33710000000000001</v>
       </c>
       <c r="J10" s="9">
         <f>IFERROR(H10/I10,"")</f>
-        <v>0.40875912408759124</v>
+        <v>0.35657075051913378</v>
       </c>
       <c r="K10" s="9">
         <f>IFERROR(J10/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.6857215552508477E-2</v>
+        <v>1.9570601480527621E-2</v>
       </c>
       <c r="L10" s="12">
         <f>F10/(1-(F10*(1+H10)-F10)/(F10*(1+H10)))</f>
-        <v>175.991952</v>
+        <v>152.14556400000001</v>
       </c>
       <c r="M10" s="12">
         <f>F10/(1+I10-H10)</f>
-        <v>150.30076558512576</v>
+        <v>111.61147177253677</v>
       </c>
       <c r="N10" s="12">
         <f>L10-F10</f>
-        <v>11.081952000000001</v>
+        <v>16.325564000000014</v>
       </c>
       <c r="O10" s="12">
         <f>0.5*(M10-F10)</f>
-        <v>-7.3046172074371185</v>
+        <v>-12.10426411373161</v>
       </c>
       <c r="P10" s="15">
         <f>N10+O10</f>
-        <v>3.7773347925628826</v>
+        <v>4.2212998862684046</v>
       </c>
       <c r="Q10" s="12">
         <f>MAX($P$2:$P$280)-P10</f>
-        <v>99.851175236090441</v>
+        <v>99.407210142384912</v>
       </c>
       <c r="R10" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q10)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.0014904658213353E-2</v>
+        <v>1.0059632481061082E-2</v>
       </c>
       <c r="S10" s="9">
         <f>Q10/MAX($Q$2:$Q$28)</f>
-        <v>0.45144478720335951</v>
+        <v>0.44943754265386154</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>33</v>
+        <v>36</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D11" s="8">
-        <v>45562</v>
+        <v>45482</v>
       </c>
       <c r="E11" s="2">
-        <v>4.0300000000000002E-2</v>
+        <v>0.18820000000000001</v>
       </c>
       <c r="F11" s="1">
-        <v>668.82</v>
+        <v>227.38</v>
       </c>
       <c r="G11" s="1">
         <f>E11*F11</f>
-        <v>26.953446000000003</v>
+        <v>42.792915999999998</v>
       </c>
       <c r="H11" s="11">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="I11" s="11">
-        <v>0.28000000000000003</v>
+        <v>0.2271</v>
       </c>
       <c r="J11" s="9">
         <f>IFERROR(H11/I11,"")</f>
-        <v>0.17857142857142858</v>
+        <v>0.66050198150594452</v>
       </c>
       <c r="K11" s="9">
         <f>IFERROR(J11/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.1732903477977237E-2</v>
+        <v>3.6252051067935331E-2</v>
       </c>
       <c r="L11" s="12">
         <f>F11/(1-(F11*(1+H11)-F11)/(F11*(1+H11)))</f>
-        <v>702.26100000000008</v>
+        <v>261.48699999999997</v>
       </c>
       <c r="M11" s="12">
         <f>F11/(1+I11-H11)</f>
-        <v>543.7560975609756</v>
+        <v>211.10389007520189</v>
       </c>
       <c r="N11" s="12">
         <f>L11-F11</f>
-        <v>33.441000000000031</v>
+        <v>34.106999999999971</v>
       </c>
       <c r="O11" s="12">
         <f>0.5*(M11-F11)</f>
-        <v>-62.531951219512223</v>
+        <v>-8.1380549623990532</v>
       </c>
       <c r="P11" s="15">
         <f>N11+O11</f>
-        <v>-29.090951219512192</v>
+        <v>25.968945037600918</v>
       </c>
       <c r="Q11" s="12">
         <f>MAX($P$2:$P$280)-P11</f>
-        <v>132.71946124816552</v>
+        <v>77.659564991052406</v>
       </c>
       <c r="R11" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q11)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>7.5346900190481469E-3</v>
+        <v>1.2876713900151457E-2</v>
       </c>
       <c r="S11" s="9">
         <f>Q11/MAX($Q$2:$Q$28)</f>
-        <v>0.60004810959166965</v>
+        <v>0.35111260041553638</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
@@ -1532,139 +1553,139 @@
         <v>39</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D12" s="8">
         <v>45580</v>
       </c>
       <c r="E12" s="2">
-        <v>0.19139999999999999</v>
+        <v>0.18010000000000001</v>
       </c>
       <c r="F12" s="1">
-        <v>135.82</v>
+        <v>133.19999999999999</v>
       </c>
       <c r="G12" s="1">
         <f>E12*F12</f>
-        <v>25.995947999999999</v>
+        <v>23.989319999999999</v>
       </c>
       <c r="H12" s="11">
-        <v>0.1202</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I12" s="11">
-        <v>0.33710000000000001</v>
+        <v>0.1623</v>
       </c>
       <c r="J12" s="9">
         <f>IFERROR(H12/I12,"")</f>
-        <v>0.35657075051913378</v>
+        <v>0.43130006161429457</v>
       </c>
       <c r="K12" s="9">
         <f>IFERROR(J12/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.3428217113901029E-2</v>
+        <v>2.3672164954897022E-2</v>
       </c>
       <c r="L12" s="12">
         <f>F12/(1-(F12*(1+H12)-F12)/(F12*(1+H12)))</f>
-        <v>152.14556400000001</v>
+        <v>142.524</v>
       </c>
       <c r="M12" s="12">
         <f>F12/(1+I12-H12)</f>
-        <v>111.61147177253677</v>
+        <v>121.94452073606151</v>
       </c>
       <c r="N12" s="12">
         <f>L12-F12</f>
-        <v>16.325564000000014</v>
+        <v>9.3240000000000123</v>
       </c>
       <c r="O12" s="12">
         <f>0.5*(M12-F12)</f>
-        <v>-12.10426411373161</v>
+        <v>-5.6277396319692414</v>
       </c>
       <c r="P12" s="15">
         <f>N12+O12</f>
-        <v>4.2212998862684046</v>
+        <v>3.6962603680307708</v>
       </c>
       <c r="Q12" s="12">
         <f>MAX($P$2:$P$280)-P12</f>
-        <v>99.407210142384912</v>
+        <v>99.932249660622546</v>
       </c>
       <c r="R12" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q12)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.0059632481061084E-2</v>
+        <v>1.0006779627158154E-2</v>
       </c>
       <c r="S12" s="9">
         <f>Q12/MAX($Q$2:$Q$28)</f>
-        <v>0.44943754265386154</v>
+        <v>0.45181133898649067</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>60</v>
+        <v>37</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="D13" s="8">
-        <v>45580</v>
+        <v>45511</v>
       </c>
       <c r="E13" s="2">
-        <v>0.18010000000000001</v>
+        <v>0.14610000000000001</v>
       </c>
       <c r="F13" s="1">
-        <v>133.19999999999999</v>
+        <v>273.45999999999998</v>
       </c>
       <c r="G13" s="1">
         <f>E13*F13</f>
-        <v>23.989319999999999</v>
+        <v>39.952506</v>
       </c>
       <c r="H13" s="11">
-        <v>7.0000000000000007E-2</v>
+        <v>0.25</v>
       </c>
       <c r="I13" s="11">
-        <v>0.1623</v>
+        <v>0.26</v>
       </c>
       <c r="J13" s="9">
         <f>IFERROR(H13/I13,"")</f>
-        <v>0.43130006161429457</v>
+        <v>0.96153846153846145</v>
       </c>
       <c r="K13" s="9">
         <f>IFERROR(J13/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.8338251160610457E-2</v>
+        <v>5.277462049697508E-2</v>
       </c>
       <c r="L13" s="12">
         <f>F13/(1-(F13*(1+H13)-F13)/(F13*(1+H13)))</f>
-        <v>142.524</v>
+        <v>341.82499999999999</v>
       </c>
       <c r="M13" s="12">
         <f>F13/(1+I13-H13)</f>
-        <v>121.94452073606151</v>
+        <v>270.75247524752473</v>
       </c>
       <c r="N13" s="12">
         <f>L13-F13</f>
-        <v>9.3240000000000123</v>
+        <v>68.365000000000009</v>
       </c>
       <c r="O13" s="12">
         <f>0.5*(M13-F13)</f>
-        <v>-5.6277396319692414</v>
+        <v>-1.3537623762376256</v>
       </c>
       <c r="P13" s="15">
         <f>N13+O13</f>
-        <v>3.6962603680307708</v>
+        <v>67.011237623762383</v>
       </c>
       <c r="Q13" s="12">
         <f>MAX($P$2:$P$280)-P13</f>
-        <v>99.932249660622546</v>
+        <v>36.61727240489094</v>
       </c>
       <c r="R13" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q13)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.0006779627158154E-2</v>
+        <v>2.7309516365463388E-2</v>
       </c>
       <c r="S13" s="9">
         <f>Q13/MAX($Q$2:$Q$28)</f>
-        <v>0.45181133898649067</v>
+        <v>0.1655531515749106</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
@@ -1672,70 +1693,69 @@
         <v>36</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D14" s="8">
-        <v>45483</v>
+        <v>45574</v>
       </c>
       <c r="E14" s="2">
-        <v>0.1195</v>
+        <v>0.13370000000000001</v>
       </c>
       <c r="F14" s="1">
-        <v>167.24</v>
+        <v>423.77</v>
       </c>
       <c r="G14" s="1">
         <f>E14*F14</f>
-        <v>19.98518</v>
+        <v>56.658049000000005</v>
       </c>
       <c r="H14" s="11">
-        <f>190.41/F14-1</f>
-        <v>0.13854341066730447</v>
+        <v>0.15</v>
       </c>
       <c r="I14" s="11">
-        <v>0.26790000000000003</v>
+        <v>0.1963</v>
       </c>
       <c r="J14" s="9">
         <f>IFERROR(H14/I14,"")</f>
-        <v>0.51714598979956872</v>
+        <v>0.76413652572592972</v>
       </c>
       <c r="K14" s="9">
         <f>IFERROR(J14/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.3978694301111501E-2</v>
+        <v>4.1940095759185496E-2</v>
       </c>
       <c r="L14" s="12">
         <f>F14/(1-(F14*(1+H14)-F14)/(F14*(1+H14)))</f>
-        <v>190.41</v>
+        <v>487.33549999999991</v>
       </c>
       <c r="M14" s="12">
         <f>F14/(1+I14-H14)</f>
-        <v>148.08431772538498</v>
+        <v>405.01768135334032</v>
       </c>
       <c r="N14" s="12">
         <f>L14-F14</f>
-        <v>23.169999999999987</v>
+        <v>63.565499999999929</v>
       </c>
       <c r="O14" s="12">
         <f>0.5*(M14-F14)</f>
-        <v>-9.5778411373075159</v>
+        <v>-9.3761593233298299</v>
       </c>
       <c r="P14" s="15">
         <f>N14+O14</f>
-        <v>13.592158862692472</v>
+        <v>54.189340676670099</v>
       </c>
       <c r="Q14" s="12">
         <f>MAX($P$2:$P$280)-P14</f>
-        <v>90.036351165960852</v>
+        <v>49.439169351983224</v>
       </c>
       <c r="R14" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q14)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.1106625124742505E-2</v>
+        <v>2.0226877051280505E-2</v>
       </c>
       <c r="S14" s="9">
         <f>Q14/MAX($Q$2:$Q$28)</f>
-        <v>0.40707023524338853</v>
+        <v>0.22352321076687609</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
@@ -1743,139 +1763,140 @@
         <v>36</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="D15" s="8">
-        <v>45481</v>
+        <v>45483</v>
       </c>
       <c r="E15" s="2">
-        <v>2.8500000000000001E-2</v>
+        <v>0.1195</v>
       </c>
       <c r="F15" s="1">
-        <v>700.32</v>
+        <v>167.24</v>
       </c>
       <c r="G15" s="1">
         <f>E15*F15</f>
-        <v>19.959120000000002</v>
+        <v>19.98518</v>
       </c>
       <c r="H15" s="11">
-        <v>0.1</v>
+        <f>190.41/F15-1</f>
+        <v>0.13854341066730447</v>
       </c>
       <c r="I15" s="11">
-        <v>0.45340000000000003</v>
+        <v>0.26790000000000003</v>
       </c>
       <c r="J15" s="9">
         <f>IFERROR(H15/I15,"")</f>
-        <v>0.22055580061755625</v>
+        <v>0.51714598979956872</v>
       </c>
       <c r="K15" s="9">
         <f>IFERROR(J15/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.4491455552861165E-2</v>
+        <v>2.8383870687332977E-2</v>
       </c>
       <c r="L15" s="12">
         <f>F15/(1-(F15*(1+H15)-F15)/(F15*(1+H15)))</f>
-        <v>770.35200000000009</v>
+        <v>190.41</v>
       </c>
       <c r="M15" s="12">
         <f>F15/(1+I15-H15)</f>
-        <v>517.45234224915032</v>
+        <v>148.08431772538498</v>
       </c>
       <c r="N15" s="12">
         <f>L15-F15</f>
-        <v>70.032000000000039</v>
+        <v>23.169999999999987</v>
       </c>
       <c r="O15" s="12">
         <f>0.5*(M15-F15)</f>
-        <v>-91.433828875424865</v>
+        <v>-9.5778411373075159</v>
       </c>
       <c r="P15" s="15">
         <f>N15+O15</f>
-        <v>-21.401828875424826</v>
+        <v>13.592158862692472</v>
       </c>
       <c r="Q15" s="12">
         <f>MAX($P$2:$P$280)-P15</f>
-        <v>125.03033890407815</v>
+        <v>90.036351165960852</v>
       </c>
       <c r="R15" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q15)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>7.9980587812945834E-3</v>
+        <v>1.1106625124742506E-2</v>
       </c>
       <c r="S15" s="9">
         <f>Q15/MAX($Q$2:$Q$28)</f>
-        <v>0.565284230326356</v>
+        <v>0.40707023524338853</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>26</v>
+        <v>39</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D16" s="8">
-        <v>45511</v>
+        <v>45562</v>
       </c>
       <c r="E16" s="2">
-        <v>0.45179999999999998</v>
+        <v>4.0300000000000002E-2</v>
       </c>
       <c r="F16" s="1">
-        <v>77.430000000000007</v>
+        <v>668.82</v>
       </c>
       <c r="G16" s="1">
         <f>E16*F16</f>
-        <v>34.982874000000002</v>
+        <v>26.953446000000003</v>
       </c>
       <c r="H16" s="11">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="I16" s="11">
-        <v>0.25990000000000002</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="J16" s="9">
         <f>IFERROR(H16/I16,"")</f>
-        <v>0.38476337052712584</v>
+        <v>0.17857142857142858</v>
       </c>
       <c r="K16" s="9">
         <f>IFERROR(J16/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.5280592334233368E-2</v>
+        <v>9.8010009494382301E-3</v>
       </c>
       <c r="L16" s="12">
         <f>F16/(1-(F16*(1+H16)-F16)/(F16*(1+H16)))</f>
-        <v>85.173000000000016</v>
+        <v>702.26100000000008</v>
       </c>
       <c r="M16" s="12">
         <f>F16/(1+I16-H16)</f>
-        <v>66.755754806448849</v>
+        <v>543.7560975609756</v>
       </c>
       <c r="N16" s="12">
         <f>L16-F16</f>
-        <v>7.7430000000000092</v>
+        <v>33.441000000000031</v>
       </c>
       <c r="O16" s="12">
         <f>0.5*(M16-F16)</f>
-        <v>-5.3371225967755791</v>
+        <v>-62.531951219512223</v>
       </c>
       <c r="P16" s="15">
         <f>N16+O16</f>
-        <v>2.4058774032244301</v>
+        <v>-29.090951219512192</v>
       </c>
       <c r="Q16" s="12">
         <f>MAX($P$2:$P$280)-P16</f>
-        <v>101.2226326254289</v>
+        <v>132.71946124816552</v>
       </c>
       <c r="R16" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q16)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.8792135124608719E-3</v>
+        <v>7.5346900190481469E-3</v>
       </c>
       <c r="S16" s="9">
         <f>Q16/MAX($Q$2:$Q$28)</f>
-        <v>0.45764538812592725</v>
+        <v>0.60004810959166965</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
@@ -1913,7 +1934,7 @@
       </c>
       <c r="K17" s="9">
         <f>IFERROR(J17/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>5.5306615721104818E-2</v>
+        <v>4.6200004475466405E-2</v>
       </c>
       <c r="L17" s="12">
         <f>F17/(1-(F17*(1+H17)-F17)/(F17*(1+H17)))</f>
@@ -1950,72 +1971,72 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>50</v>
+        <v>36</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" t="s">
+        <v>62</v>
       </c>
       <c r="D18" s="8">
-        <v>45511</v>
+        <v>45481</v>
       </c>
       <c r="E18" s="2">
-        <v>1</v>
+        <v>2.8500000000000001E-2</v>
       </c>
       <c r="F18" s="1">
-        <v>10.92</v>
+        <v>700.32</v>
       </c>
       <c r="G18" s="1">
         <f>E18*F18</f>
-        <v>10.92</v>
+        <v>19.959120000000002</v>
       </c>
       <c r="H18" s="11">
-        <v>1</v>
-      </c>
-      <c r="I18" s="13">
-        <v>1.8652</v>
+        <v>0.1</v>
+      </c>
+      <c r="I18" s="11">
+        <v>0.45340000000000003</v>
       </c>
       <c r="J18" s="9">
         <f>IFERROR(H18/I18,"")</f>
-        <v>0.53613553506326406</v>
+        <v>0.22055580061755625</v>
       </c>
       <c r="K18" s="9">
         <f>IFERROR(J18/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.5226388310461362E-2</v>
+        <v>1.2105338623037955E-2</v>
       </c>
       <c r="L18" s="12">
         <f>F18/(1-(F18*(1+H18)-F18)/(F18*(1+H18)))</f>
-        <v>21.84</v>
+        <v>770.35200000000009</v>
       </c>
       <c r="M18" s="12">
         <f>F18/(1+I18-H18)</f>
-        <v>5.8546000428908433</v>
+        <v>517.45234224915032</v>
       </c>
       <c r="N18" s="12">
         <f>L18-F18</f>
-        <v>10.92</v>
+        <v>70.032000000000039</v>
       </c>
       <c r="O18" s="12">
         <f>0.5*(M18-F18)</f>
-        <v>-2.5326999785545783</v>
+        <v>-91.433828875424865</v>
       </c>
       <c r="P18" s="15">
         <f>N18+O18</f>
-        <v>8.3873000214454212</v>
+        <v>-21.401828875424826</v>
       </c>
       <c r="Q18" s="12">
         <f>MAX($P$2:$P$280)-P18</f>
-        <v>95.241210007207897</v>
+        <v>125.03033890407815</v>
       </c>
       <c r="R18" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q18)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.0499656607935993E-2</v>
+        <v>7.9980587812945834E-3</v>
       </c>
       <c r="S18" s="9">
         <f>Q18/MAX($Q$2:$Q$28)</f>
-        <v>0.43060232073416616</v>
+        <v>0.565284230326356</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
@@ -2053,7 +2074,7 @@
       </c>
       <c r="K19" s="9">
         <f>IFERROR(J19/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.8815652771097514E-2</v>
+        <v>1.5717527295777228E-2</v>
       </c>
       <c r="L19" s="12">
         <f>F19/(1-(F19*(1+H19)-F19)/(F19*(1+H19)))</f>
@@ -2124,7 +2145,7 @@
       </c>
       <c r="K20" s="9">
         <f>IFERROR(J20/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>5.7322165046489537E-3</v>
+        <v>4.7883679866541976E-3</v>
       </c>
       <c r="L20" s="12">
         <f>F20/(1-(F20*(1+H20)-F20)/(F20*(1+H20)))</f>
@@ -2194,7 +2215,7 @@
       </c>
       <c r="K21" s="9">
         <f>IFERROR(J21/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.5427156486657085E-2</v>
+        <v>1.2886970020393072E-2</v>
       </c>
       <c r="L21" s="12">
         <f>F21/(1-(F21*(1+H21)-F21)/(F21*(1+H21)))</f>
@@ -2265,7 +2286,7 @@
       </c>
       <c r="K22" s="9">
         <f>IFERROR(J22/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.6637025524867311E-2</v>
+        <v>2.2251057715548812E-2</v>
       </c>
       <c r="L22" s="12">
         <f>F22/(1-(F22*(1+H22)-F22)/(F22*(1+H22)))</f>
@@ -2335,7 +2356,7 @@
       </c>
       <c r="K23" s="9">
         <f>IFERROR(J23/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.4644337179050337E-2</v>
+        <v>1.2233047247441474E-2</v>
       </c>
       <c r="L23" s="12">
         <f>F23/(1-(F23*(1+H23)-F23)/(F23*(1+H23)))</f>
@@ -2405,7 +2426,7 @@
       </c>
       <c r="K24" s="9">
         <f>IFERROR(J24/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.4460860384810206E-3</v>
+        <v>3.7140076679424883E-3</v>
       </c>
       <c r="L24" s="12">
         <f>F24/(1-(F24*(1+H24)-F24)/(F24*(1+H24)))</f>
@@ -2476,7 +2497,7 @@
       </c>
       <c r="K25" s="9">
         <f>IFERROR(J25/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.1360397014526166E-2</v>
+        <v>9.4898302141800187E-3</v>
       </c>
       <c r="L25" s="12">
         <f>F25/(1-(F25*(1+H25)-F25)/(F25*(1+H25)))</f>
@@ -2546,7 +2567,7 @@
       </c>
       <c r="K26" s="9">
         <f>IFERROR(J26/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.5520479061017406E-3</v>
+        <v>3.8025221918286051E-3</v>
       </c>
       <c r="L26" s="12">
         <f>F26/(1-(F26*(1+H26)-F26)/(F26*(1+H26)))</f>
@@ -2616,7 +2637,7 @@
       </c>
       <c r="K27" s="9">
         <f>IFERROR(J27/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.837865623637414E-3</v>
+        <v>3.2059348900031598E-3</v>
       </c>
       <c r="L27" s="12">
         <f>F27/(1-(F27*(1+H27)-F27)/(F27*(1+H27)))</f>
@@ -2663,7 +2684,7 @@
       </c>
       <c r="D28" s="8">
         <f ca="1">TODAY()-20</f>
-        <v>45608</v>
+        <v>45610</v>
       </c>
       <c r="E28" s="2">
         <v>1E-35</v>
@@ -2687,7 +2708,7 @@
       </c>
       <c r="K28" s="9">
         <f>IFERROR(J28/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.3140851895334505E-2</v>
+        <v>1.0977121063370818E-2</v>
       </c>
       <c r="L28" s="12">
         <f>F28/(1-(F28*(1+H28)-F28)/(F28*(1+H28)))</f>
@@ -2757,7 +2778,7 @@
       </c>
       <c r="K29" s="9">
         <f>IFERROR(J29/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.6662598048504797E-2</v>
+        <v>2.2272419548868331E-2</v>
       </c>
       <c r="L29" s="12">
         <f>F29/(1-(F29*(1+H29)-F29)/(F29*(1+H29)))</f>
@@ -2827,7 +2848,7 @@
       </c>
       <c r="K30" s="9">
         <f>IFERROR(J30/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.4206832438774088E-2</v>
+        <v>2.0221012485156772E-2</v>
       </c>
       <c r="L30" s="12">
         <f>F30/(1-(F30*(1+H30)-F30)/(F30*(1+H30)))</f>
@@ -2855,7 +2876,7 @@
       </c>
       <c r="R30" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q30)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.7362915665023548E-3</v>
+        <v>9.7362915665023565E-3</v>
       </c>
       <c r="S30" s="9">
         <f>Q30/MAX($Q$2:$Q$28)</f>
@@ -2897,7 +2918,7 @@
       </c>
       <c r="K31" s="9">
         <f>IFERROR(J31/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.3802839651115019E-2</v>
+        <v>3.6590403544569397E-2</v>
       </c>
       <c r="L31" s="12">
         <v>21.2</v>
@@ -2966,7 +2987,7 @@
       </c>
       <c r="K32" s="9">
         <f>IFERROR(J32/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.1498245408417693E-2</v>
+        <v>9.6049809304494665E-3</v>
       </c>
       <c r="L32" s="12">
         <f>F32/(1-(F32*(1+H32)-F32)/(F32*(1+H32)))</f>
@@ -3036,7 +3057,7 @@
       </c>
       <c r="K33" s="9">
         <f>IFERROR(J33/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.1498245408417693E-2</v>
+        <v>9.6049809304494665E-3</v>
       </c>
       <c r="L33" s="12">
         <f>F33/(1-(F33*(1+H33)-F33)/(F33*(1+H33)))</f>
@@ -3106,7 +3127,7 @@
       </c>
       <c r="K34" s="9">
         <f>IFERROR(J34/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.4206832438774088E-2</v>
+        <v>2.0221012485156772E-2</v>
       </c>
       <c r="L34" s="12">
         <f>F34/(1-(F34*(1+H34)-F34)/(F34*(1+H34)))</f>
@@ -3134,7 +3155,7 @@
       </c>
       <c r="R34" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q34)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.8909491459875307E-3</v>
+        <v>9.8909491459875324E-3</v>
       </c>
       <c r="S34" s="9">
         <f>Q34/MAX($Q$2:$Q$28)</f>
@@ -3176,7 +3197,7 @@
       </c>
       <c r="K35" s="9">
         <f>IFERROR(J35/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.2996490816835385E-2</v>
+        <v>1.9209961860898933E-2</v>
       </c>
       <c r="L35" s="12">
         <f>F35/(1-(F35*(1+H35)-F35)/(F35*(1+H35)))</f>
@@ -3246,7 +3267,7 @@
       </c>
       <c r="K36" s="9">
         <f>IFERROR(J36/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.2852129738336261E-2</v>
+        <v>2.7442802658427044E-2</v>
       </c>
       <c r="L36" s="12">
         <f>F36/(1-(F36*(1+H36)-F36)/(F36*(1+H36)))</f>
@@ -3274,7 +3295,7 @@
       </c>
       <c r="R36" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q36)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.8550624007713392E-3</v>
+        <v>9.855062400771341E-3</v>
       </c>
       <c r="S36" s="9">
         <f>Q36/MAX($Q$2:$Q$28)</f>
@@ -3316,7 +3337,7 @@
       </c>
       <c r="K37" s="9">
         <f>IFERROR(J37/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.2852129738336261E-2</v>
+        <v>2.7442802658427044E-2</v>
       </c>
       <c r="L37" s="12">
         <f>F37/(1-(F37*(1+H37)-F37)/(F37*(1+H37)))</f>
@@ -3386,7 +3407,7 @@
       </c>
       <c r="K38" s="9">
         <f>IFERROR(J38/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.2852129738336261E-2</v>
+        <v>2.7442802658427044E-2</v>
       </c>
       <c r="L38" s="12">
         <f>F38/(1-(F38*(1+H38)-F38)/(F38*(1+H38)))</f>
@@ -3414,20 +3435,230 @@
       </c>
       <c r="R38" s="9">
         <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q38)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.7662873256486194E-3</v>
+        <v>9.7662873256486177E-3</v>
       </c>
       <c r="S38" s="9">
         <f>Q38/MAX($Q$2:$Q$28)</f>
         <v>0.46293707644821847</v>
       </c>
     </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>98</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C39" t="s">
+        <v>102</v>
+      </c>
+      <c r="D39" s="8">
+        <v>45630</v>
+      </c>
+      <c r="E39" s="2">
+        <v>0</v>
+      </c>
+      <c r="F39" s="1">
+        <v>59.17</v>
+      </c>
+      <c r="G39" s="1">
+        <f>E39*F39</f>
+        <v>0</v>
+      </c>
+      <c r="H39" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="I39" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="J39" s="9">
+        <f>IFERROR(H39/I39,"")</f>
+        <v>1</v>
+      </c>
+      <c r="K39" s="9">
+        <f>IFERROR(J39/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>5.4885605316854089E-2</v>
+      </c>
+      <c r="L39" s="12">
+        <f>F39/(1-(F39*(1+H39)-F39)/(F39*(1+H39)))</f>
+        <v>71.004000000000005</v>
+      </c>
+      <c r="M39" s="12">
+        <f>F39/(1+I39-H39)</f>
+        <v>59.17</v>
+      </c>
+      <c r="N39" s="12">
+        <f>L39-F39</f>
+        <v>11.834000000000003</v>
+      </c>
+      <c r="O39" s="12">
+        <f>0.5*(M39-F39)</f>
+        <v>0</v>
+      </c>
+      <c r="P39" s="15">
+        <f>N39+O39</f>
+        <v>11.834000000000003</v>
+      </c>
+      <c r="Q39" s="12">
+        <f>MAX($P$2:$P$280)-P39</f>
+        <v>91.79451002865332</v>
+      </c>
+      <c r="R39" s="9">
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q39)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.0893897681766084E-2</v>
+      </c>
+      <c r="S39" s="9">
+        <f>Q39/MAX($Q$2:$Q$28)</f>
+        <v>0.41501918178068498</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C40" t="s">
+        <v>100</v>
+      </c>
+      <c r="D40" s="8">
+        <v>45630</v>
+      </c>
+      <c r="E40" s="2">
+        <v>0</v>
+      </c>
+      <c r="F40" s="1">
+        <v>19.309999999999999</v>
+      </c>
+      <c r="G40" s="1">
+        <f>E40*F40</f>
+        <v>0</v>
+      </c>
+      <c r="H40" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="I40" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="J40" s="9">
+        <f>IFERROR(H40/I40,"")</f>
+        <v>1</v>
+      </c>
+      <c r="K40" s="9">
+        <f>IFERROR(J40/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>5.4885605316854089E-2</v>
+      </c>
+      <c r="L40" s="12">
+        <f>F40/(1-(F40*(1+H40)-F40)/(F40*(1+H40)))</f>
+        <v>23.171999999999997</v>
+      </c>
+      <c r="M40" s="12">
+        <f>F40/(1+I40-H40)</f>
+        <v>19.309999999999999</v>
+      </c>
+      <c r="N40" s="12">
+        <f>L40-F40</f>
+        <v>3.8619999999999983</v>
+      </c>
+      <c r="O40" s="12">
+        <f>0.5*(M40-F40)</f>
+        <v>0</v>
+      </c>
+      <c r="P40" s="15">
+        <f>N40+O40</f>
+        <v>3.8619999999999983</v>
+      </c>
+      <c r="Q40" s="12">
+        <f>MAX($P$2:$P$280)-P40</f>
+        <v>99.766510028653329</v>
+      </c>
+      <c r="R40" s="9">
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q40)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.002340364229235E-2</v>
+      </c>
+      <c r="S40" s="9">
+        <f>Q40/MAX($Q$2:$Q$28)</f>
+        <v>0.45106200085693343</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>98</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C41" t="s">
+        <v>101</v>
+      </c>
+      <c r="D41" s="8">
+        <v>45630</v>
+      </c>
+      <c r="E41" s="2">
+        <v>0</v>
+      </c>
+      <c r="F41" s="1">
+        <v>323.75</v>
+      </c>
+      <c r="G41" s="1">
+        <f>E41*F41</f>
+        <v>0</v>
+      </c>
+      <c r="H41" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="I41" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="J41" s="9">
+        <f>IFERROR(H41/I41,"")</f>
+        <v>1</v>
+      </c>
+      <c r="K41" s="9">
+        <f>IFERROR(J41/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>5.4885605316854089E-2</v>
+      </c>
+      <c r="L41" s="12">
+        <f>F41/(1-(F41*(1+H41)-F41)/(F41*(1+H41)))</f>
+        <v>388.5</v>
+      </c>
+      <c r="M41" s="12">
+        <f>F41/(1+I41-H41)</f>
+        <v>323.75</v>
+      </c>
+      <c r="N41" s="12">
+        <f>L41-F41</f>
+        <v>64.75</v>
+      </c>
+      <c r="O41" s="12">
+        <f>0.5*(M41-F41)</f>
+        <v>0</v>
+      </c>
+      <c r="P41" s="15">
+        <f>N41+O41</f>
+        <v>64.75</v>
+      </c>
+      <c r="Q41" s="12">
+        <f>MAX($P$2:$P$280)-P41</f>
+        <v>38.878510028653324</v>
+      </c>
+      <c r="R41" s="9">
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q41)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>2.572115030290522E-2</v>
+      </c>
+      <c r="S41" s="9">
+        <f>Q41/MAX($Q$2:$Q$28)</f>
+        <v>0.17577660598555703</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:S33" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S38">
-      <sortCondition descending="1" ref="G1:G33"/>
+      <sortCondition descending="1" ref="E1:E33"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="R2:R38">
+  <conditionalFormatting sqref="R2:R41">
     <cfRule type="iconSet" priority="3">
       <iconSet iconSet="3Symbols">
         <cfvo type="percent" val="0"/>
@@ -3466,7 +3697,7 @@
               <x14:cfIcon iconSet="3Arrows" iconId="0"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>S2:S38</xm:sqref>
+          <xm:sqref>S2:S41</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/Open Positions.xlsx
+++ b/Open Positions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\StockSillines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27F885E9-960E-415C-868D-BE949A6D127A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6861DC2-F36E-494A-A4E6-92F19D7A78B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -866,7 +866,7 @@
         <v>15.3</v>
       </c>
       <c r="G2" s="1">
-        <f>E2*F2</f>
+        <f t="shared" ref="G2:G41" si="0">E2*F2</f>
         <v>29.980350000000001</v>
       </c>
       <c r="H2" s="11">
@@ -876,43 +876,43 @@
         <v>0.39532299999999998</v>
       </c>
       <c r="J2" s="9">
-        <f>IFERROR(H2/I2,"")</f>
+        <f t="shared" ref="J2:J41" si="1">IFERROR(H2/I2,"")</f>
         <v>0.88535197800279775</v>
       </c>
       <c r="K2" s="9">
-        <f>IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.8593079231157639E-2</v>
+        <f t="shared" ref="K2:K41" si="2">IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>4.8490794985327837E-2</v>
       </c>
       <c r="L2" s="12">
-        <f>F2/(1-(F2*(1+H2)-F2)/(F2*(1+H2)))</f>
+        <f t="shared" ref="L2:L30" si="3">F2/(1-(F2*(1+H2)-F2)/(F2*(1+H2)))</f>
         <v>20.655000000000001</v>
       </c>
       <c r="M2" s="12">
-        <f>F2/(1+I2-H2)</f>
+        <f t="shared" ref="M2:M41" si="4">F2/(1+I2-H2)</f>
         <v>14.636624277854791</v>
       </c>
       <c r="N2" s="12">
-        <f>L2-F2</f>
+        <f t="shared" ref="N2:N41" si="5">L2-F2</f>
         <v>5.3550000000000004</v>
       </c>
       <c r="O2" s="12">
-        <f>0.5*(M2-F2)</f>
+        <f t="shared" ref="O2:O41" si="6">0.5*(M2-F2)</f>
         <v>-0.33168786107260484</v>
       </c>
       <c r="P2" s="15">
-        <f>N2+O2</f>
+        <f t="shared" ref="P2:P41" si="7">N2+O2</f>
         <v>5.0233121389273956</v>
       </c>
       <c r="Q2" s="12">
-        <f>MAX($P$2:$P$280)-P2</f>
+        <f t="shared" ref="Q2:Q41" si="8">MAX($P$2:$P$280)-P2</f>
         <v>98.605197889725929</v>
       </c>
       <c r="R2" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q2)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" ref="R2:R41" si="9">IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q2)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
         <v>1.0141453203291973E-2</v>
       </c>
       <c r="S2" s="9">
-        <f>Q2/MAX($Q$2:$Q$28)</f>
+        <f t="shared" ref="S2:S41" si="10">Q2/MAX($Q$2:$Q$28)</f>
         <v>0.44581150370259182</v>
       </c>
     </row>
@@ -936,7 +936,7 @@
         <v>51.15</v>
       </c>
       <c r="G3" s="1">
-        <f>E3*F3</f>
+        <f t="shared" si="0"/>
         <v>54.996479999999998</v>
       </c>
       <c r="H3" s="11">
@@ -947,43 +947,43 @@
         <v>0.19980000000000001</v>
       </c>
       <c r="J3" s="9">
-        <f>IFERROR(H3/I3,"")</f>
+        <f t="shared" si="1"/>
         <v>0.92242242242242245</v>
       </c>
       <c r="K3" s="9">
-        <f>IFERROR(J3/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>5.0627713012493539E-2</v>
+        <f t="shared" si="2"/>
+        <v>5.05211460378234E-2</v>
       </c>
       <c r="L3" s="12">
-        <f>F3/(1-(F3*(1+H3)-F3)/(F3*(1+H3)))</f>
+        <f t="shared" si="3"/>
         <v>60.576944999999995</v>
       </c>
       <c r="M3" s="12">
-        <f>F3/(1+I3-H3)</f>
+        <f t="shared" si="4"/>
         <v>50.369276218611525</v>
       </c>
       <c r="N3" s="12">
-        <f>L3-F3</f>
+        <f t="shared" si="5"/>
         <v>9.4269449999999964</v>
       </c>
       <c r="O3" s="12">
-        <f>0.5*(M3-F3)</f>
+        <f t="shared" si="6"/>
         <v>-0.39036189069423699</v>
       </c>
       <c r="P3" s="15">
-        <f>N3+O3</f>
+        <f t="shared" si="7"/>
         <v>9.0365831093057594</v>
       </c>
       <c r="Q3" s="12">
-        <f>MAX($P$2:$P$280)-P3</f>
+        <f t="shared" si="8"/>
         <v>94.591926919347571</v>
       </c>
       <c r="R3" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q3)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>1.0571726706155752E-2</v>
       </c>
       <c r="S3" s="9">
-        <f>Q3/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0.42766679729399837</v>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
         <v>10.92</v>
       </c>
       <c r="G4" s="1">
-        <f>E4*F4</f>
+        <f t="shared" si="0"/>
         <v>10.92</v>
       </c>
       <c r="H4" s="11">
@@ -1017,43 +1017,43 @@
         <v>1.8652</v>
       </c>
       <c r="J4" s="9">
-        <f>IFERROR(H4/I4,"")</f>
+        <f t="shared" si="1"/>
         <v>0.53613553506326406</v>
       </c>
       <c r="K4" s="9">
-        <f>IFERROR(J4/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.9426123373822697E-2</v>
+        <f t="shared" si="2"/>
+        <v>2.9364183918974232E-2</v>
       </c>
       <c r="L4" s="12">
-        <f>F4/(1-(F4*(1+H4)-F4)/(F4*(1+H4)))</f>
+        <f t="shared" si="3"/>
         <v>21.84</v>
       </c>
       <c r="M4" s="12">
-        <f>F4/(1+I4-H4)</f>
+        <f t="shared" si="4"/>
         <v>5.8546000428908433</v>
       </c>
       <c r="N4" s="12">
-        <f>L4-F4</f>
+        <f t="shared" si="5"/>
         <v>10.92</v>
       </c>
       <c r="O4" s="12">
-        <f>0.5*(M4-F4)</f>
+        <f t="shared" si="6"/>
         <v>-2.5326999785545783</v>
       </c>
       <c r="P4" s="15">
-        <f>N4+O4</f>
+        <f t="shared" si="7"/>
         <v>8.3873000214454212</v>
       </c>
       <c r="Q4" s="12">
-        <f>MAX($P$2:$P$280)-P4</f>
+        <f t="shared" si="8"/>
         <v>95.241210007207897</v>
       </c>
       <c r="R4" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q4)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>1.0499656607935993E-2</v>
       </c>
       <c r="S4" s="9">
-        <f>Q4/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0.43060232073416616</v>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
         <v>77.430000000000007</v>
       </c>
       <c r="G5" s="1">
-        <f>E5*F5</f>
+        <f t="shared" si="0"/>
         <v>34.982874000000002</v>
       </c>
       <c r="H5" s="11">
@@ -1087,43 +1087,43 @@
         <v>0.25990000000000002</v>
       </c>
       <c r="J5" s="9">
-        <f>IFERROR(H5/I5,"")</f>
+        <f t="shared" si="1"/>
         <v>0.38476337052712584</v>
       </c>
       <c r="K5" s="9">
-        <f>IFERROR(J5/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.1117970495134315E-2</v>
+        <f t="shared" si="2"/>
+        <v>2.1073518986406591E-2</v>
       </c>
       <c r="L5" s="12">
-        <f>F5/(1-(F5*(1+H5)-F5)/(F5*(1+H5)))</f>
+        <f t="shared" si="3"/>
         <v>85.173000000000016</v>
       </c>
       <c r="M5" s="12">
-        <f>F5/(1+I5-H5)</f>
+        <f t="shared" si="4"/>
         <v>66.755754806448849</v>
       </c>
       <c r="N5" s="12">
-        <f>L5-F5</f>
+        <f t="shared" si="5"/>
         <v>7.7430000000000092</v>
       </c>
       <c r="O5" s="12">
-        <f>0.5*(M5-F5)</f>
+        <f t="shared" si="6"/>
         <v>-5.3371225967755791</v>
       </c>
       <c r="P5" s="15">
-        <f>N5+O5</f>
+        <f t="shared" si="7"/>
         <v>2.4058774032244301</v>
       </c>
       <c r="Q5" s="12">
-        <f>MAX($P$2:$P$280)-P5</f>
+        <f t="shared" si="8"/>
         <v>101.2226326254289</v>
       </c>
       <c r="R5" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q5)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.8792135124608736E-3</v>
+        <f t="shared" si="9"/>
+        <v>9.8792135124608719E-3</v>
       </c>
       <c r="S5" s="9">
-        <f>Q5/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0.45764538812592725</v>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         <v>142.78</v>
       </c>
       <c r="G6" s="1">
-        <f>E6*F6</f>
+        <f t="shared" si="0"/>
         <v>50.187169999999995</v>
       </c>
       <c r="H6" s="11">
@@ -1157,185 +1157,185 @@
         <v>0.18340000000000001</v>
       </c>
       <c r="J6" s="9">
-        <f>IFERROR(H6/I6,"")</f>
+        <f t="shared" si="1"/>
         <v>0.38167938931297712</v>
       </c>
       <c r="K6" s="9">
-        <f>IFERROR(J6/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.0948704319409959E-2</v>
+        <f t="shared" si="2"/>
+        <v>2.0904609101401041E-2</v>
       </c>
       <c r="L6" s="12">
-        <f>F6/(1-(F6*(1+H6)-F6)/(F6*(1+H6)))</f>
+        <f t="shared" si="3"/>
         <v>152.77460000000002</v>
       </c>
       <c r="M6" s="12">
-        <f>F6/(1+I6-H6)</f>
+        <f t="shared" si="4"/>
         <v>128.23783007005568</v>
       </c>
       <c r="N6" s="12">
-        <f>L6-F6</f>
+        <f t="shared" si="5"/>
         <v>9.9946000000000197</v>
       </c>
       <c r="O6" s="12">
-        <f>0.5*(M6-F6)</f>
+        <f t="shared" si="6"/>
         <v>-7.2710849649721609</v>
       </c>
       <c r="P6" s="15">
-        <f>N6+O6</f>
+        <f t="shared" si="7"/>
         <v>2.7235150350278587</v>
       </c>
       <c r="Q6" s="12">
-        <f>MAX($P$2:$P$280)-P6</f>
+        <f t="shared" si="8"/>
         <v>100.90499499362546</v>
       </c>
       <c r="R6" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q6)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>9.9103121709997969E-3</v>
       </c>
       <c r="S6" s="9">
-        <f>Q6/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0.45620929232877483</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>21</v>
+        <v>38</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D7" s="8">
-        <v>45484</v>
+        <v>45460</v>
       </c>
       <c r="E7" s="2">
-        <v>0.33389999999999997</v>
+        <v>0.33529999999999999</v>
       </c>
       <c r="F7" s="1">
-        <v>188.53</v>
+        <v>163.15</v>
       </c>
       <c r="G7" s="1">
-        <f>E7*F7</f>
-        <v>62.950166999999993</v>
+        <f t="shared" si="0"/>
+        <v>54.704194999999999</v>
       </c>
       <c r="H7" s="11">
-        <f>227.4/F7-1</f>
-        <v>0.20617408370020684</v>
+        <v>6.7199999999999996E-2</v>
       </c>
       <c r="I7" s="11">
-        <v>0.37</v>
+        <v>0.16439999999999999</v>
       </c>
       <c r="J7" s="9">
-        <f>IFERROR(H7/I7,"")</f>
-        <v>0.55722725324380229</v>
+        <f t="shared" si="1"/>
+        <v>0.40875912408759124</v>
       </c>
       <c r="K7" s="9">
-        <f>IFERROR(J7/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.0583755093334032E-2</v>
+        <f t="shared" si="2"/>
+        <v>2.2387768228887304E-2</v>
       </c>
       <c r="L7" s="12">
-        <f>F7/(1-(F7*(1+H7)-F7)/(F7*(1+H7)))</f>
-        <v>227.4</v>
+        <f t="shared" si="3"/>
+        <v>174.11367999999999</v>
       </c>
       <c r="M7" s="12">
-        <f>F7/(1+I7-H7)</f>
-        <v>161.9915808365931</v>
+        <f t="shared" si="4"/>
+        <v>148.69668246445497</v>
       </c>
       <c r="N7" s="12">
-        <f>L7-F7</f>
-        <v>38.870000000000005</v>
+        <f t="shared" si="5"/>
+        <v>10.963679999999982</v>
       </c>
       <c r="O7" s="12">
-        <f>0.5*(M7-F7)</f>
-        <v>-13.26920958170345</v>
+        <f t="shared" si="6"/>
+        <v>-7.2266587677725198</v>
       </c>
       <c r="P7" s="15">
-        <f>N7+O7</f>
-        <v>25.600790418296555</v>
+        <f t="shared" si="7"/>
+        <v>3.7370212322274625</v>
       </c>
       <c r="Q7" s="12">
-        <f>MAX($P$2:$P$280)-P7</f>
-        <v>78.027719610356769</v>
+        <f t="shared" si="8"/>
+        <v>99.891488796425861</v>
       </c>
       <c r="R7" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q7)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.2815958290126271E-2</v>
+        <f t="shared" si="9"/>
+        <v>1.0010862907829442E-2</v>
       </c>
       <c r="S7" s="9">
-        <f>Q7/MAX($Q$2:$Q$28)</f>
-        <v>0.35277709242954441</v>
+        <f t="shared" si="10"/>
+        <v>0.45162705192507163</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>15</v>
+        <v>36</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D8" s="8">
-        <v>45460</v>
+        <v>45484</v>
       </c>
       <c r="E8" s="2">
-        <v>0.33529999999999999</v>
+        <v>0.33389999999999997</v>
       </c>
       <c r="F8" s="1">
-        <v>163.15</v>
+        <v>188.53</v>
       </c>
       <c r="G8" s="1">
-        <f>E8*F8</f>
-        <v>54.704194999999999</v>
+        <f t="shared" si="0"/>
+        <v>62.950166999999993</v>
       </c>
       <c r="H8" s="11">
-        <v>6.7199999999999996E-2</v>
+        <f>227.4/F8-1</f>
+        <v>0.20617408370020684</v>
       </c>
       <c r="I8" s="11">
-        <v>0.16439999999999999</v>
+        <v>0.37</v>
       </c>
       <c r="J8" s="9">
-        <f>IFERROR(H8/I8,"")</f>
-        <v>0.40875912408759124</v>
+        <f t="shared" si="1"/>
+        <v>0.55722725324380229</v>
       </c>
       <c r="K8" s="9">
-        <f>IFERROR(J8/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.2434991954334519E-2</v>
+        <f t="shared" si="2"/>
+        <v>3.0519378923437823E-2</v>
       </c>
       <c r="L8" s="12">
-        <f>F8/(1-(F8*(1+H8)-F8)/(F8*(1+H8)))</f>
-        <v>174.11367999999999</v>
+        <f t="shared" si="3"/>
+        <v>227.4</v>
       </c>
       <c r="M8" s="12">
-        <f>F8/(1+I8-H8)</f>
-        <v>148.69668246445497</v>
+        <f t="shared" si="4"/>
+        <v>161.9915808365931</v>
       </c>
       <c r="N8" s="12">
-        <f>L8-F8</f>
-        <v>10.963679999999982</v>
+        <f t="shared" si="5"/>
+        <v>38.870000000000005</v>
       </c>
       <c r="O8" s="12">
-        <f>0.5*(M8-F8)</f>
-        <v>-7.2266587677725198</v>
+        <f t="shared" si="6"/>
+        <v>-13.26920958170345</v>
       </c>
       <c r="P8" s="15">
-        <f>N8+O8</f>
-        <v>3.7370212322274625</v>
+        <f t="shared" si="7"/>
+        <v>25.600790418296555</v>
       </c>
       <c r="Q8" s="12">
-        <f>MAX($P$2:$P$280)-P8</f>
-        <v>99.891488796425861</v>
+        <f t="shared" si="8"/>
+        <v>78.027719610356769</v>
       </c>
       <c r="R8" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q8)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.0010862907829442E-2</v>
+        <f t="shared" si="9"/>
+        <v>1.2815958290126271E-2</v>
       </c>
       <c r="S8" s="9">
-        <f>Q8/MAX($Q$2:$Q$28)</f>
-        <v>0.45162705192507163</v>
+        <f t="shared" si="10"/>
+        <v>0.35277709242954441</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
@@ -1358,7 +1358,7 @@
         <v>188.12</v>
       </c>
       <c r="G9" s="1">
-        <f>E9*F9</f>
+        <f t="shared" si="0"/>
         <v>36.269536000000002</v>
       </c>
       <c r="H9" s="11">
@@ -1368,43 +1368,43 @@
         <v>0.37780000000000002</v>
       </c>
       <c r="J9" s="9">
-        <f>IFERROR(H9/I9,"")</f>
+        <f t="shared" si="1"/>
         <v>0.39703546850185278</v>
       </c>
       <c r="K9" s="9">
-        <f>IFERROR(J9/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.1791532020984945E-2</v>
+        <f t="shared" si="2"/>
+        <v>2.1745662723267889E-2</v>
       </c>
       <c r="L9" s="12">
-        <f>F9/(1-(F9*(1+H9)-F9)/(F9*(1+H9)))</f>
+        <f t="shared" si="3"/>
         <v>216.33799999999999</v>
       </c>
       <c r="M9" s="12">
-        <f>F9/(1+I9-H9)</f>
+        <f t="shared" si="4"/>
         <v>153.21713634142367</v>
       </c>
       <c r="N9" s="12">
-        <f>L9-F9</f>
+        <f t="shared" si="5"/>
         <v>28.217999999999989</v>
       </c>
       <c r="O9" s="12">
-        <f>0.5*(M9-F9)</f>
+        <f t="shared" si="6"/>
         <v>-17.451431829288168</v>
       </c>
       <c r="P9" s="15">
-        <f>N9+O9</f>
+        <f t="shared" si="7"/>
         <v>10.766568170711821</v>
       </c>
       <c r="Q9" s="12">
-        <f>MAX($P$2:$P$280)-P9</f>
+        <f t="shared" si="8"/>
         <v>92.861941857941503</v>
       </c>
       <c r="R9" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q9)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>1.0768674227486882E-2</v>
       </c>
       <c r="S9" s="9">
-        <f>Q9/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0.41984522948505815</v>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
         <v>135.82</v>
       </c>
       <c r="G10" s="1">
-        <f>E10*F10</f>
+        <f t="shared" si="0"/>
         <v>25.995947999999999</v>
       </c>
       <c r="H10" s="11">
@@ -1438,43 +1438,43 @@
         <v>0.33710000000000001</v>
       </c>
       <c r="J10" s="9">
-        <f>IFERROR(H10/I10,"")</f>
+        <f t="shared" si="1"/>
         <v>0.35657075051913378</v>
       </c>
       <c r="K10" s="9">
-        <f>IFERROR(J10/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.9570601480527621E-2</v>
+        <f t="shared" si="2"/>
+        <v>1.9529407050280691E-2</v>
       </c>
       <c r="L10" s="12">
-        <f>F10/(1-(F10*(1+H10)-F10)/(F10*(1+H10)))</f>
+        <f t="shared" si="3"/>
         <v>152.14556400000001</v>
       </c>
       <c r="M10" s="12">
-        <f>F10/(1+I10-H10)</f>
+        <f t="shared" si="4"/>
         <v>111.61147177253677</v>
       </c>
       <c r="N10" s="12">
-        <f>L10-F10</f>
+        <f t="shared" si="5"/>
         <v>16.325564000000014</v>
       </c>
       <c r="O10" s="12">
-        <f>0.5*(M10-F10)</f>
+        <f t="shared" si="6"/>
         <v>-12.10426411373161</v>
       </c>
       <c r="P10" s="15">
-        <f>N10+O10</f>
+        <f t="shared" si="7"/>
         <v>4.2212998862684046</v>
       </c>
       <c r="Q10" s="12">
-        <f>MAX($P$2:$P$280)-P10</f>
+        <f t="shared" si="8"/>
         <v>99.407210142384912</v>
       </c>
       <c r="R10" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q10)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>1.0059632481061082E-2</v>
       </c>
       <c r="S10" s="9">
-        <f>Q10/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0.44943754265386154</v>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
         <v>227.38</v>
       </c>
       <c r="G11" s="1">
-        <f>E11*F11</f>
+        <f t="shared" si="0"/>
         <v>42.792915999999998</v>
       </c>
       <c r="H11" s="11">
@@ -1508,43 +1508,43 @@
         <v>0.2271</v>
       </c>
       <c r="J11" s="9">
-        <f>IFERROR(H11/I11,"")</f>
+        <f t="shared" si="1"/>
         <v>0.66050198150594452</v>
       </c>
       <c r="K11" s="9">
-        <f>IFERROR(J11/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.6252051067935331E-2</v>
+        <f t="shared" si="2"/>
+        <v>3.6175743623296383E-2</v>
       </c>
       <c r="L11" s="12">
-        <f>F11/(1-(F11*(1+H11)-F11)/(F11*(1+H11)))</f>
+        <f t="shared" si="3"/>
         <v>261.48699999999997</v>
       </c>
       <c r="M11" s="12">
-        <f>F11/(1+I11-H11)</f>
+        <f t="shared" si="4"/>
         <v>211.10389007520189</v>
       </c>
       <c r="N11" s="12">
-        <f>L11-F11</f>
+        <f t="shared" si="5"/>
         <v>34.106999999999971</v>
       </c>
       <c r="O11" s="12">
-        <f>0.5*(M11-F11)</f>
+        <f t="shared" si="6"/>
         <v>-8.1380549623990532</v>
       </c>
       <c r="P11" s="15">
-        <f>N11+O11</f>
+        <f t="shared" si="7"/>
         <v>25.968945037600918</v>
       </c>
       <c r="Q11" s="12">
-        <f>MAX($P$2:$P$280)-P11</f>
+        <f t="shared" si="8"/>
         <v>77.659564991052406</v>
       </c>
       <c r="R11" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q11)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.2876713900151457E-2</v>
+        <f t="shared" si="9"/>
+        <v>1.2876713900151458E-2</v>
       </c>
       <c r="S11" s="9">
-        <f>Q11/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0.35111260041553638</v>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
         <v>133.19999999999999</v>
       </c>
       <c r="G12" s="1">
-        <f>E12*F12</f>
+        <f t="shared" si="0"/>
         <v>23.989319999999999</v>
       </c>
       <c r="H12" s="11">
@@ -1578,43 +1578,43 @@
         <v>0.1623</v>
       </c>
       <c r="J12" s="9">
-        <f>IFERROR(H12/I12,"")</f>
+        <f t="shared" si="1"/>
         <v>0.43130006161429457</v>
       </c>
       <c r="K12" s="9">
-        <f>IFERROR(J12/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.3672164954897022E-2</v>
+        <f t="shared" si="2"/>
+        <v>2.3622337086857372E-2</v>
       </c>
       <c r="L12" s="12">
-        <f>F12/(1-(F12*(1+H12)-F12)/(F12*(1+H12)))</f>
+        <f t="shared" si="3"/>
         <v>142.524</v>
       </c>
       <c r="M12" s="12">
-        <f>F12/(1+I12-H12)</f>
+        <f t="shared" si="4"/>
         <v>121.94452073606151</v>
       </c>
       <c r="N12" s="12">
-        <f>L12-F12</f>
+        <f t="shared" si="5"/>
         <v>9.3240000000000123</v>
       </c>
       <c r="O12" s="12">
-        <f>0.5*(M12-F12)</f>
+        <f t="shared" si="6"/>
         <v>-5.6277396319692414</v>
       </c>
       <c r="P12" s="15">
-        <f>N12+O12</f>
+        <f t="shared" si="7"/>
         <v>3.6962603680307708</v>
       </c>
       <c r="Q12" s="12">
-        <f>MAX($P$2:$P$280)-P12</f>
+        <f t="shared" si="8"/>
         <v>99.932249660622546</v>
       </c>
       <c r="R12" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q12)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>1.0006779627158154E-2</v>
       </c>
       <c r="S12" s="9">
-        <f>Q12/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0.45181133898649067</v>
       </c>
     </row>
@@ -1638,7 +1638,7 @@
         <v>273.45999999999998</v>
       </c>
       <c r="G13" s="1">
-        <f>E13*F13</f>
+        <f t="shared" si="0"/>
         <v>39.952506</v>
       </c>
       <c r="H13" s="11">
@@ -1648,43 +1648,43 @@
         <v>0.26</v>
       </c>
       <c r="J13" s="9">
-        <f>IFERROR(H13/I13,"")</f>
+        <f t="shared" si="1"/>
         <v>0.96153846153846145</v>
       </c>
       <c r="K13" s="9">
-        <f>IFERROR(J13/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>5.277462049697508E-2</v>
+        <f t="shared" si="2"/>
+        <v>5.2663534466991083E-2</v>
       </c>
       <c r="L13" s="12">
-        <f>F13/(1-(F13*(1+H13)-F13)/(F13*(1+H13)))</f>
+        <f t="shared" si="3"/>
         <v>341.82499999999999</v>
       </c>
       <c r="M13" s="12">
-        <f>F13/(1+I13-H13)</f>
+        <f t="shared" si="4"/>
         <v>270.75247524752473</v>
       </c>
       <c r="N13" s="12">
-        <f>L13-F13</f>
+        <f t="shared" si="5"/>
         <v>68.365000000000009</v>
       </c>
       <c r="O13" s="12">
-        <f>0.5*(M13-F13)</f>
+        <f t="shared" si="6"/>
         <v>-1.3537623762376256</v>
       </c>
       <c r="P13" s="15">
-        <f>N13+O13</f>
+        <f t="shared" si="7"/>
         <v>67.011237623762383</v>
       </c>
       <c r="Q13" s="12">
-        <f>MAX($P$2:$P$280)-P13</f>
+        <f t="shared" si="8"/>
         <v>36.61727240489094</v>
       </c>
       <c r="R13" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q13)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>2.7309516365463388E-2</v>
       </c>
       <c r="S13" s="9">
-        <f>Q13/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0.1655531515749106</v>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
         <v>423.77</v>
       </c>
       <c r="G14" s="1">
-        <f>E14*F14</f>
+        <f t="shared" si="0"/>
         <v>56.658049000000005</v>
       </c>
       <c r="H14" s="11">
@@ -1718,43 +1718,43 @@
         <v>0.1963</v>
       </c>
       <c r="J14" s="9">
-        <f>IFERROR(H14/I14,"")</f>
+        <f t="shared" si="1"/>
         <v>0.76413652572592972</v>
       </c>
       <c r="K14" s="9">
-        <f>IFERROR(J14/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.1940095759185496E-2</v>
+        <f t="shared" si="2"/>
+        <v>4.1851815470456494E-2</v>
       </c>
       <c r="L14" s="12">
-        <f>F14/(1-(F14*(1+H14)-F14)/(F14*(1+H14)))</f>
+        <f t="shared" si="3"/>
         <v>487.33549999999991</v>
       </c>
       <c r="M14" s="12">
-        <f>F14/(1+I14-H14)</f>
+        <f t="shared" si="4"/>
         <v>405.01768135334032</v>
       </c>
       <c r="N14" s="12">
-        <f>L14-F14</f>
+        <f t="shared" si="5"/>
         <v>63.565499999999929</v>
       </c>
       <c r="O14" s="12">
-        <f>0.5*(M14-F14)</f>
+        <f t="shared" si="6"/>
         <v>-9.3761593233298299</v>
       </c>
       <c r="P14" s="15">
-        <f>N14+O14</f>
+        <f t="shared" si="7"/>
         <v>54.189340676670099</v>
       </c>
       <c r="Q14" s="12">
-        <f>MAX($P$2:$P$280)-P14</f>
+        <f t="shared" si="8"/>
         <v>49.439169351983224</v>
       </c>
       <c r="R14" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q14)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>2.0226877051280505E-2</v>
       </c>
       <c r="S14" s="9">
-        <f>Q14/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0.22352321076687609</v>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
         <v>167.24</v>
       </c>
       <c r="G15" s="1">
-        <f>E15*F15</f>
+        <f t="shared" si="0"/>
         <v>19.98518</v>
       </c>
       <c r="H15" s="11">
@@ -1789,43 +1789,43 @@
         <v>0.26790000000000003</v>
       </c>
       <c r="J15" s="9">
-        <f>IFERROR(H15/I15,"")</f>
+        <f t="shared" si="1"/>
         <v>0.51714598979956872</v>
       </c>
       <c r="K15" s="9">
-        <f>IFERROR(J15/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.8383870687332977E-2</v>
+        <f t="shared" si="2"/>
+        <v>2.8324125084606841E-2</v>
       </c>
       <c r="L15" s="12">
-        <f>F15/(1-(F15*(1+H15)-F15)/(F15*(1+H15)))</f>
+        <f t="shared" si="3"/>
         <v>190.41</v>
       </c>
       <c r="M15" s="12">
-        <f>F15/(1+I15-H15)</f>
+        <f t="shared" si="4"/>
         <v>148.08431772538498</v>
       </c>
       <c r="N15" s="12">
-        <f>L15-F15</f>
+        <f t="shared" si="5"/>
         <v>23.169999999999987</v>
       </c>
       <c r="O15" s="12">
-        <f>0.5*(M15-F15)</f>
+        <f t="shared" si="6"/>
         <v>-9.5778411373075159</v>
       </c>
       <c r="P15" s="15">
-        <f>N15+O15</f>
+        <f t="shared" si="7"/>
         <v>13.592158862692472</v>
       </c>
       <c r="Q15" s="12">
-        <f>MAX($P$2:$P$280)-P15</f>
+        <f t="shared" si="8"/>
         <v>90.036351165960852</v>
       </c>
       <c r="R15" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q15)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>1.1106625124742506E-2</v>
       </c>
       <c r="S15" s="9">
-        <f>Q15/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0.40707023524338853</v>
       </c>
     </row>
@@ -1849,7 +1849,7 @@
         <v>668.82</v>
       </c>
       <c r="G16" s="1">
-        <f>E16*F16</f>
+        <f t="shared" si="0"/>
         <v>26.953446000000003</v>
       </c>
       <c r="H16" s="11">
@@ -1859,43 +1859,43 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="J16" s="9">
-        <f>IFERROR(H16/I16,"")</f>
+        <f t="shared" si="1"/>
         <v>0.17857142857142858</v>
       </c>
       <c r="K16" s="9">
-        <f>IFERROR(J16/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>9.8010009494382301E-3</v>
+        <f t="shared" si="2"/>
+        <v>9.7803706867269167E-3</v>
       </c>
       <c r="L16" s="12">
-        <f>F16/(1-(F16*(1+H16)-F16)/(F16*(1+H16)))</f>
+        <f t="shared" si="3"/>
         <v>702.26100000000008</v>
       </c>
       <c r="M16" s="12">
-        <f>F16/(1+I16-H16)</f>
+        <f t="shared" si="4"/>
         <v>543.7560975609756</v>
       </c>
       <c r="N16" s="12">
-        <f>L16-F16</f>
+        <f t="shared" si="5"/>
         <v>33.441000000000031</v>
       </c>
       <c r="O16" s="12">
-        <f>0.5*(M16-F16)</f>
+        <f t="shared" si="6"/>
         <v>-62.531951219512223</v>
       </c>
       <c r="P16" s="15">
-        <f>N16+O16</f>
+        <f t="shared" si="7"/>
         <v>-29.090951219512192</v>
       </c>
       <c r="Q16" s="12">
-        <f>MAX($P$2:$P$280)-P16</f>
+        <f t="shared" si="8"/>
         <v>132.71946124816552</v>
       </c>
       <c r="R16" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q16)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>7.5346900190481469E-3</v>
       </c>
       <c r="S16" s="9">
-        <f>Q16/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0.60004810959166965</v>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
         <v>455.4</v>
       </c>
       <c r="G17" s="1">
-        <f>E17*F17</f>
+        <f t="shared" si="0"/>
         <v>14.982659999999999</v>
       </c>
       <c r="H17" s="11">
@@ -1929,43 +1929,43 @@
         <v>0.29699999999999999</v>
       </c>
       <c r="J17" s="9">
-        <f>IFERROR(H17/I17,"")</f>
+        <f t="shared" si="1"/>
         <v>0.84175084175084181</v>
       </c>
       <c r="K17" s="9">
-        <f>IFERROR(J17/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.6200004475466405E-2</v>
+        <f t="shared" si="2"/>
+        <v>4.6102757445850781E-2</v>
       </c>
       <c r="L17" s="12">
-        <f>F17/(1-(F17*(1+H17)-F17)/(F17*(1+H17)))</f>
+        <f t="shared" si="3"/>
         <v>569.25</v>
       </c>
       <c r="M17" s="12">
-        <f>F17/(1+I17-H17)</f>
+        <f t="shared" si="4"/>
         <v>434.95702005730658</v>
       </c>
       <c r="N17" s="12">
-        <f>L17-F17</f>
+        <f t="shared" si="5"/>
         <v>113.85000000000002</v>
       </c>
       <c r="O17" s="12">
-        <f>0.5*(M17-F17)</f>
+        <f t="shared" si="6"/>
         <v>-10.221489971346699</v>
       </c>
       <c r="P17" s="15">
-        <f>N17+O17</f>
+        <f t="shared" si="7"/>
         <v>103.62851002865332</v>
       </c>
       <c r="Q17" s="12">
-        <f>MAX($P$2:$P$280)-P17</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R17" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q17)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S17" s="9">
-        <f>Q17/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
         <v>700.32</v>
       </c>
       <c r="G18" s="1">
-        <f>E18*F18</f>
+        <f t="shared" si="0"/>
         <v>19.959120000000002</v>
       </c>
       <c r="H18" s="11">
@@ -1999,43 +1999,43 @@
         <v>0.45340000000000003</v>
       </c>
       <c r="J18" s="9">
-        <f>IFERROR(H18/I18,"")</f>
+        <f t="shared" si="1"/>
         <v>0.22055580061755625</v>
       </c>
       <c r="K18" s="9">
-        <f>IFERROR(J18/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.2105338623037955E-2</v>
+        <f t="shared" si="2"/>
+        <v>1.2079857928026187E-2</v>
       </c>
       <c r="L18" s="12">
-        <f>F18/(1-(F18*(1+H18)-F18)/(F18*(1+H18)))</f>
+        <f t="shared" si="3"/>
         <v>770.35200000000009</v>
       </c>
       <c r="M18" s="12">
-        <f>F18/(1+I18-H18)</f>
+        <f t="shared" si="4"/>
         <v>517.45234224915032</v>
       </c>
       <c r="N18" s="12">
-        <f>L18-F18</f>
+        <f t="shared" si="5"/>
         <v>70.032000000000039</v>
       </c>
       <c r="O18" s="12">
-        <f>0.5*(M18-F18)</f>
+        <f t="shared" si="6"/>
         <v>-91.433828875424865</v>
       </c>
       <c r="P18" s="15">
-        <f>N18+O18</f>
+        <f t="shared" si="7"/>
         <v>-21.401828875424826</v>
       </c>
       <c r="Q18" s="12">
-        <f>MAX($P$2:$P$280)-P18</f>
+        <f t="shared" si="8"/>
         <v>125.03033890407815</v>
       </c>
       <c r="R18" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q18)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>7.9980587812945834E-3</v>
       </c>
       <c r="S18" s="9">
-        <f>Q18/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0.565284230326356</v>
       </c>
     </row>
@@ -2059,7 +2059,7 @@
         <v>147.01</v>
       </c>
       <c r="G19" s="1">
-        <f>E19*F19</f>
+        <f t="shared" si="0"/>
         <v>1.4700999999999999E-17</v>
       </c>
       <c r="H19" s="11">
@@ -2069,43 +2069,43 @@
         <v>0.52380000000000004</v>
       </c>
       <c r="J19" s="9">
-        <f>IFERROR(H19/I19,"")</f>
+        <f t="shared" si="1"/>
         <v>0.28636884306987398</v>
       </c>
       <c r="K19" s="9">
-        <f>IFERROR(J19/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.5717527295777228E-2</v>
+        <f t="shared" si="2"/>
+        <v>1.5684443254773976E-2</v>
       </c>
       <c r="L19" s="12">
-        <f>F19/(1-(F19*(1+H19)-F19)/(F19*(1+H19)))</f>
+        <f t="shared" si="3"/>
         <v>169.06149999999997</v>
       </c>
       <c r="M19" s="12">
-        <f>F19/(1+I19-H19)</f>
+        <f t="shared" si="4"/>
         <v>107.00975396709855</v>
       </c>
       <c r="N19" s="12">
-        <f>L19-F19</f>
+        <f t="shared" si="5"/>
         <v>22.051499999999976</v>
       </c>
       <c r="O19" s="12">
-        <f>0.5*(M19-F19)</f>
+        <f t="shared" si="6"/>
         <v>-20.000123016450722</v>
       </c>
       <c r="P19" s="15">
-        <f>N19+O19</f>
+        <f t="shared" si="7"/>
         <v>2.0513769835492539</v>
       </c>
       <c r="Q19" s="12">
-        <f>MAX($P$2:$P$280)-P19</f>
+        <f t="shared" si="8"/>
         <v>101.57713304510406</v>
       </c>
       <c r="R19" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q19)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>9.8447354244184312E-3</v>
       </c>
       <c r="S19" s="9">
-        <f>Q19/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0.45924814709341422</v>
       </c>
     </row>
@@ -2129,7 +2129,7 @@
         <v>187.36</v>
       </c>
       <c r="G20" s="1">
-        <f>E20*F20</f>
+        <f t="shared" si="0"/>
         <v>1.8736000000000003E-20</v>
       </c>
       <c r="H20" s="11">
@@ -2140,43 +2140,43 @@
         <v>0.52980000000000005</v>
       </c>
       <c r="J20" s="9">
-        <f>IFERROR(H20/I20,"")</f>
+        <f t="shared" si="1"/>
         <v>8.7242692487602053E-2</v>
       </c>
       <c r="K20" s="9">
-        <f>IFERROR(J20/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.7883679866541976E-3</v>
+        <f t="shared" si="2"/>
+        <v>4.7782888845264923E-3</v>
       </c>
       <c r="L20" s="12">
-        <f>F20/(1-(F20*(1+H20)-F20)/(F20*(1+H20)))</f>
+        <f t="shared" si="3"/>
         <v>196.01999999999998</v>
       </c>
       <c r="M20" s="12">
-        <f>F20/(1+I20-H20)</f>
+        <f t="shared" si="4"/>
         <v>126.28921179127629</v>
       </c>
       <c r="N20" s="12">
-        <f>L20-F20</f>
+        <f t="shared" si="5"/>
         <v>8.6599999999999682</v>
       </c>
       <c r="O20" s="12">
-        <f>0.5*(M20-F20)</f>
+        <f t="shared" si="6"/>
         <v>-30.535394104361863</v>
       </c>
       <c r="P20" s="15">
-        <f>N20+O20</f>
+        <f t="shared" si="7"/>
         <v>-21.875394104361895</v>
       </c>
       <c r="Q20" s="12">
-        <f>MAX($P$2:$P$280)-P20</f>
+        <f t="shared" si="8"/>
         <v>125.50390413301523</v>
       </c>
       <c r="R20" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q20)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>7.9678796202240099E-3</v>
       </c>
       <c r="S20" s="9">
-        <f>Q20/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0.5674253023117275</v>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
         <v>169.34</v>
       </c>
       <c r="G21" s="1">
-        <f>E21*F21</f>
+        <f t="shared" si="0"/>
         <v>1.6934000000000002E-20</v>
       </c>
       <c r="H21" s="11">
@@ -2210,43 +2210,43 @@
         <v>0.4259</v>
       </c>
       <c r="J21" s="9">
-        <f>IFERROR(H21/I21,"")</f>
+        <f t="shared" si="1"/>
         <v>0.23479690068091102</v>
       </c>
       <c r="K21" s="9">
-        <f>IFERROR(J21/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.2886970020393072E-2</v>
+        <f t="shared" si="2"/>
+        <v>1.2859844058621913E-2</v>
       </c>
       <c r="L21" s="12">
-        <f>F21/(1-(F21*(1+H21)-F21)/(F21*(1+H21)))</f>
+        <f t="shared" si="3"/>
         <v>186.27400000000003</v>
       </c>
       <c r="M21" s="12">
-        <f>F21/(1+I21-H21)</f>
+        <f t="shared" si="4"/>
         <v>127.71702239987934</v>
       </c>
       <c r="N21" s="12">
-        <f>L21-F21</f>
+        <f t="shared" si="5"/>
         <v>16.934000000000026</v>
       </c>
       <c r="O21" s="12">
-        <f>0.5*(M21-F21)</f>
+        <f t="shared" si="6"/>
         <v>-20.811488800060332</v>
       </c>
       <c r="P21" s="15">
-        <f>N21+O21</f>
+        <f t="shared" si="7"/>
         <v>-3.8774888000603056</v>
       </c>
       <c r="Q21" s="12">
-        <f>MAX($P$2:$P$280)-P21</f>
+        <f t="shared" si="8"/>
         <v>107.50599882871363</v>
       </c>
       <c r="R21" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q21)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>9.3018065121488955E-3</v>
       </c>
       <c r="S21" s="9">
-        <f>Q21/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0.48605359575949542</v>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
         <v>113.58</v>
       </c>
       <c r="G22" s="1">
-        <f>E22*F22</f>
+        <f t="shared" si="0"/>
         <v>1.1358E-20</v>
       </c>
       <c r="H22" s="11">
@@ -2281,43 +2281,43 @@
         <v>0.16439999999999999</v>
       </c>
       <c r="J22" s="9">
-        <f>IFERROR(H22/I22,"")</f>
+        <f t="shared" si="1"/>
         <v>0.40540789496797319</v>
       </c>
       <c r="K22" s="9">
-        <f>IFERROR(J22/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.2251057715548812E-2</v>
+        <f t="shared" si="2"/>
+        <v>2.2204221155829606E-2</v>
       </c>
       <c r="L22" s="12">
-        <f>F22/(1-(F22*(1+H22)-F22)/(F22*(1+H22)))</f>
+        <f t="shared" si="3"/>
         <v>121.15000000000002</v>
       </c>
       <c r="M22" s="12">
-        <f>F22/(1+I22-H22)</f>
+        <f t="shared" si="4"/>
         <v>103.46609203186667</v>
       </c>
       <c r="N22" s="12">
-        <f>L22-F22</f>
+        <f t="shared" si="5"/>
         <v>7.5700000000000216</v>
       </c>
       <c r="O22" s="12">
-        <f>0.5*(M22-F22)</f>
+        <f t="shared" si="6"/>
         <v>-5.0569539840666664</v>
       </c>
       <c r="P22" s="15">
-        <f>N22+O22</f>
+        <f t="shared" si="7"/>
         <v>2.5130460159333552</v>
       </c>
       <c r="Q22" s="12">
-        <f>MAX($P$2:$P$280)-P22</f>
+        <f t="shared" si="8"/>
         <v>101.11546401271997</v>
       </c>
       <c r="R22" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q22)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>9.8896841325299516E-3</v>
       </c>
       <c r="S22" s="9">
-        <f>Q22/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0.45716085991236471</v>
       </c>
     </row>
@@ -2341,7 +2341,7 @@
         <v>64.349999999999994</v>
       </c>
       <c r="G23" s="1">
-        <f>E23*F23</f>
+        <f t="shared" si="0"/>
         <v>6.4349999999999995E-21</v>
       </c>
       <c r="H23" s="11">
@@ -2351,43 +2351,43 @@
         <v>0.67300000000000004</v>
       </c>
       <c r="J23" s="9">
-        <f>IFERROR(H23/I23,"")</f>
+        <f t="shared" si="1"/>
         <v>0.22288261515601782</v>
       </c>
       <c r="K23" s="9">
-        <f>IFERROR(J23/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.2233047247441474E-2</v>
+        <f t="shared" si="2"/>
+        <v>1.2207297736776536E-2</v>
       </c>
       <c r="L23" s="12">
-        <f>F23/(1-(F23*(1+H23)-F23)/(F23*(1+H23)))</f>
+        <f t="shared" si="3"/>
         <v>74.002499999999984</v>
       </c>
       <c r="M23" s="12">
-        <f>F23/(1+I23-H23)</f>
+        <f t="shared" si="4"/>
         <v>42.252133946158892</v>
       </c>
       <c r="N23" s="12">
-        <f>L23-F23</f>
+        <f t="shared" si="5"/>
         <v>9.6524999999999892</v>
       </c>
       <c r="O23" s="12">
-        <f>0.5*(M23-F23)</f>
+        <f t="shared" si="6"/>
         <v>-11.048933026920551</v>
       </c>
       <c r="P23" s="15">
-        <f>N23+O23</f>
+        <f t="shared" si="7"/>
         <v>-1.3964330269205618</v>
       </c>
       <c r="Q23" s="12">
-        <f>MAX($P$2:$P$280)-P23</f>
+        <f t="shared" si="8"/>
         <v>105.02494305557389</v>
       </c>
       <c r="R23" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q23)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.5215476524548141E-3</v>
+        <f t="shared" si="9"/>
+        <v>9.5215476524548124E-3</v>
       </c>
       <c r="S23" s="9">
-        <f>Q23/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0.47483630469710741</v>
       </c>
     </row>
@@ -2411,7 +2411,7 @@
         <v>20.82</v>
       </c>
       <c r="G24" s="1">
-        <f>E24*F24</f>
+        <f t="shared" si="0"/>
         <v>2.0820000000000001E-21</v>
       </c>
       <c r="H24" s="13">
@@ -2421,43 +2421,43 @@
         <v>0.7389</v>
       </c>
       <c r="J24" s="9">
-        <f>IFERROR(H24/I24,"")</f>
+        <f t="shared" si="1"/>
         <v>6.7668155366084726E-2</v>
       </c>
       <c r="K24" s="9">
-        <f>IFERROR(J24/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.7140076679424883E-3</v>
+        <f t="shared" si="2"/>
+        <v>3.7061900017370912E-3</v>
       </c>
       <c r="L24" s="12">
-        <f>F24/(1-(F24*(1+H24)-F24)/(F24*(1+H24)))</f>
+        <f t="shared" si="3"/>
         <v>21.861000000000001</v>
       </c>
       <c r="M24" s="12">
-        <f>F24/(1+I24-H24)</f>
+        <f t="shared" si="4"/>
         <v>12.327550476641601</v>
       </c>
       <c r="N24" s="12">
-        <f>L24-F24</f>
+        <f t="shared" si="5"/>
         <v>1.0410000000000004</v>
       </c>
       <c r="O24" s="12">
-        <f>0.5*(M24-F24)</f>
+        <f t="shared" si="6"/>
         <v>-4.2462247616791995</v>
       </c>
       <c r="P24" s="15">
-        <f>N24+O24</f>
+        <f t="shared" si="7"/>
         <v>-3.2052247616791991</v>
       </c>
       <c r="Q24" s="12">
-        <f>MAX($P$2:$P$280)-P24</f>
+        <f t="shared" si="8"/>
         <v>106.83373479033253</v>
       </c>
       <c r="R24" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q24)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>9.3603392408077718E-3</v>
       </c>
       <c r="S24" s="9">
-        <f>Q24/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0.48301417138583286</v>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
         <v>13.04</v>
       </c>
       <c r="G25" s="1">
-        <f>E25*F25</f>
+        <f t="shared" si="0"/>
         <v>1.304E-21</v>
       </c>
       <c r="H25" s="11">
@@ -2492,43 +2492,43 @@
         <v>0.30159999999999998</v>
       </c>
       <c r="J25" s="9">
-        <f>IFERROR(H25/I25,"")</f>
+        <f t="shared" si="1"/>
         <v>0.17290198694895167</v>
       </c>
       <c r="K25" s="9">
-        <f>IFERROR(J25/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>9.4898302141800187E-3</v>
+        <f t="shared" si="2"/>
+        <v>9.4698549390612539E-3</v>
       </c>
       <c r="L25" s="12">
-        <f>F25/(1-(F25*(1+H25)-F25)/(F25*(1+H25)))</f>
+        <f t="shared" si="3"/>
         <v>13.72</v>
       </c>
       <c r="M25" s="12">
-        <f>F25/(1+I25-H25)</f>
+        <f t="shared" si="4"/>
         <v>10.436569040286594</v>
       </c>
       <c r="N25" s="12">
-        <f>L25-F25</f>
+        <f t="shared" si="5"/>
         <v>0.68000000000000149</v>
       </c>
       <c r="O25" s="12">
-        <f>0.5*(M25-F25)</f>
+        <f t="shared" si="6"/>
         <v>-1.3017154798567026</v>
       </c>
       <c r="P25" s="15">
-        <f>N25+O25</f>
+        <f t="shared" si="7"/>
         <v>-0.62171547985670106</v>
       </c>
       <c r="Q25" s="12">
-        <f>MAX($P$2:$P$280)-P25</f>
+        <f t="shared" si="8"/>
         <v>104.25022550851003</v>
       </c>
       <c r="R25" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q25)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>9.5923053894820514E-3</v>
       </c>
       <c r="S25" s="9">
-        <f>Q25/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0.47133366992741127</v>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
         <v>11.05</v>
       </c>
       <c r="G26" s="1">
-        <f>E26*F26</f>
+        <f t="shared" si="0"/>
         <v>1.1050000000000002E-21</v>
       </c>
       <c r="H26" s="11">
@@ -2562,43 +2562,43 @@
         <v>0.72170000000000001</v>
       </c>
       <c r="J26" s="9">
-        <f>IFERROR(H26/I26,"")</f>
+        <f t="shared" si="1"/>
         <v>6.9280864625190522E-2</v>
       </c>
       <c r="K26" s="9">
-        <f>IFERROR(J26/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.8025221918286051E-3</v>
+        <f t="shared" si="2"/>
+        <v>3.7945182101753309E-3</v>
       </c>
       <c r="L26" s="12">
-        <f>F26/(1-(F26*(1+H26)-F26)/(F26*(1+H26)))</f>
+        <f t="shared" si="3"/>
         <v>11.602500000000001</v>
       </c>
       <c r="M26" s="12">
-        <f>F26/(1+I26-H26)</f>
+        <f t="shared" si="4"/>
         <v>6.6100376861877139</v>
       </c>
       <c r="N26" s="12">
-        <f>L26-F26</f>
+        <f t="shared" si="5"/>
         <v>0.55250000000000021</v>
       </c>
       <c r="O26" s="12">
-        <f>0.5*(M26-F26)</f>
+        <f t="shared" si="6"/>
         <v>-2.2199811569061434</v>
       </c>
       <c r="P26" s="15">
-        <f>N26+O26</f>
+        <f t="shared" si="7"/>
         <v>-1.6674811569061432</v>
       </c>
       <c r="Q26" s="12">
-        <f>MAX($P$2:$P$280)-P26</f>
+        <f t="shared" si="8"/>
         <v>105.29599118555947</v>
       </c>
       <c r="R26" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q26)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.4970377194867252E-3</v>
+        <f t="shared" si="9"/>
+        <v>9.4970377194867235E-3</v>
       </c>
       <c r="S26" s="9">
-        <f>Q26/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0.47606176113338761</v>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
         <v>10.47</v>
       </c>
       <c r="G27" s="1">
-        <f>E27*F27</f>
+        <f t="shared" si="0"/>
         <v>1.0470000000000001E-21</v>
       </c>
       <c r="H27" s="11">
@@ -2632,43 +2632,43 @@
         <v>0.85599999999999998</v>
       </c>
       <c r="J27" s="9">
-        <f>IFERROR(H27/I27,"")</f>
+        <f t="shared" si="1"/>
         <v>5.8411214953271035E-2</v>
       </c>
       <c r="K27" s="9">
-        <f>IFERROR(J27/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.2059348900031598E-3</v>
+        <f t="shared" si="2"/>
+        <v>3.1991866732284306E-3</v>
       </c>
       <c r="L27" s="12">
-        <f>F27/(1-(F27*(1+H27)-F27)/(F27*(1+H27)))</f>
+        <f t="shared" si="3"/>
         <v>10.993500000000001</v>
       </c>
       <c r="M27" s="12">
-        <f>F27/(1+I27-H27)</f>
+        <f t="shared" si="4"/>
         <v>5.7973421926910307</v>
       </c>
       <c r="N27" s="12">
-        <f>L27-F27</f>
+        <f t="shared" si="5"/>
         <v>0.5235000000000003</v>
       </c>
       <c r="O27" s="12">
-        <f>0.5*(M27-F27)</f>
+        <f t="shared" si="6"/>
         <v>-2.336328903654485</v>
       </c>
       <c r="P27" s="15">
-        <f>N27+O27</f>
+        <f t="shared" si="7"/>
         <v>-1.8128289036544847</v>
       </c>
       <c r="Q27" s="12">
-        <f>MAX($P$2:$P$280)-P27</f>
+        <f t="shared" si="8"/>
         <v>105.44133893230781</v>
       </c>
       <c r="R27" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q27)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>9.4839463357155301E-3</v>
       </c>
       <c r="S27" s="9">
-        <f>Q27/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0.47671890395064692</v>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="D28" s="8">
         <f ca="1">TODAY()-20</f>
-        <v>45610</v>
+        <v>45616</v>
       </c>
       <c r="E28" s="2">
         <v>1E-35</v>
@@ -2693,7 +2693,7 @@
         <v>2742.9</v>
       </c>
       <c r="G28" s="1">
-        <f>E28*F28</f>
+        <f t="shared" si="0"/>
         <v>2.7429E-32</v>
       </c>
       <c r="H28" s="11">
@@ -2703,43 +2703,43 @@
         <v>0.5</v>
       </c>
       <c r="J28" s="9">
-        <f>IFERROR(H28/I28,"")</f>
+        <f t="shared" si="1"/>
         <v>0.2</v>
       </c>
       <c r="K28" s="9">
-        <f>IFERROR(J28/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.0977121063370818E-2</v>
+        <f t="shared" si="2"/>
+        <v>1.0954015169134147E-2</v>
       </c>
       <c r="L28" s="12">
-        <f>F28/(1-(F28*(1+H28)-F28)/(F28*(1+H28)))</f>
+        <f t="shared" si="3"/>
         <v>3017.1900000000005</v>
       </c>
       <c r="M28" s="12">
-        <f>F28/(1+I28-H28)</f>
+        <f t="shared" si="4"/>
         <v>1959.214285714286</v>
       </c>
       <c r="N28" s="12">
-        <f>L28-F28</f>
+        <f t="shared" si="5"/>
         <v>274.29000000000042</v>
       </c>
       <c r="O28" s="12">
-        <f>0.5*(M28-F28)</f>
+        <f t="shared" si="6"/>
         <v>-391.84285714285704</v>
       </c>
       <c r="P28" s="15">
-        <f>N28+O28</f>
+        <f t="shared" si="7"/>
         <v>-117.55285714285662</v>
       </c>
       <c r="Q28" s="12">
-        <f>MAX($P$2:$P$280)-P28</f>
+        <f t="shared" si="8"/>
         <v>221.18136717150995</v>
       </c>
       <c r="R28" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q28)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>4.5211765022890619E-3</v>
+        <f t="shared" si="9"/>
+        <v>4.5211765022890611E-3</v>
       </c>
       <c r="S28" s="9">
-        <f>Q28/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
         <v>86.6</v>
       </c>
       <c r="G29" s="1">
-        <f>E29*F29</f>
+        <f t="shared" si="0"/>
         <v>8.6599999999999988E-34</v>
       </c>
       <c r="H29" s="11">
@@ -2773,43 +2773,43 @@
         <v>0.17249999999999999</v>
       </c>
       <c r="J29" s="9">
-        <f>IFERROR(H29/I29,"")</f>
+        <f t="shared" si="1"/>
         <v>0.40579710144927544</v>
       </c>
       <c r="K29" s="9">
-        <f>IFERROR(J29/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.2272419548868331E-2</v>
+        <f t="shared" si="2"/>
+        <v>2.2225538024330155E-2</v>
       </c>
       <c r="L29" s="12">
-        <f>F29/(1-(F29*(1+H29)-F29)/(F29*(1+H29)))</f>
+        <f t="shared" si="3"/>
         <v>92.662000000000006</v>
       </c>
       <c r="M29" s="12">
-        <f>F29/(1+I29-H29)</f>
+        <f t="shared" si="4"/>
         <v>78.548752834467123</v>
       </c>
       <c r="N29" s="12">
-        <f>L29-F29</f>
+        <f t="shared" si="5"/>
         <v>6.0620000000000118</v>
       </c>
       <c r="O29" s="12">
-        <f>0.5*(M29-F29)</f>
+        <f t="shared" si="6"/>
         <v>-4.0256235827664355</v>
       </c>
       <c r="P29" s="15">
-        <f>N29+O29</f>
+        <f t="shared" si="7"/>
         <v>2.0363764172335763</v>
       </c>
       <c r="Q29" s="12">
-        <f>MAX($P$2:$P$280)-P29</f>
+        <f t="shared" si="8"/>
         <v>101.59213361141974</v>
       </c>
       <c r="R29" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q29)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>9.8432818019641658E-3</v>
       </c>
       <c r="S29" s="9">
-        <f>Q29/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0.45931596730136171</v>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
         <v>56</v>
       </c>
       <c r="G30" s="1">
-        <f>E30*F30</f>
+        <f t="shared" si="0"/>
         <v>5.5999999999999999E-34</v>
       </c>
       <c r="H30" s="11">
@@ -2843,43 +2843,43 @@
         <v>0.19</v>
       </c>
       <c r="J30" s="9">
-        <f>IFERROR(H30/I30,"")</f>
+        <f t="shared" si="1"/>
         <v>0.36842105263157898</v>
       </c>
       <c r="K30" s="9">
-        <f>IFERROR(J30/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.0221012485156772E-2</v>
+        <f t="shared" si="2"/>
+        <v>2.0178448995773427E-2</v>
       </c>
       <c r="L30" s="12">
-        <f>F30/(1-(F30*(1+H30)-F30)/(F30*(1+H30)))</f>
+        <f t="shared" si="3"/>
         <v>59.92</v>
       </c>
       <c r="M30" s="12">
-        <f>F30/(1+I30-H30)</f>
+        <f t="shared" si="4"/>
         <v>50.000000000000007</v>
       </c>
       <c r="N30" s="12">
-        <f>L30-F30</f>
+        <f t="shared" si="5"/>
         <v>3.9200000000000017</v>
       </c>
       <c r="O30" s="12">
-        <f>0.5*(M30-F30)</f>
+        <f t="shared" si="6"/>
         <v>-2.9999999999999964</v>
       </c>
       <c r="P30" s="15">
-        <f>N30+O30</f>
+        <f t="shared" si="7"/>
         <v>0.92000000000000526</v>
       </c>
       <c r="Q30" s="12">
-        <f>MAX($P$2:$P$280)-P30</f>
+        <f t="shared" si="8"/>
         <v>102.70851002865332</v>
       </c>
       <c r="R30" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q30)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>9.7362915665023565E-3</v>
       </c>
       <c r="S30" s="9">
-        <f>Q30/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0.46436330212666782</v>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
         <v>20.399999999999999</v>
       </c>
       <c r="G31" s="1">
-        <f>E31*F31</f>
+        <f t="shared" si="0"/>
         <v>2.0399999999999999E-34</v>
       </c>
       <c r="H31" s="11">
@@ -2913,42 +2913,42 @@
         <v>0.15</v>
       </c>
       <c r="J31" s="9">
-        <f>IFERROR(H31/I31,"")</f>
+        <f t="shared" si="1"/>
         <v>0.66666666666666674</v>
       </c>
       <c r="K31" s="9">
-        <f>IFERROR(J31/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.6590403544569397E-2</v>
+        <f t="shared" si="2"/>
+        <v>3.6513383897113824E-2</v>
       </c>
       <c r="L31" s="12">
         <v>21.2</v>
       </c>
       <c r="M31" s="12">
-        <f>F31/(1+I31-H31)</f>
+        <f t="shared" si="4"/>
         <v>19.428571428571431</v>
       </c>
       <c r="N31" s="12">
-        <f>L31-F31</f>
+        <f t="shared" si="5"/>
         <v>0.80000000000000071</v>
       </c>
       <c r="O31" s="12">
-        <f>0.5*(M31-F31)</f>
+        <f t="shared" si="6"/>
         <v>-0.48571428571428399</v>
       </c>
       <c r="P31" s="15">
-        <f>N31+O31</f>
+        <f t="shared" si="7"/>
         <v>0.31428571428571672</v>
       </c>
       <c r="Q31" s="12">
-        <f>MAX($P$2:$P$280)-P31</f>
+        <f t="shared" si="8"/>
         <v>103.31422431436761</v>
       </c>
       <c r="R31" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q31)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>9.6792092921993977E-3</v>
       </c>
       <c r="S31" s="9">
-        <f>Q31/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0.46710184332234006</v>
       </c>
     </row>
@@ -2972,7 +2972,7 @@
         <v>47.42</v>
       </c>
       <c r="G32" s="1">
-        <f>E32*F32</f>
+        <f t="shared" si="0"/>
         <v>4.7420000000000006E-44</v>
       </c>
       <c r="H32" s="11">
@@ -2982,43 +2982,43 @@
         <v>0.4</v>
       </c>
       <c r="J32" s="9">
-        <f>IFERROR(H32/I32,"")</f>
+        <f t="shared" si="1"/>
         <v>0.17500000000000002</v>
       </c>
       <c r="K32" s="9">
-        <f>IFERROR(J32/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>9.6049809304494665E-3</v>
+        <f t="shared" si="2"/>
+        <v>9.5847632729923783E-3</v>
       </c>
       <c r="L32" s="12">
-        <f>F32/(1-(F32*(1+H32)-F32)/(F32*(1+H32)))</f>
+        <f t="shared" ref="L32:L41" si="11">F32/(1-(F32*(1+H32)-F32)/(F32*(1+H32)))</f>
         <v>50.739400000000003</v>
       </c>
       <c r="M32" s="12">
-        <f>F32/(1+I32-H32)</f>
+        <f t="shared" si="4"/>
         <v>35.654135338345867</v>
       </c>
       <c r="N32" s="12">
-        <f>L32-F32</f>
+        <f t="shared" si="5"/>
         <v>3.3194000000000017</v>
       </c>
       <c r="O32" s="12">
-        <f>0.5*(M32-F32)</f>
+        <f t="shared" si="6"/>
         <v>-5.8829323308270673</v>
       </c>
       <c r="P32" s="15">
-        <f>N32+O32</f>
+        <f t="shared" si="7"/>
         <v>-2.5635323308270657</v>
       </c>
       <c r="Q32" s="12">
-        <f>MAX($P$2:$P$280)-P32</f>
+        <f t="shared" si="8"/>
         <v>106.19204235948038</v>
       </c>
       <c r="R32" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q32)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>9.4169014719088714E-3</v>
       </c>
       <c r="S32" s="9">
-        <f>Q32/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0.48011296664576736</v>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
         <v>41.8</v>
       </c>
       <c r="G33" s="1">
-        <f>E33*F33</f>
+        <f t="shared" si="0"/>
         <v>4.1799999999999994E-44</v>
       </c>
       <c r="H33" s="11">
@@ -3052,43 +3052,43 @@
         <v>0.4</v>
       </c>
       <c r="J33" s="9">
-        <f>IFERROR(H33/I33,"")</f>
+        <f t="shared" si="1"/>
         <v>0.17500000000000002</v>
       </c>
       <c r="K33" s="9">
-        <f>IFERROR(J33/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>9.6049809304494665E-3</v>
+        <f t="shared" si="2"/>
+        <v>9.5847632729923783E-3</v>
       </c>
       <c r="L33" s="12">
-        <f>F33/(1-(F33*(1+H33)-F33)/(F33*(1+H33)))</f>
+        <f t="shared" si="11"/>
         <v>44.725999999999999</v>
       </c>
       <c r="M33" s="12">
-        <f>F33/(1+I33-H33)</f>
+        <f t="shared" si="4"/>
         <v>31.428571428571431</v>
       </c>
       <c r="N33" s="12">
-        <f>L33-F33</f>
+        <f t="shared" si="5"/>
         <v>2.9260000000000019</v>
       </c>
       <c r="O33" s="12">
-        <f>0.5*(M33-F33)</f>
+        <f t="shared" si="6"/>
         <v>-5.1857142857142833</v>
       </c>
       <c r="P33" s="15">
-        <f>N33+O33</f>
+        <f t="shared" si="7"/>
         <v>-2.2597142857142813</v>
       </c>
       <c r="Q33" s="12">
-        <f>MAX($P$2:$P$280)-P33</f>
+        <f t="shared" si="8"/>
         <v>105.8882243143676</v>
       </c>
       <c r="R33" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q33)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>9.4439207614922058E-3</v>
       </c>
       <c r="S33" s="9">
-        <f>Q33/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0.47873935163923209</v>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
         <v>153.7552</v>
       </c>
       <c r="G34" s="1">
-        <f>E34*F34</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H34" s="11">
@@ -3122,43 +3122,43 @@
         <v>0.19</v>
       </c>
       <c r="J34" s="9">
-        <f>IFERROR(H34/I34,"")</f>
+        <f t="shared" si="1"/>
         <v>0.36842105263157898</v>
       </c>
       <c r="K34" s="9">
-        <f>IFERROR(J34/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.0221012485156772E-2</v>
+        <f t="shared" si="2"/>
+        <v>2.0178448995773427E-2</v>
       </c>
       <c r="L34" s="12">
-        <f>F34/(1-(F34*(1+H34)-F34)/(F34*(1+H34)))</f>
+        <f t="shared" si="11"/>
         <v>164.51806400000001</v>
       </c>
       <c r="M34" s="12">
-        <f>F34/(1+I34-H34)</f>
+        <f t="shared" si="4"/>
         <v>137.28142857142859</v>
       </c>
       <c r="N34" s="12">
-        <f>L34-F34</f>
+        <f t="shared" si="5"/>
         <v>10.762864000000008</v>
       </c>
       <c r="O34" s="12">
-        <f>0.5*(M34-F34)</f>
+        <f t="shared" si="6"/>
         <v>-8.2368857142857053</v>
       </c>
       <c r="P34" s="15">
-        <f>N34+O34</f>
+        <f t="shared" si="7"/>
         <v>2.5259782857143023</v>
       </c>
       <c r="Q34" s="12">
-        <f>MAX($P$2:$P$280)-P34</f>
+        <f t="shared" si="8"/>
         <v>101.10253174293902</v>
       </c>
       <c r="R34" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q34)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.8909491459875324E-3</v>
+        <f t="shared" si="9"/>
+        <v>9.8909491459875307E-3</v>
       </c>
       <c r="S34" s="9">
-        <f>Q34/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0.45710239083810988</v>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
         <v>133.53</v>
       </c>
       <c r="G35" s="1">
-        <f>E35*F35</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H35" s="11">
@@ -3192,43 +3192,43 @@
         <v>0.2</v>
       </c>
       <c r="J35" s="9">
-        <f>IFERROR(H35/I35,"")</f>
+        <f t="shared" si="1"/>
         <v>0.35000000000000003</v>
       </c>
       <c r="K35" s="9">
-        <f>IFERROR(J35/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.9209961860898933E-2</v>
+        <f t="shared" si="2"/>
+        <v>1.9169526545984757E-2</v>
       </c>
       <c r="L35" s="12">
-        <f>F35/(1-(F35*(1+H35)-F35)/(F35*(1+H35)))</f>
+        <f t="shared" si="11"/>
         <v>142.87710000000001</v>
       </c>
       <c r="M35" s="12">
-        <f>F35/(1+I35-H35)</f>
+        <f t="shared" si="4"/>
         <v>118.16814159292036</v>
       </c>
       <c r="N35" s="12">
-        <f>L35-F35</f>
+        <f t="shared" si="5"/>
         <v>9.3471000000000117</v>
       </c>
       <c r="O35" s="12">
-        <f>0.5*(M35-F35)</f>
+        <f t="shared" si="6"/>
         <v>-7.6809292035398187</v>
       </c>
       <c r="P35" s="15">
-        <f>N35+O35</f>
+        <f t="shared" si="7"/>
         <v>1.6661707964601931</v>
       </c>
       <c r="Q35" s="12">
-        <f>MAX($P$2:$P$280)-P35</f>
+        <f t="shared" si="8"/>
         <v>101.96233923219313</v>
       </c>
       <c r="R35" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q35)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>9.8075427410777224E-3</v>
       </c>
       <c r="S35" s="9">
-        <f>Q35/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0.46098973225501771</v>
       </c>
     </row>
@@ -3252,7 +3252,7 @@
         <v>39.56</v>
       </c>
       <c r="G36" s="1">
-        <f>E36*F36</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H36" s="11">
@@ -3262,43 +3262,43 @@
         <v>0.2</v>
       </c>
       <c r="J36" s="9">
-        <f>IFERROR(H36/I36,"")</f>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
       <c r="K36" s="9">
-        <f>IFERROR(J36/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.7442802658427044E-2</v>
+        <f t="shared" si="2"/>
+        <v>2.7385037922835365E-2</v>
       </c>
       <c r="L36" s="12">
-        <f>F36/(1-(F36*(1+H36)-F36)/(F36*(1+H36)))</f>
+        <f t="shared" si="11"/>
         <v>43.516000000000005</v>
       </c>
       <c r="M36" s="12">
-        <f>F36/(1+I36-H36)</f>
+        <f t="shared" si="4"/>
         <v>35.963636363636368</v>
       </c>
       <c r="N36" s="12">
-        <f>L36-F36</f>
+        <f t="shared" si="5"/>
         <v>3.9560000000000031</v>
       </c>
       <c r="O36" s="12">
-        <f>0.5*(M36-F36)</f>
+        <f t="shared" si="6"/>
         <v>-1.798181818181817</v>
       </c>
       <c r="P36" s="15">
-        <f>N36+O36</f>
+        <f t="shared" si="7"/>
         <v>2.1578181818181861</v>
       </c>
       <c r="Q36" s="12">
-        <f>MAX($P$2:$P$280)-P36</f>
+        <f t="shared" si="8"/>
         <v>101.47069184683514</v>
       </c>
       <c r="R36" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q36)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>9.855062400771341E-3</v>
       </c>
       <c r="S36" s="9">
-        <f>Q36/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0.4587669076489253</v>
       </c>
     </row>
@@ -3322,7 +3322,7 @@
         <v>26.63</v>
       </c>
       <c r="G37" s="1">
-        <f>E37*F37</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H37" s="11">
@@ -3332,43 +3332,43 @@
         <v>0.2</v>
       </c>
       <c r="J37" s="9">
-        <f>IFERROR(H37/I37,"")</f>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
       <c r="K37" s="9">
-        <f>IFERROR(J37/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.7442802658427044E-2</v>
+        <f t="shared" si="2"/>
+        <v>2.7385037922835365E-2</v>
       </c>
       <c r="L37" s="12">
-        <f>F37/(1-(F37*(1+H37)-F37)/(F37*(1+H37)))</f>
+        <f t="shared" si="11"/>
         <v>29.293000000000003</v>
       </c>
       <c r="M37" s="12">
-        <f>F37/(1+I37-H37)</f>
+        <f t="shared" si="4"/>
         <v>24.209090909090911</v>
       </c>
       <c r="N37" s="12">
-        <f>L37-F37</f>
+        <f t="shared" si="5"/>
         <v>2.6630000000000038</v>
       </c>
       <c r="O37" s="12">
-        <f>0.5*(M37-F37)</f>
+        <f t="shared" si="6"/>
         <v>-1.2104545454545441</v>
       </c>
       <c r="P37" s="15">
-        <f>N37+O37</f>
+        <f t="shared" si="7"/>
         <v>1.4525454545454597</v>
       </c>
       <c r="Q37" s="12">
-        <f>MAX($P$2:$P$280)-P37</f>
+        <f t="shared" si="8"/>
         <v>102.17596457410787</v>
       </c>
       <c r="R37" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q37)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.7870375304820682E-3</v>
+        <f t="shared" si="9"/>
+        <v>9.7870375304820699E-3</v>
       </c>
       <c r="S37" s="9">
-        <f>Q37/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0.46195557013117605</v>
       </c>
     </row>
@@ -3386,60 +3386,60 @@
         <v>45627</v>
       </c>
       <c r="E38" s="2">
-        <v>0</v>
+        <v>0.9385</v>
       </c>
       <c r="F38" s="1">
-        <v>22.65</v>
+        <v>21.31</v>
       </c>
       <c r="G38" s="1">
-        <f>E38*F38</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>19.999434999999998</v>
       </c>
       <c r="H38" s="11">
-        <v>0.1</v>
+        <f>L38/F38-1</f>
+        <v>0.24730173627404972</v>
       </c>
       <c r="I38" s="11">
-        <v>0.2</v>
+        <v>0.45929999999999999</v>
       </c>
       <c r="J38" s="9">
-        <f>IFERROR(H38/I38,"")</f>
-        <v>0.5</v>
+        <f t="shared" si="1"/>
+        <v>0.53843182293500924</v>
       </c>
       <c r="K38" s="9">
-        <f>IFERROR(J38/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.7442802658427044E-2</v>
+        <f t="shared" si="2"/>
+        <v>2.9489951779873208E-2</v>
       </c>
       <c r="L38" s="12">
-        <f>F38/(1-(F38*(1+H38)-F38)/(F38*(1+H38)))</f>
-        <v>24.914999999999999</v>
+        <v>26.58</v>
       </c>
       <c r="M38" s="12">
-        <f>F38/(1+I38-H38)</f>
-        <v>20.590909090909093</v>
+        <f t="shared" si="4"/>
+        <v>17.582533439023546</v>
       </c>
       <c r="N38" s="12">
-        <f>L38-F38</f>
-        <v>2.2650000000000006</v>
+        <f t="shared" si="5"/>
+        <v>5.27</v>
       </c>
       <c r="O38" s="12">
-        <f>0.5*(M38-F38)</f>
-        <v>-1.0295454545454525</v>
+        <f t="shared" si="6"/>
+        <v>-1.8637332804882263</v>
       </c>
       <c r="P38" s="15">
-        <f>N38+O38</f>
-        <v>1.235454545454548</v>
+        <f t="shared" si="7"/>
+        <v>3.4062667195117733</v>
       </c>
       <c r="Q38" s="12">
-        <f>MAX($P$2:$P$280)-P38</f>
-        <v>102.39305548319878</v>
+        <f t="shared" si="8"/>
+        <v>100.22224330914155</v>
       </c>
       <c r="R38" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q38)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.7662873256486177E-3</v>
+        <f t="shared" si="9"/>
+        <v>9.9778249516471081E-3</v>
       </c>
       <c r="S38" s="9">
-        <f>Q38/MAX($Q$2:$Q$28)</f>
-        <v>0.46293707644821847</v>
+        <f t="shared" si="10"/>
+        <v>0.4531224514559879</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
@@ -3462,7 +3462,7 @@
         <v>59.17</v>
       </c>
       <c r="G39" s="1">
-        <f>E39*F39</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H39" s="11">
@@ -3472,43 +3472,43 @@
         <v>0.2</v>
       </c>
       <c r="J39" s="9">
-        <f>IFERROR(H39/I39,"")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="K39" s="9">
-        <f>IFERROR(J39/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>5.4885605316854089E-2</v>
+        <f t="shared" si="2"/>
+        <v>5.4770075845670729E-2</v>
       </c>
       <c r="L39" s="12">
-        <f>F39/(1-(F39*(1+H39)-F39)/(F39*(1+H39)))</f>
+        <f t="shared" si="11"/>
         <v>71.004000000000005</v>
       </c>
       <c r="M39" s="12">
-        <f>F39/(1+I39-H39)</f>
+        <f t="shared" si="4"/>
         <v>59.17</v>
       </c>
       <c r="N39" s="12">
-        <f>L39-F39</f>
+        <f t="shared" si="5"/>
         <v>11.834000000000003</v>
       </c>
       <c r="O39" s="12">
-        <f>0.5*(M39-F39)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P39" s="15">
-        <f>N39+O39</f>
+        <f t="shared" si="7"/>
         <v>11.834000000000003</v>
       </c>
       <c r="Q39" s="12">
-        <f>MAX($P$2:$P$280)-P39</f>
+        <f t="shared" si="8"/>
         <v>91.79451002865332</v>
       </c>
       <c r="R39" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q39)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>1.0893897681766084E-2</v>
       </c>
       <c r="S39" s="9">
-        <f>Q39/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0.41501918178068498</v>
       </c>
     </row>
@@ -3532,7 +3532,7 @@
         <v>19.309999999999999</v>
       </c>
       <c r="G40" s="1">
-        <f>E40*F40</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H40" s="11">
@@ -3542,43 +3542,43 @@
         <v>0.2</v>
       </c>
       <c r="J40" s="9">
-        <f>IFERROR(H40/I40,"")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="K40" s="9">
-        <f>IFERROR(J40/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>5.4885605316854089E-2</v>
+        <f t="shared" si="2"/>
+        <v>5.4770075845670729E-2</v>
       </c>
       <c r="L40" s="12">
-        <f>F40/(1-(F40*(1+H40)-F40)/(F40*(1+H40)))</f>
+        <f t="shared" si="11"/>
         <v>23.171999999999997</v>
       </c>
       <c r="M40" s="12">
-        <f>F40/(1+I40-H40)</f>
+        <f t="shared" si="4"/>
         <v>19.309999999999999</v>
       </c>
       <c r="N40" s="12">
-        <f>L40-F40</f>
+        <f t="shared" si="5"/>
         <v>3.8619999999999983</v>
       </c>
       <c r="O40" s="12">
-        <f>0.5*(M40-F40)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P40" s="15">
-        <f>N40+O40</f>
+        <f t="shared" si="7"/>
         <v>3.8619999999999983</v>
       </c>
       <c r="Q40" s="12">
-        <f>MAX($P$2:$P$280)-P40</f>
+        <f t="shared" si="8"/>
         <v>99.766510028653329</v>
       </c>
       <c r="R40" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q40)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>1.002340364229235E-2</v>
       </c>
       <c r="S40" s="9">
-        <f>Q40/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0.45106200085693343</v>
       </c>
     </row>
@@ -3602,7 +3602,7 @@
         <v>323.75</v>
       </c>
       <c r="G41" s="1">
-        <f>E41*F41</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H41" s="11">
@@ -3612,49 +3612,49 @@
         <v>0.2</v>
       </c>
       <c r="J41" s="9">
-        <f>IFERROR(H41/I41,"")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="K41" s="9">
-        <f>IFERROR(J41/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>5.4885605316854089E-2</v>
+        <f t="shared" si="2"/>
+        <v>5.4770075845670729E-2</v>
       </c>
       <c r="L41" s="12">
-        <f>F41/(1-(F41*(1+H41)-F41)/(F41*(1+H41)))</f>
+        <f t="shared" si="11"/>
         <v>388.5</v>
       </c>
       <c r="M41" s="12">
-        <f>F41/(1+I41-H41)</f>
+        <f t="shared" si="4"/>
         <v>323.75</v>
       </c>
       <c r="N41" s="12">
-        <f>L41-F41</f>
+        <f t="shared" si="5"/>
         <v>64.75</v>
       </c>
       <c r="O41" s="12">
-        <f>0.5*(M41-F41)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P41" s="15">
-        <f>N41+O41</f>
+        <f t="shared" si="7"/>
         <v>64.75</v>
       </c>
       <c r="Q41" s="12">
-        <f>MAX($P$2:$P$280)-P41</f>
+        <f t="shared" si="8"/>
         <v>38.878510028653324</v>
       </c>
       <c r="R41" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q41)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>2.572115030290522E-2</v>
       </c>
       <c r="S41" s="9">
-        <f>Q41/MAX($Q$2:$Q$28)</f>
+        <f t="shared" si="10"/>
         <v>0.17577660598555703</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:S33" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S38">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S41">
       <sortCondition descending="1" ref="E1:E33"/>
     </sortState>
   </autoFilter>

--- a/Open Positions.xlsx
+++ b/Open Positions.xlsx
@@ -1,25 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\StockSillines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6861DC2-F36E-494A-A4E6-92F19D7A78B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF8447AA-5C45-4A34-92AF-8624794E4227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Positions" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Positions!$A$1:$S$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Positions!$A$1:$S$41</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="8" r:id="rId3"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="109">
   <si>
     <t>Name</t>
   </si>
@@ -198,12 +201,6 @@
     <t>Maxeon Solar</t>
   </si>
   <si>
-    <t>SEDG</t>
-  </si>
-  <si>
-    <t>SolarEdge</t>
-  </si>
-  <si>
     <t>SolarWinds</t>
   </si>
   <si>
@@ -355,6 +352,24 @@
   </si>
   <si>
     <t>HCA Healthcare</t>
+  </si>
+  <si>
+    <t>YPF</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Initial Volume $</t>
+  </si>
+  <si>
+    <t>$%</t>
+  </si>
+  <si>
+    <t>WK05</t>
   </si>
 </sst>
 </file>
@@ -366,7 +381,7 @@
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -381,8 +396,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -425,12 +448,36 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -440,7 +487,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -481,13 +528,45 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="2" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="6">
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -498,6 +577,1069 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="samuel walton" refreshedDate="45685.263780324072" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="40" xr:uid="{B79BBC45-DF34-46CE-BF36-02BCF50A32DD}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:S41" sheet="Positions"/>
+  </cacheSource>
+  <cacheFields count="19">
+    <cacheField name="Chapter" numFmtId="0">
+      <sharedItems count="9">
+        <s v="Banking"/>
+        <s v="Energy"/>
+        <s v="US Consumer"/>
+        <s v="Tech"/>
+        <s v="Asia Consumer"/>
+        <s v="Forex"/>
+        <s v="Automotive"/>
+        <s v="Industrials"/>
+        <s v="Health"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Name" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Ticker" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Date" numFmtId="165">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2024-06-17T00:00:00" maxDate="2025-01-09T00:00:00"/>
+    </cacheField>
+    <cacheField name="Volume" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="9.9999999999999998E-20" maxValue="1.9595"/>
+    </cacheField>
+    <cacheField name="Price" numFmtId="44">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="10.92" maxValue="2742.9"/>
+    </cacheField>
+    <cacheField name="Value" numFmtId="44">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="1.092E-18" maxValue="89.991048000000006"/>
+    </cacheField>
+    <cacheField name="Expected Return QoQ%" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.3206831119544589E-2" maxValue="1"/>
+    </cacheField>
+    <cacheField name="Volatility" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.15" maxValue="1.8652"/>
+    </cacheField>
+    <cacheField name="Ranking" numFmtId="9">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="6.2678050433266491E-2" maxValue="1"/>
+    </cacheField>
+    <cacheField name="Mix %" numFmtId="9">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.3695067959548818E-3" maxValue="5.3758959837820829E-2"/>
+    </cacheField>
+    <cacheField name="Target Price" numFmtId="44">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="11.602500000000001" maxValue="3017.1900000000005"/>
+    </cacheField>
+    <cacheField name="Tolerance" numFmtId="44">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="5.8546000428908433" maxValue="1959.214285714286"/>
+    </cacheField>
+    <cacheField name="Unit Profit" numFmtId="44">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.55250000000000021" maxValue="274.29000000000042"/>
+    </cacheField>
+    <cacheField name="Unit Half Loss" numFmtId="44">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-391.84285714285704" maxValue="0"/>
+    </cacheField>
+    <cacheField name="Balance Risk" numFmtId="44">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-117.55285714285662" maxValue="114.13244508118439"/>
+    </cacheField>
+    <cacheField name="Normalized Risk" numFmtId="44">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="231.68530222404101"/>
+    </cacheField>
+    <cacheField name="Risk Mix" numFmtId="9">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="2.2382348581474875E-2"/>
+    </cacheField>
+    <cacheField name="Normalized Risk %" numFmtId="9">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="1.6176498268314992"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="40">
+  <r>
+    <x v="0"/>
+    <s v="ING Group NV"/>
+    <s v="ING"/>
+    <d v="2024-11-27T00:00:00"/>
+    <n v="1.9595"/>
+    <n v="15.3"/>
+    <n v="29.980350000000001"/>
+    <n v="0.35"/>
+    <n v="0.39532299999999998"/>
+    <n v="0.88535197800279775"/>
+    <n v="4.7595601427787633E-2"/>
+    <n v="20.655000000000001"/>
+    <n v="14.636624277854791"/>
+    <n v="5.3550000000000004"/>
+    <n v="-0.33168786107260484"/>
+    <n v="5.0233121389273956"/>
+    <n v="109.10913294225699"/>
+    <n v="9.165135612700933E-3"/>
+    <n v="0.76181081974332665"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="APA"/>
+    <s v="APA"/>
+    <d v="2024-12-01T00:00:00"/>
+    <n v="1.8976999999999999"/>
+    <n v="21.73"/>
+    <n v="41.237020999999999"/>
+    <n v="0.22319374137137582"/>
+    <n v="0.45929999999999999"/>
+    <n v="0.48594326447066366"/>
+    <n v="2.6123804438137953E-2"/>
+    <n v="26.58"/>
+    <n v="17.579394852436032"/>
+    <n v="4.8499999999999979"/>
+    <n v="-2.0753025737819843"/>
+    <n v="2.7746974262180135"/>
+    <n v="111.35774765496637"/>
+    <n v="8.9800666864996662E-3"/>
+    <n v="0.77751087134654673"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="Altaria"/>
+    <s v="MO"/>
+    <d v="2024-09-18T00:00:00"/>
+    <n v="1.7345999999999999"/>
+    <n v="51.88"/>
+    <n v="89.991048000000006"/>
+    <n v="0.18430000000000002"/>
+    <n v="0.19980000000000001"/>
+    <n v="0.92242242242242245"/>
+    <n v="4.9588469960512409E-2"/>
+    <n v="61.441483999999996"/>
+    <n v="51.088133924175295"/>
+    <n v="9.561483999999993"/>
+    <n v="-0.39593303791235357"/>
+    <n v="9.1655509620876394"/>
+    <n v="104.96689411909675"/>
+    <n v="9.526813271862531E-3"/>
+    <n v="0.73288929623425103"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Maxeon Solar"/>
+    <s v="MAXN"/>
+    <d v="2024-08-07T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="10.92"/>
+    <n v="1.092E-18"/>
+    <n v="1"/>
+    <n v="1.8652"/>
+    <n v="0.53613553506326406"/>
+    <n v="2.8822088697094593E-2"/>
+    <n v="21.84"/>
+    <n v="5.8546000428908433"/>
+    <n v="10.92"/>
+    <n v="-2.5326999785545783"/>
+    <n v="8.3873000214454212"/>
+    <n v="105.74514505973896"/>
+    <n v="9.456698928684306E-3"/>
+    <n v="0.73832312171768166"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="NextEra Energy"/>
+    <s v="NEE"/>
+    <d v="2024-08-07T00:00:00"/>
+    <n v="0.45179999999999998"/>
+    <n v="77.430000000000007"/>
+    <n v="34.982874000000002"/>
+    <n v="0.1"/>
+    <n v="0.25990000000000002"/>
+    <n v="0.38476337052712584"/>
+    <n v="2.0684478583232333E-2"/>
+    <n v="85.173000000000016"/>
+    <n v="66.755754806448849"/>
+    <n v="7.7430000000000092"/>
+    <n v="-5.3371225967755791"/>
+    <n v="2.4058774032244301"/>
+    <n v="111.72656767795996"/>
+    <n v="8.9504226325326178E-3"/>
+    <n v="0.78008600943515383"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="YPF"/>
+    <s v="YPF"/>
+    <d v="2024-12-01T00:00:00"/>
+    <n v="0.45129999999999998"/>
+    <n v="44.38"/>
+    <n v="20.028694000000002"/>
+    <n v="0.1"/>
+    <n v="0.2"/>
+    <n v="0.5"/>
+    <n v="2.6879479918910414E-2"/>
+    <n v="48.818000000000005"/>
+    <n v="40.345454545454551"/>
+    <n v="4.4380000000000024"/>
+    <n v="-2.0172727272727258"/>
+    <n v="2.4207272727272766"/>
+    <n v="111.71171780845711"/>
+    <n v="8.9516124146852508E-3"/>
+    <n v="0.77998232616910645"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="Pepsi"/>
+    <s v="PEP"/>
+    <d v="2024-06-17T00:00:00"/>
+    <n v="0.43659999999999999"/>
+    <n v="160.25"/>
+    <n v="69.965149999999994"/>
+    <n v="6.7199999999999996E-2"/>
+    <n v="0.16439999999999999"/>
+    <n v="0.40875912408759124"/>
+    <n v="2.1974465335167639E-2"/>
+    <n v="171.0188"/>
+    <n v="146.05359095880419"/>
+    <n v="10.768799999999999"/>
+    <n v="-7.0982045205979034"/>
+    <n v="3.6705954794020954"/>
+    <n v="110.46184960178229"/>
+    <n v="9.0528992915203284E-3"/>
+    <n v="0.7712556220204998"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="TSMC"/>
+    <s v="TSM"/>
+    <d v="2024-07-11T00:00:00"/>
+    <n v="0.4108"/>
+    <n v="189.76"/>
+    <n v="77.953407999999996"/>
+    <n v="0.19835581787521095"/>
+    <n v="0.37"/>
+    <n v="0.53609680506813773"/>
+    <n v="2.8820006612842078E-2"/>
+    <n v="227.4"/>
+    <n v="161.96043380326287"/>
+    <n v="37.640000000000015"/>
+    <n v="-13.899783098368559"/>
+    <n v="23.740216901631456"/>
+    <n v="90.39222817955293"/>
+    <n v="1.10628979962041E-2"/>
+    <n v="0.6311275288415521"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="Kimberly Clark"/>
+    <s v="KMB"/>
+    <d v="2024-09-09T00:00:00"/>
+    <n v="0.35149999999999998"/>
+    <n v="142.78"/>
+    <n v="50.187169999999995"/>
+    <n v="7.0000000000000007E-2"/>
+    <n v="0.18340000000000001"/>
+    <n v="0.38167938931297712"/>
+    <n v="2.0518686961000319E-2"/>
+    <n v="152.77460000000002"/>
+    <n v="128.23783007005568"/>
+    <n v="9.9946000000000197"/>
+    <n v="-7.2710849649721609"/>
+    <n v="2.7235150350278587"/>
+    <n v="111.40893004615653"/>
+    <n v="8.9759411528833617E-3"/>
+    <n v="0.77786823189316223"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="Yum! Brands"/>
+    <s v="YUM"/>
+    <d v="2024-10-15T00:00:00"/>
+    <n v="0.25669999999999998"/>
+    <n v="132.38999999999999"/>
+    <n v="33.984512999999993"/>
+    <n v="7.0000000000000007E-2"/>
+    <n v="0.1623"/>
+    <n v="0.43130006161429457"/>
+    <n v="2.3186242690372512E-2"/>
+    <n v="141.65729999999999"/>
+    <n v="121.20296621807194"/>
+    <n v="9.2673000000000059"/>
+    <n v="-5.5935168909640254"/>
+    <n v="3.6737831090359805"/>
+    <n v="110.45866197214841"/>
+    <n v="9.0531605411999731E-3"/>
+    <n v="0.77123336567330925"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="Visa"/>
+    <s v="V"/>
+    <d v="2024-08-07T00:00:00"/>
+    <n v="0.1938"/>
+    <n v="283.43"/>
+    <n v="54.928733999999999"/>
+    <n v="0.25"/>
+    <n v="0.26"/>
+    <n v="0.96153846153846145"/>
+    <n v="5.1691307536366179E-2"/>
+    <n v="354.28750000000002"/>
+    <n v="280.62376237623761"/>
+    <n v="70.857500000000016"/>
+    <n v="-1.4031188118811997"/>
+    <n v="69.454381188118816"/>
+    <n v="44.67806389306557"/>
+    <n v="2.2382348581474875E-2"/>
+    <n v="0.311946686414727"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="QualComm2"/>
+    <s v="QCOM"/>
+    <d v="2024-09-09T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="188.12"/>
+    <n v="1.8812000000000001E-17"/>
+    <n v="0.15"/>
+    <n v="0.37780000000000002"/>
+    <n v="0.39703546850185278"/>
+    <n v="2.1344213805381481E-2"/>
+    <n v="216.33799999999999"/>
+    <n v="153.21713634142367"/>
+    <n v="28.217999999999989"/>
+    <n v="-17.451431829288168"/>
+    <n v="10.766568170711821"/>
+    <n v="103.36587691047256"/>
+    <n v="9.6743725288193673E-3"/>
+    <n v="0.72171083482377829"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="MSG"/>
+    <s v="INGR"/>
+    <d v="2024-10-15T00:00:00"/>
+    <n v="0.19139999999999999"/>
+    <n v="135.82"/>
+    <n v="25.995947999999999"/>
+    <n v="0.1202"/>
+    <n v="0.33710000000000001"/>
+    <n v="0.35657075051913378"/>
+    <n v="1.9168872656499743E-2"/>
+    <n v="152.14556400000001"/>
+    <n v="111.61147177253677"/>
+    <n v="16.325564000000014"/>
+    <n v="-12.10426411373161"/>
+    <n v="4.2212998862684046"/>
+    <n v="109.91114519491597"/>
+    <n v="9.0982583997883393E-3"/>
+    <n v="0.76741054907089512"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="Apple2"/>
+    <s v="AAPL"/>
+    <d v="2024-07-09T00:00:00"/>
+    <n v="0.18820000000000001"/>
+    <n v="227.38"/>
+    <n v="42.792915999999998"/>
+    <n v="0.15"/>
+    <n v="0.2271"/>
+    <n v="0.66050198150594452"/>
+    <n v="3.5507899496579148E-2"/>
+    <n v="261.48699999999997"/>
+    <n v="211.10389007520189"/>
+    <n v="34.106999999999971"/>
+    <n v="-8.1380549623990532"/>
+    <n v="25.968945037600918"/>
+    <n v="88.163500043583468"/>
+    <n v="1.1342562392664218E-2"/>
+    <n v="0.6155663272953309"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="Microsoft"/>
+    <s v="MSFT"/>
+    <d v="2024-10-09T00:00:00"/>
+    <n v="0.13370000000000001"/>
+    <n v="423.77"/>
+    <n v="56.658049000000005"/>
+    <n v="0.15"/>
+    <n v="0.1963"/>
+    <n v="0.76413652572592972"/>
+    <n v="4.10791847971122E-2"/>
+    <n v="487.33549999999991"/>
+    <n v="405.01768135334032"/>
+    <n v="63.565499999999929"/>
+    <n v="-9.3761593233298299"/>
+    <n v="54.189340676670099"/>
+    <n v="59.943104404514287"/>
+    <n v="1.6682485999585474E-2"/>
+    <n v="0.41852871774290379"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="Master Card"/>
+    <s v="MA"/>
+    <d v="2024-08-07T00:00:00"/>
+    <n v="0.12939999999999999"/>
+    <n v="501.56"/>
+    <n v="64.901863999999989"/>
+    <n v="0.25"/>
+    <n v="0.29699999999999999"/>
+    <n v="0.84175084175084181"/>
+    <n v="4.5251649695135378E-2"/>
+    <n v="626.95000000000005"/>
+    <n v="479.04489016236869"/>
+    <n v="125.39000000000004"/>
+    <n v="-11.257554918815657"/>
+    <n v="114.13244508118439"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="Google"/>
+    <s v="GOOGL"/>
+    <d v="2024-07-10T00:00:00"/>
+    <n v="0.1195"/>
+    <n v="167.24"/>
+    <n v="19.98518"/>
+    <n v="0.13854341066730447"/>
+    <n v="0.26790000000000003"/>
+    <n v="0.51714598979956872"/>
+    <n v="2.7801230495925113E-2"/>
+    <n v="190.41"/>
+    <n v="148.08431772538498"/>
+    <n v="23.169999999999987"/>
+    <n v="-9.5778411373075159"/>
+    <n v="13.592158862692472"/>
+    <n v="100.54028621849191"/>
+    <n v="9.9462617186788418E-3"/>
+    <n v="0.70198227953907921"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="First Solar"/>
+    <s v="FSLR"/>
+    <d v="2024-08-07T00:00:00"/>
+    <n v="0.158"/>
+    <n v="189.72"/>
+    <n v="29.975760000000001"/>
+    <n v="3.3206831119544589E-2"/>
+    <n v="0.52980000000000005"/>
+    <n v="6.2678050433266491E-2"/>
+    <n v="3.3695067959548818E-3"/>
+    <n v="196.02"/>
+    <n v="126.76791792516488"/>
+    <n v="6.3000000000000114"/>
+    <n v="-31.476041037417559"/>
+    <n v="-25.176041037417548"/>
+    <n v="139.30848611860193"/>
+    <n v="7.1783135964067412E-3"/>
+    <n v="0.97266570767617244"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="LVMH"/>
+    <s v="MC.PA"/>
+    <d v="2024-09-27T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="668.82"/>
+    <n v="6.6881999999999999E-17"/>
+    <n v="0.05"/>
+    <n v="0.28000000000000003"/>
+    <n v="0.17857142857142858"/>
+    <n v="9.5998142567537189E-3"/>
+    <n v="702.26100000000008"/>
+    <n v="543.7560975609756"/>
+    <n v="33.441000000000031"/>
+    <n v="-62.531951219512223"/>
+    <n v="-29.090951219512192"/>
+    <n v="143.22339630069658"/>
+    <n v="6.9820994741704532E-3"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="ASML"/>
+    <s v="ASML"/>
+    <d v="2024-07-08T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="700.32"/>
+    <n v="7.0031999999999998E-17"/>
+    <n v="0.1"/>
+    <n v="0.45340000000000003"/>
+    <n v="0.22055580061755625"/>
+    <n v="1.1856850427397625E-2"/>
+    <n v="770.35200000000009"/>
+    <n v="517.45234224915032"/>
+    <n v="70.032000000000039"/>
+    <n v="-91.433828875424865"/>
+    <n v="-21.401828875424826"/>
+    <n v="135.53427395660921"/>
+    <n v="7.3782075249847591E-3"/>
+    <n v="0.94631378292451529"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="Nvidia"/>
+    <s v="NVDA"/>
+    <d v="2024-07-09T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="147.01"/>
+    <n v="1.4700999999999999E-17"/>
+    <n v="0.15"/>
+    <n v="0.52380000000000004"/>
+    <n v="0.28636884306987398"/>
+    <n v="1.5394891133396571E-2"/>
+    <n v="169.06149999999997"/>
+    <n v="107.00975396709855"/>
+    <n v="22.051499999999976"/>
+    <n v="-20.000123016450722"/>
+    <n v="2.0513769835492539"/>
+    <n v="112.08106809763513"/>
+    <n v="8.9221134039237406E-3"/>
+    <n v="0.78256116662896091"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="Applied Material"/>
+    <s v="AMAT"/>
+    <d v="2024-07-08T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="169.34"/>
+    <n v="1.6933999999999999E-17"/>
+    <n v="0.1"/>
+    <n v="0.4259"/>
+    <n v="0.23479690068091102"/>
+    <n v="1.2622437153749902E-2"/>
+    <n v="186.27400000000003"/>
+    <n v="127.71702239987934"/>
+    <n v="16.934000000000026"/>
+    <n v="-20.811488800060332"/>
+    <n v="-3.8774888000603056"/>
+    <n v="118.00993388124469"/>
+    <n v="8.4738628953585915E-3"/>
+    <n v="0.82395709729912847"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Duke Energy"/>
+    <s v="DUK"/>
+    <d v="2024-08-07T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="113.58"/>
+    <n v="1.1357999999999999E-17"/>
+    <n v="6.664905793273479E-2"/>
+    <n v="0.16439999999999999"/>
+    <n v="0.40540789496797319"/>
+    <n v="2.1794306743518756E-2"/>
+    <n v="121.15000000000002"/>
+    <n v="103.46609203186667"/>
+    <n v="7.5700000000000216"/>
+    <n v="-5.0569539840666664"/>
+    <n v="2.5130460159333552"/>
+    <n v="111.61939906525103"/>
+    <n v="8.9590161600441431E-3"/>
+    <n v="0.77933774752071117"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="Palantir"/>
+    <s v="PLTR"/>
+    <d v="2024-07-08T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="64.349999999999994"/>
+    <n v="6.4349999999999993E-18"/>
+    <n v="0.15"/>
+    <n v="0.67300000000000004"/>
+    <n v="0.22288261515601782"/>
+    <n v="1.1981937556720838E-2"/>
+    <n v="74.002499999999984"/>
+    <n v="42.252133946158892"/>
+    <n v="9.6524999999999892"/>
+    <n v="-11.048933026920551"/>
+    <n v="-1.3964330269205618"/>
+    <n v="115.52887810810495"/>
+    <n v="8.6558444639638962E-3"/>
+    <n v="0.80663411909010196"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Jinko Solar"/>
+    <s v="JKS"/>
+    <d v="2024-08-07T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="20.82"/>
+    <n v="2.0820000000000002E-18"/>
+    <n v="0.05"/>
+    <n v="0.7389"/>
+    <n v="6.7668155366084726E-2"/>
+    <n v="3.6377696466247688E-3"/>
+    <n v="21.861000000000001"/>
+    <n v="12.327550476641601"/>
+    <n v="1.0410000000000004"/>
+    <n v="-4.2462247616791995"/>
+    <n v="-3.2052247616791991"/>
+    <n v="117.33766984286359"/>
+    <n v="8.5224122938454584E-3"/>
+    <n v="0.81926328291024408"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="SolarWinds"/>
+    <s v="SWI"/>
+    <d v="2024-08-07T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="13.04"/>
+    <n v="1.304E-18"/>
+    <n v="5.2147239263803824E-2"/>
+    <n v="0.30159999999999998"/>
+    <n v="0.17290198694895167"/>
+    <n v="9.2950309722681142E-3"/>
+    <n v="13.72"/>
+    <n v="10.436569040286594"/>
+    <n v="0.68000000000000149"/>
+    <n v="-1.3017154798567026"/>
+    <n v="-0.62171547985670106"/>
+    <n v="114.75416056104109"/>
+    <n v="8.7142809908671744E-3"/>
+    <n v="0.80122496411211674"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Canadian Solar"/>
+    <s v="CSIQ"/>
+    <d v="2024-08-07T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="11.05"/>
+    <n v="1.1050000000000001E-18"/>
+    <n v="0.05"/>
+    <n v="0.72170000000000001"/>
+    <n v="6.9280864625190522E-2"/>
+    <n v="3.7244672189151191E-3"/>
+    <n v="11.602500000000001"/>
+    <n v="6.6100376861877139"/>
+    <n v="0.55250000000000021"/>
+    <n v="-2.2199811569061434"/>
+    <n v="-1.6674811569061432"/>
+    <n v="115.79992623809053"/>
+    <n v="8.6355840844315329E-3"/>
+    <n v="0.80852660409594923"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <s v="Gold"/>
+    <s v="GC=F"/>
+    <d v="2025-01-08T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="2742.9"/>
+    <n v="2.7429000000000002E-16"/>
+    <n v="0.1"/>
+    <n v="0.5"/>
+    <n v="0.2"/>
+    <n v="1.0751791967564166E-2"/>
+    <n v="3017.1900000000005"/>
+    <n v="1959.214285714286"/>
+    <n v="274.29000000000042"/>
+    <n v="-391.84285714285704"/>
+    <n v="-117.55285714285662"/>
+    <n v="231.68530222404101"/>
+    <n v="4.316199562080957E-3"/>
+    <n v="1.6176498268314992"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="Walmart"/>
+    <s v="WMT"/>
+    <d v="2024-08-01T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="86.6"/>
+    <n v="8.6599999999999986E-18"/>
+    <n v="7.0000000000000007E-2"/>
+    <n v="0.17249999999999999"/>
+    <n v="0.40579710144927544"/>
+    <n v="2.1815230079115702E-2"/>
+    <n v="92.662000000000006"/>
+    <n v="78.548752834467123"/>
+    <n v="6.0620000000000118"/>
+    <n v="-4.0256235827664355"/>
+    <n v="2.0363764172335763"/>
+    <n v="112.0960686639508"/>
+    <n v="8.9209194570227766E-3"/>
+    <n v="0.78266590207514586"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <s v="Aptive Autoparts"/>
+    <s v="APTV"/>
+    <d v="2024-09-27T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="56"/>
+    <n v="5.5999999999999995E-18"/>
+    <n v="7.0000000000000007E-2"/>
+    <n v="0.19"/>
+    <n v="0.36842105263157898"/>
+    <n v="1.9805932571828729E-2"/>
+    <n v="59.92"/>
+    <n v="50.000000000000007"/>
+    <n v="3.9200000000000017"/>
+    <n v="-2.9999999999999964"/>
+    <n v="0.92000000000000526"/>
+    <n v="113.21244508118438"/>
+    <n v="8.832951176727102E-3"/>
+    <n v="0.79046055327088882"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <s v="Mexican Peso"/>
+    <s v="USDMXN=X"/>
+    <d v="2024-10-15T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="20.399999999999999"/>
+    <n v="2.0399999999999999E-18"/>
+    <n v="0.1"/>
+    <n v="0.15"/>
+    <n v="0.66666666666666674"/>
+    <n v="3.5839306558547224E-2"/>
+    <n v="21.2"/>
+    <n v="19.428571428571431"/>
+    <n v="0.80000000000000071"/>
+    <n v="-0.48571428571428399"/>
+    <n v="0.31428571428571672"/>
+    <n v="113.81815936689867"/>
+    <n v="8.7859442250902055E-3"/>
+    <n v="0.79468971066667204"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="Yum China Holding"/>
+    <s v="YUMC"/>
+    <d v="2024-10-09T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="47.42"/>
+    <n v="4.7419999999999999E-18"/>
+    <n v="7.0000000000000007E-2"/>
+    <n v="0.4"/>
+    <n v="0.17500000000000002"/>
+    <n v="9.4078179716186455E-3"/>
+    <n v="50.739400000000003"/>
+    <n v="35.654135338345867"/>
+    <n v="3.3194000000000017"/>
+    <n v="-5.8829323308270673"/>
+    <n v="-2.5635323308270657"/>
+    <n v="116.69597741201144"/>
+    <n v="8.5692756697976005E-3"/>
+    <n v="0.81478292252621221"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="MSG"/>
+    <s v="DAR"/>
+    <d v="2024-08-03T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="41.8"/>
+    <n v="4.1799999999999993E-18"/>
+    <n v="7.0000000000000007E-2"/>
+    <n v="0.4"/>
+    <n v="0.17500000000000002"/>
+    <n v="9.4078179716186455E-3"/>
+    <n v="44.725999999999999"/>
+    <n v="31.428571428571431"/>
+    <n v="2.9260000000000019"/>
+    <n v="-5.1857142857142833"/>
+    <n v="-2.2597142857142813"/>
+    <n v="116.39215936689867"/>
+    <n v="8.5916440200042785E-3"/>
+    <n v="0.81266163471318675"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <s v="Japan Yen"/>
+    <s v="USDJPY=X"/>
+    <d v="2024-10-09T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="153.7552"/>
+    <n v="1.5375519999999999E-17"/>
+    <n v="7.0000000000000007E-2"/>
+    <n v="0.19"/>
+    <n v="0.36842105263157898"/>
+    <n v="1.9805932571828729E-2"/>
+    <n v="164.51806400000001"/>
+    <n v="137.28142857142859"/>
+    <n v="10.762864000000008"/>
+    <n v="-8.2368857142857053"/>
+    <n v="2.5259782857143023"/>
+    <n v="111.60646679547008"/>
+    <n v="8.9600542756415637E-3"/>
+    <n v="0.77924745312667376"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="3M"/>
+    <s v="MMM"/>
+    <d v="2024-12-01T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="133.53"/>
+    <n v="1.3353E-17"/>
+    <n v="7.0000000000000007E-2"/>
+    <n v="0.2"/>
+    <n v="0.35000000000000003"/>
+    <n v="1.8815635943237291E-2"/>
+    <n v="142.87710000000001"/>
+    <n v="118.16814159292036"/>
+    <n v="9.3471000000000117"/>
+    <n v="-7.6809292035398187"/>
+    <n v="1.6661707964601931"/>
+    <n v="112.46627428472419"/>
+    <n v="8.8915544358512261E-3"/>
+    <n v="0.78525071454528272"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Excelon"/>
+    <s v="EXC"/>
+    <d v="2024-12-01T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="39.56"/>
+    <n v="3.9560000000000004E-18"/>
+    <n v="0.1"/>
+    <n v="0.2"/>
+    <n v="0.5"/>
+    <n v="2.6879479918910414E-2"/>
+    <n v="43.516000000000005"/>
+    <n v="35.963636363636368"/>
+    <n v="3.9560000000000031"/>
+    <n v="-1.798181818181817"/>
+    <n v="2.1578181818181861"/>
+    <n v="111.9746268993662"/>
+    <n v="8.9305946149632592E-3"/>
+    <n v="0.78181798359449739"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="PG&amp;E"/>
+    <s v="PCG"/>
+    <d v="2024-12-01T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="26.63"/>
+    <n v="2.663E-18"/>
+    <n v="0.1"/>
+    <n v="0.2"/>
+    <n v="0.5"/>
+    <n v="2.6879479918910414E-2"/>
+    <n v="29.293000000000003"/>
+    <n v="24.209090909090911"/>
+    <n v="2.6630000000000038"/>
+    <n v="-1.2104545454545441"/>
+    <n v="1.4525454545454597"/>
+    <n v="112.67989962663893"/>
+    <n v="8.8746972912956655E-3"/>
+    <n v="0.78674226793273505"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="Agios"/>
+    <s v="AGIO"/>
+    <d v="2024-12-04T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="59.17"/>
+    <n v="5.9170000000000002E-18"/>
+    <n v="0.2"/>
+    <n v="0.2"/>
+    <n v="1"/>
+    <n v="5.3758959837820829E-2"/>
+    <n v="71.004000000000005"/>
+    <n v="59.17"/>
+    <n v="11.834000000000003"/>
+    <n v="0"/>
+    <n v="11.834000000000003"/>
+    <n v="102.29844508118438"/>
+    <n v="9.7753196464168812E-3"/>
+    <n v="0.71425791960979246"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="Albertson Companies"/>
+    <s v="ACI"/>
+    <d v="2024-12-04T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="19.309999999999999"/>
+    <n v="1.931E-18"/>
+    <n v="0.2"/>
+    <n v="0.2"/>
+    <n v="1"/>
+    <n v="5.3758959837820829E-2"/>
+    <n v="23.171999999999997"/>
+    <n v="19.309999999999999"/>
+    <n v="3.8619999999999983"/>
+    <n v="0"/>
+    <n v="3.8619999999999983"/>
+    <n v="110.27044508118439"/>
+    <n v="9.0686130745529347E-3"/>
+    <n v="0.76991921661787932"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="HCA Healthcare"/>
+    <s v="HCA"/>
+    <d v="2024-12-04T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="323.75"/>
+    <n v="3.2375000000000002E-17"/>
+    <n v="0.2"/>
+    <n v="0.2"/>
+    <n v="1"/>
+    <n v="5.3758959837820829E-2"/>
+    <n v="388.5"/>
+    <n v="323.75"/>
+    <n v="64.75"/>
+    <n v="0"/>
+    <n v="64.75"/>
+    <n v="49.382445081184386"/>
+    <n v="2.0250111114506527E-2"/>
+    <n v="0.34479314383458876"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{26B2B253-9CE0-4227-B980-7D5C03945A28}" name="PivotTable1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:C13" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="19">
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="10">
+        <item x="4"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="8"/>
+        <item x="7"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField dataField="1" numFmtId="44" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="10">
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Initial Volume $" fld="6" baseField="0" baseItem="0" numFmtId="44"/>
+    <dataField name="$%" fld="6" baseField="0" baseItem="7" numFmtId="9">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{E15A36E0-9728-4e99-A89B-3F7291B0FE68}">
+          <x14:dataField pivotShowAs="percentOfParentRow"/>
+        </ext>
+      </extLst>
+    </dataField>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="5">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="4">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -795,7 +1937,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D1" s="17" t="s">
         <v>1</v>
@@ -810,40 +1952,40 @@
         <v>4</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I1" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="K1" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="L1" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="M1" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="N1" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="O1" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="P1" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="Q1" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="P1" s="16" t="s">
+      <c r="R1" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="S1" s="16" t="s">
         <v>70</v>
-      </c>
-      <c r="Q1" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="R1" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="S1" s="16" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
@@ -851,10 +1993,10 @@
         <v>37</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D2" s="8">
         <v>45623</v>
@@ -866,7 +2008,7 @@
         <v>15.3</v>
       </c>
       <c r="G2" s="1">
-        <f t="shared" ref="G2:G41" si="0">E2*F2</f>
+        <f>E2*F2</f>
         <v>29.980350000000001</v>
       </c>
       <c r="H2" s="11">
@@ -876,185 +2018,185 @@
         <v>0.39532299999999998</v>
       </c>
       <c r="J2" s="9">
-        <f t="shared" ref="J2:J41" si="1">IFERROR(H2/I2,"")</f>
+        <f>IFERROR(H2/I2,"")</f>
         <v>0.88535197800279775</v>
       </c>
       <c r="K2" s="9">
-        <f t="shared" ref="K2:K41" si="2">IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.8490794985327837E-2</v>
+        <f>IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>4.7595601427787633E-2</v>
       </c>
       <c r="L2" s="12">
-        <f t="shared" ref="L2:L30" si="3">F2/(1-(F2*(1+H2)-F2)/(F2*(1+H2)))</f>
+        <f>F2/(1-(F2*(1+H2)-F2)/(F2*(1+H2)))</f>
         <v>20.655000000000001</v>
       </c>
       <c r="M2" s="12">
-        <f t="shared" ref="M2:M41" si="4">F2/(1+I2-H2)</f>
+        <f>F2/(1+I2-H2)</f>
         <v>14.636624277854791</v>
       </c>
       <c r="N2" s="12">
-        <f t="shared" ref="N2:N41" si="5">L2-F2</f>
+        <f>L2-F2</f>
         <v>5.3550000000000004</v>
       </c>
       <c r="O2" s="12">
-        <f t="shared" ref="O2:O41" si="6">0.5*(M2-F2)</f>
+        <f>0.5*(M2-F2)</f>
         <v>-0.33168786107260484</v>
       </c>
       <c r="P2" s="15">
-        <f t="shared" ref="P2:P41" si="7">N2+O2</f>
+        <f>N2+O2</f>
         <v>5.0233121389273956</v>
       </c>
       <c r="Q2" s="12">
-        <f t="shared" ref="Q2:Q41" si="8">MAX($P$2:$P$280)-P2</f>
-        <v>98.605197889725929</v>
+        <f>MAX($P$2:$P$280)-P2</f>
+        <v>109.10913294225699</v>
       </c>
       <c r="R2" s="9">
-        <f t="shared" ref="R2:R41" si="9">IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q2)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.0141453203291973E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q2)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.165135612700933E-3</v>
       </c>
       <c r="S2" s="9">
-        <f t="shared" ref="S2:S41" si="10">Q2/MAX($Q$2:$Q$28)</f>
-        <v>0.44581150370259182</v>
+        <f>Q2/MAX($Q$2:$Q$28)</f>
+        <v>0.76181081974332665</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="8">
+        <v>45627</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1.8976999999999999</v>
+      </c>
+      <c r="F3" s="1">
+        <v>21.73</v>
+      </c>
+      <c r="G3" s="1">
+        <f>E3*F3</f>
+        <v>41.237020999999999</v>
+      </c>
+      <c r="H3" s="11">
+        <f>L3/F3-1</f>
+        <v>0.22319374137137582</v>
+      </c>
+      <c r="I3" s="11">
+        <v>0.45929999999999999</v>
+      </c>
+      <c r="J3" s="9">
+        <f>IFERROR(H3/I3,"")</f>
+        <v>0.48594326447066366</v>
+      </c>
+      <c r="K3" s="9">
+        <f>IFERROR(J3/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>2.6123804438137953E-2</v>
+      </c>
+      <c r="L3" s="12">
+        <v>26.58</v>
+      </c>
+      <c r="M3" s="12">
+        <f>F3/(1+I3-H3)</f>
+        <v>17.579394852436032</v>
+      </c>
+      <c r="N3" s="12">
+        <f>L3-F3</f>
+        <v>4.8499999999999979</v>
+      </c>
+      <c r="O3" s="12">
+        <f>0.5*(M3-F3)</f>
+        <v>-2.0753025737819843</v>
+      </c>
+      <c r="P3" s="15">
+        <f>N3+O3</f>
+        <v>2.7746974262180135</v>
+      </c>
+      <c r="Q3" s="12">
+        <f>MAX($P$2:$P$280)-P3</f>
+        <v>111.35774765496637</v>
+      </c>
+      <c r="R3" s="9">
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q3)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>8.9800666864996662E-3</v>
+      </c>
+      <c r="S3" s="9">
+        <f>Q3/MAX($Q$2:$Q$28)</f>
+        <v>0.77751087134654673</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C4" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D4" s="8">
         <v>45553</v>
       </c>
-      <c r="E3" s="2">
-        <v>1.0751999999999999</v>
-      </c>
-      <c r="F3" s="1">
-        <v>51.15</v>
-      </c>
-      <c r="G3" s="1">
-        <f t="shared" si="0"/>
-        <v>54.996479999999998</v>
-      </c>
-      <c r="H3" s="11">
+      <c r="E4" s="2">
+        <v>1.7345999999999999</v>
+      </c>
+      <c r="F4" s="1">
+        <v>51.88</v>
+      </c>
+      <c r="G4" s="1">
+        <f>E4*F4</f>
+        <v>89.991048000000006</v>
+      </c>
+      <c r="H4" s="11">
         <f>16.68%+7%/4</f>
         <v>0.18430000000000002</v>
       </c>
-      <c r="I3" s="11">
+      <c r="I4" s="11">
         <v>0.19980000000000001</v>
       </c>
-      <c r="J3" s="9">
-        <f t="shared" si="1"/>
+      <c r="J4" s="9">
+        <f>IFERROR(H4/I4,"")</f>
         <v>0.92242242242242245</v>
       </c>
-      <c r="K3" s="9">
-        <f t="shared" si="2"/>
-        <v>5.05211460378234E-2</v>
-      </c>
-      <c r="L3" s="12">
-        <f t="shared" si="3"/>
-        <v>60.576944999999995</v>
-      </c>
-      <c r="M3" s="12">
-        <f t="shared" si="4"/>
-        <v>50.369276218611525</v>
-      </c>
-      <c r="N3" s="12">
-        <f t="shared" si="5"/>
-        <v>9.4269449999999964</v>
-      </c>
-      <c r="O3" s="12">
-        <f t="shared" si="6"/>
-        <v>-0.39036189069423699</v>
-      </c>
-      <c r="P3" s="15">
-        <f t="shared" si="7"/>
-        <v>9.0365831093057594</v>
-      </c>
-      <c r="Q3" s="12">
-        <f t="shared" si="8"/>
-        <v>94.591926919347571</v>
-      </c>
-      <c r="R3" s="9">
-        <f t="shared" si="9"/>
-        <v>1.0571726706155752E-2</v>
-      </c>
-      <c r="S3" s="9">
-        <f t="shared" si="10"/>
-        <v>0.42766679729399837</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4" s="8">
-        <v>45511</v>
-      </c>
-      <c r="E4" s="2">
-        <v>1</v>
-      </c>
-      <c r="F4" s="1">
-        <v>10.92</v>
-      </c>
-      <c r="G4" s="1">
-        <f t="shared" si="0"/>
-        <v>10.92</v>
-      </c>
-      <c r="H4" s="11">
-        <v>1</v>
-      </c>
-      <c r="I4" s="13">
-        <v>1.8652</v>
-      </c>
-      <c r="J4" s="9">
-        <f t="shared" si="1"/>
-        <v>0.53613553506326406</v>
-      </c>
       <c r="K4" s="9">
-        <f t="shared" si="2"/>
-        <v>2.9364183918974232E-2</v>
+        <f>IFERROR(J4/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>4.9588469960512409E-2</v>
       </c>
       <c r="L4" s="12">
-        <f t="shared" si="3"/>
-        <v>21.84</v>
+        <f>F4/(1-(F4*(1+H4)-F4)/(F4*(1+H4)))</f>
+        <v>61.441483999999996</v>
       </c>
       <c r="M4" s="12">
-        <f t="shared" si="4"/>
-        <v>5.8546000428908433</v>
+        <f>F4/(1+I4-H4)</f>
+        <v>51.088133924175295</v>
       </c>
       <c r="N4" s="12">
-        <f t="shared" si="5"/>
-        <v>10.92</v>
+        <f>L4-F4</f>
+        <v>9.561483999999993</v>
       </c>
       <c r="O4" s="12">
-        <f t="shared" si="6"/>
-        <v>-2.5326999785545783</v>
+        <f>0.5*(M4-F4)</f>
+        <v>-0.39593303791235357</v>
       </c>
       <c r="P4" s="15">
-        <f t="shared" si="7"/>
-        <v>8.3873000214454212</v>
+        <f>N4+O4</f>
+        <v>9.1655509620876394</v>
       </c>
       <c r="Q4" s="12">
-        <f t="shared" si="8"/>
-        <v>95.241210007207897</v>
+        <f>MAX($P$2:$P$280)-P4</f>
+        <v>104.96689411909675</v>
       </c>
       <c r="R4" s="9">
-        <f t="shared" si="9"/>
-        <v>1.0499656607935993E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q4)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.526813271862531E-3</v>
       </c>
       <c r="S4" s="9">
-        <f t="shared" si="10"/>
-        <v>0.43060232073416616</v>
+        <f>Q4/MAX($Q$2:$Q$28)</f>
+        <v>0.73288929623425103</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
@@ -1062,280 +2204,279 @@
         <v>40</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
+        <v>51</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>50</v>
       </c>
       <c r="D5" s="8">
         <v>45511</v>
       </c>
       <c r="E5" s="2">
-        <v>0.45179999999999998</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F5" s="1">
-        <v>77.430000000000007</v>
+        <v>10.92</v>
       </c>
       <c r="G5" s="1">
-        <f t="shared" si="0"/>
-        <v>34.982874000000002</v>
+        <f>E5*F5</f>
+        <v>1.092E-18</v>
       </c>
       <c r="H5" s="11">
-        <v>0.1</v>
-      </c>
-      <c r="I5" s="11">
-        <v>0.25990000000000002</v>
+        <v>1</v>
+      </c>
+      <c r="I5" s="13">
+        <v>1.8652</v>
       </c>
       <c r="J5" s="9">
-        <f t="shared" si="1"/>
-        <v>0.38476337052712584</v>
+        <f>IFERROR(H5/I5,"")</f>
+        <v>0.53613553506326406</v>
       </c>
       <c r="K5" s="9">
-        <f t="shared" si="2"/>
-        <v>2.1073518986406591E-2</v>
+        <f>IFERROR(J5/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>2.8822088697094593E-2</v>
       </c>
       <c r="L5" s="12">
-        <f t="shared" si="3"/>
-        <v>85.173000000000016</v>
+        <f>F5/(1-(F5*(1+H5)-F5)/(F5*(1+H5)))</f>
+        <v>21.84</v>
       </c>
       <c r="M5" s="12">
-        <f t="shared" si="4"/>
-        <v>66.755754806448849</v>
+        <f>F5/(1+I5-H5)</f>
+        <v>5.8546000428908433</v>
       </c>
       <c r="N5" s="12">
-        <f t="shared" si="5"/>
-        <v>7.7430000000000092</v>
+        <f>L5-F5</f>
+        <v>10.92</v>
       </c>
       <c r="O5" s="12">
-        <f t="shared" si="6"/>
-        <v>-5.3371225967755791</v>
+        <f>0.5*(M5-F5)</f>
+        <v>-2.5326999785545783</v>
       </c>
       <c r="P5" s="15">
-        <f t="shared" si="7"/>
-        <v>2.4058774032244301</v>
+        <f>N5+O5</f>
+        <v>8.3873000214454212</v>
       </c>
       <c r="Q5" s="12">
-        <f t="shared" si="8"/>
-        <v>101.2226326254289</v>
+        <f>MAX($P$2:$P$280)-P5</f>
+        <v>105.74514505973896</v>
       </c>
       <c r="R5" s="9">
-        <f t="shared" si="9"/>
-        <v>9.8792135124608719E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q5)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.456698928684306E-3</v>
       </c>
       <c r="S5" s="9">
-        <f t="shared" si="10"/>
-        <v>0.45764538812592725</v>
+        <f>Q5/MAX($Q$2:$Q$28)</f>
+        <v>0.73832312171768166</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>19</v>
+        <v>40</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D6" s="8">
-        <v>45544</v>
+        <v>45511</v>
       </c>
       <c r="E6" s="2">
-        <v>0.35149999999999998</v>
+        <v>0.45179999999999998</v>
       </c>
       <c r="F6" s="1">
-        <v>142.78</v>
+        <v>77.430000000000007</v>
       </c>
       <c r="G6" s="1">
-        <f t="shared" si="0"/>
-        <v>50.187169999999995</v>
+        <f>E6*F6</f>
+        <v>34.982874000000002</v>
       </c>
       <c r="H6" s="11">
-        <v>7.0000000000000007E-2</v>
+        <v>0.1</v>
       </c>
       <c r="I6" s="11">
-        <v>0.18340000000000001</v>
+        <v>0.25990000000000002</v>
       </c>
       <c r="J6" s="9">
-        <f t="shared" si="1"/>
-        <v>0.38167938931297712</v>
+        <f>IFERROR(H6/I6,"")</f>
+        <v>0.38476337052712584</v>
       </c>
       <c r="K6" s="9">
-        <f t="shared" si="2"/>
-        <v>2.0904609101401041E-2</v>
+        <f>IFERROR(J6/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>2.0684478583232333E-2</v>
       </c>
       <c r="L6" s="12">
-        <f t="shared" si="3"/>
-        <v>152.77460000000002</v>
+        <f>F6/(1-(F6*(1+H6)-F6)/(F6*(1+H6)))</f>
+        <v>85.173000000000016</v>
       </c>
       <c r="M6" s="12">
-        <f t="shared" si="4"/>
-        <v>128.23783007005568</v>
+        <f>F6/(1+I6-H6)</f>
+        <v>66.755754806448849</v>
       </c>
       <c r="N6" s="12">
-        <f t="shared" si="5"/>
-        <v>9.9946000000000197</v>
+        <f>L6-F6</f>
+        <v>7.7430000000000092</v>
       </c>
       <c r="O6" s="12">
-        <f t="shared" si="6"/>
-        <v>-7.2710849649721609</v>
+        <f>0.5*(M6-F6)</f>
+        <v>-5.3371225967755791</v>
       </c>
       <c r="P6" s="15">
-        <f t="shared" si="7"/>
-        <v>2.7235150350278587</v>
+        <f>N6+O6</f>
+        <v>2.4058774032244301</v>
       </c>
       <c r="Q6" s="12">
-        <f t="shared" si="8"/>
-        <v>100.90499499362546</v>
+        <f>MAX($P$2:$P$280)-P6</f>
+        <v>111.72656767795996</v>
       </c>
       <c r="R6" s="9">
-        <f t="shared" si="9"/>
-        <v>9.9103121709997969E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q6)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>8.9504226325326178E-3</v>
       </c>
       <c r="S6" s="9">
-        <f t="shared" si="10"/>
-        <v>0.45620929232877483</v>
+        <f>Q6/MAX($Q$2:$Q$28)</f>
+        <v>0.78008600943515383</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>15</v>
+        <v>40</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>103</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>103</v>
       </c>
       <c r="D7" s="8">
-        <v>45460</v>
+        <v>45627</v>
       </c>
       <c r="E7" s="2">
-        <v>0.33529999999999999</v>
+        <v>0.45129999999999998</v>
       </c>
       <c r="F7" s="1">
-        <v>163.15</v>
+        <v>44.38</v>
       </c>
       <c r="G7" s="1">
-        <f t="shared" si="0"/>
-        <v>54.704194999999999</v>
+        <f>E7*F7</f>
+        <v>20.028694000000002</v>
       </c>
       <c r="H7" s="11">
-        <v>6.7199999999999996E-2</v>
+        <v>0.1</v>
       </c>
       <c r="I7" s="11">
-        <v>0.16439999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="J7" s="9">
-        <f t="shared" si="1"/>
-        <v>0.40875912408759124</v>
+        <f>IFERROR(H7/I7,"")</f>
+        <v>0.5</v>
       </c>
       <c r="K7" s="9">
-        <f t="shared" si="2"/>
-        <v>2.2387768228887304E-2</v>
+        <f>IFERROR(J7/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>2.6879479918910414E-2</v>
       </c>
       <c r="L7" s="12">
-        <f t="shared" si="3"/>
-        <v>174.11367999999999</v>
+        <f>F7/(1-(F7*(1+H7)-F7)/(F7*(1+H7)))</f>
+        <v>48.818000000000005</v>
       </c>
       <c r="M7" s="12">
-        <f t="shared" si="4"/>
-        <v>148.69668246445497</v>
+        <f>F7/(1+I7-H7)</f>
+        <v>40.345454545454551</v>
       </c>
       <c r="N7" s="12">
-        <f t="shared" si="5"/>
-        <v>10.963679999999982</v>
+        <f>L7-F7</f>
+        <v>4.4380000000000024</v>
       </c>
       <c r="O7" s="12">
-        <f t="shared" si="6"/>
-        <v>-7.2266587677725198</v>
+        <f>0.5*(M7-F7)</f>
+        <v>-2.0172727272727258</v>
       </c>
       <c r="P7" s="15">
-        <f t="shared" si="7"/>
-        <v>3.7370212322274625</v>
+        <f>N7+O7</f>
+        <v>2.4207272727272766</v>
       </c>
       <c r="Q7" s="12">
-        <f t="shared" si="8"/>
-        <v>99.891488796425861</v>
+        <f>MAX($P$2:$P$280)-P7</f>
+        <v>111.71171780845711</v>
       </c>
       <c r="R7" s="9">
-        <f t="shared" si="9"/>
-        <v>1.0010862907829442E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q7)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>8.9516124146852508E-3</v>
       </c>
       <c r="S7" s="9">
-        <f t="shared" si="10"/>
-        <v>0.45162705192507163</v>
+        <f>Q7/MAX($Q$2:$Q$28)</f>
+        <v>0.77998232616910645</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>21</v>
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D8" s="8">
-        <v>45484</v>
+        <v>45460</v>
       </c>
       <c r="E8" s="2">
-        <v>0.33389999999999997</v>
+        <v>0.43659999999999999</v>
       </c>
       <c r="F8" s="1">
-        <v>188.53</v>
+        <v>160.25</v>
       </c>
       <c r="G8" s="1">
-        <f t="shared" si="0"/>
-        <v>62.950166999999993</v>
+        <f>E8*F8</f>
+        <v>69.965149999999994</v>
       </c>
       <c r="H8" s="11">
-        <f>227.4/F8-1</f>
-        <v>0.20617408370020684</v>
+        <v>6.7199999999999996E-2</v>
       </c>
       <c r="I8" s="11">
-        <v>0.37</v>
+        <v>0.16439999999999999</v>
       </c>
       <c r="J8" s="9">
-        <f t="shared" si="1"/>
-        <v>0.55722725324380229</v>
+        <f>IFERROR(H8/I8,"")</f>
+        <v>0.40875912408759124</v>
       </c>
       <c r="K8" s="9">
-        <f t="shared" si="2"/>
-        <v>3.0519378923437823E-2</v>
+        <f>IFERROR(J8/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>2.1974465335167639E-2</v>
       </c>
       <c r="L8" s="12">
-        <f t="shared" si="3"/>
-        <v>227.4</v>
+        <f>F8/(1-(F8*(1+H8)-F8)/(F8*(1+H8)))</f>
+        <v>171.0188</v>
       </c>
       <c r="M8" s="12">
-        <f t="shared" si="4"/>
-        <v>161.9915808365931</v>
+        <f>F8/(1+I8-H8)</f>
+        <v>146.05359095880419</v>
       </c>
       <c r="N8" s="12">
-        <f t="shared" si="5"/>
-        <v>38.870000000000005</v>
+        <f>L8-F8</f>
+        <v>10.768799999999999</v>
       </c>
       <c r="O8" s="12">
-        <f t="shared" si="6"/>
-        <v>-13.26920958170345</v>
+        <f>0.5*(M8-F8)</f>
+        <v>-7.0982045205979034</v>
       </c>
       <c r="P8" s="15">
-        <f t="shared" si="7"/>
-        <v>25.600790418296555</v>
+        <f>N8+O8</f>
+        <v>3.6705954794020954</v>
       </c>
       <c r="Q8" s="12">
-        <f t="shared" si="8"/>
-        <v>78.027719610356769</v>
+        <f>MAX($P$2:$P$280)-P8</f>
+        <v>110.46184960178229</v>
       </c>
       <c r="R8" s="9">
-        <f t="shared" si="9"/>
-        <v>1.2815958290126271E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q8)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.0528992915203284E-3</v>
       </c>
       <c r="S8" s="9">
-        <f t="shared" si="10"/>
-        <v>0.35277709242954441</v>
+        <f>Q8/MAX($Q$2:$Q$28)</f>
+        <v>0.7712556220204998</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
@@ -1343,419 +2484,420 @@
         <v>36</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D9" s="8">
-        <v>45544</v>
+        <v>45484</v>
       </c>
       <c r="E9" s="2">
-        <v>0.1928</v>
+        <v>0.4108</v>
       </c>
       <c r="F9" s="1">
-        <v>188.12</v>
+        <v>189.76</v>
       </c>
       <c r="G9" s="1">
-        <f t="shared" si="0"/>
-        <v>36.269536000000002</v>
+        <f>E9*F9</f>
+        <v>77.953407999999996</v>
       </c>
       <c r="H9" s="11">
-        <v>0.15</v>
+        <f>227.4/F9-1</f>
+        <v>0.19835581787521095</v>
       </c>
       <c r="I9" s="11">
-        <v>0.37780000000000002</v>
+        <v>0.37</v>
       </c>
       <c r="J9" s="9">
-        <f t="shared" si="1"/>
-        <v>0.39703546850185278</v>
+        <f>IFERROR(H9/I9,"")</f>
+        <v>0.53609680506813773</v>
       </c>
       <c r="K9" s="9">
-        <f t="shared" si="2"/>
-        <v>2.1745662723267889E-2</v>
+        <f>IFERROR(J9/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>2.8820006612842078E-2</v>
       </c>
       <c r="L9" s="12">
-        <f t="shared" si="3"/>
-        <v>216.33799999999999</v>
+        <f>F9/(1-(F9*(1+H9)-F9)/(F9*(1+H9)))</f>
+        <v>227.4</v>
       </c>
       <c r="M9" s="12">
-        <f t="shared" si="4"/>
-        <v>153.21713634142367</v>
+        <f>F9/(1+I9-H9)</f>
+        <v>161.96043380326287</v>
       </c>
       <c r="N9" s="12">
-        <f t="shared" si="5"/>
-        <v>28.217999999999989</v>
+        <f>L9-F9</f>
+        <v>37.640000000000015</v>
       </c>
       <c r="O9" s="12">
-        <f t="shared" si="6"/>
-        <v>-17.451431829288168</v>
+        <f>0.5*(M9-F9)</f>
+        <v>-13.899783098368559</v>
       </c>
       <c r="P9" s="15">
-        <f t="shared" si="7"/>
-        <v>10.766568170711821</v>
+        <f>N9+O9</f>
+        <v>23.740216901631456</v>
       </c>
       <c r="Q9" s="12">
-        <f t="shared" si="8"/>
-        <v>92.861941857941503</v>
+        <f>MAX($P$2:$P$280)-P9</f>
+        <v>90.39222817955293</v>
       </c>
       <c r="R9" s="9">
-        <f t="shared" si="9"/>
-        <v>1.0768674227486882E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q9)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.10628979962041E-2</v>
       </c>
       <c r="S9" s="9">
-        <f t="shared" si="10"/>
-        <v>0.41984522948505815</v>
+        <f>Q9/MAX($Q$2:$Q$28)</f>
+        <v>0.6311275288415521</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>42</v>
+        <v>38</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="D10" s="8">
-        <v>45580</v>
+        <v>45544</v>
       </c>
       <c r="E10" s="2">
-        <v>0.19139999999999999</v>
+        <v>0.35149999999999998</v>
       </c>
       <c r="F10" s="1">
-        <v>135.82</v>
+        <v>142.78</v>
       </c>
       <c r="G10" s="1">
-        <f t="shared" si="0"/>
-        <v>25.995947999999999</v>
+        <f>E10*F10</f>
+        <v>50.187169999999995</v>
       </c>
       <c r="H10" s="11">
-        <v>0.1202</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I10" s="11">
-        <v>0.33710000000000001</v>
+        <v>0.18340000000000001</v>
       </c>
       <c r="J10" s="9">
-        <f t="shared" si="1"/>
-        <v>0.35657075051913378</v>
+        <f>IFERROR(H10/I10,"")</f>
+        <v>0.38167938931297712</v>
       </c>
       <c r="K10" s="9">
-        <f t="shared" si="2"/>
-        <v>1.9529407050280691E-2</v>
+        <f>IFERROR(J10/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>2.0518686961000319E-2</v>
       </c>
       <c r="L10" s="12">
-        <f t="shared" si="3"/>
-        <v>152.14556400000001</v>
+        <f>F10/(1-(F10*(1+H10)-F10)/(F10*(1+H10)))</f>
+        <v>152.77460000000002</v>
       </c>
       <c r="M10" s="12">
-        <f t="shared" si="4"/>
-        <v>111.61147177253677</v>
+        <f>F10/(1+I10-H10)</f>
+        <v>128.23783007005568</v>
       </c>
       <c r="N10" s="12">
-        <f t="shared" si="5"/>
-        <v>16.325564000000014</v>
+        <f>L10-F10</f>
+        <v>9.9946000000000197</v>
       </c>
       <c r="O10" s="12">
-        <f t="shared" si="6"/>
-        <v>-12.10426411373161</v>
+        <f>0.5*(M10-F10)</f>
+        <v>-7.2710849649721609</v>
       </c>
       <c r="P10" s="15">
-        <f t="shared" si="7"/>
-        <v>4.2212998862684046</v>
+        <f>N10+O10</f>
+        <v>2.7235150350278587</v>
       </c>
       <c r="Q10" s="12">
-        <f t="shared" si="8"/>
-        <v>99.407210142384912</v>
+        <f>MAX($P$2:$P$280)-P10</f>
+        <v>111.40893004615653</v>
       </c>
       <c r="R10" s="9">
-        <f t="shared" si="9"/>
-        <v>1.0059632481061082E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q10)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>8.9759411528833617E-3</v>
       </c>
       <c r="S10" s="9">
-        <f t="shared" si="10"/>
-        <v>0.44943754265386154</v>
+        <f>Q10/MAX($Q$2:$Q$28)</f>
+        <v>0.77786823189316223</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>14</v>
+        <v>39</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D11" s="8">
-        <v>45482</v>
+        <v>45580</v>
       </c>
       <c r="E11" s="2">
-        <v>0.18820000000000001</v>
+        <v>0.25669999999999998</v>
       </c>
       <c r="F11" s="1">
-        <v>227.38</v>
+        <v>132.38999999999999</v>
       </c>
       <c r="G11" s="1">
-        <f t="shared" si="0"/>
-        <v>42.792915999999998</v>
+        <f>E11*F11</f>
+        <v>33.984512999999993</v>
       </c>
       <c r="H11" s="11">
-        <v>0.15</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I11" s="11">
-        <v>0.2271</v>
+        <v>0.1623</v>
       </c>
       <c r="J11" s="9">
-        <f t="shared" si="1"/>
-        <v>0.66050198150594452</v>
+        <f>IFERROR(H11/I11,"")</f>
+        <v>0.43130006161429457</v>
       </c>
       <c r="K11" s="9">
-        <f t="shared" si="2"/>
-        <v>3.6175743623296383E-2</v>
+        <f>IFERROR(J11/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>2.3186242690372512E-2</v>
       </c>
       <c r="L11" s="12">
-        <f t="shared" si="3"/>
-        <v>261.48699999999997</v>
+        <f>F11/(1-(F11*(1+H11)-F11)/(F11*(1+H11)))</f>
+        <v>141.65729999999999</v>
       </c>
       <c r="M11" s="12">
-        <f t="shared" si="4"/>
-        <v>211.10389007520189</v>
+        <f>F11/(1+I11-H11)</f>
+        <v>121.20296621807194</v>
       </c>
       <c r="N11" s="12">
-        <f t="shared" si="5"/>
-        <v>34.106999999999971</v>
+        <f>L11-F11</f>
+        <v>9.2673000000000059</v>
       </c>
       <c r="O11" s="12">
-        <f t="shared" si="6"/>
-        <v>-8.1380549623990532</v>
+        <f>0.5*(M11-F11)</f>
+        <v>-5.5935168909640254</v>
       </c>
       <c r="P11" s="15">
-        <f t="shared" si="7"/>
-        <v>25.968945037600918</v>
+        <f>N11+O11</f>
+        <v>3.6737831090359805</v>
       </c>
       <c r="Q11" s="12">
-        <f t="shared" si="8"/>
-        <v>77.659564991052406</v>
+        <f>MAX($P$2:$P$280)-P11</f>
+        <v>110.45866197214841</v>
       </c>
       <c r="R11" s="9">
-        <f t="shared" si="9"/>
-        <v>1.2876713900151458E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q11)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.0531605411999731E-3</v>
       </c>
       <c r="S11" s="9">
-        <f t="shared" si="10"/>
-        <v>0.35111260041553638</v>
+        <f>Q11/MAX($Q$2:$Q$28)</f>
+        <v>0.77123336567330925</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>60</v>
+        <v>37</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="D12" s="8">
-        <v>45580</v>
+        <v>45511</v>
       </c>
       <c r="E12" s="2">
-        <v>0.18010000000000001</v>
+        <v>0.1938</v>
       </c>
       <c r="F12" s="1">
-        <v>133.19999999999999</v>
+        <v>283.43</v>
       </c>
       <c r="G12" s="1">
-        <f t="shared" si="0"/>
-        <v>23.989319999999999</v>
+        <f>E12*F12</f>
+        <v>54.928733999999999</v>
       </c>
       <c r="H12" s="11">
-        <v>7.0000000000000007E-2</v>
+        <v>0.25</v>
       </c>
       <c r="I12" s="11">
-        <v>0.1623</v>
+        <v>0.26</v>
       </c>
       <c r="J12" s="9">
-        <f t="shared" si="1"/>
-        <v>0.43130006161429457</v>
+        <f>IFERROR(H12/I12,"")</f>
+        <v>0.96153846153846145</v>
       </c>
       <c r="K12" s="9">
-        <f t="shared" si="2"/>
-        <v>2.3622337086857372E-2</v>
+        <f>IFERROR(J12/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>5.1691307536366179E-2</v>
       </c>
       <c r="L12" s="12">
-        <f t="shared" si="3"/>
-        <v>142.524</v>
+        <f>F12/(1-(F12*(1+H12)-F12)/(F12*(1+H12)))</f>
+        <v>354.28750000000002</v>
       </c>
       <c r="M12" s="12">
-        <f t="shared" si="4"/>
-        <v>121.94452073606151</v>
+        <f>F12/(1+I12-H12)</f>
+        <v>280.62376237623761</v>
       </c>
       <c r="N12" s="12">
-        <f t="shared" si="5"/>
-        <v>9.3240000000000123</v>
+        <f>L12-F12</f>
+        <v>70.857500000000016</v>
       </c>
       <c r="O12" s="12">
-        <f t="shared" si="6"/>
-        <v>-5.6277396319692414</v>
+        <f>0.5*(M12-F12)</f>
+        <v>-1.4031188118811997</v>
       </c>
       <c r="P12" s="15">
-        <f t="shared" si="7"/>
-        <v>3.6962603680307708</v>
+        <f>N12+O12</f>
+        <v>69.454381188118816</v>
       </c>
       <c r="Q12" s="12">
-        <f t="shared" si="8"/>
-        <v>99.932249660622546</v>
+        <f>MAX($P$2:$P$280)-P12</f>
+        <v>44.67806389306557</v>
       </c>
       <c r="R12" s="9">
-        <f t="shared" si="9"/>
-        <v>1.0006779627158154E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q12)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>2.2382348581474875E-2</v>
       </c>
       <c r="S12" s="9">
-        <f t="shared" si="10"/>
-        <v>0.45181133898649067</v>
+        <f>Q12/MAX($Q$2:$Q$28)</f>
+        <v>0.311946686414727</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>7</v>
+        <v>36</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D13" s="8">
-        <v>45511</v>
+        <v>45544</v>
       </c>
       <c r="E13" s="2">
-        <v>0.14610000000000001</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F13" s="1">
-        <v>273.45999999999998</v>
+        <v>188.12</v>
       </c>
       <c r="G13" s="1">
-        <f t="shared" si="0"/>
-        <v>39.952506</v>
+        <f>E13*F13</f>
+        <v>1.8812000000000001E-17</v>
       </c>
       <c r="H13" s="11">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="I13" s="11">
-        <v>0.26</v>
+        <v>0.37780000000000002</v>
       </c>
       <c r="J13" s="9">
-        <f t="shared" si="1"/>
-        <v>0.96153846153846145</v>
+        <f>IFERROR(H13/I13,"")</f>
+        <v>0.39703546850185278</v>
       </c>
       <c r="K13" s="9">
-        <f t="shared" si="2"/>
-        <v>5.2663534466991083E-2</v>
+        <f>IFERROR(J13/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>2.1344213805381481E-2</v>
       </c>
       <c r="L13" s="12">
-        <f t="shared" si="3"/>
-        <v>341.82499999999999</v>
+        <f>F13/(1-(F13*(1+H13)-F13)/(F13*(1+H13)))</f>
+        <v>216.33799999999999</v>
       </c>
       <c r="M13" s="12">
-        <f t="shared" si="4"/>
-        <v>270.75247524752473</v>
+        <f>F13/(1+I13-H13)</f>
+        <v>153.21713634142367</v>
       </c>
       <c r="N13" s="12">
-        <f t="shared" si="5"/>
-        <v>68.365000000000009</v>
+        <f>L13-F13</f>
+        <v>28.217999999999989</v>
       </c>
       <c r="O13" s="12">
-        <f t="shared" si="6"/>
-        <v>-1.3537623762376256</v>
+        <f>0.5*(M13-F13)</f>
+        <v>-17.451431829288168</v>
       </c>
       <c r="P13" s="15">
-        <f t="shared" si="7"/>
-        <v>67.011237623762383</v>
+        <f>N13+O13</f>
+        <v>10.766568170711821</v>
       </c>
       <c r="Q13" s="12">
-        <f t="shared" si="8"/>
-        <v>36.61727240489094</v>
+        <f>MAX($P$2:$P$280)-P13</f>
+        <v>103.36587691047256</v>
       </c>
       <c r="R13" s="9">
-        <f t="shared" si="9"/>
-        <v>2.7309516365463388E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q13)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.6743725288193673E-3</v>
       </c>
       <c r="S13" s="9">
-        <f t="shared" si="10"/>
-        <v>0.1655531515749106</v>
+        <f>Q13/MAX($Q$2:$Q$28)</f>
+        <v>0.72171083482377829</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>11</v>
+        <v>39</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="D14" s="8">
-        <v>45574</v>
+        <v>45580</v>
       </c>
       <c r="E14" s="2">
-        <v>0.13370000000000001</v>
+        <v>0.19139999999999999</v>
       </c>
       <c r="F14" s="1">
-        <v>423.77</v>
+        <v>135.82</v>
       </c>
       <c r="G14" s="1">
-        <f t="shared" si="0"/>
-        <v>56.658049000000005</v>
+        <f>E14*F14</f>
+        <v>25.995947999999999</v>
       </c>
       <c r="H14" s="11">
-        <v>0.15</v>
+        <v>0.1202</v>
       </c>
       <c r="I14" s="11">
-        <v>0.1963</v>
+        <v>0.33710000000000001</v>
       </c>
       <c r="J14" s="9">
-        <f t="shared" si="1"/>
-        <v>0.76413652572592972</v>
+        <f>IFERROR(H14/I14,"")</f>
+        <v>0.35657075051913378</v>
       </c>
       <c r="K14" s="9">
-        <f t="shared" si="2"/>
-        <v>4.1851815470456494E-2</v>
+        <f>IFERROR(J14/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>1.9168872656499743E-2</v>
       </c>
       <c r="L14" s="12">
-        <f t="shared" si="3"/>
-        <v>487.33549999999991</v>
+        <f>F14/(1-(F14*(1+H14)-F14)/(F14*(1+H14)))</f>
+        <v>152.14556400000001</v>
       </c>
       <c r="M14" s="12">
-        <f t="shared" si="4"/>
-        <v>405.01768135334032</v>
+        <f>F14/(1+I14-H14)</f>
+        <v>111.61147177253677</v>
       </c>
       <c r="N14" s="12">
-        <f t="shared" si="5"/>
-        <v>63.565499999999929</v>
+        <f>L14-F14</f>
+        <v>16.325564000000014</v>
       </c>
       <c r="O14" s="12">
-        <f t="shared" si="6"/>
-        <v>-9.3761593233298299</v>
+        <f>0.5*(M14-F14)</f>
+        <v>-12.10426411373161</v>
       </c>
       <c r="P14" s="15">
-        <f t="shared" si="7"/>
-        <v>54.189340676670099</v>
+        <f>N14+O14</f>
+        <v>4.2212998862684046</v>
       </c>
       <c r="Q14" s="12">
-        <f t="shared" si="8"/>
-        <v>49.439169351983224</v>
+        <f>MAX($P$2:$P$280)-P14</f>
+        <v>109.91114519491597</v>
       </c>
       <c r="R14" s="9">
-        <f t="shared" si="9"/>
-        <v>2.0226877051280505E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q14)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.0982583997883393E-3</v>
       </c>
       <c r="S14" s="9">
-        <f t="shared" si="10"/>
-        <v>0.22352321076687609</v>
+        <f>Q14/MAX($Q$2:$Q$28)</f>
+        <v>0.76741054907089512</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
@@ -1763,140 +2905,139 @@
         <v>36</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D15" s="8">
-        <v>45483</v>
+        <v>45482</v>
       </c>
       <c r="E15" s="2">
-        <v>0.1195</v>
+        <v>0.18820000000000001</v>
       </c>
       <c r="F15" s="1">
-        <v>167.24</v>
+        <v>227.38</v>
       </c>
       <c r="G15" s="1">
-        <f t="shared" si="0"/>
-        <v>19.98518</v>
+        <f>E15*F15</f>
+        <v>42.792915999999998</v>
       </c>
       <c r="H15" s="11">
-        <f>190.41/F15-1</f>
-        <v>0.13854341066730447</v>
+        <v>0.15</v>
       </c>
       <c r="I15" s="11">
-        <v>0.26790000000000003</v>
+        <v>0.2271</v>
       </c>
       <c r="J15" s="9">
-        <f t="shared" si="1"/>
-        <v>0.51714598979956872</v>
+        <f>IFERROR(H15/I15,"")</f>
+        <v>0.66050198150594452</v>
       </c>
       <c r="K15" s="9">
-        <f t="shared" si="2"/>
-        <v>2.8324125084606841E-2</v>
+        <f>IFERROR(J15/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>3.5507899496579148E-2</v>
       </c>
       <c r="L15" s="12">
-        <f t="shared" si="3"/>
-        <v>190.41</v>
+        <f>F15/(1-(F15*(1+H15)-F15)/(F15*(1+H15)))</f>
+        <v>261.48699999999997</v>
       </c>
       <c r="M15" s="12">
-        <f t="shared" si="4"/>
-        <v>148.08431772538498</v>
+        <f>F15/(1+I15-H15)</f>
+        <v>211.10389007520189</v>
       </c>
       <c r="N15" s="12">
-        <f t="shared" si="5"/>
-        <v>23.169999999999987</v>
+        <f>L15-F15</f>
+        <v>34.106999999999971</v>
       </c>
       <c r="O15" s="12">
-        <f t="shared" si="6"/>
-        <v>-9.5778411373075159</v>
+        <f>0.5*(M15-F15)</f>
+        <v>-8.1380549623990532</v>
       </c>
       <c r="P15" s="15">
-        <f t="shared" si="7"/>
-        <v>13.592158862692472</v>
+        <f>N15+O15</f>
+        <v>25.968945037600918</v>
       </c>
       <c r="Q15" s="12">
-        <f t="shared" si="8"/>
-        <v>90.036351165960852</v>
+        <f>MAX($P$2:$P$280)-P15</f>
+        <v>88.163500043583468</v>
       </c>
       <c r="R15" s="9">
-        <f t="shared" si="9"/>
-        <v>1.1106625124742506E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q15)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.1342562392664218E-2</v>
       </c>
       <c r="S15" s="9">
-        <f t="shared" si="10"/>
-        <v>0.40707023524338853</v>
+        <f>Q15/MAX($Q$2:$Q$28)</f>
+        <v>0.6155663272953309</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>33</v>
+        <v>36</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D16" s="8">
-        <v>45562</v>
+        <v>45574</v>
       </c>
       <c r="E16" s="2">
-        <v>4.0300000000000002E-2</v>
+        <v>0.13370000000000001</v>
       </c>
       <c r="F16" s="1">
-        <v>668.82</v>
+        <v>423.77</v>
       </c>
       <c r="G16" s="1">
-        <f t="shared" si="0"/>
-        <v>26.953446000000003</v>
+        <f>E16*F16</f>
+        <v>56.658049000000005</v>
       </c>
       <c r="H16" s="11">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="I16" s="11">
-        <v>0.28000000000000003</v>
+        <v>0.1963</v>
       </c>
       <c r="J16" s="9">
-        <f t="shared" si="1"/>
-        <v>0.17857142857142858</v>
+        <f>IFERROR(H16/I16,"")</f>
+        <v>0.76413652572592972</v>
       </c>
       <c r="K16" s="9">
-        <f t="shared" si="2"/>
-        <v>9.7803706867269167E-3</v>
+        <f>IFERROR(J16/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>4.10791847971122E-2</v>
       </c>
       <c r="L16" s="12">
-        <f t="shared" si="3"/>
-        <v>702.26100000000008</v>
+        <f>F16/(1-(F16*(1+H16)-F16)/(F16*(1+H16)))</f>
+        <v>487.33549999999991</v>
       </c>
       <c r="M16" s="12">
-        <f t="shared" si="4"/>
-        <v>543.7560975609756</v>
+        <f>F16/(1+I16-H16)</f>
+        <v>405.01768135334032</v>
       </c>
       <c r="N16" s="12">
-        <f t="shared" si="5"/>
-        <v>33.441000000000031</v>
+        <f>L16-F16</f>
+        <v>63.565499999999929</v>
       </c>
       <c r="O16" s="12">
-        <f t="shared" si="6"/>
-        <v>-62.531951219512223</v>
+        <f>0.5*(M16-F16)</f>
+        <v>-9.3761593233298299</v>
       </c>
       <c r="P16" s="15">
-        <f t="shared" si="7"/>
-        <v>-29.090951219512192</v>
+        <f>N16+O16</f>
+        <v>54.189340676670099</v>
       </c>
       <c r="Q16" s="12">
-        <f t="shared" si="8"/>
-        <v>132.71946124816552</v>
+        <f>MAX($P$2:$P$280)-P16</f>
+        <v>59.943104404514287</v>
       </c>
       <c r="R16" s="9">
-        <f t="shared" si="9"/>
-        <v>7.5346900190481469E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q16)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>1.6682485999585474E-2</v>
       </c>
       <c r="S16" s="9">
-        <f t="shared" si="10"/>
-        <v>0.60004810959166965</v>
+        <f>Q16/MAX($Q$2:$Q$28)</f>
+        <v>0.41852871774290379</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
@@ -1913,14 +3054,14 @@
         <v>45511</v>
       </c>
       <c r="E17" s="2">
-        <v>3.2899999999999999E-2</v>
+        <v>0.12939999999999999</v>
       </c>
       <c r="F17" s="1">
-        <v>455.4</v>
+        <v>501.56</v>
       </c>
       <c r="G17" s="1">
-        <f t="shared" si="0"/>
-        <v>14.982659999999999</v>
+        <f>E17*F17</f>
+        <v>64.901863999999989</v>
       </c>
       <c r="H17" s="11">
         <v>0.25</v>
@@ -1929,43 +3070,43 @@
         <v>0.29699999999999999</v>
       </c>
       <c r="J17" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H17/I17,"")</f>
         <v>0.84175084175084181</v>
       </c>
       <c r="K17" s="9">
-        <f t="shared" si="2"/>
-        <v>4.6102757445850781E-2</v>
+        <f>IFERROR(J17/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>4.5251649695135378E-2</v>
       </c>
       <c r="L17" s="12">
-        <f t="shared" si="3"/>
-        <v>569.25</v>
+        <f>F17/(1-(F17*(1+H17)-F17)/(F17*(1+H17)))</f>
+        <v>626.95000000000005</v>
       </c>
       <c r="M17" s="12">
-        <f t="shared" si="4"/>
-        <v>434.95702005730658</v>
+        <f>F17/(1+I17-H17)</f>
+        <v>479.04489016236869</v>
       </c>
       <c r="N17" s="12">
-        <f t="shared" si="5"/>
-        <v>113.85000000000002</v>
+        <f>L17-F17</f>
+        <v>125.39000000000004</v>
       </c>
       <c r="O17" s="12">
-        <f t="shared" si="6"/>
-        <v>-10.221489971346699</v>
+        <f>0.5*(M17-F17)</f>
+        <v>-11.257554918815657</v>
       </c>
       <c r="P17" s="15">
-        <f t="shared" si="7"/>
-        <v>103.62851002865332</v>
+        <f>N17+O17</f>
+        <v>114.13244508118439</v>
       </c>
       <c r="Q17" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($P$2:$P$280)-P17</f>
         <v>0</v>
       </c>
       <c r="R17" s="9">
-        <f t="shared" si="9"/>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q17)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
         <v>0</v>
       </c>
       <c r="S17" s="9">
-        <f t="shared" si="10"/>
+        <f>Q17/MAX($Q$2:$Q$28)</f>
         <v>0</v>
       </c>
     </row>
@@ -1974,210 +3115,211 @@
         <v>36</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="D18" s="8">
-        <v>45481</v>
+        <v>45483</v>
       </c>
       <c r="E18" s="2">
-        <v>2.8500000000000001E-2</v>
+        <v>0.1195</v>
       </c>
       <c r="F18" s="1">
-        <v>700.32</v>
+        <v>167.24</v>
       </c>
       <c r="G18" s="1">
-        <f t="shared" si="0"/>
-        <v>19.959120000000002</v>
+        <f>E18*F18</f>
+        <v>19.98518</v>
       </c>
       <c r="H18" s="11">
-        <v>0.1</v>
+        <f>190.41/F18-1</f>
+        <v>0.13854341066730447</v>
       </c>
       <c r="I18" s="11">
-        <v>0.45340000000000003</v>
+        <v>0.26790000000000003</v>
       </c>
       <c r="J18" s="9">
-        <f t="shared" si="1"/>
-        <v>0.22055580061755625</v>
+        <f>IFERROR(H18/I18,"")</f>
+        <v>0.51714598979956872</v>
       </c>
       <c r="K18" s="9">
-        <f t="shared" si="2"/>
-        <v>1.2079857928026187E-2</v>
+        <f>IFERROR(J18/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>2.7801230495925113E-2</v>
       </c>
       <c r="L18" s="12">
-        <f t="shared" si="3"/>
-        <v>770.35200000000009</v>
+        <f>F18/(1-(F18*(1+H18)-F18)/(F18*(1+H18)))</f>
+        <v>190.41</v>
       </c>
       <c r="M18" s="12">
-        <f t="shared" si="4"/>
-        <v>517.45234224915032</v>
+        <f>F18/(1+I18-H18)</f>
+        <v>148.08431772538498</v>
       </c>
       <c r="N18" s="12">
-        <f t="shared" si="5"/>
-        <v>70.032000000000039</v>
+        <f>L18-F18</f>
+        <v>23.169999999999987</v>
       </c>
       <c r="O18" s="12">
-        <f t="shared" si="6"/>
-        <v>-91.433828875424865</v>
+        <f>0.5*(M18-F18)</f>
+        <v>-9.5778411373075159</v>
       </c>
       <c r="P18" s="15">
-        <f t="shared" si="7"/>
-        <v>-21.401828875424826</v>
+        <f>N18+O18</f>
+        <v>13.592158862692472</v>
       </c>
       <c r="Q18" s="12">
-        <f t="shared" si="8"/>
-        <v>125.03033890407815</v>
+        <f>MAX($P$2:$P$280)-P18</f>
+        <v>100.54028621849191</v>
       </c>
       <c r="R18" s="9">
-        <f t="shared" si="9"/>
-        <v>7.9980587812945834E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q18)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.9462617186788418E-3</v>
       </c>
       <c r="S18" s="9">
-        <f t="shared" si="10"/>
-        <v>0.565284230326356</v>
+        <f>Q18/MAX($Q$2:$Q$28)</f>
+        <v>0.70198227953907921</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>23</v>
+        <v>40</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="C19" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="D19" s="8">
-        <v>45482</v>
+        <v>45511</v>
       </c>
       <c r="E19" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>0.158</v>
       </c>
       <c r="F19" s="1">
-        <v>147.01</v>
+        <v>189.72</v>
       </c>
       <c r="G19" s="1">
-        <f t="shared" si="0"/>
-        <v>1.4700999999999999E-17</v>
+        <f>E19*F19</f>
+        <v>29.975760000000001</v>
       </c>
       <c r="H19" s="11">
-        <v>0.15</v>
+        <f>196.02/F19-1</f>
+        <v>3.3206831119544589E-2</v>
       </c>
       <c r="I19" s="11">
-        <v>0.52380000000000004</v>
+        <v>0.52980000000000005</v>
       </c>
       <c r="J19" s="9">
-        <f t="shared" si="1"/>
-        <v>0.28636884306987398</v>
+        <f>IFERROR(H19/I19,"")</f>
+        <v>6.2678050433266491E-2</v>
       </c>
       <c r="K19" s="9">
-        <f t="shared" si="2"/>
-        <v>1.5684443254773976E-2</v>
+        <f>IFERROR(J19/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>3.3695067959548818E-3</v>
       </c>
       <c r="L19" s="12">
-        <f t="shared" si="3"/>
-        <v>169.06149999999997</v>
+        <f>F19/(1-(F19*(1+H19)-F19)/(F19*(1+H19)))</f>
+        <v>196.02</v>
       </c>
       <c r="M19" s="12">
-        <f t="shared" si="4"/>
-        <v>107.00975396709855</v>
+        <f>F19/(1+I19-H19)</f>
+        <v>126.76791792516488</v>
       </c>
       <c r="N19" s="12">
-        <f t="shared" si="5"/>
-        <v>22.051499999999976</v>
+        <f>L19-F19</f>
+        <v>6.3000000000000114</v>
       </c>
       <c r="O19" s="12">
-        <f t="shared" si="6"/>
-        <v>-20.000123016450722</v>
+        <f>0.5*(M19-F19)</f>
+        <v>-31.476041037417559</v>
       </c>
       <c r="P19" s="15">
-        <f t="shared" si="7"/>
-        <v>2.0513769835492539</v>
+        <f>N19+O19</f>
+        <v>-25.176041037417548</v>
       </c>
       <c r="Q19" s="12">
-        <f t="shared" si="8"/>
-        <v>101.57713304510406</v>
+        <f>MAX($P$2:$P$280)-P19</f>
+        <v>139.30848611860193</v>
       </c>
       <c r="R19" s="9">
-        <f t="shared" si="9"/>
-        <v>9.8447354244184312E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q19)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>7.1783135964067412E-3</v>
       </c>
       <c r="S19" s="9">
-        <f t="shared" si="10"/>
-        <v>0.45924814709341422</v>
+        <f>Q19/MAX($Q$2:$Q$28)</f>
+        <v>0.97266570767617244</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>47</v>
+        <v>39</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="C20" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="D20" s="8">
-        <v>45511</v>
+        <v>45562</v>
       </c>
       <c r="E20" s="2">
-        <v>1E-22</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F20" s="1">
-        <v>187.36</v>
+        <v>668.82</v>
       </c>
       <c r="G20" s="1">
-        <f t="shared" si="0"/>
-        <v>1.8736000000000003E-20</v>
+        <f>E20*F20</f>
+        <v>6.6881999999999999E-17</v>
       </c>
       <c r="H20" s="11">
-        <f>196.02/F20-1</f>
-        <v>4.6221178479931568E-2</v>
+        <v>0.05</v>
       </c>
       <c r="I20" s="11">
-        <v>0.52980000000000005</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="J20" s="9">
-        <f t="shared" si="1"/>
-        <v>8.7242692487602053E-2</v>
+        <f>IFERROR(H20/I20,"")</f>
+        <v>0.17857142857142858</v>
       </c>
       <c r="K20" s="9">
-        <f t="shared" si="2"/>
-        <v>4.7782888845264923E-3</v>
+        <f>IFERROR(J20/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>9.5998142567537189E-3</v>
       </c>
       <c r="L20" s="12">
-        <f t="shared" si="3"/>
-        <v>196.01999999999998</v>
+        <f>F20/(1-(F20*(1+H20)-F20)/(F20*(1+H20)))</f>
+        <v>702.26100000000008</v>
       </c>
       <c r="M20" s="12">
-        <f t="shared" si="4"/>
-        <v>126.28921179127629</v>
+        <f>F20/(1+I20-H20)</f>
+        <v>543.7560975609756</v>
       </c>
       <c r="N20" s="12">
-        <f t="shared" si="5"/>
-        <v>8.6599999999999682</v>
+        <f>L20-F20</f>
+        <v>33.441000000000031</v>
       </c>
       <c r="O20" s="12">
-        <f t="shared" si="6"/>
-        <v>-30.535394104361863</v>
+        <f>0.5*(M20-F20)</f>
+        <v>-62.531951219512223</v>
       </c>
       <c r="P20" s="15">
-        <f t="shared" si="7"/>
-        <v>-21.875394104361895</v>
+        <f>N20+O20</f>
+        <v>-29.090951219512192</v>
       </c>
       <c r="Q20" s="12">
-        <f t="shared" si="8"/>
-        <v>125.50390413301523</v>
+        <f>MAX($P$2:$P$280)-P20</f>
+        <v>143.22339630069658</v>
       </c>
       <c r="R20" s="9">
-        <f t="shared" si="9"/>
-        <v>7.9678796202240099E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q20)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>6.9820994741704532E-3</v>
       </c>
       <c r="S20" s="9">
-        <f t="shared" si="10"/>
-        <v>0.5674253023117275</v>
+        <f>Q20/MAX($Q$2:$Q$28)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
@@ -2185,140 +3327,139 @@
         <v>36</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="C21" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D21" s="8">
         <v>45481</v>
       </c>
       <c r="E21" s="2">
-        <v>1E-22</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F21" s="1">
-        <v>169.34</v>
+        <v>700.32</v>
       </c>
       <c r="G21" s="1">
-        <f t="shared" si="0"/>
-        <v>1.6934000000000002E-20</v>
+        <f>E21*F21</f>
+        <v>7.0031999999999998E-17</v>
       </c>
       <c r="H21" s="11">
         <v>0.1</v>
       </c>
       <c r="I21" s="11">
-        <v>0.4259</v>
+        <v>0.45340000000000003</v>
       </c>
       <c r="J21" s="9">
-        <f t="shared" si="1"/>
-        <v>0.23479690068091102</v>
+        <f>IFERROR(H21/I21,"")</f>
+        <v>0.22055580061755625</v>
       </c>
       <c r="K21" s="9">
-        <f t="shared" si="2"/>
-        <v>1.2859844058621913E-2</v>
+        <f>IFERROR(J21/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>1.1856850427397625E-2</v>
       </c>
       <c r="L21" s="12">
-        <f t="shared" si="3"/>
-        <v>186.27400000000003</v>
+        <f>F21/(1-(F21*(1+H21)-F21)/(F21*(1+H21)))</f>
+        <v>770.35200000000009</v>
       </c>
       <c r="M21" s="12">
-        <f t="shared" si="4"/>
-        <v>127.71702239987934</v>
+        <f>F21/(1+I21-H21)</f>
+        <v>517.45234224915032</v>
       </c>
       <c r="N21" s="12">
-        <f t="shared" si="5"/>
-        <v>16.934000000000026</v>
+        <f>L21-F21</f>
+        <v>70.032000000000039</v>
       </c>
       <c r="O21" s="12">
-        <f t="shared" si="6"/>
-        <v>-20.811488800060332</v>
+        <f>0.5*(M21-F21)</f>
+        <v>-91.433828875424865</v>
       </c>
       <c r="P21" s="15">
-        <f t="shared" si="7"/>
-        <v>-3.8774888000603056</v>
+        <f>N21+O21</f>
+        <v>-21.401828875424826</v>
       </c>
       <c r="Q21" s="12">
-        <f t="shared" si="8"/>
-        <v>107.50599882871363</v>
+        <f>MAX($P$2:$P$280)-P21</f>
+        <v>135.53427395660921</v>
       </c>
       <c r="R21" s="9">
-        <f t="shared" si="9"/>
-        <v>9.3018065121488955E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q21)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>7.3782075249847591E-3</v>
       </c>
       <c r="S21" s="9">
-        <f t="shared" si="10"/>
-        <v>0.48605359575949542</v>
+        <f>Q21/MAX($Q$2:$Q$28)</f>
+        <v>0.94631378292451529</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>40</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>32</v>
+        <v>36</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" t="s">
+        <v>24</v>
       </c>
       <c r="D22" s="8">
-        <v>45511</v>
+        <v>45482</v>
       </c>
       <c r="E22" s="2">
-        <v>1E-22</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F22" s="1">
-        <v>113.58</v>
+        <v>147.01</v>
       </c>
       <c r="G22" s="1">
-        <f t="shared" si="0"/>
-        <v>1.1358E-20</v>
+        <f>E22*F22</f>
+        <v>1.4700999999999999E-17</v>
       </c>
       <c r="H22" s="11">
-        <f>121.15/F22-1</f>
-        <v>6.664905793273479E-2</v>
+        <v>0.15</v>
       </c>
       <c r="I22" s="11">
-        <v>0.16439999999999999</v>
+        <v>0.52380000000000004</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" si="1"/>
-        <v>0.40540789496797319</v>
+        <f>IFERROR(H22/I22,"")</f>
+        <v>0.28636884306987398</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" si="2"/>
-        <v>2.2204221155829606E-2</v>
+        <f>IFERROR(J22/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>1.5394891133396571E-2</v>
       </c>
       <c r="L22" s="12">
-        <f t="shared" si="3"/>
-        <v>121.15000000000002</v>
+        <f>F22/(1-(F22*(1+H22)-F22)/(F22*(1+H22)))</f>
+        <v>169.06149999999997</v>
       </c>
       <c r="M22" s="12">
-        <f t="shared" si="4"/>
-        <v>103.46609203186667</v>
+        <f>F22/(1+I22-H22)</f>
+        <v>107.00975396709855</v>
       </c>
       <c r="N22" s="12">
-        <f t="shared" si="5"/>
-        <v>7.5700000000000216</v>
+        <f>L22-F22</f>
+        <v>22.051499999999976</v>
       </c>
       <c r="O22" s="12">
-        <f t="shared" si="6"/>
-        <v>-5.0569539840666664</v>
+        <f>0.5*(M22-F22)</f>
+        <v>-20.000123016450722</v>
       </c>
       <c r="P22" s="15">
-        <f t="shared" si="7"/>
-        <v>2.5130460159333552</v>
+        <f>N22+O22</f>
+        <v>2.0513769835492539</v>
       </c>
       <c r="Q22" s="12">
-        <f t="shared" si="8"/>
-        <v>101.11546401271997</v>
+        <f>MAX($P$2:$P$280)-P22</f>
+        <v>112.08106809763513</v>
       </c>
       <c r="R22" s="9">
-        <f t="shared" si="9"/>
-        <v>9.8896841325299516E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q22)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>8.9221134039237406E-3</v>
       </c>
       <c r="S22" s="9">
-        <f t="shared" si="10"/>
-        <v>0.45716085991236471</v>
+        <f>Q22/MAX($Q$2:$Q$28)</f>
+        <v>0.78256116662896091</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
@@ -2326,69 +3467,69 @@
         <v>36</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="C23" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
       <c r="D23" s="8">
         <v>45481</v>
       </c>
       <c r="E23" s="2">
-        <v>1E-22</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F23" s="1">
-        <v>64.349999999999994</v>
+        <v>169.34</v>
       </c>
       <c r="G23" s="1">
-        <f t="shared" si="0"/>
-        <v>6.4349999999999995E-21</v>
+        <f>E23*F23</f>
+        <v>1.6933999999999999E-17</v>
       </c>
       <c r="H23" s="11">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I23" s="11">
-        <v>0.67300000000000004</v>
+        <v>0.4259</v>
       </c>
       <c r="J23" s="9">
-        <f t="shared" si="1"/>
-        <v>0.22288261515601782</v>
+        <f>IFERROR(H23/I23,"")</f>
+        <v>0.23479690068091102</v>
       </c>
       <c r="K23" s="9">
-        <f t="shared" si="2"/>
-        <v>1.2207297736776536E-2</v>
+        <f>IFERROR(J23/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>1.2622437153749902E-2</v>
       </c>
       <c r="L23" s="12">
-        <f t="shared" si="3"/>
-        <v>74.002499999999984</v>
+        <f>F23/(1-(F23*(1+H23)-F23)/(F23*(1+H23)))</f>
+        <v>186.27400000000003</v>
       </c>
       <c r="M23" s="12">
-        <f t="shared" si="4"/>
-        <v>42.252133946158892</v>
+        <f>F23/(1+I23-H23)</f>
+        <v>127.71702239987934</v>
       </c>
       <c r="N23" s="12">
-        <f t="shared" si="5"/>
-        <v>9.6524999999999892</v>
+        <f>L23-F23</f>
+        <v>16.934000000000026</v>
       </c>
       <c r="O23" s="12">
-        <f t="shared" si="6"/>
-        <v>-11.048933026920551</v>
+        <f>0.5*(M23-F23)</f>
+        <v>-20.811488800060332</v>
       </c>
       <c r="P23" s="15">
-        <f t="shared" si="7"/>
-        <v>-1.3964330269205618</v>
+        <f>N23+O23</f>
+        <v>-3.8774888000603056</v>
       </c>
       <c r="Q23" s="12">
-        <f t="shared" si="8"/>
-        <v>105.02494305557389</v>
+        <f>MAX($P$2:$P$280)-P23</f>
+        <v>118.00993388124469</v>
       </c>
       <c r="R23" s="9">
-        <f t="shared" si="9"/>
-        <v>9.5215476524548124E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q23)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>8.4738628953585915E-3</v>
       </c>
       <c r="S23" s="9">
-        <f t="shared" si="10"/>
-        <v>0.47483630469710741</v>
+        <f>Q23/MAX($Q$2:$Q$28)</f>
+        <v>0.82395709729912847</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
@@ -2396,140 +3537,140 @@
         <v>40</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D24" s="8">
         <v>45511</v>
       </c>
       <c r="E24" s="2">
-        <v>1E-22</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F24" s="1">
-        <v>20.82</v>
+        <v>113.58</v>
       </c>
       <c r="G24" s="1">
-        <f t="shared" si="0"/>
-        <v>2.0820000000000001E-21</v>
-      </c>
-      <c r="H24" s="13">
-        <v>0.05</v>
+        <f>E24*F24</f>
+        <v>1.1357999999999999E-17</v>
+      </c>
+      <c r="H24" s="11">
+        <f>121.15/F24-1</f>
+        <v>6.664905793273479E-2</v>
       </c>
       <c r="I24" s="11">
-        <v>0.7389</v>
+        <v>0.16439999999999999</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" si="1"/>
-        <v>6.7668155366084726E-2</v>
+        <f>IFERROR(H24/I24,"")</f>
+        <v>0.40540789496797319</v>
       </c>
       <c r="K24" s="9">
-        <f t="shared" si="2"/>
-        <v>3.7061900017370912E-3</v>
+        <f>IFERROR(J24/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>2.1794306743518756E-2</v>
       </c>
       <c r="L24" s="12">
-        <f t="shared" si="3"/>
-        <v>21.861000000000001</v>
+        <f>F24/(1-(F24*(1+H24)-F24)/(F24*(1+H24)))</f>
+        <v>121.15000000000002</v>
       </c>
       <c r="M24" s="12">
-        <f t="shared" si="4"/>
-        <v>12.327550476641601</v>
+        <f>F24/(1+I24-H24)</f>
+        <v>103.46609203186667</v>
       </c>
       <c r="N24" s="12">
-        <f t="shared" si="5"/>
-        <v>1.0410000000000004</v>
+        <f>L24-F24</f>
+        <v>7.5700000000000216</v>
       </c>
       <c r="O24" s="12">
-        <f t="shared" si="6"/>
-        <v>-4.2462247616791995</v>
+        <f>0.5*(M24-F24)</f>
+        <v>-5.0569539840666664</v>
       </c>
       <c r="P24" s="15">
-        <f t="shared" si="7"/>
-        <v>-3.2052247616791991</v>
+        <f>N24+O24</f>
+        <v>2.5130460159333552</v>
       </c>
       <c r="Q24" s="12">
-        <f t="shared" si="8"/>
-        <v>106.83373479033253</v>
+        <f>MAX($P$2:$P$280)-P24</f>
+        <v>111.61939906525103</v>
       </c>
       <c r="R24" s="9">
-        <f t="shared" si="9"/>
-        <v>9.3603392408077718E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q24)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>8.9590161600441431E-3</v>
       </c>
       <c r="S24" s="9">
-        <f t="shared" si="10"/>
-        <v>0.48301417138583286</v>
+        <f>Q24/MAX($Q$2:$Q$28)</f>
+        <v>0.77933774752071117</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>54</v>
+        <v>36</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>83</v>
       </c>
       <c r="C25" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="D25" s="8">
-        <v>45511</v>
+        <v>45481</v>
       </c>
       <c r="E25" s="2">
-        <v>1E-22</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F25" s="1">
-        <v>13.04</v>
+        <v>64.349999999999994</v>
       </c>
       <c r="G25" s="1">
-        <f t="shared" si="0"/>
-        <v>1.304E-21</v>
+        <f>E25*F25</f>
+        <v>6.4349999999999993E-18</v>
       </c>
       <c r="H25" s="11">
-        <f>13.72/F25-1</f>
-        <v>5.2147239263803824E-2</v>
+        <v>0.15</v>
       </c>
       <c r="I25" s="11">
-        <v>0.30159999999999998</v>
+        <v>0.67300000000000004</v>
       </c>
       <c r="J25" s="9">
-        <f t="shared" si="1"/>
-        <v>0.17290198694895167</v>
+        <f>IFERROR(H25/I25,"")</f>
+        <v>0.22288261515601782</v>
       </c>
       <c r="K25" s="9">
-        <f t="shared" si="2"/>
-        <v>9.4698549390612539E-3</v>
+        <f>IFERROR(J25/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>1.1981937556720838E-2</v>
       </c>
       <c r="L25" s="12">
-        <f t="shared" si="3"/>
-        <v>13.72</v>
+        <f>F25/(1-(F25*(1+H25)-F25)/(F25*(1+H25)))</f>
+        <v>74.002499999999984</v>
       </c>
       <c r="M25" s="12">
-        <f t="shared" si="4"/>
-        <v>10.436569040286594</v>
+        <f>F25/(1+I25-H25)</f>
+        <v>42.252133946158892</v>
       </c>
       <c r="N25" s="12">
-        <f t="shared" si="5"/>
-        <v>0.68000000000000149</v>
+        <f>L25-F25</f>
+        <v>9.6524999999999892</v>
       </c>
       <c r="O25" s="12">
-        <f t="shared" si="6"/>
-        <v>-1.3017154798567026</v>
+        <f>0.5*(M25-F25)</f>
+        <v>-11.048933026920551</v>
       </c>
       <c r="P25" s="15">
-        <f t="shared" si="7"/>
-        <v>-0.62171547985670106</v>
+        <f>N25+O25</f>
+        <v>-1.3964330269205618</v>
       </c>
       <c r="Q25" s="12">
-        <f t="shared" si="8"/>
-        <v>104.25022550851003</v>
+        <f>MAX($P$2:$P$280)-P25</f>
+        <v>115.52887810810495</v>
       </c>
       <c r="R25" s="9">
-        <f t="shared" si="9"/>
-        <v>9.5923053894820514E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q25)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>8.6558444639638962E-3</v>
       </c>
       <c r="S25" s="9">
-        <f t="shared" si="10"/>
-        <v>0.47133366992741127</v>
+        <f>Q25/MAX($Q$2:$Q$28)</f>
+        <v>0.80663411909010196</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
@@ -2537,69 +3678,69 @@
         <v>40</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26" t="s">
-        <v>44</v>
+        <v>49</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>48</v>
       </c>
       <c r="D26" s="8">
         <v>45511</v>
       </c>
       <c r="E26" s="2">
-        <v>1E-22</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F26" s="1">
-        <v>11.05</v>
+        <v>20.82</v>
       </c>
       <c r="G26" s="1">
-        <f t="shared" si="0"/>
-        <v>1.1050000000000002E-21</v>
-      </c>
-      <c r="H26" s="11">
+        <f>E26*F26</f>
+        <v>2.0820000000000002E-18</v>
+      </c>
+      <c r="H26" s="13">
         <v>0.05</v>
       </c>
       <c r="I26" s="11">
-        <v>0.72170000000000001</v>
+        <v>0.7389</v>
       </c>
       <c r="J26" s="9">
-        <f t="shared" si="1"/>
-        <v>6.9280864625190522E-2</v>
+        <f>IFERROR(H26/I26,"")</f>
+        <v>6.7668155366084726E-2</v>
       </c>
       <c r="K26" s="9">
-        <f t="shared" si="2"/>
-        <v>3.7945182101753309E-3</v>
+        <f>IFERROR(J26/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>3.6377696466247688E-3</v>
       </c>
       <c r="L26" s="12">
-        <f t="shared" si="3"/>
-        <v>11.602500000000001</v>
+        <f>F26/(1-(F26*(1+H26)-F26)/(F26*(1+H26)))</f>
+        <v>21.861000000000001</v>
       </c>
       <c r="M26" s="12">
-        <f t="shared" si="4"/>
-        <v>6.6100376861877139</v>
+        <f>F26/(1+I26-H26)</f>
+        <v>12.327550476641601</v>
       </c>
       <c r="N26" s="12">
-        <f t="shared" si="5"/>
-        <v>0.55250000000000021</v>
+        <f>L26-F26</f>
+        <v>1.0410000000000004</v>
       </c>
       <c r="O26" s="12">
-        <f t="shared" si="6"/>
-        <v>-2.2199811569061434</v>
+        <f>0.5*(M26-F26)</f>
+        <v>-4.2462247616791995</v>
       </c>
       <c r="P26" s="15">
-        <f t="shared" si="7"/>
-        <v>-1.6674811569061432</v>
+        <f>N26+O26</f>
+        <v>-3.2052247616791991</v>
       </c>
       <c r="Q26" s="12">
-        <f t="shared" si="8"/>
-        <v>105.29599118555947</v>
+        <f>MAX($P$2:$P$280)-P26</f>
+        <v>117.33766984286359</v>
       </c>
       <c r="R26" s="9">
-        <f t="shared" si="9"/>
-        <v>9.4970377194867235E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q26)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>8.5224122938454584E-3</v>
       </c>
       <c r="S26" s="9">
-        <f t="shared" si="10"/>
-        <v>0.47606176113338761</v>
+        <f>Q26/MAX($Q$2:$Q$28)</f>
+        <v>0.81926328291024408</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
@@ -2607,419 +3748,420 @@
         <v>40</v>
       </c>
       <c r="B27" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" t="s">
         <v>53</v>
-      </c>
-      <c r="C27" t="s">
-        <v>52</v>
       </c>
       <c r="D27" s="8">
         <v>45511</v>
       </c>
       <c r="E27" s="2">
-        <v>1E-22</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F27" s="1">
-        <v>10.47</v>
+        <v>13.04</v>
       </c>
       <c r="G27" s="1">
-        <f t="shared" si="0"/>
-        <v>1.0470000000000001E-21</v>
+        <f>E27*F27</f>
+        <v>1.304E-18</v>
       </c>
       <c r="H27" s="11">
-        <v>0.05</v>
+        <f>13.72/F27-1</f>
+        <v>5.2147239263803824E-2</v>
       </c>
       <c r="I27" s="11">
-        <v>0.85599999999999998</v>
+        <v>0.30159999999999998</v>
       </c>
       <c r="J27" s="9">
-        <f t="shared" si="1"/>
-        <v>5.8411214953271035E-2</v>
+        <f>IFERROR(H27/I27,"")</f>
+        <v>0.17290198694895167</v>
       </c>
       <c r="K27" s="9">
-        <f t="shared" si="2"/>
-        <v>3.1991866732284306E-3</v>
+        <f>IFERROR(J27/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>9.2950309722681142E-3</v>
       </c>
       <c r="L27" s="12">
-        <f t="shared" si="3"/>
-        <v>10.993500000000001</v>
+        <f>F27/(1-(F27*(1+H27)-F27)/(F27*(1+H27)))</f>
+        <v>13.72</v>
       </c>
       <c r="M27" s="12">
-        <f t="shared" si="4"/>
-        <v>5.7973421926910307</v>
+        <f>F27/(1+I27-H27)</f>
+        <v>10.436569040286594</v>
       </c>
       <c r="N27" s="12">
-        <f t="shared" si="5"/>
-        <v>0.5235000000000003</v>
+        <f>L27-F27</f>
+        <v>0.68000000000000149</v>
       </c>
       <c r="O27" s="12">
-        <f t="shared" si="6"/>
-        <v>-2.336328903654485</v>
+        <f>0.5*(M27-F27)</f>
+        <v>-1.3017154798567026</v>
       </c>
       <c r="P27" s="15">
-        <f t="shared" si="7"/>
-        <v>-1.8128289036544847</v>
+        <f>N27+O27</f>
+        <v>-0.62171547985670106</v>
       </c>
       <c r="Q27" s="12">
-        <f t="shared" si="8"/>
-        <v>105.44133893230781</v>
+        <f>MAX($P$2:$P$280)-P27</f>
+        <v>114.75416056104109</v>
       </c>
       <c r="R27" s="9">
-        <f t="shared" si="9"/>
-        <v>9.4839463357155301E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q27)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>8.7142809908671744E-3</v>
       </c>
       <c r="S27" s="9">
-        <f t="shared" si="10"/>
-        <v>0.47671890395064692</v>
+        <f>Q27/MAX($Q$2:$Q$28)</f>
+        <v>0.80122496411211674</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>82</v>
+        <v>45</v>
+      </c>
+      <c r="C28" t="s">
+        <v>44</v>
       </c>
       <c r="D28" s="8">
-        <f ca="1">TODAY()-20</f>
-        <v>45616</v>
+        <v>45511</v>
       </c>
       <c r="E28" s="2">
-        <v>1E-35</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F28" s="1">
-        <v>2742.9</v>
+        <v>11.05</v>
       </c>
       <c r="G28" s="1">
-        <f t="shared" si="0"/>
-        <v>2.7429E-32</v>
+        <f>E28*F28</f>
+        <v>1.1050000000000001E-18</v>
       </c>
       <c r="H28" s="11">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="I28" s="11">
-        <v>0.5</v>
+        <v>0.72170000000000001</v>
       </c>
       <c r="J28" s="9">
-        <f t="shared" si="1"/>
-        <v>0.2</v>
+        <f>IFERROR(H28/I28,"")</f>
+        <v>6.9280864625190522E-2</v>
       </c>
       <c r="K28" s="9">
-        <f t="shared" si="2"/>
-        <v>1.0954015169134147E-2</v>
+        <f>IFERROR(J28/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>3.7244672189151191E-3</v>
       </c>
       <c r="L28" s="12">
-        <f t="shared" si="3"/>
-        <v>3017.1900000000005</v>
+        <f>F28/(1-(F28*(1+H28)-F28)/(F28*(1+H28)))</f>
+        <v>11.602500000000001</v>
       </c>
       <c r="M28" s="12">
-        <f t="shared" si="4"/>
-        <v>1959.214285714286</v>
+        <f>F28/(1+I28-H28)</f>
+        <v>6.6100376861877139</v>
       </c>
       <c r="N28" s="12">
-        <f t="shared" si="5"/>
-        <v>274.29000000000042</v>
+        <f>L28-F28</f>
+        <v>0.55250000000000021</v>
       </c>
       <c r="O28" s="12">
-        <f t="shared" si="6"/>
-        <v>-391.84285714285704</v>
+        <f>0.5*(M28-F28)</f>
+        <v>-2.2199811569061434</v>
       </c>
       <c r="P28" s="15">
-        <f t="shared" si="7"/>
-        <v>-117.55285714285662</v>
+        <f>N28+O28</f>
+        <v>-1.6674811569061432</v>
       </c>
       <c r="Q28" s="12">
-        <f t="shared" si="8"/>
-        <v>221.18136717150995</v>
+        <f>MAX($P$2:$P$280)-P28</f>
+        <v>115.79992623809053</v>
       </c>
       <c r="R28" s="9">
-        <f t="shared" si="9"/>
-        <v>4.5211765022890611E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q28)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>8.6355840844315329E-3</v>
       </c>
       <c r="S28" s="9">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f>Q28/MAX($Q$2:$Q$28)</f>
+        <v>0.80852660409594923</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29" t="s">
-        <v>57</v>
+        <v>74</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>80</v>
       </c>
       <c r="D29" s="8">
-        <v>45505</v>
+        <f ca="1">TODAY()-20</f>
+        <v>45665</v>
       </c>
       <c r="E29" s="2">
-        <v>1E-35</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F29" s="1">
-        <v>86.6</v>
+        <v>2742.9</v>
       </c>
       <c r="G29" s="1">
-        <f t="shared" si="0"/>
-        <v>8.6599999999999988E-34</v>
+        <f>E29*F29</f>
+        <v>2.7429000000000002E-16</v>
       </c>
       <c r="H29" s="11">
-        <v>7.0000000000000007E-2</v>
+        <v>0.1</v>
       </c>
       <c r="I29" s="11">
-        <v>0.17249999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J29" s="9">
-        <f t="shared" si="1"/>
-        <v>0.40579710144927544</v>
+        <f>IFERROR(H29/I29,"")</f>
+        <v>0.2</v>
       </c>
       <c r="K29" s="9">
-        <f t="shared" si="2"/>
-        <v>2.2225538024330155E-2</v>
+        <f>IFERROR(J29/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>1.0751791967564166E-2</v>
       </c>
       <c r="L29" s="12">
-        <f t="shared" si="3"/>
-        <v>92.662000000000006</v>
+        <f>F29/(1-(F29*(1+H29)-F29)/(F29*(1+H29)))</f>
+        <v>3017.1900000000005</v>
       </c>
       <c r="M29" s="12">
-        <f t="shared" si="4"/>
-        <v>78.548752834467123</v>
+        <f>F29/(1+I29-H29)</f>
+        <v>1959.214285714286</v>
       </c>
       <c r="N29" s="12">
-        <f t="shared" si="5"/>
-        <v>6.0620000000000118</v>
+        <f>L29-F29</f>
+        <v>274.29000000000042</v>
       </c>
       <c r="O29" s="12">
-        <f t="shared" si="6"/>
-        <v>-4.0256235827664355</v>
+        <f>0.5*(M29-F29)</f>
+        <v>-391.84285714285704</v>
       </c>
       <c r="P29" s="15">
-        <f t="shared" si="7"/>
-        <v>2.0363764172335763</v>
+        <f>N29+O29</f>
+        <v>-117.55285714285662</v>
       </c>
       <c r="Q29" s="12">
-        <f t="shared" si="8"/>
-        <v>101.59213361141974</v>
+        <f>MAX($P$2:$P$280)-P29</f>
+        <v>231.68530222404101</v>
       </c>
       <c r="R29" s="9">
-        <f t="shared" si="9"/>
-        <v>9.8432818019641658E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q29)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>4.316199562080957E-3</v>
       </c>
       <c r="S29" s="9">
-        <f t="shared" si="10"/>
-        <v>0.45931596730136171</v>
+        <f>Q29/MAX($Q$2:$Q$28)</f>
+        <v>1.6176498268314992</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="C30" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="D30" s="8">
-        <v>45562</v>
+        <v>45505</v>
       </c>
       <c r="E30" s="2">
-        <v>1E-35</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F30" s="1">
-        <v>56</v>
+        <v>86.6</v>
       </c>
       <c r="G30" s="1">
-        <f t="shared" si="0"/>
-        <v>5.5999999999999999E-34</v>
+        <f>E30*F30</f>
+        <v>8.6599999999999986E-18</v>
       </c>
       <c r="H30" s="11">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="I30" s="11">
-        <v>0.19</v>
+        <v>0.17249999999999999</v>
       </c>
       <c r="J30" s="9">
-        <f t="shared" si="1"/>
-        <v>0.36842105263157898</v>
+        <f>IFERROR(H30/I30,"")</f>
+        <v>0.40579710144927544</v>
       </c>
       <c r="K30" s="9">
-        <f t="shared" si="2"/>
-        <v>2.0178448995773427E-2</v>
+        <f>IFERROR(J30/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>2.1815230079115702E-2</v>
       </c>
       <c r="L30" s="12">
-        <f t="shared" si="3"/>
-        <v>59.92</v>
+        <f>F30/(1-(F30*(1+H30)-F30)/(F30*(1+H30)))</f>
+        <v>92.662000000000006</v>
       </c>
       <c r="M30" s="12">
-        <f t="shared" si="4"/>
-        <v>50.000000000000007</v>
+        <f>F30/(1+I30-H30)</f>
+        <v>78.548752834467123</v>
       </c>
       <c r="N30" s="12">
-        <f t="shared" si="5"/>
-        <v>3.9200000000000017</v>
+        <f>L30-F30</f>
+        <v>6.0620000000000118</v>
       </c>
       <c r="O30" s="12">
-        <f t="shared" si="6"/>
-        <v>-2.9999999999999964</v>
+        <f>0.5*(M30-F30)</f>
+        <v>-4.0256235827664355</v>
       </c>
       <c r="P30" s="15">
-        <f t="shared" si="7"/>
-        <v>0.92000000000000526</v>
+        <f>N30+O30</f>
+        <v>2.0363764172335763</v>
       </c>
       <c r="Q30" s="12">
-        <f t="shared" si="8"/>
-        <v>102.70851002865332</v>
+        <f>MAX($P$2:$P$280)-P30</f>
+        <v>112.0960686639508</v>
       </c>
       <c r="R30" s="9">
-        <f t="shared" si="9"/>
-        <v>9.7362915665023565E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q30)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>8.9209194570227766E-3</v>
       </c>
       <c r="S30" s="9">
-        <f t="shared" si="10"/>
-        <v>0.46436330212666782</v>
+        <f>Q30/MAX($Q$2:$Q$28)</f>
+        <v>0.78266590207514586</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C31" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D31" s="8">
-        <v>45580</v>
+        <v>45562</v>
       </c>
       <c r="E31" s="2">
-        <v>1E-35</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F31" s="1">
-        <v>20.399999999999999</v>
+        <v>56</v>
       </c>
       <c r="G31" s="1">
-        <f t="shared" si="0"/>
-        <v>2.0399999999999999E-34</v>
+        <f>E31*F31</f>
+        <v>5.5999999999999995E-18</v>
       </c>
       <c r="H31" s="11">
-        <v>0.1</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I31" s="11">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="J31" s="9">
-        <f t="shared" si="1"/>
-        <v>0.66666666666666674</v>
+        <f>IFERROR(H31/I31,"")</f>
+        <v>0.36842105263157898</v>
       </c>
       <c r="K31" s="9">
-        <f t="shared" si="2"/>
-        <v>3.6513383897113824E-2</v>
+        <f>IFERROR(J31/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>1.9805932571828729E-2</v>
       </c>
       <c r="L31" s="12">
-        <v>21.2</v>
+        <f>F31/(1-(F31*(1+H31)-F31)/(F31*(1+H31)))</f>
+        <v>59.92</v>
       </c>
       <c r="M31" s="12">
-        <f t="shared" si="4"/>
-        <v>19.428571428571431</v>
+        <f>F31/(1+I31-H31)</f>
+        <v>50.000000000000007</v>
       </c>
       <c r="N31" s="12">
-        <f t="shared" si="5"/>
-        <v>0.80000000000000071</v>
+        <f>L31-F31</f>
+        <v>3.9200000000000017</v>
       </c>
       <c r="O31" s="12">
-        <f t="shared" si="6"/>
-        <v>-0.48571428571428399</v>
+        <f>0.5*(M31-F31)</f>
+        <v>-2.9999999999999964</v>
       </c>
       <c r="P31" s="15">
-        <f t="shared" si="7"/>
-        <v>0.31428571428571672</v>
+        <f>N31+O31</f>
+        <v>0.92000000000000526</v>
       </c>
       <c r="Q31" s="12">
-        <f t="shared" si="8"/>
-        <v>103.31422431436761</v>
+        <f>MAX($P$2:$P$280)-P31</f>
+        <v>113.21244508118438</v>
       </c>
       <c r="R31" s="9">
-        <f t="shared" si="9"/>
-        <v>9.6792092921993977E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q31)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>8.832951176727102E-3</v>
       </c>
       <c r="S31" s="9">
-        <f t="shared" si="10"/>
-        <v>0.46710184332234006</v>
+        <f>Q31/MAX($Q$2:$Q$28)</f>
+        <v>0.79046055327088882</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>59</v>
+        <v>74</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>75</v>
       </c>
       <c r="C32" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="D32" s="8">
-        <v>45574</v>
+        <v>45580</v>
       </c>
       <c r="E32" s="2">
-        <v>9.9999999999999998E-46</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F32" s="1">
-        <v>47.42</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="G32" s="1">
-        <f t="shared" si="0"/>
-        <v>4.7420000000000006E-44</v>
+        <f>E32*F32</f>
+        <v>2.0399999999999999E-18</v>
       </c>
       <c r="H32" s="11">
-        <v>7.0000000000000007E-2</v>
+        <v>0.1</v>
       </c>
       <c r="I32" s="11">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
       <c r="J32" s="9">
-        <f t="shared" si="1"/>
-        <v>0.17500000000000002</v>
+        <f>IFERROR(H32/I32,"")</f>
+        <v>0.66666666666666674</v>
       </c>
       <c r="K32" s="9">
-        <f t="shared" si="2"/>
-        <v>9.5847632729923783E-3</v>
+        <f>IFERROR(J32/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>3.5839306558547224E-2</v>
       </c>
       <c r="L32" s="12">
-        <f t="shared" ref="L32:L41" si="11">F32/(1-(F32*(1+H32)-F32)/(F32*(1+H32)))</f>
-        <v>50.739400000000003</v>
+        <v>21.2</v>
       </c>
       <c r="M32" s="12">
-        <f t="shared" si="4"/>
-        <v>35.654135338345867</v>
+        <f>F32/(1+I32-H32)</f>
+        <v>19.428571428571431</v>
       </c>
       <c r="N32" s="12">
-        <f t="shared" si="5"/>
-        <v>3.3194000000000017</v>
+        <f>L32-F32</f>
+        <v>0.80000000000000071</v>
       </c>
       <c r="O32" s="12">
-        <f t="shared" si="6"/>
-        <v>-5.8829323308270673</v>
+        <f>0.5*(M32-F32)</f>
+        <v>-0.48571428571428399</v>
       </c>
       <c r="P32" s="15">
-        <f t="shared" si="7"/>
-        <v>-2.5635323308270657</v>
+        <f>N32+O32</f>
+        <v>0.31428571428571672</v>
       </c>
       <c r="Q32" s="12">
-        <f t="shared" si="8"/>
-        <v>106.19204235948038</v>
+        <f>MAX($P$2:$P$280)-P32</f>
+        <v>113.81815936689867</v>
       </c>
       <c r="R32" s="9">
-        <f t="shared" si="9"/>
-        <v>9.4169014719088714E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q32)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>8.7859442250902055E-3</v>
       </c>
       <c r="S32" s="9">
-        <f t="shared" si="10"/>
-        <v>0.48011296664576736</v>
+        <f>Q32/MAX($Q$2:$Q$28)</f>
+        <v>0.79468971066667204</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
@@ -3027,23 +4169,23 @@
         <v>39</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="C33" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="D33" s="8">
-        <v>45507</v>
+        <v>45574</v>
       </c>
       <c r="E33" s="2">
-        <v>9.9999999999999998E-46</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F33" s="1">
-        <v>41.8</v>
+        <v>47.42</v>
       </c>
       <c r="G33" s="1">
-        <f t="shared" si="0"/>
-        <v>4.1799999999999994E-44</v>
+        <f>E33*F33</f>
+        <v>4.7419999999999999E-18</v>
       </c>
       <c r="H33" s="11">
         <v>7.0000000000000007E-2</v>
@@ -3052,254 +4194,254 @@
         <v>0.4</v>
       </c>
       <c r="J33" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H33/I33,"")</f>
         <v>0.17500000000000002</v>
       </c>
       <c r="K33" s="9">
-        <f t="shared" si="2"/>
-        <v>9.5847632729923783E-3</v>
+        <f>IFERROR(J33/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>9.4078179716186455E-3</v>
       </c>
       <c r="L33" s="12">
-        <f t="shared" si="11"/>
-        <v>44.725999999999999</v>
+        <f>F33/(1-(F33*(1+H33)-F33)/(F33*(1+H33)))</f>
+        <v>50.739400000000003</v>
       </c>
       <c r="M33" s="12">
-        <f t="shared" si="4"/>
-        <v>31.428571428571431</v>
+        <f>F33/(1+I33-H33)</f>
+        <v>35.654135338345867</v>
       </c>
       <c r="N33" s="12">
-        <f t="shared" si="5"/>
-        <v>2.9260000000000019</v>
+        <f>L33-F33</f>
+        <v>3.3194000000000017</v>
       </c>
       <c r="O33" s="12">
-        <f t="shared" si="6"/>
-        <v>-5.1857142857142833</v>
+        <f>0.5*(M33-F33)</f>
+        <v>-5.8829323308270673</v>
       </c>
       <c r="P33" s="15">
-        <f t="shared" si="7"/>
-        <v>-2.2597142857142813</v>
+        <f>N33+O33</f>
+        <v>-2.5635323308270657</v>
       </c>
       <c r="Q33" s="12">
-        <f t="shared" si="8"/>
-        <v>105.8882243143676</v>
+        <f>MAX($P$2:$P$280)-P33</f>
+        <v>116.69597741201144</v>
       </c>
       <c r="R33" s="9">
-        <f t="shared" si="9"/>
-        <v>9.4439207614922058E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q33)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>8.5692756697976005E-3</v>
       </c>
       <c r="S33" s="9">
-        <f t="shared" si="10"/>
-        <v>0.47873935163923209</v>
+        <f>Q33/MAX($Q$2:$Q$28)</f>
+        <v>0.81478292252621221</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>76</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>79</v>
+        <v>39</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="C34" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="D34" s="8">
-        <v>45574</v>
+        <v>45507</v>
       </c>
       <c r="E34" s="2">
-        <v>0</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F34" s="1">
-        <v>153.7552</v>
+        <v>41.8</v>
       </c>
       <c r="G34" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>E34*F34</f>
+        <v>4.1799999999999993E-18</v>
       </c>
       <c r="H34" s="11">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="I34" s="11">
-        <v>0.19</v>
+        <v>0.4</v>
       </c>
       <c r="J34" s="9">
-        <f t="shared" si="1"/>
-        <v>0.36842105263157898</v>
+        <f>IFERROR(H34/I34,"")</f>
+        <v>0.17500000000000002</v>
       </c>
       <c r="K34" s="9">
-        <f t="shared" si="2"/>
-        <v>2.0178448995773427E-2</v>
+        <f>IFERROR(J34/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>9.4078179716186455E-3</v>
       </c>
       <c r="L34" s="12">
-        <f t="shared" si="11"/>
-        <v>164.51806400000001</v>
+        <f>F34/(1-(F34*(1+H34)-F34)/(F34*(1+H34)))</f>
+        <v>44.725999999999999</v>
       </c>
       <c r="M34" s="12">
-        <f t="shared" si="4"/>
-        <v>137.28142857142859</v>
+        <f>F34/(1+I34-H34)</f>
+        <v>31.428571428571431</v>
       </c>
       <c r="N34" s="12">
-        <f t="shared" si="5"/>
-        <v>10.762864000000008</v>
+        <f>L34-F34</f>
+        <v>2.9260000000000019</v>
       </c>
       <c r="O34" s="12">
-        <f t="shared" si="6"/>
-        <v>-8.2368857142857053</v>
+        <f>0.5*(M34-F34)</f>
+        <v>-5.1857142857142833</v>
       </c>
       <c r="P34" s="15">
-        <f t="shared" si="7"/>
-        <v>2.5259782857143023</v>
+        <f>N34+O34</f>
+        <v>-2.2597142857142813</v>
       </c>
       <c r="Q34" s="12">
-        <f t="shared" si="8"/>
-        <v>101.10253174293902</v>
+        <f>MAX($P$2:$P$280)-P34</f>
+        <v>116.39215936689867</v>
       </c>
       <c r="R34" s="9">
-        <f t="shared" si="9"/>
-        <v>9.8909491459875307E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q34)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>8.5916440200042785E-3</v>
       </c>
       <c r="S34" s="9">
-        <f t="shared" si="10"/>
-        <v>0.45710239083810988</v>
+        <f>Q34/MAX($Q$2:$Q$28)</f>
+        <v>0.81266163471318675</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>89</v>
-      </c>
-      <c r="B35" t="s">
-        <v>90</v>
+        <v>74</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>77</v>
       </c>
       <c r="C35" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="D35" s="8">
-        <v>45627</v>
+        <v>45574</v>
       </c>
       <c r="E35" s="2">
-        <v>0</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F35" s="1">
-        <v>133.53</v>
+        <v>153.7552</v>
       </c>
       <c r="G35" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>E35*F35</f>
+        <v>1.5375519999999999E-17</v>
       </c>
       <c r="H35" s="11">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="I35" s="11">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="J35" s="9">
-        <f t="shared" si="1"/>
-        <v>0.35000000000000003</v>
+        <f>IFERROR(H35/I35,"")</f>
+        <v>0.36842105263157898</v>
       </c>
       <c r="K35" s="9">
-        <f t="shared" si="2"/>
-        <v>1.9169526545984757E-2</v>
+        <f>IFERROR(J35/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>1.9805932571828729E-2</v>
       </c>
       <c r="L35" s="12">
-        <f t="shared" si="11"/>
-        <v>142.87710000000001</v>
+        <f>F35/(1-(F35*(1+H35)-F35)/(F35*(1+H35)))</f>
+        <v>164.51806400000001</v>
       </c>
       <c r="M35" s="12">
-        <f t="shared" si="4"/>
-        <v>118.16814159292036</v>
+        <f>F35/(1+I35-H35)</f>
+        <v>137.28142857142859</v>
       </c>
       <c r="N35" s="12">
-        <f t="shared" si="5"/>
-        <v>9.3471000000000117</v>
+        <f>L35-F35</f>
+        <v>10.762864000000008</v>
       </c>
       <c r="O35" s="12">
-        <f t="shared" si="6"/>
-        <v>-7.6809292035398187</v>
+        <f>0.5*(M35-F35)</f>
+        <v>-8.2368857142857053</v>
       </c>
       <c r="P35" s="15">
-        <f t="shared" si="7"/>
-        <v>1.6661707964601931</v>
+        <f>N35+O35</f>
+        <v>2.5259782857143023</v>
       </c>
       <c r="Q35" s="12">
-        <f t="shared" si="8"/>
-        <v>101.96233923219313</v>
+        <f>MAX($P$2:$P$280)-P35</f>
+        <v>111.60646679547008</v>
       </c>
       <c r="R35" s="9">
-        <f t="shared" si="9"/>
-        <v>9.8075427410777224E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q35)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>8.9600542756415637E-3</v>
       </c>
       <c r="S35" s="9">
-        <f t="shared" si="10"/>
-        <v>0.46098973225501771</v>
+        <f>Q35/MAX($Q$2:$Q$28)</f>
+        <v>0.77924745312667376</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>40</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>92</v>
+        <v>87</v>
+      </c>
+      <c r="B36" t="s">
+        <v>88</v>
       </c>
       <c r="C36" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D36" s="8">
         <v>45627</v>
       </c>
       <c r="E36" s="2">
-        <v>0</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F36" s="1">
-        <v>39.56</v>
+        <v>133.53</v>
       </c>
       <c r="G36" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>E36*F36</f>
+        <v>1.3353E-17</v>
       </c>
       <c r="H36" s="11">
-        <v>0.1</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I36" s="11">
         <v>0.2</v>
       </c>
       <c r="J36" s="9">
-        <f t="shared" si="1"/>
-        <v>0.5</v>
+        <f>IFERROR(H36/I36,"")</f>
+        <v>0.35000000000000003</v>
       </c>
       <c r="K36" s="9">
-        <f t="shared" si="2"/>
-        <v>2.7385037922835365E-2</v>
+        <f>IFERROR(J36/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>1.8815635943237291E-2</v>
       </c>
       <c r="L36" s="12">
-        <f t="shared" si="11"/>
-        <v>43.516000000000005</v>
+        <f>F36/(1-(F36*(1+H36)-F36)/(F36*(1+H36)))</f>
+        <v>142.87710000000001</v>
       </c>
       <c r="M36" s="12">
-        <f t="shared" si="4"/>
-        <v>35.963636363636368</v>
+        <f>F36/(1+I36-H36)</f>
+        <v>118.16814159292036</v>
       </c>
       <c r="N36" s="12">
-        <f t="shared" si="5"/>
-        <v>3.9560000000000031</v>
+        <f>L36-F36</f>
+        <v>9.3471000000000117</v>
       </c>
       <c r="O36" s="12">
-        <f t="shared" si="6"/>
-        <v>-1.798181818181817</v>
+        <f>0.5*(M36-F36)</f>
+        <v>-7.6809292035398187</v>
       </c>
       <c r="P36" s="15">
-        <f t="shared" si="7"/>
-        <v>2.1578181818181861</v>
+        <f>N36+O36</f>
+        <v>1.6661707964601931</v>
       </c>
       <c r="Q36" s="12">
-        <f t="shared" si="8"/>
-        <v>101.47069184683514</v>
+        <f>MAX($P$2:$P$280)-P36</f>
+        <v>112.46627428472419</v>
       </c>
       <c r="R36" s="9">
-        <f t="shared" si="9"/>
-        <v>9.855062400771341E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q36)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>8.8915544358512261E-3</v>
       </c>
       <c r="S36" s="9">
-        <f t="shared" si="10"/>
-        <v>0.4587669076489253</v>
+        <f>Q36/MAX($Q$2:$Q$28)</f>
+        <v>0.78525071454528272</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
@@ -3307,23 +4449,23 @@
         <v>40</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C37" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D37" s="8">
         <v>45627</v>
       </c>
       <c r="E37" s="2">
-        <v>0</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F37" s="1">
-        <v>26.63</v>
+        <v>39.56</v>
       </c>
       <c r="G37" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>E37*F37</f>
+        <v>3.9560000000000004E-18</v>
       </c>
       <c r="H37" s="11">
         <v>0.1</v>
@@ -3332,44 +4474,44 @@
         <v>0.2</v>
       </c>
       <c r="J37" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H37/I37,"")</f>
         <v>0.5</v>
       </c>
       <c r="K37" s="9">
-        <f t="shared" si="2"/>
-        <v>2.7385037922835365E-2</v>
+        <f>IFERROR(J37/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>2.6879479918910414E-2</v>
       </c>
       <c r="L37" s="12">
-        <f t="shared" si="11"/>
-        <v>29.293000000000003</v>
+        <f>F37/(1-(F37*(1+H37)-F37)/(F37*(1+H37)))</f>
+        <v>43.516000000000005</v>
       </c>
       <c r="M37" s="12">
-        <f t="shared" si="4"/>
-        <v>24.209090909090911</v>
+        <f>F37/(1+I37-H37)</f>
+        <v>35.963636363636368</v>
       </c>
       <c r="N37" s="12">
-        <f t="shared" si="5"/>
-        <v>2.6630000000000038</v>
+        <f>L37-F37</f>
+        <v>3.9560000000000031</v>
       </c>
       <c r="O37" s="12">
-        <f t="shared" si="6"/>
-        <v>-1.2104545454545441</v>
+        <f>0.5*(M37-F37)</f>
+        <v>-1.798181818181817</v>
       </c>
       <c r="P37" s="15">
-        <f t="shared" si="7"/>
-        <v>1.4525454545454597</v>
+        <f>N37+O37</f>
+        <v>2.1578181818181861</v>
       </c>
       <c r="Q37" s="12">
-        <f t="shared" si="8"/>
-        <v>102.17596457410787</v>
+        <f>MAX($P$2:$P$280)-P37</f>
+        <v>111.9746268993662</v>
       </c>
       <c r="R37" s="9">
-        <f t="shared" si="9"/>
-        <v>9.7870375304820699E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q37)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>8.9305946149632592E-3</v>
       </c>
       <c r="S37" s="9">
-        <f t="shared" si="10"/>
-        <v>0.46195557013117605</v>
+        <f>Q37/MAX($Q$2:$Q$28)</f>
+        <v>0.78181798359449739</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
@@ -3377,93 +4519,93 @@
         <v>40</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C38" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D38" s="8">
         <v>45627</v>
       </c>
       <c r="E38" s="2">
-        <v>0.9385</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F38" s="1">
-        <v>21.31</v>
+        <v>26.63</v>
       </c>
       <c r="G38" s="1">
-        <f t="shared" si="0"/>
-        <v>19.999434999999998</v>
+        <f>E38*F38</f>
+        <v>2.663E-18</v>
       </c>
       <c r="H38" s="11">
-        <f>L38/F38-1</f>
-        <v>0.24730173627404972</v>
+        <v>0.1</v>
       </c>
       <c r="I38" s="11">
-        <v>0.45929999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="J38" s="9">
-        <f t="shared" si="1"/>
-        <v>0.53843182293500924</v>
+        <f>IFERROR(H38/I38,"")</f>
+        <v>0.5</v>
       </c>
       <c r="K38" s="9">
-        <f t="shared" si="2"/>
-        <v>2.9489951779873208E-2</v>
+        <f>IFERROR(J38/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>2.6879479918910414E-2</v>
       </c>
       <c r="L38" s="12">
-        <v>26.58</v>
+        <f>F38/(1-(F38*(1+H38)-F38)/(F38*(1+H38)))</f>
+        <v>29.293000000000003</v>
       </c>
       <c r="M38" s="12">
-        <f t="shared" si="4"/>
-        <v>17.582533439023546</v>
+        <f>F38/(1+I38-H38)</f>
+        <v>24.209090909090911</v>
       </c>
       <c r="N38" s="12">
-        <f t="shared" si="5"/>
-        <v>5.27</v>
+        <f>L38-F38</f>
+        <v>2.6630000000000038</v>
       </c>
       <c r="O38" s="12">
-        <f t="shared" si="6"/>
-        <v>-1.8637332804882263</v>
+        <f>0.5*(M38-F38)</f>
+        <v>-1.2104545454545441</v>
       </c>
       <c r="P38" s="15">
-        <f t="shared" si="7"/>
-        <v>3.4062667195117733</v>
+        <f>N38+O38</f>
+        <v>1.4525454545454597</v>
       </c>
       <c r="Q38" s="12">
-        <f t="shared" si="8"/>
-        <v>100.22224330914155</v>
+        <f>MAX($P$2:$P$280)-P38</f>
+        <v>112.67989962663893</v>
       </c>
       <c r="R38" s="9">
-        <f t="shared" si="9"/>
-        <v>9.9778249516471081E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q38)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>8.8746972912956655E-3</v>
       </c>
       <c r="S38" s="9">
-        <f t="shared" si="10"/>
-        <v>0.4531224514559879</v>
+        <f>Q38/MAX($Q$2:$Q$28)</f>
+        <v>0.78674226793273505</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C39" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D39" s="8">
         <v>45630</v>
       </c>
       <c r="E39" s="2">
-        <v>0</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F39" s="1">
         <v>59.17</v>
       </c>
       <c r="G39" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>E39*F39</f>
+        <v>5.9170000000000002E-18</v>
       </c>
       <c r="H39" s="11">
         <v>0.2</v>
@@ -3472,44 +4614,44 @@
         <v>0.2</v>
       </c>
       <c r="J39" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H39/I39,"")</f>
         <v>1</v>
       </c>
       <c r="K39" s="9">
-        <f t="shared" si="2"/>
-        <v>5.4770075845670729E-2</v>
+        <f>IFERROR(J39/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>5.3758959837820829E-2</v>
       </c>
       <c r="L39" s="12">
-        <f t="shared" si="11"/>
+        <f>F39/(1-(F39*(1+H39)-F39)/(F39*(1+H39)))</f>
         <v>71.004000000000005</v>
       </c>
       <c r="M39" s="12">
-        <f t="shared" si="4"/>
+        <f>F39/(1+I39-H39)</f>
         <v>59.17</v>
       </c>
       <c r="N39" s="12">
-        <f t="shared" si="5"/>
+        <f>L39-F39</f>
         <v>11.834000000000003</v>
       </c>
       <c r="O39" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(M39-F39)</f>
         <v>0</v>
       </c>
       <c r="P39" s="15">
-        <f t="shared" si="7"/>
+        <f>N39+O39</f>
         <v>11.834000000000003</v>
       </c>
       <c r="Q39" s="12">
-        <f t="shared" si="8"/>
-        <v>91.79451002865332</v>
+        <f>MAX($P$2:$P$280)-P39</f>
+        <v>102.29844508118438</v>
       </c>
       <c r="R39" s="9">
-        <f t="shared" si="9"/>
-        <v>1.0893897681766084E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q39)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.7753196464168812E-3</v>
       </c>
       <c r="S39" s="9">
-        <f t="shared" si="10"/>
-        <v>0.41501918178068498</v>
+        <f>Q39/MAX($Q$2:$Q$28)</f>
+        <v>0.71425791960979246</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
@@ -3517,23 +4659,23 @@
         <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C40" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D40" s="8">
         <v>45630</v>
       </c>
       <c r="E40" s="2">
-        <v>0</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F40" s="1">
         <v>19.309999999999999</v>
       </c>
       <c r="G40" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>E40*F40</f>
+        <v>1.931E-18</v>
       </c>
       <c r="H40" s="11">
         <v>0.2</v>
@@ -3542,68 +4684,68 @@
         <v>0.2</v>
       </c>
       <c r="J40" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H40/I40,"")</f>
         <v>1</v>
       </c>
       <c r="K40" s="9">
-        <f t="shared" si="2"/>
-        <v>5.4770075845670729E-2</v>
+        <f>IFERROR(J40/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>5.3758959837820829E-2</v>
       </c>
       <c r="L40" s="12">
-        <f t="shared" si="11"/>
+        <f>F40/(1-(F40*(1+H40)-F40)/(F40*(1+H40)))</f>
         <v>23.171999999999997</v>
       </c>
       <c r="M40" s="12">
-        <f t="shared" si="4"/>
+        <f>F40/(1+I40-H40)</f>
         <v>19.309999999999999</v>
       </c>
       <c r="N40" s="12">
-        <f t="shared" si="5"/>
+        <f>L40-F40</f>
         <v>3.8619999999999983</v>
       </c>
       <c r="O40" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(M40-F40)</f>
         <v>0</v>
       </c>
       <c r="P40" s="15">
-        <f t="shared" si="7"/>
+        <f>N40+O40</f>
         <v>3.8619999999999983</v>
       </c>
       <c r="Q40" s="12">
-        <f t="shared" si="8"/>
-        <v>99.766510028653329</v>
+        <f>MAX($P$2:$P$280)-P40</f>
+        <v>110.27044508118439</v>
       </c>
       <c r="R40" s="9">
-        <f t="shared" si="9"/>
-        <v>1.002340364229235E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q40)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>9.0686130745529347E-3</v>
       </c>
       <c r="S40" s="9">
-        <f t="shared" si="10"/>
-        <v>0.45106200085693343</v>
+        <f>Q40/MAX($Q$2:$Q$28)</f>
+        <v>0.76991921661787932</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C41" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D41" s="8">
         <v>45630</v>
       </c>
       <c r="E41" s="2">
-        <v>0</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F41" s="1">
         <v>323.75</v>
       </c>
       <c r="G41" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>E41*F41</f>
+        <v>3.2375000000000002E-17</v>
       </c>
       <c r="H41" s="11">
         <v>0.2</v>
@@ -3612,50 +4754,50 @@
         <v>0.2</v>
       </c>
       <c r="J41" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H41/I41,"")</f>
         <v>1</v>
       </c>
       <c r="K41" s="9">
-        <f t="shared" si="2"/>
-        <v>5.4770075845670729E-2</v>
+        <f>IFERROR(J41/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>5.3758959837820829E-2</v>
       </c>
       <c r="L41" s="12">
-        <f t="shared" si="11"/>
+        <f>F41/(1-(F41*(1+H41)-F41)/(F41*(1+H41)))</f>
         <v>388.5</v>
       </c>
       <c r="M41" s="12">
-        <f t="shared" si="4"/>
+        <f>F41/(1+I41-H41)</f>
         <v>323.75</v>
       </c>
       <c r="N41" s="12">
-        <f t="shared" si="5"/>
+        <f>L41-F41</f>
         <v>64.75</v>
       </c>
       <c r="O41" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(M41-F41)</f>
         <v>0</v>
       </c>
       <c r="P41" s="15">
-        <f t="shared" si="7"/>
+        <f>N41+O41</f>
         <v>64.75</v>
       </c>
       <c r="Q41" s="12">
-        <f t="shared" si="8"/>
-        <v>38.878510028653324</v>
+        <f>MAX($P$2:$P$280)-P41</f>
+        <v>49.382445081184386</v>
       </c>
       <c r="R41" s="9">
-        <f t="shared" si="9"/>
-        <v>2.572115030290522E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q41)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+        <v>2.0250111114506527E-2</v>
       </c>
       <c r="S41" s="9">
-        <f t="shared" si="10"/>
-        <v>0.17577660598555703</v>
+        <f>Q41/MAX($Q$2:$Q$28)</f>
+        <v>0.34479314383458876</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S33" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:S41" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S41">
-      <sortCondition descending="1" ref="E1:E33"/>
+      <sortCondition descending="1" ref="E1:E41"/>
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="R2:R41">
@@ -3706,10 +4848,214 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A09BB01-2590-4471-B7D1-AC4B730D30F2}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFDF4B0C-3879-4A30-880B-B04980CC1636}">
+  <dimension ref="A2:F13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E2" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="F2" s="26"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="12">
+        <v>210.14336800000001</v>
+      </c>
+      <c r="C4" s="22">
+        <v>0.28262220609768579</v>
+      </c>
+      <c r="E4" s="12">
+        <v>233.65908899999999</v>
+      </c>
+      <c r="F4" s="22">
+        <v>0.30679033555941537</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="12">
+        <v>197.38955299999998</v>
+      </c>
+      <c r="C5" s="22">
+        <v>0.26546957660589154</v>
+      </c>
+      <c r="E5" s="12">
+        <v>210.14336800000001</v>
+      </c>
+      <c r="F5" s="22">
+        <v>0.27591460131176709</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="12">
+        <v>149.810948</v>
+      </c>
+      <c r="C6" s="22">
+        <v>0.20148102233397955</v>
+      </c>
+      <c r="E6" s="12">
+        <v>149.810948</v>
+      </c>
+      <c r="F6" s="22">
+        <v>0.19669917915067334</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="12">
+        <v>126.22434900000002</v>
+      </c>
+      <c r="C7" s="22">
+        <v>0.16975936151182378</v>
+      </c>
+      <c r="E7" s="12">
+        <v>108.030807</v>
+      </c>
+      <c r="F7" s="22">
+        <v>0.14184257788612895</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="12">
+        <v>59.980460999999991</v>
+      </c>
+      <c r="C8" s="22">
+        <v>8.06678334506193E-2</v>
+      </c>
+      <c r="E8" s="12">
+        <v>59.980460999999991</v>
+      </c>
+      <c r="F8" s="22">
+        <v>7.875330609201521E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" s="12">
+        <v>2.9170551999999998E-16</v>
+      </c>
+      <c r="C9" s="22">
+        <v>3.9231529587587362E-19</v>
+      </c>
+      <c r="E9" s="12">
+        <v>2.9170551999999998E-16</v>
+      </c>
+      <c r="F9" s="22">
+        <v>3.830042937697739E-19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="B10" s="12">
+        <v>3.8291999999999999E-17</v>
+      </c>
+      <c r="C10" s="22">
+        <v>5.1498981951657802E-20</v>
+      </c>
+      <c r="E10" s="12">
+        <v>3.8291999999999999E-17</v>
+      </c>
+      <c r="F10" s="22">
+        <v>5.0276732565884192E-20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" s="12">
+        <v>1.3353E-17</v>
+      </c>
+      <c r="C11" s="22">
+        <v>1.795847451166005E-20</v>
+      </c>
+      <c r="E11" s="12">
+        <v>1.3353E-17</v>
+      </c>
+      <c r="F11" s="22">
+        <v>1.7532257650481865E-20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" s="12">
+        <v>5.5999999999999995E-18</v>
+      </c>
+      <c r="C12" s="22">
+        <v>7.5314504055490353E-21</v>
+      </c>
+      <c r="E12" s="12">
+        <v>5.5999999999999995E-18</v>
+      </c>
+      <c r="F12" s="22">
+        <v>7.3527029763123223E-21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" s="12">
+        <v>743.54867899999999</v>
+      </c>
+      <c r="C13" s="22">
+        <v>1</v>
+      </c>
+      <c r="E13" s="24">
+        <v>761.62467300000003</v>
+      </c>
+      <c r="F13" s="25">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E2:F2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Open Positions.xlsx
+++ b/Open Positions.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\StockSillines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF8447AA-5C45-4A34-92AF-8624794E4227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C935C0-7E1E-4D9F-8B9C-A41E0CDE580F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Positions" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Positions!$A$1:$S$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Positions!$A$1:$T$45</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="8" r:id="rId3"/>
+    <pivotCache cacheId="10" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="132">
   <si>
     <t>Name</t>
   </si>
@@ -370,6 +371,75 @@
   </si>
   <si>
     <t>WK05</t>
+  </si>
+  <si>
+    <t>WK05 Start</t>
+  </si>
+  <si>
+    <t>Target Value</t>
+  </si>
+  <si>
+    <t>Target Return %</t>
+  </si>
+  <si>
+    <t>Target P&amp;L</t>
+  </si>
+  <si>
+    <t>Actual P&amp;L vs LV</t>
+  </si>
+  <si>
+    <t>WK50</t>
+  </si>
+  <si>
+    <t>ETF</t>
+  </si>
+  <si>
+    <t>ETF1</t>
+  </si>
+  <si>
+    <t>BOTZ.UK</t>
+  </si>
+  <si>
+    <t>ETF2</t>
+  </si>
+  <si>
+    <t>BATT.NL</t>
+  </si>
+  <si>
+    <t>ETF3</t>
+  </si>
+  <si>
+    <t>VBTC.DE</t>
+  </si>
+  <si>
+    <t>ETF5</t>
+  </si>
+  <si>
+    <t>BONDS</t>
+  </si>
+  <si>
+    <t>Emerging Markets</t>
+  </si>
+  <si>
+    <t>VWO.US</t>
+  </si>
+  <si>
+    <t>Return:</t>
+  </si>
+  <si>
+    <t>Optimal</t>
+  </si>
+  <si>
+    <t>Expected</t>
+  </si>
+  <si>
+    <t>Portfolio</t>
+  </si>
+  <si>
+    <t>Volatility:</t>
+  </si>
+  <si>
+    <t>Delta</t>
   </si>
 </sst>
 </file>
@@ -405,7 +475,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -454,8 +524,26 @@
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -481,13 +569,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -541,13 +644,39 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="2" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="12">
     <dxf>
       <alignment vertical="center"/>
     </dxf>
@@ -555,10 +684,28 @@
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
       <alignment vertical="center"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
@@ -580,13 +727,13 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="samuel walton" refreshedDate="45685.263780324072" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="40" xr:uid="{B79BBC45-DF34-46CE-BF36-02BCF50A32DD}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="samuel walton" refreshedDate="45686.939110069441" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="47" xr:uid="{A9649E00-87AB-4DC2-85FE-D21B9DD48B57}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:S41" sheet="Positions"/>
+    <worksheetSource ref="A1:T1048576" sheet="Positions"/>
   </cacheSource>
-  <cacheFields count="19">
+  <cacheFields count="22">
     <cacheField name="Chapter" numFmtId="0">
-      <sharedItems count="9">
+      <sharedItems containsBlank="1" count="11">
         <s v="Banking"/>
         <s v="Energy"/>
         <s v="US Consumer"/>
@@ -596,62 +743,116 @@
         <s v="Automotive"/>
         <s v="Industrials"/>
         <s v="Health"/>
+        <s v="ETF"/>
+        <m/>
       </sharedItems>
     </cacheField>
     <cacheField name="Name" numFmtId="0">
-      <sharedItems/>
+      <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Ticker" numFmtId="0">
-      <sharedItems/>
+      <sharedItems containsBlank="1" count="46">
+        <s v="ING"/>
+        <s v="APA"/>
+        <s v="MO"/>
+        <s v="MAXN"/>
+        <s v="NEE"/>
+        <s v="YPF"/>
+        <s v="PEP"/>
+        <s v="TSM"/>
+        <s v="KMB"/>
+        <s v="YUM"/>
+        <s v="V"/>
+        <s v="QCOM"/>
+        <s v="INGR"/>
+        <s v="AAPL"/>
+        <s v="MSFT"/>
+        <s v="MA"/>
+        <s v="GOOGL"/>
+        <s v="FSLR"/>
+        <s v="MC.PA"/>
+        <s v="ASML"/>
+        <s v="NVDA"/>
+        <s v="AMAT"/>
+        <s v="DUK"/>
+        <s v="PLTR"/>
+        <s v="JKS"/>
+        <s v="SWI"/>
+        <s v="CSIQ"/>
+        <s v="GC=F"/>
+        <s v="WMT"/>
+        <s v="APTV"/>
+        <s v="USDMXN=X"/>
+        <s v="YUMC"/>
+        <s v="DAR"/>
+        <s v="USDJPY=X"/>
+        <s v="MMM"/>
+        <s v="EXC"/>
+        <s v="PCG"/>
+        <s v="AGIO"/>
+        <s v="ACI"/>
+        <s v="HCA"/>
+        <s v="BOTZ.UK"/>
+        <s v="BATT.NL"/>
+        <s v="VBTC.DE"/>
+        <s v="BONDS"/>
+        <s v="VWO.US"/>
+        <m/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Date" numFmtId="165">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2024-06-17T00:00:00" maxDate="2025-01-09T00:00:00"/>
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2024-06-17T00:00:00" maxDate="2025-01-10T00:00:00"/>
     </cacheField>
     <cacheField name="Volume" numFmtId="164">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="9.9999999999999998E-20" maxValue="1.9595"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="9.9999999999999998E-20" maxValue="2"/>
     </cacheField>
     <cacheField name="Price" numFmtId="44">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="10.92" maxValue="2742.9"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="10.92" maxValue="2742.9"/>
     </cacheField>
     <cacheField name="Value" numFmtId="44">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="1.092E-18" maxValue="89.991048000000006"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="1.092E-18" maxValue="89.991048000000006"/>
     </cacheField>
     <cacheField name="Expected Return QoQ%" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.3206831119544589E-2" maxValue="1"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="2.5000000000000001E-2" maxValue="1"/>
     </cacheField>
     <cacheField name="Volatility" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.15" maxValue="1.8652"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0.15" maxValue="1.8652"/>
     </cacheField>
-    <cacheField name="Ranking" numFmtId="9">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="6.2678050433266491E-2" maxValue="1"/>
+    <cacheField name="Ranking" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="6.7668155366084726E-2" maxValue="1"/>
     </cacheField>
-    <cacheField name="Mix %" numFmtId="9">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.3695067959548818E-3" maxValue="5.3758959837820829E-2"/>
+    <cacheField name="Mix %" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="3.3543196439026418E-3" maxValue="4.9570135697593234E-2"/>
     </cacheField>
-    <cacheField name="Target Price" numFmtId="44">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="11.602500000000001" maxValue="3017.1900000000005"/>
+    <cacheField name="Target Price" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="11.602500000000001" maxValue="3017.1900000000005"/>
     </cacheField>
-    <cacheField name="Tolerance" numFmtId="44">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="5.8546000428908433" maxValue="1959.214285714286"/>
+    <cacheField name="Target Value" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="1.16025E-18" maxValue="106.57639814639998"/>
     </cacheField>
-    <cacheField name="Unit Profit" numFmtId="44">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.55250000000000021" maxValue="274.29000000000042"/>
+    <cacheField name="Tolerance" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="5.8546000428908433" maxValue="1959.214285714286"/>
     </cacheField>
-    <cacheField name="Unit Half Loss" numFmtId="44">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-391.84285714285704" maxValue="0"/>
+    <cacheField name="Unit Profit" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0.55250000000000021" maxValue="274.29000000000042"/>
     </cacheField>
-    <cacheField name="Balance Risk" numFmtId="44">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-117.55285714285662" maxValue="114.13244508118439"/>
+    <cacheField name="Unit Half Loss" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-391.84285714285704" maxValue="0"/>
     </cacheField>
-    <cacheField name="Normalized Risk" numFmtId="44">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="231.68530222404101"/>
+    <cacheField name="Balance Risk" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-117.55285714285662" maxValue="114.13244508118439"/>
     </cacheField>
-    <cacheField name="Risk Mix" numFmtId="9">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="2.2382348581474875E-2"/>
+    <cacheField name="Normalized Risk" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="231.68530222404101"/>
     </cacheField>
-    <cacheField name="Normalized Risk %" numFmtId="9">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="1.6176498268314992"/>
+    <cacheField name="Risk Mix" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="2.2382348581474875E-2"/>
     </cacheField>
+    <cacheField name="Normalized Risk %" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="1.6176498268314992"/>
+    </cacheField>
+    <cacheField name="TargetReturn%_Metric" numFmtId="0" formula="'Target Value'/Value-1" databaseField="0"/>
+    <cacheField name="TargetP&amp;L_metric" numFmtId="0" formula="'Target Value'-Value" databaseField="0"/>
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
@@ -662,11 +863,11 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="40">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="47">
   <r>
     <x v="0"/>
     <s v="ING Group NV"/>
-    <s v="ING"/>
+    <x v="0"/>
     <d v="2024-11-27T00:00:00"/>
     <n v="1.9595"/>
     <n v="15.3"/>
@@ -674,8 +875,9 @@
     <n v="0.35"/>
     <n v="0.39532299999999998"/>
     <n v="0.88535197800279775"/>
-    <n v="4.7595601427787633E-2"/>
+    <n v="4.3887017689731266E-2"/>
     <n v="20.655000000000001"/>
+    <n v="40.4734725"/>
     <n v="14.636624277854791"/>
     <n v="5.3550000000000004"/>
     <n v="-0.33168786107260484"/>
@@ -687,7 +889,7 @@
   <r>
     <x v="1"/>
     <s v="APA"/>
-    <s v="APA"/>
+    <x v="1"/>
     <d v="2024-12-01T00:00:00"/>
     <n v="1.8976999999999999"/>
     <n v="21.73"/>
@@ -695,20 +897,21 @@
     <n v="0.22319374137137582"/>
     <n v="0.45929999999999999"/>
     <n v="0.48594326447066366"/>
-    <n v="2.6123804438137953E-2"/>
+    <n v="2.4088273561142234E-2"/>
     <n v="26.58"/>
+    <n v="50.440865999999993"/>
     <n v="17.579394852436032"/>
     <n v="4.8499999999999979"/>
     <n v="-2.0753025737819843"/>
     <n v="2.7746974262180135"/>
     <n v="111.35774765496637"/>
-    <n v="8.9800666864996662E-3"/>
+    <n v="8.980066686499668E-3"/>
     <n v="0.77751087134654673"/>
   </r>
   <r>
     <x v="2"/>
     <s v="Altaria"/>
-    <s v="MO"/>
+    <x v="2"/>
     <d v="2024-09-18T00:00:00"/>
     <n v="1.7345999999999999"/>
     <n v="51.88"/>
@@ -716,8 +919,9 @@
     <n v="0.18430000000000002"/>
     <n v="0.19980000000000001"/>
     <n v="0.92242242242242245"/>
-    <n v="4.9588469960512409E-2"/>
+    <n v="4.5724604649982147E-2"/>
     <n v="61.441483999999996"/>
+    <n v="106.57639814639998"/>
     <n v="51.088133924175295"/>
     <n v="9.561483999999993"/>
     <n v="-0.39593303791235357"/>
@@ -729,7 +933,7 @@
   <r>
     <x v="1"/>
     <s v="Maxeon Solar"/>
-    <s v="MAXN"/>
+    <x v="3"/>
     <d v="2024-08-07T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="10.92"/>
@@ -737,8 +941,9 @@
     <n v="1"/>
     <n v="1.8652"/>
     <n v="0.53613553506326406"/>
-    <n v="2.8822088697094593E-2"/>
+    <n v="2.6576311225387755E-2"/>
     <n v="21.84"/>
+    <n v="2.1840000000000001E-18"/>
     <n v="5.8546000428908433"/>
     <n v="10.92"/>
     <n v="-2.5326999785545783"/>
@@ -750,7 +955,7 @@
   <r>
     <x v="1"/>
     <s v="NextEra Energy"/>
-    <s v="NEE"/>
+    <x v="4"/>
     <d v="2024-08-07T00:00:00"/>
     <n v="0.45179999999999998"/>
     <n v="77.430000000000007"/>
@@ -758,8 +963,9 @@
     <n v="0.1"/>
     <n v="0.25990000000000002"/>
     <n v="0.38476337052712584"/>
-    <n v="2.0684478583232333E-2"/>
+    <n v="1.9072772488492973E-2"/>
     <n v="85.173000000000016"/>
+    <n v="38.481161400000005"/>
     <n v="66.755754806448849"/>
     <n v="7.7430000000000092"/>
     <n v="-5.3371225967755791"/>
@@ -771,28 +977,29 @@
   <r>
     <x v="1"/>
     <s v="YPF"/>
-    <s v="YPF"/>
+    <x v="5"/>
     <d v="2024-12-01T00:00:00"/>
-    <n v="0.45129999999999998"/>
-    <n v="44.38"/>
-    <n v="20.028694000000002"/>
+    <n v="0.71050000000000002"/>
+    <n v="42.26"/>
+    <n v="30.025729999999999"/>
     <n v="0.1"/>
     <n v="0.2"/>
     <n v="0.5"/>
-    <n v="2.6879479918910414E-2"/>
-    <n v="48.818000000000005"/>
-    <n v="40.345454545454551"/>
-    <n v="4.4380000000000024"/>
-    <n v="-2.0172727272727258"/>
-    <n v="2.4207272727272766"/>
-    <n v="111.71171780845711"/>
-    <n v="8.9516124146852508E-3"/>
-    <n v="0.77998232616910645"/>
+    <n v="2.4785067848796617E-2"/>
+    <n v="46.486000000000004"/>
+    <n v="33.028303000000001"/>
+    <n v="38.418181818181822"/>
+    <n v="4.2260000000000062"/>
+    <n v="-1.9209090909090882"/>
+    <n v="2.305090909090918"/>
+    <n v="111.82735417209346"/>
+    <n v="8.9423558967609926E-3"/>
+    <n v="0.78078971076284676"/>
   </r>
   <r>
     <x v="2"/>
     <s v="Pepsi"/>
-    <s v="PEP"/>
+    <x v="6"/>
     <d v="2024-06-17T00:00:00"/>
     <n v="0.43659999999999999"/>
     <n v="160.25"/>
@@ -800,8 +1007,9 @@
     <n v="6.7199999999999996E-2"/>
     <n v="0.16439999999999999"/>
     <n v="0.40875912408759124"/>
-    <n v="2.1974465335167639E-2"/>
+    <n v="2.0262245248651251E-2"/>
     <n v="171.0188"/>
+    <n v="74.666808079999996"/>
     <n v="146.05359095880419"/>
     <n v="10.768799999999999"/>
     <n v="-7.0982045205979034"/>
@@ -813,7 +1021,7 @@
   <r>
     <x v="3"/>
     <s v="TSMC"/>
-    <s v="TSM"/>
+    <x v="7"/>
     <d v="2024-07-11T00:00:00"/>
     <n v="0.4108"/>
     <n v="189.76"/>
@@ -821,8 +1029,9 @@
     <n v="0.19835581787521095"/>
     <n v="0.37"/>
     <n v="0.53609680506813773"/>
-    <n v="2.8820006612842078E-2"/>
+    <n v="2.6574391374273774E-2"/>
     <n v="227.4"/>
+    <n v="93.41592"/>
     <n v="161.96043380326287"/>
     <n v="37.640000000000015"/>
     <n v="-13.899783098368559"/>
@@ -834,7 +1043,7 @@
   <r>
     <x v="2"/>
     <s v="Kimberly Clark"/>
-    <s v="KMB"/>
+    <x v="8"/>
     <d v="2024-09-09T00:00:00"/>
     <n v="0.35149999999999998"/>
     <n v="142.78"/>
@@ -842,8 +1051,9 @@
     <n v="7.0000000000000007E-2"/>
     <n v="0.18340000000000001"/>
     <n v="0.38167938931297712"/>
-    <n v="2.0518686961000319E-2"/>
+    <n v="1.8919899121218792E-2"/>
     <n v="152.77460000000002"/>
+    <n v="53.700271900000004"/>
     <n v="128.23783007005568"/>
     <n v="9.9946000000000197"/>
     <n v="-7.2710849649721609"/>
@@ -855,7 +1065,7 @@
   <r>
     <x v="4"/>
     <s v="Yum! Brands"/>
-    <s v="YUM"/>
+    <x v="9"/>
     <d v="2024-10-15T00:00:00"/>
     <n v="0.25669999999999998"/>
     <n v="132.38999999999999"/>
@@ -863,8 +1073,9 @@
     <n v="7.0000000000000007E-2"/>
     <n v="0.1623"/>
     <n v="0.43130006161429457"/>
-    <n v="2.3186242690372512E-2"/>
+    <n v="2.1379602580600905E-2"/>
     <n v="141.65729999999999"/>
+    <n v="36.363428909999996"/>
     <n v="121.20296621807194"/>
     <n v="9.2673000000000059"/>
     <n v="-5.5935168909640254"/>
@@ -876,16 +1087,17 @@
   <r>
     <x v="0"/>
     <s v="Visa"/>
-    <s v="V"/>
+    <x v="10"/>
     <d v="2024-08-07T00:00:00"/>
-    <n v="0.1938"/>
+    <n v="9.9999999999999998E-20"/>
     <n v="283.43"/>
-    <n v="54.928733999999999"/>
+    <n v="2.8342999999999998E-17"/>
     <n v="0.25"/>
     <n v="0.26"/>
     <n v="0.96153846153846145"/>
-    <n v="5.1691307536366179E-2"/>
+    <n v="4.766359201691657E-2"/>
     <n v="354.28750000000002"/>
+    <n v="3.542875E-17"/>
     <n v="280.62376237623761"/>
     <n v="70.857500000000016"/>
     <n v="-1.4031188118811997"/>
@@ -897,7 +1109,7 @@
   <r>
     <x v="3"/>
     <s v="QualComm2"/>
-    <s v="QCOM"/>
+    <x v="11"/>
     <d v="2024-09-09T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="188.12"/>
@@ -905,8 +1117,9 @@
     <n v="0.15"/>
     <n v="0.37780000000000002"/>
     <n v="0.39703546850185278"/>
-    <n v="2.1344213805381481E-2"/>
+    <n v="1.9681102050394347E-2"/>
     <n v="216.33799999999999"/>
+    <n v="2.16338E-17"/>
     <n v="153.21713634142367"/>
     <n v="28.217999999999989"/>
     <n v="-17.451431829288168"/>
@@ -918,7 +1131,7 @@
   <r>
     <x v="4"/>
     <s v="MSG"/>
-    <s v="INGR"/>
+    <x v="12"/>
     <d v="2024-10-15T00:00:00"/>
     <n v="0.19139999999999999"/>
     <n v="135.82"/>
@@ -926,20 +1139,21 @@
     <n v="0.1202"/>
     <n v="0.33710000000000001"/>
     <n v="0.35657075051913378"/>
-    <n v="1.9168872656499743E-2"/>
+    <n v="1.7675260489026123E-2"/>
     <n v="152.14556400000001"/>
+    <n v="29.120660949599998"/>
     <n v="111.61147177253677"/>
     <n v="16.325564000000014"/>
     <n v="-12.10426411373161"/>
     <n v="4.2212998862684046"/>
     <n v="109.91114519491597"/>
-    <n v="9.0982583997883393E-3"/>
+    <n v="9.0982583997883375E-3"/>
     <n v="0.76741054907089512"/>
   </r>
   <r>
     <x v="3"/>
     <s v="Apple2"/>
-    <s v="AAPL"/>
+    <x v="13"/>
     <d v="2024-07-09T00:00:00"/>
     <n v="0.18820000000000001"/>
     <n v="227.38"/>
@@ -947,8 +1161,9 @@
     <n v="0.15"/>
     <n v="0.2271"/>
     <n v="0.66050198150594452"/>
-    <n v="3.5507899496579148E-2"/>
+    <n v="3.2741172851778889E-2"/>
     <n v="261.48699999999997"/>
+    <n v="49.211853399999995"/>
     <n v="211.10389007520189"/>
     <n v="34.106999999999971"/>
     <n v="-8.1380549623990532"/>
@@ -960,7 +1175,7 @@
   <r>
     <x v="3"/>
     <s v="Microsoft"/>
-    <s v="MSFT"/>
+    <x v="14"/>
     <d v="2024-10-09T00:00:00"/>
     <n v="0.13370000000000001"/>
     <n v="423.77"/>
@@ -968,20 +1183,21 @@
     <n v="0.15"/>
     <n v="0.1963"/>
     <n v="0.76413652572592972"/>
-    <n v="4.10791847971122E-2"/>
+    <n v="3.7878351271721782E-2"/>
     <n v="487.33549999999991"/>
+    <n v="65.156756349999995"/>
     <n v="405.01768135334032"/>
     <n v="63.565499999999929"/>
     <n v="-9.3761593233298299"/>
     <n v="54.189340676670099"/>
     <n v="59.943104404514287"/>
-    <n v="1.6682485999585474E-2"/>
+    <n v="1.6682485999585477E-2"/>
     <n v="0.41852871774290379"/>
   </r>
   <r>
     <x v="0"/>
     <s v="Master Card"/>
-    <s v="MA"/>
+    <x v="15"/>
     <d v="2024-08-07T00:00:00"/>
     <n v="0.12939999999999999"/>
     <n v="501.56"/>
@@ -989,8 +1205,9 @@
     <n v="0.25"/>
     <n v="0.29699999999999999"/>
     <n v="0.84175084175084181"/>
-    <n v="4.5251649695135378E-2"/>
+    <n v="4.1725703449152558E-2"/>
     <n v="626.95000000000005"/>
+    <n v="81.127330000000001"/>
     <n v="479.04489016236869"/>
     <n v="125.39000000000004"/>
     <n v="-11.257554918815657"/>
@@ -1002,16 +1219,17 @@
   <r>
     <x v="3"/>
     <s v="Google"/>
-    <s v="GOOGL"/>
+    <x v="16"/>
     <d v="2024-07-10T00:00:00"/>
-    <n v="0.1195"/>
+    <n v="9.9999999999999998E-20"/>
     <n v="167.24"/>
-    <n v="19.98518"/>
+    <n v="1.6724000000000001E-17"/>
     <n v="0.13854341066730447"/>
     <n v="0.26790000000000003"/>
     <n v="0.51714598979956872"/>
-    <n v="2.7801230495925113E-2"/>
+    <n v="2.5634996889830789E-2"/>
     <n v="190.41"/>
+    <n v="1.9040999999999999E-17"/>
     <n v="148.08431772538498"/>
     <n v="23.169999999999987"/>
     <n v="-9.5778411373075159"/>
@@ -1023,28 +1241,29 @@
   <r>
     <x v="1"/>
     <s v="First Solar"/>
-    <s v="FSLR"/>
+    <x v="17"/>
     <d v="2024-08-07T00:00:00"/>
-    <n v="0.158"/>
-    <n v="189.72"/>
-    <n v="29.975760000000001"/>
-    <n v="3.3206831119544589E-2"/>
+    <n v="0.25169999999999998"/>
+    <n v="178.56"/>
+    <n v="44.943551999999997"/>
+    <n v="9.7782258064516236E-2"/>
     <n v="0.52980000000000005"/>
-    <n v="6.2678050433266491E-2"/>
-    <n v="3.3695067959548818E-3"/>
+    <n v="0.18456447350795815"/>
+    <n v="9.1488859967443371E-3"/>
     <n v="196.02"/>
-    <n v="126.76791792516488"/>
-    <n v="6.3000000000000114"/>
-    <n v="-31.476041037417559"/>
-    <n v="-25.176041037417548"/>
-    <n v="139.30848611860193"/>
-    <n v="7.1783135964067412E-3"/>
-    <n v="0.97266570767617244"/>
+    <n v="49.338234"/>
+    <n v="124.69119255370553"/>
+    <n v="17.460000000000008"/>
+    <n v="-26.934403723147234"/>
+    <n v="-9.4744037231472262"/>
+    <n v="123.60684880433161"/>
+    <n v="8.0901666022000929E-3"/>
+    <n v="0.86303531404059042"/>
   </r>
   <r>
     <x v="4"/>
     <s v="LVMH"/>
-    <s v="MC.PA"/>
+    <x v="18"/>
     <d v="2024-09-27T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="668.82"/>
@@ -1052,8 +1271,9 @@
     <n v="0.05"/>
     <n v="0.28000000000000003"/>
     <n v="0.17857142857142858"/>
-    <n v="9.5998142567537189E-3"/>
+    <n v="8.8518099459987919E-3"/>
     <n v="702.26100000000008"/>
+    <n v="7.0226100000000009E-17"/>
     <n v="543.7560975609756"/>
     <n v="33.441000000000031"/>
     <n v="-62.531951219512223"/>
@@ -1065,7 +1285,7 @@
   <r>
     <x v="3"/>
     <s v="ASML"/>
-    <s v="ASML"/>
+    <x v="19"/>
     <d v="2024-07-08T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="700.32"/>
@@ -1073,8 +1293,9 @@
     <n v="0.1"/>
     <n v="0.45340000000000003"/>
     <n v="0.22055580061755625"/>
-    <n v="1.1856850427397625E-2"/>
+    <n v="1.0932980965503582E-2"/>
     <n v="770.35200000000009"/>
+    <n v="7.7035200000000004E-17"/>
     <n v="517.45234224915032"/>
     <n v="70.032000000000039"/>
     <n v="-91.433828875424865"/>
@@ -1086,7 +1307,7 @@
   <r>
     <x v="3"/>
     <s v="Nvidia"/>
-    <s v="NVDA"/>
+    <x v="20"/>
     <d v="2024-07-09T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="147.01"/>
@@ -1094,8 +1315,9 @@
     <n v="0.15"/>
     <n v="0.52380000000000004"/>
     <n v="0.28636884306987398"/>
-    <n v="1.5394891133396571E-2"/>
+    <n v="1.4195342410536434E-2"/>
     <n v="169.06149999999997"/>
+    <n v="1.6906149999999997E-17"/>
     <n v="107.00975396709855"/>
     <n v="22.051499999999976"/>
     <n v="-20.000123016450722"/>
@@ -1107,7 +1329,7 @@
   <r>
     <x v="3"/>
     <s v="Applied Material"/>
-    <s v="AMAT"/>
+    <x v="21"/>
     <d v="2024-07-08T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="169.34"/>
@@ -1115,20 +1337,21 @@
     <n v="0.1"/>
     <n v="0.4259"/>
     <n v="0.23479690068091102"/>
-    <n v="1.2622437153749902E-2"/>
+    <n v="1.1638914228127082E-2"/>
     <n v="186.27400000000003"/>
+    <n v="1.8627400000000003E-17"/>
     <n v="127.71702239987934"/>
     <n v="16.934000000000026"/>
     <n v="-20.811488800060332"/>
     <n v="-3.8774888000603056"/>
     <n v="118.00993388124469"/>
-    <n v="8.4738628953585915E-3"/>
+    <n v="8.4738628953585898E-3"/>
     <n v="0.82395709729912847"/>
   </r>
   <r>
     <x v="1"/>
     <s v="Duke Energy"/>
-    <s v="DUK"/>
+    <x v="22"/>
     <d v="2024-08-07T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="113.58"/>
@@ -1136,20 +1359,21 @@
     <n v="6.664905793273479E-2"/>
     <n v="0.16439999999999999"/>
     <n v="0.40540789496797319"/>
-    <n v="2.1794306743518756E-2"/>
+    <n v="2.0096124366438057E-2"/>
     <n v="121.15000000000002"/>
+    <n v="1.2115000000000002E-17"/>
     <n v="103.46609203186667"/>
     <n v="7.5700000000000216"/>
     <n v="-5.0569539840666664"/>
     <n v="2.5130460159333552"/>
     <n v="111.61939906525103"/>
-    <n v="8.9590161600441431E-3"/>
+    <n v="8.9590161600441413E-3"/>
     <n v="0.77933774752071117"/>
   </r>
   <r>
     <x v="3"/>
     <s v="Palantir"/>
-    <s v="PLTR"/>
+    <x v="23"/>
     <d v="2024-07-08T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="64.349999999999994"/>
@@ -1157,8 +1381,9 @@
     <n v="0.15"/>
     <n v="0.67300000000000004"/>
     <n v="0.22288261515601782"/>
-    <n v="1.1981937556720838E-2"/>
+    <n v="1.1048321477918253E-2"/>
     <n v="74.002499999999984"/>
+    <n v="7.4002499999999988E-18"/>
     <n v="42.252133946158892"/>
     <n v="9.6524999999999892"/>
     <n v="-11.048933026920551"/>
@@ -1170,7 +1395,7 @@
   <r>
     <x v="1"/>
     <s v="Jinko Solar"/>
-    <s v="JKS"/>
+    <x v="24"/>
     <d v="2024-08-07T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="20.82"/>
@@ -1178,20 +1403,21 @@
     <n v="0.05"/>
     <n v="0.7389"/>
     <n v="6.7668155366084726E-2"/>
-    <n v="3.6377696466247688E-3"/>
+    <n v="3.3543196439026418E-3"/>
     <n v="21.861000000000001"/>
+    <n v="2.1860999999999999E-18"/>
     <n v="12.327550476641601"/>
     <n v="1.0410000000000004"/>
     <n v="-4.2462247616791995"/>
     <n v="-3.2052247616791991"/>
     <n v="117.33766984286359"/>
-    <n v="8.5224122938454584E-3"/>
+    <n v="8.5224122938454567E-3"/>
     <n v="0.81926328291024408"/>
   </r>
   <r>
     <x v="1"/>
     <s v="SolarWinds"/>
-    <s v="SWI"/>
+    <x v="25"/>
     <d v="2024-08-07T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="13.04"/>
@@ -1199,8 +1425,9 @@
     <n v="5.2147239263803824E-2"/>
     <n v="0.30159999999999998"/>
     <n v="0.17290198694895167"/>
-    <n v="9.2950309722681142E-3"/>
+    <n v="8.5707749554430283E-3"/>
     <n v="13.72"/>
+    <n v="1.3720000000000001E-18"/>
     <n v="10.436569040286594"/>
     <n v="0.68000000000000149"/>
     <n v="-1.3017154798567026"/>
@@ -1212,7 +1439,7 @@
   <r>
     <x v="1"/>
     <s v="Canadian Solar"/>
-    <s v="CSIQ"/>
+    <x v="26"/>
     <d v="2024-08-07T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="11.05"/>
@@ -1220,8 +1447,9 @@
     <n v="0.05"/>
     <n v="0.72170000000000001"/>
     <n v="6.9280864625190522E-2"/>
-    <n v="3.7244672189151191E-3"/>
+    <n v="3.434261860717281E-3"/>
     <n v="11.602500000000001"/>
+    <n v="1.16025E-18"/>
     <n v="6.6100376861877139"/>
     <n v="0.55250000000000021"/>
     <n v="-2.2199811569061434"/>
@@ -1233,16 +1461,17 @@
   <r>
     <x v="5"/>
     <s v="Gold"/>
-    <s v="GC=F"/>
-    <d v="2025-01-08T00:00:00"/>
+    <x v="27"/>
+    <d v="2025-01-09T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="2742.9"/>
     <n v="2.7429000000000002E-16"/>
     <n v="0.1"/>
     <n v="0.5"/>
     <n v="0.2"/>
-    <n v="1.0751791967564166E-2"/>
+    <n v="9.9140271395186472E-3"/>
     <n v="3017.1900000000005"/>
+    <n v="3.0171900000000003E-16"/>
     <n v="1959.214285714286"/>
     <n v="274.29000000000042"/>
     <n v="-391.84285714285704"/>
@@ -1254,7 +1483,7 @@
   <r>
     <x v="2"/>
     <s v="Walmart"/>
-    <s v="WMT"/>
+    <x v="28"/>
     <d v="2024-08-01T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="86.6"/>
@@ -1262,20 +1491,21 @@
     <n v="7.0000000000000007E-2"/>
     <n v="0.17249999999999999"/>
     <n v="0.40579710144927544"/>
-    <n v="2.1815230079115702E-2"/>
+    <n v="2.0115417384530591E-2"/>
     <n v="92.662000000000006"/>
+    <n v="9.2662000000000008E-18"/>
     <n v="78.548752834467123"/>
     <n v="6.0620000000000118"/>
     <n v="-4.0256235827664355"/>
     <n v="2.0363764172335763"/>
     <n v="112.0960686639508"/>
-    <n v="8.9209194570227766E-3"/>
+    <n v="8.9209194570227784E-3"/>
     <n v="0.78266590207514586"/>
   </r>
   <r>
     <x v="6"/>
     <s v="Aptive Autoparts"/>
-    <s v="APTV"/>
+    <x v="29"/>
     <d v="2024-09-27T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="56"/>
@@ -1283,8 +1513,9 @@
     <n v="7.0000000000000007E-2"/>
     <n v="0.19"/>
     <n v="0.36842105263157898"/>
-    <n v="1.9805932571828729E-2"/>
+    <n v="1.826268157279751E-2"/>
     <n v="59.92"/>
+    <n v="5.9920000000000002E-18"/>
     <n v="50.000000000000007"/>
     <n v="3.9200000000000017"/>
     <n v="-2.9999999999999964"/>
@@ -1296,7 +1527,7 @@
   <r>
     <x v="5"/>
     <s v="Mexican Peso"/>
-    <s v="USDMXN=X"/>
+    <x v="30"/>
     <d v="2024-10-15T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="20.399999999999999"/>
@@ -1304,20 +1535,21 @@
     <n v="0.1"/>
     <n v="0.15"/>
     <n v="0.66666666666666674"/>
-    <n v="3.5839306558547224E-2"/>
+    <n v="3.3046757131728825E-2"/>
     <n v="21.2"/>
+    <n v="2.1199999999999999E-18"/>
     <n v="19.428571428571431"/>
     <n v="0.80000000000000071"/>
     <n v="-0.48571428571428399"/>
     <n v="0.31428571428571672"/>
     <n v="113.81815936689867"/>
-    <n v="8.7859442250902055E-3"/>
+    <n v="8.7859442250902038E-3"/>
     <n v="0.79468971066667204"/>
   </r>
   <r>
     <x v="4"/>
     <s v="Yum China Holding"/>
-    <s v="YUMC"/>
+    <x v="31"/>
     <d v="2024-10-09T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="47.42"/>
@@ -1325,8 +1557,9 @@
     <n v="7.0000000000000007E-2"/>
     <n v="0.4"/>
     <n v="0.17500000000000002"/>
-    <n v="9.4078179716186455E-3"/>
+    <n v="8.6747737470788174E-3"/>
     <n v="50.739400000000003"/>
+    <n v="5.0739400000000001E-18"/>
     <n v="35.654135338345867"/>
     <n v="3.3194000000000017"/>
     <n v="-5.8829323308270673"/>
@@ -1338,7 +1571,7 @@
   <r>
     <x v="4"/>
     <s v="MSG"/>
-    <s v="DAR"/>
+    <x v="32"/>
     <d v="2024-08-03T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="41.8"/>
@@ -1346,8 +1579,9 @@
     <n v="7.0000000000000007E-2"/>
     <n v="0.4"/>
     <n v="0.17500000000000002"/>
-    <n v="9.4078179716186455E-3"/>
+    <n v="8.6747737470788174E-3"/>
     <n v="44.725999999999999"/>
+    <n v="4.4725999999999996E-18"/>
     <n v="31.428571428571431"/>
     <n v="2.9260000000000019"/>
     <n v="-5.1857142857142833"/>
@@ -1359,7 +1593,7 @@
   <r>
     <x v="5"/>
     <s v="Japan Yen"/>
-    <s v="USDJPY=X"/>
+    <x v="33"/>
     <d v="2024-10-09T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="153.7552"/>
@@ -1367,20 +1601,21 @@
     <n v="7.0000000000000007E-2"/>
     <n v="0.19"/>
     <n v="0.36842105263157898"/>
-    <n v="1.9805932571828729E-2"/>
+    <n v="1.826268157279751E-2"/>
     <n v="164.51806400000001"/>
+    <n v="1.6451806399999999E-17"/>
     <n v="137.28142857142859"/>
     <n v="10.762864000000008"/>
     <n v="-8.2368857142857053"/>
     <n v="2.5259782857143023"/>
     <n v="111.60646679547008"/>
-    <n v="8.9600542756415637E-3"/>
+    <n v="8.9600542756415654E-3"/>
     <n v="0.77924745312667376"/>
   </r>
   <r>
     <x v="7"/>
     <s v="3M"/>
-    <s v="MMM"/>
+    <x v="34"/>
     <d v="2024-12-01T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="133.53"/>
@@ -1388,8 +1623,9 @@
     <n v="7.0000000000000007E-2"/>
     <n v="0.2"/>
     <n v="0.35000000000000003"/>
-    <n v="1.8815635943237291E-2"/>
+    <n v="1.7349547494157635E-2"/>
     <n v="142.87710000000001"/>
+    <n v="1.428771E-17"/>
     <n v="118.16814159292036"/>
     <n v="9.3471000000000117"/>
     <n v="-7.6809292035398187"/>
@@ -1401,28 +1637,29 @@
   <r>
     <x v="1"/>
     <s v="Excelon"/>
-    <s v="EXC"/>
+    <x v="35"/>
     <d v="2024-12-01T00:00:00"/>
-    <n v="9.9999999999999998E-20"/>
-    <n v="39.56"/>
-    <n v="3.9560000000000004E-18"/>
+    <n v="0.27450000000000002"/>
+    <n v="39.799999999999997"/>
+    <n v="10.9251"/>
     <n v="0.1"/>
     <n v="0.2"/>
     <n v="0.5"/>
-    <n v="2.6879479918910414E-2"/>
-    <n v="43.516000000000005"/>
-    <n v="35.963636363636368"/>
-    <n v="3.9560000000000031"/>
-    <n v="-1.798181818181817"/>
-    <n v="2.1578181818181861"/>
-    <n v="111.9746268993662"/>
-    <n v="8.9305946149632592E-3"/>
-    <n v="0.78181798359449739"/>
+    <n v="2.4785067848796617E-2"/>
+    <n v="43.78"/>
+    <n v="12.017610000000001"/>
+    <n v="36.181818181818187"/>
+    <n v="3.980000000000004"/>
+    <n v="-1.8090909090909051"/>
+    <n v="2.1709090909090989"/>
+    <n v="111.96153599027528"/>
+    <n v="8.931638809303739E-3"/>
+    <n v="0.78172658156501729"/>
   </r>
   <r>
     <x v="1"/>
     <s v="PG&amp;E"/>
-    <s v="PCG"/>
+    <x v="36"/>
     <d v="2024-12-01T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="26.63"/>
@@ -1430,8 +1667,9 @@
     <n v="0.1"/>
     <n v="0.2"/>
     <n v="0.5"/>
-    <n v="2.6879479918910414E-2"/>
+    <n v="2.4785067848796617E-2"/>
     <n v="29.293000000000003"/>
+    <n v="2.9293000000000003E-18"/>
     <n v="24.209090909090911"/>
     <n v="2.6630000000000038"/>
     <n v="-1.2104545454545441"/>
@@ -1443,7 +1681,7 @@
   <r>
     <x v="8"/>
     <s v="Agios"/>
-    <s v="AGIO"/>
+    <x v="37"/>
     <d v="2024-12-04T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="59.17"/>
@@ -1451,8 +1689,9 @@
     <n v="0.2"/>
     <n v="0.2"/>
     <n v="1"/>
-    <n v="5.3758959837820829E-2"/>
+    <n v="4.9570135697593234E-2"/>
     <n v="71.004000000000005"/>
+    <n v="7.1003999999999996E-18"/>
     <n v="59.17"/>
     <n v="11.834000000000003"/>
     <n v="0"/>
@@ -1464,7 +1703,7 @@
   <r>
     <x v="2"/>
     <s v="Albertson Companies"/>
-    <s v="ACI"/>
+    <x v="38"/>
     <d v="2024-12-04T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="19.309999999999999"/>
@@ -1472,20 +1711,21 @@
     <n v="0.2"/>
     <n v="0.2"/>
     <n v="1"/>
-    <n v="5.3758959837820829E-2"/>
+    <n v="4.9570135697593234E-2"/>
     <n v="23.171999999999997"/>
+    <n v="2.3171999999999995E-18"/>
     <n v="19.309999999999999"/>
     <n v="3.8619999999999983"/>
     <n v="0"/>
     <n v="3.8619999999999983"/>
     <n v="110.27044508118439"/>
-    <n v="9.0686130745529347E-3"/>
+    <n v="9.0686130745529329E-3"/>
     <n v="0.76991921661787932"/>
   </r>
   <r>
     <x v="8"/>
     <s v="HCA Healthcare"/>
-    <s v="HCA"/>
+    <x v="39"/>
     <d v="2024-12-04T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="323.75"/>
@@ -1493,35 +1733,192 @@
     <n v="0.2"/>
     <n v="0.2"/>
     <n v="1"/>
-    <n v="5.3758959837820829E-2"/>
+    <n v="4.9570135697593234E-2"/>
     <n v="388.5"/>
+    <n v="3.8849999999999999E-17"/>
     <n v="323.75"/>
     <n v="64.75"/>
     <n v="0"/>
     <n v="64.75"/>
     <n v="49.382445081184386"/>
-    <n v="2.0250111114506527E-2"/>
+    <n v="2.0250111114506524E-2"/>
     <n v="0.34479314383458876"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <s v="ETF1"/>
+    <x v="40"/>
+    <d v="2024-07-08T00:00:00"/>
+    <n v="2"/>
+    <n v="20.928000000000001"/>
+    <n v="41.856000000000002"/>
+    <n v="4.4999999999999998E-2"/>
+    <n v="0.2"/>
+    <n v="0.22499999999999998"/>
+    <n v="1.1153280531958477E-2"/>
+    <n v="21.869759999999999"/>
+    <n v="43.739519999999999"/>
+    <n v="18.119480519480518"/>
+    <n v="0.9417599999999986"/>
+    <n v="-1.4042597402597412"/>
+    <n v="-0.46249974025974261"/>
+    <n v="114.59494482144413"/>
+    <n v="8.7263884245343277E-3"/>
+    <n v="0.80011330398039715"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <s v="ETF2"/>
+    <x v="41"/>
+    <d v="2024-07-08T00:00:00"/>
+    <n v="2"/>
+    <n v="16.399999999999999"/>
+    <n v="32.799999999999997"/>
+    <n v="4.4999999999999998E-2"/>
+    <n v="0.2"/>
+    <n v="0.22499999999999998"/>
+    <n v="1.1153280531958477E-2"/>
+    <n v="17.137999999999998"/>
+    <n v="34.275999999999996"/>
+    <n v="14.199134199134198"/>
+    <n v="0.73799999999999955"/>
+    <n v="-1.1004329004329003"/>
+    <n v="-0.36243290043290077"/>
+    <n v="114.49487798161729"/>
+    <n v="8.7340151597048287E-3"/>
+    <n v="0.79941462735066027"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <s v="ETF3"/>
+    <x v="42"/>
+    <d v="2024-07-08T00:00:00"/>
+    <n v="1"/>
+    <n v="48.68"/>
+    <n v="48.68"/>
+    <n v="2.5000000000000001E-2"/>
+    <n v="0.2"/>
+    <n v="0.125"/>
+    <n v="6.1962669621991543E-3"/>
+    <n v="49.896999999999998"/>
+    <n v="49.896999999999998"/>
+    <n v="41.42978723404255"/>
+    <n v="1.2169999999999987"/>
+    <n v="-3.6251063829787249"/>
+    <n v="-2.4081063829787261"/>
+    <n v="116.54055146416312"/>
+    <n v="8.5807042049865865E-3"/>
+    <n v="0.81369772309746791"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <s v="ETF5"/>
+    <x v="43"/>
+    <d v="2024-07-08T00:00:00"/>
+    <n v="1"/>
+    <n v="51.28"/>
+    <n v="51.28"/>
+    <n v="2.5000000000000001E-2"/>
+    <n v="0.2"/>
+    <n v="0.125"/>
+    <n v="6.1962669621991543E-3"/>
+    <n v="52.561999999999998"/>
+    <n v="52.561999999999998"/>
+    <n v="43.642553191489363"/>
+    <n v="1.2819999999999965"/>
+    <n v="-3.8187234042553193"/>
+    <n v="-2.5367234042553228"/>
+    <n v="116.66916848543971"/>
+    <n v="8.571244768276547E-3"/>
+    <n v="0.81459573993409262"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <s v="Emerging Markets"/>
+    <x v="44"/>
+    <d v="2024-07-08T00:00:00"/>
+    <n v="1"/>
+    <n v="44.14"/>
+    <n v="44.14"/>
+    <n v="0.15"/>
+    <n v="0.2"/>
+    <n v="0.74999999999999989"/>
+    <n v="3.7177601773194922E-2"/>
+    <n v="50.760999999999996"/>
+    <n v="50.760999999999996"/>
+    <n v="42.038095238095238"/>
+    <n v="6.6209999999999951"/>
+    <n v="-1.0509523809523813"/>
+    <n v="5.5700476190476138"/>
+    <n v="108.56239746213677"/>
+    <n v="9.2112925227979536E-3"/>
+    <n v="0.75799345823506892"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <m/>
+    <x v="45"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="10"/>
+    <m/>
+    <x v="45"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{26B2B253-9CE0-4227-B980-7D5C03945A28}" name="PivotTable1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:C13" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="19">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{42F2A961-4B24-4134-99E9-0FE83E8807F0}" name="PivotTable1" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:E19" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="22">
     <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="10">
-        <item x="4"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="8"/>
-        <item x="7"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item t="default"/>
+      <items count="12">
+        <item sd="0" x="4"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="2"/>
+        <item x="9"/>
+        <item h="1" sd="0" x="10"/>
+        <item t="default" sd="0"/>
       </items>
       <autoSortScope>
         <pivotArea dataOnly="0" outline="0" fieldPosition="0">
@@ -1534,7 +1931,57 @@
       </autoSortScope>
     </pivotField>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="47">
+        <item x="13"/>
+        <item x="38"/>
+        <item x="37"/>
+        <item x="21"/>
+        <item x="1"/>
+        <item x="29"/>
+        <item x="19"/>
+        <item x="41"/>
+        <item x="43"/>
+        <item x="40"/>
+        <item x="26"/>
+        <item x="32"/>
+        <item x="22"/>
+        <item x="35"/>
+        <item x="17"/>
+        <item x="27"/>
+        <item x="16"/>
+        <item x="39"/>
+        <item x="0"/>
+        <item x="12"/>
+        <item x="24"/>
+        <item x="8"/>
+        <item x="15"/>
+        <item x="3"/>
+        <item x="18"/>
+        <item x="34"/>
+        <item x="2"/>
+        <item x="14"/>
+        <item x="4"/>
+        <item x="20"/>
+        <item x="36"/>
+        <item x="6"/>
+        <item x="23"/>
+        <item x="11"/>
+        <item x="25"/>
+        <item x="7"/>
+        <item x="33"/>
+        <item x="30"/>
+        <item x="10"/>
+        <item x="42"/>
+        <item x="28"/>
+        <item x="5"/>
+        <item x="9"/>
+        <item x="31"/>
+        <item x="45"/>
+        <item x="44"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField numFmtId="165" showAll="0"/>
     <pivotField numFmtId="164" showAll="0"/>
     <pivotField numFmtId="44" showAll="0"/>
@@ -1549,13 +1996,35 @@
     <pivotField numFmtId="44" showAll="0"/>
     <pivotField numFmtId="44" showAll="0"/>
     <pivotField numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
     <pivotField numFmtId="9" showAll="0"/>
     <pivotField numFmtId="9" showAll="0"/>
+    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
-  <rowFields count="1">
+  <rowFields count="2">
     <field x="0"/>
+    <field x="2"/>
   </rowFields>
-  <rowItems count="10">
+  <rowItems count="16">
+    <i>
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="39"/>
+    </i>
+    <i r="1">
+      <x v="45"/>
+    </i>
     <i>
       <x v="8"/>
     </i>
@@ -1563,10 +2032,10 @@
       <x v="7"/>
     </i>
     <i>
-      <x v="2"/>
+      <x v="3"/>
     </i>
     <i>
-      <x v="3"/>
+      <x v="2"/>
     </i>
     <i>
       <x/>
@@ -1590,15 +2059,21 @@
   <colFields count="1">
     <field x="-2"/>
   </colFields>
-  <colItems count="2">
+  <colItems count="4">
     <i>
       <x/>
     </i>
     <i i="1">
       <x v="1"/>
     </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+    <i i="3">
+      <x v="3"/>
+    </i>
   </colItems>
-  <dataFields count="2">
+  <dataFields count="4">
     <dataField name="Initial Volume $" fld="6" baseField="0" baseItem="0" numFmtId="44"/>
     <dataField name="$%" fld="6" baseField="0" baseItem="7" numFmtId="9">
       <extLst>
@@ -1607,9 +2082,11 @@
         </ext>
       </extLst>
     </dataField>
+    <dataField name="Target Return %" fld="20" baseField="0" baseItem="0" numFmtId="10"/>
+    <dataField name="Target P&amp;L" fld="21" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
-  <formats count="2">
-    <format dxfId="5">
+  <formats count="3">
+    <format dxfId="11">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -1619,12 +2096,21 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="4">
+    <format dxfId="10">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
             <x v="0"/>
             <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="9">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="2"/>
           </reference>
         </references>
       </pivotArea>
@@ -1905,7 +2391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S41"/>
+  <dimension ref="A1:T46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
@@ -1920,16 +2406,17 @@
     <col min="10" max="10" width="9.140625" style="10"/>
     <col min="11" max="11" width="7.5703125" style="10" customWidth="1"/>
     <col min="12" max="12" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>35</v>
       </c>
@@ -1967,35 +2454,38 @@
         <v>64</v>
       </c>
       <c r="M1" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="N1" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="O1" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="P1" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="P1" s="16" t="s">
+      <c r="Q1" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="Q1" s="16" t="s">
+      <c r="R1" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="R1" s="16" t="s">
+      <c r="S1" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="S1" s="16" t="s">
+      <c r="T1" s="16" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>37</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="32" t="s">
         <v>86</v>
       </c>
       <c r="D2" s="8">
@@ -2008,7 +2498,7 @@
         <v>15.3</v>
       </c>
       <c r="G2" s="1">
-        <f>E2*F2</f>
+        <f t="shared" ref="G2:G41" si="0">E2*F2</f>
         <v>29.980350000000001</v>
       </c>
       <c r="H2" s="11">
@@ -2018,47 +2508,51 @@
         <v>0.39532299999999998</v>
       </c>
       <c r="J2" s="9">
-        <f>IFERROR(H2/I2,"")</f>
+        <f t="shared" ref="J2:J41" si="1">IFERROR(H2/I2,"")</f>
         <v>0.88535197800279775</v>
       </c>
       <c r="K2" s="9">
         <f>IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.7595601427787633E-2</v>
+        <v>4.3887017689731266E-2</v>
       </c>
       <c r="L2" s="12">
         <f>F2/(1-(F2*(1+H2)-F2)/(F2*(1+H2)))</f>
         <v>20.655000000000001</v>
       </c>
       <c r="M2" s="12">
-        <f>F2/(1+I2-H2)</f>
+        <f>L2*E2</f>
+        <v>40.4734725</v>
+      </c>
+      <c r="N2" s="12">
+        <f t="shared" ref="N2:N41" si="2">F2/(1+I2-H2)</f>
         <v>14.636624277854791</v>
       </c>
-      <c r="N2" s="12">
-        <f>L2-F2</f>
+      <c r="O2" s="12">
+        <f t="shared" ref="O2:O41" si="3">L2-F2</f>
         <v>5.3550000000000004</v>
       </c>
-      <c r="O2" s="12">
-        <f>0.5*(M2-F2)</f>
+      <c r="P2" s="12">
+        <f t="shared" ref="P2:P41" si="4">0.5*(N2-F2)</f>
         <v>-0.33168786107260484</v>
       </c>
-      <c r="P2" s="15">
-        <f>N2+O2</f>
+      <c r="Q2" s="15">
+        <f t="shared" ref="Q2:Q41" si="5">O2+P2</f>
         <v>5.0233121389273956</v>
       </c>
-      <c r="Q2" s="12">
-        <f>MAX($P$2:$P$280)-P2</f>
+      <c r="R2" s="12">
+        <f>MAX($Q$2:$Q$279)-Q2</f>
         <v>109.10913294225699</v>
       </c>
-      <c r="R2" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q2)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+      <c r="S2" s="9">
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R2)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>9.165135612700933E-3</v>
       </c>
-      <c r="S2" s="9">
-        <f>Q2/MAX($Q$2:$Q$28)</f>
+      <c r="T2" s="9">
+        <f t="shared" ref="T2:T41" si="6">R2/MAX($R$2:$R$28)</f>
         <v>0.76181081974332665</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>40</v>
       </c>
@@ -2078,7 +2572,7 @@
         <v>21.73</v>
       </c>
       <c r="G3" s="1">
-        <f>E3*F3</f>
+        <f t="shared" si="0"/>
         <v>41.237020999999999</v>
       </c>
       <c r="H3" s="11">
@@ -2089,46 +2583,50 @@
         <v>0.45929999999999999</v>
       </c>
       <c r="J3" s="9">
-        <f>IFERROR(H3/I3,"")</f>
+        <f t="shared" si="1"/>
         <v>0.48594326447066366</v>
       </c>
       <c r="K3" s="9">
         <f>IFERROR(J3/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.6123804438137953E-2</v>
+        <v>2.4088273561142234E-2</v>
       </c>
       <c r="L3" s="12">
         <v>26.58</v>
       </c>
       <c r="M3" s="12">
-        <f>F3/(1+I3-H3)</f>
+        <f t="shared" ref="M3:M41" si="7">L3*E3</f>
+        <v>50.440865999999993</v>
+      </c>
+      <c r="N3" s="12">
+        <f t="shared" si="2"/>
         <v>17.579394852436032</v>
       </c>
-      <c r="N3" s="12">
-        <f>L3-F3</f>
+      <c r="O3" s="12">
+        <f t="shared" si="3"/>
         <v>4.8499999999999979</v>
       </c>
-      <c r="O3" s="12">
-        <f>0.5*(M3-F3)</f>
+      <c r="P3" s="12">
+        <f t="shared" si="4"/>
         <v>-2.0753025737819843</v>
       </c>
-      <c r="P3" s="15">
-        <f>N3+O3</f>
+      <c r="Q3" s="15">
+        <f t="shared" si="5"/>
         <v>2.7746974262180135</v>
       </c>
-      <c r="Q3" s="12">
-        <f>MAX($P$2:$P$280)-P3</f>
+      <c r="R3" s="12">
+        <f>MAX($Q$2:$Q$279)-Q3</f>
         <v>111.35774765496637</v>
       </c>
-      <c r="R3" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q3)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>8.9800666864996662E-3</v>
-      </c>
       <c r="S3" s="9">
-        <f>Q3/MAX($Q$2:$Q$28)</f>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R3)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>8.980066686499668E-3</v>
+      </c>
+      <c r="T3" s="9">
+        <f t="shared" si="6"/>
         <v>0.77751087134654673</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>38</v>
       </c>
@@ -2148,7 +2646,7 @@
         <v>51.88</v>
       </c>
       <c r="G4" s="1">
-        <f>E4*F4</f>
+        <f t="shared" si="0"/>
         <v>89.991048000000006</v>
       </c>
       <c r="H4" s="11">
@@ -2159,47 +2657,51 @@
         <v>0.19980000000000001</v>
       </c>
       <c r="J4" s="9">
-        <f>IFERROR(H4/I4,"")</f>
+        <f t="shared" si="1"/>
         <v>0.92242242242242245</v>
       </c>
       <c r="K4" s="9">
         <f>IFERROR(J4/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.9588469960512409E-2</v>
+        <v>4.5724604649982147E-2</v>
       </c>
       <c r="L4" s="12">
-        <f>F4/(1-(F4*(1+H4)-F4)/(F4*(1+H4)))</f>
+        <f t="shared" ref="L4:L31" si="8">F4/(1-(F4*(1+H4)-F4)/(F4*(1+H4)))</f>
         <v>61.441483999999996</v>
       </c>
       <c r="M4" s="12">
-        <f>F4/(1+I4-H4)</f>
+        <f t="shared" si="7"/>
+        <v>106.57639814639998</v>
+      </c>
+      <c r="N4" s="12">
+        <f t="shared" si="2"/>
         <v>51.088133924175295</v>
       </c>
-      <c r="N4" s="12">
-        <f>L4-F4</f>
+      <c r="O4" s="12">
+        <f t="shared" si="3"/>
         <v>9.561483999999993</v>
       </c>
-      <c r="O4" s="12">
-        <f>0.5*(M4-F4)</f>
+      <c r="P4" s="12">
+        <f t="shared" si="4"/>
         <v>-0.39593303791235357</v>
       </c>
-      <c r="P4" s="15">
-        <f>N4+O4</f>
+      <c r="Q4" s="15">
+        <f t="shared" si="5"/>
         <v>9.1655509620876394</v>
       </c>
-      <c r="Q4" s="12">
-        <f>MAX($P$2:$P$280)-P4</f>
+      <c r="R4" s="12">
+        <f>MAX($Q$2:$Q$279)-Q4</f>
         <v>104.96689411909675</v>
       </c>
-      <c r="R4" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q4)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+      <c r="S4" s="9">
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R4)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>9.526813271862531E-3</v>
       </c>
-      <c r="S4" s="9">
-        <f>Q4/MAX($Q$2:$Q$28)</f>
+      <c r="T4" s="9">
+        <f t="shared" si="6"/>
         <v>0.73288929623425103</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -2219,7 +2721,7 @@
         <v>10.92</v>
       </c>
       <c r="G5" s="1">
-        <f>E5*F5</f>
+        <f t="shared" si="0"/>
         <v>1.092E-18</v>
       </c>
       <c r="H5" s="11">
@@ -2229,47 +2731,51 @@
         <v>1.8652</v>
       </c>
       <c r="J5" s="9">
-        <f>IFERROR(H5/I5,"")</f>
+        <f t="shared" si="1"/>
         <v>0.53613553506326406</v>
       </c>
       <c r="K5" s="9">
         <f>IFERROR(J5/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.8822088697094593E-2</v>
+        <v>2.6576311225387755E-2</v>
       </c>
       <c r="L5" s="12">
-        <f>F5/(1-(F5*(1+H5)-F5)/(F5*(1+H5)))</f>
+        <f t="shared" si="8"/>
         <v>21.84</v>
       </c>
       <c r="M5" s="12">
-        <f>F5/(1+I5-H5)</f>
+        <f t="shared" si="7"/>
+        <v>2.1840000000000001E-18</v>
+      </c>
+      <c r="N5" s="12">
+        <f t="shared" si="2"/>
         <v>5.8546000428908433</v>
       </c>
-      <c r="N5" s="12">
-        <f>L5-F5</f>
+      <c r="O5" s="12">
+        <f t="shared" si="3"/>
         <v>10.92</v>
       </c>
-      <c r="O5" s="12">
-        <f>0.5*(M5-F5)</f>
+      <c r="P5" s="12">
+        <f t="shared" si="4"/>
         <v>-2.5326999785545783</v>
       </c>
-      <c r="P5" s="15">
-        <f>N5+O5</f>
+      <c r="Q5" s="15">
+        <f t="shared" si="5"/>
         <v>8.3873000214454212</v>
       </c>
-      <c r="Q5" s="12">
-        <f>MAX($P$2:$P$280)-P5</f>
+      <c r="R5" s="12">
+        <f>MAX($Q$2:$Q$279)-Q5</f>
         <v>105.74514505973896</v>
       </c>
-      <c r="R5" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q5)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+      <c r="S5" s="9">
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R5)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>9.456698928684306E-3</v>
       </c>
-      <c r="S5" s="9">
-        <f>Q5/MAX($Q$2:$Q$28)</f>
+      <c r="T5" s="9">
+        <f t="shared" si="6"/>
         <v>0.73832312171768166</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>40</v>
       </c>
@@ -2289,7 +2795,7 @@
         <v>77.430000000000007</v>
       </c>
       <c r="G6" s="1">
-        <f>E6*F6</f>
+        <f t="shared" si="0"/>
         <v>34.982874000000002</v>
       </c>
       <c r="H6" s="11">
@@ -2299,47 +2805,51 @@
         <v>0.25990000000000002</v>
       </c>
       <c r="J6" s="9">
-        <f>IFERROR(H6/I6,"")</f>
+        <f t="shared" si="1"/>
         <v>0.38476337052712584</v>
       </c>
       <c r="K6" s="9">
         <f>IFERROR(J6/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.0684478583232333E-2</v>
+        <v>1.9072772488492973E-2</v>
       </c>
       <c r="L6" s="12">
-        <f>F6/(1-(F6*(1+H6)-F6)/(F6*(1+H6)))</f>
+        <f t="shared" si="8"/>
         <v>85.173000000000016</v>
       </c>
       <c r="M6" s="12">
-        <f>F6/(1+I6-H6)</f>
+        <f t="shared" si="7"/>
+        <v>38.481161400000005</v>
+      </c>
+      <c r="N6" s="12">
+        <f t="shared" si="2"/>
         <v>66.755754806448849</v>
       </c>
-      <c r="N6" s="12">
-        <f>L6-F6</f>
+      <c r="O6" s="12">
+        <f t="shared" si="3"/>
         <v>7.7430000000000092</v>
       </c>
-      <c r="O6" s="12">
-        <f>0.5*(M6-F6)</f>
+      <c r="P6" s="12">
+        <f t="shared" si="4"/>
         <v>-5.3371225967755791</v>
       </c>
-      <c r="P6" s="15">
-        <f>N6+O6</f>
+      <c r="Q6" s="15">
+        <f t="shared" si="5"/>
         <v>2.4058774032244301</v>
       </c>
-      <c r="Q6" s="12">
-        <f>MAX($P$2:$P$280)-P6</f>
+      <c r="R6" s="12">
+        <f>MAX($Q$2:$Q$279)-Q6</f>
         <v>111.72656767795996</v>
       </c>
-      <c r="R6" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q6)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+      <c r="S6" s="9">
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R6)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>8.9504226325326178E-3</v>
       </c>
-      <c r="S6" s="9">
-        <f>Q6/MAX($Q$2:$Q$28)</f>
+      <c r="T6" s="9">
+        <f t="shared" si="6"/>
         <v>0.78008600943515383</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -2353,14 +2863,14 @@
         <v>45627</v>
       </c>
       <c r="E7" s="2">
-        <v>0.45129999999999998</v>
+        <v>0.71050000000000002</v>
       </c>
       <c r="F7" s="1">
-        <v>44.38</v>
+        <v>42.26</v>
       </c>
       <c r="G7" s="1">
-        <f>E7*F7</f>
-        <v>20.028694000000002</v>
+        <f t="shared" si="0"/>
+        <v>30.025729999999999</v>
       </c>
       <c r="H7" s="11">
         <v>0.1</v>
@@ -2369,47 +2879,51 @@
         <v>0.2</v>
       </c>
       <c r="J7" s="9">
-        <f>IFERROR(H7/I7,"")</f>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
       <c r="K7" s="9">
         <f>IFERROR(J7/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.6879479918910414E-2</v>
+        <v>2.4785067848796617E-2</v>
       </c>
       <c r="L7" s="12">
-        <f>F7/(1-(F7*(1+H7)-F7)/(F7*(1+H7)))</f>
-        <v>48.818000000000005</v>
+        <f t="shared" si="8"/>
+        <v>46.486000000000004</v>
       </c>
       <c r="M7" s="12">
-        <f>F7/(1+I7-H7)</f>
-        <v>40.345454545454551</v>
+        <f t="shared" si="7"/>
+        <v>33.028303000000001</v>
       </c>
       <c r="N7" s="12">
-        <f>L7-F7</f>
-        <v>4.4380000000000024</v>
+        <f t="shared" si="2"/>
+        <v>38.418181818181822</v>
       </c>
       <c r="O7" s="12">
-        <f>0.5*(M7-F7)</f>
-        <v>-2.0172727272727258</v>
-      </c>
-      <c r="P7" s="15">
-        <f>N7+O7</f>
-        <v>2.4207272727272766</v>
-      </c>
-      <c r="Q7" s="12">
-        <f>MAX($P$2:$P$280)-P7</f>
-        <v>111.71171780845711</v>
-      </c>
-      <c r="R7" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q7)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>8.9516124146852508E-3</v>
+        <f t="shared" si="3"/>
+        <v>4.2260000000000062</v>
+      </c>
+      <c r="P7" s="12">
+        <f t="shared" si="4"/>
+        <v>-1.9209090909090882</v>
+      </c>
+      <c r="Q7" s="15">
+        <f t="shared" si="5"/>
+        <v>2.305090909090918</v>
+      </c>
+      <c r="R7" s="12">
+        <f>MAX($Q$2:$Q$279)-Q7</f>
+        <v>111.82735417209346</v>
       </c>
       <c r="S7" s="9">
-        <f>Q7/MAX($Q$2:$Q$28)</f>
-        <v>0.77998232616910645</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R7)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>8.9423558967609926E-3</v>
+      </c>
+      <c r="T7" s="9">
+        <f t="shared" si="6"/>
+        <v>0.78078971076284676</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -2429,7 +2943,7 @@
         <v>160.25</v>
       </c>
       <c r="G8" s="1">
-        <f>E8*F8</f>
+        <f t="shared" si="0"/>
         <v>69.965149999999994</v>
       </c>
       <c r="H8" s="11">
@@ -2439,47 +2953,51 @@
         <v>0.16439999999999999</v>
       </c>
       <c r="J8" s="9">
-        <f>IFERROR(H8/I8,"")</f>
+        <f t="shared" si="1"/>
         <v>0.40875912408759124</v>
       </c>
       <c r="K8" s="9">
         <f>IFERROR(J8/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.1974465335167639E-2</v>
+        <v>2.0262245248651251E-2</v>
       </c>
       <c r="L8" s="12">
-        <f>F8/(1-(F8*(1+H8)-F8)/(F8*(1+H8)))</f>
+        <f t="shared" si="8"/>
         <v>171.0188</v>
       </c>
       <c r="M8" s="12">
-        <f>F8/(1+I8-H8)</f>
+        <f t="shared" si="7"/>
+        <v>74.666808079999996</v>
+      </c>
+      <c r="N8" s="12">
+        <f t="shared" si="2"/>
         <v>146.05359095880419</v>
       </c>
-      <c r="N8" s="12">
-        <f>L8-F8</f>
+      <c r="O8" s="12">
+        <f t="shared" si="3"/>
         <v>10.768799999999999</v>
       </c>
-      <c r="O8" s="12">
-        <f>0.5*(M8-F8)</f>
+      <c r="P8" s="12">
+        <f t="shared" si="4"/>
         <v>-7.0982045205979034</v>
       </c>
-      <c r="P8" s="15">
-        <f>N8+O8</f>
+      <c r="Q8" s="15">
+        <f t="shared" si="5"/>
         <v>3.6705954794020954</v>
       </c>
-      <c r="Q8" s="12">
-        <f>MAX($P$2:$P$280)-P8</f>
+      <c r="R8" s="12">
+        <f>MAX($Q$2:$Q$279)-Q8</f>
         <v>110.46184960178229</v>
       </c>
-      <c r="R8" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q8)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+      <c r="S8" s="9">
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R8)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>9.0528992915203284E-3</v>
       </c>
-      <c r="S8" s="9">
-        <f>Q8/MAX($Q$2:$Q$28)</f>
+      <c r="T8" s="9">
+        <f t="shared" si="6"/>
         <v>0.7712556220204998</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>36</v>
       </c>
@@ -2499,7 +3017,7 @@
         <v>189.76</v>
       </c>
       <c r="G9" s="1">
-        <f>E9*F9</f>
+        <f t="shared" si="0"/>
         <v>77.953407999999996</v>
       </c>
       <c r="H9" s="11">
@@ -2510,47 +3028,51 @@
         <v>0.37</v>
       </c>
       <c r="J9" s="9">
-        <f>IFERROR(H9/I9,"")</f>
+        <f t="shared" si="1"/>
         <v>0.53609680506813773</v>
       </c>
       <c r="K9" s="9">
         <f>IFERROR(J9/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.8820006612842078E-2</v>
+        <v>2.6574391374273774E-2</v>
       </c>
       <c r="L9" s="12">
-        <f>F9/(1-(F9*(1+H9)-F9)/(F9*(1+H9)))</f>
+        <f t="shared" si="8"/>
         <v>227.4</v>
       </c>
       <c r="M9" s="12">
-        <f>F9/(1+I9-H9)</f>
+        <f t="shared" si="7"/>
+        <v>93.41592</v>
+      </c>
+      <c r="N9" s="12">
+        <f t="shared" si="2"/>
         <v>161.96043380326287</v>
       </c>
-      <c r="N9" s="12">
-        <f>L9-F9</f>
+      <c r="O9" s="12">
+        <f t="shared" si="3"/>
         <v>37.640000000000015</v>
       </c>
-      <c r="O9" s="12">
-        <f>0.5*(M9-F9)</f>
+      <c r="P9" s="12">
+        <f t="shared" si="4"/>
         <v>-13.899783098368559</v>
       </c>
-      <c r="P9" s="15">
-        <f>N9+O9</f>
+      <c r="Q9" s="15">
+        <f t="shared" si="5"/>
         <v>23.740216901631456</v>
       </c>
-      <c r="Q9" s="12">
-        <f>MAX($P$2:$P$280)-P9</f>
+      <c r="R9" s="12">
+        <f>MAX($Q$2:$Q$279)-Q9</f>
         <v>90.39222817955293</v>
       </c>
-      <c r="R9" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q9)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+      <c r="S9" s="9">
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R9)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>1.10628979962041E-2</v>
       </c>
-      <c r="S9" s="9">
-        <f>Q9/MAX($Q$2:$Q$28)</f>
+      <c r="T9" s="9">
+        <f t="shared" si="6"/>
         <v>0.6311275288415521</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -2570,7 +3092,7 @@
         <v>142.78</v>
       </c>
       <c r="G10" s="1">
-        <f>E10*F10</f>
+        <f t="shared" si="0"/>
         <v>50.187169999999995</v>
       </c>
       <c r="H10" s="11">
@@ -2580,47 +3102,51 @@
         <v>0.18340000000000001</v>
       </c>
       <c r="J10" s="9">
-        <f>IFERROR(H10/I10,"")</f>
+        <f t="shared" si="1"/>
         <v>0.38167938931297712</v>
       </c>
       <c r="K10" s="9">
         <f>IFERROR(J10/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.0518686961000319E-2</v>
+        <v>1.8919899121218792E-2</v>
       </c>
       <c r="L10" s="12">
-        <f>F10/(1-(F10*(1+H10)-F10)/(F10*(1+H10)))</f>
+        <f t="shared" si="8"/>
         <v>152.77460000000002</v>
       </c>
       <c r="M10" s="12">
-        <f>F10/(1+I10-H10)</f>
+        <f t="shared" si="7"/>
+        <v>53.700271900000004</v>
+      </c>
+      <c r="N10" s="12">
+        <f t="shared" si="2"/>
         <v>128.23783007005568</v>
       </c>
-      <c r="N10" s="12">
-        <f>L10-F10</f>
+      <c r="O10" s="12">
+        <f t="shared" si="3"/>
         <v>9.9946000000000197</v>
       </c>
-      <c r="O10" s="12">
-        <f>0.5*(M10-F10)</f>
+      <c r="P10" s="12">
+        <f t="shared" si="4"/>
         <v>-7.2710849649721609</v>
       </c>
-      <c r="P10" s="15">
-        <f>N10+O10</f>
+      <c r="Q10" s="15">
+        <f t="shared" si="5"/>
         <v>2.7235150350278587</v>
       </c>
-      <c r="Q10" s="12">
-        <f>MAX($P$2:$P$280)-P10</f>
+      <c r="R10" s="12">
+        <f>MAX($Q$2:$Q$279)-Q10</f>
         <v>111.40893004615653</v>
       </c>
-      <c r="R10" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q10)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+      <c r="S10" s="9">
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R10)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>8.9759411528833617E-3</v>
       </c>
-      <c r="S10" s="9">
-        <f>Q10/MAX($Q$2:$Q$28)</f>
+      <c r="T10" s="9">
+        <f t="shared" si="6"/>
         <v>0.77786823189316223</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>39</v>
       </c>
@@ -2640,7 +3166,7 @@
         <v>132.38999999999999</v>
       </c>
       <c r="G11" s="1">
-        <f>E11*F11</f>
+        <f t="shared" si="0"/>
         <v>33.984512999999993</v>
       </c>
       <c r="H11" s="11">
@@ -2650,47 +3176,51 @@
         <v>0.1623</v>
       </c>
       <c r="J11" s="9">
-        <f>IFERROR(H11/I11,"")</f>
+        <f t="shared" si="1"/>
         <v>0.43130006161429457</v>
       </c>
       <c r="K11" s="9">
         <f>IFERROR(J11/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.3186242690372512E-2</v>
+        <v>2.1379602580600905E-2</v>
       </c>
       <c r="L11" s="12">
-        <f>F11/(1-(F11*(1+H11)-F11)/(F11*(1+H11)))</f>
+        <f t="shared" si="8"/>
         <v>141.65729999999999</v>
       </c>
       <c r="M11" s="12">
-        <f>F11/(1+I11-H11)</f>
+        <f t="shared" si="7"/>
+        <v>36.363428909999996</v>
+      </c>
+      <c r="N11" s="12">
+        <f t="shared" si="2"/>
         <v>121.20296621807194</v>
       </c>
-      <c r="N11" s="12">
-        <f>L11-F11</f>
+      <c r="O11" s="12">
+        <f t="shared" si="3"/>
         <v>9.2673000000000059</v>
       </c>
-      <c r="O11" s="12">
-        <f>0.5*(M11-F11)</f>
+      <c r="P11" s="12">
+        <f t="shared" si="4"/>
         <v>-5.5935168909640254</v>
       </c>
-      <c r="P11" s="15">
-        <f>N11+O11</f>
+      <c r="Q11" s="15">
+        <f t="shared" si="5"/>
         <v>3.6737831090359805</v>
       </c>
-      <c r="Q11" s="12">
-        <f>MAX($P$2:$P$280)-P11</f>
+      <c r="R11" s="12">
+        <f>MAX($Q$2:$Q$279)-Q11</f>
         <v>110.45866197214841</v>
       </c>
-      <c r="R11" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q11)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+      <c r="S11" s="9">
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R11)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>9.0531605411999731E-3</v>
       </c>
-      <c r="S11" s="9">
-        <f>Q11/MAX($Q$2:$Q$28)</f>
+      <c r="T11" s="9">
+        <f t="shared" si="6"/>
         <v>0.77123336567330925</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -2704,14 +3234,14 @@
         <v>45511</v>
       </c>
       <c r="E12" s="2">
-        <v>0.1938</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F12" s="1">
         <v>283.43</v>
       </c>
       <c r="G12" s="1">
-        <f>E12*F12</f>
-        <v>54.928733999999999</v>
+        <f t="shared" si="0"/>
+        <v>2.8342999999999998E-17</v>
       </c>
       <c r="H12" s="11">
         <v>0.25</v>
@@ -2720,47 +3250,51 @@
         <v>0.26</v>
       </c>
       <c r="J12" s="9">
-        <f>IFERROR(H12/I12,"")</f>
+        <f t="shared" si="1"/>
         <v>0.96153846153846145</v>
       </c>
       <c r="K12" s="9">
         <f>IFERROR(J12/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>5.1691307536366179E-2</v>
+        <v>4.766359201691657E-2</v>
       </c>
       <c r="L12" s="12">
-        <f>F12/(1-(F12*(1+H12)-F12)/(F12*(1+H12)))</f>
+        <f t="shared" si="8"/>
         <v>354.28750000000002</v>
       </c>
       <c r="M12" s="12">
-        <f>F12/(1+I12-H12)</f>
+        <f t="shared" si="7"/>
+        <v>3.542875E-17</v>
+      </c>
+      <c r="N12" s="12">
+        <f t="shared" si="2"/>
         <v>280.62376237623761</v>
       </c>
-      <c r="N12" s="12">
-        <f>L12-F12</f>
+      <c r="O12" s="12">
+        <f t="shared" si="3"/>
         <v>70.857500000000016</v>
       </c>
-      <c r="O12" s="12">
-        <f>0.5*(M12-F12)</f>
+      <c r="P12" s="12">
+        <f t="shared" si="4"/>
         <v>-1.4031188118811997</v>
       </c>
-      <c r="P12" s="15">
-        <f>N12+O12</f>
+      <c r="Q12" s="15">
+        <f t="shared" si="5"/>
         <v>69.454381188118816</v>
       </c>
-      <c r="Q12" s="12">
-        <f>MAX($P$2:$P$280)-P12</f>
+      <c r="R12" s="12">
+        <f>MAX($Q$2:$Q$279)-Q12</f>
         <v>44.67806389306557</v>
       </c>
-      <c r="R12" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q12)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+      <c r="S12" s="9">
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R12)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>2.2382348581474875E-2</v>
       </c>
-      <c r="S12" s="9">
-        <f>Q12/MAX($Q$2:$Q$28)</f>
+      <c r="T12" s="9">
+        <f t="shared" si="6"/>
         <v>0.311946686414727</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -2780,7 +3314,7 @@
         <v>188.12</v>
       </c>
       <c r="G13" s="1">
-        <f>E13*F13</f>
+        <f t="shared" si="0"/>
         <v>1.8812000000000001E-17</v>
       </c>
       <c r="H13" s="11">
@@ -2790,47 +3324,51 @@
         <v>0.37780000000000002</v>
       </c>
       <c r="J13" s="9">
-        <f>IFERROR(H13/I13,"")</f>
+        <f t="shared" si="1"/>
         <v>0.39703546850185278</v>
       </c>
       <c r="K13" s="9">
         <f>IFERROR(J13/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.1344213805381481E-2</v>
+        <v>1.9681102050394347E-2</v>
       </c>
       <c r="L13" s="12">
-        <f>F13/(1-(F13*(1+H13)-F13)/(F13*(1+H13)))</f>
+        <f t="shared" si="8"/>
         <v>216.33799999999999</v>
       </c>
       <c r="M13" s="12">
-        <f>F13/(1+I13-H13)</f>
+        <f t="shared" si="7"/>
+        <v>2.16338E-17</v>
+      </c>
+      <c r="N13" s="12">
+        <f t="shared" si="2"/>
         <v>153.21713634142367</v>
       </c>
-      <c r="N13" s="12">
-        <f>L13-F13</f>
+      <c r="O13" s="12">
+        <f t="shared" si="3"/>
         <v>28.217999999999989</v>
       </c>
-      <c r="O13" s="12">
-        <f>0.5*(M13-F13)</f>
+      <c r="P13" s="12">
+        <f t="shared" si="4"/>
         <v>-17.451431829288168</v>
       </c>
-      <c r="P13" s="15">
-        <f>N13+O13</f>
+      <c r="Q13" s="15">
+        <f t="shared" si="5"/>
         <v>10.766568170711821</v>
       </c>
-      <c r="Q13" s="12">
-        <f>MAX($P$2:$P$280)-P13</f>
+      <c r="R13" s="12">
+        <f>MAX($Q$2:$Q$279)-Q13</f>
         <v>103.36587691047256</v>
       </c>
-      <c r="R13" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q13)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+      <c r="S13" s="9">
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R13)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>9.6743725288193673E-3</v>
       </c>
-      <c r="S13" s="9">
-        <f>Q13/MAX($Q$2:$Q$28)</f>
+      <c r="T13" s="9">
+        <f t="shared" si="6"/>
         <v>0.72171083482377829</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -2850,7 +3388,7 @@
         <v>135.82</v>
       </c>
       <c r="G14" s="1">
-        <f>E14*F14</f>
+        <f t="shared" si="0"/>
         <v>25.995947999999999</v>
       </c>
       <c r="H14" s="11">
@@ -2860,47 +3398,51 @@
         <v>0.33710000000000001</v>
       </c>
       <c r="J14" s="9">
-        <f>IFERROR(H14/I14,"")</f>
+        <f t="shared" si="1"/>
         <v>0.35657075051913378</v>
       </c>
       <c r="K14" s="9">
         <f>IFERROR(J14/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.9168872656499743E-2</v>
+        <v>1.7675260489026123E-2</v>
       </c>
       <c r="L14" s="12">
-        <f>F14/(1-(F14*(1+H14)-F14)/(F14*(1+H14)))</f>
+        <f t="shared" si="8"/>
         <v>152.14556400000001</v>
       </c>
       <c r="M14" s="12">
-        <f>F14/(1+I14-H14)</f>
+        <f t="shared" si="7"/>
+        <v>29.120660949599998</v>
+      </c>
+      <c r="N14" s="12">
+        <f t="shared" si="2"/>
         <v>111.61147177253677</v>
       </c>
-      <c r="N14" s="12">
-        <f>L14-F14</f>
+      <c r="O14" s="12">
+        <f t="shared" si="3"/>
         <v>16.325564000000014</v>
       </c>
-      <c r="O14" s="12">
-        <f>0.5*(M14-F14)</f>
+      <c r="P14" s="12">
+        <f t="shared" si="4"/>
         <v>-12.10426411373161</v>
       </c>
-      <c r="P14" s="15">
-        <f>N14+O14</f>
+      <c r="Q14" s="15">
+        <f t="shared" si="5"/>
         <v>4.2212998862684046</v>
       </c>
-      <c r="Q14" s="12">
-        <f>MAX($P$2:$P$280)-P14</f>
+      <c r="R14" s="12">
+        <f>MAX($Q$2:$Q$279)-Q14</f>
         <v>109.91114519491597</v>
       </c>
-      <c r="R14" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q14)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.0982583997883393E-3</v>
-      </c>
       <c r="S14" s="9">
-        <f>Q14/MAX($Q$2:$Q$28)</f>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R14)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>9.0982583997883375E-3</v>
+      </c>
+      <c r="T14" s="9">
+        <f t="shared" si="6"/>
         <v>0.76741054907089512</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -2920,7 +3462,7 @@
         <v>227.38</v>
       </c>
       <c r="G15" s="1">
-        <f>E15*F15</f>
+        <f t="shared" si="0"/>
         <v>42.792915999999998</v>
       </c>
       <c r="H15" s="11">
@@ -2930,47 +3472,51 @@
         <v>0.2271</v>
       </c>
       <c r="J15" s="9">
-        <f>IFERROR(H15/I15,"")</f>
+        <f t="shared" si="1"/>
         <v>0.66050198150594452</v>
       </c>
       <c r="K15" s="9">
         <f>IFERROR(J15/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.5507899496579148E-2</v>
+        <v>3.2741172851778889E-2</v>
       </c>
       <c r="L15" s="12">
-        <f>F15/(1-(F15*(1+H15)-F15)/(F15*(1+H15)))</f>
+        <f t="shared" si="8"/>
         <v>261.48699999999997</v>
       </c>
       <c r="M15" s="12">
-        <f>F15/(1+I15-H15)</f>
+        <f t="shared" si="7"/>
+        <v>49.211853399999995</v>
+      </c>
+      <c r="N15" s="12">
+        <f t="shared" si="2"/>
         <v>211.10389007520189</v>
       </c>
-      <c r="N15" s="12">
-        <f>L15-F15</f>
+      <c r="O15" s="12">
+        <f t="shared" si="3"/>
         <v>34.106999999999971</v>
       </c>
-      <c r="O15" s="12">
-        <f>0.5*(M15-F15)</f>
+      <c r="P15" s="12">
+        <f t="shared" si="4"/>
         <v>-8.1380549623990532</v>
       </c>
-      <c r="P15" s="15">
-        <f>N15+O15</f>
+      <c r="Q15" s="15">
+        <f t="shared" si="5"/>
         <v>25.968945037600918</v>
       </c>
-      <c r="Q15" s="12">
-        <f>MAX($P$2:$P$280)-P15</f>
+      <c r="R15" s="12">
+        <f>MAX($Q$2:$Q$279)-Q15</f>
         <v>88.163500043583468</v>
       </c>
-      <c r="R15" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q15)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+      <c r="S15" s="9">
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R15)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>1.1342562392664218E-2</v>
       </c>
-      <c r="S15" s="9">
-        <f>Q15/MAX($Q$2:$Q$28)</f>
+      <c r="T15" s="9">
+        <f t="shared" si="6"/>
         <v>0.6155663272953309</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -2990,7 +3536,7 @@
         <v>423.77</v>
       </c>
       <c r="G16" s="1">
-        <f>E16*F16</f>
+        <f t="shared" si="0"/>
         <v>56.658049000000005</v>
       </c>
       <c r="H16" s="11">
@@ -3000,47 +3546,51 @@
         <v>0.1963</v>
       </c>
       <c r="J16" s="9">
-        <f>IFERROR(H16/I16,"")</f>
+        <f t="shared" si="1"/>
         <v>0.76413652572592972</v>
       </c>
       <c r="K16" s="9">
         <f>IFERROR(J16/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.10791847971122E-2</v>
+        <v>3.7878351271721782E-2</v>
       </c>
       <c r="L16" s="12">
-        <f>F16/(1-(F16*(1+H16)-F16)/(F16*(1+H16)))</f>
+        <f t="shared" si="8"/>
         <v>487.33549999999991</v>
       </c>
       <c r="M16" s="12">
-        <f>F16/(1+I16-H16)</f>
+        <f t="shared" si="7"/>
+        <v>65.156756349999995</v>
+      </c>
+      <c r="N16" s="12">
+        <f t="shared" si="2"/>
         <v>405.01768135334032</v>
       </c>
-      <c r="N16" s="12">
-        <f>L16-F16</f>
+      <c r="O16" s="12">
+        <f t="shared" si="3"/>
         <v>63.565499999999929</v>
       </c>
-      <c r="O16" s="12">
-        <f>0.5*(M16-F16)</f>
+      <c r="P16" s="12">
+        <f t="shared" si="4"/>
         <v>-9.3761593233298299</v>
       </c>
-      <c r="P16" s="15">
-        <f>N16+O16</f>
+      <c r="Q16" s="15">
+        <f t="shared" si="5"/>
         <v>54.189340676670099</v>
       </c>
-      <c r="Q16" s="12">
-        <f>MAX($P$2:$P$280)-P16</f>
+      <c r="R16" s="12">
+        <f>MAX($Q$2:$Q$279)-Q16</f>
         <v>59.943104404514287</v>
       </c>
-      <c r="R16" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q16)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>1.6682485999585474E-2</v>
-      </c>
       <c r="S16" s="9">
-        <f>Q16/MAX($Q$2:$Q$28)</f>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R16)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>1.6682485999585477E-2</v>
+      </c>
+      <c r="T16" s="9">
+        <f t="shared" si="6"/>
         <v>0.41852871774290379</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -3060,7 +3610,7 @@
         <v>501.56</v>
       </c>
       <c r="G17" s="1">
-        <f>E17*F17</f>
+        <f t="shared" si="0"/>
         <v>64.901863999999989</v>
       </c>
       <c r="H17" s="11">
@@ -3070,47 +3620,51 @@
         <v>0.29699999999999999</v>
       </c>
       <c r="J17" s="9">
-        <f>IFERROR(H17/I17,"")</f>
+        <f t="shared" si="1"/>
         <v>0.84175084175084181</v>
       </c>
       <c r="K17" s="9">
         <f>IFERROR(J17/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.5251649695135378E-2</v>
+        <v>4.1725703449152558E-2</v>
       </c>
       <c r="L17" s="12">
-        <f>F17/(1-(F17*(1+H17)-F17)/(F17*(1+H17)))</f>
+        <f t="shared" si="8"/>
         <v>626.95000000000005</v>
       </c>
       <c r="M17" s="12">
-        <f>F17/(1+I17-H17)</f>
+        <f t="shared" si="7"/>
+        <v>81.127330000000001</v>
+      </c>
+      <c r="N17" s="12">
+        <f t="shared" si="2"/>
         <v>479.04489016236869</v>
       </c>
-      <c r="N17" s="12">
-        <f>L17-F17</f>
+      <c r="O17" s="12">
+        <f t="shared" si="3"/>
         <v>125.39000000000004</v>
       </c>
-      <c r="O17" s="12">
-        <f>0.5*(M17-F17)</f>
+      <c r="P17" s="12">
+        <f t="shared" si="4"/>
         <v>-11.257554918815657</v>
       </c>
-      <c r="P17" s="15">
-        <f>N17+O17</f>
+      <c r="Q17" s="15">
+        <f t="shared" si="5"/>
         <v>114.13244508118439</v>
       </c>
-      <c r="Q17" s="12">
-        <f>MAX($P$2:$P$280)-P17</f>
+      <c r="R17" s="12">
+        <f>MAX($Q$2:$Q$279)-Q17</f>
         <v>0</v>
       </c>
-      <c r="R17" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q17)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+      <c r="S17" s="9">
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R17)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>0</v>
       </c>
-      <c r="S17" s="9">
-        <f>Q17/MAX($Q$2:$Q$28)</f>
+      <c r="T17" s="9">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -3124,14 +3678,14 @@
         <v>45483</v>
       </c>
       <c r="E18" s="2">
-        <v>0.1195</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F18" s="1">
         <v>167.24</v>
       </c>
       <c r="G18" s="1">
-        <f>E18*F18</f>
-        <v>19.98518</v>
+        <f t="shared" si="0"/>
+        <v>1.6724000000000001E-17</v>
       </c>
       <c r="H18" s="11">
         <f>190.41/F18-1</f>
@@ -3141,47 +3695,51 @@
         <v>0.26790000000000003</v>
       </c>
       <c r="J18" s="9">
-        <f>IFERROR(H18/I18,"")</f>
+        <f t="shared" si="1"/>
         <v>0.51714598979956872</v>
       </c>
       <c r="K18" s="9">
         <f>IFERROR(J18/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.7801230495925113E-2</v>
+        <v>2.5634996889830789E-2</v>
       </c>
       <c r="L18" s="12">
-        <f>F18/(1-(F18*(1+H18)-F18)/(F18*(1+H18)))</f>
+        <f t="shared" si="8"/>
         <v>190.41</v>
       </c>
       <c r="M18" s="12">
-        <f>F18/(1+I18-H18)</f>
+        <f t="shared" si="7"/>
+        <v>1.9040999999999999E-17</v>
+      </c>
+      <c r="N18" s="12">
+        <f t="shared" si="2"/>
         <v>148.08431772538498</v>
       </c>
-      <c r="N18" s="12">
-        <f>L18-F18</f>
+      <c r="O18" s="12">
+        <f t="shared" si="3"/>
         <v>23.169999999999987</v>
       </c>
-      <c r="O18" s="12">
-        <f>0.5*(M18-F18)</f>
+      <c r="P18" s="12">
+        <f t="shared" si="4"/>
         <v>-9.5778411373075159</v>
       </c>
-      <c r="P18" s="15">
-        <f>N18+O18</f>
+      <c r="Q18" s="15">
+        <f t="shared" si="5"/>
         <v>13.592158862692472</v>
       </c>
-      <c r="Q18" s="12">
-        <f>MAX($P$2:$P$280)-P18</f>
+      <c r="R18" s="12">
+        <f>MAX($Q$2:$Q$279)-Q18</f>
         <v>100.54028621849191</v>
       </c>
-      <c r="R18" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q18)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+      <c r="S18" s="9">
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R18)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>9.9462617186788418E-3</v>
       </c>
-      <c r="S18" s="9">
-        <f>Q18/MAX($Q$2:$Q$28)</f>
+      <c r="T18" s="9">
+        <f t="shared" si="6"/>
         <v>0.70198227953907921</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -3195,64 +3753,68 @@
         <v>45511</v>
       </c>
       <c r="E19" s="2">
-        <v>0.158</v>
+        <v>0.25169999999999998</v>
       </c>
       <c r="F19" s="1">
-        <v>189.72</v>
+        <v>178.56</v>
       </c>
       <c r="G19" s="1">
-        <f>E19*F19</f>
-        <v>29.975760000000001</v>
+        <f t="shared" si="0"/>
+        <v>44.943551999999997</v>
       </c>
       <c r="H19" s="11">
         <f>196.02/F19-1</f>
-        <v>3.3206831119544589E-2</v>
+        <v>9.7782258064516236E-2</v>
       </c>
       <c r="I19" s="11">
         <v>0.52980000000000005</v>
       </c>
       <c r="J19" s="9">
-        <f>IFERROR(H19/I19,"")</f>
-        <v>6.2678050433266491E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.18456447350795815</v>
       </c>
       <c r="K19" s="9">
         <f>IFERROR(J19/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.3695067959548818E-3</v>
+        <v>9.1488859967443371E-3</v>
       </c>
       <c r="L19" s="12">
-        <f>F19/(1-(F19*(1+H19)-F19)/(F19*(1+H19)))</f>
+        <f t="shared" si="8"/>
         <v>196.02</v>
       </c>
       <c r="M19" s="12">
-        <f>F19/(1+I19-H19)</f>
-        <v>126.76791792516488</v>
+        <f t="shared" si="7"/>
+        <v>49.338234</v>
       </c>
       <c r="N19" s="12">
-        <f>L19-F19</f>
-        <v>6.3000000000000114</v>
+        <f t="shared" si="2"/>
+        <v>124.69119255370553</v>
       </c>
       <c r="O19" s="12">
-        <f>0.5*(M19-F19)</f>
-        <v>-31.476041037417559</v>
-      </c>
-      <c r="P19" s="15">
-        <f>N19+O19</f>
-        <v>-25.176041037417548</v>
-      </c>
-      <c r="Q19" s="12">
-        <f>MAX($P$2:$P$280)-P19</f>
-        <v>139.30848611860193</v>
-      </c>
-      <c r="R19" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q19)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>7.1783135964067412E-3</v>
+        <f t="shared" si="3"/>
+        <v>17.460000000000008</v>
+      </c>
+      <c r="P19" s="12">
+        <f t="shared" si="4"/>
+        <v>-26.934403723147234</v>
+      </c>
+      <c r="Q19" s="15">
+        <f t="shared" si="5"/>
+        <v>-9.4744037231472262</v>
+      </c>
+      <c r="R19" s="12">
+        <f>MAX($Q$2:$Q$279)-Q19</f>
+        <v>123.60684880433161</v>
       </c>
       <c r="S19" s="9">
-        <f>Q19/MAX($Q$2:$Q$28)</f>
-        <v>0.97266570767617244</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R19)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>8.0901666022000929E-3</v>
+      </c>
+      <c r="T19" s="9">
+        <f t="shared" si="6"/>
+        <v>0.86303531404059042</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>39</v>
       </c>
@@ -3272,7 +3834,7 @@
         <v>668.82</v>
       </c>
       <c r="G20" s="1">
-        <f>E20*F20</f>
+        <f t="shared" si="0"/>
         <v>6.6881999999999999E-17</v>
       </c>
       <c r="H20" s="11">
@@ -3282,47 +3844,51 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="J20" s="9">
-        <f>IFERROR(H20/I20,"")</f>
+        <f t="shared" si="1"/>
         <v>0.17857142857142858</v>
       </c>
       <c r="K20" s="9">
         <f>IFERROR(J20/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>9.5998142567537189E-3</v>
+        <v>8.8518099459987919E-3</v>
       </c>
       <c r="L20" s="12">
-        <f>F20/(1-(F20*(1+H20)-F20)/(F20*(1+H20)))</f>
+        <f t="shared" si="8"/>
         <v>702.26100000000008</v>
       </c>
       <c r="M20" s="12">
-        <f>F20/(1+I20-H20)</f>
+        <f t="shared" si="7"/>
+        <v>7.0226100000000009E-17</v>
+      </c>
+      <c r="N20" s="12">
+        <f t="shared" si="2"/>
         <v>543.7560975609756</v>
       </c>
-      <c r="N20" s="12">
-        <f>L20-F20</f>
+      <c r="O20" s="12">
+        <f t="shared" si="3"/>
         <v>33.441000000000031</v>
       </c>
-      <c r="O20" s="12">
-        <f>0.5*(M20-F20)</f>
+      <c r="P20" s="12">
+        <f t="shared" si="4"/>
         <v>-62.531951219512223</v>
       </c>
-      <c r="P20" s="15">
-        <f>N20+O20</f>
+      <c r="Q20" s="15">
+        <f t="shared" si="5"/>
         <v>-29.090951219512192</v>
       </c>
-      <c r="Q20" s="12">
-        <f>MAX($P$2:$P$280)-P20</f>
+      <c r="R20" s="12">
+        <f>MAX($Q$2:$Q$279)-Q20</f>
         <v>143.22339630069658</v>
       </c>
-      <c r="R20" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q20)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+      <c r="S20" s="9">
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R20)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>6.9820994741704532E-3</v>
       </c>
-      <c r="S20" s="9">
-        <f>Q20/MAX($Q$2:$Q$28)</f>
+      <c r="T20" s="9">
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -3342,7 +3908,7 @@
         <v>700.32</v>
       </c>
       <c r="G21" s="1">
-        <f>E21*F21</f>
+        <f t="shared" si="0"/>
         <v>7.0031999999999998E-17</v>
       </c>
       <c r="H21" s="11">
@@ -3352,47 +3918,51 @@
         <v>0.45340000000000003</v>
       </c>
       <c r="J21" s="9">
-        <f>IFERROR(H21/I21,"")</f>
+        <f t="shared" si="1"/>
         <v>0.22055580061755625</v>
       </c>
       <c r="K21" s="9">
         <f>IFERROR(J21/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.1856850427397625E-2</v>
+        <v>1.0932980965503582E-2</v>
       </c>
       <c r="L21" s="12">
-        <f>F21/(1-(F21*(1+H21)-F21)/(F21*(1+H21)))</f>
+        <f t="shared" si="8"/>
         <v>770.35200000000009</v>
       </c>
       <c r="M21" s="12">
-        <f>F21/(1+I21-H21)</f>
+        <f t="shared" si="7"/>
+        <v>7.7035200000000004E-17</v>
+      </c>
+      <c r="N21" s="12">
+        <f t="shared" si="2"/>
         <v>517.45234224915032</v>
       </c>
-      <c r="N21" s="12">
-        <f>L21-F21</f>
+      <c r="O21" s="12">
+        <f t="shared" si="3"/>
         <v>70.032000000000039</v>
       </c>
-      <c r="O21" s="12">
-        <f>0.5*(M21-F21)</f>
+      <c r="P21" s="12">
+        <f t="shared" si="4"/>
         <v>-91.433828875424865</v>
       </c>
-      <c r="P21" s="15">
-        <f>N21+O21</f>
+      <c r="Q21" s="15">
+        <f t="shared" si="5"/>
         <v>-21.401828875424826</v>
       </c>
-      <c r="Q21" s="12">
-        <f>MAX($P$2:$P$280)-P21</f>
+      <c r="R21" s="12">
+        <f>MAX($Q$2:$Q$279)-Q21</f>
         <v>135.53427395660921</v>
       </c>
-      <c r="R21" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q21)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+      <c r="S21" s="9">
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R21)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>7.3782075249847591E-3</v>
       </c>
-      <c r="S21" s="9">
-        <f>Q21/MAX($Q$2:$Q$28)</f>
+      <c r="T21" s="9">
+        <f t="shared" si="6"/>
         <v>0.94631378292451529</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -3412,7 +3982,7 @@
         <v>147.01</v>
       </c>
       <c r="G22" s="1">
-        <f>E22*F22</f>
+        <f t="shared" si="0"/>
         <v>1.4700999999999999E-17</v>
       </c>
       <c r="H22" s="11">
@@ -3422,47 +3992,51 @@
         <v>0.52380000000000004</v>
       </c>
       <c r="J22" s="9">
-        <f>IFERROR(H22/I22,"")</f>
+        <f t="shared" si="1"/>
         <v>0.28636884306987398</v>
       </c>
       <c r="K22" s="9">
         <f>IFERROR(J22/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.5394891133396571E-2</v>
+        <v>1.4195342410536434E-2</v>
       </c>
       <c r="L22" s="12">
-        <f>F22/(1-(F22*(1+H22)-F22)/(F22*(1+H22)))</f>
+        <f t="shared" si="8"/>
         <v>169.06149999999997</v>
       </c>
       <c r="M22" s="12">
-        <f>F22/(1+I22-H22)</f>
+        <f t="shared" si="7"/>
+        <v>1.6906149999999997E-17</v>
+      </c>
+      <c r="N22" s="12">
+        <f t="shared" si="2"/>
         <v>107.00975396709855</v>
       </c>
-      <c r="N22" s="12">
-        <f>L22-F22</f>
+      <c r="O22" s="12">
+        <f t="shared" si="3"/>
         <v>22.051499999999976</v>
       </c>
-      <c r="O22" s="12">
-        <f>0.5*(M22-F22)</f>
+      <c r="P22" s="12">
+        <f t="shared" si="4"/>
         <v>-20.000123016450722</v>
       </c>
-      <c r="P22" s="15">
-        <f>N22+O22</f>
+      <c r="Q22" s="15">
+        <f t="shared" si="5"/>
         <v>2.0513769835492539</v>
       </c>
-      <c r="Q22" s="12">
-        <f>MAX($P$2:$P$280)-P22</f>
+      <c r="R22" s="12">
+        <f>MAX($Q$2:$Q$279)-Q22</f>
         <v>112.08106809763513</v>
       </c>
-      <c r="R22" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q22)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+      <c r="S22" s="9">
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R22)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>8.9221134039237406E-3</v>
       </c>
-      <c r="S22" s="9">
-        <f>Q22/MAX($Q$2:$Q$28)</f>
+      <c r="T22" s="9">
+        <f t="shared" si="6"/>
         <v>0.78256116662896091</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>36</v>
       </c>
@@ -3482,7 +4056,7 @@
         <v>169.34</v>
       </c>
       <c r="G23" s="1">
-        <f>E23*F23</f>
+        <f t="shared" si="0"/>
         <v>1.6933999999999999E-17</v>
       </c>
       <c r="H23" s="11">
@@ -3492,47 +4066,51 @@
         <v>0.4259</v>
       </c>
       <c r="J23" s="9">
-        <f>IFERROR(H23/I23,"")</f>
+        <f t="shared" si="1"/>
         <v>0.23479690068091102</v>
       </c>
       <c r="K23" s="9">
         <f>IFERROR(J23/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.2622437153749902E-2</v>
+        <v>1.1638914228127082E-2</v>
       </c>
       <c r="L23" s="12">
-        <f>F23/(1-(F23*(1+H23)-F23)/(F23*(1+H23)))</f>
+        <f t="shared" si="8"/>
         <v>186.27400000000003</v>
       </c>
       <c r="M23" s="12">
-        <f>F23/(1+I23-H23)</f>
+        <f t="shared" si="7"/>
+        <v>1.8627400000000003E-17</v>
+      </c>
+      <c r="N23" s="12">
+        <f t="shared" si="2"/>
         <v>127.71702239987934</v>
       </c>
-      <c r="N23" s="12">
-        <f>L23-F23</f>
+      <c r="O23" s="12">
+        <f t="shared" si="3"/>
         <v>16.934000000000026</v>
       </c>
-      <c r="O23" s="12">
-        <f>0.5*(M23-F23)</f>
+      <c r="P23" s="12">
+        <f t="shared" si="4"/>
         <v>-20.811488800060332</v>
       </c>
-      <c r="P23" s="15">
-        <f>N23+O23</f>
+      <c r="Q23" s="15">
+        <f t="shared" si="5"/>
         <v>-3.8774888000603056</v>
       </c>
-      <c r="Q23" s="12">
-        <f>MAX($P$2:$P$280)-P23</f>
+      <c r="R23" s="12">
+        <f>MAX($Q$2:$Q$279)-Q23</f>
         <v>118.00993388124469</v>
       </c>
-      <c r="R23" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q23)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>8.4738628953585915E-3</v>
-      </c>
       <c r="S23" s="9">
-        <f>Q23/MAX($Q$2:$Q$28)</f>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R23)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>8.4738628953585898E-3</v>
+      </c>
+      <c r="T23" s="9">
+        <f t="shared" si="6"/>
         <v>0.82395709729912847</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -3552,7 +4130,7 @@
         <v>113.58</v>
       </c>
       <c r="G24" s="1">
-        <f>E24*F24</f>
+        <f t="shared" si="0"/>
         <v>1.1357999999999999E-17</v>
       </c>
       <c r="H24" s="11">
@@ -3563,47 +4141,51 @@
         <v>0.16439999999999999</v>
       </c>
       <c r="J24" s="9">
-        <f>IFERROR(H24/I24,"")</f>
+        <f t="shared" si="1"/>
         <v>0.40540789496797319</v>
       </c>
       <c r="K24" s="9">
         <f>IFERROR(J24/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.1794306743518756E-2</v>
+        <v>2.0096124366438057E-2</v>
       </c>
       <c r="L24" s="12">
-        <f>F24/(1-(F24*(1+H24)-F24)/(F24*(1+H24)))</f>
+        <f t="shared" si="8"/>
         <v>121.15000000000002</v>
       </c>
       <c r="M24" s="12">
-        <f>F24/(1+I24-H24)</f>
+        <f t="shared" si="7"/>
+        <v>1.2115000000000002E-17</v>
+      </c>
+      <c r="N24" s="12">
+        <f t="shared" si="2"/>
         <v>103.46609203186667</v>
       </c>
-      <c r="N24" s="12">
-        <f>L24-F24</f>
+      <c r="O24" s="12">
+        <f t="shared" si="3"/>
         <v>7.5700000000000216</v>
       </c>
-      <c r="O24" s="12">
-        <f>0.5*(M24-F24)</f>
+      <c r="P24" s="12">
+        <f t="shared" si="4"/>
         <v>-5.0569539840666664</v>
       </c>
-      <c r="P24" s="15">
-        <f>N24+O24</f>
+      <c r="Q24" s="15">
+        <f t="shared" si="5"/>
         <v>2.5130460159333552</v>
       </c>
-      <c r="Q24" s="12">
-        <f>MAX($P$2:$P$280)-P24</f>
+      <c r="R24" s="12">
+        <f>MAX($Q$2:$Q$279)-Q24</f>
         <v>111.61939906525103</v>
       </c>
-      <c r="R24" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q24)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>8.9590161600441431E-3</v>
-      </c>
       <c r="S24" s="9">
-        <f>Q24/MAX($Q$2:$Q$28)</f>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R24)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>8.9590161600441413E-3</v>
+      </c>
+      <c r="T24" s="9">
+        <f t="shared" si="6"/>
         <v>0.77933774752071117</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>36</v>
       </c>
@@ -3623,7 +4205,7 @@
         <v>64.349999999999994</v>
       </c>
       <c r="G25" s="1">
-        <f>E25*F25</f>
+        <f t="shared" si="0"/>
         <v>6.4349999999999993E-18</v>
       </c>
       <c r="H25" s="11">
@@ -3633,47 +4215,51 @@
         <v>0.67300000000000004</v>
       </c>
       <c r="J25" s="9">
-        <f>IFERROR(H25/I25,"")</f>
+        <f t="shared" si="1"/>
         <v>0.22288261515601782</v>
       </c>
       <c r="K25" s="9">
         <f>IFERROR(J25/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.1981937556720838E-2</v>
+        <v>1.1048321477918253E-2</v>
       </c>
       <c r="L25" s="12">
-        <f>F25/(1-(F25*(1+H25)-F25)/(F25*(1+H25)))</f>
+        <f t="shared" si="8"/>
         <v>74.002499999999984</v>
       </c>
       <c r="M25" s="12">
-        <f>F25/(1+I25-H25)</f>
+        <f t="shared" si="7"/>
+        <v>7.4002499999999988E-18</v>
+      </c>
+      <c r="N25" s="12">
+        <f t="shared" si="2"/>
         <v>42.252133946158892</v>
       </c>
-      <c r="N25" s="12">
-        <f>L25-F25</f>
+      <c r="O25" s="12">
+        <f t="shared" si="3"/>
         <v>9.6524999999999892</v>
       </c>
-      <c r="O25" s="12">
-        <f>0.5*(M25-F25)</f>
+      <c r="P25" s="12">
+        <f t="shared" si="4"/>
         <v>-11.048933026920551</v>
       </c>
-      <c r="P25" s="15">
-        <f>N25+O25</f>
+      <c r="Q25" s="15">
+        <f t="shared" si="5"/>
         <v>-1.3964330269205618</v>
       </c>
-      <c r="Q25" s="12">
-        <f>MAX($P$2:$P$280)-P25</f>
+      <c r="R25" s="12">
+        <f>MAX($Q$2:$Q$279)-Q25</f>
         <v>115.52887810810495</v>
       </c>
-      <c r="R25" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q25)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+      <c r="S25" s="9">
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R25)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>8.6558444639638962E-3</v>
       </c>
-      <c r="S25" s="9">
-        <f>Q25/MAX($Q$2:$Q$28)</f>
+      <c r="T25" s="9">
+        <f t="shared" si="6"/>
         <v>0.80663411909010196</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>40</v>
       </c>
@@ -3693,7 +4279,7 @@
         <v>20.82</v>
       </c>
       <c r="G26" s="1">
-        <f>E26*F26</f>
+        <f t="shared" si="0"/>
         <v>2.0820000000000002E-18</v>
       </c>
       <c r="H26" s="13">
@@ -3703,47 +4289,51 @@
         <v>0.7389</v>
       </c>
       <c r="J26" s="9">
-        <f>IFERROR(H26/I26,"")</f>
+        <f t="shared" si="1"/>
         <v>6.7668155366084726E-2</v>
       </c>
       <c r="K26" s="9">
         <f>IFERROR(J26/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.6377696466247688E-3</v>
+        <v>3.3543196439026418E-3</v>
       </c>
       <c r="L26" s="12">
-        <f>F26/(1-(F26*(1+H26)-F26)/(F26*(1+H26)))</f>
+        <f t="shared" si="8"/>
         <v>21.861000000000001</v>
       </c>
       <c r="M26" s="12">
-        <f>F26/(1+I26-H26)</f>
+        <f t="shared" si="7"/>
+        <v>2.1860999999999999E-18</v>
+      </c>
+      <c r="N26" s="12">
+        <f t="shared" si="2"/>
         <v>12.327550476641601</v>
       </c>
-      <c r="N26" s="12">
-        <f>L26-F26</f>
+      <c r="O26" s="12">
+        <f t="shared" si="3"/>
         <v>1.0410000000000004</v>
       </c>
-      <c r="O26" s="12">
-        <f>0.5*(M26-F26)</f>
+      <c r="P26" s="12">
+        <f t="shared" si="4"/>
         <v>-4.2462247616791995</v>
       </c>
-      <c r="P26" s="15">
-        <f>N26+O26</f>
+      <c r="Q26" s="15">
+        <f t="shared" si="5"/>
         <v>-3.2052247616791991</v>
       </c>
-      <c r="Q26" s="12">
-        <f>MAX($P$2:$P$280)-P26</f>
+      <c r="R26" s="12">
+        <f>MAX($Q$2:$Q$279)-Q26</f>
         <v>117.33766984286359</v>
       </c>
-      <c r="R26" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q26)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>8.5224122938454584E-3</v>
-      </c>
       <c r="S26" s="9">
-        <f>Q26/MAX($Q$2:$Q$28)</f>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R26)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>8.5224122938454567E-3</v>
+      </c>
+      <c r="T26" s="9">
+        <f t="shared" si="6"/>
         <v>0.81926328291024408</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -3763,7 +4353,7 @@
         <v>13.04</v>
       </c>
       <c r="G27" s="1">
-        <f>E27*F27</f>
+        <f t="shared" si="0"/>
         <v>1.304E-18</v>
       </c>
       <c r="H27" s="11">
@@ -3774,47 +4364,51 @@
         <v>0.30159999999999998</v>
       </c>
       <c r="J27" s="9">
-        <f>IFERROR(H27/I27,"")</f>
+        <f t="shared" si="1"/>
         <v>0.17290198694895167</v>
       </c>
       <c r="K27" s="9">
         <f>IFERROR(J27/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>9.2950309722681142E-3</v>
+        <v>8.5707749554430283E-3</v>
       </c>
       <c r="L27" s="12">
-        <f>F27/(1-(F27*(1+H27)-F27)/(F27*(1+H27)))</f>
+        <f t="shared" si="8"/>
         <v>13.72</v>
       </c>
       <c r="M27" s="12">
-        <f>F27/(1+I27-H27)</f>
+        <f t="shared" si="7"/>
+        <v>1.3720000000000001E-18</v>
+      </c>
+      <c r="N27" s="12">
+        <f t="shared" si="2"/>
         <v>10.436569040286594</v>
       </c>
-      <c r="N27" s="12">
-        <f>L27-F27</f>
+      <c r="O27" s="12">
+        <f t="shared" si="3"/>
         <v>0.68000000000000149</v>
       </c>
-      <c r="O27" s="12">
-        <f>0.5*(M27-F27)</f>
+      <c r="P27" s="12">
+        <f t="shared" si="4"/>
         <v>-1.3017154798567026</v>
       </c>
-      <c r="P27" s="15">
-        <f>N27+O27</f>
+      <c r="Q27" s="15">
+        <f t="shared" si="5"/>
         <v>-0.62171547985670106</v>
       </c>
-      <c r="Q27" s="12">
-        <f>MAX($P$2:$P$280)-P27</f>
+      <c r="R27" s="12">
+        <f>MAX($Q$2:$Q$279)-Q27</f>
         <v>114.75416056104109</v>
       </c>
-      <c r="R27" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q27)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+      <c r="S27" s="9">
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R27)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>8.7142809908671744E-3</v>
       </c>
-      <c r="S27" s="9">
-        <f>Q27/MAX($Q$2:$Q$28)</f>
+      <c r="T27" s="9">
+        <f t="shared" si="6"/>
         <v>0.80122496411211674</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -3834,7 +4428,7 @@
         <v>11.05</v>
       </c>
       <c r="G28" s="1">
-        <f>E28*F28</f>
+        <f t="shared" si="0"/>
         <v>1.1050000000000001E-18</v>
       </c>
       <c r="H28" s="11">
@@ -3844,47 +4438,51 @@
         <v>0.72170000000000001</v>
       </c>
       <c r="J28" s="9">
-        <f>IFERROR(H28/I28,"")</f>
+        <f t="shared" si="1"/>
         <v>6.9280864625190522E-2</v>
       </c>
       <c r="K28" s="9">
         <f>IFERROR(J28/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.7244672189151191E-3</v>
+        <v>3.434261860717281E-3</v>
       </c>
       <c r="L28" s="12">
-        <f>F28/(1-(F28*(1+H28)-F28)/(F28*(1+H28)))</f>
+        <f t="shared" si="8"/>
         <v>11.602500000000001</v>
       </c>
       <c r="M28" s="12">
-        <f>F28/(1+I28-H28)</f>
+        <f t="shared" si="7"/>
+        <v>1.16025E-18</v>
+      </c>
+      <c r="N28" s="12">
+        <f t="shared" si="2"/>
         <v>6.6100376861877139</v>
       </c>
-      <c r="N28" s="12">
-        <f>L28-F28</f>
+      <c r="O28" s="12">
+        <f t="shared" si="3"/>
         <v>0.55250000000000021</v>
       </c>
-      <c r="O28" s="12">
-        <f>0.5*(M28-F28)</f>
+      <c r="P28" s="12">
+        <f t="shared" si="4"/>
         <v>-2.2199811569061434</v>
       </c>
-      <c r="P28" s="15">
-        <f>N28+O28</f>
+      <c r="Q28" s="15">
+        <f t="shared" si="5"/>
         <v>-1.6674811569061432</v>
       </c>
-      <c r="Q28" s="12">
-        <f>MAX($P$2:$P$280)-P28</f>
+      <c r="R28" s="12">
+        <f>MAX($Q$2:$Q$279)-Q28</f>
         <v>115.79992623809053</v>
       </c>
-      <c r="R28" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q28)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+      <c r="S28" s="9">
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R28)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>8.6355840844315329E-3</v>
       </c>
-      <c r="S28" s="9">
-        <f>Q28/MAX($Q$2:$Q$28)</f>
+      <c r="T28" s="9">
+        <f t="shared" si="6"/>
         <v>0.80852660409594923</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>74</v>
       </c>
@@ -3896,7 +4494,7 @@
       </c>
       <c r="D29" s="8">
         <f ca="1">TODAY()-20</f>
-        <v>45665</v>
+        <v>45666</v>
       </c>
       <c r="E29" s="2">
         <v>9.9999999999999998E-20</v>
@@ -3905,7 +4503,7 @@
         <v>2742.9</v>
       </c>
       <c r="G29" s="1">
-        <f>E29*F29</f>
+        <f t="shared" si="0"/>
         <v>2.7429000000000002E-16</v>
       </c>
       <c r="H29" s="11">
@@ -3915,47 +4513,51 @@
         <v>0.5</v>
       </c>
       <c r="J29" s="9">
-        <f>IFERROR(H29/I29,"")</f>
+        <f t="shared" si="1"/>
         <v>0.2</v>
       </c>
       <c r="K29" s="9">
         <f>IFERROR(J29/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.0751791967564166E-2</v>
+        <v>9.9140271395186472E-3</v>
       </c>
       <c r="L29" s="12">
-        <f>F29/(1-(F29*(1+H29)-F29)/(F29*(1+H29)))</f>
+        <f t="shared" si="8"/>
         <v>3017.1900000000005</v>
       </c>
       <c r="M29" s="12">
-        <f>F29/(1+I29-H29)</f>
+        <f t="shared" si="7"/>
+        <v>3.0171900000000003E-16</v>
+      </c>
+      <c r="N29" s="12">
+        <f t="shared" si="2"/>
         <v>1959.214285714286</v>
       </c>
-      <c r="N29" s="12">
-        <f>L29-F29</f>
+      <c r="O29" s="12">
+        <f t="shared" si="3"/>
         <v>274.29000000000042</v>
       </c>
-      <c r="O29" s="12">
-        <f>0.5*(M29-F29)</f>
+      <c r="P29" s="12">
+        <f t="shared" si="4"/>
         <v>-391.84285714285704</v>
       </c>
-      <c r="P29" s="15">
-        <f>N29+O29</f>
+      <c r="Q29" s="15">
+        <f t="shared" si="5"/>
         <v>-117.55285714285662</v>
       </c>
-      <c r="Q29" s="12">
-        <f>MAX($P$2:$P$280)-P29</f>
+      <c r="R29" s="12">
+        <f>MAX($Q$2:$Q$279)-Q29</f>
         <v>231.68530222404101</v>
       </c>
-      <c r="R29" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q29)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+      <c r="S29" s="9">
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R29)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>4.316199562080957E-3</v>
       </c>
-      <c r="S29" s="9">
-        <f>Q29/MAX($Q$2:$Q$28)</f>
+      <c r="T29" s="9">
+        <f t="shared" si="6"/>
         <v>1.6176498268314992</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -3975,7 +4577,7 @@
         <v>86.6</v>
       </c>
       <c r="G30" s="1">
-        <f>E30*F30</f>
+        <f t="shared" si="0"/>
         <v>8.6599999999999986E-18</v>
       </c>
       <c r="H30" s="11">
@@ -3985,47 +4587,51 @@
         <v>0.17249999999999999</v>
       </c>
       <c r="J30" s="9">
-        <f>IFERROR(H30/I30,"")</f>
+        <f t="shared" si="1"/>
         <v>0.40579710144927544</v>
       </c>
       <c r="K30" s="9">
         <f>IFERROR(J30/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.1815230079115702E-2</v>
+        <v>2.0115417384530591E-2</v>
       </c>
       <c r="L30" s="12">
-        <f>F30/(1-(F30*(1+H30)-F30)/(F30*(1+H30)))</f>
+        <f t="shared" si="8"/>
         <v>92.662000000000006</v>
       </c>
       <c r="M30" s="12">
-        <f>F30/(1+I30-H30)</f>
+        <f t="shared" si="7"/>
+        <v>9.2662000000000008E-18</v>
+      </c>
+      <c r="N30" s="12">
+        <f t="shared" si="2"/>
         <v>78.548752834467123</v>
       </c>
-      <c r="N30" s="12">
-        <f>L30-F30</f>
+      <c r="O30" s="12">
+        <f t="shared" si="3"/>
         <v>6.0620000000000118</v>
       </c>
-      <c r="O30" s="12">
-        <f>0.5*(M30-F30)</f>
+      <c r="P30" s="12">
+        <f t="shared" si="4"/>
         <v>-4.0256235827664355</v>
       </c>
-      <c r="P30" s="15">
-        <f>N30+O30</f>
+      <c r="Q30" s="15">
+        <f t="shared" si="5"/>
         <v>2.0363764172335763</v>
       </c>
-      <c r="Q30" s="12">
-        <f>MAX($P$2:$P$280)-P30</f>
+      <c r="R30" s="12">
+        <f>MAX($Q$2:$Q$279)-Q30</f>
         <v>112.0960686639508</v>
       </c>
-      <c r="R30" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q30)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>8.9209194570227766E-3</v>
-      </c>
       <c r="S30" s="9">
-        <f>Q30/MAX($Q$2:$Q$28)</f>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R30)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>8.9209194570227784E-3</v>
+      </c>
+      <c r="T30" s="9">
+        <f t="shared" si="6"/>
         <v>0.78266590207514586</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>71</v>
       </c>
@@ -4045,7 +4651,7 @@
         <v>56</v>
       </c>
       <c r="G31" s="1">
-        <f>E31*F31</f>
+        <f t="shared" si="0"/>
         <v>5.5999999999999995E-18</v>
       </c>
       <c r="H31" s="11">
@@ -4055,47 +4661,51 @@
         <v>0.19</v>
       </c>
       <c r="J31" s="9">
-        <f>IFERROR(H31/I31,"")</f>
+        <f t="shared" si="1"/>
         <v>0.36842105263157898</v>
       </c>
       <c r="K31" s="9">
         <f>IFERROR(J31/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.9805932571828729E-2</v>
+        <v>1.826268157279751E-2</v>
       </c>
       <c r="L31" s="12">
-        <f>F31/(1-(F31*(1+H31)-F31)/(F31*(1+H31)))</f>
+        <f t="shared" si="8"/>
         <v>59.92</v>
       </c>
       <c r="M31" s="12">
-        <f>F31/(1+I31-H31)</f>
+        <f t="shared" si="7"/>
+        <v>5.9920000000000002E-18</v>
+      </c>
+      <c r="N31" s="12">
+        <f t="shared" si="2"/>
         <v>50.000000000000007</v>
       </c>
-      <c r="N31" s="12">
-        <f>L31-F31</f>
+      <c r="O31" s="12">
+        <f t="shared" si="3"/>
         <v>3.9200000000000017</v>
       </c>
-      <c r="O31" s="12">
-        <f>0.5*(M31-F31)</f>
+      <c r="P31" s="12">
+        <f t="shared" si="4"/>
         <v>-2.9999999999999964</v>
       </c>
-      <c r="P31" s="15">
-        <f>N31+O31</f>
+      <c r="Q31" s="15">
+        <f t="shared" si="5"/>
         <v>0.92000000000000526</v>
       </c>
-      <c r="Q31" s="12">
-        <f>MAX($P$2:$P$280)-P31</f>
+      <c r="R31" s="12">
+        <f>MAX($Q$2:$Q$279)-Q31</f>
         <v>113.21244508118438</v>
       </c>
-      <c r="R31" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q31)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+      <c r="S31" s="9">
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R31)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>8.832951176727102E-3</v>
       </c>
-      <c r="S31" s="9">
-        <f>Q31/MAX($Q$2:$Q$28)</f>
+      <c r="T31" s="9">
+        <f t="shared" si="6"/>
         <v>0.79046055327088882</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>74</v>
       </c>
@@ -4115,7 +4725,7 @@
         <v>20.399999999999999</v>
       </c>
       <c r="G32" s="1">
-        <f>E32*F32</f>
+        <f t="shared" si="0"/>
         <v>2.0399999999999999E-18</v>
       </c>
       <c r="H32" s="11">
@@ -4125,46 +4735,50 @@
         <v>0.15</v>
       </c>
       <c r="J32" s="9">
-        <f>IFERROR(H32/I32,"")</f>
+        <f t="shared" si="1"/>
         <v>0.66666666666666674</v>
       </c>
       <c r="K32" s="9">
         <f>IFERROR(J32/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.5839306558547224E-2</v>
+        <v>3.3046757131728825E-2</v>
       </c>
       <c r="L32" s="12">
         <v>21.2</v>
       </c>
       <c r="M32" s="12">
-        <f>F32/(1+I32-H32)</f>
+        <f t="shared" si="7"/>
+        <v>2.1199999999999999E-18</v>
+      </c>
+      <c r="N32" s="12">
+        <f t="shared" si="2"/>
         <v>19.428571428571431</v>
       </c>
-      <c r="N32" s="12">
-        <f>L32-F32</f>
+      <c r="O32" s="12">
+        <f t="shared" si="3"/>
         <v>0.80000000000000071</v>
       </c>
-      <c r="O32" s="12">
-        <f>0.5*(M32-F32)</f>
+      <c r="P32" s="12">
+        <f t="shared" si="4"/>
         <v>-0.48571428571428399</v>
       </c>
-      <c r="P32" s="15">
-        <f>N32+O32</f>
+      <c r="Q32" s="15">
+        <f t="shared" si="5"/>
         <v>0.31428571428571672</v>
       </c>
-      <c r="Q32" s="12">
-        <f>MAX($P$2:$P$280)-P32</f>
+      <c r="R32" s="12">
+        <f>MAX($Q$2:$Q$279)-Q32</f>
         <v>113.81815936689867</v>
       </c>
-      <c r="R32" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q32)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>8.7859442250902055E-3</v>
-      </c>
       <c r="S32" s="9">
-        <f>Q32/MAX($Q$2:$Q$28)</f>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R32)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>8.7859442250902038E-3</v>
+      </c>
+      <c r="T32" s="9">
+        <f t="shared" si="6"/>
         <v>0.79468971066667204</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>39</v>
       </c>
@@ -4184,7 +4798,7 @@
         <v>47.42</v>
       </c>
       <c r="G33" s="1">
-        <f>E33*F33</f>
+        <f t="shared" si="0"/>
         <v>4.7419999999999999E-18</v>
       </c>
       <c r="H33" s="11">
@@ -4194,47 +4808,51 @@
         <v>0.4</v>
       </c>
       <c r="J33" s="9">
-        <f>IFERROR(H33/I33,"")</f>
+        <f t="shared" si="1"/>
         <v>0.17500000000000002</v>
       </c>
       <c r="K33" s="9">
         <f>IFERROR(J33/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>9.4078179716186455E-3</v>
+        <v>8.6747737470788174E-3</v>
       </c>
       <c r="L33" s="12">
-        <f>F33/(1-(F33*(1+H33)-F33)/(F33*(1+H33)))</f>
+        <f t="shared" ref="L33:L41" si="9">F33/(1-(F33*(1+H33)-F33)/(F33*(1+H33)))</f>
         <v>50.739400000000003</v>
       </c>
       <c r="M33" s="12">
-        <f>F33/(1+I33-H33)</f>
+        <f t="shared" si="7"/>
+        <v>5.0739400000000001E-18</v>
+      </c>
+      <c r="N33" s="12">
+        <f t="shared" si="2"/>
         <v>35.654135338345867</v>
       </c>
-      <c r="N33" s="12">
-        <f>L33-F33</f>
+      <c r="O33" s="12">
+        <f t="shared" si="3"/>
         <v>3.3194000000000017</v>
       </c>
-      <c r="O33" s="12">
-        <f>0.5*(M33-F33)</f>
+      <c r="P33" s="12">
+        <f t="shared" si="4"/>
         <v>-5.8829323308270673</v>
       </c>
-      <c r="P33" s="15">
-        <f>N33+O33</f>
+      <c r="Q33" s="15">
+        <f t="shared" si="5"/>
         <v>-2.5635323308270657</v>
       </c>
-      <c r="Q33" s="12">
-        <f>MAX($P$2:$P$280)-P33</f>
+      <c r="R33" s="12">
+        <f>MAX($Q$2:$Q$279)-Q33</f>
         <v>116.69597741201144</v>
       </c>
-      <c r="R33" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q33)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+      <c r="S33" s="9">
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R33)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>8.5692756697976005E-3</v>
       </c>
-      <c r="S33" s="9">
-        <f>Q33/MAX($Q$2:$Q$28)</f>
+      <c r="T33" s="9">
+        <f t="shared" si="6"/>
         <v>0.81478292252621221</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>39</v>
       </c>
@@ -4254,7 +4872,7 @@
         <v>41.8</v>
       </c>
       <c r="G34" s="1">
-        <f>E34*F34</f>
+        <f t="shared" si="0"/>
         <v>4.1799999999999993E-18</v>
       </c>
       <c r="H34" s="11">
@@ -4264,47 +4882,51 @@
         <v>0.4</v>
       </c>
       <c r="J34" s="9">
-        <f>IFERROR(H34/I34,"")</f>
+        <f t="shared" si="1"/>
         <v>0.17500000000000002</v>
       </c>
       <c r="K34" s="9">
         <f>IFERROR(J34/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>9.4078179716186455E-3</v>
+        <v>8.6747737470788174E-3</v>
       </c>
       <c r="L34" s="12">
-        <f>F34/(1-(F34*(1+H34)-F34)/(F34*(1+H34)))</f>
+        <f t="shared" si="9"/>
         <v>44.725999999999999</v>
       </c>
       <c r="M34" s="12">
-        <f>F34/(1+I34-H34)</f>
+        <f t="shared" si="7"/>
+        <v>4.4725999999999996E-18</v>
+      </c>
+      <c r="N34" s="12">
+        <f t="shared" si="2"/>
         <v>31.428571428571431</v>
       </c>
-      <c r="N34" s="12">
-        <f>L34-F34</f>
+      <c r="O34" s="12">
+        <f t="shared" si="3"/>
         <v>2.9260000000000019</v>
       </c>
-      <c r="O34" s="12">
-        <f>0.5*(M34-F34)</f>
+      <c r="P34" s="12">
+        <f t="shared" si="4"/>
         <v>-5.1857142857142833</v>
       </c>
-      <c r="P34" s="15">
-        <f>N34+O34</f>
+      <c r="Q34" s="15">
+        <f t="shared" si="5"/>
         <v>-2.2597142857142813</v>
       </c>
-      <c r="Q34" s="12">
-        <f>MAX($P$2:$P$280)-P34</f>
+      <c r="R34" s="12">
+        <f>MAX($Q$2:$Q$279)-Q34</f>
         <v>116.39215936689867</v>
       </c>
-      <c r="R34" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q34)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+      <c r="S34" s="9">
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R34)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>8.5916440200042785E-3</v>
       </c>
-      <c r="S34" s="9">
-        <f>Q34/MAX($Q$2:$Q$28)</f>
+      <c r="T34" s="9">
+        <f t="shared" si="6"/>
         <v>0.81266163471318675</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>74</v>
       </c>
@@ -4324,7 +4946,7 @@
         <v>153.7552</v>
       </c>
       <c r="G35" s="1">
-        <f>E35*F35</f>
+        <f t="shared" si="0"/>
         <v>1.5375519999999999E-17</v>
       </c>
       <c r="H35" s="11">
@@ -4334,54 +4956,58 @@
         <v>0.19</v>
       </c>
       <c r="J35" s="9">
-        <f>IFERROR(H35/I35,"")</f>
+        <f t="shared" si="1"/>
         <v>0.36842105263157898</v>
       </c>
       <c r="K35" s="9">
         <f>IFERROR(J35/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.9805932571828729E-2</v>
+        <v>1.826268157279751E-2</v>
       </c>
       <c r="L35" s="12">
-        <f>F35/(1-(F35*(1+H35)-F35)/(F35*(1+H35)))</f>
+        <f t="shared" si="9"/>
         <v>164.51806400000001</v>
       </c>
       <c r="M35" s="12">
-        <f>F35/(1+I35-H35)</f>
+        <f t="shared" si="7"/>
+        <v>1.6451806399999999E-17</v>
+      </c>
+      <c r="N35" s="12">
+        <f t="shared" si="2"/>
         <v>137.28142857142859</v>
       </c>
-      <c r="N35" s="12">
-        <f>L35-F35</f>
+      <c r="O35" s="12">
+        <f t="shared" si="3"/>
         <v>10.762864000000008</v>
       </c>
-      <c r="O35" s="12">
-        <f>0.5*(M35-F35)</f>
+      <c r="P35" s="12">
+        <f t="shared" si="4"/>
         <v>-8.2368857142857053</v>
       </c>
-      <c r="P35" s="15">
-        <f>N35+O35</f>
+      <c r="Q35" s="15">
+        <f t="shared" si="5"/>
         <v>2.5259782857143023</v>
       </c>
-      <c r="Q35" s="12">
-        <f>MAX($P$2:$P$280)-P35</f>
+      <c r="R35" s="12">
+        <f>MAX($Q$2:$Q$279)-Q35</f>
         <v>111.60646679547008</v>
       </c>
-      <c r="R35" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q35)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>8.9600542756415637E-3</v>
-      </c>
       <c r="S35" s="9">
-        <f>Q35/MAX($Q$2:$Q$28)</f>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R35)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>8.9600542756415654E-3</v>
+      </c>
+      <c r="T35" s="9">
+        <f t="shared" si="6"/>
         <v>0.77924745312667376</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>87</v>
       </c>
       <c r="B36" t="s">
         <v>88</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="32" t="s">
         <v>89</v>
       </c>
       <c r="D36" s="8">
@@ -4394,7 +5020,7 @@
         <v>133.53</v>
       </c>
       <c r="G36" s="1">
-        <f>E36*F36</f>
+        <f t="shared" si="0"/>
         <v>1.3353E-17</v>
       </c>
       <c r="H36" s="11">
@@ -4404,68 +5030,72 @@
         <v>0.2</v>
       </c>
       <c r="J36" s="9">
-        <f>IFERROR(H36/I36,"")</f>
+        <f t="shared" si="1"/>
         <v>0.35000000000000003</v>
       </c>
       <c r="K36" s="9">
         <f>IFERROR(J36/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.8815635943237291E-2</v>
+        <v>1.7349547494157635E-2</v>
       </c>
       <c r="L36" s="12">
-        <f>F36/(1-(F36*(1+H36)-F36)/(F36*(1+H36)))</f>
+        <f t="shared" si="9"/>
         <v>142.87710000000001</v>
       </c>
       <c r="M36" s="12">
-        <f>F36/(1+I36-H36)</f>
+        <f t="shared" si="7"/>
+        <v>1.428771E-17</v>
+      </c>
+      <c r="N36" s="12">
+        <f t="shared" si="2"/>
         <v>118.16814159292036</v>
       </c>
-      <c r="N36" s="12">
-        <f>L36-F36</f>
+      <c r="O36" s="12">
+        <f t="shared" si="3"/>
         <v>9.3471000000000117</v>
       </c>
-      <c r="O36" s="12">
-        <f>0.5*(M36-F36)</f>
+      <c r="P36" s="12">
+        <f t="shared" si="4"/>
         <v>-7.6809292035398187</v>
       </c>
-      <c r="P36" s="15">
-        <f>N36+O36</f>
+      <c r="Q36" s="15">
+        <f t="shared" si="5"/>
         <v>1.6661707964601931</v>
       </c>
-      <c r="Q36" s="12">
-        <f>MAX($P$2:$P$280)-P36</f>
+      <c r="R36" s="12">
+        <f>MAX($Q$2:$Q$279)-Q36</f>
         <v>112.46627428472419</v>
       </c>
-      <c r="R36" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q36)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+      <c r="S36" s="9">
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R36)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>8.8915544358512261E-3</v>
       </c>
-      <c r="S36" s="9">
-        <f>Q36/MAX($Q$2:$Q$28)</f>
+      <c r="T36" s="9">
+        <f t="shared" si="6"/>
         <v>0.78525071454528272</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>40</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="32" t="s">
         <v>91</v>
       </c>
       <c r="D37" s="8">
         <v>45627</v>
       </c>
       <c r="E37" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>0.27450000000000002</v>
       </c>
       <c r="F37" s="1">
-        <v>39.56</v>
+        <v>39.799999999999997</v>
       </c>
       <c r="G37" s="1">
-        <f>E37*F37</f>
-        <v>3.9560000000000004E-18</v>
+        <f t="shared" si="0"/>
+        <v>10.9251</v>
       </c>
       <c r="H37" s="11">
         <v>0.1</v>
@@ -4474,54 +5104,58 @@
         <v>0.2</v>
       </c>
       <c r="J37" s="9">
-        <f>IFERROR(H37/I37,"")</f>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
       <c r="K37" s="9">
         <f>IFERROR(J37/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.6879479918910414E-2</v>
+        <v>2.4785067848796617E-2</v>
       </c>
       <c r="L37" s="12">
-        <f>F37/(1-(F37*(1+H37)-F37)/(F37*(1+H37)))</f>
-        <v>43.516000000000005</v>
+        <f t="shared" si="9"/>
+        <v>43.78</v>
       </c>
       <c r="M37" s="12">
-        <f>F37/(1+I37-H37)</f>
-        <v>35.963636363636368</v>
+        <f t="shared" si="7"/>
+        <v>12.017610000000001</v>
       </c>
       <c r="N37" s="12">
-        <f>L37-F37</f>
-        <v>3.9560000000000031</v>
+        <f t="shared" si="2"/>
+        <v>36.181818181818187</v>
       </c>
       <c r="O37" s="12">
-        <f>0.5*(M37-F37)</f>
-        <v>-1.798181818181817</v>
-      </c>
-      <c r="P37" s="15">
-        <f>N37+O37</f>
-        <v>2.1578181818181861</v>
-      </c>
-      <c r="Q37" s="12">
-        <f>MAX($P$2:$P$280)-P37</f>
-        <v>111.9746268993662</v>
-      </c>
-      <c r="R37" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q37)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>8.9305946149632592E-3</v>
+        <f t="shared" si="3"/>
+        <v>3.980000000000004</v>
+      </c>
+      <c r="P37" s="12">
+        <f t="shared" si="4"/>
+        <v>-1.8090909090909051</v>
+      </c>
+      <c r="Q37" s="15">
+        <f t="shared" si="5"/>
+        <v>2.1709090909090989</v>
+      </c>
+      <c r="R37" s="12">
+        <f>MAX($Q$2:$Q$279)-Q37</f>
+        <v>111.96153599027528</v>
       </c>
       <c r="S37" s="9">
-        <f>Q37/MAX($Q$2:$Q$28)</f>
-        <v>0.78181798359449739</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R37)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>8.931638809303739E-3</v>
+      </c>
+      <c r="T37" s="9">
+        <f t="shared" si="6"/>
+        <v>0.78172658156501729</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>40</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="32" t="s">
         <v>92</v>
       </c>
       <c r="D38" s="8">
@@ -4534,7 +5168,7 @@
         <v>26.63</v>
       </c>
       <c r="G38" s="1">
-        <f>E38*F38</f>
+        <f t="shared" si="0"/>
         <v>2.663E-18</v>
       </c>
       <c r="H38" s="11">
@@ -4544,54 +5178,58 @@
         <v>0.2</v>
       </c>
       <c r="J38" s="9">
-        <f>IFERROR(H38/I38,"")</f>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
       <c r="K38" s="9">
         <f>IFERROR(J38/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.6879479918910414E-2</v>
+        <v>2.4785067848796617E-2</v>
       </c>
       <c r="L38" s="12">
-        <f>F38/(1-(F38*(1+H38)-F38)/(F38*(1+H38)))</f>
+        <f t="shared" si="9"/>
         <v>29.293000000000003</v>
       </c>
       <c r="M38" s="12">
-        <f>F38/(1+I38-H38)</f>
+        <f t="shared" si="7"/>
+        <v>2.9293000000000003E-18</v>
+      </c>
+      <c r="N38" s="12">
+        <f t="shared" si="2"/>
         <v>24.209090909090911</v>
       </c>
-      <c r="N38" s="12">
-        <f>L38-F38</f>
+      <c r="O38" s="12">
+        <f t="shared" si="3"/>
         <v>2.6630000000000038</v>
       </c>
-      <c r="O38" s="12">
-        <f>0.5*(M38-F38)</f>
+      <c r="P38" s="12">
+        <f t="shared" si="4"/>
         <v>-1.2104545454545441</v>
       </c>
-      <c r="P38" s="15">
-        <f>N38+O38</f>
+      <c r="Q38" s="15">
+        <f t="shared" si="5"/>
         <v>1.4525454545454597</v>
       </c>
-      <c r="Q38" s="12">
-        <f>MAX($P$2:$P$280)-P38</f>
+      <c r="R38" s="12">
+        <f>MAX($Q$2:$Q$279)-Q38</f>
         <v>112.67989962663893</v>
       </c>
-      <c r="R38" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q38)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+      <c r="S38" s="9">
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R38)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>8.8746972912956655E-3</v>
       </c>
-      <c r="S38" s="9">
-        <f>Q38/MAX($Q$2:$Q$28)</f>
+      <c r="T38" s="9">
+        <f t="shared" si="6"/>
         <v>0.78674226793273505</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>96</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="32" t="s">
         <v>100</v>
       </c>
       <c r="D39" s="8">
@@ -4604,7 +5242,7 @@
         <v>59.17</v>
       </c>
       <c r="G39" s="1">
-        <f>E39*F39</f>
+        <f t="shared" si="0"/>
         <v>5.9170000000000002E-18</v>
       </c>
       <c r="H39" s="11">
@@ -4614,54 +5252,58 @@
         <v>0.2</v>
       </c>
       <c r="J39" s="9">
-        <f>IFERROR(H39/I39,"")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="K39" s="9">
         <f>IFERROR(J39/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>5.3758959837820829E-2</v>
+        <v>4.9570135697593234E-2</v>
       </c>
       <c r="L39" s="12">
-        <f>F39/(1-(F39*(1+H39)-F39)/(F39*(1+H39)))</f>
+        <f t="shared" si="9"/>
         <v>71.004000000000005</v>
       </c>
       <c r="M39" s="12">
-        <f>F39/(1+I39-H39)</f>
+        <f t="shared" si="7"/>
+        <v>7.1003999999999996E-18</v>
+      </c>
+      <c r="N39" s="12">
+        <f t="shared" si="2"/>
         <v>59.17</v>
       </c>
-      <c r="N39" s="12">
-        <f>L39-F39</f>
+      <c r="O39" s="12">
+        <f t="shared" si="3"/>
         <v>11.834000000000003</v>
       </c>
-      <c r="O39" s="12">
-        <f>0.5*(M39-F39)</f>
+      <c r="P39" s="12">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="P39" s="15">
-        <f>N39+O39</f>
+      <c r="Q39" s="15">
+        <f t="shared" si="5"/>
         <v>11.834000000000003</v>
       </c>
-      <c r="Q39" s="12">
-        <f>MAX($P$2:$P$280)-P39</f>
+      <c r="R39" s="12">
+        <f>MAX($Q$2:$Q$279)-Q39</f>
         <v>102.29844508118438</v>
       </c>
-      <c r="R39" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q39)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
+      <c r="S39" s="9">
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R39)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>9.7753196464168812E-3</v>
       </c>
-      <c r="S39" s="9">
-        <f>Q39/MAX($Q$2:$Q$28)</f>
+      <c r="T39" s="9">
+        <f t="shared" si="6"/>
         <v>0.71425791960979246</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="32" t="s">
         <v>98</v>
       </c>
       <c r="D40" s="8">
@@ -4674,7 +5316,7 @@
         <v>19.309999999999999</v>
       </c>
       <c r="G40" s="1">
-        <f>E40*F40</f>
+        <f t="shared" si="0"/>
         <v>1.931E-18</v>
       </c>
       <c r="H40" s="11">
@@ -4684,54 +5326,58 @@
         <v>0.2</v>
       </c>
       <c r="J40" s="9">
-        <f>IFERROR(H40/I40,"")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="K40" s="9">
         <f>IFERROR(J40/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>5.3758959837820829E-2</v>
+        <v>4.9570135697593234E-2</v>
       </c>
       <c r="L40" s="12">
-        <f>F40/(1-(F40*(1+H40)-F40)/(F40*(1+H40)))</f>
+        <f t="shared" si="9"/>
         <v>23.171999999999997</v>
       </c>
       <c r="M40" s="12">
-        <f>F40/(1+I40-H40)</f>
+        <f t="shared" si="7"/>
+        <v>2.3171999999999995E-18</v>
+      </c>
+      <c r="N40" s="12">
+        <f t="shared" si="2"/>
         <v>19.309999999999999</v>
       </c>
-      <c r="N40" s="12">
-        <f>L40-F40</f>
+      <c r="O40" s="12">
+        <f t="shared" si="3"/>
         <v>3.8619999999999983</v>
       </c>
-      <c r="O40" s="12">
-        <f>0.5*(M40-F40)</f>
+      <c r="P40" s="12">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="P40" s="15">
-        <f>N40+O40</f>
+      <c r="Q40" s="15">
+        <f t="shared" si="5"/>
         <v>3.8619999999999983</v>
       </c>
-      <c r="Q40" s="12">
-        <f>MAX($P$2:$P$280)-P40</f>
+      <c r="R40" s="12">
+        <f>MAX($Q$2:$Q$279)-Q40</f>
         <v>110.27044508118439</v>
       </c>
-      <c r="R40" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q40)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>9.0686130745529347E-3</v>
-      </c>
       <c r="S40" s="9">
-        <f>Q40/MAX($Q$2:$Q$28)</f>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R40)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>9.0686130745529329E-3</v>
+      </c>
+      <c r="T40" s="9">
+        <f t="shared" si="6"/>
         <v>0.76991921661787932</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>96</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="32" t="s">
         <v>99</v>
       </c>
       <c r="D41" s="8">
@@ -4744,7 +5390,7 @@
         <v>323.75</v>
       </c>
       <c r="G41" s="1">
-        <f>E41*F41</f>
+        <f t="shared" si="0"/>
         <v>3.2375000000000002E-17</v>
       </c>
       <c r="H41" s="11">
@@ -4754,54 +5400,424 @@
         <v>0.2</v>
       </c>
       <c r="J41" s="9">
-        <f>IFERROR(H41/I41,"")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="K41" s="9">
         <f>IFERROR(J41/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>5.3758959837820829E-2</v>
+        <v>4.9570135697593234E-2</v>
       </c>
       <c r="L41" s="12">
-        <f>F41/(1-(F41*(1+H41)-F41)/(F41*(1+H41)))</f>
+        <f t="shared" si="9"/>
         <v>388.5</v>
       </c>
       <c r="M41" s="12">
-        <f>F41/(1+I41-H41)</f>
+        <f t="shared" si="7"/>
+        <v>3.8849999999999999E-17</v>
+      </c>
+      <c r="N41" s="12">
+        <f t="shared" si="2"/>
         <v>323.75</v>
       </c>
-      <c r="N41" s="12">
-        <f>L41-F41</f>
+      <c r="O41" s="12">
+        <f t="shared" si="3"/>
         <v>64.75</v>
       </c>
-      <c r="O41" s="12">
-        <f>0.5*(M41-F41)</f>
+      <c r="P41" s="12">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="P41" s="15">
-        <f>N41+O41</f>
+      <c r="Q41" s="15">
+        <f t="shared" si="5"/>
         <v>64.75</v>
       </c>
-      <c r="Q41" s="12">
-        <f>MAX($P$2:$P$280)-P41</f>
+      <c r="R41" s="12">
+        <f>MAX($Q$2:$Q$279)-Q41</f>
         <v>49.382445081184386</v>
       </c>
-      <c r="R41" s="9">
-        <f>IFERROR((SUBTOTAL(109,$Q$2:$Q$1048576)/Q41)/SUBTOTAL(109,$Q$2:$Q$1048576),0)</f>
-        <v>2.0250111114506527E-2</v>
-      </c>
       <c r="S41" s="9">
-        <f>Q41/MAX($Q$2:$Q$28)</f>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R41)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>2.0250111114506524E-2</v>
+      </c>
+      <c r="T41" s="9">
+        <f t="shared" si="6"/>
         <v>0.34479314383458876</v>
       </c>
     </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>115</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C42" t="s">
+        <v>117</v>
+      </c>
+      <c r="D42" s="8">
+        <v>45481</v>
+      </c>
+      <c r="E42" s="2">
+        <v>2</v>
+      </c>
+      <c r="F42" s="1">
+        <v>20.928000000000001</v>
+      </c>
+      <c r="G42" s="1">
+        <f t="shared" ref="G42" si="10">E42*F42</f>
+        <v>41.856000000000002</v>
+      </c>
+      <c r="H42" s="11">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="I42" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="J42" s="9">
+        <f t="shared" ref="J42" si="11">IFERROR(H42/I42,"")</f>
+        <v>0.22499999999999998</v>
+      </c>
+      <c r="K42" s="9">
+        <f>IFERROR(J42/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>1.1153280531958477E-2</v>
+      </c>
+      <c r="L42" s="12">
+        <f t="shared" ref="L42" si="12">F42/(1-(F42*(1+H42)-F42)/(F42*(1+H42)))</f>
+        <v>21.869759999999999</v>
+      </c>
+      <c r="M42" s="12">
+        <f t="shared" ref="M42" si="13">L42*E42</f>
+        <v>43.739519999999999</v>
+      </c>
+      <c r="N42" s="12">
+        <f t="shared" ref="N42" si="14">F42/(1+I42-H42)</f>
+        <v>18.119480519480518</v>
+      </c>
+      <c r="O42" s="12">
+        <f t="shared" ref="O42" si="15">L42-F42</f>
+        <v>0.9417599999999986</v>
+      </c>
+      <c r="P42" s="12">
+        <f t="shared" ref="P42" si="16">0.5*(N42-F42)</f>
+        <v>-1.4042597402597412</v>
+      </c>
+      <c r="Q42" s="15">
+        <f t="shared" ref="Q42" si="17">O42+P42</f>
+        <v>-0.46249974025974261</v>
+      </c>
+      <c r="R42" s="12">
+        <f>MAX($Q$2:$Q$279)-Q42</f>
+        <v>114.59494482144413</v>
+      </c>
+      <c r="S42" s="9">
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R42)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>8.7263884245343277E-3</v>
+      </c>
+      <c r="T42" s="9">
+        <f t="shared" ref="T42" si="18">R42/MAX($R$2:$R$28)</f>
+        <v>0.80011330398039715</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>115</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C43" t="s">
+        <v>119</v>
+      </c>
+      <c r="D43" s="8">
+        <v>45481</v>
+      </c>
+      <c r="E43" s="2">
+        <v>2</v>
+      </c>
+      <c r="F43" s="1">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="G43" s="1">
+        <f t="shared" ref="G43" si="19">E43*F43</f>
+        <v>32.799999999999997</v>
+      </c>
+      <c r="H43" s="11">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="I43" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="J43" s="9">
+        <f t="shared" ref="J43" si="20">IFERROR(H43/I43,"")</f>
+        <v>0.22499999999999998</v>
+      </c>
+      <c r="K43" s="9">
+        <f>IFERROR(J43/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>1.1153280531958477E-2</v>
+      </c>
+      <c r="L43" s="12">
+        <f t="shared" ref="L43" si="21">F43/(1-(F43*(1+H43)-F43)/(F43*(1+H43)))</f>
+        <v>17.137999999999998</v>
+      </c>
+      <c r="M43" s="12">
+        <f t="shared" ref="M43" si="22">L43*E43</f>
+        <v>34.275999999999996</v>
+      </c>
+      <c r="N43" s="12">
+        <f t="shared" ref="N43" si="23">F43/(1+I43-H43)</f>
+        <v>14.199134199134198</v>
+      </c>
+      <c r="O43" s="12">
+        <f t="shared" ref="O43" si="24">L43-F43</f>
+        <v>0.73799999999999955</v>
+      </c>
+      <c r="P43" s="12">
+        <f t="shared" ref="P43" si="25">0.5*(N43-F43)</f>
+        <v>-1.1004329004329003</v>
+      </c>
+      <c r="Q43" s="15">
+        <f t="shared" ref="Q43" si="26">O43+P43</f>
+        <v>-0.36243290043290077</v>
+      </c>
+      <c r="R43" s="12">
+        <f>MAX($Q$2:$Q$279)-Q43</f>
+        <v>114.49487798161729</v>
+      </c>
+      <c r="S43" s="9">
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R43)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>8.7340151597048287E-3</v>
+      </c>
+      <c r="T43" s="9">
+        <f t="shared" ref="T43" si="27">R43/MAX($R$2:$R$28)</f>
+        <v>0.79941462735066027</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>115</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C44" t="s">
+        <v>121</v>
+      </c>
+      <c r="D44" s="8">
+        <v>45481</v>
+      </c>
+      <c r="E44" s="2">
+        <v>1</v>
+      </c>
+      <c r="F44" s="1">
+        <v>48.68</v>
+      </c>
+      <c r="G44" s="1">
+        <f t="shared" ref="G44" si="28">E44*F44</f>
+        <v>48.68</v>
+      </c>
+      <c r="H44" s="11">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I44" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="J44" s="9">
+        <f t="shared" ref="J44" si="29">IFERROR(H44/I44,"")</f>
+        <v>0.125</v>
+      </c>
+      <c r="K44" s="9">
+        <f>IFERROR(J44/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>6.1962669621991543E-3</v>
+      </c>
+      <c r="L44" s="12">
+        <f t="shared" ref="L44" si="30">F44/(1-(F44*(1+H44)-F44)/(F44*(1+H44)))</f>
+        <v>49.896999999999998</v>
+      </c>
+      <c r="M44" s="12">
+        <f t="shared" ref="M44" si="31">L44*E44</f>
+        <v>49.896999999999998</v>
+      </c>
+      <c r="N44" s="12">
+        <f t="shared" ref="N44" si="32">F44/(1+I44-H44)</f>
+        <v>41.42978723404255</v>
+      </c>
+      <c r="O44" s="12">
+        <f t="shared" ref="O44" si="33">L44-F44</f>
+        <v>1.2169999999999987</v>
+      </c>
+      <c r="P44" s="12">
+        <f t="shared" ref="P44" si="34">0.5*(N44-F44)</f>
+        <v>-3.6251063829787249</v>
+      </c>
+      <c r="Q44" s="15">
+        <f t="shared" ref="Q44" si="35">O44+P44</f>
+        <v>-2.4081063829787261</v>
+      </c>
+      <c r="R44" s="12">
+        <f>MAX($Q$2:$Q$279)-Q44</f>
+        <v>116.54055146416312</v>
+      </c>
+      <c r="S44" s="9">
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R44)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>8.5807042049865865E-3</v>
+      </c>
+      <c r="T44" s="9">
+        <f t="shared" ref="T44" si="36">R44/MAX($R$2:$R$28)</f>
+        <v>0.81369772309746791</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>115</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C45" t="s">
+        <v>123</v>
+      </c>
+      <c r="D45" s="8">
+        <v>45481</v>
+      </c>
+      <c r="E45" s="2">
+        <v>1</v>
+      </c>
+      <c r="F45" s="1">
+        <v>51.28</v>
+      </c>
+      <c r="G45" s="1">
+        <f t="shared" ref="G45" si="37">E45*F45</f>
+        <v>51.28</v>
+      </c>
+      <c r="H45" s="11">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I45" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="J45" s="9">
+        <f t="shared" ref="J45" si="38">IFERROR(H45/I45,"")</f>
+        <v>0.125</v>
+      </c>
+      <c r="K45" s="9">
+        <f>IFERROR(J45/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>6.1962669621991543E-3</v>
+      </c>
+      <c r="L45" s="12">
+        <f t="shared" ref="L45" si="39">F45/(1-(F45*(1+H45)-F45)/(F45*(1+H45)))</f>
+        <v>52.561999999999998</v>
+      </c>
+      <c r="M45" s="12">
+        <f t="shared" ref="M45" si="40">L45*E45</f>
+        <v>52.561999999999998</v>
+      </c>
+      <c r="N45" s="12">
+        <f t="shared" ref="N45" si="41">F45/(1+I45-H45)</f>
+        <v>43.642553191489363</v>
+      </c>
+      <c r="O45" s="12">
+        <f t="shared" ref="O45" si="42">L45-F45</f>
+        <v>1.2819999999999965</v>
+      </c>
+      <c r="P45" s="12">
+        <f t="shared" ref="P45" si="43">0.5*(N45-F45)</f>
+        <v>-3.8187234042553193</v>
+      </c>
+      <c r="Q45" s="15">
+        <f t="shared" ref="Q45" si="44">O45+P45</f>
+        <v>-2.5367234042553228</v>
+      </c>
+      <c r="R45" s="12">
+        <f>MAX($Q$2:$Q$279)-Q45</f>
+        <v>116.66916848543971</v>
+      </c>
+      <c r="S45" s="9">
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R45)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>8.571244768276547E-3</v>
+      </c>
+      <c r="T45" s="9">
+        <f t="shared" ref="T45" si="45">R45/MAX($R$2:$R$28)</f>
+        <v>0.81459573993409262</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>115</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C46" t="s">
+        <v>125</v>
+      </c>
+      <c r="D46" s="8">
+        <v>45481</v>
+      </c>
+      <c r="E46" s="2">
+        <v>1</v>
+      </c>
+      <c r="F46" s="1">
+        <v>44.14</v>
+      </c>
+      <c r="G46" s="1">
+        <f t="shared" ref="G46" si="46">E46*F46</f>
+        <v>44.14</v>
+      </c>
+      <c r="H46" s="11">
+        <v>0.15</v>
+      </c>
+      <c r="I46" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="J46" s="9">
+        <f t="shared" ref="J46" si="47">IFERROR(H46/I46,"")</f>
+        <v>0.74999999999999989</v>
+      </c>
+      <c r="K46" s="9">
+        <f>IFERROR(J46/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>3.7177601773194922E-2</v>
+      </c>
+      <c r="L46" s="12">
+        <f t="shared" ref="L46" si="48">F46/(1-(F46*(1+H46)-F46)/(F46*(1+H46)))</f>
+        <v>50.760999999999996</v>
+      </c>
+      <c r="M46" s="12">
+        <f t="shared" ref="M46" si="49">L46*E46</f>
+        <v>50.760999999999996</v>
+      </c>
+      <c r="N46" s="12">
+        <f t="shared" ref="N46" si="50">F46/(1+I46-H46)</f>
+        <v>42.038095238095238</v>
+      </c>
+      <c r="O46" s="12">
+        <f t="shared" ref="O46" si="51">L46-F46</f>
+        <v>6.6209999999999951</v>
+      </c>
+      <c r="P46" s="12">
+        <f t="shared" ref="P46" si="52">0.5*(N46-F46)</f>
+        <v>-1.0509523809523813</v>
+      </c>
+      <c r="Q46" s="15">
+        <f t="shared" ref="Q46" si="53">O46+P46</f>
+        <v>5.5700476190476138</v>
+      </c>
+      <c r="R46" s="12">
+        <f>MAX($Q$2:$Q$279)-Q46</f>
+        <v>108.56239746213677</v>
+      </c>
+      <c r="S46" s="9">
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R46)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>9.2112925227979536E-3</v>
+      </c>
+      <c r="T46" s="9">
+        <f t="shared" ref="T46" si="54">R46/MAX($R$2:$R$28)</f>
+        <v>0.75799345823506892</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S41" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S41">
-      <sortCondition descending="1" ref="E1:E41"/>
-    </sortState>
-  </autoFilter>
-  <conditionalFormatting sqref="R2:R41">
-    <cfRule type="iconSet" priority="3">
+  <autoFilter ref="A1:T45" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="S2:S46">
+    <cfRule type="iconSet" priority="8">
       <iconSet iconSet="3Symbols">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="33"/>
@@ -4815,7 +5831,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="7" id="{2048185B-3E19-4351-A3A9-6DB74B32B9C2}">
+          <x14:cfRule type="iconSet" priority="10" id="{2048185B-3E19-4351-A3A9-6DB74B32B9C2}">
             <x14:iconSet iconSet="5Arrows" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -4839,7 +5855,7 @@
               <x14:cfIcon iconSet="3Arrows" iconId="0"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>S2:S41</xm:sqref>
+          <xm:sqref>T2:T46</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -4848,24 +5864,484 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFDF4B0C-3879-4A30-880B-B04980CC1636}">
-  <dimension ref="A2:F13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD6C5064-D029-4982-9C03-6BDB75C18181}">
+  <dimension ref="B2:J16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E2" s="26" t="s">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2" s="29">
+        <v>8.8700000000000001E-2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H2" t="s">
+        <v>129</v>
+      </c>
+      <c r="I2" t="s">
+        <v>126</v>
+      </c>
+      <c r="J2" s="29">
+        <v>0.24129999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E3" s="29">
+        <v>0.1077</v>
+      </c>
+      <c r="G3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J3" s="29">
+        <v>0.30709999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" s="42" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="42" t="s">
+        <v>127</v>
+      </c>
+      <c r="E5" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="G5" s="42" t="s">
+        <v>82</v>
+      </c>
+      <c r="H5" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="I5" s="42" t="s">
+        <v>127</v>
+      </c>
+      <c r="J5" s="42" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="37">
+        <v>0.25440000000000002</v>
+      </c>
+      <c r="D6" s="37">
+        <v>0</v>
+      </c>
+      <c r="E6" s="37">
+        <f>D6-C6</f>
+        <v>-0.25440000000000002</v>
+      </c>
+      <c r="G6" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="H6" s="37">
+        <v>0.25440000000000002</v>
+      </c>
+      <c r="I6" s="37">
+        <v>0.2651</v>
+      </c>
+      <c r="J6" s="37">
+        <f>I6-H6</f>
+        <v>1.0699999999999987E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="37">
+        <v>0</v>
+      </c>
+      <c r="D7" s="37">
+        <v>0</v>
+      </c>
+      <c r="E7" s="37">
+        <f>D7-C7</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7" s="37">
+        <v>0</v>
+      </c>
+      <c r="I7" s="37">
+        <v>0.1207</v>
+      </c>
+      <c r="J7" s="37">
+        <f t="shared" ref="J7:J16" si="0">I7-H7</f>
+        <v>0.1207</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B8" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="39">
+        <v>0.21579999999999999</v>
+      </c>
+      <c r="D8" s="39">
+        <v>5.21E-2</v>
+      </c>
+      <c r="E8" s="39">
+        <f>D8-C8</f>
+        <v>-0.16369999999999998</v>
+      </c>
+      <c r="G8" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="39">
+        <v>0.21579999999999999</v>
+      </c>
+      <c r="I8" s="39">
+        <v>5.4899999999999997E-2</v>
+      </c>
+      <c r="J8" s="39">
+        <f t="shared" si="0"/>
+        <v>-0.16089999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" s="41">
+        <v>0.1852</v>
+      </c>
+      <c r="D9" s="41">
+        <v>0.1951</v>
+      </c>
+      <c r="E9" s="41">
+        <f>D9-C9</f>
+        <v>9.8999999999999921E-3</v>
+      </c>
+      <c r="G9" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="H9" s="41">
+        <v>0.1852</v>
+      </c>
+      <c r="I9" s="41">
+        <v>0.27689999999999998</v>
+      </c>
+      <c r="J9" s="41">
+        <f t="shared" si="0"/>
+        <v>9.1699999999999976E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="39">
+        <v>0.2772</v>
+      </c>
+      <c r="D10" s="39">
+        <v>0</v>
+      </c>
+      <c r="E10" s="39">
+        <f>D10-C10</f>
+        <v>-0.2772</v>
+      </c>
+      <c r="G10" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="H10" s="39">
+        <v>0.2772</v>
+      </c>
+      <c r="I10" s="39">
+        <v>0</v>
+      </c>
+      <c r="J10" s="39">
+        <f t="shared" si="0"/>
+        <v>-0.2772</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="37">
+        <v>0</v>
+      </c>
+      <c r="D11" s="37">
+        <v>0.33910000000000001</v>
+      </c>
+      <c r="E11" s="37">
+        <f>D11-C11</f>
+        <v>0.33910000000000001</v>
+      </c>
+      <c r="G11" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="37">
+        <v>0</v>
+      </c>
+      <c r="I11" s="37">
+        <v>0</v>
+      </c>
+      <c r="J11" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="37">
+        <v>0</v>
+      </c>
+      <c r="D12" s="37">
+        <v>0</v>
+      </c>
+      <c r="E12" s="37">
+        <f>D12-C12</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="H12" s="37">
+        <v>0</v>
+      </c>
+      <c r="I12" s="37">
+        <v>0</v>
+      </c>
+      <c r="J12" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="37">
+        <v>0</v>
+      </c>
+      <c r="D13" s="37">
+        <v>0</v>
+      </c>
+      <c r="E13" s="37">
+        <f>D13-C13</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="H13" s="37">
+        <v>0</v>
+      </c>
+      <c r="I13" s="37">
+        <v>0</v>
+      </c>
+      <c r="J13" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="37">
+        <v>0</v>
+      </c>
+      <c r="D14" s="37">
+        <v>0</v>
+      </c>
+      <c r="E14" s="37">
+        <f>D14-C14</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="H14" s="37">
+        <v>0</v>
+      </c>
+      <c r="I14" s="37">
+        <v>0</v>
+      </c>
+      <c r="J14" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B15" s="40" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" s="41">
+        <v>6.7400000000000002E-2</v>
+      </c>
+      <c r="D15" s="41">
+        <v>0.19650000000000001</v>
+      </c>
+      <c r="E15" s="41">
+        <f>D15-C15</f>
+        <v>0.12909999999999999</v>
+      </c>
+      <c r="G15" s="40" t="s">
+        <v>91</v>
+      </c>
+      <c r="H15" s="41">
+        <v>6.7400000000000002E-2</v>
+      </c>
+      <c r="I15" s="41">
+        <v>0.16420000000000001</v>
+      </c>
+      <c r="J15" s="41">
+        <f t="shared" si="0"/>
+        <v>9.6800000000000011E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B16" s="40" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" s="41">
+        <v>0</v>
+      </c>
+      <c r="D16" s="41">
+        <v>0.2172</v>
+      </c>
+      <c r="E16" s="41">
+        <f>D16-C16</f>
+        <v>0.2172</v>
+      </c>
+      <c r="G16" s="40" t="s">
+        <v>92</v>
+      </c>
+      <c r="H16" s="41">
+        <v>0</v>
+      </c>
+      <c r="I16" s="41">
+        <v>0.1183</v>
+      </c>
+      <c r="J16" s="41">
+        <f t="shared" si="0"/>
+        <v>0.1183</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFDF4B0C-3879-4A30-880B-B04980CC1636}">
+  <dimension ref="A1:V19"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="12" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="15.5703125" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="13" max="13" width="6" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="5.5703125" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="0" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.140625" customWidth="1" outlineLevel="1"/>
+    <col min="21" max="21" width="10.5703125" customWidth="1" outlineLevel="1"/>
+    <col min="22" max="22" width="15" customWidth="1" outlineLevel="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="H1" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="O1" s="33"/>
+      <c r="R1" s="33" t="s">
         <v>108</v>
       </c>
-      <c r="F2" s="26"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="S1" s="33"/>
+      <c r="T1" s="33"/>
+      <c r="U1" s="33"/>
+      <c r="V1" s="33"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="H2" s="34">
+        <v>46000</v>
+      </c>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="34">
+        <v>45684</v>
+      </c>
+      <c r="O2" s="33"/>
+      <c r="R2" s="34">
+        <v>45685</v>
+      </c>
+      <c r="S2" s="34"/>
+      <c r="T2" s="34"/>
+      <c r="U2" s="34"/>
+      <c r="V2" s="34"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
         <v>104</v>
       </c>
@@ -4875,187 +6351,750 @@
       <c r="C3" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="D3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="I3" s="23" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J3" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="K3" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="L3" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="N3" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="O3" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q3" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="R3" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="S3" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="T3" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="U3" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="V3" s="28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="12">
+        <v>218.75600000000003</v>
+      </c>
+      <c r="C4" s="22">
+        <v>0.23693336344898536</v>
+      </c>
+      <c r="D4" s="29">
+        <v>5.7047669549634916E-2</v>
+      </c>
+      <c r="E4" s="12">
+        <v>12.479519999999951</v>
+      </c>
+      <c r="F4" s="12"/>
+      <c r="G4" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" s="12">
+        <v>238.614968</v>
+      </c>
+      <c r="I4" s="22">
+        <v>0.38101621514787376</v>
+      </c>
+      <c r="J4" s="29">
+        <v>0.15967772461784535</v>
+      </c>
+      <c r="K4" s="12">
+        <v>38.101495149999977</v>
+      </c>
+      <c r="L4" s="12">
+        <v>1.7999999999999998</v>
+      </c>
+      <c r="N4" s="12">
+        <v>233.65908899999999</v>
+      </c>
+      <c r="O4" s="22">
+        <v>0.30679033555941537</v>
+      </c>
+      <c r="Q4" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="12">
+      <c r="R4" s="12">
         <v>210.14336800000001</v>
       </c>
-      <c r="C4" s="22">
-        <v>0.28262220609768579</v>
-      </c>
-      <c r="E4" s="12">
-        <v>233.65908899999999</v>
-      </c>
-      <c r="F4" s="22">
-        <v>0.30679033555941537</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
+      <c r="S4" s="22">
+        <v>0.29827679581416749</v>
+      </c>
+      <c r="T4" s="29">
+        <v>0.11801519297244734</v>
+      </c>
+      <c r="U4" s="12">
+        <v>24.8001101264</v>
+      </c>
+      <c r="V4" s="12"/>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" s="35" t="s">
+        <v>119</v>
+      </c>
+      <c r="B5" s="12">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="C5" s="22">
+        <v>0.14993874453729267</v>
+      </c>
+      <c r="D5" s="29">
+        <v>4.4999999999999929E-2</v>
+      </c>
+      <c r="E5" s="12">
+        <v>1.4759999999999991</v>
+      </c>
+      <c r="F5" s="12"/>
+      <c r="G5" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="12">
+        <v>159.887845</v>
+      </c>
+      <c r="I5" s="22">
+        <v>0.25530611956434301</v>
+      </c>
+      <c r="J5" s="29">
+        <v>0.1083576745186603</v>
+      </c>
+      <c r="K5" s="12">
+        <v>17.32507506799999</v>
+      </c>
+      <c r="L5" s="12"/>
+      <c r="N5" s="12">
+        <v>210.14336800000001</v>
+      </c>
+      <c r="O5" s="22">
+        <v>0.27591460131176709</v>
+      </c>
+      <c r="Q5" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="12">
-        <v>197.38955299999998</v>
-      </c>
-      <c r="C5" s="22">
-        <v>0.26546957660589154</v>
-      </c>
-      <c r="E5" s="12">
+      <c r="R5" s="12">
+        <v>177.40437299999999</v>
+      </c>
+      <c r="S5" s="22">
+        <v>0.25180717547965348</v>
+      </c>
+      <c r="T5" s="29">
+        <v>0.17124807148919596</v>
+      </c>
+      <c r="U5" s="12">
+        <v>30.380156749999998</v>
+      </c>
+      <c r="V5" s="12"/>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" s="35" t="s">
+        <v>123</v>
+      </c>
+      <c r="B6" s="12">
+        <v>51.28</v>
+      </c>
+      <c r="C6" s="22">
+        <v>0.23441642743513319</v>
+      </c>
+      <c r="D6" s="29">
+        <v>2.4999999999999911E-2</v>
+      </c>
+      <c r="E6" s="12">
+        <v>1.2819999999999965</v>
+      </c>
+      <c r="F6" s="12"/>
+      <c r="G6" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="12">
+        <v>84.915515999999997</v>
+      </c>
+      <c r="I6" s="22">
+        <v>0.13559161348859186</v>
+      </c>
+      <c r="J6" s="29">
+        <v>0.28530609176301791</v>
+      </c>
+      <c r="K6" s="12">
+        <v>24.226914000000008</v>
+      </c>
+      <c r="L6" s="12"/>
+      <c r="N6" s="12">
+        <v>149.810948</v>
+      </c>
+      <c r="O6" s="22">
+        <v>0.19669917915067334</v>
+      </c>
+      <c r="Q6" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="R6" s="12">
+        <v>162.11427700000002</v>
+      </c>
+      <c r="S6" s="22">
+        <v>0.23010446420222211</v>
+      </c>
+      <c r="T6" s="29">
+        <v>0.13072196842971429</v>
+      </c>
+      <c r="U6" s="12">
+        <v>21.191897399999959</v>
+      </c>
+      <c r="V6" s="12"/>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" s="12">
+        <v>41.856000000000002</v>
+      </c>
+      <c r="C7" s="22">
+        <v>0.19133646619978423</v>
+      </c>
+      <c r="D7" s="29">
+        <v>4.4999999999999929E-2</v>
+      </c>
+      <c r="E7" s="12">
+        <v>1.8835199999999972</v>
+      </c>
+      <c r="F7" s="12"/>
+      <c r="G7" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="12">
+        <v>76.938714000000004</v>
+      </c>
+      <c r="I7" s="22">
+        <v>0.12285439531448307</v>
+      </c>
+      <c r="J7" s="29">
+        <v>7.9955036025166626E-2</v>
+      </c>
+      <c r="K7" s="12">
+        <v>6.1516376495999907</v>
+      </c>
+      <c r="L7" s="12">
+        <v>-4.4000000000000004</v>
+      </c>
+      <c r="N7" s="12">
+        <v>108.030807</v>
+      </c>
+      <c r="O7" s="22">
+        <v>0.14184257788612895</v>
+      </c>
+      <c r="Q7" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="R7" s="12">
+        <v>94.882213999999991</v>
+      </c>
+      <c r="S7" s="22">
+        <v>0.13467549816596705</v>
+      </c>
+      <c r="T7" s="29">
+        <v>0.28159743932619463</v>
+      </c>
+      <c r="U7" s="12">
+        <v>26.71858850000001</v>
+      </c>
+      <c r="V7" s="12">
+        <v>10.31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" s="35" t="s">
+        <v>121</v>
+      </c>
+      <c r="B8" s="12">
+        <v>48.68</v>
+      </c>
+      <c r="C8" s="22">
+        <v>0.22253103914864047</v>
+      </c>
+      <c r="D8" s="29">
+        <v>2.4999999999999911E-2</v>
+      </c>
+      <c r="E8" s="12">
+        <v>1.2169999999999987</v>
+      </c>
+      <c r="F8" s="12"/>
+      <c r="G8" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="12">
+        <v>65.902309000000002</v>
+      </c>
+      <c r="I8" s="22">
+        <v>0.10523165648470827</v>
+      </c>
+      <c r="J8" s="29">
+        <v>0.29383162280399011</v>
+      </c>
+      <c r="K8" s="12">
+        <v>19.364182400000004</v>
+      </c>
+      <c r="L8" s="12"/>
+      <c r="N8" s="12">
+        <v>59.980460999999991</v>
+      </c>
+      <c r="O8" s="22">
+        <v>7.875330609201521E-2</v>
+      </c>
+      <c r="Q8" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="R8" s="12">
+        <v>59.980460999999991</v>
+      </c>
+      <c r="S8" s="22">
+        <v>8.5136066337989938E-2</v>
+      </c>
+      <c r="T8" s="29">
+        <v>9.1757028336277635E-2</v>
+      </c>
+      <c r="U8" s="12">
+        <v>5.5036288595999991</v>
+      </c>
+      <c r="V8" s="12"/>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" s="35" t="s">
+        <v>125</v>
+      </c>
+      <c r="B9" s="12">
+        <v>44.14</v>
+      </c>
+      <c r="C9" s="22">
+        <v>0.20177732267914936</v>
+      </c>
+      <c r="D9" s="29">
+        <v>0.14999999999999991</v>
+      </c>
+      <c r="E9" s="12">
+        <v>6.6209999999999951</v>
+      </c>
+      <c r="F9" s="12"/>
+      <c r="G9" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="H9" s="12">
+        <v>2.9170551999999998E-16</v>
+      </c>
+      <c r="I9" s="22">
+        <v>4.657902817234096E-19</v>
+      </c>
+      <c r="J9" s="29">
+        <v>9.799364235548258E-2</v>
+      </c>
+      <c r="K9" s="12">
+        <v>2.8585286400000075E-17</v>
+      </c>
+      <c r="L9" s="12"/>
+      <c r="N9" s="12">
+        <v>2.9170551999999998E-16</v>
+      </c>
+      <c r="O9" s="22">
+        <v>3.830042937697739E-19</v>
+      </c>
+      <c r="Q9" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="R9" s="12">
+        <v>2.9170551999999998E-16</v>
+      </c>
+      <c r="S9" s="22">
+        <v>4.1404584239320622E-19</v>
+      </c>
+      <c r="T9" s="29">
+        <v>9.799364235548258E-2</v>
+      </c>
+      <c r="U9" s="12">
+        <v>2.8585286400000075E-17</v>
+      </c>
+      <c r="V9" s="12"/>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="12">
         <v>210.14336800000001</v>
       </c>
-      <c r="F5" s="22">
-        <v>0.27591460131176709</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
+      <c r="C10" s="22">
+        <v>0.2276050713431306</v>
+      </c>
+      <c r="D10" s="29">
+        <v>0.11801519297244734</v>
+      </c>
+      <c r="E10" s="12">
+        <v>24.8001101264</v>
+      </c>
+      <c r="F10" s="12"/>
+      <c r="G10" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="H10" s="12">
+        <v>3.8291999999999999E-17</v>
+      </c>
+      <c r="I10" s="22">
+        <v>6.1143997095950747E-20</v>
+      </c>
+      <c r="J10" s="29">
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="K10" s="12">
+        <v>7.6584000000000023E-18</v>
+      </c>
+      <c r="L10" s="12"/>
+      <c r="N10" s="12">
+        <v>3.8291999999999999E-17</v>
+      </c>
+      <c r="O10" s="22">
+        <v>5.0276732565884192E-20</v>
+      </c>
+      <c r="Q10" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="R10" s="12">
+        <v>3.8291999999999999E-17</v>
+      </c>
+      <c r="S10" s="22">
+        <v>5.4351537114966676E-20</v>
+      </c>
+      <c r="T10" s="29">
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="U10" s="12">
+        <v>7.6584000000000023E-18</v>
+      </c>
+      <c r="V10" s="12"/>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="12">
+        <v>177.40437299999999</v>
+      </c>
+      <c r="C11" s="22">
+        <v>0.19214565445267037</v>
+      </c>
+      <c r="D11" s="29">
+        <v>0.17124807148919596</v>
+      </c>
+      <c r="E11" s="12">
+        <v>30.380156749999998</v>
+      </c>
+      <c r="F11" s="12"/>
+      <c r="G11" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="H11" s="12">
+        <v>1.3353E-17</v>
+      </c>
+      <c r="I11" s="22">
+        <v>2.1321837282519334E-20</v>
+      </c>
+      <c r="J11" s="29">
+        <v>7.0000000000000062E-2</v>
+      </c>
+      <c r="K11" s="12">
+        <v>9.3470999999999986E-19</v>
+      </c>
+      <c r="L11" s="12"/>
+      <c r="N11" s="12">
+        <v>1.3353E-17</v>
+      </c>
+      <c r="O11" s="22">
+        <v>1.7532257650481865E-20</v>
+      </c>
+      <c r="Q11" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="R11" s="12">
+        <v>1.3353E-17</v>
+      </c>
+      <c r="S11" s="22">
+        <v>1.8953203674296199E-20</v>
+      </c>
+      <c r="T11" s="29">
+        <v>7.0000000000000062E-2</v>
+      </c>
+      <c r="U11" s="12">
+        <v>9.3470999999999986E-19</v>
+      </c>
+      <c r="V11" s="12"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="12">
+        <v>162.11427700000002</v>
+      </c>
+      <c r="C12" s="22">
+        <v>0.17558503955416302</v>
+      </c>
+      <c r="D12" s="29">
+        <v>0.13072196842971429</v>
+      </c>
+      <c r="E12" s="12">
+        <v>21.191897399999959</v>
+      </c>
+      <c r="F12" s="12"/>
+      <c r="G12" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="H12" s="12">
+        <v>5.5999999999999995E-18</v>
+      </c>
+      <c r="I12" s="22">
+        <v>8.9419822348616982E-21</v>
+      </c>
+      <c r="J12" s="29">
+        <v>7.0000000000000062E-2</v>
+      </c>
+      <c r="K12" s="12">
+        <v>3.9200000000000069E-19</v>
+      </c>
+      <c r="L12" s="12"/>
+      <c r="N12" s="12">
+        <v>5.5999999999999995E-18</v>
+      </c>
+      <c r="O12" s="22">
+        <v>7.3527029763123223E-21</v>
+      </c>
+      <c r="Q12" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="R12" s="12">
+        <v>5.5999999999999995E-18</v>
+      </c>
+      <c r="S12" s="22">
+        <v>7.9486213267474501E-21</v>
+      </c>
+      <c r="T12" s="29">
+        <v>7.0000000000000062E-2</v>
+      </c>
+      <c r="U12" s="12">
+        <v>3.9200000000000069E-19</v>
+      </c>
+      <c r="V12" s="12"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A13" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="12">
-        <v>149.810948</v>
-      </c>
-      <c r="C6" s="22">
-        <v>0.20148102233397955</v>
-      </c>
-      <c r="E6" s="12">
-        <v>149.810948</v>
-      </c>
-      <c r="F6" s="22">
-        <v>0.19669917915067334</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="12">
-        <v>126.22434900000002</v>
-      </c>
-      <c r="C7" s="22">
-        <v>0.16975936151182378</v>
-      </c>
-      <c r="E7" s="12">
-        <v>108.030807</v>
-      </c>
-      <c r="F7" s="22">
-        <v>0.14184257788612895</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
+      <c r="B13" s="12">
+        <v>94.882213999999991</v>
+      </c>
+      <c r="C13" s="22">
+        <v>0.10276637941133684</v>
+      </c>
+      <c r="D13" s="29">
+        <v>0.28159743932619463</v>
+      </c>
+      <c r="E13" s="12">
+        <v>26.71858850000001</v>
+      </c>
+      <c r="F13" s="12"/>
+      <c r="G13" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="H13" s="24">
+        <v>626.25935200000004</v>
+      </c>
+      <c r="I13" s="25">
+        <v>1</v>
+      </c>
+      <c r="J13" s="30">
+        <v>0.16793250900243595</v>
+      </c>
+      <c r="K13" s="24">
+        <v>105.16930426759973</v>
+      </c>
+      <c r="L13" s="24">
+        <f>SUM(L4:L12)</f>
+        <v>-2.6000000000000005</v>
+      </c>
+      <c r="N13" s="24">
+        <v>761.62467300000003</v>
+      </c>
+      <c r="O13" s="25">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="R13" s="24">
+        <v>704.52469299999996</v>
+      </c>
+      <c r="S13" s="25">
+        <v>1</v>
+      </c>
+      <c r="T13" s="30">
+        <v>0.15413850318515387</v>
+      </c>
+      <c r="U13" s="24">
+        <v>108.59438163600009</v>
+      </c>
+      <c r="V13" s="24">
+        <f>SUM(V4:V12)</f>
+        <v>10.31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A14" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B14" s="12">
         <v>59.980460999999991</v>
       </c>
-      <c r="C8" s="22">
-        <v>8.06678334506193E-2</v>
-      </c>
-      <c r="E8" s="12">
-        <v>59.980460999999991</v>
-      </c>
-      <c r="F8" s="22">
-        <v>7.875330609201521E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
+      <c r="C14" s="22">
+        <v>6.4964491789714057E-2</v>
+      </c>
+      <c r="D14" s="29">
+        <v>9.1757028336277635E-2</v>
+      </c>
+      <c r="E14" s="12">
+        <v>5.5036288595999991</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A15" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B15" s="12">
         <v>2.9170551999999998E-16</v>
       </c>
-      <c r="C9" s="22">
-        <v>3.9231529587587362E-19</v>
-      </c>
-      <c r="E9" s="12">
-        <v>2.9170551999999998E-16</v>
-      </c>
-      <c r="F9" s="22">
-        <v>3.830042937697739E-19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
+      <c r="C15" s="22">
+        <v>3.1594456833291544E-19</v>
+      </c>
+      <c r="D15" s="29">
+        <v>9.799364235548258E-2</v>
+      </c>
+      <c r="E15" s="12">
+        <v>2.8585286400000075E-17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B16" s="12">
         <v>3.8291999999999999E-17</v>
       </c>
-      <c r="C10" s="22">
-        <v>5.1498981951657802E-20</v>
-      </c>
-      <c r="E10" s="12">
-        <v>3.8291999999999999E-17</v>
-      </c>
-      <c r="F10" s="22">
-        <v>5.0276732565884192E-20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
+      <c r="C16" s="22">
+        <v>4.147384461769527E-20</v>
+      </c>
+      <c r="D16" s="29">
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="E16" s="12">
+        <v>7.6584000000000023E-18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B17" s="12">
         <v>1.3353E-17</v>
       </c>
-      <c r="C11" s="22">
-        <v>1.795847451166005E-20</v>
-      </c>
-      <c r="E11" s="12">
-        <v>1.3353E-17</v>
-      </c>
-      <c r="F11" s="22">
-        <v>1.7532257650481865E-20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
+      <c r="C17" s="22">
+        <v>1.4462557379611534E-20</v>
+      </c>
+      <c r="D17" s="29">
+        <v>7.0000000000000062E-2</v>
+      </c>
+      <c r="E17" s="12">
+        <v>9.3470999999999986E-19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B18" s="12">
         <v>5.5999999999999995E-18</v>
       </c>
-      <c r="C12" s="22">
-        <v>7.5314504055490353E-21</v>
-      </c>
-      <c r="E12" s="12">
-        <v>5.5999999999999995E-18</v>
-      </c>
-      <c r="F12" s="22">
-        <v>7.3527029763123223E-21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
+      <c r="C18" s="22">
+        <v>6.0653277410188415E-21</v>
+      </c>
+      <c r="D18" s="29">
+        <v>7.0000000000000062E-2</v>
+      </c>
+      <c r="E18" s="12">
+        <v>3.9200000000000069E-19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="B13" s="12">
-        <v>743.54867899999999</v>
-      </c>
-      <c r="C13" s="22">
+      <c r="B19" s="12">
+        <v>923.28069299999981</v>
+      </c>
+      <c r="C19" s="22">
         <v>1</v>
       </c>
-      <c r="E13" s="24">
-        <v>761.62467300000003</v>
-      </c>
-      <c r="F13" s="25">
-        <v>1</v>
+      <c r="D19" s="29">
+        <v>0.13113444541182484</v>
+      </c>
+      <c r="E19" s="12">
+        <v>121.07390163600019</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="E2:F2"/>
+  <mergeCells count="6">
+    <mergeCell ref="H1:L1"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="R2:V2"/>
+    <mergeCell ref="R1:V1"/>
   </mergeCells>
+  <conditionalFormatting sqref="G4:G12">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Open Positions.xlsx
+++ b/Open Positions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\StockSillines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C935C0-7E1E-4D9F-8B9C-A41E0CDE580F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39C45243-A628-4F28-9D91-00311C8EF72A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Positions" sheetId="1" r:id="rId1"/>
@@ -18,11 +18,11 @@
     <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Positions!$A$1:$T$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Positions!$A$1:$T$46</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="10" r:id="rId4"/>
+    <pivotCache cacheId="5" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="132">
   <si>
     <t>Name</t>
   </si>
@@ -394,21 +394,12 @@
     <t>ETF</t>
   </si>
   <si>
-    <t>ETF1</t>
-  </si>
-  <si>
     <t>BOTZ.UK</t>
   </si>
   <si>
-    <t>ETF2</t>
-  </si>
-  <si>
     <t>BATT.NL</t>
   </si>
   <si>
-    <t>ETF3</t>
-  </si>
-  <si>
     <t>VBTC.DE</t>
   </si>
   <si>
@@ -418,9 +409,6 @@
     <t>BONDS</t>
   </si>
   <si>
-    <t>Emerging Markets</t>
-  </si>
-  <si>
     <t>VWO.US</t>
   </si>
   <si>
@@ -440,6 +428,18 @@
   </si>
   <si>
     <t>Delta</t>
+  </si>
+  <si>
+    <t>Robotics &amp; AI</t>
+  </si>
+  <si>
+    <t>Batterey Value-Chain</t>
+  </si>
+  <si>
+    <t>Emergin Markets</t>
+  </si>
+  <si>
+    <t>Bitcoin ETF</t>
   </si>
 </sst>
 </file>
@@ -590,7 +590,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -654,15 +654,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -670,22 +661,28 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="12">
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
+  <dxfs count="9">
     <dxf>
       <alignment vertical="center"/>
     </dxf>
@@ -727,23 +724,23 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="samuel walton" refreshedDate="45686.939110069441" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="47" xr:uid="{A9649E00-87AB-4DC2-85FE-D21B9DD48B57}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="samuel walton" refreshedDate="45691.704963310185" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{A9649E00-87AB-4DC2-85FE-D21B9DD48B57}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:T1048576" sheet="Positions"/>
   </cacheSource>
   <cacheFields count="22">
     <cacheField name="Chapter" numFmtId="0">
       <sharedItems containsBlank="1" count="11">
+        <s v="ETF"/>
         <s v="Banking"/>
         <s v="Energy"/>
         <s v="US Consumer"/>
         <s v="Tech"/>
+        <s v="Health"/>
         <s v="Asia Consumer"/>
         <s v="Forex"/>
         <s v="Automotive"/>
         <s v="Industrials"/>
-        <s v="Health"/>
-        <s v="ETF"/>
         <m/>
       </sharedItems>
     </cacheField>
@@ -752,24 +749,31 @@
     </cacheField>
     <cacheField name="Ticker" numFmtId="0">
       <sharedItems containsBlank="1" count="46">
+        <s v="BOTZ.UK"/>
+        <s v="BATT.NL"/>
         <s v="ING"/>
         <s v="APA"/>
         <s v="MO"/>
-        <s v="MAXN"/>
+        <s v="VWO.US"/>
+        <s v="VBTC.DE"/>
+        <s v="BONDS"/>
+        <s v="YPF"/>
         <s v="NEE"/>
-        <s v="YPF"/>
         <s v="PEP"/>
         <s v="TSM"/>
         <s v="KMB"/>
+        <s v="AGIO"/>
+        <s v="EXC"/>
         <s v="YUM"/>
-        <s v="V"/>
-        <s v="QCOM"/>
+        <s v="FSLR"/>
         <s v="INGR"/>
         <s v="AAPL"/>
         <s v="MSFT"/>
         <s v="MA"/>
+        <s v="MAXN"/>
+        <s v="V"/>
+        <s v="QCOM"/>
         <s v="GOOGL"/>
-        <s v="FSLR"/>
         <s v="MC.PA"/>
         <s v="ASML"/>
         <s v="NVDA"/>
@@ -787,21 +791,14 @@
         <s v="DAR"/>
         <s v="USDJPY=X"/>
         <s v="MMM"/>
-        <s v="EXC"/>
         <s v="PCG"/>
-        <s v="AGIO"/>
         <s v="ACI"/>
         <s v="HCA"/>
-        <s v="BOTZ.UK"/>
-        <s v="BATT.NL"/>
-        <s v="VBTC.DE"/>
-        <s v="BONDS"/>
-        <s v="VWO.US"/>
         <m/>
       </sharedItems>
     </cacheField>
     <cacheField name="Date" numFmtId="165">
-      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2024-06-17T00:00:00" maxDate="2025-01-10T00:00:00"/>
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2024-06-17T00:00:00" maxDate="2025-02-01T00:00:00"/>
     </cacheField>
     <cacheField name="Volume" numFmtId="164">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="9.9999999999999998E-20" maxValue="2"/>
@@ -822,7 +819,7 @@
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="6.7668155366084726E-2" maxValue="1"/>
     </cacheField>
     <cacheField name="Mix %" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="3.3543196439026418E-3" maxValue="4.9570135697593234E-2"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="3.4439460009693403E-3" maxValue="5.0894634002324905E-2"/>
     </cacheField>
     <cacheField name="Target Price" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="11.602500000000001" maxValue="3017.1900000000005"/>
@@ -863,11 +860,55 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="47">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="48">
   <r>
     <x v="0"/>
+    <s v="Robotics &amp; AI"/>
+    <x v="0"/>
+    <d v="2024-07-08T00:00:00"/>
+    <n v="2"/>
+    <n v="20.928000000000001"/>
+    <n v="41.856000000000002"/>
+    <n v="4.4999999999999998E-2"/>
+    <n v="0.2"/>
+    <n v="0.22499999999999998"/>
+    <n v="1.1451292650523102E-2"/>
+    <n v="21.869759999999999"/>
+    <n v="43.739519999999999"/>
+    <n v="18.119480519480518"/>
+    <n v="0.9417599999999986"/>
+    <n v="-1.4042597402597412"/>
+    <n v="-0.46249974025974261"/>
+    <n v="114.59494482144413"/>
+    <n v="8.7263884245343277E-3"/>
+    <n v="0.80011330398039715"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="Batterey Value-Chain"/>
+    <x v="1"/>
+    <d v="2024-07-08T00:00:00"/>
+    <n v="2"/>
+    <n v="16.399999999999999"/>
+    <n v="32.799999999999997"/>
+    <n v="4.4999999999999998E-2"/>
+    <n v="0.2"/>
+    <n v="0.22499999999999998"/>
+    <n v="1.1451292650523102E-2"/>
+    <n v="17.137999999999998"/>
+    <n v="34.275999999999996"/>
+    <n v="14.199134199134198"/>
+    <n v="0.73799999999999955"/>
+    <n v="-1.1004329004329003"/>
+    <n v="-0.36243290043290077"/>
+    <n v="114.49487798161729"/>
+    <n v="8.7340151597048287E-3"/>
+    <n v="0.79941462735066027"/>
+  </r>
+  <r>
+    <x v="1"/>
     <s v="ING Group NV"/>
-    <x v="0"/>
+    <x v="2"/>
     <d v="2024-11-27T00:00:00"/>
     <n v="1.9595"/>
     <n v="15.3"/>
@@ -875,7 +916,7 @@
     <n v="0.35"/>
     <n v="0.39532299999999998"/>
     <n v="0.88535197800279775"/>
-    <n v="4.3887017689731266E-2"/>
+    <n v="4.5059664883686804E-2"/>
     <n v="20.655000000000001"/>
     <n v="40.4734725"/>
     <n v="14.636624277854791"/>
@@ -887,9 +928,9 @@
     <n v="0.76181081974332665"/>
   </r>
   <r>
-    <x v="1"/>
+    <x v="2"/>
     <s v="APA"/>
-    <x v="1"/>
+    <x v="3"/>
     <d v="2024-12-01T00:00:00"/>
     <n v="1.8976999999999999"/>
     <n v="21.73"/>
@@ -897,7 +938,7 @@
     <n v="0.22319374137137582"/>
     <n v="0.45929999999999999"/>
     <n v="0.48594326447066366"/>
-    <n v="2.4088273561142234E-2"/>
+    <n v="2.4731904591129405E-2"/>
     <n v="26.58"/>
     <n v="50.440865999999993"/>
     <n v="17.579394852436032"/>
@@ -909,9 +950,9 @@
     <n v="0.77751087134654673"/>
   </r>
   <r>
-    <x v="2"/>
+    <x v="3"/>
     <s v="Altaria"/>
-    <x v="2"/>
+    <x v="4"/>
     <d v="2024-09-18T00:00:00"/>
     <n v="1.7345999999999999"/>
     <n v="51.88"/>
@@ -919,7 +960,7 @@
     <n v="0.18430000000000002"/>
     <n v="0.19980000000000001"/>
     <n v="0.92242242242242245"/>
-    <n v="4.5724604649982147E-2"/>
+    <n v="4.6946351584727132E-2"/>
     <n v="61.441483999999996"/>
     <n v="106.57639814639998"/>
     <n v="51.088133924175295"/>
@@ -931,31 +972,97 @@
     <n v="0.73288929623425103"/>
   </r>
   <r>
-    <x v="1"/>
-    <s v="Maxeon Solar"/>
-    <x v="3"/>
-    <d v="2024-08-07T00:00:00"/>
-    <n v="9.9999999999999998E-20"/>
-    <n v="10.92"/>
-    <n v="1.092E-18"/>
+    <x v="0"/>
+    <s v="Emergin Markets"/>
+    <x v="5"/>
+    <d v="2025-01-31T00:00:00"/>
     <n v="1"/>
-    <n v="1.8652"/>
-    <n v="0.53613553506326406"/>
-    <n v="2.6576311225387755E-2"/>
-    <n v="21.84"/>
-    <n v="2.1840000000000001E-18"/>
-    <n v="5.8546000428908433"/>
-    <n v="10.92"/>
-    <n v="-2.5326999785545783"/>
-    <n v="8.3873000214454212"/>
-    <n v="105.74514505973896"/>
-    <n v="9.456698928684306E-3"/>
-    <n v="0.73832312171768166"/>
+    <n v="44.24"/>
+    <n v="44.24"/>
+    <n v="4.4999999999999998E-2"/>
+    <n v="0.2"/>
+    <n v="0.22499999999999998"/>
+    <n v="1.1451292650523102E-2"/>
+    <n v="46.230800000000002"/>
+    <n v="46.230800000000002"/>
+    <n v="38.303030303030305"/>
+    <n v="1.9908000000000001"/>
+    <n v="-2.9684848484848487"/>
+    <n v="-0.9776848484848486"/>
+    <n v="115.11012992966923"/>
+    <n v="8.6873327361456972E-3"/>
+    <n v="0.80371037765363607"/>
   </r>
   <r>
-    <x v="1"/>
+    <x v="0"/>
+    <s v="Bitcoin ETF"/>
+    <x v="6"/>
+    <d v="2024-07-08T00:00:00"/>
+    <n v="1"/>
+    <n v="48.68"/>
+    <n v="48.68"/>
+    <n v="2.5000000000000001E-2"/>
+    <n v="0.2"/>
+    <n v="0.125"/>
+    <n v="6.3618292502906132E-3"/>
+    <n v="49.896999999999998"/>
+    <n v="49.896999999999998"/>
+    <n v="41.42978723404255"/>
+    <n v="1.2169999999999987"/>
+    <n v="-3.6251063829787249"/>
+    <n v="-2.4081063829787261"/>
+    <n v="116.54055146416312"/>
+    <n v="8.5807042049865865E-3"/>
+    <n v="0.81369772309746791"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="ETF5"/>
+    <x v="7"/>
+    <d v="2024-07-08T00:00:00"/>
+    <n v="1"/>
+    <n v="51.28"/>
+    <n v="51.28"/>
+    <n v="2.5000000000000001E-2"/>
+    <n v="0.2"/>
+    <n v="0.125"/>
+    <n v="6.3618292502906132E-3"/>
+    <n v="52.561999999999998"/>
+    <n v="52.561999999999998"/>
+    <n v="43.642553191489363"/>
+    <n v="1.2819999999999965"/>
+    <n v="-3.8187234042553193"/>
+    <n v="-2.5367234042553228"/>
+    <n v="116.66916848543971"/>
+    <n v="8.5712447682765452E-3"/>
+    <n v="0.81459573993409262"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="YPF"/>
+    <x v="8"/>
+    <d v="2024-12-01T00:00:00"/>
+    <n v="0.95840000000000003"/>
+    <n v="41.76"/>
+    <n v="40.022784000000001"/>
+    <n v="0.1"/>
+    <n v="0.2"/>
+    <n v="0.5"/>
+    <n v="2.5447317001162453E-2"/>
+    <n v="45.936"/>
+    <n v="44.025062400000003"/>
+    <n v="37.963636363636368"/>
+    <n v="4.1760000000000019"/>
+    <n v="-1.8981818181818149"/>
+    <n v="2.2778181818181871"/>
+    <n v="111.8546268993662"/>
+    <n v="8.9401755449927331E-3"/>
+    <n v="0.78098013165759694"/>
+  </r>
+  <r>
+    <x v="2"/>
     <s v="NextEra Energy"/>
-    <x v="4"/>
+    <x v="9"/>
     <d v="2024-08-07T00:00:00"/>
     <n v="0.45179999999999998"/>
     <n v="77.430000000000007"/>
@@ -963,7 +1070,7 @@
     <n v="0.1"/>
     <n v="0.25990000000000002"/>
     <n v="0.38476337052712584"/>
-    <n v="1.9072772488492973E-2"/>
+    <n v="1.9582390920478997E-2"/>
     <n v="85.173000000000016"/>
     <n v="38.481161400000005"/>
     <n v="66.755754806448849"/>
@@ -975,31 +1082,9 @@
     <n v="0.78008600943515383"/>
   </r>
   <r>
-    <x v="1"/>
-    <s v="YPF"/>
-    <x v="5"/>
-    <d v="2024-12-01T00:00:00"/>
-    <n v="0.71050000000000002"/>
-    <n v="42.26"/>
-    <n v="30.025729999999999"/>
-    <n v="0.1"/>
-    <n v="0.2"/>
-    <n v="0.5"/>
-    <n v="2.4785067848796617E-2"/>
-    <n v="46.486000000000004"/>
-    <n v="33.028303000000001"/>
-    <n v="38.418181818181822"/>
-    <n v="4.2260000000000062"/>
-    <n v="-1.9209090909090882"/>
-    <n v="2.305090909090918"/>
-    <n v="111.82735417209346"/>
-    <n v="8.9423558967609926E-3"/>
-    <n v="0.78078971076284676"/>
-  </r>
-  <r>
-    <x v="2"/>
+    <x v="3"/>
     <s v="Pepsi"/>
-    <x v="6"/>
+    <x v="10"/>
     <d v="2024-06-17T00:00:00"/>
     <n v="0.43659999999999999"/>
     <n v="160.25"/>
@@ -1007,7 +1092,7 @@
     <n v="6.7199999999999996E-2"/>
     <n v="0.16439999999999999"/>
     <n v="0.40875912408759124"/>
-    <n v="2.0262245248651251E-2"/>
+    <n v="2.0803646015548866E-2"/>
     <n v="171.0188"/>
     <n v="74.666808079999996"/>
     <n v="146.05359095880419"/>
@@ -1019,9 +1104,9 @@
     <n v="0.7712556220204998"/>
   </r>
   <r>
-    <x v="3"/>
+    <x v="4"/>
     <s v="TSMC"/>
-    <x v="7"/>
+    <x v="11"/>
     <d v="2024-07-11T00:00:00"/>
     <n v="0.4108"/>
     <n v="189.76"/>
@@ -1029,7 +1114,7 @@
     <n v="0.19835581787521095"/>
     <n v="0.37"/>
     <n v="0.53609680506813773"/>
-    <n v="2.6574391374273774E-2"/>
+    <n v="2.728445068375859E-2"/>
     <n v="227.4"/>
     <n v="93.41592"/>
     <n v="161.96043380326287"/>
@@ -1037,13 +1122,13 @@
     <n v="-13.899783098368559"/>
     <n v="23.740216901631456"/>
     <n v="90.39222817955293"/>
-    <n v="1.10628979962041E-2"/>
+    <n v="1.1062897996204102E-2"/>
     <n v="0.6311275288415521"/>
   </r>
   <r>
-    <x v="2"/>
+    <x v="3"/>
     <s v="Kimberly Clark"/>
-    <x v="8"/>
+    <x v="12"/>
     <d v="2024-09-09T00:00:00"/>
     <n v="0.35149999999999998"/>
     <n v="142.78"/>
@@ -1051,7 +1136,7 @@
     <n v="7.0000000000000007E-2"/>
     <n v="0.18340000000000001"/>
     <n v="0.38167938931297712"/>
-    <n v="1.8919899121218792E-2"/>
+    <n v="1.9425432825314851E-2"/>
     <n v="152.77460000000002"/>
     <n v="53.700271900000004"/>
     <n v="128.23783007005568"/>
@@ -1063,9 +1148,53 @@
     <n v="0.77786823189316223"/>
   </r>
   <r>
-    <x v="4"/>
+    <x v="5"/>
+    <s v="Agios"/>
+    <x v="13"/>
+    <d v="2024-12-04T00:00:00"/>
+    <n v="0.28749999999999998"/>
+    <n v="34.78"/>
+    <n v="9.99925"/>
+    <n v="0.2"/>
+    <n v="0.2"/>
+    <n v="1"/>
+    <n v="5.0894634002324905E-2"/>
+    <n v="41.735999999999997"/>
+    <n v="11.999099999999999"/>
+    <n v="34.78"/>
+    <n v="6.955999999999996"/>
+    <n v="0"/>
+    <n v="6.955999999999996"/>
+    <n v="107.1764450811844"/>
+    <n v="9.3304083676456744E-3"/>
+    <n v="0.74831660084479601"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="Excelon"/>
+    <x v="14"/>
+    <d v="2024-12-01T00:00:00"/>
+    <n v="0.27450000000000002"/>
+    <n v="39.799999999999997"/>
+    <n v="10.9251"/>
+    <n v="0.1"/>
+    <n v="0.2"/>
+    <n v="0.5"/>
+    <n v="2.5447317001162453E-2"/>
+    <n v="43.78"/>
+    <n v="12.017610000000001"/>
+    <n v="36.181818181818187"/>
+    <n v="3.980000000000004"/>
+    <n v="-1.8090909090909051"/>
+    <n v="2.1709090909090989"/>
+    <n v="111.96153599027528"/>
+    <n v="8.931638809303739E-3"/>
+    <n v="0.78172658156501729"/>
+  </r>
+  <r>
+    <x v="6"/>
     <s v="Yum! Brands"/>
-    <x v="9"/>
+    <x v="15"/>
     <d v="2024-10-15T00:00:00"/>
     <n v="0.25669999999999998"/>
     <n v="132.38999999999999"/>
@@ -1073,7 +1202,7 @@
     <n v="7.0000000000000007E-2"/>
     <n v="0.1623"/>
     <n v="0.43130006161429457"/>
-    <n v="2.1379602580600905E-2"/>
+    <n v="2.1950858781039705E-2"/>
     <n v="141.65729999999999"/>
     <n v="36.363428909999996"/>
     <n v="121.20296621807194"/>
@@ -1085,9 +1214,141 @@
     <n v="0.77123336567330925"/>
   </r>
   <r>
-    <x v="0"/>
+    <x v="2"/>
+    <s v="First Solar"/>
+    <x v="16"/>
+    <d v="2024-08-07T00:00:00"/>
+    <n v="0.25169999999999998"/>
+    <n v="178.56"/>
+    <n v="44.943551999999997"/>
+    <n v="9.7782258064516236E-2"/>
+    <n v="0.52980000000000005"/>
+    <n v="0.18456447350795815"/>
+    <n v="9.3933413290193217E-3"/>
+    <n v="196.02"/>
+    <n v="49.338234"/>
+    <n v="124.69119255370553"/>
+    <n v="17.460000000000008"/>
+    <n v="-26.934403723147234"/>
+    <n v="-9.4744037231472262"/>
+    <n v="123.60684880433161"/>
+    <n v="8.0901666022000929E-3"/>
+    <n v="0.86303531404059042"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <s v="MSG"/>
+    <x v="17"/>
+    <d v="2024-10-15T00:00:00"/>
+    <n v="0.19139999999999999"/>
+    <n v="135.82"/>
+    <n v="25.995947999999999"/>
+    <n v="0.1202"/>
+    <n v="0.33710000000000001"/>
+    <n v="0.35657075051913378"/>
+    <n v="1.8147537843605618E-2"/>
+    <n v="152.14556400000001"/>
+    <n v="29.120660949599998"/>
+    <n v="111.61147177253677"/>
+    <n v="16.325564000000014"/>
+    <n v="-12.10426411373161"/>
+    <n v="4.2212998862684046"/>
+    <n v="109.91114519491597"/>
+    <n v="9.0982583997883393E-3"/>
+    <n v="0.76741054907089512"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="Apple2"/>
+    <x v="18"/>
+    <d v="2024-07-09T00:00:00"/>
+    <n v="0.18820000000000001"/>
+    <n v="227.38"/>
+    <n v="42.792915999999998"/>
+    <n v="0.15"/>
+    <n v="0.2271"/>
+    <n v="0.66050198150594452"/>
+    <n v="3.3616006606555421E-2"/>
+    <n v="261.48699999999997"/>
+    <n v="49.211853399999995"/>
+    <n v="211.10389007520189"/>
+    <n v="34.106999999999971"/>
+    <n v="-8.1380549623990532"/>
+    <n v="25.968945037600918"/>
+    <n v="88.163500043583468"/>
+    <n v="1.1342562392664218E-2"/>
+    <n v="0.6155663272953309"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="Microsoft"/>
+    <x v="19"/>
+    <d v="2024-10-09T00:00:00"/>
+    <n v="0.13370000000000001"/>
+    <n v="423.77"/>
+    <n v="56.658049000000005"/>
+    <n v="0.15"/>
+    <n v="0.1963"/>
+    <n v="0.76413652572592972"/>
+    <n v="3.8890448804629323E-2"/>
+    <n v="487.33549999999991"/>
+    <n v="65.156756349999995"/>
+    <n v="405.01768135334032"/>
+    <n v="63.565499999999929"/>
+    <n v="-9.3761593233298299"/>
+    <n v="54.189340676670099"/>
+    <n v="59.943104404514287"/>
+    <n v="1.6682485999585474E-2"/>
+    <n v="0.41852871774290379"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Master Card"/>
+    <x v="20"/>
+    <d v="2024-08-07T00:00:00"/>
+    <n v="0.12939999999999999"/>
+    <n v="501.56"/>
+    <n v="64.901863999999989"/>
+    <n v="0.25"/>
+    <n v="0.29699999999999999"/>
+    <n v="0.84175084175084181"/>
+    <n v="4.2840601012058006E-2"/>
+    <n v="626.95000000000005"/>
+    <n v="81.127330000000001"/>
+    <n v="479.04489016236869"/>
+    <n v="125.39000000000004"/>
+    <n v="-11.257554918815657"/>
+    <n v="114.13244508118439"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="Maxeon Solar"/>
+    <x v="21"/>
+    <d v="2024-08-07T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="10.92"/>
+    <n v="1.092E-18"/>
+    <n v="1"/>
+    <n v="1.8652"/>
+    <n v="0.53613553506326406"/>
+    <n v="2.7286421832685457E-2"/>
+    <n v="21.84"/>
+    <n v="2.1840000000000001E-18"/>
+    <n v="5.8546000428908433"/>
+    <n v="10.92"/>
+    <n v="-2.5326999785545783"/>
+    <n v="8.3873000214454212"/>
+    <n v="105.74514505973896"/>
+    <n v="9.4566989286843078E-3"/>
+    <n v="0.73832312171768166"/>
+  </r>
+  <r>
+    <x v="1"/>
     <s v="Visa"/>
-    <x v="10"/>
+    <x v="22"/>
     <d v="2024-08-07T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="283.43"/>
@@ -1095,7 +1356,7 @@
     <n v="0.25"/>
     <n v="0.26"/>
     <n v="0.96153846153846145"/>
-    <n v="4.766359201691657E-2"/>
+    <n v="4.8937148079158561E-2"/>
     <n v="354.28750000000002"/>
     <n v="3.542875E-17"/>
     <n v="280.62376237623761"/>
@@ -1107,9 +1368,9 @@
     <n v="0.311946686414727"/>
   </r>
   <r>
-    <x v="3"/>
+    <x v="4"/>
     <s v="QualComm2"/>
-    <x v="11"/>
+    <x v="23"/>
     <d v="2024-09-09T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="188.12"/>
@@ -1117,7 +1378,7 @@
     <n v="0.15"/>
     <n v="0.37780000000000002"/>
     <n v="0.39703546850185278"/>
-    <n v="1.9681102050394347E-2"/>
+    <n v="2.0206974855343396E-2"/>
     <n v="216.33799999999999"/>
     <n v="2.16338E-17"/>
     <n v="153.21713634142367"/>
@@ -1125,101 +1386,13 @@
     <n v="-17.451431829288168"/>
     <n v="10.766568170711821"/>
     <n v="103.36587691047256"/>
-    <n v="9.6743725288193673E-3"/>
+    <n v="9.674372528819369E-3"/>
     <n v="0.72171083482377829"/>
   </r>
   <r>
     <x v="4"/>
-    <s v="MSG"/>
-    <x v="12"/>
-    <d v="2024-10-15T00:00:00"/>
-    <n v="0.19139999999999999"/>
-    <n v="135.82"/>
-    <n v="25.995947999999999"/>
-    <n v="0.1202"/>
-    <n v="0.33710000000000001"/>
-    <n v="0.35657075051913378"/>
-    <n v="1.7675260489026123E-2"/>
-    <n v="152.14556400000001"/>
-    <n v="29.120660949599998"/>
-    <n v="111.61147177253677"/>
-    <n v="16.325564000000014"/>
-    <n v="-12.10426411373161"/>
-    <n v="4.2212998862684046"/>
-    <n v="109.91114519491597"/>
-    <n v="9.0982583997883375E-3"/>
-    <n v="0.76741054907089512"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <s v="Apple2"/>
-    <x v="13"/>
-    <d v="2024-07-09T00:00:00"/>
-    <n v="0.18820000000000001"/>
-    <n v="227.38"/>
-    <n v="42.792915999999998"/>
-    <n v="0.15"/>
-    <n v="0.2271"/>
-    <n v="0.66050198150594452"/>
-    <n v="3.2741172851778889E-2"/>
-    <n v="261.48699999999997"/>
-    <n v="49.211853399999995"/>
-    <n v="211.10389007520189"/>
-    <n v="34.106999999999971"/>
-    <n v="-8.1380549623990532"/>
-    <n v="25.968945037600918"/>
-    <n v="88.163500043583468"/>
-    <n v="1.1342562392664218E-2"/>
-    <n v="0.6155663272953309"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <s v="Microsoft"/>
-    <x v="14"/>
-    <d v="2024-10-09T00:00:00"/>
-    <n v="0.13370000000000001"/>
-    <n v="423.77"/>
-    <n v="56.658049000000005"/>
-    <n v="0.15"/>
-    <n v="0.1963"/>
-    <n v="0.76413652572592972"/>
-    <n v="3.7878351271721782E-2"/>
-    <n v="487.33549999999991"/>
-    <n v="65.156756349999995"/>
-    <n v="405.01768135334032"/>
-    <n v="63.565499999999929"/>
-    <n v="-9.3761593233298299"/>
-    <n v="54.189340676670099"/>
-    <n v="59.943104404514287"/>
-    <n v="1.6682485999585477E-2"/>
-    <n v="0.41852871774290379"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <s v="Master Card"/>
-    <x v="15"/>
-    <d v="2024-08-07T00:00:00"/>
-    <n v="0.12939999999999999"/>
-    <n v="501.56"/>
-    <n v="64.901863999999989"/>
-    <n v="0.25"/>
-    <n v="0.29699999999999999"/>
-    <n v="0.84175084175084181"/>
-    <n v="4.1725703449152558E-2"/>
-    <n v="626.95000000000005"/>
-    <n v="81.127330000000001"/>
-    <n v="479.04489016236869"/>
-    <n v="125.39000000000004"/>
-    <n v="-11.257554918815657"/>
-    <n v="114.13244508118439"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="3"/>
     <s v="Google"/>
-    <x v="16"/>
+    <x v="24"/>
     <d v="2024-07-10T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="167.24"/>
@@ -1227,7 +1400,7 @@
     <n v="0.13854341066730447"/>
     <n v="0.26790000000000003"/>
     <n v="0.51714598979956872"/>
-    <n v="2.5634996889830789E-2"/>
+    <n v="2.6319955876619099E-2"/>
     <n v="190.41"/>
     <n v="1.9040999999999999E-17"/>
     <n v="148.08431772538498"/>
@@ -1239,31 +1412,9 @@
     <n v="0.70198227953907921"/>
   </r>
   <r>
-    <x v="1"/>
-    <s v="First Solar"/>
-    <x v="17"/>
-    <d v="2024-08-07T00:00:00"/>
-    <n v="0.25169999999999998"/>
-    <n v="178.56"/>
-    <n v="44.943551999999997"/>
-    <n v="9.7782258064516236E-2"/>
-    <n v="0.52980000000000005"/>
-    <n v="0.18456447350795815"/>
-    <n v="9.1488859967443371E-3"/>
-    <n v="196.02"/>
-    <n v="49.338234"/>
-    <n v="124.69119255370553"/>
-    <n v="17.460000000000008"/>
-    <n v="-26.934403723147234"/>
-    <n v="-9.4744037231472262"/>
-    <n v="123.60684880433161"/>
-    <n v="8.0901666022000929E-3"/>
-    <n v="0.86303531404059042"/>
-  </r>
-  <r>
-    <x v="4"/>
+    <x v="6"/>
     <s v="LVMH"/>
-    <x v="18"/>
+    <x v="25"/>
     <d v="2024-09-27T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="668.82"/>
@@ -1271,7 +1422,7 @@
     <n v="0.05"/>
     <n v="0.28000000000000003"/>
     <n v="0.17857142857142858"/>
-    <n v="8.8518099459987919E-3"/>
+    <n v="9.0883275004151626E-3"/>
     <n v="702.26100000000008"/>
     <n v="7.0226100000000009E-17"/>
     <n v="543.7560975609756"/>
@@ -1279,13 +1430,13 @@
     <n v="-62.531951219512223"/>
     <n v="-29.090951219512192"/>
     <n v="143.22339630069658"/>
-    <n v="6.9820994741704532E-3"/>
+    <n v="6.9820994741704541E-3"/>
     <n v="1"/>
   </r>
   <r>
-    <x v="3"/>
+    <x v="4"/>
     <s v="ASML"/>
-    <x v="19"/>
+    <x v="26"/>
     <d v="2024-07-08T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="700.32"/>
@@ -1293,7 +1444,7 @@
     <n v="0.1"/>
     <n v="0.45340000000000003"/>
     <n v="0.22055580061755625"/>
-    <n v="1.0932980965503582E-2"/>
+    <n v="1.1225106749520271E-2"/>
     <n v="770.35200000000009"/>
     <n v="7.7035200000000004E-17"/>
     <n v="517.45234224915032"/>
@@ -1305,9 +1456,9 @@
     <n v="0.94631378292451529"/>
   </r>
   <r>
-    <x v="3"/>
+    <x v="4"/>
     <s v="Nvidia"/>
-    <x v="20"/>
+    <x v="27"/>
     <d v="2024-07-09T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="147.01"/>
@@ -1315,7 +1466,7 @@
     <n v="0.15"/>
     <n v="0.52380000000000004"/>
     <n v="0.28636884306987398"/>
-    <n v="1.4195342410536434E-2"/>
+    <n v="1.4574637457710454E-2"/>
     <n v="169.06149999999997"/>
     <n v="1.6906149999999997E-17"/>
     <n v="107.00975396709855"/>
@@ -1327,9 +1478,9 @@
     <n v="0.78256116662896091"/>
   </r>
   <r>
-    <x v="3"/>
+    <x v="4"/>
     <s v="Applied Material"/>
-    <x v="21"/>
+    <x v="28"/>
     <d v="2024-07-08T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="169.34"/>
@@ -1337,7 +1488,7 @@
     <n v="0.1"/>
     <n v="0.4259"/>
     <n v="0.23479690068091102"/>
-    <n v="1.1638914228127082E-2"/>
+    <n v="1.1949902325035199E-2"/>
     <n v="186.27400000000003"/>
     <n v="1.8627400000000003E-17"/>
     <n v="127.71702239987934"/>
@@ -1349,9 +1500,9 @@
     <n v="0.82395709729912847"/>
   </r>
   <r>
-    <x v="1"/>
+    <x v="2"/>
     <s v="Duke Energy"/>
-    <x v="22"/>
+    <x v="29"/>
     <d v="2024-08-07T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="113.58"/>
@@ -1359,7 +1510,7 @@
     <n v="6.664905793273479E-2"/>
     <n v="0.16439999999999999"/>
     <n v="0.40540789496797319"/>
-    <n v="2.0096124366438057E-2"/>
+    <n v="2.0633086436047974E-2"/>
     <n v="121.15000000000002"/>
     <n v="1.2115000000000002E-17"/>
     <n v="103.46609203186667"/>
@@ -1371,9 +1522,9 @@
     <n v="0.77933774752071117"/>
   </r>
   <r>
-    <x v="3"/>
+    <x v="4"/>
     <s v="Palantir"/>
-    <x v="23"/>
+    <x v="30"/>
     <d v="2024-07-08T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="64.349999999999994"/>
@@ -1381,7 +1532,7 @@
     <n v="0.15"/>
     <n v="0.67300000000000004"/>
     <n v="0.22288261515601782"/>
-    <n v="1.1048321477918253E-2"/>
+    <n v="1.1343529123846561E-2"/>
     <n v="74.002499999999984"/>
     <n v="7.4002499999999988E-18"/>
     <n v="42.252133946158892"/>
@@ -1393,9 +1544,9 @@
     <n v="0.80663411909010196"/>
   </r>
   <r>
-    <x v="1"/>
+    <x v="2"/>
     <s v="Jinko Solar"/>
-    <x v="24"/>
+    <x v="31"/>
     <d v="2024-08-07T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="20.82"/>
@@ -1403,7 +1554,7 @@
     <n v="0.05"/>
     <n v="0.7389"/>
     <n v="6.7668155366084726E-2"/>
-    <n v="3.3543196439026418E-3"/>
+    <n v="3.4439460009693403E-3"/>
     <n v="21.861000000000001"/>
     <n v="2.1860999999999999E-18"/>
     <n v="12.327550476641601"/>
@@ -1415,9 +1566,9 @@
     <n v="0.81926328291024408"/>
   </r>
   <r>
-    <x v="1"/>
+    <x v="2"/>
     <s v="SolarWinds"/>
-    <x v="25"/>
+    <x v="32"/>
     <d v="2024-08-07T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="13.04"/>
@@ -1425,7 +1576,7 @@
     <n v="5.2147239263803824E-2"/>
     <n v="0.30159999999999998"/>
     <n v="0.17290198694895167"/>
-    <n v="8.5707749554430283E-3"/>
+    <n v="8.7997833440416531E-3"/>
     <n v="13.72"/>
     <n v="1.3720000000000001E-18"/>
     <n v="10.436569040286594"/>
@@ -1437,9 +1588,9 @@
     <n v="0.80122496411211674"/>
   </r>
   <r>
-    <x v="1"/>
+    <x v="2"/>
     <s v="Canadian Solar"/>
-    <x v="26"/>
+    <x v="33"/>
     <d v="2024-08-07T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="11.05"/>
@@ -1447,7 +1598,7 @@
     <n v="0.05"/>
     <n v="0.72170000000000001"/>
     <n v="6.9280864625190522E-2"/>
-    <n v="3.434261860717281E-3"/>
+    <n v="3.5260242484636906E-3"/>
     <n v="11.602500000000001"/>
     <n v="1.16025E-18"/>
     <n v="6.6100376861877139"/>
@@ -1459,17 +1610,17 @@
     <n v="0.80852660409594923"/>
   </r>
   <r>
-    <x v="5"/>
+    <x v="7"/>
     <s v="Gold"/>
-    <x v="27"/>
-    <d v="2025-01-09T00:00:00"/>
+    <x v="34"/>
+    <d v="2025-01-14T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="2742.9"/>
     <n v="2.7429000000000002E-16"/>
     <n v="0.1"/>
     <n v="0.5"/>
     <n v="0.2"/>
-    <n v="9.9140271395186472E-3"/>
+    <n v="1.0178926800464982E-2"/>
     <n v="3017.1900000000005"/>
     <n v="3.0171900000000003E-16"/>
     <n v="1959.214285714286"/>
@@ -1481,9 +1632,9 @@
     <n v="1.6176498268314992"/>
   </r>
   <r>
-    <x v="2"/>
+    <x v="3"/>
     <s v="Walmart"/>
-    <x v="28"/>
+    <x v="35"/>
     <d v="2024-08-01T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="86.6"/>
@@ -1491,7 +1642,7 @@
     <n v="7.0000000000000007E-2"/>
     <n v="0.17249999999999999"/>
     <n v="0.40579710144927544"/>
-    <n v="2.0115417384530591E-2"/>
+    <n v="2.0652894957465185E-2"/>
     <n v="92.662000000000006"/>
     <n v="9.2662000000000008E-18"/>
     <n v="78.548752834467123"/>
@@ -1499,13 +1650,13 @@
     <n v="-4.0256235827664355"/>
     <n v="2.0363764172335763"/>
     <n v="112.0960686639508"/>
-    <n v="8.9209194570227784E-3"/>
+    <n v="8.9209194570227766E-3"/>
     <n v="0.78266590207514586"/>
   </r>
   <r>
-    <x v="6"/>
+    <x v="8"/>
     <s v="Aptive Autoparts"/>
-    <x v="29"/>
+    <x v="36"/>
     <d v="2024-09-27T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="56"/>
@@ -1513,7 +1664,7 @@
     <n v="7.0000000000000007E-2"/>
     <n v="0.19"/>
     <n v="0.36842105263157898"/>
-    <n v="1.826268157279751E-2"/>
+    <n v="1.8750654632435495E-2"/>
     <n v="59.92"/>
     <n v="5.9920000000000002E-18"/>
     <n v="50.000000000000007"/>
@@ -1525,9 +1676,9 @@
     <n v="0.79046055327088882"/>
   </r>
   <r>
-    <x v="5"/>
+    <x v="7"/>
     <s v="Mexican Peso"/>
-    <x v="30"/>
+    <x v="37"/>
     <d v="2024-10-15T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="20.399999999999999"/>
@@ -1535,7 +1686,7 @@
     <n v="0.1"/>
     <n v="0.15"/>
     <n v="0.66666666666666674"/>
-    <n v="3.3046757131728825E-2"/>
+    <n v="3.3929756001549939E-2"/>
     <n v="21.2"/>
     <n v="2.1199999999999999E-18"/>
     <n v="19.428571428571431"/>
@@ -1543,13 +1694,13 @@
     <n v="-0.48571428571428399"/>
     <n v="0.31428571428571672"/>
     <n v="113.81815936689867"/>
-    <n v="8.7859442250902038E-3"/>
+    <n v="8.7859442250902055E-3"/>
     <n v="0.79468971066667204"/>
   </r>
   <r>
-    <x v="4"/>
+    <x v="6"/>
     <s v="Yum China Holding"/>
-    <x v="31"/>
+    <x v="38"/>
     <d v="2024-10-09T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="47.42"/>
@@ -1557,7 +1708,7 @@
     <n v="7.0000000000000007E-2"/>
     <n v="0.4"/>
     <n v="0.17500000000000002"/>
-    <n v="8.6747737470788174E-3"/>
+    <n v="8.90656095040686E-3"/>
     <n v="50.739400000000003"/>
     <n v="5.0739400000000001E-18"/>
     <n v="35.654135338345867"/>
@@ -1565,13 +1716,13 @@
     <n v="-5.8829323308270673"/>
     <n v="-2.5635323308270657"/>
     <n v="116.69597741201144"/>
-    <n v="8.5692756697976005E-3"/>
+    <n v="8.5692756697975988E-3"/>
     <n v="0.81478292252621221"/>
   </r>
   <r>
-    <x v="4"/>
+    <x v="6"/>
     <s v="MSG"/>
-    <x v="32"/>
+    <x v="39"/>
     <d v="2024-08-03T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="41.8"/>
@@ -1579,7 +1730,7 @@
     <n v="7.0000000000000007E-2"/>
     <n v="0.4"/>
     <n v="0.17500000000000002"/>
-    <n v="8.6747737470788174E-3"/>
+    <n v="8.90656095040686E-3"/>
     <n v="44.725999999999999"/>
     <n v="4.4725999999999996E-18"/>
     <n v="31.428571428571431"/>
@@ -1587,13 +1738,13 @@
     <n v="-5.1857142857142833"/>
     <n v="-2.2597142857142813"/>
     <n v="116.39215936689867"/>
-    <n v="8.5916440200042785E-3"/>
+    <n v="8.5916440200042802E-3"/>
     <n v="0.81266163471318675"/>
   </r>
   <r>
-    <x v="5"/>
+    <x v="7"/>
     <s v="Japan Yen"/>
-    <x v="33"/>
+    <x v="40"/>
     <d v="2024-10-09T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="153.7552"/>
@@ -1601,7 +1752,7 @@
     <n v="7.0000000000000007E-2"/>
     <n v="0.19"/>
     <n v="0.36842105263157898"/>
-    <n v="1.826268157279751E-2"/>
+    <n v="1.8750654632435495E-2"/>
     <n v="164.51806400000001"/>
     <n v="1.6451806399999999E-17"/>
     <n v="137.28142857142859"/>
@@ -1613,9 +1764,9 @@
     <n v="0.77924745312667376"/>
   </r>
   <r>
-    <x v="7"/>
+    <x v="9"/>
     <s v="3M"/>
-    <x v="34"/>
+    <x v="41"/>
     <d v="2024-12-01T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="133.53"/>
@@ -1623,7 +1774,7 @@
     <n v="7.0000000000000007E-2"/>
     <n v="0.2"/>
     <n v="0.35000000000000003"/>
-    <n v="1.7349547494157635E-2"/>
+    <n v="1.781312190081372E-2"/>
     <n v="142.87710000000001"/>
     <n v="1.428771E-17"/>
     <n v="118.16814159292036"/>
@@ -1635,31 +1786,9 @@
     <n v="0.78525071454528272"/>
   </r>
   <r>
-    <x v="1"/>
-    <s v="Excelon"/>
-    <x v="35"/>
-    <d v="2024-12-01T00:00:00"/>
-    <n v="0.27450000000000002"/>
-    <n v="39.799999999999997"/>
-    <n v="10.9251"/>
-    <n v="0.1"/>
-    <n v="0.2"/>
-    <n v="0.5"/>
-    <n v="2.4785067848796617E-2"/>
-    <n v="43.78"/>
-    <n v="12.017610000000001"/>
-    <n v="36.181818181818187"/>
-    <n v="3.980000000000004"/>
-    <n v="-1.8090909090909051"/>
-    <n v="2.1709090909090989"/>
-    <n v="111.96153599027528"/>
-    <n v="8.931638809303739E-3"/>
-    <n v="0.78172658156501729"/>
-  </r>
-  <r>
-    <x v="1"/>
+    <x v="2"/>
     <s v="PG&amp;E"/>
-    <x v="36"/>
+    <x v="42"/>
     <d v="2024-12-01T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="26.63"/>
@@ -1667,7 +1796,7 @@
     <n v="0.1"/>
     <n v="0.2"/>
     <n v="0.5"/>
-    <n v="2.4785067848796617E-2"/>
+    <n v="2.5447317001162453E-2"/>
     <n v="29.293000000000003"/>
     <n v="2.9293000000000003E-18"/>
     <n v="24.209090909090911"/>
@@ -1675,35 +1804,13 @@
     <n v="-1.2104545454545441"/>
     <n v="1.4525454545454597"/>
     <n v="112.67989962663893"/>
-    <n v="8.8746972912956655E-3"/>
+    <n v="8.8746972912956672E-3"/>
     <n v="0.78674226793273505"/>
   </r>
   <r>
-    <x v="8"/>
-    <s v="Agios"/>
-    <x v="37"/>
-    <d v="2024-12-04T00:00:00"/>
-    <n v="9.9999999999999998E-20"/>
-    <n v="59.17"/>
-    <n v="5.9170000000000002E-18"/>
-    <n v="0.2"/>
-    <n v="0.2"/>
-    <n v="1"/>
-    <n v="4.9570135697593234E-2"/>
-    <n v="71.004000000000005"/>
-    <n v="7.1003999999999996E-18"/>
-    <n v="59.17"/>
-    <n v="11.834000000000003"/>
-    <n v="0"/>
-    <n v="11.834000000000003"/>
-    <n v="102.29844508118438"/>
-    <n v="9.7753196464168812E-3"/>
-    <n v="0.71425791960979246"/>
-  </r>
-  <r>
-    <x v="2"/>
+    <x v="3"/>
     <s v="Albertson Companies"/>
-    <x v="38"/>
+    <x v="43"/>
     <d v="2024-12-04T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="19.309999999999999"/>
@@ -1711,7 +1818,7 @@
     <n v="0.2"/>
     <n v="0.2"/>
     <n v="1"/>
-    <n v="4.9570135697593234E-2"/>
+    <n v="5.0894634002324905E-2"/>
     <n v="23.171999999999997"/>
     <n v="2.3171999999999995E-18"/>
     <n v="19.309999999999999"/>
@@ -1723,9 +1830,9 @@
     <n v="0.76991921661787932"/>
   </r>
   <r>
-    <x v="8"/>
+    <x v="5"/>
     <s v="HCA Healthcare"/>
-    <x v="39"/>
+    <x v="44"/>
     <d v="2024-12-04T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="323.75"/>
@@ -1733,7 +1840,7 @@
     <n v="0.2"/>
     <n v="0.2"/>
     <n v="1"/>
-    <n v="4.9570135697593234E-2"/>
+    <n v="5.0894634002324905E-2"/>
     <n v="388.5"/>
     <n v="3.8849999999999999E-17"/>
     <n v="323.75"/>
@@ -1745,114 +1852,26 @@
     <n v="0.34479314383458876"/>
   </r>
   <r>
-    <x v="9"/>
-    <s v="ETF1"/>
-    <x v="40"/>
-    <d v="2024-07-08T00:00:00"/>
-    <n v="2"/>
-    <n v="20.928000000000001"/>
-    <n v="41.856000000000002"/>
-    <n v="4.4999999999999998E-2"/>
-    <n v="0.2"/>
-    <n v="0.22499999999999998"/>
-    <n v="1.1153280531958477E-2"/>
-    <n v="21.869759999999999"/>
-    <n v="43.739519999999999"/>
-    <n v="18.119480519480518"/>
-    <n v="0.9417599999999986"/>
-    <n v="-1.4042597402597412"/>
-    <n v="-0.46249974025974261"/>
-    <n v="114.59494482144413"/>
-    <n v="8.7263884245343277E-3"/>
-    <n v="0.80011330398039715"/>
-  </r>
-  <r>
-    <x v="9"/>
-    <s v="ETF2"/>
-    <x v="41"/>
-    <d v="2024-07-08T00:00:00"/>
-    <n v="2"/>
-    <n v="16.399999999999999"/>
-    <n v="32.799999999999997"/>
-    <n v="4.4999999999999998E-2"/>
-    <n v="0.2"/>
-    <n v="0.22499999999999998"/>
-    <n v="1.1153280531958477E-2"/>
-    <n v="17.137999999999998"/>
-    <n v="34.275999999999996"/>
-    <n v="14.199134199134198"/>
-    <n v="0.73799999999999955"/>
-    <n v="-1.1004329004329003"/>
-    <n v="-0.36243290043290077"/>
-    <n v="114.49487798161729"/>
-    <n v="8.7340151597048287E-3"/>
-    <n v="0.79941462735066027"/>
-  </r>
-  <r>
-    <x v="9"/>
-    <s v="ETF3"/>
-    <x v="42"/>
-    <d v="2024-07-08T00:00:00"/>
-    <n v="1"/>
-    <n v="48.68"/>
-    <n v="48.68"/>
-    <n v="2.5000000000000001E-2"/>
-    <n v="0.2"/>
-    <n v="0.125"/>
-    <n v="6.1962669621991543E-3"/>
-    <n v="49.896999999999998"/>
-    <n v="49.896999999999998"/>
-    <n v="41.42978723404255"/>
-    <n v="1.2169999999999987"/>
-    <n v="-3.6251063829787249"/>
-    <n v="-2.4081063829787261"/>
-    <n v="116.54055146416312"/>
-    <n v="8.5807042049865865E-3"/>
-    <n v="0.81369772309746791"/>
-  </r>
-  <r>
-    <x v="9"/>
-    <s v="ETF5"/>
-    <x v="43"/>
-    <d v="2024-07-08T00:00:00"/>
-    <n v="1"/>
-    <n v="51.28"/>
-    <n v="51.28"/>
-    <n v="2.5000000000000001E-2"/>
-    <n v="0.2"/>
-    <n v="0.125"/>
-    <n v="6.1962669621991543E-3"/>
-    <n v="52.561999999999998"/>
-    <n v="52.561999999999998"/>
-    <n v="43.642553191489363"/>
-    <n v="1.2819999999999965"/>
-    <n v="-3.8187234042553193"/>
-    <n v="-2.5367234042553228"/>
-    <n v="116.66916848543971"/>
-    <n v="8.571244768276547E-3"/>
-    <n v="0.81459573993409262"/>
-  </r>
-  <r>
-    <x v="9"/>
-    <s v="Emerging Markets"/>
-    <x v="44"/>
-    <d v="2024-07-08T00:00:00"/>
-    <n v="1"/>
-    <n v="44.14"/>
-    <n v="44.14"/>
-    <n v="0.15"/>
-    <n v="0.2"/>
-    <n v="0.74999999999999989"/>
-    <n v="3.7177601773194922E-2"/>
-    <n v="50.760999999999996"/>
-    <n v="50.760999999999996"/>
-    <n v="42.038095238095238"/>
-    <n v="6.6209999999999951"/>
-    <n v="-1.0509523809523813"/>
-    <n v="5.5700476190476138"/>
-    <n v="108.56239746213677"/>
-    <n v="9.2112925227979536E-3"/>
-    <n v="0.75799345823506892"/>
+    <x v="10"/>
+    <m/>
+    <x v="45"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
   </r>
   <r>
     <x v="10"/>
@@ -1902,21 +1921,21 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{42F2A961-4B24-4134-99E9-0FE83E8807F0}" name="PivotTable1" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:E19" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{42F2A961-4B24-4134-99E9-0FE83E8807F0}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:E14" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="22">
     <pivotField axis="axisRow" showAll="0" sortType="descending">
       <items count="12">
+        <item sd="0" x="6"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="9"/>
         <item sd="0" x="4"/>
-        <item sd="0" x="6"/>
+        <item sd="0" x="3"/>
         <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="5"/>
-        <item sd="0" x="8"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="2"/>
-        <item x="9"/>
         <item h="1" sd="0" x="10"/>
         <item t="default" sd="0"/>
       </items>
@@ -1933,52 +1952,52 @@
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
       <items count="47">
+        <item x="18"/>
+        <item x="43"/>
         <item x="13"/>
-        <item x="38"/>
+        <item x="28"/>
+        <item x="3"/>
+        <item x="36"/>
+        <item x="26"/>
+        <item x="1"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="33"/>
+        <item x="39"/>
+        <item x="29"/>
+        <item x="14"/>
+        <item x="16"/>
+        <item x="34"/>
+        <item x="24"/>
+        <item x="44"/>
+        <item x="2"/>
+        <item x="17"/>
+        <item x="31"/>
+        <item x="12"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="25"/>
+        <item x="41"/>
+        <item x="4"/>
+        <item x="19"/>
+        <item x="9"/>
+        <item x="27"/>
+        <item x="42"/>
+        <item x="10"/>
+        <item x="30"/>
+        <item x="23"/>
+        <item x="32"/>
+        <item x="11"/>
+        <item x="40"/>
         <item x="37"/>
-        <item x="21"/>
-        <item x="1"/>
-        <item x="29"/>
-        <item x="19"/>
-        <item x="41"/>
-        <item x="43"/>
-        <item x="40"/>
-        <item x="26"/>
-        <item x="32"/>
         <item x="22"/>
+        <item x="6"/>
         <item x="35"/>
-        <item x="17"/>
-        <item x="27"/>
-        <item x="16"/>
-        <item x="39"/>
-        <item x="0"/>
-        <item x="12"/>
-        <item x="24"/>
         <item x="8"/>
         <item x="15"/>
-        <item x="3"/>
-        <item x="18"/>
-        <item x="34"/>
-        <item x="2"/>
-        <item x="14"/>
-        <item x="4"/>
-        <item x="20"/>
-        <item x="36"/>
-        <item x="6"/>
-        <item x="23"/>
-        <item x="11"/>
-        <item x="25"/>
-        <item x="7"/>
-        <item x="33"/>
-        <item x="30"/>
-        <item x="10"/>
-        <item x="42"/>
-        <item x="28"/>
+        <item x="38"/>
+        <item x="45"/>
         <item x="5"/>
-        <item x="9"/>
-        <item x="31"/>
-        <item x="45"/>
-        <item x="44"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -2006,24 +2025,9 @@
     <field x="0"/>
     <field x="2"/>
   </rowFields>
-  <rowItems count="16">
+  <rowItems count="11">
     <i>
       <x v="9"/>
-    </i>
-    <i r="1">
-      <x v="7"/>
-    </i>
-    <i r="1">
-      <x v="8"/>
-    </i>
-    <i r="1">
-      <x v="9"/>
-    </i>
-    <i r="1">
-      <x v="39"/>
-    </i>
-    <i r="1">
-      <x v="45"/>
     </i>
     <i>
       <x v="8"/>
@@ -2041,10 +2045,10 @@
       <x/>
     </i>
     <i>
-      <x v="4"/>
+      <x v="5"/>
     </i>
     <i>
-      <x v="5"/>
+      <x v="4"/>
     </i>
     <i>
       <x v="6"/>
@@ -2086,7 +2090,7 @@
     <dataField name="Target P&amp;L" fld="21" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="11">
+    <format dxfId="8">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -2096,7 +2100,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="10">
+    <format dxfId="7">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -2106,7 +2110,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="9">
+    <format dxfId="6">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -2391,7 +2395,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T46"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:T51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
@@ -2478,1647 +2483,1646 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="C2" s="32" t="s">
-        <v>86</v>
+        <v>115</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C2" t="s">
+        <v>116</v>
       </c>
       <c r="D2" s="8">
-        <v>45623</v>
+        <v>45481</v>
       </c>
       <c r="E2" s="2">
-        <v>1.9595</v>
+        <v>2</v>
       </c>
       <c r="F2" s="1">
-        <v>15.3</v>
+        <v>20.928000000000001</v>
       </c>
       <c r="G2" s="1">
-        <f t="shared" ref="G2:G41" si="0">E2*F2</f>
-        <v>29.980350000000001</v>
-      </c>
-      <c r="H2" s="11">
-        <v>0.35</v>
+        <f>E2*F2</f>
+        <v>41.856000000000002</v>
+      </c>
+      <c r="H2" s="13">
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="I2" s="11">
-        <v>0.39532299999999998</v>
+        <v>0.2</v>
       </c>
       <c r="J2" s="9">
-        <f t="shared" ref="J2:J41" si="1">IFERROR(H2/I2,"")</f>
-        <v>0.88535197800279775</v>
+        <f>IFERROR(H2/I2,"")</f>
+        <v>0.22499999999999998</v>
       </c>
       <c r="K2" s="9">
         <f>IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.3887017689731266E-2</v>
+        <v>0.1395190259239823</v>
       </c>
       <c r="L2" s="12">
         <f>F2/(1-(F2*(1+H2)-F2)/(F2*(1+H2)))</f>
-        <v>20.655000000000001</v>
+        <v>21.869759999999999</v>
       </c>
       <c r="M2" s="12">
         <f>L2*E2</f>
-        <v>40.4734725</v>
+        <v>43.739519999999999</v>
       </c>
       <c r="N2" s="12">
-        <f t="shared" ref="N2:N41" si="2">F2/(1+I2-H2)</f>
-        <v>14.636624277854791</v>
+        <f>F2/(1+I2-H2)</f>
+        <v>18.119480519480518</v>
       </c>
       <c r="O2" s="12">
-        <f t="shared" ref="O2:O41" si="3">L2-F2</f>
-        <v>5.3550000000000004</v>
+        <f>L2-F2</f>
+        <v>0.9417599999999986</v>
       </c>
       <c r="P2" s="12">
-        <f t="shared" ref="P2:P41" si="4">0.5*(N2-F2)</f>
-        <v>-0.33168786107260484</v>
+        <f>0.5*(N2-F2)</f>
+        <v>-1.4042597402597412</v>
       </c>
       <c r="Q2" s="15">
-        <f t="shared" ref="Q2:Q41" si="5">O2+P2</f>
-        <v>5.0233121389273956</v>
+        <f>O2+P2</f>
+        <v>-0.46249974025974261</v>
       </c>
       <c r="R2" s="12">
         <f>MAX($Q$2:$Q$279)-Q2</f>
-        <v>109.10913294225699</v>
+        <v>114.59494482144413</v>
       </c>
       <c r="S2" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R2)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>9.165135612700933E-3</v>
+        <v>8.7263884245343277E-3</v>
       </c>
       <c r="T2" s="9">
-        <f t="shared" ref="T2:T41" si="6">R2/MAX($R$2:$R$28)</f>
-        <v>0.76181081974332665</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R2/MAX($R$2:$R$28)</f>
+        <v>0.80011330398039715</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>115</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>94</v>
+        <v>129</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="D3" s="8">
-        <v>45627</v>
+        <v>45481</v>
       </c>
       <c r="E3" s="2">
-        <v>1.8976999999999999</v>
+        <v>2</v>
       </c>
       <c r="F3" s="1">
-        <v>21.73</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="G3" s="1">
-        <f t="shared" si="0"/>
-        <v>41.237020999999999</v>
-      </c>
-      <c r="H3" s="11">
-        <f>L3/F3-1</f>
-        <v>0.22319374137137582</v>
+        <f>E3*F3</f>
+        <v>32.799999999999997</v>
+      </c>
+      <c r="H3" s="13">
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="I3" s="11">
-        <v>0.45929999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="J3" s="9">
-        <f t="shared" si="1"/>
-        <v>0.48594326447066366</v>
+        <f>IFERROR(H3/I3,"")</f>
+        <v>0.22499999999999998</v>
       </c>
       <c r="K3" s="9">
         <f>IFERROR(J3/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.4088273561142234E-2</v>
+        <v>0.1395190259239823</v>
       </c>
       <c r="L3" s="12">
-        <v>26.58</v>
+        <f>F3/(1-(F3*(1+H3)-F3)/(F3*(1+H3)))</f>
+        <v>17.137999999999998</v>
       </c>
       <c r="M3" s="12">
-        <f t="shared" ref="M3:M41" si="7">L3*E3</f>
-        <v>50.440865999999993</v>
+        <f>L3*E3</f>
+        <v>34.275999999999996</v>
       </c>
       <c r="N3" s="12">
-        <f t="shared" si="2"/>
-        <v>17.579394852436032</v>
+        <f>F3/(1+I3-H3)</f>
+        <v>14.199134199134198</v>
       </c>
       <c r="O3" s="12">
-        <f t="shared" si="3"/>
-        <v>4.8499999999999979</v>
+        <f>L3-F3</f>
+        <v>0.73799999999999955</v>
       </c>
       <c r="P3" s="12">
-        <f t="shared" si="4"/>
-        <v>-2.0753025737819843</v>
+        <f>0.5*(N3-F3)</f>
+        <v>-1.1004329004329003</v>
       </c>
       <c r="Q3" s="15">
-        <f t="shared" si="5"/>
-        <v>2.7746974262180135</v>
+        <f>O3+P3</f>
+        <v>-0.36243290043290077</v>
       </c>
       <c r="R3" s="12">
         <f>MAX($Q$2:$Q$279)-Q3</f>
-        <v>111.35774765496637</v>
+        <v>114.49487798161729</v>
       </c>
       <c r="S3" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R3)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.980066686499668E-3</v>
+        <v>8.7340151597048287E-3</v>
       </c>
       <c r="T3" s="9">
-        <f t="shared" si="6"/>
+        <f>R3/MAX($R$2:$R$28)</f>
+        <v>0.79941462735066027</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" s="8">
+        <v>45623</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1.9595</v>
+      </c>
+      <c r="F4" s="1">
+        <v>15.3</v>
+      </c>
+      <c r="G4" s="1">
+        <f>E4*F4</f>
+        <v>29.980350000000001</v>
+      </c>
+      <c r="H4" s="13">
+        <v>0.35</v>
+      </c>
+      <c r="I4" s="11">
+        <v>0.39532299999999998</v>
+      </c>
+      <c r="J4" s="9">
+        <f>IFERROR(H4/I4,"")</f>
+        <v>0.88535197800279775</v>
+      </c>
+      <c r="K4" s="9">
+        <f>IFERROR(J4/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>0.54899309142587271</v>
+      </c>
+      <c r="L4" s="12">
+        <f>F4/(1-(F4*(1+H4)-F4)/(F4*(1+H4)))</f>
+        <v>20.655000000000001</v>
+      </c>
+      <c r="M4" s="12">
+        <f>L4*E4</f>
+        <v>40.4734725</v>
+      </c>
+      <c r="N4" s="12">
+        <f>F4/(1+I4-H4)</f>
+        <v>14.636624277854791</v>
+      </c>
+      <c r="O4" s="12">
+        <f>L4-F4</f>
+        <v>5.3550000000000004</v>
+      </c>
+      <c r="P4" s="12">
+        <f>0.5*(N4-F4)</f>
+        <v>-0.33168786107260484</v>
+      </c>
+      <c r="Q4" s="15">
+        <f>O4+P4</f>
+        <v>5.0233121389273956</v>
+      </c>
+      <c r="R4" s="12">
+        <f>MAX($Q$2:$Q$279)-Q4</f>
+        <v>109.10913294225699</v>
+      </c>
+      <c r="S4" s="9">
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R4)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>9.1651356127009313E-3</v>
+      </c>
+      <c r="T4" s="9">
+        <f>R4/MAX($R$2:$R$28)</f>
+        <v>0.76181081974332665</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D5" s="8">
+        <v>45627</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1.8976999999999999</v>
+      </c>
+      <c r="F5" s="1">
+        <v>21.73</v>
+      </c>
+      <c r="G5" s="1">
+        <f>E5*F5</f>
+        <v>41.237020999999999</v>
+      </c>
+      <c r="H5" s="13">
+        <f>L5/F5-1</f>
+        <v>0.22319374137137582</v>
+      </c>
+      <c r="I5" s="11">
+        <v>0.45929999999999999</v>
+      </c>
+      <c r="J5" s="9">
+        <f>IFERROR(H5/I5,"")</f>
+        <v>0.48594326447066366</v>
+      </c>
+      <c r="K5" s="9">
+        <f>IFERROR(J5/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>0.30132591517007606</v>
+      </c>
+      <c r="L5" s="12">
+        <v>26.58</v>
+      </c>
+      <c r="M5" s="12">
+        <f>L5*E5</f>
+        <v>50.440865999999993</v>
+      </c>
+      <c r="N5" s="12">
+        <f>F5/(1+I5-H5)</f>
+        <v>17.579394852436032</v>
+      </c>
+      <c r="O5" s="12">
+        <f>L5-F5</f>
+        <v>4.8499999999999979</v>
+      </c>
+      <c r="P5" s="12">
+        <f>0.5*(N5-F5)</f>
+        <v>-2.0753025737819843</v>
+      </c>
+      <c r="Q5" s="15">
+        <f>O5+P5</f>
+        <v>2.7746974262180135</v>
+      </c>
+      <c r="R5" s="12">
+        <f>MAX($Q$2:$Q$279)-Q5</f>
+        <v>111.35774765496637</v>
+      </c>
+      <c r="S5" s="9">
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R5)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>8.9800666864996662E-3</v>
+      </c>
+      <c r="T5" s="9">
+        <f>R5/MAX($R$2:$R$28)</f>
         <v>0.77751087134654673</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="6" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C6" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D6" s="8">
         <v>45553</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E6" s="2">
         <v>1.7345999999999999</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F6" s="1">
         <v>51.88</v>
       </c>
-      <c r="G4" s="1">
-        <f t="shared" si="0"/>
+      <c r="G6" s="1">
+        <f>E6*F6</f>
         <v>89.991048000000006</v>
       </c>
-      <c r="H4" s="11">
+      <c r="H6" s="13">
         <f>16.68%+7%/4</f>
         <v>0.18430000000000002</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I6" s="11">
         <v>0.19980000000000001</v>
       </c>
-      <c r="J4" s="9">
-        <f t="shared" si="1"/>
+      <c r="J6" s="9">
+        <f>IFERROR(H6/I6,"")</f>
         <v>0.92242242242242245</v>
-      </c>
-      <c r="K4" s="9">
-        <f>IFERROR(J4/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.5724604649982147E-2</v>
-      </c>
-      <c r="L4" s="12">
-        <f t="shared" ref="L4:L31" si="8">F4/(1-(F4*(1+H4)-F4)/(F4*(1+H4)))</f>
-        <v>61.441483999999996</v>
-      </c>
-      <c r="M4" s="12">
-        <f t="shared" si="7"/>
-        <v>106.57639814639998</v>
-      </c>
-      <c r="N4" s="12">
-        <f t="shared" si="2"/>
-        <v>51.088133924175295</v>
-      </c>
-      <c r="O4" s="12">
-        <f t="shared" si="3"/>
-        <v>9.561483999999993</v>
-      </c>
-      <c r="P4" s="12">
-        <f t="shared" si="4"/>
-        <v>-0.39593303791235357</v>
-      </c>
-      <c r="Q4" s="15">
-        <f t="shared" si="5"/>
-        <v>9.1655509620876394</v>
-      </c>
-      <c r="R4" s="12">
-        <f>MAX($Q$2:$Q$279)-Q4</f>
-        <v>104.96689411909675</v>
-      </c>
-      <c r="S4" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R4)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>9.526813271862531E-3</v>
-      </c>
-      <c r="T4" s="9">
-        <f t="shared" si="6"/>
-        <v>0.73288929623425103</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" s="8">
-        <v>45511</v>
-      </c>
-      <c r="E5" s="2">
-        <v>9.9999999999999998E-20</v>
-      </c>
-      <c r="F5" s="1">
-        <v>10.92</v>
-      </c>
-      <c r="G5" s="1">
-        <f t="shared" si="0"/>
-        <v>1.092E-18</v>
-      </c>
-      <c r="H5" s="11">
-        <v>1</v>
-      </c>
-      <c r="I5" s="13">
-        <v>1.8652</v>
-      </c>
-      <c r="J5" s="9">
-        <f t="shared" si="1"/>
-        <v>0.53613553506326406</v>
-      </c>
-      <c r="K5" s="9">
-        <f>IFERROR(J5/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.6576311225387755E-2</v>
-      </c>
-      <c r="L5" s="12">
-        <f t="shared" si="8"/>
-        <v>21.84</v>
-      </c>
-      <c r="M5" s="12">
-        <f t="shared" si="7"/>
-        <v>2.1840000000000001E-18</v>
-      </c>
-      <c r="N5" s="12">
-        <f t="shared" si="2"/>
-        <v>5.8546000428908433</v>
-      </c>
-      <c r="O5" s="12">
-        <f t="shared" si="3"/>
-        <v>10.92</v>
-      </c>
-      <c r="P5" s="12">
-        <f t="shared" si="4"/>
-        <v>-2.5326999785545783</v>
-      </c>
-      <c r="Q5" s="15">
-        <f t="shared" si="5"/>
-        <v>8.3873000214454212</v>
-      </c>
-      <c r="R5" s="12">
-        <f>MAX($Q$2:$Q$279)-Q5</f>
-        <v>105.74514505973896</v>
-      </c>
-      <c r="S5" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R5)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>9.456698928684306E-3</v>
-      </c>
-      <c r="T5" s="9">
-        <f t="shared" si="6"/>
-        <v>0.73832312171768166</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="8">
-        <v>45511</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0.45179999999999998</v>
-      </c>
-      <c r="F6" s="1">
-        <v>77.430000000000007</v>
-      </c>
-      <c r="G6" s="1">
-        <f t="shared" si="0"/>
-        <v>34.982874000000002</v>
-      </c>
-      <c r="H6" s="11">
-        <v>0.1</v>
-      </c>
-      <c r="I6" s="11">
-        <v>0.25990000000000002</v>
-      </c>
-      <c r="J6" s="9">
-        <f t="shared" si="1"/>
-        <v>0.38476337052712584</v>
       </c>
       <c r="K6" s="9">
         <f>IFERROR(J6/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.9072772488492973E-2</v>
+        <v>0.57197990163029566</v>
       </c>
       <c r="L6" s="12">
-        <f t="shared" si="8"/>
-        <v>85.173000000000016</v>
+        <f>F6/(1-(F6*(1+H6)-F6)/(F6*(1+H6)))</f>
+        <v>61.441483999999996</v>
       </c>
       <c r="M6" s="12">
-        <f t="shared" si="7"/>
-        <v>38.481161400000005</v>
+        <f>L6*E6</f>
+        <v>106.57639814639998</v>
       </c>
       <c r="N6" s="12">
-        <f t="shared" si="2"/>
-        <v>66.755754806448849</v>
+        <f>F6/(1+I6-H6)</f>
+        <v>51.088133924175295</v>
       </c>
       <c r="O6" s="12">
-        <f t="shared" si="3"/>
-        <v>7.7430000000000092</v>
+        <f>L6-F6</f>
+        <v>9.561483999999993</v>
       </c>
       <c r="P6" s="12">
-        <f t="shared" si="4"/>
-        <v>-5.3371225967755791</v>
+        <f>0.5*(N6-F6)</f>
+        <v>-0.39593303791235357</v>
       </c>
       <c r="Q6" s="15">
-        <f t="shared" si="5"/>
-        <v>2.4058774032244301</v>
+        <f>O6+P6</f>
+        <v>9.1655509620876394</v>
       </c>
       <c r="R6" s="12">
         <f>MAX($Q$2:$Q$279)-Q6</f>
-        <v>111.72656767795996</v>
+        <v>104.96689411909675</v>
       </c>
       <c r="S6" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R6)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.9504226325326178E-3</v>
+        <v>9.526813271862531E-3</v>
       </c>
       <c r="T6" s="9">
-        <f t="shared" si="6"/>
-        <v>0.78008600943515383</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R6/MAX($R$2:$R$28)</f>
+        <v>0.73288929623425103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>115</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D7" s="8">
-        <v>45627</v>
+        <v>45688</v>
       </c>
       <c r="E7" s="2">
-        <v>0.71050000000000002</v>
+        <v>1</v>
       </c>
       <c r="F7" s="1">
-        <v>42.26</v>
+        <v>44.24</v>
       </c>
       <c r="G7" s="1">
-        <f t="shared" si="0"/>
-        <v>30.025729999999999</v>
-      </c>
-      <c r="H7" s="11">
-        <v>0.1</v>
+        <f>E7*F7</f>
+        <v>44.24</v>
+      </c>
+      <c r="H7" s="13">
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="I7" s="11">
         <v>0.2</v>
       </c>
       <c r="J7" s="9">
-        <f t="shared" si="1"/>
-        <v>0.5</v>
+        <f>IFERROR(H7/I7,"")</f>
+        <v>0.22499999999999998</v>
       </c>
       <c r="K7" s="9">
         <f>IFERROR(J7/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.4785067848796617E-2</v>
+        <v>0.1395190259239823</v>
       </c>
       <c r="L7" s="12">
-        <f t="shared" si="8"/>
-        <v>46.486000000000004</v>
+        <f>F7/(1-(F7*(1+H7)-F7)/(F7*(1+H7)))</f>
+        <v>46.230800000000002</v>
       </c>
       <c r="M7" s="12">
-        <f t="shared" si="7"/>
-        <v>33.028303000000001</v>
+        <f>L7*E7</f>
+        <v>46.230800000000002</v>
       </c>
       <c r="N7" s="12">
-        <f t="shared" si="2"/>
-        <v>38.418181818181822</v>
+        <f>F7/(1+I7-H7)</f>
+        <v>38.303030303030305</v>
       </c>
       <c r="O7" s="12">
-        <f t="shared" si="3"/>
-        <v>4.2260000000000062</v>
+        <f>L7-F7</f>
+        <v>1.9908000000000001</v>
       </c>
       <c r="P7" s="12">
-        <f t="shared" si="4"/>
-        <v>-1.9209090909090882</v>
+        <f>0.5*(N7-F7)</f>
+        <v>-2.9684848484848487</v>
       </c>
       <c r="Q7" s="15">
-        <f t="shared" si="5"/>
-        <v>2.305090909090918</v>
+        <f>O7+P7</f>
+        <v>-0.9776848484848486</v>
       </c>
       <c r="R7" s="12">
         <f>MAX($Q$2:$Q$279)-Q7</f>
-        <v>111.82735417209346</v>
+        <v>115.11012992966923</v>
       </c>
       <c r="S7" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R7)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.9423558967609926E-3</v>
+        <v>8.6873327361456972E-3</v>
       </c>
       <c r="T7" s="9">
-        <f t="shared" si="6"/>
-        <v>0.78078971076284676</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R7/MAX($R$2:$R$28)</f>
+        <v>0.80371037765363607</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>15</v>
+        <v>115</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>131</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="D8" s="8">
-        <v>45460</v>
+        <v>45481</v>
       </c>
       <c r="E8" s="2">
-        <v>0.43659999999999999</v>
+        <v>1</v>
       </c>
       <c r="F8" s="1">
-        <v>160.25</v>
+        <v>48.68</v>
       </c>
       <c r="G8" s="1">
-        <f t="shared" si="0"/>
-        <v>69.965149999999994</v>
-      </c>
-      <c r="H8" s="11">
-        <v>6.7199999999999996E-2</v>
+        <f>E8*F8</f>
+        <v>48.68</v>
+      </c>
+      <c r="H8" s="13">
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="I8" s="11">
-        <v>0.16439999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="J8" s="9">
-        <f t="shared" si="1"/>
-        <v>0.40875912408759124</v>
+        <f>IFERROR(H8/I8,"")</f>
+        <v>0.125</v>
       </c>
       <c r="K8" s="9">
         <f>IFERROR(J8/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.0262245248651251E-2</v>
+        <v>7.751056995776795E-2</v>
       </c>
       <c r="L8" s="12">
-        <f t="shared" si="8"/>
-        <v>171.0188</v>
+        <f>F8/(1-(F8*(1+H8)-F8)/(F8*(1+H8)))</f>
+        <v>49.896999999999998</v>
       </c>
       <c r="M8" s="12">
-        <f t="shared" si="7"/>
-        <v>74.666808079999996</v>
+        <f>L8*E8</f>
+        <v>49.896999999999998</v>
       </c>
       <c r="N8" s="12">
-        <f t="shared" si="2"/>
-        <v>146.05359095880419</v>
+        <f>F8/(1+I8-H8)</f>
+        <v>41.42978723404255</v>
       </c>
       <c r="O8" s="12">
-        <f t="shared" si="3"/>
-        <v>10.768799999999999</v>
+        <f>L8-F8</f>
+        <v>1.2169999999999987</v>
       </c>
       <c r="P8" s="12">
-        <f t="shared" si="4"/>
-        <v>-7.0982045205979034</v>
+        <f>0.5*(N8-F8)</f>
+        <v>-3.6251063829787249</v>
       </c>
       <c r="Q8" s="15">
-        <f t="shared" si="5"/>
-        <v>3.6705954794020954</v>
+        <f>O8+P8</f>
+        <v>-2.4081063829787261</v>
       </c>
       <c r="R8" s="12">
         <f>MAX($Q$2:$Q$279)-Q8</f>
-        <v>110.46184960178229</v>
+        <v>116.54055146416312</v>
       </c>
       <c r="S8" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R8)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>9.0528992915203284E-3</v>
+        <v>8.5807042049865848E-3</v>
       </c>
       <c r="T8" s="9">
-        <f t="shared" si="6"/>
-        <v>0.7712556220204998</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R8/MAX($R$2:$R$28)</f>
+        <v>0.81369772309746791</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>21</v>
+        <v>115</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>119</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>120</v>
       </c>
       <c r="D9" s="8">
-        <v>45484</v>
+        <v>45481</v>
       </c>
       <c r="E9" s="2">
-        <v>0.4108</v>
+        <v>1</v>
       </c>
       <c r="F9" s="1">
-        <v>189.76</v>
+        <v>51.28</v>
       </c>
       <c r="G9" s="1">
-        <f t="shared" si="0"/>
-        <v>77.953407999999996</v>
-      </c>
-      <c r="H9" s="11">
-        <f>227.4/F9-1</f>
-        <v>0.19835581787521095</v>
+        <f>E9*F9</f>
+        <v>51.28</v>
+      </c>
+      <c r="H9" s="13">
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="I9" s="11">
-        <v>0.37</v>
+        <v>0.2</v>
       </c>
       <c r="J9" s="9">
-        <f t="shared" si="1"/>
-        <v>0.53609680506813773</v>
+        <f>IFERROR(H9/I9,"")</f>
+        <v>0.125</v>
       </c>
       <c r="K9" s="9">
         <f>IFERROR(J9/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.6574391374273774E-2</v>
+        <v>7.751056995776795E-2</v>
       </c>
       <c r="L9" s="12">
-        <f t="shared" si="8"/>
-        <v>227.4</v>
+        <f>F9/(1-(F9*(1+H9)-F9)/(F9*(1+H9)))</f>
+        <v>52.561999999999998</v>
       </c>
       <c r="M9" s="12">
-        <f t="shared" si="7"/>
-        <v>93.41592</v>
+        <f>L9*E9</f>
+        <v>52.561999999999998</v>
       </c>
       <c r="N9" s="12">
-        <f t="shared" si="2"/>
-        <v>161.96043380326287</v>
+        <f>F9/(1+I9-H9)</f>
+        <v>43.642553191489363</v>
       </c>
       <c r="O9" s="12">
-        <f t="shared" si="3"/>
-        <v>37.640000000000015</v>
+        <f>L9-F9</f>
+        <v>1.2819999999999965</v>
       </c>
       <c r="P9" s="12">
-        <f t="shared" si="4"/>
-        <v>-13.899783098368559</v>
+        <f>0.5*(N9-F9)</f>
+        <v>-3.8187234042553193</v>
       </c>
       <c r="Q9" s="15">
-        <f t="shared" si="5"/>
-        <v>23.740216901631456</v>
+        <f>O9+P9</f>
+        <v>-2.5367234042553228</v>
       </c>
       <c r="R9" s="12">
         <f>MAX($Q$2:$Q$279)-Q9</f>
-        <v>90.39222817955293</v>
+        <v>116.66916848543971</v>
       </c>
       <c r="S9" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R9)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>1.10628979962041E-2</v>
+        <v>8.5712447682765452E-3</v>
       </c>
       <c r="T9" s="9">
-        <f t="shared" si="6"/>
-        <v>0.6311275288415521</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R9/MAX($R$2:$R$28)</f>
+        <v>0.81459573993409262</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>19</v>
+        <v>40</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>103</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="D10" s="8">
-        <v>45544</v>
+        <v>45627</v>
       </c>
       <c r="E10" s="2">
-        <v>0.35149999999999998</v>
+        <v>0.95840000000000003</v>
       </c>
       <c r="F10" s="1">
-        <v>142.78</v>
+        <v>41.76</v>
       </c>
       <c r="G10" s="1">
-        <f t="shared" si="0"/>
-        <v>50.187169999999995</v>
-      </c>
-      <c r="H10" s="11">
-        <v>7.0000000000000007E-2</v>
+        <f>E10*F10</f>
+        <v>40.022784000000001</v>
+      </c>
+      <c r="H10" s="13">
+        <v>0.1</v>
       </c>
       <c r="I10" s="11">
-        <v>0.18340000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="J10" s="9">
-        <f t="shared" si="1"/>
-        <v>0.38167938931297712</v>
+        <f>IFERROR(H10/I10,"")</f>
+        <v>0.5</v>
       </c>
       <c r="K10" s="9">
         <f>IFERROR(J10/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.8919899121218792E-2</v>
+        <v>0.3100422798310718</v>
       </c>
       <c r="L10" s="12">
-        <f t="shared" si="8"/>
-        <v>152.77460000000002</v>
+        <f>F10/(1-(F10*(1+H10)-F10)/(F10*(1+H10)))</f>
+        <v>45.936</v>
       </c>
       <c r="M10" s="12">
-        <f t="shared" si="7"/>
-        <v>53.700271900000004</v>
+        <f>L10*E10</f>
+        <v>44.025062400000003</v>
       </c>
       <c r="N10" s="12">
-        <f t="shared" si="2"/>
-        <v>128.23783007005568</v>
+        <f>F10/(1+I10-H10)</f>
+        <v>37.963636363636368</v>
       </c>
       <c r="O10" s="12">
-        <f t="shared" si="3"/>
-        <v>9.9946000000000197</v>
+        <f>L10-F10</f>
+        <v>4.1760000000000019</v>
       </c>
       <c r="P10" s="12">
-        <f t="shared" si="4"/>
-        <v>-7.2710849649721609</v>
+        <f>0.5*(N10-F10)</f>
+        <v>-1.8981818181818149</v>
       </c>
       <c r="Q10" s="15">
-        <f t="shared" si="5"/>
-        <v>2.7235150350278587</v>
+        <f>O10+P10</f>
+        <v>2.2778181818181871</v>
       </c>
       <c r="R10" s="12">
         <f>MAX($Q$2:$Q$279)-Q10</f>
-        <v>111.40893004615653</v>
+        <v>111.8546268993662</v>
       </c>
       <c r="S10" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R10)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.9759411528833617E-3</v>
+        <v>8.9401755449927331E-3</v>
       </c>
       <c r="T10" s="9">
-        <f t="shared" si="6"/>
-        <v>0.77786823189316223</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R10/MAX($R$2:$R$28)</f>
+        <v>0.78098013165759694</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="D11" s="8">
-        <v>45580</v>
+        <v>45511</v>
       </c>
       <c r="E11" s="2">
-        <v>0.25669999999999998</v>
+        <v>0.45179999999999998</v>
       </c>
       <c r="F11" s="1">
-        <v>132.38999999999999</v>
+        <v>77.430000000000007</v>
       </c>
       <c r="G11" s="1">
-        <f t="shared" si="0"/>
-        <v>33.984512999999993</v>
-      </c>
-      <c r="H11" s="11">
-        <v>7.0000000000000007E-2</v>
+        <f>E11*F11</f>
+        <v>34.982874000000002</v>
+      </c>
+      <c r="H11" s="13">
+        <v>0.1</v>
       </c>
       <c r="I11" s="11">
-        <v>0.1623</v>
+        <v>0.25990000000000002</v>
       </c>
       <c r="J11" s="9">
-        <f t="shared" si="1"/>
-        <v>0.43130006161429457</v>
+        <f>IFERROR(H11/I11,"")</f>
+        <v>0.38476337052712584</v>
       </c>
       <c r="K11" s="9">
         <f>IFERROR(J11/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.1379602580600905E-2</v>
+        <v>0.23858582518743501</v>
       </c>
       <c r="L11" s="12">
-        <f t="shared" si="8"/>
-        <v>141.65729999999999</v>
+        <f>F11/(1-(F11*(1+H11)-F11)/(F11*(1+H11)))</f>
+        <v>85.173000000000016</v>
       </c>
       <c r="M11" s="12">
-        <f t="shared" si="7"/>
-        <v>36.363428909999996</v>
+        <f>L11*E11</f>
+        <v>38.481161400000005</v>
       </c>
       <c r="N11" s="12">
-        <f t="shared" si="2"/>
-        <v>121.20296621807194</v>
+        <f>F11/(1+I11-H11)</f>
+        <v>66.755754806448849</v>
       </c>
       <c r="O11" s="12">
-        <f t="shared" si="3"/>
-        <v>9.2673000000000059</v>
+        <f>L11-F11</f>
+        <v>7.7430000000000092</v>
       </c>
       <c r="P11" s="12">
-        <f t="shared" si="4"/>
-        <v>-5.5935168909640254</v>
+        <f>0.5*(N11-F11)</f>
+        <v>-5.3371225967755791</v>
       </c>
       <c r="Q11" s="15">
-        <f t="shared" si="5"/>
-        <v>3.6737831090359805</v>
+        <f>O11+P11</f>
+        <v>2.4058774032244301</v>
       </c>
       <c r="R11" s="12">
         <f>MAX($Q$2:$Q$279)-Q11</f>
-        <v>110.45866197214841</v>
+        <v>111.72656767795996</v>
       </c>
       <c r="S11" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R11)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>9.0531605411999731E-3</v>
+        <v>8.9504226325326161E-3</v>
       </c>
       <c r="T11" s="9">
-        <f t="shared" si="6"/>
-        <v>0.77123336567330925</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R11/MAX($R$2:$R$28)</f>
+        <v>0.78008600943515383</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>7</v>
+        <v>38</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D12" s="8">
-        <v>45511</v>
+        <v>45460</v>
       </c>
       <c r="E12" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>0.43659999999999999</v>
       </c>
       <c r="F12" s="1">
-        <v>283.43</v>
+        <v>160.25</v>
       </c>
       <c r="G12" s="1">
-        <f t="shared" si="0"/>
-        <v>2.8342999999999998E-17</v>
-      </c>
-      <c r="H12" s="11">
-        <v>0.25</v>
+        <f>E12*F12</f>
+        <v>69.965149999999994</v>
+      </c>
+      <c r="H12" s="13">
+        <v>6.7199999999999996E-2</v>
       </c>
       <c r="I12" s="11">
-        <v>0.26</v>
+        <v>0.16439999999999999</v>
       </c>
       <c r="J12" s="9">
-        <f t="shared" si="1"/>
-        <v>0.96153846153846145</v>
+        <f>IFERROR(H12/I12,"")</f>
+        <v>0.40875912408759124</v>
       </c>
       <c r="K12" s="9">
         <f>IFERROR(J12/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.766359201691657E-2</v>
+        <v>0.25346522146773753</v>
       </c>
       <c r="L12" s="12">
-        <f t="shared" si="8"/>
-        <v>354.28750000000002</v>
+        <f>F12/(1-(F12*(1+H12)-F12)/(F12*(1+H12)))</f>
+        <v>171.0188</v>
       </c>
       <c r="M12" s="12">
-        <f t="shared" si="7"/>
-        <v>3.542875E-17</v>
+        <f>L12*E12</f>
+        <v>74.666808079999996</v>
       </c>
       <c r="N12" s="12">
-        <f t="shared" si="2"/>
-        <v>280.62376237623761</v>
+        <f>F12/(1+I12-H12)</f>
+        <v>146.05359095880419</v>
       </c>
       <c r="O12" s="12">
-        <f t="shared" si="3"/>
-        <v>70.857500000000016</v>
+        <f>L12-F12</f>
+        <v>10.768799999999999</v>
       </c>
       <c r="P12" s="12">
-        <f t="shared" si="4"/>
-        <v>-1.4031188118811997</v>
+        <f>0.5*(N12-F12)</f>
+        <v>-7.0982045205979034</v>
       </c>
       <c r="Q12" s="15">
-        <f t="shared" si="5"/>
-        <v>69.454381188118816</v>
+        <f>O12+P12</f>
+        <v>3.6705954794020954</v>
       </c>
       <c r="R12" s="12">
         <f>MAX($Q$2:$Q$279)-Q12</f>
-        <v>44.67806389306557</v>
+        <v>110.46184960178229</v>
       </c>
       <c r="S12" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R12)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>2.2382348581474875E-2</v>
+        <v>9.0528992915203301E-3</v>
       </c>
       <c r="T12" s="9">
-        <f t="shared" si="6"/>
-        <v>0.311946686414727</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R12/MAX($R$2:$R$28)</f>
+        <v>0.7712556220204998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>36</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D13" s="8">
-        <v>45544</v>
+        <v>45484</v>
       </c>
       <c r="E13" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>0.4108</v>
       </c>
       <c r="F13" s="1">
-        <v>188.12</v>
+        <v>189.76</v>
       </c>
       <c r="G13" s="1">
-        <f t="shared" si="0"/>
-        <v>1.8812000000000001E-17</v>
-      </c>
-      <c r="H13" s="11">
-        <v>0.15</v>
+        <f>E13*F13</f>
+        <v>77.953407999999996</v>
+      </c>
+      <c r="H13" s="13">
+        <f>227.4/F13-1</f>
+        <v>0.19835581787521095</v>
       </c>
       <c r="I13" s="11">
-        <v>0.37780000000000002</v>
+        <v>0.37</v>
       </c>
       <c r="J13" s="9">
-        <f t="shared" si="1"/>
-        <v>0.39703546850185278</v>
+        <f>IFERROR(H13/I13,"")</f>
+        <v>0.53609680506813773</v>
       </c>
       <c r="K13" s="9">
         <f>IFERROR(J13/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.9681102050394347E-2</v>
+        <v>0.33242535130695822</v>
       </c>
       <c r="L13" s="12">
-        <f t="shared" si="8"/>
-        <v>216.33799999999999</v>
+        <f>F13/(1-(F13*(1+H13)-F13)/(F13*(1+H13)))</f>
+        <v>227.4</v>
       </c>
       <c r="M13" s="12">
-        <f t="shared" si="7"/>
-        <v>2.16338E-17</v>
+        <f>L13*E13</f>
+        <v>93.41592</v>
       </c>
       <c r="N13" s="12">
-        <f t="shared" si="2"/>
-        <v>153.21713634142367</v>
+        <f>F13/(1+I13-H13)</f>
+        <v>161.96043380326287</v>
       </c>
       <c r="O13" s="12">
-        <f t="shared" si="3"/>
-        <v>28.217999999999989</v>
+        <f>L13-F13</f>
+        <v>37.640000000000015</v>
       </c>
       <c r="P13" s="12">
-        <f t="shared" si="4"/>
-        <v>-17.451431829288168</v>
+        <f>0.5*(N13-F13)</f>
+        <v>-13.899783098368559</v>
       </c>
       <c r="Q13" s="15">
-        <f t="shared" si="5"/>
-        <v>10.766568170711821</v>
+        <f>O13+P13</f>
+        <v>23.740216901631456</v>
       </c>
       <c r="R13" s="12">
         <f>MAX($Q$2:$Q$279)-Q13</f>
-        <v>103.36587691047256</v>
+        <v>90.39222817955293</v>
       </c>
       <c r="S13" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R13)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>9.6743725288193673E-3</v>
+        <v>1.1062897996204102E-2</v>
       </c>
       <c r="T13" s="9">
-        <f t="shared" si="6"/>
-        <v>0.72171083482377829</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R13/MAX($R$2:$R$28)</f>
+        <v>0.6311275288415521</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>42</v>
+        <v>38</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="D14" s="8">
-        <v>45580</v>
+        <v>45544</v>
       </c>
       <c r="E14" s="2">
-        <v>0.19139999999999999</v>
+        <v>0.35149999999999998</v>
       </c>
       <c r="F14" s="1">
-        <v>135.82</v>
+        <v>142.78</v>
       </c>
       <c r="G14" s="1">
-        <f t="shared" si="0"/>
-        <v>25.995947999999999</v>
-      </c>
-      <c r="H14" s="11">
-        <v>0.1202</v>
+        <f>E14*F14</f>
+        <v>50.187169999999995</v>
+      </c>
+      <c r="H14" s="13">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I14" s="11">
-        <v>0.33710000000000001</v>
+        <v>0.18340000000000001</v>
       </c>
       <c r="J14" s="9">
-        <f t="shared" si="1"/>
-        <v>0.35657075051913378</v>
+        <f>IFERROR(H14/I14,"")</f>
+        <v>0.38167938931297712</v>
       </c>
       <c r="K14" s="9">
         <f>IFERROR(J14/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.7675260489026123E-2</v>
+        <v>0.23667349605425328</v>
       </c>
       <c r="L14" s="12">
-        <f t="shared" si="8"/>
-        <v>152.14556400000001</v>
+        <f>F14/(1-(F14*(1+H14)-F14)/(F14*(1+H14)))</f>
+        <v>152.77460000000002</v>
       </c>
       <c r="M14" s="12">
-        <f t="shared" si="7"/>
-        <v>29.120660949599998</v>
+        <f>L14*E14</f>
+        <v>53.700271900000004</v>
       </c>
       <c r="N14" s="12">
-        <f t="shared" si="2"/>
-        <v>111.61147177253677</v>
+        <f>F14/(1+I14-H14)</f>
+        <v>128.23783007005568</v>
       </c>
       <c r="O14" s="12">
-        <f t="shared" si="3"/>
-        <v>16.325564000000014</v>
+        <f>L14-F14</f>
+        <v>9.9946000000000197</v>
       </c>
       <c r="P14" s="12">
-        <f t="shared" si="4"/>
-        <v>-12.10426411373161</v>
+        <f>0.5*(N14-F14)</f>
+        <v>-7.2710849649721609</v>
       </c>
       <c r="Q14" s="15">
-        <f t="shared" si="5"/>
-        <v>4.2212998862684046</v>
+        <f>O14+P14</f>
+        <v>2.7235150350278587</v>
       </c>
       <c r="R14" s="12">
         <f>MAX($Q$2:$Q$279)-Q14</f>
-        <v>109.91114519491597</v>
+        <v>111.40893004615653</v>
       </c>
       <c r="S14" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R14)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>9.0982583997883375E-3</v>
+        <v>8.9759411528833617E-3</v>
       </c>
       <c r="T14" s="9">
-        <f t="shared" si="6"/>
-        <v>0.76741054907089512</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R14/MAX($R$2:$R$28)</f>
+        <v>0.77786823189316223</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" t="s">
-        <v>13</v>
+        <v>96</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>100</v>
       </c>
       <c r="D15" s="8">
-        <v>45482</v>
+        <v>45630</v>
       </c>
       <c r="E15" s="2">
-        <v>0.18820000000000001</v>
+        <v>0.28749999999999998</v>
       </c>
       <c r="F15" s="1">
-        <v>227.38</v>
+        <v>34.78</v>
       </c>
       <c r="G15" s="1">
-        <f t="shared" si="0"/>
-        <v>42.792915999999998</v>
-      </c>
-      <c r="H15" s="11">
-        <v>0.15</v>
+        <f>E15*F15</f>
+        <v>9.99925</v>
+      </c>
+      <c r="H15" s="13">
+        <v>0.2</v>
       </c>
       <c r="I15" s="11">
-        <v>0.2271</v>
+        <v>0.2</v>
       </c>
       <c r="J15" s="9">
-        <f t="shared" si="1"/>
-        <v>0.66050198150594452</v>
+        <f>IFERROR(H15/I15,"")</f>
+        <v>1</v>
       </c>
       <c r="K15" s="9">
         <f>IFERROR(J15/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.2741172851778889E-2</v>
+        <v>0.6200845596621436</v>
       </c>
       <c r="L15" s="12">
-        <f t="shared" si="8"/>
-        <v>261.48699999999997</v>
+        <f>F15/(1-(F15*(1+H15)-F15)/(F15*(1+H15)))</f>
+        <v>41.735999999999997</v>
       </c>
       <c r="M15" s="12">
-        <f t="shared" si="7"/>
-        <v>49.211853399999995</v>
+        <f>L15*E15</f>
+        <v>11.999099999999999</v>
       </c>
       <c r="N15" s="12">
-        <f t="shared" si="2"/>
-        <v>211.10389007520189</v>
+        <f>F15/(1+I15-H15)</f>
+        <v>34.78</v>
       </c>
       <c r="O15" s="12">
-        <f t="shared" si="3"/>
-        <v>34.106999999999971</v>
+        <f>L15-F15</f>
+        <v>6.955999999999996</v>
       </c>
       <c r="P15" s="12">
-        <f t="shared" si="4"/>
-        <v>-8.1380549623990532</v>
+        <f>0.5*(N15-F15)</f>
+        <v>0</v>
       </c>
       <c r="Q15" s="15">
-        <f t="shared" si="5"/>
-        <v>25.968945037600918</v>
+        <f>O15+P15</f>
+        <v>6.955999999999996</v>
       </c>
       <c r="R15" s="12">
         <f>MAX($Q$2:$Q$279)-Q15</f>
-        <v>88.163500043583468</v>
+        <v>107.1764450811844</v>
       </c>
       <c r="S15" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R15)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>1.1342562392664218E-2</v>
+        <v>9.3304083676456744E-3</v>
       </c>
       <c r="T15" s="9">
-        <f t="shared" si="6"/>
-        <v>0.6155663272953309</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R15/MAX($R$2:$R$28)</f>
+        <v>0.74831660084479601</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" t="s">
-        <v>12</v>
+        <v>40</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>91</v>
       </c>
       <c r="D16" s="8">
-        <v>45574</v>
+        <v>45627</v>
       </c>
       <c r="E16" s="2">
-        <v>0.13370000000000001</v>
+        <v>0.27450000000000002</v>
       </c>
       <c r="F16" s="1">
-        <v>423.77</v>
+        <v>39.799999999999997</v>
       </c>
       <c r="G16" s="1">
-        <f t="shared" si="0"/>
-        <v>56.658049000000005</v>
-      </c>
-      <c r="H16" s="11">
-        <v>0.15</v>
+        <f>E16*F16</f>
+        <v>10.9251</v>
+      </c>
+      <c r="H16" s="13">
+        <v>0.1</v>
       </c>
       <c r="I16" s="11">
-        <v>0.1963</v>
+        <v>0.2</v>
       </c>
       <c r="J16" s="9">
-        <f t="shared" si="1"/>
-        <v>0.76413652572592972</v>
+        <f>IFERROR(H16/I16,"")</f>
+        <v>0.5</v>
       </c>
       <c r="K16" s="9">
         <f>IFERROR(J16/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.7878351271721782E-2</v>
+        <v>0.3100422798310718</v>
       </c>
       <c r="L16" s="12">
-        <f t="shared" si="8"/>
-        <v>487.33549999999991</v>
+        <f>F16/(1-(F16*(1+H16)-F16)/(F16*(1+H16)))</f>
+        <v>43.78</v>
       </c>
       <c r="M16" s="12">
-        <f t="shared" si="7"/>
-        <v>65.156756349999995</v>
+        <f>L16*E16</f>
+        <v>12.017610000000001</v>
       </c>
       <c r="N16" s="12">
-        <f t="shared" si="2"/>
-        <v>405.01768135334032</v>
+        <f>F16/(1+I16-H16)</f>
+        <v>36.181818181818187</v>
       </c>
       <c r="O16" s="12">
-        <f t="shared" si="3"/>
-        <v>63.565499999999929</v>
+        <f>L16-F16</f>
+        <v>3.980000000000004</v>
       </c>
       <c r="P16" s="12">
-        <f t="shared" si="4"/>
-        <v>-9.3761593233298299</v>
+        <f>0.5*(N16-F16)</f>
+        <v>-1.8090909090909051</v>
       </c>
       <c r="Q16" s="15">
-        <f t="shared" si="5"/>
-        <v>54.189340676670099</v>
+        <f>O16+P16</f>
+        <v>2.1709090909090989</v>
       </c>
       <c r="R16" s="12">
         <f>MAX($Q$2:$Q$279)-Q16</f>
-        <v>59.943104404514287</v>
+        <v>111.96153599027528</v>
       </c>
       <c r="S16" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R16)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>1.6682485999585477E-2</v>
+        <v>8.931638809303739E-3</v>
       </c>
       <c r="T16" s="9">
-        <f t="shared" si="6"/>
-        <v>0.41852871774290379</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R16/MAX($R$2:$R$28)</f>
+        <v>0.78172658156501729</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>8</v>
+        <v>39</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="D17" s="8">
-        <v>45511</v>
+        <v>45580</v>
       </c>
       <c r="E17" s="2">
-        <v>0.12939999999999999</v>
+        <v>0.25669999999999998</v>
       </c>
       <c r="F17" s="1">
-        <v>501.56</v>
+        <v>132.38999999999999</v>
       </c>
       <c r="G17" s="1">
-        <f t="shared" si="0"/>
-        <v>64.901863999999989</v>
-      </c>
-      <c r="H17" s="11">
-        <v>0.25</v>
+        <f>E17*F17</f>
+        <v>33.984512999999993</v>
+      </c>
+      <c r="H17" s="13">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I17" s="11">
-        <v>0.29699999999999999</v>
+        <v>0.1623</v>
       </c>
       <c r="J17" s="9">
-        <f t="shared" si="1"/>
-        <v>0.84175084175084181</v>
+        <f>IFERROR(H17/I17,"")</f>
+        <v>0.43130006161429457</v>
       </c>
       <c r="K17" s="9">
         <f>IFERROR(J17/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.1725703449152558E-2</v>
+        <v>0.26744250878835524</v>
       </c>
       <c r="L17" s="12">
-        <f t="shared" si="8"/>
-        <v>626.95000000000005</v>
+        <f>F17/(1-(F17*(1+H17)-F17)/(F17*(1+H17)))</f>
+        <v>141.65729999999999</v>
       </c>
       <c r="M17" s="12">
-        <f t="shared" si="7"/>
-        <v>81.127330000000001</v>
+        <f>L17*E17</f>
+        <v>36.363428909999996</v>
       </c>
       <c r="N17" s="12">
-        <f t="shared" si="2"/>
-        <v>479.04489016236869</v>
+        <f>F17/(1+I17-H17)</f>
+        <v>121.20296621807194</v>
       </c>
       <c r="O17" s="12">
-        <f t="shared" si="3"/>
-        <v>125.39000000000004</v>
+        <f>L17-F17</f>
+        <v>9.2673000000000059</v>
       </c>
       <c r="P17" s="12">
-        <f t="shared" si="4"/>
-        <v>-11.257554918815657</v>
+        <f>0.5*(N17-F17)</f>
+        <v>-5.5935168909640254</v>
       </c>
       <c r="Q17" s="15">
-        <f t="shared" si="5"/>
-        <v>114.13244508118439</v>
+        <f>O17+P17</f>
+        <v>3.6737831090359805</v>
       </c>
       <c r="R17" s="12">
         <f>MAX($Q$2:$Q$279)-Q17</f>
-        <v>0</v>
+        <v>110.45866197214841</v>
       </c>
       <c r="S17" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R17)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>0</v>
+        <v>9.0531605411999748E-3</v>
       </c>
       <c r="T17" s="9">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R17/MAX($R$2:$R$28)</f>
+        <v>0.77123336567330925</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>18</v>
+        <v>40</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="C18" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D18" s="8">
-        <v>45483</v>
+        <v>45511</v>
       </c>
       <c r="E18" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>0.25169999999999998</v>
       </c>
       <c r="F18" s="1">
-        <v>167.24</v>
+        <v>178.56</v>
       </c>
       <c r="G18" s="1">
-        <f t="shared" si="0"/>
-        <v>1.6724000000000001E-17</v>
-      </c>
-      <c r="H18" s="11">
-        <f>190.41/F18-1</f>
-        <v>0.13854341066730447</v>
+        <f>E18*F18</f>
+        <v>44.943551999999997</v>
+      </c>
+      <c r="H18" s="13">
+        <f>196.02/F18-1</f>
+        <v>9.7782258064516236E-2</v>
       </c>
       <c r="I18" s="11">
-        <v>0.26790000000000003</v>
+        <v>0.52980000000000005</v>
       </c>
       <c r="J18" s="9">
-        <f t="shared" si="1"/>
-        <v>0.51714598979956872</v>
+        <f>IFERROR(H18/I18,"")</f>
+        <v>0.18456447350795815</v>
       </c>
       <c r="K18" s="9">
         <f>IFERROR(J18/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.5634996889830789E-2</v>
+        <v>0.1144455802844576</v>
       </c>
       <c r="L18" s="12">
-        <f t="shared" si="8"/>
-        <v>190.41</v>
+        <f>F18/(1-(F18*(1+H18)-F18)/(F18*(1+H18)))</f>
+        <v>196.02</v>
       </c>
       <c r="M18" s="12">
-        <f t="shared" si="7"/>
-        <v>1.9040999999999999E-17</v>
+        <f>L18*E18</f>
+        <v>49.338234</v>
       </c>
       <c r="N18" s="12">
-        <f t="shared" si="2"/>
-        <v>148.08431772538498</v>
+        <f>F18/(1+I18-H18)</f>
+        <v>124.69119255370553</v>
       </c>
       <c r="O18" s="12">
-        <f t="shared" si="3"/>
-        <v>23.169999999999987</v>
+        <f>L18-F18</f>
+        <v>17.460000000000008</v>
       </c>
       <c r="P18" s="12">
-        <f t="shared" si="4"/>
-        <v>-9.5778411373075159</v>
+        <f>0.5*(N18-F18)</f>
+        <v>-26.934403723147234</v>
       </c>
       <c r="Q18" s="15">
-        <f t="shared" si="5"/>
-        <v>13.592158862692472</v>
+        <f>O18+P18</f>
+        <v>-9.4744037231472262</v>
       </c>
       <c r="R18" s="12">
         <f>MAX($Q$2:$Q$279)-Q18</f>
-        <v>100.54028621849191</v>
+        <v>123.60684880433161</v>
       </c>
       <c r="S18" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R18)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>9.9462617186788418E-3</v>
+        <v>8.0901666022000929E-3</v>
       </c>
       <c r="T18" s="9">
-        <f t="shared" si="6"/>
-        <v>0.70198227953907921</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R18/MAX($R$2:$R$28)</f>
+        <v>0.86303531404059042</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>47</v>
+        <v>39</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D19" s="8">
-        <v>45511</v>
+        <v>45580</v>
       </c>
       <c r="E19" s="2">
-        <v>0.25169999999999998</v>
+        <v>0.19139999999999999</v>
       </c>
       <c r="F19" s="1">
-        <v>178.56</v>
+        <v>135.82</v>
       </c>
       <c r="G19" s="1">
-        <f t="shared" si="0"/>
-        <v>44.943551999999997</v>
-      </c>
-      <c r="H19" s="11">
-        <f>196.02/F19-1</f>
-        <v>9.7782258064516236E-2</v>
+        <f>E19*F19</f>
+        <v>25.995947999999999</v>
+      </c>
+      <c r="H19" s="13">
+        <v>0.1202</v>
       </c>
       <c r="I19" s="11">
-        <v>0.52980000000000005</v>
+        <v>0.33710000000000001</v>
       </c>
       <c r="J19" s="9">
-        <f t="shared" si="1"/>
-        <v>0.18456447350795815</v>
+        <f>IFERROR(H19/I19,"")</f>
+        <v>0.35657075051913378</v>
       </c>
       <c r="K19" s="9">
         <f>IFERROR(J19/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>9.1488859967443371E-3</v>
+        <v>0.22110401682405711</v>
       </c>
       <c r="L19" s="12">
-        <f t="shared" si="8"/>
-        <v>196.02</v>
+        <f>F19/(1-(F19*(1+H19)-F19)/(F19*(1+H19)))</f>
+        <v>152.14556400000001</v>
       </c>
       <c r="M19" s="12">
-        <f t="shared" si="7"/>
-        <v>49.338234</v>
+        <f>L19*E19</f>
+        <v>29.120660949599998</v>
       </c>
       <c r="N19" s="12">
-        <f t="shared" si="2"/>
-        <v>124.69119255370553</v>
+        <f>F19/(1+I19-H19)</f>
+        <v>111.61147177253677</v>
       </c>
       <c r="O19" s="12">
-        <f t="shared" si="3"/>
-        <v>17.460000000000008</v>
+        <f>L19-F19</f>
+        <v>16.325564000000014</v>
       </c>
       <c r="P19" s="12">
-        <f t="shared" si="4"/>
-        <v>-26.934403723147234</v>
+        <f>0.5*(N19-F19)</f>
+        <v>-12.10426411373161</v>
       </c>
       <c r="Q19" s="15">
-        <f t="shared" si="5"/>
-        <v>-9.4744037231472262</v>
+        <f>O19+P19</f>
+        <v>4.2212998862684046</v>
       </c>
       <c r="R19" s="12">
         <f>MAX($Q$2:$Q$279)-Q19</f>
-        <v>123.60684880433161</v>
+        <v>109.91114519491597</v>
       </c>
       <c r="S19" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R19)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.0901666022000929E-3</v>
+        <v>9.0982583997883393E-3</v>
       </c>
       <c r="T19" s="9">
-        <f t="shared" si="6"/>
-        <v>0.86303531404059042</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R19/MAX($R$2:$R$28)</f>
+        <v>0.76741054907089512</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>33</v>
+        <v>36</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D20" s="8">
-        <v>45562</v>
+        <v>45482</v>
       </c>
       <c r="E20" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>0.18820000000000001</v>
       </c>
       <c r="F20" s="1">
-        <v>668.82</v>
+        <v>227.38</v>
       </c>
       <c r="G20" s="1">
-        <f t="shared" si="0"/>
-        <v>6.6881999999999999E-17</v>
-      </c>
-      <c r="H20" s="11">
-        <v>0.05</v>
+        <f>E20*F20</f>
+        <v>42.792915999999998</v>
+      </c>
+      <c r="H20" s="13">
+        <v>0.15</v>
       </c>
       <c r="I20" s="11">
-        <v>0.28000000000000003</v>
+        <v>0.2271</v>
       </c>
       <c r="J20" s="9">
-        <f t="shared" si="1"/>
-        <v>0.17857142857142858</v>
+        <f>IFERROR(H20/I20,"")</f>
+        <v>0.66050198150594452</v>
       </c>
       <c r="K20" s="9">
         <f>IFERROR(J20/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>8.8518099459987919E-3</v>
+        <v>0.40956708035808692</v>
       </c>
       <c r="L20" s="12">
-        <f t="shared" si="8"/>
-        <v>702.26100000000008</v>
+        <f>F20/(1-(F20*(1+H20)-F20)/(F20*(1+H20)))</f>
+        <v>261.48699999999997</v>
       </c>
       <c r="M20" s="12">
-        <f t="shared" si="7"/>
-        <v>7.0226100000000009E-17</v>
+        <f>L20*E20</f>
+        <v>49.211853399999995</v>
       </c>
       <c r="N20" s="12">
-        <f t="shared" si="2"/>
-        <v>543.7560975609756</v>
+        <f>F20/(1+I20-H20)</f>
+        <v>211.10389007520189</v>
       </c>
       <c r="O20" s="12">
-        <f t="shared" si="3"/>
-        <v>33.441000000000031</v>
+        <f>L20-F20</f>
+        <v>34.106999999999971</v>
       </c>
       <c r="P20" s="12">
-        <f t="shared" si="4"/>
-        <v>-62.531951219512223</v>
+        <f>0.5*(N20-F20)</f>
+        <v>-8.1380549623990532</v>
       </c>
       <c r="Q20" s="15">
-        <f t="shared" si="5"/>
-        <v>-29.090951219512192</v>
+        <f>O20+P20</f>
+        <v>25.968945037600918</v>
       </c>
       <c r="R20" s="12">
         <f>MAX($Q$2:$Q$279)-Q20</f>
-        <v>143.22339630069658</v>
+        <v>88.163500043583468</v>
       </c>
       <c r="S20" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R20)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>6.9820994741704532E-3</v>
+        <v>1.1342562392664218E-2</v>
       </c>
       <c r="T20" s="9">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R20/MAX($R$2:$R$28)</f>
+        <v>0.6155663272953309</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>36</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="C21" t="s">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="D21" s="8">
-        <v>45481</v>
+        <v>45574</v>
       </c>
       <c r="E21" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>0.13370000000000001</v>
       </c>
       <c r="F21" s="1">
-        <v>700.32</v>
+        <v>423.77</v>
       </c>
       <c r="G21" s="1">
-        <f t="shared" si="0"/>
-        <v>7.0031999999999998E-17</v>
-      </c>
-      <c r="H21" s="11">
-        <v>0.1</v>
+        <f>E21*F21</f>
+        <v>56.658049000000005</v>
+      </c>
+      <c r="H21" s="13">
+        <v>0.15</v>
       </c>
       <c r="I21" s="11">
-        <v>0.45340000000000003</v>
+        <v>0.1963</v>
       </c>
       <c r="J21" s="9">
-        <f t="shared" si="1"/>
-        <v>0.22055580061755625</v>
+        <f>IFERROR(H21/I21,"")</f>
+        <v>0.76413652572592972</v>
       </c>
       <c r="K21" s="9">
         <f>IFERROR(J21/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.0932980965503582E-2</v>
+        <v>0.47382926107652334</v>
       </c>
       <c r="L21" s="12">
-        <f t="shared" si="8"/>
-        <v>770.35200000000009</v>
+        <f>F21/(1-(F21*(1+H21)-F21)/(F21*(1+H21)))</f>
+        <v>487.33549999999991</v>
       </c>
       <c r="M21" s="12">
-        <f t="shared" si="7"/>
-        <v>7.7035200000000004E-17</v>
+        <f>L21*E21</f>
+        <v>65.156756349999995</v>
       </c>
       <c r="N21" s="12">
-        <f t="shared" si="2"/>
-        <v>517.45234224915032</v>
+        <f>F21/(1+I21-H21)</f>
+        <v>405.01768135334032</v>
       </c>
       <c r="O21" s="12">
-        <f t="shared" si="3"/>
-        <v>70.032000000000039</v>
+        <f>L21-F21</f>
+        <v>63.565499999999929</v>
       </c>
       <c r="P21" s="12">
-        <f t="shared" si="4"/>
-        <v>-91.433828875424865</v>
+        <f>0.5*(N21-F21)</f>
+        <v>-9.3761593233298299</v>
       </c>
       <c r="Q21" s="15">
-        <f t="shared" si="5"/>
-        <v>-21.401828875424826</v>
+        <f>O21+P21</f>
+        <v>54.189340676670099</v>
       </c>
       <c r="R21" s="12">
         <f>MAX($Q$2:$Q$279)-Q21</f>
-        <v>135.53427395660921</v>
+        <v>59.943104404514287</v>
       </c>
       <c r="S21" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R21)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>7.3782075249847591E-3</v>
+        <v>1.6682485999585474E-2</v>
       </c>
       <c r="T21" s="9">
-        <f t="shared" si="6"/>
-        <v>0.94631378292451529</v>
+        <f>R21/MAX($R$2:$R$28)</f>
+        <v>0.41852871774290379</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>36</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>23</v>
+        <v>37</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="C22" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D22" s="8">
-        <v>45482</v>
+        <v>45511</v>
       </c>
       <c r="E22" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>0.12939999999999999</v>
       </c>
       <c r="F22" s="1">
-        <v>147.01</v>
+        <v>501.56</v>
       </c>
       <c r="G22" s="1">
-        <f t="shared" si="0"/>
-        <v>1.4700999999999999E-17</v>
-      </c>
-      <c r="H22" s="11">
-        <v>0.15</v>
+        <f>E22*F22</f>
+        <v>64.901863999999989</v>
+      </c>
+      <c r="H22" s="13">
+        <v>0.25</v>
       </c>
       <c r="I22" s="11">
-        <v>0.52380000000000004</v>
+        <v>0.29699999999999999</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" si="1"/>
-        <v>0.28636884306987398</v>
+        <f>IFERROR(H22/I22,"")</f>
+        <v>0.84175084175084181</v>
       </c>
       <c r="K22" s="9">
         <f>IFERROR(J22/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.4195342410536434E-2</v>
+        <v>0.52195670005230943</v>
       </c>
       <c r="L22" s="12">
-        <f t="shared" si="8"/>
-        <v>169.06149999999997</v>
+        <f>F22/(1-(F22*(1+H22)-F22)/(F22*(1+H22)))</f>
+        <v>626.95000000000005</v>
       </c>
       <c r="M22" s="12">
-        <f t="shared" si="7"/>
-        <v>1.6906149999999997E-17</v>
+        <f>L22*E22</f>
+        <v>81.127330000000001</v>
       </c>
       <c r="N22" s="12">
-        <f t="shared" si="2"/>
-        <v>107.00975396709855</v>
+        <f>F22/(1+I22-H22)</f>
+        <v>479.04489016236869</v>
       </c>
       <c r="O22" s="12">
-        <f t="shared" si="3"/>
-        <v>22.051499999999976</v>
+        <f>L22-F22</f>
+        <v>125.39000000000004</v>
       </c>
       <c r="P22" s="12">
-        <f t="shared" si="4"/>
-        <v>-20.000123016450722</v>
+        <f>0.5*(N22-F22)</f>
+        <v>-11.257554918815657</v>
       </c>
       <c r="Q22" s="15">
-        <f t="shared" si="5"/>
-        <v>2.0513769835492539</v>
+        <f>O22+P22</f>
+        <v>114.13244508118439</v>
       </c>
       <c r="R22" s="12">
         <f>MAX($Q$2:$Q$279)-Q22</f>
-        <v>112.08106809763513</v>
+        <v>0</v>
       </c>
       <c r="S22" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R22)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.9221134039237406E-3</v>
+        <v>0</v>
       </c>
       <c r="T22" s="9">
-        <f t="shared" si="6"/>
-        <v>0.78256116662896091</v>
+        <f>R22/MAX($R$2:$R$28)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>36</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" t="s">
-        <v>30</v>
+        <v>40</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>50</v>
       </c>
       <c r="D23" s="8">
-        <v>45481</v>
+        <v>45511</v>
       </c>
       <c r="E23" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F23" s="1">
-        <v>169.34</v>
+        <v>10.92</v>
       </c>
       <c r="G23" s="1">
-        <f t="shared" si="0"/>
-        <v>1.6933999999999999E-17</v>
-      </c>
-      <c r="H23" s="11">
-        <v>0.1</v>
-      </c>
-      <c r="I23" s="11">
-        <v>0.4259</v>
+        <f>E23*F23</f>
+        <v>1.092E-18</v>
+      </c>
+      <c r="H23" s="13">
+        <v>1</v>
+      </c>
+      <c r="I23" s="13">
+        <v>1.8652</v>
       </c>
       <c r="J23" s="9">
-        <f t="shared" si="1"/>
-        <v>0.23479690068091102</v>
+        <f>IFERROR(H23/I23,"")</f>
+        <v>0.53613553506326406</v>
       </c>
       <c r="K23" s="9">
         <f>IFERROR(J23/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.1638914228127082E-2</v>
+        <v>0.33244936717893181</v>
       </c>
       <c r="L23" s="12">
-        <f t="shared" si="8"/>
-        <v>186.27400000000003</v>
+        <f>F23/(1-(F23*(1+H23)-F23)/(F23*(1+H23)))</f>
+        <v>21.84</v>
       </c>
       <c r="M23" s="12">
-        <f t="shared" si="7"/>
-        <v>1.8627400000000003E-17</v>
+        <f>L23*E23</f>
+        <v>2.1840000000000001E-18</v>
       </c>
       <c r="N23" s="12">
-        <f t="shared" si="2"/>
-        <v>127.71702239987934</v>
+        <f>F23/(1+I23-H23)</f>
+        <v>5.8546000428908433</v>
       </c>
       <c r="O23" s="12">
-        <f t="shared" si="3"/>
-        <v>16.934000000000026</v>
+        <f>L23-F23</f>
+        <v>10.92</v>
       </c>
       <c r="P23" s="12">
-        <f t="shared" si="4"/>
-        <v>-20.811488800060332</v>
+        <f>0.5*(N23-F23)</f>
+        <v>-2.5326999785545783</v>
       </c>
       <c r="Q23" s="15">
-        <f t="shared" si="5"/>
-        <v>-3.8774888000603056</v>
+        <f>O23+P23</f>
+        <v>8.3873000214454212</v>
       </c>
       <c r="R23" s="12">
         <f>MAX($Q$2:$Q$279)-Q23</f>
-        <v>118.00993388124469</v>
+        <v>105.74514505973896</v>
       </c>
       <c r="S23" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R23)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.4738628953585898E-3</v>
+        <v>9.4566989286843078E-3</v>
       </c>
       <c r="T23" s="9">
-        <f t="shared" si="6"/>
-        <v>0.82395709729912847</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R23/MAX($R$2:$R$28)</f>
+        <v>0.73832312171768166</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>32</v>
+        <v>37</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" t="s">
+        <v>25</v>
       </c>
       <c r="D24" s="8">
         <v>45511</v>
@@ -4127,1697 +4131,1730 @@
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F24" s="1">
-        <v>113.58</v>
+        <v>283.43</v>
       </c>
       <c r="G24" s="1">
-        <f t="shared" si="0"/>
-        <v>1.1357999999999999E-17</v>
-      </c>
-      <c r="H24" s="11">
-        <f>121.15/F24-1</f>
-        <v>6.664905793273479E-2</v>
+        <f>E24*F24</f>
+        <v>2.8342999999999998E-17</v>
+      </c>
+      <c r="H24" s="13">
+        <v>0.25</v>
       </c>
       <c r="I24" s="11">
-        <v>0.16439999999999999</v>
+        <v>0.26</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" si="1"/>
-        <v>0.40540789496797319</v>
+        <f>IFERROR(H24/I24,"")</f>
+        <v>0.96153846153846145</v>
       </c>
       <c r="K24" s="9">
         <f>IFERROR(J24/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.0096124366438057E-2</v>
+        <v>0.59623515352129186</v>
       </c>
       <c r="L24" s="12">
-        <f t="shared" si="8"/>
-        <v>121.15000000000002</v>
+        <f>F24/(1-(F24*(1+H24)-F24)/(F24*(1+H24)))</f>
+        <v>354.28750000000002</v>
       </c>
       <c r="M24" s="12">
-        <f t="shared" si="7"/>
-        <v>1.2115000000000002E-17</v>
+        <f>L24*E24</f>
+        <v>3.542875E-17</v>
       </c>
       <c r="N24" s="12">
-        <f t="shared" si="2"/>
-        <v>103.46609203186667</v>
+        <f>F24/(1+I24-H24)</f>
+        <v>280.62376237623761</v>
       </c>
       <c r="O24" s="12">
-        <f t="shared" si="3"/>
-        <v>7.5700000000000216</v>
+        <f>L24-F24</f>
+        <v>70.857500000000016</v>
       </c>
       <c r="P24" s="12">
-        <f t="shared" si="4"/>
-        <v>-5.0569539840666664</v>
+        <f>0.5*(N24-F24)</f>
+        <v>-1.4031188118811997</v>
       </c>
       <c r="Q24" s="15">
-        <f t="shared" si="5"/>
-        <v>2.5130460159333552</v>
+        <f>O24+P24</f>
+        <v>69.454381188118816</v>
       </c>
       <c r="R24" s="12">
         <f>MAX($Q$2:$Q$279)-Q24</f>
-        <v>111.61939906525103</v>
+        <v>44.67806389306557</v>
       </c>
       <c r="S24" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R24)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.9590161600441413E-3</v>
+        <v>2.2382348581474875E-2</v>
       </c>
       <c r="T24" s="9">
-        <f t="shared" si="6"/>
-        <v>0.77933774752071117</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R24/MAX($R$2:$R$28)</f>
+        <v>0.311946686414727</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>36</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>83</v>
+        <v>10</v>
       </c>
       <c r="C25" t="s">
-        <v>84</v>
+        <v>9</v>
       </c>
       <c r="D25" s="8">
-        <v>45481</v>
+        <v>45544</v>
       </c>
       <c r="E25" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F25" s="1">
-        <v>64.349999999999994</v>
+        <v>188.12</v>
       </c>
       <c r="G25" s="1">
-        <f t="shared" si="0"/>
-        <v>6.4349999999999993E-18</v>
-      </c>
-      <c r="H25" s="11">
+        <f>E25*F25</f>
+        <v>1.8812000000000001E-17</v>
+      </c>
+      <c r="H25" s="13">
         <v>0.15</v>
       </c>
       <c r="I25" s="11">
-        <v>0.67300000000000004</v>
+        <v>0.37780000000000002</v>
       </c>
       <c r="J25" s="9">
-        <f t="shared" si="1"/>
-        <v>0.22288261515601782</v>
+        <f>IFERROR(H25/I25,"")</f>
+        <v>0.39703546850185278</v>
       </c>
       <c r="K25" s="9">
         <f>IFERROR(J25/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.1048321477918253E-2</v>
+        <v>0.24619556365622425</v>
       </c>
       <c r="L25" s="12">
-        <f t="shared" si="8"/>
-        <v>74.002499999999984</v>
+        <f>F25/(1-(F25*(1+H25)-F25)/(F25*(1+H25)))</f>
+        <v>216.33799999999999</v>
       </c>
       <c r="M25" s="12">
-        <f t="shared" si="7"/>
-        <v>7.4002499999999988E-18</v>
+        <f>L25*E25</f>
+        <v>2.16338E-17</v>
       </c>
       <c r="N25" s="12">
-        <f t="shared" si="2"/>
-        <v>42.252133946158892</v>
+        <f>F25/(1+I25-H25)</f>
+        <v>153.21713634142367</v>
       </c>
       <c r="O25" s="12">
-        <f t="shared" si="3"/>
-        <v>9.6524999999999892</v>
+        <f>L25-F25</f>
+        <v>28.217999999999989</v>
       </c>
       <c r="P25" s="12">
-        <f t="shared" si="4"/>
-        <v>-11.048933026920551</v>
+        <f>0.5*(N25-F25)</f>
+        <v>-17.451431829288168</v>
       </c>
       <c r="Q25" s="15">
-        <f t="shared" si="5"/>
-        <v>-1.3964330269205618</v>
+        <f>O25+P25</f>
+        <v>10.766568170711821</v>
       </c>
       <c r="R25" s="12">
         <f>MAX($Q$2:$Q$279)-Q25</f>
-        <v>115.52887810810495</v>
+        <v>103.36587691047256</v>
       </c>
       <c r="S25" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R25)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.6558444639638962E-3</v>
+        <v>9.6743725288193673E-3</v>
       </c>
       <c r="T25" s="9">
-        <f t="shared" si="6"/>
-        <v>0.80663411909010196</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R25/MAX($R$2:$R$28)</f>
+        <v>0.72171083482377829</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>48</v>
+        <v>36</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" t="s">
+        <v>17</v>
       </c>
       <c r="D26" s="8">
-        <v>45511</v>
+        <v>45483</v>
       </c>
       <c r="E26" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F26" s="1">
-        <v>20.82</v>
+        <v>167.24</v>
       </c>
       <c r="G26" s="1">
-        <f t="shared" si="0"/>
-        <v>2.0820000000000002E-18</v>
+        <f>E26*F26</f>
+        <v>1.6724000000000001E-17</v>
       </c>
       <c r="H26" s="13">
-        <v>0.05</v>
+        <f>190.41/F26-1</f>
+        <v>0.13854341066730447</v>
       </c>
       <c r="I26" s="11">
-        <v>0.7389</v>
+        <v>0.26790000000000003</v>
       </c>
       <c r="J26" s="9">
-        <f t="shared" si="1"/>
-        <v>6.7668155366084726E-2</v>
+        <f>IFERROR(H26/I26,"")</f>
+        <v>0.51714598979956872</v>
       </c>
       <c r="K26" s="9">
         <f>IFERROR(J26/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.3543196439026418E-3</v>
+        <v>0.32067424336590894</v>
       </c>
       <c r="L26" s="12">
-        <f t="shared" si="8"/>
-        <v>21.861000000000001</v>
+        <f>F26/(1-(F26*(1+H26)-F26)/(F26*(1+H26)))</f>
+        <v>190.41</v>
       </c>
       <c r="M26" s="12">
-        <f t="shared" si="7"/>
-        <v>2.1860999999999999E-18</v>
+        <f>L26*E26</f>
+        <v>1.9040999999999999E-17</v>
       </c>
       <c r="N26" s="12">
-        <f t="shared" si="2"/>
-        <v>12.327550476641601</v>
+        <f>F26/(1+I26-H26)</f>
+        <v>148.08431772538498</v>
       </c>
       <c r="O26" s="12">
-        <f t="shared" si="3"/>
-        <v>1.0410000000000004</v>
+        <f>L26-F26</f>
+        <v>23.169999999999987</v>
       </c>
       <c r="P26" s="12">
-        <f t="shared" si="4"/>
-        <v>-4.2462247616791995</v>
+        <f>0.5*(N26-F26)</f>
+        <v>-9.5778411373075159</v>
       </c>
       <c r="Q26" s="15">
-        <f t="shared" si="5"/>
-        <v>-3.2052247616791991</v>
+        <f>O26+P26</f>
+        <v>13.592158862692472</v>
       </c>
       <c r="R26" s="12">
         <f>MAX($Q$2:$Q$279)-Q26</f>
-        <v>117.33766984286359</v>
+        <v>100.54028621849191</v>
       </c>
       <c r="S26" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R26)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.5224122938454567E-3</v>
+        <v>9.9462617186788418E-3</v>
       </c>
       <c r="T26" s="9">
-        <f t="shared" si="6"/>
-        <v>0.81926328291024408</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R26/MAX($R$2:$R$28)</f>
+        <v>0.70198227953907921</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>52</v>
+        <v>39</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="C27" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="D27" s="8">
-        <v>45511</v>
+        <v>45562</v>
       </c>
       <c r="E27" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F27" s="1">
-        <v>13.04</v>
+        <v>668.82</v>
       </c>
       <c r="G27" s="1">
-        <f t="shared" si="0"/>
-        <v>1.304E-18</v>
-      </c>
-      <c r="H27" s="11">
-        <f>13.72/F27-1</f>
-        <v>5.2147239263803824E-2</v>
+        <f>E27*F27</f>
+        <v>6.6881999999999999E-17</v>
+      </c>
+      <c r="H27" s="13">
+        <v>0.05</v>
       </c>
       <c r="I27" s="11">
-        <v>0.30159999999999998</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="J27" s="9">
-        <f t="shared" si="1"/>
-        <v>0.17290198694895167</v>
+        <f>IFERROR(H27/I27,"")</f>
+        <v>0.17857142857142858</v>
       </c>
       <c r="K27" s="9">
         <f>IFERROR(J27/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>8.5707749554430283E-3</v>
+        <v>0.11072938565395421</v>
       </c>
       <c r="L27" s="12">
-        <f t="shared" si="8"/>
-        <v>13.72</v>
+        <f>F27/(1-(F27*(1+H27)-F27)/(F27*(1+H27)))</f>
+        <v>702.26100000000008</v>
       </c>
       <c r="M27" s="12">
-        <f t="shared" si="7"/>
-        <v>1.3720000000000001E-18</v>
+        <f>L27*E27</f>
+        <v>7.0226100000000009E-17</v>
       </c>
       <c r="N27" s="12">
-        <f t="shared" si="2"/>
-        <v>10.436569040286594</v>
+        <f>F27/(1+I27-H27)</f>
+        <v>543.7560975609756</v>
       </c>
       <c r="O27" s="12">
-        <f t="shared" si="3"/>
-        <v>0.68000000000000149</v>
+        <f>L27-F27</f>
+        <v>33.441000000000031</v>
       </c>
       <c r="P27" s="12">
-        <f t="shared" si="4"/>
-        <v>-1.3017154798567026</v>
+        <f>0.5*(N27-F27)</f>
+        <v>-62.531951219512223</v>
       </c>
       <c r="Q27" s="15">
-        <f t="shared" si="5"/>
-        <v>-0.62171547985670106</v>
+        <f>O27+P27</f>
+        <v>-29.090951219512192</v>
       </c>
       <c r="R27" s="12">
         <f>MAX($Q$2:$Q$279)-Q27</f>
-        <v>114.75416056104109</v>
+        <v>143.22339630069658</v>
       </c>
       <c r="S27" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R27)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.7142809908671744E-3</v>
+        <v>6.9820994741704532E-3</v>
       </c>
       <c r="T27" s="9">
-        <f t="shared" si="6"/>
-        <v>0.80122496411211674</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R27/MAX($R$2:$R$28)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>45</v>
+        <v>36</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="C28" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="D28" s="8">
-        <v>45511</v>
+        <v>45481</v>
       </c>
       <c r="E28" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F28" s="1">
-        <v>11.05</v>
+        <v>700.32</v>
       </c>
       <c r="G28" s="1">
-        <f t="shared" si="0"/>
-        <v>1.1050000000000001E-18</v>
-      </c>
-      <c r="H28" s="11">
-        <v>0.05</v>
+        <f>E28*F28</f>
+        <v>7.0031999999999998E-17</v>
+      </c>
+      <c r="H28" s="13">
+        <v>0.1</v>
       </c>
       <c r="I28" s="11">
-        <v>0.72170000000000001</v>
+        <v>0.45340000000000003</v>
       </c>
       <c r="J28" s="9">
-        <f t="shared" si="1"/>
-        <v>6.9280864625190522E-2</v>
+        <f>IFERROR(H28/I28,"")</f>
+        <v>0.22055580061755625</v>
       </c>
       <c r="K28" s="9">
         <f>IFERROR(J28/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.434261860717281E-3</v>
+        <v>0.13676324650686891</v>
       </c>
       <c r="L28" s="12">
-        <f t="shared" si="8"/>
-        <v>11.602500000000001</v>
+        <f>F28/(1-(F28*(1+H28)-F28)/(F28*(1+H28)))</f>
+        <v>770.35200000000009</v>
       </c>
       <c r="M28" s="12">
-        <f t="shared" si="7"/>
-        <v>1.16025E-18</v>
+        <f>L28*E28</f>
+        <v>7.7035200000000004E-17</v>
       </c>
       <c r="N28" s="12">
-        <f t="shared" si="2"/>
-        <v>6.6100376861877139</v>
+        <f>F28/(1+I28-H28)</f>
+        <v>517.45234224915032</v>
       </c>
       <c r="O28" s="12">
-        <f t="shared" si="3"/>
-        <v>0.55250000000000021</v>
+        <f>L28-F28</f>
+        <v>70.032000000000039</v>
       </c>
       <c r="P28" s="12">
-        <f t="shared" si="4"/>
-        <v>-2.2199811569061434</v>
+        <f>0.5*(N28-F28)</f>
+        <v>-91.433828875424865</v>
       </c>
       <c r="Q28" s="15">
-        <f t="shared" si="5"/>
-        <v>-1.6674811569061432</v>
+        <f>O28+P28</f>
+        <v>-21.401828875424826</v>
       </c>
       <c r="R28" s="12">
         <f>MAX($Q$2:$Q$279)-Q28</f>
-        <v>115.79992623809053</v>
+        <v>135.53427395660921</v>
       </c>
       <c r="S28" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R28)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.6355840844315329E-3</v>
+        <v>7.37820752498476E-3</v>
       </c>
       <c r="T28" s="9">
-        <f t="shared" si="6"/>
-        <v>0.80852660409594923</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R28/MAX($R$2:$R$28)</f>
+        <v>0.94631378292451529</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>74</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C29" s="14" t="s">
-        <v>80</v>
+        <v>36</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" t="s">
+        <v>24</v>
       </c>
       <c r="D29" s="8">
-        <f ca="1">TODAY()-20</f>
-        <v>45666</v>
+        <v>45482</v>
       </c>
       <c r="E29" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F29" s="1">
-        <v>2742.9</v>
+        <v>147.01</v>
       </c>
       <c r="G29" s="1">
-        <f t="shared" si="0"/>
-        <v>2.7429000000000002E-16</v>
-      </c>
-      <c r="H29" s="11">
-        <v>0.1</v>
+        <f>E29*F29</f>
+        <v>1.4700999999999999E-17</v>
+      </c>
+      <c r="H29" s="13">
+        <v>0.15</v>
       </c>
       <c r="I29" s="11">
-        <v>0.5</v>
+        <v>0.52380000000000004</v>
       </c>
       <c r="J29" s="9">
-        <f t="shared" si="1"/>
-        <v>0.2</v>
+        <f>IFERROR(H29/I29,"")</f>
+        <v>0.28636884306987398</v>
       </c>
       <c r="K29" s="9">
         <f>IFERROR(J29/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>9.9140271395186472E-3</v>
+        <v>0.17757289795594031</v>
       </c>
       <c r="L29" s="12">
-        <f t="shared" si="8"/>
-        <v>3017.1900000000005</v>
+        <f>F29/(1-(F29*(1+H29)-F29)/(F29*(1+H29)))</f>
+        <v>169.06149999999997</v>
       </c>
       <c r="M29" s="12">
-        <f t="shared" si="7"/>
-        <v>3.0171900000000003E-16</v>
+        <f>L29*E29</f>
+        <v>1.6906149999999997E-17</v>
       </c>
       <c r="N29" s="12">
-        <f t="shared" si="2"/>
-        <v>1959.214285714286</v>
+        <f>F29/(1+I29-H29)</f>
+        <v>107.00975396709855</v>
       </c>
       <c r="O29" s="12">
-        <f t="shared" si="3"/>
-        <v>274.29000000000042</v>
+        <f>L29-F29</f>
+        <v>22.051499999999976</v>
       </c>
       <c r="P29" s="12">
-        <f t="shared" si="4"/>
-        <v>-391.84285714285704</v>
+        <f>0.5*(N29-F29)</f>
+        <v>-20.000123016450722</v>
       </c>
       <c r="Q29" s="15">
-        <f t="shared" si="5"/>
-        <v>-117.55285714285662</v>
+        <f>O29+P29</f>
+        <v>2.0513769835492539</v>
       </c>
       <c r="R29" s="12">
         <f>MAX($Q$2:$Q$279)-Q29</f>
-        <v>231.68530222404101</v>
+        <v>112.08106809763513</v>
       </c>
       <c r="S29" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R29)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>4.316199562080957E-3</v>
+        <v>8.9221134039237406E-3</v>
       </c>
       <c r="T29" s="9">
-        <f t="shared" si="6"/>
-        <v>1.6176498268314992</v>
+        <f>R29/MAX($R$2:$R$28)</f>
+        <v>0.78256116662896091</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>54</v>
+        <v>36</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="C30" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="D30" s="8">
-        <v>45505</v>
+        <v>45481</v>
       </c>
       <c r="E30" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F30" s="1">
-        <v>86.6</v>
+        <v>169.34</v>
       </c>
       <c r="G30" s="1">
-        <f t="shared" si="0"/>
-        <v>8.6599999999999986E-18</v>
-      </c>
-      <c r="H30" s="11">
-        <v>7.0000000000000007E-2</v>
+        <f>E30*F30</f>
+        <v>1.6933999999999999E-17</v>
+      </c>
+      <c r="H30" s="13">
+        <v>0.1</v>
       </c>
       <c r="I30" s="11">
-        <v>0.17249999999999999</v>
+        <v>0.4259</v>
       </c>
       <c r="J30" s="9">
-        <f t="shared" si="1"/>
-        <v>0.40579710144927544</v>
+        <f>IFERROR(H30/I30,"")</f>
+        <v>0.23479690068091102</v>
       </c>
       <c r="K30" s="9">
         <f>IFERROR(J30/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.0115417384530591E-2</v>
+        <v>0.14559393276875876</v>
       </c>
       <c r="L30" s="12">
-        <f t="shared" si="8"/>
-        <v>92.662000000000006</v>
+        <f>F30/(1-(F30*(1+H30)-F30)/(F30*(1+H30)))</f>
+        <v>186.27400000000003</v>
       </c>
       <c r="M30" s="12">
-        <f t="shared" si="7"/>
-        <v>9.2662000000000008E-18</v>
+        <f>L30*E30</f>
+        <v>1.8627400000000003E-17</v>
       </c>
       <c r="N30" s="12">
-        <f t="shared" si="2"/>
-        <v>78.548752834467123</v>
+        <f>F30/(1+I30-H30)</f>
+        <v>127.71702239987934</v>
       </c>
       <c r="O30" s="12">
-        <f t="shared" si="3"/>
-        <v>6.0620000000000118</v>
+        <f>L30-F30</f>
+        <v>16.934000000000026</v>
       </c>
       <c r="P30" s="12">
-        <f t="shared" si="4"/>
-        <v>-4.0256235827664355</v>
+        <f>0.5*(N30-F30)</f>
+        <v>-20.811488800060332</v>
       </c>
       <c r="Q30" s="15">
-        <f t="shared" si="5"/>
-        <v>2.0363764172335763</v>
+        <f>O30+P30</f>
+        <v>-3.8774888000603056</v>
       </c>
       <c r="R30" s="12">
         <f>MAX($Q$2:$Q$279)-Q30</f>
-        <v>112.0960686639508</v>
+        <v>118.00993388124469</v>
       </c>
       <c r="S30" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R30)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.9209194570227784E-3</v>
+        <v>8.4738628953585915E-3</v>
       </c>
       <c r="T30" s="9">
-        <f t="shared" si="6"/>
-        <v>0.78266590207514586</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R30/MAX($R$2:$R$28)</f>
+        <v>0.82395709729912847</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>71</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C31" t="s">
-        <v>73</v>
+        <v>40</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>32</v>
       </c>
       <c r="D31" s="8">
-        <v>45562</v>
+        <v>45511</v>
       </c>
       <c r="E31" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F31" s="1">
-        <v>56</v>
+        <v>113.58</v>
       </c>
       <c r="G31" s="1">
-        <f t="shared" si="0"/>
-        <v>5.5999999999999995E-18</v>
-      </c>
-      <c r="H31" s="11">
-        <v>7.0000000000000007E-2</v>
+        <f>E31*F31</f>
+        <v>1.1357999999999999E-17</v>
+      </c>
+      <c r="H31" s="13">
+        <f>121.15/F31-1</f>
+        <v>6.664905793273479E-2</v>
       </c>
       <c r="I31" s="11">
-        <v>0.19</v>
+        <v>0.16439999999999999</v>
       </c>
       <c r="J31" s="9">
-        <f t="shared" si="1"/>
-        <v>0.36842105263157898</v>
+        <f>IFERROR(H31/I31,"")</f>
+        <v>0.40540789496797319</v>
       </c>
       <c r="K31" s="9">
         <f>IFERROR(J31/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.826268157279751E-2</v>
+        <v>0.25138717603477223</v>
       </c>
       <c r="L31" s="12">
-        <f t="shared" si="8"/>
-        <v>59.92</v>
+        <f>F31/(1-(F31*(1+H31)-F31)/(F31*(1+H31)))</f>
+        <v>121.15000000000002</v>
       </c>
       <c r="M31" s="12">
-        <f t="shared" si="7"/>
-        <v>5.9920000000000002E-18</v>
+        <f>L31*E31</f>
+        <v>1.2115000000000002E-17</v>
       </c>
       <c r="N31" s="12">
-        <f t="shared" si="2"/>
-        <v>50.000000000000007</v>
+        <f>F31/(1+I31-H31)</f>
+        <v>103.46609203186667</v>
       </c>
       <c r="O31" s="12">
-        <f t="shared" si="3"/>
-        <v>3.9200000000000017</v>
+        <f>L31-F31</f>
+        <v>7.5700000000000216</v>
       </c>
       <c r="P31" s="12">
-        <f t="shared" si="4"/>
-        <v>-2.9999999999999964</v>
+        <f>0.5*(N31-F31)</f>
+        <v>-5.0569539840666664</v>
       </c>
       <c r="Q31" s="15">
-        <f t="shared" si="5"/>
-        <v>0.92000000000000526</v>
+        <f>O31+P31</f>
+        <v>2.5130460159333552</v>
       </c>
       <c r="R31" s="12">
         <f>MAX($Q$2:$Q$279)-Q31</f>
-        <v>113.21244508118438</v>
+        <v>111.61939906525103</v>
       </c>
       <c r="S31" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R31)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.832951176727102E-3</v>
+        <v>8.9590161600441413E-3</v>
       </c>
       <c r="T31" s="9">
-        <f t="shared" si="6"/>
-        <v>0.79046055327088882</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R31/MAX($R$2:$R$28)</f>
+        <v>0.77933774752071117</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>74</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>75</v>
+        <v>36</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>83</v>
       </c>
       <c r="C32" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D32" s="8">
-        <v>45580</v>
+        <v>45481</v>
       </c>
       <c r="E32" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F32" s="1">
-        <v>20.399999999999999</v>
+        <v>64.349999999999994</v>
       </c>
       <c r="G32" s="1">
-        <f t="shared" si="0"/>
-        <v>2.0399999999999999E-18</v>
-      </c>
-      <c r="H32" s="11">
-        <v>0.1</v>
+        <f>E32*F32</f>
+        <v>6.4349999999999993E-18</v>
+      </c>
+      <c r="H32" s="13">
+        <v>0.15</v>
       </c>
       <c r="I32" s="11">
-        <v>0.15</v>
+        <v>0.67300000000000004</v>
       </c>
       <c r="J32" s="9">
-        <f t="shared" si="1"/>
-        <v>0.66666666666666674</v>
+        <f>IFERROR(H32/I32,"")</f>
+        <v>0.22288261515601782</v>
       </c>
       <c r="K32" s="9">
         <f>IFERROR(J32/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.3046757131728825E-2</v>
+        <v>0.1382060682753663</v>
       </c>
       <c r="L32" s="12">
-        <v>21.2</v>
+        <f>F32/(1-(F32*(1+H32)-F32)/(F32*(1+H32)))</f>
+        <v>74.002499999999984</v>
       </c>
       <c r="M32" s="12">
-        <f t="shared" si="7"/>
-        <v>2.1199999999999999E-18</v>
+        <f>L32*E32</f>
+        <v>7.4002499999999988E-18</v>
       </c>
       <c r="N32" s="12">
-        <f t="shared" si="2"/>
-        <v>19.428571428571431</v>
+        <f>F32/(1+I32-H32)</f>
+        <v>42.252133946158892</v>
       </c>
       <c r="O32" s="12">
-        <f t="shared" si="3"/>
-        <v>0.80000000000000071</v>
+        <f>L32-F32</f>
+        <v>9.6524999999999892</v>
       </c>
       <c r="P32" s="12">
-        <f t="shared" si="4"/>
-        <v>-0.48571428571428399</v>
+        <f>0.5*(N32-F32)</f>
+        <v>-11.048933026920551</v>
       </c>
       <c r="Q32" s="15">
-        <f t="shared" si="5"/>
-        <v>0.31428571428571672</v>
+        <f>O32+P32</f>
+        <v>-1.3964330269205618</v>
       </c>
       <c r="R32" s="12">
         <f>MAX($Q$2:$Q$279)-Q32</f>
-        <v>113.81815936689867</v>
+        <v>115.52887810810495</v>
       </c>
       <c r="S32" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R32)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.7859442250902038E-3</v>
+        <v>8.6558444639638962E-3</v>
       </c>
       <c r="T32" s="9">
-        <f t="shared" si="6"/>
-        <v>0.79468971066667204</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R32/MAX($R$2:$R$28)</f>
+        <v>0.80663411909010196</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C33" t="s">
-        <v>56</v>
+        <v>40</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>48</v>
       </c>
       <c r="D33" s="8">
-        <v>45574</v>
+        <v>45511</v>
       </c>
       <c r="E33" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F33" s="1">
-        <v>47.42</v>
+        <v>20.82</v>
       </c>
       <c r="G33" s="1">
-        <f t="shared" si="0"/>
-        <v>4.7419999999999999E-18</v>
-      </c>
-      <c r="H33" s="11">
-        <v>7.0000000000000007E-2</v>
+        <f>E33*F33</f>
+        <v>2.0820000000000002E-18</v>
+      </c>
+      <c r="H33" s="13">
+        <v>0.05</v>
       </c>
       <c r="I33" s="11">
-        <v>0.4</v>
+        <v>0.7389</v>
       </c>
       <c r="J33" s="9">
-        <f t="shared" si="1"/>
-        <v>0.17500000000000002</v>
+        <f>IFERROR(H33/I33,"")</f>
+        <v>6.7668155366084726E-2</v>
       </c>
       <c r="K33" s="9">
         <f>IFERROR(J33/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>8.6747737470788174E-3</v>
+        <v>4.1959978323328165E-2</v>
       </c>
       <c r="L33" s="12">
-        <f t="shared" ref="L33:L41" si="9">F33/(1-(F33*(1+H33)-F33)/(F33*(1+H33)))</f>
-        <v>50.739400000000003</v>
+        <f>F33/(1-(F33*(1+H33)-F33)/(F33*(1+H33)))</f>
+        <v>21.861000000000001</v>
       </c>
       <c r="M33" s="12">
-        <f t="shared" si="7"/>
-        <v>5.0739400000000001E-18</v>
+        <f>L33*E33</f>
+        <v>2.1860999999999999E-18</v>
       </c>
       <c r="N33" s="12">
-        <f t="shared" si="2"/>
-        <v>35.654135338345867</v>
+        <f>F33/(1+I33-H33)</f>
+        <v>12.327550476641601</v>
       </c>
       <c r="O33" s="12">
-        <f t="shared" si="3"/>
-        <v>3.3194000000000017</v>
+        <f>L33-F33</f>
+        <v>1.0410000000000004</v>
       </c>
       <c r="P33" s="12">
-        <f t="shared" si="4"/>
-        <v>-5.8829323308270673</v>
+        <f>0.5*(N33-F33)</f>
+        <v>-4.2462247616791995</v>
       </c>
       <c r="Q33" s="15">
-        <f t="shared" si="5"/>
-        <v>-2.5635323308270657</v>
+        <f>O33+P33</f>
+        <v>-3.2052247616791991</v>
       </c>
       <c r="R33" s="12">
         <f>MAX($Q$2:$Q$279)-Q33</f>
-        <v>116.69597741201144</v>
+        <v>117.33766984286359</v>
       </c>
       <c r="S33" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R33)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.5692756697976005E-3</v>
+        <v>8.5224122938454567E-3</v>
       </c>
       <c r="T33" s="9">
-        <f t="shared" si="6"/>
-        <v>0.81478292252621221</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R33/MAX($R$2:$R$28)</f>
+        <v>0.81926328291024408</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="C34" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D34" s="8">
-        <v>45507</v>
+        <v>45511</v>
       </c>
       <c r="E34" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F34" s="1">
-        <v>41.8</v>
+        <v>13.04</v>
       </c>
       <c r="G34" s="1">
-        <f t="shared" si="0"/>
-        <v>4.1799999999999993E-18</v>
-      </c>
-      <c r="H34" s="11">
-        <v>7.0000000000000007E-2</v>
+        <f>E34*F34</f>
+        <v>1.304E-18</v>
+      </c>
+      <c r="H34" s="13">
+        <f>13.72/F34-1</f>
+        <v>5.2147239263803824E-2</v>
       </c>
       <c r="I34" s="11">
-        <v>0.4</v>
+        <v>0.30159999999999998</v>
       </c>
       <c r="J34" s="9">
-        <f t="shared" si="1"/>
-        <v>0.17500000000000002</v>
+        <f>IFERROR(H34/I34,"")</f>
+        <v>0.17290198694895167</v>
       </c>
       <c r="K34" s="9">
         <f>IFERROR(J34/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>8.6747737470788174E-3</v>
+        <v>0.10721385244195039</v>
       </c>
       <c r="L34" s="12">
-        <f t="shared" si="9"/>
-        <v>44.725999999999999</v>
+        <f>F34/(1-(F34*(1+H34)-F34)/(F34*(1+H34)))</f>
+        <v>13.72</v>
       </c>
       <c r="M34" s="12">
-        <f t="shared" si="7"/>
-        <v>4.4725999999999996E-18</v>
+        <f>L34*E34</f>
+        <v>1.3720000000000001E-18</v>
       </c>
       <c r="N34" s="12">
-        <f t="shared" si="2"/>
-        <v>31.428571428571431</v>
+        <f>F34/(1+I34-H34)</f>
+        <v>10.436569040286594</v>
       </c>
       <c r="O34" s="12">
-        <f t="shared" si="3"/>
-        <v>2.9260000000000019</v>
+        <f>L34-F34</f>
+        <v>0.68000000000000149</v>
       </c>
       <c r="P34" s="12">
-        <f t="shared" si="4"/>
-        <v>-5.1857142857142833</v>
+        <f>0.5*(N34-F34)</f>
+        <v>-1.3017154798567026</v>
       </c>
       <c r="Q34" s="15">
-        <f t="shared" si="5"/>
-        <v>-2.2597142857142813</v>
+        <f>O34+P34</f>
+        <v>-0.62171547985670106</v>
       </c>
       <c r="R34" s="12">
         <f>MAX($Q$2:$Q$279)-Q34</f>
-        <v>116.39215936689867</v>
+        <v>114.75416056104109</v>
       </c>
       <c r="S34" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R34)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.5916440200042785E-3</v>
+        <v>8.7142809908671744E-3</v>
       </c>
       <c r="T34" s="9">
-        <f t="shared" si="6"/>
-        <v>0.81266163471318675</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R34/MAX($R$2:$R$28)</f>
+        <v>0.80122496411211674</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="C35" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="D35" s="8">
-        <v>45574</v>
+        <v>45511</v>
       </c>
       <c r="E35" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F35" s="1">
-        <v>153.7552</v>
+        <v>11.05</v>
       </c>
       <c r="G35" s="1">
-        <f t="shared" si="0"/>
-        <v>1.5375519999999999E-17</v>
-      </c>
-      <c r="H35" s="11">
-        <v>7.0000000000000007E-2</v>
+        <f>E35*F35</f>
+        <v>1.1050000000000001E-18</v>
+      </c>
+      <c r="H35" s="13">
+        <v>0.05</v>
       </c>
       <c r="I35" s="11">
-        <v>0.19</v>
+        <v>0.72170000000000001</v>
       </c>
       <c r="J35" s="9">
-        <f t="shared" si="1"/>
-        <v>0.36842105263157898</v>
+        <f>IFERROR(H35/I35,"")</f>
+        <v>6.9280864625190522E-2</v>
       </c>
       <c r="K35" s="9">
         <f>IFERROR(J35/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.826268157279751E-2</v>
+        <v>4.2959994434123842E-2</v>
       </c>
       <c r="L35" s="12">
-        <f t="shared" si="9"/>
-        <v>164.51806400000001</v>
+        <f>F35/(1-(F35*(1+H35)-F35)/(F35*(1+H35)))</f>
+        <v>11.602500000000001</v>
       </c>
       <c r="M35" s="12">
-        <f t="shared" si="7"/>
-        <v>1.6451806399999999E-17</v>
+        <f>L35*E35</f>
+        <v>1.16025E-18</v>
       </c>
       <c r="N35" s="12">
-        <f t="shared" si="2"/>
-        <v>137.28142857142859</v>
+        <f>F35/(1+I35-H35)</f>
+        <v>6.6100376861877139</v>
       </c>
       <c r="O35" s="12">
-        <f t="shared" si="3"/>
-        <v>10.762864000000008</v>
+        <f>L35-F35</f>
+        <v>0.55250000000000021</v>
       </c>
       <c r="P35" s="12">
-        <f t="shared" si="4"/>
-        <v>-8.2368857142857053</v>
+        <f>0.5*(N35-F35)</f>
+        <v>-2.2199811569061434</v>
       </c>
       <c r="Q35" s="15">
-        <f t="shared" si="5"/>
-        <v>2.5259782857143023</v>
+        <f>O35+P35</f>
+        <v>-1.6674811569061432</v>
       </c>
       <c r="R35" s="12">
         <f>MAX($Q$2:$Q$279)-Q35</f>
-        <v>111.60646679547008</v>
+        <v>115.79992623809053</v>
       </c>
       <c r="S35" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R35)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.9600542756415654E-3</v>
+        <v>8.6355840844315312E-3</v>
       </c>
       <c r="T35" s="9">
-        <f t="shared" si="6"/>
-        <v>0.77924745312667376</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R35/MAX($R$2:$R$28)</f>
+        <v>0.80852660409594923</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>87</v>
-      </c>
-      <c r="B36" t="s">
-        <v>88</v>
-      </c>
-      <c r="C36" s="32" t="s">
-        <v>89</v>
+        <v>74</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>80</v>
       </c>
       <c r="D36" s="8">
-        <v>45627</v>
+        <f ca="1">TODAY()-20</f>
+        <v>45671</v>
       </c>
       <c r="E36" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F36" s="1">
-        <v>133.53</v>
+        <v>2742.9</v>
       </c>
       <c r="G36" s="1">
-        <f t="shared" si="0"/>
-        <v>1.3353E-17</v>
-      </c>
-      <c r="H36" s="11">
-        <v>7.0000000000000007E-2</v>
+        <f>E36*F36</f>
+        <v>2.7429000000000002E-16</v>
+      </c>
+      <c r="H36" s="13">
+        <v>0.1</v>
       </c>
       <c r="I36" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="J36" s="9">
+        <f>IFERROR(H36/I36,"")</f>
         <v>0.2</v>
-      </c>
-      <c r="J36" s="9">
-        <f t="shared" si="1"/>
-        <v>0.35000000000000003</v>
       </c>
       <c r="K36" s="9">
         <f>IFERROR(J36/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.7349547494157635E-2</v>
+        <v>0.12401691193242873</v>
       </c>
       <c r="L36" s="12">
-        <f t="shared" si="9"/>
-        <v>142.87710000000001</v>
+        <f>F36/(1-(F36*(1+H36)-F36)/(F36*(1+H36)))</f>
+        <v>3017.1900000000005</v>
       </c>
       <c r="M36" s="12">
-        <f t="shared" si="7"/>
-        <v>1.428771E-17</v>
+        <f>L36*E36</f>
+        <v>3.0171900000000003E-16</v>
       </c>
       <c r="N36" s="12">
-        <f t="shared" si="2"/>
-        <v>118.16814159292036</v>
+        <f>F36/(1+I36-H36)</f>
+        <v>1959.214285714286</v>
       </c>
       <c r="O36" s="12">
-        <f t="shared" si="3"/>
-        <v>9.3471000000000117</v>
+        <f>L36-F36</f>
+        <v>274.29000000000042</v>
       </c>
       <c r="P36" s="12">
-        <f t="shared" si="4"/>
-        <v>-7.6809292035398187</v>
+        <f>0.5*(N36-F36)</f>
+        <v>-391.84285714285704</v>
       </c>
       <c r="Q36" s="15">
-        <f t="shared" si="5"/>
-        <v>1.6661707964601931</v>
+        <f>O36+P36</f>
+        <v>-117.55285714285662</v>
       </c>
       <c r="R36" s="12">
         <f>MAX($Q$2:$Q$279)-Q36</f>
-        <v>112.46627428472419</v>
+        <v>231.68530222404101</v>
       </c>
       <c r="S36" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R36)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.8915544358512261E-3</v>
+        <v>4.316199562080957E-3</v>
       </c>
       <c r="T36" s="9">
-        <f t="shared" si="6"/>
-        <v>0.78525071454528272</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R36/MAX($R$2:$R$28)</f>
+        <v>1.6176498268314992</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C37" s="32" t="s">
-        <v>91</v>
+        <v>38</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" t="s">
+        <v>55</v>
       </c>
       <c r="D37" s="8">
-        <v>45627</v>
+        <v>45505</v>
       </c>
       <c r="E37" s="2">
-        <v>0.27450000000000002</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F37" s="1">
-        <v>39.799999999999997</v>
+        <v>86.6</v>
       </c>
       <c r="G37" s="1">
-        <f t="shared" si="0"/>
-        <v>10.9251</v>
-      </c>
-      <c r="H37" s="11">
-        <v>0.1</v>
+        <f>E37*F37</f>
+        <v>8.6599999999999986E-18</v>
+      </c>
+      <c r="H37" s="13">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I37" s="11">
-        <v>0.2</v>
+        <v>0.17249999999999999</v>
       </c>
       <c r="J37" s="9">
-        <f t="shared" si="1"/>
-        <v>0.5</v>
+        <f>IFERROR(H37/I37,"")</f>
+        <v>0.40579710144927544</v>
       </c>
       <c r="K37" s="9">
         <f>IFERROR(J37/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.4785067848796617E-2</v>
+        <v>0.25162851696434818</v>
       </c>
       <c r="L37" s="12">
-        <f t="shared" si="9"/>
-        <v>43.78</v>
+        <f>F37/(1-(F37*(1+H37)-F37)/(F37*(1+H37)))</f>
+        <v>92.662000000000006</v>
       </c>
       <c r="M37" s="12">
-        <f t="shared" si="7"/>
-        <v>12.017610000000001</v>
+        <f>L37*E37</f>
+        <v>9.2662000000000008E-18</v>
       </c>
       <c r="N37" s="12">
-        <f t="shared" si="2"/>
-        <v>36.181818181818187</v>
+        <f>F37/(1+I37-H37)</f>
+        <v>78.548752834467123</v>
       </c>
       <c r="O37" s="12">
-        <f t="shared" si="3"/>
-        <v>3.980000000000004</v>
+        <f>L37-F37</f>
+        <v>6.0620000000000118</v>
       </c>
       <c r="P37" s="12">
-        <f t="shared" si="4"/>
-        <v>-1.8090909090909051</v>
+        <f>0.5*(N37-F37)</f>
+        <v>-4.0256235827664355</v>
       </c>
       <c r="Q37" s="15">
-        <f t="shared" si="5"/>
-        <v>2.1709090909090989</v>
+        <f>O37+P37</f>
+        <v>2.0363764172335763</v>
       </c>
       <c r="R37" s="12">
         <f>MAX($Q$2:$Q$279)-Q37</f>
-        <v>111.96153599027528</v>
+        <v>112.0960686639508</v>
       </c>
       <c r="S37" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R37)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.931638809303739E-3</v>
+        <v>8.9209194570227784E-3</v>
       </c>
       <c r="T37" s="9">
-        <f t="shared" si="6"/>
-        <v>0.78172658156501729</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R37/MAX($R$2:$R$28)</f>
+        <v>0.78266590207514586</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C38" s="32" t="s">
-        <v>92</v>
+        <v>71</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C38" t="s">
+        <v>73</v>
       </c>
       <c r="D38" s="8">
-        <v>45627</v>
+        <v>45562</v>
       </c>
       <c r="E38" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F38" s="1">
-        <v>26.63</v>
+        <v>56</v>
       </c>
       <c r="G38" s="1">
-        <f t="shared" si="0"/>
-        <v>2.663E-18</v>
-      </c>
-      <c r="H38" s="11">
-        <v>0.1</v>
+        <f>E38*F38</f>
+        <v>5.5999999999999995E-18</v>
+      </c>
+      <c r="H38" s="13">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I38" s="11">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="J38" s="9">
-        <f t="shared" si="1"/>
-        <v>0.5</v>
+        <f>IFERROR(H38/I38,"")</f>
+        <v>0.36842105263157898</v>
       </c>
       <c r="K38" s="9">
         <f>IFERROR(J38/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.4785067848796617E-2</v>
+        <v>0.22845220619131607</v>
       </c>
       <c r="L38" s="12">
-        <f t="shared" si="9"/>
-        <v>29.293000000000003</v>
+        <f>F38/(1-(F38*(1+H38)-F38)/(F38*(1+H38)))</f>
+        <v>59.92</v>
       </c>
       <c r="M38" s="12">
-        <f t="shared" si="7"/>
-        <v>2.9293000000000003E-18</v>
+        <f>L38*E38</f>
+        <v>5.9920000000000002E-18</v>
       </c>
       <c r="N38" s="12">
-        <f t="shared" si="2"/>
-        <v>24.209090909090911</v>
+        <f>F38/(1+I38-H38)</f>
+        <v>50.000000000000007</v>
       </c>
       <c r="O38" s="12">
-        <f t="shared" si="3"/>
-        <v>2.6630000000000038</v>
+        <f>L38-F38</f>
+        <v>3.9200000000000017</v>
       </c>
       <c r="P38" s="12">
-        <f t="shared" si="4"/>
-        <v>-1.2104545454545441</v>
+        <f>0.5*(N38-F38)</f>
+        <v>-2.9999999999999964</v>
       </c>
       <c r="Q38" s="15">
-        <f t="shared" si="5"/>
-        <v>1.4525454545454597</v>
+        <f>O38+P38</f>
+        <v>0.92000000000000526</v>
       </c>
       <c r="R38" s="12">
         <f>MAX($Q$2:$Q$279)-Q38</f>
-        <v>112.67989962663893</v>
+        <v>113.21244508118438</v>
       </c>
       <c r="S38" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R38)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.8746972912956655E-3</v>
+        <v>8.832951176727102E-3</v>
       </c>
       <c r="T38" s="9">
-        <f t="shared" si="6"/>
-        <v>0.78674226793273505</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R38/MAX($R$2:$R$28)</f>
+        <v>0.79046055327088882</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>96</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="C39" s="32" t="s">
-        <v>100</v>
+        <v>74</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C39" t="s">
+        <v>76</v>
       </c>
       <c r="D39" s="8">
-        <v>45630</v>
+        <v>45580</v>
       </c>
       <c r="E39" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F39" s="1">
-        <v>59.17</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="G39" s="1">
-        <f t="shared" si="0"/>
-        <v>5.9170000000000002E-18</v>
-      </c>
-      <c r="H39" s="11">
-        <v>0.2</v>
+        <f>E39*F39</f>
+        <v>2.0399999999999999E-18</v>
+      </c>
+      <c r="H39" s="13">
+        <v>0.1</v>
       </c>
       <c r="I39" s="11">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="J39" s="9">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>IFERROR(H39/I39,"")</f>
+        <v>0.66666666666666674</v>
       </c>
       <c r="K39" s="9">
         <f>IFERROR(J39/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.9570135697593234E-2</v>
+        <v>0.41338970644142908</v>
       </c>
       <c r="L39" s="12">
-        <f t="shared" si="9"/>
-        <v>71.004000000000005</v>
+        <v>21.2</v>
       </c>
       <c r="M39" s="12">
-        <f t="shared" si="7"/>
-        <v>7.1003999999999996E-18</v>
+        <f>L39*E39</f>
+        <v>2.1199999999999999E-18</v>
       </c>
       <c r="N39" s="12">
-        <f t="shared" si="2"/>
-        <v>59.17</v>
+        <f>F39/(1+I39-H39)</f>
+        <v>19.428571428571431</v>
       </c>
       <c r="O39" s="12">
-        <f t="shared" si="3"/>
-        <v>11.834000000000003</v>
+        <f>L39-F39</f>
+        <v>0.80000000000000071</v>
       </c>
       <c r="P39" s="12">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f>0.5*(N39-F39)</f>
+        <v>-0.48571428571428399</v>
       </c>
       <c r="Q39" s="15">
-        <f t="shared" si="5"/>
-        <v>11.834000000000003</v>
+        <f>O39+P39</f>
+        <v>0.31428571428571672</v>
       </c>
       <c r="R39" s="12">
         <f>MAX($Q$2:$Q$279)-Q39</f>
-        <v>102.29844508118438</v>
+        <v>113.81815936689867</v>
       </c>
       <c r="S39" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R39)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>9.7753196464168812E-3</v>
+        <v>8.7859442250902055E-3</v>
       </c>
       <c r="T39" s="9">
-        <f t="shared" si="6"/>
-        <v>0.71425791960979246</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R39/MAX($R$2:$R$28)</f>
+        <v>0.79468971066667204</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C40" s="32" t="s">
-        <v>98</v>
+        <v>39</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C40" t="s">
+        <v>56</v>
       </c>
       <c r="D40" s="8">
-        <v>45630</v>
+        <v>45574</v>
       </c>
       <c r="E40" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F40" s="1">
-        <v>19.309999999999999</v>
+        <v>47.42</v>
       </c>
       <c r="G40" s="1">
-        <f t="shared" si="0"/>
-        <v>1.931E-18</v>
-      </c>
-      <c r="H40" s="11">
-        <v>0.2</v>
+        <f>E40*F40</f>
+        <v>4.7419999999999999E-18</v>
+      </c>
+      <c r="H40" s="13">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I40" s="11">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J40" s="9">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>IFERROR(H40/I40,"")</f>
+        <v>0.17500000000000002</v>
       </c>
       <c r="K40" s="9">
         <f>IFERROR(J40/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.9570135697593234E-2</v>
+        <v>0.10851479794087514</v>
       </c>
       <c r="L40" s="12">
-        <f t="shared" si="9"/>
-        <v>23.171999999999997</v>
+        <f>F40/(1-(F40*(1+H40)-F40)/(F40*(1+H40)))</f>
+        <v>50.739400000000003</v>
       </c>
       <c r="M40" s="12">
-        <f t="shared" si="7"/>
-        <v>2.3171999999999995E-18</v>
+        <f>L40*E40</f>
+        <v>5.0739400000000001E-18</v>
       </c>
       <c r="N40" s="12">
-        <f t="shared" si="2"/>
-        <v>19.309999999999999</v>
+        <f>F40/(1+I40-H40)</f>
+        <v>35.654135338345867</v>
       </c>
       <c r="O40" s="12">
-        <f t="shared" si="3"/>
-        <v>3.8619999999999983</v>
+        <f>L40-F40</f>
+        <v>3.3194000000000017</v>
       </c>
       <c r="P40" s="12">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f>0.5*(N40-F40)</f>
+        <v>-5.8829323308270673</v>
       </c>
       <c r="Q40" s="15">
-        <f t="shared" si="5"/>
-        <v>3.8619999999999983</v>
+        <f>O40+P40</f>
+        <v>-2.5635323308270657</v>
       </c>
       <c r="R40" s="12">
         <f>MAX($Q$2:$Q$279)-Q40</f>
-        <v>110.27044508118439</v>
+        <v>116.69597741201144</v>
       </c>
       <c r="S40" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R40)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>9.0686130745529329E-3</v>
+        <v>8.5692756697976005E-3</v>
       </c>
       <c r="T40" s="9">
-        <f t="shared" si="6"/>
-        <v>0.76991921661787932</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R40/MAX($R$2:$R$28)</f>
+        <v>0.81478292252621221</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>96</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C41" s="32" t="s">
-        <v>99</v>
+        <v>39</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C41" t="s">
+        <v>41</v>
       </c>
       <c r="D41" s="8">
-        <v>45630</v>
+        <v>45507</v>
       </c>
       <c r="E41" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F41" s="1">
-        <v>323.75</v>
+        <v>41.8</v>
       </c>
       <c r="G41" s="1">
-        <f t="shared" si="0"/>
-        <v>3.2375000000000002E-17</v>
-      </c>
-      <c r="H41" s="11">
-        <v>0.2</v>
+        <f>E41*F41</f>
+        <v>4.1799999999999993E-18</v>
+      </c>
+      <c r="H41" s="13">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I41" s="11">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J41" s="9">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>IFERROR(H41/I41,"")</f>
+        <v>0.17500000000000002</v>
       </c>
       <c r="K41" s="9">
         <f>IFERROR(J41/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.9570135697593234E-2</v>
+        <v>0.10851479794087514</v>
       </c>
       <c r="L41" s="12">
-        <f t="shared" si="9"/>
-        <v>388.5</v>
+        <f>F41/(1-(F41*(1+H41)-F41)/(F41*(1+H41)))</f>
+        <v>44.725999999999999</v>
       </c>
       <c r="M41" s="12">
-        <f t="shared" si="7"/>
-        <v>3.8849999999999999E-17</v>
+        <f>L41*E41</f>
+        <v>4.4725999999999996E-18</v>
       </c>
       <c r="N41" s="12">
-        <f t="shared" si="2"/>
-        <v>323.75</v>
+        <f>F41/(1+I41-H41)</f>
+        <v>31.428571428571431</v>
       </c>
       <c r="O41" s="12">
-        <f t="shared" si="3"/>
-        <v>64.75</v>
+        <f>L41-F41</f>
+        <v>2.9260000000000019</v>
       </c>
       <c r="P41" s="12">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f>0.5*(N41-F41)</f>
+        <v>-5.1857142857142833</v>
       </c>
       <c r="Q41" s="15">
-        <f t="shared" si="5"/>
-        <v>64.75</v>
+        <f>O41+P41</f>
+        <v>-2.2597142857142813</v>
       </c>
       <c r="R41" s="12">
         <f>MAX($Q$2:$Q$279)-Q41</f>
-        <v>49.382445081184386</v>
+        <v>116.39215936689867</v>
       </c>
       <c r="S41" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R41)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>2.0250111114506524E-2</v>
+        <v>8.5916440200042785E-3</v>
       </c>
       <c r="T41" s="9">
-        <f t="shared" si="6"/>
-        <v>0.34479314383458876</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R41/MAX($R$2:$R$28)</f>
+        <v>0.81266163471318675</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="C42" t="s">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="D42" s="8">
-        <v>45481</v>
+        <v>45574</v>
       </c>
       <c r="E42" s="2">
-        <v>2</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F42" s="1">
-        <v>20.928000000000001</v>
+        <v>153.7552</v>
       </c>
       <c r="G42" s="1">
-        <f t="shared" ref="G42" si="10">E42*F42</f>
-        <v>41.856000000000002</v>
-      </c>
-      <c r="H42" s="11">
-        <v>4.4999999999999998E-2</v>
+        <f>E42*F42</f>
+        <v>1.5375519999999999E-17</v>
+      </c>
+      <c r="H42" s="13">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I42" s="11">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="J42" s="9">
-        <f t="shared" ref="J42" si="11">IFERROR(H42/I42,"")</f>
-        <v>0.22499999999999998</v>
+        <f>IFERROR(H42/I42,"")</f>
+        <v>0.36842105263157898</v>
       </c>
       <c r="K42" s="9">
         <f>IFERROR(J42/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.1153280531958477E-2</v>
+        <v>0.22845220619131607</v>
       </c>
       <c r="L42" s="12">
-        <f t="shared" ref="L42" si="12">F42/(1-(F42*(1+H42)-F42)/(F42*(1+H42)))</f>
-        <v>21.869759999999999</v>
+        <f>F42/(1-(F42*(1+H42)-F42)/(F42*(1+H42)))</f>
+        <v>164.51806400000001</v>
       </c>
       <c r="M42" s="12">
-        <f t="shared" ref="M42" si="13">L42*E42</f>
-        <v>43.739519999999999</v>
+        <f>L42*E42</f>
+        <v>1.6451806399999999E-17</v>
       </c>
       <c r="N42" s="12">
-        <f t="shared" ref="N42" si="14">F42/(1+I42-H42)</f>
-        <v>18.119480519480518</v>
+        <f>F42/(1+I42-H42)</f>
+        <v>137.28142857142859</v>
       </c>
       <c r="O42" s="12">
-        <f t="shared" ref="O42" si="15">L42-F42</f>
-        <v>0.9417599999999986</v>
+        <f>L42-F42</f>
+        <v>10.762864000000008</v>
       </c>
       <c r="P42" s="12">
-        <f t="shared" ref="P42" si="16">0.5*(N42-F42)</f>
-        <v>-1.4042597402597412</v>
+        <f>0.5*(N42-F42)</f>
+        <v>-8.2368857142857053</v>
       </c>
       <c r="Q42" s="15">
-        <f t="shared" ref="Q42" si="17">O42+P42</f>
-        <v>-0.46249974025974261</v>
+        <f>O42+P42</f>
+        <v>2.5259782857143023</v>
       </c>
       <c r="R42" s="12">
         <f>MAX($Q$2:$Q$279)-Q42</f>
-        <v>114.59494482144413</v>
+        <v>111.60646679547008</v>
       </c>
       <c r="S42" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R42)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.7263884245343277E-3</v>
+        <v>8.9600542756415654E-3</v>
       </c>
       <c r="T42" s="9">
-        <f t="shared" ref="T42" si="18">R42/MAX($R$2:$R$28)</f>
-        <v>0.80011330398039715</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R42/MAX($R$2:$R$28)</f>
+        <v>0.77924745312667376</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>115</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="C43" t="s">
-        <v>119</v>
+        <v>87</v>
+      </c>
+      <c r="B43" t="s">
+        <v>88</v>
+      </c>
+      <c r="C43" s="32" t="s">
+        <v>89</v>
       </c>
       <c r="D43" s="8">
-        <v>45481</v>
+        <v>45627</v>
       </c>
       <c r="E43" s="2">
-        <v>2</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F43" s="1">
-        <v>16.399999999999999</v>
+        <v>133.53</v>
       </c>
       <c r="G43" s="1">
-        <f t="shared" ref="G43" si="19">E43*F43</f>
-        <v>32.799999999999997</v>
-      </c>
-      <c r="H43" s="11">
-        <v>4.4999999999999998E-2</v>
+        <f>E43*F43</f>
+        <v>1.3353E-17</v>
+      </c>
+      <c r="H43" s="13">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I43" s="11">
         <v>0.2</v>
       </c>
       <c r="J43" s="9">
-        <f t="shared" ref="J43" si="20">IFERROR(H43/I43,"")</f>
-        <v>0.22499999999999998</v>
+        <f>IFERROR(H43/I43,"")</f>
+        <v>0.35000000000000003</v>
       </c>
       <c r="K43" s="9">
         <f>IFERROR(J43/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.1153280531958477E-2</v>
+        <v>0.21702959588175028</v>
       </c>
       <c r="L43" s="12">
-        <f t="shared" ref="L43" si="21">F43/(1-(F43*(1+H43)-F43)/(F43*(1+H43)))</f>
-        <v>17.137999999999998</v>
+        <f>F43/(1-(F43*(1+H43)-F43)/(F43*(1+H43)))</f>
+        <v>142.87710000000001</v>
       </c>
       <c r="M43" s="12">
-        <f t="shared" ref="M43" si="22">L43*E43</f>
-        <v>34.275999999999996</v>
+        <f>L43*E43</f>
+        <v>1.428771E-17</v>
       </c>
       <c r="N43" s="12">
-        <f t="shared" ref="N43" si="23">F43/(1+I43-H43)</f>
-        <v>14.199134199134198</v>
+        <f>F43/(1+I43-H43)</f>
+        <v>118.16814159292036</v>
       </c>
       <c r="O43" s="12">
-        <f t="shared" ref="O43" si="24">L43-F43</f>
-        <v>0.73799999999999955</v>
+        <f>L43-F43</f>
+        <v>9.3471000000000117</v>
       </c>
       <c r="P43" s="12">
-        <f t="shared" ref="P43" si="25">0.5*(N43-F43)</f>
-        <v>-1.1004329004329003</v>
+        <f>0.5*(N43-F43)</f>
+        <v>-7.6809292035398187</v>
       </c>
       <c r="Q43" s="15">
-        <f t="shared" ref="Q43" si="26">O43+P43</f>
-        <v>-0.36243290043290077</v>
+        <f>O43+P43</f>
+        <v>1.6661707964601931</v>
       </c>
       <c r="R43" s="12">
         <f>MAX($Q$2:$Q$279)-Q43</f>
-        <v>114.49487798161729</v>
+        <v>112.46627428472419</v>
       </c>
       <c r="S43" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R43)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.7340151597048287E-3</v>
+        <v>8.8915544358512261E-3</v>
       </c>
       <c r="T43" s="9">
-        <f t="shared" ref="T43" si="27">R43/MAX($R$2:$R$28)</f>
-        <v>0.79941462735066027</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R43/MAX($R$2:$R$28)</f>
+        <v>0.78525071454528272</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>115</v>
+        <v>40</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="C44" t="s">
-        <v>121</v>
+        <v>93</v>
+      </c>
+      <c r="C44" s="32" t="s">
+        <v>92</v>
       </c>
       <c r="D44" s="8">
-        <v>45481</v>
+        <v>45627</v>
       </c>
       <c r="E44" s="2">
-        <v>1</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F44" s="1">
-        <v>48.68</v>
+        <v>26.63</v>
       </c>
       <c r="G44" s="1">
-        <f t="shared" ref="G44" si="28">E44*F44</f>
-        <v>48.68</v>
-      </c>
-      <c r="H44" s="11">
-        <v>2.5000000000000001E-2</v>
+        <f>E44*F44</f>
+        <v>2.663E-18</v>
+      </c>
+      <c r="H44" s="13">
+        <v>0.1</v>
       </c>
       <c r="I44" s="11">
         <v>0.2</v>
       </c>
       <c r="J44" s="9">
-        <f t="shared" ref="J44" si="29">IFERROR(H44/I44,"")</f>
-        <v>0.125</v>
+        <f>IFERROR(H44/I44,"")</f>
+        <v>0.5</v>
       </c>
       <c r="K44" s="9">
         <f>IFERROR(J44/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>6.1962669621991543E-3</v>
+        <v>0.3100422798310718</v>
       </c>
       <c r="L44" s="12">
-        <f t="shared" ref="L44" si="30">F44/(1-(F44*(1+H44)-F44)/(F44*(1+H44)))</f>
-        <v>49.896999999999998</v>
+        <f>F44/(1-(F44*(1+H44)-F44)/(F44*(1+H44)))</f>
+        <v>29.293000000000003</v>
       </c>
       <c r="M44" s="12">
-        <f t="shared" ref="M44" si="31">L44*E44</f>
-        <v>49.896999999999998</v>
+        <f>L44*E44</f>
+        <v>2.9293000000000003E-18</v>
       </c>
       <c r="N44" s="12">
-        <f t="shared" ref="N44" si="32">F44/(1+I44-H44)</f>
-        <v>41.42978723404255</v>
+        <f>F44/(1+I44-H44)</f>
+        <v>24.209090909090911</v>
       </c>
       <c r="O44" s="12">
-        <f t="shared" ref="O44" si="33">L44-F44</f>
-        <v>1.2169999999999987</v>
+        <f>L44-F44</f>
+        <v>2.6630000000000038</v>
       </c>
       <c r="P44" s="12">
-        <f t="shared" ref="P44" si="34">0.5*(N44-F44)</f>
-        <v>-3.6251063829787249</v>
+        <f>0.5*(N44-F44)</f>
+        <v>-1.2104545454545441</v>
       </c>
       <c r="Q44" s="15">
-        <f t="shared" ref="Q44" si="35">O44+P44</f>
-        <v>-2.4081063829787261</v>
+        <f>O44+P44</f>
+        <v>1.4525454545454597</v>
       </c>
       <c r="R44" s="12">
         <f>MAX($Q$2:$Q$279)-Q44</f>
-        <v>116.54055146416312</v>
+        <v>112.67989962663893</v>
       </c>
       <c r="S44" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R44)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.5807042049865865E-3</v>
+        <v>8.8746972912956655E-3</v>
       </c>
       <c r="T44" s="9">
-        <f t="shared" ref="T44" si="36">R44/MAX($R$2:$R$28)</f>
-        <v>0.81369772309746791</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R44/MAX($R$2:$R$28)</f>
+        <v>0.78674226793273505</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>115</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C45" t="s">
-        <v>123</v>
+        <v>38</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C45" s="32" t="s">
+        <v>98</v>
       </c>
       <c r="D45" s="8">
-        <v>45481</v>
+        <v>45630</v>
       </c>
       <c r="E45" s="2">
-        <v>1</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F45" s="1">
-        <v>51.28</v>
+        <v>19.309999999999999</v>
       </c>
       <c r="G45" s="1">
-        <f t="shared" ref="G45" si="37">E45*F45</f>
-        <v>51.28</v>
-      </c>
-      <c r="H45" s="11">
-        <v>2.5000000000000001E-2</v>
+        <f>E45*F45</f>
+        <v>1.931E-18</v>
+      </c>
+      <c r="H45" s="13">
+        <v>0.2</v>
       </c>
       <c r="I45" s="11">
         <v>0.2</v>
       </c>
       <c r="J45" s="9">
-        <f t="shared" ref="J45" si="38">IFERROR(H45/I45,"")</f>
-        <v>0.125</v>
+        <f>IFERROR(H45/I45,"")</f>
+        <v>1</v>
       </c>
       <c r="K45" s="9">
         <f>IFERROR(J45/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>6.1962669621991543E-3</v>
+        <v>0.6200845596621436</v>
       </c>
       <c r="L45" s="12">
-        <f t="shared" ref="L45" si="39">F45/(1-(F45*(1+H45)-F45)/(F45*(1+H45)))</f>
-        <v>52.561999999999998</v>
+        <f>F45/(1-(F45*(1+H45)-F45)/(F45*(1+H45)))</f>
+        <v>23.171999999999997</v>
       </c>
       <c r="M45" s="12">
-        <f t="shared" ref="M45" si="40">L45*E45</f>
-        <v>52.561999999999998</v>
+        <f>L45*E45</f>
+        <v>2.3171999999999995E-18</v>
       </c>
       <c r="N45" s="12">
-        <f t="shared" ref="N45" si="41">F45/(1+I45-H45)</f>
-        <v>43.642553191489363</v>
+        <f>F45/(1+I45-H45)</f>
+        <v>19.309999999999999</v>
       </c>
       <c r="O45" s="12">
-        <f t="shared" ref="O45" si="42">L45-F45</f>
-        <v>1.2819999999999965</v>
+        <f>L45-F45</f>
+        <v>3.8619999999999983</v>
       </c>
       <c r="P45" s="12">
-        <f t="shared" ref="P45" si="43">0.5*(N45-F45)</f>
-        <v>-3.8187234042553193</v>
+        <f>0.5*(N45-F45)</f>
+        <v>0</v>
       </c>
       <c r="Q45" s="15">
-        <f t="shared" ref="Q45" si="44">O45+P45</f>
-        <v>-2.5367234042553228</v>
+        <f>O45+P45</f>
+        <v>3.8619999999999983</v>
       </c>
       <c r="R45" s="12">
         <f>MAX($Q$2:$Q$279)-Q45</f>
-        <v>116.66916848543971</v>
+        <v>110.27044508118439</v>
       </c>
       <c r="S45" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R45)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.571244768276547E-3</v>
+        <v>9.0686130745529347E-3</v>
       </c>
       <c r="T45" s="9">
-        <f t="shared" ref="T45" si="45">R45/MAX($R$2:$R$28)</f>
-        <v>0.81459573993409262</v>
-      </c>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+        <f>R45/MAX($R$2:$R$28)</f>
+        <v>0.76991921661787932</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="C46" t="s">
-        <v>125</v>
+        <v>102</v>
+      </c>
+      <c r="C46" s="32" t="s">
+        <v>99</v>
       </c>
       <c r="D46" s="8">
-        <v>45481</v>
+        <v>45630</v>
       </c>
       <c r="E46" s="2">
-        <v>1</v>
+        <v>9.9999999999999998E-20</v>
       </c>
       <c r="F46" s="1">
-        <v>44.14</v>
+        <v>323.75</v>
       </c>
       <c r="G46" s="1">
-        <f t="shared" ref="G46" si="46">E46*F46</f>
-        <v>44.14</v>
-      </c>
-      <c r="H46" s="11">
-        <v>0.15</v>
+        <f>E46*F46</f>
+        <v>3.2375000000000002E-17</v>
+      </c>
+      <c r="H46" s="13">
+        <v>0.2</v>
       </c>
       <c r="I46" s="11">
         <v>0.2</v>
       </c>
       <c r="J46" s="9">
-        <f t="shared" ref="J46" si="47">IFERROR(H46/I46,"")</f>
-        <v>0.74999999999999989</v>
+        <f>IFERROR(H46/I46,"")</f>
+        <v>1</v>
       </c>
       <c r="K46" s="9">
         <f>IFERROR(J46/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.7177601773194922E-2</v>
+        <v>0.6200845596621436</v>
       </c>
       <c r="L46" s="12">
-        <f t="shared" ref="L46" si="48">F46/(1-(F46*(1+H46)-F46)/(F46*(1+H46)))</f>
-        <v>50.760999999999996</v>
+        <f>F46/(1-(F46*(1+H46)-F46)/(F46*(1+H46)))</f>
+        <v>388.5</v>
       </c>
       <c r="M46" s="12">
-        <f t="shared" ref="M46" si="49">L46*E46</f>
-        <v>50.760999999999996</v>
+        <f>L46*E46</f>
+        <v>3.8849999999999999E-17</v>
       </c>
       <c r="N46" s="12">
-        <f t="shared" ref="N46" si="50">F46/(1+I46-H46)</f>
-        <v>42.038095238095238</v>
+        <f>F46/(1+I46-H46)</f>
+        <v>323.75</v>
       </c>
       <c r="O46" s="12">
-        <f t="shared" ref="O46" si="51">L46-F46</f>
-        <v>6.6209999999999951</v>
+        <f>L46-F46</f>
+        <v>64.75</v>
       </c>
       <c r="P46" s="12">
-        <f t="shared" ref="P46" si="52">0.5*(N46-F46)</f>
-        <v>-1.0509523809523813</v>
+        <f>0.5*(N46-F46)</f>
+        <v>0</v>
       </c>
       <c r="Q46" s="15">
-        <f t="shared" ref="Q46" si="53">O46+P46</f>
-        <v>5.5700476190476138</v>
+        <f>O46+P46</f>
+        <v>64.75</v>
       </c>
       <c r="R46" s="12">
         <f>MAX($Q$2:$Q$279)-Q46</f>
-        <v>108.56239746213677</v>
+        <v>49.382445081184386</v>
       </c>
       <c r="S46" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R46)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>9.2112925227979536E-3</v>
+        <v>2.0250111114506527E-2</v>
       </c>
       <c r="T46" s="9">
-        <f t="shared" ref="T46" si="54">R46/MAX($R$2:$R$28)</f>
-        <v>0.75799345823506892</v>
+        <f>R46/MAX($R$2:$R$28)</f>
+        <v>0.34479314383458876</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="D47" s="46"/>
+    </row>
+    <row r="49" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D49" s="8">
+        <f ca="1">TODAY()-90</f>
+        <v>45601</v>
+      </c>
+    </row>
+    <row r="50" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D50" s="8">
+        <f>D23</f>
+        <v>45511</v>
+      </c>
+    </row>
+    <row r="51" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D51" s="46" t="b">
+        <f ca="1">D50-D49&lt;7/4</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T45" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:T46" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="AMAT"/>
+        <filter val="MA"/>
+        <filter val="MAXN"/>
+      </filters>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T46">
+      <sortCondition descending="1" ref="E1:E45"/>
+    </sortState>
+  </autoFilter>
   <conditionalFormatting sqref="S2:S46">
-    <cfRule type="iconSet" priority="8">
+    <cfRule type="iconSet" priority="11">
       <iconSet iconSet="3Symbols">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="33"/>
@@ -5831,7 +5868,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="10" id="{2048185B-3E19-4351-A3A9-6DB74B32B9C2}">
+          <x14:cfRule type="iconSet" priority="13" id="{2048185B-3E19-4351-A3A9-6DB74B32B9C2}">
             <x14:iconSet iconSet="5Arrows" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -5881,25 +5918,25 @@
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E2" s="29">
         <v>8.8700000000000001E-2</v>
       </c>
       <c r="G2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="H2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="J2" s="29">
         <v>0.24129999999999999</v>
@@ -5907,361 +5944,361 @@
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E3" s="29">
         <v>0.1077</v>
       </c>
       <c r="G3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="H3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="J3" s="29">
         <v>0.30709999999999998</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B5" s="42" t="s">
+      <c r="B5" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="C5" s="42" t="s">
+      <c r="C5" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="42" t="s">
+      <c r="D5" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="E5" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="E5" s="42" t="s">
-        <v>131</v>
-      </c>
-      <c r="G5" s="42" t="s">
+      <c r="G5" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="H5" s="42" t="s">
+      <c r="H5" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="I5" s="42" t="s">
+      <c r="I5" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="J5" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="J5" s="42" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="C6" s="37">
+      <c r="C6" s="34">
         <v>0.25440000000000002</v>
       </c>
-      <c r="D6" s="37">
+      <c r="D6" s="34">
         <v>0</v>
       </c>
-      <c r="E6" s="37">
-        <f>D6-C6</f>
+      <c r="E6" s="34">
+        <f t="shared" ref="E6:E16" si="0">D6-C6</f>
         <v>-0.25440000000000002</v>
       </c>
-      <c r="G6" s="36" t="s">
+      <c r="G6" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="H6" s="37">
+      <c r="H6" s="34">
         <v>0.25440000000000002</v>
       </c>
-      <c r="I6" s="37">
+      <c r="I6" s="34">
         <v>0.2651</v>
       </c>
-      <c r="J6" s="37">
+      <c r="J6" s="34">
         <f>I6-H6</f>
         <v>1.0699999999999987E-2</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="37">
+      <c r="C7" s="34">
         <v>0</v>
       </c>
-      <c r="D7" s="37">
+      <c r="D7" s="34">
         <v>0</v>
       </c>
-      <c r="E7" s="37">
-        <f>D7-C7</f>
+      <c r="E7" s="34">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G7" s="36" t="s">
+      <c r="G7" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="H7" s="37">
+      <c r="H7" s="34">
         <v>0</v>
       </c>
-      <c r="I7" s="37">
+      <c r="I7" s="34">
         <v>0.1207</v>
       </c>
-      <c r="J7" s="37">
-        <f t="shared" ref="J7:J16" si="0">I7-H7</f>
+      <c r="J7" s="34">
+        <f t="shared" ref="J7:J16" si="1">I7-H7</f>
         <v>0.1207</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="39">
+      <c r="C8" s="36">
         <v>0.21579999999999999</v>
       </c>
-      <c r="D8" s="39">
+      <c r="D8" s="36">
         <v>5.21E-2</v>
       </c>
-      <c r="E8" s="39">
-        <f>D8-C8</f>
+      <c r="E8" s="36">
+        <f t="shared" si="0"/>
         <v>-0.16369999999999998</v>
       </c>
-      <c r="G8" s="38" t="s">
+      <c r="G8" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="H8" s="39">
+      <c r="H8" s="36">
         <v>0.21579999999999999</v>
       </c>
-      <c r="I8" s="39">
+      <c r="I8" s="36">
         <v>5.4899999999999997E-2</v>
       </c>
-      <c r="J8" s="39">
+      <c r="J8" s="36">
+        <f t="shared" si="1"/>
+        <v>-0.16089999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" s="37" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" s="38">
+        <v>0.1852</v>
+      </c>
+      <c r="D9" s="38">
+        <v>0.1951</v>
+      </c>
+      <c r="E9" s="38">
         <f t="shared" si="0"/>
-        <v>-0.16089999999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B9" s="40" t="s">
+        <v>9.8999999999999921E-3</v>
+      </c>
+      <c r="G9" s="37" t="s">
         <v>103</v>
       </c>
-      <c r="C9" s="41">
+      <c r="H9" s="38">
         <v>0.1852</v>
       </c>
-      <c r="D9" s="41">
-        <v>0.1951</v>
-      </c>
-      <c r="E9" s="41">
-        <f>D9-C9</f>
-        <v>9.8999999999999921E-3</v>
-      </c>
-      <c r="G9" s="40" t="s">
-        <v>103</v>
-      </c>
-      <c r="H9" s="41">
-        <v>0.1852</v>
-      </c>
-      <c r="I9" s="41">
+      <c r="I9" s="38">
         <v>0.27689999999999998</v>
       </c>
-      <c r="J9" s="41">
-        <f t="shared" si="0"/>
+      <c r="J9" s="38">
+        <f t="shared" si="1"/>
         <v>9.1699999999999976E-2</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="39">
+      <c r="C10" s="36">
         <v>0.2772</v>
       </c>
-      <c r="D10" s="39">
+      <c r="D10" s="36">
         <v>0</v>
       </c>
-      <c r="E10" s="39">
-        <f>D10-C10</f>
-        <v>-0.2772</v>
-      </c>
-      <c r="G10" s="38" t="s">
-        <v>46</v>
-      </c>
-      <c r="H10" s="39">
-        <v>0.2772</v>
-      </c>
-      <c r="I10" s="39">
-        <v>0</v>
-      </c>
-      <c r="J10" s="39">
+      <c r="E10" s="36">
         <f t="shared" si="0"/>
         <v>-0.2772</v>
       </c>
+      <c r="G10" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="H10" s="36">
+        <v>0.2772</v>
+      </c>
+      <c r="I10" s="36">
+        <v>0</v>
+      </c>
+      <c r="J10" s="36">
+        <f t="shared" si="1"/>
+        <v>-0.2772</v>
+      </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B11" s="36" t="s">
+      <c r="B11" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="37">
+      <c r="C11" s="34">
         <v>0</v>
       </c>
-      <c r="D11" s="37">
+      <c r="D11" s="34">
         <v>0.33910000000000001</v>
       </c>
-      <c r="E11" s="37">
-        <f>D11-C11</f>
+      <c r="E11" s="34">
+        <f t="shared" si="0"/>
         <v>0.33910000000000001</v>
       </c>
-      <c r="G11" s="36" t="s">
+      <c r="G11" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="H11" s="37">
+      <c r="H11" s="34">
         <v>0</v>
       </c>
-      <c r="I11" s="37">
+      <c r="I11" s="34">
         <v>0</v>
       </c>
-      <c r="J11" s="37">
+      <c r="J11" s="34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="34">
+        <v>0</v>
+      </c>
+      <c r="D12" s="34">
+        <v>0</v>
+      </c>
+      <c r="E12" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B12" s="36" t="s">
+      <c r="G12" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="37">
+      <c r="H12" s="34">
         <v>0</v>
       </c>
-      <c r="D12" s="37">
+      <c r="I12" s="34">
         <v>0</v>
       </c>
-      <c r="E12" s="37">
-        <f>D12-C12</f>
+      <c r="J12" s="34">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G12" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="H12" s="37">
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="34">
         <v>0</v>
       </c>
-      <c r="I12" s="37">
+      <c r="D13" s="34">
         <v>0</v>
       </c>
-      <c r="J12" s="37">
+      <c r="E13" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B13" s="36" t="s">
+      <c r="G13" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="37">
+      <c r="H13" s="34">
         <v>0</v>
       </c>
-      <c r="D13" s="37">
+      <c r="I13" s="34">
         <v>0</v>
       </c>
-      <c r="E13" s="37">
-        <f>D13-C13</f>
+      <c r="J13" s="34">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G13" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="H13" s="37">
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="34">
         <v>0</v>
       </c>
-      <c r="I13" s="37">
+      <c r="D14" s="34">
         <v>0</v>
       </c>
-      <c r="J13" s="37">
+      <c r="E14" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B14" s="36" t="s">
+      <c r="G14" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="37">
+      <c r="H14" s="34">
         <v>0</v>
       </c>
-      <c r="D14" s="37">
+      <c r="I14" s="34">
         <v>0</v>
       </c>
-      <c r="E14" s="37">
-        <f>D14-C14</f>
+      <c r="J14" s="34">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G14" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="H14" s="37">
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B15" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" s="38">
+        <v>6.7400000000000002E-2</v>
+      </c>
+      <c r="D15" s="38">
+        <v>0.19650000000000001</v>
+      </c>
+      <c r="E15" s="38">
+        <f t="shared" si="0"/>
+        <v>0.12909999999999999</v>
+      </c>
+      <c r="G15" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="H15" s="38">
+        <v>6.7400000000000002E-2</v>
+      </c>
+      <c r="I15" s="38">
+        <v>0.16420000000000001</v>
+      </c>
+      <c r="J15" s="38">
+        <f t="shared" si="1"/>
+        <v>9.6800000000000011E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B16" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" s="38">
         <v>0</v>
       </c>
-      <c r="I14" s="37">
+      <c r="D16" s="38">
+        <v>0.2172</v>
+      </c>
+      <c r="E16" s="38">
+        <f t="shared" si="0"/>
+        <v>0.2172</v>
+      </c>
+      <c r="G16" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="H16" s="38">
         <v>0</v>
       </c>
-      <c r="J14" s="37">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B15" s="40" t="s">
-        <v>91</v>
-      </c>
-      <c r="C15" s="41">
-        <v>6.7400000000000002E-2</v>
-      </c>
-      <c r="D15" s="41">
-        <v>0.19650000000000001</v>
-      </c>
-      <c r="E15" s="41">
-        <f>D15-C15</f>
-        <v>0.12909999999999999</v>
-      </c>
-      <c r="G15" s="40" t="s">
-        <v>91</v>
-      </c>
-      <c r="H15" s="41">
-        <v>6.7400000000000002E-2</v>
-      </c>
-      <c r="I15" s="41">
-        <v>0.16420000000000001</v>
-      </c>
-      <c r="J15" s="41">
-        <f t="shared" si="0"/>
-        <v>9.6800000000000011E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B16" s="40" t="s">
-        <v>92</v>
-      </c>
-      <c r="C16" s="41">
-        <v>0</v>
-      </c>
-      <c r="D16" s="41">
-        <v>0.2172</v>
-      </c>
-      <c r="E16" s="41">
-        <f>D16-C16</f>
-        <v>0.2172</v>
-      </c>
-      <c r="G16" s="40" t="s">
-        <v>92</v>
-      </c>
-      <c r="H16" s="41">
-        <v>0</v>
-      </c>
-      <c r="I16" s="41">
+      <c r="I16" s="38">
         <v>0.1183</v>
       </c>
-      <c r="J16" s="41">
-        <f t="shared" si="0"/>
+      <c r="J16" s="38">
+        <f t="shared" si="1"/>
         <v>0.1183</v>
       </c>
     </row>
@@ -6272,22 +6309,22 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFDF4B0C-3879-4A30-880B-B04980CC1636}">
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:AC14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.140625" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="12" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="15.5703125" bestFit="1" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="13" width="6" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="12" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="15.5703125" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="13" max="13" width="6" customWidth="1" collapsed="1"/>
     <col min="14" max="14" width="15.140625" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="5.5703125" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="0" hidden="1" customWidth="1"/>
@@ -6297,51 +6334,71 @@
     <col min="20" max="20" width="15.140625" customWidth="1" outlineLevel="1"/>
     <col min="21" max="21" width="10.5703125" customWidth="1" outlineLevel="1"/>
     <col min="22" max="22" width="15" customWidth="1" outlineLevel="1"/>
+    <col min="24" max="24" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="H1" s="33" t="s">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="H1" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
       <c r="M1" s="26"/>
-      <c r="N1" s="33" t="s">
+      <c r="N1" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="O1" s="33"/>
-      <c r="R1" s="33" t="s">
+      <c r="O1" s="40"/>
+      <c r="R1" s="40" t="s">
         <v>108</v>
       </c>
-      <c r="S1" s="33"/>
-      <c r="T1" s="33"/>
-      <c r="U1" s="33"/>
-      <c r="V1" s="33"/>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="H2" s="34">
+      <c r="S1" s="40"/>
+      <c r="T1" s="40"/>
+      <c r="U1" s="40"/>
+      <c r="V1" s="40"/>
+      <c r="Y1" s="40" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z1" s="40"/>
+      <c r="AA1" s="40"/>
+      <c r="AB1" s="40"/>
+      <c r="AC1" s="40"/>
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="H2" s="41">
         <v>46000</v>
       </c>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
       <c r="M2" s="27"/>
-      <c r="N2" s="34">
+      <c r="N2" s="41">
         <v>45684</v>
       </c>
-      <c r="O2" s="33"/>
-      <c r="R2" s="34">
+      <c r="O2" s="40"/>
+      <c r="R2" s="41">
         <v>45685</v>
       </c>
-      <c r="S2" s="34"/>
-      <c r="T2" s="34"/>
-      <c r="U2" s="34"/>
-      <c r="V2" s="34"/>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="S2" s="41"/>
+      <c r="T2" s="41"/>
+      <c r="U2" s="41"/>
+      <c r="V2" s="41"/>
+      <c r="Y2" s="41">
+        <v>45688</v>
+      </c>
+      <c r="Z2" s="41"/>
+      <c r="AA2" s="41"/>
+      <c r="AB2" s="41"/>
+      <c r="AC2" s="41"/>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
         <v>104</v>
       </c>
@@ -6399,22 +6456,40 @@
       <c r="V3" s="28" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="X3" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y3" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="Z3" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="AA3" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="AB3" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC3" s="28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
         <v>115</v>
       </c>
       <c r="B4" s="12">
-        <v>218.75600000000003</v>
+        <v>218.85600000000002</v>
       </c>
       <c r="C4" s="22">
-        <v>0.23693336344898536</v>
+        <v>0.23199208873650332</v>
       </c>
       <c r="D4" s="29">
-        <v>5.7047669549634916E-2</v>
+        <v>3.586522645026835E-2</v>
       </c>
       <c r="E4" s="12">
-        <v>12.479519999999951</v>
+        <v>7.849319999999949</v>
       </c>
       <c r="F4" s="12"/>
       <c r="G4" s="21" t="s">
@@ -6457,22 +6532,38 @@
         <v>24.8001101264</v>
       </c>
       <c r="V4" s="12"/>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A5" s="35" t="s">
-        <v>119</v>
+      <c r="X4" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y4" s="43">
+        <v>218.85600000000002</v>
+      </c>
+      <c r="Z4" s="44">
+        <v>0.23199208873650332</v>
+      </c>
+      <c r="AA4" s="45">
+        <v>3.586522645026835E-2</v>
+      </c>
+      <c r="AB4" s="43">
+        <v>7.849319999999949</v>
+      </c>
+      <c r="AC4" s="12"/>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A5" s="21" t="s">
+        <v>38</v>
       </c>
       <c r="B5" s="12">
-        <v>32.799999999999997</v>
+        <v>210.14336800000001</v>
       </c>
       <c r="C5" s="22">
-        <v>0.14993874453729267</v>
+        <v>0.22275651056605106</v>
       </c>
       <c r="D5" s="29">
-        <v>4.4999999999999929E-2</v>
+        <v>0.11801519297244734</v>
       </c>
       <c r="E5" s="12">
-        <v>1.4759999999999991</v>
+        <v>24.8001101264</v>
       </c>
       <c r="F5" s="12"/>
       <c r="G5" s="21" t="s">
@@ -6513,22 +6604,38 @@
         <v>30.380156749999998</v>
       </c>
       <c r="V5" s="12"/>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" s="35" t="s">
-        <v>123</v>
+      <c r="X5" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y5" s="43">
+        <v>210.14336800000001</v>
+      </c>
+      <c r="Z5" s="44">
+        <v>0.22275651056605106</v>
+      </c>
+      <c r="AA5" s="45">
+        <v>0.11801519297244734</v>
+      </c>
+      <c r="AB5" s="43">
+        <v>24.8001101264</v>
+      </c>
+      <c r="AC5" s="12"/>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A6" s="21" t="s">
+        <v>36</v>
       </c>
       <c r="B6" s="12">
-        <v>51.28</v>
+        <v>177.40437299999999</v>
       </c>
       <c r="C6" s="22">
-        <v>0.23441642743513319</v>
+        <v>0.18805246848731463</v>
       </c>
       <c r="D6" s="29">
-        <v>2.4999999999999911E-2</v>
+        <v>0.17124807148919596</v>
       </c>
       <c r="E6" s="12">
-        <v>1.2819999999999965</v>
+        <v>30.380156749999998</v>
       </c>
       <c r="F6" s="12"/>
       <c r="G6" s="21" t="s">
@@ -6569,22 +6676,38 @@
         <v>21.191897399999959</v>
       </c>
       <c r="V6" s="12"/>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" s="35" t="s">
-        <v>117</v>
+      <c r="X6" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y6" s="43">
+        <v>177.40437299999999</v>
+      </c>
+      <c r="Z6" s="44">
+        <v>0.18805246848731463</v>
+      </c>
+      <c r="AA6" s="45">
+        <v>0.17124807148919596</v>
+      </c>
+      <c r="AB6" s="43">
+        <v>30.380156749999998</v>
+      </c>
+      <c r="AC6" s="12"/>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
+        <v>40</v>
       </c>
       <c r="B7" s="12">
-        <v>41.856000000000002</v>
+        <v>172.11133100000001</v>
       </c>
       <c r="C7" s="22">
-        <v>0.19133646619978423</v>
+        <v>0.18244172960261401</v>
       </c>
       <c r="D7" s="29">
-        <v>4.4999999999999929E-2</v>
+        <v>0.1289374887235053</v>
       </c>
       <c r="E7" s="12">
-        <v>1.8835199999999972</v>
+        <v>22.191602799999998</v>
       </c>
       <c r="F7" s="12"/>
       <c r="G7" s="21" t="s">
@@ -6629,22 +6752,40 @@
       <c r="V7" s="12">
         <v>10.31</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" s="35" t="s">
-        <v>121</v>
+      <c r="X7" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y7" s="43">
+        <v>172.11133100000001</v>
+      </c>
+      <c r="Z7" s="44">
+        <v>0.18244172960261401</v>
+      </c>
+      <c r="AA7" s="45">
+        <v>0.1289374887235053</v>
+      </c>
+      <c r="AB7" s="43">
+        <v>22.191602799999998</v>
+      </c>
+      <c r="AC7" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
+        <v>37</v>
       </c>
       <c r="B8" s="12">
-        <v>48.68</v>
+        <v>94.882213999999991</v>
       </c>
       <c r="C8" s="22">
-        <v>0.22253103914864047</v>
+        <v>0.10057719692310878</v>
       </c>
       <c r="D8" s="29">
-        <v>2.4999999999999911E-2</v>
+        <v>0.28159743932619463</v>
       </c>
       <c r="E8" s="12">
-        <v>1.2169999999999987</v>
+        <v>26.71858850000001</v>
       </c>
       <c r="F8" s="12"/>
       <c r="G8" s="21" t="s">
@@ -6685,22 +6826,38 @@
         <v>5.5036288595999991</v>
       </c>
       <c r="V8" s="12"/>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" s="35" t="s">
-        <v>125</v>
+      <c r="X8" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y8" s="43">
+        <v>94.882213999999991</v>
+      </c>
+      <c r="Z8" s="44">
+        <v>0.10057719692310878</v>
+      </c>
+      <c r="AA8" s="45">
+        <v>0.28159743932619463</v>
+      </c>
+      <c r="AB8" s="43">
+        <v>26.71858850000001</v>
+      </c>
+      <c r="AC8" s="12"/>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A9" s="21" t="s">
+        <v>39</v>
       </c>
       <c r="B9" s="12">
-        <v>44.14</v>
+        <v>59.980460999999991</v>
       </c>
       <c r="C9" s="22">
-        <v>0.20177732267914936</v>
+        <v>6.35805846345011E-2</v>
       </c>
       <c r="D9" s="29">
-        <v>0.14999999999999991</v>
+        <v>9.1757028336277635E-2</v>
       </c>
       <c r="E9" s="12">
-        <v>6.6209999999999951</v>
+        <v>5.5036288595999991</v>
       </c>
       <c r="F9" s="12"/>
       <c r="G9" s="21" t="s">
@@ -6741,22 +6898,38 @@
         <v>2.8585286400000075E-17</v>
       </c>
       <c r="V9" s="12"/>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="X9" s="42" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y9" s="43">
+        <v>59.980460999999991</v>
+      </c>
+      <c r="Z9" s="44">
+        <v>6.35805846345011E-2</v>
+      </c>
+      <c r="AA9" s="45">
+        <v>9.1757028336277635E-2</v>
+      </c>
+      <c r="AB9" s="43">
+        <v>5.5036288595999991</v>
+      </c>
+      <c r="AC9" s="12"/>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="21" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="B10" s="12">
-        <v>210.14336800000001</v>
+        <v>9.99925</v>
       </c>
       <c r="C10" s="22">
-        <v>0.2276050713431306</v>
+        <v>1.0599421049907156E-2</v>
       </c>
       <c r="D10" s="29">
-        <v>0.11801519297244734</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="E10" s="12">
-        <v>24.8001101264</v>
+        <v>1.9998499999999986</v>
       </c>
       <c r="F10" s="12"/>
       <c r="G10" s="21" t="s">
@@ -6797,22 +6970,38 @@
         <v>7.6584000000000023E-18</v>
       </c>
       <c r="V10" s="12"/>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="X10" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="Y10" s="43">
+        <v>9.99925</v>
+      </c>
+      <c r="Z10" s="44">
+        <v>1.0599421049907156E-2</v>
+      </c>
+      <c r="AA10" s="45">
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AB10" s="43">
+        <v>1.9998499999999986</v>
+      </c>
+      <c r="AC10" s="12"/>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="21" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="B11" s="12">
-        <v>177.40437299999999</v>
+        <v>2.9170551999999998E-16</v>
       </c>
       <c r="C11" s="22">
-        <v>0.19214565445267037</v>
+        <v>3.0921415396775884E-19</v>
       </c>
       <c r="D11" s="29">
-        <v>0.17124807148919596</v>
+        <v>9.799364235548258E-2</v>
       </c>
       <c r="E11" s="12">
-        <v>30.380156749999998</v>
+        <v>2.8585286400000075E-17</v>
       </c>
       <c r="F11" s="12"/>
       <c r="G11" s="21" t="s">
@@ -6853,22 +7042,38 @@
         <v>9.3470999999999986E-19</v>
       </c>
       <c r="V11" s="12"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="X11" s="42" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y11" s="43">
+        <v>2.9170551999999998E-16</v>
+      </c>
+      <c r="Z11" s="44">
+        <v>3.0921415396775884E-19</v>
+      </c>
+      <c r="AA11" s="45">
+        <v>9.799364235548258E-2</v>
+      </c>
+      <c r="AB11" s="43">
+        <v>2.8585286400000075E-17</v>
+      </c>
+      <c r="AC11" s="12"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="21" t="s">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="B12" s="12">
-        <v>162.11427700000002</v>
+        <v>1.3353E-17</v>
       </c>
       <c r="C12" s="22">
-        <v>0.17558503955416302</v>
+        <v>1.4154468513079507E-20</v>
       </c>
       <c r="D12" s="29">
-        <v>0.13072196842971429</v>
+        <v>7.0000000000000062E-2</v>
       </c>
       <c r="E12" s="12">
-        <v>21.191897399999959</v>
+        <v>9.3470999999999986E-19</v>
       </c>
       <c r="F12" s="12"/>
       <c r="G12" s="21" t="s">
@@ -6909,22 +7114,38 @@
         <v>3.9200000000000069E-19</v>
       </c>
       <c r="V12" s="12"/>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="X12" s="42" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y12" s="43">
+        <v>1.3353E-17</v>
+      </c>
+      <c r="Z12" s="44">
+        <v>1.4154468513079507E-20</v>
+      </c>
+      <c r="AA12" s="45">
+        <v>7.0000000000000062E-2</v>
+      </c>
+      <c r="AB12" s="43">
+        <v>9.3470999999999986E-19</v>
+      </c>
+      <c r="AC12" s="12"/>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="21" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B13" s="12">
-        <v>94.882213999999991</v>
+        <v>5.5999999999999995E-18</v>
       </c>
       <c r="C13" s="22">
-        <v>0.10276637941133684</v>
+        <v>5.9361209970227834E-21</v>
       </c>
       <c r="D13" s="29">
-        <v>0.28159743932619463</v>
+        <v>7.0000000000000062E-2</v>
       </c>
       <c r="E13" s="12">
-        <v>26.71858850000001</v>
+        <v>3.9200000000000069E-19</v>
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="31" t="s">
@@ -6971,111 +7192,62 @@
         <f>SUM(V4:V12)</f>
         <v>10.31</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="X13" s="42" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y13" s="43">
+        <v>5.5999999999999995E-18</v>
+      </c>
+      <c r="Z13" s="44">
+        <v>5.9361209970227834E-21</v>
+      </c>
+      <c r="AA13" s="45">
+        <v>7.0000000000000062E-2</v>
+      </c>
+      <c r="AB13" s="43">
+        <v>3.9200000000000069E-19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="21" t="s">
-        <v>39</v>
+        <v>105</v>
       </c>
       <c r="B14" s="12">
-        <v>59.980460999999991</v>
+        <v>943.37699699999996</v>
       </c>
       <c r="C14" s="22">
-        <v>6.4964491789714057E-2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="29">
-        <v>9.1757028336277635E-2</v>
+        <v>0.12661243322217675</v>
       </c>
       <c r="E14" s="12">
-        <v>5.5036288595999991</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="B15" s="12">
-        <v>2.9170551999999998E-16</v>
-      </c>
-      <c r="C15" s="22">
-        <v>3.1594456833291544E-19</v>
-      </c>
-      <c r="D15" s="29">
-        <v>9.799364235548258E-2</v>
-      </c>
-      <c r="E15" s="12">
-        <v>2.8585286400000075E-17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="B16" s="12">
-        <v>3.8291999999999999E-17</v>
-      </c>
-      <c r="C16" s="22">
-        <v>4.147384461769527E-20</v>
-      </c>
-      <c r="D16" s="29">
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="E16" s="12">
-        <v>7.6584000000000023E-18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="B17" s="12">
-        <v>1.3353E-17</v>
-      </c>
-      <c r="C17" s="22">
-        <v>1.4462557379611534E-20</v>
-      </c>
-      <c r="D17" s="29">
-        <v>7.0000000000000062E-2</v>
-      </c>
-      <c r="E17" s="12">
-        <v>9.3470999999999986E-19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="B18" s="12">
-        <v>5.5999999999999995E-18</v>
-      </c>
-      <c r="C18" s="22">
-        <v>6.0653277410188415E-21</v>
-      </c>
-      <c r="D18" s="29">
-        <v>7.0000000000000062E-2</v>
-      </c>
-      <c r="E18" s="12">
-        <v>3.9200000000000069E-19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="21" t="s">
+        <v>119.4432570360002</v>
+      </c>
+      <c r="X14" s="31" t="s">
         <v>105</v>
       </c>
-      <c r="B19" s="12">
-        <v>923.28069299999981</v>
-      </c>
-      <c r="C19" s="22">
+      <c r="Y14" s="24">
+        <v>943.37699699999996</v>
+      </c>
+      <c r="Z14" s="25">
         <v>1</v>
       </c>
-      <c r="D19" s="29">
-        <v>0.13113444541182484</v>
-      </c>
-      <c r="E19" s="12">
-        <v>121.07390163600019</v>
+      <c r="AA14" s="30">
+        <v>0.12661243322217675</v>
+      </c>
+      <c r="AB14" s="24">
+        <v>119.4432570360002</v>
+      </c>
+      <c r="AC14" s="24">
+        <f>SUM(AC4:AC13)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
+    <mergeCell ref="Y1:AC1"/>
+    <mergeCell ref="Y2:AC2"/>
     <mergeCell ref="H1:L1"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="N2:O2"/>

--- a/Open Positions.xlsx
+++ b/Open Positions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\StockSillines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39C45243-A628-4F28-9D91-00311C8EF72A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E231CD-60A9-4DC1-907D-C312377AE26E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Positions" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="132">
   <si>
     <t>Name</t>
   </si>
@@ -661,12 +661,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -676,31 +670,19 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
     </dxf>
@@ -1921,7 +1903,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{42F2A961-4B24-4134-99E9-0FE83E8807F0}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{42F2A961-4B24-4134-99E9-0FE83E8807F0}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:E14" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="22">
     <pivotField axis="axisRow" showAll="0" sortType="descending">
@@ -2090,7 +2072,7 @@
     <dataField name="Target P&amp;L" fld="21" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="8">
+    <format dxfId="2">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -2100,7 +2082,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="7">
+    <format dxfId="1">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -2110,7 +2092,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="6">
+    <format dxfId="0">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -2395,7 +2377,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:T51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2483,7 +2464,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>115</v>
       </c>
@@ -2503,7 +2484,7 @@
         <v>20.928000000000001</v>
       </c>
       <c r="G2" s="1">
-        <f>E2*F2</f>
+        <f t="shared" ref="G2:G46" si="0">E2*F2</f>
         <v>41.856000000000002</v>
       </c>
       <c r="H2" s="13">
@@ -2513,51 +2494,51 @@
         <v>0.2</v>
       </c>
       <c r="J2" s="9">
-        <f>IFERROR(H2/I2,"")</f>
+        <f t="shared" ref="J2:J46" si="1">IFERROR(H2/I2,"")</f>
         <v>0.22499999999999998</v>
       </c>
       <c r="K2" s="9">
-        <f>IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.1395190259239823</v>
+        <f t="shared" ref="K2:K46" si="2">IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>1.1451292650523102E-2</v>
       </c>
       <c r="L2" s="12">
         <f>F2/(1-(F2*(1+H2)-F2)/(F2*(1+H2)))</f>
         <v>21.869759999999999</v>
       </c>
       <c r="M2" s="12">
-        <f>L2*E2</f>
+        <f t="shared" ref="M2:M46" si="3">L2*E2</f>
         <v>43.739519999999999</v>
       </c>
       <c r="N2" s="12">
-        <f>F2/(1+I2-H2)</f>
+        <f t="shared" ref="N2:N46" si="4">F2/(1+I2-H2)</f>
         <v>18.119480519480518</v>
       </c>
       <c r="O2" s="12">
-        <f>L2-F2</f>
+        <f t="shared" ref="O2:O46" si="5">L2-F2</f>
         <v>0.9417599999999986</v>
       </c>
       <c r="P2" s="12">
-        <f>0.5*(N2-F2)</f>
+        <f t="shared" ref="P2:P46" si="6">0.5*(N2-F2)</f>
         <v>-1.4042597402597412</v>
       </c>
       <c r="Q2" s="15">
-        <f>O2+P2</f>
+        <f t="shared" ref="Q2:Q46" si="7">O2+P2</f>
         <v>-0.46249974025974261</v>
       </c>
       <c r="R2" s="12">
-        <f>MAX($Q$2:$Q$279)-Q2</f>
+        <f t="shared" ref="R2:R46" si="8">MAX($Q$2:$Q$279)-Q2</f>
         <v>114.59494482144413</v>
       </c>
       <c r="S2" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R2)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" ref="S2:S46" si="9">IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R2)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>8.7263884245343277E-3</v>
       </c>
       <c r="T2" s="9">
-        <f>R2/MAX($R$2:$R$28)</f>
+        <f t="shared" ref="T2:T46" si="10">R2/MAX($R$2:$R$28)</f>
         <v>0.80011330398039715</v>
       </c>
     </row>
-    <row r="3" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>115</v>
       </c>
@@ -2577,7 +2558,7 @@
         <v>16.399999999999999</v>
       </c>
       <c r="G3" s="1">
-        <f>E3*F3</f>
+        <f t="shared" si="0"/>
         <v>32.799999999999997</v>
       </c>
       <c r="H3" s="13">
@@ -2587,51 +2568,51 @@
         <v>0.2</v>
       </c>
       <c r="J3" s="9">
-        <f>IFERROR(H3/I3,"")</f>
+        <f t="shared" si="1"/>
         <v>0.22499999999999998</v>
       </c>
       <c r="K3" s="9">
-        <f>IFERROR(J3/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.1395190259239823</v>
+        <f t="shared" si="2"/>
+        <v>1.1451292650523102E-2</v>
       </c>
       <c r="L3" s="12">
         <f>F3/(1-(F3*(1+H3)-F3)/(F3*(1+H3)))</f>
         <v>17.137999999999998</v>
       </c>
       <c r="M3" s="12">
-        <f>L3*E3</f>
+        <f t="shared" si="3"/>
         <v>34.275999999999996</v>
       </c>
       <c r="N3" s="12">
-        <f>F3/(1+I3-H3)</f>
+        <f t="shared" si="4"/>
         <v>14.199134199134198</v>
       </c>
       <c r="O3" s="12">
-        <f>L3-F3</f>
+        <f t="shared" si="5"/>
         <v>0.73799999999999955</v>
       </c>
       <c r="P3" s="12">
-        <f>0.5*(N3-F3)</f>
+        <f t="shared" si="6"/>
         <v>-1.1004329004329003</v>
       </c>
       <c r="Q3" s="15">
-        <f>O3+P3</f>
+        <f t="shared" si="7"/>
         <v>-0.36243290043290077</v>
       </c>
       <c r="R3" s="12">
-        <f>MAX($Q$2:$Q$279)-Q3</f>
+        <f t="shared" si="8"/>
         <v>114.49487798161729</v>
       </c>
       <c r="S3" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R3)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.7340151597048287E-3</v>
       </c>
       <c r="T3" s="9">
-        <f>R3/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.79941462735066027</v>
       </c>
     </row>
-    <row r="4" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>37</v>
       </c>
@@ -2651,7 +2632,7 @@
         <v>15.3</v>
       </c>
       <c r="G4" s="1">
-        <f>E4*F4</f>
+        <f t="shared" si="0"/>
         <v>29.980350000000001</v>
       </c>
       <c r="H4" s="13">
@@ -2661,51 +2642,51 @@
         <v>0.39532299999999998</v>
       </c>
       <c r="J4" s="9">
-        <f>IFERROR(H4/I4,"")</f>
+        <f t="shared" si="1"/>
         <v>0.88535197800279775</v>
       </c>
       <c r="K4" s="9">
-        <f>IFERROR(J4/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.54899309142587271</v>
+        <f t="shared" si="2"/>
+        <v>4.5059664883686804E-2</v>
       </c>
       <c r="L4" s="12">
         <f>F4/(1-(F4*(1+H4)-F4)/(F4*(1+H4)))</f>
         <v>20.655000000000001</v>
       </c>
       <c r="M4" s="12">
-        <f>L4*E4</f>
+        <f t="shared" si="3"/>
         <v>40.4734725</v>
       </c>
       <c r="N4" s="12">
-        <f>F4/(1+I4-H4)</f>
+        <f t="shared" si="4"/>
         <v>14.636624277854791</v>
       </c>
       <c r="O4" s="12">
-        <f>L4-F4</f>
+        <f t="shared" si="5"/>
         <v>5.3550000000000004</v>
       </c>
       <c r="P4" s="12">
-        <f>0.5*(N4-F4)</f>
+        <f t="shared" si="6"/>
         <v>-0.33168786107260484</v>
       </c>
       <c r="Q4" s="15">
-        <f>O4+P4</f>
+        <f t="shared" si="7"/>
         <v>5.0233121389273956</v>
       </c>
       <c r="R4" s="12">
-        <f>MAX($Q$2:$Q$279)-Q4</f>
+        <f t="shared" si="8"/>
         <v>109.10913294225699</v>
       </c>
       <c r="S4" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R4)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>9.1651356127009313E-3</v>
+        <f t="shared" si="9"/>
+        <v>9.165135612700933E-3</v>
       </c>
       <c r="T4" s="9">
-        <f>R4/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.76181081974332665</v>
       </c>
     </row>
-    <row r="5" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -2725,7 +2706,7 @@
         <v>21.73</v>
       </c>
       <c r="G5" s="1">
-        <f>E5*F5</f>
+        <f t="shared" si="0"/>
         <v>41.237020999999999</v>
       </c>
       <c r="H5" s="13">
@@ -2736,50 +2717,50 @@
         <v>0.45929999999999999</v>
       </c>
       <c r="J5" s="9">
-        <f>IFERROR(H5/I5,"")</f>
+        <f t="shared" si="1"/>
         <v>0.48594326447066366</v>
       </c>
       <c r="K5" s="9">
-        <f>IFERROR(J5/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.30132591517007606</v>
+        <f t="shared" si="2"/>
+        <v>2.4731904591129405E-2</v>
       </c>
       <c r="L5" s="12">
         <v>26.58</v>
       </c>
       <c r="M5" s="12">
-        <f>L5*E5</f>
+        <f t="shared" si="3"/>
         <v>50.440865999999993</v>
       </c>
       <c r="N5" s="12">
-        <f>F5/(1+I5-H5)</f>
+        <f t="shared" si="4"/>
         <v>17.579394852436032</v>
       </c>
       <c r="O5" s="12">
-        <f>L5-F5</f>
+        <f t="shared" si="5"/>
         <v>4.8499999999999979</v>
       </c>
       <c r="P5" s="12">
-        <f>0.5*(N5-F5)</f>
+        <f t="shared" si="6"/>
         <v>-2.0753025737819843</v>
       </c>
       <c r="Q5" s="15">
-        <f>O5+P5</f>
+        <f t="shared" si="7"/>
         <v>2.7746974262180135</v>
       </c>
       <c r="R5" s="12">
-        <f>MAX($Q$2:$Q$279)-Q5</f>
+        <f t="shared" si="8"/>
         <v>111.35774765496637</v>
       </c>
       <c r="S5" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R5)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.9800666864996662E-3</v>
+        <f t="shared" si="9"/>
+        <v>8.980066686499668E-3</v>
       </c>
       <c r="T5" s="9">
-        <f>R5/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.77751087134654673</v>
       </c>
     </row>
-    <row r="6" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -2799,7 +2780,7 @@
         <v>51.88</v>
       </c>
       <c r="G6" s="1">
-        <f>E6*F6</f>
+        <f t="shared" si="0"/>
         <v>89.991048000000006</v>
       </c>
       <c r="H6" s="13">
@@ -2810,51 +2791,51 @@
         <v>0.19980000000000001</v>
       </c>
       <c r="J6" s="9">
-        <f>IFERROR(H6/I6,"")</f>
+        <f t="shared" si="1"/>
         <v>0.92242242242242245</v>
       </c>
       <c r="K6" s="9">
-        <f>IFERROR(J6/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.57197990163029566</v>
+        <f t="shared" si="2"/>
+        <v>4.6946351584727132E-2</v>
       </c>
       <c r="L6" s="12">
-        <f>F6/(1-(F6*(1+H6)-F6)/(F6*(1+H6)))</f>
+        <f t="shared" ref="L6:L38" si="11">F6/(1-(F6*(1+H6)-F6)/(F6*(1+H6)))</f>
         <v>61.441483999999996</v>
       </c>
       <c r="M6" s="12">
-        <f>L6*E6</f>
+        <f t="shared" si="3"/>
         <v>106.57639814639998</v>
       </c>
       <c r="N6" s="12">
-        <f>F6/(1+I6-H6)</f>
+        <f t="shared" si="4"/>
         <v>51.088133924175295</v>
       </c>
       <c r="O6" s="12">
-        <f>L6-F6</f>
+        <f t="shared" si="5"/>
         <v>9.561483999999993</v>
       </c>
       <c r="P6" s="12">
-        <f>0.5*(N6-F6)</f>
+        <f t="shared" si="6"/>
         <v>-0.39593303791235357</v>
       </c>
       <c r="Q6" s="15">
-        <f>O6+P6</f>
+        <f t="shared" si="7"/>
         <v>9.1655509620876394</v>
       </c>
       <c r="R6" s="12">
-        <f>MAX($Q$2:$Q$279)-Q6</f>
+        <f t="shared" si="8"/>
         <v>104.96689411909675</v>
       </c>
       <c r="S6" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R6)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>9.526813271862531E-3</v>
       </c>
       <c r="T6" s="9">
-        <f>R6/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.73288929623425103</v>
       </c>
     </row>
-    <row r="7" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>115</v>
       </c>
@@ -2874,7 +2855,7 @@
         <v>44.24</v>
       </c>
       <c r="G7" s="1">
-        <f>E7*F7</f>
+        <f t="shared" si="0"/>
         <v>44.24</v>
       </c>
       <c r="H7" s="13">
@@ -2884,51 +2865,51 @@
         <v>0.2</v>
       </c>
       <c r="J7" s="9">
-        <f>IFERROR(H7/I7,"")</f>
+        <f t="shared" si="1"/>
         <v>0.22499999999999998</v>
       </c>
       <c r="K7" s="9">
-        <f>IFERROR(J7/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.1395190259239823</v>
+        <f t="shared" si="2"/>
+        <v>1.1451292650523102E-2</v>
       </c>
       <c r="L7" s="12">
-        <f>F7/(1-(F7*(1+H7)-F7)/(F7*(1+H7)))</f>
+        <f t="shared" si="11"/>
         <v>46.230800000000002</v>
       </c>
       <c r="M7" s="12">
-        <f>L7*E7</f>
+        <f t="shared" si="3"/>
         <v>46.230800000000002</v>
       </c>
       <c r="N7" s="12">
-        <f>F7/(1+I7-H7)</f>
+        <f t="shared" si="4"/>
         <v>38.303030303030305</v>
       </c>
       <c r="O7" s="12">
-        <f>L7-F7</f>
+        <f t="shared" si="5"/>
         <v>1.9908000000000001</v>
       </c>
       <c r="P7" s="12">
-        <f>0.5*(N7-F7)</f>
+        <f t="shared" si="6"/>
         <v>-2.9684848484848487</v>
       </c>
       <c r="Q7" s="15">
-        <f>O7+P7</f>
+        <f t="shared" si="7"/>
         <v>-0.9776848484848486</v>
       </c>
       <c r="R7" s="12">
-        <f>MAX($Q$2:$Q$279)-Q7</f>
+        <f t="shared" si="8"/>
         <v>115.11012992966923</v>
       </c>
       <c r="S7" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R7)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.6873327361456972E-3</v>
       </c>
       <c r="T7" s="9">
-        <f>R7/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.80371037765363607</v>
       </c>
     </row>
-    <row r="8" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>115</v>
       </c>
@@ -2948,7 +2929,7 @@
         <v>48.68</v>
       </c>
       <c r="G8" s="1">
-        <f>E8*F8</f>
+        <f t="shared" si="0"/>
         <v>48.68</v>
       </c>
       <c r="H8" s="13">
@@ -2958,51 +2939,51 @@
         <v>0.2</v>
       </c>
       <c r="J8" s="9">
-        <f>IFERROR(H8/I8,"")</f>
+        <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
       <c r="K8" s="9">
-        <f>IFERROR(J8/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>7.751056995776795E-2</v>
+        <f t="shared" si="2"/>
+        <v>6.3618292502906132E-3</v>
       </c>
       <c r="L8" s="12">
-        <f>F8/(1-(F8*(1+H8)-F8)/(F8*(1+H8)))</f>
+        <f t="shared" si="11"/>
         <v>49.896999999999998</v>
       </c>
       <c r="M8" s="12">
-        <f>L8*E8</f>
+        <f t="shared" si="3"/>
         <v>49.896999999999998</v>
       </c>
       <c r="N8" s="12">
-        <f>F8/(1+I8-H8)</f>
+        <f t="shared" si="4"/>
         <v>41.42978723404255</v>
       </c>
       <c r="O8" s="12">
-        <f>L8-F8</f>
+        <f t="shared" si="5"/>
         <v>1.2169999999999987</v>
       </c>
       <c r="P8" s="12">
-        <f>0.5*(N8-F8)</f>
+        <f t="shared" si="6"/>
         <v>-3.6251063829787249</v>
       </c>
       <c r="Q8" s="15">
-        <f>O8+P8</f>
+        <f t="shared" si="7"/>
         <v>-2.4081063829787261</v>
       </c>
       <c r="R8" s="12">
-        <f>MAX($Q$2:$Q$279)-Q8</f>
+        <f t="shared" si="8"/>
         <v>116.54055146416312</v>
       </c>
       <c r="S8" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R8)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.5807042049865848E-3</v>
+        <f t="shared" si="9"/>
+        <v>8.5807042049865865E-3</v>
       </c>
       <c r="T8" s="9">
-        <f>R8/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.81369772309746791</v>
       </c>
     </row>
-    <row r="9" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>115</v>
       </c>
@@ -3022,7 +3003,7 @@
         <v>51.28</v>
       </c>
       <c r="G9" s="1">
-        <f>E9*F9</f>
+        <f t="shared" si="0"/>
         <v>51.28</v>
       </c>
       <c r="H9" s="13">
@@ -3032,51 +3013,51 @@
         <v>0.2</v>
       </c>
       <c r="J9" s="9">
-        <f>IFERROR(H9/I9,"")</f>
+        <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
       <c r="K9" s="9">
-        <f>IFERROR(J9/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>7.751056995776795E-2</v>
+        <f t="shared" si="2"/>
+        <v>6.3618292502906132E-3</v>
       </c>
       <c r="L9" s="12">
-        <f>F9/(1-(F9*(1+H9)-F9)/(F9*(1+H9)))</f>
+        <f t="shared" si="11"/>
         <v>52.561999999999998</v>
       </c>
       <c r="M9" s="12">
-        <f>L9*E9</f>
+        <f t="shared" si="3"/>
         <v>52.561999999999998</v>
       </c>
       <c r="N9" s="12">
-        <f>F9/(1+I9-H9)</f>
+        <f t="shared" si="4"/>
         <v>43.642553191489363</v>
       </c>
       <c r="O9" s="12">
-        <f>L9-F9</f>
+        <f t="shared" si="5"/>
         <v>1.2819999999999965</v>
       </c>
       <c r="P9" s="12">
-        <f>0.5*(N9-F9)</f>
+        <f t="shared" si="6"/>
         <v>-3.8187234042553193</v>
       </c>
       <c r="Q9" s="15">
-        <f>O9+P9</f>
+        <f t="shared" si="7"/>
         <v>-2.5367234042553228</v>
       </c>
       <c r="R9" s="12">
-        <f>MAX($Q$2:$Q$279)-Q9</f>
+        <f t="shared" si="8"/>
         <v>116.66916848543971</v>
       </c>
       <c r="S9" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R9)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.5712447682765452E-3</v>
       </c>
       <c r="T9" s="9">
-        <f>R9/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.81459573993409262</v>
       </c>
     </row>
-    <row r="10" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -3096,7 +3077,7 @@
         <v>41.76</v>
       </c>
       <c r="G10" s="1">
-        <f>E10*F10</f>
+        <f t="shared" si="0"/>
         <v>40.022784000000001</v>
       </c>
       <c r="H10" s="13">
@@ -3106,51 +3087,51 @@
         <v>0.2</v>
       </c>
       <c r="J10" s="9">
-        <f>IFERROR(H10/I10,"")</f>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
       <c r="K10" s="9">
-        <f>IFERROR(J10/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.3100422798310718</v>
+        <f t="shared" si="2"/>
+        <v>2.5447317001162453E-2</v>
       </c>
       <c r="L10" s="12">
-        <f>F10/(1-(F10*(1+H10)-F10)/(F10*(1+H10)))</f>
+        <f t="shared" si="11"/>
         <v>45.936</v>
       </c>
       <c r="M10" s="12">
-        <f>L10*E10</f>
+        <f t="shared" si="3"/>
         <v>44.025062400000003</v>
       </c>
       <c r="N10" s="12">
-        <f>F10/(1+I10-H10)</f>
+        <f t="shared" si="4"/>
         <v>37.963636363636368</v>
       </c>
       <c r="O10" s="12">
-        <f>L10-F10</f>
+        <f t="shared" si="5"/>
         <v>4.1760000000000019</v>
       </c>
       <c r="P10" s="12">
-        <f>0.5*(N10-F10)</f>
+        <f t="shared" si="6"/>
         <v>-1.8981818181818149</v>
       </c>
       <c r="Q10" s="15">
-        <f>O10+P10</f>
+        <f t="shared" si="7"/>
         <v>2.2778181818181871</v>
       </c>
       <c r="R10" s="12">
-        <f>MAX($Q$2:$Q$279)-Q10</f>
+        <f t="shared" si="8"/>
         <v>111.8546268993662</v>
       </c>
       <c r="S10" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R10)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.9401755449927331E-3</v>
       </c>
       <c r="T10" s="9">
-        <f>R10/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.78098013165759694</v>
       </c>
     </row>
-    <row r="11" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -3170,7 +3151,7 @@
         <v>77.430000000000007</v>
       </c>
       <c r="G11" s="1">
-        <f>E11*F11</f>
+        <f t="shared" si="0"/>
         <v>34.982874000000002</v>
       </c>
       <c r="H11" s="13">
@@ -3180,51 +3161,51 @@
         <v>0.25990000000000002</v>
       </c>
       <c r="J11" s="9">
-        <f>IFERROR(H11/I11,"")</f>
+        <f t="shared" si="1"/>
         <v>0.38476337052712584</v>
       </c>
       <c r="K11" s="9">
-        <f>IFERROR(J11/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.23858582518743501</v>
+        <f t="shared" si="2"/>
+        <v>1.9582390920478997E-2</v>
       </c>
       <c r="L11" s="12">
-        <f>F11/(1-(F11*(1+H11)-F11)/(F11*(1+H11)))</f>
+        <f t="shared" si="11"/>
         <v>85.173000000000016</v>
       </c>
       <c r="M11" s="12">
-        <f>L11*E11</f>
+        <f t="shared" si="3"/>
         <v>38.481161400000005</v>
       </c>
       <c r="N11" s="12">
-        <f>F11/(1+I11-H11)</f>
+        <f t="shared" si="4"/>
         <v>66.755754806448849</v>
       </c>
       <c r="O11" s="12">
-        <f>L11-F11</f>
+        <f t="shared" si="5"/>
         <v>7.7430000000000092</v>
       </c>
       <c r="P11" s="12">
-        <f>0.5*(N11-F11)</f>
+        <f t="shared" si="6"/>
         <v>-5.3371225967755791</v>
       </c>
       <c r="Q11" s="15">
-        <f>O11+P11</f>
+        <f t="shared" si="7"/>
         <v>2.4058774032244301</v>
       </c>
       <c r="R11" s="12">
-        <f>MAX($Q$2:$Q$279)-Q11</f>
+        <f t="shared" si="8"/>
         <v>111.72656767795996</v>
       </c>
       <c r="S11" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R11)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.9504226325326161E-3</v>
+        <f t="shared" si="9"/>
+        <v>8.9504226325326178E-3</v>
       </c>
       <c r="T11" s="9">
-        <f>R11/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.78008600943515383</v>
       </c>
     </row>
-    <row r="12" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -3244,7 +3225,7 @@
         <v>160.25</v>
       </c>
       <c r="G12" s="1">
-        <f>E12*F12</f>
+        <f t="shared" si="0"/>
         <v>69.965149999999994</v>
       </c>
       <c r="H12" s="13">
@@ -3254,51 +3235,51 @@
         <v>0.16439999999999999</v>
       </c>
       <c r="J12" s="9">
-        <f>IFERROR(H12/I12,"")</f>
+        <f t="shared" si="1"/>
         <v>0.40875912408759124</v>
       </c>
       <c r="K12" s="9">
-        <f>IFERROR(J12/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.25346522146773753</v>
+        <f t="shared" si="2"/>
+        <v>2.0803646015548866E-2</v>
       </c>
       <c r="L12" s="12">
-        <f>F12/(1-(F12*(1+H12)-F12)/(F12*(1+H12)))</f>
+        <f t="shared" si="11"/>
         <v>171.0188</v>
       </c>
       <c r="M12" s="12">
-        <f>L12*E12</f>
+        <f t="shared" si="3"/>
         <v>74.666808079999996</v>
       </c>
       <c r="N12" s="12">
-        <f>F12/(1+I12-H12)</f>
+        <f t="shared" si="4"/>
         <v>146.05359095880419</v>
       </c>
       <c r="O12" s="12">
-        <f>L12-F12</f>
+        <f t="shared" si="5"/>
         <v>10.768799999999999</v>
       </c>
       <c r="P12" s="12">
-        <f>0.5*(N12-F12)</f>
+        <f t="shared" si="6"/>
         <v>-7.0982045205979034</v>
       </c>
       <c r="Q12" s="15">
-        <f>O12+P12</f>
+        <f t="shared" si="7"/>
         <v>3.6705954794020954</v>
       </c>
       <c r="R12" s="12">
-        <f>MAX($Q$2:$Q$279)-Q12</f>
+        <f t="shared" si="8"/>
         <v>110.46184960178229</v>
       </c>
       <c r="S12" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R12)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>9.0528992915203301E-3</v>
+        <f t="shared" si="9"/>
+        <v>9.0528992915203284E-3</v>
       </c>
       <c r="T12" s="9">
-        <f>R12/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.7712556220204998</v>
       </c>
     </row>
-    <row r="13" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -3318,7 +3299,7 @@
         <v>189.76</v>
       </c>
       <c r="G13" s="1">
-        <f>E13*F13</f>
+        <f t="shared" si="0"/>
         <v>77.953407999999996</v>
       </c>
       <c r="H13" s="13">
@@ -3329,51 +3310,51 @@
         <v>0.37</v>
       </c>
       <c r="J13" s="9">
-        <f>IFERROR(H13/I13,"")</f>
+        <f t="shared" si="1"/>
         <v>0.53609680506813773</v>
       </c>
       <c r="K13" s="9">
-        <f>IFERROR(J13/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.33242535130695822</v>
+        <f t="shared" si="2"/>
+        <v>2.728445068375859E-2</v>
       </c>
       <c r="L13" s="12">
-        <f>F13/(1-(F13*(1+H13)-F13)/(F13*(1+H13)))</f>
+        <f t="shared" si="11"/>
         <v>227.4</v>
       </c>
       <c r="M13" s="12">
-        <f>L13*E13</f>
+        <f t="shared" si="3"/>
         <v>93.41592</v>
       </c>
       <c r="N13" s="12">
-        <f>F13/(1+I13-H13)</f>
+        <f t="shared" si="4"/>
         <v>161.96043380326287</v>
       </c>
       <c r="O13" s="12">
-        <f>L13-F13</f>
+        <f t="shared" si="5"/>
         <v>37.640000000000015</v>
       </c>
       <c r="P13" s="12">
-        <f>0.5*(N13-F13)</f>
+        <f t="shared" si="6"/>
         <v>-13.899783098368559</v>
       </c>
       <c r="Q13" s="15">
-        <f>O13+P13</f>
+        <f t="shared" si="7"/>
         <v>23.740216901631456</v>
       </c>
       <c r="R13" s="12">
-        <f>MAX($Q$2:$Q$279)-Q13</f>
+        <f t="shared" si="8"/>
         <v>90.39222817955293</v>
       </c>
       <c r="S13" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R13)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>1.1062897996204102E-2</v>
       </c>
       <c r="T13" s="9">
-        <f>R13/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.6311275288415521</v>
       </c>
     </row>
-    <row r="14" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -3393,7 +3374,7 @@
         <v>142.78</v>
       </c>
       <c r="G14" s="1">
-        <f>E14*F14</f>
+        <f t="shared" si="0"/>
         <v>50.187169999999995</v>
       </c>
       <c r="H14" s="13">
@@ -3403,51 +3384,51 @@
         <v>0.18340000000000001</v>
       </c>
       <c r="J14" s="9">
-        <f>IFERROR(H14/I14,"")</f>
+        <f t="shared" si="1"/>
         <v>0.38167938931297712</v>
       </c>
       <c r="K14" s="9">
-        <f>IFERROR(J14/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.23667349605425328</v>
+        <f t="shared" si="2"/>
+        <v>1.9425432825314851E-2</v>
       </c>
       <c r="L14" s="12">
-        <f>F14/(1-(F14*(1+H14)-F14)/(F14*(1+H14)))</f>
+        <f t="shared" si="11"/>
         <v>152.77460000000002</v>
       </c>
       <c r="M14" s="12">
-        <f>L14*E14</f>
+        <f t="shared" si="3"/>
         <v>53.700271900000004</v>
       </c>
       <c r="N14" s="12">
-        <f>F14/(1+I14-H14)</f>
+        <f t="shared" si="4"/>
         <v>128.23783007005568</v>
       </c>
       <c r="O14" s="12">
-        <f>L14-F14</f>
+        <f t="shared" si="5"/>
         <v>9.9946000000000197</v>
       </c>
       <c r="P14" s="12">
-        <f>0.5*(N14-F14)</f>
+        <f t="shared" si="6"/>
         <v>-7.2710849649721609</v>
       </c>
       <c r="Q14" s="15">
-        <f>O14+P14</f>
+        <f t="shared" si="7"/>
         <v>2.7235150350278587</v>
       </c>
       <c r="R14" s="12">
-        <f>MAX($Q$2:$Q$279)-Q14</f>
+        <f t="shared" si="8"/>
         <v>111.40893004615653</v>
       </c>
       <c r="S14" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R14)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.9759411528833617E-3</v>
       </c>
       <c r="T14" s="9">
-        <f>R14/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.77786823189316223</v>
       </c>
     </row>
-    <row r="15" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>96</v>
       </c>
@@ -3467,7 +3448,7 @@
         <v>34.78</v>
       </c>
       <c r="G15" s="1">
-        <f>E15*F15</f>
+        <f t="shared" si="0"/>
         <v>9.99925</v>
       </c>
       <c r="H15" s="13">
@@ -3477,51 +3458,51 @@
         <v>0.2</v>
       </c>
       <c r="J15" s="9">
-        <f>IFERROR(H15/I15,"")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="K15" s="9">
-        <f>IFERROR(J15/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.6200845596621436</v>
+        <f t="shared" si="2"/>
+        <v>5.0894634002324905E-2</v>
       </c>
       <c r="L15" s="12">
-        <f>F15/(1-(F15*(1+H15)-F15)/(F15*(1+H15)))</f>
+        <f t="shared" si="11"/>
         <v>41.735999999999997</v>
       </c>
       <c r="M15" s="12">
-        <f>L15*E15</f>
+        <f t="shared" si="3"/>
         <v>11.999099999999999</v>
       </c>
       <c r="N15" s="12">
-        <f>F15/(1+I15-H15)</f>
+        <f t="shared" si="4"/>
         <v>34.78</v>
       </c>
       <c r="O15" s="12">
-        <f>L15-F15</f>
+        <f t="shared" si="5"/>
         <v>6.955999999999996</v>
       </c>
       <c r="P15" s="12">
-        <f>0.5*(N15-F15)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q15" s="15">
-        <f>O15+P15</f>
+        <f t="shared" si="7"/>
         <v>6.955999999999996</v>
       </c>
       <c r="R15" s="12">
-        <f>MAX($Q$2:$Q$279)-Q15</f>
+        <f t="shared" si="8"/>
         <v>107.1764450811844</v>
       </c>
       <c r="S15" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R15)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>9.3304083676456744E-3</v>
       </c>
       <c r="T15" s="9">
-        <f>R15/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.74831660084479601</v>
       </c>
     </row>
-    <row r="16" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -3541,7 +3522,7 @@
         <v>39.799999999999997</v>
       </c>
       <c r="G16" s="1">
-        <f>E16*F16</f>
+        <f t="shared" si="0"/>
         <v>10.9251</v>
       </c>
       <c r="H16" s="13">
@@ -3551,51 +3532,51 @@
         <v>0.2</v>
       </c>
       <c r="J16" s="9">
-        <f>IFERROR(H16/I16,"")</f>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
       <c r="K16" s="9">
-        <f>IFERROR(J16/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.3100422798310718</v>
+        <f t="shared" si="2"/>
+        <v>2.5447317001162453E-2</v>
       </c>
       <c r="L16" s="12">
-        <f>F16/(1-(F16*(1+H16)-F16)/(F16*(1+H16)))</f>
+        <f t="shared" si="11"/>
         <v>43.78</v>
       </c>
       <c r="M16" s="12">
-        <f>L16*E16</f>
+        <f t="shared" si="3"/>
         <v>12.017610000000001</v>
       </c>
       <c r="N16" s="12">
-        <f>F16/(1+I16-H16)</f>
+        <f t="shared" si="4"/>
         <v>36.181818181818187</v>
       </c>
       <c r="O16" s="12">
-        <f>L16-F16</f>
+        <f t="shared" si="5"/>
         <v>3.980000000000004</v>
       </c>
       <c r="P16" s="12">
-        <f>0.5*(N16-F16)</f>
+        <f t="shared" si="6"/>
         <v>-1.8090909090909051</v>
       </c>
       <c r="Q16" s="15">
-        <f>O16+P16</f>
+        <f t="shared" si="7"/>
         <v>2.1709090909090989</v>
       </c>
       <c r="R16" s="12">
-        <f>MAX($Q$2:$Q$279)-Q16</f>
+        <f t="shared" si="8"/>
         <v>111.96153599027528</v>
       </c>
       <c r="S16" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R16)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.931638809303739E-3</v>
       </c>
       <c r="T16" s="9">
-        <f>R16/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.78172658156501729</v>
       </c>
     </row>
-    <row r="17" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -3615,7 +3596,7 @@
         <v>132.38999999999999</v>
       </c>
       <c r="G17" s="1">
-        <f>E17*F17</f>
+        <f t="shared" si="0"/>
         <v>33.984512999999993</v>
       </c>
       <c r="H17" s="13">
@@ -3625,51 +3606,51 @@
         <v>0.1623</v>
       </c>
       <c r="J17" s="9">
-        <f>IFERROR(H17/I17,"")</f>
+        <f t="shared" si="1"/>
         <v>0.43130006161429457</v>
       </c>
       <c r="K17" s="9">
-        <f>IFERROR(J17/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.26744250878835524</v>
+        <f t="shared" si="2"/>
+        <v>2.1950858781039705E-2</v>
       </c>
       <c r="L17" s="12">
-        <f>F17/(1-(F17*(1+H17)-F17)/(F17*(1+H17)))</f>
+        <f t="shared" si="11"/>
         <v>141.65729999999999</v>
       </c>
       <c r="M17" s="12">
-        <f>L17*E17</f>
+        <f t="shared" si="3"/>
         <v>36.363428909999996</v>
       </c>
       <c r="N17" s="12">
-        <f>F17/(1+I17-H17)</f>
+        <f t="shared" si="4"/>
         <v>121.20296621807194</v>
       </c>
       <c r="O17" s="12">
-        <f>L17-F17</f>
+        <f t="shared" si="5"/>
         <v>9.2673000000000059</v>
       </c>
       <c r="P17" s="12">
-        <f>0.5*(N17-F17)</f>
+        <f t="shared" si="6"/>
         <v>-5.5935168909640254</v>
       </c>
       <c r="Q17" s="15">
-        <f>O17+P17</f>
+        <f t="shared" si="7"/>
         <v>3.6737831090359805</v>
       </c>
       <c r="R17" s="12">
-        <f>MAX($Q$2:$Q$279)-Q17</f>
+        <f t="shared" si="8"/>
         <v>110.45866197214841</v>
       </c>
       <c r="S17" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R17)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>9.0531605411999748E-3</v>
+        <f t="shared" si="9"/>
+        <v>9.0531605411999731E-3</v>
       </c>
       <c r="T17" s="9">
-        <f>R17/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.77123336567330925</v>
       </c>
     </row>
-    <row r="18" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -3689,7 +3670,7 @@
         <v>178.56</v>
       </c>
       <c r="G18" s="1">
-        <f>E18*F18</f>
+        <f t="shared" si="0"/>
         <v>44.943551999999997</v>
       </c>
       <c r="H18" s="13">
@@ -3700,51 +3681,51 @@
         <v>0.52980000000000005</v>
       </c>
       <c r="J18" s="9">
-        <f>IFERROR(H18/I18,"")</f>
+        <f t="shared" si="1"/>
         <v>0.18456447350795815</v>
       </c>
       <c r="K18" s="9">
-        <f>IFERROR(J18/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.1144455802844576</v>
+        <f t="shared" si="2"/>
+        <v>9.3933413290193217E-3</v>
       </c>
       <c r="L18" s="12">
-        <f>F18/(1-(F18*(1+H18)-F18)/(F18*(1+H18)))</f>
+        <f t="shared" si="11"/>
         <v>196.02</v>
       </c>
       <c r="M18" s="12">
-        <f>L18*E18</f>
+        <f t="shared" si="3"/>
         <v>49.338234</v>
       </c>
       <c r="N18" s="12">
-        <f>F18/(1+I18-H18)</f>
+        <f t="shared" si="4"/>
         <v>124.69119255370553</v>
       </c>
       <c r="O18" s="12">
-        <f>L18-F18</f>
+        <f t="shared" si="5"/>
         <v>17.460000000000008</v>
       </c>
       <c r="P18" s="12">
-        <f>0.5*(N18-F18)</f>
+        <f t="shared" si="6"/>
         <v>-26.934403723147234</v>
       </c>
       <c r="Q18" s="15">
-        <f>O18+P18</f>
+        <f t="shared" si="7"/>
         <v>-9.4744037231472262</v>
       </c>
       <c r="R18" s="12">
-        <f>MAX($Q$2:$Q$279)-Q18</f>
+        <f t="shared" si="8"/>
         <v>123.60684880433161</v>
       </c>
       <c r="S18" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R18)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.0901666022000929E-3</v>
       </c>
       <c r="T18" s="9">
-        <f>R18/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.86303531404059042</v>
       </c>
     </row>
-    <row r="19" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -3764,7 +3745,7 @@
         <v>135.82</v>
       </c>
       <c r="G19" s="1">
-        <f>E19*F19</f>
+        <f t="shared" si="0"/>
         <v>25.995947999999999</v>
       </c>
       <c r="H19" s="13">
@@ -3774,51 +3755,51 @@
         <v>0.33710000000000001</v>
       </c>
       <c r="J19" s="9">
-        <f>IFERROR(H19/I19,"")</f>
+        <f t="shared" si="1"/>
         <v>0.35657075051913378</v>
       </c>
       <c r="K19" s="9">
-        <f>IFERROR(J19/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.22110401682405711</v>
+        <f t="shared" si="2"/>
+        <v>1.8147537843605618E-2</v>
       </c>
       <c r="L19" s="12">
-        <f>F19/(1-(F19*(1+H19)-F19)/(F19*(1+H19)))</f>
+        <f t="shared" si="11"/>
         <v>152.14556400000001</v>
       </c>
       <c r="M19" s="12">
-        <f>L19*E19</f>
+        <f t="shared" si="3"/>
         <v>29.120660949599998</v>
       </c>
       <c r="N19" s="12">
-        <f>F19/(1+I19-H19)</f>
+        <f t="shared" si="4"/>
         <v>111.61147177253677</v>
       </c>
       <c r="O19" s="12">
-        <f>L19-F19</f>
+        <f t="shared" si="5"/>
         <v>16.325564000000014</v>
       </c>
       <c r="P19" s="12">
-        <f>0.5*(N19-F19)</f>
+        <f t="shared" si="6"/>
         <v>-12.10426411373161</v>
       </c>
       <c r="Q19" s="15">
-        <f>O19+P19</f>
+        <f t="shared" si="7"/>
         <v>4.2212998862684046</v>
       </c>
       <c r="R19" s="12">
-        <f>MAX($Q$2:$Q$279)-Q19</f>
+        <f t="shared" si="8"/>
         <v>109.91114519491597</v>
       </c>
       <c r="S19" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R19)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>9.0982583997883393E-3</v>
       </c>
       <c r="T19" s="9">
-        <f>R19/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.76741054907089512</v>
       </c>
     </row>
-    <row r="20" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -3838,7 +3819,7 @@
         <v>227.38</v>
       </c>
       <c r="G20" s="1">
-        <f>E20*F20</f>
+        <f t="shared" si="0"/>
         <v>42.792915999999998</v>
       </c>
       <c r="H20" s="13">
@@ -3848,51 +3829,51 @@
         <v>0.2271</v>
       </c>
       <c r="J20" s="9">
-        <f>IFERROR(H20/I20,"")</f>
+        <f t="shared" si="1"/>
         <v>0.66050198150594452</v>
       </c>
       <c r="K20" s="9">
-        <f>IFERROR(J20/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.40956708035808692</v>
+        <f t="shared" si="2"/>
+        <v>3.3616006606555421E-2</v>
       </c>
       <c r="L20" s="12">
-        <f>F20/(1-(F20*(1+H20)-F20)/(F20*(1+H20)))</f>
+        <f t="shared" si="11"/>
         <v>261.48699999999997</v>
       </c>
       <c r="M20" s="12">
-        <f>L20*E20</f>
+        <f t="shared" si="3"/>
         <v>49.211853399999995</v>
       </c>
       <c r="N20" s="12">
-        <f>F20/(1+I20-H20)</f>
+        <f t="shared" si="4"/>
         <v>211.10389007520189</v>
       </c>
       <c r="O20" s="12">
-        <f>L20-F20</f>
+        <f t="shared" si="5"/>
         <v>34.106999999999971</v>
       </c>
       <c r="P20" s="12">
-        <f>0.5*(N20-F20)</f>
+        <f t="shared" si="6"/>
         <v>-8.1380549623990532</v>
       </c>
       <c r="Q20" s="15">
-        <f>O20+P20</f>
+        <f t="shared" si="7"/>
         <v>25.968945037600918</v>
       </c>
       <c r="R20" s="12">
-        <f>MAX($Q$2:$Q$279)-Q20</f>
+        <f t="shared" si="8"/>
         <v>88.163500043583468</v>
       </c>
       <c r="S20" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R20)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>1.1342562392664218E-2</v>
       </c>
       <c r="T20" s="9">
-        <f>R20/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.6155663272953309</v>
       </c>
     </row>
-    <row r="21" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -3912,7 +3893,7 @@
         <v>423.77</v>
       </c>
       <c r="G21" s="1">
-        <f>E21*F21</f>
+        <f t="shared" si="0"/>
         <v>56.658049000000005</v>
       </c>
       <c r="H21" s="13">
@@ -3922,47 +3903,47 @@
         <v>0.1963</v>
       </c>
       <c r="J21" s="9">
-        <f>IFERROR(H21/I21,"")</f>
+        <f t="shared" si="1"/>
         <v>0.76413652572592972</v>
       </c>
       <c r="K21" s="9">
-        <f>IFERROR(J21/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.47382926107652334</v>
+        <f t="shared" si="2"/>
+        <v>3.8890448804629323E-2</v>
       </c>
       <c r="L21" s="12">
-        <f>F21/(1-(F21*(1+H21)-F21)/(F21*(1+H21)))</f>
+        <f t="shared" si="11"/>
         <v>487.33549999999991</v>
       </c>
       <c r="M21" s="12">
-        <f>L21*E21</f>
+        <f t="shared" si="3"/>
         <v>65.156756349999995</v>
       </c>
       <c r="N21" s="12">
-        <f>F21/(1+I21-H21)</f>
+        <f t="shared" si="4"/>
         <v>405.01768135334032</v>
       </c>
       <c r="O21" s="12">
-        <f>L21-F21</f>
+        <f t="shared" si="5"/>
         <v>63.565499999999929</v>
       </c>
       <c r="P21" s="12">
-        <f>0.5*(N21-F21)</f>
+        <f t="shared" si="6"/>
         <v>-9.3761593233298299</v>
       </c>
       <c r="Q21" s="15">
-        <f>O21+P21</f>
+        <f t="shared" si="7"/>
         <v>54.189340676670099</v>
       </c>
       <c r="R21" s="12">
-        <f>MAX($Q$2:$Q$279)-Q21</f>
+        <f t="shared" si="8"/>
         <v>59.943104404514287</v>
       </c>
       <c r="S21" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R21)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>1.6682485999585474E-2</v>
       </c>
       <c r="T21" s="9">
-        <f>R21/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.41852871774290379</v>
       </c>
     </row>
@@ -3986,7 +3967,7 @@
         <v>501.56</v>
       </c>
       <c r="G22" s="1">
-        <f>E22*F22</f>
+        <f t="shared" si="0"/>
         <v>64.901863999999989</v>
       </c>
       <c r="H22" s="13">
@@ -3996,47 +3977,47 @@
         <v>0.29699999999999999</v>
       </c>
       <c r="J22" s="9">
-        <f>IFERROR(H22/I22,"")</f>
+        <f t="shared" si="1"/>
         <v>0.84175084175084181</v>
       </c>
       <c r="K22" s="9">
-        <f>IFERROR(J22/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.52195670005230943</v>
+        <f t="shared" si="2"/>
+        <v>4.2840601012058006E-2</v>
       </c>
       <c r="L22" s="12">
-        <f>F22/(1-(F22*(1+H22)-F22)/(F22*(1+H22)))</f>
+        <f t="shared" si="11"/>
         <v>626.95000000000005</v>
       </c>
       <c r="M22" s="12">
-        <f>L22*E22</f>
+        <f t="shared" si="3"/>
         <v>81.127330000000001</v>
       </c>
       <c r="N22" s="12">
-        <f>F22/(1+I22-H22)</f>
+        <f t="shared" si="4"/>
         <v>479.04489016236869</v>
       </c>
       <c r="O22" s="12">
-        <f>L22-F22</f>
+        <f t="shared" si="5"/>
         <v>125.39000000000004</v>
       </c>
       <c r="P22" s="12">
-        <f>0.5*(N22-F22)</f>
+        <f t="shared" si="6"/>
         <v>-11.257554918815657</v>
       </c>
       <c r="Q22" s="15">
-        <f>O22+P22</f>
+        <f t="shared" si="7"/>
         <v>114.13244508118439</v>
       </c>
       <c r="R22" s="12">
-        <f>MAX($Q$2:$Q$279)-Q22</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="S22" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R22)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T22" s="9">
-        <f>R22/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -4060,7 +4041,7 @@
         <v>10.92</v>
       </c>
       <c r="G23" s="1">
-        <f>E23*F23</f>
+        <f t="shared" si="0"/>
         <v>1.092E-18</v>
       </c>
       <c r="H23" s="13">
@@ -4070,51 +4051,51 @@
         <v>1.8652</v>
       </c>
       <c r="J23" s="9">
-        <f>IFERROR(H23/I23,"")</f>
+        <f t="shared" si="1"/>
         <v>0.53613553506326406</v>
       </c>
       <c r="K23" s="9">
-        <f>IFERROR(J23/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.33244936717893181</v>
+        <f t="shared" si="2"/>
+        <v>2.7286421832685457E-2</v>
       </c>
       <c r="L23" s="12">
-        <f>F23/(1-(F23*(1+H23)-F23)/(F23*(1+H23)))</f>
+        <f t="shared" si="11"/>
         <v>21.84</v>
       </c>
       <c r="M23" s="12">
-        <f>L23*E23</f>
+        <f t="shared" si="3"/>
         <v>2.1840000000000001E-18</v>
       </c>
       <c r="N23" s="12">
-        <f>F23/(1+I23-H23)</f>
+        <f t="shared" si="4"/>
         <v>5.8546000428908433</v>
       </c>
       <c r="O23" s="12">
-        <f>L23-F23</f>
+        <f t="shared" si="5"/>
         <v>10.92</v>
       </c>
       <c r="P23" s="12">
-        <f>0.5*(N23-F23)</f>
+        <f t="shared" si="6"/>
         <v>-2.5326999785545783</v>
       </c>
       <c r="Q23" s="15">
-        <f>O23+P23</f>
+        <f t="shared" si="7"/>
         <v>8.3873000214454212</v>
       </c>
       <c r="R23" s="12">
-        <f>MAX($Q$2:$Q$279)-Q23</f>
+        <f t="shared" si="8"/>
         <v>105.74514505973896</v>
       </c>
       <c r="S23" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R23)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>9.4566989286843078E-3</v>
       </c>
       <c r="T23" s="9">
-        <f>R23/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.73832312171768166</v>
       </c>
     </row>
-    <row r="24" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>37</v>
       </c>
@@ -4134,7 +4115,7 @@
         <v>283.43</v>
       </c>
       <c r="G24" s="1">
-        <f>E24*F24</f>
+        <f t="shared" si="0"/>
         <v>2.8342999999999998E-17</v>
       </c>
       <c r="H24" s="13">
@@ -4144,51 +4125,51 @@
         <v>0.26</v>
       </c>
       <c r="J24" s="9">
-        <f>IFERROR(H24/I24,"")</f>
+        <f t="shared" si="1"/>
         <v>0.96153846153846145</v>
       </c>
       <c r="K24" s="9">
-        <f>IFERROR(J24/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.59623515352129186</v>
+        <f t="shared" si="2"/>
+        <v>4.8937148079158561E-2</v>
       </c>
       <c r="L24" s="12">
-        <f>F24/(1-(F24*(1+H24)-F24)/(F24*(1+H24)))</f>
+        <f t="shared" si="11"/>
         <v>354.28750000000002</v>
       </c>
       <c r="M24" s="12">
-        <f>L24*E24</f>
+        <f t="shared" si="3"/>
         <v>3.542875E-17</v>
       </c>
       <c r="N24" s="12">
-        <f>F24/(1+I24-H24)</f>
+        <f t="shared" si="4"/>
         <v>280.62376237623761</v>
       </c>
       <c r="O24" s="12">
-        <f>L24-F24</f>
+        <f t="shared" si="5"/>
         <v>70.857500000000016</v>
       </c>
       <c r="P24" s="12">
-        <f>0.5*(N24-F24)</f>
+        <f t="shared" si="6"/>
         <v>-1.4031188118811997</v>
       </c>
       <c r="Q24" s="15">
-        <f>O24+P24</f>
+        <f t="shared" si="7"/>
         <v>69.454381188118816</v>
       </c>
       <c r="R24" s="12">
-        <f>MAX($Q$2:$Q$279)-Q24</f>
+        <f t="shared" si="8"/>
         <v>44.67806389306557</v>
       </c>
       <c r="S24" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R24)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>2.2382348581474875E-2</v>
       </c>
       <c r="T24" s="9">
-        <f>R24/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.311946686414727</v>
       </c>
     </row>
-    <row r="25" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>36</v>
       </c>
@@ -4208,7 +4189,7 @@
         <v>188.12</v>
       </c>
       <c r="G25" s="1">
-        <f>E25*F25</f>
+        <f t="shared" si="0"/>
         <v>1.8812000000000001E-17</v>
       </c>
       <c r="H25" s="13">
@@ -4218,51 +4199,51 @@
         <v>0.37780000000000002</v>
       </c>
       <c r="J25" s="9">
-        <f>IFERROR(H25/I25,"")</f>
+        <f t="shared" si="1"/>
         <v>0.39703546850185278</v>
       </c>
       <c r="K25" s="9">
-        <f>IFERROR(J25/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.24619556365622425</v>
+        <f t="shared" si="2"/>
+        <v>2.0206974855343396E-2</v>
       </c>
       <c r="L25" s="12">
-        <f>F25/(1-(F25*(1+H25)-F25)/(F25*(1+H25)))</f>
+        <f t="shared" si="11"/>
         <v>216.33799999999999</v>
       </c>
       <c r="M25" s="12">
-        <f>L25*E25</f>
+        <f t="shared" si="3"/>
         <v>2.16338E-17</v>
       </c>
       <c r="N25" s="12">
-        <f>F25/(1+I25-H25)</f>
+        <f t="shared" si="4"/>
         <v>153.21713634142367</v>
       </c>
       <c r="O25" s="12">
-        <f>L25-F25</f>
+        <f t="shared" si="5"/>
         <v>28.217999999999989</v>
       </c>
       <c r="P25" s="12">
-        <f>0.5*(N25-F25)</f>
+        <f t="shared" si="6"/>
         <v>-17.451431829288168</v>
       </c>
       <c r="Q25" s="15">
-        <f>O25+P25</f>
+        <f t="shared" si="7"/>
         <v>10.766568170711821</v>
       </c>
       <c r="R25" s="12">
-        <f>MAX($Q$2:$Q$279)-Q25</f>
+        <f t="shared" si="8"/>
         <v>103.36587691047256</v>
       </c>
       <c r="S25" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R25)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>9.6743725288193673E-3</v>
+        <f t="shared" si="9"/>
+        <v>9.674372528819369E-3</v>
       </c>
       <c r="T25" s="9">
-        <f>R25/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.72171083482377829</v>
       </c>
     </row>
-    <row r="26" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>36</v>
       </c>
@@ -4282,7 +4263,7 @@
         <v>167.24</v>
       </c>
       <c r="G26" s="1">
-        <f>E26*F26</f>
+        <f t="shared" si="0"/>
         <v>1.6724000000000001E-17</v>
       </c>
       <c r="H26" s="13">
@@ -4293,51 +4274,51 @@
         <v>0.26790000000000003</v>
       </c>
       <c r="J26" s="9">
-        <f>IFERROR(H26/I26,"")</f>
+        <f t="shared" si="1"/>
         <v>0.51714598979956872</v>
       </c>
       <c r="K26" s="9">
-        <f>IFERROR(J26/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.32067424336590894</v>
+        <f t="shared" si="2"/>
+        <v>2.6319955876619099E-2</v>
       </c>
       <c r="L26" s="12">
-        <f>F26/(1-(F26*(1+H26)-F26)/(F26*(1+H26)))</f>
+        <f t="shared" si="11"/>
         <v>190.41</v>
       </c>
       <c r="M26" s="12">
-        <f>L26*E26</f>
+        <f t="shared" si="3"/>
         <v>1.9040999999999999E-17</v>
       </c>
       <c r="N26" s="12">
-        <f>F26/(1+I26-H26)</f>
+        <f t="shared" si="4"/>
         <v>148.08431772538498</v>
       </c>
       <c r="O26" s="12">
-        <f>L26-F26</f>
+        <f t="shared" si="5"/>
         <v>23.169999999999987</v>
       </c>
       <c r="P26" s="12">
-        <f>0.5*(N26-F26)</f>
+        <f t="shared" si="6"/>
         <v>-9.5778411373075159</v>
       </c>
       <c r="Q26" s="15">
-        <f>O26+P26</f>
+        <f t="shared" si="7"/>
         <v>13.592158862692472</v>
       </c>
       <c r="R26" s="12">
-        <f>MAX($Q$2:$Q$279)-Q26</f>
+        <f t="shared" si="8"/>
         <v>100.54028621849191</v>
       </c>
       <c r="S26" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R26)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>9.9462617186788418E-3</v>
       </c>
       <c r="T26" s="9">
-        <f>R26/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.70198227953907921</v>
       </c>
     </row>
-    <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -4357,7 +4338,7 @@
         <v>668.82</v>
       </c>
       <c r="G27" s="1">
-        <f>E27*F27</f>
+        <f t="shared" si="0"/>
         <v>6.6881999999999999E-17</v>
       </c>
       <c r="H27" s="13">
@@ -4367,51 +4348,51 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="J27" s="9">
-        <f>IFERROR(H27/I27,"")</f>
+        <f t="shared" si="1"/>
         <v>0.17857142857142858</v>
       </c>
       <c r="K27" s="9">
-        <f>IFERROR(J27/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.11072938565395421</v>
+        <f t="shared" si="2"/>
+        <v>9.0883275004151626E-3</v>
       </c>
       <c r="L27" s="12">
-        <f>F27/(1-(F27*(1+H27)-F27)/(F27*(1+H27)))</f>
+        <f t="shared" si="11"/>
         <v>702.26100000000008</v>
       </c>
       <c r="M27" s="12">
-        <f>L27*E27</f>
+        <f t="shared" si="3"/>
         <v>7.0226100000000009E-17</v>
       </c>
       <c r="N27" s="12">
-        <f>F27/(1+I27-H27)</f>
+        <f t="shared" si="4"/>
         <v>543.7560975609756</v>
       </c>
       <c r="O27" s="12">
-        <f>L27-F27</f>
+        <f t="shared" si="5"/>
         <v>33.441000000000031</v>
       </c>
       <c r="P27" s="12">
-        <f>0.5*(N27-F27)</f>
+        <f t="shared" si="6"/>
         <v>-62.531951219512223</v>
       </c>
       <c r="Q27" s="15">
-        <f>O27+P27</f>
+        <f t="shared" si="7"/>
         <v>-29.090951219512192</v>
       </c>
       <c r="R27" s="12">
-        <f>MAX($Q$2:$Q$279)-Q27</f>
+        <f t="shared" si="8"/>
         <v>143.22339630069658</v>
       </c>
       <c r="S27" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R27)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>6.9820994741704532E-3</v>
+        <f t="shared" si="9"/>
+        <v>6.9820994741704541E-3</v>
       </c>
       <c r="T27" s="9">
-        <f>R27/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -4431,7 +4412,7 @@
         <v>700.32</v>
       </c>
       <c r="G28" s="1">
-        <f>E28*F28</f>
+        <f t="shared" si="0"/>
         <v>7.0031999999999998E-17</v>
       </c>
       <c r="H28" s="13">
@@ -4441,51 +4422,51 @@
         <v>0.45340000000000003</v>
       </c>
       <c r="J28" s="9">
-        <f>IFERROR(H28/I28,"")</f>
+        <f t="shared" si="1"/>
         <v>0.22055580061755625</v>
       </c>
       <c r="K28" s="9">
-        <f>IFERROR(J28/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.13676324650686891</v>
+        <f t="shared" si="2"/>
+        <v>1.1225106749520271E-2</v>
       </c>
       <c r="L28" s="12">
-        <f>F28/(1-(F28*(1+H28)-F28)/(F28*(1+H28)))</f>
+        <f t="shared" si="11"/>
         <v>770.35200000000009</v>
       </c>
       <c r="M28" s="12">
-        <f>L28*E28</f>
+        <f t="shared" si="3"/>
         <v>7.7035200000000004E-17</v>
       </c>
       <c r="N28" s="12">
-        <f>F28/(1+I28-H28)</f>
+        <f t="shared" si="4"/>
         <v>517.45234224915032</v>
       </c>
       <c r="O28" s="12">
-        <f>L28-F28</f>
+        <f t="shared" si="5"/>
         <v>70.032000000000039</v>
       </c>
       <c r="P28" s="12">
-        <f>0.5*(N28-F28)</f>
+        <f t="shared" si="6"/>
         <v>-91.433828875424865</v>
       </c>
       <c r="Q28" s="15">
-        <f>O28+P28</f>
+        <f t="shared" si="7"/>
         <v>-21.401828875424826</v>
       </c>
       <c r="R28" s="12">
-        <f>MAX($Q$2:$Q$279)-Q28</f>
+        <f t="shared" si="8"/>
         <v>135.53427395660921</v>
       </c>
       <c r="S28" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R28)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>7.37820752498476E-3</v>
+        <f t="shared" si="9"/>
+        <v>7.3782075249847591E-3</v>
       </c>
       <c r="T28" s="9">
-        <f>R28/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.94631378292451529</v>
       </c>
     </row>
-    <row r="29" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -4505,7 +4486,7 @@
         <v>147.01</v>
       </c>
       <c r="G29" s="1">
-        <f>E29*F29</f>
+        <f t="shared" si="0"/>
         <v>1.4700999999999999E-17</v>
       </c>
       <c r="H29" s="13">
@@ -4515,47 +4496,47 @@
         <v>0.52380000000000004</v>
       </c>
       <c r="J29" s="9">
-        <f>IFERROR(H29/I29,"")</f>
+        <f t="shared" si="1"/>
         <v>0.28636884306987398</v>
       </c>
       <c r="K29" s="9">
-        <f>IFERROR(J29/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.17757289795594031</v>
+        <f t="shared" si="2"/>
+        <v>1.4574637457710454E-2</v>
       </c>
       <c r="L29" s="12">
-        <f>F29/(1-(F29*(1+H29)-F29)/(F29*(1+H29)))</f>
+        <f t="shared" si="11"/>
         <v>169.06149999999997</v>
       </c>
       <c r="M29" s="12">
-        <f>L29*E29</f>
+        <f t="shared" si="3"/>
         <v>1.6906149999999997E-17</v>
       </c>
       <c r="N29" s="12">
-        <f>F29/(1+I29-H29)</f>
+        <f t="shared" si="4"/>
         <v>107.00975396709855</v>
       </c>
       <c r="O29" s="12">
-        <f>L29-F29</f>
+        <f t="shared" si="5"/>
         <v>22.051499999999976</v>
       </c>
       <c r="P29" s="12">
-        <f>0.5*(N29-F29)</f>
+        <f t="shared" si="6"/>
         <v>-20.000123016450722</v>
       </c>
       <c r="Q29" s="15">
-        <f>O29+P29</f>
+        <f t="shared" si="7"/>
         <v>2.0513769835492539</v>
       </c>
       <c r="R29" s="12">
-        <f>MAX($Q$2:$Q$279)-Q29</f>
+        <f t="shared" si="8"/>
         <v>112.08106809763513</v>
       </c>
       <c r="S29" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R29)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.9221134039237406E-3</v>
       </c>
       <c r="T29" s="9">
-        <f>R29/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.78256116662896091</v>
       </c>
     </row>
@@ -4579,7 +4560,7 @@
         <v>169.34</v>
       </c>
       <c r="G30" s="1">
-        <f>E30*F30</f>
+        <f t="shared" si="0"/>
         <v>1.6933999999999999E-17</v>
       </c>
       <c r="H30" s="13">
@@ -4589,51 +4570,51 @@
         <v>0.4259</v>
       </c>
       <c r="J30" s="9">
-        <f>IFERROR(H30/I30,"")</f>
+        <f t="shared" si="1"/>
         <v>0.23479690068091102</v>
       </c>
       <c r="K30" s="9">
-        <f>IFERROR(J30/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.14559393276875876</v>
+        <f t="shared" si="2"/>
+        <v>1.1949902325035199E-2</v>
       </c>
       <c r="L30" s="12">
-        <f>F30/(1-(F30*(1+H30)-F30)/(F30*(1+H30)))</f>
+        <f t="shared" si="11"/>
         <v>186.27400000000003</v>
       </c>
       <c r="M30" s="12">
-        <f>L30*E30</f>
+        <f t="shared" si="3"/>
         <v>1.8627400000000003E-17</v>
       </c>
       <c r="N30" s="12">
-        <f>F30/(1+I30-H30)</f>
+        <f t="shared" si="4"/>
         <v>127.71702239987934</v>
       </c>
       <c r="O30" s="12">
-        <f>L30-F30</f>
+        <f t="shared" si="5"/>
         <v>16.934000000000026</v>
       </c>
       <c r="P30" s="12">
-        <f>0.5*(N30-F30)</f>
+        <f t="shared" si="6"/>
         <v>-20.811488800060332</v>
       </c>
       <c r="Q30" s="15">
-        <f>O30+P30</f>
+        <f t="shared" si="7"/>
         <v>-3.8774888000603056</v>
       </c>
       <c r="R30" s="12">
-        <f>MAX($Q$2:$Q$279)-Q30</f>
+        <f t="shared" si="8"/>
         <v>118.00993388124469</v>
       </c>
       <c r="S30" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R30)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.4738628953585915E-3</v>
+        <f t="shared" si="9"/>
+        <v>8.4738628953585898E-3</v>
       </c>
       <c r="T30" s="9">
-        <f>R30/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.82395709729912847</v>
       </c>
     </row>
-    <row r="31" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>40</v>
       </c>
@@ -4653,7 +4634,7 @@
         <v>113.58</v>
       </c>
       <c r="G31" s="1">
-        <f>E31*F31</f>
+        <f t="shared" si="0"/>
         <v>1.1357999999999999E-17</v>
       </c>
       <c r="H31" s="13">
@@ -4664,51 +4645,51 @@
         <v>0.16439999999999999</v>
       </c>
       <c r="J31" s="9">
-        <f>IFERROR(H31/I31,"")</f>
+        <f t="shared" si="1"/>
         <v>0.40540789496797319</v>
       </c>
       <c r="K31" s="9">
-        <f>IFERROR(J31/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.25138717603477223</v>
+        <f t="shared" si="2"/>
+        <v>2.0633086436047974E-2</v>
       </c>
       <c r="L31" s="12">
-        <f>F31/(1-(F31*(1+H31)-F31)/(F31*(1+H31)))</f>
+        <f t="shared" si="11"/>
         <v>121.15000000000002</v>
       </c>
       <c r="M31" s="12">
-        <f>L31*E31</f>
+        <f t="shared" si="3"/>
         <v>1.2115000000000002E-17</v>
       </c>
       <c r="N31" s="12">
-        <f>F31/(1+I31-H31)</f>
+        <f t="shared" si="4"/>
         <v>103.46609203186667</v>
       </c>
       <c r="O31" s="12">
-        <f>L31-F31</f>
+        <f t="shared" si="5"/>
         <v>7.5700000000000216</v>
       </c>
       <c r="P31" s="12">
-        <f>0.5*(N31-F31)</f>
+        <f t="shared" si="6"/>
         <v>-5.0569539840666664</v>
       </c>
       <c r="Q31" s="15">
-        <f>O31+P31</f>
+        <f t="shared" si="7"/>
         <v>2.5130460159333552</v>
       </c>
       <c r="R31" s="12">
-        <f>MAX($Q$2:$Q$279)-Q31</f>
+        <f t="shared" si="8"/>
         <v>111.61939906525103</v>
       </c>
       <c r="S31" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R31)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.9590161600441413E-3</v>
       </c>
       <c r="T31" s="9">
-        <f>R31/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.77933774752071117</v>
       </c>
     </row>
-    <row r="32" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -4728,7 +4709,7 @@
         <v>64.349999999999994</v>
       </c>
       <c r="G32" s="1">
-        <f>E32*F32</f>
+        <f t="shared" si="0"/>
         <v>6.4349999999999993E-18</v>
       </c>
       <c r="H32" s="13">
@@ -4738,51 +4719,51 @@
         <v>0.67300000000000004</v>
       </c>
       <c r="J32" s="9">
-        <f>IFERROR(H32/I32,"")</f>
+        <f t="shared" si="1"/>
         <v>0.22288261515601782</v>
       </c>
       <c r="K32" s="9">
-        <f>IFERROR(J32/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.1382060682753663</v>
+        <f t="shared" si="2"/>
+        <v>1.1343529123846561E-2</v>
       </c>
       <c r="L32" s="12">
-        <f>F32/(1-(F32*(1+H32)-F32)/(F32*(1+H32)))</f>
+        <f t="shared" si="11"/>
         <v>74.002499999999984</v>
       </c>
       <c r="M32" s="12">
-        <f>L32*E32</f>
+        <f t="shared" si="3"/>
         <v>7.4002499999999988E-18</v>
       </c>
       <c r="N32" s="12">
-        <f>F32/(1+I32-H32)</f>
+        <f t="shared" si="4"/>
         <v>42.252133946158892</v>
       </c>
       <c r="O32" s="12">
-        <f>L32-F32</f>
+        <f t="shared" si="5"/>
         <v>9.6524999999999892</v>
       </c>
       <c r="P32" s="12">
-        <f>0.5*(N32-F32)</f>
+        <f t="shared" si="6"/>
         <v>-11.048933026920551</v>
       </c>
       <c r="Q32" s="15">
-        <f>O32+P32</f>
+        <f t="shared" si="7"/>
         <v>-1.3964330269205618</v>
       </c>
       <c r="R32" s="12">
-        <f>MAX($Q$2:$Q$279)-Q32</f>
+        <f t="shared" si="8"/>
         <v>115.52887810810495</v>
       </c>
       <c r="S32" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R32)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.6558444639638962E-3</v>
       </c>
       <c r="T32" s="9">
-        <f>R32/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.80663411909010196</v>
       </c>
     </row>
-    <row r="33" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -4802,7 +4783,7 @@
         <v>20.82</v>
       </c>
       <c r="G33" s="1">
-        <f>E33*F33</f>
+        <f t="shared" si="0"/>
         <v>2.0820000000000002E-18</v>
       </c>
       <c r="H33" s="13">
@@ -4812,51 +4793,51 @@
         <v>0.7389</v>
       </c>
       <c r="J33" s="9">
-        <f>IFERROR(H33/I33,"")</f>
+        <f t="shared" si="1"/>
         <v>6.7668155366084726E-2</v>
       </c>
       <c r="K33" s="9">
-        <f>IFERROR(J33/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.1959978323328165E-2</v>
+        <f t="shared" si="2"/>
+        <v>3.4439460009693403E-3</v>
       </c>
       <c r="L33" s="12">
-        <f>F33/(1-(F33*(1+H33)-F33)/(F33*(1+H33)))</f>
+        <f t="shared" si="11"/>
         <v>21.861000000000001</v>
       </c>
       <c r="M33" s="12">
-        <f>L33*E33</f>
+        <f t="shared" si="3"/>
         <v>2.1860999999999999E-18</v>
       </c>
       <c r="N33" s="12">
-        <f>F33/(1+I33-H33)</f>
+        <f t="shared" si="4"/>
         <v>12.327550476641601</v>
       </c>
       <c r="O33" s="12">
-        <f>L33-F33</f>
+        <f t="shared" si="5"/>
         <v>1.0410000000000004</v>
       </c>
       <c r="P33" s="12">
-        <f>0.5*(N33-F33)</f>
+        <f t="shared" si="6"/>
         <v>-4.2462247616791995</v>
       </c>
       <c r="Q33" s="15">
-        <f>O33+P33</f>
+        <f t="shared" si="7"/>
         <v>-3.2052247616791991</v>
       </c>
       <c r="R33" s="12">
-        <f>MAX($Q$2:$Q$279)-Q33</f>
+        <f t="shared" si="8"/>
         <v>117.33766984286359</v>
       </c>
       <c r="S33" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R33)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.5224122938454567E-3</v>
       </c>
       <c r="T33" s="9">
-        <f>R33/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.81926328291024408</v>
       </c>
     </row>
-    <row r="34" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>40</v>
       </c>
@@ -4876,7 +4857,7 @@
         <v>13.04</v>
       </c>
       <c r="G34" s="1">
-        <f>E34*F34</f>
+        <f t="shared" si="0"/>
         <v>1.304E-18</v>
       </c>
       <c r="H34" s="13">
@@ -4887,51 +4868,51 @@
         <v>0.30159999999999998</v>
       </c>
       <c r="J34" s="9">
-        <f>IFERROR(H34/I34,"")</f>
+        <f t="shared" si="1"/>
         <v>0.17290198694895167</v>
       </c>
       <c r="K34" s="9">
-        <f>IFERROR(J34/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.10721385244195039</v>
+        <f t="shared" si="2"/>
+        <v>8.7997833440416531E-3</v>
       </c>
       <c r="L34" s="12">
-        <f>F34/(1-(F34*(1+H34)-F34)/(F34*(1+H34)))</f>
+        <f t="shared" si="11"/>
         <v>13.72</v>
       </c>
       <c r="M34" s="12">
-        <f>L34*E34</f>
+        <f t="shared" si="3"/>
         <v>1.3720000000000001E-18</v>
       </c>
       <c r="N34" s="12">
-        <f>F34/(1+I34-H34)</f>
+        <f t="shared" si="4"/>
         <v>10.436569040286594</v>
       </c>
       <c r="O34" s="12">
-        <f>L34-F34</f>
+        <f t="shared" si="5"/>
         <v>0.68000000000000149</v>
       </c>
       <c r="P34" s="12">
-        <f>0.5*(N34-F34)</f>
+        <f t="shared" si="6"/>
         <v>-1.3017154798567026</v>
       </c>
       <c r="Q34" s="15">
-        <f>O34+P34</f>
+        <f t="shared" si="7"/>
         <v>-0.62171547985670106</v>
       </c>
       <c r="R34" s="12">
-        <f>MAX($Q$2:$Q$279)-Q34</f>
+        <f t="shared" si="8"/>
         <v>114.75416056104109</v>
       </c>
       <c r="S34" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R34)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.7142809908671744E-3</v>
       </c>
       <c r="T34" s="9">
-        <f>R34/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.80122496411211674</v>
       </c>
     </row>
-    <row r="35" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>40</v>
       </c>
@@ -4951,7 +4932,7 @@
         <v>11.05</v>
       </c>
       <c r="G35" s="1">
-        <f>E35*F35</f>
+        <f t="shared" si="0"/>
         <v>1.1050000000000001E-18</v>
       </c>
       <c r="H35" s="13">
@@ -4961,51 +4942,51 @@
         <v>0.72170000000000001</v>
       </c>
       <c r="J35" s="9">
-        <f>IFERROR(H35/I35,"")</f>
+        <f t="shared" si="1"/>
         <v>6.9280864625190522E-2</v>
       </c>
       <c r="K35" s="9">
-        <f>IFERROR(J35/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.2959994434123842E-2</v>
+        <f t="shared" si="2"/>
+        <v>3.5260242484636906E-3</v>
       </c>
       <c r="L35" s="12">
-        <f>F35/(1-(F35*(1+H35)-F35)/(F35*(1+H35)))</f>
+        <f t="shared" si="11"/>
         <v>11.602500000000001</v>
       </c>
       <c r="M35" s="12">
-        <f>L35*E35</f>
+        <f t="shared" si="3"/>
         <v>1.16025E-18</v>
       </c>
       <c r="N35" s="12">
-        <f>F35/(1+I35-H35)</f>
+        <f t="shared" si="4"/>
         <v>6.6100376861877139</v>
       </c>
       <c r="O35" s="12">
-        <f>L35-F35</f>
+        <f t="shared" si="5"/>
         <v>0.55250000000000021</v>
       </c>
       <c r="P35" s="12">
-        <f>0.5*(N35-F35)</f>
+        <f t="shared" si="6"/>
         <v>-2.2199811569061434</v>
       </c>
       <c r="Q35" s="15">
-        <f>O35+P35</f>
+        <f t="shared" si="7"/>
         <v>-1.6674811569061432</v>
       </c>
       <c r="R35" s="12">
-        <f>MAX($Q$2:$Q$279)-Q35</f>
+        <f t="shared" si="8"/>
         <v>115.79992623809053</v>
       </c>
       <c r="S35" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R35)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.6355840844315312E-3</v>
+        <f t="shared" si="9"/>
+        <v>8.6355840844315329E-3</v>
       </c>
       <c r="T35" s="9">
-        <f>R35/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.80852660409594923</v>
       </c>
     </row>
-    <row r="36" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>74</v>
       </c>
@@ -5017,7 +4998,7 @@
       </c>
       <c r="D36" s="8">
         <f ca="1">TODAY()-20</f>
-        <v>45671</v>
+        <v>45672</v>
       </c>
       <c r="E36" s="2">
         <v>9.9999999999999998E-20</v>
@@ -5026,7 +5007,7 @@
         <v>2742.9</v>
       </c>
       <c r="G36" s="1">
-        <f>E36*F36</f>
+        <f t="shared" si="0"/>
         <v>2.7429000000000002E-16</v>
       </c>
       <c r="H36" s="13">
@@ -5036,51 +5017,51 @@
         <v>0.5</v>
       </c>
       <c r="J36" s="9">
-        <f>IFERROR(H36/I36,"")</f>
+        <f t="shared" si="1"/>
         <v>0.2</v>
       </c>
       <c r="K36" s="9">
-        <f>IFERROR(J36/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.12401691193242873</v>
+        <f t="shared" si="2"/>
+        <v>1.0178926800464982E-2</v>
       </c>
       <c r="L36" s="12">
-        <f>F36/(1-(F36*(1+H36)-F36)/(F36*(1+H36)))</f>
+        <f t="shared" si="11"/>
         <v>3017.1900000000005</v>
       </c>
       <c r="M36" s="12">
-        <f>L36*E36</f>
+        <f t="shared" si="3"/>
         <v>3.0171900000000003E-16</v>
       </c>
       <c r="N36" s="12">
-        <f>F36/(1+I36-H36)</f>
+        <f t="shared" si="4"/>
         <v>1959.214285714286</v>
       </c>
       <c r="O36" s="12">
-        <f>L36-F36</f>
+        <f t="shared" si="5"/>
         <v>274.29000000000042</v>
       </c>
       <c r="P36" s="12">
-        <f>0.5*(N36-F36)</f>
+        <f t="shared" si="6"/>
         <v>-391.84285714285704</v>
       </c>
       <c r="Q36" s="15">
-        <f>O36+P36</f>
+        <f t="shared" si="7"/>
         <v>-117.55285714285662</v>
       </c>
       <c r="R36" s="12">
-        <f>MAX($Q$2:$Q$279)-Q36</f>
+        <f t="shared" si="8"/>
         <v>231.68530222404101</v>
       </c>
       <c r="S36" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R36)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>4.316199562080957E-3</v>
       </c>
       <c r="T36" s="9">
-        <f>R36/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>1.6176498268314992</v>
       </c>
     </row>
-    <row r="37" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>38</v>
       </c>
@@ -5100,7 +5081,7 @@
         <v>86.6</v>
       </c>
       <c r="G37" s="1">
-        <f>E37*F37</f>
+        <f t="shared" si="0"/>
         <v>8.6599999999999986E-18</v>
       </c>
       <c r="H37" s="13">
@@ -5110,51 +5091,51 @@
         <v>0.17249999999999999</v>
       </c>
       <c r="J37" s="9">
-        <f>IFERROR(H37/I37,"")</f>
+        <f t="shared" si="1"/>
         <v>0.40579710144927544</v>
       </c>
       <c r="K37" s="9">
-        <f>IFERROR(J37/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.25162851696434818</v>
+        <f t="shared" si="2"/>
+        <v>2.0652894957465185E-2</v>
       </c>
       <c r="L37" s="12">
-        <f>F37/(1-(F37*(1+H37)-F37)/(F37*(1+H37)))</f>
+        <f t="shared" si="11"/>
         <v>92.662000000000006</v>
       </c>
       <c r="M37" s="12">
-        <f>L37*E37</f>
+        <f t="shared" si="3"/>
         <v>9.2662000000000008E-18</v>
       </c>
       <c r="N37" s="12">
-        <f>F37/(1+I37-H37)</f>
+        <f t="shared" si="4"/>
         <v>78.548752834467123</v>
       </c>
       <c r="O37" s="12">
-        <f>L37-F37</f>
+        <f t="shared" si="5"/>
         <v>6.0620000000000118</v>
       </c>
       <c r="P37" s="12">
-        <f>0.5*(N37-F37)</f>
+        <f t="shared" si="6"/>
         <v>-4.0256235827664355</v>
       </c>
       <c r="Q37" s="15">
-        <f>O37+P37</f>
+        <f t="shared" si="7"/>
         <v>2.0363764172335763</v>
       </c>
       <c r="R37" s="12">
-        <f>MAX($Q$2:$Q$279)-Q37</f>
+        <f t="shared" si="8"/>
         <v>112.0960686639508</v>
       </c>
       <c r="S37" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R37)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.9209194570227784E-3</v>
+        <f t="shared" si="9"/>
+        <v>8.9209194570227766E-3</v>
       </c>
       <c r="T37" s="9">
-        <f>R37/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.78266590207514586</v>
       </c>
     </row>
-    <row r="38" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>71</v>
       </c>
@@ -5174,7 +5155,7 @@
         <v>56</v>
       </c>
       <c r="G38" s="1">
-        <f>E38*F38</f>
+        <f t="shared" si="0"/>
         <v>5.5999999999999995E-18</v>
       </c>
       <c r="H38" s="13">
@@ -5184,51 +5165,51 @@
         <v>0.19</v>
       </c>
       <c r="J38" s="9">
-        <f>IFERROR(H38/I38,"")</f>
+        <f t="shared" si="1"/>
         <v>0.36842105263157898</v>
       </c>
       <c r="K38" s="9">
-        <f>IFERROR(J38/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.22845220619131607</v>
+        <f t="shared" si="2"/>
+        <v>1.8750654632435495E-2</v>
       </c>
       <c r="L38" s="12">
-        <f>F38/(1-(F38*(1+H38)-F38)/(F38*(1+H38)))</f>
+        <f t="shared" si="11"/>
         <v>59.92</v>
       </c>
       <c r="M38" s="12">
-        <f>L38*E38</f>
+        <f t="shared" si="3"/>
         <v>5.9920000000000002E-18</v>
       </c>
       <c r="N38" s="12">
-        <f>F38/(1+I38-H38)</f>
+        <f t="shared" si="4"/>
         <v>50.000000000000007</v>
       </c>
       <c r="O38" s="12">
-        <f>L38-F38</f>
+        <f t="shared" si="5"/>
         <v>3.9200000000000017</v>
       </c>
       <c r="P38" s="12">
-        <f>0.5*(N38-F38)</f>
+        <f t="shared" si="6"/>
         <v>-2.9999999999999964</v>
       </c>
       <c r="Q38" s="15">
-        <f>O38+P38</f>
+        <f t="shared" si="7"/>
         <v>0.92000000000000526</v>
       </c>
       <c r="R38" s="12">
-        <f>MAX($Q$2:$Q$279)-Q38</f>
+        <f t="shared" si="8"/>
         <v>113.21244508118438</v>
       </c>
       <c r="S38" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R38)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.832951176727102E-3</v>
       </c>
       <c r="T38" s="9">
-        <f>R38/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.79046055327088882</v>
       </c>
     </row>
-    <row r="39" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>74</v>
       </c>
@@ -5248,7 +5229,7 @@
         <v>20.399999999999999</v>
       </c>
       <c r="G39" s="1">
-        <f>E39*F39</f>
+        <f t="shared" si="0"/>
         <v>2.0399999999999999E-18</v>
       </c>
       <c r="H39" s="13">
@@ -5258,50 +5239,50 @@
         <v>0.15</v>
       </c>
       <c r="J39" s="9">
-        <f>IFERROR(H39/I39,"")</f>
+        <f t="shared" si="1"/>
         <v>0.66666666666666674</v>
       </c>
       <c r="K39" s="9">
-        <f>IFERROR(J39/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.41338970644142908</v>
+        <f t="shared" si="2"/>
+        <v>3.3929756001549939E-2</v>
       </c>
       <c r="L39" s="12">
         <v>21.2</v>
       </c>
       <c r="M39" s="12">
-        <f>L39*E39</f>
+        <f t="shared" si="3"/>
         <v>2.1199999999999999E-18</v>
       </c>
       <c r="N39" s="12">
-        <f>F39/(1+I39-H39)</f>
+        <f t="shared" si="4"/>
         <v>19.428571428571431</v>
       </c>
       <c r="O39" s="12">
-        <f>L39-F39</f>
+        <f t="shared" si="5"/>
         <v>0.80000000000000071</v>
       </c>
       <c r="P39" s="12">
-        <f>0.5*(N39-F39)</f>
+        <f t="shared" si="6"/>
         <v>-0.48571428571428399</v>
       </c>
       <c r="Q39" s="15">
-        <f>O39+P39</f>
+        <f t="shared" si="7"/>
         <v>0.31428571428571672</v>
       </c>
       <c r="R39" s="12">
-        <f>MAX($Q$2:$Q$279)-Q39</f>
+        <f t="shared" si="8"/>
         <v>113.81815936689867</v>
       </c>
       <c r="S39" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R39)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.7859442250902055E-3</v>
       </c>
       <c r="T39" s="9">
-        <f>R39/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.79468971066667204</v>
       </c>
     </row>
-    <row r="40" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>39</v>
       </c>
@@ -5321,7 +5302,7 @@
         <v>47.42</v>
       </c>
       <c r="G40" s="1">
-        <f>E40*F40</f>
+        <f t="shared" si="0"/>
         <v>4.7419999999999999E-18</v>
       </c>
       <c r="H40" s="13">
@@ -5331,51 +5312,51 @@
         <v>0.4</v>
       </c>
       <c r="J40" s="9">
-        <f>IFERROR(H40/I40,"")</f>
+        <f t="shared" si="1"/>
         <v>0.17500000000000002</v>
       </c>
       <c r="K40" s="9">
-        <f>IFERROR(J40/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.10851479794087514</v>
+        <f t="shared" si="2"/>
+        <v>8.90656095040686E-3</v>
       </c>
       <c r="L40" s="12">
-        <f>F40/(1-(F40*(1+H40)-F40)/(F40*(1+H40)))</f>
+        <f t="shared" ref="L40:L46" si="12">F40/(1-(F40*(1+H40)-F40)/(F40*(1+H40)))</f>
         <v>50.739400000000003</v>
       </c>
       <c r="M40" s="12">
-        <f>L40*E40</f>
+        <f t="shared" si="3"/>
         <v>5.0739400000000001E-18</v>
       </c>
       <c r="N40" s="12">
-        <f>F40/(1+I40-H40)</f>
+        <f t="shared" si="4"/>
         <v>35.654135338345867</v>
       </c>
       <c r="O40" s="12">
-        <f>L40-F40</f>
+        <f t="shared" si="5"/>
         <v>3.3194000000000017</v>
       </c>
       <c r="P40" s="12">
-        <f>0.5*(N40-F40)</f>
+        <f t="shared" si="6"/>
         <v>-5.8829323308270673</v>
       </c>
       <c r="Q40" s="15">
-        <f>O40+P40</f>
+        <f t="shared" si="7"/>
         <v>-2.5635323308270657</v>
       </c>
       <c r="R40" s="12">
-        <f>MAX($Q$2:$Q$279)-Q40</f>
+        <f t="shared" si="8"/>
         <v>116.69597741201144</v>
       </c>
       <c r="S40" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R40)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.5692756697976005E-3</v>
+        <f t="shared" si="9"/>
+        <v>8.5692756697975988E-3</v>
       </c>
       <c r="T40" s="9">
-        <f>R40/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.81478292252621221</v>
       </c>
     </row>
-    <row r="41" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -5395,7 +5376,7 @@
         <v>41.8</v>
       </c>
       <c r="G41" s="1">
-        <f>E41*F41</f>
+        <f t="shared" si="0"/>
         <v>4.1799999999999993E-18</v>
       </c>
       <c r="H41" s="13">
@@ -5405,51 +5386,51 @@
         <v>0.4</v>
       </c>
       <c r="J41" s="9">
-        <f>IFERROR(H41/I41,"")</f>
+        <f t="shared" si="1"/>
         <v>0.17500000000000002</v>
       </c>
       <c r="K41" s="9">
-        <f>IFERROR(J41/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.10851479794087514</v>
+        <f t="shared" si="2"/>
+        <v>8.90656095040686E-3</v>
       </c>
       <c r="L41" s="12">
-        <f>F41/(1-(F41*(1+H41)-F41)/(F41*(1+H41)))</f>
+        <f t="shared" si="12"/>
         <v>44.725999999999999</v>
       </c>
       <c r="M41" s="12">
-        <f>L41*E41</f>
+        <f t="shared" si="3"/>
         <v>4.4725999999999996E-18</v>
       </c>
       <c r="N41" s="12">
-        <f>F41/(1+I41-H41)</f>
+        <f t="shared" si="4"/>
         <v>31.428571428571431</v>
       </c>
       <c r="O41" s="12">
-        <f>L41-F41</f>
+        <f t="shared" si="5"/>
         <v>2.9260000000000019</v>
       </c>
       <c r="P41" s="12">
-        <f>0.5*(N41-F41)</f>
+        <f t="shared" si="6"/>
         <v>-5.1857142857142833</v>
       </c>
       <c r="Q41" s="15">
-        <f>O41+P41</f>
+        <f t="shared" si="7"/>
         <v>-2.2597142857142813</v>
       </c>
       <c r="R41" s="12">
-        <f>MAX($Q$2:$Q$279)-Q41</f>
+        <f t="shared" si="8"/>
         <v>116.39215936689867</v>
       </c>
       <c r="S41" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R41)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.5916440200042785E-3</v>
+        <f t="shared" si="9"/>
+        <v>8.5916440200042802E-3</v>
       </c>
       <c r="T41" s="9">
-        <f>R41/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.81266163471318675</v>
       </c>
     </row>
-    <row r="42" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>74</v>
       </c>
@@ -5469,7 +5450,7 @@
         <v>153.7552</v>
       </c>
       <c r="G42" s="1">
-        <f>E42*F42</f>
+        <f t="shared" si="0"/>
         <v>1.5375519999999999E-17</v>
       </c>
       <c r="H42" s="13">
@@ -5479,51 +5460,51 @@
         <v>0.19</v>
       </c>
       <c r="J42" s="9">
-        <f>IFERROR(H42/I42,"")</f>
+        <f t="shared" si="1"/>
         <v>0.36842105263157898</v>
       </c>
       <c r="K42" s="9">
-        <f>IFERROR(J42/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.22845220619131607</v>
+        <f t="shared" si="2"/>
+        <v>1.8750654632435495E-2</v>
       </c>
       <c r="L42" s="12">
-        <f>F42/(1-(F42*(1+H42)-F42)/(F42*(1+H42)))</f>
+        <f t="shared" si="12"/>
         <v>164.51806400000001</v>
       </c>
       <c r="M42" s="12">
-        <f>L42*E42</f>
+        <f t="shared" si="3"/>
         <v>1.6451806399999999E-17</v>
       </c>
       <c r="N42" s="12">
-        <f>F42/(1+I42-H42)</f>
+        <f t="shared" si="4"/>
         <v>137.28142857142859</v>
       </c>
       <c r="O42" s="12">
-        <f>L42-F42</f>
+        <f t="shared" si="5"/>
         <v>10.762864000000008</v>
       </c>
       <c r="P42" s="12">
-        <f>0.5*(N42-F42)</f>
+        <f t="shared" si="6"/>
         <v>-8.2368857142857053</v>
       </c>
       <c r="Q42" s="15">
-        <f>O42+P42</f>
+        <f t="shared" si="7"/>
         <v>2.5259782857143023</v>
       </c>
       <c r="R42" s="12">
-        <f>MAX($Q$2:$Q$279)-Q42</f>
+        <f t="shared" si="8"/>
         <v>111.60646679547008</v>
       </c>
       <c r="S42" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R42)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.9600542756415654E-3</v>
       </c>
       <c r="T42" s="9">
-        <f>R42/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.77924745312667376</v>
       </c>
     </row>
-    <row r="43" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>87</v>
       </c>
@@ -5543,7 +5524,7 @@
         <v>133.53</v>
       </c>
       <c r="G43" s="1">
-        <f>E43*F43</f>
+        <f t="shared" si="0"/>
         <v>1.3353E-17</v>
       </c>
       <c r="H43" s="13">
@@ -5553,51 +5534,51 @@
         <v>0.2</v>
       </c>
       <c r="J43" s="9">
-        <f>IFERROR(H43/I43,"")</f>
+        <f t="shared" si="1"/>
         <v>0.35000000000000003</v>
       </c>
       <c r="K43" s="9">
-        <f>IFERROR(J43/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.21702959588175028</v>
+        <f t="shared" si="2"/>
+        <v>1.781312190081372E-2</v>
       </c>
       <c r="L43" s="12">
-        <f>F43/(1-(F43*(1+H43)-F43)/(F43*(1+H43)))</f>
+        <f t="shared" si="12"/>
         <v>142.87710000000001</v>
       </c>
       <c r="M43" s="12">
-        <f>L43*E43</f>
+        <f t="shared" si="3"/>
         <v>1.428771E-17</v>
       </c>
       <c r="N43" s="12">
-        <f>F43/(1+I43-H43)</f>
+        <f t="shared" si="4"/>
         <v>118.16814159292036</v>
       </c>
       <c r="O43" s="12">
-        <f>L43-F43</f>
+        <f t="shared" si="5"/>
         <v>9.3471000000000117</v>
       </c>
       <c r="P43" s="12">
-        <f>0.5*(N43-F43)</f>
+        <f t="shared" si="6"/>
         <v>-7.6809292035398187</v>
       </c>
       <c r="Q43" s="15">
-        <f>O43+P43</f>
+        <f t="shared" si="7"/>
         <v>1.6661707964601931</v>
       </c>
       <c r="R43" s="12">
-        <f>MAX($Q$2:$Q$279)-Q43</f>
+        <f t="shared" si="8"/>
         <v>112.46627428472419</v>
       </c>
       <c r="S43" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R43)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.8915544358512261E-3</v>
       </c>
       <c r="T43" s="9">
-        <f>R43/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.78525071454528272</v>
       </c>
     </row>
-    <row r="44" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>40</v>
       </c>
@@ -5617,7 +5598,7 @@
         <v>26.63</v>
       </c>
       <c r="G44" s="1">
-        <f>E44*F44</f>
+        <f t="shared" si="0"/>
         <v>2.663E-18</v>
       </c>
       <c r="H44" s="13">
@@ -5627,51 +5608,51 @@
         <v>0.2</v>
       </c>
       <c r="J44" s="9">
-        <f>IFERROR(H44/I44,"")</f>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
       <c r="K44" s="9">
-        <f>IFERROR(J44/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.3100422798310718</v>
+        <f t="shared" si="2"/>
+        <v>2.5447317001162453E-2</v>
       </c>
       <c r="L44" s="12">
-        <f>F44/(1-(F44*(1+H44)-F44)/(F44*(1+H44)))</f>
+        <f t="shared" si="12"/>
         <v>29.293000000000003</v>
       </c>
       <c r="M44" s="12">
-        <f>L44*E44</f>
+        <f t="shared" si="3"/>
         <v>2.9293000000000003E-18</v>
       </c>
       <c r="N44" s="12">
-        <f>F44/(1+I44-H44)</f>
+        <f t="shared" si="4"/>
         <v>24.209090909090911</v>
       </c>
       <c r="O44" s="12">
-        <f>L44-F44</f>
+        <f t="shared" si="5"/>
         <v>2.6630000000000038</v>
       </c>
       <c r="P44" s="12">
-        <f>0.5*(N44-F44)</f>
+        <f t="shared" si="6"/>
         <v>-1.2104545454545441</v>
       </c>
       <c r="Q44" s="15">
-        <f>O44+P44</f>
+        <f t="shared" si="7"/>
         <v>1.4525454545454597</v>
       </c>
       <c r="R44" s="12">
-        <f>MAX($Q$2:$Q$279)-Q44</f>
+        <f t="shared" si="8"/>
         <v>112.67989962663893</v>
       </c>
       <c r="S44" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R44)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.8746972912956655E-3</v>
+        <f t="shared" si="9"/>
+        <v>8.8746972912956672E-3</v>
       </c>
       <c r="T44" s="9">
-        <f>R44/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.78674226793273505</v>
       </c>
     </row>
-    <row r="45" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>38</v>
       </c>
@@ -5691,7 +5672,7 @@
         <v>19.309999999999999</v>
       </c>
       <c r="G45" s="1">
-        <f>E45*F45</f>
+        <f t="shared" si="0"/>
         <v>1.931E-18</v>
       </c>
       <c r="H45" s="13">
@@ -5701,51 +5682,51 @@
         <v>0.2</v>
       </c>
       <c r="J45" s="9">
-        <f>IFERROR(H45/I45,"")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="K45" s="9">
-        <f>IFERROR(J45/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.6200845596621436</v>
+        <f t="shared" si="2"/>
+        <v>5.0894634002324905E-2</v>
       </c>
       <c r="L45" s="12">
-        <f>F45/(1-(F45*(1+H45)-F45)/(F45*(1+H45)))</f>
+        <f t="shared" si="12"/>
         <v>23.171999999999997</v>
       </c>
       <c r="M45" s="12">
-        <f>L45*E45</f>
+        <f t="shared" si="3"/>
         <v>2.3171999999999995E-18</v>
       </c>
       <c r="N45" s="12">
-        <f>F45/(1+I45-H45)</f>
+        <f t="shared" si="4"/>
         <v>19.309999999999999</v>
       </c>
       <c r="O45" s="12">
-        <f>L45-F45</f>
+        <f t="shared" si="5"/>
         <v>3.8619999999999983</v>
       </c>
       <c r="P45" s="12">
-        <f>0.5*(N45-F45)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q45" s="15">
-        <f>O45+P45</f>
+        <f t="shared" si="7"/>
         <v>3.8619999999999983</v>
       </c>
       <c r="R45" s="12">
-        <f>MAX($Q$2:$Q$279)-Q45</f>
+        <f t="shared" si="8"/>
         <v>110.27044508118439</v>
       </c>
       <c r="S45" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R45)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>9.0686130745529347E-3</v>
+        <f t="shared" si="9"/>
+        <v>9.0686130745529329E-3</v>
       </c>
       <c r="T45" s="9">
-        <f>R45/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.76991921661787932</v>
       </c>
     </row>
-    <row r="46" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>96</v>
       </c>
@@ -5765,7 +5746,7 @@
         <v>323.75</v>
       </c>
       <c r="G46" s="1">
-        <f>E46*F46</f>
+        <f t="shared" si="0"/>
         <v>3.2375000000000002E-17</v>
       </c>
       <c r="H46" s="13">
@@ -5775,84 +5756,58 @@
         <v>0.2</v>
       </c>
       <c r="J46" s="9">
-        <f>IFERROR(H46/I46,"")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="K46" s="9">
-        <f>IFERROR(J46/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>0.6200845596621436</v>
+        <f t="shared" si="2"/>
+        <v>5.0894634002324905E-2</v>
       </c>
       <c r="L46" s="12">
-        <f>F46/(1-(F46*(1+H46)-F46)/(F46*(1+H46)))</f>
+        <f t="shared" si="12"/>
         <v>388.5</v>
       </c>
       <c r="M46" s="12">
-        <f>L46*E46</f>
+        <f t="shared" si="3"/>
         <v>3.8849999999999999E-17</v>
       </c>
       <c r="N46" s="12">
-        <f>F46/(1+I46-H46)</f>
+        <f t="shared" si="4"/>
         <v>323.75</v>
       </c>
       <c r="O46" s="12">
-        <f>L46-F46</f>
+        <f t="shared" si="5"/>
         <v>64.75</v>
       </c>
       <c r="P46" s="12">
-        <f>0.5*(N46-F46)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q46" s="15">
-        <f>O46+P46</f>
+        <f t="shared" si="7"/>
         <v>64.75</v>
       </c>
       <c r="R46" s="12">
-        <f>MAX($Q$2:$Q$279)-Q46</f>
+        <f t="shared" si="8"/>
         <v>49.382445081184386</v>
       </c>
       <c r="S46" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R46)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>2.0250111114506527E-2</v>
+        <f t="shared" si="9"/>
+        <v>2.0250111114506524E-2</v>
       </c>
       <c r="T46" s="9">
-        <f>R46/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.34479314383458876</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="D47" s="46"/>
-    </row>
-    <row r="49" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D49" s="8">
-        <f ca="1">TODAY()-90</f>
-        <v>45601</v>
-      </c>
-    </row>
-    <row r="50" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D50" s="8">
-        <f>D23</f>
-        <v>45511</v>
-      </c>
+      <c r="D47" s="44"/>
     </row>
     <row r="51" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D51" s="46" t="b">
-        <f ca="1">D50-D49&lt;7/4</f>
-        <v>1</v>
-      </c>
+      <c r="D51" s="44"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T46" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="AMAT"/>
-        <filter val="MA"/>
-        <filter val="MAXN"/>
-      </filters>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T46">
-      <sortCondition descending="1" ref="E1:E45"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:T46" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="S2:S46">
     <cfRule type="iconSet" priority="11">
       <iconSet iconSet="3Symbols">
@@ -5902,7 +5857,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD6C5064-D029-4982-9C03-6BDB75C18181}">
-  <dimension ref="B2:J16"/>
+  <dimension ref="B2:U42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.140625" bestFit="1" customWidth="1"/>
@@ -5916,7 +5871,7 @@
     <col min="11" max="11" width="7.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>124</v>
       </c>
@@ -5941,8 +5896,32 @@
       <c r="J2" s="29">
         <v>0.24129999999999999</v>
       </c>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="M2" t="s">
+        <v>124</v>
+      </c>
+      <c r="N2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O2" t="s">
+        <v>122</v>
+      </c>
+      <c r="P2" s="29">
+        <v>0.44950000000000001</v>
+      </c>
+      <c r="R2" t="s">
+        <v>124</v>
+      </c>
+      <c r="S2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T2" t="s">
+        <v>122</v>
+      </c>
+      <c r="U2" s="29">
+        <v>0.54500000000000004</v>
+      </c>
+    </row>
+    <row r="3" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>124</v>
       </c>
@@ -5967,8 +5946,32 @@
       <c r="J3" s="29">
         <v>0.30709999999999998</v>
       </c>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="M3" t="s">
+        <v>124</v>
+      </c>
+      <c r="N3" t="s">
+        <v>125</v>
+      </c>
+      <c r="O3" t="s">
+        <v>126</v>
+      </c>
+      <c r="P3" s="29">
+        <v>0.46850000000000003</v>
+      </c>
+      <c r="R3" t="s">
+        <v>124</v>
+      </c>
+      <c r="S3" t="s">
+        <v>125</v>
+      </c>
+      <c r="T3" t="s">
+        <v>126</v>
+      </c>
+      <c r="U3" s="29">
+        <v>0.3967</v>
+      </c>
+    </row>
+    <row r="5" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B5" s="39" t="s">
         <v>82</v>
       </c>
@@ -5993,8 +5996,32 @@
       <c r="J5" s="39" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="M5" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="N5" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="O5" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="P5" s="39" t="s">
+        <v>127</v>
+      </c>
+      <c r="R5" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="S5" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="T5" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="U5" s="39" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="6" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B6" s="33" t="s">
         <v>94</v>
       </c>
@@ -6021,8 +6048,34 @@
         <f>I6-H6</f>
         <v>1.0699999999999987E-2</v>
       </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="M6" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="N6" s="34">
+        <v>4.1399999999999999E-2</v>
+      </c>
+      <c r="O6" s="34">
+        <v>0.59519999999999995</v>
+      </c>
+      <c r="P6" s="34">
+        <f>O6-N6</f>
+        <v>0.55379999999999996</v>
+      </c>
+      <c r="R6" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="S6" s="34">
+        <v>4.1399999999999999E-2</v>
+      </c>
+      <c r="T6" s="34">
+        <v>0</v>
+      </c>
+      <c r="U6" s="34">
+        <f>T6-S6</f>
+        <v>-4.1399999999999999E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B7" s="33" t="s">
         <v>50</v>
       </c>
@@ -6049,8 +6102,34 @@
         <f t="shared" ref="J7:J16" si="1">I7-H7</f>
         <v>0.1207</v>
       </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="M7" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="N7" s="34">
+        <v>5.6899999999999999E-2</v>
+      </c>
+      <c r="O7" s="34">
+        <v>0</v>
+      </c>
+      <c r="P7" s="34">
+        <f t="shared" ref="P7:P42" si="2">O7-N7</f>
+        <v>-5.6899999999999999E-2</v>
+      </c>
+      <c r="R7" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="S7" s="34">
+        <v>5.6899999999999999E-2</v>
+      </c>
+      <c r="T7" s="34">
+        <v>0</v>
+      </c>
+      <c r="U7" s="34">
+        <f t="shared" ref="U7:U42" si="3">T7-S7</f>
+        <v>-5.6899999999999999E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B8" s="35" t="s">
         <v>27</v>
       </c>
@@ -6077,8 +6156,34 @@
         <f t="shared" si="1"/>
         <v>-0.16089999999999999</v>
       </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="M8" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="N8" s="34">
+        <v>0.1242</v>
+      </c>
+      <c r="O8" s="34">
+        <v>0</v>
+      </c>
+      <c r="P8" s="34">
+        <f t="shared" si="2"/>
+        <v>-0.1242</v>
+      </c>
+      <c r="R8" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="S8" s="34">
+        <v>0.1242</v>
+      </c>
+      <c r="T8" s="34">
+        <v>0</v>
+      </c>
+      <c r="U8" s="34">
+        <f t="shared" si="3"/>
+        <v>-0.1242</v>
+      </c>
+    </row>
+    <row r="9" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B9" s="37" t="s">
         <v>103</v>
       </c>
@@ -6105,8 +6210,34 @@
         <f t="shared" si="1"/>
         <v>9.1699999999999976E-2</v>
       </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="M9" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="N9" s="34">
+        <v>5.5199999999999999E-2</v>
+      </c>
+      <c r="O9" s="34">
+        <v>0</v>
+      </c>
+      <c r="P9" s="34">
+        <f t="shared" si="2"/>
+        <v>-5.5199999999999999E-2</v>
+      </c>
+      <c r="R9" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="S9" s="34">
+        <v>5.5199999999999999E-2</v>
+      </c>
+      <c r="T9" s="34">
+        <v>0</v>
+      </c>
+      <c r="U9" s="34">
+        <f t="shared" si="3"/>
+        <v>-5.5199999999999999E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B10" s="35" t="s">
         <v>46</v>
       </c>
@@ -6133,8 +6264,34 @@
         <f t="shared" si="1"/>
         <v>-0.2772</v>
       </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="M10" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="N10" s="34">
+        <v>4.8300000000000003E-2</v>
+      </c>
+      <c r="O10" s="34">
+        <v>0</v>
+      </c>
+      <c r="P10" s="34">
+        <f t="shared" si="2"/>
+        <v>-4.8300000000000003E-2</v>
+      </c>
+      <c r="R10" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="S10" s="34">
+        <v>4.8300000000000003E-2</v>
+      </c>
+      <c r="T10" s="34">
+        <v>0</v>
+      </c>
+      <c r="U10" s="34">
+        <f t="shared" si="3"/>
+        <v>-4.8300000000000003E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B11" s="33" t="s">
         <v>32</v>
       </c>
@@ -6161,8 +6318,34 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="M11" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="N11" s="34">
+        <v>9.6600000000000005E-2</v>
+      </c>
+      <c r="O11" s="34">
+        <v>0</v>
+      </c>
+      <c r="P11" s="34">
+        <f t="shared" si="2"/>
+        <v>-9.6600000000000005E-2</v>
+      </c>
+      <c r="R11" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="S11" s="34">
+        <v>9.6600000000000005E-2</v>
+      </c>
+      <c r="T11" s="34">
+        <v>0</v>
+      </c>
+      <c r="U11" s="34">
+        <f t="shared" si="3"/>
+        <v>-9.6600000000000005E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B12" s="33" t="s">
         <v>48</v>
       </c>
@@ -6189,8 +6372,34 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="M12" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="N12" s="34">
+        <v>0.1076</v>
+      </c>
+      <c r="O12" s="34">
+        <v>0</v>
+      </c>
+      <c r="P12" s="34">
+        <f t="shared" si="2"/>
+        <v>-0.1076</v>
+      </c>
+      <c r="R12" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="S12" s="34">
+        <v>0.1076</v>
+      </c>
+      <c r="T12" s="34">
+        <v>0</v>
+      </c>
+      <c r="U12" s="34">
+        <f t="shared" si="3"/>
+        <v>-0.1076</v>
+      </c>
+    </row>
+    <row r="13" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B13" s="33" t="s">
         <v>53</v>
       </c>
@@ -6217,8 +6426,34 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="M13" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="N13" s="34">
+        <v>6.93E-2</v>
+      </c>
+      <c r="O13" s="34">
+        <v>0</v>
+      </c>
+      <c r="P13" s="34">
+        <f t="shared" si="2"/>
+        <v>-6.93E-2</v>
+      </c>
+      <c r="R13" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="S13" s="34">
+        <v>6.93E-2</v>
+      </c>
+      <c r="T13" s="34">
+        <v>0</v>
+      </c>
+      <c r="U13" s="34">
+        <f t="shared" si="3"/>
+        <v>-6.93E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B14" s="33" t="s">
         <v>44</v>
       </c>
@@ -6245,8 +6480,34 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="M14" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="N14" s="34">
+        <v>1.38E-2</v>
+      </c>
+      <c r="O14" s="34">
+        <v>0</v>
+      </c>
+      <c r="P14" s="34">
+        <f t="shared" si="2"/>
+        <v>-1.38E-2</v>
+      </c>
+      <c r="R14" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="S14" s="34">
+        <v>1.38E-2</v>
+      </c>
+      <c r="T14" s="34">
+        <v>0</v>
+      </c>
+      <c r="U14" s="34">
+        <f t="shared" si="3"/>
+        <v>-1.38E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B15" s="37" t="s">
         <v>91</v>
       </c>
@@ -6273,8 +6534,34 @@
         <f t="shared" si="1"/>
         <v>9.6800000000000011E-2</v>
       </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="M15" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="N15" s="34">
+        <v>1.5100000000000001E-2</v>
+      </c>
+      <c r="O15" s="34">
+        <v>0</v>
+      </c>
+      <c r="P15" s="34">
+        <f t="shared" si="2"/>
+        <v>-1.5100000000000001E-2</v>
+      </c>
+      <c r="R15" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="S15" s="34">
+        <v>1.5100000000000001E-2</v>
+      </c>
+      <c r="T15" s="34">
+        <v>0</v>
+      </c>
+      <c r="U15" s="34">
+        <f t="shared" si="3"/>
+        <v>-1.5100000000000001E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B16" s="37" t="s">
         <v>92</v>
       </c>
@@ -6300,6 +6587,760 @@
       <c r="J16" s="38">
         <f t="shared" si="1"/>
         <v>0.1183</v>
+      </c>
+      <c r="M16" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="N16" s="34">
+        <v>4.6899999999999997E-2</v>
+      </c>
+      <c r="O16" s="34">
+        <v>0</v>
+      </c>
+      <c r="P16" s="34">
+        <f t="shared" si="2"/>
+        <v>-4.6899999999999997E-2</v>
+      </c>
+      <c r="R16" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="S16" s="34">
+        <v>4.6899999999999997E-2</v>
+      </c>
+      <c r="T16" s="34">
+        <v>0</v>
+      </c>
+      <c r="U16" s="34">
+        <f t="shared" si="3"/>
+        <v>-4.6899999999999997E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="13:21" x14ac:dyDescent="0.25">
+      <c r="M17" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="N17" s="34">
+        <v>6.2E-2</v>
+      </c>
+      <c r="O17" s="34">
+        <v>0</v>
+      </c>
+      <c r="P17" s="34">
+        <f t="shared" si="2"/>
+        <v>-6.2E-2</v>
+      </c>
+      <c r="R17" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="S17" s="34">
+        <v>6.2E-2</v>
+      </c>
+      <c r="T17" s="34">
+        <v>0</v>
+      </c>
+      <c r="U17" s="34">
+        <f t="shared" si="3"/>
+        <v>-6.2E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="13:21" x14ac:dyDescent="0.25">
+      <c r="M18" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="N18" s="34">
+        <v>3.5900000000000001E-2</v>
+      </c>
+      <c r="O18" s="34">
+        <v>0</v>
+      </c>
+      <c r="P18" s="34">
+        <f t="shared" si="2"/>
+        <v>-3.5900000000000001E-2</v>
+      </c>
+      <c r="R18" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="S18" s="34">
+        <v>3.5900000000000001E-2</v>
+      </c>
+      <c r="T18" s="34">
+        <v>0</v>
+      </c>
+      <c r="U18" s="34">
+        <f t="shared" si="3"/>
+        <v>-3.5900000000000001E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="13:21" x14ac:dyDescent="0.25">
+      <c r="M19" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="N19" s="34">
+        <v>5.91E-2</v>
+      </c>
+      <c r="O19" s="34">
+        <v>0</v>
+      </c>
+      <c r="P19" s="34">
+        <f t="shared" si="2"/>
+        <v>-5.91E-2</v>
+      </c>
+      <c r="R19" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="S19" s="34">
+        <v>5.91E-2</v>
+      </c>
+      <c r="T19" s="34">
+        <v>0</v>
+      </c>
+      <c r="U19" s="34">
+        <f t="shared" si="3"/>
+        <v>-5.91E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="13:21" x14ac:dyDescent="0.25">
+      <c r="M20" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="N20" s="34">
+        <v>7.8200000000000006E-2</v>
+      </c>
+      <c r="O20" s="34">
+        <v>0</v>
+      </c>
+      <c r="P20" s="34">
+        <f t="shared" si="2"/>
+        <v>-7.8200000000000006E-2</v>
+      </c>
+      <c r="R20" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="S20" s="34">
+        <v>7.8200000000000006E-2</v>
+      </c>
+      <c r="T20" s="34">
+        <v>0</v>
+      </c>
+      <c r="U20" s="34">
+        <f t="shared" si="3"/>
+        <v>-7.8200000000000006E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="13:21" x14ac:dyDescent="0.25">
+      <c r="M21" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="N21" s="34">
+        <v>8.9599999999999999E-2</v>
+      </c>
+      <c r="O21" s="34">
+        <v>0</v>
+      </c>
+      <c r="P21" s="34">
+        <f t="shared" si="2"/>
+        <v>-8.9599999999999999E-2</v>
+      </c>
+      <c r="R21" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="S21" s="34">
+        <v>8.9599999999999999E-2</v>
+      </c>
+      <c r="T21" s="34">
+        <v>0</v>
+      </c>
+      <c r="U21" s="34">
+        <f t="shared" si="3"/>
+        <v>-8.9599999999999999E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="13:21" x14ac:dyDescent="0.25">
+      <c r="M22" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="N22" s="34">
+        <v>0</v>
+      </c>
+      <c r="O22" s="34">
+        <v>0.1867</v>
+      </c>
+      <c r="P22" s="34">
+        <f t="shared" si="2"/>
+        <v>0.1867</v>
+      </c>
+      <c r="R22" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="S22" s="34">
+        <v>0</v>
+      </c>
+      <c r="T22" s="34">
+        <v>0</v>
+      </c>
+      <c r="U22" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="13:21" x14ac:dyDescent="0.25">
+      <c r="M23" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="N23" s="34">
+        <v>0</v>
+      </c>
+      <c r="O23" s="34">
+        <v>0.21809999999999999</v>
+      </c>
+      <c r="P23" s="34">
+        <f t="shared" si="2"/>
+        <v>0.21809999999999999</v>
+      </c>
+      <c r="R23" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="S23" s="34">
+        <v>0</v>
+      </c>
+      <c r="T23" s="34">
+        <v>0</v>
+      </c>
+      <c r="U23" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="13:21" x14ac:dyDescent="0.25">
+      <c r="M24" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="N24" s="34">
+        <v>0</v>
+      </c>
+      <c r="O24" s="34">
+        <v>0</v>
+      </c>
+      <c r="P24" s="34">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R24" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="S24" s="34">
+        <v>0</v>
+      </c>
+      <c r="T24" s="34">
+        <v>0</v>
+      </c>
+      <c r="U24" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="13:21" x14ac:dyDescent="0.25">
+      <c r="M25" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="N25" s="34">
+        <v>0</v>
+      </c>
+      <c r="O25" s="34">
+        <v>0</v>
+      </c>
+      <c r="P25" s="34">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R25" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="S25" s="34">
+        <v>0</v>
+      </c>
+      <c r="T25" s="34">
+        <v>0</v>
+      </c>
+      <c r="U25" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="13:21" x14ac:dyDescent="0.25">
+      <c r="M26" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="N26" s="34">
+        <v>0</v>
+      </c>
+      <c r="O26" s="34">
+        <v>0</v>
+      </c>
+      <c r="P26" s="34">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R26" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="S26" s="34">
+        <v>0</v>
+      </c>
+      <c r="T26" s="34">
+        <v>0</v>
+      </c>
+      <c r="U26" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="13:21" x14ac:dyDescent="0.25">
+      <c r="M27" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="N27" s="34">
+        <v>0</v>
+      </c>
+      <c r="O27" s="34">
+        <v>0</v>
+      </c>
+      <c r="P27" s="34">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R27" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="S27" s="34">
+        <v>0</v>
+      </c>
+      <c r="T27" s="34">
+        <v>0</v>
+      </c>
+      <c r="U27" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="13:21" x14ac:dyDescent="0.25">
+      <c r="M28" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="N28" s="34">
+        <v>0</v>
+      </c>
+      <c r="O28" s="34">
+        <v>0</v>
+      </c>
+      <c r="P28" s="34">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R28" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="S28" s="34">
+        <v>0</v>
+      </c>
+      <c r="T28" s="34">
+        <v>0.73240000000000005</v>
+      </c>
+      <c r="U28" s="34">
+        <f t="shared" si="3"/>
+        <v>0.73240000000000005</v>
+      </c>
+    </row>
+    <row r="29" spans="13:21" x14ac:dyDescent="0.25">
+      <c r="M29" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="N29" s="34">
+        <v>0</v>
+      </c>
+      <c r="O29" s="34">
+        <v>0</v>
+      </c>
+      <c r="P29" s="34">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R29" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="S29" s="34">
+        <v>0</v>
+      </c>
+      <c r="T29" s="34">
+        <v>0</v>
+      </c>
+      <c r="U29" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="13:21" x14ac:dyDescent="0.25">
+      <c r="M30" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="N30" s="34">
+        <v>0</v>
+      </c>
+      <c r="O30" s="34">
+        <v>0</v>
+      </c>
+      <c r="P30" s="34">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R30" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="S30" s="34">
+        <v>0</v>
+      </c>
+      <c r="T30" s="34">
+        <v>0</v>
+      </c>
+      <c r="U30" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="13:21" x14ac:dyDescent="0.25">
+      <c r="M31" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="N31" s="34">
+        <v>0</v>
+      </c>
+      <c r="O31" s="34">
+        <v>0</v>
+      </c>
+      <c r="P31" s="34">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R31" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="S31" s="34">
+        <v>0</v>
+      </c>
+      <c r="T31" s="34">
+        <v>0.2676</v>
+      </c>
+      <c r="U31" s="34">
+        <f t="shared" si="3"/>
+        <v>0.2676</v>
+      </c>
+    </row>
+    <row r="32" spans="13:21" x14ac:dyDescent="0.25">
+      <c r="M32" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="N32" s="34">
+        <v>0</v>
+      </c>
+      <c r="O32" s="34">
+        <v>0</v>
+      </c>
+      <c r="P32" s="34">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R32" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="S32" s="34">
+        <v>0</v>
+      </c>
+      <c r="T32" s="34">
+        <v>0</v>
+      </c>
+      <c r="U32" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="13:21" x14ac:dyDescent="0.25">
+      <c r="M33" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="N33" s="34">
+        <v>0</v>
+      </c>
+      <c r="O33" s="34">
+        <v>0</v>
+      </c>
+      <c r="P33" s="34">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R33" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="S33" s="34">
+        <v>0</v>
+      </c>
+      <c r="T33" s="34">
+        <v>0</v>
+      </c>
+      <c r="U33" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="13:21" x14ac:dyDescent="0.25">
+      <c r="M34" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="N34" s="34">
+        <v>0</v>
+      </c>
+      <c r="O34" s="34">
+        <v>0</v>
+      </c>
+      <c r="P34" s="34">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R34" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="S34" s="34">
+        <v>0</v>
+      </c>
+      <c r="T34" s="34">
+        <v>0</v>
+      </c>
+      <c r="U34" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="13:21" x14ac:dyDescent="0.25">
+      <c r="M35" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="N35" s="34">
+        <v>0</v>
+      </c>
+      <c r="O35" s="34">
+        <v>0</v>
+      </c>
+      <c r="P35" s="34">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R35" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="S35" s="34">
+        <v>0</v>
+      </c>
+      <c r="T35" s="34">
+        <v>0</v>
+      </c>
+      <c r="U35" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="13:21" x14ac:dyDescent="0.25">
+      <c r="M36" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="N36" s="34">
+        <v>0</v>
+      </c>
+      <c r="O36" s="34">
+        <v>0</v>
+      </c>
+      <c r="P36" s="34">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R36" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="S36" s="34">
+        <v>0</v>
+      </c>
+      <c r="T36" s="34">
+        <v>0</v>
+      </c>
+      <c r="U36" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="13:21" x14ac:dyDescent="0.25">
+      <c r="M37" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="N37" s="34">
+        <v>0</v>
+      </c>
+      <c r="O37" s="34">
+        <v>0</v>
+      </c>
+      <c r="P37" s="34">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R37" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="S37" s="34">
+        <v>0</v>
+      </c>
+      <c r="T37" s="34">
+        <v>0</v>
+      </c>
+      <c r="U37" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="13:21" x14ac:dyDescent="0.25">
+      <c r="M38" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="N38" s="34">
+        <v>0</v>
+      </c>
+      <c r="O38" s="34">
+        <v>0</v>
+      </c>
+      <c r="P38" s="34">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R38" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="S38" s="34">
+        <v>0</v>
+      </c>
+      <c r="T38" s="34">
+        <v>0</v>
+      </c>
+      <c r="U38" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="13:21" x14ac:dyDescent="0.25">
+      <c r="M39" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="N39" s="34">
+        <v>0</v>
+      </c>
+      <c r="O39" s="34">
+        <v>0</v>
+      </c>
+      <c r="P39" s="34">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R39" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="S39" s="34">
+        <v>0</v>
+      </c>
+      <c r="T39" s="34">
+        <v>0</v>
+      </c>
+      <c r="U39" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="13:21" x14ac:dyDescent="0.25">
+      <c r="M40" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="N40" s="34">
+        <v>0</v>
+      </c>
+      <c r="O40" s="34">
+        <v>0</v>
+      </c>
+      <c r="P40" s="34">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R40" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="S40" s="34">
+        <v>0</v>
+      </c>
+      <c r="T40" s="34">
+        <v>0</v>
+      </c>
+      <c r="U40" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="13:21" x14ac:dyDescent="0.25">
+      <c r="M41" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="N41" s="34">
+        <v>0</v>
+      </c>
+      <c r="O41" s="34">
+        <v>0</v>
+      </c>
+      <c r="P41" s="34">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R41" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="S41" s="34">
+        <v>0</v>
+      </c>
+      <c r="T41" s="34">
+        <v>0</v>
+      </c>
+      <c r="U41" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="13:21" x14ac:dyDescent="0.25">
+      <c r="M42" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="N42" s="34">
+        <v>0</v>
+      </c>
+      <c r="O42" s="34">
+        <v>0</v>
+      </c>
+      <c r="P42" s="34">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R42" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="S42" s="34">
+        <v>0</v>
+      </c>
+      <c r="T42" s="34">
+        <v>0</v>
+      </c>
+      <c r="U42" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6343,60 +7384,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="H1" s="40" t="s">
+      <c r="H1" s="45" t="s">
         <v>114</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
       <c r="M1" s="26"/>
-      <c r="N1" s="40" t="s">
+      <c r="N1" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="O1" s="40"/>
-      <c r="R1" s="40" t="s">
+      <c r="O1" s="45"/>
+      <c r="R1" s="45" t="s">
         <v>108</v>
       </c>
-      <c r="S1" s="40"/>
-      <c r="T1" s="40"/>
-      <c r="U1" s="40"/>
-      <c r="V1" s="40"/>
-      <c r="Y1" s="40" t="s">
+      <c r="S1" s="45"/>
+      <c r="T1" s="45"/>
+      <c r="U1" s="45"/>
+      <c r="V1" s="45"/>
+      <c r="Y1" s="45" t="s">
         <v>108</v>
       </c>
-      <c r="Z1" s="40"/>
-      <c r="AA1" s="40"/>
-      <c r="AB1" s="40"/>
-      <c r="AC1" s="40"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
+      <c r="AB1" s="45"/>
+      <c r="AC1" s="45"/>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="H2" s="41">
+      <c r="H2" s="46">
         <v>46000</v>
       </c>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
       <c r="M2" s="27"/>
-      <c r="N2" s="41">
+      <c r="N2" s="46">
         <v>45684</v>
       </c>
-      <c r="O2" s="40"/>
-      <c r="R2" s="41">
+      <c r="O2" s="45"/>
+      <c r="R2" s="46">
         <v>45685</v>
       </c>
-      <c r="S2" s="41"/>
-      <c r="T2" s="41"/>
-      <c r="U2" s="41"/>
-      <c r="V2" s="41"/>
-      <c r="Y2" s="41">
+      <c r="S2" s="46"/>
+      <c r="T2" s="46"/>
+      <c r="U2" s="46"/>
+      <c r="V2" s="46"/>
+      <c r="Y2" s="46">
         <v>45688</v>
       </c>
-      <c r="Z2" s="41"/>
-      <c r="AA2" s="41"/>
-      <c r="AB2" s="41"/>
-      <c r="AC2" s="41"/>
+      <c r="Z2" s="46"/>
+      <c r="AA2" s="46"/>
+      <c r="AB2" s="46"/>
+      <c r="AC2" s="46"/>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
@@ -6532,19 +7573,19 @@
         <v>24.8001101264</v>
       </c>
       <c r="V4" s="12"/>
-      <c r="X4" s="42" t="s">
+      <c r="X4" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="Y4" s="43">
+      <c r="Y4" s="41">
         <v>218.85600000000002</v>
       </c>
-      <c r="Z4" s="44">
+      <c r="Z4" s="42">
         <v>0.23199208873650332</v>
       </c>
-      <c r="AA4" s="45">
+      <c r="AA4" s="43">
         <v>3.586522645026835E-2</v>
       </c>
-      <c r="AB4" s="43">
+      <c r="AB4" s="41">
         <v>7.849319999999949</v>
       </c>
       <c r="AC4" s="12"/>
@@ -6604,19 +7645,19 @@
         <v>30.380156749999998</v>
       </c>
       <c r="V5" s="12"/>
-      <c r="X5" s="42" t="s">
+      <c r="X5" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="Y5" s="43">
+      <c r="Y5" s="41">
         <v>210.14336800000001</v>
       </c>
-      <c r="Z5" s="44">
+      <c r="Z5" s="42">
         <v>0.22275651056605106</v>
       </c>
-      <c r="AA5" s="45">
+      <c r="AA5" s="43">
         <v>0.11801519297244734</v>
       </c>
-      <c r="AB5" s="43">
+      <c r="AB5" s="41">
         <v>24.8001101264</v>
       </c>
       <c r="AC5" s="12"/>
@@ -6676,19 +7717,19 @@
         <v>21.191897399999959</v>
       </c>
       <c r="V6" s="12"/>
-      <c r="X6" s="42" t="s">
+      <c r="X6" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="Y6" s="43">
+      <c r="Y6" s="41">
         <v>177.40437299999999</v>
       </c>
-      <c r="Z6" s="44">
+      <c r="Z6" s="42">
         <v>0.18805246848731463</v>
       </c>
-      <c r="AA6" s="45">
+      <c r="AA6" s="43">
         <v>0.17124807148919596</v>
       </c>
-      <c r="AB6" s="43">
+      <c r="AB6" s="41">
         <v>30.380156749999998</v>
       </c>
       <c r="AC6" s="12"/>
@@ -6752,19 +7793,19 @@
       <c r="V7" s="12">
         <v>10.31</v>
       </c>
-      <c r="X7" s="42" t="s">
+      <c r="X7" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="Y7" s="43">
+      <c r="Y7" s="41">
         <v>172.11133100000001</v>
       </c>
-      <c r="Z7" s="44">
+      <c r="Z7" s="42">
         <v>0.18244172960261401</v>
       </c>
-      <c r="AA7" s="45">
+      <c r="AA7" s="43">
         <v>0.1289374887235053</v>
       </c>
-      <c r="AB7" s="43">
+      <c r="AB7" s="41">
         <v>22.191602799999998</v>
       </c>
       <c r="AC7" s="12">
@@ -6826,19 +7867,19 @@
         <v>5.5036288595999991</v>
       </c>
       <c r="V8" s="12"/>
-      <c r="X8" s="42" t="s">
+      <c r="X8" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="Y8" s="43">
+      <c r="Y8" s="41">
         <v>94.882213999999991</v>
       </c>
-      <c r="Z8" s="44">
+      <c r="Z8" s="42">
         <v>0.10057719692310878</v>
       </c>
-      <c r="AA8" s="45">
+      <c r="AA8" s="43">
         <v>0.28159743932619463</v>
       </c>
-      <c r="AB8" s="43">
+      <c r="AB8" s="41">
         <v>26.71858850000001</v>
       </c>
       <c r="AC8" s="12"/>
@@ -6898,19 +7939,19 @@
         <v>2.8585286400000075E-17</v>
       </c>
       <c r="V9" s="12"/>
-      <c r="X9" s="42" t="s">
+      <c r="X9" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="Y9" s="43">
+      <c r="Y9" s="41">
         <v>59.980460999999991</v>
       </c>
-      <c r="Z9" s="44">
+      <c r="Z9" s="42">
         <v>6.35805846345011E-2</v>
       </c>
-      <c r="AA9" s="45">
+      <c r="AA9" s="43">
         <v>9.1757028336277635E-2</v>
       </c>
-      <c r="AB9" s="43">
+      <c r="AB9" s="41">
         <v>5.5036288595999991</v>
       </c>
       <c r="AC9" s="12"/>
@@ -6970,19 +8011,19 @@
         <v>7.6584000000000023E-18</v>
       </c>
       <c r="V10" s="12"/>
-      <c r="X10" s="42" t="s">
+      <c r="X10" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="Y10" s="43">
+      <c r="Y10" s="41">
         <v>9.99925</v>
       </c>
-      <c r="Z10" s="44">
+      <c r="Z10" s="42">
         <v>1.0599421049907156E-2</v>
       </c>
-      <c r="AA10" s="45">
+      <c r="AA10" s="43">
         <v>0.19999999999999996</v>
       </c>
-      <c r="AB10" s="43">
+      <c r="AB10" s="41">
         <v>1.9998499999999986</v>
       </c>
       <c r="AC10" s="12"/>
@@ -7042,19 +8083,19 @@
         <v>9.3470999999999986E-19</v>
       </c>
       <c r="V11" s="12"/>
-      <c r="X11" s="42" t="s">
+      <c r="X11" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="Y11" s="43">
+      <c r="Y11" s="41">
         <v>2.9170551999999998E-16</v>
       </c>
-      <c r="Z11" s="44">
+      <c r="Z11" s="42">
         <v>3.0921415396775884E-19</v>
       </c>
-      <c r="AA11" s="45">
+      <c r="AA11" s="43">
         <v>9.799364235548258E-2</v>
       </c>
-      <c r="AB11" s="43">
+      <c r="AB11" s="41">
         <v>2.8585286400000075E-17</v>
       </c>
       <c r="AC11" s="12"/>
@@ -7114,19 +8155,19 @@
         <v>3.9200000000000069E-19</v>
       </c>
       <c r="V12" s="12"/>
-      <c r="X12" s="42" t="s">
+      <c r="X12" s="40" t="s">
         <v>87</v>
       </c>
-      <c r="Y12" s="43">
+      <c r="Y12" s="41">
         <v>1.3353E-17</v>
       </c>
-      <c r="Z12" s="44">
+      <c r="Z12" s="42">
         <v>1.4154468513079507E-20</v>
       </c>
-      <c r="AA12" s="45">
+      <c r="AA12" s="43">
         <v>7.0000000000000062E-2</v>
       </c>
-      <c r="AB12" s="43">
+      <c r="AB12" s="41">
         <v>9.3470999999999986E-19</v>
       </c>
       <c r="AC12" s="12"/>
@@ -7192,19 +8233,19 @@
         <f>SUM(V4:V12)</f>
         <v>10.31</v>
       </c>
-      <c r="X13" s="42" t="s">
+      <c r="X13" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="Y13" s="43">
+      <c r="Y13" s="41">
         <v>5.5999999999999995E-18</v>
       </c>
-      <c r="Z13" s="44">
+      <c r="Z13" s="42">
         <v>5.9361209970227834E-21</v>
       </c>
-      <c r="AA13" s="45">
+      <c r="AA13" s="43">
         <v>7.0000000000000062E-2</v>
       </c>
-      <c r="AB13" s="43">
+      <c r="AB13" s="41">
         <v>3.9200000000000069E-19</v>
       </c>
     </row>

--- a/Open Positions.xlsx
+++ b/Open Positions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\StockSillines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E231CD-60A9-4DC1-907D-C312377AE26E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B825B88-2EFF-4757-9500-158D87505ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Positions" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="132">
   <si>
     <t>Name</t>
   </si>
@@ -2484,7 +2484,7 @@
         <v>20.928000000000001</v>
       </c>
       <c r="G2" s="1">
-        <f t="shared" ref="G2:G46" si="0">E2*F2</f>
+        <f>E2*F2</f>
         <v>41.856000000000002</v>
       </c>
       <c r="H2" s="13">
@@ -2494,11 +2494,11 @@
         <v>0.2</v>
       </c>
       <c r="J2" s="9">
-        <f t="shared" ref="J2:J46" si="1">IFERROR(H2/I2,"")</f>
+        <f>IFERROR(H2/I2,"")</f>
         <v>0.22499999999999998</v>
       </c>
       <c r="K2" s="9">
-        <f t="shared" ref="K2:K46" si="2">IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f>IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>1.1451292650523102E-2</v>
       </c>
       <c r="L2" s="12">
@@ -2506,35 +2506,35 @@
         <v>21.869759999999999</v>
       </c>
       <c r="M2" s="12">
-        <f t="shared" ref="M2:M46" si="3">L2*E2</f>
+        <f>L2*E2</f>
         <v>43.739519999999999</v>
       </c>
       <c r="N2" s="12">
-        <f t="shared" ref="N2:N46" si="4">F2/(1+I2-H2)</f>
+        <f>F2/(1+I2-H2)</f>
         <v>18.119480519480518</v>
       </c>
       <c r="O2" s="12">
-        <f t="shared" ref="O2:O46" si="5">L2-F2</f>
+        <f>L2-F2</f>
         <v>0.9417599999999986</v>
       </c>
       <c r="P2" s="12">
-        <f t="shared" ref="P2:P46" si="6">0.5*(N2-F2)</f>
+        <f>0.5*(N2-F2)</f>
         <v>-1.4042597402597412</v>
       </c>
       <c r="Q2" s="15">
-        <f t="shared" ref="Q2:Q46" si="7">O2+P2</f>
+        <f>O2+P2</f>
         <v>-0.46249974025974261</v>
       </c>
       <c r="R2" s="12">
-        <f t="shared" ref="R2:R46" si="8">MAX($Q$2:$Q$279)-Q2</f>
+        <f>MAX($Q$2:$Q$279)-Q2</f>
         <v>114.59494482144413</v>
       </c>
       <c r="S2" s="9">
-        <f t="shared" ref="S2:S46" si="9">IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R2)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R2)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>8.7263884245343277E-3</v>
       </c>
       <c r="T2" s="9">
-        <f t="shared" ref="T2:T46" si="10">R2/MAX($R$2:$R$28)</f>
+        <f>R2/MAX($R$2:$R$28)</f>
         <v>0.80011330398039715</v>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
         <v>16.399999999999999</v>
       </c>
       <c r="G3" s="1">
-        <f t="shared" si="0"/>
+        <f>E3*F3</f>
         <v>32.799999999999997</v>
       </c>
       <c r="H3" s="13">
@@ -2568,11 +2568,11 @@
         <v>0.2</v>
       </c>
       <c r="J3" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H3/I3,"")</f>
         <v>0.22499999999999998</v>
       </c>
       <c r="K3" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J3/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>1.1451292650523102E-2</v>
       </c>
       <c r="L3" s="12">
@@ -2580,35 +2580,35 @@
         <v>17.137999999999998</v>
       </c>
       <c r="M3" s="12">
-        <f t="shared" si="3"/>
+        <f>L3*E3</f>
         <v>34.275999999999996</v>
       </c>
       <c r="N3" s="12">
-        <f t="shared" si="4"/>
+        <f>F3/(1+I3-H3)</f>
         <v>14.199134199134198</v>
       </c>
       <c r="O3" s="12">
-        <f t="shared" si="5"/>
+        <f>L3-F3</f>
         <v>0.73799999999999955</v>
       </c>
       <c r="P3" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N3-F3)</f>
         <v>-1.1004329004329003</v>
       </c>
       <c r="Q3" s="15">
-        <f t="shared" si="7"/>
+        <f>O3+P3</f>
         <v>-0.36243290043290077</v>
       </c>
       <c r="R3" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q3</f>
         <v>114.49487798161729</v>
       </c>
       <c r="S3" s="9">
-        <f t="shared" si="9"/>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R3)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>8.7340151597048287E-3</v>
       </c>
       <c r="T3" s="9">
-        <f t="shared" si="10"/>
+        <f>R3/MAX($R$2:$R$28)</f>
         <v>0.79941462735066027</v>
       </c>
     </row>
@@ -2632,7 +2632,7 @@
         <v>15.3</v>
       </c>
       <c r="G4" s="1">
-        <f t="shared" si="0"/>
+        <f>E4*F4</f>
         <v>29.980350000000001</v>
       </c>
       <c r="H4" s="13">
@@ -2642,11 +2642,11 @@
         <v>0.39532299999999998</v>
       </c>
       <c r="J4" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H4/I4,"")</f>
         <v>0.88535197800279775</v>
       </c>
       <c r="K4" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J4/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>4.5059664883686804E-2</v>
       </c>
       <c r="L4" s="12">
@@ -2654,35 +2654,35 @@
         <v>20.655000000000001</v>
       </c>
       <c r="M4" s="12">
-        <f t="shared" si="3"/>
+        <f>L4*E4</f>
         <v>40.4734725</v>
       </c>
       <c r="N4" s="12">
-        <f t="shared" si="4"/>
+        <f>F4/(1+I4-H4)</f>
         <v>14.636624277854791</v>
       </c>
       <c r="O4" s="12">
-        <f t="shared" si="5"/>
+        <f>L4-F4</f>
         <v>5.3550000000000004</v>
       </c>
       <c r="P4" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N4-F4)</f>
         <v>-0.33168786107260484</v>
       </c>
       <c r="Q4" s="15">
-        <f t="shared" si="7"/>
+        <f>O4+P4</f>
         <v>5.0233121389273956</v>
       </c>
       <c r="R4" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q4</f>
         <v>109.10913294225699</v>
       </c>
       <c r="S4" s="9">
-        <f t="shared" si="9"/>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R4)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>9.165135612700933E-3</v>
       </c>
       <c r="T4" s="9">
-        <f t="shared" si="10"/>
+        <f>R4/MAX($R$2:$R$28)</f>
         <v>0.76181081974332665</v>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
         <v>21.73</v>
       </c>
       <c r="G5" s="1">
-        <f t="shared" si="0"/>
+        <f>E5*F5</f>
         <v>41.237020999999999</v>
       </c>
       <c r="H5" s="13">
@@ -2717,46 +2717,46 @@
         <v>0.45929999999999999</v>
       </c>
       <c r="J5" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H5/I5,"")</f>
         <v>0.48594326447066366</v>
       </c>
       <c r="K5" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J5/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>2.4731904591129405E-2</v>
       </c>
       <c r="L5" s="12">
         <v>26.58</v>
       </c>
       <c r="M5" s="12">
-        <f t="shared" si="3"/>
+        <f>L5*E5</f>
         <v>50.440865999999993</v>
       </c>
       <c r="N5" s="12">
-        <f t="shared" si="4"/>
+        <f>F5/(1+I5-H5)</f>
         <v>17.579394852436032</v>
       </c>
       <c r="O5" s="12">
-        <f t="shared" si="5"/>
+        <f>L5-F5</f>
         <v>4.8499999999999979</v>
       </c>
       <c r="P5" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N5-F5)</f>
         <v>-2.0753025737819843</v>
       </c>
       <c r="Q5" s="15">
-        <f t="shared" si="7"/>
+        <f>O5+P5</f>
         <v>2.7746974262180135</v>
       </c>
       <c r="R5" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q5</f>
         <v>111.35774765496637</v>
       </c>
       <c r="S5" s="9">
-        <f t="shared" si="9"/>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R5)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>8.980066686499668E-3</v>
       </c>
       <c r="T5" s="9">
-        <f t="shared" si="10"/>
+        <f>R5/MAX($R$2:$R$28)</f>
         <v>0.77751087134654673</v>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
         <v>51.88</v>
       </c>
       <c r="G6" s="1">
-        <f t="shared" si="0"/>
+        <f>E6*F6</f>
         <v>89.991048000000006</v>
       </c>
       <c r="H6" s="13">
@@ -2791,47 +2791,47 @@
         <v>0.19980000000000001</v>
       </c>
       <c r="J6" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H6/I6,"")</f>
         <v>0.92242242242242245</v>
       </c>
       <c r="K6" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J6/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>4.6946351584727132E-2</v>
       </c>
       <c r="L6" s="12">
-        <f t="shared" ref="L6:L38" si="11">F6/(1-(F6*(1+H6)-F6)/(F6*(1+H6)))</f>
+        <f>F6/(1-(F6*(1+H6)-F6)/(F6*(1+H6)))</f>
         <v>61.441483999999996</v>
       </c>
       <c r="M6" s="12">
-        <f t="shared" si="3"/>
+        <f>L6*E6</f>
         <v>106.57639814639998</v>
       </c>
       <c r="N6" s="12">
-        <f t="shared" si="4"/>
+        <f>F6/(1+I6-H6)</f>
         <v>51.088133924175295</v>
       </c>
       <c r="O6" s="12">
-        <f t="shared" si="5"/>
+        <f>L6-F6</f>
         <v>9.561483999999993</v>
       </c>
       <c r="P6" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N6-F6)</f>
         <v>-0.39593303791235357</v>
       </c>
       <c r="Q6" s="15">
-        <f t="shared" si="7"/>
+        <f>O6+P6</f>
         <v>9.1655509620876394</v>
       </c>
       <c r="R6" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q6</f>
         <v>104.96689411909675</v>
       </c>
       <c r="S6" s="9">
-        <f t="shared" si="9"/>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R6)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>9.526813271862531E-3</v>
       </c>
       <c r="T6" s="9">
-        <f t="shared" si="10"/>
+        <f>R6/MAX($R$2:$R$28)</f>
         <v>0.73288929623425103</v>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
         <v>44.24</v>
       </c>
       <c r="G7" s="1">
-        <f t="shared" si="0"/>
+        <f>E7*F7</f>
         <v>44.24</v>
       </c>
       <c r="H7" s="13">
@@ -2865,47 +2865,47 @@
         <v>0.2</v>
       </c>
       <c r="J7" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H7/I7,"")</f>
         <v>0.22499999999999998</v>
       </c>
       <c r="K7" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J7/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>1.1451292650523102E-2</v>
       </c>
       <c r="L7" s="12">
-        <f t="shared" si="11"/>
+        <f>F7/(1-(F7*(1+H7)-F7)/(F7*(1+H7)))</f>
         <v>46.230800000000002</v>
       </c>
       <c r="M7" s="12">
-        <f t="shared" si="3"/>
+        <f>L7*E7</f>
         <v>46.230800000000002</v>
       </c>
       <c r="N7" s="12">
-        <f t="shared" si="4"/>
+        <f>F7/(1+I7-H7)</f>
         <v>38.303030303030305</v>
       </c>
       <c r="O7" s="12">
-        <f t="shared" si="5"/>
+        <f>L7-F7</f>
         <v>1.9908000000000001</v>
       </c>
       <c r="P7" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N7-F7)</f>
         <v>-2.9684848484848487</v>
       </c>
       <c r="Q7" s="15">
-        <f t="shared" si="7"/>
+        <f>O7+P7</f>
         <v>-0.9776848484848486</v>
       </c>
       <c r="R7" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q7</f>
         <v>115.11012992966923</v>
       </c>
       <c r="S7" s="9">
-        <f t="shared" si="9"/>
-        <v>8.6873327361456972E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R7)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>8.6873327361456955E-3</v>
       </c>
       <c r="T7" s="9">
-        <f t="shared" si="10"/>
+        <f>R7/MAX($R$2:$R$28)</f>
         <v>0.80371037765363607</v>
       </c>
     </row>
@@ -2929,7 +2929,7 @@
         <v>48.68</v>
       </c>
       <c r="G8" s="1">
-        <f t="shared" si="0"/>
+        <f>E8*F8</f>
         <v>48.68</v>
       </c>
       <c r="H8" s="13">
@@ -2939,47 +2939,47 @@
         <v>0.2</v>
       </c>
       <c r="J8" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H8/I8,"")</f>
         <v>0.125</v>
       </c>
       <c r="K8" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J8/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>6.3618292502906132E-3</v>
       </c>
       <c r="L8" s="12">
-        <f t="shared" si="11"/>
+        <f>F8/(1-(F8*(1+H8)-F8)/(F8*(1+H8)))</f>
         <v>49.896999999999998</v>
       </c>
       <c r="M8" s="12">
-        <f t="shared" si="3"/>
+        <f>L8*E8</f>
         <v>49.896999999999998</v>
       </c>
       <c r="N8" s="12">
-        <f t="shared" si="4"/>
+        <f>F8/(1+I8-H8)</f>
         <v>41.42978723404255</v>
       </c>
       <c r="O8" s="12">
-        <f t="shared" si="5"/>
+        <f>L8-F8</f>
         <v>1.2169999999999987</v>
       </c>
       <c r="P8" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N8-F8)</f>
         <v>-3.6251063829787249</v>
       </c>
       <c r="Q8" s="15">
-        <f t="shared" si="7"/>
+        <f>O8+P8</f>
         <v>-2.4081063829787261</v>
       </c>
       <c r="R8" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q8</f>
         <v>116.54055146416312</v>
       </c>
       <c r="S8" s="9">
-        <f t="shared" si="9"/>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R8)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>8.5807042049865865E-3</v>
       </c>
       <c r="T8" s="9">
-        <f t="shared" si="10"/>
+        <f>R8/MAX($R$2:$R$28)</f>
         <v>0.81369772309746791</v>
       </c>
     </row>
@@ -3003,7 +3003,7 @@
         <v>51.28</v>
       </c>
       <c r="G9" s="1">
-        <f t="shared" si="0"/>
+        <f>E9*F9</f>
         <v>51.28</v>
       </c>
       <c r="H9" s="13">
@@ -3013,47 +3013,47 @@
         <v>0.2</v>
       </c>
       <c r="J9" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H9/I9,"")</f>
         <v>0.125</v>
       </c>
       <c r="K9" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J9/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>6.3618292502906132E-3</v>
       </c>
       <c r="L9" s="12">
-        <f t="shared" si="11"/>
+        <f>F9/(1-(F9*(1+H9)-F9)/(F9*(1+H9)))</f>
         <v>52.561999999999998</v>
       </c>
       <c r="M9" s="12">
-        <f t="shared" si="3"/>
+        <f>L9*E9</f>
         <v>52.561999999999998</v>
       </c>
       <c r="N9" s="12">
-        <f t="shared" si="4"/>
+        <f>F9/(1+I9-H9)</f>
         <v>43.642553191489363</v>
       </c>
       <c r="O9" s="12">
-        <f t="shared" si="5"/>
+        <f>L9-F9</f>
         <v>1.2819999999999965</v>
       </c>
       <c r="P9" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N9-F9)</f>
         <v>-3.8187234042553193</v>
       </c>
       <c r="Q9" s="15">
-        <f t="shared" si="7"/>
+        <f>O9+P9</f>
         <v>-2.5367234042553228</v>
       </c>
       <c r="R9" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q9</f>
         <v>116.66916848543971</v>
       </c>
       <c r="S9" s="9">
-        <f t="shared" si="9"/>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R9)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>8.5712447682765452E-3</v>
       </c>
       <c r="T9" s="9">
-        <f t="shared" si="10"/>
+        <f>R9/MAX($R$2:$R$28)</f>
         <v>0.81459573993409262</v>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
         <v>41.76</v>
       </c>
       <c r="G10" s="1">
-        <f t="shared" si="0"/>
+        <f>E10*F10</f>
         <v>40.022784000000001</v>
       </c>
       <c r="H10" s="13">
@@ -3087,47 +3087,47 @@
         <v>0.2</v>
       </c>
       <c r="J10" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H10/I10,"")</f>
         <v>0.5</v>
       </c>
       <c r="K10" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J10/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>2.5447317001162453E-2</v>
       </c>
       <c r="L10" s="12">
-        <f t="shared" si="11"/>
+        <f>F10/(1-(F10*(1+H10)-F10)/(F10*(1+H10)))</f>
         <v>45.936</v>
       </c>
       <c r="M10" s="12">
-        <f t="shared" si="3"/>
+        <f>L10*E10</f>
         <v>44.025062400000003</v>
       </c>
       <c r="N10" s="12">
-        <f t="shared" si="4"/>
+        <f>F10/(1+I10-H10)</f>
         <v>37.963636363636368</v>
       </c>
       <c r="O10" s="12">
-        <f t="shared" si="5"/>
+        <f>L10-F10</f>
         <v>4.1760000000000019</v>
       </c>
       <c r="P10" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N10-F10)</f>
         <v>-1.8981818181818149</v>
       </c>
       <c r="Q10" s="15">
-        <f t="shared" si="7"/>
+        <f>O10+P10</f>
         <v>2.2778181818181871</v>
       </c>
       <c r="R10" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q10</f>
         <v>111.8546268993662</v>
       </c>
       <c r="S10" s="9">
-        <f t="shared" si="9"/>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R10)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>8.9401755449927331E-3</v>
       </c>
       <c r="T10" s="9">
-        <f t="shared" si="10"/>
+        <f>R10/MAX($R$2:$R$28)</f>
         <v>0.78098013165759694</v>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
         <v>77.430000000000007</v>
       </c>
       <c r="G11" s="1">
-        <f t="shared" si="0"/>
+        <f>E11*F11</f>
         <v>34.982874000000002</v>
       </c>
       <c r="H11" s="13">
@@ -3161,47 +3161,47 @@
         <v>0.25990000000000002</v>
       </c>
       <c r="J11" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H11/I11,"")</f>
         <v>0.38476337052712584</v>
       </c>
       <c r="K11" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J11/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>1.9582390920478997E-2</v>
       </c>
       <c r="L11" s="12">
-        <f t="shared" si="11"/>
+        <f>F11/(1-(F11*(1+H11)-F11)/(F11*(1+H11)))</f>
         <v>85.173000000000016</v>
       </c>
       <c r="M11" s="12">
-        <f t="shared" si="3"/>
+        <f>L11*E11</f>
         <v>38.481161400000005</v>
       </c>
       <c r="N11" s="12">
-        <f t="shared" si="4"/>
+        <f>F11/(1+I11-H11)</f>
         <v>66.755754806448849</v>
       </c>
       <c r="O11" s="12">
-        <f t="shared" si="5"/>
+        <f>L11-F11</f>
         <v>7.7430000000000092</v>
       </c>
       <c r="P11" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N11-F11)</f>
         <v>-5.3371225967755791</v>
       </c>
       <c r="Q11" s="15">
-        <f t="shared" si="7"/>
+        <f>O11+P11</f>
         <v>2.4058774032244301</v>
       </c>
       <c r="R11" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q11</f>
         <v>111.72656767795996</v>
       </c>
       <c r="S11" s="9">
-        <f t="shared" si="9"/>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R11)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>8.9504226325326178E-3</v>
       </c>
       <c r="T11" s="9">
-        <f t="shared" si="10"/>
+        <f>R11/MAX($R$2:$R$28)</f>
         <v>0.78008600943515383</v>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
         <v>160.25</v>
       </c>
       <c r="G12" s="1">
-        <f t="shared" si="0"/>
+        <f>E12*F12</f>
         <v>69.965149999999994</v>
       </c>
       <c r="H12" s="13">
@@ -3235,47 +3235,47 @@
         <v>0.16439999999999999</v>
       </c>
       <c r="J12" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H12/I12,"")</f>
         <v>0.40875912408759124</v>
       </c>
       <c r="K12" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J12/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>2.0803646015548866E-2</v>
       </c>
       <c r="L12" s="12">
-        <f t="shared" si="11"/>
+        <f>F12/(1-(F12*(1+H12)-F12)/(F12*(1+H12)))</f>
         <v>171.0188</v>
       </c>
       <c r="M12" s="12">
-        <f t="shared" si="3"/>
+        <f>L12*E12</f>
         <v>74.666808079999996</v>
       </c>
       <c r="N12" s="12">
-        <f t="shared" si="4"/>
+        <f>F12/(1+I12-H12)</f>
         <v>146.05359095880419</v>
       </c>
       <c r="O12" s="12">
-        <f t="shared" si="5"/>
+        <f>L12-F12</f>
         <v>10.768799999999999</v>
       </c>
       <c r="P12" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N12-F12)</f>
         <v>-7.0982045205979034</v>
       </c>
       <c r="Q12" s="15">
-        <f t="shared" si="7"/>
+        <f>O12+P12</f>
         <v>3.6705954794020954</v>
       </c>
       <c r="R12" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q12</f>
         <v>110.46184960178229</v>
       </c>
       <c r="S12" s="9">
-        <f t="shared" si="9"/>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R12)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>9.0528992915203284E-3</v>
       </c>
       <c r="T12" s="9">
-        <f t="shared" si="10"/>
+        <f>R12/MAX($R$2:$R$28)</f>
         <v>0.7712556220204998</v>
       </c>
     </row>
@@ -3299,7 +3299,7 @@
         <v>189.76</v>
       </c>
       <c r="G13" s="1">
-        <f t="shared" si="0"/>
+        <f>E13*F13</f>
         <v>77.953407999999996</v>
       </c>
       <c r="H13" s="13">
@@ -3310,47 +3310,47 @@
         <v>0.37</v>
       </c>
       <c r="J13" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H13/I13,"")</f>
         <v>0.53609680506813773</v>
       </c>
       <c r="K13" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J13/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>2.728445068375859E-2</v>
       </c>
       <c r="L13" s="12">
-        <f t="shared" si="11"/>
+        <f>F13/(1-(F13*(1+H13)-F13)/(F13*(1+H13)))</f>
         <v>227.4</v>
       </c>
       <c r="M13" s="12">
-        <f t="shared" si="3"/>
+        <f>L13*E13</f>
         <v>93.41592</v>
       </c>
       <c r="N13" s="12">
-        <f t="shared" si="4"/>
+        <f>F13/(1+I13-H13)</f>
         <v>161.96043380326287</v>
       </c>
       <c r="O13" s="12">
-        <f t="shared" si="5"/>
+        <f>L13-F13</f>
         <v>37.640000000000015</v>
       </c>
       <c r="P13" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N13-F13)</f>
         <v>-13.899783098368559</v>
       </c>
       <c r="Q13" s="15">
-        <f t="shared" si="7"/>
+        <f>O13+P13</f>
         <v>23.740216901631456</v>
       </c>
       <c r="R13" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q13</f>
         <v>90.39222817955293</v>
       </c>
       <c r="S13" s="9">
-        <f t="shared" si="9"/>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R13)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>1.1062897996204102E-2</v>
       </c>
       <c r="T13" s="9">
-        <f t="shared" si="10"/>
+        <f>R13/MAX($R$2:$R$28)</f>
         <v>0.6311275288415521</v>
       </c>
     </row>
@@ -3374,7 +3374,7 @@
         <v>142.78</v>
       </c>
       <c r="G14" s="1">
-        <f t="shared" si="0"/>
+        <f>E14*F14</f>
         <v>50.187169999999995</v>
       </c>
       <c r="H14" s="13">
@@ -3384,419 +3384,419 @@
         <v>0.18340000000000001</v>
       </c>
       <c r="J14" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H14/I14,"")</f>
         <v>0.38167938931297712</v>
       </c>
       <c r="K14" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J14/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>1.9425432825314851E-2</v>
       </c>
       <c r="L14" s="12">
-        <f t="shared" si="11"/>
+        <f>F14/(1-(F14*(1+H14)-F14)/(F14*(1+H14)))</f>
         <v>152.77460000000002</v>
       </c>
       <c r="M14" s="12">
-        <f t="shared" si="3"/>
+        <f>L14*E14</f>
         <v>53.700271900000004</v>
       </c>
       <c r="N14" s="12">
-        <f t="shared" si="4"/>
+        <f>F14/(1+I14-H14)</f>
         <v>128.23783007005568</v>
       </c>
       <c r="O14" s="12">
-        <f t="shared" si="5"/>
+        <f>L14-F14</f>
         <v>9.9946000000000197</v>
       </c>
       <c r="P14" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N14-F14)</f>
         <v>-7.2710849649721609</v>
       </c>
       <c r="Q14" s="15">
-        <f t="shared" si="7"/>
+        <f>O14+P14</f>
         <v>2.7235150350278587</v>
       </c>
       <c r="R14" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q14</f>
         <v>111.40893004615653</v>
       </c>
       <c r="S14" s="9">
-        <f t="shared" si="9"/>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R14)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>8.9759411528833617E-3</v>
       </c>
       <c r="T14" s="9">
-        <f t="shared" si="10"/>
+        <f>R14/MAX($R$2:$R$28)</f>
         <v>0.77786823189316223</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>96</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="C15" s="32" t="s">
-        <v>100</v>
+        <v>39</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" t="s">
+        <v>43</v>
       </c>
       <c r="D15" s="8">
-        <v>45630</v>
+        <v>45580</v>
       </c>
       <c r="E15" s="2">
-        <v>0.28749999999999998</v>
+        <v>0.34860000000000002</v>
       </c>
       <c r="F15" s="1">
-        <v>34.78</v>
+        <v>131.91</v>
       </c>
       <c r="G15" s="1">
-        <f t="shared" si="0"/>
-        <v>9.99925</v>
+        <f>E15*F15</f>
+        <v>45.983826000000001</v>
       </c>
       <c r="H15" s="13">
-        <v>0.2</v>
+        <v>0.1202</v>
       </c>
       <c r="I15" s="11">
-        <v>0.2</v>
+        <v>0.33710000000000001</v>
       </c>
       <c r="J15" s="9">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>IFERROR(H15/I15,"")</f>
+        <v>0.35657075051913378</v>
       </c>
       <c r="K15" s="9">
-        <f t="shared" si="2"/>
-        <v>5.0894634002324905E-2</v>
+        <f>IFERROR(J15/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>1.8147537843605618E-2</v>
       </c>
       <c r="L15" s="12">
-        <f t="shared" si="11"/>
-        <v>41.735999999999997</v>
+        <f>F15/(1-(F15*(1+H15)-F15)/(F15*(1+H15)))</f>
+        <v>147.76558199999999</v>
       </c>
       <c r="M15" s="12">
-        <f t="shared" si="3"/>
-        <v>11.999099999999999</v>
+        <f>L15*E15</f>
+        <v>51.511081885199999</v>
       </c>
       <c r="N15" s="12">
-        <f t="shared" si="4"/>
-        <v>34.78</v>
+        <f>F15/(1+I15-H15)</f>
+        <v>108.39838934998768</v>
       </c>
       <c r="O15" s="12">
-        <f t="shared" si="5"/>
-        <v>6.955999999999996</v>
+        <f>L15-F15</f>
+        <v>15.855581999999998</v>
       </c>
       <c r="P15" s="12">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>0.5*(N15-F15)</f>
+        <v>-11.755805325006158</v>
       </c>
       <c r="Q15" s="15">
-        <f t="shared" si="7"/>
-        <v>6.955999999999996</v>
+        <f>O15+P15</f>
+        <v>4.0997766749938407</v>
       </c>
       <c r="R15" s="12">
-        <f t="shared" si="8"/>
-        <v>107.1764450811844</v>
+        <f>MAX($Q$2:$Q$279)-Q15</f>
+        <v>110.03266840619054</v>
       </c>
       <c r="S15" s="9">
-        <f t="shared" si="9"/>
-        <v>9.3304083676456744E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R15)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>9.0882100242125827E-3</v>
       </c>
       <c r="T15" s="9">
-        <f t="shared" si="10"/>
-        <v>0.74831660084479601</v>
+        <f>R15/MAX($R$2:$R$28)</f>
+        <v>0.76825903622043479</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="D16" s="8">
-        <v>45627</v>
+        <v>45630</v>
       </c>
       <c r="E16" s="2">
-        <v>0.27450000000000002</v>
+        <v>0.28749999999999998</v>
       </c>
       <c r="F16" s="1">
-        <v>39.799999999999997</v>
+        <v>34.78</v>
       </c>
       <c r="G16" s="1">
-        <f t="shared" si="0"/>
-        <v>10.9251</v>
+        <f>E16*F16</f>
+        <v>9.99925</v>
       </c>
       <c r="H16" s="13">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="I16" s="11">
         <v>0.2</v>
       </c>
       <c r="J16" s="9">
-        <f t="shared" si="1"/>
-        <v>0.5</v>
+        <f>IFERROR(H16/I16,"")</f>
+        <v>1</v>
       </c>
       <c r="K16" s="9">
-        <f t="shared" si="2"/>
-        <v>2.5447317001162453E-2</v>
+        <f>IFERROR(J16/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>5.0894634002324905E-2</v>
       </c>
       <c r="L16" s="12">
-        <f t="shared" si="11"/>
-        <v>43.78</v>
+        <f>F16/(1-(F16*(1+H16)-F16)/(F16*(1+H16)))</f>
+        <v>41.735999999999997</v>
       </c>
       <c r="M16" s="12">
-        <f t="shared" si="3"/>
-        <v>12.017610000000001</v>
+        <f>L16*E16</f>
+        <v>11.999099999999999</v>
       </c>
       <c r="N16" s="12">
-        <f t="shared" si="4"/>
-        <v>36.181818181818187</v>
+        <f>F16/(1+I16-H16)</f>
+        <v>34.78</v>
       </c>
       <c r="O16" s="12">
-        <f t="shared" si="5"/>
-        <v>3.980000000000004</v>
+        <f>L16-F16</f>
+        <v>6.955999999999996</v>
       </c>
       <c r="P16" s="12">
-        <f t="shared" si="6"/>
-        <v>-1.8090909090909051</v>
+        <f>0.5*(N16-F16)</f>
+        <v>0</v>
       </c>
       <c r="Q16" s="15">
-        <f t="shared" si="7"/>
-        <v>2.1709090909090989</v>
+        <f>O16+P16</f>
+        <v>6.955999999999996</v>
       </c>
       <c r="R16" s="12">
-        <f t="shared" si="8"/>
-        <v>111.96153599027528</v>
+        <f>MAX($Q$2:$Q$279)-Q16</f>
+        <v>107.1764450811844</v>
       </c>
       <c r="S16" s="9">
-        <f t="shared" si="9"/>
-        <v>8.931638809303739E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R16)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>9.3304083676456744E-3</v>
       </c>
       <c r="T16" s="9">
-        <f t="shared" si="10"/>
-        <v>0.78172658156501729</v>
+        <f>R16/MAX($R$2:$R$28)</f>
+        <v>0.74831660084479601</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17" t="s">
-        <v>59</v>
+        <v>40</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>91</v>
       </c>
       <c r="D17" s="8">
-        <v>45580</v>
+        <v>45627</v>
       </c>
       <c r="E17" s="2">
-        <v>0.25669999999999998</v>
+        <v>0.27450000000000002</v>
       </c>
       <c r="F17" s="1">
-        <v>132.38999999999999</v>
+        <v>39.799999999999997</v>
       </c>
       <c r="G17" s="1">
-        <f t="shared" si="0"/>
-        <v>33.984512999999993</v>
+        <f>E17*F17</f>
+        <v>10.9251</v>
       </c>
       <c r="H17" s="13">
-        <v>7.0000000000000007E-2</v>
+        <v>0.1</v>
       </c>
       <c r="I17" s="11">
-        <v>0.1623</v>
+        <v>0.2</v>
       </c>
       <c r="J17" s="9">
-        <f t="shared" si="1"/>
-        <v>0.43130006161429457</v>
+        <f>IFERROR(H17/I17,"")</f>
+        <v>0.5</v>
       </c>
       <c r="K17" s="9">
-        <f t="shared" si="2"/>
-        <v>2.1950858781039705E-2</v>
+        <f>IFERROR(J17/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>2.5447317001162453E-2</v>
       </c>
       <c r="L17" s="12">
-        <f t="shared" si="11"/>
-        <v>141.65729999999999</v>
+        <f>F17/(1-(F17*(1+H17)-F17)/(F17*(1+H17)))</f>
+        <v>43.78</v>
       </c>
       <c r="M17" s="12">
-        <f t="shared" si="3"/>
-        <v>36.363428909999996</v>
+        <f>L17*E17</f>
+        <v>12.017610000000001</v>
       </c>
       <c r="N17" s="12">
-        <f t="shared" si="4"/>
-        <v>121.20296621807194</v>
+        <f>F17/(1+I17-H17)</f>
+        <v>36.181818181818187</v>
       </c>
       <c r="O17" s="12">
-        <f t="shared" si="5"/>
-        <v>9.2673000000000059</v>
+        <f>L17-F17</f>
+        <v>3.980000000000004</v>
       </c>
       <c r="P17" s="12">
-        <f t="shared" si="6"/>
-        <v>-5.5935168909640254</v>
+        <f>0.5*(N17-F17)</f>
+        <v>-1.8090909090909051</v>
       </c>
       <c r="Q17" s="15">
-        <f t="shared" si="7"/>
-        <v>3.6737831090359805</v>
+        <f>O17+P17</f>
+        <v>2.1709090909090989</v>
       </c>
       <c r="R17" s="12">
-        <f t="shared" si="8"/>
-        <v>110.45866197214841</v>
+        <f>MAX($Q$2:$Q$279)-Q17</f>
+        <v>111.96153599027528</v>
       </c>
       <c r="S17" s="9">
-        <f t="shared" si="9"/>
-        <v>9.0531605411999731E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R17)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>8.931638809303739E-3</v>
       </c>
       <c r="T17" s="9">
-        <f t="shared" si="10"/>
-        <v>0.77123336567330925</v>
+        <f>R17/MAX($R$2:$R$28)</f>
+        <v>0.78172658156501729</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>47</v>
+        <v>39</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="D18" s="8">
-        <v>45511</v>
+        <v>45580</v>
       </c>
       <c r="E18" s="2">
-        <v>0.25169999999999998</v>
+        <v>0.25669999999999998</v>
       </c>
       <c r="F18" s="1">
-        <v>178.56</v>
+        <v>132.38999999999999</v>
       </c>
       <c r="G18" s="1">
-        <f t="shared" si="0"/>
-        <v>44.943551999999997</v>
+        <f>E18*F18</f>
+        <v>33.984512999999993</v>
       </c>
       <c r="H18" s="13">
-        <f>196.02/F18-1</f>
-        <v>9.7782258064516236E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I18" s="11">
-        <v>0.52980000000000005</v>
+        <v>0.1623</v>
       </c>
       <c r="J18" s="9">
-        <f t="shared" si="1"/>
-        <v>0.18456447350795815</v>
+        <f>IFERROR(H18/I18,"")</f>
+        <v>0.43130006161429457</v>
       </c>
       <c r="K18" s="9">
-        <f t="shared" si="2"/>
-        <v>9.3933413290193217E-3</v>
+        <f>IFERROR(J18/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>2.1950858781039705E-2</v>
       </c>
       <c r="L18" s="12">
-        <f t="shared" si="11"/>
-        <v>196.02</v>
+        <f>F18/(1-(F18*(1+H18)-F18)/(F18*(1+H18)))</f>
+        <v>141.65729999999999</v>
       </c>
       <c r="M18" s="12">
-        <f t="shared" si="3"/>
-        <v>49.338234</v>
+        <f>L18*E18</f>
+        <v>36.363428909999996</v>
       </c>
       <c r="N18" s="12">
-        <f t="shared" si="4"/>
-        <v>124.69119255370553</v>
+        <f>F18/(1+I18-H18)</f>
+        <v>121.20296621807194</v>
       </c>
       <c r="O18" s="12">
-        <f t="shared" si="5"/>
-        <v>17.460000000000008</v>
+        <f>L18-F18</f>
+        <v>9.2673000000000059</v>
       </c>
       <c r="P18" s="12">
-        <f t="shared" si="6"/>
-        <v>-26.934403723147234</v>
+        <f>0.5*(N18-F18)</f>
+        <v>-5.5935168909640254</v>
       </c>
       <c r="Q18" s="15">
-        <f t="shared" si="7"/>
-        <v>-9.4744037231472262</v>
+        <f>O18+P18</f>
+        <v>3.6737831090359805</v>
       </c>
       <c r="R18" s="12">
-        <f t="shared" si="8"/>
-        <v>123.60684880433161</v>
+        <f>MAX($Q$2:$Q$279)-Q18</f>
+        <v>110.45866197214841</v>
       </c>
       <c r="S18" s="9">
-        <f t="shared" si="9"/>
-        <v>8.0901666022000929E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R18)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>9.0531605411999748E-3</v>
       </c>
       <c r="T18" s="9">
-        <f t="shared" si="10"/>
-        <v>0.86303531404059042</v>
+        <f>R18/MAX($R$2:$R$28)</f>
+        <v>0.77123336567330925</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="C19" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D19" s="8">
-        <v>45580</v>
+        <v>45511</v>
       </c>
       <c r="E19" s="2">
-        <v>0.19139999999999999</v>
+        <v>0.25169999999999998</v>
       </c>
       <c r="F19" s="1">
-        <v>135.82</v>
+        <v>178.56</v>
       </c>
       <c r="G19" s="1">
-        <f t="shared" si="0"/>
-        <v>25.995947999999999</v>
+        <f>E19*F19</f>
+        <v>44.943551999999997</v>
       </c>
       <c r="H19" s="13">
-        <v>0.1202</v>
+        <f>196.02/F19-1</f>
+        <v>9.7782258064516236E-2</v>
       </c>
       <c r="I19" s="11">
-        <v>0.33710000000000001</v>
+        <v>0.52980000000000005</v>
       </c>
       <c r="J19" s="9">
-        <f t="shared" si="1"/>
-        <v>0.35657075051913378</v>
+        <f>IFERROR(H19/I19,"")</f>
+        <v>0.18456447350795815</v>
       </c>
       <c r="K19" s="9">
-        <f t="shared" si="2"/>
-        <v>1.8147537843605618E-2</v>
+        <f>IFERROR(J19/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <v>9.3933413290193217E-3</v>
       </c>
       <c r="L19" s="12">
-        <f t="shared" si="11"/>
-        <v>152.14556400000001</v>
+        <f>F19/(1-(F19*(1+H19)-F19)/(F19*(1+H19)))</f>
+        <v>196.02</v>
       </c>
       <c r="M19" s="12">
-        <f t="shared" si="3"/>
-        <v>29.120660949599998</v>
+        <f>L19*E19</f>
+        <v>49.338234</v>
       </c>
       <c r="N19" s="12">
-        <f t="shared" si="4"/>
-        <v>111.61147177253677</v>
+        <f>F19/(1+I19-H19)</f>
+        <v>124.69119255370553</v>
       </c>
       <c r="O19" s="12">
-        <f t="shared" si="5"/>
-        <v>16.325564000000014</v>
+        <f>L19-F19</f>
+        <v>17.460000000000008</v>
       </c>
       <c r="P19" s="12">
-        <f t="shared" si="6"/>
-        <v>-12.10426411373161</v>
+        <f>0.5*(N19-F19)</f>
+        <v>-26.934403723147234</v>
       </c>
       <c r="Q19" s="15">
-        <f t="shared" si="7"/>
-        <v>4.2212998862684046</v>
+        <f>O19+P19</f>
+        <v>-9.4744037231472262</v>
       </c>
       <c r="R19" s="12">
-        <f t="shared" si="8"/>
-        <v>109.91114519491597</v>
+        <f>MAX($Q$2:$Q$279)-Q19</f>
+        <v>123.60684880433161</v>
       </c>
       <c r="S19" s="9">
-        <f t="shared" si="9"/>
-        <v>9.0982583997883393E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R19)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>8.0901666022000929E-3</v>
       </c>
       <c r="T19" s="9">
-        <f t="shared" si="10"/>
-        <v>0.76741054907089512</v>
+        <f>R19/MAX($R$2:$R$28)</f>
+        <v>0.86303531404059042</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -3819,7 +3819,7 @@
         <v>227.38</v>
       </c>
       <c r="G20" s="1">
-        <f t="shared" si="0"/>
+        <f>E20*F20</f>
         <v>42.792915999999998</v>
       </c>
       <c r="H20" s="13">
@@ -3829,47 +3829,47 @@
         <v>0.2271</v>
       </c>
       <c r="J20" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H20/I20,"")</f>
         <v>0.66050198150594452</v>
       </c>
       <c r="K20" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J20/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>3.3616006606555421E-2</v>
       </c>
       <c r="L20" s="12">
-        <f t="shared" si="11"/>
+        <f>F20/(1-(F20*(1+H20)-F20)/(F20*(1+H20)))</f>
         <v>261.48699999999997</v>
       </c>
       <c r="M20" s="12">
-        <f t="shared" si="3"/>
+        <f>L20*E20</f>
         <v>49.211853399999995</v>
       </c>
       <c r="N20" s="12">
-        <f t="shared" si="4"/>
+        <f>F20/(1+I20-H20)</f>
         <v>211.10389007520189</v>
       </c>
       <c r="O20" s="12">
-        <f t="shared" si="5"/>
+        <f>L20-F20</f>
         <v>34.106999999999971</v>
       </c>
       <c r="P20" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N20-F20)</f>
         <v>-8.1380549623990532</v>
       </c>
       <c r="Q20" s="15">
-        <f t="shared" si="7"/>
+        <f>O20+P20</f>
         <v>25.968945037600918</v>
       </c>
       <c r="R20" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q20</f>
         <v>88.163500043583468</v>
       </c>
       <c r="S20" s="9">
-        <f t="shared" si="9"/>
-        <v>1.1342562392664218E-2</v>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R20)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>1.1342562392664219E-2</v>
       </c>
       <c r="T20" s="9">
-        <f t="shared" si="10"/>
+        <f>R20/MAX($R$2:$R$28)</f>
         <v>0.6155663272953309</v>
       </c>
     </row>
@@ -3893,7 +3893,7 @@
         <v>423.77</v>
       </c>
       <c r="G21" s="1">
-        <f t="shared" si="0"/>
+        <f>E21*F21</f>
         <v>56.658049000000005</v>
       </c>
       <c r="H21" s="13">
@@ -3903,47 +3903,47 @@
         <v>0.1963</v>
       </c>
       <c r="J21" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H21/I21,"")</f>
         <v>0.76413652572592972</v>
       </c>
       <c r="K21" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J21/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>3.8890448804629323E-2</v>
       </c>
       <c r="L21" s="12">
-        <f t="shared" si="11"/>
+        <f>F21/(1-(F21*(1+H21)-F21)/(F21*(1+H21)))</f>
         <v>487.33549999999991</v>
       </c>
       <c r="M21" s="12">
-        <f t="shared" si="3"/>
+        <f>L21*E21</f>
         <v>65.156756349999995</v>
       </c>
       <c r="N21" s="12">
-        <f t="shared" si="4"/>
+        <f>F21/(1+I21-H21)</f>
         <v>405.01768135334032</v>
       </c>
       <c r="O21" s="12">
-        <f t="shared" si="5"/>
+        <f>L21-F21</f>
         <v>63.565499999999929</v>
       </c>
       <c r="P21" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N21-F21)</f>
         <v>-9.3761593233298299</v>
       </c>
       <c r="Q21" s="15">
-        <f t="shared" si="7"/>
+        <f>O21+P21</f>
         <v>54.189340676670099</v>
       </c>
       <c r="R21" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q21</f>
         <v>59.943104404514287</v>
       </c>
       <c r="S21" s="9">
-        <f t="shared" si="9"/>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R21)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>1.6682485999585474E-2</v>
       </c>
       <c r="T21" s="9">
-        <f t="shared" si="10"/>
+        <f>R21/MAX($R$2:$R$28)</f>
         <v>0.41852871774290379</v>
       </c>
     </row>
@@ -3967,7 +3967,7 @@
         <v>501.56</v>
       </c>
       <c r="G22" s="1">
-        <f t="shared" si="0"/>
+        <f>E22*F22</f>
         <v>64.901863999999989</v>
       </c>
       <c r="H22" s="13">
@@ -3977,47 +3977,47 @@
         <v>0.29699999999999999</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H22/I22,"")</f>
         <v>0.84175084175084181</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J22/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>4.2840601012058006E-2</v>
       </c>
       <c r="L22" s="12">
-        <f t="shared" si="11"/>
+        <f>F22/(1-(F22*(1+H22)-F22)/(F22*(1+H22)))</f>
         <v>626.95000000000005</v>
       </c>
       <c r="M22" s="12">
-        <f t="shared" si="3"/>
+        <f>L22*E22</f>
         <v>81.127330000000001</v>
       </c>
       <c r="N22" s="12">
-        <f t="shared" si="4"/>
+        <f>F22/(1+I22-H22)</f>
         <v>479.04489016236869</v>
       </c>
       <c r="O22" s="12">
-        <f t="shared" si="5"/>
+        <f>L22-F22</f>
         <v>125.39000000000004</v>
       </c>
       <c r="P22" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N22-F22)</f>
         <v>-11.257554918815657</v>
       </c>
       <c r="Q22" s="15">
-        <f t="shared" si="7"/>
+        <f>O22+P22</f>
         <v>114.13244508118439</v>
       </c>
       <c r="R22" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q22</f>
         <v>0</v>
       </c>
       <c r="S22" s="9">
-        <f t="shared" si="9"/>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R22)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>0</v>
       </c>
       <c r="T22" s="9">
-        <f t="shared" si="10"/>
+        <f>R22/MAX($R$2:$R$28)</f>
         <v>0</v>
       </c>
     </row>
@@ -4041,7 +4041,7 @@
         <v>10.92</v>
       </c>
       <c r="G23" s="1">
-        <f t="shared" si="0"/>
+        <f>E23*F23</f>
         <v>1.092E-18</v>
       </c>
       <c r="H23" s="13">
@@ -4051,47 +4051,47 @@
         <v>1.8652</v>
       </c>
       <c r="J23" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H23/I23,"")</f>
         <v>0.53613553506326406</v>
       </c>
       <c r="K23" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J23/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>2.7286421832685457E-2</v>
       </c>
       <c r="L23" s="12">
-        <f t="shared" si="11"/>
+        <f>F23/(1-(F23*(1+H23)-F23)/(F23*(1+H23)))</f>
         <v>21.84</v>
       </c>
       <c r="M23" s="12">
-        <f t="shared" si="3"/>
+        <f>L23*E23</f>
         <v>2.1840000000000001E-18</v>
       </c>
       <c r="N23" s="12">
-        <f t="shared" si="4"/>
+        <f>F23/(1+I23-H23)</f>
         <v>5.8546000428908433</v>
       </c>
       <c r="O23" s="12">
-        <f t="shared" si="5"/>
+        <f>L23-F23</f>
         <v>10.92</v>
       </c>
       <c r="P23" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N23-F23)</f>
         <v>-2.5326999785545783</v>
       </c>
       <c r="Q23" s="15">
-        <f t="shared" si="7"/>
+        <f>O23+P23</f>
         <v>8.3873000214454212</v>
       </c>
       <c r="R23" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q23</f>
         <v>105.74514505973896</v>
       </c>
       <c r="S23" s="9">
-        <f t="shared" si="9"/>
-        <v>9.4566989286843078E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R23)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>9.456698928684306E-3</v>
       </c>
       <c r="T23" s="9">
-        <f t="shared" si="10"/>
+        <f>R23/MAX($R$2:$R$28)</f>
         <v>0.73832312171768166</v>
       </c>
     </row>
@@ -4115,7 +4115,7 @@
         <v>283.43</v>
       </c>
       <c r="G24" s="1">
-        <f t="shared" si="0"/>
+        <f>E24*F24</f>
         <v>2.8342999999999998E-17</v>
       </c>
       <c r="H24" s="13">
@@ -4125,47 +4125,47 @@
         <v>0.26</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H24/I24,"")</f>
         <v>0.96153846153846145</v>
       </c>
       <c r="K24" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J24/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>4.8937148079158561E-2</v>
       </c>
       <c r="L24" s="12">
-        <f t="shared" si="11"/>
+        <f>F24/(1-(F24*(1+H24)-F24)/(F24*(1+H24)))</f>
         <v>354.28750000000002</v>
       </c>
       <c r="M24" s="12">
-        <f t="shared" si="3"/>
+        <f>L24*E24</f>
         <v>3.542875E-17</v>
       </c>
       <c r="N24" s="12">
-        <f t="shared" si="4"/>
+        <f>F24/(1+I24-H24)</f>
         <v>280.62376237623761</v>
       </c>
       <c r="O24" s="12">
-        <f t="shared" si="5"/>
+        <f>L24-F24</f>
         <v>70.857500000000016</v>
       </c>
       <c r="P24" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N24-F24)</f>
         <v>-1.4031188118811997</v>
       </c>
       <c r="Q24" s="15">
-        <f t="shared" si="7"/>
+        <f>O24+P24</f>
         <v>69.454381188118816</v>
       </c>
       <c r="R24" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q24</f>
         <v>44.67806389306557</v>
       </c>
       <c r="S24" s="9">
-        <f t="shared" si="9"/>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R24)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>2.2382348581474875E-2</v>
       </c>
       <c r="T24" s="9">
-        <f t="shared" si="10"/>
+        <f>R24/MAX($R$2:$R$28)</f>
         <v>0.311946686414727</v>
       </c>
     </row>
@@ -4189,7 +4189,7 @@
         <v>188.12</v>
       </c>
       <c r="G25" s="1">
-        <f t="shared" si="0"/>
+        <f>E25*F25</f>
         <v>1.8812000000000001E-17</v>
       </c>
       <c r="H25" s="13">
@@ -4199,47 +4199,47 @@
         <v>0.37780000000000002</v>
       </c>
       <c r="J25" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H25/I25,"")</f>
         <v>0.39703546850185278</v>
       </c>
       <c r="K25" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J25/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>2.0206974855343396E-2</v>
       </c>
       <c r="L25" s="12">
-        <f t="shared" si="11"/>
+        <f>F25/(1-(F25*(1+H25)-F25)/(F25*(1+H25)))</f>
         <v>216.33799999999999</v>
       </c>
       <c r="M25" s="12">
-        <f t="shared" si="3"/>
+        <f>L25*E25</f>
         <v>2.16338E-17</v>
       </c>
       <c r="N25" s="12">
-        <f t="shared" si="4"/>
+        <f>F25/(1+I25-H25)</f>
         <v>153.21713634142367</v>
       </c>
       <c r="O25" s="12">
-        <f t="shared" si="5"/>
+        <f>L25-F25</f>
         <v>28.217999999999989</v>
       </c>
       <c r="P25" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N25-F25)</f>
         <v>-17.451431829288168</v>
       </c>
       <c r="Q25" s="15">
-        <f t="shared" si="7"/>
+        <f>O25+P25</f>
         <v>10.766568170711821</v>
       </c>
       <c r="R25" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q25</f>
         <v>103.36587691047256</v>
       </c>
       <c r="S25" s="9">
-        <f t="shared" si="9"/>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R25)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>9.674372528819369E-3</v>
       </c>
       <c r="T25" s="9">
-        <f t="shared" si="10"/>
+        <f>R25/MAX($R$2:$R$28)</f>
         <v>0.72171083482377829</v>
       </c>
     </row>
@@ -4263,7 +4263,7 @@
         <v>167.24</v>
       </c>
       <c r="G26" s="1">
-        <f t="shared" si="0"/>
+        <f>E26*F26</f>
         <v>1.6724000000000001E-17</v>
       </c>
       <c r="H26" s="13">
@@ -4274,47 +4274,47 @@
         <v>0.26790000000000003</v>
       </c>
       <c r="J26" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H26/I26,"")</f>
         <v>0.51714598979956872</v>
       </c>
       <c r="K26" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J26/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>2.6319955876619099E-2</v>
       </c>
       <c r="L26" s="12">
-        <f t="shared" si="11"/>
+        <f>F26/(1-(F26*(1+H26)-F26)/(F26*(1+H26)))</f>
         <v>190.41</v>
       </c>
       <c r="M26" s="12">
-        <f t="shared" si="3"/>
+        <f>L26*E26</f>
         <v>1.9040999999999999E-17</v>
       </c>
       <c r="N26" s="12">
-        <f t="shared" si="4"/>
+        <f>F26/(1+I26-H26)</f>
         <v>148.08431772538498</v>
       </c>
       <c r="O26" s="12">
-        <f t="shared" si="5"/>
+        <f>L26-F26</f>
         <v>23.169999999999987</v>
       </c>
       <c r="P26" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N26-F26)</f>
         <v>-9.5778411373075159</v>
       </c>
       <c r="Q26" s="15">
-        <f t="shared" si="7"/>
+        <f>O26+P26</f>
         <v>13.592158862692472</v>
       </c>
       <c r="R26" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q26</f>
         <v>100.54028621849191</v>
       </c>
       <c r="S26" s="9">
-        <f t="shared" si="9"/>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R26)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>9.9462617186788418E-3</v>
       </c>
       <c r="T26" s="9">
-        <f t="shared" si="10"/>
+        <f>R26/MAX($R$2:$R$28)</f>
         <v>0.70198227953907921</v>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
         <v>668.82</v>
       </c>
       <c r="G27" s="1">
-        <f t="shared" si="0"/>
+        <f>E27*F27</f>
         <v>6.6881999999999999E-17</v>
       </c>
       <c r="H27" s="13">
@@ -4348,47 +4348,47 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="J27" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H27/I27,"")</f>
         <v>0.17857142857142858</v>
       </c>
       <c r="K27" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J27/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>9.0883275004151626E-3</v>
       </c>
       <c r="L27" s="12">
-        <f t="shared" si="11"/>
+        <f>F27/(1-(F27*(1+H27)-F27)/(F27*(1+H27)))</f>
         <v>702.26100000000008</v>
       </c>
       <c r="M27" s="12">
-        <f t="shared" si="3"/>
+        <f>L27*E27</f>
         <v>7.0226100000000009E-17</v>
       </c>
       <c r="N27" s="12">
-        <f t="shared" si="4"/>
+        <f>F27/(1+I27-H27)</f>
         <v>543.7560975609756</v>
       </c>
       <c r="O27" s="12">
-        <f t="shared" si="5"/>
+        <f>L27-F27</f>
         <v>33.441000000000031</v>
       </c>
       <c r="P27" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N27-F27)</f>
         <v>-62.531951219512223</v>
       </c>
       <c r="Q27" s="15">
-        <f t="shared" si="7"/>
+        <f>O27+P27</f>
         <v>-29.090951219512192</v>
       </c>
       <c r="R27" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q27</f>
         <v>143.22339630069658</v>
       </c>
       <c r="S27" s="9">
-        <f t="shared" si="9"/>
-        <v>6.9820994741704541E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R27)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>6.9820994741704523E-3</v>
       </c>
       <c r="T27" s="9">
-        <f t="shared" si="10"/>
+        <f>R27/MAX($R$2:$R$28)</f>
         <v>1</v>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
         <v>700.32</v>
       </c>
       <c r="G28" s="1">
-        <f t="shared" si="0"/>
+        <f>E28*F28</f>
         <v>7.0031999999999998E-17</v>
       </c>
       <c r="H28" s="13">
@@ -4422,47 +4422,47 @@
         <v>0.45340000000000003</v>
       </c>
       <c r="J28" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H28/I28,"")</f>
         <v>0.22055580061755625</v>
       </c>
       <c r="K28" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J28/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>1.1225106749520271E-2</v>
       </c>
       <c r="L28" s="12">
-        <f t="shared" si="11"/>
+        <f>F28/(1-(F28*(1+H28)-F28)/(F28*(1+H28)))</f>
         <v>770.35200000000009</v>
       </c>
       <c r="M28" s="12">
-        <f t="shared" si="3"/>
+        <f>L28*E28</f>
         <v>7.7035200000000004E-17</v>
       </c>
       <c r="N28" s="12">
-        <f t="shared" si="4"/>
+        <f>F28/(1+I28-H28)</f>
         <v>517.45234224915032</v>
       </c>
       <c r="O28" s="12">
-        <f t="shared" si="5"/>
+        <f>L28-F28</f>
         <v>70.032000000000039</v>
       </c>
       <c r="P28" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N28-F28)</f>
         <v>-91.433828875424865</v>
       </c>
       <c r="Q28" s="15">
-        <f t="shared" si="7"/>
+        <f>O28+P28</f>
         <v>-21.401828875424826</v>
       </c>
       <c r="R28" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q28</f>
         <v>135.53427395660921</v>
       </c>
       <c r="S28" s="9">
-        <f t="shared" si="9"/>
-        <v>7.3782075249847591E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R28)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>7.37820752498476E-3</v>
       </c>
       <c r="T28" s="9">
-        <f t="shared" si="10"/>
+        <f>R28/MAX($R$2:$R$28)</f>
         <v>0.94631378292451529</v>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
         <v>147.01</v>
       </c>
       <c r="G29" s="1">
-        <f t="shared" si="0"/>
+        <f>E29*F29</f>
         <v>1.4700999999999999E-17</v>
       </c>
       <c r="H29" s="13">
@@ -4496,47 +4496,47 @@
         <v>0.52380000000000004</v>
       </c>
       <c r="J29" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H29/I29,"")</f>
         <v>0.28636884306987398</v>
       </c>
       <c r="K29" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J29/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>1.4574637457710454E-2</v>
       </c>
       <c r="L29" s="12">
-        <f t="shared" si="11"/>
+        <f>F29/(1-(F29*(1+H29)-F29)/(F29*(1+H29)))</f>
         <v>169.06149999999997</v>
       </c>
       <c r="M29" s="12">
-        <f t="shared" si="3"/>
+        <f>L29*E29</f>
         <v>1.6906149999999997E-17</v>
       </c>
       <c r="N29" s="12">
-        <f t="shared" si="4"/>
+        <f>F29/(1+I29-H29)</f>
         <v>107.00975396709855</v>
       </c>
       <c r="O29" s="12">
-        <f t="shared" si="5"/>
+        <f>L29-F29</f>
         <v>22.051499999999976</v>
       </c>
       <c r="P29" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N29-F29)</f>
         <v>-20.000123016450722</v>
       </c>
       <c r="Q29" s="15">
-        <f t="shared" si="7"/>
+        <f>O29+P29</f>
         <v>2.0513769835492539</v>
       </c>
       <c r="R29" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q29</f>
         <v>112.08106809763513</v>
       </c>
       <c r="S29" s="9">
-        <f t="shared" si="9"/>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R29)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>8.9221134039237406E-3</v>
       </c>
       <c r="T29" s="9">
-        <f t="shared" si="10"/>
+        <f>R29/MAX($R$2:$R$28)</f>
         <v>0.78256116662896091</v>
       </c>
     </row>
@@ -4560,7 +4560,7 @@
         <v>169.34</v>
       </c>
       <c r="G30" s="1">
-        <f t="shared" si="0"/>
+        <f>E30*F30</f>
         <v>1.6933999999999999E-17</v>
       </c>
       <c r="H30" s="13">
@@ -4570,47 +4570,47 @@
         <v>0.4259</v>
       </c>
       <c r="J30" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H30/I30,"")</f>
         <v>0.23479690068091102</v>
       </c>
       <c r="K30" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J30/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>1.1949902325035199E-2</v>
       </c>
       <c r="L30" s="12">
-        <f t="shared" si="11"/>
+        <f>F30/(1-(F30*(1+H30)-F30)/(F30*(1+H30)))</f>
         <v>186.27400000000003</v>
       </c>
       <c r="M30" s="12">
-        <f t="shared" si="3"/>
+        <f>L30*E30</f>
         <v>1.8627400000000003E-17</v>
       </c>
       <c r="N30" s="12">
-        <f t="shared" si="4"/>
+        <f>F30/(1+I30-H30)</f>
         <v>127.71702239987934</v>
       </c>
       <c r="O30" s="12">
-        <f t="shared" si="5"/>
+        <f>L30-F30</f>
         <v>16.934000000000026</v>
       </c>
       <c r="P30" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N30-F30)</f>
         <v>-20.811488800060332</v>
       </c>
       <c r="Q30" s="15">
-        <f t="shared" si="7"/>
+        <f>O30+P30</f>
         <v>-3.8774888000603056</v>
       </c>
       <c r="R30" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q30</f>
         <v>118.00993388124469</v>
       </c>
       <c r="S30" s="9">
-        <f t="shared" si="9"/>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R30)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>8.4738628953585898E-3</v>
       </c>
       <c r="T30" s="9">
-        <f t="shared" si="10"/>
+        <f>R30/MAX($R$2:$R$28)</f>
         <v>0.82395709729912847</v>
       </c>
     </row>
@@ -4634,7 +4634,7 @@
         <v>113.58</v>
       </c>
       <c r="G31" s="1">
-        <f t="shared" si="0"/>
+        <f>E31*F31</f>
         <v>1.1357999999999999E-17</v>
       </c>
       <c r="H31" s="13">
@@ -4645,47 +4645,47 @@
         <v>0.16439999999999999</v>
       </c>
       <c r="J31" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H31/I31,"")</f>
         <v>0.40540789496797319</v>
       </c>
       <c r="K31" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J31/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>2.0633086436047974E-2</v>
       </c>
       <c r="L31" s="12">
-        <f t="shared" si="11"/>
+        <f>F31/(1-(F31*(1+H31)-F31)/(F31*(1+H31)))</f>
         <v>121.15000000000002</v>
       </c>
       <c r="M31" s="12">
-        <f t="shared" si="3"/>
+        <f>L31*E31</f>
         <v>1.2115000000000002E-17</v>
       </c>
       <c r="N31" s="12">
-        <f t="shared" si="4"/>
+        <f>F31/(1+I31-H31)</f>
         <v>103.46609203186667</v>
       </c>
       <c r="O31" s="12">
-        <f t="shared" si="5"/>
+        <f>L31-F31</f>
         <v>7.5700000000000216</v>
       </c>
       <c r="P31" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N31-F31)</f>
         <v>-5.0569539840666664</v>
       </c>
       <c r="Q31" s="15">
-        <f t="shared" si="7"/>
+        <f>O31+P31</f>
         <v>2.5130460159333552</v>
       </c>
       <c r="R31" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q31</f>
         <v>111.61939906525103</v>
       </c>
       <c r="S31" s="9">
-        <f t="shared" si="9"/>
-        <v>8.9590161600441413E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R31)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>8.9590161600441431E-3</v>
       </c>
       <c r="T31" s="9">
-        <f t="shared" si="10"/>
+        <f>R31/MAX($R$2:$R$28)</f>
         <v>0.77933774752071117</v>
       </c>
     </row>
@@ -4709,7 +4709,7 @@
         <v>64.349999999999994</v>
       </c>
       <c r="G32" s="1">
-        <f t="shared" si="0"/>
+        <f>E32*F32</f>
         <v>6.4349999999999993E-18</v>
       </c>
       <c r="H32" s="13">
@@ -4719,47 +4719,47 @@
         <v>0.67300000000000004</v>
       </c>
       <c r="J32" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H32/I32,"")</f>
         <v>0.22288261515601782</v>
       </c>
       <c r="K32" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J32/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>1.1343529123846561E-2</v>
       </c>
       <c r="L32" s="12">
-        <f t="shared" si="11"/>
+        <f>F32/(1-(F32*(1+H32)-F32)/(F32*(1+H32)))</f>
         <v>74.002499999999984</v>
       </c>
       <c r="M32" s="12">
-        <f t="shared" si="3"/>
+        <f>L32*E32</f>
         <v>7.4002499999999988E-18</v>
       </c>
       <c r="N32" s="12">
-        <f t="shared" si="4"/>
+        <f>F32/(1+I32-H32)</f>
         <v>42.252133946158892</v>
       </c>
       <c r="O32" s="12">
-        <f t="shared" si="5"/>
+        <f>L32-F32</f>
         <v>9.6524999999999892</v>
       </c>
       <c r="P32" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N32-F32)</f>
         <v>-11.048933026920551</v>
       </c>
       <c r="Q32" s="15">
-        <f t="shared" si="7"/>
+        <f>O32+P32</f>
         <v>-1.3964330269205618</v>
       </c>
       <c r="R32" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q32</f>
         <v>115.52887810810495</v>
       </c>
       <c r="S32" s="9">
-        <f t="shared" si="9"/>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R32)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>8.6558444639638962E-3</v>
       </c>
       <c r="T32" s="9">
-        <f t="shared" si="10"/>
+        <f>R32/MAX($R$2:$R$28)</f>
         <v>0.80663411909010196</v>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
         <v>20.82</v>
       </c>
       <c r="G33" s="1">
-        <f t="shared" si="0"/>
+        <f>E33*F33</f>
         <v>2.0820000000000002E-18</v>
       </c>
       <c r="H33" s="13">
@@ -4793,47 +4793,47 @@
         <v>0.7389</v>
       </c>
       <c r="J33" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H33/I33,"")</f>
         <v>6.7668155366084726E-2</v>
       </c>
       <c r="K33" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J33/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>3.4439460009693403E-3</v>
       </c>
       <c r="L33" s="12">
-        <f t="shared" si="11"/>
+        <f>F33/(1-(F33*(1+H33)-F33)/(F33*(1+H33)))</f>
         <v>21.861000000000001</v>
       </c>
       <c r="M33" s="12">
-        <f t="shared" si="3"/>
+        <f>L33*E33</f>
         <v>2.1860999999999999E-18</v>
       </c>
       <c r="N33" s="12">
-        <f t="shared" si="4"/>
+        <f>F33/(1+I33-H33)</f>
         <v>12.327550476641601</v>
       </c>
       <c r="O33" s="12">
-        <f t="shared" si="5"/>
+        <f>L33-F33</f>
         <v>1.0410000000000004</v>
       </c>
       <c r="P33" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N33-F33)</f>
         <v>-4.2462247616791995</v>
       </c>
       <c r="Q33" s="15">
-        <f t="shared" si="7"/>
+        <f>O33+P33</f>
         <v>-3.2052247616791991</v>
       </c>
       <c r="R33" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q33</f>
         <v>117.33766984286359</v>
       </c>
       <c r="S33" s="9">
-        <f t="shared" si="9"/>
-        <v>8.5224122938454567E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R33)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>8.5224122938454584E-3</v>
       </c>
       <c r="T33" s="9">
-        <f t="shared" si="10"/>
+        <f>R33/MAX($R$2:$R$28)</f>
         <v>0.81926328291024408</v>
       </c>
     </row>
@@ -4857,7 +4857,7 @@
         <v>13.04</v>
       </c>
       <c r="G34" s="1">
-        <f t="shared" si="0"/>
+        <f>E34*F34</f>
         <v>1.304E-18</v>
       </c>
       <c r="H34" s="13">
@@ -4868,47 +4868,47 @@
         <v>0.30159999999999998</v>
       </c>
       <c r="J34" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H34/I34,"")</f>
         <v>0.17290198694895167</v>
       </c>
       <c r="K34" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J34/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>8.7997833440416531E-3</v>
       </c>
       <c r="L34" s="12">
-        <f t="shared" si="11"/>
+        <f>F34/(1-(F34*(1+H34)-F34)/(F34*(1+H34)))</f>
         <v>13.72</v>
       </c>
       <c r="M34" s="12">
-        <f t="shared" si="3"/>
+        <f>L34*E34</f>
         <v>1.3720000000000001E-18</v>
       </c>
       <c r="N34" s="12">
-        <f t="shared" si="4"/>
+        <f>F34/(1+I34-H34)</f>
         <v>10.436569040286594</v>
       </c>
       <c r="O34" s="12">
-        <f t="shared" si="5"/>
+        <f>L34-F34</f>
         <v>0.68000000000000149</v>
       </c>
       <c r="P34" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N34-F34)</f>
         <v>-1.3017154798567026</v>
       </c>
       <c r="Q34" s="15">
-        <f t="shared" si="7"/>
+        <f>O34+P34</f>
         <v>-0.62171547985670106</v>
       </c>
       <c r="R34" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q34</f>
         <v>114.75416056104109</v>
       </c>
       <c r="S34" s="9">
-        <f t="shared" si="9"/>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R34)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>8.7142809908671744E-3</v>
       </c>
       <c r="T34" s="9">
-        <f t="shared" si="10"/>
+        <f>R34/MAX($R$2:$R$28)</f>
         <v>0.80122496411211674</v>
       </c>
     </row>
@@ -4932,7 +4932,7 @@
         <v>11.05</v>
       </c>
       <c r="G35" s="1">
-        <f t="shared" si="0"/>
+        <f>E35*F35</f>
         <v>1.1050000000000001E-18</v>
       </c>
       <c r="H35" s="13">
@@ -4942,47 +4942,47 @@
         <v>0.72170000000000001</v>
       </c>
       <c r="J35" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H35/I35,"")</f>
         <v>6.9280864625190522E-2</v>
       </c>
       <c r="K35" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J35/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>3.5260242484636906E-3</v>
       </c>
       <c r="L35" s="12">
-        <f t="shared" si="11"/>
+        <f>F35/(1-(F35*(1+H35)-F35)/(F35*(1+H35)))</f>
         <v>11.602500000000001</v>
       </c>
       <c r="M35" s="12">
-        <f t="shared" si="3"/>
+        <f>L35*E35</f>
         <v>1.16025E-18</v>
       </c>
       <c r="N35" s="12">
-        <f t="shared" si="4"/>
+        <f>F35/(1+I35-H35)</f>
         <v>6.6100376861877139</v>
       </c>
       <c r="O35" s="12">
-        <f t="shared" si="5"/>
+        <f>L35-F35</f>
         <v>0.55250000000000021</v>
       </c>
       <c r="P35" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N35-F35)</f>
         <v>-2.2199811569061434</v>
       </c>
       <c r="Q35" s="15">
-        <f t="shared" si="7"/>
+        <f>O35+P35</f>
         <v>-1.6674811569061432</v>
       </c>
       <c r="R35" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q35</f>
         <v>115.79992623809053</v>
       </c>
       <c r="S35" s="9">
-        <f t="shared" si="9"/>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R35)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>8.6355840844315329E-3</v>
       </c>
       <c r="T35" s="9">
-        <f t="shared" si="10"/>
+        <f>R35/MAX($R$2:$R$28)</f>
         <v>0.80852660409594923</v>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
         <v>2742.9</v>
       </c>
       <c r="G36" s="1">
-        <f t="shared" si="0"/>
+        <f>E36*F36</f>
         <v>2.7429000000000002E-16</v>
       </c>
       <c r="H36" s="13">
@@ -5017,47 +5017,47 @@
         <v>0.5</v>
       </c>
       <c r="J36" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H36/I36,"")</f>
         <v>0.2</v>
       </c>
       <c r="K36" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J36/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>1.0178926800464982E-2</v>
       </c>
       <c r="L36" s="12">
-        <f t="shared" si="11"/>
+        <f>F36/(1-(F36*(1+H36)-F36)/(F36*(1+H36)))</f>
         <v>3017.1900000000005</v>
       </c>
       <c r="M36" s="12">
-        <f t="shared" si="3"/>
+        <f>L36*E36</f>
         <v>3.0171900000000003E-16</v>
       </c>
       <c r="N36" s="12">
-        <f t="shared" si="4"/>
+        <f>F36/(1+I36-H36)</f>
         <v>1959.214285714286</v>
       </c>
       <c r="O36" s="12">
-        <f t="shared" si="5"/>
+        <f>L36-F36</f>
         <v>274.29000000000042</v>
       </c>
       <c r="P36" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N36-F36)</f>
         <v>-391.84285714285704</v>
       </c>
       <c r="Q36" s="15">
-        <f t="shared" si="7"/>
+        <f>O36+P36</f>
         <v>-117.55285714285662</v>
       </c>
       <c r="R36" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q36</f>
         <v>231.68530222404101</v>
       </c>
       <c r="S36" s="9">
-        <f t="shared" si="9"/>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R36)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>4.316199562080957E-3</v>
       </c>
       <c r="T36" s="9">
-        <f t="shared" si="10"/>
+        <f>R36/MAX($R$2:$R$28)</f>
         <v>1.6176498268314992</v>
       </c>
     </row>
@@ -5081,7 +5081,7 @@
         <v>86.6</v>
       </c>
       <c r="G37" s="1">
-        <f t="shared" si="0"/>
+        <f>E37*F37</f>
         <v>8.6599999999999986E-18</v>
       </c>
       <c r="H37" s="13">
@@ -5091,47 +5091,47 @@
         <v>0.17249999999999999</v>
       </c>
       <c r="J37" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H37/I37,"")</f>
         <v>0.40579710144927544</v>
       </c>
       <c r="K37" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J37/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>2.0652894957465185E-2</v>
       </c>
       <c r="L37" s="12">
-        <f t="shared" si="11"/>
+        <f>F37/(1-(F37*(1+H37)-F37)/(F37*(1+H37)))</f>
         <v>92.662000000000006</v>
       </c>
       <c r="M37" s="12">
-        <f t="shared" si="3"/>
+        <f>L37*E37</f>
         <v>9.2662000000000008E-18</v>
       </c>
       <c r="N37" s="12">
-        <f t="shared" si="4"/>
+        <f>F37/(1+I37-H37)</f>
         <v>78.548752834467123</v>
       </c>
       <c r="O37" s="12">
-        <f t="shared" si="5"/>
+        <f>L37-F37</f>
         <v>6.0620000000000118</v>
       </c>
       <c r="P37" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N37-F37)</f>
         <v>-4.0256235827664355</v>
       </c>
       <c r="Q37" s="15">
-        <f t="shared" si="7"/>
+        <f>O37+P37</f>
         <v>2.0363764172335763</v>
       </c>
       <c r="R37" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q37</f>
         <v>112.0960686639508</v>
       </c>
       <c r="S37" s="9">
-        <f t="shared" si="9"/>
-        <v>8.9209194570227766E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R37)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>8.9209194570227784E-3</v>
       </c>
       <c r="T37" s="9">
-        <f t="shared" si="10"/>
+        <f>R37/MAX($R$2:$R$28)</f>
         <v>0.78266590207514586</v>
       </c>
     </row>
@@ -5155,7 +5155,7 @@
         <v>56</v>
       </c>
       <c r="G38" s="1">
-        <f t="shared" si="0"/>
+        <f>E38*F38</f>
         <v>5.5999999999999995E-18</v>
       </c>
       <c r="H38" s="13">
@@ -5165,47 +5165,47 @@
         <v>0.19</v>
       </c>
       <c r="J38" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H38/I38,"")</f>
         <v>0.36842105263157898</v>
       </c>
       <c r="K38" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J38/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>1.8750654632435495E-2</v>
       </c>
       <c r="L38" s="12">
-        <f t="shared" si="11"/>
+        <f>F38/(1-(F38*(1+H38)-F38)/(F38*(1+H38)))</f>
         <v>59.92</v>
       </c>
       <c r="M38" s="12">
-        <f t="shared" si="3"/>
+        <f>L38*E38</f>
         <v>5.9920000000000002E-18</v>
       </c>
       <c r="N38" s="12">
-        <f t="shared" si="4"/>
+        <f>F38/(1+I38-H38)</f>
         <v>50.000000000000007</v>
       </c>
       <c r="O38" s="12">
-        <f t="shared" si="5"/>
+        <f>L38-F38</f>
         <v>3.9200000000000017</v>
       </c>
       <c r="P38" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N38-F38)</f>
         <v>-2.9999999999999964</v>
       </c>
       <c r="Q38" s="15">
-        <f t="shared" si="7"/>
+        <f>O38+P38</f>
         <v>0.92000000000000526</v>
       </c>
       <c r="R38" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q38</f>
         <v>113.21244508118438</v>
       </c>
       <c r="S38" s="9">
-        <f t="shared" si="9"/>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R38)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>8.832951176727102E-3</v>
       </c>
       <c r="T38" s="9">
-        <f t="shared" si="10"/>
+        <f>R38/MAX($R$2:$R$28)</f>
         <v>0.79046055327088882</v>
       </c>
     </row>
@@ -5229,7 +5229,7 @@
         <v>20.399999999999999</v>
       </c>
       <c r="G39" s="1">
-        <f t="shared" si="0"/>
+        <f>E39*F39</f>
         <v>2.0399999999999999E-18</v>
       </c>
       <c r="H39" s="13">
@@ -5239,46 +5239,46 @@
         <v>0.15</v>
       </c>
       <c r="J39" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H39/I39,"")</f>
         <v>0.66666666666666674</v>
       </c>
       <c r="K39" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J39/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>3.3929756001549939E-2</v>
       </c>
       <c r="L39" s="12">
         <v>21.2</v>
       </c>
       <c r="M39" s="12">
-        <f t="shared" si="3"/>
+        <f>L39*E39</f>
         <v>2.1199999999999999E-18</v>
       </c>
       <c r="N39" s="12">
-        <f t="shared" si="4"/>
+        <f>F39/(1+I39-H39)</f>
         <v>19.428571428571431</v>
       </c>
       <c r="O39" s="12">
-        <f t="shared" si="5"/>
+        <f>L39-F39</f>
         <v>0.80000000000000071</v>
       </c>
       <c r="P39" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N39-F39)</f>
         <v>-0.48571428571428399</v>
       </c>
       <c r="Q39" s="15">
-        <f t="shared" si="7"/>
+        <f>O39+P39</f>
         <v>0.31428571428571672</v>
       </c>
       <c r="R39" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q39</f>
         <v>113.81815936689867</v>
       </c>
       <c r="S39" s="9">
-        <f t="shared" si="9"/>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R39)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>8.7859442250902055E-3</v>
       </c>
       <c r="T39" s="9">
-        <f t="shared" si="10"/>
+        <f>R39/MAX($R$2:$R$28)</f>
         <v>0.79468971066667204</v>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
         <v>47.42</v>
       </c>
       <c r="G40" s="1">
-        <f t="shared" si="0"/>
+        <f>E40*F40</f>
         <v>4.7419999999999999E-18</v>
       </c>
       <c r="H40" s="13">
@@ -5312,47 +5312,47 @@
         <v>0.4</v>
       </c>
       <c r="J40" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H40/I40,"")</f>
         <v>0.17500000000000002</v>
       </c>
       <c r="K40" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J40/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>8.90656095040686E-3</v>
       </c>
       <c r="L40" s="12">
-        <f t="shared" ref="L40:L46" si="12">F40/(1-(F40*(1+H40)-F40)/(F40*(1+H40)))</f>
+        <f>F40/(1-(F40*(1+H40)-F40)/(F40*(1+H40)))</f>
         <v>50.739400000000003</v>
       </c>
       <c r="M40" s="12">
-        <f t="shared" si="3"/>
+        <f>L40*E40</f>
         <v>5.0739400000000001E-18</v>
       </c>
       <c r="N40" s="12">
-        <f t="shared" si="4"/>
+        <f>F40/(1+I40-H40)</f>
         <v>35.654135338345867</v>
       </c>
       <c r="O40" s="12">
-        <f t="shared" si="5"/>
+        <f>L40-F40</f>
         <v>3.3194000000000017</v>
       </c>
       <c r="P40" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N40-F40)</f>
         <v>-5.8829323308270673</v>
       </c>
       <c r="Q40" s="15">
-        <f t="shared" si="7"/>
+        <f>O40+P40</f>
         <v>-2.5635323308270657</v>
       </c>
       <c r="R40" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q40</f>
         <v>116.69597741201144</v>
       </c>
       <c r="S40" s="9">
-        <f t="shared" si="9"/>
-        <v>8.5692756697975988E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R40)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>8.5692756697976005E-3</v>
       </c>
       <c r="T40" s="9">
-        <f t="shared" si="10"/>
+        <f>R40/MAX($R$2:$R$28)</f>
         <v>0.81478292252621221</v>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
         <v>41.8</v>
       </c>
       <c r="G41" s="1">
-        <f t="shared" si="0"/>
+        <f>E41*F41</f>
         <v>4.1799999999999993E-18</v>
       </c>
       <c r="H41" s="13">
@@ -5386,47 +5386,47 @@
         <v>0.4</v>
       </c>
       <c r="J41" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H41/I41,"")</f>
         <v>0.17500000000000002</v>
       </c>
       <c r="K41" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J41/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>8.90656095040686E-3</v>
       </c>
       <c r="L41" s="12">
-        <f t="shared" si="12"/>
+        <f>F41/(1-(F41*(1+H41)-F41)/(F41*(1+H41)))</f>
         <v>44.725999999999999</v>
       </c>
       <c r="M41" s="12">
-        <f t="shared" si="3"/>
+        <f>L41*E41</f>
         <v>4.4725999999999996E-18</v>
       </c>
       <c r="N41" s="12">
-        <f t="shared" si="4"/>
+        <f>F41/(1+I41-H41)</f>
         <v>31.428571428571431</v>
       </c>
       <c r="O41" s="12">
-        <f t="shared" si="5"/>
+        <f>L41-F41</f>
         <v>2.9260000000000019</v>
       </c>
       <c r="P41" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N41-F41)</f>
         <v>-5.1857142857142833</v>
       </c>
       <c r="Q41" s="15">
-        <f t="shared" si="7"/>
+        <f>O41+P41</f>
         <v>-2.2597142857142813</v>
       </c>
       <c r="R41" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q41</f>
         <v>116.39215936689867</v>
       </c>
       <c r="S41" s="9">
-        <f t="shared" si="9"/>
-        <v>8.5916440200042802E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R41)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>8.5916440200042785E-3</v>
       </c>
       <c r="T41" s="9">
-        <f t="shared" si="10"/>
+        <f>R41/MAX($R$2:$R$28)</f>
         <v>0.81266163471318675</v>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
         <v>153.7552</v>
       </c>
       <c r="G42" s="1">
-        <f t="shared" si="0"/>
+        <f>E42*F42</f>
         <v>1.5375519999999999E-17</v>
       </c>
       <c r="H42" s="13">
@@ -5460,47 +5460,47 @@
         <v>0.19</v>
       </c>
       <c r="J42" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H42/I42,"")</f>
         <v>0.36842105263157898</v>
       </c>
       <c r="K42" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J42/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>1.8750654632435495E-2</v>
       </c>
       <c r="L42" s="12">
-        <f t="shared" si="12"/>
+        <f>F42/(1-(F42*(1+H42)-F42)/(F42*(1+H42)))</f>
         <v>164.51806400000001</v>
       </c>
       <c r="M42" s="12">
-        <f t="shared" si="3"/>
+        <f>L42*E42</f>
         <v>1.6451806399999999E-17</v>
       </c>
       <c r="N42" s="12">
-        <f t="shared" si="4"/>
+        <f>F42/(1+I42-H42)</f>
         <v>137.28142857142859</v>
       </c>
       <c r="O42" s="12">
-        <f t="shared" si="5"/>
+        <f>L42-F42</f>
         <v>10.762864000000008</v>
       </c>
       <c r="P42" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N42-F42)</f>
         <v>-8.2368857142857053</v>
       </c>
       <c r="Q42" s="15">
-        <f t="shared" si="7"/>
+        <f>O42+P42</f>
         <v>2.5259782857143023</v>
       </c>
       <c r="R42" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q42</f>
         <v>111.60646679547008</v>
       </c>
       <c r="S42" s="9">
-        <f t="shared" si="9"/>
-        <v>8.9600542756415654E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R42)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>8.9600542756415637E-3</v>
       </c>
       <c r="T42" s="9">
-        <f t="shared" si="10"/>
+        <f>R42/MAX($R$2:$R$28)</f>
         <v>0.77924745312667376</v>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
         <v>133.53</v>
       </c>
       <c r="G43" s="1">
-        <f t="shared" si="0"/>
+        <f>E43*F43</f>
         <v>1.3353E-17</v>
       </c>
       <c r="H43" s="13">
@@ -5534,47 +5534,47 @@
         <v>0.2</v>
       </c>
       <c r="J43" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H43/I43,"")</f>
         <v>0.35000000000000003</v>
       </c>
       <c r="K43" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J43/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>1.781312190081372E-2</v>
       </c>
       <c r="L43" s="12">
-        <f t="shared" si="12"/>
+        <f>F43/(1-(F43*(1+H43)-F43)/(F43*(1+H43)))</f>
         <v>142.87710000000001</v>
       </c>
       <c r="M43" s="12">
-        <f t="shared" si="3"/>
+        <f>L43*E43</f>
         <v>1.428771E-17</v>
       </c>
       <c r="N43" s="12">
-        <f t="shared" si="4"/>
+        <f>F43/(1+I43-H43)</f>
         <v>118.16814159292036</v>
       </c>
       <c r="O43" s="12">
-        <f t="shared" si="5"/>
+        <f>L43-F43</f>
         <v>9.3471000000000117</v>
       </c>
       <c r="P43" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N43-F43)</f>
         <v>-7.6809292035398187</v>
       </c>
       <c r="Q43" s="15">
-        <f t="shared" si="7"/>
+        <f>O43+P43</f>
         <v>1.6661707964601931</v>
       </c>
       <c r="R43" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q43</f>
         <v>112.46627428472419</v>
       </c>
       <c r="S43" s="9">
-        <f t="shared" si="9"/>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R43)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>8.8915544358512261E-3</v>
       </c>
       <c r="T43" s="9">
-        <f t="shared" si="10"/>
+        <f>R43/MAX($R$2:$R$28)</f>
         <v>0.78525071454528272</v>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
         <v>26.63</v>
       </c>
       <c r="G44" s="1">
-        <f t="shared" si="0"/>
+        <f>E44*F44</f>
         <v>2.663E-18</v>
       </c>
       <c r="H44" s="13">
@@ -5608,47 +5608,47 @@
         <v>0.2</v>
       </c>
       <c r="J44" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H44/I44,"")</f>
         <v>0.5</v>
       </c>
       <c r="K44" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J44/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>2.5447317001162453E-2</v>
       </c>
       <c r="L44" s="12">
-        <f t="shared" si="12"/>
+        <f>F44/(1-(F44*(1+H44)-F44)/(F44*(1+H44)))</f>
         <v>29.293000000000003</v>
       </c>
       <c r="M44" s="12">
-        <f t="shared" si="3"/>
+        <f>L44*E44</f>
         <v>2.9293000000000003E-18</v>
       </c>
       <c r="N44" s="12">
-        <f t="shared" si="4"/>
+        <f>F44/(1+I44-H44)</f>
         <v>24.209090909090911</v>
       </c>
       <c r="O44" s="12">
-        <f t="shared" si="5"/>
+        <f>L44-F44</f>
         <v>2.6630000000000038</v>
       </c>
       <c r="P44" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N44-F44)</f>
         <v>-1.2104545454545441</v>
       </c>
       <c r="Q44" s="15">
-        <f t="shared" si="7"/>
+        <f>O44+P44</f>
         <v>1.4525454545454597</v>
       </c>
       <c r="R44" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q44</f>
         <v>112.67989962663893</v>
       </c>
       <c r="S44" s="9">
-        <f t="shared" si="9"/>
-        <v>8.8746972912956672E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R44)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>8.8746972912956655E-3</v>
       </c>
       <c r="T44" s="9">
-        <f t="shared" si="10"/>
+        <f>R44/MAX($R$2:$R$28)</f>
         <v>0.78674226793273505</v>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
         <v>19.309999999999999</v>
       </c>
       <c r="G45" s="1">
-        <f t="shared" si="0"/>
+        <f>E45*F45</f>
         <v>1.931E-18</v>
       </c>
       <c r="H45" s="13">
@@ -5682,47 +5682,47 @@
         <v>0.2</v>
       </c>
       <c r="J45" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H45/I45,"")</f>
         <v>1</v>
       </c>
       <c r="K45" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J45/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>5.0894634002324905E-2</v>
       </c>
       <c r="L45" s="12">
-        <f t="shared" si="12"/>
+        <f>F45/(1-(F45*(1+H45)-F45)/(F45*(1+H45)))</f>
         <v>23.171999999999997</v>
       </c>
       <c r="M45" s="12">
-        <f t="shared" si="3"/>
+        <f>L45*E45</f>
         <v>2.3171999999999995E-18</v>
       </c>
       <c r="N45" s="12">
-        <f t="shared" si="4"/>
+        <f>F45/(1+I45-H45)</f>
         <v>19.309999999999999</v>
       </c>
       <c r="O45" s="12">
-        <f t="shared" si="5"/>
+        <f>L45-F45</f>
         <v>3.8619999999999983</v>
       </c>
       <c r="P45" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N45-F45)</f>
         <v>0</v>
       </c>
       <c r="Q45" s="15">
-        <f t="shared" si="7"/>
+        <f>O45+P45</f>
         <v>3.8619999999999983</v>
       </c>
       <c r="R45" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q45</f>
         <v>110.27044508118439</v>
       </c>
       <c r="S45" s="9">
-        <f t="shared" si="9"/>
-        <v>9.0686130745529329E-3</v>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R45)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <v>9.0686130745529347E-3</v>
       </c>
       <c r="T45" s="9">
-        <f t="shared" si="10"/>
+        <f>R45/MAX($R$2:$R$28)</f>
         <v>0.76991921661787932</v>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
         <v>323.75</v>
       </c>
       <c r="G46" s="1">
-        <f t="shared" si="0"/>
+        <f>E46*F46</f>
         <v>3.2375000000000002E-17</v>
       </c>
       <c r="H46" s="13">
@@ -5756,47 +5756,47 @@
         <v>0.2</v>
       </c>
       <c r="J46" s="9">
-        <f t="shared" si="1"/>
+        <f>IFERROR(H46/I46,"")</f>
         <v>1</v>
       </c>
       <c r="K46" s="9">
-        <f t="shared" si="2"/>
+        <f>IFERROR(J46/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>5.0894634002324905E-2</v>
       </c>
       <c r="L46" s="12">
-        <f t="shared" si="12"/>
+        <f>F46/(1-(F46*(1+H46)-F46)/(F46*(1+H46)))</f>
         <v>388.5</v>
       </c>
       <c r="M46" s="12">
-        <f t="shared" si="3"/>
+        <f>L46*E46</f>
         <v>3.8849999999999999E-17</v>
       </c>
       <c r="N46" s="12">
-        <f t="shared" si="4"/>
+        <f>F46/(1+I46-H46)</f>
         <v>323.75</v>
       </c>
       <c r="O46" s="12">
-        <f t="shared" si="5"/>
+        <f>L46-F46</f>
         <v>64.75</v>
       </c>
       <c r="P46" s="12">
-        <f t="shared" si="6"/>
+        <f>0.5*(N46-F46)</f>
         <v>0</v>
       </c>
       <c r="Q46" s="15">
-        <f t="shared" si="7"/>
+        <f>O46+P46</f>
         <v>64.75</v>
       </c>
       <c r="R46" s="12">
-        <f t="shared" si="8"/>
+        <f>MAX($Q$2:$Q$279)-Q46</f>
         <v>49.382445081184386</v>
       </c>
       <c r="S46" s="9">
-        <f t="shared" si="9"/>
+        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R46)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>2.0250111114506524E-2</v>
       </c>
       <c r="T46" s="9">
-        <f t="shared" si="10"/>
+        <f>R46/MAX($R$2:$R$28)</f>
         <v>0.34479314383458876</v>
       </c>
     </row>
@@ -5807,7 +5807,11 @@
       <c r="D51" s="44"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T46" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:T46" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T46">
+      <sortCondition descending="1" ref="E1:E46"/>
+    </sortState>
+  </autoFilter>
   <conditionalFormatting sqref="S2:S46">
     <cfRule type="iconSet" priority="11">
       <iconSet iconSet="3Symbols">
@@ -5857,7 +5861,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD6C5064-D029-4982-9C03-6BDB75C18181}">
-  <dimension ref="B2:U42"/>
+  <dimension ref="B1:Z42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.140625" bestFit="1" customWidth="1"/>
@@ -5871,7 +5875,21 @@
     <col min="11" max="11" width="7.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="W1" t="s">
+        <v>124</v>
+      </c>
+      <c r="X1" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>122</v>
+      </c>
+      <c r="Z1" s="29">
+        <v>0.2356</v>
+      </c>
+    </row>
+    <row r="2" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>124</v>
       </c>
@@ -5920,8 +5938,20 @@
       <c r="U2" s="29">
         <v>0.54500000000000004</v>
       </c>
-    </row>
-    <row r="3" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W2" t="s">
+        <v>124</v>
+      </c>
+      <c r="X2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z2" s="29">
+        <v>0.22670000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>124</v>
       </c>
@@ -5971,7 +6001,12 @@
         <v>0.3967</v>
       </c>
     </row>
-    <row r="5" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="W4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B5" s="39" t="s">
         <v>82</v>
       </c>
@@ -6020,8 +6055,20 @@
       <c r="U5" s="39" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="6" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W5" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="X5" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y5" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z5" s="39" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="6" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B6" s="33" t="s">
         <v>94</v>
       </c>
@@ -6074,8 +6121,21 @@
         <f>T6-S6</f>
         <v>-4.1399999999999999E-2</v>
       </c>
-    </row>
-    <row r="7" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W6" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="X6" s="34">
+        <v>0.43940000000000001</v>
+      </c>
+      <c r="Y6" s="34">
+        <v>0.15629999999999999</v>
+      </c>
+      <c r="Z6" s="34">
+        <f>Y6-X6</f>
+        <v>-0.28310000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B7" s="33" t="s">
         <v>50</v>
       </c>
@@ -6128,8 +6188,21 @@
         <f t="shared" ref="U7:U42" si="3">T7-S7</f>
         <v>-5.6899999999999999E-2</v>
       </c>
-    </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W7" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="X7" s="34">
+        <v>0.2412</v>
+      </c>
+      <c r="Y7" s="34">
+        <v>0.1038</v>
+      </c>
+      <c r="Z7" s="34">
+        <f t="shared" ref="Z7:Z14" si="4">Y7-X7</f>
+        <v>-0.13739999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B8" s="35" t="s">
         <v>27</v>
       </c>
@@ -6182,8 +6255,21 @@
         <f t="shared" si="3"/>
         <v>-0.1242</v>
       </c>
-    </row>
-    <row r="9" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W8" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="X8" s="34">
+        <v>0.31940000000000002</v>
+      </c>
+      <c r="Y8" s="34">
+        <v>0.3624</v>
+      </c>
+      <c r="Z8" s="34">
+        <f t="shared" si="4"/>
+        <v>4.2999999999999983E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B9" s="37" t="s">
         <v>103</v>
       </c>
@@ -6236,8 +6322,21 @@
         <f t="shared" si="3"/>
         <v>-5.5199999999999999E-2</v>
       </c>
-    </row>
-    <row r="10" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W9" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="X9" s="34">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="34">
+        <v>7.6200000000000004E-2</v>
+      </c>
+      <c r="Z9" s="34">
+        <f t="shared" si="4"/>
+        <v>7.6200000000000004E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B10" s="35" t="s">
         <v>46</v>
       </c>
@@ -6290,8 +6389,21 @@
         <f t="shared" si="3"/>
         <v>-4.8300000000000003E-2</v>
       </c>
-    </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W10" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="X10" s="34">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="34">
+        <v>0.27429999999999999</v>
+      </c>
+      <c r="Z10" s="34">
+        <f t="shared" si="4"/>
+        <v>0.27429999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B11" s="33" t="s">
         <v>32</v>
       </c>
@@ -6344,8 +6456,21 @@
         <f t="shared" si="3"/>
         <v>-9.6600000000000005E-2</v>
       </c>
-    </row>
-    <row r="12" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W11" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="X11" s="34">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="34">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B12" s="33" t="s">
         <v>48</v>
       </c>
@@ -6398,8 +6523,21 @@
         <f t="shared" si="3"/>
         <v>-0.1076</v>
       </c>
-    </row>
-    <row r="13" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W12" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="X12" s="34">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="34">
+        <v>2.7E-2</v>
+      </c>
+      <c r="Z12" s="34">
+        <f t="shared" si="4"/>
+        <v>2.7E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B13" s="33" t="s">
         <v>53</v>
       </c>
@@ -6452,8 +6590,21 @@
         <f t="shared" si="3"/>
         <v>-6.93E-2</v>
       </c>
-    </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W13" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="X13" s="34">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="34">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B14" s="33" t="s">
         <v>44</v>
       </c>
@@ -6506,8 +6657,21 @@
         <f t="shared" si="3"/>
         <v>-1.38E-2</v>
       </c>
-    </row>
-    <row r="15" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W14" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="X14" s="34">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="34">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B15" s="37" t="s">
         <v>91</v>
       </c>
@@ -6561,7 +6725,7 @@
         <v>-1.5100000000000001E-2</v>
       </c>
     </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B16" s="37" t="s">
         <v>92</v>
       </c>

--- a/Open Positions.xlsx
+++ b/Open Positions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\StockSillines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B825B88-2EFF-4757-9500-158D87505ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CF6D7E0-0C88-4158-8EE9-C8F002657B58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Positions" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId4"/>
+    <pivotCache cacheId="20" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="134">
   <si>
     <t>Name</t>
   </si>
@@ -440,6 +440,12 @@
   </si>
   <si>
     <t>Bitcoin ETF</t>
+  </si>
+  <si>
+    <t>Ingredion</t>
+  </si>
+  <si>
+    <t>WK06</t>
   </si>
 </sst>
 </file>
@@ -682,7 +688,106 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="36">
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
     </dxf>
@@ -706,20 +811,20 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="samuel walton" refreshedDate="45691.704963310185" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{A9649E00-87AB-4DC2-85FE-D21B9DD48B57}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="samuel walton" refreshedDate="45697.530279976854" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="51" xr:uid="{A9649E00-87AB-4DC2-85FE-D21B9DD48B57}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:T1048576" sheet="Positions"/>
   </cacheSource>
   <cacheFields count="22">
     <cacheField name="Chapter" numFmtId="0">
       <sharedItems containsBlank="1" count="11">
+        <s v="Energy"/>
         <s v="ETF"/>
         <s v="Banking"/>
-        <s v="Energy"/>
         <s v="US Consumer"/>
         <s v="Tech"/>
+        <s v="Asia Consumer"/>
         <s v="Health"/>
-        <s v="Asia Consumer"/>
         <s v="Forex"/>
         <s v="Automotive"/>
         <s v="Industrials"/>
@@ -731,27 +836,28 @@
     </cacheField>
     <cacheField name="Ticker" numFmtId="0">
       <sharedItems containsBlank="1" count="46">
+        <s v="APA"/>
         <s v="BOTZ.UK"/>
         <s v="BATT.NL"/>
         <s v="ING"/>
-        <s v="APA"/>
         <s v="MO"/>
         <s v="VWO.US"/>
         <s v="VBTC.DE"/>
         <s v="BONDS"/>
+        <s v="ACI"/>
         <s v="YPF"/>
+        <s v="EXC"/>
+        <s v="KMB"/>
+        <s v="PEP"/>
         <s v="NEE"/>
-        <s v="PEP"/>
         <s v="TSM"/>
-        <s v="KMB"/>
+        <s v="INGR"/>
         <s v="AGIO"/>
-        <s v="EXC"/>
-        <s v="YUM"/>
         <s v="FSLR"/>
-        <s v="INGR"/>
         <s v="AAPL"/>
         <s v="MSFT"/>
         <s v="MA"/>
+        <s v="YUM"/>
         <s v="MAXN"/>
         <s v="V"/>
         <s v="QCOM"/>
@@ -774,16 +880,15 @@
         <s v="USDJPY=X"/>
         <s v="MMM"/>
         <s v="PCG"/>
-        <s v="ACI"/>
         <s v="HCA"/>
         <m/>
       </sharedItems>
     </cacheField>
-    <cacheField name="Date" numFmtId="165">
+    <cacheField name="Date" numFmtId="0">
       <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2024-06-17T00:00:00" maxDate="2025-02-01T00:00:00"/>
     </cacheField>
     <cacheField name="Volume" numFmtId="164">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="9.9999999999999998E-20" maxValue="2"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="9.9999999999999998E-20" maxValue="2.2953000000000001"/>
     </cacheField>
     <cacheField name="Price" numFmtId="44">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="10.92" maxValue="2742.9"/>
@@ -792,7 +897,7 @@
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="1.092E-18" maxValue="89.991048000000006"/>
     </cacheField>
     <cacheField name="Expected Return QoQ%" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="2.5000000000000001E-2" maxValue="1"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="2.4701323861801683E-2" maxValue="1"/>
     </cacheField>
     <cacheField name="Volatility" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0.15" maxValue="1.8652"/>
@@ -801,7 +906,7 @@
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="6.7668155366084726E-2" maxValue="1"/>
     </cacheField>
     <cacheField name="Mix %" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="3.4439460009693403E-3" maxValue="5.0894634002324905E-2"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="3.521195576577426E-3" maxValue="5.2036228230661195E-2"/>
     </cacheField>
     <cacheField name="Target Price" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="11.602500000000001" maxValue="3017.1900000000005"/>
@@ -842,11 +947,33 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="48">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="51">
   <r>
     <x v="0"/>
+    <s v="APA"/>
+    <x v="0"/>
+    <d v="2024-12-01T00:00:00"/>
+    <n v="2.2953000000000001"/>
+    <n v="21.78"/>
+    <n v="49.991634000000005"/>
+    <n v="0.22038567493112926"/>
+    <n v="0.45929999999999999"/>
+    <n v="0.47982946860685666"/>
+    <n v="2.4968515740223275E-2"/>
+    <n v="26.58"/>
+    <n v="61.009073999999998"/>
+    <n v="17.579908117366596"/>
+    <n v="4.7999999999999972"/>
+    <n v="-2.1000459413167025"/>
+    <n v="2.6999540586832946"/>
+    <n v="111.4324910225011"/>
+    <n v="8.9740433048209802E-3"/>
+    <n v="0.77803273697370867"/>
+  </r>
+  <r>
+    <x v="1"/>
     <s v="Robotics &amp; AI"/>
-    <x v="0"/>
+    <x v="1"/>
     <d v="2024-07-08T00:00:00"/>
     <n v="2"/>
     <n v="20.928000000000001"/>
@@ -854,7 +981,7 @@
     <n v="4.4999999999999998E-2"/>
     <n v="0.2"/>
     <n v="0.22499999999999998"/>
-    <n v="1.1451292650523102E-2"/>
+    <n v="1.1708151351898769E-2"/>
     <n v="21.869759999999999"/>
     <n v="43.739519999999999"/>
     <n v="18.119480519480518"/>
@@ -866,31 +993,31 @@
     <n v="0.80011330398039715"/>
   </r>
   <r>
-    <x v="0"/>
+    <x v="1"/>
     <s v="Batterey Value-Chain"/>
-    <x v="1"/>
+    <x v="2"/>
     <d v="2024-07-08T00:00:00"/>
     <n v="2"/>
-    <n v="16.399999999999999"/>
-    <n v="32.799999999999997"/>
+    <n v="16.399000000000001"/>
+    <n v="32.798000000000002"/>
     <n v="4.4999999999999998E-2"/>
     <n v="0.2"/>
     <n v="0.22499999999999998"/>
-    <n v="1.1451292650523102E-2"/>
-    <n v="17.137999999999998"/>
-    <n v="34.275999999999996"/>
-    <n v="14.199134199134198"/>
-    <n v="0.73799999999999955"/>
-    <n v="-1.1004329004329003"/>
-    <n v="-0.36243290043290077"/>
-    <n v="114.49487798161729"/>
-    <n v="8.7340151597048287E-3"/>
-    <n v="0.79941462735066027"/>
+    <n v="1.1708151351898769E-2"/>
+    <n v="17.136955"/>
+    <n v="34.273910000000001"/>
+    <n v="14.198268398268398"/>
+    <n v="0.73795499999999947"/>
+    <n v="-1.1003658008658013"/>
+    <n v="-0.3624108008658018"/>
+    <n v="114.49485588205019"/>
+    <n v="8.7340168455268905E-3"/>
+    <n v="0.79941447304928448"/>
   </r>
   <r>
-    <x v="1"/>
+    <x v="2"/>
     <s v="ING Group NV"/>
-    <x v="2"/>
+    <x v="3"/>
     <d v="2024-11-27T00:00:00"/>
     <n v="1.9595"/>
     <n v="15.3"/>
@@ -898,7 +1025,7 @@
     <n v="0.35"/>
     <n v="0.39532299999999998"/>
     <n v="0.88535197800279775"/>
-    <n v="4.5059664883686804E-2"/>
+    <n v="4.6070377591820914E-2"/>
     <n v="20.655000000000001"/>
     <n v="40.4734725"/>
     <n v="14.636624277854791"/>
@@ -906,30 +1033,8 @@
     <n v="-0.33168786107260484"/>
     <n v="5.0233121389273956"/>
     <n v="109.10913294225699"/>
-    <n v="9.165135612700933E-3"/>
+    <n v="9.1651356127009313E-3"/>
     <n v="0.76181081974332665"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <s v="APA"/>
-    <x v="3"/>
-    <d v="2024-12-01T00:00:00"/>
-    <n v="1.8976999999999999"/>
-    <n v="21.73"/>
-    <n v="41.237020999999999"/>
-    <n v="0.22319374137137582"/>
-    <n v="0.45929999999999999"/>
-    <n v="0.48594326447066366"/>
-    <n v="2.4731904591129405E-2"/>
-    <n v="26.58"/>
-    <n v="50.440865999999993"/>
-    <n v="17.579394852436032"/>
-    <n v="4.8499999999999979"/>
-    <n v="-2.0753025737819843"/>
-    <n v="2.7746974262180135"/>
-    <n v="111.35774765496637"/>
-    <n v="8.980066686499668E-3"/>
-    <n v="0.77751087134654673"/>
   </r>
   <r>
     <x v="3"/>
@@ -942,7 +1047,7 @@
     <n v="0.18430000000000002"/>
     <n v="0.19980000000000001"/>
     <n v="0.92242242242242245"/>
-    <n v="4.6946351584727132E-2"/>
+    <n v="4.7999383698252546E-2"/>
     <n v="61.441483999999996"/>
     <n v="106.57639814639998"/>
     <n v="51.088133924175295"/>
@@ -954,7 +1059,7 @@
     <n v="0.73288929623425103"/>
   </r>
   <r>
-    <x v="0"/>
+    <x v="1"/>
     <s v="Emergin Markets"/>
     <x v="5"/>
     <d v="2025-01-31T00:00:00"/>
@@ -964,7 +1069,7 @@
     <n v="4.4999999999999998E-2"/>
     <n v="0.2"/>
     <n v="0.22499999999999998"/>
-    <n v="1.1451292650523102E-2"/>
+    <n v="1.1708151351898769E-2"/>
     <n v="46.230800000000002"/>
     <n v="46.230800000000002"/>
     <n v="38.303030303030305"/>
@@ -972,11 +1077,11 @@
     <n v="-2.9684848484848487"/>
     <n v="-0.9776848484848486"/>
     <n v="115.11012992966923"/>
-    <n v="8.6873327361456972E-3"/>
+    <n v="8.6873327361456955E-3"/>
     <n v="0.80371037765363607"/>
   </r>
   <r>
-    <x v="0"/>
+    <x v="1"/>
     <s v="Bitcoin ETF"/>
     <x v="6"/>
     <d v="2024-07-08T00:00:00"/>
@@ -986,7 +1091,7 @@
     <n v="2.5000000000000001E-2"/>
     <n v="0.2"/>
     <n v="0.125"/>
-    <n v="6.3618292502906132E-3"/>
+    <n v="6.5045285288326494E-3"/>
     <n v="49.896999999999998"/>
     <n v="49.896999999999998"/>
     <n v="41.42978723404255"/>
@@ -994,11 +1099,11 @@
     <n v="-3.6251063829787249"/>
     <n v="-2.4081063829787261"/>
     <n v="116.54055146416312"/>
-    <n v="8.5807042049865865E-3"/>
+    <n v="8.5807042049865848E-3"/>
     <n v="0.81369772309746791"/>
   </r>
   <r>
-    <x v="0"/>
+    <x v="1"/>
     <s v="ETF5"/>
     <x v="7"/>
     <d v="2024-07-08T00:00:00"/>
@@ -1008,7 +1113,7 @@
     <n v="2.5000000000000001E-2"/>
     <n v="0.2"/>
     <n v="0.125"/>
-    <n v="6.3618292502906132E-3"/>
+    <n v="6.5045285288326494E-3"/>
     <n v="52.561999999999998"/>
     <n v="52.561999999999998"/>
     <n v="43.642553191489363"/>
@@ -1020,9 +1125,31 @@
     <n v="0.81459573993409262"/>
   </r>
   <r>
-    <x v="2"/>
+    <x v="3"/>
+    <s v="Albertson Companies"/>
+    <x v="8"/>
+    <d v="2024-12-04T00:00:00"/>
+    <n v="1"/>
+    <n v="20.36"/>
+    <n v="20.36"/>
+    <n v="0.2"/>
+    <n v="0.2"/>
+    <n v="1"/>
+    <n v="5.2036228230661195E-2"/>
+    <n v="24.431999999999999"/>
+    <n v="24.431999999999999"/>
+    <n v="20.36"/>
+    <n v="4.0719999999999992"/>
+    <n v="0"/>
+    <n v="4.0719999999999992"/>
+    <n v="110.06044508118438"/>
+    <n v="9.0859163731562727E-3"/>
+    <n v="0.76845297572830351"/>
+  </r>
+  <r>
+    <x v="0"/>
     <s v="YPF"/>
-    <x v="8"/>
+    <x v="9"/>
     <d v="2024-12-01T00:00:00"/>
     <n v="0.95840000000000003"/>
     <n v="41.76"/>
@@ -1030,7 +1157,7 @@
     <n v="0.1"/>
     <n v="0.2"/>
     <n v="0.5"/>
-    <n v="2.5447317001162453E-2"/>
+    <n v="2.6018114115330598E-2"/>
     <n v="45.936"/>
     <n v="44.025062400000003"/>
     <n v="37.963636363636368"/>
@@ -1042,9 +1169,75 @@
     <n v="0.78098013165759694"/>
   </r>
   <r>
-    <x v="2"/>
+    <x v="0"/>
+    <s v="Excelon"/>
+    <x v="10"/>
+    <d v="2024-12-01T00:00:00"/>
+    <n v="0.52039999999999997"/>
+    <n v="40.340000000000003"/>
+    <n v="20.992936"/>
+    <n v="0.1"/>
+    <n v="0.2"/>
+    <n v="0.5"/>
+    <n v="2.6018114115330598E-2"/>
+    <n v="44.374000000000009"/>
+    <n v="23.092229600000003"/>
+    <n v="36.672727272727279"/>
+    <n v="4.034000000000006"/>
+    <n v="-1.8336363636363622"/>
+    <n v="2.2003636363636438"/>
+    <n v="111.93208144482074"/>
+    <n v="8.9339891395923948E-3"/>
+    <n v="0.78152092699868725"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="Kimberly Clark"/>
+    <x v="11"/>
+    <d v="2024-09-09T00:00:00"/>
+    <n v="0.51380000000000003"/>
+    <n v="138.53"/>
+    <n v="71.176714000000004"/>
+    <n v="7.0000000000000007E-2"/>
+    <n v="0.18340000000000001"/>
+    <n v="0.38167938931297712"/>
+    <n v="1.9861155813229465E-2"/>
+    <n v="148.22710000000001"/>
+    <n v="76.159083980000005"/>
+    <n v="124.42069337165439"/>
+    <n v="9.697100000000006"/>
+    <n v="-7.0546533141728034"/>
+    <n v="2.6424466858272027"/>
+    <n v="111.48999839535719"/>
+    <n v="8.969414426340536E-3"/>
+    <n v="0.77843425917148812"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="Pepsi"/>
+    <x v="12"/>
+    <d v="2024-06-17T00:00:00"/>
+    <n v="0.51239999999999997"/>
+    <n v="157.99"/>
+    <n v="80.954076000000001"/>
+    <n v="6.7199999999999996E-2"/>
+    <n v="0.16439999999999999"/>
+    <n v="0.40875912408759124"/>
+    <n v="2.1270283072387059E-2"/>
+    <n v="168.60692800000001"/>
+    <n v="86.394189907200001"/>
+    <n v="143.99380240612467"/>
+    <n v="10.616928000000001"/>
+    <n v="-6.9980987969376685"/>
+    <n v="3.618829203062333"/>
+    <n v="110.51361587812205"/>
+    <n v="9.0486587743435348E-3"/>
+    <n v="0.77161705931131142"/>
+  </r>
+  <r>
+    <x v="0"/>
     <s v="NextEra Energy"/>
-    <x v="9"/>
+    <x v="13"/>
     <d v="2024-08-07T00:00:00"/>
     <n v="0.45179999999999998"/>
     <n v="77.430000000000007"/>
@@ -1052,7 +1245,7 @@
     <n v="0.1"/>
     <n v="0.25990000000000002"/>
     <n v="0.38476337052712584"/>
-    <n v="1.9582390920478997E-2"/>
+    <n v="2.0021634563547979E-2"/>
     <n v="85.173000000000016"/>
     <n v="38.481161400000005"/>
     <n v="66.755754806448849"/>
@@ -1064,31 +1257,9 @@
     <n v="0.78008600943515383"/>
   </r>
   <r>
-    <x v="3"/>
-    <s v="Pepsi"/>
-    <x v="10"/>
-    <d v="2024-06-17T00:00:00"/>
-    <n v="0.43659999999999999"/>
-    <n v="160.25"/>
-    <n v="69.965149999999994"/>
-    <n v="6.7199999999999996E-2"/>
-    <n v="0.16439999999999999"/>
-    <n v="0.40875912408759124"/>
-    <n v="2.0803646015548866E-2"/>
-    <n v="171.0188"/>
-    <n v="74.666808079999996"/>
-    <n v="146.05359095880419"/>
-    <n v="10.768799999999999"/>
-    <n v="-7.0982045205979034"/>
-    <n v="3.6705954794020954"/>
-    <n v="110.46184960178229"/>
-    <n v="9.0528992915203284E-3"/>
-    <n v="0.7712556220204998"/>
-  </r>
-  <r>
     <x v="4"/>
     <s v="TSMC"/>
-    <x v="11"/>
+    <x v="14"/>
     <d v="2024-07-11T00:00:00"/>
     <n v="0.4108"/>
     <n v="189.76"/>
@@ -1096,7 +1267,7 @@
     <n v="0.19835581787521095"/>
     <n v="0.37"/>
     <n v="0.53609680506813773"/>
-    <n v="2.728445068375859E-2"/>
+    <n v="2.7896455702253901E-2"/>
     <n v="227.4"/>
     <n v="93.41592"/>
     <n v="161.96043380326287"/>
@@ -1108,31 +1279,31 @@
     <n v="0.6311275288415521"/>
   </r>
   <r>
-    <x v="3"/>
-    <s v="Kimberly Clark"/>
-    <x v="12"/>
-    <d v="2024-09-09T00:00:00"/>
-    <n v="0.35149999999999998"/>
-    <n v="142.78"/>
-    <n v="50.187169999999995"/>
-    <n v="7.0000000000000007E-2"/>
-    <n v="0.18340000000000001"/>
-    <n v="0.38167938931297712"/>
-    <n v="1.9425432825314851E-2"/>
-    <n v="152.77460000000002"/>
-    <n v="53.700271900000004"/>
-    <n v="128.23783007005568"/>
-    <n v="9.9946000000000197"/>
-    <n v="-7.2710849649721609"/>
-    <n v="2.7235150350278587"/>
-    <n v="111.40893004615653"/>
-    <n v="8.9759411528833617E-3"/>
-    <n v="0.77786823189316223"/>
+    <x v="5"/>
+    <s v="Ingredion"/>
+    <x v="15"/>
+    <d v="2024-10-15T00:00:00"/>
+    <n v="0.34860000000000002"/>
+    <n v="131.91"/>
+    <n v="45.983826000000001"/>
+    <n v="0.1202"/>
+    <n v="0.33710000000000001"/>
+    <n v="0.35657075051913378"/>
+    <n v="1.8554596954391801E-2"/>
+    <n v="147.76558199999999"/>
+    <n v="51.511081885199999"/>
+    <n v="108.39838934998768"/>
+    <n v="15.855581999999998"/>
+    <n v="-11.755805325006158"/>
+    <n v="4.0997766749938407"/>
+    <n v="110.03266840619054"/>
+    <n v="9.0882100242125827E-3"/>
+    <n v="0.76825903622043479"/>
   </r>
   <r>
-    <x v="5"/>
+    <x v="6"/>
     <s v="Agios"/>
-    <x v="13"/>
+    <x v="16"/>
     <d v="2024-12-04T00:00:00"/>
     <n v="0.28749999999999998"/>
     <n v="34.78"/>
@@ -1140,7 +1311,7 @@
     <n v="0.2"/>
     <n v="0.2"/>
     <n v="1"/>
-    <n v="5.0894634002324905E-2"/>
+    <n v="5.2036228230661195E-2"/>
     <n v="41.735999999999997"/>
     <n v="11.999099999999999"/>
     <n v="34.78"/>
@@ -1152,53 +1323,9 @@
     <n v="0.74831660084479601"/>
   </r>
   <r>
-    <x v="2"/>
-    <s v="Excelon"/>
-    <x v="14"/>
-    <d v="2024-12-01T00:00:00"/>
-    <n v="0.27450000000000002"/>
-    <n v="39.799999999999997"/>
-    <n v="10.9251"/>
-    <n v="0.1"/>
-    <n v="0.2"/>
-    <n v="0.5"/>
-    <n v="2.5447317001162453E-2"/>
-    <n v="43.78"/>
-    <n v="12.017610000000001"/>
-    <n v="36.181818181818187"/>
-    <n v="3.980000000000004"/>
-    <n v="-1.8090909090909051"/>
-    <n v="2.1709090909090989"/>
-    <n v="111.96153599027528"/>
-    <n v="8.931638809303739E-3"/>
-    <n v="0.78172658156501729"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <s v="Yum! Brands"/>
-    <x v="15"/>
-    <d v="2024-10-15T00:00:00"/>
-    <n v="0.25669999999999998"/>
-    <n v="132.38999999999999"/>
-    <n v="33.984512999999993"/>
-    <n v="7.0000000000000007E-2"/>
-    <n v="0.1623"/>
-    <n v="0.43130006161429457"/>
-    <n v="2.1950858781039705E-2"/>
-    <n v="141.65729999999999"/>
-    <n v="36.363428909999996"/>
-    <n v="121.20296621807194"/>
-    <n v="9.2673000000000059"/>
-    <n v="-5.5935168909640254"/>
-    <n v="3.6737831090359805"/>
-    <n v="110.45866197214841"/>
-    <n v="9.0531605411999731E-3"/>
-    <n v="0.77123336567330925"/>
-  </r>
-  <r>
-    <x v="2"/>
+    <x v="0"/>
     <s v="First Solar"/>
-    <x v="16"/>
+    <x v="17"/>
     <d v="2024-08-07T00:00:00"/>
     <n v="0.25169999999999998"/>
     <n v="178.56"/>
@@ -1206,7 +1333,7 @@
     <n v="9.7782258064516236E-2"/>
     <n v="0.52980000000000005"/>
     <n v="0.18456447350795815"/>
-    <n v="9.3933413290193217E-3"/>
+    <n v="9.6040390667319325E-3"/>
     <n v="196.02"/>
     <n v="49.338234"/>
     <n v="124.69119255370553"/>
@@ -1216,28 +1343,6 @@
     <n v="123.60684880433161"/>
     <n v="8.0901666022000929E-3"/>
     <n v="0.86303531404059042"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <s v="MSG"/>
-    <x v="17"/>
-    <d v="2024-10-15T00:00:00"/>
-    <n v="0.19139999999999999"/>
-    <n v="135.82"/>
-    <n v="25.995947999999999"/>
-    <n v="0.1202"/>
-    <n v="0.33710000000000001"/>
-    <n v="0.35657075051913378"/>
-    <n v="1.8147537843605618E-2"/>
-    <n v="152.14556400000001"/>
-    <n v="29.120660949599998"/>
-    <n v="111.61147177253677"/>
-    <n v="16.325564000000014"/>
-    <n v="-12.10426411373161"/>
-    <n v="4.2212998862684046"/>
-    <n v="109.91114519491597"/>
-    <n v="9.0982583997883393E-3"/>
-    <n v="0.76741054907089512"/>
   </r>
   <r>
     <x v="4"/>
@@ -1250,7 +1355,7 @@
     <n v="0.15"/>
     <n v="0.2271"/>
     <n v="0.66050198150594452"/>
-    <n v="3.3616006606555421E-2"/>
+    <n v="3.437003185644729E-2"/>
     <n v="261.48699999999997"/>
     <n v="49.211853399999995"/>
     <n v="211.10389007520189"/>
@@ -1266,25 +1371,25 @@
     <s v="Microsoft"/>
     <x v="19"/>
     <d v="2024-10-09T00:00:00"/>
-    <n v="0.13370000000000001"/>
-    <n v="423.77"/>
-    <n v="56.658049000000005"/>
+    <n v="0.16059999999999999"/>
+    <n v="421.18"/>
+    <n v="67.641508000000002"/>
     <n v="0.15"/>
     <n v="0.1963"/>
     <n v="0.76413652572592972"/>
-    <n v="3.8890448804629323E-2"/>
-    <n v="487.33549999999991"/>
-    <n v="65.156756349999995"/>
-    <n v="405.01768135334032"/>
-    <n v="63.565499999999929"/>
-    <n v="-9.3761593233298299"/>
-    <n v="54.189340676670099"/>
-    <n v="59.943104404514287"/>
-    <n v="1.6682485999585474E-2"/>
-    <n v="0.41852871774290379"/>
+    <n v="3.9762782652058987E-2"/>
+    <n v="484.35699999999997"/>
+    <n v="77.787734199999989"/>
+    <n v="402.54229188569246"/>
+    <n v="63.176999999999964"/>
+    <n v="-9.3188540571537715"/>
+    <n v="53.858145942846193"/>
+    <n v="60.274299138338193"/>
+    <n v="1.6590819209773906E-2"/>
+    <n v="0.4208411523197837"/>
   </r>
   <r>
-    <x v="1"/>
+    <x v="2"/>
     <s v="Master Card"/>
     <x v="20"/>
     <d v="2024-08-07T00:00:00"/>
@@ -1294,7 +1399,7 @@
     <n v="0.25"/>
     <n v="0.29699999999999999"/>
     <n v="0.84175084175084181"/>
-    <n v="4.2840601012058006E-2"/>
+    <n v="4.3801538914697978E-2"/>
     <n v="626.95000000000005"/>
     <n v="81.127330000000001"/>
     <n v="479.04489016236869"/>
@@ -1306,9 +1411,31 @@
     <n v="0"/>
   </r>
   <r>
-    <x v="2"/>
+    <x v="5"/>
+    <s v="Yum! Brands"/>
+    <x v="21"/>
+    <d v="2024-10-15T00:00:00"/>
+    <n v="2.9999999999999997E-4"/>
+    <n v="130.51"/>
+    <n v="3.9152999999999993E-2"/>
+    <n v="7.0000000000000007E-2"/>
+    <n v="0.1623"/>
+    <n v="0.43130006161429457"/>
+    <n v="2.2443228442059669E-2"/>
+    <n v="139.64570000000001"/>
+    <n v="4.1893710000000001E-2"/>
+    <n v="119.48182733681222"/>
+    <n v="9.1357000000000141"/>
+    <n v="-5.5140863315938873"/>
+    <n v="3.6216136684061269"/>
+    <n v="110.51083141277826"/>
+    <n v="9.0488867671696012E-3"/>
+    <n v="0.77159761789729864"/>
+  </r>
+  <r>
+    <x v="0"/>
     <s v="Maxeon Solar"/>
-    <x v="21"/>
+    <x v="22"/>
     <d v="2024-08-07T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="10.92"/>
@@ -1316,7 +1443,7 @@
     <n v="1"/>
     <n v="1.8652"/>
     <n v="0.53613553506326406"/>
-    <n v="2.7286421832685457E-2"/>
+    <n v="2.7898471065119668E-2"/>
     <n v="21.84"/>
     <n v="2.1840000000000001E-18"/>
     <n v="5.8546000428908433"/>
@@ -1324,13 +1451,13 @@
     <n v="-2.5326999785545783"/>
     <n v="8.3873000214454212"/>
     <n v="105.74514505973896"/>
-    <n v="9.4566989286843078E-3"/>
+    <n v="9.456698928684306E-3"/>
     <n v="0.73832312171768166"/>
   </r>
   <r>
-    <x v="1"/>
+    <x v="2"/>
     <s v="Visa"/>
-    <x v="22"/>
+    <x v="23"/>
     <d v="2024-08-07T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="283.43"/>
@@ -1338,7 +1465,7 @@
     <n v="0.25"/>
     <n v="0.26"/>
     <n v="0.96153846153846145"/>
-    <n v="4.8937148079158561E-2"/>
+    <n v="5.0034834837174219E-2"/>
     <n v="354.28750000000002"/>
     <n v="3.542875E-17"/>
     <n v="280.62376237623761"/>
@@ -1352,7 +1479,7 @@
   <r>
     <x v="4"/>
     <s v="QualComm2"/>
-    <x v="23"/>
+    <x v="24"/>
     <d v="2024-09-09T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="188.12"/>
@@ -1360,7 +1487,7 @@
     <n v="0.15"/>
     <n v="0.37780000000000002"/>
     <n v="0.39703546850185278"/>
-    <n v="2.0206974855343396E-2"/>
+    <n v="2.0660228254629907E-2"/>
     <n v="216.33799999999999"/>
     <n v="2.16338E-17"/>
     <n v="153.21713634142367"/>
@@ -1374,29 +1501,29 @@
   <r>
     <x v="4"/>
     <s v="Google"/>
-    <x v="24"/>
-    <d v="2024-07-10T00:00:00"/>
-    <n v="9.9999999999999998E-20"/>
-    <n v="167.24"/>
-    <n v="1.6724000000000001E-17"/>
-    <n v="0.13854341066730447"/>
+    <x v="25"/>
+    <d v="2025-01-21T00:00:00"/>
+    <n v="5.3800000000000001E-2"/>
+    <n v="185.82"/>
+    <n v="9.9971160000000001"/>
+    <n v="2.4701323861801683E-2"/>
     <n v="0.26790000000000003"/>
-    <n v="0.51714598979956872"/>
-    <n v="2.6319955876619099E-2"/>
-    <n v="190.41"/>
-    <n v="1.9040999999999999E-17"/>
-    <n v="148.08431772538498"/>
-    <n v="23.169999999999987"/>
-    <n v="-9.5778411373075159"/>
-    <n v="13.592158862692472"/>
-    <n v="100.54028621849191"/>
-    <n v="9.9462617186788418E-3"/>
-    <n v="0.70198227953907921"/>
+    <n v="9.2203523187016356E-2"/>
+    <n v="4.7979235762306447E-3"/>
+    <n v="190.40999999999997"/>
+    <n v="10.244057999999999"/>
+    <n v="149.46927113630838"/>
+    <n v="4.589999999999975"/>
+    <n v="-18.175364431845807"/>
+    <n v="-13.585364431845832"/>
+    <n v="127.71780951303022"/>
+    <n v="7.8297615956056336E-3"/>
+    <n v="0.8917384506431304"/>
   </r>
   <r>
-    <x v="6"/>
+    <x v="5"/>
     <s v="LVMH"/>
-    <x v="25"/>
+    <x v="26"/>
     <d v="2024-09-27T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="668.82"/>
@@ -1404,7 +1531,7 @@
     <n v="0.05"/>
     <n v="0.28000000000000003"/>
     <n v="0.17857142857142858"/>
-    <n v="9.0883275004151626E-3"/>
+    <n v="9.2921836126180716E-3"/>
     <n v="702.26100000000008"/>
     <n v="7.0226100000000009E-17"/>
     <n v="543.7560975609756"/>
@@ -1412,13 +1539,13 @@
     <n v="-62.531951219512223"/>
     <n v="-29.090951219512192"/>
     <n v="143.22339630069658"/>
-    <n v="6.9820994741704541E-3"/>
+    <n v="6.9820994741704532E-3"/>
     <n v="1"/>
   </r>
   <r>
     <x v="4"/>
     <s v="ASML"/>
-    <x v="26"/>
+    <x v="27"/>
     <d v="2024-07-08T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="700.32"/>
@@ -1426,7 +1553,7 @@
     <n v="0.1"/>
     <n v="0.45340000000000003"/>
     <n v="0.22055580061755625"/>
-    <n v="1.1225106749520271E-2"/>
+    <n v="1.1476891978531363E-2"/>
     <n v="770.35200000000009"/>
     <n v="7.7035200000000004E-17"/>
     <n v="517.45234224915032"/>
@@ -1434,13 +1561,13 @@
     <n v="-91.433828875424865"/>
     <n v="-21.401828875424826"/>
     <n v="135.53427395660921"/>
-    <n v="7.3782075249847591E-3"/>
+    <n v="7.37820752498476E-3"/>
     <n v="0.94631378292451529"/>
   </r>
   <r>
     <x v="4"/>
     <s v="Nvidia"/>
-    <x v="27"/>
+    <x v="28"/>
     <d v="2024-07-09T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="147.01"/>
@@ -1448,7 +1575,7 @@
     <n v="0.15"/>
     <n v="0.52380000000000004"/>
     <n v="0.28636884306987398"/>
-    <n v="1.4574637457710454E-2"/>
+    <n v="1.4901554476134362E-2"/>
     <n v="169.06149999999997"/>
     <n v="1.6906149999999997E-17"/>
     <n v="107.00975396709855"/>
@@ -1462,7 +1589,7 @@
   <r>
     <x v="4"/>
     <s v="Applied Material"/>
-    <x v="28"/>
+    <x v="29"/>
     <d v="2024-07-08T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="169.34"/>
@@ -1470,7 +1597,7 @@
     <n v="0.1"/>
     <n v="0.4259"/>
     <n v="0.23479690068091102"/>
-    <n v="1.1949902325035199E-2"/>
+    <n v="1.2217945111683776E-2"/>
     <n v="186.27400000000003"/>
     <n v="1.8627400000000003E-17"/>
     <n v="127.71702239987934"/>
@@ -1478,13 +1605,13 @@
     <n v="-20.811488800060332"/>
     <n v="-3.8774888000603056"/>
     <n v="118.00993388124469"/>
-    <n v="8.4738628953585898E-3"/>
+    <n v="8.4738628953585915E-3"/>
     <n v="0.82395709729912847"/>
   </r>
   <r>
-    <x v="2"/>
+    <x v="0"/>
     <s v="Duke Energy"/>
-    <x v="29"/>
+    <x v="30"/>
     <d v="2024-08-07T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="113.58"/>
@@ -1492,7 +1619,7 @@
     <n v="6.664905793273479E-2"/>
     <n v="0.16439999999999999"/>
     <n v="0.40540789496797319"/>
-    <n v="2.0633086436047974E-2"/>
+    <n v="2.1095897749065375E-2"/>
     <n v="121.15000000000002"/>
     <n v="1.2115000000000002E-17"/>
     <n v="103.46609203186667"/>
@@ -1500,13 +1627,13 @@
     <n v="-5.0569539840666664"/>
     <n v="2.5130460159333552"/>
     <n v="111.61939906525103"/>
-    <n v="8.9590161600441413E-3"/>
+    <n v="8.9590161600441431E-3"/>
     <n v="0.77933774752071117"/>
   </r>
   <r>
     <x v="4"/>
     <s v="Palantir"/>
-    <x v="30"/>
+    <x v="31"/>
     <d v="2024-07-08T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="64.349999999999994"/>
@@ -1514,7 +1641,7 @@
     <n v="0.15"/>
     <n v="0.67300000000000004"/>
     <n v="0.22288261515601782"/>
-    <n v="1.1343529123846561E-2"/>
+    <n v="1.1597970630905169E-2"/>
     <n v="74.002499999999984"/>
     <n v="7.4002499999999988E-18"/>
     <n v="42.252133946158892"/>
@@ -1526,9 +1653,9 @@
     <n v="0.80663411909010196"/>
   </r>
   <r>
-    <x v="2"/>
+    <x v="0"/>
     <s v="Jinko Solar"/>
-    <x v="31"/>
+    <x v="32"/>
     <d v="2024-08-07T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="20.82"/>
@@ -1536,7 +1663,7 @@
     <n v="0.05"/>
     <n v="0.7389"/>
     <n v="6.7668155366084726E-2"/>
-    <n v="3.4439460009693403E-3"/>
+    <n v="3.521195576577426E-3"/>
     <n v="21.861000000000001"/>
     <n v="2.1860999999999999E-18"/>
     <n v="12.327550476641601"/>
@@ -1548,9 +1675,9 @@
     <n v="0.81926328291024408"/>
   </r>
   <r>
-    <x v="2"/>
+    <x v="0"/>
     <s v="SolarWinds"/>
-    <x v="32"/>
+    <x v="33"/>
     <d v="2024-08-07T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="13.04"/>
@@ -1558,7 +1685,7 @@
     <n v="5.2147239263803824E-2"/>
     <n v="0.30159999999999998"/>
     <n v="0.17290198694895167"/>
-    <n v="8.7997833440416531E-3"/>
+    <n v="8.9971672544104531E-3"/>
     <n v="13.72"/>
     <n v="1.3720000000000001E-18"/>
     <n v="10.436569040286594"/>
@@ -1570,9 +1697,9 @@
     <n v="0.80122496411211674"/>
   </r>
   <r>
-    <x v="2"/>
+    <x v="0"/>
     <s v="Canadian Solar"/>
-    <x v="33"/>
+    <x v="34"/>
     <d v="2024-08-07T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="11.05"/>
@@ -1580,7 +1707,7 @@
     <n v="0.05"/>
     <n v="0.72170000000000001"/>
     <n v="6.9280864625190522E-2"/>
-    <n v="3.5260242484636906E-3"/>
+    <n v="3.6051148836539555E-3"/>
     <n v="11.602500000000001"/>
     <n v="1.16025E-18"/>
     <n v="6.6100376861877139"/>
@@ -1588,21 +1715,21 @@
     <n v="-2.2199811569061434"/>
     <n v="-1.6674811569061432"/>
     <n v="115.79992623809053"/>
-    <n v="8.6355840844315329E-3"/>
+    <n v="8.6355840844315312E-3"/>
     <n v="0.80852660409594923"/>
   </r>
   <r>
     <x v="7"/>
     <s v="Gold"/>
-    <x v="34"/>
-    <d v="2025-01-14T00:00:00"/>
+    <x v="35"/>
+    <d v="2025-01-20T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="2742.9"/>
     <n v="2.7429000000000002E-16"/>
     <n v="0.1"/>
     <n v="0.5"/>
     <n v="0.2"/>
-    <n v="1.0178926800464982E-2"/>
+    <n v="1.040724564613224E-2"/>
     <n v="3017.1900000000005"/>
     <n v="3.0171900000000003E-16"/>
     <n v="1959.214285714286"/>
@@ -1616,7 +1743,7 @@
   <r>
     <x v="3"/>
     <s v="Walmart"/>
-    <x v="35"/>
+    <x v="36"/>
     <d v="2024-08-01T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="86.6"/>
@@ -1624,7 +1751,7 @@
     <n v="7.0000000000000007E-2"/>
     <n v="0.17249999999999999"/>
     <n v="0.40579710144927544"/>
-    <n v="2.0652894957465185E-2"/>
+    <n v="2.1116150586355274E-2"/>
     <n v="92.662000000000006"/>
     <n v="9.2662000000000008E-18"/>
     <n v="78.548752834467123"/>
@@ -1638,7 +1765,7 @@
   <r>
     <x v="8"/>
     <s v="Aptive Autoparts"/>
-    <x v="36"/>
+    <x v="37"/>
     <d v="2024-09-27T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="56"/>
@@ -1646,7 +1773,7 @@
     <n v="7.0000000000000007E-2"/>
     <n v="0.19"/>
     <n v="0.36842105263157898"/>
-    <n v="1.8750654632435495E-2"/>
+    <n v="1.9171241979717285E-2"/>
     <n v="59.92"/>
     <n v="5.9920000000000002E-18"/>
     <n v="50.000000000000007"/>
@@ -1660,7 +1787,7 @@
   <r>
     <x v="7"/>
     <s v="Mexican Peso"/>
-    <x v="37"/>
+    <x v="38"/>
     <d v="2024-10-15T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="20.399999999999999"/>
@@ -1668,7 +1795,7 @@
     <n v="0.1"/>
     <n v="0.15"/>
     <n v="0.66666666666666674"/>
-    <n v="3.3929756001549939E-2"/>
+    <n v="3.4690818820440804E-2"/>
     <n v="21.2"/>
     <n v="2.1199999999999999E-18"/>
     <n v="19.428571428571431"/>
@@ -1680,9 +1807,9 @@
     <n v="0.79468971066667204"/>
   </r>
   <r>
-    <x v="6"/>
+    <x v="5"/>
     <s v="Yum China Holding"/>
-    <x v="38"/>
+    <x v="39"/>
     <d v="2024-10-09T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="47.42"/>
@@ -1690,7 +1817,7 @@
     <n v="7.0000000000000007E-2"/>
     <n v="0.4"/>
     <n v="0.17500000000000002"/>
-    <n v="8.90656095040686E-3"/>
+    <n v="9.1063399403657104E-3"/>
     <n v="50.739400000000003"/>
     <n v="5.0739400000000001E-18"/>
     <n v="35.654135338345867"/>
@@ -1698,13 +1825,13 @@
     <n v="-5.8829323308270673"/>
     <n v="-2.5635323308270657"/>
     <n v="116.69597741201144"/>
-    <n v="8.5692756697975988E-3"/>
+    <n v="8.5692756697976005E-3"/>
     <n v="0.81478292252621221"/>
   </r>
   <r>
-    <x v="6"/>
+    <x v="5"/>
     <s v="MSG"/>
-    <x v="39"/>
+    <x v="40"/>
     <d v="2024-08-03T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="41.8"/>
@@ -1712,7 +1839,7 @@
     <n v="7.0000000000000007E-2"/>
     <n v="0.4"/>
     <n v="0.17500000000000002"/>
-    <n v="8.90656095040686E-3"/>
+    <n v="9.1063399403657104E-3"/>
     <n v="44.725999999999999"/>
     <n v="4.4725999999999996E-18"/>
     <n v="31.428571428571431"/>
@@ -1720,13 +1847,13 @@
     <n v="-5.1857142857142833"/>
     <n v="-2.2597142857142813"/>
     <n v="116.39215936689867"/>
-    <n v="8.5916440200042802E-3"/>
+    <n v="8.5916440200042785E-3"/>
     <n v="0.81266163471318675"/>
   </r>
   <r>
     <x v="7"/>
     <s v="Japan Yen"/>
-    <x v="40"/>
+    <x v="41"/>
     <d v="2024-10-09T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="153.7552"/>
@@ -1734,7 +1861,7 @@
     <n v="7.0000000000000007E-2"/>
     <n v="0.19"/>
     <n v="0.36842105263157898"/>
-    <n v="1.8750654632435495E-2"/>
+    <n v="1.9171241979717285E-2"/>
     <n v="164.51806400000001"/>
     <n v="1.6451806399999999E-17"/>
     <n v="137.28142857142859"/>
@@ -1742,13 +1869,13 @@
     <n v="-8.2368857142857053"/>
     <n v="2.5259782857143023"/>
     <n v="111.60646679547008"/>
-    <n v="8.9600542756415654E-3"/>
+    <n v="8.9600542756415637E-3"/>
     <n v="0.77924745312667376"/>
   </r>
   <r>
     <x v="9"/>
     <s v="3M"/>
-    <x v="41"/>
+    <x v="42"/>
     <d v="2024-12-01T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="133.53"/>
@@ -1756,7 +1883,7 @@
     <n v="7.0000000000000007E-2"/>
     <n v="0.2"/>
     <n v="0.35000000000000003"/>
-    <n v="1.781312190081372E-2"/>
+    <n v="1.8212679880731421E-2"/>
     <n v="142.87710000000001"/>
     <n v="1.428771E-17"/>
     <n v="118.16814159292036"/>
@@ -1768,9 +1895,9 @@
     <n v="0.78525071454528272"/>
   </r>
   <r>
-    <x v="2"/>
+    <x v="0"/>
     <s v="PG&amp;E"/>
-    <x v="42"/>
+    <x v="43"/>
     <d v="2024-12-01T00:00:00"/>
     <n v="9.9999999999999998E-20"/>
     <n v="26.63"/>
@@ -1778,7 +1905,7 @@
     <n v="0.1"/>
     <n v="0.2"/>
     <n v="0.5"/>
-    <n v="2.5447317001162453E-2"/>
+    <n v="2.6018114115330598E-2"/>
     <n v="29.293000000000003"/>
     <n v="2.9293000000000003E-18"/>
     <n v="24.209090909090911"/>
@@ -1790,29 +1917,7 @@
     <n v="0.78674226793273505"/>
   </r>
   <r>
-    <x v="3"/>
-    <s v="Albertson Companies"/>
-    <x v="43"/>
-    <d v="2024-12-04T00:00:00"/>
-    <n v="9.9999999999999998E-20"/>
-    <n v="19.309999999999999"/>
-    <n v="1.931E-18"/>
-    <n v="0.2"/>
-    <n v="0.2"/>
-    <n v="1"/>
-    <n v="5.0894634002324905E-2"/>
-    <n v="23.171999999999997"/>
-    <n v="2.3171999999999995E-18"/>
-    <n v="19.309999999999999"/>
-    <n v="3.8619999999999983"/>
-    <n v="0"/>
-    <n v="3.8619999999999983"/>
-    <n v="110.27044508118439"/>
-    <n v="9.0686130745529329E-3"/>
-    <n v="0.76991921661787932"/>
-  </r>
-  <r>
-    <x v="5"/>
+    <x v="6"/>
     <s v="HCA Healthcare"/>
     <x v="44"/>
     <d v="2024-12-04T00:00:00"/>
@@ -1822,7 +1927,7 @@
     <n v="0.2"/>
     <n v="0.2"/>
     <n v="1"/>
-    <n v="5.0894634002324905E-2"/>
+    <n v="5.2036228230661195E-2"/>
     <n v="388.5"/>
     <n v="3.8849999999999999E-17"/>
     <n v="323.75"/>
@@ -1899,25 +2004,91 @@
     <m/>
     <m/>
   </r>
+  <r>
+    <x v="10"/>
+    <m/>
+    <x v="45"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="10"/>
+    <m/>
+    <x v="45"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="10"/>
+    <m/>
+    <x v="45"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{42F2A961-4B24-4134-99E9-0FE83E8807F0}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{42F2A961-4B24-4134-99E9-0FE83E8807F0}" name="PivotTable1" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:E14" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="22">
     <pivotField axis="axisRow" showAll="0" sortType="descending">
       <items count="12">
+        <item sd="0" x="5"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="0"/>
+        <item sd="0" x="7"/>
         <item sd="0" x="6"/>
-        <item sd="0" x="8"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="5"/>
         <item sd="0" x="9"/>
         <item sd="0" x="4"/>
         <item sd="0" x="3"/>
-        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
         <item h="1" sd="0" x="10"/>
         <item t="default" sd="0"/>
       </items>
@@ -1932,56 +2103,65 @@
       </autoSortScope>
     </pivotField>
     <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
       <items count="47">
         <item x="18"/>
-        <item x="43"/>
+        <item x="8"/>
+        <item x="16"/>
+        <item x="29"/>
+        <item x="0"/>
+        <item x="37"/>
+        <item x="27"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item x="1"/>
+        <item x="34"/>
+        <item x="40"/>
+        <item x="30"/>
+        <item x="10"/>
+        <item x="17"/>
+        <item x="35"/>
+        <item x="25"/>
+        <item x="44"/>
+        <item x="3"/>
+        <item x="15"/>
+        <item x="32"/>
+        <item x="11"/>
+        <item x="20"/>
+        <item x="22"/>
+        <item x="26"/>
+        <item x="42"/>
+        <item x="4"/>
+        <item x="19"/>
         <item x="13"/>
         <item x="28"/>
-        <item x="3"/>
+        <item x="43"/>
+        <item x="12"/>
+        <item x="31"/>
+        <item x="24"/>
+        <item x="33"/>
+        <item x="14"/>
+        <item x="41"/>
+        <item x="38"/>
+        <item x="23"/>
+        <item x="6"/>
         <item x="36"/>
-        <item x="26"/>
-        <item x="1"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="33"/>
+        <item x="9"/>
+        <item x="21"/>
         <item x="39"/>
-        <item x="29"/>
-        <item x="14"/>
-        <item x="16"/>
-        <item x="34"/>
-        <item x="24"/>
-        <item x="44"/>
-        <item x="2"/>
-        <item x="17"/>
-        <item x="31"/>
-        <item x="12"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="25"/>
-        <item x="41"/>
-        <item x="4"/>
-        <item x="19"/>
-        <item x="9"/>
-        <item x="27"/>
-        <item x="42"/>
-        <item x="10"/>
-        <item x="30"/>
-        <item x="23"/>
-        <item x="32"/>
-        <item x="11"/>
-        <item x="40"/>
-        <item x="37"/>
-        <item x="22"/>
-        <item x="6"/>
-        <item x="35"/>
-        <item x="8"/>
-        <item x="15"/>
-        <item x="38"/>
         <item x="45"/>
         <item x="5"/>
         <item t="default"/>
       </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
     </pivotField>
     <pivotField numFmtId="165" showAll="0"/>
     <pivotField numFmtId="164" showAll="0"/>
@@ -2009,10 +2189,10 @@
   </rowFields>
   <rowItems count="11">
     <i>
-      <x v="9"/>
+      <x v="8"/>
     </i>
     <i>
-      <x v="8"/>
+      <x v="9"/>
     </i>
     <i>
       <x v="7"/>
@@ -2072,7 +2252,7 @@
     <dataField name="Target P&amp;L" fld="21" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="2">
+    <format dxfId="35">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -2082,7 +2262,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="1">
+    <format dxfId="34">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -2092,7 +2272,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="0">
+    <format dxfId="33">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -2466,76 +2646,76 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>40</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="D2" s="8">
-        <v>45481</v>
+        <v>45627</v>
       </c>
       <c r="E2" s="2">
-        <v>2</v>
+        <v>2.2953000000000001</v>
       </c>
       <c r="F2" s="1">
-        <v>20.928000000000001</v>
+        <v>21.78</v>
       </c>
       <c r="G2" s="1">
         <f>E2*F2</f>
-        <v>41.856000000000002</v>
+        <v>49.991634000000005</v>
       </c>
       <c r="H2" s="13">
-        <v>4.4999999999999998E-2</v>
+        <f>L2/F2-1</f>
+        <v>0.22038567493112926</v>
       </c>
       <c r="I2" s="11">
-        <v>0.2</v>
+        <v>0.45929999999999999</v>
       </c>
       <c r="J2" s="9">
         <f>IFERROR(H2/I2,"")</f>
-        <v>0.22499999999999998</v>
+        <v>0.47982946860685666</v>
       </c>
       <c r="K2" s="9">
         <f>IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.1451292650523102E-2</v>
+        <v>2.4968515740223275E-2</v>
       </c>
       <c r="L2" s="12">
-        <f>F2/(1-(F2*(1+H2)-F2)/(F2*(1+H2)))</f>
-        <v>21.869759999999999</v>
+        <v>26.58</v>
       </c>
       <c r="M2" s="12">
         <f>L2*E2</f>
-        <v>43.739519999999999</v>
+        <v>61.009073999999998</v>
       </c>
       <c r="N2" s="12">
         <f>F2/(1+I2-H2)</f>
-        <v>18.119480519480518</v>
+        <v>17.579908117366596</v>
       </c>
       <c r="O2" s="12">
         <f>L2-F2</f>
-        <v>0.9417599999999986</v>
+        <v>4.7999999999999972</v>
       </c>
       <c r="P2" s="12">
         <f>0.5*(N2-F2)</f>
-        <v>-1.4042597402597412</v>
+        <v>-2.1000459413167025</v>
       </c>
       <c r="Q2" s="15">
         <f>O2+P2</f>
-        <v>-0.46249974025974261</v>
+        <v>2.6999540586832946</v>
       </c>
       <c r="R2" s="12">
         <f>MAX($Q$2:$Q$279)-Q2</f>
-        <v>114.59494482144413</v>
+        <v>111.4324910225011</v>
       </c>
       <c r="S2" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R2)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.7263884245343277E-3</v>
+        <v>8.9740433048209802E-3</v>
       </c>
       <c r="T2" s="9">
         <f>R2/MAX($R$2:$R$28)</f>
-        <v>0.80011330398039715</v>
+        <v>0.77803273697370867</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -2543,10 +2723,10 @@
         <v>115</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D3" s="8">
         <v>45481</v>
@@ -2555,11 +2735,11 @@
         <v>2</v>
       </c>
       <c r="F3" s="1">
-        <v>16.399999999999999</v>
+        <v>20.928000000000001</v>
       </c>
       <c r="G3" s="1">
         <f>E3*F3</f>
-        <v>32.799999999999997</v>
+        <v>41.856000000000002</v>
       </c>
       <c r="H3" s="13">
         <v>4.4999999999999998E-2</v>
@@ -2573,191 +2753,191 @@
       </c>
       <c r="K3" s="9">
         <f>IFERROR(J3/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.1451292650523102E-2</v>
+        <v>1.1708151351898769E-2</v>
       </c>
       <c r="L3" s="12">
         <f>F3/(1-(F3*(1+H3)-F3)/(F3*(1+H3)))</f>
-        <v>17.137999999999998</v>
+        <v>21.869759999999999</v>
       </c>
       <c r="M3" s="12">
         <f>L3*E3</f>
-        <v>34.275999999999996</v>
+        <v>43.739519999999999</v>
       </c>
       <c r="N3" s="12">
         <f>F3/(1+I3-H3)</f>
-        <v>14.199134199134198</v>
+        <v>18.119480519480518</v>
       </c>
       <c r="O3" s="12">
         <f>L3-F3</f>
-        <v>0.73799999999999955</v>
+        <v>0.9417599999999986</v>
       </c>
       <c r="P3" s="12">
         <f>0.5*(N3-F3)</f>
-        <v>-1.1004329004329003</v>
+        <v>-1.4042597402597412</v>
       </c>
       <c r="Q3" s="15">
         <f>O3+P3</f>
-        <v>-0.36243290043290077</v>
+        <v>-0.46249974025974261</v>
       </c>
       <c r="R3" s="12">
         <f>MAX($Q$2:$Q$279)-Q3</f>
-        <v>114.49487798161729</v>
+        <v>114.59494482144413</v>
       </c>
       <c r="S3" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R3)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.7340151597048287E-3</v>
+        <v>8.7263884245343277E-3</v>
       </c>
       <c r="T3" s="9">
         <f>R3/MAX($R$2:$R$28)</f>
-        <v>0.79941462735066027</v>
+        <v>0.80011330398039715</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="C4" s="32" t="s">
-        <v>86</v>
+        <v>115</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C4" t="s">
+        <v>117</v>
       </c>
       <c r="D4" s="8">
-        <v>45623</v>
+        <v>45481</v>
       </c>
       <c r="E4" s="2">
-        <v>1.9595</v>
+        <v>2</v>
       </c>
       <c r="F4" s="1">
-        <v>15.3</v>
+        <v>16.399000000000001</v>
       </c>
       <c r="G4" s="1">
         <f>E4*F4</f>
-        <v>29.980350000000001</v>
+        <v>32.798000000000002</v>
       </c>
       <c r="H4" s="13">
-        <v>0.35</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="I4" s="11">
-        <v>0.39532299999999998</v>
+        <v>0.2</v>
       </c>
       <c r="J4" s="9">
         <f>IFERROR(H4/I4,"")</f>
-        <v>0.88535197800279775</v>
+        <v>0.22499999999999998</v>
       </c>
       <c r="K4" s="9">
         <f>IFERROR(J4/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.5059664883686804E-2</v>
+        <v>1.1708151351898769E-2</v>
       </c>
       <c r="L4" s="12">
         <f>F4/(1-(F4*(1+H4)-F4)/(F4*(1+H4)))</f>
-        <v>20.655000000000001</v>
+        <v>17.136955</v>
       </c>
       <c r="M4" s="12">
         <f>L4*E4</f>
-        <v>40.4734725</v>
+        <v>34.273910000000001</v>
       </c>
       <c r="N4" s="12">
         <f>F4/(1+I4-H4)</f>
-        <v>14.636624277854791</v>
+        <v>14.198268398268398</v>
       </c>
       <c r="O4" s="12">
         <f>L4-F4</f>
-        <v>5.3550000000000004</v>
+        <v>0.73795499999999947</v>
       </c>
       <c r="P4" s="12">
         <f>0.5*(N4-F4)</f>
-        <v>-0.33168786107260484</v>
+        <v>-1.1003658008658013</v>
       </c>
       <c r="Q4" s="15">
         <f>O4+P4</f>
-        <v>5.0233121389273956</v>
+        <v>-0.3624108008658018</v>
       </c>
       <c r="R4" s="12">
         <f>MAX($Q$2:$Q$279)-Q4</f>
-        <v>109.10913294225699</v>
+        <v>114.49485588205019</v>
       </c>
       <c r="S4" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R4)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>9.165135612700933E-3</v>
+        <v>8.7340168455268905E-3</v>
       </c>
       <c r="T4" s="9">
         <f>R4/MAX($R$2:$R$28)</f>
-        <v>0.76181081974332665</v>
+        <v>0.79941447304928448</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C5" t="s">
-        <v>94</v>
+        <v>37</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>86</v>
       </c>
       <c r="D5" s="8">
-        <v>45627</v>
+        <v>45623</v>
       </c>
       <c r="E5" s="2">
-        <v>1.8976999999999999</v>
+        <v>1.9595</v>
       </c>
       <c r="F5" s="1">
-        <v>21.73</v>
+        <v>15.3</v>
       </c>
       <c r="G5" s="1">
         <f>E5*F5</f>
-        <v>41.237020999999999</v>
+        <v>29.980350000000001</v>
       </c>
       <c r="H5" s="13">
-        <f>L5/F5-1</f>
-        <v>0.22319374137137582</v>
+        <v>0.35</v>
       </c>
       <c r="I5" s="11">
-        <v>0.45929999999999999</v>
+        <v>0.39532299999999998</v>
       </c>
       <c r="J5" s="9">
         <f>IFERROR(H5/I5,"")</f>
-        <v>0.48594326447066366</v>
+        <v>0.88535197800279775</v>
       </c>
       <c r="K5" s="9">
         <f>IFERROR(J5/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.4731904591129405E-2</v>
+        <v>4.6070377591820914E-2</v>
       </c>
       <c r="L5" s="12">
-        <v>26.58</v>
+        <f>F5/(1-(F5*(1+H5)-F5)/(F5*(1+H5)))</f>
+        <v>20.655000000000001</v>
       </c>
       <c r="M5" s="12">
         <f>L5*E5</f>
-        <v>50.440865999999993</v>
+        <v>40.4734725</v>
       </c>
       <c r="N5" s="12">
         <f>F5/(1+I5-H5)</f>
-        <v>17.579394852436032</v>
+        <v>14.636624277854791</v>
       </c>
       <c r="O5" s="12">
         <f>L5-F5</f>
-        <v>4.8499999999999979</v>
+        <v>5.3550000000000004</v>
       </c>
       <c r="P5" s="12">
         <f>0.5*(N5-F5)</f>
-        <v>-2.0753025737819843</v>
+        <v>-0.33168786107260484</v>
       </c>
       <c r="Q5" s="15">
         <f>O5+P5</f>
-        <v>2.7746974262180135</v>
+        <v>5.0233121389273956</v>
       </c>
       <c r="R5" s="12">
         <f>MAX($Q$2:$Q$279)-Q5</f>
-        <v>111.35774765496637</v>
+        <v>109.10913294225699</v>
       </c>
       <c r="S5" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R5)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.980066686499668E-3</v>
+        <v>9.1651356127009313E-3</v>
       </c>
       <c r="T5" s="9">
         <f>R5/MAX($R$2:$R$28)</f>
-        <v>0.77751087134654673</v>
+        <v>0.76181081974332665</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -2796,7 +2976,7 @@
       </c>
       <c r="K6" s="9">
         <f>IFERROR(J6/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.6946351584727132E-2</v>
+        <v>4.7999383698252546E-2</v>
       </c>
       <c r="L6" s="12">
         <f>F6/(1-(F6*(1+H6)-F6)/(F6*(1+H6)))</f>
@@ -2870,7 +3050,7 @@
       </c>
       <c r="K7" s="9">
         <f>IFERROR(J7/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.1451292650523102E-2</v>
+        <v>1.1708151351898769E-2</v>
       </c>
       <c r="L7" s="12">
         <f>F7/(1-(F7*(1+H7)-F7)/(F7*(1+H7)))</f>
@@ -2944,7 +3124,7 @@
       </c>
       <c r="K8" s="9">
         <f>IFERROR(J8/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>6.3618292502906132E-3</v>
+        <v>6.5045285288326494E-3</v>
       </c>
       <c r="L8" s="12">
         <f>F8/(1-(F8*(1+H8)-F8)/(F8*(1+H8)))</f>
@@ -2976,7 +3156,7 @@
       </c>
       <c r="S8" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R8)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.5807042049865865E-3</v>
+        <v>8.5807042049865848E-3</v>
       </c>
       <c r="T8" s="9">
         <f>R8/MAX($R$2:$R$28)</f>
@@ -3018,7 +3198,7 @@
       </c>
       <c r="K9" s="9">
         <f>IFERROR(J9/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>6.3618292502906132E-3</v>
+        <v>6.5045285288326494E-3</v>
       </c>
       <c r="L9" s="12">
         <f>F9/(1-(F9*(1+H9)-F9)/(F9*(1+H9)))</f>
@@ -3059,76 +3239,76 @@
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="C10" t="s">
-        <v>103</v>
+        <v>38</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C10" s="32" t="s">
+        <v>98</v>
       </c>
       <c r="D10" s="8">
-        <v>45627</v>
+        <v>45630</v>
       </c>
       <c r="E10" s="2">
-        <v>0.95840000000000003</v>
+        <v>1</v>
       </c>
       <c r="F10" s="1">
-        <v>41.76</v>
+        <v>20.36</v>
       </c>
       <c r="G10" s="1">
         <f>E10*F10</f>
-        <v>40.022784000000001</v>
+        <v>20.36</v>
       </c>
       <c r="H10" s="13">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="I10" s="11">
         <v>0.2</v>
       </c>
       <c r="J10" s="9">
         <f>IFERROR(H10/I10,"")</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K10" s="9">
         <f>IFERROR(J10/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.5447317001162453E-2</v>
+        <v>5.2036228230661195E-2</v>
       </c>
       <c r="L10" s="12">
         <f>F10/(1-(F10*(1+H10)-F10)/(F10*(1+H10)))</f>
-        <v>45.936</v>
+        <v>24.431999999999999</v>
       </c>
       <c r="M10" s="12">
         <f>L10*E10</f>
-        <v>44.025062400000003</v>
+        <v>24.431999999999999</v>
       </c>
       <c r="N10" s="12">
         <f>F10/(1+I10-H10)</f>
-        <v>37.963636363636368</v>
+        <v>20.36</v>
       </c>
       <c r="O10" s="12">
         <f>L10-F10</f>
-        <v>4.1760000000000019</v>
+        <v>4.0719999999999992</v>
       </c>
       <c r="P10" s="12">
         <f>0.5*(N10-F10)</f>
-        <v>-1.8981818181818149</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="15">
         <f>O10+P10</f>
-        <v>2.2778181818181871</v>
+        <v>4.0719999999999992</v>
       </c>
       <c r="R10" s="12">
         <f>MAX($Q$2:$Q$279)-Q10</f>
-        <v>111.8546268993662</v>
+        <v>110.06044508118438</v>
       </c>
       <c r="S10" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R10)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.9401755449927331E-3</v>
+        <v>9.0859163731562727E-3</v>
       </c>
       <c r="T10" s="9">
         <f>R10/MAX($R$2:$R$28)</f>
-        <v>0.78098013165759694</v>
+        <v>0.76845297572830351</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -3136,222 +3316,221 @@
         <v>40</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="D11" s="8">
-        <v>45511</v>
+        <v>45627</v>
       </c>
       <c r="E11" s="2">
-        <v>0.45179999999999998</v>
+        <v>0.95840000000000003</v>
       </c>
       <c r="F11" s="1">
-        <v>77.430000000000007</v>
+        <v>41.76</v>
       </c>
       <c r="G11" s="1">
         <f>E11*F11</f>
-        <v>34.982874000000002</v>
+        <v>40.022784000000001</v>
       </c>
       <c r="H11" s="13">
         <v>0.1</v>
       </c>
       <c r="I11" s="11">
-        <v>0.25990000000000002</v>
+        <v>0.2</v>
       </c>
       <c r="J11" s="9">
         <f>IFERROR(H11/I11,"")</f>
-        <v>0.38476337052712584</v>
+        <v>0.5</v>
       </c>
       <c r="K11" s="9">
         <f>IFERROR(J11/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.9582390920478997E-2</v>
+        <v>2.6018114115330598E-2</v>
       </c>
       <c r="L11" s="12">
         <f>F11/(1-(F11*(1+H11)-F11)/(F11*(1+H11)))</f>
-        <v>85.173000000000016</v>
+        <v>45.936</v>
       </c>
       <c r="M11" s="12">
         <f>L11*E11</f>
-        <v>38.481161400000005</v>
+        <v>44.025062400000003</v>
       </c>
       <c r="N11" s="12">
         <f>F11/(1+I11-H11)</f>
-        <v>66.755754806448849</v>
+        <v>37.963636363636368</v>
       </c>
       <c r="O11" s="12">
         <f>L11-F11</f>
-        <v>7.7430000000000092</v>
+        <v>4.1760000000000019</v>
       </c>
       <c r="P11" s="12">
         <f>0.5*(N11-F11)</f>
-        <v>-5.3371225967755791</v>
+        <v>-1.8981818181818149</v>
       </c>
       <c r="Q11" s="15">
         <f>O11+P11</f>
-        <v>2.4058774032244301</v>
+        <v>2.2778181818181871</v>
       </c>
       <c r="R11" s="12">
         <f>MAX($Q$2:$Q$279)-Q11</f>
-        <v>111.72656767795996</v>
+        <v>111.8546268993662</v>
       </c>
       <c r="S11" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R11)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.9504226325326178E-3</v>
+        <v>8.9401755449927331E-3</v>
       </c>
       <c r="T11" s="9">
         <f>R11/MAX($R$2:$R$28)</f>
-        <v>0.78008600943515383</v>
+        <v>0.78098013165759694</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" t="s">
-        <v>16</v>
+        <v>40</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="32" t="s">
+        <v>91</v>
       </c>
       <c r="D12" s="8">
-        <v>45460</v>
+        <v>45627</v>
       </c>
       <c r="E12" s="2">
-        <v>0.43659999999999999</v>
+        <v>0.52039999999999997</v>
       </c>
       <c r="F12" s="1">
-        <v>160.25</v>
+        <v>40.340000000000003</v>
       </c>
       <c r="G12" s="1">
         <f>E12*F12</f>
-        <v>69.965149999999994</v>
+        <v>20.992936</v>
       </c>
       <c r="H12" s="13">
-        <v>6.7199999999999996E-2</v>
+        <v>0.1</v>
       </c>
       <c r="I12" s="11">
-        <v>0.16439999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="J12" s="9">
         <f>IFERROR(H12/I12,"")</f>
-        <v>0.40875912408759124</v>
+        <v>0.5</v>
       </c>
       <c r="K12" s="9">
         <f>IFERROR(J12/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.0803646015548866E-2</v>
+        <v>2.6018114115330598E-2</v>
       </c>
       <c r="L12" s="12">
         <f>F12/(1-(F12*(1+H12)-F12)/(F12*(1+H12)))</f>
-        <v>171.0188</v>
+        <v>44.374000000000009</v>
       </c>
       <c r="M12" s="12">
         <f>L12*E12</f>
-        <v>74.666808079999996</v>
+        <v>23.092229600000003</v>
       </c>
       <c r="N12" s="12">
         <f>F12/(1+I12-H12)</f>
-        <v>146.05359095880419</v>
+        <v>36.672727272727279</v>
       </c>
       <c r="O12" s="12">
         <f>L12-F12</f>
-        <v>10.768799999999999</v>
+        <v>4.034000000000006</v>
       </c>
       <c r="P12" s="12">
         <f>0.5*(N12-F12)</f>
-        <v>-7.0982045205979034</v>
+        <v>-1.8336363636363622</v>
       </c>
       <c r="Q12" s="15">
         <f>O12+P12</f>
-        <v>3.6705954794020954</v>
+        <v>2.2003636363636438</v>
       </c>
       <c r="R12" s="12">
         <f>MAX($Q$2:$Q$279)-Q12</f>
-        <v>110.46184960178229</v>
+        <v>111.93208144482074</v>
       </c>
       <c r="S12" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R12)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>9.0528992915203284E-3</v>
+        <v>8.9339891395923948E-3</v>
       </c>
       <c r="T12" s="9">
         <f>R12/MAX($R$2:$R$28)</f>
-        <v>0.7712556220204998</v>
+        <v>0.78152092699868725</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>21</v>
+        <v>38</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D13" s="8">
-        <v>45484</v>
+        <v>45544</v>
       </c>
       <c r="E13" s="2">
-        <v>0.4108</v>
+        <v>0.51380000000000003</v>
       </c>
       <c r="F13" s="1">
-        <v>189.76</v>
+        <v>138.53</v>
       </c>
       <c r="G13" s="1">
         <f>E13*F13</f>
-        <v>77.953407999999996</v>
+        <v>71.176714000000004</v>
       </c>
       <c r="H13" s="13">
-        <f>227.4/F13-1</f>
-        <v>0.19835581787521095</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I13" s="11">
-        <v>0.37</v>
+        <v>0.18340000000000001</v>
       </c>
       <c r="J13" s="9">
         <f>IFERROR(H13/I13,"")</f>
-        <v>0.53609680506813773</v>
+        <v>0.38167938931297712</v>
       </c>
       <c r="K13" s="9">
         <f>IFERROR(J13/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.728445068375859E-2</v>
+        <v>1.9861155813229465E-2</v>
       </c>
       <c r="L13" s="12">
         <f>F13/(1-(F13*(1+H13)-F13)/(F13*(1+H13)))</f>
-        <v>227.4</v>
+        <v>148.22710000000001</v>
       </c>
       <c r="M13" s="12">
         <f>L13*E13</f>
-        <v>93.41592</v>
+        <v>76.159083980000005</v>
       </c>
       <c r="N13" s="12">
         <f>F13/(1+I13-H13)</f>
-        <v>161.96043380326287</v>
+        <v>124.42069337165439</v>
       </c>
       <c r="O13" s="12">
         <f>L13-F13</f>
-        <v>37.640000000000015</v>
+        <v>9.697100000000006</v>
       </c>
       <c r="P13" s="12">
         <f>0.5*(N13-F13)</f>
-        <v>-13.899783098368559</v>
+        <v>-7.0546533141728034</v>
       </c>
       <c r="Q13" s="15">
         <f>O13+P13</f>
-        <v>23.740216901631456</v>
+        <v>2.6424466858272027</v>
       </c>
       <c r="R13" s="12">
         <f>MAX($Q$2:$Q$279)-Q13</f>
-        <v>90.39222817955293</v>
+        <v>111.48999839535719</v>
       </c>
       <c r="S13" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R13)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>1.1062897996204102E-2</v>
+        <v>8.969414426340536E-3</v>
       </c>
       <c r="T13" s="9">
         <f>R13/MAX($R$2:$R$28)</f>
-        <v>0.6311275288415521</v>
+        <v>0.77843425917148812</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -3359,369 +3538,370 @@
         <v>38</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D14" s="8">
-        <v>45544</v>
+        <v>45460</v>
       </c>
       <c r="E14" s="2">
-        <v>0.35149999999999998</v>
+        <v>0.51239999999999997</v>
       </c>
       <c r="F14" s="1">
-        <v>142.78</v>
+        <v>157.99</v>
       </c>
       <c r="G14" s="1">
         <f>E14*F14</f>
-        <v>50.187169999999995</v>
+        <v>80.954076000000001</v>
       </c>
       <c r="H14" s="13">
-        <v>7.0000000000000007E-2</v>
+        <v>6.7199999999999996E-2</v>
       </c>
       <c r="I14" s="11">
-        <v>0.18340000000000001</v>
+        <v>0.16439999999999999</v>
       </c>
       <c r="J14" s="9">
         <f>IFERROR(H14/I14,"")</f>
-        <v>0.38167938931297712</v>
+        <v>0.40875912408759124</v>
       </c>
       <c r="K14" s="9">
         <f>IFERROR(J14/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.9425432825314851E-2</v>
+        <v>2.1270283072387059E-2</v>
       </c>
       <c r="L14" s="12">
         <f>F14/(1-(F14*(1+H14)-F14)/(F14*(1+H14)))</f>
-        <v>152.77460000000002</v>
+        <v>168.60692800000001</v>
       </c>
       <c r="M14" s="12">
         <f>L14*E14</f>
-        <v>53.700271900000004</v>
+        <v>86.394189907200001</v>
       </c>
       <c r="N14" s="12">
         <f>F14/(1+I14-H14)</f>
-        <v>128.23783007005568</v>
+        <v>143.99380240612467</v>
       </c>
       <c r="O14" s="12">
         <f>L14-F14</f>
-        <v>9.9946000000000197</v>
+        <v>10.616928000000001</v>
       </c>
       <c r="P14" s="12">
         <f>0.5*(N14-F14)</f>
-        <v>-7.2710849649721609</v>
+        <v>-6.9980987969376685</v>
       </c>
       <c r="Q14" s="15">
         <f>O14+P14</f>
-        <v>2.7235150350278587</v>
+        <v>3.618829203062333</v>
       </c>
       <c r="R14" s="12">
         <f>MAX($Q$2:$Q$279)-Q14</f>
-        <v>111.40893004615653</v>
+        <v>110.51361587812205</v>
       </c>
       <c r="S14" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R14)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.9759411528833617E-3</v>
+        <v>9.0486587743435348E-3</v>
       </c>
       <c r="T14" s="9">
         <f>R14/MAX($R$2:$R$28)</f>
-        <v>0.77786823189316223</v>
+        <v>0.77161705931131142</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>39</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="D15" s="8">
-        <v>45580</v>
+        <v>45511</v>
       </c>
       <c r="E15" s="2">
-        <v>0.34860000000000002</v>
+        <v>0.45179999999999998</v>
       </c>
       <c r="F15" s="1">
-        <v>131.91</v>
+        <v>77.430000000000007</v>
       </c>
       <c r="G15" s="1">
         <f>E15*F15</f>
-        <v>45.983826000000001</v>
+        <v>34.982874000000002</v>
       </c>
       <c r="H15" s="13">
-        <v>0.1202</v>
+        <v>0.1</v>
       </c>
       <c r="I15" s="11">
-        <v>0.33710000000000001</v>
+        <v>0.25990000000000002</v>
       </c>
       <c r="J15" s="9">
         <f>IFERROR(H15/I15,"")</f>
-        <v>0.35657075051913378</v>
+        <v>0.38476337052712584</v>
       </c>
       <c r="K15" s="9">
         <f>IFERROR(J15/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.8147537843605618E-2</v>
+        <v>2.0021634563547979E-2</v>
       </c>
       <c r="L15" s="12">
         <f>F15/(1-(F15*(1+H15)-F15)/(F15*(1+H15)))</f>
-        <v>147.76558199999999</v>
+        <v>85.173000000000016</v>
       </c>
       <c r="M15" s="12">
         <f>L15*E15</f>
-        <v>51.511081885199999</v>
+        <v>38.481161400000005</v>
       </c>
       <c r="N15" s="12">
         <f>F15/(1+I15-H15)</f>
-        <v>108.39838934998768</v>
+        <v>66.755754806448849</v>
       </c>
       <c r="O15" s="12">
         <f>L15-F15</f>
-        <v>15.855581999999998</v>
+        <v>7.7430000000000092</v>
       </c>
       <c r="P15" s="12">
         <f>0.5*(N15-F15)</f>
-        <v>-11.755805325006158</v>
+        <v>-5.3371225967755791</v>
       </c>
       <c r="Q15" s="15">
         <f>O15+P15</f>
-        <v>4.0997766749938407</v>
+        <v>2.4058774032244301</v>
       </c>
       <c r="R15" s="12">
         <f>MAX($Q$2:$Q$279)-Q15</f>
-        <v>110.03266840619054</v>
+        <v>111.72656767795996</v>
       </c>
       <c r="S15" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R15)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>9.0882100242125827E-3</v>
+        <v>8.9504226325326178E-3</v>
       </c>
       <c r="T15" s="9">
         <f>R15/MAX($R$2:$R$28)</f>
-        <v>0.76825903622043479</v>
+        <v>0.78008600943515383</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="C16" s="32" t="s">
-        <v>100</v>
+        <v>36</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" t="s">
+        <v>22</v>
       </c>
       <c r="D16" s="8">
-        <v>45630</v>
+        <v>45484</v>
       </c>
       <c r="E16" s="2">
-        <v>0.28749999999999998</v>
+        <v>0.4108</v>
       </c>
       <c r="F16" s="1">
-        <v>34.78</v>
+        <v>189.76</v>
       </c>
       <c r="G16" s="1">
         <f>E16*F16</f>
-        <v>9.99925</v>
+        <v>77.953407999999996</v>
       </c>
       <c r="H16" s="13">
-        <v>0.2</v>
+        <f>227.4/F16-1</f>
+        <v>0.19835581787521095</v>
       </c>
       <c r="I16" s="11">
-        <v>0.2</v>
+        <v>0.37</v>
       </c>
       <c r="J16" s="9">
         <f>IFERROR(H16/I16,"")</f>
-        <v>1</v>
+        <v>0.53609680506813773</v>
       </c>
       <c r="K16" s="9">
         <f>IFERROR(J16/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>5.0894634002324905E-2</v>
+        <v>2.7896455702253901E-2</v>
       </c>
       <c r="L16" s="12">
         <f>F16/(1-(F16*(1+H16)-F16)/(F16*(1+H16)))</f>
-        <v>41.735999999999997</v>
+        <v>227.4</v>
       </c>
       <c r="M16" s="12">
         <f>L16*E16</f>
-        <v>11.999099999999999</v>
+        <v>93.41592</v>
       </c>
       <c r="N16" s="12">
         <f>F16/(1+I16-H16)</f>
-        <v>34.78</v>
+        <v>161.96043380326287</v>
       </c>
       <c r="O16" s="12">
         <f>L16-F16</f>
-        <v>6.955999999999996</v>
+        <v>37.640000000000015</v>
       </c>
       <c r="P16" s="12">
         <f>0.5*(N16-F16)</f>
-        <v>0</v>
+        <v>-13.899783098368559</v>
       </c>
       <c r="Q16" s="15">
         <f>O16+P16</f>
-        <v>6.955999999999996</v>
+        <v>23.740216901631456</v>
       </c>
       <c r="R16" s="12">
         <f>MAX($Q$2:$Q$279)-Q16</f>
-        <v>107.1764450811844</v>
+        <v>90.39222817955293</v>
       </c>
       <c r="S16" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R16)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>9.3304083676456744E-3</v>
+        <v>1.1062897996204102E-2</v>
       </c>
       <c r="T16" s="9">
         <f>R16/MAX($R$2:$R$28)</f>
-        <v>0.74831660084479601</v>
+        <v>0.6311275288415521</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C17" s="32" t="s">
-        <v>91</v>
+        <v>39</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C17" t="s">
+        <v>43</v>
       </c>
       <c r="D17" s="8">
-        <v>45627</v>
+        <v>45580</v>
       </c>
       <c r="E17" s="2">
-        <v>0.27450000000000002</v>
+        <v>0.34860000000000002</v>
       </c>
       <c r="F17" s="1">
-        <v>39.799999999999997</v>
+        <v>131.91</v>
       </c>
       <c r="G17" s="1">
         <f>E17*F17</f>
-        <v>10.9251</v>
+        <v>45.983826000000001</v>
       </c>
       <c r="H17" s="13">
-        <v>0.1</v>
+        <v>0.1202</v>
       </c>
       <c r="I17" s="11">
-        <v>0.2</v>
+        <v>0.33710000000000001</v>
       </c>
       <c r="J17" s="9">
         <f>IFERROR(H17/I17,"")</f>
-        <v>0.5</v>
+        <v>0.35657075051913378</v>
       </c>
       <c r="K17" s="9">
         <f>IFERROR(J17/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.5447317001162453E-2</v>
+        <v>1.8554596954391801E-2</v>
       </c>
       <c r="L17" s="12">
         <f>F17/(1-(F17*(1+H17)-F17)/(F17*(1+H17)))</f>
-        <v>43.78</v>
+        <v>147.76558199999999</v>
       </c>
       <c r="M17" s="12">
         <f>L17*E17</f>
-        <v>12.017610000000001</v>
+        <v>51.511081885199999</v>
       </c>
       <c r="N17" s="12">
         <f>F17/(1+I17-H17)</f>
-        <v>36.181818181818187</v>
+        <v>108.39838934998768</v>
       </c>
       <c r="O17" s="12">
         <f>L17-F17</f>
-        <v>3.980000000000004</v>
+        <v>15.855581999999998</v>
       </c>
       <c r="P17" s="12">
         <f>0.5*(N17-F17)</f>
-        <v>-1.8090909090909051</v>
+        <v>-11.755805325006158</v>
       </c>
       <c r="Q17" s="15">
         <f>O17+P17</f>
-        <v>2.1709090909090989</v>
+        <v>4.0997766749938407</v>
       </c>
       <c r="R17" s="12">
         <f>MAX($Q$2:$Q$279)-Q17</f>
-        <v>111.96153599027528</v>
+        <v>110.03266840619054</v>
       </c>
       <c r="S17" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R17)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.931638809303739E-3</v>
+        <v>9.0882100242125827E-3</v>
       </c>
       <c r="T17" s="9">
         <f>R17/MAX($R$2:$R$28)</f>
-        <v>0.78172658156501729</v>
+        <v>0.76825903622043479</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C18" t="s">
-        <v>59</v>
+        <v>96</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" s="32" t="s">
+        <v>100</v>
       </c>
       <c r="D18" s="8">
-        <v>45580</v>
+        <v>45630</v>
       </c>
       <c r="E18" s="2">
-        <v>0.25669999999999998</v>
+        <v>0.28749999999999998</v>
       </c>
       <c r="F18" s="1">
-        <v>132.38999999999999</v>
+        <v>34.78</v>
       </c>
       <c r="G18" s="1">
         <f>E18*F18</f>
-        <v>33.984512999999993</v>
+        <v>9.99925</v>
       </c>
       <c r="H18" s="13">
-        <v>7.0000000000000007E-2</v>
+        <v>0.2</v>
       </c>
       <c r="I18" s="11">
-        <v>0.1623</v>
+        <v>0.2</v>
       </c>
       <c r="J18" s="9">
         <f>IFERROR(H18/I18,"")</f>
-        <v>0.43130006161429457</v>
+        <v>1</v>
       </c>
       <c r="K18" s="9">
         <f>IFERROR(J18/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.1950858781039705E-2</v>
+        <v>5.2036228230661195E-2</v>
       </c>
       <c r="L18" s="12">
         <f>F18/(1-(F18*(1+H18)-F18)/(F18*(1+H18)))</f>
-        <v>141.65729999999999</v>
+        <v>41.735999999999997</v>
       </c>
       <c r="M18" s="12">
         <f>L18*E18</f>
-        <v>36.363428909999996</v>
+        <v>11.999099999999999</v>
       </c>
       <c r="N18" s="12">
         <f>F18/(1+I18-H18)</f>
-        <v>121.20296621807194</v>
+        <v>34.78</v>
       </c>
       <c r="O18" s="12">
         <f>L18-F18</f>
-        <v>9.2673000000000059</v>
+        <v>6.955999999999996</v>
       </c>
       <c r="P18" s="12">
         <f>0.5*(N18-F18)</f>
-        <v>-5.5935168909640254</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="15">
         <f>O18+P18</f>
-        <v>3.6737831090359805</v>
+        <v>6.955999999999996</v>
       </c>
       <c r="R18" s="12">
         <f>MAX($Q$2:$Q$279)-Q18</f>
-        <v>110.45866197214841</v>
+        <v>107.1764450811844</v>
       </c>
       <c r="S18" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R18)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>9.0531605411999748E-3</v>
+        <v>9.3304083676456744E-3</v>
       </c>
       <c r="T18" s="9">
         <f>R18/MAX($R$2:$R$28)</f>
-        <v>0.77123336567330925</v>
+        <v>0.74831660084479601</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -3760,7 +3940,7 @@
       </c>
       <c r="K19" s="9">
         <f>IFERROR(J19/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>9.3933413290193217E-3</v>
+        <v>9.6040390667319325E-3</v>
       </c>
       <c r="L19" s="12">
         <f>F19/(1-(F19*(1+H19)-F19)/(F19*(1+H19)))</f>
@@ -3834,7 +4014,7 @@
       </c>
       <c r="K20" s="9">
         <f>IFERROR(J20/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.3616006606555421E-2</v>
+        <v>3.437003185644729E-2</v>
       </c>
       <c r="L20" s="12">
         <f>F20/(1-(F20*(1+H20)-F20)/(F20*(1+H20)))</f>
@@ -3866,7 +4046,7 @@
       </c>
       <c r="S20" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R20)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>1.1342562392664219E-2</v>
+        <v>1.1342562392664218E-2</v>
       </c>
       <c r="T20" s="9">
         <f>R20/MAX($R$2:$R$28)</f>
@@ -3887,14 +4067,14 @@
         <v>45574</v>
       </c>
       <c r="E21" s="2">
-        <v>0.13370000000000001</v>
+        <v>0.16059999999999999</v>
       </c>
       <c r="F21" s="1">
-        <v>423.77</v>
+        <v>421.18</v>
       </c>
       <c r="G21" s="1">
         <f>E21*F21</f>
-        <v>56.658049000000005</v>
+        <v>67.641508000000002</v>
       </c>
       <c r="H21" s="13">
         <v>0.15</v>
@@ -3908,43 +4088,43 @@
       </c>
       <c r="K21" s="9">
         <f>IFERROR(J21/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.8890448804629323E-2</v>
+        <v>3.9762782652058987E-2</v>
       </c>
       <c r="L21" s="12">
         <f>F21/(1-(F21*(1+H21)-F21)/(F21*(1+H21)))</f>
-        <v>487.33549999999991</v>
+        <v>484.35699999999997</v>
       </c>
       <c r="M21" s="12">
         <f>L21*E21</f>
-        <v>65.156756349999995</v>
+        <v>77.787734199999989</v>
       </c>
       <c r="N21" s="12">
         <f>F21/(1+I21-H21)</f>
-        <v>405.01768135334032</v>
+        <v>402.54229188569246</v>
       </c>
       <c r="O21" s="12">
         <f>L21-F21</f>
-        <v>63.565499999999929</v>
+        <v>63.176999999999964</v>
       </c>
       <c r="P21" s="12">
         <f>0.5*(N21-F21)</f>
-        <v>-9.3761593233298299</v>
+        <v>-9.3188540571537715</v>
       </c>
       <c r="Q21" s="15">
         <f>O21+P21</f>
-        <v>54.189340676670099</v>
+        <v>53.858145942846193</v>
       </c>
       <c r="R21" s="12">
         <f>MAX($Q$2:$Q$279)-Q21</f>
-        <v>59.943104404514287</v>
+        <v>60.274299138338193</v>
       </c>
       <c r="S21" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R21)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>1.6682485999585474E-2</v>
+        <v>1.6590819209773906E-2</v>
       </c>
       <c r="T21" s="9">
         <f>R21/MAX($R$2:$R$28)</f>
-        <v>0.41852871774290379</v>
+        <v>0.4208411523197837</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -3982,7 +4162,7 @@
       </c>
       <c r="K22" s="9">
         <f>IFERROR(J22/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.2840601012058006E-2</v>
+        <v>4.3801538914697978E-2</v>
       </c>
       <c r="L22" s="12">
         <f>F22/(1-(F22*(1+H22)-F22)/(F22*(1+H22)))</f>
@@ -4023,87 +4203,87 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>40</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>50</v>
+        <v>39</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" t="s">
+        <v>59</v>
       </c>
       <c r="D23" s="8">
-        <v>45511</v>
+        <v>45580</v>
       </c>
       <c r="E23" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="F23" s="1">
-        <v>10.92</v>
+        <v>130.51</v>
       </c>
       <c r="G23" s="1">
         <f>E23*F23</f>
-        <v>1.092E-18</v>
+        <v>3.9152999999999993E-2</v>
       </c>
       <c r="H23" s="13">
-        <v>1</v>
-      </c>
-      <c r="I23" s="13">
-        <v>1.8652</v>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I23" s="11">
+        <v>0.1623</v>
       </c>
       <c r="J23" s="9">
         <f>IFERROR(H23/I23,"")</f>
-        <v>0.53613553506326406</v>
+        <v>0.43130006161429457</v>
       </c>
       <c r="K23" s="9">
         <f>IFERROR(J23/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.7286421832685457E-2</v>
+        <v>2.2443228442059669E-2</v>
       </c>
       <c r="L23" s="12">
         <f>F23/(1-(F23*(1+H23)-F23)/(F23*(1+H23)))</f>
-        <v>21.84</v>
+        <v>139.64570000000001</v>
       </c>
       <c r="M23" s="12">
         <f>L23*E23</f>
-        <v>2.1840000000000001E-18</v>
+        <v>4.1893710000000001E-2</v>
       </c>
       <c r="N23" s="12">
         <f>F23/(1+I23-H23)</f>
-        <v>5.8546000428908433</v>
+        <v>119.48182733681222</v>
       </c>
       <c r="O23" s="12">
         <f>L23-F23</f>
-        <v>10.92</v>
+        <v>9.1357000000000141</v>
       </c>
       <c r="P23" s="12">
         <f>0.5*(N23-F23)</f>
-        <v>-2.5326999785545783</v>
+        <v>-5.5140863315938873</v>
       </c>
       <c r="Q23" s="15">
         <f>O23+P23</f>
-        <v>8.3873000214454212</v>
+        <v>3.6216136684061269</v>
       </c>
       <c r="R23" s="12">
         <f>MAX($Q$2:$Q$279)-Q23</f>
-        <v>105.74514505973896</v>
+        <v>110.51083141277826</v>
       </c>
       <c r="S23" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R23)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>9.456698928684306E-3</v>
+        <v>9.0488867671696012E-3</v>
       </c>
       <c r="T23" s="9">
         <f>R23/MAX($R$2:$R$28)</f>
-        <v>0.73832312171768166</v>
+        <v>0.77159761789729864</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" t="s">
-        <v>25</v>
+        <v>40</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>50</v>
       </c>
       <c r="D24" s="8">
         <v>45511</v>
@@ -4112,135 +4292,135 @@
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F24" s="1">
-        <v>283.43</v>
+        <v>10.92</v>
       </c>
       <c r="G24" s="1">
         <f>E24*F24</f>
-        <v>2.8342999999999998E-17</v>
+        <v>1.092E-18</v>
       </c>
       <c r="H24" s="13">
-        <v>0.25</v>
-      </c>
-      <c r="I24" s="11">
-        <v>0.26</v>
+        <v>1</v>
+      </c>
+      <c r="I24" s="13">
+        <v>1.8652</v>
       </c>
       <c r="J24" s="9">
         <f>IFERROR(H24/I24,"")</f>
-        <v>0.96153846153846145</v>
+        <v>0.53613553506326406</v>
       </c>
       <c r="K24" s="9">
         <f>IFERROR(J24/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.8937148079158561E-2</v>
+        <v>2.7898471065119668E-2</v>
       </c>
       <c r="L24" s="12">
         <f>F24/(1-(F24*(1+H24)-F24)/(F24*(1+H24)))</f>
-        <v>354.28750000000002</v>
+        <v>21.84</v>
       </c>
       <c r="M24" s="12">
         <f>L24*E24</f>
-        <v>3.542875E-17</v>
+        <v>2.1840000000000001E-18</v>
       </c>
       <c r="N24" s="12">
         <f>F24/(1+I24-H24)</f>
-        <v>280.62376237623761</v>
+        <v>5.8546000428908433</v>
       </c>
       <c r="O24" s="12">
         <f>L24-F24</f>
-        <v>70.857500000000016</v>
+        <v>10.92</v>
       </c>
       <c r="P24" s="12">
         <f>0.5*(N24-F24)</f>
-        <v>-1.4031188118811997</v>
+        <v>-2.5326999785545783</v>
       </c>
       <c r="Q24" s="15">
         <f>O24+P24</f>
-        <v>69.454381188118816</v>
+        <v>8.3873000214454212</v>
       </c>
       <c r="R24" s="12">
         <f>MAX($Q$2:$Q$279)-Q24</f>
-        <v>44.67806389306557</v>
+        <v>105.74514505973896</v>
       </c>
       <c r="S24" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R24)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>2.2382348581474875E-2</v>
+        <v>9.456698928684306E-3</v>
       </c>
       <c r="T24" s="9">
         <f>R24/MAX($R$2:$R$28)</f>
-        <v>0.311946686414727</v>
+        <v>0.73832312171768166</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>10</v>
+        <v>37</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="C25" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D25" s="8">
-        <v>45544</v>
+        <v>45511</v>
       </c>
       <c r="E25" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F25" s="1">
-        <v>188.12</v>
+        <v>283.43</v>
       </c>
       <c r="G25" s="1">
         <f>E25*F25</f>
-        <v>1.8812000000000001E-17</v>
+        <v>2.8342999999999998E-17</v>
       </c>
       <c r="H25" s="13">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="I25" s="11">
-        <v>0.37780000000000002</v>
+        <v>0.26</v>
       </c>
       <c r="J25" s="9">
         <f>IFERROR(H25/I25,"")</f>
-        <v>0.39703546850185278</v>
+        <v>0.96153846153846145</v>
       </c>
       <c r="K25" s="9">
         <f>IFERROR(J25/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.0206974855343396E-2</v>
+        <v>5.0034834837174219E-2</v>
       </c>
       <c r="L25" s="12">
         <f>F25/(1-(F25*(1+H25)-F25)/(F25*(1+H25)))</f>
-        <v>216.33799999999999</v>
+        <v>354.28750000000002</v>
       </c>
       <c r="M25" s="12">
         <f>L25*E25</f>
-        <v>2.16338E-17</v>
+        <v>3.542875E-17</v>
       </c>
       <c r="N25" s="12">
         <f>F25/(1+I25-H25)</f>
-        <v>153.21713634142367</v>
+        <v>280.62376237623761</v>
       </c>
       <c r="O25" s="12">
         <f>L25-F25</f>
-        <v>28.217999999999989</v>
+        <v>70.857500000000016</v>
       </c>
       <c r="P25" s="12">
         <f>0.5*(N25-F25)</f>
-        <v>-17.451431829288168</v>
+        <v>-1.4031188118811997</v>
       </c>
       <c r="Q25" s="15">
         <f>O25+P25</f>
-        <v>10.766568170711821</v>
+        <v>69.454381188118816</v>
       </c>
       <c r="R25" s="12">
         <f>MAX($Q$2:$Q$279)-Q25</f>
-        <v>103.36587691047256</v>
+        <v>44.67806389306557</v>
       </c>
       <c r="S25" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R25)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>9.674372528819369E-3</v>
+        <v>2.2382348581474875E-2</v>
       </c>
       <c r="T25" s="9">
         <f>R25/MAX($R$2:$R$28)</f>
-        <v>0.72171083482377829</v>
+        <v>0.311946686414727</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -4248,222 +4428,222 @@
         <v>36</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D26" s="8">
-        <v>45483</v>
+        <v>45544</v>
       </c>
       <c r="E26" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F26" s="1">
-        <v>167.24</v>
+        <v>188.12</v>
       </c>
       <c r="G26" s="1">
         <f>E26*F26</f>
-        <v>1.6724000000000001E-17</v>
+        <v>1.8812000000000001E-17</v>
       </c>
       <c r="H26" s="13">
-        <f>190.41/F26-1</f>
-        <v>0.13854341066730447</v>
+        <v>0.15</v>
       </c>
       <c r="I26" s="11">
-        <v>0.26790000000000003</v>
+        <v>0.37780000000000002</v>
       </c>
       <c r="J26" s="9">
         <f>IFERROR(H26/I26,"")</f>
-        <v>0.51714598979956872</v>
+        <v>0.39703546850185278</v>
       </c>
       <c r="K26" s="9">
         <f>IFERROR(J26/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.6319955876619099E-2</v>
+        <v>2.0660228254629907E-2</v>
       </c>
       <c r="L26" s="12">
         <f>F26/(1-(F26*(1+H26)-F26)/(F26*(1+H26)))</f>
-        <v>190.41</v>
+        <v>216.33799999999999</v>
       </c>
       <c r="M26" s="12">
         <f>L26*E26</f>
-        <v>1.9040999999999999E-17</v>
+        <v>2.16338E-17</v>
       </c>
       <c r="N26" s="12">
         <f>F26/(1+I26-H26)</f>
-        <v>148.08431772538498</v>
+        <v>153.21713634142367</v>
       </c>
       <c r="O26" s="12">
         <f>L26-F26</f>
-        <v>23.169999999999987</v>
+        <v>28.217999999999989</v>
       </c>
       <c r="P26" s="12">
         <f>0.5*(N26-F26)</f>
-        <v>-9.5778411373075159</v>
+        <v>-17.451431829288168</v>
       </c>
       <c r="Q26" s="15">
         <f>O26+P26</f>
-        <v>13.592158862692472</v>
+        <v>10.766568170711821</v>
       </c>
       <c r="R26" s="12">
         <f>MAX($Q$2:$Q$279)-Q26</f>
-        <v>100.54028621849191</v>
+        <v>103.36587691047256</v>
       </c>
       <c r="S26" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R26)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>9.9462617186788418E-3</v>
+        <v>9.674372528819369E-3</v>
       </c>
       <c r="T26" s="9">
         <f>R26/MAX($R$2:$R$28)</f>
-        <v>0.70198227953907921</v>
+        <v>0.72171083482377829</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>33</v>
+        <v>36</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="C27" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="D27" s="8">
-        <v>45562</v>
+        <v>45678</v>
       </c>
       <c r="E27" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>5.3800000000000001E-2</v>
       </c>
       <c r="F27" s="1">
-        <v>668.82</v>
+        <v>185.82</v>
       </c>
       <c r="G27" s="1">
         <f>E27*F27</f>
-        <v>6.6881999999999999E-17</v>
+        <v>9.9971160000000001</v>
       </c>
       <c r="H27" s="13">
-        <v>0.05</v>
+        <f>190.41/F27-1</f>
+        <v>2.4701323861801683E-2</v>
       </c>
       <c r="I27" s="11">
-        <v>0.28000000000000003</v>
+        <v>0.26790000000000003</v>
       </c>
       <c r="J27" s="9">
         <f>IFERROR(H27/I27,"")</f>
-        <v>0.17857142857142858</v>
+        <v>9.2203523187016356E-2</v>
       </c>
       <c r="K27" s="9">
         <f>IFERROR(J27/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>9.0883275004151626E-3</v>
+        <v>4.7979235762306447E-3</v>
       </c>
       <c r="L27" s="12">
         <f>F27/(1-(F27*(1+H27)-F27)/(F27*(1+H27)))</f>
-        <v>702.26100000000008</v>
+        <v>190.40999999999997</v>
       </c>
       <c r="M27" s="12">
         <f>L27*E27</f>
-        <v>7.0226100000000009E-17</v>
+        <v>10.244057999999999</v>
       </c>
       <c r="N27" s="12">
         <f>F27/(1+I27-H27)</f>
-        <v>543.7560975609756</v>
+        <v>149.46927113630838</v>
       </c>
       <c r="O27" s="12">
         <f>L27-F27</f>
-        <v>33.441000000000031</v>
+        <v>4.589999999999975</v>
       </c>
       <c r="P27" s="12">
         <f>0.5*(N27-F27)</f>
-        <v>-62.531951219512223</v>
+        <v>-18.175364431845807</v>
       </c>
       <c r="Q27" s="15">
         <f>O27+P27</f>
-        <v>-29.090951219512192</v>
+        <v>-13.585364431845832</v>
       </c>
       <c r="R27" s="12">
         <f>MAX($Q$2:$Q$279)-Q27</f>
-        <v>143.22339630069658</v>
+        <v>127.71780951303022</v>
       </c>
       <c r="S27" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R27)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>6.9820994741704523E-3</v>
+        <v>7.8297615956056336E-3</v>
       </c>
       <c r="T27" s="9">
         <f>R27/MAX($R$2:$R$28)</f>
-        <v>1</v>
+        <v>0.8917384506431304</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>60</v>
+        <v>39</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="C28" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="D28" s="8">
-        <v>45481</v>
+        <v>45562</v>
       </c>
       <c r="E28" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F28" s="1">
-        <v>700.32</v>
+        <v>668.82</v>
       </c>
       <c r="G28" s="1">
         <f>E28*F28</f>
-        <v>7.0031999999999998E-17</v>
+        <v>6.6881999999999999E-17</v>
       </c>
       <c r="H28" s="13">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="I28" s="11">
-        <v>0.45340000000000003</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="J28" s="9">
         <f>IFERROR(H28/I28,"")</f>
-        <v>0.22055580061755625</v>
+        <v>0.17857142857142858</v>
       </c>
       <c r="K28" s="9">
         <f>IFERROR(J28/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.1225106749520271E-2</v>
+        <v>9.2921836126180716E-3</v>
       </c>
       <c r="L28" s="12">
         <f>F28/(1-(F28*(1+H28)-F28)/(F28*(1+H28)))</f>
-        <v>770.35200000000009</v>
+        <v>702.26100000000008</v>
       </c>
       <c r="M28" s="12">
         <f>L28*E28</f>
-        <v>7.7035200000000004E-17</v>
+        <v>7.0226100000000009E-17</v>
       </c>
       <c r="N28" s="12">
         <f>F28/(1+I28-H28)</f>
-        <v>517.45234224915032</v>
+        <v>543.7560975609756</v>
       </c>
       <c r="O28" s="12">
         <f>L28-F28</f>
-        <v>70.032000000000039</v>
+        <v>33.441000000000031</v>
       </c>
       <c r="P28" s="12">
         <f>0.5*(N28-F28)</f>
-        <v>-91.433828875424865</v>
+        <v>-62.531951219512223</v>
       </c>
       <c r="Q28" s="15">
         <f>O28+P28</f>
-        <v>-21.401828875424826</v>
+        <v>-29.090951219512192</v>
       </c>
       <c r="R28" s="12">
         <f>MAX($Q$2:$Q$279)-Q28</f>
-        <v>135.53427395660921</v>
+        <v>143.22339630069658</v>
       </c>
       <c r="S28" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R28)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>7.37820752498476E-3</v>
+        <v>6.9820994741704532E-3</v>
       </c>
       <c r="T28" s="9">
         <f>R28/MAX($R$2:$R$28)</f>
-        <v>0.94631378292451529</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -4471,73 +4651,73 @@
         <v>36</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="C29" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="D29" s="8">
-        <v>45482</v>
+        <v>45481</v>
       </c>
       <c r="E29" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F29" s="1">
-        <v>147.01</v>
+        <v>700.32</v>
       </c>
       <c r="G29" s="1">
         <f>E29*F29</f>
-        <v>1.4700999999999999E-17</v>
+        <v>7.0031999999999998E-17</v>
       </c>
       <c r="H29" s="13">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I29" s="11">
-        <v>0.52380000000000004</v>
+        <v>0.45340000000000003</v>
       </c>
       <c r="J29" s="9">
         <f>IFERROR(H29/I29,"")</f>
-        <v>0.28636884306987398</v>
+        <v>0.22055580061755625</v>
       </c>
       <c r="K29" s="9">
         <f>IFERROR(J29/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.4574637457710454E-2</v>
+        <v>1.1476891978531363E-2</v>
       </c>
       <c r="L29" s="12">
         <f>F29/(1-(F29*(1+H29)-F29)/(F29*(1+H29)))</f>
-        <v>169.06149999999997</v>
+        <v>770.35200000000009</v>
       </c>
       <c r="M29" s="12">
         <f>L29*E29</f>
-        <v>1.6906149999999997E-17</v>
+        <v>7.7035200000000004E-17</v>
       </c>
       <c r="N29" s="12">
         <f>F29/(1+I29-H29)</f>
-        <v>107.00975396709855</v>
+        <v>517.45234224915032</v>
       </c>
       <c r="O29" s="12">
         <f>L29-F29</f>
-        <v>22.051499999999976</v>
+        <v>70.032000000000039</v>
       </c>
       <c r="P29" s="12">
         <f>0.5*(N29-F29)</f>
-        <v>-20.000123016450722</v>
+        <v>-91.433828875424865</v>
       </c>
       <c r="Q29" s="15">
         <f>O29+P29</f>
-        <v>2.0513769835492539</v>
+        <v>-21.401828875424826</v>
       </c>
       <c r="R29" s="12">
         <f>MAX($Q$2:$Q$279)-Q29</f>
-        <v>112.08106809763513</v>
+        <v>135.53427395660921</v>
       </c>
       <c r="S29" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R29)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.9221134039237406E-3</v>
+        <v>7.37820752498476E-3</v>
       </c>
       <c r="T29" s="9">
         <f>R29/MAX($R$2:$R$28)</f>
-        <v>0.78256116662896091</v>
+        <v>0.94631378292451529</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -4545,296 +4725,296 @@
         <v>36</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C30" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D30" s="8">
-        <v>45481</v>
+        <v>45482</v>
       </c>
       <c r="E30" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F30" s="1">
-        <v>169.34</v>
+        <v>147.01</v>
       </c>
       <c r="G30" s="1">
         <f>E30*F30</f>
-        <v>1.6933999999999999E-17</v>
+        <v>1.4700999999999999E-17</v>
       </c>
       <c r="H30" s="13">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="I30" s="11">
-        <v>0.4259</v>
+        <v>0.52380000000000004</v>
       </c>
       <c r="J30" s="9">
         <f>IFERROR(H30/I30,"")</f>
-        <v>0.23479690068091102</v>
+        <v>0.28636884306987398</v>
       </c>
       <c r="K30" s="9">
         <f>IFERROR(J30/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.1949902325035199E-2</v>
+        <v>1.4901554476134362E-2</v>
       </c>
       <c r="L30" s="12">
         <f>F30/(1-(F30*(1+H30)-F30)/(F30*(1+H30)))</f>
-        <v>186.27400000000003</v>
+        <v>169.06149999999997</v>
       </c>
       <c r="M30" s="12">
         <f>L30*E30</f>
-        <v>1.8627400000000003E-17</v>
+        <v>1.6906149999999997E-17</v>
       </c>
       <c r="N30" s="12">
         <f>F30/(1+I30-H30)</f>
-        <v>127.71702239987934</v>
+        <v>107.00975396709855</v>
       </c>
       <c r="O30" s="12">
         <f>L30-F30</f>
-        <v>16.934000000000026</v>
+        <v>22.051499999999976</v>
       </c>
       <c r="P30" s="12">
         <f>0.5*(N30-F30)</f>
-        <v>-20.811488800060332</v>
+        <v>-20.000123016450722</v>
       </c>
       <c r="Q30" s="15">
         <f>O30+P30</f>
-        <v>-3.8774888000603056</v>
+        <v>2.0513769835492539</v>
       </c>
       <c r="R30" s="12">
         <f>MAX($Q$2:$Q$279)-Q30</f>
-        <v>118.00993388124469</v>
+        <v>112.08106809763513</v>
       </c>
       <c r="S30" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R30)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.4738628953585898E-3</v>
+        <v>8.9221134039237406E-3</v>
       </c>
       <c r="T30" s="9">
         <f>R30/MAX($R$2:$R$28)</f>
-        <v>0.82395709729912847</v>
+        <v>0.78256116662896091</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="14" t="s">
-        <v>32</v>
+        <v>36</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" t="s">
+        <v>30</v>
       </c>
       <c r="D31" s="8">
-        <v>45511</v>
+        <v>45481</v>
       </c>
       <c r="E31" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F31" s="1">
-        <v>113.58</v>
+        <v>169.34</v>
       </c>
       <c r="G31" s="1">
         <f>E31*F31</f>
-        <v>1.1357999999999999E-17</v>
+        <v>1.6933999999999999E-17</v>
       </c>
       <c r="H31" s="13">
-        <f>121.15/F31-1</f>
-        <v>6.664905793273479E-2</v>
+        <v>0.1</v>
       </c>
       <c r="I31" s="11">
-        <v>0.16439999999999999</v>
+        <v>0.4259</v>
       </c>
       <c r="J31" s="9">
         <f>IFERROR(H31/I31,"")</f>
-        <v>0.40540789496797319</v>
+        <v>0.23479690068091102</v>
       </c>
       <c r="K31" s="9">
         <f>IFERROR(J31/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.0633086436047974E-2</v>
+        <v>1.2217945111683776E-2</v>
       </c>
       <c r="L31" s="12">
         <f>F31/(1-(F31*(1+H31)-F31)/(F31*(1+H31)))</f>
-        <v>121.15000000000002</v>
+        <v>186.27400000000003</v>
       </c>
       <c r="M31" s="12">
         <f>L31*E31</f>
-        <v>1.2115000000000002E-17</v>
+        <v>1.8627400000000003E-17</v>
       </c>
       <c r="N31" s="12">
         <f>F31/(1+I31-H31)</f>
-        <v>103.46609203186667</v>
+        <v>127.71702239987934</v>
       </c>
       <c r="O31" s="12">
         <f>L31-F31</f>
-        <v>7.5700000000000216</v>
+        <v>16.934000000000026</v>
       </c>
       <c r="P31" s="12">
         <f>0.5*(N31-F31)</f>
-        <v>-5.0569539840666664</v>
+        <v>-20.811488800060332</v>
       </c>
       <c r="Q31" s="15">
         <f>O31+P31</f>
-        <v>2.5130460159333552</v>
+        <v>-3.8774888000603056</v>
       </c>
       <c r="R31" s="12">
         <f>MAX($Q$2:$Q$279)-Q31</f>
-        <v>111.61939906525103</v>
+        <v>118.00993388124469</v>
       </c>
       <c r="S31" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R31)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.9590161600441431E-3</v>
+        <v>8.4738628953585915E-3</v>
       </c>
       <c r="T31" s="9">
         <f>R31/MAX($R$2:$R$28)</f>
-        <v>0.77933774752071117</v>
+        <v>0.82395709729912847</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>36</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C32" t="s">
-        <v>84</v>
+        <v>40</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>32</v>
       </c>
       <c r="D32" s="8">
-        <v>45481</v>
+        <v>45511</v>
       </c>
       <c r="E32" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F32" s="1">
-        <v>64.349999999999994</v>
+        <v>113.58</v>
       </c>
       <c r="G32" s="1">
         <f>E32*F32</f>
-        <v>6.4349999999999993E-18</v>
+        <v>1.1357999999999999E-17</v>
       </c>
       <c r="H32" s="13">
-        <v>0.15</v>
+        <f>121.15/F32-1</f>
+        <v>6.664905793273479E-2</v>
       </c>
       <c r="I32" s="11">
-        <v>0.67300000000000004</v>
+        <v>0.16439999999999999</v>
       </c>
       <c r="J32" s="9">
         <f>IFERROR(H32/I32,"")</f>
-        <v>0.22288261515601782</v>
+        <v>0.40540789496797319</v>
       </c>
       <c r="K32" s="9">
         <f>IFERROR(J32/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.1343529123846561E-2</v>
+        <v>2.1095897749065375E-2</v>
       </c>
       <c r="L32" s="12">
         <f>F32/(1-(F32*(1+H32)-F32)/(F32*(1+H32)))</f>
-        <v>74.002499999999984</v>
+        <v>121.15000000000002</v>
       </c>
       <c r="M32" s="12">
         <f>L32*E32</f>
-        <v>7.4002499999999988E-18</v>
+        <v>1.2115000000000002E-17</v>
       </c>
       <c r="N32" s="12">
         <f>F32/(1+I32-H32)</f>
-        <v>42.252133946158892</v>
+        <v>103.46609203186667</v>
       </c>
       <c r="O32" s="12">
         <f>L32-F32</f>
-        <v>9.6524999999999892</v>
+        <v>7.5700000000000216</v>
       </c>
       <c r="P32" s="12">
         <f>0.5*(N32-F32)</f>
-        <v>-11.048933026920551</v>
+        <v>-5.0569539840666664</v>
       </c>
       <c r="Q32" s="15">
         <f>O32+P32</f>
-        <v>-1.3964330269205618</v>
+        <v>2.5130460159333552</v>
       </c>
       <c r="R32" s="12">
         <f>MAX($Q$2:$Q$279)-Q32</f>
-        <v>115.52887810810495</v>
+        <v>111.61939906525103</v>
       </c>
       <c r="S32" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R32)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.6558444639638962E-3</v>
+        <v>8.9590161600441431E-3</v>
       </c>
       <c r="T32" s="9">
         <f>R32/MAX($R$2:$R$28)</f>
-        <v>0.80663411909010196</v>
+        <v>0.77933774752071117</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>48</v>
+        <v>36</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C33" t="s">
+        <v>84</v>
       </c>
       <c r="D33" s="8">
-        <v>45511</v>
+        <v>45481</v>
       </c>
       <c r="E33" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F33" s="1">
-        <v>20.82</v>
+        <v>64.349999999999994</v>
       </c>
       <c r="G33" s="1">
         <f>E33*F33</f>
-        <v>2.0820000000000002E-18</v>
+        <v>6.4349999999999993E-18</v>
       </c>
       <c r="H33" s="13">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="I33" s="11">
-        <v>0.7389</v>
+        <v>0.67300000000000004</v>
       </c>
       <c r="J33" s="9">
         <f>IFERROR(H33/I33,"")</f>
-        <v>6.7668155366084726E-2</v>
+        <v>0.22288261515601782</v>
       </c>
       <c r="K33" s="9">
         <f>IFERROR(J33/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.4439460009693403E-3</v>
+        <v>1.1597970630905169E-2</v>
       </c>
       <c r="L33" s="12">
         <f>F33/(1-(F33*(1+H33)-F33)/(F33*(1+H33)))</f>
-        <v>21.861000000000001</v>
+        <v>74.002499999999984</v>
       </c>
       <c r="M33" s="12">
         <f>L33*E33</f>
-        <v>2.1860999999999999E-18</v>
+        <v>7.4002499999999988E-18</v>
       </c>
       <c r="N33" s="12">
         <f>F33/(1+I33-H33)</f>
-        <v>12.327550476641601</v>
+        <v>42.252133946158892</v>
       </c>
       <c r="O33" s="12">
         <f>L33-F33</f>
-        <v>1.0410000000000004</v>
+        <v>9.6524999999999892</v>
       </c>
       <c r="P33" s="12">
         <f>0.5*(N33-F33)</f>
-        <v>-4.2462247616791995</v>
+        <v>-11.048933026920551</v>
       </c>
       <c r="Q33" s="15">
         <f>O33+P33</f>
-        <v>-3.2052247616791991</v>
+        <v>-1.3964330269205618</v>
       </c>
       <c r="R33" s="12">
         <f>MAX($Q$2:$Q$279)-Q33</f>
-        <v>117.33766984286359</v>
+        <v>115.52887810810495</v>
       </c>
       <c r="S33" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R33)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.5224122938454584E-3</v>
+        <v>8.6558444639638962E-3</v>
       </c>
       <c r="T33" s="9">
         <f>R33/MAX($R$2:$R$28)</f>
-        <v>0.81926328291024408</v>
+        <v>0.80663411909010196</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -4842,10 +5022,10 @@
         <v>40</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C34" t="s">
-        <v>53</v>
+        <v>49</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>48</v>
       </c>
       <c r="D34" s="8">
         <v>45511</v>
@@ -4854,62 +5034,61 @@
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F34" s="1">
-        <v>13.04</v>
+        <v>20.82</v>
       </c>
       <c r="G34" s="1">
         <f>E34*F34</f>
-        <v>1.304E-18</v>
+        <v>2.0820000000000002E-18</v>
       </c>
       <c r="H34" s="13">
-        <f>13.72/F34-1</f>
-        <v>5.2147239263803824E-2</v>
+        <v>0.05</v>
       </c>
       <c r="I34" s="11">
-        <v>0.30159999999999998</v>
+        <v>0.7389</v>
       </c>
       <c r="J34" s="9">
         <f>IFERROR(H34/I34,"")</f>
-        <v>0.17290198694895167</v>
+        <v>6.7668155366084726E-2</v>
       </c>
       <c r="K34" s="9">
         <f>IFERROR(J34/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>8.7997833440416531E-3</v>
+        <v>3.521195576577426E-3</v>
       </c>
       <c r="L34" s="12">
         <f>F34/(1-(F34*(1+H34)-F34)/(F34*(1+H34)))</f>
-        <v>13.72</v>
+        <v>21.861000000000001</v>
       </c>
       <c r="M34" s="12">
         <f>L34*E34</f>
-        <v>1.3720000000000001E-18</v>
+        <v>2.1860999999999999E-18</v>
       </c>
       <c r="N34" s="12">
         <f>F34/(1+I34-H34)</f>
-        <v>10.436569040286594</v>
+        <v>12.327550476641601</v>
       </c>
       <c r="O34" s="12">
         <f>L34-F34</f>
-        <v>0.68000000000000149</v>
+        <v>1.0410000000000004</v>
       </c>
       <c r="P34" s="12">
         <f>0.5*(N34-F34)</f>
-        <v>-1.3017154798567026</v>
+        <v>-4.2462247616791995</v>
       </c>
       <c r="Q34" s="15">
         <f>O34+P34</f>
-        <v>-0.62171547985670106</v>
+        <v>-3.2052247616791991</v>
       </c>
       <c r="R34" s="12">
         <f>MAX($Q$2:$Q$279)-Q34</f>
-        <v>114.75416056104109</v>
+        <v>117.33766984286359</v>
       </c>
       <c r="S34" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R34)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.7142809908671744E-3</v>
+        <v>8.5224122938454567E-3</v>
       </c>
       <c r="T34" s="9">
         <f>R34/MAX($R$2:$R$28)</f>
-        <v>0.80122496411211674</v>
+        <v>0.81926328291024408</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -4917,10 +5096,10 @@
         <v>40</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C35" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D35" s="8">
         <v>45511</v>
@@ -4929,431 +5108,432 @@
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F35" s="1">
-        <v>11.05</v>
+        <v>13.04</v>
       </c>
       <c r="G35" s="1">
         <f>E35*F35</f>
-        <v>1.1050000000000001E-18</v>
+        <v>1.304E-18</v>
       </c>
       <c r="H35" s="13">
-        <v>0.05</v>
+        <f>13.72/F35-1</f>
+        <v>5.2147239263803824E-2</v>
       </c>
       <c r="I35" s="11">
-        <v>0.72170000000000001</v>
+        <v>0.30159999999999998</v>
       </c>
       <c r="J35" s="9">
         <f>IFERROR(H35/I35,"")</f>
-        <v>6.9280864625190522E-2</v>
+        <v>0.17290198694895167</v>
       </c>
       <c r="K35" s="9">
         <f>IFERROR(J35/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.5260242484636906E-3</v>
+        <v>8.9971672544104531E-3</v>
       </c>
       <c r="L35" s="12">
         <f>F35/(1-(F35*(1+H35)-F35)/(F35*(1+H35)))</f>
-        <v>11.602500000000001</v>
+        <v>13.72</v>
       </c>
       <c r="M35" s="12">
         <f>L35*E35</f>
-        <v>1.16025E-18</v>
+        <v>1.3720000000000001E-18</v>
       </c>
       <c r="N35" s="12">
         <f>F35/(1+I35-H35)</f>
-        <v>6.6100376861877139</v>
+        <v>10.436569040286594</v>
       </c>
       <c r="O35" s="12">
         <f>L35-F35</f>
-        <v>0.55250000000000021</v>
+        <v>0.68000000000000149</v>
       </c>
       <c r="P35" s="12">
         <f>0.5*(N35-F35)</f>
-        <v>-2.2199811569061434</v>
+        <v>-1.3017154798567026</v>
       </c>
       <c r="Q35" s="15">
         <f>O35+P35</f>
-        <v>-1.6674811569061432</v>
+        <v>-0.62171547985670106</v>
       </c>
       <c r="R35" s="12">
         <f>MAX($Q$2:$Q$279)-Q35</f>
-        <v>115.79992623809053</v>
+        <v>114.75416056104109</v>
       </c>
       <c r="S35" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R35)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.6355840844315329E-3</v>
+        <v>8.7142809908671744E-3</v>
       </c>
       <c r="T35" s="9">
         <f>R35/MAX($R$2:$R$28)</f>
-        <v>0.80852660409594923</v>
+        <v>0.80122496411211674</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>80</v>
+        <v>45</v>
+      </c>
+      <c r="C36" t="s">
+        <v>44</v>
       </c>
       <c r="D36" s="8">
-        <f ca="1">TODAY()-20</f>
-        <v>45672</v>
+        <v>45511</v>
       </c>
       <c r="E36" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F36" s="1">
-        <v>2742.9</v>
+        <v>11.05</v>
       </c>
       <c r="G36" s="1">
         <f>E36*F36</f>
-        <v>2.7429000000000002E-16</v>
+        <v>1.1050000000000001E-18</v>
       </c>
       <c r="H36" s="13">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="I36" s="11">
-        <v>0.5</v>
+        <v>0.72170000000000001</v>
       </c>
       <c r="J36" s="9">
         <f>IFERROR(H36/I36,"")</f>
-        <v>0.2</v>
+        <v>6.9280864625190522E-2</v>
       </c>
       <c r="K36" s="9">
         <f>IFERROR(J36/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.0178926800464982E-2</v>
+        <v>3.6051148836539555E-3</v>
       </c>
       <c r="L36" s="12">
         <f>F36/(1-(F36*(1+H36)-F36)/(F36*(1+H36)))</f>
-        <v>3017.1900000000005</v>
+        <v>11.602500000000001</v>
       </c>
       <c r="M36" s="12">
         <f>L36*E36</f>
-        <v>3.0171900000000003E-16</v>
+        <v>1.16025E-18</v>
       </c>
       <c r="N36" s="12">
         <f>F36/(1+I36-H36)</f>
-        <v>1959.214285714286</v>
+        <v>6.6100376861877139</v>
       </c>
       <c r="O36" s="12">
         <f>L36-F36</f>
-        <v>274.29000000000042</v>
+        <v>0.55250000000000021</v>
       </c>
       <c r="P36" s="12">
         <f>0.5*(N36-F36)</f>
-        <v>-391.84285714285704</v>
+        <v>-2.2199811569061434</v>
       </c>
       <c r="Q36" s="15">
         <f>O36+P36</f>
-        <v>-117.55285714285662</v>
+        <v>-1.6674811569061432</v>
       </c>
       <c r="R36" s="12">
         <f>MAX($Q$2:$Q$279)-Q36</f>
-        <v>231.68530222404101</v>
+        <v>115.79992623809053</v>
       </c>
       <c r="S36" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R36)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>4.316199562080957E-3</v>
+        <v>8.6355840844315312E-3</v>
       </c>
       <c r="T36" s="9">
         <f>R36/MAX($R$2:$R$28)</f>
-        <v>1.6176498268314992</v>
+        <v>0.80852660409594923</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C37" t="s">
-        <v>55</v>
+        <v>74</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>80</v>
       </c>
       <c r="D37" s="8">
-        <v>45505</v>
+        <f ca="1">TODAY()-20</f>
+        <v>45677</v>
       </c>
       <c r="E37" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F37" s="1">
-        <v>86.6</v>
+        <v>2742.9</v>
       </c>
       <c r="G37" s="1">
         <f>E37*F37</f>
-        <v>8.6599999999999986E-18</v>
+        <v>2.7429000000000002E-16</v>
       </c>
       <c r="H37" s="13">
-        <v>7.0000000000000007E-2</v>
+        <v>0.1</v>
       </c>
       <c r="I37" s="11">
-        <v>0.17249999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J37" s="9">
         <f>IFERROR(H37/I37,"")</f>
-        <v>0.40579710144927544</v>
+        <v>0.2</v>
       </c>
       <c r="K37" s="9">
         <f>IFERROR(J37/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.0652894957465185E-2</v>
+        <v>1.040724564613224E-2</v>
       </c>
       <c r="L37" s="12">
         <f>F37/(1-(F37*(1+H37)-F37)/(F37*(1+H37)))</f>
-        <v>92.662000000000006</v>
+        <v>3017.1900000000005</v>
       </c>
       <c r="M37" s="12">
         <f>L37*E37</f>
-        <v>9.2662000000000008E-18</v>
+        <v>3.0171900000000003E-16</v>
       </c>
       <c r="N37" s="12">
         <f>F37/(1+I37-H37)</f>
-        <v>78.548752834467123</v>
+        <v>1959.214285714286</v>
       </c>
       <c r="O37" s="12">
         <f>L37-F37</f>
-        <v>6.0620000000000118</v>
+        <v>274.29000000000042</v>
       </c>
       <c r="P37" s="12">
         <f>0.5*(N37-F37)</f>
-        <v>-4.0256235827664355</v>
+        <v>-391.84285714285704</v>
       </c>
       <c r="Q37" s="15">
         <f>O37+P37</f>
-        <v>2.0363764172335763</v>
+        <v>-117.55285714285662</v>
       </c>
       <c r="R37" s="12">
         <f>MAX($Q$2:$Q$279)-Q37</f>
-        <v>112.0960686639508</v>
+        <v>231.68530222404101</v>
       </c>
       <c r="S37" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R37)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.9209194570227784E-3</v>
+        <v>4.316199562080957E-3</v>
       </c>
       <c r="T37" s="9">
         <f>R37/MAX($R$2:$R$28)</f>
-        <v>0.78266590207514586</v>
+        <v>1.6176498268314992</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="C38" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="D38" s="8">
-        <v>45562</v>
+        <v>45505</v>
       </c>
       <c r="E38" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F38" s="1">
-        <v>56</v>
+        <v>86.6</v>
       </c>
       <c r="G38" s="1">
         <f>E38*F38</f>
-        <v>5.5999999999999995E-18</v>
+        <v>8.6599999999999986E-18</v>
       </c>
       <c r="H38" s="13">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="I38" s="11">
-        <v>0.19</v>
+        <v>0.17249999999999999</v>
       </c>
       <c r="J38" s="9">
         <f>IFERROR(H38/I38,"")</f>
-        <v>0.36842105263157898</v>
+        <v>0.40579710144927544</v>
       </c>
       <c r="K38" s="9">
         <f>IFERROR(J38/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.8750654632435495E-2</v>
+        <v>2.1116150586355274E-2</v>
       </c>
       <c r="L38" s="12">
         <f>F38/(1-(F38*(1+H38)-F38)/(F38*(1+H38)))</f>
-        <v>59.92</v>
+        <v>92.662000000000006</v>
       </c>
       <c r="M38" s="12">
         <f>L38*E38</f>
-        <v>5.9920000000000002E-18</v>
+        <v>9.2662000000000008E-18</v>
       </c>
       <c r="N38" s="12">
         <f>F38/(1+I38-H38)</f>
-        <v>50.000000000000007</v>
+        <v>78.548752834467123</v>
       </c>
       <c r="O38" s="12">
         <f>L38-F38</f>
-        <v>3.9200000000000017</v>
+        <v>6.0620000000000118</v>
       </c>
       <c r="P38" s="12">
         <f>0.5*(N38-F38)</f>
-        <v>-2.9999999999999964</v>
+        <v>-4.0256235827664355</v>
       </c>
       <c r="Q38" s="15">
         <f>O38+P38</f>
-        <v>0.92000000000000526</v>
+        <v>2.0363764172335763</v>
       </c>
       <c r="R38" s="12">
         <f>MAX($Q$2:$Q$279)-Q38</f>
-        <v>113.21244508118438</v>
+        <v>112.0960686639508</v>
       </c>
       <c r="S38" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R38)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.832951176727102E-3</v>
+        <v>8.9209194570227766E-3</v>
       </c>
       <c r="T38" s="9">
         <f>R38/MAX($R$2:$R$28)</f>
-        <v>0.79046055327088882</v>
+        <v>0.78266590207514586</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C39" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D39" s="8">
-        <v>45580</v>
+        <v>45562</v>
       </c>
       <c r="E39" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F39" s="1">
-        <v>20.399999999999999</v>
+        <v>56</v>
       </c>
       <c r="G39" s="1">
         <f>E39*F39</f>
-        <v>2.0399999999999999E-18</v>
+        <v>5.5999999999999995E-18</v>
       </c>
       <c r="H39" s="13">
-        <v>0.1</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I39" s="11">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="J39" s="9">
         <f>IFERROR(H39/I39,"")</f>
-        <v>0.66666666666666674</v>
+        <v>0.36842105263157898</v>
       </c>
       <c r="K39" s="9">
         <f>IFERROR(J39/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.3929756001549939E-2</v>
+        <v>1.9171241979717285E-2</v>
       </c>
       <c r="L39" s="12">
-        <v>21.2</v>
+        <f>F39/(1-(F39*(1+H39)-F39)/(F39*(1+H39)))</f>
+        <v>59.92</v>
       </c>
       <c r="M39" s="12">
         <f>L39*E39</f>
-        <v>2.1199999999999999E-18</v>
+        <v>5.9920000000000002E-18</v>
       </c>
       <c r="N39" s="12">
         <f>F39/(1+I39-H39)</f>
-        <v>19.428571428571431</v>
+        <v>50.000000000000007</v>
       </c>
       <c r="O39" s="12">
         <f>L39-F39</f>
-        <v>0.80000000000000071</v>
+        <v>3.9200000000000017</v>
       </c>
       <c r="P39" s="12">
         <f>0.5*(N39-F39)</f>
-        <v>-0.48571428571428399</v>
+        <v>-2.9999999999999964</v>
       </c>
       <c r="Q39" s="15">
         <f>O39+P39</f>
-        <v>0.31428571428571672</v>
+        <v>0.92000000000000526</v>
       </c>
       <c r="R39" s="12">
         <f>MAX($Q$2:$Q$279)-Q39</f>
-        <v>113.81815936689867</v>
+        <v>113.21244508118438</v>
       </c>
       <c r="S39" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R39)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.7859442250902055E-3</v>
+        <v>8.832951176727102E-3</v>
       </c>
       <c r="T39" s="9">
         <f>R39/MAX($R$2:$R$28)</f>
-        <v>0.79468971066667204</v>
+        <v>0.79046055327088882</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>57</v>
+        <v>74</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>75</v>
       </c>
       <c r="C40" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="D40" s="8">
-        <v>45574</v>
+        <v>45580</v>
       </c>
       <c r="E40" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F40" s="1">
-        <v>47.42</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="G40" s="1">
         <f>E40*F40</f>
-        <v>4.7419999999999999E-18</v>
+        <v>2.0399999999999999E-18</v>
       </c>
       <c r="H40" s="13">
-        <v>7.0000000000000007E-2</v>
+        <v>0.1</v>
       </c>
       <c r="I40" s="11">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
       <c r="J40" s="9">
         <f>IFERROR(H40/I40,"")</f>
-        <v>0.17500000000000002</v>
+        <v>0.66666666666666674</v>
       </c>
       <c r="K40" s="9">
         <f>IFERROR(J40/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>8.90656095040686E-3</v>
+        <v>3.4690818820440804E-2</v>
       </c>
       <c r="L40" s="12">
-        <f>F40/(1-(F40*(1+H40)-F40)/(F40*(1+H40)))</f>
-        <v>50.739400000000003</v>
+        <v>21.2</v>
       </c>
       <c r="M40" s="12">
         <f>L40*E40</f>
-        <v>5.0739400000000001E-18</v>
+        <v>2.1199999999999999E-18</v>
       </c>
       <c r="N40" s="12">
         <f>F40/(1+I40-H40)</f>
-        <v>35.654135338345867</v>
+        <v>19.428571428571431</v>
       </c>
       <c r="O40" s="12">
         <f>L40-F40</f>
-        <v>3.3194000000000017</v>
+        <v>0.80000000000000071</v>
       </c>
       <c r="P40" s="12">
         <f>0.5*(N40-F40)</f>
-        <v>-5.8829323308270673</v>
+        <v>-0.48571428571428399</v>
       </c>
       <c r="Q40" s="15">
         <f>O40+P40</f>
-        <v>-2.5635323308270657</v>
+        <v>0.31428571428571672</v>
       </c>
       <c r="R40" s="12">
         <f>MAX($Q$2:$Q$279)-Q40</f>
-        <v>116.69597741201144</v>
+        <v>113.81815936689867</v>
       </c>
       <c r="S40" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R40)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.5692756697976005E-3</v>
+        <v>8.7859442250902055E-3</v>
       </c>
       <c r="T40" s="9">
         <f>R40/MAX($R$2:$R$28)</f>
-        <v>0.81478292252621221</v>
+        <v>0.79468971066667204</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -5361,23 +5541,23 @@
         <v>39</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="C41" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="D41" s="8">
-        <v>45507</v>
+        <v>45574</v>
       </c>
       <c r="E41" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F41" s="1">
-        <v>41.8</v>
+        <v>47.42</v>
       </c>
       <c r="G41" s="1">
         <f>E41*F41</f>
-        <v>4.1799999999999993E-18</v>
+        <v>4.7419999999999999E-18</v>
       </c>
       <c r="H41" s="13">
         <v>7.0000000000000007E-2</v>
@@ -5391,202 +5571,202 @@
       </c>
       <c r="K41" s="9">
         <f>IFERROR(J41/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>8.90656095040686E-3</v>
+        <v>9.1063399403657104E-3</v>
       </c>
       <c r="L41" s="12">
         <f>F41/(1-(F41*(1+H41)-F41)/(F41*(1+H41)))</f>
-        <v>44.725999999999999</v>
+        <v>50.739400000000003</v>
       </c>
       <c r="M41" s="12">
         <f>L41*E41</f>
-        <v>4.4725999999999996E-18</v>
+        <v>5.0739400000000001E-18</v>
       </c>
       <c r="N41" s="12">
         <f>F41/(1+I41-H41)</f>
-        <v>31.428571428571431</v>
+        <v>35.654135338345867</v>
       </c>
       <c r="O41" s="12">
         <f>L41-F41</f>
-        <v>2.9260000000000019</v>
+        <v>3.3194000000000017</v>
       </c>
       <c r="P41" s="12">
         <f>0.5*(N41-F41)</f>
-        <v>-5.1857142857142833</v>
+        <v>-5.8829323308270673</v>
       </c>
       <c r="Q41" s="15">
         <f>O41+P41</f>
-        <v>-2.2597142857142813</v>
+        <v>-2.5635323308270657</v>
       </c>
       <c r="R41" s="12">
         <f>MAX($Q$2:$Q$279)-Q41</f>
-        <v>116.39215936689867</v>
+        <v>116.69597741201144</v>
       </c>
       <c r="S41" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R41)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.5916440200042785E-3</v>
+        <v>8.5692756697976005E-3</v>
       </c>
       <c r="T41" s="9">
         <f>R41/MAX($R$2:$R$28)</f>
-        <v>0.81266163471318675</v>
+        <v>0.81478292252621221</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>74</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>77</v>
+        <v>39</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="C42" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="D42" s="8">
-        <v>45574</v>
+        <v>45507</v>
       </c>
       <c r="E42" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F42" s="1">
-        <v>153.7552</v>
+        <v>41.8</v>
       </c>
       <c r="G42" s="1">
         <f>E42*F42</f>
-        <v>1.5375519999999999E-17</v>
+        <v>4.1799999999999993E-18</v>
       </c>
       <c r="H42" s="13">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="I42" s="11">
-        <v>0.19</v>
+        <v>0.4</v>
       </c>
       <c r="J42" s="9">
         <f>IFERROR(H42/I42,"")</f>
-        <v>0.36842105263157898</v>
+        <v>0.17500000000000002</v>
       </c>
       <c r="K42" s="9">
         <f>IFERROR(J42/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.8750654632435495E-2</v>
+        <v>9.1063399403657104E-3</v>
       </c>
       <c r="L42" s="12">
         <f>F42/(1-(F42*(1+H42)-F42)/(F42*(1+H42)))</f>
-        <v>164.51806400000001</v>
+        <v>44.725999999999999</v>
       </c>
       <c r="M42" s="12">
         <f>L42*E42</f>
-        <v>1.6451806399999999E-17</v>
+        <v>4.4725999999999996E-18</v>
       </c>
       <c r="N42" s="12">
         <f>F42/(1+I42-H42)</f>
-        <v>137.28142857142859</v>
+        <v>31.428571428571431</v>
       </c>
       <c r="O42" s="12">
         <f>L42-F42</f>
-        <v>10.762864000000008</v>
+        <v>2.9260000000000019</v>
       </c>
       <c r="P42" s="12">
         <f>0.5*(N42-F42)</f>
-        <v>-8.2368857142857053</v>
+        <v>-5.1857142857142833</v>
       </c>
       <c r="Q42" s="15">
         <f>O42+P42</f>
-        <v>2.5259782857143023</v>
+        <v>-2.2597142857142813</v>
       </c>
       <c r="R42" s="12">
         <f>MAX($Q$2:$Q$279)-Q42</f>
-        <v>111.60646679547008</v>
+        <v>116.39215936689867</v>
       </c>
       <c r="S42" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R42)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.9600542756415637E-3</v>
+        <v>8.5916440200042785E-3</v>
       </c>
       <c r="T42" s="9">
         <f>R42/MAX($R$2:$R$28)</f>
-        <v>0.77924745312667376</v>
+        <v>0.81266163471318675</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>87</v>
-      </c>
-      <c r="B43" t="s">
-        <v>88</v>
-      </c>
-      <c r="C43" s="32" t="s">
-        <v>89</v>
+        <v>74</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C43" t="s">
+        <v>78</v>
       </c>
       <c r="D43" s="8">
-        <v>45627</v>
+        <v>45574</v>
       </c>
       <c r="E43" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F43" s="1">
-        <v>133.53</v>
+        <v>153.7552</v>
       </c>
       <c r="G43" s="1">
         <f>E43*F43</f>
-        <v>1.3353E-17</v>
+        <v>1.5375519999999999E-17</v>
       </c>
       <c r="H43" s="13">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="I43" s="11">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="J43" s="9">
         <f>IFERROR(H43/I43,"")</f>
-        <v>0.35000000000000003</v>
+        <v>0.36842105263157898</v>
       </c>
       <c r="K43" s="9">
         <f>IFERROR(J43/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.781312190081372E-2</v>
+        <v>1.9171241979717285E-2</v>
       </c>
       <c r="L43" s="12">
         <f>F43/(1-(F43*(1+H43)-F43)/(F43*(1+H43)))</f>
-        <v>142.87710000000001</v>
+        <v>164.51806400000001</v>
       </c>
       <c r="M43" s="12">
         <f>L43*E43</f>
-        <v>1.428771E-17</v>
+        <v>1.6451806399999999E-17</v>
       </c>
       <c r="N43" s="12">
         <f>F43/(1+I43-H43)</f>
-        <v>118.16814159292036</v>
+        <v>137.28142857142859</v>
       </c>
       <c r="O43" s="12">
         <f>L43-F43</f>
-        <v>9.3471000000000117</v>
+        <v>10.762864000000008</v>
       </c>
       <c r="P43" s="12">
         <f>0.5*(N43-F43)</f>
-        <v>-7.6809292035398187</v>
+        <v>-8.2368857142857053</v>
       </c>
       <c r="Q43" s="15">
         <f>O43+P43</f>
-        <v>1.6661707964601931</v>
+        <v>2.5259782857143023</v>
       </c>
       <c r="R43" s="12">
         <f>MAX($Q$2:$Q$279)-Q43</f>
-        <v>112.46627428472419</v>
+        <v>111.60646679547008</v>
       </c>
       <c r="S43" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R43)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.8915544358512261E-3</v>
+        <v>8.9600542756415637E-3</v>
       </c>
       <c r="T43" s="9">
         <f>R43/MAX($R$2:$R$28)</f>
-        <v>0.78525071454528272</v>
+        <v>0.77924745312667376</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>40</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>93</v>
+        <v>87</v>
+      </c>
+      <c r="B44" t="s">
+        <v>88</v>
       </c>
       <c r="C44" s="32" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D44" s="8">
         <v>45627</v>
@@ -5595,135 +5775,135 @@
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F44" s="1">
-        <v>26.63</v>
+        <v>133.53</v>
       </c>
       <c r="G44" s="1">
         <f>E44*F44</f>
-        <v>2.663E-18</v>
+        <v>1.3353E-17</v>
       </c>
       <c r="H44" s="13">
-        <v>0.1</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I44" s="11">
         <v>0.2</v>
       </c>
       <c r="J44" s="9">
         <f>IFERROR(H44/I44,"")</f>
-        <v>0.5</v>
+        <v>0.35000000000000003</v>
       </c>
       <c r="K44" s="9">
         <f>IFERROR(J44/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.5447317001162453E-2</v>
+        <v>1.8212679880731421E-2</v>
       </c>
       <c r="L44" s="12">
         <f>F44/(1-(F44*(1+H44)-F44)/(F44*(1+H44)))</f>
-        <v>29.293000000000003</v>
+        <v>142.87710000000001</v>
       </c>
       <c r="M44" s="12">
         <f>L44*E44</f>
-        <v>2.9293000000000003E-18</v>
+        <v>1.428771E-17</v>
       </c>
       <c r="N44" s="12">
         <f>F44/(1+I44-H44)</f>
-        <v>24.209090909090911</v>
+        <v>118.16814159292036</v>
       </c>
       <c r="O44" s="12">
         <f>L44-F44</f>
-        <v>2.6630000000000038</v>
+        <v>9.3471000000000117</v>
       </c>
       <c r="P44" s="12">
         <f>0.5*(N44-F44)</f>
-        <v>-1.2104545454545441</v>
+        <v>-7.6809292035398187</v>
       </c>
       <c r="Q44" s="15">
         <f>O44+P44</f>
-        <v>1.4525454545454597</v>
+        <v>1.6661707964601931</v>
       </c>
       <c r="R44" s="12">
         <f>MAX($Q$2:$Q$279)-Q44</f>
-        <v>112.67989962663893</v>
+        <v>112.46627428472419</v>
       </c>
       <c r="S44" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R44)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>8.8746972912956655E-3</v>
+        <v>8.8915544358512261E-3</v>
       </c>
       <c r="T44" s="9">
         <f>R44/MAX($R$2:$R$28)</f>
-        <v>0.78674226793273505</v>
+        <v>0.78525071454528272</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>101</v>
+        <v>40</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>93</v>
       </c>
       <c r="C45" s="32" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D45" s="8">
-        <v>45630</v>
+        <v>45627</v>
       </c>
       <c r="E45" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F45" s="1">
-        <v>19.309999999999999</v>
+        <v>26.63</v>
       </c>
       <c r="G45" s="1">
         <f>E45*F45</f>
-        <v>1.931E-18</v>
+        <v>2.663E-18</v>
       </c>
       <c r="H45" s="13">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I45" s="11">
         <v>0.2</v>
       </c>
       <c r="J45" s="9">
         <f>IFERROR(H45/I45,"")</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K45" s="9">
         <f>IFERROR(J45/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>5.0894634002324905E-2</v>
+        <v>2.6018114115330598E-2</v>
       </c>
       <c r="L45" s="12">
         <f>F45/(1-(F45*(1+H45)-F45)/(F45*(1+H45)))</f>
-        <v>23.171999999999997</v>
+        <v>29.293000000000003</v>
       </c>
       <c r="M45" s="12">
         <f>L45*E45</f>
-        <v>2.3171999999999995E-18</v>
+        <v>2.9293000000000003E-18</v>
       </c>
       <c r="N45" s="12">
         <f>F45/(1+I45-H45)</f>
-        <v>19.309999999999999</v>
+        <v>24.209090909090911</v>
       </c>
       <c r="O45" s="12">
         <f>L45-F45</f>
-        <v>3.8619999999999983</v>
+        <v>2.6630000000000038</v>
       </c>
       <c r="P45" s="12">
         <f>0.5*(N45-F45)</f>
-        <v>0</v>
+        <v>-1.2104545454545441</v>
       </c>
       <c r="Q45" s="15">
         <f>O45+P45</f>
-        <v>3.8619999999999983</v>
+        <v>1.4525454545454597</v>
       </c>
       <c r="R45" s="12">
         <f>MAX($Q$2:$Q$279)-Q45</f>
-        <v>110.27044508118439</v>
+        <v>112.67989962663893</v>
       </c>
       <c r="S45" s="9">
         <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R45)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
-        <v>9.0686130745529347E-3</v>
+        <v>8.8746972912956672E-3</v>
       </c>
       <c r="T45" s="9">
         <f>R45/MAX($R$2:$R$28)</f>
-        <v>0.76991921661787932</v>
+        <v>0.78674226793273505</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
@@ -5761,7 +5941,7 @@
       </c>
       <c r="K46" s="9">
         <f>IFERROR(J46/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>5.0894634002324905E-2</v>
+        <v>5.2036228230661195E-2</v>
       </c>
       <c r="L46" s="12">
         <f>F46/(1-(F46*(1+H46)-F46)/(F46*(1+H46)))</f>
@@ -7514,8 +7694,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFDF4B0C-3879-4A30-880B-B04980CC1636}">
-  <dimension ref="A1:AC14"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AR14"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelCol="2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
@@ -7523,31 +7703,41 @@
     <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.140625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="12" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="15.5703125" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="13" width="6" customWidth="1" collapsed="1"/>
-    <col min="14" max="14" width="15.140625" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="5.5703125" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="0" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.140625" customWidth="1" outlineLevel="1"/>
-    <col min="21" max="21" width="10.5703125" customWidth="1" outlineLevel="1"/>
-    <col min="22" max="22" width="15" customWidth="1" outlineLevel="1"/>
-    <col min="24" max="24" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="15.140625" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="5.5703125" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="10.140625" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="11" max="11" width="12" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="12" max="12" width="15.5703125" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="13" max="13" width="6" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="14" max="14" width="15.140625" customWidth="1" outlineLevel="1"/>
+    <col min="15" max="15" width="5.5703125" customWidth="1" outlineLevel="1"/>
+    <col min="16" max="16" width="9.140625" customWidth="1" outlineLevel="1"/>
+    <col min="17" max="17" width="14.28515625" customWidth="1" outlineLevel="1"/>
+    <col min="18" max="18" width="15.140625" customWidth="1" outlineLevel="1"/>
+    <col min="19" max="19" width="5.5703125" customWidth="1" outlineLevel="1"/>
+    <col min="20" max="20" width="15.140625" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="21" max="21" width="10.5703125" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="22" max="22" width="15" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="23" max="23" width="9.140625" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="24" max="24" width="14.28515625" customWidth="1" outlineLevel="1"/>
+    <col min="25" max="25" width="15.140625" customWidth="1" outlineLevel="1"/>
+    <col min="26" max="26" width="5.5703125" customWidth="1" outlineLevel="1"/>
+    <col min="27" max="27" width="15.140625" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="28" max="28" width="10.5703125" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="29" max="29" width="15.5703125" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="30" max="30" width="9.140625" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="31" max="31" width="14.28515625" customWidth="1" outlineLevel="1"/>
+    <col min="32" max="32" width="15.140625" customWidth="1" outlineLevel="1"/>
+    <col min="33" max="33" width="5.5703125" customWidth="1" outlineLevel="1"/>
+    <col min="34" max="34" width="15.140625" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="35" max="35" width="10.5703125" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="36" max="36" width="15.5703125" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="37" max="37" width="9.140625" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="38" max="44" width="9.140625" customWidth="1" outlineLevel="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="H1" s="45" t="s">
         <v>114</v>
       </c>
@@ -7574,8 +7764,15 @@
       <c r="AA1" s="45"/>
       <c r="AB1" s="45"/>
       <c r="AC1" s="45"/>
-    </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AF1" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="AG1" s="45"/>
+      <c r="AH1" s="45"/>
+      <c r="AI1" s="45"/>
+      <c r="AJ1" s="45"/>
+    </row>
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="H2" s="46">
         <v>46000</v>
       </c>
@@ -7602,8 +7799,15 @@
       <c r="AA2" s="46"/>
       <c r="AB2" s="46"/>
       <c r="AC2" s="46"/>
-    </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AF2" s="46">
+        <v>45695</v>
+      </c>
+      <c r="AG2" s="46"/>
+      <c r="AH2" s="46"/>
+      <c r="AI2" s="46"/>
+      <c r="AJ2" s="46"/>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
         <v>104</v>
       </c>
@@ -7679,22 +7883,40 @@
       <c r="AC3" s="28" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AE3" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="AF3" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="AG3" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="AH3" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="AI3" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="AJ3" s="28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
-        <v>115</v>
+        <v>38</v>
       </c>
       <c r="B4" s="12">
-        <v>218.85600000000002</v>
+        <v>262.48183799999998</v>
       </c>
       <c r="C4" s="22">
-        <v>0.23199208873650332</v>
+        <v>0.25694241418020713</v>
       </c>
       <c r="D4" s="29">
-        <v>3.586522645026835E-2</v>
+        <v>0.11840756019698384</v>
       </c>
       <c r="E4" s="12">
-        <v>7.849319999999949</v>
+        <v>31.07983403359998</v>
       </c>
       <c r="F4" s="12"/>
       <c r="G4" s="21" t="s">
@@ -7753,22 +7975,38 @@
         <v>7.849319999999949</v>
       </c>
       <c r="AC4" s="12"/>
-    </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AE4" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF4" s="41">
+        <v>262.48183799999998</v>
+      </c>
+      <c r="AG4" s="42">
+        <v>0.2578025874699007</v>
+      </c>
+      <c r="AH4" s="43">
+        <v>0.11840756019698384</v>
+      </c>
+      <c r="AI4" s="41">
+        <v>31.07983403359998</v>
+      </c>
+      <c r="AJ4" s="12"/>
+    </row>
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" s="21" t="s">
-        <v>38</v>
+        <v>115</v>
       </c>
       <c r="B5" s="12">
-        <v>210.14336800000001</v>
+        <v>218.85400000000001</v>
       </c>
       <c r="C5" s="22">
-        <v>0.22275651056605106</v>
+        <v>0.21423529925523863</v>
       </c>
       <c r="D5" s="29">
-        <v>0.11801519297244734</v>
+        <v>3.5865142972027142E-2</v>
       </c>
       <c r="E5" s="12">
-        <v>24.8001101264</v>
+        <v>7.8492300000000057</v>
       </c>
       <c r="F5" s="12"/>
       <c r="G5" s="21" t="s">
@@ -7825,22 +8063,38 @@
         <v>24.8001101264</v>
       </c>
       <c r="AC5" s="12"/>
-    </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AE5" s="40" t="s">
+        <v>115</v>
+      </c>
+      <c r="AF5" s="41">
+        <v>218.85600000000002</v>
+      </c>
+      <c r="AG5" s="42">
+        <v>0.21495446509069555</v>
+      </c>
+      <c r="AH5" s="43">
+        <v>3.586522645026835E-2</v>
+      </c>
+      <c r="AI5" s="41">
+        <v>7.849319999999949</v>
+      </c>
+      <c r="AJ5" s="12"/>
+    </row>
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
         <v>36</v>
       </c>
       <c r="B6" s="12">
-        <v>177.40437299999999</v>
+        <v>198.38494800000001</v>
       </c>
       <c r="C6" s="22">
-        <v>0.18805246848731463</v>
+        <v>0.19419822668315384</v>
       </c>
       <c r="D6" s="29">
-        <v>0.17124807148919596</v>
+        <v>0.16268682642193188</v>
       </c>
       <c r="E6" s="12">
-        <v>30.380156749999998</v>
+        <v>32.274617599999971</v>
       </c>
       <c r="F6" s="12"/>
       <c r="G6" s="21" t="s">
@@ -7897,22 +8151,38 @@
         <v>30.380156749999998</v>
       </c>
       <c r="AC6" s="12"/>
-    </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AE6" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF6" s="41">
+        <v>196.93234799999999</v>
+      </c>
+      <c r="AG6" s="42">
+        <v>0.19342164493271694</v>
+      </c>
+      <c r="AH6" s="43">
+        <v>0.17126296386818063</v>
+      </c>
+      <c r="AI6" s="41">
+        <v>33.727217599999989</v>
+      </c>
+      <c r="AJ6" s="12"/>
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" s="21" t="s">
         <v>40</v>
       </c>
       <c r="B7" s="12">
-        <v>172.11133100000001</v>
+        <v>190.93378000000001</v>
       </c>
       <c r="C7" s="22">
-        <v>0.18244172960261401</v>
+        <v>0.18690430833447821</v>
       </c>
       <c r="D7" s="29">
-        <v>0.1289374887235053</v>
+        <v>0.13099819948046898</v>
       </c>
       <c r="E7" s="12">
-        <v>22.191602799999998</v>
+        <v>25.011981399999968</v>
       </c>
       <c r="F7" s="12"/>
       <c r="G7" s="21" t="s">
@@ -7975,8 +8245,26 @@
       <c r="AC7" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AE7" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="AF7" s="41">
+        <v>188.97588910000002</v>
+      </c>
+      <c r="AG7" s="42">
+        <v>0.18560702542552684</v>
+      </c>
+      <c r="AH7" s="43">
+        <v>0.14271594343831007</v>
+      </c>
+      <c r="AI7" s="41">
+        <v>26.969872299999963</v>
+      </c>
+      <c r="AJ7" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" s="21" t="s">
         <v>37</v>
       </c>
@@ -7984,7 +8272,7 @@
         <v>94.882213999999991</v>
       </c>
       <c r="C8" s="22">
-        <v>0.10057719692310878</v>
+        <v>9.2879817185381977E-2</v>
       </c>
       <c r="D8" s="29">
         <v>0.28159743932619463</v>
@@ -8047,22 +8335,38 @@
         <v>26.71858850000001</v>
       </c>
       <c r="AC8" s="12"/>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AE8" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF8" s="41">
+        <v>94.882213999999991</v>
+      </c>
+      <c r="AG8" s="42">
+        <v>9.3190753541099625E-2</v>
+      </c>
+      <c r="AH8" s="43">
+        <v>0.28159743932619463</v>
+      </c>
+      <c r="AI8" s="41">
+        <v>26.71858850000001</v>
+      </c>
+      <c r="AJ8" s="12"/>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
         <v>39</v>
       </c>
       <c r="B9" s="12">
-        <v>59.980460999999991</v>
+        <v>46.022978999999999</v>
       </c>
       <c r="C9" s="22">
-        <v>6.35805846345011E-2</v>
+        <v>4.5051708804420124E-2</v>
       </c>
       <c r="D9" s="29">
-        <v>9.1757028336277635E-2</v>
+        <v>0.12015729349462578</v>
       </c>
       <c r="E9" s="12">
-        <v>5.5036288595999991</v>
+        <v>5.5299965951999965</v>
       </c>
       <c r="F9" s="12"/>
       <c r="G9" s="21" t="s">
@@ -8119,8 +8423,26 @@
         <v>5.5036288595999991</v>
       </c>
       <c r="AC9" s="12"/>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AE9" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF9" s="41">
+        <v>46.022978999999999</v>
+      </c>
+      <c r="AG9" s="42">
+        <v>4.5202529667111309E-2</v>
+      </c>
+      <c r="AH9" s="43">
+        <v>0.12015729349462578</v>
+      </c>
+      <c r="AI9" s="41">
+        <v>5.5299965951999965</v>
+      </c>
+      <c r="AJ9" s="12">
+        <v>2.76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" s="21" t="s">
         <v>96</v>
       </c>
@@ -8128,7 +8450,7 @@
         <v>9.99925</v>
       </c>
       <c r="C10" s="22">
-        <v>1.0599421049907156E-2</v>
+        <v>9.7882255571200196E-3</v>
       </c>
       <c r="D10" s="29">
         <v>0.19999999999999996</v>
@@ -8191,8 +8513,24 @@
         <v>1.9998499999999986</v>
       </c>
       <c r="AC10" s="12"/>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AE10" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="AF10" s="41">
+        <v>9.99925</v>
+      </c>
+      <c r="AG10" s="42">
+        <v>9.8209938729490499E-3</v>
+      </c>
+      <c r="AH10" s="43">
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AI10" s="41">
+        <v>1.9998499999999986</v>
+      </c>
+      <c r="AJ10" s="12"/>
+    </row>
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" s="21" t="s">
         <v>74</v>
       </c>
@@ -8200,7 +8538,7 @@
         <v>2.9170551999999998E-16</v>
       </c>
       <c r="C11" s="22">
-        <v>3.0921415396775884E-19</v>
+        <v>2.8554935880360874E-19</v>
       </c>
       <c r="D11" s="29">
         <v>9.799364235548258E-2</v>
@@ -8263,8 +8601,24 @@
         <v>2.8585286400000075E-17</v>
       </c>
       <c r="AC11" s="12"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AE11" s="40" t="s">
+        <v>74</v>
+      </c>
+      <c r="AF11" s="41">
+        <v>2.9170551999999998E-16</v>
+      </c>
+      <c r="AG11" s="42">
+        <v>2.8650530036006862E-19</v>
+      </c>
+      <c r="AH11" s="43">
+        <v>9.799364235548258E-2</v>
+      </c>
+      <c r="AI11" s="41">
+        <v>2.8585286400000075E-17</v>
+      </c>
+      <c r="AJ11" s="12"/>
+    </row>
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" s="21" t="s">
         <v>87</v>
       </c>
@@ -8272,7 +8626,7 @@
         <v>1.3353E-17</v>
       </c>
       <c r="C12" s="22">
-        <v>1.4154468513079507E-20</v>
+        <v>1.3071197926266831E-20</v>
       </c>
       <c r="D12" s="29">
         <v>7.0000000000000062E-2</v>
@@ -8335,8 +8689,24 @@
         <v>9.3470999999999986E-19</v>
       </c>
       <c r="AC12" s="12"/>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AE12" s="40" t="s">
+        <v>87</v>
+      </c>
+      <c r="AF12" s="41">
+        <v>1.3353E-17</v>
+      </c>
+      <c r="AG12" s="42">
+        <v>1.3114956740304389E-20</v>
+      </c>
+      <c r="AH12" s="43">
+        <v>7.0000000000000062E-2</v>
+      </c>
+      <c r="AI12" s="41">
+        <v>9.3470999999999986E-19</v>
+      </c>
+      <c r="AJ12" s="12"/>
+    </row>
+    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" s="21" t="s">
         <v>71</v>
       </c>
@@ -8344,7 +8714,7 @@
         <v>5.5999999999999995E-18</v>
       </c>
       <c r="C13" s="22">
-        <v>5.9361209970227834E-21</v>
+        <v>5.4818174482958324E-21</v>
       </c>
       <c r="D13" s="29">
         <v>7.0000000000000062E-2</v>
@@ -8412,22 +8782,37 @@
       <c r="AB13" s="41">
         <v>3.9200000000000069E-19</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AE13" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="AF13" s="41">
+        <v>5.5999999999999995E-18</v>
+      </c>
+      <c r="AG13" s="42">
+        <v>5.5001690815325816E-21</v>
+      </c>
+      <c r="AH13" s="43">
+        <v>7.0000000000000062E-2</v>
+      </c>
+      <c r="AI13" s="41">
+        <v>3.9200000000000069E-19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" s="21" t="s">
         <v>105</v>
       </c>
       <c r="B14" s="12">
-        <v>943.37699699999996</v>
+        <v>1021.5590090000001</v>
       </c>
       <c r="C14" s="22">
         <v>1</v>
       </c>
       <c r="D14" s="29">
-        <v>0.12661243322217675</v>
+        <v>0.1277107802676134</v>
       </c>
       <c r="E14" s="12">
-        <v>119.4432570360002</v>
+        <v>130.46409812879995</v>
       </c>
       <c r="X14" s="31" t="s">
         <v>105</v>
@@ -8448,9 +8833,30 @@
         <f>SUM(AC4:AC13)</f>
         <v>0</v>
       </c>
+      <c r="AE14" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="AF14" s="24">
+        <v>1018.1505181</v>
+      </c>
+      <c r="AG14" s="25">
+        <v>1</v>
+      </c>
+      <c r="AH14" s="30">
+        <v>0.13148810185612581</v>
+      </c>
+      <c r="AI14" s="24">
+        <v>133.87467902879996</v>
+      </c>
+      <c r="AJ14" s="24">
+        <f>SUM(AJ4:AJ13)</f>
+        <v>2.76</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
+    <mergeCell ref="AF1:AJ1"/>
+    <mergeCell ref="AF2:AJ2"/>
     <mergeCell ref="Y1:AC1"/>
     <mergeCell ref="Y2:AC2"/>
     <mergeCell ref="H1:L1"/>

--- a/Open Positions.xlsx
+++ b/Open Positions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\StockSillines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CF6D7E0-0C88-4158-8EE9-C8F002657B58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{296838DE-1829-4FDC-83E8-09A3018BC897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Positions" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="20" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="137">
   <si>
     <t>Name</t>
   </si>
@@ -446,6 +446,15 @@
   </si>
   <si>
     <t>WK06</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>Consumer</t>
+  </si>
+  <si>
+    <t>Others</t>
   </si>
 </sst>
 </file>
@@ -688,106 +697,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="36">
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
     </dxf>
@@ -2074,7 +1984,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{42F2A961-4B24-4134-99E9-0FE83E8807F0}" name="PivotTable1" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{42F2A961-4B24-4134-99E9-0FE83E8807F0}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:E14" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="22">
     <pivotField axis="axisRow" showAll="0" sortType="descending">
@@ -2252,7 +2162,7 @@
     <dataField name="Target P&amp;L" fld="21" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="35">
+    <format dxfId="2">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -2262,7 +2172,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="34">
+    <format dxfId="1">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -2272,7 +2182,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="33">
+    <format dxfId="0">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -2664,7 +2574,7 @@
         <v>21.78</v>
       </c>
       <c r="G2" s="1">
-        <f>E2*F2</f>
+        <f t="shared" ref="G2:G46" si="0">E2*F2</f>
         <v>49.991634000000005</v>
       </c>
       <c r="H2" s="13">
@@ -2675,46 +2585,46 @@
         <v>0.45929999999999999</v>
       </c>
       <c r="J2" s="9">
-        <f>IFERROR(H2/I2,"")</f>
+        <f t="shared" ref="J2:J46" si="1">IFERROR(H2/I2,"")</f>
         <v>0.47982946860685666</v>
       </c>
       <c r="K2" s="9">
-        <f>IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" ref="K2:K46" si="2">IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
         <v>2.4968515740223275E-2</v>
       </c>
       <c r="L2" s="12">
         <v>26.58</v>
       </c>
       <c r="M2" s="12">
-        <f>L2*E2</f>
+        <f t="shared" ref="M2:M46" si="3">L2*E2</f>
         <v>61.009073999999998</v>
       </c>
       <c r="N2" s="12">
-        <f>F2/(1+I2-H2)</f>
+        <f t="shared" ref="N2:N46" si="4">F2/(1+I2-H2)</f>
         <v>17.579908117366596</v>
       </c>
       <c r="O2" s="12">
-        <f>L2-F2</f>
+        <f t="shared" ref="O2:O46" si="5">L2-F2</f>
         <v>4.7999999999999972</v>
       </c>
       <c r="P2" s="12">
-        <f>0.5*(N2-F2)</f>
+        <f t="shared" ref="P2:P46" si="6">0.5*(N2-F2)</f>
         <v>-2.1000459413167025</v>
       </c>
       <c r="Q2" s="15">
-        <f>O2+P2</f>
+        <f t="shared" ref="Q2:Q46" si="7">O2+P2</f>
         <v>2.6999540586832946</v>
       </c>
       <c r="R2" s="12">
-        <f>MAX($Q$2:$Q$279)-Q2</f>
+        <f t="shared" ref="R2:R46" si="8">MAX($Q$2:$Q$279)-Q2</f>
         <v>111.4324910225011</v>
       </c>
       <c r="S2" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R2)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" ref="S2:S46" si="9">IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R2)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
         <v>8.9740433048209802E-3</v>
       </c>
       <c r="T2" s="9">
-        <f>R2/MAX($R$2:$R$28)</f>
+        <f t="shared" ref="T2:T46" si="10">R2/MAX($R$2:$R$28)</f>
         <v>0.77803273697370867</v>
       </c>
     </row>
@@ -2738,7 +2648,7 @@
         <v>20.928000000000001</v>
       </c>
       <c r="G3" s="1">
-        <f>E3*F3</f>
+        <f t="shared" si="0"/>
         <v>41.856000000000002</v>
       </c>
       <c r="H3" s="13">
@@ -2748,47 +2658,47 @@
         <v>0.2</v>
       </c>
       <c r="J3" s="9">
-        <f>IFERROR(H3/I3,"")</f>
+        <f t="shared" si="1"/>
         <v>0.22499999999999998</v>
       </c>
       <c r="K3" s="9">
-        <f>IFERROR(J3/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>1.1708151351898769E-2</v>
       </c>
       <c r="L3" s="12">
-        <f>F3/(1-(F3*(1+H3)-F3)/(F3*(1+H3)))</f>
+        <f t="shared" ref="L3:L39" si="11">F3/(1-(F3*(1+H3)-F3)/(F3*(1+H3)))</f>
         <v>21.869759999999999</v>
       </c>
       <c r="M3" s="12">
-        <f>L3*E3</f>
+        <f t="shared" si="3"/>
         <v>43.739519999999999</v>
       </c>
       <c r="N3" s="12">
-        <f>F3/(1+I3-H3)</f>
+        <f t="shared" si="4"/>
         <v>18.119480519480518</v>
       </c>
       <c r="O3" s="12">
-        <f>L3-F3</f>
+        <f t="shared" si="5"/>
         <v>0.9417599999999986</v>
       </c>
       <c r="P3" s="12">
-        <f>0.5*(N3-F3)</f>
+        <f t="shared" si="6"/>
         <v>-1.4042597402597412</v>
       </c>
       <c r="Q3" s="15">
-        <f>O3+P3</f>
+        <f t="shared" si="7"/>
         <v>-0.46249974025974261</v>
       </c>
       <c r="R3" s="12">
-        <f>MAX($Q$2:$Q$279)-Q3</f>
+        <f t="shared" si="8"/>
         <v>114.59494482144413</v>
       </c>
       <c r="S3" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R3)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.7263884245343277E-3</v>
       </c>
       <c r="T3" s="9">
-        <f>R3/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.80011330398039715</v>
       </c>
     </row>
@@ -2812,7 +2722,7 @@
         <v>16.399000000000001</v>
       </c>
       <c r="G4" s="1">
-        <f>E4*F4</f>
+        <f t="shared" si="0"/>
         <v>32.798000000000002</v>
       </c>
       <c r="H4" s="13">
@@ -2822,47 +2732,47 @@
         <v>0.2</v>
       </c>
       <c r="J4" s="9">
-        <f>IFERROR(H4/I4,"")</f>
+        <f t="shared" si="1"/>
         <v>0.22499999999999998</v>
       </c>
       <c r="K4" s="9">
-        <f>IFERROR(J4/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>1.1708151351898769E-2</v>
       </c>
       <c r="L4" s="12">
-        <f>F4/(1-(F4*(1+H4)-F4)/(F4*(1+H4)))</f>
+        <f t="shared" si="11"/>
         <v>17.136955</v>
       </c>
       <c r="M4" s="12">
-        <f>L4*E4</f>
+        <f t="shared" si="3"/>
         <v>34.273910000000001</v>
       </c>
       <c r="N4" s="12">
-        <f>F4/(1+I4-H4)</f>
+        <f t="shared" si="4"/>
         <v>14.198268398268398</v>
       </c>
       <c r="O4" s="12">
-        <f>L4-F4</f>
+        <f t="shared" si="5"/>
         <v>0.73795499999999947</v>
       </c>
       <c r="P4" s="12">
-        <f>0.5*(N4-F4)</f>
+        <f t="shared" si="6"/>
         <v>-1.1003658008658013</v>
       </c>
       <c r="Q4" s="15">
-        <f>O4+P4</f>
+        <f t="shared" si="7"/>
         <v>-0.3624108008658018</v>
       </c>
       <c r="R4" s="12">
-        <f>MAX($Q$2:$Q$279)-Q4</f>
+        <f t="shared" si="8"/>
         <v>114.49485588205019</v>
       </c>
       <c r="S4" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R4)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.7340168455268905E-3</v>
       </c>
       <c r="T4" s="9">
-        <f>R4/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.79941447304928448</v>
       </c>
     </row>
@@ -2886,7 +2796,7 @@
         <v>15.3</v>
       </c>
       <c r="G5" s="1">
-        <f>E5*F5</f>
+        <f t="shared" si="0"/>
         <v>29.980350000000001</v>
       </c>
       <c r="H5" s="13">
@@ -2896,47 +2806,47 @@
         <v>0.39532299999999998</v>
       </c>
       <c r="J5" s="9">
-        <f>IFERROR(H5/I5,"")</f>
+        <f t="shared" si="1"/>
         <v>0.88535197800279775</v>
       </c>
       <c r="K5" s="9">
-        <f>IFERROR(J5/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>4.6070377591820914E-2</v>
       </c>
       <c r="L5" s="12">
-        <f>F5/(1-(F5*(1+H5)-F5)/(F5*(1+H5)))</f>
+        <f t="shared" si="11"/>
         <v>20.655000000000001</v>
       </c>
       <c r="M5" s="12">
-        <f>L5*E5</f>
+        <f t="shared" si="3"/>
         <v>40.4734725</v>
       </c>
       <c r="N5" s="12">
-        <f>F5/(1+I5-H5)</f>
+        <f t="shared" si="4"/>
         <v>14.636624277854791</v>
       </c>
       <c r="O5" s="12">
-        <f>L5-F5</f>
+        <f t="shared" si="5"/>
         <v>5.3550000000000004</v>
       </c>
       <c r="P5" s="12">
-        <f>0.5*(N5-F5)</f>
+        <f t="shared" si="6"/>
         <v>-0.33168786107260484</v>
       </c>
       <c r="Q5" s="15">
-        <f>O5+P5</f>
+        <f t="shared" si="7"/>
         <v>5.0233121389273956</v>
       </c>
       <c r="R5" s="12">
-        <f>MAX($Q$2:$Q$279)-Q5</f>
+        <f t="shared" si="8"/>
         <v>109.10913294225699</v>
       </c>
       <c r="S5" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R5)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>9.1651356127009313E-3</v>
       </c>
       <c r="T5" s="9">
-        <f>R5/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.76181081974332665</v>
       </c>
     </row>
@@ -2960,7 +2870,7 @@
         <v>51.88</v>
       </c>
       <c r="G6" s="1">
-        <f>E6*F6</f>
+        <f t="shared" si="0"/>
         <v>89.991048000000006</v>
       </c>
       <c r="H6" s="13">
@@ -2971,47 +2881,47 @@
         <v>0.19980000000000001</v>
       </c>
       <c r="J6" s="9">
-        <f>IFERROR(H6/I6,"")</f>
+        <f t="shared" si="1"/>
         <v>0.92242242242242245</v>
       </c>
       <c r="K6" s="9">
-        <f>IFERROR(J6/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>4.7999383698252546E-2</v>
       </c>
       <c r="L6" s="12">
-        <f>F6/(1-(F6*(1+H6)-F6)/(F6*(1+H6)))</f>
+        <f t="shared" si="11"/>
         <v>61.441483999999996</v>
       </c>
       <c r="M6" s="12">
-        <f>L6*E6</f>
+        <f t="shared" si="3"/>
         <v>106.57639814639998</v>
       </c>
       <c r="N6" s="12">
-        <f>F6/(1+I6-H6)</f>
+        <f t="shared" si="4"/>
         <v>51.088133924175295</v>
       </c>
       <c r="O6" s="12">
-        <f>L6-F6</f>
+        <f t="shared" si="5"/>
         <v>9.561483999999993</v>
       </c>
       <c r="P6" s="12">
-        <f>0.5*(N6-F6)</f>
+        <f t="shared" si="6"/>
         <v>-0.39593303791235357</v>
       </c>
       <c r="Q6" s="15">
-        <f>O6+P6</f>
+        <f t="shared" si="7"/>
         <v>9.1655509620876394</v>
       </c>
       <c r="R6" s="12">
-        <f>MAX($Q$2:$Q$279)-Q6</f>
+        <f t="shared" si="8"/>
         <v>104.96689411909675</v>
       </c>
       <c r="S6" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R6)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>9.526813271862531E-3</v>
       </c>
       <c r="T6" s="9">
-        <f>R6/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.73288929623425103</v>
       </c>
     </row>
@@ -3035,7 +2945,7 @@
         <v>44.24</v>
       </c>
       <c r="G7" s="1">
-        <f>E7*F7</f>
+        <f t="shared" si="0"/>
         <v>44.24</v>
       </c>
       <c r="H7" s="13">
@@ -3045,47 +2955,47 @@
         <v>0.2</v>
       </c>
       <c r="J7" s="9">
-        <f>IFERROR(H7/I7,"")</f>
+        <f t="shared" si="1"/>
         <v>0.22499999999999998</v>
       </c>
       <c r="K7" s="9">
-        <f>IFERROR(J7/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>1.1708151351898769E-2</v>
       </c>
       <c r="L7" s="12">
-        <f>F7/(1-(F7*(1+H7)-F7)/(F7*(1+H7)))</f>
+        <f t="shared" si="11"/>
         <v>46.230800000000002</v>
       </c>
       <c r="M7" s="12">
-        <f>L7*E7</f>
+        <f t="shared" si="3"/>
         <v>46.230800000000002</v>
       </c>
       <c r="N7" s="12">
-        <f>F7/(1+I7-H7)</f>
+        <f t="shared" si="4"/>
         <v>38.303030303030305</v>
       </c>
       <c r="O7" s="12">
-        <f>L7-F7</f>
+        <f t="shared" si="5"/>
         <v>1.9908000000000001</v>
       </c>
       <c r="P7" s="12">
-        <f>0.5*(N7-F7)</f>
+        <f t="shared" si="6"/>
         <v>-2.9684848484848487</v>
       </c>
       <c r="Q7" s="15">
-        <f>O7+P7</f>
+        <f t="shared" si="7"/>
         <v>-0.9776848484848486</v>
       </c>
       <c r="R7" s="12">
-        <f>MAX($Q$2:$Q$279)-Q7</f>
+        <f t="shared" si="8"/>
         <v>115.11012992966923</v>
       </c>
       <c r="S7" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R7)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.6873327361456955E-3</v>
       </c>
       <c r="T7" s="9">
-        <f>R7/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.80371037765363607</v>
       </c>
     </row>
@@ -3109,7 +3019,7 @@
         <v>48.68</v>
       </c>
       <c r="G8" s="1">
-        <f>E8*F8</f>
+        <f t="shared" si="0"/>
         <v>48.68</v>
       </c>
       <c r="H8" s="13">
@@ -3119,47 +3029,47 @@
         <v>0.2</v>
       </c>
       <c r="J8" s="9">
-        <f>IFERROR(H8/I8,"")</f>
+        <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
       <c r="K8" s="9">
-        <f>IFERROR(J8/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>6.5045285288326494E-3</v>
       </c>
       <c r="L8" s="12">
-        <f>F8/(1-(F8*(1+H8)-F8)/(F8*(1+H8)))</f>
+        <f t="shared" si="11"/>
         <v>49.896999999999998</v>
       </c>
       <c r="M8" s="12">
-        <f>L8*E8</f>
+        <f t="shared" si="3"/>
         <v>49.896999999999998</v>
       </c>
       <c r="N8" s="12">
-        <f>F8/(1+I8-H8)</f>
+        <f t="shared" si="4"/>
         <v>41.42978723404255</v>
       </c>
       <c r="O8" s="12">
-        <f>L8-F8</f>
+        <f t="shared" si="5"/>
         <v>1.2169999999999987</v>
       </c>
       <c r="P8" s="12">
-        <f>0.5*(N8-F8)</f>
+        <f t="shared" si="6"/>
         <v>-3.6251063829787249</v>
       </c>
       <c r="Q8" s="15">
-        <f>O8+P8</f>
+        <f t="shared" si="7"/>
         <v>-2.4081063829787261</v>
       </c>
       <c r="R8" s="12">
-        <f>MAX($Q$2:$Q$279)-Q8</f>
+        <f t="shared" si="8"/>
         <v>116.54055146416312</v>
       </c>
       <c r="S8" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R8)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.5807042049865848E-3</v>
       </c>
       <c r="T8" s="9">
-        <f>R8/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.81369772309746791</v>
       </c>
     </row>
@@ -3183,7 +3093,7 @@
         <v>51.28</v>
       </c>
       <c r="G9" s="1">
-        <f>E9*F9</f>
+        <f t="shared" si="0"/>
         <v>51.28</v>
       </c>
       <c r="H9" s="13">
@@ -3193,47 +3103,47 @@
         <v>0.2</v>
       </c>
       <c r="J9" s="9">
-        <f>IFERROR(H9/I9,"")</f>
+        <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
       <c r="K9" s="9">
-        <f>IFERROR(J9/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>6.5045285288326494E-3</v>
       </c>
       <c r="L9" s="12">
-        <f>F9/(1-(F9*(1+H9)-F9)/(F9*(1+H9)))</f>
+        <f t="shared" si="11"/>
         <v>52.561999999999998</v>
       </c>
       <c r="M9" s="12">
-        <f>L9*E9</f>
+        <f t="shared" si="3"/>
         <v>52.561999999999998</v>
       </c>
       <c r="N9" s="12">
-        <f>F9/(1+I9-H9)</f>
+        <f t="shared" si="4"/>
         <v>43.642553191489363</v>
       </c>
       <c r="O9" s="12">
-        <f>L9-F9</f>
+        <f t="shared" si="5"/>
         <v>1.2819999999999965</v>
       </c>
       <c r="P9" s="12">
-        <f>0.5*(N9-F9)</f>
+        <f t="shared" si="6"/>
         <v>-3.8187234042553193</v>
       </c>
       <c r="Q9" s="15">
-        <f>O9+P9</f>
+        <f t="shared" si="7"/>
         <v>-2.5367234042553228</v>
       </c>
       <c r="R9" s="12">
-        <f>MAX($Q$2:$Q$279)-Q9</f>
+        <f t="shared" si="8"/>
         <v>116.66916848543971</v>
       </c>
       <c r="S9" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R9)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.5712447682765452E-3</v>
       </c>
       <c r="T9" s="9">
-        <f>R9/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.81459573993409262</v>
       </c>
     </row>
@@ -3257,7 +3167,7 @@
         <v>20.36</v>
       </c>
       <c r="G10" s="1">
-        <f>E10*F10</f>
+        <f t="shared" si="0"/>
         <v>20.36</v>
       </c>
       <c r="H10" s="13">
@@ -3267,47 +3177,47 @@
         <v>0.2</v>
       </c>
       <c r="J10" s="9">
-        <f>IFERROR(H10/I10,"")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="K10" s="9">
-        <f>IFERROR(J10/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>5.2036228230661195E-2</v>
       </c>
       <c r="L10" s="12">
-        <f>F10/(1-(F10*(1+H10)-F10)/(F10*(1+H10)))</f>
+        <f t="shared" si="11"/>
         <v>24.431999999999999</v>
       </c>
       <c r="M10" s="12">
-        <f>L10*E10</f>
+        <f t="shared" si="3"/>
         <v>24.431999999999999</v>
       </c>
       <c r="N10" s="12">
-        <f>F10/(1+I10-H10)</f>
+        <f t="shared" si="4"/>
         <v>20.36</v>
       </c>
       <c r="O10" s="12">
-        <f>L10-F10</f>
+        <f t="shared" si="5"/>
         <v>4.0719999999999992</v>
       </c>
       <c r="P10" s="12">
-        <f>0.5*(N10-F10)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q10" s="15">
-        <f>O10+P10</f>
+        <f t="shared" si="7"/>
         <v>4.0719999999999992</v>
       </c>
       <c r="R10" s="12">
-        <f>MAX($Q$2:$Q$279)-Q10</f>
+        <f t="shared" si="8"/>
         <v>110.06044508118438</v>
       </c>
       <c r="S10" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R10)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>9.0859163731562727E-3</v>
       </c>
       <c r="T10" s="9">
-        <f>R10/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.76845297572830351</v>
       </c>
     </row>
@@ -3331,7 +3241,7 @@
         <v>41.76</v>
       </c>
       <c r="G11" s="1">
-        <f>E11*F11</f>
+        <f t="shared" si="0"/>
         <v>40.022784000000001</v>
       </c>
       <c r="H11" s="13">
@@ -3341,47 +3251,47 @@
         <v>0.2</v>
       </c>
       <c r="J11" s="9">
-        <f>IFERROR(H11/I11,"")</f>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
       <c r="K11" s="9">
-        <f>IFERROR(J11/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>2.6018114115330598E-2</v>
       </c>
       <c r="L11" s="12">
-        <f>F11/(1-(F11*(1+H11)-F11)/(F11*(1+H11)))</f>
+        <f t="shared" si="11"/>
         <v>45.936</v>
       </c>
       <c r="M11" s="12">
-        <f>L11*E11</f>
+        <f t="shared" si="3"/>
         <v>44.025062400000003</v>
       </c>
       <c r="N11" s="12">
-        <f>F11/(1+I11-H11)</f>
+        <f t="shared" si="4"/>
         <v>37.963636363636368</v>
       </c>
       <c r="O11" s="12">
-        <f>L11-F11</f>
+        <f t="shared" si="5"/>
         <v>4.1760000000000019</v>
       </c>
       <c r="P11" s="12">
-        <f>0.5*(N11-F11)</f>
+        <f t="shared" si="6"/>
         <v>-1.8981818181818149</v>
       </c>
       <c r="Q11" s="15">
-        <f>O11+P11</f>
+        <f t="shared" si="7"/>
         <v>2.2778181818181871</v>
       </c>
       <c r="R11" s="12">
-        <f>MAX($Q$2:$Q$279)-Q11</f>
+        <f t="shared" si="8"/>
         <v>111.8546268993662</v>
       </c>
       <c r="S11" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R11)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.9401755449927331E-3</v>
       </c>
       <c r="T11" s="9">
-        <f>R11/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.78098013165759694</v>
       </c>
     </row>
@@ -3405,7 +3315,7 @@
         <v>40.340000000000003</v>
       </c>
       <c r="G12" s="1">
-        <f>E12*F12</f>
+        <f t="shared" si="0"/>
         <v>20.992936</v>
       </c>
       <c r="H12" s="13">
@@ -3415,47 +3325,47 @@
         <v>0.2</v>
       </c>
       <c r="J12" s="9">
-        <f>IFERROR(H12/I12,"")</f>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
       <c r="K12" s="9">
-        <f>IFERROR(J12/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>2.6018114115330598E-2</v>
       </c>
       <c r="L12" s="12">
-        <f>F12/(1-(F12*(1+H12)-F12)/(F12*(1+H12)))</f>
+        <f t="shared" si="11"/>
         <v>44.374000000000009</v>
       </c>
       <c r="M12" s="12">
-        <f>L12*E12</f>
+        <f t="shared" si="3"/>
         <v>23.092229600000003</v>
       </c>
       <c r="N12" s="12">
-        <f>F12/(1+I12-H12)</f>
+        <f t="shared" si="4"/>
         <v>36.672727272727279</v>
       </c>
       <c r="O12" s="12">
-        <f>L12-F12</f>
+        <f t="shared" si="5"/>
         <v>4.034000000000006</v>
       </c>
       <c r="P12" s="12">
-        <f>0.5*(N12-F12)</f>
+        <f t="shared" si="6"/>
         <v>-1.8336363636363622</v>
       </c>
       <c r="Q12" s="15">
-        <f>O12+P12</f>
+        <f t="shared" si="7"/>
         <v>2.2003636363636438</v>
       </c>
       <c r="R12" s="12">
-        <f>MAX($Q$2:$Q$279)-Q12</f>
+        <f t="shared" si="8"/>
         <v>111.93208144482074</v>
       </c>
       <c r="S12" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R12)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.9339891395923948E-3</v>
       </c>
       <c r="T12" s="9">
-        <f>R12/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.78152092699868725</v>
       </c>
     </row>
@@ -3479,7 +3389,7 @@
         <v>138.53</v>
       </c>
       <c r="G13" s="1">
-        <f>E13*F13</f>
+        <f t="shared" si="0"/>
         <v>71.176714000000004</v>
       </c>
       <c r="H13" s="13">
@@ -3489,47 +3399,47 @@
         <v>0.18340000000000001</v>
       </c>
       <c r="J13" s="9">
-        <f>IFERROR(H13/I13,"")</f>
+        <f t="shared" si="1"/>
         <v>0.38167938931297712</v>
       </c>
       <c r="K13" s="9">
-        <f>IFERROR(J13/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>1.9861155813229465E-2</v>
       </c>
       <c r="L13" s="12">
-        <f>F13/(1-(F13*(1+H13)-F13)/(F13*(1+H13)))</f>
+        <f t="shared" si="11"/>
         <v>148.22710000000001</v>
       </c>
       <c r="M13" s="12">
-        <f>L13*E13</f>
+        <f t="shared" si="3"/>
         <v>76.159083980000005</v>
       </c>
       <c r="N13" s="12">
-        <f>F13/(1+I13-H13)</f>
+        <f t="shared" si="4"/>
         <v>124.42069337165439</v>
       </c>
       <c r="O13" s="12">
-        <f>L13-F13</f>
+        <f t="shared" si="5"/>
         <v>9.697100000000006</v>
       </c>
       <c r="P13" s="12">
-        <f>0.5*(N13-F13)</f>
+        <f t="shared" si="6"/>
         <v>-7.0546533141728034</v>
       </c>
       <c r="Q13" s="15">
-        <f>O13+P13</f>
+        <f t="shared" si="7"/>
         <v>2.6424466858272027</v>
       </c>
       <c r="R13" s="12">
-        <f>MAX($Q$2:$Q$279)-Q13</f>
+        <f t="shared" si="8"/>
         <v>111.48999839535719</v>
       </c>
       <c r="S13" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R13)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.969414426340536E-3</v>
       </c>
       <c r="T13" s="9">
-        <f>R13/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.77843425917148812</v>
       </c>
     </row>
@@ -3553,7 +3463,7 @@
         <v>157.99</v>
       </c>
       <c r="G14" s="1">
-        <f>E14*F14</f>
+        <f t="shared" si="0"/>
         <v>80.954076000000001</v>
       </c>
       <c r="H14" s="13">
@@ -3563,47 +3473,47 @@
         <v>0.16439999999999999</v>
       </c>
       <c r="J14" s="9">
-        <f>IFERROR(H14/I14,"")</f>
+        <f t="shared" si="1"/>
         <v>0.40875912408759124</v>
       </c>
       <c r="K14" s="9">
-        <f>IFERROR(J14/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>2.1270283072387059E-2</v>
       </c>
       <c r="L14" s="12">
-        <f>F14/(1-(F14*(1+H14)-F14)/(F14*(1+H14)))</f>
+        <f t="shared" si="11"/>
         <v>168.60692800000001</v>
       </c>
       <c r="M14" s="12">
-        <f>L14*E14</f>
+        <f t="shared" si="3"/>
         <v>86.394189907200001</v>
       </c>
       <c r="N14" s="12">
-        <f>F14/(1+I14-H14)</f>
+        <f t="shared" si="4"/>
         <v>143.99380240612467</v>
       </c>
       <c r="O14" s="12">
-        <f>L14-F14</f>
+        <f t="shared" si="5"/>
         <v>10.616928000000001</v>
       </c>
       <c r="P14" s="12">
-        <f>0.5*(N14-F14)</f>
+        <f t="shared" si="6"/>
         <v>-6.9980987969376685</v>
       </c>
       <c r="Q14" s="15">
-        <f>O14+P14</f>
+        <f t="shared" si="7"/>
         <v>3.618829203062333</v>
       </c>
       <c r="R14" s="12">
-        <f>MAX($Q$2:$Q$279)-Q14</f>
+        <f t="shared" si="8"/>
         <v>110.51361587812205</v>
       </c>
       <c r="S14" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R14)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>9.0486587743435348E-3</v>
       </c>
       <c r="T14" s="9">
-        <f>R14/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.77161705931131142</v>
       </c>
     </row>
@@ -3627,7 +3537,7 @@
         <v>77.430000000000007</v>
       </c>
       <c r="G15" s="1">
-        <f>E15*F15</f>
+        <f t="shared" si="0"/>
         <v>34.982874000000002</v>
       </c>
       <c r="H15" s="13">
@@ -3637,47 +3547,47 @@
         <v>0.25990000000000002</v>
       </c>
       <c r="J15" s="9">
-        <f>IFERROR(H15/I15,"")</f>
+        <f t="shared" si="1"/>
         <v>0.38476337052712584</v>
       </c>
       <c r="K15" s="9">
-        <f>IFERROR(J15/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>2.0021634563547979E-2</v>
       </c>
       <c r="L15" s="12">
-        <f>F15/(1-(F15*(1+H15)-F15)/(F15*(1+H15)))</f>
+        <f t="shared" si="11"/>
         <v>85.173000000000016</v>
       </c>
       <c r="M15" s="12">
-        <f>L15*E15</f>
+        <f t="shared" si="3"/>
         <v>38.481161400000005</v>
       </c>
       <c r="N15" s="12">
-        <f>F15/(1+I15-H15)</f>
+        <f t="shared" si="4"/>
         <v>66.755754806448849</v>
       </c>
       <c r="O15" s="12">
-        <f>L15-F15</f>
+        <f t="shared" si="5"/>
         <v>7.7430000000000092</v>
       </c>
       <c r="P15" s="12">
-        <f>0.5*(N15-F15)</f>
+        <f t="shared" si="6"/>
         <v>-5.3371225967755791</v>
       </c>
       <c r="Q15" s="15">
-        <f>O15+P15</f>
+        <f t="shared" si="7"/>
         <v>2.4058774032244301</v>
       </c>
       <c r="R15" s="12">
-        <f>MAX($Q$2:$Q$279)-Q15</f>
+        <f t="shared" si="8"/>
         <v>111.72656767795996</v>
       </c>
       <c r="S15" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R15)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.9504226325326178E-3</v>
       </c>
       <c r="T15" s="9">
-        <f>R15/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.78008600943515383</v>
       </c>
     </row>
@@ -3701,7 +3611,7 @@
         <v>189.76</v>
       </c>
       <c r="G16" s="1">
-        <f>E16*F16</f>
+        <f t="shared" si="0"/>
         <v>77.953407999999996</v>
       </c>
       <c r="H16" s="13">
@@ -3712,47 +3622,47 @@
         <v>0.37</v>
       </c>
       <c r="J16" s="9">
-        <f>IFERROR(H16/I16,"")</f>
+        <f t="shared" si="1"/>
         <v>0.53609680506813773</v>
       </c>
       <c r="K16" s="9">
-        <f>IFERROR(J16/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>2.7896455702253901E-2</v>
       </c>
       <c r="L16" s="12">
-        <f>F16/(1-(F16*(1+H16)-F16)/(F16*(1+H16)))</f>
+        <f t="shared" si="11"/>
         <v>227.4</v>
       </c>
       <c r="M16" s="12">
-        <f>L16*E16</f>
+        <f t="shared" si="3"/>
         <v>93.41592</v>
       </c>
       <c r="N16" s="12">
-        <f>F16/(1+I16-H16)</f>
+        <f t="shared" si="4"/>
         <v>161.96043380326287</v>
       </c>
       <c r="O16" s="12">
-        <f>L16-F16</f>
+        <f t="shared" si="5"/>
         <v>37.640000000000015</v>
       </c>
       <c r="P16" s="12">
-        <f>0.5*(N16-F16)</f>
+        <f t="shared" si="6"/>
         <v>-13.899783098368559</v>
       </c>
       <c r="Q16" s="15">
-        <f>O16+P16</f>
+        <f t="shared" si="7"/>
         <v>23.740216901631456</v>
       </c>
       <c r="R16" s="12">
-        <f>MAX($Q$2:$Q$279)-Q16</f>
+        <f t="shared" si="8"/>
         <v>90.39222817955293</v>
       </c>
       <c r="S16" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R16)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>1.1062897996204102E-2</v>
       </c>
       <c r="T16" s="9">
-        <f>R16/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.6311275288415521</v>
       </c>
     </row>
@@ -3776,7 +3686,7 @@
         <v>131.91</v>
       </c>
       <c r="G17" s="1">
-        <f>E17*F17</f>
+        <f t="shared" si="0"/>
         <v>45.983826000000001</v>
       </c>
       <c r="H17" s="13">
@@ -3786,47 +3696,47 @@
         <v>0.33710000000000001</v>
       </c>
       <c r="J17" s="9">
-        <f>IFERROR(H17/I17,"")</f>
+        <f t="shared" si="1"/>
         <v>0.35657075051913378</v>
       </c>
       <c r="K17" s="9">
-        <f>IFERROR(J17/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>1.8554596954391801E-2</v>
       </c>
       <c r="L17" s="12">
-        <f>F17/(1-(F17*(1+H17)-F17)/(F17*(1+H17)))</f>
+        <f t="shared" si="11"/>
         <v>147.76558199999999</v>
       </c>
       <c r="M17" s="12">
-        <f>L17*E17</f>
+        <f t="shared" si="3"/>
         <v>51.511081885199999</v>
       </c>
       <c r="N17" s="12">
-        <f>F17/(1+I17-H17)</f>
+        <f t="shared" si="4"/>
         <v>108.39838934998768</v>
       </c>
       <c r="O17" s="12">
-        <f>L17-F17</f>
+        <f t="shared" si="5"/>
         <v>15.855581999999998</v>
       </c>
       <c r="P17" s="12">
-        <f>0.5*(N17-F17)</f>
+        <f t="shared" si="6"/>
         <v>-11.755805325006158</v>
       </c>
       <c r="Q17" s="15">
-        <f>O17+P17</f>
+        <f t="shared" si="7"/>
         <v>4.0997766749938407</v>
       </c>
       <c r="R17" s="12">
-        <f>MAX($Q$2:$Q$279)-Q17</f>
+        <f t="shared" si="8"/>
         <v>110.03266840619054</v>
       </c>
       <c r="S17" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R17)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>9.0882100242125827E-3</v>
       </c>
       <c r="T17" s="9">
-        <f>R17/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.76825903622043479</v>
       </c>
     </row>
@@ -3850,7 +3760,7 @@
         <v>34.78</v>
       </c>
       <c r="G18" s="1">
-        <f>E18*F18</f>
+        <f t="shared" si="0"/>
         <v>9.99925</v>
       </c>
       <c r="H18" s="13">
@@ -3860,47 +3770,47 @@
         <v>0.2</v>
       </c>
       <c r="J18" s="9">
-        <f>IFERROR(H18/I18,"")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="K18" s="9">
-        <f>IFERROR(J18/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>5.2036228230661195E-2</v>
       </c>
       <c r="L18" s="12">
-        <f>F18/(1-(F18*(1+H18)-F18)/(F18*(1+H18)))</f>
+        <f t="shared" si="11"/>
         <v>41.735999999999997</v>
       </c>
       <c r="M18" s="12">
-        <f>L18*E18</f>
+        <f t="shared" si="3"/>
         <v>11.999099999999999</v>
       </c>
       <c r="N18" s="12">
-        <f>F18/(1+I18-H18)</f>
+        <f t="shared" si="4"/>
         <v>34.78</v>
       </c>
       <c r="O18" s="12">
-        <f>L18-F18</f>
+        <f t="shared" si="5"/>
         <v>6.955999999999996</v>
       </c>
       <c r="P18" s="12">
-        <f>0.5*(N18-F18)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q18" s="15">
-        <f>O18+P18</f>
+        <f t="shared" si="7"/>
         <v>6.955999999999996</v>
       </c>
       <c r="R18" s="12">
-        <f>MAX($Q$2:$Q$279)-Q18</f>
+        <f t="shared" si="8"/>
         <v>107.1764450811844</v>
       </c>
       <c r="S18" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R18)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>9.3304083676456744E-3</v>
       </c>
       <c r="T18" s="9">
-        <f>R18/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.74831660084479601</v>
       </c>
     </row>
@@ -3924,7 +3834,7 @@
         <v>178.56</v>
       </c>
       <c r="G19" s="1">
-        <f>E19*F19</f>
+        <f t="shared" si="0"/>
         <v>44.943551999999997</v>
       </c>
       <c r="H19" s="13">
@@ -3935,47 +3845,47 @@
         <v>0.52980000000000005</v>
       </c>
       <c r="J19" s="9">
-        <f>IFERROR(H19/I19,"")</f>
+        <f t="shared" si="1"/>
         <v>0.18456447350795815</v>
       </c>
       <c r="K19" s="9">
-        <f>IFERROR(J19/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>9.6040390667319325E-3</v>
       </c>
       <c r="L19" s="12">
-        <f>F19/(1-(F19*(1+H19)-F19)/(F19*(1+H19)))</f>
+        <f t="shared" si="11"/>
         <v>196.02</v>
       </c>
       <c r="M19" s="12">
-        <f>L19*E19</f>
+        <f t="shared" si="3"/>
         <v>49.338234</v>
       </c>
       <c r="N19" s="12">
-        <f>F19/(1+I19-H19)</f>
+        <f t="shared" si="4"/>
         <v>124.69119255370553</v>
       </c>
       <c r="O19" s="12">
-        <f>L19-F19</f>
+        <f t="shared" si="5"/>
         <v>17.460000000000008</v>
       </c>
       <c r="P19" s="12">
-        <f>0.5*(N19-F19)</f>
+        <f t="shared" si="6"/>
         <v>-26.934403723147234</v>
       </c>
       <c r="Q19" s="15">
-        <f>O19+P19</f>
+        <f t="shared" si="7"/>
         <v>-9.4744037231472262</v>
       </c>
       <c r="R19" s="12">
-        <f>MAX($Q$2:$Q$279)-Q19</f>
+        <f t="shared" si="8"/>
         <v>123.60684880433161</v>
       </c>
       <c r="S19" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R19)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.0901666022000929E-3</v>
       </c>
       <c r="T19" s="9">
-        <f>R19/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.86303531404059042</v>
       </c>
     </row>
@@ -3999,7 +3909,7 @@
         <v>227.38</v>
       </c>
       <c r="G20" s="1">
-        <f>E20*F20</f>
+        <f t="shared" si="0"/>
         <v>42.792915999999998</v>
       </c>
       <c r="H20" s="13">
@@ -4009,47 +3919,47 @@
         <v>0.2271</v>
       </c>
       <c r="J20" s="9">
-        <f>IFERROR(H20/I20,"")</f>
+        <f t="shared" si="1"/>
         <v>0.66050198150594452</v>
       </c>
       <c r="K20" s="9">
-        <f>IFERROR(J20/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>3.437003185644729E-2</v>
       </c>
       <c r="L20" s="12">
-        <f>F20/(1-(F20*(1+H20)-F20)/(F20*(1+H20)))</f>
+        <f t="shared" si="11"/>
         <v>261.48699999999997</v>
       </c>
       <c r="M20" s="12">
-        <f>L20*E20</f>
+        <f t="shared" si="3"/>
         <v>49.211853399999995</v>
       </c>
       <c r="N20" s="12">
-        <f>F20/(1+I20-H20)</f>
+        <f t="shared" si="4"/>
         <v>211.10389007520189</v>
       </c>
       <c r="O20" s="12">
-        <f>L20-F20</f>
+        <f t="shared" si="5"/>
         <v>34.106999999999971</v>
       </c>
       <c r="P20" s="12">
-        <f>0.5*(N20-F20)</f>
+        <f t="shared" si="6"/>
         <v>-8.1380549623990532</v>
       </c>
       <c r="Q20" s="15">
-        <f>O20+P20</f>
+        <f t="shared" si="7"/>
         <v>25.968945037600918</v>
       </c>
       <c r="R20" s="12">
-        <f>MAX($Q$2:$Q$279)-Q20</f>
+        <f t="shared" si="8"/>
         <v>88.163500043583468</v>
       </c>
       <c r="S20" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R20)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>1.1342562392664218E-2</v>
       </c>
       <c r="T20" s="9">
-        <f>R20/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.6155663272953309</v>
       </c>
     </row>
@@ -4073,7 +3983,7 @@
         <v>421.18</v>
       </c>
       <c r="G21" s="1">
-        <f>E21*F21</f>
+        <f t="shared" si="0"/>
         <v>67.641508000000002</v>
       </c>
       <c r="H21" s="13">
@@ -4083,47 +3993,47 @@
         <v>0.1963</v>
       </c>
       <c r="J21" s="9">
-        <f>IFERROR(H21/I21,"")</f>
+        <f t="shared" si="1"/>
         <v>0.76413652572592972</v>
       </c>
       <c r="K21" s="9">
-        <f>IFERROR(J21/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>3.9762782652058987E-2</v>
       </c>
       <c r="L21" s="12">
-        <f>F21/(1-(F21*(1+H21)-F21)/(F21*(1+H21)))</f>
+        <f t="shared" si="11"/>
         <v>484.35699999999997</v>
       </c>
       <c r="M21" s="12">
-        <f>L21*E21</f>
+        <f t="shared" si="3"/>
         <v>77.787734199999989</v>
       </c>
       <c r="N21" s="12">
-        <f>F21/(1+I21-H21)</f>
+        <f t="shared" si="4"/>
         <v>402.54229188569246</v>
       </c>
       <c r="O21" s="12">
-        <f>L21-F21</f>
+        <f t="shared" si="5"/>
         <v>63.176999999999964</v>
       </c>
       <c r="P21" s="12">
-        <f>0.5*(N21-F21)</f>
+        <f t="shared" si="6"/>
         <v>-9.3188540571537715</v>
       </c>
       <c r="Q21" s="15">
-        <f>O21+P21</f>
+        <f t="shared" si="7"/>
         <v>53.858145942846193</v>
       </c>
       <c r="R21" s="12">
-        <f>MAX($Q$2:$Q$279)-Q21</f>
+        <f t="shared" si="8"/>
         <v>60.274299138338193</v>
       </c>
       <c r="S21" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R21)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>1.6590819209773906E-2</v>
       </c>
       <c r="T21" s="9">
-        <f>R21/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.4208411523197837</v>
       </c>
     </row>
@@ -4147,7 +4057,7 @@
         <v>501.56</v>
       </c>
       <c r="G22" s="1">
-        <f>E22*F22</f>
+        <f t="shared" si="0"/>
         <v>64.901863999999989</v>
       </c>
       <c r="H22" s="13">
@@ -4157,47 +4067,47 @@
         <v>0.29699999999999999</v>
       </c>
       <c r="J22" s="9">
-        <f>IFERROR(H22/I22,"")</f>
+        <f t="shared" si="1"/>
         <v>0.84175084175084181</v>
       </c>
       <c r="K22" s="9">
-        <f>IFERROR(J22/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>4.3801538914697978E-2</v>
       </c>
       <c r="L22" s="12">
-        <f>F22/(1-(F22*(1+H22)-F22)/(F22*(1+H22)))</f>
+        <f t="shared" si="11"/>
         <v>626.95000000000005</v>
       </c>
       <c r="M22" s="12">
-        <f>L22*E22</f>
+        <f t="shared" si="3"/>
         <v>81.127330000000001</v>
       </c>
       <c r="N22" s="12">
-        <f>F22/(1+I22-H22)</f>
+        <f t="shared" si="4"/>
         <v>479.04489016236869</v>
       </c>
       <c r="O22" s="12">
-        <f>L22-F22</f>
+        <f t="shared" si="5"/>
         <v>125.39000000000004</v>
       </c>
       <c r="P22" s="12">
-        <f>0.5*(N22-F22)</f>
+        <f t="shared" si="6"/>
         <v>-11.257554918815657</v>
       </c>
       <c r="Q22" s="15">
-        <f>O22+P22</f>
+        <f t="shared" si="7"/>
         <v>114.13244508118439</v>
       </c>
       <c r="R22" s="12">
-        <f>MAX($Q$2:$Q$279)-Q22</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="S22" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R22)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T22" s="9">
-        <f>R22/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -4221,7 +4131,7 @@
         <v>130.51</v>
       </c>
       <c r="G23" s="1">
-        <f>E23*F23</f>
+        <f t="shared" si="0"/>
         <v>3.9152999999999993E-2</v>
       </c>
       <c r="H23" s="13">
@@ -4231,47 +4141,47 @@
         <v>0.1623</v>
       </c>
       <c r="J23" s="9">
-        <f>IFERROR(H23/I23,"")</f>
+        <f t="shared" si="1"/>
         <v>0.43130006161429457</v>
       </c>
       <c r="K23" s="9">
-        <f>IFERROR(J23/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>2.2443228442059669E-2</v>
       </c>
       <c r="L23" s="12">
-        <f>F23/(1-(F23*(1+H23)-F23)/(F23*(1+H23)))</f>
+        <f t="shared" si="11"/>
         <v>139.64570000000001</v>
       </c>
       <c r="M23" s="12">
-        <f>L23*E23</f>
+        <f t="shared" si="3"/>
         <v>4.1893710000000001E-2</v>
       </c>
       <c r="N23" s="12">
-        <f>F23/(1+I23-H23)</f>
+        <f t="shared" si="4"/>
         <v>119.48182733681222</v>
       </c>
       <c r="O23" s="12">
-        <f>L23-F23</f>
+        <f t="shared" si="5"/>
         <v>9.1357000000000141</v>
       </c>
       <c r="P23" s="12">
-        <f>0.5*(N23-F23)</f>
+        <f t="shared" si="6"/>
         <v>-5.5140863315938873</v>
       </c>
       <c r="Q23" s="15">
-        <f>O23+P23</f>
+        <f t="shared" si="7"/>
         <v>3.6216136684061269</v>
       </c>
       <c r="R23" s="12">
-        <f>MAX($Q$2:$Q$279)-Q23</f>
+        <f t="shared" si="8"/>
         <v>110.51083141277826</v>
       </c>
       <c r="S23" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R23)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>9.0488867671696012E-3</v>
       </c>
       <c r="T23" s="9">
-        <f>R23/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.77159761789729864</v>
       </c>
     </row>
@@ -4295,7 +4205,7 @@
         <v>10.92</v>
       </c>
       <c r="G24" s="1">
-        <f>E24*F24</f>
+        <f t="shared" si="0"/>
         <v>1.092E-18</v>
       </c>
       <c r="H24" s="13">
@@ -4305,47 +4215,47 @@
         <v>1.8652</v>
       </c>
       <c r="J24" s="9">
-        <f>IFERROR(H24/I24,"")</f>
+        <f t="shared" si="1"/>
         <v>0.53613553506326406</v>
       </c>
       <c r="K24" s="9">
-        <f>IFERROR(J24/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>2.7898471065119668E-2</v>
       </c>
       <c r="L24" s="12">
-        <f>F24/(1-(F24*(1+H24)-F24)/(F24*(1+H24)))</f>
+        <f t="shared" si="11"/>
         <v>21.84</v>
       </c>
       <c r="M24" s="12">
-        <f>L24*E24</f>
+        <f t="shared" si="3"/>
         <v>2.1840000000000001E-18</v>
       </c>
       <c r="N24" s="12">
-        <f>F24/(1+I24-H24)</f>
+        <f t="shared" si="4"/>
         <v>5.8546000428908433</v>
       </c>
       <c r="O24" s="12">
-        <f>L24-F24</f>
+        <f t="shared" si="5"/>
         <v>10.92</v>
       </c>
       <c r="P24" s="12">
-        <f>0.5*(N24-F24)</f>
+        <f t="shared" si="6"/>
         <v>-2.5326999785545783</v>
       </c>
       <c r="Q24" s="15">
-        <f>O24+P24</f>
+        <f t="shared" si="7"/>
         <v>8.3873000214454212</v>
       </c>
       <c r="R24" s="12">
-        <f>MAX($Q$2:$Q$279)-Q24</f>
+        <f t="shared" si="8"/>
         <v>105.74514505973896</v>
       </c>
       <c r="S24" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R24)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>9.456698928684306E-3</v>
       </c>
       <c r="T24" s="9">
-        <f>R24/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.73832312171768166</v>
       </c>
     </row>
@@ -4369,7 +4279,7 @@
         <v>283.43</v>
       </c>
       <c r="G25" s="1">
-        <f>E25*F25</f>
+        <f t="shared" si="0"/>
         <v>2.8342999999999998E-17</v>
       </c>
       <c r="H25" s="13">
@@ -4379,47 +4289,47 @@
         <v>0.26</v>
       </c>
       <c r="J25" s="9">
-        <f>IFERROR(H25/I25,"")</f>
+        <f t="shared" si="1"/>
         <v>0.96153846153846145</v>
       </c>
       <c r="K25" s="9">
-        <f>IFERROR(J25/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>5.0034834837174219E-2</v>
       </c>
       <c r="L25" s="12">
-        <f>F25/(1-(F25*(1+H25)-F25)/(F25*(1+H25)))</f>
+        <f t="shared" si="11"/>
         <v>354.28750000000002</v>
       </c>
       <c r="M25" s="12">
-        <f>L25*E25</f>
+        <f t="shared" si="3"/>
         <v>3.542875E-17</v>
       </c>
       <c r="N25" s="12">
-        <f>F25/(1+I25-H25)</f>
+        <f t="shared" si="4"/>
         <v>280.62376237623761</v>
       </c>
       <c r="O25" s="12">
-        <f>L25-F25</f>
+        <f t="shared" si="5"/>
         <v>70.857500000000016</v>
       </c>
       <c r="P25" s="12">
-        <f>0.5*(N25-F25)</f>
+        <f t="shared" si="6"/>
         <v>-1.4031188118811997</v>
       </c>
       <c r="Q25" s="15">
-        <f>O25+P25</f>
+        <f t="shared" si="7"/>
         <v>69.454381188118816</v>
       </c>
       <c r="R25" s="12">
-        <f>MAX($Q$2:$Q$279)-Q25</f>
+        <f t="shared" si="8"/>
         <v>44.67806389306557</v>
       </c>
       <c r="S25" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R25)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>2.2382348581474875E-2</v>
       </c>
       <c r="T25" s="9">
-        <f>R25/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.311946686414727</v>
       </c>
     </row>
@@ -4443,7 +4353,7 @@
         <v>188.12</v>
       </c>
       <c r="G26" s="1">
-        <f>E26*F26</f>
+        <f t="shared" si="0"/>
         <v>1.8812000000000001E-17</v>
       </c>
       <c r="H26" s="13">
@@ -4453,47 +4363,47 @@
         <v>0.37780000000000002</v>
       </c>
       <c r="J26" s="9">
-        <f>IFERROR(H26/I26,"")</f>
+        <f t="shared" si="1"/>
         <v>0.39703546850185278</v>
       </c>
       <c r="K26" s="9">
-        <f>IFERROR(J26/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>2.0660228254629907E-2</v>
       </c>
       <c r="L26" s="12">
-        <f>F26/(1-(F26*(1+H26)-F26)/(F26*(1+H26)))</f>
+        <f t="shared" si="11"/>
         <v>216.33799999999999</v>
       </c>
       <c r="M26" s="12">
-        <f>L26*E26</f>
+        <f t="shared" si="3"/>
         <v>2.16338E-17</v>
       </c>
       <c r="N26" s="12">
-        <f>F26/(1+I26-H26)</f>
+        <f t="shared" si="4"/>
         <v>153.21713634142367</v>
       </c>
       <c r="O26" s="12">
-        <f>L26-F26</f>
+        <f t="shared" si="5"/>
         <v>28.217999999999989</v>
       </c>
       <c r="P26" s="12">
-        <f>0.5*(N26-F26)</f>
+        <f t="shared" si="6"/>
         <v>-17.451431829288168</v>
       </c>
       <c r="Q26" s="15">
-        <f>O26+P26</f>
+        <f t="shared" si="7"/>
         <v>10.766568170711821</v>
       </c>
       <c r="R26" s="12">
-        <f>MAX($Q$2:$Q$279)-Q26</f>
+        <f t="shared" si="8"/>
         <v>103.36587691047256</v>
       </c>
       <c r="S26" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R26)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>9.674372528819369E-3</v>
       </c>
       <c r="T26" s="9">
-        <f>R26/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.72171083482377829</v>
       </c>
     </row>
@@ -4517,7 +4427,7 @@
         <v>185.82</v>
       </c>
       <c r="G27" s="1">
-        <f>E27*F27</f>
+        <f t="shared" si="0"/>
         <v>9.9971160000000001</v>
       </c>
       <c r="H27" s="13">
@@ -4528,47 +4438,47 @@
         <v>0.26790000000000003</v>
       </c>
       <c r="J27" s="9">
-        <f>IFERROR(H27/I27,"")</f>
+        <f t="shared" si="1"/>
         <v>9.2203523187016356E-2</v>
       </c>
       <c r="K27" s="9">
-        <f>IFERROR(J27/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>4.7979235762306447E-3</v>
       </c>
       <c r="L27" s="12">
-        <f>F27/(1-(F27*(1+H27)-F27)/(F27*(1+H27)))</f>
+        <f t="shared" si="11"/>
         <v>190.40999999999997</v>
       </c>
       <c r="M27" s="12">
-        <f>L27*E27</f>
+        <f t="shared" si="3"/>
         <v>10.244057999999999</v>
       </c>
       <c r="N27" s="12">
-        <f>F27/(1+I27-H27)</f>
+        <f t="shared" si="4"/>
         <v>149.46927113630838</v>
       </c>
       <c r="O27" s="12">
-        <f>L27-F27</f>
+        <f t="shared" si="5"/>
         <v>4.589999999999975</v>
       </c>
       <c r="P27" s="12">
-        <f>0.5*(N27-F27)</f>
+        <f t="shared" si="6"/>
         <v>-18.175364431845807</v>
       </c>
       <c r="Q27" s="15">
-        <f>O27+P27</f>
+        <f t="shared" si="7"/>
         <v>-13.585364431845832</v>
       </c>
       <c r="R27" s="12">
-        <f>MAX($Q$2:$Q$279)-Q27</f>
+        <f t="shared" si="8"/>
         <v>127.71780951303022</v>
       </c>
       <c r="S27" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R27)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>7.8297615956056336E-3</v>
       </c>
       <c r="T27" s="9">
-        <f>R27/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.8917384506431304</v>
       </c>
     </row>
@@ -4592,7 +4502,7 @@
         <v>668.82</v>
       </c>
       <c r="G28" s="1">
-        <f>E28*F28</f>
+        <f t="shared" si="0"/>
         <v>6.6881999999999999E-17</v>
       </c>
       <c r="H28" s="13">
@@ -4602,47 +4512,47 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="J28" s="9">
-        <f>IFERROR(H28/I28,"")</f>
+        <f t="shared" si="1"/>
         <v>0.17857142857142858</v>
       </c>
       <c r="K28" s="9">
-        <f>IFERROR(J28/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>9.2921836126180716E-3</v>
       </c>
       <c r="L28" s="12">
-        <f>F28/(1-(F28*(1+H28)-F28)/(F28*(1+H28)))</f>
+        <f t="shared" si="11"/>
         <v>702.26100000000008</v>
       </c>
       <c r="M28" s="12">
-        <f>L28*E28</f>
+        <f t="shared" si="3"/>
         <v>7.0226100000000009E-17</v>
       </c>
       <c r="N28" s="12">
-        <f>F28/(1+I28-H28)</f>
+        <f t="shared" si="4"/>
         <v>543.7560975609756</v>
       </c>
       <c r="O28" s="12">
-        <f>L28-F28</f>
+        <f t="shared" si="5"/>
         <v>33.441000000000031</v>
       </c>
       <c r="P28" s="12">
-        <f>0.5*(N28-F28)</f>
+        <f t="shared" si="6"/>
         <v>-62.531951219512223</v>
       </c>
       <c r="Q28" s="15">
-        <f>O28+P28</f>
+        <f t="shared" si="7"/>
         <v>-29.090951219512192</v>
       </c>
       <c r="R28" s="12">
-        <f>MAX($Q$2:$Q$279)-Q28</f>
+        <f t="shared" si="8"/>
         <v>143.22339630069658</v>
       </c>
       <c r="S28" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R28)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>6.9820994741704532E-3</v>
       </c>
       <c r="T28" s="9">
-        <f>R28/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -4666,7 +4576,7 @@
         <v>700.32</v>
       </c>
       <c r="G29" s="1">
-        <f>E29*F29</f>
+        <f t="shared" si="0"/>
         <v>7.0031999999999998E-17</v>
       </c>
       <c r="H29" s="13">
@@ -4676,47 +4586,47 @@
         <v>0.45340000000000003</v>
       </c>
       <c r="J29" s="9">
-        <f>IFERROR(H29/I29,"")</f>
+        <f t="shared" si="1"/>
         <v>0.22055580061755625</v>
       </c>
       <c r="K29" s="9">
-        <f>IFERROR(J29/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>1.1476891978531363E-2</v>
       </c>
       <c r="L29" s="12">
-        <f>F29/(1-(F29*(1+H29)-F29)/(F29*(1+H29)))</f>
+        <f t="shared" si="11"/>
         <v>770.35200000000009</v>
       </c>
       <c r="M29" s="12">
-        <f>L29*E29</f>
+        <f t="shared" si="3"/>
         <v>7.7035200000000004E-17</v>
       </c>
       <c r="N29" s="12">
-        <f>F29/(1+I29-H29)</f>
+        <f t="shared" si="4"/>
         <v>517.45234224915032</v>
       </c>
       <c r="O29" s="12">
-        <f>L29-F29</f>
+        <f t="shared" si="5"/>
         <v>70.032000000000039</v>
       </c>
       <c r="P29" s="12">
-        <f>0.5*(N29-F29)</f>
+        <f t="shared" si="6"/>
         <v>-91.433828875424865</v>
       </c>
       <c r="Q29" s="15">
-        <f>O29+P29</f>
+        <f t="shared" si="7"/>
         <v>-21.401828875424826</v>
       </c>
       <c r="R29" s="12">
-        <f>MAX($Q$2:$Q$279)-Q29</f>
+        <f t="shared" si="8"/>
         <v>135.53427395660921</v>
       </c>
       <c r="S29" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R29)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>7.37820752498476E-3</v>
       </c>
       <c r="T29" s="9">
-        <f>R29/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.94631378292451529</v>
       </c>
     </row>
@@ -4740,7 +4650,7 @@
         <v>147.01</v>
       </c>
       <c r="G30" s="1">
-        <f>E30*F30</f>
+        <f t="shared" si="0"/>
         <v>1.4700999999999999E-17</v>
       </c>
       <c r="H30" s="13">
@@ -4750,47 +4660,47 @@
         <v>0.52380000000000004</v>
       </c>
       <c r="J30" s="9">
-        <f>IFERROR(H30/I30,"")</f>
+        <f t="shared" si="1"/>
         <v>0.28636884306987398</v>
       </c>
       <c r="K30" s="9">
-        <f>IFERROR(J30/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>1.4901554476134362E-2</v>
       </c>
       <c r="L30" s="12">
-        <f>F30/(1-(F30*(1+H30)-F30)/(F30*(1+H30)))</f>
+        <f t="shared" si="11"/>
         <v>169.06149999999997</v>
       </c>
       <c r="M30" s="12">
-        <f>L30*E30</f>
+        <f t="shared" si="3"/>
         <v>1.6906149999999997E-17</v>
       </c>
       <c r="N30" s="12">
-        <f>F30/(1+I30-H30)</f>
+        <f t="shared" si="4"/>
         <v>107.00975396709855</v>
       </c>
       <c r="O30" s="12">
-        <f>L30-F30</f>
+        <f t="shared" si="5"/>
         <v>22.051499999999976</v>
       </c>
       <c r="P30" s="12">
-        <f>0.5*(N30-F30)</f>
+        <f t="shared" si="6"/>
         <v>-20.000123016450722</v>
       </c>
       <c r="Q30" s="15">
-        <f>O30+P30</f>
+        <f t="shared" si="7"/>
         <v>2.0513769835492539</v>
       </c>
       <c r="R30" s="12">
-        <f>MAX($Q$2:$Q$279)-Q30</f>
+        <f t="shared" si="8"/>
         <v>112.08106809763513</v>
       </c>
       <c r="S30" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R30)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.9221134039237406E-3</v>
       </c>
       <c r="T30" s="9">
-        <f>R30/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.78256116662896091</v>
       </c>
     </row>
@@ -4814,7 +4724,7 @@
         <v>169.34</v>
       </c>
       <c r="G31" s="1">
-        <f>E31*F31</f>
+        <f t="shared" si="0"/>
         <v>1.6933999999999999E-17</v>
       </c>
       <c r="H31" s="13">
@@ -4824,47 +4734,47 @@
         <v>0.4259</v>
       </c>
       <c r="J31" s="9">
-        <f>IFERROR(H31/I31,"")</f>
+        <f t="shared" si="1"/>
         <v>0.23479690068091102</v>
       </c>
       <c r="K31" s="9">
-        <f>IFERROR(J31/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>1.2217945111683776E-2</v>
       </c>
       <c r="L31" s="12">
-        <f>F31/(1-(F31*(1+H31)-F31)/(F31*(1+H31)))</f>
+        <f t="shared" si="11"/>
         <v>186.27400000000003</v>
       </c>
       <c r="M31" s="12">
-        <f>L31*E31</f>
+        <f t="shared" si="3"/>
         <v>1.8627400000000003E-17</v>
       </c>
       <c r="N31" s="12">
-        <f>F31/(1+I31-H31)</f>
+        <f t="shared" si="4"/>
         <v>127.71702239987934</v>
       </c>
       <c r="O31" s="12">
-        <f>L31-F31</f>
+        <f t="shared" si="5"/>
         <v>16.934000000000026</v>
       </c>
       <c r="P31" s="12">
-        <f>0.5*(N31-F31)</f>
+        <f t="shared" si="6"/>
         <v>-20.811488800060332</v>
       </c>
       <c r="Q31" s="15">
-        <f>O31+P31</f>
+        <f t="shared" si="7"/>
         <v>-3.8774888000603056</v>
       </c>
       <c r="R31" s="12">
-        <f>MAX($Q$2:$Q$279)-Q31</f>
+        <f t="shared" si="8"/>
         <v>118.00993388124469</v>
       </c>
       <c r="S31" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R31)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.4738628953585915E-3</v>
       </c>
       <c r="T31" s="9">
-        <f>R31/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.82395709729912847</v>
       </c>
     </row>
@@ -4888,7 +4798,7 @@
         <v>113.58</v>
       </c>
       <c r="G32" s="1">
-        <f>E32*F32</f>
+        <f t="shared" si="0"/>
         <v>1.1357999999999999E-17</v>
       </c>
       <c r="H32" s="13">
@@ -4899,47 +4809,47 @@
         <v>0.16439999999999999</v>
       </c>
       <c r="J32" s="9">
-        <f>IFERROR(H32/I32,"")</f>
+        <f t="shared" si="1"/>
         <v>0.40540789496797319</v>
       </c>
       <c r="K32" s="9">
-        <f>IFERROR(J32/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>2.1095897749065375E-2</v>
       </c>
       <c r="L32" s="12">
-        <f>F32/(1-(F32*(1+H32)-F32)/(F32*(1+H32)))</f>
+        <f t="shared" si="11"/>
         <v>121.15000000000002</v>
       </c>
       <c r="M32" s="12">
-        <f>L32*E32</f>
+        <f t="shared" si="3"/>
         <v>1.2115000000000002E-17</v>
       </c>
       <c r="N32" s="12">
-        <f>F32/(1+I32-H32)</f>
+        <f t="shared" si="4"/>
         <v>103.46609203186667</v>
       </c>
       <c r="O32" s="12">
-        <f>L32-F32</f>
+        <f t="shared" si="5"/>
         <v>7.5700000000000216</v>
       </c>
       <c r="P32" s="12">
-        <f>0.5*(N32-F32)</f>
+        <f t="shared" si="6"/>
         <v>-5.0569539840666664</v>
       </c>
       <c r="Q32" s="15">
-        <f>O32+P32</f>
+        <f t="shared" si="7"/>
         <v>2.5130460159333552</v>
       </c>
       <c r="R32" s="12">
-        <f>MAX($Q$2:$Q$279)-Q32</f>
+        <f t="shared" si="8"/>
         <v>111.61939906525103</v>
       </c>
       <c r="S32" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R32)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.9590161600441431E-3</v>
       </c>
       <c r="T32" s="9">
-        <f>R32/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.77933774752071117</v>
       </c>
     </row>
@@ -4963,7 +4873,7 @@
         <v>64.349999999999994</v>
       </c>
       <c r="G33" s="1">
-        <f>E33*F33</f>
+        <f t="shared" si="0"/>
         <v>6.4349999999999993E-18</v>
       </c>
       <c r="H33" s="13">
@@ -4973,47 +4883,47 @@
         <v>0.67300000000000004</v>
       </c>
       <c r="J33" s="9">
-        <f>IFERROR(H33/I33,"")</f>
+        <f t="shared" si="1"/>
         <v>0.22288261515601782</v>
       </c>
       <c r="K33" s="9">
-        <f>IFERROR(J33/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>1.1597970630905169E-2</v>
       </c>
       <c r="L33" s="12">
-        <f>F33/(1-(F33*(1+H33)-F33)/(F33*(1+H33)))</f>
+        <f t="shared" si="11"/>
         <v>74.002499999999984</v>
       </c>
       <c r="M33" s="12">
-        <f>L33*E33</f>
+        <f t="shared" si="3"/>
         <v>7.4002499999999988E-18</v>
       </c>
       <c r="N33" s="12">
-        <f>F33/(1+I33-H33)</f>
+        <f t="shared" si="4"/>
         <v>42.252133946158892</v>
       </c>
       <c r="O33" s="12">
-        <f>L33-F33</f>
+        <f t="shared" si="5"/>
         <v>9.6524999999999892</v>
       </c>
       <c r="P33" s="12">
-        <f>0.5*(N33-F33)</f>
+        <f t="shared" si="6"/>
         <v>-11.048933026920551</v>
       </c>
       <c r="Q33" s="15">
-        <f>O33+P33</f>
+        <f t="shared" si="7"/>
         <v>-1.3964330269205618</v>
       </c>
       <c r="R33" s="12">
-        <f>MAX($Q$2:$Q$279)-Q33</f>
+        <f t="shared" si="8"/>
         <v>115.52887810810495</v>
       </c>
       <c r="S33" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R33)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.6558444639638962E-3</v>
       </c>
       <c r="T33" s="9">
-        <f>R33/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.80663411909010196</v>
       </c>
     </row>
@@ -5037,7 +4947,7 @@
         <v>20.82</v>
       </c>
       <c r="G34" s="1">
-        <f>E34*F34</f>
+        <f t="shared" si="0"/>
         <v>2.0820000000000002E-18</v>
       </c>
       <c r="H34" s="13">
@@ -5047,47 +4957,47 @@
         <v>0.7389</v>
       </c>
       <c r="J34" s="9">
-        <f>IFERROR(H34/I34,"")</f>
+        <f t="shared" si="1"/>
         <v>6.7668155366084726E-2</v>
       </c>
       <c r="K34" s="9">
-        <f>IFERROR(J34/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>3.521195576577426E-3</v>
       </c>
       <c r="L34" s="12">
-        <f>F34/(1-(F34*(1+H34)-F34)/(F34*(1+H34)))</f>
+        <f t="shared" si="11"/>
         <v>21.861000000000001</v>
       </c>
       <c r="M34" s="12">
-        <f>L34*E34</f>
+        <f t="shared" si="3"/>
         <v>2.1860999999999999E-18</v>
       </c>
       <c r="N34" s="12">
-        <f>F34/(1+I34-H34)</f>
+        <f t="shared" si="4"/>
         <v>12.327550476641601</v>
       </c>
       <c r="O34" s="12">
-        <f>L34-F34</f>
+        <f t="shared" si="5"/>
         <v>1.0410000000000004</v>
       </c>
       <c r="P34" s="12">
-        <f>0.5*(N34-F34)</f>
+        <f t="shared" si="6"/>
         <v>-4.2462247616791995</v>
       </c>
       <c r="Q34" s="15">
-        <f>O34+P34</f>
+        <f t="shared" si="7"/>
         <v>-3.2052247616791991</v>
       </c>
       <c r="R34" s="12">
-        <f>MAX($Q$2:$Q$279)-Q34</f>
+        <f t="shared" si="8"/>
         <v>117.33766984286359</v>
       </c>
       <c r="S34" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R34)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.5224122938454567E-3</v>
       </c>
       <c r="T34" s="9">
-        <f>R34/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.81926328291024408</v>
       </c>
     </row>
@@ -5111,7 +5021,7 @@
         <v>13.04</v>
       </c>
       <c r="G35" s="1">
-        <f>E35*F35</f>
+        <f t="shared" si="0"/>
         <v>1.304E-18</v>
       </c>
       <c r="H35" s="13">
@@ -5122,47 +5032,47 @@
         <v>0.30159999999999998</v>
       </c>
       <c r="J35" s="9">
-        <f>IFERROR(H35/I35,"")</f>
+        <f t="shared" si="1"/>
         <v>0.17290198694895167</v>
       </c>
       <c r="K35" s="9">
-        <f>IFERROR(J35/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>8.9971672544104531E-3</v>
       </c>
       <c r="L35" s="12">
-        <f>F35/(1-(F35*(1+H35)-F35)/(F35*(1+H35)))</f>
+        <f t="shared" si="11"/>
         <v>13.72</v>
       </c>
       <c r="M35" s="12">
-        <f>L35*E35</f>
+        <f t="shared" si="3"/>
         <v>1.3720000000000001E-18</v>
       </c>
       <c r="N35" s="12">
-        <f>F35/(1+I35-H35)</f>
+        <f t="shared" si="4"/>
         <v>10.436569040286594</v>
       </c>
       <c r="O35" s="12">
-        <f>L35-F35</f>
+        <f t="shared" si="5"/>
         <v>0.68000000000000149</v>
       </c>
       <c r="P35" s="12">
-        <f>0.5*(N35-F35)</f>
+        <f t="shared" si="6"/>
         <v>-1.3017154798567026</v>
       </c>
       <c r="Q35" s="15">
-        <f>O35+P35</f>
+        <f t="shared" si="7"/>
         <v>-0.62171547985670106</v>
       </c>
       <c r="R35" s="12">
-        <f>MAX($Q$2:$Q$279)-Q35</f>
+        <f t="shared" si="8"/>
         <v>114.75416056104109</v>
       </c>
       <c r="S35" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R35)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.7142809908671744E-3</v>
       </c>
       <c r="T35" s="9">
-        <f>R35/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.80122496411211674</v>
       </c>
     </row>
@@ -5186,7 +5096,7 @@
         <v>11.05</v>
       </c>
       <c r="G36" s="1">
-        <f>E36*F36</f>
+        <f t="shared" si="0"/>
         <v>1.1050000000000001E-18</v>
       </c>
       <c r="H36" s="13">
@@ -5196,47 +5106,47 @@
         <v>0.72170000000000001</v>
       </c>
       <c r="J36" s="9">
-        <f>IFERROR(H36/I36,"")</f>
+        <f t="shared" si="1"/>
         <v>6.9280864625190522E-2</v>
       </c>
       <c r="K36" s="9">
-        <f>IFERROR(J36/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>3.6051148836539555E-3</v>
       </c>
       <c r="L36" s="12">
-        <f>F36/(1-(F36*(1+H36)-F36)/(F36*(1+H36)))</f>
+        <f t="shared" si="11"/>
         <v>11.602500000000001</v>
       </c>
       <c r="M36" s="12">
-        <f>L36*E36</f>
+        <f t="shared" si="3"/>
         <v>1.16025E-18</v>
       </c>
       <c r="N36" s="12">
-        <f>F36/(1+I36-H36)</f>
+        <f t="shared" si="4"/>
         <v>6.6100376861877139</v>
       </c>
       <c r="O36" s="12">
-        <f>L36-F36</f>
+        <f t="shared" si="5"/>
         <v>0.55250000000000021</v>
       </c>
       <c r="P36" s="12">
-        <f>0.5*(N36-F36)</f>
+        <f t="shared" si="6"/>
         <v>-2.2199811569061434</v>
       </c>
       <c r="Q36" s="15">
-        <f>O36+P36</f>
+        <f t="shared" si="7"/>
         <v>-1.6674811569061432</v>
       </c>
       <c r="R36" s="12">
-        <f>MAX($Q$2:$Q$279)-Q36</f>
+        <f t="shared" si="8"/>
         <v>115.79992623809053</v>
       </c>
       <c r="S36" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R36)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.6355840844315312E-3</v>
       </c>
       <c r="T36" s="9">
-        <f>R36/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.80852660409594923</v>
       </c>
     </row>
@@ -5261,7 +5171,7 @@
         <v>2742.9</v>
       </c>
       <c r="G37" s="1">
-        <f>E37*F37</f>
+        <f t="shared" si="0"/>
         <v>2.7429000000000002E-16</v>
       </c>
       <c r="H37" s="13">
@@ -5271,47 +5181,47 @@
         <v>0.5</v>
       </c>
       <c r="J37" s="9">
-        <f>IFERROR(H37/I37,"")</f>
+        <f t="shared" si="1"/>
         <v>0.2</v>
       </c>
       <c r="K37" s="9">
-        <f>IFERROR(J37/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>1.040724564613224E-2</v>
       </c>
       <c r="L37" s="12">
-        <f>F37/(1-(F37*(1+H37)-F37)/(F37*(1+H37)))</f>
+        <f t="shared" si="11"/>
         <v>3017.1900000000005</v>
       </c>
       <c r="M37" s="12">
-        <f>L37*E37</f>
+        <f t="shared" si="3"/>
         <v>3.0171900000000003E-16</v>
       </c>
       <c r="N37" s="12">
-        <f>F37/(1+I37-H37)</f>
+        <f t="shared" si="4"/>
         <v>1959.214285714286</v>
       </c>
       <c r="O37" s="12">
-        <f>L37-F37</f>
+        <f t="shared" si="5"/>
         <v>274.29000000000042</v>
       </c>
       <c r="P37" s="12">
-        <f>0.5*(N37-F37)</f>
+        <f t="shared" si="6"/>
         <v>-391.84285714285704</v>
       </c>
       <c r="Q37" s="15">
-        <f>O37+P37</f>
+        <f t="shared" si="7"/>
         <v>-117.55285714285662</v>
       </c>
       <c r="R37" s="12">
-        <f>MAX($Q$2:$Q$279)-Q37</f>
+        <f t="shared" si="8"/>
         <v>231.68530222404101</v>
       </c>
       <c r="S37" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R37)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>4.316199562080957E-3</v>
       </c>
       <c r="T37" s="9">
-        <f>R37/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>1.6176498268314992</v>
       </c>
     </row>
@@ -5335,7 +5245,7 @@
         <v>86.6</v>
       </c>
       <c r="G38" s="1">
-        <f>E38*F38</f>
+        <f t="shared" si="0"/>
         <v>8.6599999999999986E-18</v>
       </c>
       <c r="H38" s="13">
@@ -5345,47 +5255,47 @@
         <v>0.17249999999999999</v>
       </c>
       <c r="J38" s="9">
-        <f>IFERROR(H38/I38,"")</f>
+        <f t="shared" si="1"/>
         <v>0.40579710144927544</v>
       </c>
       <c r="K38" s="9">
-        <f>IFERROR(J38/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>2.1116150586355274E-2</v>
       </c>
       <c r="L38" s="12">
-        <f>F38/(1-(F38*(1+H38)-F38)/(F38*(1+H38)))</f>
+        <f t="shared" si="11"/>
         <v>92.662000000000006</v>
       </c>
       <c r="M38" s="12">
-        <f>L38*E38</f>
+        <f t="shared" si="3"/>
         <v>9.2662000000000008E-18</v>
       </c>
       <c r="N38" s="12">
-        <f>F38/(1+I38-H38)</f>
+        <f t="shared" si="4"/>
         <v>78.548752834467123</v>
       </c>
       <c r="O38" s="12">
-        <f>L38-F38</f>
+        <f t="shared" si="5"/>
         <v>6.0620000000000118</v>
       </c>
       <c r="P38" s="12">
-        <f>0.5*(N38-F38)</f>
+        <f t="shared" si="6"/>
         <v>-4.0256235827664355</v>
       </c>
       <c r="Q38" s="15">
-        <f>O38+P38</f>
+        <f t="shared" si="7"/>
         <v>2.0363764172335763</v>
       </c>
       <c r="R38" s="12">
-        <f>MAX($Q$2:$Q$279)-Q38</f>
+        <f t="shared" si="8"/>
         <v>112.0960686639508</v>
       </c>
       <c r="S38" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R38)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.9209194570227766E-3</v>
       </c>
       <c r="T38" s="9">
-        <f>R38/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.78266590207514586</v>
       </c>
     </row>
@@ -5409,7 +5319,7 @@
         <v>56</v>
       </c>
       <c r="G39" s="1">
-        <f>E39*F39</f>
+        <f t="shared" si="0"/>
         <v>5.5999999999999995E-18</v>
       </c>
       <c r="H39" s="13">
@@ -5419,47 +5329,47 @@
         <v>0.19</v>
       </c>
       <c r="J39" s="9">
-        <f>IFERROR(H39/I39,"")</f>
+        <f t="shared" si="1"/>
         <v>0.36842105263157898</v>
       </c>
       <c r="K39" s="9">
-        <f>IFERROR(J39/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>1.9171241979717285E-2</v>
       </c>
       <c r="L39" s="12">
-        <f>F39/(1-(F39*(1+H39)-F39)/(F39*(1+H39)))</f>
+        <f t="shared" si="11"/>
         <v>59.92</v>
       </c>
       <c r="M39" s="12">
-        <f>L39*E39</f>
+        <f t="shared" si="3"/>
         <v>5.9920000000000002E-18</v>
       </c>
       <c r="N39" s="12">
-        <f>F39/(1+I39-H39)</f>
+        <f t="shared" si="4"/>
         <v>50.000000000000007</v>
       </c>
       <c r="O39" s="12">
-        <f>L39-F39</f>
+        <f t="shared" si="5"/>
         <v>3.9200000000000017</v>
       </c>
       <c r="P39" s="12">
-        <f>0.5*(N39-F39)</f>
+        <f t="shared" si="6"/>
         <v>-2.9999999999999964</v>
       </c>
       <c r="Q39" s="15">
-        <f>O39+P39</f>
+        <f t="shared" si="7"/>
         <v>0.92000000000000526</v>
       </c>
       <c r="R39" s="12">
-        <f>MAX($Q$2:$Q$279)-Q39</f>
+        <f t="shared" si="8"/>
         <v>113.21244508118438</v>
       </c>
       <c r="S39" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R39)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.832951176727102E-3</v>
       </c>
       <c r="T39" s="9">
-        <f>R39/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.79046055327088882</v>
       </c>
     </row>
@@ -5483,7 +5393,7 @@
         <v>20.399999999999999</v>
       </c>
       <c r="G40" s="1">
-        <f>E40*F40</f>
+        <f t="shared" si="0"/>
         <v>2.0399999999999999E-18</v>
       </c>
       <c r="H40" s="13">
@@ -5493,46 +5403,46 @@
         <v>0.15</v>
       </c>
       <c r="J40" s="9">
-        <f>IFERROR(H40/I40,"")</f>
+        <f t="shared" si="1"/>
         <v>0.66666666666666674</v>
       </c>
       <c r="K40" s="9">
-        <f>IFERROR(J40/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>3.4690818820440804E-2</v>
       </c>
       <c r="L40" s="12">
         <v>21.2</v>
       </c>
       <c r="M40" s="12">
-        <f>L40*E40</f>
+        <f t="shared" si="3"/>
         <v>2.1199999999999999E-18</v>
       </c>
       <c r="N40" s="12">
-        <f>F40/(1+I40-H40)</f>
+        <f t="shared" si="4"/>
         <v>19.428571428571431</v>
       </c>
       <c r="O40" s="12">
-        <f>L40-F40</f>
+        <f t="shared" si="5"/>
         <v>0.80000000000000071</v>
       </c>
       <c r="P40" s="12">
-        <f>0.5*(N40-F40)</f>
+        <f t="shared" si="6"/>
         <v>-0.48571428571428399</v>
       </c>
       <c r="Q40" s="15">
-        <f>O40+P40</f>
+        <f t="shared" si="7"/>
         <v>0.31428571428571672</v>
       </c>
       <c r="R40" s="12">
-        <f>MAX($Q$2:$Q$279)-Q40</f>
+        <f t="shared" si="8"/>
         <v>113.81815936689867</v>
       </c>
       <c r="S40" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R40)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.7859442250902055E-3</v>
       </c>
       <c r="T40" s="9">
-        <f>R40/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.79468971066667204</v>
       </c>
     </row>
@@ -5556,7 +5466,7 @@
         <v>47.42</v>
       </c>
       <c r="G41" s="1">
-        <f>E41*F41</f>
+        <f t="shared" si="0"/>
         <v>4.7419999999999999E-18</v>
       </c>
       <c r="H41" s="13">
@@ -5566,47 +5476,47 @@
         <v>0.4</v>
       </c>
       <c r="J41" s="9">
-        <f>IFERROR(H41/I41,"")</f>
+        <f t="shared" si="1"/>
         <v>0.17500000000000002</v>
       </c>
       <c r="K41" s="9">
-        <f>IFERROR(J41/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>9.1063399403657104E-3</v>
       </c>
       <c r="L41" s="12">
-        <f>F41/(1-(F41*(1+H41)-F41)/(F41*(1+H41)))</f>
+        <f t="shared" ref="L41:L46" si="12">F41/(1-(F41*(1+H41)-F41)/(F41*(1+H41)))</f>
         <v>50.739400000000003</v>
       </c>
       <c r="M41" s="12">
-        <f>L41*E41</f>
+        <f t="shared" si="3"/>
         <v>5.0739400000000001E-18</v>
       </c>
       <c r="N41" s="12">
-        <f>F41/(1+I41-H41)</f>
+        <f t="shared" si="4"/>
         <v>35.654135338345867</v>
       </c>
       <c r="O41" s="12">
-        <f>L41-F41</f>
+        <f t="shared" si="5"/>
         <v>3.3194000000000017</v>
       </c>
       <c r="P41" s="12">
-        <f>0.5*(N41-F41)</f>
+        <f t="shared" si="6"/>
         <v>-5.8829323308270673</v>
       </c>
       <c r="Q41" s="15">
-        <f>O41+P41</f>
+        <f t="shared" si="7"/>
         <v>-2.5635323308270657</v>
       </c>
       <c r="R41" s="12">
-        <f>MAX($Q$2:$Q$279)-Q41</f>
+        <f t="shared" si="8"/>
         <v>116.69597741201144</v>
       </c>
       <c r="S41" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R41)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.5692756697976005E-3</v>
       </c>
       <c r="T41" s="9">
-        <f>R41/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.81478292252621221</v>
       </c>
     </row>
@@ -5630,7 +5540,7 @@
         <v>41.8</v>
       </c>
       <c r="G42" s="1">
-        <f>E42*F42</f>
+        <f t="shared" si="0"/>
         <v>4.1799999999999993E-18</v>
       </c>
       <c r="H42" s="13">
@@ -5640,47 +5550,47 @@
         <v>0.4</v>
       </c>
       <c r="J42" s="9">
-        <f>IFERROR(H42/I42,"")</f>
+        <f t="shared" si="1"/>
         <v>0.17500000000000002</v>
       </c>
       <c r="K42" s="9">
-        <f>IFERROR(J42/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>9.1063399403657104E-3</v>
       </c>
       <c r="L42" s="12">
-        <f>F42/(1-(F42*(1+H42)-F42)/(F42*(1+H42)))</f>
+        <f t="shared" si="12"/>
         <v>44.725999999999999</v>
       </c>
       <c r="M42" s="12">
-        <f>L42*E42</f>
+        <f t="shared" si="3"/>
         <v>4.4725999999999996E-18</v>
       </c>
       <c r="N42" s="12">
-        <f>F42/(1+I42-H42)</f>
+        <f t="shared" si="4"/>
         <v>31.428571428571431</v>
       </c>
       <c r="O42" s="12">
-        <f>L42-F42</f>
+        <f t="shared" si="5"/>
         <v>2.9260000000000019</v>
       </c>
       <c r="P42" s="12">
-        <f>0.5*(N42-F42)</f>
+        <f t="shared" si="6"/>
         <v>-5.1857142857142833</v>
       </c>
       <c r="Q42" s="15">
-        <f>O42+P42</f>
+        <f t="shared" si="7"/>
         <v>-2.2597142857142813</v>
       </c>
       <c r="R42" s="12">
-        <f>MAX($Q$2:$Q$279)-Q42</f>
+        <f t="shared" si="8"/>
         <v>116.39215936689867</v>
       </c>
       <c r="S42" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R42)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.5916440200042785E-3</v>
       </c>
       <c r="T42" s="9">
-        <f>R42/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.81266163471318675</v>
       </c>
     </row>
@@ -5704,7 +5614,7 @@
         <v>153.7552</v>
       </c>
       <c r="G43" s="1">
-        <f>E43*F43</f>
+        <f t="shared" si="0"/>
         <v>1.5375519999999999E-17</v>
       </c>
       <c r="H43" s="13">
@@ -5714,47 +5624,47 @@
         <v>0.19</v>
       </c>
       <c r="J43" s="9">
-        <f>IFERROR(H43/I43,"")</f>
+        <f t="shared" si="1"/>
         <v>0.36842105263157898</v>
       </c>
       <c r="K43" s="9">
-        <f>IFERROR(J43/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>1.9171241979717285E-2</v>
       </c>
       <c r="L43" s="12">
-        <f>F43/(1-(F43*(1+H43)-F43)/(F43*(1+H43)))</f>
+        <f t="shared" si="12"/>
         <v>164.51806400000001</v>
       </c>
       <c r="M43" s="12">
-        <f>L43*E43</f>
+        <f t="shared" si="3"/>
         <v>1.6451806399999999E-17</v>
       </c>
       <c r="N43" s="12">
-        <f>F43/(1+I43-H43)</f>
+        <f t="shared" si="4"/>
         <v>137.28142857142859</v>
       </c>
       <c r="O43" s="12">
-        <f>L43-F43</f>
+        <f t="shared" si="5"/>
         <v>10.762864000000008</v>
       </c>
       <c r="P43" s="12">
-        <f>0.5*(N43-F43)</f>
+        <f t="shared" si="6"/>
         <v>-8.2368857142857053</v>
       </c>
       <c r="Q43" s="15">
-        <f>O43+P43</f>
+        <f t="shared" si="7"/>
         <v>2.5259782857143023</v>
       </c>
       <c r="R43" s="12">
-        <f>MAX($Q$2:$Q$279)-Q43</f>
+        <f t="shared" si="8"/>
         <v>111.60646679547008</v>
       </c>
       <c r="S43" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R43)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.9600542756415637E-3</v>
       </c>
       <c r="T43" s="9">
-        <f>R43/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.77924745312667376</v>
       </c>
     </row>
@@ -5778,7 +5688,7 @@
         <v>133.53</v>
       </c>
       <c r="G44" s="1">
-        <f>E44*F44</f>
+        <f t="shared" si="0"/>
         <v>1.3353E-17</v>
       </c>
       <c r="H44" s="13">
@@ -5788,47 +5698,47 @@
         <v>0.2</v>
       </c>
       <c r="J44" s="9">
-        <f>IFERROR(H44/I44,"")</f>
+        <f t="shared" si="1"/>
         <v>0.35000000000000003</v>
       </c>
       <c r="K44" s="9">
-        <f>IFERROR(J44/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>1.8212679880731421E-2</v>
       </c>
       <c r="L44" s="12">
-        <f>F44/(1-(F44*(1+H44)-F44)/(F44*(1+H44)))</f>
+        <f t="shared" si="12"/>
         <v>142.87710000000001</v>
       </c>
       <c r="M44" s="12">
-        <f>L44*E44</f>
+        <f t="shared" si="3"/>
         <v>1.428771E-17</v>
       </c>
       <c r="N44" s="12">
-        <f>F44/(1+I44-H44)</f>
+        <f t="shared" si="4"/>
         <v>118.16814159292036</v>
       </c>
       <c r="O44" s="12">
-        <f>L44-F44</f>
+        <f t="shared" si="5"/>
         <v>9.3471000000000117</v>
       </c>
       <c r="P44" s="12">
-        <f>0.5*(N44-F44)</f>
+        <f t="shared" si="6"/>
         <v>-7.6809292035398187</v>
       </c>
       <c r="Q44" s="15">
-        <f>O44+P44</f>
+        <f t="shared" si="7"/>
         <v>1.6661707964601931</v>
       </c>
       <c r="R44" s="12">
-        <f>MAX($Q$2:$Q$279)-Q44</f>
+        <f t="shared" si="8"/>
         <v>112.46627428472419</v>
       </c>
       <c r="S44" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R44)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.8915544358512261E-3</v>
       </c>
       <c r="T44" s="9">
-        <f>R44/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.78525071454528272</v>
       </c>
     </row>
@@ -5852,7 +5762,7 @@
         <v>26.63</v>
       </c>
       <c r="G45" s="1">
-        <f>E45*F45</f>
+        <f t="shared" si="0"/>
         <v>2.663E-18</v>
       </c>
       <c r="H45" s="13">
@@ -5862,47 +5772,47 @@
         <v>0.2</v>
       </c>
       <c r="J45" s="9">
-        <f>IFERROR(H45/I45,"")</f>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
       <c r="K45" s="9">
-        <f>IFERROR(J45/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>2.6018114115330598E-2</v>
       </c>
       <c r="L45" s="12">
-        <f>F45/(1-(F45*(1+H45)-F45)/(F45*(1+H45)))</f>
+        <f t="shared" si="12"/>
         <v>29.293000000000003</v>
       </c>
       <c r="M45" s="12">
-        <f>L45*E45</f>
+        <f t="shared" si="3"/>
         <v>2.9293000000000003E-18</v>
       </c>
       <c r="N45" s="12">
-        <f>F45/(1+I45-H45)</f>
+        <f t="shared" si="4"/>
         <v>24.209090909090911</v>
       </c>
       <c r="O45" s="12">
-        <f>L45-F45</f>
+        <f t="shared" si="5"/>
         <v>2.6630000000000038</v>
       </c>
       <c r="P45" s="12">
-        <f>0.5*(N45-F45)</f>
+        <f t="shared" si="6"/>
         <v>-1.2104545454545441</v>
       </c>
       <c r="Q45" s="15">
-        <f>O45+P45</f>
+        <f t="shared" si="7"/>
         <v>1.4525454545454597</v>
       </c>
       <c r="R45" s="12">
-        <f>MAX($Q$2:$Q$279)-Q45</f>
+        <f t="shared" si="8"/>
         <v>112.67989962663893</v>
       </c>
       <c r="S45" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R45)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>8.8746972912956672E-3</v>
       </c>
       <c r="T45" s="9">
-        <f>R45/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.78674226793273505</v>
       </c>
     </row>
@@ -5926,7 +5836,7 @@
         <v>323.75</v>
       </c>
       <c r="G46" s="1">
-        <f>E46*F46</f>
+        <f t="shared" si="0"/>
         <v>3.2375000000000002E-17</v>
       </c>
       <c r="H46" s="13">
@@ -5936,47 +5846,47 @@
         <v>0.2</v>
       </c>
       <c r="J46" s="9">
-        <f>IFERROR(H46/I46,"")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="K46" s="9">
-        <f>IFERROR(J46/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
+        <f t="shared" si="2"/>
         <v>5.2036228230661195E-2</v>
       </c>
       <c r="L46" s="12">
-        <f>F46/(1-(F46*(1+H46)-F46)/(F46*(1+H46)))</f>
+        <f t="shared" si="12"/>
         <v>388.5</v>
       </c>
       <c r="M46" s="12">
-        <f>L46*E46</f>
+        <f t="shared" si="3"/>
         <v>3.8849999999999999E-17</v>
       </c>
       <c r="N46" s="12">
-        <f>F46/(1+I46-H46)</f>
+        <f t="shared" si="4"/>
         <v>323.75</v>
       </c>
       <c r="O46" s="12">
-        <f>L46-F46</f>
+        <f t="shared" si="5"/>
         <v>64.75</v>
       </c>
       <c r="P46" s="12">
-        <f>0.5*(N46-F46)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q46" s="15">
-        <f>O46+P46</f>
+        <f t="shared" si="7"/>
         <v>64.75</v>
       </c>
       <c r="R46" s="12">
-        <f>MAX($Q$2:$Q$279)-Q46</f>
+        <f t="shared" si="8"/>
         <v>49.382445081184386</v>
       </c>
       <c r="S46" s="9">
-        <f>IFERROR((SUBTOTAL(109,$R$2:$R$1048576)/R46)/SUBTOTAL(109,$R$2:$R$1048576),0)</f>
+        <f t="shared" si="9"/>
         <v>2.0250111114506524E-2</v>
       </c>
       <c r="T46" s="9">
-        <f>R46/MAX($R$2:$R$28)</f>
+        <f t="shared" si="10"/>
         <v>0.34479314383458876</v>
       </c>
     </row>
@@ -6041,7 +5951,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD6C5064-D029-4982-9C03-6BDB75C18181}">
-  <dimension ref="B1:Z42"/>
+  <dimension ref="B1:AJ42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.140625" bestFit="1" customWidth="1"/>
@@ -6053,9 +5963,12 @@
     <col min="9" max="9" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="7.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:36" x14ac:dyDescent="0.25">
       <c r="W1" t="s">
         <v>124</v>
       </c>
@@ -6069,7 +5982,7 @@
         <v>0.2356</v>
       </c>
     </row>
-    <row r="2" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>124</v>
       </c>
@@ -6130,8 +6043,32 @@
       <c r="Z2" s="29">
         <v>0.22670000000000001</v>
       </c>
-    </row>
-    <row r="3" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="AB2" t="s">
+        <v>124</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AE2" s="29">
+        <v>8.2299999999999998E-2</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>124</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AJ2" s="29">
+        <v>5.79E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>124</v>
       </c>
@@ -6180,13 +6117,37 @@
       <c r="U3" s="29">
         <v>0.3967</v>
       </c>
-    </row>
-    <row r="4" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="AB3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>125</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>126</v>
+      </c>
+      <c r="AE3" s="29">
+        <v>0.11260000000000001</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>126</v>
+      </c>
+      <c r="AJ3" s="29">
+        <v>0.2074</v>
+      </c>
+    </row>
+    <row r="4" spans="2:36" x14ac:dyDescent="0.25">
       <c r="W4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B5" s="39" t="s">
         <v>82</v>
       </c>
@@ -6247,8 +6208,14 @@
       <c r="Z5" s="39" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="6" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="AB5" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="6" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B6" s="33" t="s">
         <v>94</v>
       </c>
@@ -6314,8 +6281,32 @@
         <f>Y6-X6</f>
         <v>-0.28310000000000002</v>
       </c>
-    </row>
-    <row r="7" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="AB6" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="AC6" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD6" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE6" s="39" t="s">
+        <v>127</v>
+      </c>
+      <c r="AG6" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="AH6" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI6" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="AJ6" s="39" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B7" s="33" t="s">
         <v>50</v>
       </c>
@@ -6381,8 +6372,34 @@
         <f t="shared" ref="Z7:Z14" si="4">Y7-X7</f>
         <v>-0.13739999999999999</v>
       </c>
-    </row>
-    <row r="8" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="AB7" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC7" s="34">
+        <v>0.29170000000000001</v>
+      </c>
+      <c r="AD7" s="34">
+        <v>0.16020000000000001</v>
+      </c>
+      <c r="AE7" s="34">
+        <f>AD7-AC7</f>
+        <v>-0.13150000000000001</v>
+      </c>
+      <c r="AG7" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="AH7" s="34">
+        <v>1</v>
+      </c>
+      <c r="AI7" s="34">
+        <v>5.5399999999999998E-2</v>
+      </c>
+      <c r="AJ7" s="34">
+        <f>AI7-AH7</f>
+        <v>-0.9446</v>
+      </c>
+    </row>
+    <row r="8" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B8" s="35" t="s">
         <v>27</v>
       </c>
@@ -6448,8 +6465,34 @@
         <f t="shared" si="4"/>
         <v>4.2999999999999983E-2</v>
       </c>
-    </row>
-    <row r="9" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="AB8" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="AC8" s="34">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="AD8" s="34">
+        <v>1.41E-2</v>
+      </c>
+      <c r="AE8" s="34">
+        <f t="shared" ref="AE8:AE16" si="5">AD8-AC8</f>
+        <v>-5.1900000000000002E-2</v>
+      </c>
+      <c r="AG8" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="AH8" s="34">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="34">
+        <v>0.12520000000000001</v>
+      </c>
+      <c r="AJ8" s="34">
+        <f t="shared" ref="AJ8:AJ10" si="6">AI8-AH8</f>
+        <v>0.12520000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B9" s="37" t="s">
         <v>103</v>
       </c>
@@ -6515,8 +6558,34 @@
         <f t="shared" si="4"/>
         <v>7.6200000000000004E-2</v>
       </c>
-    </row>
-    <row r="10" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="AB9" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC9" s="34">
+        <v>0.23069999999999999</v>
+      </c>
+      <c r="AD9" s="34">
+        <v>0.1757</v>
+      </c>
+      <c r="AE9" s="34">
+        <f t="shared" si="5"/>
+        <v>-5.4999999999999993E-2</v>
+      </c>
+      <c r="AG9" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="AH9" s="34">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="34">
+        <v>0.56210000000000004</v>
+      </c>
+      <c r="AJ9" s="34">
+        <f t="shared" si="6"/>
+        <v>0.56210000000000004</v>
+      </c>
+    </row>
+    <row r="10" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B10" s="35" t="s">
         <v>46</v>
       </c>
@@ -6582,8 +6651,34 @@
         <f t="shared" si="4"/>
         <v>0.27429999999999999</v>
       </c>
-    </row>
-    <row r="11" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="AB10" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC10" s="34">
+        <v>0.26240000000000002</v>
+      </c>
+      <c r="AD10" s="34">
+        <v>0.21079999999999999</v>
+      </c>
+      <c r="AE10" s="34">
+        <f t="shared" si="5"/>
+        <v>-5.1600000000000035E-2</v>
+      </c>
+      <c r="AG10" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="AH10" s="34">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="34">
+        <v>0.25729999999999997</v>
+      </c>
+      <c r="AJ10" s="34">
+        <f t="shared" si="6"/>
+        <v>0.25729999999999997</v>
+      </c>
+    </row>
+    <row r="11" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B11" s="33" t="s">
         <v>32</v>
       </c>
@@ -6649,8 +6744,21 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="AB11" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC11" s="34">
+        <v>0.14910000000000001</v>
+      </c>
+      <c r="AD11" s="34">
+        <v>0.1583</v>
+      </c>
+      <c r="AE11" s="34">
+        <f t="shared" si="5"/>
+        <v>9.199999999999986E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B12" s="33" t="s">
         <v>48</v>
       </c>
@@ -6716,8 +6824,21 @@
         <f t="shared" si="4"/>
         <v>2.7E-2</v>
       </c>
-    </row>
-    <row r="13" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="AB12" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC12" s="34">
+        <v>1E-4</v>
+      </c>
+      <c r="AD12" s="34">
+        <v>9.4299999999999995E-2</v>
+      </c>
+      <c r="AE12" s="34">
+        <f t="shared" si="5"/>
+        <v>9.4199999999999992E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B13" s="33" t="s">
         <v>53</v>
       </c>
@@ -6783,8 +6904,21 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="AB13" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC13" s="34">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="34">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="34">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B14" s="33" t="s">
         <v>44</v>
       </c>
@@ -6850,8 +6984,21 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="AB14" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC14" s="34">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="34">
+        <v>0.1656</v>
+      </c>
+      <c r="AE14" s="34">
+        <f t="shared" si="5"/>
+        <v>0.1656</v>
+      </c>
+    </row>
+    <row r="15" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B15" s="37" t="s">
         <v>91</v>
       </c>
@@ -6904,8 +7051,21 @@
         <f t="shared" si="3"/>
         <v>-1.5100000000000001E-2</v>
       </c>
-    </row>
-    <row r="16" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="AB15" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC15" s="34">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="34">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="34">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B16" s="37" t="s">
         <v>92</v>
       </c>
@@ -6957,6 +7117,19 @@
       <c r="U16" s="34">
         <f t="shared" si="3"/>
         <v>-4.6899999999999997E-2</v>
+      </c>
+      <c r="AB16" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC16" s="34">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="34">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="AE16" s="34">
+        <f t="shared" si="5"/>
+        <v>2.1000000000000001E-2</v>
       </c>
     </row>
     <row r="17" spans="13:21" x14ac:dyDescent="0.25">

--- a/Open Positions.xlsx
+++ b/Open Positions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\StockSillines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8BD20C8-3A0A-4B39-970F-3237D62DECF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88810A78-6E79-4FCB-8BA9-5F96CDB72216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Positions" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="30">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -74,305 +74,25 @@
         </ext>
       </extLst>
     </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="2"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="6"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="7"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="9"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="10"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="11"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="12"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="13"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="14"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="15"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="16"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="17"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="18"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="19"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="20"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="21"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="22"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="23"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="24"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="25"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="26"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="27"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="28"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="29"/>
-        </ext>
-      </extLst>
-    </bk>
   </futureMetadata>
   <cellMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="30">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
     </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
-    </bk>
-    <bk>
-      <rc t="2" v="5"/>
-    </bk>
-    <bk>
-      <rc t="2" v="6"/>
-    </bk>
-    <bk>
-      <rc t="2" v="7"/>
-    </bk>
-    <bk>
-      <rc t="2" v="8"/>
-    </bk>
-    <bk>
-      <rc t="2" v="9"/>
-    </bk>
-    <bk>
-      <rc t="2" v="10"/>
-    </bk>
-    <bk>
-      <rc t="2" v="11"/>
-    </bk>
-    <bk>
-      <rc t="2" v="12"/>
-    </bk>
-    <bk>
-      <rc t="2" v="13"/>
-    </bk>
-    <bk>
-      <rc t="2" v="14"/>
-    </bk>
-    <bk>
-      <rc t="2" v="15"/>
-    </bk>
-    <bk>
-      <rc t="2" v="16"/>
-    </bk>
-    <bk>
-      <rc t="2" v="17"/>
-    </bk>
-    <bk>
-      <rc t="2" v="18"/>
-    </bk>
-    <bk>
-      <rc t="2" v="19"/>
-    </bk>
-    <bk>
-      <rc t="2" v="20"/>
-    </bk>
-    <bk>
-      <rc t="2" v="21"/>
-    </bk>
-    <bk>
-      <rc t="2" v="22"/>
-    </bk>
-    <bk>
-      <rc t="2" v="23"/>
-    </bk>
-    <bk>
-      <rc t="2" v="24"/>
-    </bk>
-    <bk>
-      <rc t="2" v="25"/>
-    </bk>
-    <bk>
-      <rc t="2" v="26"/>
-    </bk>
-    <bk>
-      <rc t="2" v="27"/>
-    </bk>
-    <bk>
-      <rc t="2" v="28"/>
-    </bk>
-    <bk>
-      <rc t="2" v="29"/>
-    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="162">
   <si>
     <t>Name</t>
   </si>
@@ -1034,7 +754,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -1136,21 +856,214 @@
     <xf numFmtId="10" fontId="2" fillId="8" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="72">
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
     <dxf>
       <alignment wrapText="1"/>
     </dxf>
@@ -2612,7 +2525,7 @@
         <item sd="0" x="4"/>
         <item sd="0" x="7"/>
         <item sd="0" x="9"/>
-        <item sd="0" x="0"/>
+        <item x="0"/>
         <item sd="0" x="5"/>
         <item sd="0" x="6"/>
         <item sd="0" x="8"/>
@@ -2762,8 +2675,8 @@
   </pivotFields>
   <rowFields count="3">
     <field x="29"/>
+    <field x="0"/>
     <field x="2"/>
-    <field x="0"/>
   </rowFields>
   <rowItems count="11">
     <i>
@@ -2776,25 +2689,25 @@
       <x v="5"/>
     </i>
     <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="2">
       <x v="14"/>
     </i>
-    <i r="1">
+    <i r="2">
       <x v="41"/>
     </i>
-    <i r="1">
-      <x v="39"/>
+    <i r="2">
+      <x v="28"/>
     </i>
     <i r="1">
-      <x v="16"/>
+      <x v="7"/>
     </i>
     <i r="1">
-      <x v="27"/>
+      <x v="9"/>
     </i>
     <i r="1">
-      <x v="11"/>
-    </i>
-    <i r="1">
-      <x v="28"/>
+      <x/>
     </i>
     <i t="grand">
       <x/>
@@ -2842,7 +2755,7 @@
     <dataField name="Actual P&amp;L " fld="26" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="8">
-    <format dxfId="7">
+    <format dxfId="71">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -2852,7 +2765,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="6">
+    <format dxfId="70">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -2862,7 +2775,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="5">
+    <format dxfId="69">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -2871,7 +2784,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="4">
+    <format dxfId="68">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -2880,7 +2793,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="3">
+    <format dxfId="67">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -2889,7 +2802,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="2">
+    <format dxfId="66">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="5">
@@ -2902,7 +2815,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="1">
+    <format dxfId="65">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="5">
@@ -2915,7 +2828,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="0">
+    <format dxfId="64">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="5">
@@ -2998,116 +2911,21 @@
 </file>
 
 <file path=xl/richData/rdarray.xml><?xml version="1.0" encoding="utf-8"?>
-<arrayData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="32">
-  <a r="1">
-    <v t="i">0</v>
-  </a>
-  <a r="1">
-    <v>55.85</v>
-  </a>
-  <a r="1">
-    <v>10.050000000000001</v>
-  </a>
-  <a r="1">
-    <v>362.71</v>
-  </a>
-  <a r="1">
-    <v>44.73</v>
-  </a>
-  <a r="1">
-    <v>4.3</v>
-  </a>
-  <a r="1">
-    <v>157.16999999999999</v>
-  </a>
-  <a r="1">
-    <v>18.309999999999999</v>
-  </a>
-  <a r="1">
-    <v>84.92</v>
-  </a>
-  <a r="1">
-    <v>124.92</v>
-  </a>
-  <a r="1">
-    <v>65.12</v>
-  </a>
-  <a r="1">
-    <v>158.07</v>
-  </a>
-  <a r="1">
-    <v>16.34</v>
-  </a>
-  <a r="1">
-    <v>0.71099999999999997</v>
-  </a>
-  <a r="1">
-    <v>306.3</v>
-  </a>
-  <a r="1">
-    <v>117.49</v>
-  </a>
-  <a r="1">
-    <v>98.61</v>
-  </a>
-  <a r="1">
-    <v>155.12</v>
-  </a>
-  <a r="1">
-    <v>150.6</v>
-  </a>
-  <a r="1">
-    <v>20.530999999999999</v>
-  </a>
-  <a r="1">
-    <v>22.53</v>
-  </a>
-  <a r="1">
-    <v>709.08</v>
-  </a>
-  <a r="1">
-    <v>49.41</v>
-  </a>
-  <a r="1">
-    <v>694.9</v>
-  </a>
-  <a r="1">
-    <v>35.54</v>
-  </a>
-  <a r="1">
-    <v>20.7</v>
-  </a>
-  <a r="1">
-    <v>36.090000000000003</v>
-  </a>
-  <a r="1">
-    <v>396.99</v>
-  </a>
-  <a r="1">
-    <v>241.84</v>
-  </a>
-  <a r="1">
-    <v>153.47</v>
-  </a>
-  <a r="1">
-    <v>170.28</v>
-  </a>
+<arrayData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="1">
   <a r="46">
     <v t="e">#NULL!</v>
     <v t="e">#NULL!</v>
-    <v t="r">0</v>
+    <v t="r">2</v>
     <v t="e">#NULL!</v>
     <v t="e">#NULL!</v>
     <v t="e">#NULL!</v>
-    <v t="r">1</v>
-    <v t="r">2</v>
     <v t="r">3</v>
     <v t="r">4</v>
+    <v t="r">5</v>
+    <v t="r">6</v>
     <v t="e">#NULL!</v>
     <v t="e">#NULL!</v>
     <v t="e">#NULL!</v>
-    <v t="r">5</v>
-    <v t="r">6</v>
     <v t="r">7</v>
     <v t="r">8</v>
     <v t="r">9</v>
@@ -3115,9 +2933,9 @@
     <v t="r">11</v>
     <v t="r">12</v>
     <v t="r">13</v>
-    <v t="e">#NULL!</v>
     <v t="r">14</v>
     <v t="r">15</v>
+    <v t="e">#NULL!</v>
     <v t="r">16</v>
     <v t="r">17</v>
     <v t="r">18</v>
@@ -3129,14 +2947,16 @@
     <v t="r">24</v>
     <v t="r">25</v>
     <v t="r">26</v>
-    <v t="e">#NULL!</v>
     <v t="r">27</v>
     <v t="r">28</v>
+    <v t="e">#NULL!</v>
+    <v t="r">29</v>
+    <v t="r">30</v>
     <v t="e">#NULL!</v>
     <v t="e">#NULL!</v>
     <v t="e">#NULL!</v>
     <v t="e">#NULL!</v>
-    <v t="r">29</v>
+    <v t="r">31</v>
     <v t="e">#NULL!</v>
     <v t="i">2</v>
   </a>
@@ -3144,577 +2964,155 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="62">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="34">
   <rv s="0">
-    <fb>396.99</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>20.7</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>153.47</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>36.090000000000003</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>170.28</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>0.71099999999999997</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>157.16999999999999</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>124.92</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>306.3</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>158.07</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>16.34</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>4.3</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>150.6</fb>
+    <v>9</v>
     <v>1</v>
   </rv>
   <rv s="0">
-    <fb>10.050000000000001</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>22.53</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>49.41</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>20.530999999999999</fb>
     <v>2</v>
-  </rv>
-  <rv s="0">
-    <fb>117.49</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>18.309999999999999</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>709.08</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>65.12</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>98.61</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>84.92</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>155.12</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>362.71</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>694.9</fb>
-    <v>3</v>
-  </rv>
-  <rv s="0">
-    <fb>241.84</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>35.54</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>44.73</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>55.85</fb>
-    <v>0</v>
+    <v>11</v>
   </rv>
   <rv s="1">
-    <v>4</v>
-    <v>MO</v>
-    <v>Daily</v>
-    <v>45716</v>
-    <v>45717</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638762976000000000,638764534061689175,0</v>
-    <v>0</v>
-    <v>a1xtpr</v>
-    <v>XNYS:MO</v>
+    <fb>396.99</fb>
     <v>1</v>
   </rv>
   <rv s="1">
-    <v>4</v>
-    <v>CSIQ</v>
-    <v>Daily</v>
-    <v>45716</v>
-    <v>45717</v>
-    <v>0</v>
+    <fb>20.7</fb>
     <v>1</v>
-    <v>638762976000000000,638764532155879737,0</v>
-    <v>0</v>
-    <v>a1qepr</v>
-    <v>XNAS:CSIQ</v>
+  </rv>
+  <rv s="1">
+    <fb>153.47</fb>
+    <v>1</v>
+  </rv>
+  <rv s="1">
+    <fb>36.090000000000003</fb>
+    <v>1</v>
+  </rv>
+  <rv s="1">
+    <fb>170.28</fb>
+    <v>1</v>
+  </rv>
+  <rv s="1">
+    <fb>0.71099999999999997</fb>
+    <v>1</v>
+  </rv>
+  <rv s="1">
+    <fb>157.16999999999999</fb>
+    <v>1</v>
+  </rv>
+  <rv s="1">
+    <fb>124.92</fb>
+    <v>1</v>
+  </rv>
+  <rv s="1">
+    <fb>306.3</fb>
+    <v>1</v>
+  </rv>
+  <rv s="1">
+    <fb>158.07</fb>
+    <v>1</v>
+  </rv>
+  <rv s="1">
+    <fb>16.34</fb>
+    <v>1</v>
+  </rv>
+  <rv s="1">
+    <fb>4.3</fb>
+    <v>1</v>
+  </rv>
+  <rv s="1">
+    <fb>150.6</fb>
     <v>2</v>
   </rv>
   <rv s="1">
-    <v>4</v>
-    <v>V</v>
-    <v>Daily</v>
-    <v>45716</v>
-    <v>45717</v>
-    <v>0</v>
+    <fb>10.050000000000001</fb>
     <v>1</v>
-    <v>638762976000000000,638764532156371589,0</v>
-    <v>0</v>
-    <v>a256cw</v>
-    <v>XNYS:V</v>
+  </rv>
+  <rv s="1">
+    <fb>22.53</fb>
+    <v>1</v>
+  </rv>
+  <rv s="1">
+    <fb>49.41</fb>
+    <v>1</v>
+  </rv>
+  <rv s="1">
+    <fb>20.530999999999999</fb>
     <v>3</v>
   </rv>
   <rv s="1">
-    <v>4</v>
-    <v>VWO.US</v>
-    <v>Daily</v>
-    <v>45716</v>
-    <v>45717</v>
-    <v>0</v>
+    <fb>117.49</fb>
     <v>1</v>
-    <v>638762976000000000,638764534060952808,0</v>
-    <v>0</v>
-    <v>a25nhw</v>
-    <v>ARCX:VWO</v>
+  </rv>
+  <rv s="1">
+    <fb>18.309999999999999</fb>
+    <v>1</v>
+  </rv>
+  <rv s="1">
+    <fb>709.08</fb>
+    <v>1</v>
+  </rv>
+  <rv s="1">
+    <fb>65.12</fb>
+    <v>1</v>
+  </rv>
+  <rv s="1">
+    <fb>98.61</fb>
+    <v>1</v>
+  </rv>
+  <rv s="1">
+    <fb>84.92</fb>
+    <v>1</v>
+  </rv>
+  <rv s="1">
+    <fb>155.12</fb>
+    <v>1</v>
+  </rv>
+  <rv s="1">
+    <fb>362.71</fb>
+    <v>1</v>
+  </rv>
+  <rv s="1">
+    <fb>694.9</fb>
     <v>4</v>
   </rv>
   <rv s="1">
-    <v>4</v>
-    <v>MAXN</v>
-    <v>Daily</v>
-    <v>45716</v>
-    <v>45717</v>
-    <v>0</v>
+    <fb>241.84</fb>
     <v>1</v>
-    <v>638762976000000000,638764532156160243,0</v>
-    <v>0</v>
-    <v>bvhkk2</v>
-    <v>XNAS:MAXN</v>
-    <v>5</v>
   </rv>
   <rv s="1">
-    <v>4</v>
-    <v>QCOM</v>
-    <v>Daily</v>
-    <v>45716</v>
-    <v>45717</v>
-    <v>0</v>
+    <fb>35.54</fb>
     <v>1</v>
-    <v>638762976000000000,638764532156519327,0</v>
-    <v>0</v>
-    <v>a21k2w</v>
-    <v>XNAS:QCOM</v>
-    <v>6</v>
   </rv>
   <rv s="1">
-    <v>4</v>
-    <v>SWI</v>
-    <v>Daily</v>
-    <v>45716</v>
-    <v>45717</v>
-    <v>0</v>
+    <fb>44.73</fb>
     <v>1</v>
-    <v>638762976000000000,638764532156263508,0</v>
-    <v>0</v>
-    <v>bn8mkr</v>
-    <v>XNYS:SWI</v>
-    <v>7</v>
   </rv>
   <rv s="1">
-    <v>4</v>
-    <v>PLTR</v>
-    <v>Daily</v>
-    <v>45716</v>
-    <v>45717</v>
-    <v>0</v>
+    <fb>55.85</fb>
     <v>1</v>
-    <v>638762976000000000,638764532156401217,0</v>
-    <v>0</v>
-    <v>bvsk7w</v>
-    <v>XNAS:PLTR</v>
-    <v>8</v>
-  </rv>
-  <rv s="1">
-    <v>4</v>
-    <v>NVDA</v>
-    <v>Daily</v>
-    <v>45716</v>
-    <v>45717</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638762976000000000,638764532156192149,0</v>
-    <v>0</v>
-    <v>a1yv52</v>
-    <v>XNAS:NVDA</v>
-    <v>9</v>
-  </rv>
-  <rv s="1">
-    <v>4</v>
-    <v>APTV</v>
-    <v>Daily</v>
-    <v>45716</v>
-    <v>45717</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638762976000000000,638764532156463129,0</v>
-    <v>0</v>
-    <v>awagjc</v>
-    <v>XNYS:APTV</v>
-    <v>10</v>
-  </rv>
-  <rv s="1">
-    <v>4</v>
-    <v>AMAT</v>
-    <v>Daily</v>
-    <v>45716</v>
-    <v>45717</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638762976000000000,638764532156221398,0</v>
-    <v>0</v>
-    <v>a1nda2</v>
-    <v>XNAS:AMAT</v>
-    <v>11</v>
-  </rv>
-  <rv s="1">
-    <v>4</v>
-    <v>PCG</v>
-    <v>Daily</v>
-    <v>45716</v>
-    <v>45717</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638762976000000000,638764532156134573,0</v>
-    <v>0</v>
-    <v>a1zkar</v>
-    <v>XNYS:PCG</v>
-    <v>12</v>
-  </rv>
-  <rv s="1">
-    <v>4</v>
-    <v>GC=F</v>
-    <v>Daily</v>
-    <v>45716</v>
-    <v>45717</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638762976000000000,638764532156642224,0</v>
-    <v>0</v>
-    <v>a2losm</v>
-    <v>OTCM:JETMF</v>
-    <v>13</v>
-  </rv>
-  <rv s="1">
-    <v>4</v>
-    <v>HCA</v>
-    <v>Daily</v>
-    <v>45716</v>
-    <v>45717</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638762976000000000,638764532156433144,0</v>
-    <v>0</v>
-    <v>a1uhnm</v>
-    <v>XNYS:HCA</v>
-    <v>14</v>
-  </rv>
-  <rv s="1">
-    <v>4</v>
-    <v>DUK</v>
-    <v>Daily</v>
-    <v>45716</v>
-    <v>45717</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638762976000000000,638764532155935454,0</v>
-    <v>0</v>
-    <v>a1rdzr</v>
-    <v>XNYS:DUK</v>
-    <v>15</v>
-  </rv>
-  <rv s="1">
-    <v>4</v>
-    <v>WMT</v>
-    <v>Daily</v>
-    <v>45716</v>
-    <v>45717</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638762976000000000,638764532155910474,0</v>
-    <v>0</v>
-    <v>a25ya2</v>
-    <v>XNYS:WMT</v>
-    <v>16</v>
-  </rv>
-  <rv s="1">
-    <v>4</v>
-    <v>MMM</v>
-    <v>Daily</v>
-    <v>45716</v>
-    <v>45717</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638762976000000000,638764532156351447,0</v>
-    <v>0</v>
-    <v>a1xroc</v>
-    <v>XNYS:MMM</v>
-    <v>17</v>
-  </rv>
-  <rv s="1">
-    <v>5</v>
-    <v>USDJPY=X</v>
-    <v>Daily</v>
-    <v>45716</v>
-    <v>45717</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638762976000000000,638764532156550618,0</v>
-    <v>0</v>
-    <v>avyomw</v>
-    <v>USDJPY</v>
-    <v>18</v>
-  </rv>
-  <rv s="1">
-    <v>6</v>
-    <v>USDMXN=X</v>
-    <v>Daily</v>
-    <v>45716</v>
-    <v>45717</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638762976000000000,638764532156488796,0</v>
-    <v>0</v>
-    <v>avyqcw</v>
-    <v>USDMXN</v>
-    <v>19</v>
-  </rv>
-  <rv s="1">
-    <v>4</v>
-    <v>JKS</v>
-    <v>Daily</v>
-    <v>45716</v>
-    <v>45717</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638762976000000000,638764532156617741,0</v>
-    <v>0</v>
-    <v>a1w7f2</v>
-    <v>XNYS:JKS</v>
-    <v>20</v>
-  </rv>
-  <rv s="1">
-    <v>4</v>
-    <v>ASML</v>
-    <v>Daily</v>
-    <v>45716</v>
-    <v>45717</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638762976000000000,638764532156068741,0</v>
-    <v>0</v>
-    <v>a1ntlh</v>
-    <v>XNAS:ASML</v>
-    <v>21</v>
-  </rv>
-  <rv s="1">
-    <v>4</v>
-    <v>YUMC</v>
-    <v>Daily</v>
-    <v>45716</v>
-    <v>45717</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638762976000000000,638764532156292613,0</v>
-    <v>0</v>
-    <v>a26erw</v>
-    <v>XNYS:YUMC</v>
-    <v>22</v>
-  </rv>
-  <rv s="1">
-    <v>7</v>
-    <v>LVMH</v>
-    <v>Daily</v>
-    <v>45716</v>
-    <v>45717</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638762976000000000,638764534343783125,0</v>
-    <v>0</v>
-    <v>ae96u2</v>
-    <v>XPAR:MC</v>
-    <v>23</v>
-  </rv>
-  <rv s="1">
-    <v>4</v>
-    <v>AGIO</v>
-    <v>Daily</v>
-    <v>45716</v>
-    <v>45717</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638762976000000000,638764534059083943,0</v>
-    <v>0</v>
-    <v>a1n2qh</v>
-    <v>XNAS:AGIO</v>
-    <v>24</v>
-  </rv>
-  <rv s="1">
-    <v>4</v>
-    <v>APA</v>
-    <v>Daily</v>
-    <v>45716</v>
-    <v>45717</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638762976000000000,638764534059100384,0</v>
-    <v>0</v>
-    <v>a1nkur</v>
-    <v>XNAS:APA</v>
-    <v>25</v>
-  </rv>
-  <rv s="1">
-    <v>4</v>
-    <v>DAR</v>
-    <v>Daily</v>
-    <v>45716</v>
-    <v>45717</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638762976000000000,638764534059133380,0</v>
-    <v>0</v>
-    <v>a1qqk2</v>
-    <v>XNYS:DAR</v>
-    <v>26</v>
-  </rv>
-  <rv s="1">
-    <v>4</v>
-    <v>MSFT</v>
-    <v>Daily</v>
-    <v>45716</v>
-    <v>45717</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638762976000000000,638764534059124005,0</v>
-    <v>0</v>
-    <v>a1xzim</v>
-    <v>XNAS:MSFT</v>
-    <v>27</v>
-  </rv>
-  <rv s="1">
-    <v>4</v>
-    <v>AAPL</v>
-    <v>Daily</v>
-    <v>45716</v>
-    <v>45717</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638762976000000000,638764534059183937,0</v>
-    <v>0</v>
-    <v>a1mou2</v>
-    <v>XNAS:AAPL</v>
-    <v>28</v>
-  </rv>
-  <rv s="1">
-    <v>4</v>
-    <v>PEP</v>
-    <v>Daily</v>
-    <v>45716</v>
-    <v>45717</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638762976000000000,638764534059215680,0</v>
-    <v>0</v>
-    <v>axyhnm</v>
-    <v>XNAS:PEP</v>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <v>4</v>
-    <v>GOOGL</v>
-    <v>Daily</v>
-    <v>45716</v>
-    <v>45717</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638762976000000000,638764534061664520,0</v>
-    <v>0</v>
-    <v>a1u3rw</v>
-    <v>XNAS:GOOGL</v>
-    <v>30</v>
   </rv>
   <rv s="2">
-    <v>31</v>
+    <v>0</v>
   </rv>
   <rv s="3">
     <v>{8231C5FD-6A38-425A-8202-1B139D24CA84}</v>
     <v>0</v>
-    <v>8</v>
-    <v>60</v>
+    <v>0</v>
+    <v>32</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
 <rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="subType" t="i"/>
+  </s>
   <s t="_formattednumber">
     <k n="_Format" t="spb"/>
-  </s>
-  <s t="_stockhistorycache">
-    <k n="_Format" t="spb"/>
-    <k n="Symbol" t="s"/>
-    <k n="Interval" t="s"/>
-    <k n="StartDate" t="i"/>
-    <k n="EndDate" t="i"/>
-    <k n="f1904" t="b"/>
-    <k n="fdcompat" t="b"/>
-    <k n="etag" t="s"/>
-    <k n="Date" t="a"/>
-    <k n="EntityId" t="s"/>
-    <k n="Instrument" t="s"/>
-    <k n="Close" t="a"/>
   </s>
   <s t="_array">
     <k n="array" t="a"/>
@@ -3738,63 +3136,40 @@
       <v t="s">_Display</v>
     </a>
   </spbArrays>
-  <spbData count="9">
+  <spbData count="5">
     <spb s="0">
-      <v>1</v>
-    </spb>
-    <spb s="0">
-      <v>2</v>
-    </spb>
-    <spb s="0">
-      <v>3</v>
-    </spb>
-    <spb s="0">
-      <v>4</v>
+      <v>0</v>
     </spb>
     <spb s="1">
-      <v>5</v>
       <v>1</v>
     </spb>
     <spb s="1">
-      <v>5</v>
       <v>2</v>
     </spb>
     <spb s="1">
-      <v>5</v>
       <v>3</v>
     </spb>
     <spb s="1">
-      <v>5</v>
       <v>4</v>
-    </spb>
-    <spb s="2">
-      <v>0</v>
     </spb>
   </spbData>
 </supportingPropertyBags>
 </file>
 
 <file path=xl/richData/rdsupportingpropertybagstructure.xml><?xml version="1.0" encoding="utf-8"?>
-<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="3">
+<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="2">
+  <s>
+    <k n="^Order" t="spba"/>
+  </s>
   <s>
     <k n="_Self" t="i"/>
-  </s>
-  <s>
-    <k n="Date" t="i"/>
-    <k n="Close" t="i"/>
-  </s>
-  <s>
-    <k n="^Order" t="spba"/>
   </s>
 </spbStructures>
 </file>
 
 <file path=xl/richData/richStyles.xml><?xml version="1.0" encoding="utf-8"?>
 <richStyleSheet xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <dxfs count="2">
-    <x:dxf>
-      <x:numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-    </x:dxf>
+  <dxfs count="1">
     <x:dxf>
       <x:numFmt numFmtId="0" formatCode="General"/>
     </x:dxf>
@@ -3803,19 +3178,18 @@
     <rPr n="NumberFormat" t="s"/>
   </richProperties>
   <richStyles>
-    <rSty dxfid="1">
+    <rSty dxfid="0">
       <rpv i="0">_([$$-en-US]* #,##0.00_);_([$$-en-US]* (#,##0.00);_([$$-en-US]* "-"??_);_(@_)</rpv>
     </rSty>
-    <rSty dxfid="1">
+    <rSty dxfid="0">
       <rpv i="0">_-[$¥-ja-JP]* #,##0.00_-;-[$¥-ja-JP]* #,##0.00_-;_-[$¥-ja-JP]* "-"??_-;_-@_-</rpv>
     </rSty>
-    <rSty dxfid="1">
+    <rSty dxfid="0">
       <rpv i="0">_-[$$-es-MX]* #,##0.00_-;-[$$-es-MX]* #,##0.00_-;_-[$$-es-MX]* "-"??_-;_-@_-</rpv>
     </rSty>
-    <rSty dxfid="1">
+    <rSty dxfid="0">
       <rpv i="0">_([$€-x-euro2] * #,##0.00_);_([$€-x-euro2] * (#,##0.00);_([$€-x-euro2] * "-"??_);_(@_)</rpv>
     </rSty>
-    <rSty dxfid="0"/>
   </richStyles>
 </richStyleSheet>
 </file>
@@ -4413,17 +3787,17 @@
         <f t="shared" si="5"/>
         <v>77.787734199999989</v>
       </c>
-      <c r="O4" s="12" cm="1" vm="1">
+      <c r="O4" s="12" t="e" cm="1" vm="1">
         <f t="array" aca="1" ref="O4" ca="1">_xlfn.STOCKHISTORY(C4,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>396.99</v>
+        <v>#VALUE!</v>
       </c>
       <c r="P4" s="12">
         <f t="shared" ca="1" si="6"/>
-        <v>63.756594</v>
+        <v>67.641508000000002</v>
       </c>
       <c r="Q4" s="12">
         <f t="shared" ca="1" si="7"/>
-        <v>-3.884914000000002</v>
+        <v>0</v>
       </c>
       <c r="R4" s="12">
         <f t="shared" si="8"/>
@@ -4772,17 +4146,17 @@
         <f t="shared" si="5"/>
         <v>80.35399799999999</v>
       </c>
-      <c r="O8" s="12" cm="1" vm="2">
+      <c r="O8" s="12" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="O8" ca="1">_xlfn.STOCKHISTORY(C8,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>20.7</v>
+        <v>#VALUE!</v>
       </c>
       <c r="P8" s="12">
         <f t="shared" ca="1" si="6"/>
-        <v>62.578169999999993</v>
+        <v>64.966418999999988</v>
       </c>
       <c r="Q8" s="12">
         <f t="shared" ca="1" si="7"/>
-        <v>-2.3882489999999947</v>
+        <v>0</v>
       </c>
       <c r="R8" s="12">
         <f t="shared" si="8"/>
@@ -4862,17 +4236,17 @@
         <f t="shared" si="5"/>
         <v>86.394189907200001</v>
       </c>
-      <c r="O9" s="12" cm="1" vm="3">
+      <c r="O9" s="12" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="O9" ca="1">_xlfn.STOCKHISTORY(C9,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>153.47</v>
+        <v>#VALUE!</v>
       </c>
       <c r="P9" s="12">
         <f t="shared" ca="1" si="6"/>
-        <v>78.638027999999991</v>
+        <v>80.954076000000001</v>
       </c>
       <c r="Q9" s="12">
         <f t="shared" ca="1" si="7"/>
-        <v>-2.3160480000000092</v>
+        <v>0</v>
       </c>
       <c r="R9" s="12">
         <f t="shared" si="8"/>
@@ -4952,17 +4326,17 @@
         <f t="shared" si="5"/>
         <v>21.381618470000003</v>
       </c>
-      <c r="O10" s="12" cm="1" vm="4">
+      <c r="O10" s="12" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="O10" ca="1">_xlfn.STOCKHISTORY(C10,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>36.090000000000003</v>
+        <v>#VALUE!</v>
       </c>
       <c r="P10" s="12">
         <f t="shared" ca="1" si="6"/>
-        <v>18.864243000000005</v>
+        <v>19.982821000000001</v>
       </c>
       <c r="Q10" s="12">
         <f t="shared" ca="1" si="7"/>
-        <v>-1.1185779999999959</v>
+        <v>0</v>
       </c>
       <c r="R10" s="12">
         <f t="shared" si="8"/>
@@ -5043,17 +4417,17 @@
         <f t="shared" si="5"/>
         <v>10.244057999999999</v>
       </c>
-      <c r="O11" s="12" cm="1" vm="5">
+      <c r="O11" s="12" t="e" cm="1" vm="1">
         <f t="array" aca="1" ref="O11" ca="1">_xlfn.STOCKHISTORY(C11,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>170.28</v>
+        <v>#VALUE!</v>
       </c>
       <c r="P11" s="12">
         <f t="shared" ca="1" si="6"/>
-        <v>9.1610639999999997</v>
+        <v>9.9971160000000001</v>
       </c>
       <c r="Q11" s="12">
         <f t="shared" ca="1" si="7"/>
-        <v>-0.83605200000000046</v>
+        <v>0</v>
       </c>
       <c r="R11" s="12">
         <f t="shared" si="8"/>
@@ -5363,7 +4737,7 @@
       </c>
       <c r="D15" s="8">
         <f ca="1">TODAY()-20</f>
-        <v>45697</v>
+        <v>45698</v>
       </c>
       <c r="E15" s="2">
         <v>9.9999999999999998E-20</v>
@@ -5401,17 +4775,17 @@
         <f t="shared" si="5"/>
         <v>3.0171900000000003E-16</v>
       </c>
-      <c r="O15" s="12" cm="1" vm="6">
+      <c r="O15" s="12" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="O15" ca="1">_xlfn.STOCKHISTORY(C15,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>0.71099999999999997</v>
+        <v>#VALUE!</v>
       </c>
       <c r="P15" s="12">
         <f t="shared" ca="1" si="6"/>
-        <v>7.1099999999999989E-20</v>
+        <v>2.7429000000000002E-16</v>
       </c>
       <c r="Q15" s="12">
         <f t="shared" ca="1" si="7"/>
-        <v>-2.742189E-16</v>
+        <v>0</v>
       </c>
       <c r="R15" s="12">
         <f t="shared" si="8"/>
@@ -5491,17 +4865,17 @@
         <f t="shared" si="5"/>
         <v>2.16338E-17</v>
       </c>
-      <c r="O16" s="12" cm="1" vm="7">
+      <c r="O16" s="12" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="O16" ca="1">_xlfn.STOCKHISTORY(C16,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>157.16999999999999</v>
+        <v>#VALUE!</v>
       </c>
       <c r="P16" s="12">
         <f t="shared" ca="1" si="6"/>
-        <v>1.5716999999999997E-17</v>
+        <v>1.8812000000000001E-17</v>
       </c>
       <c r="Q16" s="12">
         <f t="shared" ca="1" si="7"/>
-        <v>-3.0950000000000039E-18</v>
+        <v>0</v>
       </c>
       <c r="R16" s="12">
         <f t="shared" si="8"/>
@@ -5581,17 +4955,17 @@
         <f t="shared" si="5"/>
         <v>1.6906149999999997E-17</v>
       </c>
-      <c r="O17" s="12" cm="1" vm="8">
+      <c r="O17" s="12" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="O17" ca="1">_xlfn.STOCKHISTORY(C17,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>124.92</v>
+        <v>#VALUE!</v>
       </c>
       <c r="P17" s="12">
         <f t="shared" ca="1" si="6"/>
-        <v>1.2491999999999999E-17</v>
+        <v>1.4700999999999999E-17</v>
       </c>
       <c r="Q17" s="12">
         <f t="shared" ca="1" si="7"/>
-        <v>-2.2089999999999996E-18</v>
+        <v>0</v>
       </c>
       <c r="R17" s="12">
         <f t="shared" si="8"/>
@@ -5671,17 +5045,17 @@
         <f t="shared" si="5"/>
         <v>3.8849999999999999E-17</v>
       </c>
-      <c r="O18" s="12" cm="1" vm="9">
+      <c r="O18" s="12" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="O18" ca="1">_xlfn.STOCKHISTORY(C18,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>306.3</v>
+        <v>#VALUE!</v>
       </c>
       <c r="P18" s="12">
         <f t="shared" ca="1" si="6"/>
-        <v>3.0629999999999998E-17</v>
+        <v>3.2375000000000002E-17</v>
       </c>
       <c r="Q18" s="12">
         <f t="shared" ca="1" si="7"/>
-        <v>-1.7450000000000042E-18</v>
+        <v>0</v>
       </c>
       <c r="R18" s="12">
         <f t="shared" si="8"/>
@@ -5761,17 +5135,17 @@
         <f t="shared" si="5"/>
         <v>1.8627400000000003E-17</v>
       </c>
-      <c r="O19" s="12" cm="1" vm="10">
+      <c r="O19" s="12" t="e" cm="1" vm="1">
         <f t="array" aca="1" ref="O19" ca="1">_xlfn.STOCKHISTORY(C19,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>158.07</v>
+        <v>#VALUE!</v>
       </c>
       <c r="P19" s="12">
         <f t="shared" ca="1" si="6"/>
-        <v>1.5806999999999999E-17</v>
+        <v>1.6933999999999999E-17</v>
       </c>
       <c r="Q19" s="12">
         <f t="shared" ca="1" si="7"/>
-        <v>-1.1270000000000002E-18</v>
+        <v>0</v>
       </c>
       <c r="R19" s="12">
         <f t="shared" si="8"/>
@@ -5851,17 +5225,17 @@
         <f t="shared" si="5"/>
         <v>2.9293000000000003E-18</v>
       </c>
-      <c r="O20" s="12" cm="1" vm="11">
+      <c r="O20" s="12" t="e" cm="1" vm="1">
         <f t="array" aca="1" ref="O20" ca="1">_xlfn.STOCKHISTORY(C20,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>16.34</v>
+        <v>#VALUE!</v>
       </c>
       <c r="P20" s="12">
         <f t="shared" ca="1" si="6"/>
-        <v>1.6339999999999999E-18</v>
+        <v>2.663E-18</v>
       </c>
       <c r="Q20" s="12">
         <f t="shared" ca="1" si="7"/>
-        <v>-1.0290000000000001E-18</v>
+        <v>0</v>
       </c>
       <c r="R20" s="12">
         <f t="shared" si="8"/>
@@ -5941,17 +5315,17 @@
         <f t="shared" si="5"/>
         <v>2.1840000000000001E-18</v>
       </c>
-      <c r="O21" s="12" cm="1" vm="12">
+      <c r="O21" s="12" t="e" cm="1" vm="1">
         <f t="array" aca="1" ref="O21" ca="1">_xlfn.STOCKHISTORY(C21,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>4.3</v>
+        <v>#VALUE!</v>
       </c>
       <c r="P21" s="12">
         <f t="shared" ca="1" si="6"/>
-        <v>4.2999999999999997E-19</v>
+        <v>1.092E-18</v>
       </c>
       <c r="Q21" s="12">
         <f t="shared" ca="1" si="7"/>
-        <v>-6.6200000000000002E-19</v>
+        <v>0</v>
       </c>
       <c r="R21" s="12">
         <f t="shared" si="8"/>
@@ -6031,17 +5405,17 @@
         <f t="shared" si="5"/>
         <v>1.6451806399999999E-17</v>
       </c>
-      <c r="O22" s="12" cm="1" vm="13">
+      <c r="O22" s="12" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="O22" ca="1">_xlfn.STOCKHISTORY(C22,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>150.6</v>
+        <v>#VALUE!</v>
       </c>
       <c r="P22" s="12">
         <f t="shared" ca="1" si="6"/>
-        <v>1.5059999999999998E-17</v>
+        <v>1.5375519999999999E-17</v>
       </c>
       <c r="Q22" s="12">
         <f t="shared" ca="1" si="7"/>
-        <v>-3.1552000000000061E-19</v>
+        <v>0</v>
       </c>
       <c r="R22" s="12">
         <f t="shared" si="8"/>
@@ -6121,17 +5495,17 @@
         <f t="shared" si="5"/>
         <v>1.16025E-18</v>
       </c>
-      <c r="O23" s="12" cm="1" vm="14">
+      <c r="O23" s="12" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="O23" ca="1">_xlfn.STOCKHISTORY(C23,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>10.050000000000001</v>
+        <v>#VALUE!</v>
       </c>
       <c r="P23" s="12">
         <f t="shared" ca="1" si="6"/>
-        <v>1.005E-18</v>
+        <v>1.1050000000000001E-18</v>
       </c>
       <c r="Q23" s="12">
         <f t="shared" ca="1" si="7"/>
-        <v>-1.0000000000000005E-19</v>
+        <v>0</v>
       </c>
       <c r="R23" s="12">
         <f t="shared" si="8"/>
@@ -6300,17 +5674,17 @@
         <f t="shared" si="5"/>
         <v>2.1860999999999999E-18</v>
       </c>
-      <c r="O25" s="12" cm="1" vm="15">
+      <c r="O25" s="12" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="O25" ca="1">_xlfn.STOCKHISTORY(C25,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>22.53</v>
+        <v>#VALUE!</v>
       </c>
       <c r="P25" s="12">
         <f t="shared" ca="1" si="6"/>
-        <v>2.2529999999999999E-18</v>
+        <v>2.0820000000000002E-18</v>
       </c>
       <c r="Q25" s="12">
         <f t="shared" ca="1" si="7"/>
-        <v>1.7099999999999971E-19</v>
+        <v>0</v>
       </c>
       <c r="R25" s="12">
         <f t="shared" si="8"/>
@@ -6390,17 +5764,17 @@
         <f t="shared" si="5"/>
         <v>5.0739400000000001E-18</v>
       </c>
-      <c r="O26" s="12" cm="1" vm="16">
+      <c r="O26" s="12" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="O26" ca="1">_xlfn.STOCKHISTORY(C26,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>49.41</v>
+        <v>#VALUE!</v>
       </c>
       <c r="P26" s="12">
         <f t="shared" ca="1" si="6"/>
-        <v>4.9409999999999994E-18</v>
+        <v>4.7419999999999999E-18</v>
       </c>
       <c r="Q26" s="12">
         <f t="shared" ca="1" si="7"/>
-        <v>1.9899999999999948E-19</v>
+        <v>0</v>
       </c>
       <c r="R26" s="12">
         <f t="shared" si="8"/>
@@ -6479,17 +5853,17 @@
         <f t="shared" si="5"/>
         <v>2.1199999999999999E-18</v>
       </c>
-      <c r="O27" s="12" cm="1" vm="17">
+      <c r="O27" s="12" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="O27" ca="1">_xlfn.STOCKHISTORY(C27,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>20.530999999999999</v>
+        <v>#VALUE!</v>
       </c>
       <c r="P27" s="12">
         <f t="shared" ca="1" si="6"/>
-        <v>2.0530999999999999E-18</v>
+        <v>1.7E-18</v>
       </c>
       <c r="Q27" s="12">
         <f t="shared" ca="1" si="7"/>
-        <v>3.5309999999999988E-19</v>
+        <v>0</v>
       </c>
       <c r="R27" s="12">
         <f t="shared" si="8"/>
@@ -6570,17 +5944,17 @@
         <f t="shared" si="5"/>
         <v>1.2115000000000002E-17</v>
       </c>
-      <c r="O28" s="12" cm="1" vm="18">
+      <c r="O28" s="12" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="O28" ca="1">_xlfn.STOCKHISTORY(C28,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>117.49</v>
+        <v>#VALUE!</v>
       </c>
       <c r="P28" s="12">
         <f t="shared" ca="1" si="6"/>
-        <v>1.1749E-17</v>
+        <v>1.1357999999999999E-17</v>
       </c>
       <c r="Q28" s="12">
         <f t="shared" ca="1" si="7"/>
-        <v>3.9100000000000046E-19</v>
+        <v>0</v>
       </c>
       <c r="R28" s="12">
         <f t="shared" si="8"/>
@@ -6661,17 +6035,17 @@
         <f t="shared" si="5"/>
         <v>1.3720000000000001E-18</v>
       </c>
-      <c r="O29" s="12" cm="1" vm="19">
+      <c r="O29" s="12" t="e" cm="1" vm="1">
         <f t="array" aca="1" ref="O29" ca="1">_xlfn.STOCKHISTORY(C29,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>18.309999999999999</v>
+        <v>#VALUE!</v>
       </c>
       <c r="P29" s="12">
         <f t="shared" ca="1" si="6"/>
-        <v>1.8309999999999997E-18</v>
+        <v>1.304E-18</v>
       </c>
       <c r="Q29" s="12">
         <f t="shared" ca="1" si="7"/>
-        <v>5.2699999999999978E-19</v>
+        <v>0</v>
       </c>
       <c r="R29" s="12">
         <f t="shared" si="8"/>
@@ -6751,17 +6125,17 @@
         <f t="shared" si="5"/>
         <v>7.7035200000000004E-17</v>
       </c>
-      <c r="O30" s="12" cm="1" vm="20">
+      <c r="O30" s="12" t="e" cm="1" vm="1">
         <f t="array" aca="1" ref="O30" ca="1">_xlfn.STOCKHISTORY(C30,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>709.08</v>
+        <v>#VALUE!</v>
       </c>
       <c r="P30" s="12">
         <f t="shared" ca="1" si="6"/>
-        <v>7.0908000000000005E-17</v>
+        <v>7.0031999999999998E-17</v>
       </c>
       <c r="Q30" s="12">
         <f t="shared" ca="1" si="7"/>
-        <v>8.7600000000000674E-19</v>
+        <v>0</v>
       </c>
       <c r="R30" s="12">
         <f t="shared" si="8"/>
@@ -6841,17 +6215,17 @@
         <f t="shared" si="5"/>
         <v>5.9920000000000002E-18</v>
       </c>
-      <c r="O31" s="12" cm="1" vm="21">
+      <c r="O31" s="12" t="e" cm="1" vm="1">
         <f t="array" aca="1" ref="O31" ca="1">_xlfn.STOCKHISTORY(C31,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>65.12</v>
+        <v>#VALUE!</v>
       </c>
       <c r="P31" s="12">
         <f t="shared" ca="1" si="6"/>
-        <v>6.5120000000000005E-18</v>
+        <v>5.5999999999999995E-18</v>
       </c>
       <c r="Q31" s="12">
         <f t="shared" ca="1" si="7"/>
-        <v>9.12000000000001E-19</v>
+        <v>0</v>
       </c>
       <c r="R31" s="12">
         <f t="shared" si="8"/>
@@ -6931,17 +6305,17 @@
         <f t="shared" si="5"/>
         <v>9.2662000000000008E-18</v>
       </c>
-      <c r="O32" s="12" cm="1" vm="22">
+      <c r="O32" s="12" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="O32" ca="1">_xlfn.STOCKHISTORY(C32,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>98.61</v>
+        <v>#VALUE!</v>
       </c>
       <c r="P32" s="12">
         <f t="shared" ca="1" si="6"/>
-        <v>9.8610000000000001E-18</v>
+        <v>8.6599999999999986E-18</v>
       </c>
       <c r="Q32" s="12">
         <f t="shared" ca="1" si="7"/>
-        <v>1.2010000000000015E-18</v>
+        <v>0</v>
       </c>
       <c r="R32" s="12">
         <f t="shared" si="8"/>
@@ -7021,17 +6395,17 @@
         <f t="shared" si="5"/>
         <v>7.4002499999999988E-18</v>
       </c>
-      <c r="O33" s="12" cm="1" vm="23">
+      <c r="O33" s="12" t="e" cm="1" vm="1">
         <f t="array" aca="1" ref="O33" ca="1">_xlfn.STOCKHISTORY(C33,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>84.92</v>
+        <v>#VALUE!</v>
       </c>
       <c r="P33" s="12">
         <f t="shared" ca="1" si="6"/>
-        <v>8.4920000000000007E-18</v>
+        <v>6.4349999999999993E-18</v>
       </c>
       <c r="Q33" s="12">
         <f t="shared" ca="1" si="7"/>
-        <v>2.0570000000000015E-18</v>
+        <v>0</v>
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
@@ -7111,17 +6485,17 @@
         <f t="shared" si="5"/>
         <v>1.428771E-17</v>
       </c>
-      <c r="O34" s="12" cm="1" vm="24">
+      <c r="O34" s="12" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="O34" ca="1">_xlfn.STOCKHISTORY(C34,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>155.12</v>
+        <v>#VALUE!</v>
       </c>
       <c r="P34" s="12">
         <f t="shared" ca="1" si="6"/>
-        <v>1.5511999999999999E-17</v>
+        <v>1.3353E-17</v>
       </c>
       <c r="Q34" s="12">
         <f t="shared" ca="1" si="7"/>
-        <v>2.1589999999999991E-18</v>
+        <v>0</v>
       </c>
       <c r="R34" s="12">
         <f t="shared" si="8"/>
@@ -7201,17 +6575,17 @@
         <f t="shared" si="5"/>
         <v>4.2086250000000001E-17</v>
       </c>
-      <c r="O35" s="12" cm="1" vm="25">
+      <c r="O35" s="12" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="O35" ca="1">_xlfn.STOCKHISTORY(C35,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>362.71</v>
+        <v>#VALUE!</v>
       </c>
       <c r="P35" s="12">
         <f t="shared" ca="1" si="6"/>
-        <v>3.6270999999999994E-17</v>
+        <v>3.3669000000000002E-17</v>
       </c>
       <c r="Q35" s="12">
         <f t="shared" ca="1" si="7"/>
-        <v>2.6019999999999928E-18</v>
+        <v>0</v>
       </c>
       <c r="R35" s="12">
         <f t="shared" si="8"/>
@@ -7291,17 +6665,17 @@
         <f t="shared" si="5"/>
         <v>7.0226100000000009E-17</v>
       </c>
-      <c r="O36" s="12" cm="1" vm="26">
+      <c r="O36" s="12" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="O36" ca="1">_xlfn.STOCKHISTORY("LVMH",TODAY()-1,TODAY(),0,0,1)</f>
-        <v>694.9</v>
+        <v>#VALUE!</v>
       </c>
       <c r="P36" s="12">
         <f t="shared" ca="1" si="6"/>
-        <v>6.9489999999999996E-17</v>
+        <v>6.6881999999999999E-17</v>
       </c>
       <c r="Q36" s="12">
         <f t="shared" ca="1" si="7"/>
-        <v>2.6079999999999972E-18</v>
+        <v>0</v>
       </c>
       <c r="R36" s="12">
         <f t="shared" si="8"/>
@@ -7381,17 +6755,17 @@
         <f t="shared" si="5"/>
         <v>2.6148699999999997E-2</v>
       </c>
-      <c r="O37" s="12" cm="1" vm="27">
+      <c r="O37" s="12" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="O37" ca="1">_xlfn.STOCKHISTORY(C37,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>241.84</v>
+        <v>#VALUE!</v>
       </c>
       <c r="P37" s="12">
         <f t="shared" ca="1" si="6"/>
-        <v>2.4184000000000001E-2</v>
+        <v>2.2738000000000001E-2</v>
       </c>
       <c r="Q37" s="12">
         <f t="shared" ca="1" si="7"/>
-        <v>1.4459999999999994E-3</v>
+        <v>0</v>
       </c>
       <c r="R37" s="12">
         <f t="shared" si="8"/>
@@ -7560,17 +6934,17 @@
         <f t="shared" si="5"/>
         <v>11.999099999999999</v>
       </c>
-      <c r="O39" s="12" cm="1" vm="28">
+      <c r="O39" s="12" t="e" cm="1" vm="1">
         <f t="array" aca="1" ref="O39" ca="1">_xlfn.STOCKHISTORY(C39,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>35.54</v>
+        <v>#VALUE!</v>
       </c>
       <c r="P39" s="12">
         <f t="shared" ca="1" si="6"/>
-        <v>10.217749999999999</v>
+        <v>9.99925</v>
       </c>
       <c r="Q39" s="12">
         <f t="shared" ca="1" si="7"/>
-        <v>0.21849999999999881</v>
+        <v>0</v>
       </c>
       <c r="R39" s="12">
         <f t="shared" si="8"/>
@@ -7650,17 +7024,17 @@
         <f t="shared" si="5"/>
         <v>96.105419999999995</v>
       </c>
-      <c r="O40" s="12" cm="1" vm="29">
+      <c r="O40" s="12" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="O40" ca="1">_xlfn.STOCKHISTORY(C40,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>44.73</v>
+        <v>#VALUE!</v>
       </c>
       <c r="P40" s="12">
         <f t="shared" ca="1" si="6"/>
-        <v>89.46</v>
+        <v>88.74</v>
       </c>
       <c r="Q40" s="12">
         <f t="shared" ca="1" si="7"/>
-        <v>0.71999999999999886</v>
+        <v>0</v>
       </c>
       <c r="R40" s="12">
         <f t="shared" si="8"/>
@@ -8097,17 +7471,17 @@
         <f t="shared" si="5"/>
         <v>106.57639814639998</v>
       </c>
-      <c r="O45" s="12" cm="1" vm="30">
+      <c r="O45" s="12" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="O45" ca="1">_xlfn.STOCKHISTORY(C45,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>55.85</v>
+        <v>#VALUE!</v>
       </c>
       <c r="P45" s="12">
         <f t="shared" ca="1" si="6"/>
-        <v>96.877409999999998</v>
+        <v>89.991048000000006</v>
       </c>
       <c r="Q45" s="12">
         <f t="shared" ca="1" si="7"/>
-        <v>6.8863619999999912</v>
+        <v>0</v>
       </c>
       <c r="R45" s="12">
         <f t="shared" si="8"/>
@@ -8292,7 +7666,7 @@
   <dimension ref="A1:BR31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelCol="2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.140625" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.140625" customWidth="1"/>
@@ -8358,132 +7732,132 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="L1" s="57" t="s">
+      <c r="L1" s="58" t="s">
         <v>114</v>
       </c>
-      <c r="M1" s="57"/>
-      <c r="N1" s="57"/>
-      <c r="O1" s="57"/>
-      <c r="P1" s="57"/>
+      <c r="M1" s="58"/>
+      <c r="N1" s="58"/>
+      <c r="O1" s="58"/>
+      <c r="P1" s="58"/>
       <c r="Q1" s="26"/>
-      <c r="R1" s="57" t="s">
+      <c r="R1" s="58" t="s">
         <v>109</v>
       </c>
-      <c r="S1" s="57"/>
-      <c r="V1" s="57" t="s">
+      <c r="S1" s="58"/>
+      <c r="V1" s="58" t="s">
         <v>108</v>
       </c>
-      <c r="W1" s="57"/>
-      <c r="X1" s="57"/>
-      <c r="Y1" s="57"/>
-      <c r="Z1" s="57"/>
-      <c r="AC1" s="57" t="s">
+      <c r="W1" s="58"/>
+      <c r="X1" s="58"/>
+      <c r="Y1" s="58"/>
+      <c r="Z1" s="58"/>
+      <c r="AC1" s="58" t="s">
         <v>108</v>
       </c>
-      <c r="AD1" s="57"/>
-      <c r="AE1" s="57"/>
-      <c r="AF1" s="57"/>
-      <c r="AG1" s="57"/>
-      <c r="AJ1" s="57" t="s">
+      <c r="AD1" s="58"/>
+      <c r="AE1" s="58"/>
+      <c r="AF1" s="58"/>
+      <c r="AG1" s="58"/>
+      <c r="AJ1" s="58" t="s">
         <v>133</v>
       </c>
-      <c r="AK1" s="57"/>
-      <c r="AL1" s="57"/>
-      <c r="AM1" s="57"/>
-      <c r="AN1" s="57"/>
-      <c r="AQ1" s="57" t="s">
+      <c r="AK1" s="58"/>
+      <c r="AL1" s="58"/>
+      <c r="AM1" s="58"/>
+      <c r="AN1" s="58"/>
+      <c r="AQ1" s="58" t="s">
         <v>141</v>
       </c>
-      <c r="AR1" s="57"/>
-      <c r="AS1" s="57"/>
-      <c r="AT1" s="57"/>
-      <c r="AU1" s="57"/>
-      <c r="AV1" s="57"/>
-      <c r="AY1" s="57" t="s">
+      <c r="AR1" s="58"/>
+      <c r="AS1" s="58"/>
+      <c r="AT1" s="58"/>
+      <c r="AU1" s="58"/>
+      <c r="AV1" s="58"/>
+      <c r="AY1" s="58" t="s">
         <v>144</v>
       </c>
-      <c r="AZ1" s="57"/>
-      <c r="BA1" s="57"/>
-      <c r="BB1" s="57"/>
-      <c r="BC1" s="57"/>
-      <c r="BD1" s="57"/>
-      <c r="BE1" s="57"/>
-      <c r="BF1" s="57"/>
+      <c r="AZ1" s="58"/>
+      <c r="BA1" s="58"/>
+      <c r="BB1" s="58"/>
+      <c r="BC1" s="58"/>
+      <c r="BD1" s="58"/>
+      <c r="BE1" s="58"/>
+      <c r="BF1" s="58"/>
       <c r="BG1" s="26"/>
-      <c r="BJ1" s="57" t="s">
+      <c r="BJ1" s="58" t="s">
         <v>146</v>
       </c>
-      <c r="BK1" s="57"/>
-      <c r="BL1" s="57"/>
-      <c r="BM1" s="57"/>
-      <c r="BN1" s="57"/>
-      <c r="BO1" s="57"/>
-      <c r="BP1" s="57"/>
-      <c r="BQ1" s="57"/>
+      <c r="BK1" s="58"/>
+      <c r="BL1" s="58"/>
+      <c r="BM1" s="58"/>
+      <c r="BN1" s="58"/>
+      <c r="BO1" s="58"/>
+      <c r="BP1" s="58"/>
+      <c r="BQ1" s="58"/>
     </row>
     <row r="2" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="L2" s="58">
+      <c r="L2" s="57">
         <v>46000</v>
       </c>
-      <c r="M2" s="58"/>
-      <c r="N2" s="58"/>
-      <c r="O2" s="58"/>
-      <c r="P2" s="58"/>
+      <c r="M2" s="57"/>
+      <c r="N2" s="57"/>
+      <c r="O2" s="57"/>
+      <c r="P2" s="57"/>
       <c r="Q2" s="27"/>
-      <c r="R2" s="58">
+      <c r="R2" s="57">
         <v>45684</v>
       </c>
-      <c r="S2" s="57"/>
-      <c r="V2" s="58">
+      <c r="S2" s="58"/>
+      <c r="V2" s="57">
         <v>45685</v>
       </c>
-      <c r="W2" s="58"/>
-      <c r="X2" s="58"/>
-      <c r="Y2" s="58"/>
-      <c r="Z2" s="58"/>
-      <c r="AC2" s="58">
+      <c r="W2" s="57"/>
+      <c r="X2" s="57"/>
+      <c r="Y2" s="57"/>
+      <c r="Z2" s="57"/>
+      <c r="AC2" s="57">
         <v>45688</v>
       </c>
-      <c r="AD2" s="58"/>
-      <c r="AE2" s="58"/>
-      <c r="AF2" s="58"/>
-      <c r="AG2" s="58"/>
-      <c r="AJ2" s="58">
+      <c r="AD2" s="57"/>
+      <c r="AE2" s="57"/>
+      <c r="AF2" s="57"/>
+      <c r="AG2" s="57"/>
+      <c r="AJ2" s="57">
         <v>45695</v>
       </c>
-      <c r="AK2" s="58"/>
-      <c r="AL2" s="58"/>
-      <c r="AM2" s="58"/>
-      <c r="AN2" s="58"/>
-      <c r="AQ2" s="58">
+      <c r="AK2" s="57"/>
+      <c r="AL2" s="57"/>
+      <c r="AM2" s="57"/>
+      <c r="AN2" s="57"/>
+      <c r="AQ2" s="57">
         <v>45702</v>
       </c>
-      <c r="AR2" s="58"/>
-      <c r="AS2" s="58"/>
-      <c r="AT2" s="58"/>
-      <c r="AU2" s="58"/>
-      <c r="AV2" s="58"/>
-      <c r="AY2" s="58">
+      <c r="AR2" s="57"/>
+      <c r="AS2" s="57"/>
+      <c r="AT2" s="57"/>
+      <c r="AU2" s="57"/>
+      <c r="AV2" s="57"/>
+      <c r="AY2" s="57">
         <v>45711</v>
       </c>
-      <c r="AZ2" s="58"/>
-      <c r="BA2" s="58"/>
-      <c r="BB2" s="58"/>
-      <c r="BC2" s="58"/>
-      <c r="BD2" s="58"/>
-      <c r="BE2" s="58"/>
-      <c r="BF2" s="58"/>
+      <c r="AZ2" s="57"/>
+      <c r="BA2" s="57"/>
+      <c r="BB2" s="57"/>
+      <c r="BC2" s="57"/>
+      <c r="BD2" s="57"/>
+      <c r="BE2" s="57"/>
+      <c r="BF2" s="57"/>
       <c r="BG2" s="27"/>
-      <c r="BJ2" s="58">
+      <c r="BJ2" s="57">
         <v>45716</v>
       </c>
-      <c r="BK2" s="58"/>
-      <c r="BL2" s="58"/>
-      <c r="BM2" s="58"/>
-      <c r="BN2" s="58"/>
-      <c r="BO2" s="58"/>
-      <c r="BP2" s="58"/>
-      <c r="BQ2" s="58"/>
+      <c r="BK2" s="57"/>
+      <c r="BL2" s="57"/>
+      <c r="BM2" s="57"/>
+      <c r="BN2" s="57"/>
+      <c r="BO2" s="57"/>
+      <c r="BP2" s="57"/>
+      <c r="BQ2" s="57"/>
     </row>
     <row r="3" spans="1:70" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
@@ -8860,25 +8234,25 @@
         <v>159</v>
       </c>
       <c r="B5" s="12">
-        <v>322.86463300000003</v>
+        <v>322.86463299999997</v>
       </c>
       <c r="C5" s="22">
         <v>0.26932825223226736</v>
       </c>
       <c r="D5" s="29">
-        <v>0.25160586050160533</v>
+        <v>0.25160586050160538</v>
       </c>
       <c r="E5" s="29">
-        <v>0.15794974174207543</v>
+        <v>0.15794974174207566</v>
       </c>
       <c r="F5" s="12">
-        <v>50.996385399999951</v>
+        <v>50.996385400000065</v>
       </c>
       <c r="G5" s="29">
-        <v>1.8397295314782763E-2</v>
+        <v>1.8397295314783121E-2</v>
       </c>
       <c r="H5" s="12">
-        <v>5.939835999999957</v>
+        <v>5.9398360000000707</v>
       </c>
       <c r="I5" s="12"/>
       <c r="J5" s="12"/>
@@ -9058,10 +8432,10 @@
         <v>35.84854366999997</v>
       </c>
       <c r="G6" s="29">
-        <v>-0.10909914865210661</v>
+        <v>-0.10909914865210643</v>
       </c>
       <c r="H6" s="12">
-        <v>-35.045755000000042</v>
+        <v>-35.045754999999986</v>
       </c>
       <c r="I6" s="12"/>
       <c r="J6" s="12"/>
@@ -9223,28 +8597,28 @@
     </row>
     <row r="7" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A7" s="54" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B7" s="12">
-        <v>59.919476999999993</v>
+        <v>174.92704699999999</v>
       </c>
       <c r="C7" s="22">
-        <v>0.18653226127899014</v>
+        <v>0.54455644924547963</v>
       </c>
       <c r="D7" s="29">
-        <v>0.52980000000000005</v>
+        <v>0.33179893763141161</v>
       </c>
       <c r="E7" s="29">
-        <v>0.12830253842168893</v>
+        <v>0.10969474606176832</v>
       </c>
       <c r="F7" s="12">
-        <v>7.6878210000000067</v>
+        <v>19.188578000000007</v>
       </c>
       <c r="G7" s="29">
-        <v>-0.22051459160766707</v>
+        <v>-0.13390845727819317</v>
       </c>
       <c r="H7" s="12">
-        <v>-13.213118999999999</v>
+        <v>-23.424210999999985</v>
       </c>
       <c r="I7" s="12"/>
       <c r="J7" s="12"/>
@@ -9413,29 +8787,29 @@
       </c>
     </row>
     <row r="8" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A8" s="54" t="s">
-        <v>103</v>
+      <c r="A8" s="59" t="s">
+        <v>46</v>
       </c>
       <c r="B8" s="12">
-        <v>60.019999999999996</v>
+        <v>59.919476999999993</v>
       </c>
       <c r="C8" s="22">
-        <v>0.18684519429241661</v>
+        <v>0.34253980746613755</v>
       </c>
       <c r="D8" s="29">
-        <v>0.2</v>
+        <v>0.52980000000000005</v>
       </c>
       <c r="E8" s="29">
-        <v>9.9999999999999867E-2</v>
+        <v>0.12830253842168893</v>
       </c>
       <c r="F8" s="12">
-        <v>6.0019999999999953</v>
+        <v>7.6878210000000067</v>
       </c>
       <c r="G8" s="29">
-        <v>-0.12574999999999997</v>
+        <v>-0.22051459160766707</v>
       </c>
       <c r="H8" s="12">
-        <v>-7.5475149999999971</v>
+        <v>-13.213118999999999</v>
       </c>
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
@@ -9596,29 +8970,29 @@
       </c>
     </row>
     <row r="9" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A9" s="54" t="s">
-        <v>118</v>
+      <c r="A9" s="59" t="s">
+        <v>103</v>
       </c>
       <c r="B9" s="12">
-        <v>48.68</v>
+        <v>60.019999999999996</v>
       </c>
       <c r="C9" s="22">
-        <v>0.15154321989594871</v>
+        <v>0.34311446416859709</v>
       </c>
       <c r="D9" s="29">
         <v>0.2</v>
       </c>
       <c r="E9" s="29">
-        <v>0.10000000000000009</v>
+        <v>9.9999999999999867E-2</v>
       </c>
       <c r="F9" s="12">
-        <v>4.8680000000000021</v>
+        <v>6.0019999999999953</v>
       </c>
       <c r="G9" s="29">
-        <v>-0.11877567789646665</v>
+        <v>-0.12574999999999997</v>
       </c>
       <c r="H9" s="12">
-        <v>-5.7819999999999965</v>
+        <v>-7.5475149999999971</v>
       </c>
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
@@ -9781,29 +9155,29 @@
       </c>
     </row>
     <row r="10" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A10" s="54" t="s">
-        <v>17</v>
+      <c r="A10" s="59" t="s">
+        <v>27</v>
       </c>
       <c r="B10" s="12">
-        <v>9.9971160000000001</v>
+        <v>54.987569999999998</v>
       </c>
       <c r="C10" s="22">
-        <v>3.1121510852779522E-2</v>
+        <v>0.31434572836526531</v>
       </c>
       <c r="D10" s="29">
-        <v>0.26790000000000003</v>
+        <v>0.25990000000000002</v>
       </c>
       <c r="E10" s="29">
-        <v>2.4701323861801683E-2</v>
+        <v>0.10000000000000009</v>
       </c>
       <c r="F10" s="12">
-        <v>0.24694199999999888</v>
+        <v>5.4987570000000048</v>
       </c>
       <c r="G10" s="29">
-        <v>-8.3629318695511837E-2</v>
+        <v>-4.8439620081411193E-2</v>
       </c>
       <c r="H10" s="12">
-        <v>-0.83605200000000046</v>
+        <v>-2.6635770000000036</v>
       </c>
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
@@ -9965,28 +9339,28 @@
     </row>
     <row r="11" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A11" s="54" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="B11" s="12">
-        <v>67.641508000000002</v>
+        <v>77.638624000000007</v>
       </c>
       <c r="C11" s="22">
-        <v>0.21057132130110051</v>
+        <v>0.24169283215388007</v>
       </c>
       <c r="D11" s="29">
-        <v>0.1963</v>
+        <v>0.20551955424660798</v>
       </c>
       <c r="E11" s="29">
-        <v>0.14999999999999991</v>
+        <v>0.13386595053513539</v>
       </c>
       <c r="F11" s="12">
-        <v>10.146226199999987</v>
+        <v>10.393168199999977</v>
       </c>
       <c r="G11" s="29">
-        <v>-5.7433876252433666E-2</v>
+        <v>-6.0806925171677483E-2</v>
       </c>
       <c r="H11" s="12">
-        <v>-3.884914000000002</v>
+        <v>-4.7209660000000042</v>
       </c>
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
@@ -10148,28 +9522,28 @@
     </row>
     <row r="12" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A12" s="54" t="s">
-        <v>41</v>
+        <v>115</v>
       </c>
       <c r="B12" s="12">
-        <v>19.982821000000001</v>
+        <v>48.68</v>
       </c>
       <c r="C12" s="22">
-        <v>6.2207498704691486E-2</v>
+        <v>0.15154321989594871</v>
       </c>
       <c r="D12" s="29">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="E12" s="29">
-        <v>7.0000000000000062E-2</v>
+        <v>0.10000000000000009</v>
       </c>
       <c r="F12" s="12">
-        <v>1.3987974700000017</v>
+        <v>4.8680000000000021</v>
       </c>
       <c r="G12" s="29">
-        <v>-5.5976981428197542E-2</v>
+        <v>-0.11877567789646665</v>
       </c>
       <c r="H12" s="12">
-        <v>-1.1185779999999959</v>
+        <v>-5.7819999999999965</v>
       </c>
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
@@ -10331,28 +9705,28 @@
     </row>
     <row r="13" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A13" s="54" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="B13" s="12">
-        <v>54.987569999999998</v>
+        <v>19.982821000000001</v>
       </c>
       <c r="C13" s="22">
-        <v>0.17117899367407297</v>
+        <v>6.2207498704691486E-2</v>
       </c>
       <c r="D13" s="29">
-        <v>0.25990000000000002</v>
+        <v>0.4</v>
       </c>
       <c r="E13" s="29">
-        <v>0.10000000000000009</v>
+        <v>7.0000000000000062E-2</v>
       </c>
       <c r="F13" s="12">
-        <v>5.4987570000000048</v>
+        <v>1.3987974700000017</v>
       </c>
       <c r="G13" s="29">
-        <v>-4.8439620081411193E-2</v>
+        <v>-5.5976981428197542E-2</v>
       </c>
       <c r="H13" s="12">
-        <v>-2.6635770000000036</v>
+        <v>-1.1185779999999959</v>
       </c>
       <c r="I13" s="12"/>
       <c r="J13" s="12"/>
@@ -10527,7 +9901,7 @@
         <v>1</v>
       </c>
       <c r="D14" s="29">
-        <v>0.25757527556851989</v>
+        <v>0.25757527556851983</v>
       </c>
       <c r="E14" s="29">
         <v>0.14012188688559091</v>
@@ -10668,16 +10042,16 @@
       </c>
     </row>
     <row r="19" spans="61:69" x14ac:dyDescent="0.25">
-      <c r="BJ19" s="58">
+      <c r="BJ19" s="57">
         <v>45715</v>
       </c>
-      <c r="BK19" s="58"/>
-      <c r="BL19" s="58"/>
-      <c r="BM19" s="58"/>
-      <c r="BN19" s="58"/>
-      <c r="BO19" s="58"/>
-      <c r="BP19" s="58"/>
-      <c r="BQ19" s="58"/>
+      <c r="BK19" s="57"/>
+      <c r="BL19" s="57"/>
+      <c r="BM19" s="57"/>
+      <c r="BN19" s="57"/>
+      <c r="BO19" s="57"/>
+      <c r="BP19" s="57"/>
+      <c r="BQ19" s="57"/>
     </row>
     <row r="20" spans="61:69" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BI20" s="28" t="s">
@@ -10993,6 +10367,12 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="L1:P1"/>
+    <mergeCell ref="L2:P2"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="V2:Z2"/>
+    <mergeCell ref="V1:Z1"/>
     <mergeCell ref="BJ19:BQ19"/>
     <mergeCell ref="BJ1:BQ1"/>
     <mergeCell ref="BJ2:BQ2"/>
@@ -11004,12 +10384,6 @@
     <mergeCell ref="AQ1:AV1"/>
     <mergeCell ref="AJ1:AN1"/>
     <mergeCell ref="AJ2:AN2"/>
-    <mergeCell ref="L1:P1"/>
-    <mergeCell ref="L2:P2"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="V2:Z2"/>
-    <mergeCell ref="V1:Z1"/>
   </mergeCells>
   <conditionalFormatting sqref="K4:K12">
     <cfRule type="colorScale" priority="1">
@@ -11042,7 +10416,7 @@
     <col min="10" max="10" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="0" hidden="1" customWidth="1"/>
+    <col min="29" max="29" width="9.140625" customWidth="1"/>
     <col min="33" max="33" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="10.140625" bestFit="1" customWidth="1"/>
@@ -12483,6 +11857,18 @@
       <c r="X18" t="s">
         <v>150</v>
       </c>
+      <c r="AD18" t="s">
+        <v>124</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>122</v>
+      </c>
+      <c r="AG18" s="29">
+        <v>0.13339999999999999</v>
+      </c>
       <c r="AL18" t="s">
         <v>154</v>
       </c>
@@ -12532,6 +11918,18 @@
       <c r="Y19" t="s">
         <v>151</v>
       </c>
+      <c r="AD19" t="s">
+        <v>124</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>126</v>
+      </c>
+      <c r="AG19" s="29">
+        <v>0.13569999999999999</v>
+      </c>
     </row>
     <row r="20" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
@@ -12578,6 +11976,12 @@
       <c r="Y20" s="29">
         <v>2.5000000000000001E-2</v>
       </c>
+      <c r="AD20" t="s">
+        <v>148</v>
+      </c>
+      <c r="AG20" s="22">
+        <v>0.81</v>
+      </c>
     </row>
     <row r="21" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
@@ -12618,6 +12022,9 @@
       <c r="Y21" s="29">
         <v>8.2000000000000003E-2</v>
       </c>
+      <c r="AD21" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="22" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
@@ -12655,6 +12062,18 @@
       <c r="Y22" s="29">
         <v>3.4000000000000002E-2</v>
       </c>
+      <c r="AD22" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="AE22" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="AF22" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="AG22" s="39" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="23" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B23" s="39" t="s">
@@ -12701,6 +12120,19 @@
       <c r="Y23" s="29">
         <v>2.8000000000000001E-2</v>
       </c>
+      <c r="AD23" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE23" s="34">
+        <v>0.2319</v>
+      </c>
+      <c r="AF23" s="34">
+        <v>6.0100000000000001E-2</v>
+      </c>
+      <c r="AG23" s="34">
+        <f t="shared" ref="AG23:AG32" si="9">AF23-AE23</f>
+        <v>-0.17180000000000001</v>
+      </c>
     </row>
     <row r="24" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B24" s="52" t="s">
@@ -12713,7 +12145,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="53">
-        <f t="shared" ref="E24:E34" si="9">D24-C24</f>
+        <f t="shared" ref="E24:E34" si="10">D24-C24</f>
         <v>-0.22159999999999999</v>
       </c>
       <c r="F24" t="s">
@@ -12750,6 +12182,19 @@
       </c>
       <c r="Y24" s="29">
         <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="AD24" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE24" s="34">
+        <v>5.7200000000000001E-2</v>
+      </c>
+      <c r="AF24" s="34">
+        <v>2.41E-2</v>
+      </c>
+      <c r="AG24" s="34">
+        <f t="shared" si="9"/>
+        <v>-3.3100000000000004E-2</v>
       </c>
     </row>
     <row r="25" spans="2:38" x14ac:dyDescent="0.25">
@@ -12763,7 +12208,7 @@
         <v>8.3099999999999993E-2</v>
       </c>
       <c r="E25" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-0.1381</v>
       </c>
       <c r="M25" s="33" t="s">
@@ -12796,6 +12241,19 @@
         <v>152</v>
       </c>
       <c r="Y25" s="29"/>
+      <c r="AD25" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE25" s="34">
+        <v>0.13170000000000001</v>
+      </c>
+      <c r="AF25" s="34">
+        <v>2.1700000000000001E-2</v>
+      </c>
+      <c r="AG25" s="34">
+        <f t="shared" si="9"/>
+        <v>-0.11000000000000001</v>
+      </c>
     </row>
     <row r="26" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B26" s="37" t="s">
@@ -12808,7 +12266,7 @@
         <v>0.56920000000000004</v>
       </c>
       <c r="E26" s="38">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.36620000000000003</v>
       </c>
       <c r="M26" s="33" t="s">
@@ -12841,6 +12299,19 @@
         <v>153</v>
       </c>
       <c r="Y26" s="29"/>
+      <c r="AD26" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE26" s="34">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="34">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B27" s="35" t="s">
@@ -12853,7 +12324,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-0.23980000000000001</v>
       </c>
       <c r="M27" s="33" t="s">
@@ -12883,19 +12354,32 @@
         <v>0</v>
       </c>
       <c r="Y27" s="29"/>
+      <c r="AD27" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="AE27" s="34">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="34">
+        <v>0.41249999999999998</v>
+      </c>
+      <c r="AG27" s="34">
+        <f t="shared" si="9"/>
+        <v>0.41249999999999998</v>
+      </c>
     </row>
     <row r="28" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B28" s="59" t="s">
+      <c r="B28" s="33" t="s">
         <v>92</v>
       </c>
-      <c r="C28" s="60">
-        <v>0</v>
-      </c>
-      <c r="D28" s="60">
-        <v>0</v>
-      </c>
-      <c r="E28" s="60">
-        <f t="shared" si="9"/>
+      <c r="C28" s="34">
+        <v>0</v>
+      </c>
+      <c r="D28" s="34">
+        <v>0</v>
+      </c>
+      <c r="E28" s="34">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M28" s="33" t="s">
@@ -12925,19 +12409,32 @@
         <v>0.73240000000000005</v>
       </c>
       <c r="Y28" s="29"/>
+      <c r="AD28" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="AE28" s="34">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="34">
+        <v>0.1847</v>
+      </c>
+      <c r="AG28" s="34">
+        <f t="shared" si="9"/>
+        <v>0.1847</v>
+      </c>
     </row>
     <row r="29" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B29" s="59" t="s">
+      <c r="B29" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="C29" s="60">
-        <v>0</v>
-      </c>
-      <c r="D29" s="60">
-        <v>0</v>
-      </c>
-      <c r="E29" s="60">
-        <f t="shared" si="9"/>
+      <c r="C29" s="34">
+        <v>0</v>
+      </c>
+      <c r="D29" s="34">
+        <v>0</v>
+      </c>
+      <c r="E29" s="34">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M29" s="33" t="s">
@@ -12967,20 +12464,32 @@
         <v>0</v>
       </c>
       <c r="Y29" s="29"/>
-      <c r="AE29" s="29"/>
+      <c r="AD29" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="AE29" s="34">
+        <v>1E-4</v>
+      </c>
+      <c r="AF29" s="34">
+        <v>0.12939999999999999</v>
+      </c>
+      <c r="AG29" s="34">
+        <f t="shared" si="9"/>
+        <v>0.1293</v>
+      </c>
     </row>
     <row r="30" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B30" s="59" t="s">
+      <c r="B30" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="C30" s="60">
-        <v>0</v>
-      </c>
-      <c r="D30" s="60">
-        <v>0</v>
-      </c>
-      <c r="E30" s="60">
-        <f t="shared" si="9"/>
+      <c r="C30" s="34">
+        <v>0</v>
+      </c>
+      <c r="D30" s="34">
+        <v>0</v>
+      </c>
+      <c r="E30" s="34">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M30" s="33" t="s">
@@ -13010,20 +12519,32 @@
         <v>0</v>
       </c>
       <c r="Z30" s="29"/>
-      <c r="AE30" s="29"/>
+      <c r="AD30" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="AE30" s="34">
+        <v>0.1174</v>
+      </c>
+      <c r="AF30" s="34">
+        <v>0.13350000000000001</v>
+      </c>
+      <c r="AG30" s="34">
+        <f t="shared" si="9"/>
+        <v>1.6100000000000003E-2</v>
+      </c>
     </row>
     <row r="31" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B31" s="59" t="s">
+      <c r="B31" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="C31" s="60">
-        <v>0</v>
-      </c>
-      <c r="D31" s="60">
-        <v>0</v>
-      </c>
-      <c r="E31" s="60">
-        <f t="shared" si="9"/>
+      <c r="C31" s="34">
+        <v>0</v>
+      </c>
+      <c r="D31" s="34">
+        <v>0</v>
+      </c>
+      <c r="E31" s="34">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M31" s="33" t="s">
@@ -13053,19 +12574,32 @@
         <v>0.2676</v>
       </c>
       <c r="Z31" s="29"/>
+      <c r="AD31" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="AE31" s="34">
+        <v>0.2039</v>
+      </c>
+      <c r="AF31" s="34">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="34">
+        <f t="shared" si="9"/>
+        <v>-0.2039</v>
+      </c>
     </row>
     <row r="32" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B32" s="59" t="s">
+      <c r="B32" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C32" s="60">
-        <v>0</v>
-      </c>
-      <c r="D32" s="60">
-        <v>0</v>
-      </c>
-      <c r="E32" s="60">
-        <f t="shared" si="9"/>
+      <c r="C32" s="34">
+        <v>0</v>
+      </c>
+      <c r="D32" s="34">
+        <v>0</v>
+      </c>
+      <c r="E32" s="34">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M32" s="33" t="s">
@@ -13093,6 +12627,19 @@
       <c r="U32" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
+      </c>
+      <c r="AD32" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE32" s="34">
+        <v>0.25779999999999997</v>
+      </c>
+      <c r="AF32" s="34">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="AG32" s="34">
+        <f t="shared" si="9"/>
+        <v>-0.22379999999999997</v>
       </c>
     </row>
     <row r="33" spans="2:31" x14ac:dyDescent="0.25">
@@ -13106,7 +12653,7 @@
         <v>4.9700000000000001E-2</v>
       </c>
       <c r="E33" s="38">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4.9700000000000001E-2</v>
       </c>
       <c r="M33" s="33" t="s">
@@ -13147,7 +12694,7 @@
         <v>0.29799999999999999</v>
       </c>
       <c r="E34" s="38">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.18359999999999999</v>
       </c>
       <c r="M34" s="33" t="s">
@@ -13452,7 +12999,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="2" id="{F293E84F-3DB7-4B95-8236-67AC7C989194}">
+          <x14:cfRule type="iconSet" priority="3" id="{F293E84F-3DB7-4B95-8236-67AC7C989194}">
             <x14:iconSet iconSet="3Triangles">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13468,7 +13015,7 @@
           <xm:sqref>AA7:AA16 AG7:AG16 AJ7:AJ16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="1" id="{1F0AE9C3-FD1B-466E-A789-59FB1655B3C7}">
+          <x14:cfRule type="iconSet" priority="2" id="{1F0AE9C3-FD1B-466E-A789-59FB1655B3C7}">
             <x14:iconSet iconSet="3Triangles">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13483,6 +13030,22 @@
           </x14:cfRule>
           <xm:sqref>AO7:AO15</xm:sqref>
         </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="1" id="{619D2448-0E18-4AF2-BD93-C4E4CCADB1BB}">
+            <x14:iconSet iconSet="3Triangles">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>AG23:AG32</xm:sqref>
+        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>

--- a/Open Positions.xlsx
+++ b/Open Positions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\StockSillines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88810A78-6E79-4FCB-8BA9-5F96CDB72216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EEFF095-C199-4D08-894E-FDED809218A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,18 +59,11 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="1">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="1"/>
         </ext>
       </extLst>
     </bk>
@@ -80,12 +73,9 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="1">
     <bk>
       <rc t="2" v="0"/>
-    </bk>
-    <bk>
-      <rc t="2" v="1"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -856,14 +846,14 @@
     <xf numFmtId="10" fontId="2" fillId="8" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="2"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -871,199 +861,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="72">
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <alignment wrapText="1"/>
     </dxf>
@@ -2755,7 +2553,7 @@
     <dataField name="Actual P&amp;L " fld="26" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="8">
-    <format dxfId="71">
+    <format dxfId="7">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -2765,7 +2563,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="70">
+    <format dxfId="6">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -2775,7 +2573,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="69">
+    <format dxfId="5">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -2784,7 +2582,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="68">
+    <format dxfId="4">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -2793,7 +2591,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="67">
+    <format dxfId="3">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -2802,7 +2600,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="66">
+    <format dxfId="2">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="5">
@@ -2815,7 +2613,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="65">
+    <format dxfId="1">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="5">
@@ -2828,7 +2626,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="64">
+    <format dxfId="0">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="5">
@@ -2915,17 +2713,18 @@
   <a r="46">
     <v t="e">#NULL!</v>
     <v t="e">#NULL!</v>
-    <v t="r">2</v>
+    <v t="r">1</v>
     <v t="e">#NULL!</v>
     <v t="e">#NULL!</v>
     <v t="e">#NULL!</v>
+    <v t="r">2</v>
     <v t="r">3</v>
     <v t="r">4</v>
     <v t="r">5</v>
-    <v t="r">6</v>
     <v t="e">#NULL!</v>
     <v t="e">#NULL!</v>
     <v t="e">#NULL!</v>
+    <v t="r">6</v>
     <v t="r">7</v>
     <v t="r">8</v>
     <v t="r">9</v>
@@ -2934,8 +2733,8 @@
     <v t="r">12</v>
     <v t="r">13</v>
     <v t="r">14</v>
+    <v t="e">#NULL!</v>
     <v t="r">15</v>
-    <v t="e">#NULL!</v>
     <v t="r">16</v>
     <v t="r">17</v>
     <v t="r">18</v>
@@ -2948,15 +2747,14 @@
     <v t="r">25</v>
     <v t="r">26</v>
     <v t="r">27</v>
+    <v t="e">#NULL!</v>
     <v t="r">28</v>
-    <v t="e">#NULL!</v>
     <v t="r">29</v>
-    <v t="r">30</v>
     <v t="e">#NULL!</v>
     <v t="e">#NULL!</v>
     <v t="e">#NULL!</v>
     <v t="e">#NULL!</v>
-    <v t="r">31</v>
+    <v t="r">30</v>
     <v t="e">#NULL!</v>
     <v t="i">2</v>
   </a>
@@ -2964,11 +2762,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="34">
-  <rv s="0">
-    <v>9</v>
-    <v>1</v>
-  </rv>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="33">
   <rv s="0">
     <v>2</v>
     <v>11</v>
@@ -3100,7 +2894,7 @@
     <v>{8231C5FD-6A38-425A-8202-1B139D24CA84}</v>
     <v>0</v>
     <v>0</v>
-    <v>32</v>
+    <v>31</v>
   </rv>
 </rvData>
 </file>
@@ -4146,7 +3940,7 @@
         <f t="shared" si="5"/>
         <v>80.35399799999999</v>
       </c>
-      <c r="O8" s="12" t="e" cm="1" vm="2">
+      <c r="O8" s="12" t="e" cm="1" vm="1">
         <f t="array" aca="1" ref="O8" ca="1">_xlfn.STOCKHISTORY(C8,TODAY()-1,TODAY(),0,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -4236,7 +4030,7 @@
         <f t="shared" si="5"/>
         <v>86.394189907200001</v>
       </c>
-      <c r="O9" s="12" t="e" cm="1" vm="2">
+      <c r="O9" s="12" t="e" cm="1" vm="1">
         <f t="array" aca="1" ref="O9" ca="1">_xlfn.STOCKHISTORY(C9,TODAY()-1,TODAY(),0,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -4326,7 +4120,7 @@
         <f t="shared" si="5"/>
         <v>21.381618470000003</v>
       </c>
-      <c r="O10" s="12" t="e" cm="1" vm="2">
+      <c r="O10" s="12" t="e" cm="1" vm="1">
         <f t="array" aca="1" ref="O10" ca="1">_xlfn.STOCKHISTORY(C10,TODAY()-1,TODAY(),0,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -4775,7 +4569,7 @@
         <f t="shared" si="5"/>
         <v>3.0171900000000003E-16</v>
       </c>
-      <c r="O15" s="12" t="e" cm="1" vm="2">
+      <c r="O15" s="12" t="e" cm="1" vm="1">
         <f t="array" aca="1" ref="O15" ca="1">_xlfn.STOCKHISTORY(C15,TODAY()-1,TODAY(),0,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -4865,7 +4659,7 @@
         <f t="shared" si="5"/>
         <v>2.16338E-17</v>
       </c>
-      <c r="O16" s="12" t="e" cm="1" vm="2">
+      <c r="O16" s="12" t="e" cm="1" vm="1">
         <f t="array" aca="1" ref="O16" ca="1">_xlfn.STOCKHISTORY(C16,TODAY()-1,TODAY(),0,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -4955,7 +4749,7 @@
         <f t="shared" si="5"/>
         <v>1.6906149999999997E-17</v>
       </c>
-      <c r="O17" s="12" t="e" cm="1" vm="2">
+      <c r="O17" s="12" t="e" cm="1" vm="1">
         <f t="array" aca="1" ref="O17" ca="1">_xlfn.STOCKHISTORY(C17,TODAY()-1,TODAY(),0,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -5045,7 +4839,7 @@
         <f t="shared" si="5"/>
         <v>3.8849999999999999E-17</v>
       </c>
-      <c r="O18" s="12" t="e" cm="1" vm="2">
+      <c r="O18" s="12" t="e" cm="1" vm="1">
         <f t="array" aca="1" ref="O18" ca="1">_xlfn.STOCKHISTORY(C18,TODAY()-1,TODAY(),0,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -5405,7 +5199,7 @@
         <f t="shared" si="5"/>
         <v>1.6451806399999999E-17</v>
       </c>
-      <c r="O22" s="12" t="e" cm="1" vm="2">
+      <c r="O22" s="12" t="e" cm="1" vm="1">
         <f t="array" aca="1" ref="O22" ca="1">_xlfn.STOCKHISTORY(C22,TODAY()-1,TODAY(),0,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -5495,7 +5289,7 @@
         <f t="shared" si="5"/>
         <v>1.16025E-18</v>
       </c>
-      <c r="O23" s="12" t="e" cm="1" vm="2">
+      <c r="O23" s="12" t="e" cm="1" vm="1">
         <f t="array" aca="1" ref="O23" ca="1">_xlfn.STOCKHISTORY(C23,TODAY()-1,TODAY(),0,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -5674,7 +5468,7 @@
         <f t="shared" si="5"/>
         <v>2.1860999999999999E-18</v>
       </c>
-      <c r="O25" s="12" t="e" cm="1" vm="2">
+      <c r="O25" s="12" t="e" cm="1" vm="1">
         <f t="array" aca="1" ref="O25" ca="1">_xlfn.STOCKHISTORY(C25,TODAY()-1,TODAY(),0,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -5764,7 +5558,7 @@
         <f t="shared" si="5"/>
         <v>5.0739400000000001E-18</v>
       </c>
-      <c r="O26" s="12" t="e" cm="1" vm="2">
+      <c r="O26" s="12" t="e" cm="1" vm="1">
         <f t="array" aca="1" ref="O26" ca="1">_xlfn.STOCKHISTORY(C26,TODAY()-1,TODAY(),0,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -5853,7 +5647,7 @@
         <f t="shared" si="5"/>
         <v>2.1199999999999999E-18</v>
       </c>
-      <c r="O27" s="12" t="e" cm="1" vm="2">
+      <c r="O27" s="12" t="e" cm="1" vm="1">
         <f t="array" aca="1" ref="O27" ca="1">_xlfn.STOCKHISTORY(C27,TODAY()-1,TODAY(),0,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -5944,7 +5738,7 @@
         <f t="shared" si="5"/>
         <v>1.2115000000000002E-17</v>
       </c>
-      <c r="O28" s="12" t="e" cm="1" vm="2">
+      <c r="O28" s="12" t="e" cm="1" vm="1">
         <f t="array" aca="1" ref="O28" ca="1">_xlfn.STOCKHISTORY(C28,TODAY()-1,TODAY(),0,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -6305,7 +6099,7 @@
         <f t="shared" si="5"/>
         <v>9.2662000000000008E-18</v>
       </c>
-      <c r="O32" s="12" t="e" cm="1" vm="2">
+      <c r="O32" s="12" t="e" cm="1" vm="1">
         <f t="array" aca="1" ref="O32" ca="1">_xlfn.STOCKHISTORY(C32,TODAY()-1,TODAY(),0,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -6485,7 +6279,7 @@
         <f t="shared" si="5"/>
         <v>1.428771E-17</v>
       </c>
-      <c r="O34" s="12" t="e" cm="1" vm="2">
+      <c r="O34" s="12" t="e" cm="1" vm="1">
         <f t="array" aca="1" ref="O34" ca="1">_xlfn.STOCKHISTORY(C34,TODAY()-1,TODAY(),0,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -6575,7 +6369,7 @@
         <f t="shared" si="5"/>
         <v>4.2086250000000001E-17</v>
       </c>
-      <c r="O35" s="12" t="e" cm="1" vm="2">
+      <c r="O35" s="12" t="e" cm="1" vm="1">
         <f t="array" aca="1" ref="O35" ca="1">_xlfn.STOCKHISTORY(C35,TODAY()-1,TODAY(),0,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -6665,7 +6459,7 @@
         <f t="shared" si="5"/>
         <v>7.0226100000000009E-17</v>
       </c>
-      <c r="O36" s="12" t="e" cm="1" vm="2">
+      <c r="O36" s="12" t="e" cm="1" vm="1">
         <f t="array" aca="1" ref="O36" ca="1">_xlfn.STOCKHISTORY("LVMH",TODAY()-1,TODAY(),0,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -6755,7 +6549,7 @@
         <f t="shared" si="5"/>
         <v>2.6148699999999997E-2</v>
       </c>
-      <c r="O37" s="12" t="e" cm="1" vm="2">
+      <c r="O37" s="12" t="e" cm="1" vm="1">
         <f t="array" aca="1" ref="O37" ca="1">_xlfn.STOCKHISTORY(C37,TODAY()-1,TODAY(),0,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -7024,7 +6818,7 @@
         <f t="shared" si="5"/>
         <v>96.105419999999995</v>
       </c>
-      <c r="O40" s="12" t="e" cm="1" vm="2">
+      <c r="O40" s="12" t="e" cm="1" vm="1">
         <f t="array" aca="1" ref="O40" ca="1">_xlfn.STOCKHISTORY(C40,TODAY()-1,TODAY(),0,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -7471,7 +7265,7 @@
         <f t="shared" si="5"/>
         <v>106.57639814639998</v>
       </c>
-      <c r="O45" s="12" t="e" cm="1" vm="2">
+      <c r="O45" s="12" t="e" cm="1" vm="1">
         <f t="array" aca="1" ref="O45" ca="1">_xlfn.STOCKHISTORY(C45,TODAY()-1,TODAY(),0,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -7796,68 +7590,68 @@
       <c r="BQ1" s="58"/>
     </row>
     <row r="2" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="L2" s="57">
+      <c r="L2" s="59">
         <v>46000</v>
       </c>
-      <c r="M2" s="57"/>
-      <c r="N2" s="57"/>
-      <c r="O2" s="57"/>
-      <c r="P2" s="57"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="59"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="59"/>
       <c r="Q2" s="27"/>
-      <c r="R2" s="57">
+      <c r="R2" s="59">
         <v>45684</v>
       </c>
       <c r="S2" s="58"/>
-      <c r="V2" s="57">
+      <c r="V2" s="59">
         <v>45685</v>
       </c>
-      <c r="W2" s="57"/>
-      <c r="X2" s="57"/>
-      <c r="Y2" s="57"/>
-      <c r="Z2" s="57"/>
-      <c r="AC2" s="57">
+      <c r="W2" s="59"/>
+      <c r="X2" s="59"/>
+      <c r="Y2" s="59"/>
+      <c r="Z2" s="59"/>
+      <c r="AC2" s="59">
         <v>45688</v>
       </c>
-      <c r="AD2" s="57"/>
-      <c r="AE2" s="57"/>
-      <c r="AF2" s="57"/>
-      <c r="AG2" s="57"/>
-      <c r="AJ2" s="57">
+      <c r="AD2" s="59"/>
+      <c r="AE2" s="59"/>
+      <c r="AF2" s="59"/>
+      <c r="AG2" s="59"/>
+      <c r="AJ2" s="59">
         <v>45695</v>
       </c>
-      <c r="AK2" s="57"/>
-      <c r="AL2" s="57"/>
-      <c r="AM2" s="57"/>
-      <c r="AN2" s="57"/>
-      <c r="AQ2" s="57">
+      <c r="AK2" s="59"/>
+      <c r="AL2" s="59"/>
+      <c r="AM2" s="59"/>
+      <c r="AN2" s="59"/>
+      <c r="AQ2" s="59">
         <v>45702</v>
       </c>
-      <c r="AR2" s="57"/>
-      <c r="AS2" s="57"/>
-      <c r="AT2" s="57"/>
-      <c r="AU2" s="57"/>
-      <c r="AV2" s="57"/>
-      <c r="AY2" s="57">
+      <c r="AR2" s="59"/>
+      <c r="AS2" s="59"/>
+      <c r="AT2" s="59"/>
+      <c r="AU2" s="59"/>
+      <c r="AV2" s="59"/>
+      <c r="AY2" s="59">
         <v>45711</v>
       </c>
-      <c r="AZ2" s="57"/>
-      <c r="BA2" s="57"/>
-      <c r="BB2" s="57"/>
-      <c r="BC2" s="57"/>
-      <c r="BD2" s="57"/>
-      <c r="BE2" s="57"/>
-      <c r="BF2" s="57"/>
+      <c r="AZ2" s="59"/>
+      <c r="BA2" s="59"/>
+      <c r="BB2" s="59"/>
+      <c r="BC2" s="59"/>
+      <c r="BD2" s="59"/>
+      <c r="BE2" s="59"/>
+      <c r="BF2" s="59"/>
       <c r="BG2" s="27"/>
-      <c r="BJ2" s="57">
+      <c r="BJ2" s="59">
         <v>45716</v>
       </c>
-      <c r="BK2" s="57"/>
-      <c r="BL2" s="57"/>
-      <c r="BM2" s="57"/>
-      <c r="BN2" s="57"/>
-      <c r="BO2" s="57"/>
-      <c r="BP2" s="57"/>
-      <c r="BQ2" s="57"/>
+      <c r="BK2" s="59"/>
+      <c r="BL2" s="59"/>
+      <c r="BM2" s="59"/>
+      <c r="BN2" s="59"/>
+      <c r="BO2" s="59"/>
+      <c r="BP2" s="59"/>
+      <c r="BQ2" s="59"/>
     </row>
     <row r="3" spans="1:70" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
@@ -8787,7 +8581,7 @@
       </c>
     </row>
     <row r="8" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A8" s="59" t="s">
+      <c r="A8" s="57" t="s">
         <v>46</v>
       </c>
       <c r="B8" s="12">
@@ -8970,7 +8764,7 @@
       </c>
     </row>
     <row r="9" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A9" s="59" t="s">
+      <c r="A9" s="57" t="s">
         <v>103</v>
       </c>
       <c r="B9" s="12">
@@ -9155,7 +8949,7 @@
       </c>
     </row>
     <row r="10" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A10" s="59" t="s">
+      <c r="A10" s="57" t="s">
         <v>27</v>
       </c>
       <c r="B10" s="12">
@@ -10042,16 +9836,16 @@
       </c>
     </row>
     <row r="19" spans="61:69" x14ac:dyDescent="0.25">
-      <c r="BJ19" s="57">
+      <c r="BJ19" s="59">
         <v>45715</v>
       </c>
-      <c r="BK19" s="57"/>
-      <c r="BL19" s="57"/>
-      <c r="BM19" s="57"/>
-      <c r="BN19" s="57"/>
-      <c r="BO19" s="57"/>
-      <c r="BP19" s="57"/>
-      <c r="BQ19" s="57"/>
+      <c r="BK19" s="59"/>
+      <c r="BL19" s="59"/>
+      <c r="BM19" s="59"/>
+      <c r="BN19" s="59"/>
+      <c r="BO19" s="59"/>
+      <c r="BP19" s="59"/>
+      <c r="BQ19" s="59"/>
     </row>
     <row r="20" spans="61:69" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BI20" s="28" t="s">
@@ -10367,12 +10161,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="L1:P1"/>
-    <mergeCell ref="L2:P2"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="V2:Z2"/>
-    <mergeCell ref="V1:Z1"/>
     <mergeCell ref="BJ19:BQ19"/>
     <mergeCell ref="BJ1:BQ1"/>
     <mergeCell ref="BJ2:BQ2"/>
@@ -10384,6 +10172,12 @@
     <mergeCell ref="AQ1:AV1"/>
     <mergeCell ref="AJ1:AN1"/>
     <mergeCell ref="AJ2:AN2"/>
+    <mergeCell ref="L1:P1"/>
+    <mergeCell ref="L2:P2"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="V2:Z2"/>
+    <mergeCell ref="V1:Z1"/>
   </mergeCells>
   <conditionalFormatting sqref="K4:K12">
     <cfRule type="colorScale" priority="1">
@@ -13015,6 +12809,22 @@
           <xm:sqref>AA7:AA16 AG7:AG16 AJ7:AJ16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="1" id="{619D2448-0E18-4AF2-BD93-C4E4CCADB1BB}">
+            <x14:iconSet iconSet="3Triangles">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>AG23:AG32</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="2" id="{1F0AE9C3-FD1B-466E-A789-59FB1655B3C7}">
             <x14:iconSet iconSet="3Triangles">
               <x14:cfvo type="percent">
@@ -13030,22 +12840,6 @@
           </x14:cfRule>
           <xm:sqref>AO7:AO15</xm:sqref>
         </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="1" id="{619D2448-0E18-4AF2-BD93-C4E4CCADB1BB}">
-            <x14:iconSet iconSet="3Triangles">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>AG23:AG32</xm:sqref>
-        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>

--- a/Open Positions.xlsx
+++ b/Open Positions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\StockSillines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8588A19-82A3-450B-9644-C77A281B7300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{449F2CD4-2E8C-4E15-B1AF-0A03AD688E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,68 +21,20 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Positions!$A$1:$X$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet1!$R$5:$U$42</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <pivotCaches>
-    <pivotCache cacheId="24" r:id="rId4"/>
+    <pivotCache cacheId="10" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="2">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="2" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="165">
   <si>
     <t>Name</t>
   </si>
@@ -587,7 +539,7 @@
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    <numFmt numFmtId="168" formatCode="0.000%"/>
+    <numFmt numFmtId="166" formatCode="0.000%"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -853,14 +805,14 @@
     <xf numFmtId="10" fontId="2" fillId="8" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -868,7 +820,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="392">
+  <dxfs count="24">
     <dxf>
       <alignment vertical="center"/>
     </dxf>
@@ -918,10 +870,13 @@
       <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment vertical="center"/>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
@@ -933,1117 +888,10 @@
       <numFmt numFmtId="14" formatCode="0.00%"/>
     </dxf>
     <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
       <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2059,7 +907,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" invalid="1" refreshedBy="samuel walton" refreshedDate="45725.944448032409" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="45" xr:uid="{35F6D15B-8E6D-4C09-9E31-06CBD6981C37}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="samuel walton" refreshedDate="45729.834199421297" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="45" xr:uid="{35F6D15B-8E6D-4C09-9E31-06CBD6981C37}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:X46" sheet="Positions"/>
   </cacheSource>
@@ -2087,17 +935,18 @@
         <s v="MO"/>
         <s v="VWO.US"/>
         <s v="PEP"/>
+        <s v="APA"/>
+        <s v="FSLR"/>
         <s v="KMB"/>
         <s v="MSFT"/>
-        <s v="APA"/>
         <s v="MA"/>
         <s v="YPF"/>
-        <s v="FSLR"/>
         <s v="NEE"/>
         <s v="ING"/>
         <s v="VBTC.DE"/>
         <s v="INGR"/>
         <s v="BOTZ.UK"/>
+        <s v="ACI"/>
         <s v="BATT.NL"/>
         <s v="EXC"/>
         <s v="DAR"/>
@@ -2119,6 +968,7 @@
         <s v="WMT"/>
         <s v="PLTR"/>
         <s v="APTV"/>
+        <s v="BONDS"/>
         <s v="YUMC"/>
         <s v="PCG"/>
         <s v="JKS"/>
@@ -2126,24 +976,22 @@
         <s v="SWI"/>
         <s v="CSIQ"/>
         <s v="MAXN"/>
-        <s v="BONDS"/>
-        <s v="ACI"/>
         <m u="1"/>
         <s v="LVMH" u="1"/>
       </sharedItems>
       <fieldGroup par="29"/>
     </cacheField>
     <cacheField name="Date" numFmtId="165">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2024-06-17T00:00:00" maxDate="2025-02-17T00:00:00"/>
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2024-06-17T00:00:00" maxDate="2025-02-22T00:00:00"/>
     </cacheField>
     <cacheField name="Volume" numFmtId="164">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="9.9999999999999998E-20" maxValue="3.1236000000000002"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="9.9999999999999998E-20" maxValue="3.8043"/>
     </cacheField>
     <cacheField name="Price" numFmtId="44">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="10.92" maxValue="2742.9"/>
     </cacheField>
     <cacheField name="Value" numFmtId="44">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="1.092E-18" maxValue="112.93678800000001"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="1.092E-18" maxValue="127.927404"/>
     </cacheField>
     <cacheField name="Expected Return QoQ%" numFmtId="10">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="2.4701323861801683E-2" maxValue="1"/>
@@ -2155,25 +1003,25 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="6.7668155366084726E-2" maxValue="1"/>
     </cacheField>
     <cacheField name="Mix %" numFmtId="9">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.2815488729667341E-3" maxValue="4.8494729244702391E-2"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.2462885036855945E-3" maxValue="4.7973651507465707E-2"/>
     </cacheField>
     <cacheField name="W/Avg Volatility" numFmtId="9">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="2.5499999999999999E-19" maxValue="41.786611560000004"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="2.5499999999999999E-19" maxValue="47.33313948"/>
     </cacheField>
     <cacheField name="Target Price" numFmtId="44">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="11.602500000000001" maxValue="3017.1900000000005"/>
     </cacheField>
     <cacheField name="Target Value" numFmtId="44">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="1.16025E-18" maxValue="137.94084000000001"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="1.16025E-18" maxValue="157.79285999999999"/>
     </cacheField>
     <cacheField name="Close Price" numFmtId="44">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.56679999999999997" maxValue="732.22"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="10.92" maxValue="2742.9"/>
     </cacheField>
     <cacheField name="Actual Value" numFmtId="44">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="5.6679999999999994E-20" maxValue="107.180154"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="1.092E-18" maxValue="119.045484"/>
     </cacheField>
     <cacheField name="Actual P&amp;L" numFmtId="44">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-12.050806000000001" maxValue="14.868336000000006"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-15.122651000000005" maxValue="11.775971999999996"/>
     </cacheField>
     <cacheField name="Tolerance" numFmtId="44">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="5.8546000428908433" maxValue="1959.214285714286"/>
@@ -2191,7 +1039,7 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="231.68530222404101"/>
     </cacheField>
     <cacheField name="Risk Mix" numFmtId="9">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="3.1618826437462423E-2"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="3.161882643746243E-2"/>
     </cacheField>
     <cacheField name="Normalized Risk %" numFmtId="9">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="1"/>
@@ -2208,6 +1056,8 @@
           <x v="3"/>
           <x v="3"/>
           <x v="3"/>
+          <x v="2"/>
+          <x v="2"/>
           <x v="3"/>
           <x v="3"/>
           <x v="2"/>
@@ -2216,9 +1066,8 @@
           <x v="2"/>
           <x v="2"/>
           <x v="2"/>
+          <x v="3"/>
           <x v="2"/>
-          <x v="2"/>
-          <x v="3"/>
           <x v="3"/>
           <x v="2"/>
           <x v="2"/>
@@ -2240,14 +1089,13 @@
           <x v="3"/>
           <x v="2"/>
           <x v="3"/>
+          <x v="3"/>
           <x v="2"/>
           <x v="2"/>
           <x v="2"/>
           <x v="3"/>
           <x v="2"/>
           <x v="2"/>
-          <x v="2"/>
-          <x v="3"/>
           <x v="2"/>
           <x v="1"/>
           <x v="0"/>
@@ -2265,16 +1113,1186 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
       <x14:pivotCacheDefinition/>
     </ext>
-    <ext xmlns:xxpvi="http://schemas.microsoft.com/office/spreadsheetml/2022/pivotVersionInfo" uri="{9F748A41-CAEA-4470-BF7A-CE61E8FFA7F9}">
-      <xxpvi:cacheVersionInfo>
-        <xxpvi:lastRefreshFeature>RichData</xxpvi:lastRefreshFeature>
-      </xxpvi:cacheVersionInfo>
-    </ext>
     <ext xmlns:xprd="http://schemas.microsoft.com/office/spreadsheetml/2022/pivotRichData" uri="{2C874A73-7782-4A18-856F-96AC7E287872}">
-      <xprd:richInfo pivotCacheGuid="{35F6D15B-8E6D-4C09-9E31-06CBD6981C37}" pivotIgnoreInvalidCache="1" r:id="rId1"/>
+      <xprd:richInfo pivotCacheGuid="{35F6D15B-8E6D-4C09-9E31-06CBD6981C37}" pivotIgnoreInvalidCache="1" r:id="rId2"/>
     </ext>
   </extLst>
 </pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="45">
+  <r>
+    <x v="0"/>
+    <s v="TSMC"/>
+    <x v="0"/>
+    <d v="2024-07-11T00:00:00"/>
+    <n v="0.69389999999999996"/>
+    <n v="184.36"/>
+    <n v="127.927404"/>
+    <n v="0.23345628118897799"/>
+    <n v="0.37"/>
+    <n v="0.63096292213237293"/>
+    <n v="3.0269595340510682E-2"/>
+    <n v="47.33313948"/>
+    <n v="227.4"/>
+    <n v="157.79285999999999"/>
+    <n v="171.56"/>
+    <n v="119.045484"/>
+    <n v="-8.8819199999999938"/>
+    <n v="162.21109399369644"/>
+    <n v="43.039999999999992"/>
+    <n v="-11.074453003151788"/>
+    <n v="31.965546996848204"/>
+    <n v="82.166898084336182"/>
+    <n v="1.2170351118446738E-2"/>
+    <n v="0.35464872952916249"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Altaria"/>
+    <x v="1"/>
+    <d v="2024-09-18T00:00:00"/>
+    <n v="1.7345999999999999"/>
+    <n v="51.88"/>
+    <n v="89.991048000000006"/>
+    <n v="0.18430000000000002"/>
+    <n v="0.19980000000000001"/>
+    <n v="0.92242242242242245"/>
+    <n v="4.4251971835965617E-2"/>
+    <n v="17.980211390400001"/>
+    <n v="61.441483999999996"/>
+    <n v="106.57639814639998"/>
+    <n v="58.55"/>
+    <n v="101.56083"/>
+    <n v="11.569781999999989"/>
+    <n v="51.088133924175295"/>
+    <n v="9.561483999999993"/>
+    <n v="-0.39593303791235357"/>
+    <n v="9.1655509620876394"/>
+    <n v="104.96689411909675"/>
+    <n v="9.526813271862531E-3"/>
+    <n v="0.45305806242984359"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="Emergin Markets"/>
+    <x v="2"/>
+    <d v="2025-01-31T00:00:00"/>
+    <n v="2"/>
+    <n v="44.37"/>
+    <n v="88.74"/>
+    <n v="8.3000000000000004E-2"/>
+    <n v="0.16800000000000001"/>
+    <n v="0.49404761904761907"/>
+    <n v="2.3701268304283655E-2"/>
+    <n v="14.90832"/>
+    <n v="48.052709999999998"/>
+    <n v="96.105419999999995"/>
+    <n v="45.24"/>
+    <n v="90.48"/>
+    <n v="1.7400000000000091"/>
+    <n v="40.894009216589858"/>
+    <n v="3.6827100000000002"/>
+    <n v="-1.7379953917050699"/>
+    <n v="1.9447146082949303"/>
+    <n v="112.18773047288946"/>
+    <n v="8.9136307133127479E-3"/>
+    <n v="0.4842246331379419"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Pepsi"/>
+    <x v="3"/>
+    <d v="2024-06-17T00:00:00"/>
+    <n v="0.51239999999999997"/>
+    <n v="157.99"/>
+    <n v="80.954076000000001"/>
+    <n v="6.7199999999999996E-2"/>
+    <n v="0.16439999999999999"/>
+    <n v="0.40875912408759124"/>
+    <n v="1.9609667769475037E-2"/>
+    <n v="13.308850094399999"/>
+    <n v="168.60692800000001"/>
+    <n v="86.394189907200001"/>
+    <n v="148.28"/>
+    <n v="75.978671999999989"/>
+    <n v="-4.9754040000000117"/>
+    <n v="143.99380240612467"/>
+    <n v="10.616928000000001"/>
+    <n v="-6.9980987969376685"/>
+    <n v="3.618829203062333"/>
+    <n v="110.51361587812205"/>
+    <n v="9.0486587743435331E-3"/>
+    <n v="0.47699882045713349"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="APA"/>
+    <x v="4"/>
+    <d v="2024-12-01T00:00:00"/>
+    <n v="3.8043"/>
+    <n v="21.02"/>
+    <n v="79.966386"/>
+    <n v="0.26450999048525214"/>
+    <n v="0.45929999999999999"/>
+    <n v="0.57589808509743556"/>
+    <n v="2.7627934038281204E-2"/>
+    <n v="36.728561089799996"/>
+    <n v="26.58"/>
+    <n v="101.11829399999999"/>
+    <n v="19.010000000000002"/>
+    <n v="72.319743000000003"/>
+    <n v="-7.6466429999999974"/>
+    <n v="17.593049684552572"/>
+    <n v="5.5599999999999987"/>
+    <n v="-1.7134751577237139"/>
+    <n v="3.8465248422762848"/>
+    <n v="110.2859202389081"/>
+    <n v="9.0673405801369646E-3"/>
+    <n v="0.47601604063887054"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="First Solar"/>
+    <x v="5"/>
+    <d v="2024-08-07T00:00:00"/>
+    <n v="0.48830000000000001"/>
+    <n v="163.65"/>
+    <n v="79.910295000000005"/>
+    <n v="0.19780018331805693"/>
+    <n v="0.52980000000000005"/>
+    <n v="0.37334877938478089"/>
+    <n v="1.7910904232943177E-2"/>
+    <n v="42.336474291000009"/>
+    <n v="196.02"/>
+    <n v="95.716566"/>
+    <n v="132.68"/>
+    <n v="64.787644"/>
+    <n v="-15.122651000000005"/>
+    <n v="122.86037726916339"/>
+    <n v="32.370000000000005"/>
+    <n v="-20.394811365418306"/>
+    <n v="11.975188634581698"/>
+    <n v="102.15725644660269"/>
+    <n v="9.7888298372881336E-3"/>
+    <n v="0.44093110553821857"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Kimberly Clark"/>
+    <x v="6"/>
+    <d v="2024-09-09T00:00:00"/>
+    <n v="0.51380000000000003"/>
+    <n v="138.53"/>
+    <n v="71.176714000000004"/>
+    <n v="7.0000000000000007E-2"/>
+    <n v="0.18340000000000001"/>
+    <n v="0.38167938931297712"/>
+    <n v="1.8310554010483097E-2"/>
+    <n v="13.053809347600001"/>
+    <n v="148.22710000000001"/>
+    <n v="76.159083980000005"/>
+    <n v="140.03"/>
+    <n v="71.947414000000009"/>
+    <n v="0.77070000000000505"/>
+    <n v="124.42069337165439"/>
+    <n v="9.697100000000006"/>
+    <n v="-7.0546533141728034"/>
+    <n v="2.6424466858272027"/>
+    <n v="111.48999839535719"/>
+    <n v="8.969414426340536E-3"/>
+    <n v="0.48121308225044729"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="Microsoft"/>
+    <x v="7"/>
+    <d v="2024-10-09T00:00:00"/>
+    <n v="0.16059999999999999"/>
+    <n v="421.18"/>
+    <n v="67.641508000000002"/>
+    <n v="0.15"/>
+    <n v="0.1963"/>
+    <n v="0.76413652572592972"/>
+    <n v="3.665841938930136E-2"/>
+    <n v="13.278028020400001"/>
+    <n v="484.35699999999997"/>
+    <n v="77.787734199999989"/>
+    <n v="378.78"/>
+    <n v="60.832067999999992"/>
+    <n v="-6.8094400000000093"/>
+    <n v="402.54229188569246"/>
+    <n v="63.176999999999964"/>
+    <n v="-9.3188540571537715"/>
+    <n v="53.858145942846193"/>
+    <n v="60.274299138338193"/>
+    <n v="1.6590819209773903E-2"/>
+    <n v="0.26015590354563189"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="Master Card"/>
+    <x v="8"/>
+    <d v="2024-08-07T00:00:00"/>
+    <n v="0.12939999999999999"/>
+    <n v="501.56"/>
+    <n v="64.901863999999989"/>
+    <n v="0.25"/>
+    <n v="0.29699999999999999"/>
+    <n v="0.84175084175084181"/>
+    <n v="4.0381861538270801E-2"/>
+    <n v="19.275853607999995"/>
+    <n v="626.95000000000005"/>
+    <n v="81.127330000000001"/>
+    <n v="519.39"/>
+    <n v="67.209065999999993"/>
+    <n v="2.3072020000000037"/>
+    <n v="479.04489016236869"/>
+    <n v="125.39000000000004"/>
+    <n v="-11.257554918815657"/>
+    <n v="114.13244508118439"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="YPF"/>
+    <x v="9"/>
+    <d v="2024-12-01T00:00:00"/>
+    <n v="1.5004999999999999"/>
+    <n v="40"/>
+    <n v="60.019999999999996"/>
+    <n v="0.1"/>
+    <n v="0.2"/>
+    <n v="0.5"/>
+    <n v="2.3986825753732854E-2"/>
+    <n v="12.004"/>
+    <n v="44"/>
+    <n v="66.021999999999991"/>
+    <n v="33.67"/>
+    <n v="50.521835000000003"/>
+    <n v="-9.4981649999999931"/>
+    <n v="36.363636363636367"/>
+    <n v="4"/>
+    <n v="-1.8181818181818166"/>
+    <n v="2.1818181818181834"/>
+    <n v="111.9506268993662"/>
+    <n v="8.9325091577996465E-3"/>
+    <n v="0.48320124679773302"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="NextEra Energy"/>
+    <x v="10"/>
+    <d v="2024-08-07T00:00:00"/>
+    <n v="0.74609999999999999"/>
+    <n v="73.7"/>
+    <n v="54.987569999999998"/>
+    <n v="0.1"/>
+    <n v="0.25990000000000002"/>
+    <n v="0.38476337052712584"/>
+    <n v="1.8458503850506239E-2"/>
+    <n v="14.291269443000001"/>
+    <n v="81.070000000000007"/>
+    <n v="60.486327000000003"/>
+    <n v="72.709999999999994"/>
+    <n v="54.248930999999992"/>
+    <n v="-0.73863900000000626"/>
+    <n v="63.539960341408751"/>
+    <n v="7.3700000000000045"/>
+    <n v="-5.080019829295626"/>
+    <n v="2.2899801707043785"/>
+    <n v="111.84246491048"/>
+    <n v="8.9411477188061934E-3"/>
+    <n v="0.48273439806866858"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="ING Group NV"/>
+    <x v="11"/>
+    <d v="2024-11-27T00:00:00"/>
+    <n v="3.1236000000000002"/>
+    <n v="16"/>
+    <n v="49.977600000000002"/>
+    <n v="0.35"/>
+    <n v="0.39532299999999998"/>
+    <n v="0.88535197800279775"/>
+    <n v="4.2473567254151669E-2"/>
+    <n v="19.757294764800001"/>
+    <n v="21.6"/>
+    <n v="67.469760000000008"/>
+    <n v="19.77"/>
+    <n v="61.753571999999998"/>
+    <n v="11.775971999999996"/>
+    <n v="15.306273754619388"/>
+    <n v="5.6000000000000014"/>
+    <n v="-0.34686312269030584"/>
+    <n v="5.2531368773096956"/>
+    <n v="108.87930820387469"/>
+    <n v="9.1844815741069612E-3"/>
+    <n v="0.46994482238924146"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="Bitcoin ETF"/>
+    <x v="12"/>
+    <d v="2024-07-08T00:00:00"/>
+    <n v="1"/>
+    <n v="48.68"/>
+    <n v="48.68"/>
+    <n v="0.1"/>
+    <n v="0.2"/>
+    <n v="0.5"/>
+    <n v="2.3986825753732854E-2"/>
+    <n v="9.7360000000000007"/>
+    <n v="53.548000000000002"/>
+    <n v="53.548000000000002"/>
+    <n v="39.76"/>
+    <n v="39.76"/>
+    <n v="-8.9200000000000017"/>
+    <n v="44.254545454545458"/>
+    <n v="4.8680000000000021"/>
+    <n v="-2.2127272727272711"/>
+    <n v="2.655272727272731"/>
+    <n v="111.47717235391166"/>
+    <n v="8.9704464051640499E-3"/>
+    <n v="0.48115772249597688"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <s v="Ingredion"/>
+    <x v="13"/>
+    <d v="2024-10-15T00:00:00"/>
+    <n v="0.34860000000000002"/>
+    <n v="131.91"/>
+    <n v="45.983826000000001"/>
+    <n v="0.1202"/>
+    <n v="0.33710000000000001"/>
+    <n v="0.35657075051913378"/>
+    <n v="1.7106000923160423E-2"/>
+    <n v="15.501147744600001"/>
+    <n v="147.76558199999999"/>
+    <n v="51.511081885199999"/>
+    <n v="130.51"/>
+    <n v="45.495786000000003"/>
+    <n v="-0.48803999999999803"/>
+    <n v="108.39838934998768"/>
+    <n v="15.855581999999998"/>
+    <n v="-11.755805325006158"/>
+    <n v="4.0997766749938407"/>
+    <n v="110.03266840619054"/>
+    <n v="9.0882100242125827E-3"/>
+    <n v="0.47492295518939875"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="Robotics &amp; AI"/>
+    <x v="14"/>
+    <d v="2024-07-08T00:00:00"/>
+    <n v="2"/>
+    <n v="20.927"/>
+    <n v="41.853999999999999"/>
+    <n v="3.5000000000000003E-2"/>
+    <n v="0.16500000000000001"/>
+    <n v="0.21212121212121213"/>
+    <n v="1.0176229107644243E-2"/>
+    <n v="6.9059100000000004"/>
+    <n v="21.659444999999998"/>
+    <n v="43.318889999999996"/>
+    <n v="19.579999999999998"/>
+    <n v="39.159999999999997"/>
+    <n v="-2.6940000000000026"/>
+    <n v="18.51946902654867"/>
+    <n v="0.73244499999999846"/>
+    <n v="-1.2037654867256649"/>
+    <n v="-0.4713204867256664"/>
+    <n v="114.60376556791005"/>
+    <n v="8.7257167776693713E-3"/>
+    <n v="0.49465272275704203"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Albertson Companies"/>
+    <x v="15"/>
+    <d v="2024-12-04T00:00:00"/>
+    <n v="2"/>
+    <n v="20.5"/>
+    <n v="41"/>
+    <n v="0.2"/>
+    <n v="0.2"/>
+    <n v="1"/>
+    <n v="4.7973651507465707E-2"/>
+    <n v="8.2000000000000011"/>
+    <n v="24.599999999999998"/>
+    <n v="49.199999999999996"/>
+    <n v="21.17"/>
+    <n v="42.34"/>
+    <n v="1.3400000000000034"/>
+    <n v="20.5"/>
+    <n v="4.0999999999999979"/>
+    <n v="0"/>
+    <n v="4.0999999999999979"/>
+    <n v="110.03244508118439"/>
+    <n v="9.0882284699042876E-3"/>
+    <n v="0.47492199127410506"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="Batterey Value-Chain"/>
+    <x v="16"/>
+    <d v="2024-07-08T00:00:00"/>
+    <n v="2"/>
+    <n v="16.399000000000001"/>
+    <n v="32.798000000000002"/>
+    <n v="3.5000000000000003E-2"/>
+    <n v="0.16500000000000001"/>
+    <n v="0.21212121212121213"/>
+    <n v="1.0176229107644243E-2"/>
+    <n v="5.4116700000000009"/>
+    <n v="16.972964999999999"/>
+    <n v="33.945929999999997"/>
+    <n v="15.192"/>
+    <n v="30.384"/>
+    <n v="-2.4140000000000015"/>
+    <n v="14.512389380530973"/>
+    <n v="0.57396499999999762"/>
+    <n v="-0.9433053097345141"/>
+    <n v="-0.36934030973451648"/>
+    <n v="114.5017853909189"/>
+    <n v="8.733488273444074E-3"/>
+    <n v="0.49421255596177188"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="Excelon"/>
+    <x v="17"/>
+    <d v="2024-12-01T00:00:00"/>
+    <n v="0.75290000000000001"/>
+    <n v="41.16"/>
+    <n v="30.989363999999998"/>
+    <n v="0.1"/>
+    <n v="0.2"/>
+    <n v="0.5"/>
+    <n v="2.3986825753732854E-2"/>
+    <n v="6.1978727999999998"/>
+    <n v="45.276000000000003"/>
+    <n v="34.088300400000001"/>
+    <n v="43.47"/>
+    <n v="32.728563000000001"/>
+    <n v="1.7391990000000028"/>
+    <n v="37.418181818181822"/>
+    <n v="4.1160000000000068"/>
+    <n v="-1.8709090909090875"/>
+    <n v="2.2450909090909192"/>
+    <n v="111.88735417209347"/>
+    <n v="8.9375605259366872E-3"/>
+    <n v="0.48292814907998677"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <s v="MSG"/>
+    <x v="18"/>
+    <d v="2024-08-03T00:00:00"/>
+    <n v="0.52270000000000005"/>
+    <n v="38.229999999999997"/>
+    <n v="19.982821000000001"/>
+    <n v="7.0000000000000007E-2"/>
+    <n v="0.4"/>
+    <n v="0.17500000000000002"/>
+    <n v="8.3953890138065007E-3"/>
+    <n v="7.9931284000000007"/>
+    <n v="40.906100000000002"/>
+    <n v="21.381618470000003"/>
+    <n v="28.49"/>
+    <n v="14.891723000000001"/>
+    <n v="-5.0910980000000006"/>
+    <n v="28.744360902255639"/>
+    <n v="2.6761000000000053"/>
+    <n v="-4.7428195488721787"/>
+    <n v="-2.0667195488721735"/>
+    <n v="116.19916463005656"/>
+    <n v="8.6059138478637217E-3"/>
+    <n v="0.50153878349042313"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <s v="Agios"/>
+    <x v="19"/>
+    <d v="2024-12-04T00:00:00"/>
+    <n v="0.28749999999999998"/>
+    <n v="34.78"/>
+    <n v="9.99925"/>
+    <n v="0.2"/>
+    <n v="0.2"/>
+    <n v="1"/>
+    <n v="4.7973651507465707E-2"/>
+    <n v="1.9998500000000001"/>
+    <n v="41.735999999999997"/>
+    <n v="11.999099999999999"/>
+    <n v="32.200000000000003"/>
+    <n v="9.2575000000000003"/>
+    <n v="-0.74174999999999969"/>
+    <n v="34.78"/>
+    <n v="6.955999999999996"/>
+    <n v="0"/>
+    <n v="6.955999999999996"/>
+    <n v="107.1764450811844"/>
+    <n v="9.3304083676456744E-3"/>
+    <n v="0.46259492532480184"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="Google"/>
+    <x v="20"/>
+    <d v="2025-01-21T00:00:00"/>
+    <n v="5.3800000000000001E-2"/>
+    <n v="185.82"/>
+    <n v="9.9971160000000001"/>
+    <n v="2.4701323861801683E-2"/>
+    <n v="0.26790000000000003"/>
+    <n v="9.2203523187016356E-2"/>
+    <n v="4.4233396891344571E-3"/>
+    <n v="2.6782273764000002"/>
+    <n v="190.40999999999997"/>
+    <n v="10.244057999999999"/>
+    <n v="162.72"/>
+    <n v="8.7543360000000003"/>
+    <n v="-1.2427799999999998"/>
+    <n v="149.46927113630838"/>
+    <n v="4.589999999999975"/>
+    <n v="-18.175364431845807"/>
+    <n v="-13.585364431845832"/>
+    <n v="127.71780951303022"/>
+    <n v="7.8297615956056353E-3"/>
+    <n v="0.55125555349008015"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <s v="Yum! Brands"/>
+    <x v="21"/>
+    <d v="2025-02-07T00:00:00"/>
+    <n v="2.9999999999999997E-4"/>
+    <n v="143.18"/>
+    <n v="4.2953999999999999E-2"/>
+    <n v="7.0000000000000007E-2"/>
+    <n v="0.1623"/>
+    <n v="0.43130006161429457"/>
+    <n v="2.0691038851032656E-2"/>
+    <n v="6.9714341999999995E-3"/>
+    <n v="153.20260000000002"/>
+    <n v="4.596078E-2"/>
+    <n v="153.15"/>
+    <n v="4.5945E-2"/>
+    <n v="2.9910000000000006E-3"/>
+    <n v="131.08120479721688"/>
+    <n v="10.022600000000011"/>
+    <n v="-6.0493976013915614"/>
+    <n v="3.9732023986084499"/>
+    <n v="110.15924268257594"/>
+    <n v="9.0777675631040951E-3"/>
+    <n v="0.47546927502570413"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="Apple2"/>
+    <x v="22"/>
+    <d v="2024-07-09T00:00:00"/>
+    <n v="1E-4"/>
+    <n v="227.38"/>
+    <n v="2.2738000000000001E-2"/>
+    <n v="0.15"/>
+    <n v="0.2271"/>
+    <n v="0.66050198150594452"/>
+    <n v="3.1686691880756741E-2"/>
+    <n v="5.1637998000000004E-3"/>
+    <n v="261.48699999999997"/>
+    <n v="2.6148699999999997E-2"/>
+    <n v="209.68"/>
+    <n v="2.0968000000000001E-2"/>
+    <n v="-1.7700000000000007E-3"/>
+    <n v="211.10389007520189"/>
+    <n v="34.106999999999971"/>
+    <n v="-8.1380549623990532"/>
+    <n v="25.968945037600918"/>
+    <n v="88.163500043583468"/>
+    <n v="1.1342562392664218E-2"/>
+    <n v="0.38053126027963941"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="Gold"/>
+    <x v="23"/>
+    <d v="2025-02-21T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="2742.9"/>
+    <n v="2.7429000000000002E-16"/>
+    <n v="0.1"/>
+    <n v="0.5"/>
+    <n v="0.2"/>
+    <n v="9.5947303014931422E-3"/>
+    <n v="1.3714500000000001E-16"/>
+    <n v="3017.1900000000005"/>
+    <n v="3.0171900000000003E-16"/>
+    <n v="2742.9"/>
+    <n v="2.7429000000000002E-16"/>
+    <n v="0"/>
+    <n v="1959.214285714286"/>
+    <n v="274.29000000000042"/>
+    <n v="-391.84285714285704"/>
+    <n v="-117.55285714285662"/>
+    <n v="231.68530222404101"/>
+    <n v="4.316199562080957E-3"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="ASML"/>
+    <x v="24"/>
+    <d v="2024-07-08T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="700.32"/>
+    <n v="7.0031999999999998E-17"/>
+    <n v="0.1"/>
+    <n v="0.45340000000000003"/>
+    <n v="0.22055580061755625"/>
+    <n v="1.0580867116776735E-2"/>
+    <n v="3.1752508800000004E-17"/>
+    <n v="770.35200000000009"/>
+    <n v="7.7035200000000004E-17"/>
+    <n v="700.32"/>
+    <n v="7.0031999999999998E-17"/>
+    <n v="0"/>
+    <n v="517.45234224915032"/>
+    <n v="70.032000000000039"/>
+    <n v="-91.433828875424865"/>
+    <n v="-21.401828875424826"/>
+    <n v="135.53427395660921"/>
+    <n v="7.37820752498476E-3"/>
+    <n v="0.58499297389847715"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <s v="LVMH"/>
+    <x v="25"/>
+    <d v="2024-09-27T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="668.82"/>
+    <n v="6.6881999999999999E-17"/>
+    <n v="0.05"/>
+    <n v="0.28000000000000003"/>
+    <n v="0.17857142857142858"/>
+    <n v="8.5667234834760197E-3"/>
+    <n v="1.872696E-17"/>
+    <n v="702.26100000000008"/>
+    <n v="7.0226100000000009E-17"/>
+    <n v="668.82"/>
+    <n v="6.6881999999999999E-17"/>
+    <n v="0"/>
+    <n v="543.7560975609756"/>
+    <n v="33.441000000000031"/>
+    <n v="-62.531951219512223"/>
+    <n v="-29.090951219512192"/>
+    <n v="143.22339630069658"/>
+    <n v="6.9820994741704541E-3"/>
+    <n v="0.61818076039281389"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="Visa"/>
+    <x v="26"/>
+    <d v="2025-01-28T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="336.69"/>
+    <n v="3.3669000000000002E-17"/>
+    <n v="0.25"/>
+    <n v="0.26"/>
+    <n v="0.96153846153846145"/>
+    <n v="4.612851106487087E-2"/>
+    <n v="8.7539400000000014E-18"/>
+    <n v="420.86250000000001"/>
+    <n v="4.2086250000000001E-17"/>
+    <n v="336.69"/>
+    <n v="3.3669000000000002E-17"/>
+    <n v="0"/>
+    <n v="333.35643564356434"/>
+    <n v="84.172500000000014"/>
+    <n v="-1.6667821782178294"/>
+    <n v="82.505717821782184"/>
+    <n v="31.626727259402202"/>
+    <n v="3.161882643746243E-2"/>
+    <n v="0.13650726634708565"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <s v="HCA Healthcare"/>
+    <x v="27"/>
+    <d v="2024-12-04T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="323.75"/>
+    <n v="3.2375000000000002E-17"/>
+    <n v="0.2"/>
+    <n v="0.2"/>
+    <n v="1"/>
+    <n v="4.7973651507465707E-2"/>
+    <n v="6.4750000000000006E-18"/>
+    <n v="388.5"/>
+    <n v="3.8849999999999999E-17"/>
+    <n v="323.75"/>
+    <n v="3.2375000000000002E-17"/>
+    <n v="0"/>
+    <n v="323.75"/>
+    <n v="64.75"/>
+    <n v="0"/>
+    <n v="64.75"/>
+    <n v="49.382445081184386"/>
+    <n v="2.0250111114506527E-2"/>
+    <n v="0.21314448783389495"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="QualComm2"/>
+    <x v="28"/>
+    <d v="2024-09-09T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="188.12"/>
+    <n v="1.8812000000000001E-17"/>
+    <n v="0.15"/>
+    <n v="0.37780000000000002"/>
+    <n v="0.39703546850185278"/>
+    <n v="1.9047241202011265E-2"/>
+    <n v="7.1071736000000005E-18"/>
+    <n v="216.33799999999999"/>
+    <n v="2.16338E-17"/>
+    <n v="188.12"/>
+    <n v="1.8812000000000001E-17"/>
+    <n v="0"/>
+    <n v="153.21713634142367"/>
+    <n v="28.217999999999989"/>
+    <n v="-17.451431829288168"/>
+    <n v="10.766568170711821"/>
+    <n v="103.36587691047256"/>
+    <n v="9.6743725288193673E-3"/>
+    <n v="0.44614775265509582"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="Applied Material"/>
+    <x v="29"/>
+    <d v="2024-07-08T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="169.34"/>
+    <n v="1.6933999999999999E-17"/>
+    <n v="0.1"/>
+    <n v="0.4259"/>
+    <n v="0.23479690068091102"/>
+    <n v="1.1264064688299064E-2"/>
+    <n v="7.2121906000000005E-18"/>
+    <n v="186.27400000000003"/>
+    <n v="1.8627400000000003E-17"/>
+    <n v="169.34"/>
+    <n v="1.6933999999999999E-17"/>
+    <n v="0"/>
+    <n v="127.71702239987934"/>
+    <n v="16.934000000000026"/>
+    <n v="-20.811488800060332"/>
+    <n v="-3.8774888000603056"/>
+    <n v="118.00993388124469"/>
+    <n v="8.4738628953585915E-3"/>
+    <n v="0.50935442493943106"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="Japan Yen"/>
+    <x v="30"/>
+    <d v="2024-10-09T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="153.7552"/>
+    <n v="1.5375519999999999E-17"/>
+    <n v="7.0000000000000007E-2"/>
+    <n v="0.19"/>
+    <n v="0.36842105263157898"/>
+    <n v="1.7674503186961052E-2"/>
+    <n v="2.9213487999999999E-18"/>
+    <n v="164.51806400000001"/>
+    <n v="1.6451806399999999E-17"/>
+    <n v="153.7552"/>
+    <n v="1.5375519999999999E-17"/>
+    <n v="0"/>
+    <n v="137.28142857142859"/>
+    <n v="10.762864000000008"/>
+    <n v="-8.2368857142857053"/>
+    <n v="2.5259782857143023"/>
+    <n v="111.60646679547008"/>
+    <n v="8.9600542756415654E-3"/>
+    <n v="0.48171578310801083"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="Nvidia"/>
+    <x v="31"/>
+    <d v="2024-07-09T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="147.01"/>
+    <n v="1.4700999999999999E-17"/>
+    <n v="0.15"/>
+    <n v="0.52380000000000004"/>
+    <n v="0.28636884306987398"/>
+    <n v="1.3738159080030272E-2"/>
+    <n v="7.7003838000000003E-18"/>
+    <n v="169.06149999999997"/>
+    <n v="1.6906149999999997E-17"/>
+    <n v="147.01"/>
+    <n v="1.4700999999999999E-17"/>
+    <n v="0"/>
+    <n v="107.00975396709855"/>
+    <n v="22.051499999999976"/>
+    <n v="-20.000123016450722"/>
+    <n v="2.0513769835492539"/>
+    <n v="112.08106809763513"/>
+    <n v="8.9221134039237406E-3"/>
+    <n v="0.48376425704057868"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="3M"/>
+    <x v="32"/>
+    <d v="2024-12-01T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="133.53"/>
+    <n v="1.3353E-17"/>
+    <n v="7.0000000000000007E-2"/>
+    <n v="0.2"/>
+    <n v="0.35000000000000003"/>
+    <n v="1.6790778027613001E-2"/>
+    <n v="2.6706000000000003E-18"/>
+    <n v="142.87710000000001"/>
+    <n v="1.428771E-17"/>
+    <n v="133.53"/>
+    <n v="1.3353E-17"/>
+    <n v="0"/>
+    <n v="118.16814159292036"/>
+    <n v="9.3471000000000117"/>
+    <n v="-7.6809292035398187"/>
+    <n v="1.6661707964601931"/>
+    <n v="112.46627428472419"/>
+    <n v="8.8915544358512243E-3"/>
+    <n v="0.48542688381660337"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="Duke Energy"/>
+    <x v="33"/>
+    <d v="2024-08-07T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="113.58"/>
+    <n v="1.1357999999999999E-17"/>
+    <n v="6.664905793273479E-2"/>
+    <n v="0.16439999999999999"/>
+    <n v="0.40540789496797319"/>
+    <n v="1.9448897071568806E-2"/>
+    <n v="1.8672551999999998E-18"/>
+    <n v="121.15000000000002"/>
+    <n v="1.2115000000000002E-17"/>
+    <n v="113.58"/>
+    <n v="1.1357999999999999E-17"/>
+    <n v="0"/>
+    <n v="103.46609203186667"/>
+    <n v="7.5700000000000216"/>
+    <n v="-5.0569539840666664"/>
+    <n v="2.5130460159333552"/>
+    <n v="111.61939906525103"/>
+    <n v="8.9590161600441413E-3"/>
+    <n v="0.48177160136517611"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Walmart"/>
+    <x v="34"/>
+    <d v="2024-08-01T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="86.6"/>
+    <n v="8.6599999999999986E-18"/>
+    <n v="7.0000000000000007E-2"/>
+    <n v="0.17249999999999999"/>
+    <n v="0.40579710144927544"/>
+    <n v="1.9467568727667247E-2"/>
+    <n v="1.4938499999999996E-18"/>
+    <n v="92.662000000000006"/>
+    <n v="9.2662000000000008E-18"/>
+    <n v="86.6"/>
+    <n v="8.6599999999999986E-18"/>
+    <n v="0"/>
+    <n v="78.548752834467123"/>
+    <n v="6.0620000000000118"/>
+    <n v="-4.0256235827664355"/>
+    <n v="2.0363764172335763"/>
+    <n v="112.0960686639508"/>
+    <n v="8.9209194570227784E-3"/>
+    <n v="0.48382900247834137"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="Palantir"/>
+    <x v="35"/>
+    <d v="2024-07-08T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="64.349999999999994"/>
+    <n v="6.4349999999999993E-18"/>
+    <n v="0.15"/>
+    <n v="0.67300000000000004"/>
+    <n v="0.22288261515601782"/>
+    <n v="1.0692492906567394E-2"/>
+    <n v="4.3307549999999997E-18"/>
+    <n v="74.002499999999984"/>
+    <n v="7.4002499999999988E-18"/>
+    <n v="64.349999999999994"/>
+    <n v="6.4349999999999993E-18"/>
+    <n v="0"/>
+    <n v="42.252133946158892"/>
+    <n v="9.6524999999999892"/>
+    <n v="-11.048933026920551"/>
+    <n v="-1.3964330269205618"/>
+    <n v="115.52887810810495"/>
+    <n v="8.6558444639638962E-3"/>
+    <n v="0.49864569309790685"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <s v="Aptive Autoparts"/>
+    <x v="36"/>
+    <d v="2024-09-27T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="56"/>
+    <n v="5.5999999999999995E-18"/>
+    <n v="7.0000000000000007E-2"/>
+    <n v="0.19"/>
+    <n v="0.36842105263157898"/>
+    <n v="1.7674503186961052E-2"/>
+    <n v="1.0639999999999999E-18"/>
+    <n v="59.92"/>
+    <n v="5.9920000000000002E-18"/>
+    <n v="56"/>
+    <n v="5.5999999999999995E-18"/>
+    <n v="0"/>
+    <n v="50.000000000000007"/>
+    <n v="3.9200000000000017"/>
+    <n v="-2.9999999999999964"/>
+    <n v="0.92000000000000526"/>
+    <n v="113.21244508118438"/>
+    <n v="8.832951176727102E-3"/>
+    <n v="0.48864750588152245"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="ETF5"/>
+    <x v="37"/>
+    <d v="2024-07-08T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="51.28"/>
+    <n v="5.128E-18"/>
+    <n v="4.2999999999999997E-2"/>
+    <n v="5.7000000000000002E-2"/>
+    <n v="0.7543859649122806"/>
+    <n v="3.6190649382825006E-2"/>
+    <n v="2.92296E-19"/>
+    <n v="53.485039999999998"/>
+    <n v="5.3485039999999993E-18"/>
+    <n v="51.28"/>
+    <n v="5.128E-18"/>
+    <n v="0"/>
+    <n v="50.57199211045365"/>
+    <n v="2.2050399999999968"/>
+    <n v="-0.35400394477317576"/>
+    <n v="1.851036055226821"/>
+    <n v="112.28140902595757"/>
+    <n v="8.9061938986606127E-3"/>
+    <n v="0.4846289684676709"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <s v="Yum China Holding"/>
+    <x v="38"/>
+    <d v="2024-10-09T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="47.42"/>
+    <n v="4.7419999999999999E-18"/>
+    <n v="7.0000000000000007E-2"/>
+    <n v="0.4"/>
+    <n v="0.17500000000000002"/>
+    <n v="8.3953890138065007E-3"/>
+    <n v="1.8968000000000002E-18"/>
+    <n v="50.739400000000003"/>
+    <n v="5.0739400000000001E-18"/>
+    <n v="47.42"/>
+    <n v="4.7419999999999999E-18"/>
+    <n v="0"/>
+    <n v="35.654135338345867"/>
+    <n v="3.3194000000000017"/>
+    <n v="-5.8829323308270673"/>
+    <n v="-2.5635323308270657"/>
+    <n v="116.69597741201144"/>
+    <n v="8.5692756697976005E-3"/>
+    <n v="0.50368312660233305"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="PG&amp;E"/>
+    <x v="39"/>
+    <d v="2024-12-01T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="26.63"/>
+    <n v="2.663E-18"/>
+    <n v="0.1"/>
+    <n v="0.2"/>
+    <n v="0.5"/>
+    <n v="2.3986825753732854E-2"/>
+    <n v="5.3260000000000006E-19"/>
+    <n v="29.293000000000003"/>
+    <n v="2.9293000000000003E-18"/>
+    <n v="26.63"/>
+    <n v="2.663E-18"/>
+    <n v="0"/>
+    <n v="24.209090909090911"/>
+    <n v="2.6630000000000038"/>
+    <n v="-1.2104545454545441"/>
+    <n v="1.4525454545454597"/>
+    <n v="112.67989962663893"/>
+    <n v="8.8746972912956655E-3"/>
+    <n v="0.48634893342382512"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="Jinko Solar"/>
+    <x v="40"/>
+    <d v="2024-08-07T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="20.82"/>
+    <n v="2.0820000000000002E-18"/>
+    <n v="0.05"/>
+    <n v="0.7389"/>
+    <n v="6.7668155366084726E-2"/>
+    <n v="3.2462885036855945E-3"/>
+    <n v="1.5383898E-18"/>
+    <n v="21.861000000000001"/>
+    <n v="2.1860999999999999E-18"/>
+    <n v="20.82"/>
+    <n v="2.0820000000000002E-18"/>
+    <n v="0"/>
+    <n v="12.327550476641601"/>
+    <n v="1.0410000000000004"/>
+    <n v="-4.2462247616791995"/>
+    <n v="-3.2052247616791991"/>
+    <n v="117.33766984286359"/>
+    <n v="8.5224122938454567E-3"/>
+    <n v="0.50645279919136776"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="Mexican Peso"/>
+    <x v="41"/>
+    <d v="2024-10-15T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="17"/>
+    <n v="1.7E-18"/>
+    <n v="0.1"/>
+    <n v="0.15"/>
+    <n v="0.66666666666666674"/>
+    <n v="3.1982434338310474E-2"/>
+    <n v="2.5499999999999999E-19"/>
+    <n v="21.2"/>
+    <n v="2.1199999999999999E-18"/>
+    <n v="17"/>
+    <n v="1.7E-18"/>
+    <n v="0"/>
+    <n v="16.190476190476193"/>
+    <n v="4.1999999999999993"/>
+    <n v="-0.40476190476190332"/>
+    <n v="3.795238095238096"/>
+    <n v="110.3372069859463"/>
+    <n v="9.0631259147911057E-3"/>
+    <n v="0.47623740447397733"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="SolarWinds"/>
+    <x v="42"/>
+    <d v="2024-08-07T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="13.04"/>
+    <n v="1.304E-18"/>
+    <n v="5.2147239263803824E-2"/>
+    <n v="0.30159999999999998"/>
+    <n v="0.17290198694895167"/>
+    <n v="8.2947396668373915E-3"/>
+    <n v="3.9328639999999997E-19"/>
+    <n v="13.72"/>
+    <n v="1.3720000000000001E-18"/>
+    <n v="13.04"/>
+    <n v="1.304E-18"/>
+    <n v="0"/>
+    <n v="10.436569040286594"/>
+    <n v="0.68000000000000149"/>
+    <n v="-1.3017154798567026"/>
+    <n v="-0.62171547985670106"/>
+    <n v="114.75416056104109"/>
+    <n v="8.7142809908671744E-3"/>
+    <n v="0.49530185756053341"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="Canadian Solar"/>
+    <x v="43"/>
+    <d v="2024-08-07T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="11.05"/>
+    <n v="1.1050000000000001E-18"/>
+    <n v="0.05"/>
+    <n v="0.72170000000000001"/>
+    <n v="6.9280864625190522E-2"/>
+    <n v="3.3236560556647991E-3"/>
+    <n v="7.9747850000000009E-19"/>
+    <n v="11.602500000000001"/>
+    <n v="1.16025E-18"/>
+    <n v="11.05"/>
+    <n v="1.1050000000000001E-18"/>
+    <n v="0"/>
+    <n v="6.6100376861877139"/>
+    <n v="0.55250000000000021"/>
+    <n v="-2.2199811569061434"/>
+    <n v="-1.6674811569061432"/>
+    <n v="115.79992623809053"/>
+    <n v="8.6355840844315329E-3"/>
+    <n v="0.49981559091785349"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="Maxeon Solar"/>
+    <x v="44"/>
+    <d v="2024-08-07T00:00:00"/>
+    <n v="9.9999999999999998E-20"/>
+    <n v="10.92"/>
+    <n v="1.092E-18"/>
+    <n v="1"/>
+    <n v="1.8652"/>
+    <n v="0.53613553506326406"/>
+    <n v="2.5720379319893693E-2"/>
+    <n v="2.0367984000000001E-18"/>
+    <n v="21.84"/>
+    <n v="2.1840000000000001E-18"/>
+    <n v="10.92"/>
+    <n v="1.092E-18"/>
+    <n v="0"/>
+    <n v="5.8546000428908433"/>
+    <n v="10.92"/>
+    <n v="-2.5326999785545783"/>
+    <n v="8.3873000214454212"/>
+    <n v="105.74514505973896"/>
+    <n v="9.456698928684306E-3"/>
+    <n v="0.45641714879903256"/>
+  </r>
+</pivotCacheRecords>
 </file>
 
 <file path=xl/pivotCache/richPivotRecords1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3453,7 +3471,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{57F4DE94-EA99-48C9-8E97-8E3ABDD6D5EB}" name="PivotTable1" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{57F4DE94-EA99-48C9-8E97-8E3ABDD6D5EB}" name="PivotTable1" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:H14" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="30">
     <pivotField axis="axisRow" showAll="0" sortType="descending">
@@ -3483,50 +3501,50 @@
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0" sortType="descending">
       <items count="48">
-        <item sd="0" x="21"/>
-        <item sd="0" x="44"/>
+        <item sd="0" x="22"/>
+        <item sd="0" x="15"/>
+        <item sd="0" x="19"/>
+        <item sd="0" x="29"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="36"/>
+        <item sd="0" x="24"/>
+        <item sd="0" x="16"/>
+        <item sd="0" x="37"/>
+        <item sd="0" x="14"/>
+        <item sd="0" x="43"/>
         <item sd="0" x="18"/>
-        <item sd="0" x="28"/>
-        <item sd="0" x="6"/>
-        <item sd="0" x="35"/>
+        <item sd="0" x="33"/>
+        <item sd="0" x="17"/>
+        <item sd="0" x="5"/>
         <item sd="0" x="23"/>
-        <item sd="0" x="15"/>
-        <item sd="0" x="43"/>
-        <item sd="0" x="14"/>
-        <item sd="0" x="41"/>
-        <item sd="0" x="17"/>
-        <item sd="0" x="32"/>
-        <item sd="0" x="16"/>
-        <item sd="0" x="9"/>
-        <item sd="0" x="22"/>
-        <item sd="0" x="19"/>
-        <item sd="0" x="26"/>
+        <item sd="0" x="20"/>
+        <item sd="0" x="27"/>
         <item sd="0" x="11"/>
         <item sd="0" x="13"/>
+        <item sd="0" x="40"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="44"/>
+        <item sd="0" x="25"/>
+        <item sd="0" x="32"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="31"/>
+        <item sd="0" x="39"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="35"/>
+        <item sd="0" x="28"/>
+        <item sd="0" x="42"/>
+        <item sd="0" x="0"/>
+        <item sd="0" x="30"/>
+        <item sd="0" x="41"/>
+        <item sd="0" x="26"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="34"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="21"/>
         <item sd="0" x="38"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="42"/>
-        <item sd="0" x="24"/>
-        <item sd="0" x="31"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="5"/>
-        <item sd="0" x="10"/>
-        <item sd="0" x="30"/>
-        <item sd="0" x="37"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="34"/>
-        <item sd="0" x="27"/>
-        <item sd="0" x="40"/>
-        <item sd="0" x="0"/>
-        <item sd="0" x="29"/>
-        <item sd="0" x="39"/>
-        <item sd="0" x="25"/>
-        <item sd="0" x="12"/>
-        <item sd="0" x="33"/>
-        <item sd="0" x="8"/>
-        <item sd="0" x="20"/>
-        <item sd="0" x="36"/>
         <item sd="0" x="2"/>
         <item sd="0" m="1" x="46"/>
         <item m="1" x="45"/>
@@ -3593,10 +3611,10 @@
   </rowFields>
   <rowItems count="11">
     <i>
-      <x v="8"/>
+      <x v="3"/>
     </i>
     <i>
-      <x v="3"/>
+      <x v="8"/>
     </i>
     <i>
       <x v="9"/>
@@ -3671,7 +3689,7 @@
     <dataField name="Actual P&amp;L " fld="26" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="8">
-    <format dxfId="128">
+    <format dxfId="23">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -3681,7 +3699,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="129">
+    <format dxfId="22">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -3691,7 +3709,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="130">
+    <format dxfId="21">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -3700,7 +3718,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="131">
+    <format dxfId="20">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -3709,7 +3727,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="132">
+    <format dxfId="19">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -3718,7 +3736,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="133">
+    <format dxfId="18">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="5">
@@ -3731,7 +3749,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="134">
+    <format dxfId="17">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="5">
@@ -3744,7 +3762,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="135">
+    <format dxfId="16">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="5">
@@ -3765,11 +3783,6 @@
     </ext>
     <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
       <xpdl:pivotTableDefinition16/>
-    </ext>
-    <ext xmlns:xxpvi="http://schemas.microsoft.com/office/spreadsheetml/2022/pivotVersionInfo" uri="{9F748A41-CAEA-4470-BF7A-CE61E8FFA7F9}">
-      <xxpvi:pivotVersionInfo>
-        <xxpvi:lastUpdateFeature>RichData</xxpvi:lastUpdateFeature>
-      </xxpvi:pivotVersionInfo>
     </ext>
   </extLst>
 </pivotTableDefinition>
@@ -4471,33 +4484,33 @@
         <v>45484</v>
       </c>
       <c r="E2" s="2">
-        <v>0.60660000000000003</v>
+        <v>0.69389999999999996</v>
       </c>
       <c r="F2" s="1">
-        <v>186.18</v>
+        <v>184.36</v>
       </c>
       <c r="G2" s="1">
         <f>E2*F2</f>
-        <v>112.93678800000001</v>
+        <v>127.927404</v>
       </c>
       <c r="H2" s="13">
         <f>227.4/F2-1</f>
-        <v>0.22139864647115703</v>
+        <v>0.23345628118897799</v>
       </c>
       <c r="I2" s="11">
         <v>0.37</v>
       </c>
       <c r="J2" s="9">
         <f>IFERROR(H2/I2,"")</f>
-        <v>0.5983747201923163</v>
+        <v>0.63096292213237293</v>
       </c>
       <c r="K2" s="9">
         <f>IFERROR(J2/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.9018020042600932E-2</v>
+        <v>3.0269595340510682E-2</v>
       </c>
       <c r="L2" s="9">
         <f>I2*G2</f>
-        <v>41.786611560000004</v>
+        <v>47.33313948</v>
       </c>
       <c r="M2" s="12">
         <f>F2/(1-(F2*(1+H2)-F2)/(F2*(1+H2)))</f>
@@ -4505,46 +4518,46 @@
       </c>
       <c r="N2" s="12">
         <f>M2*E2</f>
-        <v>137.94084000000001</v>
+        <v>157.79285999999999</v>
       </c>
       <c r="O2" s="12">
-        <v>176.69</v>
+        <v>171.56</v>
       </c>
       <c r="P2" s="12">
         <f>IFERROR(O2*E2,G2)</f>
-        <v>107.180154</v>
+        <v>119.045484</v>
       </c>
       <c r="Q2" s="12">
         <f>P2-G2</f>
-        <v>-5.7566340000000054</v>
+        <v>-8.8819199999999938</v>
       </c>
       <c r="R2" s="12">
         <f>F2/(1+I2-H2)</f>
-        <v>162.09279174885174</v>
+        <v>162.21109399369644</v>
       </c>
       <c r="S2" s="12">
         <f>M2-F2</f>
-        <v>41.22</v>
+        <v>43.039999999999992</v>
       </c>
       <c r="T2" s="12">
         <f>0.5*(R2-F2)</f>
-        <v>-12.043604125574134</v>
+        <v>-11.074453003151788</v>
       </c>
       <c r="U2" s="15">
         <f>S2+T2</f>
-        <v>29.176395874425864</v>
+        <v>31.965546996848204</v>
       </c>
       <c r="V2" s="12">
         <f>MAX($U$2:$U$278)-U2</f>
-        <v>84.956049206758522</v>
+        <v>82.166898084336182</v>
       </c>
       <c r="W2" s="9">
         <f>IFERROR((SUBTOTAL(109,$V$2:$V$1048576)/V2)/SUBTOTAL(109,$V$2:$V$1048576),0)</f>
-        <v>1.17707921841597E-2</v>
+        <v>1.2170351118446738E-2</v>
       </c>
       <c r="X2" s="9">
         <f>V2/MAX($V$2:$V$28)</f>
-        <v>0.3666872623823394</v>
+        <v>0.35464872952916249</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
@@ -4583,7 +4596,7 @@
       </c>
       <c r="K3" s="9">
         <f>IFERROR(J3/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.4732625624617869E-2</v>
+        <v>4.4251971835965617E-2</v>
       </c>
       <c r="L3" s="9">
         <f>I3*G3</f>
@@ -4597,17 +4610,16 @@
         <f>M3*E3</f>
         <v>106.57639814639998</v>
       </c>
-      <c r="O3" s="12" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="O3" ca="1">_xlfn.STOCKHISTORY(C3,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>#VALUE!</v>
+      <c r="O3" s="12">
+        <v>58.55</v>
       </c>
       <c r="P3" s="12">
-        <f ca="1">IFERROR(O3*E3,G3)</f>
-        <v>89.991048000000006</v>
+        <f>IFERROR(O3*E3,G3)</f>
+        <v>101.56083</v>
       </c>
       <c r="Q3" s="12">
-        <f ca="1">P3-G3</f>
-        <v>0</v>
+        <f>P3-G3</f>
+        <v>11.569781999999989</v>
       </c>
       <c r="R3" s="12">
         <f>F3/(1+I3-H3)</f>
@@ -4673,7 +4685,7 @@
       </c>
       <c r="K4" s="9">
         <f>IFERROR(J4/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.3958705519704158E-2</v>
+        <v>2.3701268304283655E-2</v>
       </c>
       <c r="L4" s="9">
         <f>I4*G4</f>
@@ -4687,17 +4699,16 @@
         <f>M4*E4</f>
         <v>96.105419999999995</v>
       </c>
-      <c r="O4" s="12" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="O4" ca="1">_xlfn.STOCKHISTORY(C4,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>#VALUE!</v>
+      <c r="O4" s="12">
+        <v>45.24</v>
       </c>
       <c r="P4" s="12">
-        <f ca="1">IFERROR(O4*E4,G4)</f>
-        <v>88.74</v>
+        <f>IFERROR(O4*E4,G4)</f>
+        <v>90.48</v>
       </c>
       <c r="Q4" s="12">
-        <f ca="1">P4-G4</f>
-        <v>0</v>
+        <f>P4-G4</f>
+        <v>1.7400000000000091</v>
       </c>
       <c r="R4" s="12">
         <f>F4/(1+I4-H4)</f>
@@ -4721,7 +4732,7 @@
       </c>
       <c r="W4" s="9">
         <f>IFERROR((SUBTOTAL(109,$V$2:$V$1048576)/V4)/SUBTOTAL(109,$V$2:$V$1048576),0)</f>
-        <v>8.9136307133127497E-3</v>
+        <v>8.9136307133127479E-3</v>
       </c>
       <c r="X4" s="9">
         <f>V4/MAX($V$2:$V$28)</f>
@@ -4763,7 +4774,7 @@
       </c>
       <c r="K5" s="9">
         <f>IFERROR(J5/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.9822663048929445E-2</v>
+        <v>1.9609667769475037E-2</v>
       </c>
       <c r="L5" s="9">
         <f>I5*G5</f>
@@ -4778,15 +4789,15 @@
         <v>86.394189907200001</v>
       </c>
       <c r="O5" s="12">
-        <v>154.41</v>
+        <v>148.28</v>
       </c>
       <c r="P5" s="12">
         <f>IFERROR(O5*E5,G5)</f>
-        <v>79.119683999999992</v>
+        <v>75.978671999999989</v>
       </c>
       <c r="Q5" s="12">
         <f>P5-G5</f>
-        <v>-1.8343920000000082</v>
+        <v>-4.9754040000000117</v>
       </c>
       <c r="R5" s="12">
         <f>F5/(1+I5-H5)</f>
@@ -4819,449 +4830,448 @@
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>19</v>
+        <v>40</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="D6" s="8">
-        <v>45544</v>
+        <v>45627</v>
       </c>
       <c r="E6" s="2">
-        <v>0.51380000000000003</v>
+        <v>3.8043</v>
       </c>
       <c r="F6" s="1">
-        <v>138.53</v>
+        <v>21.02</v>
       </c>
       <c r="G6" s="1">
         <f>E6*F6</f>
-        <v>71.176714000000004</v>
+        <v>79.966386</v>
       </c>
       <c r="H6" s="13">
-        <v>7.0000000000000007E-2</v>
+        <f>M6/F6-1</f>
+        <v>0.26450999048525214</v>
       </c>
       <c r="I6" s="11">
-        <v>0.18340000000000001</v>
+        <v>0.45929999999999999</v>
       </c>
       <c r="J6" s="9">
         <f>IFERROR(H6/I6,"")</f>
-        <v>0.38167938931297712</v>
+        <v>0.57589808509743556</v>
       </c>
       <c r="K6" s="9">
         <f>IFERROR(J6/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.8509438643016182E-2</v>
+        <v>2.7627934038281204E-2</v>
       </c>
       <c r="L6" s="9">
         <f>I6*G6</f>
-        <v>13.053809347600001</v>
+        <v>36.728561089799996</v>
       </c>
       <c r="M6" s="12">
-        <f>F6/(1-(F6*(1+H6)-F6)/(F6*(1+H6)))</f>
-        <v>148.22710000000001</v>
+        <v>26.58</v>
       </c>
       <c r="N6" s="12">
         <f>M6*E6</f>
-        <v>76.159083980000005</v>
+        <v>101.11829399999999</v>
       </c>
       <c r="O6" s="12">
-        <v>144.76</v>
+        <v>19.010000000000002</v>
       </c>
       <c r="P6" s="12">
         <f>IFERROR(O6*E6,G6)</f>
-        <v>74.377688000000006</v>
+        <v>72.319743000000003</v>
       </c>
       <c r="Q6" s="12">
         <f>P6-G6</f>
-        <v>3.2009740000000022</v>
+        <v>-7.6466429999999974</v>
       </c>
       <c r="R6" s="12">
         <f>F6/(1+I6-H6)</f>
-        <v>124.42069337165439</v>
+        <v>17.593049684552572</v>
       </c>
       <c r="S6" s="12">
         <f>M6-F6</f>
-        <v>9.697100000000006</v>
+        <v>5.5599999999999987</v>
       </c>
       <c r="T6" s="12">
         <f>0.5*(R6-F6)</f>
-        <v>-7.0546533141728034</v>
+        <v>-1.7134751577237139</v>
       </c>
       <c r="U6" s="15">
         <f>S6+T6</f>
-        <v>2.6424466858272027</v>
+        <v>3.8465248422762848</v>
       </c>
       <c r="V6" s="12">
         <f>MAX($U$2:$U$278)-U6</f>
-        <v>111.48999839535719</v>
+        <v>110.2859202389081</v>
       </c>
       <c r="W6" s="9">
         <f>IFERROR((SUBTOTAL(109,$V$2:$V$1048576)/V6)/SUBTOTAL(109,$V$2:$V$1048576),0)</f>
-        <v>8.969414426340536E-3</v>
+        <v>9.0673405801369646E-3</v>
       </c>
       <c r="X6" s="9">
         <f>V6/MAX($V$2:$V$28)</f>
-        <v>0.48121308225044729</v>
+        <v>0.47601604063887054</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>11</v>
+        <v>40</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="D7" s="8">
-        <v>45574</v>
+        <v>45511</v>
       </c>
       <c r="E7" s="2">
-        <v>0.16059999999999999</v>
+        <v>0.48830000000000001</v>
       </c>
       <c r="F7" s="1">
-        <v>421.18</v>
+        <v>163.65</v>
       </c>
       <c r="G7" s="1">
         <f>E7*F7</f>
-        <v>67.641508000000002</v>
+        <v>79.910295000000005</v>
       </c>
       <c r="H7" s="13">
-        <v>0.15</v>
+        <f>196.02/F7-1</f>
+        <v>0.19780018331805693</v>
       </c>
       <c r="I7" s="11">
-        <v>0.1963</v>
+        <v>0.52980000000000005</v>
       </c>
       <c r="J7" s="9">
         <f>IFERROR(H7/I7,"")</f>
-        <v>0.76413652572592972</v>
+        <v>0.37334877938478089</v>
       </c>
       <c r="K7" s="9">
         <f>IFERROR(J7/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.7056593921066527E-2</v>
+        <v>1.7910904232943177E-2</v>
       </c>
       <c r="L7" s="9">
         <f>I7*G7</f>
-        <v>13.278028020400001</v>
+        <v>42.336474291000009</v>
       </c>
       <c r="M7" s="12">
         <f>F7/(1-(F7*(1+H7)-F7)/(F7*(1+H7)))</f>
-        <v>484.35699999999997</v>
+        <v>196.02</v>
       </c>
       <c r="N7" s="12">
         <f>M7*E7</f>
-        <v>77.787734199999989</v>
-      </c>
-      <c r="O7" s="12" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="O7" ca="1">_xlfn.STOCKHISTORY(C7,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>#VALUE!</v>
+        <v>95.716566</v>
+      </c>
+      <c r="O7" s="12">
+        <v>132.68</v>
       </c>
       <c r="P7" s="12">
-        <f ca="1">IFERROR(O7*E7,G7)</f>
-        <v>67.641508000000002</v>
+        <f>IFERROR(O7*E7,G7)</f>
+        <v>64.787644</v>
       </c>
       <c r="Q7" s="12">
-        <f ca="1">P7-G7</f>
-        <v>0</v>
+        <f>P7-G7</f>
+        <v>-15.122651000000005</v>
       </c>
       <c r="R7" s="12">
         <f>F7/(1+I7-H7)</f>
-        <v>402.54229188569246</v>
+        <v>122.86037726916339</v>
       </c>
       <c r="S7" s="12">
         <f>M7-F7</f>
-        <v>63.176999999999964</v>
+        <v>32.370000000000005</v>
       </c>
       <c r="T7" s="12">
         <f>0.5*(R7-F7)</f>
-        <v>-9.3188540571537715</v>
+        <v>-20.394811365418306</v>
       </c>
       <c r="U7" s="15">
         <f>S7+T7</f>
-        <v>53.858145942846193</v>
+        <v>11.975188634581698</v>
       </c>
       <c r="V7" s="12">
         <f>MAX($U$2:$U$278)-U7</f>
-        <v>60.274299138338193</v>
+        <v>102.15725644660269</v>
       </c>
       <c r="W7" s="9">
         <f>IFERROR((SUBTOTAL(109,$V$2:$V$1048576)/V7)/SUBTOTAL(109,$V$2:$V$1048576),0)</f>
-        <v>1.6590819209773906E-2</v>
+        <v>9.7888298372881336E-3</v>
       </c>
       <c r="X7" s="9">
         <f>V7/MAX($V$2:$V$28)</f>
-        <v>0.26015590354563189</v>
+        <v>0.44093110553821857</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>94</v>
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="D8" s="8">
-        <v>45627</v>
+        <v>45544</v>
       </c>
       <c r="E8" s="2">
-        <v>3.0230999999999999</v>
+        <v>0.51380000000000003</v>
       </c>
       <c r="F8" s="1">
-        <v>21.49</v>
+        <v>138.53</v>
       </c>
       <c r="G8" s="1">
         <f>E8*F8</f>
-        <v>64.966418999999988</v>
+        <v>71.176714000000004</v>
       </c>
       <c r="H8" s="13">
-        <f>M8/F8-1</f>
-        <v>0.23685435086086559</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I8" s="11">
-        <v>0.45929999999999999</v>
+        <v>0.18340000000000001</v>
       </c>
       <c r="J8" s="9">
         <f>IFERROR(H8/I8,"")</f>
-        <v>0.5156855015477152</v>
+        <v>0.38167938931297712</v>
       </c>
       <c r="K8" s="9">
         <f>IFERROR(J8/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.5008028772975005E-2</v>
+        <v>1.8310554010483097E-2</v>
       </c>
       <c r="L8" s="9">
         <f>I8*G8</f>
-        <v>29.839076246699992</v>
+        <v>13.053809347600001</v>
       </c>
       <c r="M8" s="12">
-        <v>26.58</v>
+        <f>F8/(1-(F8*(1+H8)-F8)/(F8*(1+H8)))</f>
+        <v>148.22710000000001</v>
       </c>
       <c r="N8" s="12">
         <f>M8*E8</f>
-        <v>80.35399799999999</v>
-      </c>
-      <c r="O8" s="12" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="O8" ca="1">_xlfn.STOCKHISTORY(C8,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>#VALUE!</v>
+        <v>76.159083980000005</v>
+      </c>
+      <c r="O8" s="12">
+        <v>140.03</v>
       </c>
       <c r="P8" s="12">
-        <f ca="1">IFERROR(O8*E8,G8)</f>
-        <v>64.966418999999988</v>
+        <f>IFERROR(O8*E8,G8)</f>
+        <v>71.947414000000009</v>
       </c>
       <c r="Q8" s="12">
-        <f ca="1">P8-G8</f>
-        <v>0</v>
+        <f>P8-G8</f>
+        <v>0.77070000000000505</v>
       </c>
       <c r="R8" s="12">
         <f>F8/(1+I8-H8)</f>
-        <v>17.57951367010353</v>
+        <v>124.42069337165439</v>
       </c>
       <c r="S8" s="12">
         <f>M8-F8</f>
-        <v>5.09</v>
+        <v>9.697100000000006</v>
       </c>
       <c r="T8" s="12">
         <f>0.5*(R8-F8)</f>
-        <v>-1.955243164948234</v>
+        <v>-7.0546533141728034</v>
       </c>
       <c r="U8" s="15">
         <f>S8+T8</f>
-        <v>3.1347568350517658</v>
+        <v>2.6424466858272027</v>
       </c>
       <c r="V8" s="12">
         <f>MAX($U$2:$U$278)-U8</f>
-        <v>110.99768824613263</v>
+        <v>111.48999839535719</v>
       </c>
       <c r="W8" s="9">
         <f>IFERROR((SUBTOTAL(109,$V$2:$V$1048576)/V8)/SUBTOTAL(109,$V$2:$V$1048576),0)</f>
-        <v>9.009196640046617E-3</v>
+        <v>8.969414426340536E-3</v>
       </c>
       <c r="X8" s="9">
         <f>V8/MAX($V$2:$V$28)</f>
-        <v>0.47908817339995624</v>
+        <v>0.48121308225044729</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>8</v>
+        <v>36</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D9" s="8">
-        <v>45511</v>
+        <v>45574</v>
       </c>
       <c r="E9" s="2">
-        <v>0.12939999999999999</v>
+        <v>0.16059999999999999</v>
       </c>
       <c r="F9" s="1">
-        <v>501.56</v>
+        <v>421.18</v>
       </c>
       <c r="G9" s="1">
         <f>E9*F9</f>
-        <v>64.901863999999989</v>
+        <v>67.641508000000002</v>
       </c>
       <c r="H9" s="13">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="I9" s="11">
-        <v>0.29699999999999999</v>
+        <v>0.1963</v>
       </c>
       <c r="J9" s="9">
         <f>IFERROR(H9/I9,"")</f>
-        <v>0.84175084175084181</v>
+        <v>0.76413652572592972</v>
       </c>
       <c r="K9" s="9">
         <f>IFERROR(J9/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.08204791622074E-2</v>
+        <v>3.665841938930136E-2</v>
       </c>
       <c r="L9" s="9">
         <f>I9*G9</f>
-        <v>19.275853607999995</v>
+        <v>13.278028020400001</v>
       </c>
       <c r="M9" s="12">
         <f>F9/(1-(F9*(1+H9)-F9)/(F9*(1+H9)))</f>
-        <v>626.95000000000005</v>
+        <v>484.35699999999997</v>
       </c>
       <c r="N9" s="12">
         <f>M9*E9</f>
-        <v>81.127330000000001</v>
+        <v>77.787734199999989</v>
       </c>
       <c r="O9" s="12">
-        <v>545.15</v>
+        <v>378.78</v>
       </c>
       <c r="P9" s="12">
         <f>IFERROR(O9*E9,G9)</f>
-        <v>70.54240999999999</v>
+        <v>60.832067999999992</v>
       </c>
       <c r="Q9" s="12">
         <f>P9-G9</f>
-        <v>5.6405460000000005</v>
+        <v>-6.8094400000000093</v>
       </c>
       <c r="R9" s="12">
         <f>F9/(1+I9-H9)</f>
-        <v>479.04489016236869</v>
+        <v>402.54229188569246</v>
       </c>
       <c r="S9" s="12">
         <f>M9-F9</f>
-        <v>125.39000000000004</v>
+        <v>63.176999999999964</v>
       </c>
       <c r="T9" s="12">
         <f>0.5*(R9-F9)</f>
-        <v>-11.257554918815657</v>
+        <v>-9.3188540571537715</v>
       </c>
       <c r="U9" s="15">
         <f>S9+T9</f>
-        <v>114.13244508118439</v>
+        <v>53.858145942846193</v>
       </c>
       <c r="V9" s="12">
         <f>MAX($U$2:$U$278)-U9</f>
-        <v>0</v>
+        <v>60.274299138338193</v>
       </c>
       <c r="W9" s="9">
         <f>IFERROR((SUBTOTAL(109,$V$2:$V$1048576)/V9)/SUBTOTAL(109,$V$2:$V$1048576),0)</f>
-        <v>0</v>
+        <v>1.6590819209773903E-2</v>
       </c>
       <c r="X9" s="9">
         <f>V9/MAX($V$2:$V$28)</f>
-        <v>0</v>
+        <v>0.26015590354563189</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>103</v>
+        <v>37</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="D10" s="8">
-        <v>45627</v>
+        <v>45511</v>
       </c>
       <c r="E10" s="2">
-        <v>1.5004999999999999</v>
+        <v>0.12939999999999999</v>
       </c>
       <c r="F10" s="1">
-        <v>40</v>
+        <v>501.56</v>
       </c>
       <c r="G10" s="1">
         <f>E10*F10</f>
-        <v>60.019999999999996</v>
+        <v>64.901863999999989</v>
       </c>
       <c r="H10" s="13">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="I10" s="11">
-        <v>0.2</v>
+        <v>0.29699999999999999</v>
       </c>
       <c r="J10" s="9">
         <f>IFERROR(H10/I10,"")</f>
-        <v>0.5</v>
+        <v>0.84175084175084181</v>
       </c>
       <c r="K10" s="9">
         <f>IFERROR(J10/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.4247364622351195E-2</v>
+        <v>4.0381861538270801E-2</v>
       </c>
       <c r="L10" s="9">
         <f>I10*G10</f>
-        <v>12.004</v>
+        <v>19.275853607999995</v>
       </c>
       <c r="M10" s="12">
         <f>F10/(1-(F10*(1+H10)-F10)/(F10*(1+H10)))</f>
-        <v>44</v>
+        <v>626.95000000000005</v>
       </c>
       <c r="N10" s="12">
         <f>M10*E10</f>
-        <v>66.021999999999991</v>
+        <v>81.127330000000001</v>
       </c>
       <c r="O10" s="12">
-        <v>33.26</v>
+        <v>519.39</v>
       </c>
       <c r="P10" s="12">
         <f>IFERROR(O10*E10,G10)</f>
-        <v>49.906629999999993</v>
+        <v>67.209065999999993</v>
       </c>
       <c r="Q10" s="12">
         <f>P10-G10</f>
-        <v>-10.113370000000003</v>
+        <v>2.3072020000000037</v>
       </c>
       <c r="R10" s="12">
         <f>F10/(1+I10-H10)</f>
-        <v>36.363636363636367</v>
+        <v>479.04489016236869</v>
       </c>
       <c r="S10" s="12">
         <f>M10-F10</f>
-        <v>4</v>
+        <v>125.39000000000004</v>
       </c>
       <c r="T10" s="12">
         <f>0.5*(R10-F10)</f>
-        <v>-1.8181818181818166</v>
+        <v>-11.257554918815657</v>
       </c>
       <c r="U10" s="15">
         <f>S10+T10</f>
-        <v>2.1818181818181834</v>
+        <v>114.13244508118439</v>
       </c>
       <c r="V10" s="12">
         <f>MAX($U$2:$U$278)-U10</f>
-        <v>111.9506268993662</v>
+        <v>0</v>
       </c>
       <c r="W10" s="9">
         <f>IFERROR((SUBTOTAL(109,$V$2:$V$1048576)/V10)/SUBTOTAL(109,$V$2:$V$1048576),0)</f>
-        <v>8.9325091577996465E-3</v>
+        <v>0</v>
       </c>
       <c r="X10" s="9">
         <f>V10/MAX($V$2:$V$28)</f>
-        <v>0.48320124679773302</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
@@ -5269,89 +5279,88 @@
         <v>40</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>47</v>
+        <v>103</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>103</v>
       </c>
       <c r="D11" s="8">
-        <v>45511</v>
+        <v>45627</v>
       </c>
       <c r="E11" s="2">
-        <v>0.34489999999999998</v>
+        <v>1.5004999999999999</v>
       </c>
       <c r="F11" s="1">
-        <v>173.73</v>
+        <v>40</v>
       </c>
       <c r="G11" s="1">
         <f>E11*F11</f>
-        <v>59.919476999999993</v>
+        <v>60.019999999999996</v>
       </c>
       <c r="H11" s="13">
-        <f>196.02/F11-1</f>
-        <v>0.12830253842168893</v>
+        <v>0.1</v>
       </c>
       <c r="I11" s="11">
-        <v>0.52980000000000005</v>
+        <v>0.2</v>
       </c>
       <c r="J11" s="9">
         <f>IFERROR(H11/I11,"")</f>
-        <v>0.24217164670005459</v>
+        <v>0.5</v>
       </c>
       <c r="K11" s="9">
         <f>IFERROR(J11/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.1744048437462873E-2</v>
+        <v>2.3986825753732854E-2</v>
       </c>
       <c r="L11" s="9">
         <f>I11*G11</f>
-        <v>31.745338914599998</v>
+        <v>12.004</v>
       </c>
       <c r="M11" s="12">
         <f>F11/(1-(F11*(1+H11)-F11)/(F11*(1+H11)))</f>
-        <v>196.02</v>
+        <v>44</v>
       </c>
       <c r="N11" s="12">
         <f>M11*E11</f>
-        <v>67.607298</v>
+        <v>66.021999999999991</v>
       </c>
       <c r="O11" s="12">
-        <v>138.79</v>
+        <v>33.67</v>
       </c>
       <c r="P11" s="12">
         <f>IFERROR(O11*E11,G11)</f>
-        <v>47.868670999999992</v>
+        <v>50.521835000000003</v>
       </c>
       <c r="Q11" s="12">
         <f>P11-G11</f>
-        <v>-12.050806000000001</v>
+        <v>-9.4981649999999931</v>
       </c>
       <c r="R11" s="12">
         <f>F11/(1+I11-H11)</f>
-        <v>123.9602673303112</v>
+        <v>36.363636363636367</v>
       </c>
       <c r="S11" s="12">
         <f>M11-F11</f>
-        <v>22.29000000000002</v>
+        <v>4</v>
       </c>
       <c r="T11" s="12">
         <f>0.5*(R11-F11)</f>
-        <v>-24.884866334844396</v>
+        <v>-1.8181818181818166</v>
       </c>
       <c r="U11" s="15">
         <f>S11+T11</f>
-        <v>-2.5948663348443759</v>
+        <v>2.1818181818181834</v>
       </c>
       <c r="V11" s="12">
         <f>MAX($U$2:$U$278)-U11</f>
-        <v>116.72731141602875</v>
+        <v>111.9506268993662</v>
       </c>
       <c r="W11" s="9">
         <f>IFERROR((SUBTOTAL(109,$V$2:$V$1048576)/V11)/SUBTOTAL(109,$V$2:$V$1048576),0)</f>
-        <v>8.5669753536590249E-3</v>
+        <v>8.9325091577996465E-3</v>
       </c>
       <c r="X11" s="9">
         <f>V11/MAX($V$2:$V$28)</f>
-        <v>0.50381837041675082</v>
+        <v>0.48320124679773302</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
@@ -5389,7 +5398,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(J12/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.8658995476992072E-2</v>
+        <v>1.8458503850506239E-2</v>
       </c>
       <c r="L12" s="9">
         <f>I12*G12</f>
@@ -5403,17 +5412,16 @@
         <f>M12*E12</f>
         <v>60.486327000000003</v>
       </c>
-      <c r="O12" s="12" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="O12" ca="1">_xlfn.STOCKHISTORY(C12,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>#VALUE!</v>
+      <c r="O12" s="12">
+        <v>72.709999999999994</v>
       </c>
       <c r="P12" s="12">
-        <f ca="1">IFERROR(O12*E12,G12)</f>
-        <v>54.987569999999998</v>
+        <f>IFERROR(O12*E12,G12)</f>
+        <v>54.248930999999992</v>
       </c>
       <c r="Q12" s="12">
-        <f ca="1">P12-G12</f>
-        <v>0</v>
+        <f>P12-G12</f>
+        <v>-0.73863900000000626</v>
       </c>
       <c r="R12" s="12">
         <f>F12/(1+I12-H12)</f>
@@ -5479,7 +5487,7 @@
       </c>
       <c r="K13" s="9">
         <f>IFERROR(J13/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.2934904459507386E-2</v>
+        <v>4.2473567254151669E-2</v>
       </c>
       <c r="L13" s="9">
         <f>I13*G13</f>
@@ -5494,15 +5502,15 @@
         <v>67.469760000000008</v>
       </c>
       <c r="O13" s="12">
-        <v>20.76</v>
+        <v>19.77</v>
       </c>
       <c r="P13" s="12">
         <f>IFERROR(O13*E13,G13)</f>
-        <v>64.845936000000009</v>
+        <v>61.753571999999998</v>
       </c>
       <c r="Q13" s="12">
         <f>P13-G13</f>
-        <v>14.868336000000006</v>
+        <v>11.775971999999996</v>
       </c>
       <c r="R13" s="12">
         <f>F13/(1+I13-H13)</f>
@@ -5526,7 +5534,7 @@
       </c>
       <c r="W13" s="9">
         <f>IFERROR((SUBTOTAL(109,$V$2:$V$1048576)/V13)/SUBTOTAL(109,$V$2:$V$1048576),0)</f>
-        <v>9.1844815741069629E-3</v>
+        <v>9.1844815741069612E-3</v>
       </c>
       <c r="X13" s="9">
         <f>V13/MAX($V$2:$V$28)</f>
@@ -5568,7 +5576,7 @@
       </c>
       <c r="K14" s="9">
         <f>IFERROR(J14/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.4247364622351195E-2</v>
+        <v>2.3986825753732854E-2</v>
       </c>
       <c r="L14" s="9">
         <f>I14*G14</f>
@@ -5583,15 +5591,15 @@
         <v>53.548000000000002</v>
       </c>
       <c r="O14" s="12">
-        <v>42.991999999999997</v>
+        <v>39.76</v>
       </c>
       <c r="P14" s="12">
         <f>IFERROR(O14*E14,G14)</f>
-        <v>42.991999999999997</v>
+        <v>39.76</v>
       </c>
       <c r="Q14" s="12">
         <f>P14-G14</f>
-        <v>-5.6880000000000024</v>
+        <v>-8.9200000000000017</v>
       </c>
       <c r="R14" s="12">
         <f>F14/(1+I14-H14)</f>
@@ -5657,7 +5665,7 @@
       </c>
       <c r="K15" s="9">
         <f>IFERROR(J15/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.7291802003005716E-2</v>
+        <v>1.7106000923160423E-2</v>
       </c>
       <c r="L15" s="9">
         <f>I15*G15</f>
@@ -5672,15 +5680,15 @@
         <v>51.511081885199999</v>
       </c>
       <c r="O15" s="12">
-        <v>135.06</v>
+        <v>130.51</v>
       </c>
       <c r="P15" s="12">
         <f>IFERROR(O15*E15,G15)</f>
-        <v>47.081916000000007</v>
+        <v>45.495786000000003</v>
       </c>
       <c r="Q15" s="12">
         <f>P15-G15</f>
-        <v>1.0980900000000062</v>
+        <v>-0.48803999999999803</v>
       </c>
       <c r="R15" s="12">
         <f>F15/(1+I15-H15)</f>
@@ -5746,7 +5754,7 @@
       </c>
       <c r="K16" s="9">
         <f>IFERROR(J16/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.0286760748876266E-2</v>
+        <v>1.0176229107644243E-2</v>
       </c>
       <c r="L16" s="9">
         <f>I16*G16</f>
@@ -5761,15 +5769,15 @@
         <v>43.318889999999996</v>
       </c>
       <c r="O16" s="12">
-        <v>20.12</v>
+        <v>19.579999999999998</v>
       </c>
       <c r="P16" s="12">
         <f>IFERROR(O16*E16,G16)</f>
-        <v>40.24</v>
+        <v>39.159999999999997</v>
       </c>
       <c r="Q16" s="12">
         <f>P16-G16</f>
-        <v>-1.6139999999999972</v>
+        <v>-2.6940000000000026</v>
       </c>
       <c r="R16" s="12">
         <f>F16/(1+I16-H16)</f>
@@ -5793,7 +5801,7 @@
       </c>
       <c r="W16" s="9">
         <f>IFERROR((SUBTOTAL(109,$V$2:$V$1048576)/V16)/SUBTOTAL(109,$V$2:$V$1048576),0)</f>
-        <v>8.7257167776693696E-3</v>
+        <v>8.7257167776693713E-3</v>
       </c>
       <c r="X16" s="9">
         <f>V16/MAX($V$2:$V$28)</f>
@@ -5802,1169 +5810,1166 @@
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>115</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="C17" t="s">
-        <v>117</v>
+        <v>38</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>98</v>
       </c>
       <c r="D17" s="8">
-        <v>45481</v>
+        <v>45630</v>
       </c>
       <c r="E17" s="2">
         <v>2</v>
       </c>
       <c r="F17" s="1">
-        <v>16.399000000000001</v>
+        <v>20.5</v>
       </c>
       <c r="G17" s="1">
         <f>E17*F17</f>
-        <v>32.798000000000002</v>
+        <v>41</v>
       </c>
       <c r="H17" s="13">
-        <v>3.5000000000000003E-2</v>
+        <v>0.2</v>
       </c>
       <c r="I17" s="11">
-        <v>0.16500000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="J17" s="9">
         <f>IFERROR(H17/I17,"")</f>
-        <v>0.21212121212121213</v>
+        <v>1</v>
       </c>
       <c r="K17" s="9">
         <f>IFERROR(J17/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.0286760748876266E-2</v>
+        <v>4.7973651507465707E-2</v>
       </c>
       <c r="L17" s="9">
         <f>I17*G17</f>
-        <v>5.4116700000000009</v>
+        <v>8.2000000000000011</v>
       </c>
       <c r="M17" s="12">
         <f>F17/(1-(F17*(1+H17)-F17)/(F17*(1+H17)))</f>
-        <v>16.972964999999999</v>
+        <v>24.599999999999998</v>
       </c>
       <c r="N17" s="12">
         <f>M17*E17</f>
-        <v>33.945929999999997</v>
+        <v>49.199999999999996</v>
       </c>
       <c r="O17" s="12">
-        <v>15.555999999999999</v>
+        <v>21.17</v>
       </c>
       <c r="P17" s="12">
         <f>IFERROR(O17*E17,G17)</f>
-        <v>31.111999999999998</v>
+        <v>42.34</v>
       </c>
       <c r="Q17" s="12">
         <f>P17-G17</f>
-        <v>-1.6860000000000035</v>
+        <v>1.3400000000000034</v>
       </c>
       <c r="R17" s="12">
         <f>F17/(1+I17-H17)</f>
-        <v>14.512389380530973</v>
+        <v>20.5</v>
       </c>
       <c r="S17" s="12">
         <f>M17-F17</f>
-        <v>0.57396499999999762</v>
+        <v>4.0999999999999979</v>
       </c>
       <c r="T17" s="12">
         <f>0.5*(R17-F17)</f>
-        <v>-0.9433053097345141</v>
+        <v>0</v>
       </c>
       <c r="U17" s="15">
         <f>S17+T17</f>
-        <v>-0.36934030973451648</v>
+        <v>4.0999999999999979</v>
       </c>
       <c r="V17" s="12">
         <f>MAX($U$2:$U$278)-U17</f>
-        <v>114.5017853909189</v>
+        <v>110.03244508118439</v>
       </c>
       <c r="W17" s="9">
         <f>IFERROR((SUBTOTAL(109,$V$2:$V$1048576)/V17)/SUBTOTAL(109,$V$2:$V$1048576),0)</f>
-        <v>8.7334882734440723E-3</v>
+        <v>9.0882284699042876E-3</v>
       </c>
       <c r="X17" s="9">
         <f>V17/MAX($V$2:$V$28)</f>
-        <v>0.49421255596177188</v>
+        <v>0.47492199127410506</v>
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>115</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C18" s="32" t="s">
-        <v>91</v>
+        <v>129</v>
+      </c>
+      <c r="C18" t="s">
+        <v>117</v>
       </c>
       <c r="D18" s="8">
-        <v>45627</v>
+        <v>45481</v>
       </c>
       <c r="E18" s="2">
-        <v>0.75290000000000001</v>
+        <v>2</v>
       </c>
       <c r="F18" s="1">
-        <v>41.16</v>
+        <v>16.399000000000001</v>
       </c>
       <c r="G18" s="1">
         <f>E18*F18</f>
-        <v>30.989363999999998</v>
+        <v>32.798000000000002</v>
       </c>
       <c r="H18" s="13">
-        <v>0.1</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="I18" s="11">
-        <v>0.2</v>
+        <v>0.16500000000000001</v>
       </c>
       <c r="J18" s="9">
         <f>IFERROR(H18/I18,"")</f>
-        <v>0.5</v>
+        <v>0.21212121212121213</v>
       </c>
       <c r="K18" s="9">
         <f>IFERROR(J18/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.4247364622351195E-2</v>
+        <v>1.0176229107644243E-2</v>
       </c>
       <c r="L18" s="9">
         <f>I18*G18</f>
-        <v>6.1978727999999998</v>
+        <v>5.4116700000000009</v>
       </c>
       <c r="M18" s="12">
         <f>F18/(1-(F18*(1+H18)-F18)/(F18*(1+H18)))</f>
-        <v>45.276000000000003</v>
+        <v>16.972964999999999</v>
       </c>
       <c r="N18" s="12">
         <f>M18*E18</f>
-        <v>34.088300400000001</v>
-      </c>
-      <c r="O18" s="12" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="O18" ca="1">_xlfn.STOCKHISTORY(C18,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>#VALUE!</v>
+        <v>33.945929999999997</v>
+      </c>
+      <c r="O18" s="12">
+        <v>15.192</v>
       </c>
       <c r="P18" s="12">
-        <f ca="1">IFERROR(O18*E18,G18)</f>
-        <v>30.989363999999998</v>
+        <f>IFERROR(O18*E18,G18)</f>
+        <v>30.384</v>
       </c>
       <c r="Q18" s="12">
-        <f ca="1">P18-G18</f>
-        <v>0</v>
+        <f>P18-G18</f>
+        <v>-2.4140000000000015</v>
       </c>
       <c r="R18" s="12">
         <f>F18/(1+I18-H18)</f>
-        <v>37.418181818181822</v>
+        <v>14.512389380530973</v>
       </c>
       <c r="S18" s="12">
         <f>M18-F18</f>
-        <v>4.1160000000000068</v>
+        <v>0.57396499999999762</v>
       </c>
       <c r="T18" s="12">
         <f>0.5*(R18-F18)</f>
-        <v>-1.8709090909090875</v>
+        <v>-0.9433053097345141</v>
       </c>
       <c r="U18" s="15">
         <f>S18+T18</f>
-        <v>2.2450909090909192</v>
+        <v>-0.36934030973451648</v>
       </c>
       <c r="V18" s="12">
         <f>MAX($U$2:$U$278)-U18</f>
-        <v>111.88735417209347</v>
+        <v>114.5017853909189</v>
       </c>
       <c r="W18" s="9">
         <f>IFERROR((SUBTOTAL(109,$V$2:$V$1048576)/V18)/SUBTOTAL(109,$V$2:$V$1048576),0)</f>
-        <v>8.9375605259366855E-3</v>
+        <v>8.733488273444074E-3</v>
       </c>
       <c r="X18" s="9">
         <f>V18/MAX($V$2:$V$28)</f>
-        <v>0.48292814907998677</v>
+        <v>0.49421255596177188</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" t="s">
-        <v>41</v>
+        <v>40</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" s="32" t="s">
+        <v>91</v>
       </c>
       <c r="D19" s="8">
-        <v>45507</v>
+        <v>45627</v>
       </c>
       <c r="E19" s="2">
-        <v>0.52270000000000005</v>
+        <v>0.75290000000000001</v>
       </c>
       <c r="F19" s="1">
-        <v>38.229999999999997</v>
+        <v>41.16</v>
       </c>
       <c r="G19" s="1">
         <f>E19*F19</f>
-        <v>19.982821000000001</v>
+        <v>30.989363999999998</v>
       </c>
       <c r="H19" s="13">
-        <v>7.0000000000000007E-2</v>
+        <v>0.1</v>
       </c>
       <c r="I19" s="11">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J19" s="9">
         <f>IFERROR(H19/I19,"")</f>
-        <v>0.17500000000000002</v>
+        <v>0.5</v>
       </c>
       <c r="K19" s="9">
         <f>IFERROR(J19/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>8.4865776178229199E-3</v>
+        <v>2.3986825753732854E-2</v>
       </c>
       <c r="L19" s="9">
         <f>I19*G19</f>
-        <v>7.9931284000000007</v>
+        <v>6.1978727999999998</v>
       </c>
       <c r="M19" s="12">
         <f>F19/(1-(F19*(1+H19)-F19)/(F19*(1+H19)))</f>
-        <v>40.906100000000002</v>
+        <v>45.276000000000003</v>
       </c>
       <c r="N19" s="12">
         <f>M19*E19</f>
-        <v>21.381618470000003</v>
+        <v>34.088300400000001</v>
       </c>
       <c r="O19" s="12">
-        <v>32.200000000000003</v>
+        <v>43.47</v>
       </c>
       <c r="P19" s="12">
         <f>IFERROR(O19*E19,G19)</f>
-        <v>16.830940000000002</v>
+        <v>32.728563000000001</v>
       </c>
       <c r="Q19" s="12">
         <f>P19-G19</f>
-        <v>-3.1518809999999995</v>
+        <v>1.7391990000000028</v>
       </c>
       <c r="R19" s="12">
         <f>F19/(1+I19-H19)</f>
-        <v>28.744360902255639</v>
+        <v>37.418181818181822</v>
       </c>
       <c r="S19" s="12">
         <f>M19-F19</f>
-        <v>2.6761000000000053</v>
+        <v>4.1160000000000068</v>
       </c>
       <c r="T19" s="12">
         <f>0.5*(R19-F19)</f>
-        <v>-4.7428195488721787</v>
+        <v>-1.8709090909090875</v>
       </c>
       <c r="U19" s="15">
         <f>S19+T19</f>
-        <v>-2.0667195488721735</v>
+        <v>2.2450909090909192</v>
       </c>
       <c r="V19" s="12">
         <f>MAX($U$2:$U$278)-U19</f>
-        <v>116.19916463005656</v>
+        <v>111.88735417209347</v>
       </c>
       <c r="W19" s="9">
         <f>IFERROR((SUBTOTAL(109,$V$2:$V$1048576)/V19)/SUBTOTAL(109,$V$2:$V$1048576),0)</f>
-        <v>8.60591384786372E-3</v>
+        <v>8.9375605259366872E-3</v>
       </c>
       <c r="X19" s="9">
         <f>V19/MAX($V$2:$V$28)</f>
-        <v>0.50153878349042313</v>
+        <v>0.48292814907998677</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>96</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="C20" s="32" t="s">
-        <v>100</v>
+        <v>39</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" t="s">
+        <v>41</v>
       </c>
       <c r="D20" s="8">
-        <v>45630</v>
+        <v>45507</v>
       </c>
       <c r="E20" s="2">
-        <v>0.28749999999999998</v>
+        <v>0.52270000000000005</v>
       </c>
       <c r="F20" s="1">
-        <v>34.78</v>
+        <v>38.229999999999997</v>
       </c>
       <c r="G20" s="1">
         <f>E20*F20</f>
-        <v>9.99925</v>
+        <v>19.982821000000001</v>
       </c>
       <c r="H20" s="13">
-        <v>0.2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I20" s="11">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J20" s="9">
         <f>IFERROR(H20/I20,"")</f>
-        <v>1</v>
+        <v>0.17500000000000002</v>
       </c>
       <c r="K20" s="9">
         <f>IFERROR(J20/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.8494729244702391E-2</v>
+        <v>8.3953890138065007E-3</v>
       </c>
       <c r="L20" s="9">
         <f>I20*G20</f>
-        <v>1.9998500000000001</v>
+        <v>7.9931284000000007</v>
       </c>
       <c r="M20" s="12">
         <f>F20/(1-(F20*(1+H20)-F20)/(F20*(1+H20)))</f>
-        <v>41.735999999999997</v>
+        <v>40.906100000000002</v>
       </c>
       <c r="N20" s="12">
         <f>M20*E20</f>
-        <v>11.999099999999999</v>
+        <v>21.381618470000003</v>
       </c>
       <c r="O20" s="12">
-        <v>32.200000000000003</v>
+        <v>28.49</v>
       </c>
       <c r="P20" s="12">
         <f>IFERROR(O20*E20,G20)</f>
-        <v>9.2575000000000003</v>
+        <v>14.891723000000001</v>
       </c>
       <c r="Q20" s="12">
         <f>P20-G20</f>
-        <v>-0.74174999999999969</v>
+        <v>-5.0910980000000006</v>
       </c>
       <c r="R20" s="12">
         <f>F20/(1+I20-H20)</f>
-        <v>34.78</v>
+        <v>28.744360902255639</v>
       </c>
       <c r="S20" s="12">
         <f>M20-F20</f>
-        <v>6.955999999999996</v>
+        <v>2.6761000000000053</v>
       </c>
       <c r="T20" s="12">
         <f>0.5*(R20-F20)</f>
-        <v>0</v>
+        <v>-4.7428195488721787</v>
       </c>
       <c r="U20" s="15">
         <f>S20+T20</f>
-        <v>6.955999999999996</v>
+        <v>-2.0667195488721735</v>
       </c>
       <c r="V20" s="12">
         <f>MAX($U$2:$U$278)-U20</f>
-        <v>107.1764450811844</v>
+        <v>116.19916463005656</v>
       </c>
       <c r="W20" s="9">
         <f>IFERROR((SUBTOTAL(109,$V$2:$V$1048576)/V20)/SUBTOTAL(109,$V$2:$V$1048576),0)</f>
-        <v>9.3304083676456744E-3</v>
+        <v>8.6059138478637217E-3</v>
       </c>
       <c r="X20" s="9">
         <f>V20/MAX($V$2:$V$28)</f>
-        <v>0.46259492532480184</v>
+        <v>0.50153878349042313</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" t="s">
-        <v>17</v>
+        <v>96</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C21" s="32" t="s">
+        <v>100</v>
       </c>
       <c r="D21" s="8">
-        <v>45678</v>
+        <v>45630</v>
       </c>
       <c r="E21" s="2">
-        <v>5.3800000000000001E-2</v>
+        <v>0.28749999999999998</v>
       </c>
       <c r="F21" s="1">
-        <v>185.82</v>
+        <v>34.78</v>
       </c>
       <c r="G21" s="1">
         <f>E21*F21</f>
-        <v>9.9971160000000001</v>
+        <v>9.99925</v>
       </c>
       <c r="H21" s="13">
-        <f>190.41/F21-1</f>
-        <v>2.4701323861801683E-2</v>
+        <v>0.2</v>
       </c>
       <c r="I21" s="11">
-        <v>0.26790000000000003</v>
+        <v>0.2</v>
       </c>
       <c r="J21" s="9">
         <f>IFERROR(H21/I21,"")</f>
-        <v>9.2203523187016356E-2</v>
+        <v>1</v>
       </c>
       <c r="K21" s="9">
         <f>IFERROR(J21/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.4713848923619969E-3</v>
+        <v>4.7973651507465707E-2</v>
       </c>
       <c r="L21" s="9">
         <f>I21*G21</f>
-        <v>2.6782273764000002</v>
+        <v>1.9998500000000001</v>
       </c>
       <c r="M21" s="12">
         <f>F21/(1-(F21*(1+H21)-F21)/(F21*(1+H21)))</f>
-        <v>190.40999999999997</v>
+        <v>41.735999999999997</v>
       </c>
       <c r="N21" s="12">
         <f>M21*E21</f>
-        <v>10.244057999999999</v>
+        <v>11.999099999999999</v>
       </c>
       <c r="O21" s="12">
-        <v>173.91</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="P21" s="12">
         <f>IFERROR(O21*E21,G21)</f>
-        <v>9.3563580000000002</v>
+        <v>9.2575000000000003</v>
       </c>
       <c r="Q21" s="12">
         <f>P21-G21</f>
-        <v>-0.64075799999999994</v>
+        <v>-0.74174999999999969</v>
       </c>
       <c r="R21" s="12">
         <f>F21/(1+I21-H21)</f>
-        <v>149.46927113630838</v>
+        <v>34.78</v>
       </c>
       <c r="S21" s="12">
         <f>M21-F21</f>
-        <v>4.589999999999975</v>
+        <v>6.955999999999996</v>
       </c>
       <c r="T21" s="12">
         <f>0.5*(R21-F21)</f>
-        <v>-18.175364431845807</v>
+        <v>0</v>
       </c>
       <c r="U21" s="15">
         <f>S21+T21</f>
-        <v>-13.585364431845832</v>
+        <v>6.955999999999996</v>
       </c>
       <c r="V21" s="12">
         <f>MAX($U$2:$U$278)-U21</f>
-        <v>127.71780951303022</v>
+        <v>107.1764450811844</v>
       </c>
       <c r="W21" s="9">
         <f>IFERROR((SUBTOTAL(109,$V$2:$V$1048576)/V21)/SUBTOTAL(109,$V$2:$V$1048576),0)</f>
-        <v>7.8297615956056353E-3</v>
+        <v>9.3304083676456744E-3</v>
       </c>
       <c r="X21" s="9">
         <f>V21/MAX($V$2:$V$28)</f>
-        <v>0.55125555349008015</v>
+        <v>0.46259492532480184</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>39</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>58</v>
+        <v>36</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="D22" s="8">
-        <v>45695</v>
+        <v>45678</v>
       </c>
       <c r="E22" s="2">
-        <v>2.9999999999999997E-4</v>
+        <v>5.3800000000000001E-2</v>
       </c>
       <c r="F22" s="1">
-        <v>143.18</v>
+        <v>185.82</v>
       </c>
       <c r="G22" s="1">
         <f>E22*F22</f>
-        <v>4.2953999999999999E-2</v>
+        <v>9.9971160000000001</v>
       </c>
       <c r="H22" s="13">
-        <v>7.0000000000000007E-2</v>
+        <f>190.41/F22-1</f>
+        <v>2.4701323861801683E-2</v>
       </c>
       <c r="I22" s="11">
-        <v>0.1623</v>
+        <v>0.26790000000000003</v>
       </c>
       <c r="J22" s="9">
         <f>IFERROR(H22/I22,"")</f>
-        <v>0.43130006161429457</v>
+        <v>9.2203523187016356E-2</v>
       </c>
       <c r="K22" s="9">
         <f>IFERROR(J22/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>2.0915779711208674E-2</v>
+        <v>4.4233396891344571E-3</v>
       </c>
       <c r="L22" s="9">
         <f>I22*G22</f>
-        <v>6.9714341999999995E-3</v>
+        <v>2.6782273764000002</v>
       </c>
       <c r="M22" s="12">
         <f>F22/(1-(F22*(1+H22)-F22)/(F22*(1+H22)))</f>
-        <v>153.20260000000002</v>
+        <v>190.40999999999997</v>
       </c>
       <c r="N22" s="12">
         <f>M22*E22</f>
-        <v>4.596078E-2</v>
+        <v>10.244057999999999</v>
       </c>
       <c r="O22" s="12">
-        <v>162.47999999999999</v>
+        <v>162.72</v>
       </c>
       <c r="P22" s="12">
         <f>IFERROR(O22*E22,G22)</f>
-        <v>4.8743999999999996E-2</v>
+        <v>8.7543360000000003</v>
       </c>
       <c r="Q22" s="12">
         <f>P22-G22</f>
-        <v>5.7899999999999965E-3</v>
+        <v>-1.2427799999999998</v>
       </c>
       <c r="R22" s="12">
         <f>F22/(1+I22-H22)</f>
-        <v>131.08120479721688</v>
+        <v>149.46927113630838</v>
       </c>
       <c r="S22" s="12">
         <f>M22-F22</f>
-        <v>10.022600000000011</v>
+        <v>4.589999999999975</v>
       </c>
       <c r="T22" s="12">
         <f>0.5*(R22-F22)</f>
-        <v>-6.0493976013915614</v>
+        <v>-18.175364431845807</v>
       </c>
       <c r="U22" s="15">
         <f>S22+T22</f>
-        <v>3.9732023986084499</v>
+        <v>-13.585364431845832</v>
       </c>
       <c r="V22" s="12">
         <f>MAX($U$2:$U$278)-U22</f>
-        <v>110.15924268257594</v>
+        <v>127.71780951303022</v>
       </c>
       <c r="W22" s="9">
         <f>IFERROR((SUBTOTAL(109,$V$2:$V$1048576)/V22)/SUBTOTAL(109,$V$2:$V$1048576),0)</f>
-        <v>9.0777675631040951E-3</v>
+        <v>7.8297615956056353E-3</v>
       </c>
       <c r="X22" s="9">
         <f>V22/MAX($V$2:$V$28)</f>
-        <v>0.47546927502570413</v>
+        <v>0.55125555349008015</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>36</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>14</v>
+        <v>39</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="C23" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D23" s="8">
-        <v>45482</v>
+        <v>45695</v>
       </c>
       <c r="E23" s="2">
-        <v>1E-4</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="F23" s="1">
-        <v>227.38</v>
+        <v>143.18</v>
       </c>
       <c r="G23" s="1">
         <f>E23*F23</f>
-        <v>2.2738000000000001E-2</v>
+        <v>4.2953999999999999E-2</v>
       </c>
       <c r="H23" s="13">
-        <v>0.15</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I23" s="11">
-        <v>0.2271</v>
+        <v>0.1623</v>
       </c>
       <c r="J23" s="9">
         <f>IFERROR(H23/I23,"")</f>
-        <v>0.66050198150594452</v>
+        <v>0.43130006161429457</v>
       </c>
       <c r="K23" s="9">
         <f>IFERROR(J23/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>3.2030864758720204E-2</v>
+        <v>2.0691038851032656E-2</v>
       </c>
       <c r="L23" s="9">
         <f>I23*G23</f>
-        <v>5.1637998000000004E-3</v>
+        <v>6.9714341999999995E-3</v>
       </c>
       <c r="M23" s="12">
         <f>F23/(1-(F23*(1+H23)-F23)/(F23*(1+H23)))</f>
-        <v>261.48699999999997</v>
+        <v>153.20260000000002</v>
       </c>
       <c r="N23" s="12">
         <f>M23*E23</f>
-        <v>2.6148699999999997E-2</v>
-      </c>
-      <c r="O23" s="12" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="O23" ca="1">_xlfn.STOCKHISTORY(C23,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>#VALUE!</v>
+        <v>4.596078E-2</v>
+      </c>
+      <c r="O23" s="12">
+        <v>153.15</v>
       </c>
       <c r="P23" s="12">
-        <f ca="1">IFERROR(O23*E23,G23)</f>
-        <v>2.2738000000000001E-2</v>
+        <f>IFERROR(O23*E23,G23)</f>
+        <v>4.5945E-2</v>
       </c>
       <c r="Q23" s="12">
-        <f ca="1">P23-G23</f>
-        <v>0</v>
+        <f>P23-G23</f>
+        <v>2.9910000000000006E-3</v>
       </c>
       <c r="R23" s="12">
         <f>F23/(1+I23-H23)</f>
-        <v>211.10389007520189</v>
+        <v>131.08120479721688</v>
       </c>
       <c r="S23" s="12">
         <f>M23-F23</f>
-        <v>34.106999999999971</v>
+        <v>10.022600000000011</v>
       </c>
       <c r="T23" s="12">
         <f>0.5*(R23-F23)</f>
-        <v>-8.1380549623990532</v>
+        <v>-6.0493976013915614</v>
       </c>
       <c r="U23" s="15">
         <f>S23+T23</f>
-        <v>25.968945037600918</v>
+        <v>3.9732023986084499</v>
       </c>
       <c r="V23" s="12">
         <f>MAX($U$2:$U$278)-U23</f>
-        <v>88.163500043583468</v>
+        <v>110.15924268257594</v>
       </c>
       <c r="W23" s="9">
         <f>IFERROR((SUBTOTAL(109,$V$2:$V$1048576)/V23)/SUBTOTAL(109,$V$2:$V$1048576),0)</f>
-        <v>1.1342562392664218E-2</v>
+        <v>9.0777675631040951E-3</v>
       </c>
       <c r="X23" s="9">
         <f>V23/MAX($V$2:$V$28)</f>
-        <v>0.38053126027963941</v>
+        <v>0.47546927502570413</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>74</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>80</v>
+        <v>36</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" t="s">
+        <v>13</v>
       </c>
       <c r="D24" s="8">
-        <f ca="1">TODAY()-20</f>
-        <v>45705</v>
+        <v>45482</v>
       </c>
       <c r="E24" s="2">
-        <v>9.9999999999999998E-20</v>
+        <v>1E-4</v>
       </c>
       <c r="F24" s="1">
-        <v>2742.9</v>
+        <v>227.38</v>
       </c>
       <c r="G24" s="1">
         <f>E24*F24</f>
-        <v>2.7429000000000002E-16</v>
+        <v>2.2738000000000001E-2</v>
       </c>
       <c r="H24" s="13">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="I24" s="11">
-        <v>0.5</v>
+        <v>0.2271</v>
       </c>
       <c r="J24" s="9">
         <f>IFERROR(H24/I24,"")</f>
-        <v>0.2</v>
+        <v>0.66050198150594452</v>
       </c>
       <c r="K24" s="9">
         <f>IFERROR(J24/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>9.6989458489404792E-3</v>
+        <v>3.1686691880756741E-2</v>
       </c>
       <c r="L24" s="9">
         <f>I24*G24</f>
-        <v>1.3714500000000001E-16</v>
+        <v>5.1637998000000004E-3</v>
       </c>
       <c r="M24" s="12">
         <f>F24/(1-(F24*(1+H24)-F24)/(F24*(1+H24)))</f>
-        <v>3017.1900000000005</v>
+        <v>261.48699999999997</v>
       </c>
       <c r="N24" s="12">
         <f>M24*E24</f>
-        <v>3.0171900000000003E-16</v>
-      </c>
-      <c r="O24" s="12" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="O24" ca="1">_xlfn.STOCKHISTORY(C24,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>#VALUE!</v>
+        <v>2.6148699999999997E-2</v>
+      </c>
+      <c r="O24" s="12">
+        <v>209.68</v>
       </c>
       <c r="P24" s="12">
-        <f ca="1">IFERROR(O24*E24,G24)</f>
-        <v>2.7429000000000002E-16</v>
+        <f>IFERROR(O24*E24,G24)</f>
+        <v>2.0968000000000001E-2</v>
       </c>
       <c r="Q24" s="12">
-        <f ca="1">P24-G24</f>
-        <v>0</v>
+        <f>P24-G24</f>
+        <v>-1.7700000000000007E-3</v>
       </c>
       <c r="R24" s="12">
         <f>F24/(1+I24-H24)</f>
-        <v>1959.214285714286</v>
+        <v>211.10389007520189</v>
       </c>
       <c r="S24" s="12">
         <f>M24-F24</f>
-        <v>274.29000000000042</v>
+        <v>34.106999999999971</v>
       </c>
       <c r="T24" s="12">
         <f>0.5*(R24-F24)</f>
-        <v>-391.84285714285704</v>
+        <v>-8.1380549623990532</v>
       </c>
       <c r="U24" s="15">
         <f>S24+T24</f>
-        <v>-117.55285714285662</v>
+        <v>25.968945037600918</v>
       </c>
       <c r="V24" s="12">
         <f>MAX($U$2:$U$278)-U24</f>
-        <v>231.68530222404101</v>
+        <v>88.163500043583468</v>
       </c>
       <c r="W24" s="9">
         <f>IFERROR((SUBTOTAL(109,$V$2:$V$1048576)/V24)/SUBTOTAL(109,$V$2:$V$1048576),0)</f>
-        <v>4.316199562080957E-3</v>
+        <v>1.1342562392664218E-2</v>
       </c>
       <c r="X24" s="9">
         <f>V24/MAX($V$2:$V$28)</f>
-        <v>1</v>
+        <v>0.38053126027963941</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" t="s">
-        <v>60</v>
+        <v>74</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>80</v>
       </c>
       <c r="D25" s="8">
-        <v>45481</v>
+        <f ca="1">TODAY()-20</f>
+        <v>45709</v>
       </c>
       <c r="E25" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F25" s="1">
-        <v>700.32</v>
+        <v>2742.9</v>
       </c>
       <c r="G25" s="1">
         <f>E25*F25</f>
-        <v>7.0031999999999998E-17</v>
+        <v>2.7429000000000002E-16</v>
       </c>
       <c r="H25" s="13">
         <v>0.1</v>
       </c>
       <c r="I25" s="11">
-        <v>0.45340000000000003</v>
+        <v>0.5</v>
       </c>
       <c r="J25" s="9">
         <f>IFERROR(H25/I25,"")</f>
-        <v>0.22055580061755625</v>
+        <v>0.2</v>
       </c>
       <c r="K25" s="9">
         <f>IFERROR(J25/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.0695793834296955E-2</v>
+        <v>9.5947303014931422E-3</v>
       </c>
       <c r="L25" s="9">
         <f>I25*G25</f>
-        <v>3.1752508800000004E-17</v>
+        <v>1.3714500000000001E-16</v>
       </c>
       <c r="M25" s="12">
         <f>F25/(1-(F25*(1+H25)-F25)/(F25*(1+H25)))</f>
-        <v>770.35200000000009</v>
+        <v>3017.1900000000005</v>
       </c>
       <c r="N25" s="12">
         <f>M25*E25</f>
-        <v>7.7035200000000004E-17</v>
-      </c>
-      <c r="O25" s="12" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="O25" ca="1">_xlfn.STOCKHISTORY(C25,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>#VALUE!</v>
+        <v>3.0171900000000003E-16</v>
+      </c>
+      <c r="O25" s="46">
+        <f>F25</f>
+        <v>2742.9</v>
       </c>
       <c r="P25" s="12">
-        <f ca="1">IFERROR(O25*E25,G25)</f>
-        <v>7.0031999999999998E-17</v>
+        <f>IFERROR(O25*E25,G25)</f>
+        <v>2.7429000000000002E-16</v>
       </c>
       <c r="Q25" s="12">
-        <f ca="1">P25-G25</f>
+        <f>P25-G25</f>
         <v>0</v>
       </c>
       <c r="R25" s="12">
         <f>F25/(1+I25-H25)</f>
-        <v>517.45234224915032</v>
+        <v>1959.214285714286</v>
       </c>
       <c r="S25" s="12">
         <f>M25-F25</f>
-        <v>70.032000000000039</v>
+        <v>274.29000000000042</v>
       </c>
       <c r="T25" s="12">
         <f>0.5*(R25-F25)</f>
-        <v>-91.433828875424865</v>
+        <v>-391.84285714285704</v>
       </c>
       <c r="U25" s="15">
         <f>S25+T25</f>
-        <v>-21.401828875424826</v>
+        <v>-117.55285714285662</v>
       </c>
       <c r="V25" s="12">
         <f>MAX($U$2:$U$278)-U25</f>
-        <v>135.53427395660921</v>
+        <v>231.68530222404101</v>
       </c>
       <c r="W25" s="9">
         <f>IFERROR((SUBTOTAL(109,$V$2:$V$1048576)/V25)/SUBTOTAL(109,$V$2:$V$1048576),0)</f>
-        <v>7.3782075249847591E-3</v>
+        <v>4.316199562080957E-3</v>
       </c>
       <c r="X25" s="9">
         <f>V25/MAX($V$2:$V$28)</f>
-        <v>0.58499297389847715</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>33</v>
+        <v>36</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="C26" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="D26" s="8">
-        <v>45562</v>
+        <v>45481</v>
       </c>
       <c r="E26" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F26" s="1">
-        <v>668.82</v>
+        <v>700.32</v>
       </c>
       <c r="G26" s="1">
         <f>E26*F26</f>
-        <v>6.6881999999999999E-17</v>
+        <v>7.0031999999999998E-17</v>
       </c>
       <c r="H26" s="13">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="I26" s="11">
-        <v>0.28000000000000003</v>
+        <v>0.45340000000000003</v>
       </c>
       <c r="J26" s="9">
         <f>IFERROR(H26/I26,"")</f>
-        <v>0.17857142857142858</v>
+        <v>0.22055580061755625</v>
       </c>
       <c r="K26" s="9">
         <f>IFERROR(J26/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>8.6597730794111417E-3</v>
+        <v>1.0580867116776735E-2</v>
       </c>
       <c r="L26" s="9">
         <f>I26*G26</f>
-        <v>1.872696E-17</v>
+        <v>3.1752508800000004E-17</v>
       </c>
       <c r="M26" s="12">
         <f>F26/(1-(F26*(1+H26)-F26)/(F26*(1+H26)))</f>
-        <v>702.26100000000008</v>
+        <v>770.35200000000009</v>
       </c>
       <c r="N26" s="12">
         <f>M26*E26</f>
-        <v>7.0226100000000009E-17</v>
-      </c>
-      <c r="O26" s="12" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="O26" ca="1">_xlfn.STOCKHISTORY("LVMH",TODAY()-1,TODAY(),0,0,1)</f>
-        <v>#VALUE!</v>
+        <v>7.7035200000000004E-17</v>
+      </c>
+      <c r="O26" s="46">
+        <f>F26</f>
+        <v>700.32</v>
       </c>
       <c r="P26" s="12">
-        <f ca="1">IFERROR(O26*E26,G26)</f>
-        <v>6.6881999999999999E-17</v>
+        <f>IFERROR(O26*E26,G26)</f>
+        <v>7.0031999999999998E-17</v>
       </c>
       <c r="Q26" s="12">
-        <f ca="1">P26-G26</f>
+        <f>P26-G26</f>
         <v>0</v>
       </c>
       <c r="R26" s="12">
         <f>F26/(1+I26-H26)</f>
-        <v>543.7560975609756</v>
+        <v>517.45234224915032</v>
       </c>
       <c r="S26" s="12">
         <f>M26-F26</f>
-        <v>33.441000000000031</v>
+        <v>70.032000000000039</v>
       </c>
       <c r="T26" s="12">
         <f>0.5*(R26-F26)</f>
-        <v>-62.531951219512223</v>
+        <v>-91.433828875424865</v>
       </c>
       <c r="U26" s="15">
         <f>S26+T26</f>
-        <v>-29.090951219512192</v>
+        <v>-21.401828875424826</v>
       </c>
       <c r="V26" s="12">
         <f>MAX($U$2:$U$278)-U26</f>
-        <v>143.22339630069658</v>
+        <v>135.53427395660921</v>
       </c>
       <c r="W26" s="9">
         <f>IFERROR((SUBTOTAL(109,$V$2:$V$1048576)/V26)/SUBTOTAL(109,$V$2:$V$1048576),0)</f>
-        <v>6.9820994741704523E-3</v>
+        <v>7.37820752498476E-3</v>
       </c>
       <c r="X26" s="9">
         <f>V26/MAX($V$2:$V$28)</f>
-        <v>0.61818076039281389</v>
+        <v>0.58499297389847715</v>
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>7</v>
+        <v>39</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="C27" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D27" s="8">
-        <v>45685</v>
+        <v>45562</v>
       </c>
       <c r="E27" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F27" s="1">
-        <v>336.69</v>
+        <v>668.82</v>
       </c>
       <c r="G27" s="1">
         <f>E27*F27</f>
-        <v>3.3669000000000002E-17</v>
+        <v>6.6881999999999999E-17</v>
       </c>
       <c r="H27" s="13">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="I27" s="11">
-        <v>0.26</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="J27" s="9">
         <f>IFERROR(H27/I27,"")</f>
-        <v>0.96153846153846145</v>
+        <v>0.17857142857142858</v>
       </c>
       <c r="K27" s="9">
         <f>IFERROR(J27/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.6629547350675371E-2</v>
+        <v>8.5667234834760197E-3</v>
       </c>
       <c r="L27" s="9">
         <f>I27*G27</f>
-        <v>8.7539400000000014E-18</v>
+        <v>1.872696E-17</v>
       </c>
       <c r="M27" s="12">
         <f>F27/(1-(F27*(1+H27)-F27)/(F27*(1+H27)))</f>
-        <v>420.86250000000001</v>
+        <v>702.26100000000008</v>
       </c>
       <c r="N27" s="12">
         <f>M27*E27</f>
-        <v>4.2086250000000001E-17</v>
-      </c>
-      <c r="O27" s="12" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="O27" ca="1">_xlfn.STOCKHISTORY(C27,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>#VALUE!</v>
+        <v>7.0226100000000009E-17</v>
+      </c>
+      <c r="O27" s="46">
+        <f>F27</f>
+        <v>668.82</v>
       </c>
       <c r="P27" s="12">
-        <f ca="1">IFERROR(O27*E27,G27)</f>
-        <v>3.3669000000000002E-17</v>
+        <f>IFERROR(O27*E27,G27)</f>
+        <v>6.6881999999999999E-17</v>
       </c>
       <c r="Q27" s="12">
-        <f ca="1">P27-G27</f>
+        <f>P27-G27</f>
         <v>0</v>
       </c>
       <c r="R27" s="12">
         <f>F27/(1+I27-H27)</f>
-        <v>333.35643564356434</v>
+        <v>543.7560975609756</v>
       </c>
       <c r="S27" s="12">
         <f>M27-F27</f>
-        <v>84.172500000000014</v>
+        <v>33.441000000000031</v>
       </c>
       <c r="T27" s="12">
         <f>0.5*(R27-F27)</f>
-        <v>-1.6667821782178294</v>
+        <v>-62.531951219512223</v>
       </c>
       <c r="U27" s="15">
         <f>S27+T27</f>
-        <v>82.505717821782184</v>
+        <v>-29.090951219512192</v>
       </c>
       <c r="V27" s="12">
         <f>MAX($U$2:$U$278)-U27</f>
-        <v>31.626727259402202</v>
+        <v>143.22339630069658</v>
       </c>
       <c r="W27" s="9">
         <f>IFERROR((SUBTOTAL(109,$V$2:$V$1048576)/V27)/SUBTOTAL(109,$V$2:$V$1048576),0)</f>
-        <v>3.1618826437462423E-2</v>
+        <v>6.9820994741704541E-3</v>
       </c>
       <c r="X27" s="9">
         <f>V27/MAX($V$2:$V$28)</f>
-        <v>0.13650726634708565</v>
+        <v>0.61818076039281389</v>
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>96</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C28" s="32" t="s">
-        <v>99</v>
+        <v>37</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" t="s">
+        <v>25</v>
       </c>
       <c r="D28" s="8">
-        <v>45630</v>
+        <v>45685</v>
       </c>
       <c r="E28" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F28" s="1">
-        <v>323.75</v>
+        <v>336.69</v>
       </c>
       <c r="G28" s="1">
         <f>E28*F28</f>
-        <v>3.2375000000000002E-17</v>
+        <v>3.3669000000000002E-17</v>
       </c>
       <c r="H28" s="13">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="I28" s="11">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="J28" s="9">
         <f>IFERROR(H28/I28,"")</f>
-        <v>1</v>
+        <v>0.96153846153846145</v>
       </c>
       <c r="K28" s="9">
         <f>IFERROR(J28/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>4.8494729244702391E-2</v>
+        <v>4.612851106487087E-2</v>
       </c>
       <c r="L28" s="9">
         <f>I28*G28</f>
-        <v>6.4750000000000006E-18</v>
+        <v>8.7539400000000014E-18</v>
       </c>
       <c r="M28" s="12">
         <f>F28/(1-(F28*(1+H28)-F28)/(F28*(1+H28)))</f>
-        <v>388.5</v>
+        <v>420.86250000000001</v>
       </c>
       <c r="N28" s="12">
         <f>M28*E28</f>
-        <v>3.8849999999999999E-17</v>
-      </c>
-      <c r="O28" s="12" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="O28" ca="1">_xlfn.STOCKHISTORY(C28,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>#VALUE!</v>
+        <v>4.2086250000000001E-17</v>
+      </c>
+      <c r="O28" s="46">
+        <f>F28</f>
+        <v>336.69</v>
       </c>
       <c r="P28" s="12">
-        <f ca="1">IFERROR(O28*E28,G28)</f>
-        <v>3.2375000000000002E-17</v>
+        <f>IFERROR(O28*E28,G28)</f>
+        <v>3.3669000000000002E-17</v>
       </c>
       <c r="Q28" s="12">
-        <f ca="1">P28-G28</f>
+        <f>P28-G28</f>
         <v>0</v>
       </c>
       <c r="R28" s="12">
         <f>F28/(1+I28-H28)</f>
-        <v>323.75</v>
+        <v>333.35643564356434</v>
       </c>
       <c r="S28" s="12">
         <f>M28-F28</f>
-        <v>64.75</v>
+        <v>84.172500000000014</v>
       </c>
       <c r="T28" s="12">
         <f>0.5*(R28-F28)</f>
-        <v>0</v>
+        <v>-1.6667821782178294</v>
       </c>
       <c r="U28" s="15">
         <f>S28+T28</f>
-        <v>64.75</v>
+        <v>82.505717821782184</v>
       </c>
       <c r="V28" s="12">
         <f>MAX($U$2:$U$278)-U28</f>
-        <v>49.382445081184386</v>
+        <v>31.626727259402202</v>
       </c>
       <c r="W28" s="9">
         <f>IFERROR((SUBTOTAL(109,$V$2:$V$1048576)/V28)/SUBTOTAL(109,$V$2:$V$1048576),0)</f>
-        <v>2.0250111114506527E-2</v>
+        <v>3.161882643746243E-2</v>
       </c>
       <c r="X28" s="9">
         <f>V28/MAX($V$2:$V$28)</f>
-        <v>0.21314448783389495</v>
+        <v>0.13650726634708565</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" t="s">
-        <v>9</v>
+        <v>96</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C29" s="32" t="s">
+        <v>99</v>
       </c>
       <c r="D29" s="8">
-        <v>45544</v>
+        <v>45630</v>
       </c>
       <c r="E29" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F29" s="1">
-        <v>188.12</v>
+        <v>323.75</v>
       </c>
       <c r="G29" s="1">
         <f>E29*F29</f>
-        <v>1.8812000000000001E-17</v>
+        <v>3.2375000000000002E-17</v>
       </c>
       <c r="H29" s="13">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="I29" s="11">
-        <v>0.37780000000000002</v>
+        <v>0.2</v>
       </c>
       <c r="J29" s="9">
         <f>IFERROR(H29/I29,"")</f>
-        <v>0.39703546850185278</v>
+        <v>1</v>
       </c>
       <c r="K29" s="9">
         <f>IFERROR(J29/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.9254127545540914E-2</v>
+        <v>4.7973651507465707E-2</v>
       </c>
       <c r="L29" s="9">
         <f>I29*G29</f>
-        <v>7.1071736000000005E-18</v>
+        <v>6.4750000000000006E-18</v>
       </c>
       <c r="M29" s="12">
         <f>F29/(1-(F29*(1+H29)-F29)/(F29*(1+H29)))</f>
-        <v>216.33799999999999</v>
+        <v>388.5</v>
       </c>
       <c r="N29" s="12">
         <f>M29*E29</f>
-        <v>2.16338E-17</v>
-      </c>
-      <c r="O29" s="12" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="O29" ca="1">_xlfn.STOCKHISTORY(C29,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>#VALUE!</v>
+        <v>3.8849999999999999E-17</v>
+      </c>
+      <c r="O29" s="46">
+        <f>F29</f>
+        <v>323.75</v>
       </c>
       <c r="P29" s="12">
-        <f ca="1">IFERROR(O29*E29,G29)</f>
-        <v>1.8812000000000001E-17</v>
+        <f>IFERROR(O29*E29,G29)</f>
+        <v>3.2375000000000002E-17</v>
       </c>
       <c r="Q29" s="12">
-        <f ca="1">P29-G29</f>
+        <f>P29-G29</f>
         <v>0</v>
       </c>
       <c r="R29" s="12">
         <f>F29/(1+I29-H29)</f>
-        <v>153.21713634142367</v>
+        <v>323.75</v>
       </c>
       <c r="S29" s="12">
         <f>M29-F29</f>
-        <v>28.217999999999989</v>
+        <v>64.75</v>
       </c>
       <c r="T29" s="12">
         <f>0.5*(R29-F29)</f>
-        <v>-17.451431829288168</v>
+        <v>0</v>
       </c>
       <c r="U29" s="15">
         <f>S29+T29</f>
-        <v>10.766568170711821</v>
+        <v>64.75</v>
       </c>
       <c r="V29" s="12">
         <f>MAX($U$2:$U$278)-U29</f>
-        <v>103.36587691047256</v>
+        <v>49.382445081184386</v>
       </c>
       <c r="W29" s="9">
         <f>IFERROR((SUBTOTAL(109,$V$2:$V$1048576)/V29)/SUBTOTAL(109,$V$2:$V$1048576),0)</f>
-        <v>9.674372528819369E-3</v>
+        <v>2.0250111114506527E-2</v>
       </c>
       <c r="X29" s="9">
         <f>V29/MAX($V$2:$V$28)</f>
-        <v>0.44614775265509582</v>
+        <v>0.21314448783389495</v>
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.25">
@@ -6972,1079 +6977,1080 @@
         <v>36</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C30" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="D30" s="8">
-        <v>45481</v>
+        <v>45544</v>
       </c>
       <c r="E30" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F30" s="1">
-        <v>169.34</v>
+        <v>188.12</v>
       </c>
       <c r="G30" s="1">
         <f>E30*F30</f>
-        <v>1.6933999999999999E-17</v>
+        <v>1.8812000000000001E-17</v>
       </c>
       <c r="H30" s="13">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="I30" s="11">
-        <v>0.4259</v>
+        <v>0.37780000000000002</v>
       </c>
       <c r="J30" s="9">
         <f>IFERROR(H30/I30,"")</f>
-        <v>0.23479690068091102</v>
+        <v>0.39703546850185278</v>
       </c>
       <c r="K30" s="9">
         <f>IFERROR(J30/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.1386412126016059E-2</v>
+        <v>1.9047241202011265E-2</v>
       </c>
       <c r="L30" s="9">
         <f>I30*G30</f>
-        <v>7.2121906000000005E-18</v>
+        <v>7.1071736000000005E-18</v>
       </c>
       <c r="M30" s="12">
         <f>F30/(1-(F30*(1+H30)-F30)/(F30*(1+H30)))</f>
-        <v>186.27400000000003</v>
+        <v>216.33799999999999</v>
       </c>
       <c r="N30" s="12">
         <f>M30*E30</f>
-        <v>1.8627400000000003E-17</v>
-      </c>
-      <c r="O30" s="12" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="O30" ca="1">_xlfn.STOCKHISTORY(C30,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>#VALUE!</v>
+        <v>2.16338E-17</v>
+      </c>
+      <c r="O30" s="46">
+        <f>F30</f>
+        <v>188.12</v>
       </c>
       <c r="P30" s="12">
-        <f ca="1">IFERROR(O30*E30,G30)</f>
-        <v>1.6933999999999999E-17</v>
+        <f>IFERROR(O30*E30,G30)</f>
+        <v>1.8812000000000001E-17</v>
       </c>
       <c r="Q30" s="12">
-        <f ca="1">P30-G30</f>
+        <f>P30-G30</f>
         <v>0</v>
       </c>
       <c r="R30" s="12">
         <f>F30/(1+I30-H30)</f>
-        <v>127.71702239987934</v>
+        <v>153.21713634142367</v>
       </c>
       <c r="S30" s="12">
         <f>M30-F30</f>
-        <v>16.934000000000026</v>
+        <v>28.217999999999989</v>
       </c>
       <c r="T30" s="12">
         <f>0.5*(R30-F30)</f>
-        <v>-20.811488800060332</v>
+        <v>-17.451431829288168</v>
       </c>
       <c r="U30" s="15">
         <f>S30+T30</f>
-        <v>-3.8774888000603056</v>
+        <v>10.766568170711821</v>
       </c>
       <c r="V30" s="12">
         <f>MAX($U$2:$U$278)-U30</f>
-        <v>118.00993388124469</v>
+        <v>103.36587691047256</v>
       </c>
       <c r="W30" s="9">
         <f>IFERROR((SUBTOTAL(109,$V$2:$V$1048576)/V30)/SUBTOTAL(109,$V$2:$V$1048576),0)</f>
-        <v>8.4738628953585915E-3</v>
+        <v>9.6743725288193673E-3</v>
       </c>
       <c r="X30" s="9">
         <f>V30/MAX($V$2:$V$28)</f>
-        <v>0.50935442493943106</v>
+        <v>0.44614775265509582</v>
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>74</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>77</v>
+        <v>36</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="C31" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="D31" s="8">
-        <v>45574</v>
+        <v>45481</v>
       </c>
       <c r="E31" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F31" s="1">
-        <v>153.7552</v>
+        <v>169.34</v>
       </c>
       <c r="G31" s="1">
         <f>E31*F31</f>
-        <v>1.5375519999999999E-17</v>
+        <v>1.6933999999999999E-17</v>
       </c>
       <c r="H31" s="13">
-        <v>7.0000000000000007E-2</v>
+        <v>0.1</v>
       </c>
       <c r="I31" s="11">
-        <v>0.19</v>
+        <v>0.4259</v>
       </c>
       <c r="J31" s="9">
         <f>IFERROR(H31/I31,"")</f>
-        <v>0.36842105263157898</v>
+        <v>0.23479690068091102</v>
       </c>
       <c r="K31" s="9">
         <f>IFERROR(J31/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.7866479195416674E-2</v>
+        <v>1.1264064688299064E-2</v>
       </c>
       <c r="L31" s="9">
         <f>I31*G31</f>
-        <v>2.9213487999999999E-18</v>
+        <v>7.2121906000000005E-18</v>
       </c>
       <c r="M31" s="12">
         <f>F31/(1-(F31*(1+H31)-F31)/(F31*(1+H31)))</f>
-        <v>164.51806400000001</v>
+        <v>186.27400000000003</v>
       </c>
       <c r="N31" s="12">
         <f>M31*E31</f>
-        <v>1.6451806399999999E-17</v>
-      </c>
-      <c r="O31" s="12" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="O31" ca="1">_xlfn.STOCKHISTORY(C31,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>#VALUE!</v>
+        <v>1.8627400000000003E-17</v>
+      </c>
+      <c r="O31" s="46">
+        <f>F31</f>
+        <v>169.34</v>
       </c>
       <c r="P31" s="12">
-        <f ca="1">IFERROR(O31*E31,G31)</f>
-        <v>1.5375519999999999E-17</v>
+        <f>IFERROR(O31*E31,G31)</f>
+        <v>1.6933999999999999E-17</v>
       </c>
       <c r="Q31" s="12">
-        <f ca="1">P31-G31</f>
+        <f>P31-G31</f>
         <v>0</v>
       </c>
       <c r="R31" s="12">
         <f>F31/(1+I31-H31)</f>
-        <v>137.28142857142859</v>
+        <v>127.71702239987934</v>
       </c>
       <c r="S31" s="12">
         <f>M31-F31</f>
-        <v>10.762864000000008</v>
+        <v>16.934000000000026</v>
       </c>
       <c r="T31" s="12">
         <f>0.5*(R31-F31)</f>
-        <v>-8.2368857142857053</v>
+        <v>-20.811488800060332</v>
       </c>
       <c r="U31" s="15">
         <f>S31+T31</f>
-        <v>2.5259782857143023</v>
+        <v>-3.8774888000603056</v>
       </c>
       <c r="V31" s="12">
         <f>MAX($U$2:$U$278)-U31</f>
-        <v>111.60646679547008</v>
+        <v>118.00993388124469</v>
       </c>
       <c r="W31" s="9">
         <f>IFERROR((SUBTOTAL(109,$V$2:$V$1048576)/V31)/SUBTOTAL(109,$V$2:$V$1048576),0)</f>
-        <v>8.9600542756415637E-3</v>
+        <v>8.4738628953585915E-3</v>
       </c>
       <c r="X31" s="9">
         <f>V31/MAX($V$2:$V$28)</f>
-        <v>0.48171578310801083</v>
+        <v>0.50935442493943106</v>
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>36</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>23</v>
+        <v>74</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>77</v>
       </c>
       <c r="C32" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="D32" s="8">
-        <v>45482</v>
+        <v>45574</v>
       </c>
       <c r="E32" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F32" s="1">
-        <v>147.01</v>
+        <v>153.7552</v>
       </c>
       <c r="G32" s="1">
         <f>E32*F32</f>
-        <v>1.4700999999999999E-17</v>
+        <v>1.5375519999999999E-17</v>
       </c>
       <c r="H32" s="13">
-        <v>0.15</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I32" s="11">
-        <v>0.52380000000000004</v>
+        <v>0.19</v>
       </c>
       <c r="J32" s="9">
         <f>IFERROR(H32/I32,"")</f>
-        <v>0.28636884306987398</v>
+        <v>0.36842105263157898</v>
       </c>
       <c r="K32" s="9">
         <f>IFERROR(J32/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.3887379508792208E-2</v>
+        <v>1.7674503186961052E-2</v>
       </c>
       <c r="L32" s="9">
         <f>I32*G32</f>
-        <v>7.7003838000000003E-18</v>
+        <v>2.9213487999999999E-18</v>
       </c>
       <c r="M32" s="12">
         <f>F32/(1-(F32*(1+H32)-F32)/(F32*(1+H32)))</f>
-        <v>169.06149999999997</v>
+        <v>164.51806400000001</v>
       </c>
       <c r="N32" s="12">
         <f>M32*E32</f>
-        <v>1.6906149999999997E-17</v>
-      </c>
-      <c r="O32" s="12" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="O32" ca="1">_xlfn.STOCKHISTORY(C32,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>#VALUE!</v>
+        <v>1.6451806399999999E-17</v>
+      </c>
+      <c r="O32" s="46">
+        <f>F32</f>
+        <v>153.7552</v>
       </c>
       <c r="P32" s="12">
-        <f ca="1">IFERROR(O32*E32,G32)</f>
-        <v>1.4700999999999999E-17</v>
+        <f>IFERROR(O32*E32,G32)</f>
+        <v>1.5375519999999999E-17</v>
       </c>
       <c r="Q32" s="12">
-        <f ca="1">P32-G32</f>
+        <f>P32-G32</f>
         <v>0</v>
       </c>
       <c r="R32" s="12">
         <f>F32/(1+I32-H32)</f>
-        <v>107.00975396709855</v>
+        <v>137.28142857142859</v>
       </c>
       <c r="S32" s="12">
         <f>M32-F32</f>
-        <v>22.051499999999976</v>
+        <v>10.762864000000008</v>
       </c>
       <c r="T32" s="12">
         <f>0.5*(R32-F32)</f>
-        <v>-20.000123016450722</v>
+        <v>-8.2368857142857053</v>
       </c>
       <c r="U32" s="15">
         <f>S32+T32</f>
-        <v>2.0513769835492539</v>
+        <v>2.5259782857143023</v>
       </c>
       <c r="V32" s="12">
         <f>MAX($U$2:$U$278)-U32</f>
-        <v>112.08106809763513</v>
+        <v>111.60646679547008</v>
       </c>
       <c r="W32" s="9">
         <f>IFERROR((SUBTOTAL(109,$V$2:$V$1048576)/V32)/SUBTOTAL(109,$V$2:$V$1048576),0)</f>
-        <v>8.9221134039237406E-3</v>
+        <v>8.9600542756415654E-3</v>
       </c>
       <c r="X32" s="9">
         <f>V32/MAX($V$2:$V$28)</f>
-        <v>0.48376425704057868</v>
+        <v>0.48171578310801083</v>
       </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>87</v>
-      </c>
-      <c r="B33" t="s">
-        <v>88</v>
-      </c>
-      <c r="C33" s="32" t="s">
-        <v>89</v>
+        <v>36</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33" t="s">
+        <v>24</v>
       </c>
       <c r="D33" s="8">
-        <v>45627</v>
+        <v>45482</v>
       </c>
       <c r="E33" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F33" s="1">
-        <v>133.53</v>
+        <v>147.01</v>
       </c>
       <c r="G33" s="1">
         <f>E33*F33</f>
-        <v>1.3353E-17</v>
+        <v>1.4700999999999999E-17</v>
       </c>
       <c r="H33" s="13">
-        <v>7.0000000000000007E-2</v>
+        <v>0.15</v>
       </c>
       <c r="I33" s="11">
-        <v>0.2</v>
+        <v>0.52380000000000004</v>
       </c>
       <c r="J33" s="9">
         <f>IFERROR(H33/I33,"")</f>
-        <v>0.35000000000000003</v>
+        <v>0.28636884306987398</v>
       </c>
       <c r="K33" s="9">
         <f>IFERROR(J33/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.697315523564584E-2</v>
+        <v>1.3738159080030272E-2</v>
       </c>
       <c r="L33" s="9">
         <f>I33*G33</f>
-        <v>2.6706000000000003E-18</v>
+        <v>7.7003838000000003E-18</v>
       </c>
       <c r="M33" s="12">
         <f>F33/(1-(F33*(1+H33)-F33)/(F33*(1+H33)))</f>
-        <v>142.87710000000001</v>
+        <v>169.06149999999997</v>
       </c>
       <c r="N33" s="12">
         <f>M33*E33</f>
-        <v>1.428771E-17</v>
-      </c>
-      <c r="O33" s="12" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="O33" ca="1">_xlfn.STOCKHISTORY(C33,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>#VALUE!</v>
+        <v>1.6906149999999997E-17</v>
+      </c>
+      <c r="O33" s="46">
+        <f>F33</f>
+        <v>147.01</v>
       </c>
       <c r="P33" s="12">
-        <f ca="1">IFERROR(O33*E33,G33)</f>
-        <v>1.3353E-17</v>
+        <f>IFERROR(O33*E33,G33)</f>
+        <v>1.4700999999999999E-17</v>
       </c>
       <c r="Q33" s="12">
-        <f ca="1">P33-G33</f>
+        <f>P33-G33</f>
         <v>0</v>
       </c>
       <c r="R33" s="12">
         <f>F33/(1+I33-H33)</f>
-        <v>118.16814159292036</v>
+        <v>107.00975396709855</v>
       </c>
       <c r="S33" s="12">
         <f>M33-F33</f>
-        <v>9.3471000000000117</v>
+        <v>22.051499999999976</v>
       </c>
       <c r="T33" s="12">
         <f>0.5*(R33-F33)</f>
-        <v>-7.6809292035398187</v>
+        <v>-20.000123016450722</v>
       </c>
       <c r="U33" s="15">
         <f>S33+T33</f>
-        <v>1.6661707964601931</v>
+        <v>2.0513769835492539</v>
       </c>
       <c r="V33" s="12">
         <f>MAX($U$2:$U$278)-U33</f>
-        <v>112.46627428472419</v>
+        <v>112.08106809763513</v>
       </c>
       <c r="W33" s="9">
         <f>IFERROR((SUBTOTAL(109,$V$2:$V$1048576)/V33)/SUBTOTAL(109,$V$2:$V$1048576),0)</f>
-        <v>8.8915544358512261E-3</v>
+        <v>8.9221134039237406E-3</v>
       </c>
       <c r="X33" s="9">
         <f>V33/MAX($V$2:$V$28)</f>
-        <v>0.48542688381660337</v>
+        <v>0.48376425704057868</v>
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>32</v>
+        <v>87</v>
+      </c>
+      <c r="B34" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" s="32" t="s">
+        <v>89</v>
       </c>
       <c r="D34" s="8">
-        <v>45511</v>
+        <v>45627</v>
       </c>
       <c r="E34" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F34" s="1">
-        <v>113.58</v>
+        <v>133.53</v>
       </c>
       <c r="G34" s="1">
         <f>E34*F34</f>
-        <v>1.1357999999999999E-17</v>
+        <v>1.3353E-17</v>
       </c>
       <c r="H34" s="13">
-        <f>121.15/F34-1</f>
-        <v>6.664905793273479E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I34" s="11">
-        <v>0.16439999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="J34" s="9">
         <f>IFERROR(H34/I34,"")</f>
-        <v>0.40540789496797319</v>
+        <v>0.35000000000000003</v>
       </c>
       <c r="K34" s="9">
         <f>IFERROR(J34/SUBTOTAL(9,$J$2:$J$1048576),"")</f>
-        <v>1.9660146100136604E-2</v>
+        <v>1.6790778027613001E-2</v>
       </c>
       <c r="L34" s="9">
         <f>I34*G34</f>
-        <v>1.8672551999999998E-18</v>
+        <v>2.6706000000000003E-18</v>
       </c>
       <c r="M34" s="12">
         <f>F34/(1-(F34*(1+H34)-F34)/(F34*(1+H34)))</f>
-        <v>121.15000000000002</v>
+        <v>142.87710000000001</v>
       </c>
       <c r="N34" s="12">
         <f>M34*E34</f>
-        <v>1.2115000000000002E-17</v>
-      </c>
-      <c r="O34" s="12" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="O34" ca="1">_xlfn.STOCKHISTORY(C34,TODAY()-1,TODAY(),0,0,1)</f>
-        <v>#VALUE!</v>
+        <v>1.428771E-17</v>
+      </c>
+      <c r="O34" s="46">
+        <f>F34</f>
+        <v>133.53</v>
       </c>
       <c r="P34" s="12">
-        <f ca="1">IFERROR(O34*E34,G34)</f>
-        <v>1.1357999999999999E-17</v>
+        <f>IFERROR(O34*E34,G34)</f>
+        <v>1.3353E-17</v>
       </c>
       <c r="Q34" s="12">
-        <f ca="1">P34-G34</f>
+        <f>P34-G34</f>
         <v>0</v>
       </c>
       <c r="R34" s="12">
         <f>F34/(1+I34-H34)</f>
-        <v>103.46609203186667</v>
+        <v>118.16814159292036</v>
       </c>
       <c r="S34" s="12">
         <f>M34-F34</f>
-        <v>7.5700000000000216</v>
+        <v>9.3471000000000117</v>
       </c>
       <c r="T34" s="12">
         <f>0.5*(R34-F34)</f>
-        <v>-5.0569539840666664</v>
+        <v>-7.6809292035398187</v>
       </c>
       <c r="U34" s="15">
         <f>S34+T34</f>
-        <v>2.5130460159333552</v>
+        <v>1.6661707964601931</v>
       </c>
       <c r="V34" s="12">
         <f>MAX($U$2:$U$278)-U34</f>
-        <v>111.61939906525103</v>
+        <v>112.46627428472419</v>
       </c>
       <c r="W34" s="9">
         <f>IFERROR((SUBTOTAL(109,$V$2:$V$1048576)/V34)/SUBTOTAL(109,$V$2:$V$1048576),0)</f>
-        <v>8.9590161600441431E-3</v>
+        <v>8.8915544358512243E-3</v>
       </c>
       <c r="X34" s="9">
         <f>V34/MAX($V$2:$V$28)</f>
-        <v>0.48177160136517611</v>
+        <v>0.48542688381660337</v>
       </c>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C35" t="s">
-        <v>55</v>
+        <v>40</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>32</v>
       </c>
       <c r="D35" s="8">
-        <v>45505</v>
+        <v>45511</v>
       </c>
       <c r="E35" s="2">
         <v>9.9999999999999998E-20</v>
       </c>
       <c r="F35" s="1">
-        <v>86.6</v>
+        <v>113.58</v>
       </c>
       <c r="G35" s="1">
         <f>E35*F35</f>
-        <v>8.6599999999999986E-18</v>
+        <v>1.1357999999999999E-1